--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -12921,7 +12921,7 @@
         <v>0.193</v>
       </c>
       <c r="G162" s="6" t="n">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="H162" s="7" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>Oct 20 (est)</t>
+          <t>Oct 22 (est)</t>
         </is>
       </c>
       <c r="J162" s="3" t="inlineStr"/>
@@ -20718,7 +20718,7 @@
       </c>
       <c r="I282" s="3" t="inlineStr">
         <is>
-          <t>Jul 29 (est)  ·  Oct 28 (est)</t>
+          <t>Jul 29 (est)  ·  Nov 04 (est)</t>
         </is>
       </c>
       <c r="J282" s="3" t="inlineStr"/>
@@ -34135,17 +34135,17 @@
       </c>
       <c r="C306" s="30" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="D306" s="29" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="E306" s="29" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F306" s="29" t="inlineStr"/>
@@ -34157,21 +34157,21 @@
     </row>
     <row r="307">
       <c r="A307" s="28" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B307" s="29" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C307" s="30" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="D307" s="29" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="E307" s="29" t="inlineStr">
@@ -34197,17 +34197,17 @@
       </c>
       <c r="C308" s="30" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="D308" s="29" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="E308" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F308" s="29" t="inlineStr"/>
@@ -34228,17 +34228,17 @@
       </c>
       <c r="C309" s="30" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="D309" s="29" t="inlineStr">
         <is>
-          <t>Boston Scientific</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="E309" s="29" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F309" s="29" t="inlineStr"/>
@@ -34259,17 +34259,17 @@
       </c>
       <c r="C310" s="30" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="D310" s="29" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="E310" s="29" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F310" s="29" t="inlineStr"/>
@@ -34290,17 +34290,17 @@
       </c>
       <c r="C311" s="30" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>KMI</t>
         </is>
       </c>
       <c r="D311" s="29" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Kinder Morgan</t>
         </is>
       </c>
       <c r="E311" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F311" s="29" t="inlineStr"/>
@@ -34321,17 +34321,17 @@
       </c>
       <c r="C312" s="30" t="inlineStr">
         <is>
-          <t>KMI</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="D312" s="29" t="inlineStr">
         <is>
-          <t>Kinder Morgan</t>
+          <t>Lennox Intl</t>
         </is>
       </c>
       <c r="E312" s="29" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F312" s="29" t="inlineStr"/>
@@ -34352,17 +34352,17 @@
       </c>
       <c r="C313" s="30" t="inlineStr">
         <is>
-          <t>LII</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="D313" s="29" t="inlineStr">
         <is>
-          <t>Lennox Intl</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="E313" s="29" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F313" s="29" t="inlineStr"/>
@@ -34383,17 +34383,17 @@
       </c>
       <c r="C314" s="30" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="D314" s="29" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>O'Reilly Auto</t>
         </is>
       </c>
       <c r="E314" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F314" s="29" t="inlineStr"/>
@@ -34414,17 +34414,17 @@
       </c>
       <c r="C315" s="30" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>PKG</t>
         </is>
       </c>
       <c r="D315" s="29" t="inlineStr">
         <is>
-          <t>O'Reilly Auto</t>
+          <t>Packaging Corp</t>
         </is>
       </c>
       <c r="E315" s="29" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F315" s="29" t="inlineStr"/>
@@ -34445,17 +34445,17 @@
       </c>
       <c r="C316" s="30" t="inlineStr">
         <is>
-          <t>PKG</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="D316" s="29" t="inlineStr">
         <is>
-          <t>Packaging Corp</t>
+          <t>SAP SE</t>
         </is>
       </c>
       <c r="E316" s="29" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F316" s="29" t="inlineStr"/>
@@ -34476,17 +34476,17 @@
       </c>
       <c r="C317" s="30" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>SEIC</t>
         </is>
       </c>
       <c r="D317" s="29" t="inlineStr">
         <is>
-          <t>SAP SE</t>
+          <t>SEI Investments</t>
         </is>
       </c>
       <c r="E317" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F317" s="29" t="inlineStr"/>
@@ -34507,17 +34507,17 @@
       </c>
       <c r="C318" s="30" t="inlineStr">
         <is>
-          <t>SEIC</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="D318" s="29" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>Thermo Fisher</t>
         </is>
       </c>
       <c r="E318" s="29" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F318" s="29" t="inlineStr"/>
@@ -34538,17 +34538,17 @@
       </c>
       <c r="C319" s="30" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="D319" s="29" t="inlineStr">
         <is>
-          <t>Thermo Fisher</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="E319" s="29" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F319" s="29" t="inlineStr"/>
@@ -34569,17 +34569,17 @@
       </c>
       <c r="C320" s="30" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="D320" s="29" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="E320" s="29" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F320" s="29" t="inlineStr"/>
@@ -34591,26 +34591,26 @@
     </row>
     <row r="321">
       <c r="A321" s="28" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B321" s="29" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C321" s="30" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>BKR</t>
         </is>
       </c>
       <c r="D321" s="29" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Baker Hughes</t>
         </is>
       </c>
       <c r="E321" s="29" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F321" s="29" t="inlineStr"/>
@@ -34631,17 +34631,17 @@
       </c>
       <c r="C322" s="30" t="inlineStr">
         <is>
-          <t>BKR</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="D322" s="29" t="inlineStr">
         <is>
-          <t>Baker Hughes</t>
+          <t>Blackstone</t>
         </is>
       </c>
       <c r="E322" s="29" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F322" s="29" t="inlineStr"/>
@@ -34662,17 +34662,17 @@
       </c>
       <c r="C323" s="30" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="D323" s="29" t="inlineStr">
         <is>
-          <t>Blackstone</t>
+          <t>CBRE Group</t>
         </is>
       </c>
       <c r="E323" s="29" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F323" s="29" t="inlineStr"/>
@@ -34693,12 +34693,12 @@
       </c>
       <c r="C324" s="30" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="D324" s="29" t="inlineStr">
         <is>
-          <t>CBRE Group</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="E324" s="29" t="inlineStr">
@@ -34724,17 +34724,17 @@
       </c>
       <c r="C325" s="30" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="D325" s="29" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Dow</t>
         </is>
       </c>
       <c r="E325" s="29" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F325" s="29" t="inlineStr"/>
@@ -34755,12 +34755,12 @@
       </c>
       <c r="C326" s="30" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>FCX</t>
         </is>
       </c>
       <c r="D326" s="29" t="inlineStr">
         <is>
-          <t>Dow</t>
+          <t>Freeport-McMoRan</t>
         </is>
       </c>
       <c r="E326" s="29" t="inlineStr">
@@ -34786,17 +34786,17 @@
       </c>
       <c r="C327" s="30" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>FIX</t>
         </is>
       </c>
       <c r="D327" s="29" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan</t>
+          <t>Comfort Systems</t>
         </is>
       </c>
       <c r="E327" s="29" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F327" s="29" t="inlineStr"/>
@@ -34817,12 +34817,12 @@
       </c>
       <c r="C328" s="30" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="D328" s="29" t="inlineStr">
         <is>
-          <t>Comfort Systems</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="E328" s="29" t="inlineStr">
@@ -34848,17 +34848,17 @@
       </c>
       <c r="C329" s="30" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="D329" s="29" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E329" s="29" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F329" s="29" t="inlineStr"/>
@@ -34879,17 +34879,17 @@
       </c>
       <c r="C330" s="30" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>KNSL</t>
         </is>
       </c>
       <c r="D330" s="29" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Kinsale Capital</t>
         </is>
       </c>
       <c r="E330" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F330" s="29" t="inlineStr"/>
@@ -34910,17 +34910,17 @@
       </c>
       <c r="C331" s="30" t="inlineStr">
         <is>
-          <t>KNSL</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="D331" s="29" t="inlineStr">
         <is>
-          <t>Kinsale Capital</t>
+          <t>Pool Corp</t>
         </is>
       </c>
       <c r="E331" s="29" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F331" s="29" t="inlineStr"/>
@@ -34941,17 +34941,17 @@
       </c>
       <c r="C332" s="30" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="D332" s="29" t="inlineStr">
         <is>
-          <t>Pool Corp</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="E332" s="29" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F332" s="29" t="inlineStr"/>
@@ -34972,17 +34972,17 @@
       </c>
       <c r="C333" s="30" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="D333" s="29" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="E333" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F333" s="29" t="inlineStr"/>
@@ -36956,12 +36956,12 @@
       </c>
       <c r="C397" s="30" t="inlineStr">
         <is>
-          <t>TTMI</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="D397" s="29" t="inlineStr">
         <is>
-          <t>TTM Technologies</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="E397" s="29" t="inlineStr">
@@ -36987,17 +36987,17 @@
       </c>
       <c r="C398" s="30" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="D398" s="29" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="E398" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F398" s="29" t="inlineStr"/>
@@ -37018,17 +37018,17 @@
       </c>
       <c r="C399" s="30" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>WSO</t>
         </is>
       </c>
       <c r="D399" s="29" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Watsco</t>
         </is>
       </c>
       <c r="E399" s="29" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F399" s="29" t="inlineStr"/>
@@ -37040,26 +37040,26 @@
     </row>
     <row r="400">
       <c r="A400" s="28" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B400" s="29" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C400" s="30" t="inlineStr">
         <is>
-          <t>WSO</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="D400" s="29" t="inlineStr">
         <is>
-          <t>Watsco</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="E400" s="29" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F400" s="29" t="inlineStr"/>
@@ -37080,12 +37080,12 @@
       </c>
       <c r="C401" s="30" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>ALGM</t>
         </is>
       </c>
       <c r="D401" s="29" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Allegro MicroSystems</t>
         </is>
       </c>
       <c r="E401" s="29" t="inlineStr">
@@ -37111,17 +37111,17 @@
       </c>
       <c r="C402" s="30" t="inlineStr">
         <is>
-          <t>ALGM</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="D402" s="29" t="inlineStr">
         <is>
-          <t>Allegro MicroSystems</t>
+          <t>AMETEK</t>
         </is>
       </c>
       <c r="E402" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F402" s="29" t="inlineStr"/>
@@ -37142,17 +37142,17 @@
       </c>
       <c r="C403" s="30" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="D403" s="29" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="E403" s="29" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F403" s="29" t="inlineStr"/>
@@ -37173,17 +37173,17 @@
       </c>
       <c r="C404" s="30" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="D404" s="29" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>ASE Technology</t>
         </is>
       </c>
       <c r="E404" s="29" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F404" s="29" t="inlineStr"/>
@@ -37204,17 +37204,17 @@
       </c>
       <c r="C405" s="30" t="inlineStr">
         <is>
-          <t>ASX</t>
+          <t>CMS</t>
         </is>
       </c>
       <c r="D405" s="29" t="inlineStr">
         <is>
-          <t>ASE Technology</t>
+          <t>CMS Energy</t>
         </is>
       </c>
       <c r="E405" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F405" s="29" t="inlineStr"/>
@@ -37235,17 +37235,17 @@
       </c>
       <c r="C406" s="30" t="inlineStr">
         <is>
-          <t>CMS</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="D406" s="29" t="inlineStr">
         <is>
-          <t>CMS Energy</t>
+          <t>DexCom</t>
         </is>
       </c>
       <c r="E406" s="29" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F406" s="29" t="inlineStr"/>
@@ -37266,17 +37266,17 @@
       </c>
       <c r="C407" s="30" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>EPD</t>
         </is>
       </c>
       <c r="D407" s="29" t="inlineStr">
         <is>
-          <t>DexCom</t>
+          <t>Enterprise Products</t>
         </is>
       </c>
       <c r="E407" s="29" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F407" s="29" t="inlineStr"/>
@@ -37297,17 +37297,17 @@
       </c>
       <c r="C408" s="30" t="inlineStr">
         <is>
-          <t>EPD</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="D408" s="29" t="inlineStr">
         <is>
-          <t>Enterprise Products</t>
+          <t>Gilead Sciences</t>
         </is>
       </c>
       <c r="E408" s="29" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F408" s="29" t="inlineStr"/>
@@ -37328,17 +37328,17 @@
       </c>
       <c r="C409" s="30" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>HLI</t>
         </is>
       </c>
       <c r="D409" s="29" t="inlineStr">
         <is>
-          <t>Gilead Sciences</t>
+          <t>Houlihan Lokey</t>
         </is>
       </c>
       <c r="E409" s="29" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F409" s="29" t="inlineStr"/>
@@ -37359,12 +37359,12 @@
       </c>
       <c r="C410" s="30" t="inlineStr">
         <is>
-          <t>HLI</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="D410" s="29" t="inlineStr">
         <is>
-          <t>Houlihan Lokey</t>
+          <t>Intercontinental Ex</t>
         </is>
       </c>
       <c r="E410" s="29" t="inlineStr">
@@ -37390,17 +37390,17 @@
       </c>
       <c r="C411" s="30" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="D411" s="29" t="inlineStr">
         <is>
-          <t>Intercontinental Ex</t>
+          <t>L3Harris</t>
         </is>
       </c>
       <c r="E411" s="29" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F411" s="29" t="inlineStr"/>
@@ -37421,17 +37421,17 @@
       </c>
       <c r="C412" s="30" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="D412" s="29" t="inlineStr">
         <is>
-          <t>L3Harris</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="E412" s="29" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F412" s="29" t="inlineStr"/>
@@ -37452,17 +37452,17 @@
       </c>
       <c r="C413" s="30" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D413" s="29" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="E413" s="29" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F413" s="29" t="inlineStr"/>
@@ -37483,17 +37483,17 @@
       </c>
       <c r="C414" s="30" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="D414" s="29" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Altria</t>
         </is>
       </c>
       <c r="E414" s="29" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F414" s="29" t="inlineStr"/>
@@ -37514,17 +37514,17 @@
       </c>
       <c r="C415" s="30" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="D415" s="29" t="inlineStr">
         <is>
-          <t>Altria</t>
+          <t>Monolithic Power</t>
         </is>
       </c>
       <c r="E415" s="29" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F415" s="29" t="inlineStr"/>
@@ -37545,17 +37545,17 @@
       </c>
       <c r="C416" s="30" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="D416" s="29" t="inlineStr">
         <is>
-          <t>Monolithic Power</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="E416" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F416" s="29" t="inlineStr"/>
@@ -37576,17 +37576,17 @@
       </c>
       <c r="C417" s="30" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="D417" s="29" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="E417" s="29" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F417" s="29" t="inlineStr"/>
@@ -37607,12 +37607,12 @@
       </c>
       <c r="C418" s="30" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="D418" s="29" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Strategy (MicroStrategy)</t>
         </is>
       </c>
       <c r="E418" s="29" t="inlineStr">
@@ -37638,12 +37638,12 @@
       </c>
       <c r="C419" s="30" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="D419" s="29" t="inlineStr">
         <is>
-          <t>Strategy (MicroStrategy)</t>
+          <t>Cloudflare</t>
         </is>
       </c>
       <c r="E419" s="29" t="inlineStr">
@@ -37669,17 +37669,17 @@
       </c>
       <c r="C420" s="30" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>RIOT</t>
         </is>
       </c>
       <c r="D420" s="29" t="inlineStr">
         <is>
-          <t>Cloudflare</t>
+          <t>Riot Platforms</t>
         </is>
       </c>
       <c r="E420" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F420" s="29" t="inlineStr"/>
@@ -37700,17 +37700,17 @@
       </c>
       <c r="C421" s="30" t="inlineStr">
         <is>
-          <t>RIOT</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="D421" s="29" t="inlineStr">
         <is>
-          <t>Riot Platforms</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="E421" s="29" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F421" s="29" t="inlineStr"/>
@@ -37731,17 +37731,17 @@
       </c>
       <c r="C422" s="30" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="D422" s="29" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="E422" s="29" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F422" s="29" t="inlineStr"/>
@@ -37762,17 +37762,17 @@
       </c>
       <c r="C423" s="30" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>SYK</t>
         </is>
       </c>
       <c r="D423" s="29" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Stryker</t>
         </is>
       </c>
       <c r="E423" s="29" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F423" s="29" t="inlineStr"/>
@@ -37793,17 +37793,17 @@
       </c>
       <c r="C424" s="30" t="inlineStr">
         <is>
-          <t>SYK</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="D424" s="29" t="inlineStr">
         <is>
-          <t>Stryker</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="E424" s="29" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F424" s="29" t="inlineStr"/>
@@ -37824,17 +37824,17 @@
       </c>
       <c r="C425" s="30" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="D425" s="29" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="E425" s="29" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F425" s="29" t="inlineStr"/>
@@ -37855,12 +37855,12 @@
       </c>
       <c r="C426" s="30" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="D426" s="29" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="E426" s="29" t="inlineStr">
@@ -37886,17 +37886,17 @@
       </c>
       <c r="C427" s="30" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>WEC</t>
         </is>
       </c>
       <c r="D427" s="29" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>WEC Energy</t>
         </is>
       </c>
       <c r="E427" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F427" s="29" t="inlineStr"/>
@@ -37908,26 +37908,26 @@
     </row>
     <row r="428">
       <c r="A428" s="28" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="B428" s="29" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C428" s="30" t="inlineStr">
         <is>
-          <t>WEC</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="D428" s="29" t="inlineStr">
         <is>
-          <t>WEC Energy</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="E428" s="29" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F428" s="29" t="inlineStr"/>
@@ -37948,17 +37948,17 @@
       </c>
       <c r="C429" s="30" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>AGCO</t>
         </is>
       </c>
       <c r="D429" s="29" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>AGCO</t>
         </is>
       </c>
       <c r="E429" s="29" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F429" s="29" t="inlineStr"/>
@@ -37979,17 +37979,17 @@
       </c>
       <c r="C430" s="30" t="inlineStr">
         <is>
-          <t>AGCO</t>
+          <t>AON</t>
         </is>
       </c>
       <c r="D430" s="29" t="inlineStr">
         <is>
-          <t>AGCO</t>
+          <t>Aon</t>
         </is>
       </c>
       <c r="E430" s="29" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F430" s="29" t="inlineStr"/>
@@ -38010,17 +38010,17 @@
       </c>
       <c r="C431" s="30" t="inlineStr">
         <is>
-          <t>AON</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="D431" s="29" t="inlineStr">
         <is>
-          <t>Aon</t>
+          <t>Church &amp; Dwight</t>
         </is>
       </c>
       <c r="E431" s="29" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F431" s="29" t="inlineStr"/>
@@ -38041,12 +38041,12 @@
       </c>
       <c r="C432" s="30" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="D432" s="29" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="E432" s="29" t="inlineStr">
@@ -38072,17 +38072,17 @@
       </c>
       <c r="C433" s="30" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="D433" s="29" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="E433" s="29" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F433" s="29" t="inlineStr"/>
@@ -38103,17 +38103,17 @@
       </c>
       <c r="C434" s="30" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>FRT</t>
         </is>
       </c>
       <c r="D434" s="29" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Federal Realty</t>
         </is>
       </c>
       <c r="E434" s="29" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F434" s="29" t="inlineStr"/>
@@ -38134,17 +38134,17 @@
       </c>
       <c r="C435" s="30" t="inlineStr">
         <is>
-          <t>FRT</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="D435" s="29" t="inlineStr">
         <is>
-          <t>Federal Realty</t>
+          <t>W.W. Grainger</t>
         </is>
       </c>
       <c r="E435" s="29" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F435" s="29" t="inlineStr"/>
@@ -38165,17 +38165,17 @@
       </c>
       <c r="C436" s="30" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="D436" s="29" t="inlineStr">
         <is>
-          <t>W.W. Grainger</t>
+          <t>Linde</t>
         </is>
       </c>
       <c r="E436" s="29" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F436" s="29" t="inlineStr"/>
@@ -38196,17 +38196,17 @@
       </c>
       <c r="C437" s="30" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="D437" s="29" t="inlineStr">
         <is>
-          <t>Linde</t>
+          <t>RBC Bearings</t>
         </is>
       </c>
       <c r="E437" s="29" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F437" s="29" t="inlineStr"/>
@@ -38227,17 +38227,17 @@
       </c>
       <c r="C438" s="30" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="D438" s="29" t="inlineStr">
         <is>
-          <t>RBC Bearings</t>
+          <t>Exxon Mobil</t>
         </is>
       </c>
       <c r="E438" s="29" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F438" s="29" t="inlineStr"/>
@@ -38249,21 +38249,21 @@
     </row>
     <row r="439">
       <c r="A439" s="28" t="n">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="B439" s="29" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C439" s="30" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="D439" s="29" t="inlineStr">
         <is>
-          <t>Exxon Mobil</t>
+          <t>Diamondback Energy</t>
         </is>
       </c>
       <c r="E439" s="29" t="inlineStr">
@@ -38289,17 +38289,17 @@
       </c>
       <c r="C440" s="30" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>FN</t>
         </is>
       </c>
       <c r="D440" s="29" t="inlineStr">
         <is>
-          <t>Diamondback Energy</t>
+          <t>Fabrinet</t>
         </is>
       </c>
       <c r="E440" s="29" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F440" s="29" t="inlineStr"/>
@@ -38320,17 +38320,17 @@
       </c>
       <c r="C441" s="30" t="inlineStr">
         <is>
-          <t>FN</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="D441" s="29" t="inlineStr">
         <is>
-          <t>Fabrinet</t>
+          <t>IDEXX Labs</t>
         </is>
       </c>
       <c r="E441" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F441" s="29" t="inlineStr"/>
@@ -38351,17 +38351,17 @@
       </c>
       <c r="C442" s="30" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>O</t>
         </is>
       </c>
       <c r="D442" s="29" t="inlineStr">
         <is>
-          <t>IDEXX Labs</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="E442" s="29" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F442" s="29" t="inlineStr"/>
@@ -38382,17 +38382,17 @@
       </c>
       <c r="C443" s="30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="D443" s="29" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>ON Semiconductor</t>
         </is>
       </c>
       <c r="E443" s="29" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F443" s="29" t="inlineStr"/>
@@ -38413,12 +38413,12 @@
       </c>
       <c r="C444" s="30" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="D444" s="29" t="inlineStr">
         <is>
-          <t>ON Semiconductor</t>
+          <t>Palantir</t>
         </is>
       </c>
       <c r="E444" s="29" t="inlineStr">
@@ -38444,12 +38444,12 @@
       </c>
       <c r="C445" s="30" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SANM</t>
         </is>
       </c>
       <c r="D445" s="29" t="inlineStr">
         <is>
-          <t>Palantir</t>
+          <t>Sanmina</t>
         </is>
       </c>
       <c r="E445" s="29" t="inlineStr">
@@ -38475,17 +38475,17 @@
       </c>
       <c r="C446" s="30" t="inlineStr">
         <is>
-          <t>SANM</t>
+          <t>SPG</t>
         </is>
       </c>
       <c r="D446" s="29" t="inlineStr">
         <is>
-          <t>Sanmina</t>
+          <t>Simon Property</t>
         </is>
       </c>
       <c r="E446" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="F446" s="29" t="inlineStr"/>
@@ -38506,17 +38506,17 @@
       </c>
       <c r="C447" s="30" t="inlineStr">
         <is>
-          <t>SPG</t>
+          <t>VNOM</t>
         </is>
       </c>
       <c r="D447" s="29" t="inlineStr">
         <is>
-          <t>Simon Property</t>
+          <t>Viper Energy</t>
         </is>
       </c>
       <c r="E447" s="29" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F447" s="29" t="inlineStr"/>
@@ -38537,12 +38537,12 @@
       </c>
       <c r="C448" s="30" t="inlineStr">
         <is>
-          <t>VNOM</t>
+          <t>WMB</t>
         </is>
       </c>
       <c r="D448" s="29" t="inlineStr">
         <is>
-          <t>Viper Energy</t>
+          <t>Williams Companies</t>
         </is>
       </c>
       <c r="E448" s="29" t="inlineStr">
@@ -38559,26 +38559,26 @@
     </row>
     <row r="449">
       <c r="A449" s="28" t="n">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="B449" s="29" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="C449" s="30" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>ACLS</t>
         </is>
       </c>
       <c r="D449" s="29" t="inlineStr">
         <is>
-          <t>Williams Companies</t>
+          <t>Axcelis</t>
         </is>
       </c>
       <c r="E449" s="29" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F449" s="29" t="inlineStr"/>
@@ -38599,12 +38599,12 @@
       </c>
       <c r="C450" s="30" t="inlineStr">
         <is>
-          <t>ACLS</t>
+          <t>AEIS</t>
         </is>
       </c>
       <c r="D450" s="29" t="inlineStr">
         <is>
-          <t>Axcelis</t>
+          <t>Advanced Energy</t>
         </is>
       </c>
       <c r="E450" s="29" t="inlineStr">
@@ -38630,17 +38630,17 @@
       </c>
       <c r="C451" s="30" t="inlineStr">
         <is>
-          <t>AEIS</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="D451" s="29" t="inlineStr">
         <is>
-          <t>Advanced Energy</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="E451" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F451" s="29" t="inlineStr"/>
@@ -38661,17 +38661,17 @@
       </c>
       <c r="C452" s="30" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="D452" s="29" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Astera Labs</t>
         </is>
       </c>
       <c r="E452" s="29" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F452" s="29" t="inlineStr"/>
@@ -38692,12 +38692,12 @@
       </c>
       <c r="C453" s="30" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="D453" s="29" t="inlineStr">
         <is>
-          <t>Astera Labs</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="E453" s="29" t="inlineStr">
@@ -38723,17 +38723,17 @@
       </c>
       <c r="C454" s="30" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="D454" s="29" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="E454" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F454" s="29" t="inlineStr"/>
@@ -38754,17 +38754,17 @@
       </c>
       <c r="C455" s="30" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="D455" s="29" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="E455" s="29" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F455" s="29" t="inlineStr"/>
@@ -38785,17 +38785,17 @@
       </c>
       <c r="C456" s="30" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="D456" s="29" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="E456" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F456" s="29" t="inlineStr"/>
@@ -38816,12 +38816,12 @@
       </c>
       <c r="C457" s="30" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="D457" s="29" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="E457" s="29" t="inlineStr">
@@ -38847,17 +38847,17 @@
       </c>
       <c r="C458" s="30" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>HUT</t>
         </is>
       </c>
       <c r="D458" s="29" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Hut 8</t>
         </is>
       </c>
       <c r="E458" s="29" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F458" s="29" t="inlineStr"/>
@@ -38878,12 +38878,12 @@
       </c>
       <c r="C459" s="30" t="inlineStr">
         <is>
-          <t>HUT</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="D459" s="29" t="inlineStr">
         <is>
-          <t>Hut 8</t>
+          <t>Jack Henry</t>
         </is>
       </c>
       <c r="E459" s="29" t="inlineStr">
@@ -38909,17 +38909,17 @@
       </c>
       <c r="C460" s="30" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="D460" s="29" t="inlineStr">
         <is>
-          <t>Jack Henry</t>
+          <t>Lumentum</t>
         </is>
       </c>
       <c r="E460" s="29" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F460" s="29" t="inlineStr"/>
@@ -38940,17 +38940,17 @@
       </c>
       <c r="C461" s="30" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>MLM</t>
         </is>
       </c>
       <c r="D461" s="29" t="inlineStr">
         <is>
-          <t>Lumentum</t>
+          <t>Martin Marietta</t>
         </is>
       </c>
       <c r="E461" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F461" s="29" t="inlineStr"/>
@@ -38971,17 +38971,17 @@
       </c>
       <c r="C462" s="30" t="inlineStr">
         <is>
-          <t>MLM</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="D462" s="29" t="inlineStr">
         <is>
-          <t>Martin Marietta</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="E462" s="29" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F462" s="29" t="inlineStr"/>
@@ -39002,17 +39002,17 @@
       </c>
       <c r="C463" s="30" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="D463" s="29" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="E463" s="29" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F463" s="29" t="inlineStr"/>
@@ -39033,17 +39033,17 @@
       </c>
       <c r="C464" s="30" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="D464" s="29" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Super Micro</t>
         </is>
       </c>
       <c r="E464" s="29" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F464" s="29" t="inlineStr"/>
@@ -39064,17 +39064,17 @@
       </c>
       <c r="C465" s="30" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="D465" s="29" t="inlineStr">
         <is>
-          <t>Super Micro</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="E465" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F465" s="29" t="inlineStr"/>
@@ -39095,17 +39095,17 @@
       </c>
       <c r="C466" s="30" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="D466" s="29" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="E466" s="29" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F466" s="29" t="inlineStr"/>
@@ -39126,17 +39126,17 @@
       </c>
       <c r="C467" s="30" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>WOLF</t>
         </is>
       </c>
       <c r="D467" s="29" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Wolfspeed</t>
         </is>
       </c>
       <c r="E467" s="29" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F467" s="29" t="inlineStr"/>
@@ -39157,17 +39157,17 @@
       </c>
       <c r="C468" s="30" t="inlineStr">
         <is>
-          <t>WOLF</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="D468" s="29" t="inlineStr">
         <is>
-          <t>Wolfspeed</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="E468" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F468" s="29" t="inlineStr"/>
@@ -39179,26 +39179,26 @@
     </row>
     <row r="469">
       <c r="A469" s="28" t="n">
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="B469" s="29" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="C469" s="30" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="D469" s="29" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Arm Holdings</t>
         </is>
       </c>
       <c r="E469" s="29" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F469" s="29" t="inlineStr"/>
@@ -39219,17 +39219,17 @@
       </c>
       <c r="C470" s="30" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>ATO</t>
         </is>
       </c>
       <c r="D470" s="29" t="inlineStr">
         <is>
-          <t>Arm Holdings</t>
+          <t>Atmos Energy</t>
         </is>
       </c>
       <c r="E470" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F470" s="29" t="inlineStr"/>
@@ -39250,12 +39250,12 @@
       </c>
       <c r="C471" s="30" t="inlineStr">
         <is>
-          <t>ATO</t>
+          <t>BEPC</t>
         </is>
       </c>
       <c r="D471" s="29" t="inlineStr">
         <is>
-          <t>Atmos Energy</t>
+          <t>Brookfield Renewable</t>
         </is>
       </c>
       <c r="E471" s="29" t="inlineStr">
@@ -39281,17 +39281,17 @@
       </c>
       <c r="C472" s="30" t="inlineStr">
         <is>
-          <t>BEPC</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="D472" s="29" t="inlineStr">
         <is>
-          <t>Brookfield Renewable</t>
+          <t>Coherent</t>
         </is>
       </c>
       <c r="E472" s="29" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F472" s="29" t="inlineStr"/>
@@ -39312,17 +39312,17 @@
       </c>
       <c r="C473" s="30" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="D473" s="29" t="inlineStr">
         <is>
-          <t>Coherent</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="E473" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F473" s="29" t="inlineStr"/>
@@ -39343,17 +39343,17 @@
       </c>
       <c r="C474" s="30" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="D474" s="29" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Corpay</t>
         </is>
       </c>
       <c r="E474" s="29" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F474" s="29" t="inlineStr"/>
@@ -39374,17 +39374,17 @@
       </c>
       <c r="C475" s="30" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="D475" s="29" t="inlineStr">
         <is>
-          <t>Corpay</t>
+          <t>Dynatrace</t>
         </is>
       </c>
       <c r="E475" s="29" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F475" s="29" t="inlineStr"/>
@@ -39405,17 +39405,17 @@
       </c>
       <c r="C476" s="30" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="D476" s="29" t="inlineStr">
         <is>
-          <t>Dynatrace</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="E476" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F476" s="29" t="inlineStr"/>
@@ -39436,17 +39436,17 @@
       </c>
       <c r="C477" s="30" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="D477" s="29" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Energy Transfer</t>
         </is>
       </c>
       <c r="E477" s="29" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F477" s="29" t="inlineStr"/>
@@ -39467,17 +39467,17 @@
       </c>
       <c r="C478" s="30" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="D478" s="29" t="inlineStr">
         <is>
-          <t>Energy Transfer</t>
+          <t>Fortinet</t>
         </is>
       </c>
       <c r="E478" s="29" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F478" s="29" t="inlineStr"/>
@@ -39498,17 +39498,17 @@
       </c>
       <c r="C479" s="30" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="D479" s="29" t="inlineStr">
         <is>
-          <t>Fortinet</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="E479" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F479" s="29" t="inlineStr"/>
@@ -39529,17 +39529,17 @@
       </c>
       <c r="C480" s="30" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>HUBS</t>
         </is>
       </c>
       <c r="D480" s="29" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="E480" s="29" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F480" s="29" t="inlineStr"/>
@@ -39560,12 +39560,12 @@
       </c>
       <c r="C481" s="30" t="inlineStr">
         <is>
-          <t>HUBS</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="D481" s="29" t="inlineStr">
         <is>
-          <t>HubSpot</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="E481" s="29" t="inlineStr">
@@ -39591,17 +39591,17 @@
       </c>
       <c r="C482" s="30" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="D482" s="29" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="E482" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F482" s="29" t="inlineStr"/>
@@ -39622,17 +39622,17 @@
       </c>
       <c r="C483" s="30" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>MKSI</t>
         </is>
       </c>
       <c r="D483" s="29" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>MKS Instruments</t>
         </is>
       </c>
       <c r="E483" s="29" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F483" s="29" t="inlineStr"/>
@@ -39653,12 +39653,12 @@
       </c>
       <c r="C484" s="30" t="inlineStr">
         <is>
-          <t>MKSI</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="D484" s="29" t="inlineStr">
         <is>
-          <t>MKS Instruments</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="E484" s="29" t="inlineStr">
@@ -39684,17 +39684,17 @@
       </c>
       <c r="C485" s="30" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="D485" s="29" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Sportradar</t>
         </is>
       </c>
       <c r="E485" s="29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F485" s="29" t="inlineStr"/>
@@ -39715,17 +39715,17 @@
       </c>
       <c r="C486" s="30" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="D486" s="29" t="inlineStr">
         <is>
-          <t>Sportradar</t>
+          <t>TKO Group</t>
         </is>
       </c>
       <c r="E486" s="29" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F486" s="29" t="inlineStr"/>
@@ -39746,17 +39746,17 @@
       </c>
       <c r="C487" s="30" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="D487" s="29" t="inlineStr">
         <is>
-          <t>TKO Group</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="E487" s="29" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F487" s="29" t="inlineStr"/>
@@ -39777,12 +39777,12 @@
       </c>
       <c r="C488" s="30" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>TTMI</t>
         </is>
       </c>
       <c r="D488" s="29" t="inlineStr">
         <is>
-          <t>Trimble</t>
+          <t>TTM Technologies</t>
         </is>
       </c>
       <c r="E488" s="29" t="inlineStr">
@@ -43952,7 +43952,7 @@
       <c r="B36" s="38" t="inlineStr">
         <is>
           <t>20
-ADC CB DHR GE GM GPC HAL ISRG KO LMT NFLX OMC PCAR PEGA RTX TXN</t>
+ADC CB DHR GE GM GPC HAL ISRG KO LMT NFLX OMC PCAR PEGA TXN</t>
         </is>
       </c>
       <c r="C36" s="38" t="inlineStr">
@@ -43964,7 +43964,7 @@
       <c r="D36" s="38" t="inlineStr">
         <is>
           <t>22
-BKR BX CBRE DLR DOW FCX FIX HON INTC KNSL POOL ROP TMUS TSCO UNP</t>
+BKR BX CBRE DLR DOW FCX FIX HON INTC KNSL POOL ROP RTX TMUS TSCO UNP</t>
         </is>
       </c>
       <c r="E36" s="38" t="inlineStr">
@@ -44000,7 +44000,7 @@
       <c r="C37" s="38" t="inlineStr">
         <is>
           <t>28
-ADP AWK BA CAT CMG COHU CVS EQIX ETR FORM GOOGL KHC KLAC META MKL MSFT NOW ODFL PI PSA PSX ROL SAN SBUX SUI TEL TTMI TYL VZ WSO</t>
+ADP AWK BA CAT CMG COHU CVS EQIX ETR FORM GOOGL KHC KLAC META MKL MSFT NOW ODFL PI PSA PSX ROL SAN SBUX SUI TEL TYL VZ WSO</t>
         </is>
       </c>
       <c r="D37" s="38" t="inlineStr">
@@ -44095,7 +44095,7 @@
       <c r="C43" s="38" t="inlineStr">
         <is>
           <t>4
-ARM ATO BEPC COHR COR CPAY DT EMR ET FTNT HOOD HUBS IONQ MCD MKSI QCOM SRAD TKO TRMB U</t>
+ARM ATO BEPC COHR COR CPAY DT EMR ET FTNT HOOD HUBS IONQ MCD MKSI QCOM SRAD TKO TRMB TTMI U</t>
         </is>
       </c>
       <c r="D43" s="38" t="inlineStr">

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>94.84999999999999</v>
+        <v>96.89</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-0.062</v>
+        <v>-0.0192</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.0659</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>46239</v>
@@ -878,7 +878,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="9" t="n">
-        <v>0.3178703215603585</v>
+        <v>0.2901228196924347</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0.518186610437533</v>
+        <v>0.4862214882856848</v>
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>319.74</v>
+        <v>326.91</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>-0.07400000000000001</v>
+        <v>-0.0311</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>-0.1778</v>
+        <v>-0.162</v>
       </c>
       <c r="G3" s="17" t="n">
         <v>46322</v>
@@ -973,7 +973,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="20" t="n">
-        <v>0.3698630136986301</v>
+        <v>0.3398182986142974</v>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="20" t="n">
-        <v>0.3135672734096453</v>
+        <v>0.2847572726438468</v>
       </c>
       <c r="Q3" s="21" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>595.1900000000001</v>
+        <v>596.9299999999999</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>0.0673</v>
+        <v>0.0848</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.0604</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>46232</v>
@@ -1064,7 +1064,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="9" t="n">
-        <v>0.4029133553991161</v>
+        <v>0.3988239827115408</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>0.5625262521211712</v>
+        <v>0.5579716214631533</v>
       </c>
       <c r="Q4" s="10" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>37.91</v>
+        <v>38.9</v>
       </c>
       <c r="E5" s="20" t="n">
-        <v>0.0727</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>0.0545</v>
+        <v>0.0699</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>46238</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>70.09</v>
+        <v>70.86</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-0.0244</v>
+        <v>-0.04</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-0.2006</v>
+        <v>-0.1795</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>46315</v>
@@ -1220,7 +1220,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>0.1413896418889998</v>
+        <v>0.1289867344058707</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0.4267370523612498</v>
+        <v>0.4112334180073384</v>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>79.66</v>
+        <v>82.63</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>0.0815</v>
+        <v>0.1305</v>
       </c>
       <c r="F7" s="20" t="n">
-        <v>0.0706</v>
+        <v>0.1153</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>46231</v>
@@ -1307,7 +1307,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="20" t="n">
-        <v>0.1423550087873463</v>
+        <v>0.1012949292024689</v>
       </c>
       <c r="N7" s="14" t="inlineStr"/>
       <c r="O7" s="19" t="n"/>
@@ -1351,13 +1351,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>482.66</v>
+        <v>496.36</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.0608</v>
+        <v>0.079</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.0888</v>
+        <v>-0.0394</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>46238</v>
@@ -1386,7 +1386,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>0.1808105084324367</v>
+        <v>0.1482190345716817</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>0.3426428541830687</v>
+        <v>0.3055846562978482</v>
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>180.62</v>
+        <v>182.91</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>-0.1125</v>
+        <v>-0.1527</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>-0.0397</v>
+        <v>-0.08789999999999999</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>46237</v>
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>180.09</v>
+        <v>180.42</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.0039</v>
+        <v>-0.0124</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0.05769999999999999</v>
+        <v>-0.0454</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>46317</v>
@@ -1542,7 +1542,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>-0.05602754178466324</v>
+        <v>-0.05775412925396291</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>0.4992503748125937</v>
+        <v>0.4965081476554707</v>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
@@ -1594,13 +1594,13 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>46.38</v>
+        <v>47.43</v>
       </c>
       <c r="E11" s="20" t="n">
-        <v>0.0153</v>
+        <v>0.0191</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>-0.0435</v>
+        <v>-0.0121</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>46316</v>
@@ -1629,7 +1629,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>-0.07287623975851665</v>
+        <v>-0.09340080118068732</v>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="20" t="n">
-        <v>0.07805088400172482</v>
+        <v>0.05418511490617753</v>
       </c>
       <c r="Q11" s="21" t="inlineStr">
         <is>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>141.1</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>-0.0229</v>
+        <v>145.95</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>0.0027</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>0.0635</v>
+        <v>0.0851</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>46240</v>
@@ -1720,7 +1720,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>0.2827781715095677</v>
+        <v>0.2401507365536144</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>0.09851169383416021</v>
+        <v>0.06200753682768079</v>
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
@@ -1772,13 +1772,13 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>232.11</v>
+        <v>231.86</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>-0.0092</v>
+        <v>-0.0036</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>-0.1251</v>
+        <v>-0.1538</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>46233</v>
@@ -1807,7 +1807,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="20" t="n">
-        <v>0.3872732756020851</v>
+        <v>0.3887690847925471</v>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="20" t="n">
-        <v>0.2278660979707896</v>
+        <v>0.2291900284654532</v>
       </c>
       <c r="Q13" s="21" t="inlineStr">
         <is>
@@ -1871,13 +1871,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2957.41</v>
+        <v>3088.13</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.04219999999999999</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>-0.046</v>
+        <v>-0.013</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>0.027</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>46287</v>
@@ -1906,7 +1906,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>0.4032548750426895</v>
+        <v>0.3438553428774047</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>0.2510947078693858</v>
+        <v>0.1981360888304572</v>
       </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>85.43000000000001</v>
+        <v>88.59</v>
       </c>
       <c r="E15" s="20" t="n">
-        <v>0.1005</v>
+        <v>0.14</v>
       </c>
       <c r="F15" s="20" t="n">
-        <v>0.3513</v>
+        <v>0.1853</v>
       </c>
       <c r="G15" s="17" t="n">
         <v>46261</v>
@@ -1993,7 +1993,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="16" t="n">
-        <v>-0.2391431581411683</v>
+        <v>-0.2662828761711254</v>
       </c>
       <c r="N15" s="14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>-0.005033360646143121</v>
+        <v>-0.04052376114685634</v>
       </c>
       <c r="Q15" s="21" t="inlineStr"/>
       <c r="R15" s="19" t="n"/>
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>177.46</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>-0.0209</v>
+        <v>186.23</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.0867</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>46238</v>
@@ -2074,7 +2074,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>0.2059055561816747</v>
+        <v>0.1491166836707298</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>0.3805928096472444</v>
+        <v>0.3155775116791065</v>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
@@ -2134,13 +2134,13 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>349.97</v>
+        <v>353.3</v>
       </c>
       <c r="E17" s="20" t="n">
-        <v>0.0361</v>
+        <v>0.1014</v>
       </c>
       <c r="F17" s="20" t="n">
-        <v>0.0717</v>
+        <v>0.1756</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>46261</v>
@@ -2169,7 +2169,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="20" t="n">
-        <v>0.07152041603566012</v>
+        <v>0.06142088876309083</v>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="20" t="n">
-        <v>0.07152041603566012</v>
+        <v>0.06142088876309083</v>
       </c>
       <c r="Q17" s="21" t="inlineStr"/>
       <c r="R17" s="19" t="n"/>
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>31.79</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>0.0032</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>-0.0161</v>
+        <v>33.18</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>0.0234</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>46232</v>
@@ -2254,7 +2254,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>0.4155394778232149</v>
+        <v>0.3562386980108499</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>0.4155394778232149</v>
+        <v>0.3562386980108499</v>
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
@@ -2306,13 +2306,13 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>146.76</v>
+        <v>147.39</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>-0.1186</v>
+        <v>-0.1137</v>
       </c>
       <c r="F19" s="20" t="n">
-        <v>0.008</v>
+        <v>0.0032</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>46324</v>
@@ -2341,7 +2341,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="20" t="n">
-        <v>0.158353774870537</v>
+        <v>0.1534025374855826</v>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="20" t="n">
-        <v>0.206050695012265</v>
+        <v>0.2008955831467536</v>
       </c>
       <c r="Q19" s="21" t="inlineStr">
         <is>
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>206.04</v>
+        <v>205.07</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-0.1304</v>
+        <v>-0.1426</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.1162</v>
+        <v>-0.09380000000000001</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>46261</v>
@@ -2428,7 +2428,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>0.06775383420695015</v>
+        <v>0.07280440825084121</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="8" t="n"/>
@@ -2472,13 +2472,13 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>120.45</v>
+        <v>124.11</v>
       </c>
       <c r="E21" s="20" t="n">
-        <v>0.0092</v>
+        <v>0.0019</v>
       </c>
       <c r="F21" s="20" t="n">
-        <v>0.2855</v>
+        <v>0.0983</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>46267</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>82.64</v>
+        <v>85.45</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.0467</v>
+        <v>0.0941</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.0357</v>
+        <v>0.013</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>46315</v>
@@ -2568,7 +2568,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-0.2618586640851888</v>
+        <v>-0.286132241076653</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>0.2100677637947725</v>
+        <v>0.1702750146284376</v>
       </c>
       <c r="Q22" s="10" t="inlineStr">
         <is>
@@ -2620,13 +2620,13 @@
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>124.21</v>
+        <v>127.72</v>
       </c>
       <c r="E23" s="20" t="n">
-        <v>0.1217</v>
+        <v>0.1009</v>
       </c>
       <c r="F23" s="20" t="n">
-        <v>0.2799</v>
+        <v>0.2868</v>
       </c>
       <c r="G23" s="17" t="n">
         <v>46315</v>
@@ -2658,7 +2658,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="20" t="n">
-        <v>0.1673778278721521</v>
+        <v>0.1352959599123082</v>
       </c>
       <c r="Q23" s="21" t="inlineStr"/>
       <c r="R23" s="19" t="n"/>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>332.98</v>
+        <v>337.82</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-0.0288</v>
+        <v>-0.0316</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0.0723</v>
+        <v>0.0517</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>46252</v>
@@ -2728,7 +2728,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>0.08114601477566215</v>
+        <v>0.06565626665087919</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="9" t="n">
-        <v>0.2012733497507357</v>
+        <v>0.1840625185009769</v>
       </c>
       <c r="Q24" s="10" t="inlineStr">
         <is>
@@ -2788,13 +2788,13 @@
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>207.64</v>
+        <v>211.58</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>-0.0624</v>
+        <v>-0.049</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>-0.0209</v>
+        <v>-0.0291</v>
       </c>
       <c r="G25" s="17" t="n">
         <v>46253</v>
@@ -2823,7 +2823,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="20" t="n">
-        <v>0.2280870737815451</v>
+        <v>0.2052178844881368</v>
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="20" t="n">
-        <v>0.1076863802735504</v>
+        <v>0.08705926836184888</v>
       </c>
       <c r="Q25" s="21" t="inlineStr">
         <is>
@@ -2879,13 +2879,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>264.76</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>-0.0333</v>
+        <v>269.92</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0.0005999999999999999</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.0519</v>
+        <v>-0.029</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>46238</v>
@@ -2914,7 +2914,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="9" t="n">
-        <v>0.133101676990482</v>
+        <v>0.1114404267931238</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="9" t="n">
-        <v>0.3219519564888956</v>
+        <v>0.2966804979253111</v>
       </c>
       <c r="Q26" s="10" t="inlineStr">
         <is>
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>-0.0029</v>
+        <v>42.12</v>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>0.0336</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>-0.0721</v>
+        <v>-0.1108</v>
       </c>
       <c r="G27" s="17" t="n">
         <v>46289</v>
@@ -3027,13 +3027,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>-0.0048</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>-0.0275</v>
+        <v>91.17</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>0.0217</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>46232</v>
@@ -3062,7 +3062,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="9" t="n">
-        <v>0.2585812356979404</v>
+        <v>0.2065372381265767</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.2613798398596029</v>
       </c>
       <c r="Q28" s="10" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>183.77</v>
+        <v>186.5</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>-0.1051</v>
+        <v>-0.1187</v>
       </c>
       <c r="F29" s="20" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0097</v>
       </c>
       <c r="G29" s="17" t="n">
         <v>46317</v>
@@ -3179,13 +3179,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>238.89</v>
+        <v>242.3</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.0451</v>
+        <v>0.1362</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>0.0179</v>
+        <v>0.0665</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>46254</v>
@@ -3214,7 +3214,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="9" t="n">
-        <v>0.02557662522499901</v>
+        <v>0.01114321089558394</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="9" t="n">
-        <v>0.1092971660596928</v>
+        <v>0.09368551382583569</v>
       </c>
       <c r="Q30" s="10" t="inlineStr">
         <is>
@@ -3266,13 +3266,13 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>103.25</v>
+        <v>104</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>-0.0027</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>0.018</v>
+        <v>0.0323</v>
       </c>
       <c r="G31" s="17" t="n">
         <v>46232</v>
@@ -3301,7 +3301,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="20" t="n">
-        <v>0.162227602905569</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="N31" s="14" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="20" t="n">
-        <v>0.1138014527845036</v>
+        <v>0.1057692307692308</v>
       </c>
       <c r="Q31" s="21" t="inlineStr">
         <is>
@@ -3353,16 +3353,16 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>14.29</v>
+        <v>14.71</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>-0.0332</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>0.1001</v>
+        <v>0.1272</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>Aug 04</t>
+          <t>Aug 03</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr"/>
@@ -3414,13 +3414,13 @@
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>154.22</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>-0.0663</v>
-      </c>
-      <c r="F33" s="16" t="n">
-        <v>-0.0299</v>
+        <v>156.87</v>
+      </c>
+      <c r="E33" s="20" t="n">
+        <v>0.009300000000000001</v>
+      </c>
+      <c r="F33" s="20" t="n">
+        <v>0.0128</v>
       </c>
       <c r="G33" s="17" t="n">
         <v>46253</v>
@@ -3449,7 +3449,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="20" t="n">
-        <v>0.03747892620931138</v>
+        <v>0.01995282718174281</v>
       </c>
       <c r="N33" s="14" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="20" t="n">
-        <v>0.1347425755414343</v>
+        <v>0.1155734047300312</v>
       </c>
       <c r="Q33" s="21" t="inlineStr">
         <is>
@@ -3505,13 +3505,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>31.02</v>
+        <v>31.86</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.0319</v>
+        <v>0.0208</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>0.0409</v>
+        <v>0.0156</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>46317</v>
@@ -3540,7 +3540,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="9" t="n">
-        <v>0.1283043197936815</v>
+        <v>0.09855618330194603</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="9" t="n">
-        <v>0.2894906511927789</v>
+        <v>0.2554927809165097</v>
       </c>
       <c r="Q34" s="10" t="inlineStr">
         <is>
@@ -3592,13 +3592,13 @@
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>313.03</v>
+        <v>307.21</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>-0.1664</v>
+        <v>-0.1909</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>-0.2781</v>
+        <v>-0.3051</v>
       </c>
       <c r="G35" s="17" t="n">
         <v>46323</v>
@@ -3627,7 +3627,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="16" t="n">
-        <v>-0.584704341436923</v>
+        <v>-0.5768366915139481</v>
       </c>
       <c r="N35" s="14" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>-0.04162540331597602</v>
+        <v>-0.02346928810911097</v>
       </c>
       <c r="Q35" s="21" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>65.94</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>-0.1071</v>
+        <v>-0.1104</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-0.0596</v>
+        <v>-0.0442</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>46239</v>
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="D37" s="15" t="n">
-        <v>475.36</v>
+        <v>480.23</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>-0.0075</v>
+        <v>-0.0168</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>-0.0788</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="G37" s="17" t="n">
         <v>46261</v>
@@ -3775,7 +3775,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="16" t="n">
-        <v>-0.05334904072702797</v>
+        <v>-0.06294900360244053</v>
       </c>
       <c r="N37" s="14" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="20" t="n">
-        <v>0.3358296869740828</v>
+        <v>0.3222830726943339</v>
       </c>
       <c r="Q37" s="21" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>97.64</v>
+        <v>98.98</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>-0.0104</v>
+        <v>-0.006</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>0.01</v>
+        <v>0.0138</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>46234</v>
@@ -3866,7 +3866,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="9" t="n">
-        <v>0.1265874641540352</v>
+        <v>0.1113356233582541</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="9" t="n">
-        <v>0.07537894305612454</v>
+        <v>0.06082036775106078</v>
       </c>
       <c r="Q38" s="10" t="inlineStr">
         <is>
@@ -3922,13 +3922,13 @@
         </is>
       </c>
       <c r="D39" s="15" t="n">
-        <v>90.75</v>
+        <v>91.69</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>-0.0123</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F39" s="20" t="n">
-        <v>0.01</v>
+        <v>0.0004</v>
       </c>
       <c r="G39" s="17" t="n">
         <v>46234</v>
@@ -3957,7 +3957,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="20" t="n">
-        <v>0.04683195592286502</v>
+        <v>0.03609990184316722</v>
       </c>
       <c r="N39" s="14" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="20" t="n">
-        <v>0.1019283746556474</v>
+        <v>0.09063147562438655</v>
       </c>
       <c r="Q39" s="21" t="inlineStr">
         <is>
@@ -4013,13 +4013,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>935.03</v>
+        <v>950.27</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>-0.0271</v>
+        <v>-0.0024</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-0.0677</v>
+        <v>-0.0451</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>46289</v>
@@ -4048,7 +4048,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="9" t="n">
-        <v>0.06948440157000313</v>
+        <v>0.05233249497511236</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="9" t="n">
-        <v>0.1764328417270034</v>
+        <v>0.1575657444726236</v>
       </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
@@ -4108,13 +4108,13 @@
         </is>
       </c>
       <c r="D41" s="15" t="n">
-        <v>117.23</v>
-      </c>
-      <c r="E41" s="16" t="n">
-        <v>-0.0163</v>
+        <v>123.57</v>
+      </c>
+      <c r="E41" s="20" t="n">
+        <v>0.0339</v>
       </c>
       <c r="F41" s="20" t="n">
-        <v>0.1315</v>
+        <v>0.1244</v>
       </c>
       <c r="G41" s="17" t="n">
         <v>46261</v>
@@ -4143,7 +4143,7 @@
         <v>125</v>
       </c>
       <c r="M41" s="20" t="n">
-        <v>0.06627996246694529</v>
+        <v>0.01157238812009393</v>
       </c>
       <c r="N41" s="14" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="20" t="n">
-        <v>0.1515823594643009</v>
+        <v>0.09249817916970145</v>
       </c>
       <c r="Q41" s="21" t="inlineStr">
         <is>
@@ -4195,13 +4195,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>25.67</v>
+        <v>26.22</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.119</v>
+        <v>0.1061</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>0.07629999999999999</v>
+        <v>0.0713</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>46239</v>
@@ -4256,13 +4256,13 @@
         </is>
       </c>
       <c r="D43" s="15" t="n">
-        <v>82.25</v>
+        <v>83.7</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>0.0205</v>
+        <v>0.0129</v>
       </c>
       <c r="F43" s="20" t="n">
-        <v>0.0222</v>
+        <v>0.0409</v>
       </c>
       <c r="G43" s="17" t="n">
         <v>46231</v>
@@ -4291,7 +4291,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="20" t="n">
-        <v>0.09422492401215805</v>
+        <v>0.07526881720430104</v>
       </c>
       <c r="N43" s="14" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>88</v>
       </c>
       <c r="P43" s="20" t="n">
-        <v>0.06990881458966565</v>
+        <v>0.05137395459976102</v>
       </c>
       <c r="Q43" s="21" t="inlineStr">
         <is>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>56.87</v>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>-0.0275</v>
+        <v>58.21</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>0.008199999999999999</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>-0.119</v>
+        <v>-0.0857</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>46275</v>
@@ -4385,8 +4385,8 @@
       <c r="L44" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="M44" s="9" t="n">
-        <v>0.01986987867065241</v>
+      <c r="M44" s="5" t="n">
+        <v>-0.003607627555402866</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="9" t="n">
-        <v>0.3715491471777739</v>
+        <v>0.3399759491496306</v>
       </c>
       <c r="Q44" s="10" t="inlineStr">
         <is>
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="D45" s="15" t="n">
-        <v>60.52</v>
+        <v>60.66</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>-0.0198</v>
+        <v>-0.0021</v>
       </c>
       <c r="F45" s="16" t="n">
-        <v>-0.0118</v>
+        <v>-0.0277</v>
       </c>
       <c r="G45" s="17" t="n">
         <v>46231</v>
@@ -4473,7 +4473,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="20" t="n">
-        <v>0.1566424322538003</v>
+        <v>0.1539729640619849</v>
       </c>
       <c r="N45" s="14" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="20" t="n">
-        <v>0.1731658955717118</v>
+        <v>0.1704582921200133</v>
       </c>
       <c r="Q45" s="21" t="inlineStr">
         <is>
@@ -4533,13 +4533,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>49.96</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>0.0496</v>
+        <v>50.9</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>-0.0029</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>0.06709999999999999</v>
+        <v>0.08689999999999999</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>46301</v>
@@ -4604,13 +4604,13 @@
         </is>
       </c>
       <c r="D47" s="15" t="n">
-        <v>93.48999999999999</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>-0.0128</v>
+        <v>-0.0113</v>
       </c>
       <c r="F47" s="20" t="n">
-        <v>0.0694</v>
+        <v>0.083</v>
       </c>
       <c r="G47" s="17" t="n">
         <v>46240</v>
@@ -4667,11 +4667,11 @@
       <c r="D48" s="4" t="n">
         <v>72.98999999999999</v>
       </c>
-      <c r="E48" s="9" t="n">
-        <v>0.0128</v>
+      <c r="E48" s="5" t="n">
+        <v>-0.0109</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>0.0086</v>
+        <v>0.0141</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>46233</v>
@@ -4726,13 +4726,13 @@
         </is>
       </c>
       <c r="D49" s="15" t="n">
-        <v>136.64</v>
+        <v>139.69</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>-0.0396</v>
+        <v>-0.012</v>
       </c>
       <c r="F49" s="16" t="n">
-        <v>-0.0621</v>
+        <v>-0.0451</v>
       </c>
       <c r="G49" s="17" t="n">
         <v>46303</v>
@@ -4761,7 +4761,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="20" t="n">
-        <v>0.02459016393442633</v>
+        <v>0.002219199656382005</v>
       </c>
       <c r="N49" s="14" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="20" t="n">
-        <v>0.09777517564402821</v>
+        <v>0.07380628534612357</v>
       </c>
       <c r="Q49" s="21" t="inlineStr">
         <is>
@@ -4821,13 +4821,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>147.41</v>
+        <v>148.8</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>-0.0305</v>
+        <v>-0.0015</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>0.0311</v>
+        <v>0.0198</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>46232</v>
@@ -4856,7 +4856,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="9" t="n">
-        <v>0.1125432467268164</v>
+        <v>0.1021505376344085</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="9" t="n">
-        <v>0.09897564615697717</v>
+        <v>0.08870967741935476</v>
       </c>
       <c r="Q50" s="10" t="inlineStr">
         <is>
@@ -4920,13 +4920,13 @@
         </is>
       </c>
       <c r="D51" s="15" t="n">
-        <v>83.11</v>
+        <v>83.72</v>
       </c>
       <c r="E51" s="20" t="n">
-        <v>0.0313</v>
+        <v>0.0109</v>
       </c>
       <c r="F51" s="20" t="n">
-        <v>0.1034</v>
+        <v>0.1027</v>
       </c>
       <c r="G51" s="17" t="n">
         <v>46238</v>
@@ -4955,7 +4955,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="20" t="n">
-        <v>0.203224642040669</v>
+        <v>0.1944577161968467</v>
       </c>
       <c r="N51" s="14" t="inlineStr"/>
       <c r="O51" s="19" t="n"/>
@@ -4999,13 +4999,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>136.78</v>
+        <v>139.97</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>-0.0313</v>
+        <v>-0.003</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>0.09050000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>46253</v>
@@ -5034,7 +5034,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="9" t="n">
-        <v>0.02354145342886386</v>
+        <v>0.0002143316424948284</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>-0.01301359847930985</v>
+        <v>-0.03550760877330856</v>
       </c>
       <c r="Q52" s="10" t="inlineStr">
         <is>
@@ -5090,13 +5090,13 @@
         </is>
       </c>
       <c r="D53" s="15" t="n">
-        <v>109.47</v>
+        <v>111.44</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>-0.0801</v>
+        <v>-0.0367</v>
       </c>
       <c r="F53" s="16" t="n">
-        <v>-0.0767</v>
+        <v>-0.06269999999999999</v>
       </c>
       <c r="G53" s="17" t="n">
         <v>46254</v>
@@ -5125,7 +5125,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="20" t="n">
-        <v>0.2788891933863159</v>
+        <v>0.2562814070351759</v>
       </c>
       <c r="N53" s="14" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="20" t="n">
-        <v>0.2788891933863159</v>
+        <v>0.2562814070351759</v>
       </c>
       <c r="Q53" s="21" t="inlineStr">
         <is>
@@ -5185,13 +5185,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>57.25</v>
+        <v>60.72</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>0.0154</v>
+        <v>0.0736</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>-0.1421</v>
+        <v>-0.0616</v>
       </c>
       <c r="G54" s="6" t="n">
         <v>46316</v>
@@ -5227,7 +5227,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="9" t="n">
-        <v>0.3275109170305677</v>
+        <v>0.2516469038208169</v>
       </c>
       <c r="Q54" s="10" t="inlineStr">
         <is>
@@ -5268,13 +5268,13 @@
         </is>
       </c>
       <c r="D55" s="15" t="n">
-        <v>120.26</v>
+        <v>117.17</v>
       </c>
       <c r="E55" s="20" t="n">
-        <v>0.1248</v>
+        <v>0.1057</v>
       </c>
       <c r="F55" s="20" t="n">
-        <v>0.0317</v>
+        <v>0.0189</v>
       </c>
       <c r="G55" s="17" t="n">
         <v>46240</v>
@@ -5303,7 +5303,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="20" t="n">
-        <v>0.5217029768834192</v>
+        <v>0.5618332337629086</v>
       </c>
       <c r="N55" s="14" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="20" t="n">
-        <v>0.2057209379677365</v>
+        <v>0.2375181360416489</v>
       </c>
       <c r="Q55" s="21" t="inlineStr">
         <is>
@@ -5355,13 +5355,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>194.79</v>
+        <v>191.71</v>
       </c>
       <c r="E56" s="9" t="n">
-        <v>0.1361</v>
+        <v>0.1207</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>0.0546</v>
+        <v>0.0475</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>46234</v>
@@ -5390,7 +5390,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="9" t="n">
-        <v>0.1396888957338673</v>
+        <v>0.1579990610818423</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="9" t="n">
-        <v>0.1550900970275682</v>
+        <v>0.1736476970424078</v>
       </c>
       <c r="Q56" s="10" t="inlineStr">
         <is>
@@ -5446,13 +5446,13 @@
         </is>
       </c>
       <c r="D57" s="15" t="n">
-        <v>146.39</v>
+        <v>142.13</v>
       </c>
       <c r="E57" s="20" t="n">
-        <v>0.0888</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="F57" s="20" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0561</v>
       </c>
       <c r="G57" s="17" t="n">
         <v>46238</v>
@@ -5481,7 +5481,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="20" t="n">
-        <v>0.3388892683926499</v>
+        <v>0.3790192077675368</v>
       </c>
       <c r="N57" s="14" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="20" t="n">
-        <v>0.1612815082997474</v>
+        <v>0.1960880883698023</v>
       </c>
       <c r="Q57" s="21" t="inlineStr">
         <is>
@@ -5537,13 +5537,13 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>38.73</v>
+        <v>38.35</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>0.0732</v>
+        <v>0.0488</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>0.0086</v>
+        <v>0.0228</v>
       </c>
       <c r="G58" s="6" t="n">
         <v>46233</v>
@@ -5598,13 +5598,13 @@
         </is>
       </c>
       <c r="D59" s="15" t="n">
-        <v>20.36</v>
+        <v>19.98</v>
       </c>
       <c r="E59" s="20" t="n">
-        <v>0.075</v>
+        <v>0.042</v>
       </c>
       <c r="F59" s="20" t="n">
-        <v>0.0388</v>
+        <v>0.0286</v>
       </c>
       <c r="G59" s="17" t="n">
         <v>46238</v>
@@ -5659,13 +5659,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>204.68</v>
+        <v>199.47</v>
       </c>
       <c r="E60" s="9" t="n">
-        <v>0.1155</v>
+        <v>0.1087</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>0.0489</v>
+        <v>0.0275</v>
       </c>
       <c r="G60" s="6" t="n">
         <v>46237</v>
@@ -5720,13 +5720,13 @@
         </is>
       </c>
       <c r="D61" s="15" t="n">
-        <v>33.36</v>
+        <v>32.58</v>
       </c>
       <c r="E61" s="16" t="n">
-        <v>-0.0159</v>
+        <v>-0.0478</v>
       </c>
       <c r="F61" s="16" t="n">
-        <v>-0.1879</v>
+        <v>-0.1718</v>
       </c>
       <c r="G61" s="17" t="n">
         <v>46315</v>
@@ -5762,7 +5762,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="20" t="n">
-        <v>0.288968824940048</v>
+        <v>0.319828115408226</v>
       </c>
       <c r="Q61" s="21" t="inlineStr">
         <is>
@@ -5807,13 +5807,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>32.86</v>
-      </c>
-      <c r="E62" s="9" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>-0.0003</v>
+        <v>31.93</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>-0.0378</v>
+      </c>
+      <c r="F62" s="9" t="n">
+        <v>0.0008</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>46316</v>
@@ -5842,7 +5842,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="9" t="n">
-        <v>0.0651247717589775</v>
+        <v>0.0961478233636079</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="8" t="n"/>
@@ -5886,13 +5886,13 @@
         </is>
       </c>
       <c r="D63" s="15" t="n">
-        <v>206.77</v>
+        <v>207.05</v>
       </c>
       <c r="E63" s="20" t="n">
-        <v>0.2261</v>
+        <v>0.2062</v>
       </c>
       <c r="F63" s="20" t="n">
-        <v>0.1892</v>
+        <v>0.1717</v>
       </c>
       <c r="G63" s="17" t="n">
         <v>46239</v>
@@ -5947,13 +5947,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>52.42</v>
+        <v>52.32</v>
       </c>
       <c r="E64" s="9" t="n">
-        <v>0.1247</v>
+        <v>0.1132</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>-0.0959</v>
+        <v>-0.0508</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>46311</v>
@@ -5989,7 +5989,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="9" t="n">
-        <v>0.2018313620755436</v>
+        <v>0.2041284403669725</v>
       </c>
       <c r="Q64" s="10" t="inlineStr">
         <is>
@@ -6038,13 +6038,13 @@
         </is>
       </c>
       <c r="D65" s="15" t="n">
-        <v>45.13</v>
+        <v>43.6</v>
       </c>
       <c r="E65" s="20" t="n">
-        <v>0.0418</v>
+        <v>0.0243</v>
       </c>
       <c r="F65" s="16" t="n">
-        <v>-0.0101</v>
+        <v>-0.031</v>
       </c>
       <c r="G65" s="17" t="n">
         <v>46237</v>
@@ -6099,13 +6099,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>74</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>-0.0246</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>-0.0307</v>
+        <v>-0.0195</v>
       </c>
       <c r="G66" s="6" t="n">
         <v>46237</v>
@@ -6134,7 +6134,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="9" t="n">
-        <v>0.2027027027027027</v>
+        <v>0.2411100264956074</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="8" t="n"/>
@@ -6190,13 +6190,13 @@
         </is>
       </c>
       <c r="D67" s="15" t="n">
-        <v>156.94</v>
+        <v>154.65</v>
       </c>
       <c r="E67" s="20" t="n">
-        <v>0.1464</v>
+        <v>0.1326</v>
       </c>
       <c r="F67" s="20" t="n">
-        <v>0.0476</v>
+        <v>0.05230000000000001</v>
       </c>
       <c r="G67" s="17" t="n">
         <v>46234</v>
@@ -6225,7 +6225,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="20" t="n">
-        <v>0.1787944437364598</v>
+        <v>0.196249595861623</v>
       </c>
       <c r="N67" s="14" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="20" t="n">
-        <v>0.1787944437364598</v>
+        <v>0.196249595861623</v>
       </c>
       <c r="Q67" s="21" t="inlineStr">
         <is>
@@ -6281,13 +6281,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>125.6</v>
+        <v>126.23</v>
       </c>
       <c r="E68" s="9" t="n">
-        <v>0.0667</v>
+        <v>0.0506</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>0.07519999999999999</v>
+        <v>0.1207</v>
       </c>
       <c r="G68" s="6" t="n">
         <v>46240</v>
@@ -6316,7 +6316,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>-0.04458598726114645</v>
+        <v>-0.04935435316485783</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>115</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>-0.08439490445859868</v>
+        <v>-0.08896458844965542</v>
       </c>
       <c r="Q68" s="10" t="inlineStr"/>
       <c r="R68" s="8" t="n"/>
@@ -6362,13 +6362,13 @@
         </is>
       </c>
       <c r="D69" s="15" t="n">
-        <v>361.7</v>
+        <v>369.28</v>
       </c>
       <c r="E69" s="20" t="n">
-        <v>0.1113</v>
+        <v>0.1235</v>
       </c>
       <c r="F69" s="20" t="n">
-        <v>0.1328</v>
+        <v>0.1602</v>
       </c>
       <c r="G69" s="17" t="n">
         <v>46232</v>
@@ -6397,7 +6397,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="20" t="n">
-        <v>0.1224771910423003</v>
+        <v>0.09943674176776438</v>
       </c>
       <c r="N69" s="14" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="20" t="n">
-        <v>0.2054188554050318</v>
+        <v>0.1806759098786829</v>
       </c>
       <c r="Q69" s="21" t="inlineStr">
         <is>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>326.17</v>
+        <v>333.34</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>-0.0478</v>
+        <v>-0.0206</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>0.04969999999999999</v>
+        <v>0.0578</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>46311</v>
@@ -6480,7 +6480,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="9" t="n">
-        <v>0.2723426434068124</v>
+        <v>0.2449751004979901</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="9" t="n">
-        <v>0.1650366373363583</v>
+        <v>0.139977200455991</v>
       </c>
       <c r="Q70" s="10" t="inlineStr">
         <is>
@@ -6540,13 +6540,13 @@
         </is>
       </c>
       <c r="D71" s="15" t="n">
-        <v>62.05</v>
+        <v>61.91</v>
       </c>
       <c r="E71" s="20" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0696</v>
       </c>
       <c r="F71" s="20" t="n">
-        <v>0.1887</v>
+        <v>0.2194</v>
       </c>
       <c r="G71" s="17" t="n">
         <v>46309</v>
@@ -6601,13 +6601,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1055.67</v>
+        <v>1055.34</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>0.07440000000000001</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>-0.0202</v>
+        <v>0.094</v>
+      </c>
+      <c r="F72" s="9" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>46308</v>
@@ -6639,7 +6639,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="9" t="n">
-        <v>0.17934581829549</v>
+        <v>0.1797145943487408</v>
       </c>
       <c r="Q72" s="10" t="inlineStr">
         <is>
@@ -6684,13 +6684,13 @@
         </is>
       </c>
       <c r="D73" s="15" t="n">
-        <v>23.96</v>
-      </c>
-      <c r="E73" s="20" t="n">
-        <v>0.0209</v>
+        <v>22.69</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>-0.0258</v>
       </c>
       <c r="F73" s="16" t="n">
-        <v>-0.3091</v>
+        <v>-0.3666</v>
       </c>
       <c r="G73" s="17" t="n">
         <v>46281</v>
@@ -6745,13 +6745,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>15.79</v>
+        <v>17.57</v>
       </c>
       <c r="E74" s="9" t="n">
-        <v>0.1262</v>
+        <v>0.2954</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>-0.1776</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>46346</v>
@@ -6806,13 +6806,13 @@
         </is>
       </c>
       <c r="D75" s="15" t="n">
-        <v>494.93</v>
-      </c>
-      <c r="E75" s="20" t="n">
-        <v>0.0002</v>
+        <v>494.46</v>
+      </c>
+      <c r="E75" s="16" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F75" s="20" t="n">
-        <v>0.0234</v>
+        <v>0.0357</v>
       </c>
       <c r="G75" s="17" t="n">
         <v>46241</v>
@@ -6889,13 +6889,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>67.66</v>
+        <v>69.78</v>
       </c>
       <c r="E76" s="9" t="n">
-        <v>0.09480000000000001</v>
+        <v>0.0866</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>0.1872</v>
+        <v>0.2277</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>46230</v>
@@ -6923,8 +6923,8 @@
       <c r="L76" s="8" t="n">
         <v>68</v>
       </c>
-      <c r="M76" s="9" t="n">
-        <v>0.005025125628140754</v>
+      <c r="M76" s="5" t="n">
+        <v>-0.02550874175981658</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="8" t="n"/>
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="D77" s="15" t="n">
-        <v>130</v>
+        <v>130.88</v>
       </c>
       <c r="E77" s="20" t="n">
-        <v>0.1505</v>
+        <v>0.1341</v>
       </c>
       <c r="F77" s="20" t="n">
-        <v>0.1006</v>
+        <v>0.1269</v>
       </c>
       <c r="G77" s="17" t="n">
         <v>46310</v>
@@ -7031,13 +7031,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>132.19</v>
+        <v>131.2</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>-0.0794</v>
+        <v>-0.0745</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>0.042</v>
+        <v>0.05230000000000001</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>46308</v>
@@ -7069,7 +7069,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="9" t="n">
-        <v>0.05908162493380742</v>
+        <v>0.0670731707317074</v>
       </c>
       <c r="Q78" s="10" t="inlineStr">
         <is>
@@ -7118,13 +7118,13 @@
         </is>
       </c>
       <c r="D79" s="15" t="n">
-        <v>359.75</v>
+        <v>358.07</v>
       </c>
       <c r="E79" s="20" t="n">
-        <v>0.07339999999999999</v>
+        <v>0.0487</v>
       </c>
       <c r="F79" s="20" t="n">
-        <v>0.1054</v>
+        <v>0.1323</v>
       </c>
       <c r="G79" s="17" t="n">
         <v>46315</v>
@@ -7153,7 +7153,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="16" t="n">
-        <v>-0.004864489228630994</v>
+        <v>-0.0001954925014661747</v>
       </c>
       <c r="N79" s="14" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="20" t="n">
-        <v>0.03961084086170952</v>
+        <v>0.04448850783366383</v>
       </c>
       <c r="Q79" s="21" t="inlineStr">
         <is>
@@ -7209,13 +7209,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>59.09</v>
+        <v>59.08</v>
       </c>
       <c r="E80" s="9" t="n">
-        <v>0.0436</v>
+        <v>0.0222</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>0.1275</v>
+        <v>0.1358</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>46310</v>
@@ -7244,7 +7244,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>-0.0353697749196142</v>
+        <v>-0.03520649966147594</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="8" t="n"/>
@@ -7286,13 +7286,13 @@
         </is>
       </c>
       <c r="D81" s="15" t="n">
-        <v>14.52</v>
+        <v>13.92</v>
       </c>
       <c r="E81" s="16" t="n">
-        <v>-0.1054</v>
+        <v>-0.1476</v>
       </c>
       <c r="F81" s="16" t="n">
-        <v>-0.1524</v>
+        <v>-0.2326</v>
       </c>
       <c r="G81" s="17" t="n">
         <v>46240</v>
@@ -7347,13 +7347,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>370.58</v>
+        <v>379.34</v>
       </c>
       <c r="E82" s="9" t="n">
+        <v>0.1409</v>
+      </c>
+      <c r="F82" s="9" t="n">
         <v>0.0765</v>
-      </c>
-      <c r="F82" s="9" t="n">
-        <v>0.06</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>46239</v>
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="D83" s="15" t="n">
-        <v>62.36</v>
+        <v>63.74</v>
       </c>
       <c r="E83" s="16" t="n">
-        <v>-0.1214</v>
+        <v>-0.1336</v>
       </c>
       <c r="F83" s="16" t="n">
-        <v>-0.4014</v>
+        <v>-0.4111</v>
       </c>
       <c r="G83" s="17" t="n">
         <v>46239</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>48.35</v>
+        <v>49.84</v>
       </c>
       <c r="E84" s="9" t="n">
-        <v>0.0934</v>
+        <v>0.046</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>0.1299</v>
+        <v>0.1371</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>46238</v>
@@ -7542,13 +7542,13 @@
         </is>
       </c>
       <c r="D85" s="15" t="n">
-        <v>1061.23</v>
-      </c>
-      <c r="E85" s="16" t="n">
-        <v>-0.0146</v>
+        <v>1035.75</v>
+      </c>
+      <c r="E85" s="20" t="n">
+        <v>0.0158</v>
       </c>
       <c r="F85" s="20" t="n">
-        <v>0.06709999999999999</v>
+        <v>0.0272</v>
       </c>
       <c r="G85" s="17" t="n">
         <v>46308</v>
@@ -7577,7 +7577,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="20" t="n">
-        <v>0.2485512094456432</v>
+        <v>0.2792662321988897</v>
       </c>
       <c r="N85" s="14" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="20" t="n">
-        <v>0.1401863874937572</v>
+        <v>0.1682355780835144</v>
       </c>
       <c r="Q85" s="21" t="inlineStr">
         <is>
@@ -7629,13 +7629,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>140.23</v>
+        <v>141.73</v>
       </c>
       <c r="E86" s="9" t="n">
-        <v>0.0162</v>
+        <v>0.023</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-0.0701</v>
+        <v>-0.0277</v>
       </c>
       <c r="G86" s="6" t="n">
         <v>46232</v>
@@ -7690,13 +7690,13 @@
         </is>
       </c>
       <c r="D87" s="15" t="n">
-        <v>94.91</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>-0.0235</v>
+        <v>-0.0435</v>
       </c>
       <c r="F87" s="20" t="n">
-        <v>0.281</v>
+        <v>0.1127</v>
       </c>
       <c r="G87" s="17" t="n">
         <v>46232</v>
@@ -7751,13 +7751,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>109.99</v>
+        <v>102.53</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>-0.0526</v>
+        <v>-0.1666</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.0227</v>
+        <v>-0.1748</v>
       </c>
       <c r="G88" s="6" t="n">
         <v>46238</v>
@@ -7812,13 +7812,13 @@
         </is>
       </c>
       <c r="D89" s="15" t="n">
-        <v>145.79</v>
+        <v>147.75</v>
       </c>
       <c r="E89" s="20" t="n">
-        <v>0.1213</v>
+        <v>0.1929</v>
       </c>
       <c r="F89" s="16" t="n">
-        <v>-0.0322</v>
+        <v>-0.0037</v>
       </c>
       <c r="G89" s="17" t="n">
         <v>46233</v>
@@ -7873,13 +7873,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>150.58</v>
+        <v>154.48</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>0.1759</v>
+        <v>0.1443</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.134</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>46252</v>
@@ -7948,13 +7948,13 @@
         </is>
       </c>
       <c r="D91" s="15" t="n">
-        <v>353.21</v>
+        <v>352.92</v>
       </c>
       <c r="E91" s="20" t="n">
-        <v>0.0593</v>
+        <v>0.0725</v>
       </c>
       <c r="F91" s="20" t="n">
-        <v>0.1515</v>
+        <v>0.1893</v>
       </c>
       <c r="G91" s="17" t="n">
         <v>46308</v>
@@ -7983,7 +7983,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="16" t="n">
-        <v>-0.4450893236318337</v>
+        <v>-0.4446333446673467</v>
       </c>
       <c r="N91" s="14" t="inlineStr"/>
       <c r="O91" s="19" t="n"/>
@@ -8027,13 +8027,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>99.36</v>
+        <v>100.69</v>
       </c>
       <c r="E92" s="9" t="n">
-        <v>0.0858</v>
+        <v>0.1172</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>0.046</v>
+        <v>0.0708</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>46233</v>
@@ -8062,7 +8062,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="9" t="n">
-        <v>2.77415458937198</v>
+        <v>2.724302314033171</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="9" t="n">
-        <v>2.703703703703704</v>
+        <v>2.654782004171218</v>
       </c>
       <c r="Q92" s="10" t="inlineStr">
         <is>
@@ -8126,13 +8126,13 @@
         </is>
       </c>
       <c r="D93" s="15" t="n">
-        <v>349.1</v>
+        <v>361.53</v>
       </c>
       <c r="E93" s="20" t="n">
-        <v>0.1247</v>
+        <v>0.1008</v>
       </c>
       <c r="F93" s="20" t="n">
-        <v>0.1188</v>
+        <v>0.1739</v>
       </c>
       <c r="G93" s="17" t="n">
         <v>46317</v>
@@ -8164,7 +8164,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="16" t="n">
-        <v>-0.6705814952735606</v>
+        <v>-0.6819074488977401</v>
       </c>
       <c r="Q93" s="21" t="inlineStr">
         <is>
@@ -8213,13 +8213,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>539.66</v>
+        <v>551.84</v>
       </c>
       <c r="E94" s="9" t="n">
-        <v>0.0915</v>
+        <v>0.1058</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>0.0946</v>
+        <v>0.1176</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>46233</v>
@@ -8248,7 +8248,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>-0.321795204387948</v>
+        <v>-0.3367642795013048</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="8" t="n"/>
@@ -8290,13 +8290,13 @@
         </is>
       </c>
       <c r="D95" s="15" t="n">
-        <v>1994.7</v>
+        <v>2011.25</v>
       </c>
       <c r="E95" s="20" t="n">
-        <v>0.0496</v>
+        <v>0.0475</v>
       </c>
       <c r="F95" s="20" t="n">
-        <v>0.0733</v>
+        <v>0.08929999999999999</v>
       </c>
       <c r="G95" s="17" t="n">
         <v>46232</v>
@@ -8361,13 +8361,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>214.48</v>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>-0.0245</v>
+        <v>212.21</v>
+      </c>
+      <c r="E96" s="9" t="n">
+        <v>0.0008</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>0.063</v>
+        <v>0.0413</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>46309</v>
@@ -8396,7 +8396,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="9" t="n">
-        <v>2.114509511376352</v>
+        <v>2.147825267423778</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="9" t="n">
-        <v>1.564341663558374</v>
+        <v>1.591772301022572</v>
       </c>
       <c r="Q96" s="10" t="inlineStr">
         <is>
@@ -8456,13 +8456,13 @@
         </is>
       </c>
       <c r="D97" s="15" t="n">
-        <v>109.4</v>
+        <v>110.6</v>
       </c>
       <c r="E97" s="20" t="n">
-        <v>0.0253</v>
+        <v>0.0265</v>
       </c>
       <c r="F97" s="20" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="G97" s="17" t="n">
         <v>46230</v>
@@ -8491,7 +8491,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="20" t="n">
-        <v>1.193784277879342</v>
+        <v>1.16998191681736</v>
       </c>
       <c r="N97" s="14" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="20" t="n">
-        <v>1.193784277879342</v>
+        <v>1.16998191681736</v>
       </c>
       <c r="Q97" s="21" t="inlineStr">
         <is>
@@ -8551,13 +8551,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>250.99</v>
+        <v>248.43</v>
       </c>
       <c r="E98" s="9" t="n">
-        <v>0.0461</v>
+        <v>0.0141</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>0.1367</v>
+        <v>0.1304</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>46310</v>
@@ -8586,7 +8586,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>-0.5497828598748954</v>
+        <v>-0.5451435011874572</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="5" t="n">
-        <v>-0.5457986373959122</v>
+        <v>-0.5411182224369038</v>
       </c>
       <c r="Q98" s="10" t="inlineStr"/>
       <c r="R98" s="8" t="n"/>
@@ -8636,13 +8636,13 @@
         </is>
       </c>
       <c r="D99" s="15" t="n">
-        <v>22.53</v>
+        <v>21.25</v>
       </c>
       <c r="E99" s="16" t="n">
-        <v>-0.1783</v>
+        <v>-0.2562</v>
       </c>
       <c r="F99" s="16" t="n">
-        <v>-0.1361</v>
+        <v>-0.234</v>
       </c>
       <c r="G99" s="17" t="n">
         <v>46233</v>
@@ -8697,13 +8697,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>13.54</v>
+        <v>13.84</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>0.0127</v>
+        <v>0.0336</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>0.08410000000000001</v>
+        <v>0.1152</v>
       </c>
       <c r="G100" s="6" t="n">
         <v>46323</v>
@@ -8758,13 +8758,13 @@
         </is>
       </c>
       <c r="D101" s="15" t="n">
-        <v>99.22</v>
+        <v>100.18</v>
       </c>
       <c r="E101" s="20" t="n">
-        <v>0.1162</v>
+        <v>0.1482</v>
       </c>
       <c r="F101" s="20" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.1307</v>
       </c>
       <c r="G101" s="17" t="n">
         <v>46323</v>
@@ -8793,7 +8793,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="20" t="n">
-        <v>1.872404757105422</v>
+        <v>1.844879217408664</v>
       </c>
       <c r="N101" s="14" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="20" t="n">
-        <v>1.872404757105422</v>
+        <v>1.844879217408664</v>
       </c>
       <c r="Q101" s="21" t="inlineStr">
         <is>
@@ -8845,13 +8845,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>426.4</v>
+        <v>441.14</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>0.1202</v>
+        <v>0.1424</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>0.09269999999999999</v>
+        <v>0.1164</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>46231</v>
@@ -8920,13 +8920,13 @@
         </is>
       </c>
       <c r="D103" s="15" t="n">
-        <v>51.76</v>
+        <v>51.86</v>
       </c>
       <c r="E103" s="20" t="n">
-        <v>0.0396</v>
+        <v>0.0271</v>
       </c>
       <c r="F103" s="20" t="n">
-        <v>0.0633</v>
+        <v>0.0849</v>
       </c>
       <c r="G103" s="17" t="n">
         <v>46311</v>
@@ -8981,13 +8981,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>355.74</v>
+        <v>362.71</v>
       </c>
       <c r="E104" s="9" t="n">
-        <v>0.0708</v>
+        <v>0.0788</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>0.08960000000000001</v>
+        <v>0.1162</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>46231</v>
@@ -9016,7 +9016,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="9" t="n">
-        <v>0.4757969303423848</v>
+        <v>0.4474373466405669</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="9" t="n">
-        <v>0.526395682239838</v>
+        <v>0.4970637699539578</v>
       </c>
       <c r="Q104" s="10" t="inlineStr">
         <is>
@@ -9072,13 +9072,13 @@
         </is>
       </c>
       <c r="D105" s="15" t="n">
-        <v>75.45999999999999</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="E105" s="20" t="n">
-        <v>0.07719999999999999</v>
+        <v>0.0599</v>
       </c>
       <c r="F105" s="20" t="n">
-        <v>0.1207</v>
+        <v>0.1748</v>
       </c>
       <c r="G105" s="17" t="n">
         <v>46314</v>
@@ -9107,7 +9107,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="20" t="n">
-        <v>4.459846276172807</v>
+        <v>4.454064072014826</v>
       </c>
       <c r="N105" s="14" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="20" t="n">
-        <v>3.63821892393321</v>
+        <v>3.633306857294148</v>
       </c>
       <c r="Q105" s="21" t="inlineStr">
         <is>
@@ -9163,13 +9163,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>77.15000000000001</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>0.0194</v>
+        <v>0.0261</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>0.1154</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="G106" s="6" t="n">
         <v>46239</v>
@@ -9198,7 +9198,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>-0.1186001296176281</v>
+        <v>-0.1484032561051972</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="5" t="n">
-        <v>-0.1186001296176281</v>
+        <v>-0.1484032561051972</v>
       </c>
       <c r="Q106" s="10" t="inlineStr">
         <is>
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="D107" s="15" t="n">
-        <v>259.36</v>
+        <v>258.98</v>
       </c>
       <c r="E107" s="20" t="n">
-        <v>0.1042</v>
+        <v>0.0222</v>
       </c>
       <c r="F107" s="20" t="n">
-        <v>0.217</v>
+        <v>0.1846</v>
       </c>
       <c r="G107" s="17" t="n">
         <v>46234</v>
@@ -9289,7 +9289,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="20" t="n">
-        <v>0.1374151758173966</v>
+        <v>0.1390840991582361</v>
       </c>
       <c r="N107" s="14" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="16" t="n">
-        <v>-0.05151141270820486</v>
+        <v>-0.05011970036296245</v>
       </c>
       <c r="Q107" s="21" t="inlineStr">
         <is>
@@ -9337,13 +9337,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>103.06</v>
+        <v>105.62</v>
       </c>
       <c r="E108" s="9" t="n">
-        <v>0.1389</v>
+        <v>0.1222</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>0.1891</v>
+        <v>0.2239</v>
       </c>
       <c r="G108" s="6" t="n">
         <v>46316</v>
@@ -9372,7 +9372,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="9" t="n">
-        <v>0.08674558509606052</v>
+        <v>0.06040522628290092</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="9" t="n">
-        <v>0.1643702697457791</v>
+        <v>0.1361484567316796</v>
       </c>
       <c r="Q108" s="10" t="inlineStr">
         <is>
@@ -9436,13 +9436,13 @@
         </is>
       </c>
       <c r="D109" s="15" t="n">
-        <v>376.04</v>
+        <v>376.35</v>
       </c>
       <c r="E109" s="20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="F109" s="20" t="n">
-        <v>0.1194</v>
+        <v>0.1185</v>
       </c>
       <c r="G109" s="17" t="n">
         <v>46238</v>
@@ -9471,7 +9471,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="20" t="n">
-        <v>0.03712371024359105</v>
+        <v>0.03626943005181341</v>
       </c>
       <c r="N109" s="14" t="inlineStr">
         <is>
@@ -9519,13 +9519,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>156.36</v>
+        <v>160.18</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>0.0581</v>
+        <v>0.0273</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>0.0583</v>
+        <v>0.0793</v>
       </c>
       <c r="G110" s="6" t="n">
         <v>46240</v>
@@ -9554,7 +9554,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="9" t="n">
-        <v>0.02967510872345859</v>
+        <v>0.005119240854039163</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="9" t="n">
-        <v>0.1511895625479661</v>
+        <v>0.1237357972281183</v>
       </c>
       <c r="Q110" s="10" t="inlineStr">
         <is>
@@ -9606,13 +9606,13 @@
         </is>
       </c>
       <c r="D111" s="15" t="n">
-        <v>44.25</v>
-      </c>
-      <c r="E111" s="16" t="n">
-        <v>-0.004699999999999999</v>
+        <v>46.19</v>
+      </c>
+      <c r="E111" s="20" t="n">
+        <v>0.0442</v>
       </c>
       <c r="F111" s="16" t="n">
-        <v>-0.2323</v>
+        <v>-0.0596</v>
       </c>
       <c r="G111" s="17" t="n">
         <v>46232</v>
@@ -9641,7 +9641,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="20" t="n">
-        <v>0.2429378531073446</v>
+        <v>0.1907339250920113</v>
       </c>
       <c r="N111" s="14" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="20" t="n">
-        <v>0.4689265536723164</v>
+        <v>0.4072310023814679</v>
       </c>
       <c r="Q111" s="21" t="inlineStr">
         <is>
@@ -9693,13 +9693,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>309.89</v>
+        <v>312.14</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>0.1444</v>
+        <v>0.166</v>
       </c>
       <c r="G112" s="6" t="n">
         <v>46239</v>
@@ -9728,7 +9728,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="9" t="n">
-        <v>0.06812094614217953</v>
+        <v>0.06042160568975465</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0.06489399464326055</v>
+        <v>0.05721791503812396</v>
       </c>
       <c r="Q112" s="10" t="inlineStr">
         <is>
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="D113" s="15" t="n">
-        <v>107.74</v>
+        <v>106.87</v>
       </c>
       <c r="E113" s="20" t="n">
-        <v>0.0576</v>
+        <v>0.0242</v>
       </c>
       <c r="F113" s="20" t="n">
-        <v>0.1875</v>
+        <v>0.1495</v>
       </c>
       <c r="G113" s="17" t="n">
         <v>46239</v>
@@ -9823,7 +9823,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="20" t="n">
-        <v>0.1416372749211064</v>
+        <v>0.1509310377093665</v>
       </c>
       <c r="N113" s="14" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="20" t="n">
-        <v>0.2066085019491369</v>
+        <v>0.2164311780668101</v>
       </c>
       <c r="Q113" s="21" t="inlineStr">
         <is>
@@ -9875,13 +9875,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>191.5</v>
-      </c>
-      <c r="E114" s="9" t="n">
-        <v>0.0139</v>
+        <v>194.91</v>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>0.1082</v>
+        <v>0.0791</v>
       </c>
       <c r="G114" s="6" t="n">
         <v>46315</v>
@@ -9910,7 +9910,7 @@
         <v>212</v>
       </c>
       <c r="M114" s="9" t="n">
-        <v>0.1070496083550914</v>
+        <v>0.08768149402288238</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="9" t="n">
-        <v>0.07049608355091384</v>
+        <v>0.05176748242778721</v>
       </c>
       <c r="Q114" s="10" t="inlineStr">
         <is>
@@ -9966,13 +9966,13 @@
         </is>
       </c>
       <c r="D115" s="15" t="n">
-        <v>71.54000000000001</v>
+        <v>73.89</v>
       </c>
       <c r="E115" s="20" t="n">
-        <v>0.0257</v>
-      </c>
-      <c r="F115" s="16" t="n">
-        <v>-0.006500000000000001</v>
+        <v>0.0534</v>
+      </c>
+      <c r="F115" s="20" t="n">
+        <v>0.0214</v>
       </c>
       <c r="G115" s="17" t="n">
         <v>46233</v>
@@ -10001,7 +10001,7 @@
         <v>85</v>
       </c>
       <c r="M115" s="20" t="n">
-        <v>0.1881464914733015</v>
+        <v>0.1503586412234403</v>
       </c>
       <c r="N115" s="14" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="20" t="n">
-        <v>0.2580374615599663</v>
+        <v>0.218026796589525</v>
       </c>
       <c r="Q115" s="21" t="inlineStr">
         <is>
@@ -10053,13 +10053,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>129.31</v>
+        <v>131.56</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>0.0332</v>
+        <v>0.0288</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>-0.0331</v>
+        <v>-0.0342</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>46238</v>
@@ -10088,7 +10088,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="9" t="n">
-        <v>0.2760034026757405</v>
+        <v>0.254180602006689</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="8" t="n"/>
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="D117" s="15" t="n">
-        <v>544.3200000000001</v>
-      </c>
-      <c r="E117" s="16" t="n">
-        <v>-0.008800000000000001</v>
+        <v>558.55</v>
+      </c>
+      <c r="E117" s="20" t="n">
+        <v>0.0128</v>
       </c>
       <c r="F117" s="16" t="n">
-        <v>-0.0231</v>
+        <v>-0.0167</v>
       </c>
       <c r="G117" s="17" t="n">
         <v>46238</v>
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>337.5</v>
+        <v>358.92</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>-0.1601</v>
+        <v>-0.1131</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>-0.2271</v>
+        <v>-0.1528</v>
       </c>
       <c r="G118" s="6" t="n">
         <v>46315</v>
@@ -10242,7 +10242,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="9" t="n">
-        <v>0.4429629629629629</v>
+        <v>0.3568483227460157</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>375</v>
       </c>
       <c r="P118" s="9" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.04480106987629551</v>
       </c>
       <c r="Q118" s="10" t="inlineStr">
         <is>
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="D119" s="15" t="n">
-        <v>263.4</v>
+        <v>268.09</v>
       </c>
       <c r="E119" s="20" t="n">
-        <v>0.0929</v>
+        <v>0.0527</v>
       </c>
       <c r="F119" s="20" t="n">
-        <v>0.1443</v>
+        <v>0.1616</v>
       </c>
       <c r="G119" s="17" t="n">
         <v>46315</v>
@@ -10333,7 +10333,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="20" t="n">
-        <v>0.03264996203492795</v>
+        <v>0.01458465440710219</v>
       </c>
       <c r="N119" s="14" t="inlineStr"/>
       <c r="O119" s="19" t="n"/>
@@ -10385,13 +10385,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1196.03</v>
-      </c>
-      <c r="E120" s="9" t="n">
-        <v>0.07049999999999999</v>
+        <v>1196.33</v>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>-0.0098</v>
       </c>
       <c r="F120" s="9" t="n">
-        <v>0.1233</v>
+        <v>0.0617</v>
       </c>
       <c r="G120" s="6" t="n">
         <v>46239</v>
@@ -10420,7 +10420,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="9" t="n">
-        <v>0.07020726904843526</v>
+        <v>0.06993889645833513</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -10480,13 +10480,13 @@
         </is>
       </c>
       <c r="D121" s="15" t="n">
-        <v>83.20999999999999</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="E121" s="20" t="n">
-        <v>0.0384</v>
+        <v>0.0491</v>
       </c>
       <c r="F121" s="20" t="n">
-        <v>0.0723</v>
+        <v>0.1243</v>
       </c>
       <c r="G121" s="17" t="n">
         <v>46266</v>
@@ -10515,7 +10515,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="20" t="n">
-        <v>0.2258142050234348</v>
+        <v>0.2005649717514125</v>
       </c>
       <c r="N121" s="14" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="20" t="n">
-        <v>0.2618675639947123</v>
+        <v>0.2358757062146894</v>
       </c>
       <c r="Q121" s="21" t="inlineStr">
         <is>
@@ -10567,13 +10567,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>131.07</v>
+        <v>131.41</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>0.0868</v>
+        <v>0.0214</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>0.09480000000000001</v>
+        <v>0.09609999999999999</v>
       </c>
       <c r="G122" s="6" t="n">
         <v>46238</v>
@@ -10602,7 +10602,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="9" t="n">
-        <v>0.1444266422522317</v>
+        <v>0.1414656418841793</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="8" t="n"/>
@@ -10646,13 +10646,13 @@
         </is>
       </c>
       <c r="D123" s="15" t="n">
-        <v>155.01</v>
+        <v>156.42</v>
       </c>
       <c r="E123" s="20" t="n">
-        <v>0.0123</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F123" s="20" t="n">
-        <v>0.0279</v>
+        <v>0.0332</v>
       </c>
       <c r="G123" s="17" t="n">
         <v>46322</v>
@@ -10725,13 +10725,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>24.54</v>
+        <v>24.77</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>0.0208</v>
+        <v>0.0198</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>-0.0507</v>
+        <v>-0.0524</v>
       </c>
       <c r="G124" s="6" t="n">
         <v>46238</v>
@@ -10760,7 +10760,7 @@
         <v>28</v>
       </c>
       <c r="M124" s="9" t="n">
-        <v>0.1409942950285249</v>
+        <v>0.1303996770286637</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="8" t="n"/>
@@ -10804,13 +10804,13 @@
         </is>
       </c>
       <c r="D125" s="15" t="n">
-        <v>330.25</v>
+        <v>336.61</v>
       </c>
       <c r="E125" s="20" t="n">
-        <v>0.0528</v>
+        <v>0.0117</v>
       </c>
       <c r="F125" s="20" t="n">
-        <v>0.0551</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="G125" s="17" t="n">
         <v>46233</v>
@@ -10839,7 +10839,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="20" t="n">
-        <v>0.2657077971233914</v>
+        <v>0.2417931731083449</v>
       </c>
       <c r="N125" s="14" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="20" t="n">
-        <v>0.05980317940953823</v>
+        <v>0.03977897269837493</v>
       </c>
       <c r="Q125" s="21" t="inlineStr">
         <is>
@@ -10895,13 +10895,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>568.26</v>
+        <v>563</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>0.1545</v>
+        <v>0.0974</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>0.2679</v>
+        <v>0.1555</v>
       </c>
       <c r="G126" s="6" t="n">
         <v>46323</v>
@@ -10930,7 +10930,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="9" t="n">
-        <v>0.08225108225108227</v>
+        <v>0.09236234458259325</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="9" t="n">
-        <v>0.003061978671734785</v>
+        <v>0.01243339253996448</v>
       </c>
       <c r="Q126" s="10" t="inlineStr">
         <is>
@@ -10990,13 +10990,13 @@
         </is>
       </c>
       <c r="D127" s="15" t="n">
-        <v>420.74</v>
-      </c>
-      <c r="E127" s="20" t="n">
-        <v>0.0368</v>
+        <v>418.34</v>
+      </c>
+      <c r="E127" s="16" t="n">
+        <v>-0.0223</v>
       </c>
       <c r="F127" s="20" t="n">
-        <v>0.1164</v>
+        <v>0.09359999999999999</v>
       </c>
       <c r="G127" s="17" t="n">
         <v>46322</v>
@@ -11025,7 +11025,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="20" t="n">
-        <v>0.2501782573560868</v>
+        <v>0.2573504804704308</v>
       </c>
       <c r="N127" s="14" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="20" t="n">
-        <v>0.1408470789561249</v>
+        <v>0.1473920734330928</v>
       </c>
       <c r="Q127" s="21" t="inlineStr">
         <is>
@@ -11081,13 +11081,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>75.34999999999999</v>
-      </c>
-      <c r="E128" s="5" t="n">
-        <v>-0.0361</v>
+        <v>77.06</v>
+      </c>
+      <c r="E128" s="9" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>-0.0608</v>
+        <v>-0.0155</v>
       </c>
       <c r="G128" s="6" t="n">
         <v>46240</v>
@@ -11160,13 +11160,13 @@
         </is>
       </c>
       <c r="D129" s="15" t="n">
-        <v>250.09</v>
+        <v>257.33</v>
       </c>
       <c r="E129" s="20" t="n">
-        <v>0.1375</v>
+        <v>0.1511</v>
       </c>
       <c r="F129" s="20" t="n">
-        <v>0.1454</v>
+        <v>0.1704</v>
       </c>
       <c r="G129" s="17" t="n">
         <v>46232</v>
@@ -11195,7 +11195,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="16" t="n">
-        <v>-0.008356991483066109</v>
+        <v>-0.03625694633350167</v>
       </c>
       <c r="N129" s="14" t="inlineStr"/>
       <c r="O129" s="19" t="n"/>
@@ -11251,13 +11251,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>121.21</v>
+        <v>118.07</v>
       </c>
       <c r="E130" s="9" t="n">
-        <v>0.0579</v>
+        <v>0.0061</v>
       </c>
       <c r="F130" s="9" t="n">
-        <v>0.0599</v>
+        <v>0.0369</v>
       </c>
       <c r="G130" s="6" t="n">
         <v>46233</v>
@@ -11312,13 +11312,13 @@
         </is>
       </c>
       <c r="D131" s="15" t="n">
-        <v>241.97</v>
+        <v>239.1</v>
       </c>
       <c r="E131" s="20" t="n">
-        <v>0.028</v>
+        <v>0.0067</v>
       </c>
       <c r="F131" s="20" t="n">
-        <v>0.0546</v>
+        <v>0.0605</v>
       </c>
       <c r="G131" s="17" t="n">
         <v>46238</v>
@@ -11373,13 +11373,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>209.52</v>
+        <v>212.52</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>-0.0487</v>
+        <v>-0.0218</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>-0.0429</v>
+        <v>-0.0711</v>
       </c>
       <c r="G132" s="6" t="n">
         <v>46231</v>
@@ -11408,7 +11408,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="9" t="n">
-        <v>0.1932035127911416</v>
+        <v>0.1763598720120459</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="8" t="n"/>
@@ -11452,13 +11452,13 @@
         </is>
       </c>
       <c r="D133" s="15" t="n">
-        <v>148.92</v>
+        <v>153.96</v>
       </c>
       <c r="E133" s="20" t="n">
-        <v>0.063</v>
+        <v>0.1162</v>
       </c>
       <c r="F133" s="20" t="n">
-        <v>0.0134</v>
+        <v>0.0283</v>
       </c>
       <c r="G133" s="17" t="n">
         <v>46238</v>
@@ -11523,13 +11523,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>888.73</v>
+        <v>851.76</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>-0.1063</v>
+        <v>-0.1461</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>-0.0218</v>
+        <v>-0.0405</v>
       </c>
       <c r="G134" s="6" t="n">
         <v>46238</v>
@@ -11558,7 +11558,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="9" t="n">
-        <v>0.299607304805734</v>
+        <v>0.3560157790927022</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="9" t="n">
-        <v>0.2410968460612334</v>
+        <v>0.2949657180426412</v>
       </c>
       <c r="Q134" s="10" t="inlineStr">
         <is>
@@ -11610,13 +11610,13 @@
         </is>
       </c>
       <c r="D135" s="15" t="n">
-        <v>664.65</v>
+        <v>647.98</v>
       </c>
       <c r="E135" s="16" t="n">
-        <v>-0.0435</v>
+        <v>-0.0552</v>
       </c>
       <c r="F135" s="16" t="n">
-        <v>-0.0061</v>
+        <v>-0.031</v>
       </c>
       <c r="G135" s="17" t="n">
         <v>46238</v>
@@ -11645,7 +11645,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="20" t="n">
-        <v>0.3149778078688032</v>
+        <v>0.3488070619463564</v>
       </c>
       <c r="N135" s="14" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="20" t="n">
-        <v>0.2713458211088543</v>
+        <v>0.3040525942158708</v>
       </c>
       <c r="Q135" s="21" t="inlineStr">
         <is>
@@ -11705,13 +11705,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>205.91</v>
+        <v>211.2</v>
       </c>
       <c r="E136" s="9" t="n">
-        <v>0.2046</v>
+        <v>0.2286</v>
       </c>
       <c r="F136" s="9" t="n">
-        <v>0.2035</v>
+        <v>0.2204</v>
       </c>
       <c r="G136" s="6" t="n">
         <v>46288</v>
@@ -11740,7 +11740,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="9" t="n">
-        <v>0.2141226749550775</v>
+        <v>0.1837121212121213</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="8" t="n"/>
@@ -11784,13 +11784,13 @@
         </is>
       </c>
       <c r="D137" s="15" t="n">
-        <v>628.16</v>
+        <v>615.54</v>
       </c>
       <c r="E137" s="20" t="n">
-        <v>0.04559999999999999</v>
+        <v>0.0038</v>
       </c>
       <c r="F137" s="20" t="n">
-        <v>0.1872</v>
+        <v>0.142</v>
       </c>
       <c r="G137" s="17" t="n">
         <v>46254</v>
@@ -11819,7 +11819,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="20" t="n">
-        <v>0.1939633214467652</v>
+        <v>0.2184423433083147</v>
       </c>
       <c r="N137" s="14" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="20" t="n">
-        <v>0.02090231788079469</v>
+        <v>0.04183318712025214</v>
       </c>
       <c r="Q137" s="21" t="inlineStr">
         <is>
@@ -11871,13 +11871,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>147.94</v>
+        <v>147.8</v>
       </c>
       <c r="E138" s="9" t="n">
-        <v>0.046</v>
+        <v>0.03</v>
       </c>
       <c r="F138" s="9" t="n">
-        <v>0.04940000000000001</v>
+        <v>0.0424</v>
       </c>
       <c r="G138" s="6" t="n">
         <v>46238</v>
@@ -11913,7 +11913,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="9" t="n">
-        <v>0.2505069622820063</v>
+        <v>0.2516914749661704</v>
       </c>
       <c r="Q138" s="10" t="inlineStr">
         <is>
@@ -11952,13 +11952,13 @@
         </is>
       </c>
       <c r="D139" s="15" t="n">
-        <v>404.07</v>
+        <v>391.76</v>
       </c>
       <c r="E139" s="16" t="n">
-        <v>-0.0013</v>
-      </c>
-      <c r="F139" s="20" t="n">
-        <v>0.0023</v>
+        <v>-0.0271</v>
+      </c>
+      <c r="F139" s="16" t="n">
+        <v>-0.0253</v>
       </c>
       <c r="G139" s="17" t="n">
         <v>46234</v>
@@ -11994,7 +11994,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="20" t="n">
-        <v>0.1210928799465439</v>
+        <v>0.1563201960383909</v>
       </c>
       <c r="Q139" s="21" t="inlineStr">
         <is>
@@ -12035,13 +12035,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>47.02</v>
+        <v>47.32</v>
       </c>
       <c r="E140" s="9" t="n">
-        <v>0.0164</v>
+        <v>0.0046</v>
       </c>
       <c r="F140" s="9" t="n">
-        <v>0.0578</v>
+        <v>0.0571</v>
       </c>
       <c r="G140" s="6" t="n">
         <v>46309</v>
@@ -12114,13 +12114,13 @@
         </is>
       </c>
       <c r="D141" s="15" t="n">
-        <v>314.96</v>
+        <v>311.81</v>
       </c>
       <c r="E141" s="16" t="n">
-        <v>-0.0059</v>
+        <v>-0.0211</v>
       </c>
       <c r="F141" s="16" t="n">
-        <v>-0.0228</v>
+        <v>-0.0594</v>
       </c>
       <c r="G141" s="17" t="n">
         <v>46282</v>
@@ -12149,7 +12149,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="20" t="n">
-        <v>0.3493776987553976</v>
+        <v>0.363009525031269</v>
       </c>
       <c r="N141" s="14" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="20" t="n">
-        <v>0.02552705105410218</v>
+        <v>0.03588723902376446</v>
       </c>
       <c r="Q141" s="21" t="inlineStr">
         <is>
@@ -12201,13 +12201,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>230.67</v>
+        <v>232.35</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0263</v>
       </c>
       <c r="F142" s="9" t="n">
-        <v>0.0148</v>
+        <v>0.0259</v>
       </c>
       <c r="G142" s="6" t="n">
         <v>46244</v>
@@ -12236,7 +12236,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="9" t="n">
-        <v>0.2355312784497335</v>
+        <v>0.2265978050355068</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="8" t="n"/>
@@ -12284,13 +12284,13 @@
         </is>
       </c>
       <c r="D143" s="15" t="n">
-        <v>1733.6</v>
+        <v>1679.2</v>
       </c>
       <c r="E143" s="16" t="n">
-        <v>-0.113</v>
+        <v>-0.0944</v>
       </c>
       <c r="F143" s="16" t="n">
-        <v>-0.0796</v>
+        <v>-0.09480000000000001</v>
       </c>
       <c r="G143" s="17" t="n">
         <v>46317</v>
@@ -12345,13 +12345,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>52.19</v>
+        <v>50.66</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>-0.0184</v>
+        <v>-0.0556</v>
       </c>
       <c r="F144" s="9" t="n">
-        <v>0.1137</v>
+        <v>0.0786</v>
       </c>
       <c r="G144" s="6" t="n">
         <v>46241</v>
@@ -12406,13 +12406,13 @@
         </is>
       </c>
       <c r="D145" s="15" t="n">
-        <v>386.75</v>
+        <v>390.41</v>
       </c>
       <c r="E145" s="20" t="n">
-        <v>0.1232</v>
+        <v>0.126</v>
       </c>
       <c r="F145" s="20" t="n">
-        <v>0.1222</v>
+        <v>0.1188</v>
       </c>
       <c r="G145" s="17" t="n">
         <v>46232</v>
@@ -12441,7 +12441,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="20" t="n">
-        <v>0.03425985778926956</v>
+        <v>0.02456391998155778</v>
       </c>
       <c r="N145" s="14" t="inlineStr"/>
       <c r="O145" s="19" t="n"/>
@@ -12493,13 +12493,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>353.73</v>
+        <v>359.21</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>-0.0332</v>
+        <v>-0.0265</v>
       </c>
       <c r="F146" s="9" t="n">
-        <v>0.1248</v>
+        <v>0.1197</v>
       </c>
       <c r="G146" s="6" t="n">
         <v>46315</v>
@@ -12528,7 +12528,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="9" t="n">
-        <v>0.1025358324145534</v>
+        <v>0.08571587650677882</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="8" t="n"/>
@@ -12580,13 +12580,13 @@
         </is>
       </c>
       <c r="D147" s="15" t="n">
-        <v>1014.75</v>
+        <v>972.58</v>
       </c>
       <c r="E147" s="16" t="n">
-        <v>-0.0406</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="F147" s="16" t="n">
-        <v>-0.0521</v>
+        <v>-0.0235</v>
       </c>
       <c r="G147" s="17" t="n">
         <v>46316</v>
@@ -12615,7 +12615,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="20" t="n">
-        <v>0.24069967972407</v>
+        <v>0.2944950543914125</v>
       </c>
       <c r="N147" s="14" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="20" t="n">
-        <v>0.3303769401330377</v>
+        <v>0.3880606222624359</v>
       </c>
       <c r="Q147" s="21" t="inlineStr">
         <is>
@@ -12671,13 +12671,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1382.6</v>
+        <v>1383.45</v>
       </c>
       <c r="E148" s="9" t="n">
-        <v>0.0298</v>
+        <v>0.022</v>
       </c>
       <c r="F148" s="9" t="n">
-        <v>0.1068</v>
+        <v>0.1091</v>
       </c>
       <c r="G148" s="6" t="n">
         <v>46238</v>
@@ -12746,13 +12746,13 @@
         </is>
       </c>
       <c r="D149" s="15" t="n">
-        <v>243.15</v>
+        <v>243.73</v>
       </c>
       <c r="E149" s="20" t="n">
-        <v>0.0195</v>
-      </c>
-      <c r="F149" s="20" t="n">
-        <v>0.0005</v>
+        <v>0.0008</v>
+      </c>
+      <c r="F149" s="16" t="n">
+        <v>-0.0026</v>
       </c>
       <c r="G149" s="17" t="n">
         <v>46317</v>
@@ -12807,13 +12807,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>486.09</v>
+        <v>483.69</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>-0.0619</v>
+        <v>-0.0645</v>
       </c>
       <c r="F150" s="9" t="n">
-        <v>0.0168</v>
+        <v>0.0206</v>
       </c>
       <c r="G150" s="6" t="n">
         <v>46231</v>
@@ -12874,13 +12874,13 @@
         </is>
       </c>
       <c r="D151" s="15" t="n">
-        <v>283.02</v>
+        <v>284.6</v>
       </c>
       <c r="E151" s="20" t="n">
-        <v>0.0733</v>
+        <v>0.06309999999999999</v>
       </c>
       <c r="F151" s="20" t="n">
-        <v>0.1302</v>
+        <v>0.14</v>
       </c>
       <c r="G151" s="17" t="n">
         <v>46231</v>
@@ -12912,7 +12912,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="16" t="n">
-        <v>-0.03893717758462293</v>
+        <v>-0.0442726633872102</v>
       </c>
       <c r="Q151" s="21" t="inlineStr">
         <is>
@@ -12965,13 +12965,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>300.21</v>
+        <v>304.98</v>
       </c>
       <c r="E152" s="9" t="n">
-        <v>0.045</v>
+        <v>0.0471</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>-0.0423</v>
+        <v>-0.0311</v>
       </c>
       <c r="G152" s="6" t="n">
         <v>46232</v>
@@ -13036,13 +13036,13 @@
         </is>
       </c>
       <c r="D153" s="15" t="n">
-        <v>541.13</v>
+        <v>546.11</v>
       </c>
       <c r="E153" s="16" t="n">
-        <v>-0.0192</v>
+        <v>-0.0315</v>
       </c>
       <c r="F153" s="20" t="n">
-        <v>0.0767</v>
+        <v>0.09880000000000001</v>
       </c>
       <c r="G153" s="17" t="n">
         <v>46232</v>
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>582.6</v>
+        <v>583.23</v>
       </c>
       <c r="E154" s="9" t="n">
-        <v>0.185</v>
+        <v>0.1495</v>
       </c>
       <c r="F154" s="9" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="G154" s="6" t="n">
         <v>46315</v>
@@ -13164,13 +13164,13 @@
         </is>
       </c>
       <c r="D155" s="15" t="n">
-        <v>232.99</v>
+        <v>225.69</v>
       </c>
       <c r="E155" s="20" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.0315</v>
       </c>
       <c r="F155" s="20" t="n">
-        <v>0.0756</v>
+        <v>0.0219</v>
       </c>
       <c r="G155" s="17" t="n">
         <v>46232</v>
@@ -13199,7 +13199,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="20" t="n">
-        <v>1.46791707798618</v>
+        <v>1.547742478621118</v>
       </c>
       <c r="N155" s="14" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="20" t="n">
-        <v>0.01721103910039053</v>
+        <v>0.05011298684035625</v>
       </c>
       <c r="Q155" s="21" t="inlineStr">
         <is>
@@ -13259,13 +13259,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>113.55</v>
+        <v>116.52</v>
       </c>
       <c r="E156" s="9" t="n">
-        <v>0.1791</v>
+        <v>0.1664</v>
       </c>
       <c r="F156" s="9" t="n">
-        <v>0.1978</v>
+        <v>0.22</v>
       </c>
       <c r="G156" s="6" t="n">
         <v>46294</v>
@@ -13294,7 +13294,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="9" t="n">
-        <v>1.201673271686482</v>
+        <v>1.14555441125987</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="8" t="n"/>
@@ -13338,13 +13338,13 @@
         </is>
       </c>
       <c r="D157" s="15" t="n">
-        <v>132.24</v>
+        <v>131.77</v>
       </c>
       <c r="E157" s="20" t="n">
-        <v>0.13</v>
+        <v>0.0919</v>
       </c>
       <c r="F157" s="20" t="n">
-        <v>0.1806</v>
+        <v>0.1742</v>
       </c>
       <c r="G157" s="17" t="n">
         <v>46231</v>
@@ -13373,7 +13373,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="16" t="n">
-        <v>-0.2816091954022989</v>
+        <v>-0.2790468240115353</v>
       </c>
       <c r="N157" s="14" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="20" t="n">
-        <v>0.05111917725347845</v>
+        <v>0.05486833118312202</v>
       </c>
       <c r="Q157" s="21" t="inlineStr">
         <is>
@@ -13429,13 +13429,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>987.54</v>
+        <v>979.34</v>
       </c>
       <c r="E158" s="9" t="n">
-        <v>0.0275</v>
+        <v>0.0108</v>
       </c>
       <c r="F158" s="9" t="n">
-        <v>0.1377</v>
+        <v>0.1484</v>
       </c>
       <c r="G158" s="6" t="n">
         <v>46240</v>
@@ -13464,7 +13464,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="5" t="n">
-        <v>-0.8734228486947364</v>
+        <v>-0.8723630199930565</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="9" t="n">
-        <v>0.07742471191040366</v>
+        <v>0.08644597381910263</v>
       </c>
       <c r="Q158" s="10" t="inlineStr">
         <is>
@@ -13520,13 +13520,13 @@
         </is>
       </c>
       <c r="D159" s="15" t="n">
-        <v>595.0700000000001</v>
+        <v>578.98</v>
       </c>
       <c r="E159" s="16" t="n">
-        <v>-0.0687</v>
+        <v>-0.0815</v>
       </c>
       <c r="F159" s="20" t="n">
-        <v>0.0183</v>
+        <v>0.002</v>
       </c>
       <c r="G159" s="17" t="n">
         <v>46234</v>
@@ -13601,13 +13601,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>462.16</v>
-      </c>
-      <c r="E160" s="9" t="n">
-        <v>0.0039</v>
+        <v>457.36</v>
+      </c>
+      <c r="E160" s="5" t="n">
+        <v>-0.0408</v>
       </c>
       <c r="F160" s="9" t="n">
-        <v>0.0128</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="G160" s="6" t="n">
         <v>46238</v>
@@ -13662,13 +13662,13 @@
         </is>
       </c>
       <c r="D161" s="15" t="n">
-        <v>38.56</v>
+        <v>39.39</v>
       </c>
       <c r="E161" s="16" t="n">
-        <v>-0.1343</v>
+        <v>-0.0897</v>
       </c>
       <c r="F161" s="16" t="n">
-        <v>-0.2746</v>
+        <v>-0.203</v>
       </c>
       <c r="G161" s="17" t="n">
         <v>46323</v>
@@ -13737,13 +13737,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>212.79</v>
+        <v>218.95</v>
       </c>
       <c r="E162" s="9" t="n">
-        <v>0.1498</v>
+        <v>0.1647</v>
       </c>
       <c r="F162" s="9" t="n">
-        <v>0.189</v>
+        <v>0.2235</v>
       </c>
       <c r="G162" s="6" t="n">
         <v>46322</v>
@@ -13816,13 +13816,13 @@
         </is>
       </c>
       <c r="D163" s="15" t="n">
-        <v>40.15</v>
-      </c>
-      <c r="E163" s="20" t="n">
-        <v>0.0183</v>
+        <v>40.93</v>
+      </c>
+      <c r="E163" s="16" t="n">
+        <v>-0.0075</v>
       </c>
       <c r="F163" s="16" t="n">
-        <v>-0.2406</v>
+        <v>-0.1614</v>
       </c>
       <c r="G163" s="17" t="n">
         <v>46239</v>
@@ -13877,13 +13877,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>480.99</v>
+        <v>475.92</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>-0.004500000000000001</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F164" s="9" t="n">
-        <v>0.0424</v>
+        <v>0.05230000000000001</v>
       </c>
       <c r="G164" s="6" t="n">
         <v>46233</v>
@@ -13915,7 +13915,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="9" t="n">
-        <v>0.1642653693423979</v>
+        <v>0.176668347621449</v>
       </c>
       <c r="Q164" s="10" t="inlineStr">
         <is>
@@ -13968,13 +13968,13 @@
         </is>
       </c>
       <c r="D165" s="15" t="n">
-        <v>307.32</v>
+        <v>299.68</v>
       </c>
       <c r="E165" s="20" t="n">
-        <v>0.1822</v>
+        <v>0.1168</v>
       </c>
       <c r="F165" s="20" t="n">
-        <v>0.1336</v>
+        <v>0.1224</v>
       </c>
       <c r="G165" s="17" t="n">
         <v>46317</v>
@@ -14006,7 +14006,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="16" t="n">
-        <v>-0.04334244435767276</v>
+        <v>-0.01895355045381743</v>
       </c>
       <c r="Q165" s="21" t="inlineStr">
         <is>
@@ -14051,13 +14051,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>290.36</v>
+        <v>280.12</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>-0.0824</v>
+        <v>-0.0784</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>-0.1036</v>
+        <v>-0.1084</v>
       </c>
       <c r="G166" s="6" t="n">
         <v>46232</v>
@@ -14089,7 +14089,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="9" t="n">
-        <v>0.4637002341920374</v>
+        <v>0.5172069113237184</v>
       </c>
       <c r="Q166" s="10" t="inlineStr">
         <is>
@@ -14130,13 +14130,13 @@
         </is>
       </c>
       <c r="D167" s="15" t="n">
-        <v>238.75</v>
+        <v>239.52</v>
       </c>
       <c r="E167" s="20" t="n">
-        <v>0.0694</v>
+        <v>0.062</v>
       </c>
       <c r="F167" s="20" t="n">
-        <v>0.108</v>
+        <v>0.1172</v>
       </c>
       <c r="G167" s="17" t="n">
         <v>46231</v>
@@ -14165,7 +14165,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="20" t="n">
-        <v>0.1225130890052356</v>
+        <v>0.1189044756179024</v>
       </c>
       <c r="N167" s="14" t="inlineStr"/>
       <c r="O167" s="19" t="n"/>
@@ -14213,13 +14213,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>362.01</v>
+        <v>365.48</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>-0.09720000000000001</v>
-      </c>
-      <c r="F168" s="5" t="n">
-        <v>-0.0526</v>
+        <v>-0.1102</v>
+      </c>
+      <c r="F168" s="9" t="n">
+        <v>0.0002</v>
       </c>
       <c r="G168" s="6" t="n">
         <v>46232</v>
@@ -14288,13 +14288,13 @@
         </is>
       </c>
       <c r="D169" s="15" t="n">
-        <v>419</v>
+        <v>413.09</v>
       </c>
       <c r="E169" s="16" t="n">
-        <v>-0.0319</v>
+        <v>-0.0429</v>
       </c>
       <c r="F169" s="20" t="n">
-        <v>0.1599</v>
+        <v>0.1638</v>
       </c>
       <c r="G169" s="17" t="n">
         <v>46232</v>
@@ -14367,13 +14367,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>119.75</v>
+        <v>120.46</v>
       </c>
       <c r="E170" s="9" t="n">
-        <v>0.0688</v>
+        <v>0.0345</v>
       </c>
       <c r="F170" s="9" t="n">
-        <v>0.0776</v>
+        <v>0.1027</v>
       </c>
       <c r="G170" s="6" t="n">
         <v>46231</v>
@@ -14446,13 +14446,13 @@
         </is>
       </c>
       <c r="D171" s="15" t="n">
-        <v>100.15</v>
+        <v>95.86</v>
       </c>
       <c r="E171" s="16" t="n">
-        <v>-0.3186</v>
+        <v>-0.2935</v>
       </c>
       <c r="F171" s="16" t="n">
-        <v>-0.4362</v>
+        <v>-0.4328</v>
       </c>
       <c r="G171" s="17" t="n">
         <v>46240</v>
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>333.02</v>
+        <v>336.16</v>
       </c>
       <c r="E172" s="9" t="n">
-        <v>0.1363</v>
+        <v>0.1846</v>
       </c>
       <c r="F172" s="9" t="n">
-        <v>0.0801</v>
+        <v>0.0757</v>
       </c>
       <c r="G172" s="6" t="n">
         <v>46233</v>
@@ -14542,7 +14542,7 @@
         <v>310</v>
       </c>
       <c r="M172" s="5" t="n">
-        <v>-0.06912497747883005</v>
+        <v>-0.07782008567348889</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="9" t="n">
-        <v>0.09603026845234526</v>
+        <v>0.08579247977153728</v>
       </c>
       <c r="Q172" s="10" t="inlineStr">
         <is>
@@ -14610,13 +14610,13 @@
         </is>
       </c>
       <c r="D173" s="15" t="n">
-        <v>134.1</v>
+        <v>123.88</v>
       </c>
       <c r="E173" s="16" t="n">
-        <v>-0.2061</v>
+        <v>-0.2849</v>
       </c>
       <c r="F173" s="16" t="n">
-        <v>-0.1837</v>
+        <v>-0.2036</v>
       </c>
       <c r="G173" s="17" t="n">
         <v>46240</v>
@@ -14671,13 +14671,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>146.99</v>
+        <v>156.09</v>
       </c>
       <c r="E174" s="9" t="n">
-        <v>0.1381</v>
+        <v>0.2102</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>-0.1695</v>
+        <v>-0.1251</v>
       </c>
       <c r="G174" s="6" t="n">
         <v>46296</v>
@@ -14732,13 +14732,13 @@
         </is>
       </c>
       <c r="D175" s="15" t="n">
-        <v>225.11</v>
+        <v>240.07</v>
       </c>
       <c r="E175" s="20" t="n">
-        <v>0.1452</v>
+        <v>0.1842</v>
       </c>
       <c r="F175" s="16" t="n">
-        <v>-0.064</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="G175" s="17" t="n">
         <v>46275</v>
@@ -14793,13 +14793,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>371.86</v>
+        <v>366.33</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>-0.1</v>
+        <v>-0.0532</v>
       </c>
       <c r="F176" s="5" t="n">
-        <v>-0.1145</v>
+        <v>-0.1257</v>
       </c>
       <c r="G176" s="6" t="n">
         <v>46253</v>
@@ -14828,7 +14828,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="9" t="n">
-        <v>0.3849298122949497</v>
+        <v>0.4058362678459313</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="9" t="n">
-        <v>0.2746732641316624</v>
+        <v>0.29391532225043</v>
       </c>
       <c r="Q176" s="10" t="inlineStr">
         <is>
@@ -14888,13 +14888,13 @@
         </is>
       </c>
       <c r="D177" s="15" t="n">
-        <v>209.75</v>
+        <v>225.39</v>
       </c>
       <c r="E177" s="20" t="n">
-        <v>0.08900000000000001</v>
+        <v>0.1484</v>
       </c>
       <c r="F177" s="16" t="n">
-        <v>-0.1195</v>
+        <v>-0.0646</v>
       </c>
       <c r="G177" s="17" t="n">
         <v>46261</v>
@@ -14949,13 +14949,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>303.99</v>
+        <v>283.67</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>-0.1547</v>
+        <v>-0.1851</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>-0.105</v>
+        <v>-0.1054</v>
       </c>
       <c r="G178" s="6" t="n">
         <v>46237</v>
@@ -15010,13 +15010,13 @@
         </is>
       </c>
       <c r="D179" s="15" t="n">
-        <v>291.58</v>
+        <v>274.2</v>
       </c>
       <c r="E179" s="16" t="n">
-        <v>-0.2709</v>
+        <v>-0.3001</v>
       </c>
       <c r="F179" s="16" t="n">
-        <v>-0.0852</v>
+        <v>-0.2147</v>
       </c>
       <c r="G179" s="17" t="n">
         <v>46238</v>
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>46.03</v>
+        <v>45.14</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>-0.1694</v>
+        <v>-0.2202</v>
       </c>
       <c r="F180" s="5" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.1166</v>
       </c>
       <c r="G180" s="6" t="n">
         <v>46233</v>
@@ -15132,13 +15132,13 @@
         </is>
       </c>
       <c r="D181" s="15" t="n">
-        <v>536.25</v>
+        <v>503.84</v>
       </c>
       <c r="E181" s="16" t="n">
-        <v>-0.0895</v>
+        <v>-0.1962</v>
       </c>
       <c r="F181" s="20" t="n">
-        <v>0.1789</v>
+        <v>0.1204</v>
       </c>
       <c r="G181" s="17" t="n">
         <v>46247</v>
@@ -15167,7 +15167,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="20" t="n">
-        <v>0.37995337995338</v>
+        <v>0.468720228644014</v>
       </c>
       <c r="N181" s="14" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="20" t="n">
-        <v>0.3053613053613053</v>
+        <v>0.3893299460146079</v>
       </c>
       <c r="Q181" s="21" t="inlineStr">
         <is>
@@ -15219,13 +15219,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>70.28</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>-0.1343</v>
+        <v>-0.1628</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>-0.1588</v>
+        <v>-0.1913</v>
       </c>
       <c r="G182" s="6" t="n">
         <v>46268</v>
@@ -15284,13 +15284,13 @@
         </is>
       </c>
       <c r="D183" s="15" t="n">
-        <v>521.95</v>
-      </c>
-      <c r="E183" s="20" t="n">
-        <v>0.0043</v>
-      </c>
-      <c r="F183" s="20" t="n">
-        <v>0.0358</v>
+        <v>480.27</v>
+      </c>
+      <c r="E183" s="16" t="n">
+        <v>-0.07919999999999999</v>
+      </c>
+      <c r="F183" s="16" t="n">
+        <v>-0.073</v>
       </c>
       <c r="G183" s="17" t="n">
         <v>46238</v>
@@ -15319,7 +15319,7 @@
         <v>615</v>
       </c>
       <c r="M183" s="20" t="n">
-        <v>0.1782737810135069</v>
+        <v>0.2805297020426011</v>
       </c>
       <c r="N183" s="14" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="20" t="n">
-        <v>0.1093016572468626</v>
+        <v>0.2055718658254732</v>
       </c>
       <c r="Q183" s="21" t="inlineStr">
         <is>
@@ -15371,13 +15371,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>64.95999999999999</v>
+        <v>59.4</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>-0.2151</v>
+        <v>-0.2454</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>-0.1157</v>
+        <v>-0.1584</v>
       </c>
       <c r="G184" s="6" t="n">
         <v>46230</v>
@@ -15432,13 +15432,13 @@
         </is>
       </c>
       <c r="D185" s="15" t="n">
-        <v>173.99</v>
+        <v>169.27</v>
       </c>
       <c r="E185" s="20" t="n">
-        <v>0.0757</v>
+        <v>0.0741</v>
       </c>
       <c r="F185" s="20" t="n">
-        <v>0.1011</v>
+        <v>0.0902</v>
       </c>
       <c r="G185" s="17" t="n">
         <v>46238</v>
@@ -15467,7 +15467,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="20" t="n">
-        <v>0.1494913500775906</v>
+        <v>0.1815442783718319</v>
       </c>
       <c r="N185" s="14" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="20" t="n">
-        <v>0.1494913500775906</v>
+        <v>0.1815442783718319</v>
       </c>
       <c r="Q185" s="21" t="inlineStr">
         <is>
@@ -15523,13 +15523,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>152.67</v>
+        <v>147.98</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>-0.0621</v>
+        <v>-0.09609999999999999</v>
       </c>
       <c r="F186" s="9" t="n">
-        <v>0.09390000000000001</v>
+        <v>0.002</v>
       </c>
       <c r="G186" s="6" t="n">
         <v>46232</v>
@@ -15561,7 +15561,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="9" t="n">
-        <v>0.1790135586559246</v>
+        <v>0.2163805919718882</v>
       </c>
       <c r="Q186" s="10" t="inlineStr">
         <is>
@@ -15614,13 +15614,13 @@
         </is>
       </c>
       <c r="D187" s="15" t="n">
-        <v>27.19</v>
+        <v>26.2</v>
       </c>
       <c r="E187" s="16" t="n">
-        <v>-0.3522999999999999</v>
+        <v>-0.3308</v>
       </c>
       <c r="F187" s="16" t="n">
-        <v>-0.3977000000000001</v>
+        <v>-0.4722</v>
       </c>
       <c r="G187" s="17" t="n">
         <v>46230</v>
@@ -15675,13 +15675,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>260.01</v>
+        <v>259.14</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>-0.2759</v>
+        <v>-0.2248</v>
       </c>
       <c r="F188" s="5" t="n">
-        <v>-0.1906</v>
+        <v>-0.2271</v>
       </c>
       <c r="G188" s="6" t="n">
         <v>46232</v>
@@ -15736,13 +15736,13 @@
         </is>
       </c>
       <c r="D189" s="15" t="n">
-        <v>1757.09</v>
+        <v>1631.84</v>
       </c>
       <c r="E189" s="16" t="n">
-        <v>-0.0032</v>
+        <v>-0.0907</v>
       </c>
       <c r="F189" s="20" t="n">
-        <v>0.0766</v>
+        <v>0.0162</v>
       </c>
       <c r="G189" s="17" t="n">
         <v>46309</v>
@@ -15815,13 +15815,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>36.84</v>
+        <v>35.48</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>-0.1089</v>
+        <v>-0.1176</v>
       </c>
       <c r="F190" s="5" t="n">
-        <v>-0.0542</v>
+        <v>-0.1261</v>
       </c>
       <c r="G190" s="6" t="n">
         <v>46233</v>
@@ -15876,13 +15876,13 @@
         </is>
       </c>
       <c r="D191" s="15" t="n">
-        <v>381.92</v>
-      </c>
-      <c r="E191" s="16" t="n">
-        <v>-0.0004</v>
+        <v>379.2</v>
+      </c>
+      <c r="E191" s="20" t="n">
+        <v>0.0389</v>
       </c>
       <c r="F191" s="16" t="n">
-        <v>-0.095</v>
+        <v>-0.1111</v>
       </c>
       <c r="G191" s="17" t="n">
         <v>46268</v>
@@ -15911,7 +15911,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="20" t="n">
-        <v>0.4270004189359027</v>
+        <v>0.4372362869198312</v>
       </c>
       <c r="N191" s="14" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="20" t="n">
-        <v>0.5238793464599916</v>
+        <v>0.5348101265822786</v>
       </c>
       <c r="Q191" s="21" t="inlineStr">
         <is>
@@ -15975,13 +15975,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>147.79</v>
+        <v>147.22</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>-0.1145</v>
+        <v>-0.0423</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>-0.1542</v>
+        <v>-0.1577</v>
       </c>
       <c r="G192" s="6" t="n">
         <v>46244</v>
@@ -16036,13 +16036,13 @@
         </is>
       </c>
       <c r="D193" s="15" t="n">
-        <v>326.24</v>
+        <v>339.79</v>
       </c>
       <c r="E193" s="16" t="n">
-        <v>-0.124</v>
+        <v>-0.0993</v>
       </c>
       <c r="F193" s="16" t="n">
-        <v>-0.1454</v>
+        <v>-0.0911</v>
       </c>
       <c r="G193" s="17" t="n">
         <v>46230</v>
@@ -16071,7 +16071,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="20" t="n">
-        <v>0.3027219225110348</v>
+        <v>0.2507725359781041</v>
       </c>
       <c r="N193" s="14" t="inlineStr"/>
       <c r="O193" s="19" t="n"/>
@@ -16115,13 +16115,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>130.57</v>
+        <v>133.68</v>
       </c>
       <c r="E194" s="9" t="n">
-        <v>0.0472</v>
-      </c>
-      <c r="F194" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0279</v>
+      </c>
+      <c r="F194" s="9" t="n">
+        <v>0.0179</v>
       </c>
       <c r="G194" s="6" t="n">
         <v>46233</v>
@@ -16176,13 +16176,13 @@
         </is>
       </c>
       <c r="D195" s="15" t="n">
-        <v>390.96</v>
+        <v>368.39</v>
       </c>
       <c r="E195" s="16" t="n">
-        <v>-0.1565</v>
+        <v>-0.2317</v>
       </c>
       <c r="F195" s="16" t="n">
-        <v>-0.351</v>
+        <v>-0.3539</v>
       </c>
       <c r="G195" s="17" t="n">
         <v>46268</v>
@@ -16237,13 +16237,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>14.22</v>
+        <v>14.79</v>
       </c>
       <c r="E196" s="9" t="n">
-        <v>0.1202</v>
+        <v>0.07490000000000001</v>
       </c>
       <c r="F196" s="9" t="n">
-        <v>0.1028</v>
+        <v>0.1205</v>
       </c>
       <c r="G196" s="6" t="n">
         <v>46247</v>
@@ -16298,13 +16298,13 @@
         </is>
       </c>
       <c r="D197" s="15" t="n">
-        <v>305.28</v>
+        <v>303.1</v>
       </c>
       <c r="E197" s="16" t="n">
-        <v>-0.1572</v>
+        <v>-0.102</v>
       </c>
       <c r="F197" s="16" t="n">
-        <v>-0.1768</v>
+        <v>-0.1365</v>
       </c>
       <c r="G197" s="17" t="n">
         <v>46230</v>
@@ -16359,13 +16359,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>282.39</v>
+        <v>259.24</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>-0.2805</v>
+        <v>-0.3188</v>
       </c>
       <c r="F198" s="5" t="n">
-        <v>-0.2595</v>
+        <v>-0.3123</v>
       </c>
       <c r="G198" s="6" t="n">
         <v>46246</v>
@@ -16420,13 +16420,13 @@
         </is>
       </c>
       <c r="D199" s="15" t="n">
-        <v>50.7</v>
+        <v>46.64</v>
       </c>
       <c r="E199" s="16" t="n">
-        <v>-0.2036</v>
-      </c>
-      <c r="F199" s="20" t="n">
-        <v>0.0154</v>
+        <v>-0.2722</v>
+      </c>
+      <c r="F199" s="16" t="n">
+        <v>-0.1371</v>
       </c>
       <c r="G199" s="17" t="n">
         <v>46233</v>
@@ -16481,13 +16481,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>22.75</v>
+        <v>20.58</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>-0.1814</v>
+        <v>-0.2434</v>
       </c>
       <c r="F200" s="5" t="n">
-        <v>-0.1373</v>
+        <v>-0.2586</v>
       </c>
       <c r="G200" s="6" t="n">
         <v>46248</v>
@@ -16542,13 +16542,13 @@
         </is>
       </c>
       <c r="D201" s="15" t="n">
-        <v>213.15</v>
+        <v>202.8</v>
       </c>
       <c r="E201" s="16" t="n">
-        <v>-0.2076</v>
+        <v>-0.1479</v>
       </c>
       <c r="F201" s="16" t="n">
-        <v>-0.0383</v>
+        <v>-0.08789999999999999</v>
       </c>
       <c r="G201" s="17" t="n">
         <v>46267</v>
@@ -16603,13 +16603,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>163.66</v>
+        <v>175.51</v>
       </c>
       <c r="E202" s="9" t="n">
-        <v>0.07139999999999999</v>
+        <v>0.1082</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>-0.0861</v>
+        <v>-0.0038</v>
       </c>
       <c r="G202" s="6" t="n">
         <v>46267</v>
@@ -16638,7 +16638,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="9" t="n">
-        <v>0.2220457045093487</v>
+        <v>0.1395362087630335</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="9" t="n">
-        <v>0.5275571306366859</v>
+        <v>0.4244202609537919</v>
       </c>
       <c r="Q202" s="10" t="inlineStr">
         <is>
@@ -16694,13 +16694,13 @@
         </is>
       </c>
       <c r="D203" s="15" t="n">
-        <v>183.28</v>
+        <v>181.6</v>
       </c>
       <c r="E203" s="20" t="n">
-        <v>0.08929999999999999</v>
+        <v>0.0361</v>
       </c>
       <c r="F203" s="20" t="n">
-        <v>0.0917</v>
+        <v>0.08259999999999999</v>
       </c>
       <c r="G203" s="17" t="n">
         <v>46260</v>
@@ -16729,7 +16729,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="16" t="n">
-        <v>-0.01107594936708861</v>
+        <v>-0.001927312775330365</v>
       </c>
       <c r="N203" s="14" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="16" t="n">
-        <v>-0.03153644696639023</v>
+        <v>-0.02257709251101319</v>
       </c>
       <c r="Q203" s="21" t="inlineStr">
         <is>
@@ -16781,13 +16781,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>71.88</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>-0.2875</v>
+        <v>-0.2716</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>-0.3212</v>
+        <v>-0.3417</v>
       </c>
       <c r="G204" s="6" t="n">
         <v>46245</v>
@@ -16842,13 +16842,13 @@
         </is>
       </c>
       <c r="D205" s="15" t="n">
-        <v>114.17</v>
-      </c>
-      <c r="E205" s="16" t="n">
-        <v>-0.0464</v>
+        <v>113.82</v>
+      </c>
+      <c r="E205" s="20" t="n">
+        <v>0.0004</v>
       </c>
       <c r="F205" s="16" t="n">
-        <v>-0.0352</v>
+        <v>-0.0406</v>
       </c>
       <c r="G205" s="17" t="n">
         <v>46246</v>
@@ -16877,7 +16877,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="20" t="n">
-        <v>0.1386528860471227</v>
+        <v>0.1421542786856441</v>
       </c>
       <c r="N205" s="14" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="20" t="n">
-        <v>0.3138302531312954</v>
+        <v>0.3178703215603585</v>
       </c>
       <c r="Q205" s="21" t="inlineStr">
         <is>
@@ -16945,13 +16945,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>246.86</v>
+        <v>254.02</v>
       </c>
       <c r="E206" s="9" t="n">
-        <v>0.1087</v>
+        <v>0.0594</v>
       </c>
       <c r="F206" s="9" t="n">
-        <v>0.1038</v>
+        <v>0.1278</v>
       </c>
       <c r="G206" s="6" t="n">
         <v>46240</v>
@@ -17006,13 +17006,13 @@
         </is>
       </c>
       <c r="D207" s="15" t="n">
-        <v>437.5</v>
+        <v>422.74</v>
       </c>
       <c r="E207" s="20" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0582</v>
       </c>
       <c r="F207" s="20" t="n">
-        <v>0.4341</v>
+        <v>0.3334</v>
       </c>
       <c r="G207" s="17" t="n">
         <v>46261</v>
@@ -17067,13 +17067,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>50.44</v>
+        <v>54</v>
       </c>
       <c r="E208" s="9" t="n">
-        <v>0.1401</v>
+        <v>0.1944</v>
       </c>
       <c r="F208" s="9" t="n">
-        <v>0.0227</v>
+        <v>0.0891</v>
       </c>
       <c r="G208" s="6" t="n">
         <v>46268</v>
@@ -17128,13 +17128,13 @@
         </is>
       </c>
       <c r="D209" s="15" t="n">
-        <v>41.62</v>
+        <v>43.79</v>
       </c>
       <c r="E209" s="20" t="n">
-        <v>0.0249</v>
+        <v>0.0097</v>
       </c>
       <c r="F209" s="20" t="n">
-        <v>0.0251</v>
+        <v>0.081</v>
       </c>
       <c r="G209" s="17" t="n">
         <v>46239</v>
@@ -17189,13 +17189,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>476.04</v>
+        <v>461.54</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>-0.1622</v>
+        <v>-0.1205</v>
       </c>
       <c r="F210" s="5" t="n">
-        <v>-0.3007</v>
+        <v>-0.309</v>
       </c>
       <c r="G210" s="6" t="n">
         <v>46251</v>
@@ -17250,13 +17250,13 @@
         </is>
       </c>
       <c r="D211" s="15" t="n">
-        <v>104.04</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="E211" s="16" t="n">
-        <v>-0.2643</v>
+        <v>-0.2681</v>
       </c>
       <c r="F211" s="16" t="n">
-        <v>-0.2377</v>
+        <v>-0.2652</v>
       </c>
       <c r="G211" s="17" t="n">
         <v>46232</v>
@@ -17311,13 +17311,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>152.37</v>
+        <v>152.43</v>
       </c>
       <c r="E212" s="9" t="n">
-        <v>0.0488</v>
+        <v>0.0072</v>
       </c>
       <c r="F212" s="9" t="n">
-        <v>0.1374</v>
+        <v>0.1753</v>
       </c>
       <c r="G212" s="6" t="n">
         <v>46232</v>
@@ -17372,13 +17372,13 @@
         </is>
       </c>
       <c r="D213" s="15" t="n">
-        <v>53.53</v>
+        <v>51.71</v>
       </c>
       <c r="E213" s="16" t="n">
-        <v>-0.3605</v>
+        <v>-0.3518</v>
       </c>
       <c r="F213" s="16" t="n">
-        <v>-0.405</v>
+        <v>-0.3587</v>
       </c>
       <c r="G213" s="17" t="n">
         <v>46239</v>
@@ -17433,13 +17433,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>146.65</v>
+        <v>139.47</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>-0.2875</v>
+        <v>-0.3691</v>
       </c>
       <c r="F214" s="5" t="n">
-        <v>-0.2524</v>
+        <v>-0.2377</v>
       </c>
       <c r="G214" s="6" t="n">
         <v>46231</v>
@@ -17494,13 +17494,13 @@
         </is>
       </c>
       <c r="D215" s="15" t="n">
-        <v>31.28</v>
+        <v>33.22</v>
       </c>
       <c r="E215" s="20" t="n">
-        <v>0.1065</v>
+        <v>0.1428</v>
       </c>
       <c r="F215" s="20" t="n">
-        <v>0.1685</v>
+        <v>0.1894</v>
       </c>
       <c r="G215" s="17" t="n">
         <v>46267</v>
@@ -17555,13 +17555,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>138.23</v>
+        <v>151.16</v>
       </c>
       <c r="E216" s="9" t="n">
-        <v>0.2529</v>
+        <v>0.2443</v>
       </c>
       <c r="F216" s="9" t="n">
-        <v>0.0063</v>
+        <v>0.0636</v>
       </c>
       <c r="G216" s="6" t="n">
         <v>46268</v>
@@ -17590,7 +17590,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="9" t="n">
-        <v>0.3745207263256892</v>
+        <v>0.2569462820852078</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="8" t="n"/>
@@ -17634,13 +17634,13 @@
         </is>
       </c>
       <c r="D217" s="15" t="n">
-        <v>47.69</v>
-      </c>
-      <c r="E217" s="16" t="n">
-        <v>-0.0217</v>
+        <v>47.1</v>
+      </c>
+      <c r="E217" s="20" t="n">
+        <v>0.0776</v>
       </c>
       <c r="F217" s="20" t="n">
-        <v>0.253</v>
+        <v>0.2327</v>
       </c>
       <c r="G217" s="17" t="n">
         <v>46267</v>
@@ -17669,7 +17669,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="20" t="n">
-        <v>0.4049066890333404</v>
+        <v>0.4225053078556263</v>
       </c>
       <c r="N217" s="14" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="20" t="n">
-        <v>0.4678129586915497</v>
+        <v>0.4861995753715498</v>
       </c>
       <c r="Q217" s="21" t="inlineStr">
         <is>
@@ -17721,13 +17721,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>204.89</v>
+        <v>226.68</v>
       </c>
       <c r="E218" s="9" t="n">
-        <v>0.1337</v>
+        <v>0.2222</v>
       </c>
       <c r="F218" s="9" t="n">
-        <v>0.0349</v>
+        <v>0.1402</v>
       </c>
       <c r="G218" s="6" t="n">
         <v>46239</v>
@@ -17782,13 +17782,13 @@
         </is>
       </c>
       <c r="D219" s="15" t="n">
-        <v>214.19</v>
+        <v>217.3</v>
       </c>
       <c r="E219" s="16" t="n">
-        <v>-0.1855</v>
+        <v>-0.2</v>
       </c>
       <c r="F219" s="16" t="n">
-        <v>-0.1456</v>
+        <v>-0.1776</v>
       </c>
       <c r="G219" s="17" t="n">
         <v>46316</v>
@@ -17824,7 +17824,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="20" t="n">
-        <v>0.1671880106447547</v>
+        <v>0.1504832029452369</v>
       </c>
       <c r="Q219" s="21" t="inlineStr">
         <is>
@@ -17861,13 +17861,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>8.970000000000001</v>
+        <v>9.52</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>-0.3638</v>
+        <v>-0.3012</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>-0.4351</v>
+        <v>-0.464</v>
       </c>
       <c r="G220" s="6" t="n">
         <v>46247</v>
@@ -17922,13 +17922,13 @@
         </is>
       </c>
       <c r="D221" s="15" t="n">
-        <v>92.31999999999999</v>
+        <v>89.77</v>
       </c>
       <c r="E221" s="16" t="n">
-        <v>-0.2987</v>
+        <v>-0.3004</v>
       </c>
       <c r="F221" s="16" t="n">
-        <v>-0.2526</v>
+        <v>-0.2574</v>
       </c>
       <c r="G221" s="17" t="n">
         <v>46317</v>
@@ -17983,13 +17983,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>296.33</v>
+        <v>307.8</v>
       </c>
       <c r="E222" s="9" t="n">
-        <v>0.13</v>
+        <v>0.1497</v>
       </c>
       <c r="F222" s="5" t="n">
-        <v>-0.0264</v>
+        <v>-0.0166</v>
       </c>
       <c r="G222" s="6" t="n">
         <v>46254</v>
@@ -18044,13 +18044,13 @@
         </is>
       </c>
       <c r="D223" s="15" t="n">
-        <v>32.84</v>
+        <v>34.92</v>
       </c>
       <c r="E223" s="16" t="n">
-        <v>-0.3873</v>
+        <v>-0.2919</v>
       </c>
       <c r="F223" s="16" t="n">
-        <v>-0.4838</v>
+        <v>-0.5022</v>
       </c>
       <c r="G223" s="17" t="n">
         <v>46239</v>
@@ -18105,13 +18105,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>37.07</v>
+        <v>35.81</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>-0.263</v>
+        <v>-0.2415</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>-0.3799</v>
+        <v>-0.4409</v>
       </c>
       <c r="G224" s="6" t="n">
         <v>46261</v>
@@ -18166,13 +18166,13 @@
         </is>
       </c>
       <c r="D225" s="15" t="n">
-        <v>312.59</v>
+        <v>303.85</v>
       </c>
       <c r="E225" s="16" t="n">
-        <v>-0.1593</v>
+        <v>-0.1527</v>
       </c>
       <c r="F225" s="16" t="n">
-        <v>-0.1779</v>
+        <v>-0.1644</v>
       </c>
       <c r="G225" s="17" t="n">
         <v>46289</v>
@@ -18231,13 +18231,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>318.67</v>
+        <v>308.84</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>-0.0929</v>
+        <v>-0.0603</v>
       </c>
       <c r="F226" s="5" t="n">
-        <v>-0.1042</v>
+        <v>-0.08929999999999999</v>
       </c>
       <c r="G226" s="6" t="n">
         <v>46252</v>
@@ -18266,7 +18266,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="9" t="n">
-        <v>0.2238365707471679</v>
+        <v>0.262789794068126</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="8" t="n"/>
@@ -18322,13 +18322,13 @@
         </is>
       </c>
       <c r="D227" s="15" t="n">
-        <v>210.52</v>
+        <v>198.43</v>
       </c>
       <c r="E227" s="16" t="n">
-        <v>-0.1246</v>
+        <v>-0.2019</v>
       </c>
       <c r="F227" s="20" t="n">
-        <v>0.0466</v>
+        <v>0.0294</v>
       </c>
       <c r="G227" s="17" t="n">
         <v>46231</v>
@@ -18357,7 +18357,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="20" t="n">
-        <v>0.4487934638039141</v>
+        <v>0.5370659678476036</v>
       </c>
       <c r="N227" s="14" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="16" t="n">
-        <v>-0.1212236367091013</v>
+        <v>-0.0676812981907978</v>
       </c>
       <c r="Q227" s="21" t="inlineStr">
         <is>
@@ -18409,13 +18409,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>101.33</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>-0.178</v>
+        <v>-0.2381</v>
       </c>
       <c r="F228" s="5" t="n">
-        <v>-0.0667</v>
+        <v>-0.0892</v>
       </c>
       <c r="G228" s="6" t="n">
         <v>46239</v>
@@ -18470,13 +18470,13 @@
         </is>
       </c>
       <c r="D229" s="15" t="n">
-        <v>762.99</v>
+        <v>703.8</v>
       </c>
       <c r="E229" s="16" t="n">
-        <v>-0.0944</v>
+        <v>-0.1385</v>
       </c>
       <c r="F229" s="16" t="n">
-        <v>-0.1623</v>
+        <v>-0.1822</v>
       </c>
       <c r="G229" s="17" t="n">
         <v>46245</v>
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>105.78</v>
+        <v>106.96</v>
       </c>
       <c r="E230" s="9" t="n">
-        <v>0.0333</v>
+        <v>0.09849999999999999</v>
       </c>
       <c r="F230" s="5" t="n">
-        <v>-0.0501</v>
+        <v>-0.0429</v>
       </c>
       <c r="G230" s="6" t="n">
         <v>46231</v>
@@ -18592,13 +18592,13 @@
         </is>
       </c>
       <c r="D231" s="15" t="n">
-        <v>305.21</v>
+        <v>282.52</v>
       </c>
       <c r="E231" s="16" t="n">
-        <v>-0.1857</v>
+        <v>-0.2547</v>
       </c>
       <c r="F231" s="16" t="n">
-        <v>-0.0541</v>
+        <v>-0.1116</v>
       </c>
       <c r="G231" s="17" t="n">
         <v>46232</v>
@@ -18627,7 +18627,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="20" t="n">
-        <v>0.474394679073425</v>
+        <v>0.5928075888432678</v>
       </c>
       <c r="N231" s="14" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="20" t="n">
-        <v>0.1631335801579241</v>
+        <v>0.2565482089763557</v>
       </c>
       <c r="Q231" s="21" t="inlineStr">
         <is>
@@ -18683,13 +18683,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>78.86</v>
+        <v>76.8</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>-0.1473</v>
+        <v>-0.1266</v>
       </c>
       <c r="F232" s="5" t="n">
-        <v>-0.1957</v>
+        <v>-0.2003</v>
       </c>
       <c r="G232" s="6" t="n">
         <v>46240</v>
@@ -18744,13 +18744,13 @@
         </is>
       </c>
       <c r="D233" s="15" t="n">
-        <v>298.22</v>
+        <v>312.17</v>
       </c>
       <c r="E233" s="16" t="n">
-        <v>-0.014</v>
+        <v>-0.0059</v>
       </c>
       <c r="F233" s="16" t="n">
-        <v>-0.0297</v>
+        <v>-0.0415</v>
       </c>
       <c r="G233" s="17" t="n">
         <v>46259</v>
@@ -18805,13 +18805,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>329.18</v>
+        <v>303.67</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>-0.1374</v>
+        <v>-0.2186</v>
       </c>
       <c r="F234" s="5" t="n">
-        <v>-0.0148</v>
+        <v>-0.061</v>
       </c>
       <c r="G234" s="6" t="n">
         <v>46239</v>
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="D235" s="15" t="n">
-        <v>1333.81</v>
+        <v>1309.51</v>
       </c>
       <c r="E235" s="16" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0029</v>
       </c>
       <c r="F235" s="16" t="n">
-        <v>-0.1979</v>
+        <v>-0.1982</v>
       </c>
       <c r="G235" s="17" t="n">
         <v>46233</v>
@@ -18927,13 +18927,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>194.23</v>
+        <v>186.15</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>-0.298</v>
+        <v>-0.3022</v>
       </c>
       <c r="F236" s="5" t="n">
-        <v>-0.0674</v>
+        <v>-0.09119999999999999</v>
       </c>
       <c r="G236" s="6" t="n">
         <v>46261</v>
@@ -18962,7 +18962,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="9" t="n">
-        <v>0.2356484580136952</v>
+        <v>0.2892828364222401</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="9" t="n">
-        <v>0.2922823456726562</v>
+        <v>0.3483749664249261</v>
       </c>
       <c r="Q236" s="10" t="inlineStr">
         <is>
@@ -19014,13 +19014,13 @@
         </is>
       </c>
       <c r="D237" s="15" t="n">
-        <v>381.7</v>
+        <v>392.12</v>
       </c>
       <c r="E237" s="20" t="n">
-        <v>0.0444</v>
+        <v>0.0513</v>
       </c>
       <c r="F237" s="16" t="n">
-        <v>-0.0825</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="G237" s="17" t="n">
         <v>46232</v>
@@ -19049,7 +19049,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="20" t="n">
-        <v>0.6374115797746922</v>
+        <v>0.5938998265836989</v>
       </c>
       <c r="N237" s="14" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="20" t="n">
-        <v>0.3754257270107415</v>
+        <v>0.338875854330307</v>
       </c>
       <c r="Q237" s="21" t="inlineStr">
         <is>
@@ -19113,13 +19113,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>417.83</v>
+        <v>424.64</v>
       </c>
       <c r="E238" s="9" t="n">
-        <v>0.043</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="F238" s="9" t="n">
-        <v>0.0179</v>
+        <v>0.0318</v>
       </c>
       <c r="G238" s="6" t="n">
         <v>46239</v>
@@ -19151,7 +19151,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="9" t="n">
-        <v>0.2564918746858771</v>
+        <v>0.2363413715146948</v>
       </c>
       <c r="Q238" s="10" t="inlineStr">
         <is>
@@ -19200,13 +19200,13 @@
         </is>
       </c>
       <c r="D239" s="15" t="n">
-        <v>91.67</v>
-      </c>
-      <c r="E239" s="16" t="n">
-        <v>-0.0261</v>
+        <v>97.90000000000001</v>
+      </c>
+      <c r="E239" s="20" t="n">
+        <v>0.1894</v>
       </c>
       <c r="F239" s="16" t="n">
-        <v>-0.4268</v>
+        <v>-0.3544</v>
       </c>
       <c r="G239" s="17" t="n">
         <v>46233</v>
@@ -19261,13 +19261,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>266.99</v>
+        <v>257.04</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>-0.2844</v>
+        <v>-0.3038</v>
       </c>
       <c r="F240" s="5" t="n">
-        <v>-0.3483</v>
+        <v>-0.3428</v>
       </c>
       <c r="G240" s="6" t="n">
         <v>46240</v>
@@ -19322,13 +19322,13 @@
         </is>
       </c>
       <c r="D241" s="15" t="n">
-        <v>920.95</v>
+        <v>869.47</v>
       </c>
       <c r="E241" s="16" t="n">
-        <v>-0.1217</v>
-      </c>
-      <c r="F241" s="20" t="n">
-        <v>0.028</v>
+        <v>-0.2321</v>
+      </c>
+      <c r="F241" s="16" t="n">
+        <v>-0.0585</v>
       </c>
       <c r="G241" s="17" t="n">
         <v>46294</v>
@@ -19357,7 +19357,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="20" t="n">
-        <v>0.6558988001520168</v>
+        <v>0.7539420566552036</v>
       </c>
       <c r="N241" s="14" t="inlineStr">
         <is>
@@ -19405,13 +19405,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>187.77</v>
+        <v>185.71</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>-0.2769</v>
+        <v>-0.2272</v>
       </c>
       <c r="F242" s="5" t="n">
-        <v>-0.0975</v>
+        <v>-0.1795</v>
       </c>
       <c r="G242" s="6" t="n">
         <v>46240</v>
@@ -19466,13 +19466,13 @@
         </is>
       </c>
       <c r="D243" s="15" t="n">
-        <v>262.15</v>
+        <v>265.52</v>
       </c>
       <c r="E243" s="20" t="n">
-        <v>0.173</v>
+        <v>0.1192</v>
       </c>
       <c r="F243" s="20" t="n">
-        <v>0.2051</v>
+        <v>0.164</v>
       </c>
       <c r="G243" s="17" t="n">
         <v>46240</v>
@@ -19527,13 +19527,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>98.78</v>
+        <v>106.97</v>
       </c>
       <c r="E244" s="9" t="n">
-        <v>0.05309999999999999</v>
+        <v>0.08779999999999999</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0161</v>
       </c>
       <c r="G244" s="6" t="n">
         <v>46323</v>
@@ -19562,7 +19562,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="9" t="n">
-        <v>0.6197610852399271</v>
+        <v>0.49574647097317</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="9" t="n">
-        <v>0.5185260174124317</v>
+        <v>0.402262316537347</v>
       </c>
       <c r="Q244" s="10" t="inlineStr">
         <is>
@@ -19618,13 +19618,13 @@
         </is>
       </c>
       <c r="D245" s="15" t="n">
-        <v>55.04</v>
+        <v>57.28</v>
       </c>
       <c r="E245" s="20" t="n">
-        <v>0.1587</v>
+        <v>0.152</v>
       </c>
       <c r="F245" s="20" t="n">
-        <v>0.1824</v>
+        <v>0.1734</v>
       </c>
       <c r="G245" s="17" t="n">
         <v>46260</v>
@@ -19679,13 +19679,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>206.84</v>
+        <v>195.8</v>
       </c>
       <c r="E246" s="9" t="n">
-        <v>0.0394</v>
+        <v>0.017</v>
       </c>
       <c r="F246" s="5" t="n">
-        <v>-0.0373</v>
+        <v>-0.0861</v>
       </c>
       <c r="G246" s="6" t="n">
         <v>46260</v>
@@ -19714,7 +19714,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="9" t="n">
-        <v>0.5229162637787662</v>
+        <v>0.6087844739530132</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="9" t="n">
-        <v>0.9967124347321601</v>
+        <v>1.109295199182839</v>
       </c>
       <c r="Q246" s="10" t="inlineStr">
         <is>
@@ -19774,13 +19774,13 @@
         </is>
       </c>
       <c r="D247" s="15" t="n">
-        <v>437.98</v>
+        <v>416.06</v>
       </c>
       <c r="E247" s="16" t="n">
-        <v>-0.1608</v>
+        <v>-0.1484</v>
       </c>
       <c r="F247" s="16" t="n">
-        <v>-0.1693</v>
+        <v>-0.1777</v>
       </c>
       <c r="G247" s="17" t="n">
         <v>46240</v>
@@ -19835,13 +19835,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>269.24</v>
+        <v>263.1</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>-0.08439999999999999</v>
+        <v>-0.05019999999999999</v>
       </c>
       <c r="F248" s="5" t="n">
-        <v>-0.1907</v>
+        <v>-0.2034</v>
       </c>
       <c r="G248" s="6" t="n">
         <v>46231</v>
@@ -19892,13 +19892,13 @@
         </is>
       </c>
       <c r="D249" s="15" t="n">
-        <v>15.77</v>
+        <v>15.22</v>
       </c>
       <c r="E249" s="16" t="n">
-        <v>-0.1825</v>
+        <v>-0.1042</v>
       </c>
       <c r="F249" s="16" t="n">
-        <v>-0.373</v>
+        <v>-0.3948</v>
       </c>
       <c r="G249" s="17" t="n"/>
       <c r="H249" s="23" t="inlineStr">
@@ -19943,13 +19943,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>138.5</v>
+        <v>137.99</v>
       </c>
       <c r="E250" s="9" t="n">
-        <v>0.168</v>
+        <v>0.1103</v>
       </c>
       <c r="F250" s="9" t="n">
-        <v>0.4764</v>
+        <v>0.4568</v>
       </c>
       <c r="G250" s="6" t="n">
         <v>46259</v>
@@ -19978,7 +19978,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="9" t="n">
-        <v>0.08303249097472924</v>
+        <v>0.08703529241249358</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="5" t="n">
-        <v>-0.06137184115523465</v>
+        <v>-0.05790274657583889</v>
       </c>
       <c r="Q250" s="10" t="inlineStr">
         <is>
@@ -20033,10 +20033,10 @@
         <v>86.81</v>
       </c>
       <c r="E251" s="16" t="n">
-        <v>-0.25</v>
+        <v>-0.0424</v>
       </c>
       <c r="F251" s="16" t="n">
-        <v>-0.3165</v>
+        <v>-0.2986</v>
       </c>
       <c r="G251" s="17" t="n">
         <v>46237</v>
@@ -20091,13 +20091,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>272.62</v>
+        <v>252.92</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>-0.154</v>
+        <v>-0.2192</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0228</v>
       </c>
       <c r="G252" s="6" t="n">
         <v>46240</v>
@@ -20152,13 +20152,13 @@
         </is>
       </c>
       <c r="D253" s="15" t="n">
-        <v>114.99</v>
+        <v>120.04</v>
       </c>
       <c r="E253" s="16" t="n">
-        <v>-0.27</v>
+        <v>-0.1918</v>
       </c>
       <c r="F253" s="16" t="n">
-        <v>-0.4044</v>
+        <v>-0.4107</v>
       </c>
       <c r="G253" s="17" t="n">
         <v>46273</v>
@@ -20187,7 +20187,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="20" t="n">
-        <v>1.434994347334551</v>
+        <v>1.332555814728424</v>
       </c>
       <c r="N253" s="14" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="20" t="n">
-        <v>1.130620053917732</v>
+        <v>1.040986337887371</v>
       </c>
       <c r="Q253" s="21" t="inlineStr">
         <is>
@@ -20239,13 +20239,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>323.79</v>
+        <v>318.98</v>
       </c>
       <c r="E254" s="9" t="n">
-        <v>0.1351</v>
+        <v>0.0486</v>
       </c>
       <c r="F254" s="9" t="n">
-        <v>0.2611</v>
+        <v>0.2375</v>
       </c>
       <c r="G254" s="6" t="n">
         <v>46251</v>
@@ -20274,7 +20274,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="9" t="n">
-        <v>0.2971370332622996</v>
+        <v>0.3166969715969652</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="9" t="n">
-        <v>0.2816949257234627</v>
+        <v>0.3010220076493823</v>
       </c>
       <c r="Q254" s="10" t="inlineStr">
         <is>
@@ -20334,13 +20334,13 @@
         </is>
       </c>
       <c r="D255" s="15" t="n">
-        <v>10.84</v>
+        <v>11.59</v>
       </c>
       <c r="E255" s="20" t="n">
-        <v>0.05139999999999999</v>
-      </c>
-      <c r="F255" s="16" t="n">
-        <v>-0.0225</v>
+        <v>0.1002</v>
+      </c>
+      <c r="F255" s="20" t="n">
+        <v>0.0004</v>
       </c>
       <c r="G255" s="17" t="n">
         <v>46268</v>
@@ -20395,13 +20395,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>26.82</v>
+        <v>29.38</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>-0.1036</v>
+        <v>-0.0455</v>
       </c>
       <c r="F256" s="5" t="n">
-        <v>-0.2188</v>
+        <v>-0.1318</v>
       </c>
       <c r="G256" s="6" t="n">
         <v>46315</v>
@@ -20456,13 +20456,13 @@
         </is>
       </c>
       <c r="D257" s="15" t="n">
-        <v>127.55</v>
+        <v>127.88</v>
       </c>
       <c r="E257" s="16" t="n">
-        <v>-0.0034</v>
+        <v>-0.0351</v>
       </c>
       <c r="F257" s="16" t="n">
-        <v>-0.2008</v>
+        <v>-0.1849</v>
       </c>
       <c r="G257" s="17" t="n">
         <v>46232</v>
@@ -20517,13 +20517,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>122.92</v>
+        <v>131.6</v>
       </c>
       <c r="E258" s="9" t="n">
-        <v>0.083</v>
+        <v>0.1653</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>-0.1001</v>
+        <v>-0.0819</v>
       </c>
       <c r="G258" s="6" t="n">
         <v>46237</v>
@@ -20578,13 +20578,13 @@
         </is>
       </c>
       <c r="D259" s="15" t="n">
-        <v>135.06</v>
+        <v>130.32</v>
       </c>
       <c r="E259" s="16" t="n">
-        <v>-0.1491</v>
+        <v>-0.1763</v>
       </c>
       <c r="F259" s="16" t="n">
-        <v>-0.1793</v>
+        <v>-0.1802</v>
       </c>
       <c r="G259" s="17" t="n">
         <v>46238</v>
@@ -20649,13 +20649,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>16.21</v>
+        <v>18.95</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>-0.2946</v>
+        <v>-0.1674</v>
       </c>
       <c r="F260" s="5" t="n">
-        <v>-0.4172999999999999</v>
+        <v>-0.3574</v>
       </c>
       <c r="G260" s="6" t="n">
         <v>46240</v>
@@ -20710,13 +20710,13 @@
         </is>
       </c>
       <c r="D261" s="15" t="n">
-        <v>166.97</v>
+        <v>167.8</v>
       </c>
       <c r="E261" s="16" t="n">
-        <v>-0.1542</v>
+        <v>-0.114</v>
       </c>
       <c r="F261" s="16" t="n">
-        <v>-0.329</v>
+        <v>-0.3103</v>
       </c>
       <c r="G261" s="17" t="n">
         <v>46232</v>
@@ -20745,7 +20745,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="20" t="n">
-        <v>0.5871114571479906</v>
+        <v>0.5792610250297973</v>
       </c>
       <c r="N261" s="14" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>179</v>
       </c>
       <c r="P261" s="20" t="n">
-        <v>0.07204887105468048</v>
+        <v>0.06674612634088194</v>
       </c>
       <c r="Q261" s="21" t="inlineStr">
         <is>
@@ -20801,13 +20801,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>86.51000000000001</v>
+        <v>88.72</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>-0.1098</v>
+        <v>-0.055</v>
       </c>
       <c r="F262" s="5" t="n">
-        <v>-0.2007</v>
+        <v>-0.1663</v>
       </c>
       <c r="G262" s="6" t="n">
         <v>46231</v>
@@ -20862,13 +20862,13 @@
         </is>
       </c>
       <c r="D263" s="15" t="n">
-        <v>7.43</v>
+        <v>7.8</v>
       </c>
       <c r="E263" s="16" t="n">
-        <v>-0.234</v>
+        <v>-0.1503</v>
       </c>
       <c r="F263" s="16" t="n">
-        <v>-0.3639</v>
+        <v>-0.3627</v>
       </c>
       <c r="G263" s="17" t="n">
         <v>46247</v>
@@ -20923,13 +20923,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>73.23999999999999</v>
-      </c>
-      <c r="E264" s="5" t="n">
-        <v>-0.0172</v>
+        <v>74.91</v>
+      </c>
+      <c r="E264" s="9" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F264" s="9" t="n">
-        <v>0.0722</v>
+        <v>0.0653</v>
       </c>
       <c r="G264" s="6" t="n">
         <v>46273</v>
@@ -20984,16 +20984,16 @@
         </is>
       </c>
       <c r="D265" s="15" t="n">
-        <v>14.15</v>
+        <v>15.16</v>
       </c>
       <c r="E265" s="16" t="n">
-        <v>-0.2755</v>
+        <v>-0.1743</v>
       </c>
       <c r="F265" s="16" t="n">
-        <v>-0.4355</v>
+        <v>-0.4391</v>
       </c>
       <c r="G265" s="17" t="n">
-        <v>46245</v>
+        <v>46240</v>
       </c>
       <c r="H265" s="24" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
       </c>
       <c r="J265" s="14" t="inlineStr">
         <is>
-          <t>Aug 11</t>
+          <t>Aug 06</t>
         </is>
       </c>
       <c r="K265" s="14" t="inlineStr"/>
@@ -21045,13 +21045,13 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>367.34</v>
+        <v>379.15</v>
       </c>
       <c r="E266" s="9" t="n">
-        <v>0.1078</v>
+        <v>0.1207</v>
       </c>
       <c r="F266" s="9" t="n">
-        <v>0.1469</v>
+        <v>0.1858</v>
       </c>
       <c r="G266" s="6" t="n">
         <v>46317</v>
@@ -21120,13 +21120,13 @@
         </is>
       </c>
       <c r="D267" s="15" t="n">
-        <v>3.94</v>
+        <v>3.81</v>
       </c>
       <c r="E267" s="16" t="n">
-        <v>-0.4223</v>
+        <v>-0.3637</v>
       </c>
       <c r="F267" s="16" t="n">
-        <v>-0.2072</v>
+        <v>-0.2155</v>
       </c>
       <c r="G267" s="17" t="n">
         <v>46240</v>
@@ -21181,13 +21181,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>18.14</v>
+        <v>18.27</v>
       </c>
       <c r="E268" s="9" t="n">
-        <v>0.1997</v>
-      </c>
-      <c r="F268" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.1486</v>
+      </c>
+      <c r="F268" s="9" t="n">
+        <v>0.0142</v>
       </c>
       <c r="G268" s="6" t="n">
         <v>46261</v>
@@ -21242,13 +21242,13 @@
         </is>
       </c>
       <c r="D269" s="15" t="n">
-        <v>14.95</v>
+        <v>15.73</v>
       </c>
       <c r="E269" s="20" t="n">
-        <v>0.1893</v>
+        <v>0.1939</v>
       </c>
       <c r="F269" s="16" t="n">
-        <v>-0.058</v>
+        <v>-0.0492</v>
       </c>
       <c r="G269" s="17" t="n">
         <v>46273</v>
@@ -21303,13 +21303,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>208.43</v>
+        <v>201.2</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>-0.1623</v>
+        <v>-0.1494</v>
       </c>
       <c r="F270" s="5" t="n">
-        <v>-0.1983</v>
+        <v>-0.2356</v>
       </c>
       <c r="G270" s="6" t="n">
         <v>46230</v>
@@ -21364,13 +21364,13 @@
         </is>
       </c>
       <c r="D271" s="15" t="n">
-        <v>160</v>
+        <v>172.66</v>
       </c>
       <c r="E271" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.1133</v>
       </c>
       <c r="F271" s="16" t="n">
-        <v>-0.08650000000000001</v>
+        <v>-0.016</v>
       </c>
       <c r="G271" s="17" t="n">
         <v>46316</v>
@@ -21445,13 +21445,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>30.1</v>
+        <v>28.93</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.0553</v>
       </c>
       <c r="F272" s="5" t="n">
-        <v>-0.1887</v>
+        <v>-0.2994</v>
       </c>
       <c r="G272" s="6" t="n">
         <v>46245</v>
@@ -21506,13 +21506,13 @@
         </is>
       </c>
       <c r="D273" s="15" t="n">
-        <v>268.06</v>
+        <v>270.46</v>
       </c>
       <c r="E273" s="20" t="n">
-        <v>0.1864</v>
+        <v>0.0864</v>
       </c>
       <c r="F273" s="20" t="n">
-        <v>0.5093</v>
+        <v>0.1307</v>
       </c>
       <c r="G273" s="17" t="n">
         <v>46260</v>
@@ -21541,7 +21541,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="20" t="n">
-        <v>0.1937625904648213</v>
+        <v>0.1831694150706205</v>
       </c>
       <c r="N273" s="14" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="20" t="n">
-        <v>0.04454226665671863</v>
+        <v>0.03527323818679295</v>
       </c>
       <c r="Q273" s="21" t="inlineStr">
         <is>
@@ -21593,13 +21593,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>373.47</v>
+        <v>390.02</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>-0.195</v>
+        <v>-0.1416</v>
       </c>
       <c r="F274" s="5" t="n">
-        <v>-0.3014</v>
+        <v>-0.1885</v>
       </c>
       <c r="G274" s="6" t="n">
         <v>46260</v>
@@ -21628,7 +21628,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="9" t="n">
-        <v>0.4325113128229843</v>
+        <v>0.3717245269473361</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="8" t="n"/>
@@ -21672,13 +21672,13 @@
         </is>
       </c>
       <c r="D275" s="15" t="n">
-        <v>6.16</v>
+        <v>6.4</v>
       </c>
       <c r="E275" s="16" t="n">
-        <v>-0.0284</v>
+        <v>-0.0019</v>
       </c>
       <c r="F275" s="16" t="n">
-        <v>-0.2423</v>
+        <v>-0.2526</v>
       </c>
       <c r="G275" s="17" t="n">
         <v>46239</v>
@@ -21733,13 +21733,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>60.21</v>
+        <v>62.25</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>-0.1567</v>
+        <v>-0.08460000000000001</v>
       </c>
       <c r="F276" s="5" t="n">
-        <v>-0.2782</v>
+        <v>-0.2354</v>
       </c>
       <c r="G276" s="6" t="n">
         <v>46231</v>
@@ -21794,13 +21794,13 @@
         </is>
       </c>
       <c r="D277" s="15" t="n">
-        <v>113</v>
+        <v>113.42</v>
       </c>
       <c r="E277" s="16" t="n">
-        <v>-0.1315</v>
+        <v>-0.0626</v>
       </c>
       <c r="F277" s="16" t="n">
-        <v>-0.2343</v>
+        <v>-0.2083</v>
       </c>
       <c r="G277" s="17" t="n">
         <v>46240</v>
@@ -21855,13 +21855,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>202.94</v>
+        <v>205.43</v>
       </c>
       <c r="E278" s="9" t="n">
-        <v>0.0221</v>
+        <v>0.0389</v>
       </c>
       <c r="F278" s="5" t="n">
-        <v>-0.0271</v>
+        <v>-0.0233</v>
       </c>
       <c r="G278" s="6" t="n">
         <v>46330</v>
@@ -21916,13 +21916,13 @@
         </is>
       </c>
       <c r="D279" s="15" t="n">
-        <v>349.92</v>
+        <v>327.67</v>
       </c>
       <c r="E279" s="16" t="n">
-        <v>-0.1809</v>
+        <v>-0.2499</v>
       </c>
       <c r="F279" s="16" t="n">
-        <v>-0.1008</v>
+        <v>-0.1437</v>
       </c>
       <c r="G279" s="17" t="n">
         <v>46231</v>
@@ -21977,13 +21977,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>52.91</v>
+        <v>55.72</v>
       </c>
       <c r="E280" s="9" t="n">
-        <v>0.0552</v>
-      </c>
-      <c r="F280" s="5" t="n">
-        <v>-0.0609</v>
+        <v>0.099</v>
+      </c>
+      <c r="F280" s="9" t="n">
+        <v>0.0146</v>
       </c>
       <c r="G280" s="6" t="n">
         <v>46239</v>
@@ -22038,13 +22038,13 @@
         </is>
       </c>
       <c r="D281" s="15" t="n">
-        <v>403.41</v>
+        <v>392</v>
       </c>
       <c r="E281" s="16" t="n">
-        <v>-0.0849</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="F281" s="16" t="n">
-        <v>-0.0216</v>
+        <v>-0.07730000000000001</v>
       </c>
       <c r="G281" s="17" t="n">
         <v>46310</v>
@@ -22121,13 +22121,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>131.41</v>
+        <v>121.79</v>
       </c>
       <c r="E282" s="5" t="n">
-        <v>-0.3735</v>
+        <v>-0.364</v>
       </c>
       <c r="F282" s="5" t="n">
-        <v>-0.3328</v>
+        <v>-0.3515</v>
       </c>
       <c r="G282" s="6" t="n">
         <v>46239</v>
@@ -22182,13 +22182,13 @@
         </is>
       </c>
       <c r="D283" s="15" t="n">
-        <v>191.46</v>
+        <v>195.11</v>
       </c>
       <c r="E283" s="20" t="n">
-        <v>0.0166</v>
+        <v>0.0185</v>
       </c>
       <c r="F283" s="20" t="n">
-        <v>0.0095</v>
+        <v>0.05690000000000001</v>
       </c>
       <c r="G283" s="17" t="n">
         <v>46240</v>
@@ -22243,13 +22243,13 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>279.58</v>
+        <v>276.93</v>
       </c>
       <c r="E284" s="5" t="n">
-        <v>-0.0776</v>
+        <v>-0.0298</v>
       </c>
       <c r="F284" s="5" t="n">
-        <v>-0.1395</v>
+        <v>-0.1235</v>
       </c>
       <c r="G284" s="6" t="n">
         <v>46315</v>
@@ -22278,7 +22278,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="9" t="n">
-        <v>0.07303812862150375</v>
+        <v>0.08330625067706637</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="9" t="n">
-        <v>0.1302668288146506</v>
+        <v>0.1410825840465099</v>
       </c>
       <c r="Q284" s="10" t="inlineStr">
         <is>
@@ -22346,13 +22346,13 @@
         </is>
       </c>
       <c r="D285" s="15" t="n">
-        <v>297.15</v>
+        <v>320.15</v>
       </c>
       <c r="E285" s="20" t="n">
-        <v>0.0389</v>
-      </c>
-      <c r="F285" s="16" t="n">
-        <v>-0.0333</v>
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="F285" s="20" t="n">
+        <v>0.0461</v>
       </c>
       <c r="G285" s="17" t="n">
         <v>46232</v>
@@ -22381,7 +22381,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="20" t="n">
-        <v>0.1273767457513041</v>
+        <v>0.04638450726222091</v>
       </c>
       <c r="N285" s="14" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="20" t="n">
-        <v>0.2619888944977285</v>
+        <v>0.1713259409651726</v>
       </c>
       <c r="Q285" s="21" t="inlineStr">
         <is>
@@ -22433,13 +22433,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>28.62</v>
+        <v>30.61</v>
       </c>
       <c r="E286" s="9" t="n">
-        <v>0.0541</v>
+        <v>0.0843</v>
       </c>
       <c r="F286" s="9" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0224</v>
       </c>
       <c r="G286" s="6" t="n">
         <v>46240</v>
@@ -22494,13 +22494,13 @@
         </is>
       </c>
       <c r="D287" s="15" t="n">
-        <v>7.21</v>
+        <v>7.11</v>
       </c>
       <c r="E287" s="16" t="n">
-        <v>-0.1153</v>
+        <v>-0.0699</v>
       </c>
       <c r="F287" s="16" t="n">
-        <v>-0.2732</v>
+        <v>-0.33</v>
       </c>
       <c r="G287" s="17" t="n">
         <v>46254</v>
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>135.34</v>
+        <v>148.75</v>
       </c>
       <c r="E288" s="9" t="n">
-        <v>0.1461</v>
+        <v>0.1976</v>
       </c>
       <c r="F288" s="9" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.1441</v>
       </c>
       <c r="G288" s="6" t="n">
         <v>46254</v>
@@ -22616,13 +22616,13 @@
         </is>
       </c>
       <c r="D289" s="15" t="n">
-        <v>519.8</v>
+        <v>488.34</v>
       </c>
       <c r="E289" s="16" t="n">
-        <v>-0.1926</v>
+        <v>-0.1673</v>
       </c>
       <c r="F289" s="16" t="n">
-        <v>-0.0092</v>
+        <v>-0.08070000000000001</v>
       </c>
       <c r="G289" s="17" t="n">
         <v>46239</v>
@@ -22651,7 +22651,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="20" t="n">
-        <v>0.4043863024240094</v>
+        <v>0.4948601384281444</v>
       </c>
       <c r="N289" s="14" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="20" t="n">
-        <v>0.1061946902654868</v>
+        <v>0.1774583282139494</v>
       </c>
       <c r="Q289" s="21" t="inlineStr">
         <is>
@@ -22703,13 +22703,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>23.09</v>
+        <v>22.6</v>
       </c>
       <c r="E290" s="5" t="n">
-        <v>-0.4966</v>
+        <v>-0.5083</v>
       </c>
       <c r="F290" s="5" t="n">
-        <v>-0.6859000000000001</v>
+        <v>-0.6525</v>
       </c>
       <c r="G290" s="6" t="n">
         <v>46238</v>
@@ -22764,13 +22764,13 @@
         </is>
       </c>
       <c r="D291" s="15" t="n">
-        <v>87.98999999999999</v>
+        <v>91.27</v>
       </c>
       <c r="E291" s="20" t="n">
-        <v>0.0295</v>
+        <v>0.0553</v>
       </c>
       <c r="F291" s="16" t="n">
-        <v>-0.1209</v>
+        <v>-0.0915</v>
       </c>
       <c r="G291" s="17" t="n">
         <v>46254</v>
@@ -22825,13 +22825,13 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>142.32</v>
+        <v>147.57</v>
       </c>
       <c r="E292" s="9" t="n">
-        <v>0.1183</v>
-      </c>
-      <c r="F292" s="5" t="n">
-        <v>-0.229</v>
+        <v>0.1158</v>
+      </c>
+      <c r="F292" s="9" t="n">
+        <v>0.1348</v>
       </c>
       <c r="G292" s="6" t="n">
         <v>46266</v>
@@ -22886,13 +22886,13 @@
         </is>
       </c>
       <c r="D293" s="15" t="n">
-        <v>297.87</v>
+        <v>293.11</v>
       </c>
       <c r="E293" s="20" t="n">
-        <v>0.0687</v>
+        <v>0.0551</v>
       </c>
       <c r="F293" s="20" t="n">
-        <v>0.0286</v>
+        <v>0.0334</v>
       </c>
       <c r="G293" s="17" t="n">
         <v>46233</v>
@@ -22947,13 +22947,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>83.72</v>
+        <v>82.92</v>
       </c>
       <c r="E294" s="9" t="n">
-        <v>0.0372</v>
+        <v>0.0235</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>-0.032</v>
+        <v>-0.0556</v>
       </c>
       <c r="G294" s="6" t="n">
         <v>46252</v>
@@ -23008,13 +23008,13 @@
         </is>
       </c>
       <c r="D295" s="15" t="n">
-        <v>137.7</v>
-      </c>
-      <c r="E295" s="16" t="n">
-        <v>-0.0009</v>
+        <v>137.68</v>
+      </c>
+      <c r="E295" s="20" t="n">
+        <v>0.0034</v>
       </c>
       <c r="F295" s="16" t="n">
-        <v>-0.07200000000000001</v>
+        <v>-0.0381</v>
       </c>
       <c r="G295" s="17" t="n">
         <v>46238</v>
@@ -23043,7 +23043,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="20" t="n">
-        <v>0.2055192447349311</v>
+        <v>0.2056943637420104</v>
       </c>
       <c r="N295" s="14" t="inlineStr"/>
       <c r="O295" s="19" t="n"/>
@@ -23091,13 +23091,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>29.84</v>
-      </c>
-      <c r="E296" s="9" t="n">
-        <v>0.0157</v>
+        <v>28.8</v>
+      </c>
+      <c r="E296" s="5" t="n">
+        <v>-0.0083</v>
       </c>
       <c r="F296" s="5" t="n">
-        <v>-0.1542</v>
+        <v>-0.1717</v>
       </c>
       <c r="G296" s="6" t="n">
         <v>46317</v>
@@ -23152,13 +23152,13 @@
         </is>
       </c>
       <c r="D297" s="15" t="n">
-        <v>268.75</v>
+        <v>271.6</v>
       </c>
       <c r="E297" s="16" t="n">
-        <v>-0.0273</v>
+        <v>-0.0425</v>
       </c>
       <c r="F297" s="20" t="n">
-        <v>0.0571</v>
+        <v>0.0436</v>
       </c>
       <c r="G297" s="17" t="n">
         <v>46231</v>
@@ -23187,7 +23187,7 @@
         <v>275</v>
       </c>
       <c r="M297" s="20" t="n">
-        <v>0.02325581395348837</v>
+        <v>0.01251840942562584</v>
       </c>
       <c r="N297" s="14" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="20" t="n">
-        <v>0.1609302325581395</v>
+        <v>0.1487481590574373</v>
       </c>
       <c r="Q297" s="21" t="inlineStr">
         <is>
@@ -23251,13 +23251,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>37.44</v>
+        <v>37.03</v>
       </c>
       <c r="E298" s="5" t="n">
-        <v>-0.1882</v>
+        <v>-0.1891</v>
       </c>
       <c r="F298" s="5" t="n">
-        <v>-0.1329</v>
+        <v>-0.1168</v>
       </c>
       <c r="G298" s="6" t="n">
         <v>46230</v>
@@ -23316,13 +23316,13 @@
         </is>
       </c>
       <c r="D299" s="15" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="E299" s="20" t="n">
-        <v>0.0123</v>
+        <v>61.6</v>
+      </c>
+      <c r="E299" s="16" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F299" s="16" t="n">
-        <v>-0.0273</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="G299" s="17" t="n">
         <v>46310</v>
@@ -23377,13 +23377,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>512.28</v>
+        <v>508.26</v>
       </c>
       <c r="E300" s="5" t="n">
-        <v>-0.0067</v>
-      </c>
-      <c r="F300" s="5" t="n">
-        <v>-0.0052</v>
+        <v>-0.0219</v>
+      </c>
+      <c r="F300" s="9" t="n">
+        <v>0.0125</v>
       </c>
       <c r="G300" s="6" t="n">
         <v>46234</v>
@@ -23412,7 +23412,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="9" t="n">
-        <v>0.1126727570859687</v>
+        <v>0.1214732617164444</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="9" t="n">
-        <v>0.0248301710002343</v>
+        <v>0.03293589894935665</v>
       </c>
       <c r="Q300" s="10" t="inlineStr">
         <is>
@@ -23476,13 +23476,13 @@
         </is>
       </c>
       <c r="D301" s="15" t="n">
-        <v>559.6</v>
+        <v>571.3099999999999</v>
       </c>
       <c r="E301" s="16" t="n">
-        <v>-0.0925</v>
+        <v>-0.0726</v>
       </c>
       <c r="F301" s="16" t="n">
-        <v>-0.0024</v>
+        <v>-0.0067</v>
       </c>
       <c r="G301" s="17" t="n">
         <v>46233</v>
@@ -23511,7 +23511,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="20" t="n">
-        <v>0.1007862759113652</v>
+        <v>0.07822373142427064</v>
       </c>
       <c r="N301" s="14" t="inlineStr"/>
       <c r="O301" s="19" t="n"/>
@@ -23555,13 +23555,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>247.56</v>
+        <v>245.79</v>
       </c>
       <c r="E302" s="9" t="n">
-        <v>0.0293</v>
-      </c>
-      <c r="F302" s="9" t="n">
-        <v>0.0303</v>
+        <v>0.025</v>
+      </c>
+      <c r="F302" s="5" t="n">
+        <v>-0.0141</v>
       </c>
       <c r="G302" s="6" t="n">
         <v>46230</v>
@@ -23590,7 +23590,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="9" t="n">
-        <v>0.1431572144126676</v>
+        <v>0.1513893974531104</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="8" t="n"/>
@@ -23636,13 +23636,13 @@
         </is>
       </c>
       <c r="D303" s="15" t="n">
-        <v>254.39</v>
+        <v>250.6</v>
       </c>
       <c r="E303" s="20" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0375</v>
       </c>
       <c r="F303" s="20" t="n">
-        <v>0.1644</v>
+        <v>0.1488</v>
       </c>
       <c r="G303" s="17" t="n">
         <v>46321</v>
@@ -23671,7 +23671,7 @@
         <v>246</v>
       </c>
       <c r="M303" s="16" t="n">
-        <v>-0.03298085616572973</v>
+        <v>-0.01835594573024739</v>
       </c>
       <c r="N303" s="14" t="inlineStr"/>
       <c r="O303" s="19" t="n"/>
@@ -23719,13 +23719,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>116</v>
+        <v>118.2</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>-0.0412</v>
+        <v>-0.0409</v>
       </c>
       <c r="F304" s="9" t="n">
-        <v>0.059</v>
+        <v>0.0473</v>
       </c>
       <c r="G304" s="6" t="n">
         <v>46231</v>
@@ -23754,7 +23754,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="9" t="n">
-        <v>0.1206896551724138</v>
+        <v>0.09983079526226732</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="9" t="n">
-        <v>0.103448275862069</v>
+        <v>0.08291032148900167</v>
       </c>
       <c r="Q304" s="10" t="inlineStr">
         <is>
@@ -23814,13 +23814,13 @@
         </is>
       </c>
       <c r="D305" s="15" t="n">
-        <v>107</v>
+        <v>108.53</v>
       </c>
       <c r="E305" s="16" t="n">
-        <v>-0.0246</v>
+        <v>-0.0349</v>
       </c>
       <c r="F305" s="20" t="n">
-        <v>0.0398</v>
+        <v>0.0152</v>
       </c>
       <c r="G305" s="17" t="n">
         <v>46302</v>
@@ -23849,7 +23849,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="20" t="n">
-        <v>0.2616822429906542</v>
+        <v>0.2438956970422924</v>
       </c>
       <c r="N305" s="14" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="20" t="n">
-        <v>0.1682242990654206</v>
+        <v>0.1517552750391597</v>
       </c>
       <c r="Q305" s="21" t="inlineStr"/>
       <c r="R305" s="19" t="n"/>
@@ -23895,13 +23895,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>317.51</v>
+        <v>327.3</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>-0.0469</v>
+        <v>-0.0488</v>
       </c>
       <c r="F306" s="9" t="n">
-        <v>0.0201</v>
+        <v>0.0726</v>
       </c>
       <c r="G306" s="6" t="n">
         <v>46231</v>
@@ -23930,7 +23930,7 @@
         <v>350</v>
       </c>
       <c r="M306" s="9" t="n">
-        <v>0.1023274857484804</v>
+        <v>0.06935533150015273</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="9" t="n">
-        <v>0.2598028408554062</v>
+        <v>0.2221203788573174</v>
       </c>
       <c r="Q306" s="10" t="inlineStr">
         <is>
@@ -23982,13 +23982,13 @@
         </is>
       </c>
       <c r="D307" s="15" t="n">
-        <v>74.56</v>
+        <v>73.16</v>
       </c>
       <c r="E307" s="20" t="n">
-        <v>0.0242</v>
-      </c>
-      <c r="F307" s="16" t="n">
-        <v>-0.1561</v>
+        <v>0.0578</v>
+      </c>
+      <c r="F307" s="20" t="n">
+        <v>0.0016</v>
       </c>
       <c r="G307" s="17" t="n">
         <v>46260</v>
@@ -24039,13 +24039,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>52.29</v>
+        <v>51.67</v>
       </c>
       <c r="E308" s="5" t="n">
-        <v>-0.2646</v>
+        <v>-0.3163</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>-0.134</v>
+        <v>-0.1443</v>
       </c>
       <c r="G308" s="6" t="n">
         <v>46267</v>
@@ -24100,13 +24100,13 @@
         </is>
       </c>
       <c r="D309" s="15" t="n">
-        <v>80.63</v>
+        <v>81.02</v>
       </c>
       <c r="E309" s="20" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0518</v>
       </c>
       <c r="F309" s="20" t="n">
-        <v>0.0678</v>
+        <v>0.0868</v>
       </c>
       <c r="G309" s="17" t="n">
         <v>46233</v>
@@ -24135,14 +24135,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="20" t="n">
-        <v>0.02939352598288484</v>
+        <v>0.02443841026906942</v>
       </c>
       <c r="N309" s="14" t="inlineStr"/>
       <c r="O309" s="19" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="20" t="n">
-        <v>0.07900285253627688</v>
+        <v>0.07380893606516915</v>
       </c>
       <c r="Q309" s="21" t="inlineStr"/>
       <c r="R309" s="19" t="n"/>
@@ -24177,13 +24177,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>166.67</v>
+        <v>167.47</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>-0.0447</v>
+        <v>-0.0462</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>-0.09880000000000001</v>
+        <v>-0.1029</v>
       </c>
       <c r="G310" s="6" t="n">
         <v>46231</v>
@@ -24212,7 +24212,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="9" t="n">
-        <v>0.1999760004799905</v>
+        <v>0.1942437451483848</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="8" t="n"/>
@@ -24260,13 +24260,13 @@
         </is>
       </c>
       <c r="D311" s="15" t="n">
-        <v>139.46</v>
+        <v>143.08</v>
       </c>
       <c r="E311" s="20" t="n">
-        <v>0.0412</v>
+        <v>0.0413</v>
       </c>
       <c r="F311" s="20" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.1318</v>
       </c>
       <c r="G311" s="17" t="n">
         <v>46232</v>
@@ -24325,13 +24325,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>199.08</v>
-      </c>
-      <c r="E312" s="9" t="n">
-        <v>0.0314</v>
+        <v>192.38</v>
+      </c>
+      <c r="E312" s="5" t="n">
+        <v>-0.0032</v>
       </c>
       <c r="F312" s="9" t="n">
-        <v>0.0279</v>
+        <v>0.005</v>
       </c>
       <c r="G312" s="6" t="n">
         <v>46317</v>
@@ -24360,7 +24360,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="9" t="n">
-        <v>0.1050833835643962</v>
+        <v>0.1435700176733548</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="9" t="n">
-        <v>0.1553144464536869</v>
+        <v>0.1955504730221437</v>
       </c>
       <c r="Q312" s="10" t="inlineStr">
         <is>
@@ -24412,13 +24412,13 @@
         </is>
       </c>
       <c r="D313" s="15" t="n">
-        <v>1084.24</v>
+        <v>1045.2</v>
       </c>
       <c r="E313" s="16" t="n">
-        <v>-0.0098</v>
-      </c>
-      <c r="F313" s="20" t="n">
-        <v>0.0061</v>
+        <v>-0.04219999999999999</v>
+      </c>
+      <c r="F313" s="16" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="G313" s="17" t="n">
         <v>46232</v>
@@ -24447,7 +24447,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="20" t="n">
-        <v>0.1067660296613296</v>
+        <v>0.148105625717566</v>
       </c>
       <c r="N313" s="14" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="20" t="n">
-        <v>0.1436582306500406</v>
+        <v>0.1863758132414848</v>
       </c>
       <c r="Q313" s="21" t="inlineStr">
         <is>
@@ -24503,13 +24503,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>126.08</v>
+        <v>126.81</v>
       </c>
       <c r="E314" s="9" t="n">
-        <v>0.0117</v>
+        <v>0.0138</v>
       </c>
       <c r="F314" s="9" t="n">
-        <v>0.0493</v>
+        <v>0.0478</v>
       </c>
       <c r="G314" s="6" t="n">
         <v>46234</v>
@@ -24538,7 +24538,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="9" t="n">
-        <v>0.02315989847715737</v>
+        <v>0.01726993139342321</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>122</v>
       </c>
       <c r="P314" s="5" t="n">
-        <v>-0.03236040609137054</v>
+        <v>-0.03793076255815789</v>
       </c>
       <c r="Q314" s="10" t="inlineStr">
         <is>
@@ -24590,13 +24590,13 @@
         </is>
       </c>
       <c r="D315" s="15" t="n">
-        <v>65.59999999999999</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="E315" s="20" t="n">
-        <v>0.0582</v>
+        <v>0.0417</v>
       </c>
       <c r="F315" s="20" t="n">
-        <v>0.0504</v>
+        <v>0.0659</v>
       </c>
       <c r="G315" s="17" t="n">
         <v>46239</v>
@@ -24625,14 +24625,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="16" t="n">
-        <v>-0.009146341463414549</v>
+        <v>-0.01155717761557185</v>
       </c>
       <c r="N315" s="14" t="inlineStr"/>
       <c r="O315" s="19" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="20" t="n">
-        <v>0.02134146341463423</v>
+        <v>0.0188564476885644</v>
       </c>
       <c r="Q315" s="21" t="inlineStr">
         <is>
@@ -24673,13 +24673,13 @@
         </is>
       </c>
       <c r="D316" s="4" t="n">
-        <v>147.63</v>
+        <v>145.91</v>
       </c>
       <c r="E316" s="9" t="n">
-        <v>0.048</v>
+        <v>0.0424</v>
       </c>
       <c r="F316" s="9" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="G316" s="6" t="n">
         <v>46309</v>
@@ -24708,7 +24708,7 @@
         <v>167</v>
       </c>
       <c r="M316" s="9" t="n">
-        <v>0.1312063943642891</v>
+        <v>0.1445411555068193</v>
       </c>
       <c r="N316" s="3" t="inlineStr"/>
       <c r="O316" s="8" t="n"/>
@@ -24752,13 +24752,13 @@
         </is>
       </c>
       <c r="D317" s="15" t="n">
-        <v>322.48</v>
-      </c>
-      <c r="E317" s="20" t="n">
-        <v>0.0143</v>
+        <v>324.36</v>
+      </c>
+      <c r="E317" s="16" t="n">
+        <v>-0.0001</v>
       </c>
       <c r="F317" s="20" t="n">
-        <v>0.0592</v>
+        <v>0.0489</v>
       </c>
       <c r="G317" s="17" t="n">
         <v>46232</v>
@@ -24794,7 +24794,7 @@
         <v>316</v>
       </c>
       <c r="P317" s="16" t="n">
-        <v>-0.02009426941205662</v>
+        <v>-0.02577383154519674</v>
       </c>
       <c r="Q317" s="21" t="inlineStr">
         <is>
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>229.78</v>
+        <v>230.27</v>
       </c>
       <c r="E318" s="9" t="n">
-        <v>0.0343</v>
+        <v>0.0149</v>
       </c>
       <c r="F318" s="9" t="n">
-        <v>0.1104</v>
+        <v>0.1137</v>
       </c>
       <c r="G318" s="6" t="n">
         <v>46244</v>
@@ -24877,7 +24877,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="5" t="n">
-        <v>-0.06432239533466795</v>
+        <v>-0.06631345811438751</v>
       </c>
       <c r="Q318" s="10" t="inlineStr">
         <is>
@@ -24918,13 +24918,13 @@
         </is>
       </c>
       <c r="D319" s="15" t="n">
-        <v>121.83</v>
+        <v>122.43</v>
       </c>
       <c r="E319" s="20" t="n">
-        <v>0.0158</v>
+        <v>0.0097</v>
       </c>
       <c r="F319" s="16" t="n">
-        <v>-0.0243</v>
+        <v>-0.0206</v>
       </c>
       <c r="G319" s="17" t="n">
         <v>46230</v>
@@ -24953,7 +24953,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="20" t="n">
-        <v>0.1655585652138226</v>
+        <v>0.1598464428653107</v>
       </c>
       <c r="N319" s="14" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="20" t="n">
-        <v>0.1245177706640401</v>
+        <v>0.1190067793841378</v>
       </c>
       <c r="Q319" s="21" t="inlineStr">
         <is>
@@ -25013,13 +25013,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>252.07</v>
+        <v>249.57</v>
       </c>
       <c r="E320" s="9" t="n">
-        <v>0.1384</v>
+        <v>0.09789999999999999</v>
       </c>
       <c r="F320" s="9" t="n">
-        <v>0.1556</v>
+        <v>0.1868</v>
       </c>
       <c r="G320" s="6" t="n">
         <v>46230</v>
@@ -25048,7 +25048,7 @@
         <v>237</v>
       </c>
       <c r="M320" s="5" t="n">
-        <v>-0.05978498036259767</v>
+        <v>-0.05036663060463995</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>236</v>
       </c>
       <c r="P320" s="5" t="n">
-        <v>-0.06375213234419008</v>
+        <v>-0.05437352245862882</v>
       </c>
       <c r="Q320" s="10" t="inlineStr">
         <is>
@@ -25100,13 +25100,13 @@
         </is>
       </c>
       <c r="D321" s="15" t="n">
-        <v>179.22</v>
+        <v>177.91</v>
       </c>
       <c r="E321" s="20" t="n">
-        <v>0.0384</v>
+        <v>0.0156</v>
       </c>
       <c r="F321" s="20" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0282</v>
       </c>
       <c r="G321" s="17" t="n">
         <v>46239</v>
@@ -25135,7 +25135,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="20" t="n">
-        <v>0.1159468809284678</v>
+        <v>0.1241639030970716</v>
       </c>
       <c r="N321" s="14" t="inlineStr"/>
       <c r="O321" s="19" t="n"/>
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>134.66</v>
+        <v>134.96</v>
       </c>
       <c r="E322" s="9" t="n">
-        <v>0.0387</v>
+        <v>0.0172</v>
       </c>
       <c r="F322" s="9" t="n">
-        <v>0.0873</v>
+        <v>0.1031</v>
       </c>
       <c r="G322" s="6" t="n">
         <v>46232</v>
@@ -25214,7 +25214,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="5" t="n">
-        <v>-0.02717956334472001</v>
+        <v>-0.02934202726733853</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="8" t="n"/>
@@ -25258,13 +25258,13 @@
         </is>
       </c>
       <c r="D323" s="15" t="n">
-        <v>33.53</v>
+        <v>32.46</v>
       </c>
       <c r="E323" s="16" t="n">
-        <v>-0.1094</v>
+        <v>-0.1392</v>
       </c>
       <c r="F323" s="16" t="n">
-        <v>-0.1416</v>
+        <v>-0.1856</v>
       </c>
       <c r="G323" s="17" t="n">
         <v>46234</v>
@@ -25337,13 +25337,13 @@
         </is>
       </c>
       <c r="D324" s="4" t="n">
-        <v>40.88</v>
+        <v>40.33</v>
       </c>
       <c r="E324" s="9" t="n">
-        <v>0.1185</v>
+        <v>0.1019</v>
       </c>
       <c r="F324" s="9" t="n">
-        <v>0.0533</v>
+        <v>0.0195</v>
       </c>
       <c r="G324" s="6" t="n">
         <v>46233</v>
@@ -25398,13 +25398,13 @@
         </is>
       </c>
       <c r="D325" s="15" t="n">
-        <v>274.35</v>
+        <v>271.83</v>
       </c>
       <c r="E325" s="20" t="n">
-        <v>0.0238</v>
+        <v>0.0296</v>
       </c>
       <c r="F325" s="16" t="n">
-        <v>-0.09029999999999999</v>
+        <v>-0.0506</v>
       </c>
       <c r="G325" s="17" t="n">
         <v>46240</v>
@@ -25433,7 +25433,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="20" t="n">
-        <v>0.3996719518862765</v>
+        <v>0.4126476106390024</v>
       </c>
       <c r="N325" s="14" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="20" t="n">
-        <v>0.3850920357207945</v>
+        <v>0.3979325313615128</v>
       </c>
       <c r="Q325" s="21" t="inlineStr"/>
       <c r="R325" s="19" t="n"/>
@@ -25487,13 +25487,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>74.7</v>
+        <v>74.12</v>
       </c>
       <c r="E326" s="5" t="n">
-        <v>-0.0234</v>
+        <v>-0.0595</v>
       </c>
       <c r="F326" s="9" t="n">
-        <v>0.0067</v>
+        <v>0.013</v>
       </c>
       <c r="G326" s="6" t="n">
         <v>46231</v>
@@ -25522,7 +25522,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="9" t="n">
-        <v>0.05756358768406957</v>
+        <v>0.06583917970858061</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="8" t="n"/>
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="D327" s="15" t="n">
-        <v>130.52</v>
+        <v>129.12</v>
       </c>
       <c r="E327" s="20" t="n">
-        <v>0.0315</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F327" s="20" t="n">
-        <v>0.0444</v>
+        <v>0.0433</v>
       </c>
       <c r="G327" s="17" t="n">
         <v>46238</v>
@@ -25609,7 +25609,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="20" t="n">
-        <v>0.04198590254367138</v>
+        <v>0.05328376703841384</v>
       </c>
       <c r="N327" s="14" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="20" t="n">
-        <v>0.07263254673613231</v>
+        <v>0.08426270136307307</v>
       </c>
       <c r="Q327" s="21" t="inlineStr">
         <is>
@@ -25661,13 +25661,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>115.95</v>
-      </c>
-      <c r="E328" s="9" t="n">
-        <v>0.011</v>
+        <v>113.72</v>
+      </c>
+      <c r="E328" s="5" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F328" s="9" t="n">
-        <v>0.0355</v>
+        <v>0.0374</v>
       </c>
       <c r="G328" s="6" t="n">
         <v>46232</v>
@@ -25696,7 +25696,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="9" t="n">
-        <v>0.1297973264338076</v>
+        <v>0.151952163207879</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="9" t="n">
-        <v>0.04355325571366966</v>
+        <v>0.06401688357368977</v>
       </c>
       <c r="Q328" s="10" t="inlineStr">
         <is>
@@ -25752,13 +25752,13 @@
         </is>
       </c>
       <c r="D329" s="15" t="n">
-        <v>89.78</v>
-      </c>
-      <c r="E329" s="20" t="n">
-        <v>0.0247</v>
+        <v>88.56</v>
+      </c>
+      <c r="E329" s="16" t="n">
+        <v>-0.0001</v>
       </c>
       <c r="F329" s="20" t="n">
-        <v>0.0243</v>
+        <v>0.015</v>
       </c>
       <c r="G329" s="17" t="n">
         <v>46318</v>
@@ -25794,7 +25794,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="20" t="n">
-        <v>0.1918021831142793</v>
+        <v>0.2082204155374887</v>
       </c>
       <c r="Q329" s="21" t="inlineStr">
         <is>
@@ -25843,13 +25843,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>60.05</v>
+        <v>59.66</v>
       </c>
       <c r="E330" s="9" t="n">
-        <v>0.0617</v>
+        <v>0.0356</v>
       </c>
       <c r="F330" s="9" t="n">
-        <v>0.0438</v>
+        <v>0.0738</v>
       </c>
       <c r="G330" s="6" t="n">
         <v>46237</v>
@@ -25878,7 +25878,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="9" t="n">
-        <v>0.04912572855953377</v>
+        <v>0.05598390881662762</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="8" t="n"/>
@@ -25922,13 +25922,13 @@
         </is>
       </c>
       <c r="D331" s="15" t="n">
-        <v>40.25</v>
+        <v>40.9</v>
       </c>
       <c r="E331" s="16" t="n">
-        <v>-0.2555</v>
+        <v>-0.182</v>
       </c>
       <c r="F331" s="16" t="n">
-        <v>-0.4141</v>
+        <v>-0.3993</v>
       </c>
       <c r="G331" s="17" t="n">
         <v>46244</v>
@@ -25983,13 +25983,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>8.09</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>-0.2076</v>
+        <v>-0.1787</v>
       </c>
       <c r="F332" s="5" t="n">
-        <v>-0.338</v>
+        <v>-0.3195</v>
       </c>
       <c r="G332" s="6" t="n">
         <v>46239</v>
@@ -26044,13 +26044,13 @@
         </is>
       </c>
       <c r="D333" s="15" t="n">
-        <v>97.25</v>
-      </c>
-      <c r="E333" s="20" t="n">
-        <v>0.0153</v>
+        <v>96.77</v>
+      </c>
+      <c r="E333" s="16" t="n">
+        <v>-0.004</v>
       </c>
       <c r="F333" s="20" t="n">
-        <v>0.0336</v>
+        <v>0.0459</v>
       </c>
       <c r="G333" s="17" t="n">
         <v>46233</v>
@@ -26079,7 +26079,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="20" t="n">
-        <v>0.01799485861182519</v>
+        <v>0.02304433192104995</v>
       </c>
       <c r="N333" s="14" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="20" t="n">
-        <v>0.1516709511568123</v>
+        <v>0.1573834866177535</v>
       </c>
       <c r="Q333" s="21" t="inlineStr">
         <is>
@@ -26131,13 +26131,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>115.77</v>
-      </c>
-      <c r="E334" s="9" t="n">
-        <v>0.0014</v>
+        <v>114.1</v>
+      </c>
+      <c r="E334" s="5" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F334" s="9" t="n">
-        <v>0.0246</v>
+        <v>0.0217</v>
       </c>
       <c r="G334" s="6" t="n">
         <v>46232</v>
@@ -26166,7 +26166,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="9" t="n">
-        <v>0.09700267772307164</v>
+        <v>0.1130587204206837</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="8" t="n"/>
@@ -30473,22 +30473,22 @@
       </c>
       <c r="C107" s="13" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>SRAD</t>
         </is>
       </c>
       <c r="D107" s="14" t="inlineStr">
         <is>
-          <t>TKO Group</t>
+          <t>Sportradar</t>
         </is>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F107" s="14" t="inlineStr">
         <is>
-          <t>After close</t>
+          <t>Before open</t>
         </is>
       </c>
       <c r="G107" s="29" t="inlineStr">
@@ -30513,17 +30513,17 @@
       </c>
       <c r="C108" s="13" t="inlineStr">
         <is>
-          <t>VNOM</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>Viper Energy</t>
+          <t>TKO Group</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F108" s="14" t="inlineStr">
@@ -30553,12 +30553,12 @@
       </c>
       <c r="C109" s="13" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>VNOM</t>
         </is>
       </c>
       <c r="D109" s="14" t="inlineStr">
         <is>
-          <t>Williams Companies</t>
+          <t>Viper Energy</t>
         </is>
       </c>
       <c r="E109" s="14" t="inlineStr">
@@ -30584,26 +30584,26 @@
     </row>
     <row r="110">
       <c r="A110" s="28" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C110" s="13" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>WMB</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>Astera Labs</t>
+          <t>Williams Companies</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F110" s="14" t="inlineStr">
@@ -30633,12 +30633,12 @@
       </c>
       <c r="C111" s="13" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="D111" s="14" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Astera Labs</t>
         </is>
       </c>
       <c r="E111" s="14" t="inlineStr">
@@ -30673,22 +30673,22 @@
       </c>
       <c r="C112" s="13" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
-          <t>Before open</t>
+          <t>After close</t>
         </is>
       </c>
       <c r="G112" s="29" t="inlineStr">
@@ -30713,22 +30713,22 @@
       </c>
       <c r="C113" s="13" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="D113" s="14" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>AMETEK</t>
         </is>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F113" s="14" t="inlineStr">
         <is>
-          <t>After close</t>
+          <t>Before open</t>
         </is>
       </c>
       <c r="G113" s="29" t="inlineStr">
@@ -30753,17 +30753,17 @@
       </c>
       <c r="C114" s="13" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F114" s="14" t="inlineStr">
@@ -30793,17 +30793,17 @@
       </c>
       <c r="C115" s="13" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="D115" s="14" t="inlineStr">
         <is>
-          <t>Booking Holdings</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F115" s="14" t="inlineStr">
@@ -30833,22 +30833,22 @@
       </c>
       <c r="C116" s="13" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>Broadridge</t>
+          <t>Booking Holdings</t>
         </is>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F116" s="14" t="inlineStr">
         <is>
-          <t>Before open</t>
+          <t>After close</t>
         </is>
       </c>
       <c r="G116" s="29" t="inlineStr">
@@ -30873,12 +30873,12 @@
       </c>
       <c r="C117" s="13" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="D117" s="14" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Broadridge</t>
         </is>
       </c>
       <c r="E117" s="14" t="inlineStr">
@@ -30913,12 +30913,12 @@
       </c>
       <c r="C118" s="13" t="inlineStr">
         <is>
-          <t>CMI</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="E118" s="14" t="inlineStr">
@@ -30953,17 +30953,17 @@
       </c>
       <c r="C119" s="13" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>CMI</t>
         </is>
       </c>
       <c r="D119" s="14" t="inlineStr">
         <is>
-          <t>DuPont</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F119" s="14" t="inlineStr">
@@ -30993,17 +30993,17 @@
       </c>
       <c r="C120" s="13" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>DuPont</t>
         </is>
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="F120" s="14" t="inlineStr">
@@ -31033,22 +31033,22 @@
       </c>
       <c r="C121" s="13" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="D121" s="14" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F121" s="14" t="inlineStr">
         <is>
-          <t>After close</t>
+          <t>Before open</t>
         </is>
       </c>
       <c r="G121" s="29" t="inlineStr">
@@ -31073,17 +31073,17 @@
       </c>
       <c r="C122" s="13" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>EOG Resources</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F122" s="14" t="inlineStr">
@@ -31113,12 +31113,12 @@
       </c>
       <c r="C123" s="13" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="D123" s="14" t="inlineStr">
         <is>
-          <t>Energy Transfer</t>
+          <t>EOG Resources</t>
         </is>
       </c>
       <c r="E123" s="14" t="inlineStr">
@@ -31128,7 +31128,7 @@
       </c>
       <c r="F123" s="14" t="inlineStr">
         <is>
-          <t>Before open</t>
+          <t>After close</t>
         </is>
       </c>
       <c r="G123" s="29" t="inlineStr">
@@ -31153,20 +31153,24 @@
       </c>
       <c r="C124" s="13" t="inlineStr">
         <is>
-          <t>FOUR</t>
+          <t>ET</t>
         </is>
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>Shift4 Payments</t>
+          <t>Energy Transfer</t>
         </is>
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F124" s="14" t="inlineStr"/>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="F124" s="14" t="inlineStr">
+        <is>
+          <t>Before open</t>
+        </is>
+      </c>
       <c r="G124" s="29" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -31189,24 +31193,20 @@
       </c>
       <c r="C125" s="13" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>FOUR</t>
         </is>
       </c>
       <c r="D125" s="14" t="inlineStr">
         <is>
-          <t>Gilead Sciences</t>
+          <t>Shift4 Payments</t>
         </is>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="F125" s="14" t="inlineStr">
-        <is>
-          <t>After close</t>
-        </is>
-      </c>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F125" s="14" t="inlineStr"/>
       <c r="G125" s="29" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -31229,22 +31229,22 @@
       </c>
       <c r="C126" s="13" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>W.W. Grainger</t>
+          <t>Gilead Sciences</t>
         </is>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F126" s="14" t="inlineStr">
         <is>
-          <t>Before open</t>
+          <t>After close</t>
         </is>
       </c>
       <c r="G126" s="29" t="inlineStr">
@@ -31269,17 +31269,17 @@
       </c>
       <c r="C127" s="13" t="inlineStr">
         <is>
-          <t>HUT</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="D127" s="14" t="inlineStr">
         <is>
-          <t>Hut 8</t>
+          <t>W.W. Grainger</t>
         </is>
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F127" s="14" t="inlineStr">
@@ -31309,17 +31309,17 @@
       </c>
       <c r="C128" s="13" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>HUT</t>
         </is>
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>IDEXX Labs</t>
+          <t>Hut 8</t>
         </is>
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F128" s="14" t="inlineStr">
@@ -31349,17 +31349,17 @@
       </c>
       <c r="C129" s="13" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="D129" s="14" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>IDEXX Labs</t>
         </is>
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F129" s="14" t="inlineStr">
@@ -31389,17 +31389,17 @@
       </c>
       <c r="C130" s="13" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F130" s="14" t="inlineStr">
@@ -31429,22 +31429,22 @@
       </c>
       <c r="C131" s="13" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="D131" s="14" t="inlineStr">
         <is>
-          <t>Match Group</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F131" s="14" t="inlineStr">
         <is>
-          <t>After close</t>
+          <t>Before open</t>
         </is>
       </c>
       <c r="G131" s="29" t="inlineStr">
@@ -31469,22 +31469,22 @@
       </c>
       <c r="C132" s="13" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Match Group</t>
         </is>
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="F132" s="14" t="inlineStr">
         <is>
-          <t>Before open</t>
+          <t>After close</t>
         </is>
       </c>
       <c r="G132" s="29" t="inlineStr">
@@ -31509,17 +31509,17 @@
       </c>
       <c r="C133" s="13" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="D133" s="14" t="inlineStr">
         <is>
-          <t>Qnity Electronics</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F133" s="14" t="inlineStr">
@@ -31549,17 +31549,17 @@
       </c>
       <c r="C134" s="13" t="inlineStr">
         <is>
-          <t>ROK</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>Qnity Electronics</t>
         </is>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F134" s="14" t="inlineStr">
@@ -31589,17 +31589,17 @@
       </c>
       <c r="C135" s="13" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>ROK</t>
         </is>
       </c>
       <c r="D135" s="14" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F135" s="14" t="inlineStr">
@@ -31629,20 +31629,24 @@
       </c>
       <c r="C136" s="13" t="inlineStr">
         <is>
-          <t>SRAD</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>Sportradar</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="E136" s="14" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="F136" s="14" t="inlineStr"/>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="F136" s="14" t="inlineStr">
+        <is>
+          <t>Before open</t>
+        </is>
+      </c>
       <c r="G136" s="29" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -33433,12 +33437,12 @@
       </c>
       <c r="C182" s="13" t="inlineStr">
         <is>
-          <t>RXT</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="D182" s="14" t="inlineStr">
         <is>
-          <t>Rackspace</t>
+          <t>Rigetti Computing</t>
         </is>
       </c>
       <c r="E182" s="14" t="inlineStr">
@@ -33446,7 +33450,11 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="F182" s="14" t="inlineStr"/>
+      <c r="F182" s="14" t="inlineStr">
+        <is>
+          <t>After close</t>
+        </is>
+      </c>
       <c r="G182" s="29" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -33469,12 +33477,12 @@
       </c>
       <c r="C183" s="13" t="inlineStr">
         <is>
-          <t>SYNA</t>
+          <t>RXT</t>
         </is>
       </c>
       <c r="D183" s="14" t="inlineStr">
         <is>
-          <t>Synaptics</t>
+          <t>Rackspace</t>
         </is>
       </c>
       <c r="E183" s="14" t="inlineStr">
@@ -33482,11 +33490,7 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="F183" s="14" t="inlineStr">
-        <is>
-          <t>After close</t>
-        </is>
-      </c>
+      <c r="F183" s="14" t="inlineStr"/>
       <c r="G183" s="29" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -33509,12 +33513,12 @@
       </c>
       <c r="C184" s="13" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>SYNA</t>
         </is>
       </c>
       <c r="D184" s="14" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Synaptics</t>
         </is>
       </c>
       <c r="E184" s="14" t="inlineStr">
@@ -33549,12 +33553,12 @@
       </c>
       <c r="C185" s="13" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="D185" s="14" t="inlineStr">
         <is>
-          <t>Unity Software</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="E185" s="14" t="inlineStr">
@@ -33564,7 +33568,7 @@
       </c>
       <c r="F185" s="14" t="inlineStr">
         <is>
-          <t>Before open</t>
+          <t>After close</t>
         </is>
       </c>
       <c r="G185" s="29" t="inlineStr">
@@ -33589,17 +33593,17 @@
       </c>
       <c r="C186" s="13" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D186" s="14" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Unity Software</t>
         </is>
       </c>
       <c r="E186" s="14" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F186" s="14" t="inlineStr">
@@ -33620,29 +33624,33 @@
     </row>
     <row r="187">
       <c r="A187" s="28" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="B187" s="14" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="C187" s="13" t="inlineStr">
         <is>
-          <t>BRK.B</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="D187" s="14" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="E187" s="14" t="inlineStr">
         <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F187" s="14" t="inlineStr"/>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F187" s="14" t="inlineStr">
+        <is>
+          <t>Before open</t>
+        </is>
+      </c>
       <c r="G187" s="29" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -33665,24 +33673,20 @@
       </c>
       <c r="C188" s="13" t="inlineStr">
         <is>
-          <t>FLR</t>
+          <t>BRK.B</t>
         </is>
       </c>
       <c r="D188" s="14" t="inlineStr">
         <is>
-          <t>Fluor</t>
+          <t>Berkshire Hathaway</t>
         </is>
       </c>
       <c r="E188" s="14" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="F188" s="14" t="inlineStr">
-        <is>
-          <t>Before open</t>
-        </is>
-      </c>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="F188" s="14" t="inlineStr"/>
       <c r="G188" s="29" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -33696,26 +33700,26 @@
     </row>
     <row r="189">
       <c r="A189" s="28" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="B189" s="14" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="C189" s="13" t="inlineStr">
         <is>
-          <t>CAMT</t>
+          <t>FLR</t>
         </is>
       </c>
       <c r="D189" s="14" t="inlineStr">
         <is>
-          <t>Camtek</t>
+          <t>Fluor</t>
         </is>
       </c>
       <c r="E189" s="14" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F189" s="14" t="inlineStr">
@@ -33745,17 +33749,17 @@
       </c>
       <c r="C190" s="13" t="inlineStr">
         <is>
-          <t>FERG</t>
+          <t>CAMT</t>
         </is>
       </c>
       <c r="D190" s="14" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Camtek</t>
         </is>
       </c>
       <c r="E190" s="14" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="F190" s="14" t="inlineStr">
@@ -33785,20 +33789,24 @@
       </c>
       <c r="C191" s="13" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>FERG</t>
         </is>
       </c>
       <c r="D191" s="14" t="inlineStr">
         <is>
-          <t>Oklo</t>
+          <t>Ferguson</t>
         </is>
       </c>
       <c r="E191" s="14" t="inlineStr">
         <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="F191" s="14" t="inlineStr"/>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="F191" s="14" t="inlineStr">
+        <is>
+          <t>Before open</t>
+        </is>
+      </c>
       <c r="G191" s="29" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -33821,24 +33829,20 @@
       </c>
       <c r="C192" s="13" t="inlineStr">
         <is>
-          <t>SPG</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="D192" s="14" t="inlineStr">
         <is>
-          <t>Simon Property</t>
+          <t>Oklo</t>
         </is>
       </c>
       <c r="E192" s="14" t="inlineStr">
         <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="F192" s="14" t="inlineStr">
-        <is>
-          <t>After close</t>
-        </is>
-      </c>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="F192" s="14" t="inlineStr"/>
       <c r="G192" s="29" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -33852,29 +33856,33 @@
     </row>
     <row r="193">
       <c r="A193" s="28" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="B193" s="14" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="C193" s="13" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>SPG</t>
         </is>
       </c>
       <c r="D193" s="14" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Simon Property</t>
         </is>
       </c>
       <c r="E193" s="14" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="F193" s="14" t="inlineStr"/>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="F193" s="14" t="inlineStr">
+        <is>
+          <t>After close</t>
+        </is>
+      </c>
       <c r="G193" s="29" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -33897,12 +33905,12 @@
       </c>
       <c r="C194" s="13" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="D194" s="14" t="inlineStr">
         <is>
-          <t>Lumentum</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="E194" s="14" t="inlineStr">
@@ -33910,11 +33918,7 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="F194" s="14" t="inlineStr">
-        <is>
-          <t>After close</t>
-        </is>
-      </c>
+      <c r="F194" s="14" t="inlineStr"/>
       <c r="G194" s="29" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -33937,12 +33941,12 @@
       </c>
       <c r="C195" s="13" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="D195" s="14" t="inlineStr">
         <is>
-          <t>Rigetti Computing</t>
+          <t>Lumentum</t>
         </is>
       </c>
       <c r="E195" s="14" t="inlineStr">
@@ -33950,7 +33954,11 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="F195" s="14" t="inlineStr"/>
+      <c r="F195" s="14" t="inlineStr">
+        <is>
+          <t>After close</t>
+        </is>
+      </c>
       <c r="G195" s="29" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -34506,7 +34514,11 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="F210" s="14" t="inlineStr"/>
+      <c r="F210" s="14" t="inlineStr">
+        <is>
+          <t>Before open</t>
+        </is>
+      </c>
       <c r="G210" s="29" t="inlineStr">
         <is>
           <t>Confirmed</t>
@@ -39580,13 +39592,13 @@
       <c r="A15" s="38" t="inlineStr">
         <is>
           <t>3
-AEIS FANG NJR ON PLTR TKO VNOM WMB</t>
+AEIS FANG NJR ON PLTR SRAD TKO VNOM WMB</t>
         </is>
       </c>
       <c r="B15" s="38" t="inlineStr">
         <is>
           <t>4
-ALAB AMD AME AMGN ANET BKNG BR CAT CMI DD DUK EMR EOG ET FOUR GILD GWW HUT IDXX MCD MRK MTCH PFE Q ROK SPOT SRAD SYY WOLF</t>
+ALAB AMD AME AMGN ANET BKNG BR CAT CMI DD DUK EMR EOG ET FOUR GILD GWW HUT IDXX MCD MRK MTCH PFE Q ROK SPOT SYY WOLF</t>
         </is>
       </c>
       <c r="C15" s="38" t="inlineStr">
@@ -39598,7 +39610,7 @@
       <c r="D15" s="38" t="inlineStr">
         <is>
           <t>6
-AAOI ABNB ACLS AFL BDX CEG CLSK COP DDOG MCHP MNST MTSI NBIS NET NVMI ONTO PH QBTS RXT SYNA TWLO U ZTS</t>
+AAOI ABNB ACLS AFL BDX CEG CLSK COP DDOG MCHP MNST MTSI NBIS NET NVMI ONTO PH QBTS RGTI RXT SYNA TWLO U ZTS</t>
         </is>
       </c>
       <c r="E15" s="38" t="inlineStr">
@@ -39628,7 +39640,7 @@
       <c r="B16" s="38" t="inlineStr">
         <is>
           <t>11
-CRWV LITE RGTI SMCI</t>
+CRWV LITE SMCI</t>
         </is>
       </c>
       <c r="C16" s="38" t="inlineStr">
@@ -40664,7 +40676,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of July 26, 2026 at 17:02 UTC</t>
+          <t>Data as of July 27, 2026 at 17:21 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>96.89</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-0.0192</v>
+        <v>-0.0217</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.0659</v>
+        <v>-0.0683</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>46239</v>
@@ -878,7 +878,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="9" t="n">
-        <v>0.2901228196924347</v>
+        <v>0.2933264355923434</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0.4862214882856848</v>
+        <v>0.4899120538023796</v>
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>326.91</v>
+        <v>326.56</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>-0.0311</v>
+        <v>-0.0321</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>-0.162</v>
+        <v>-0.1629</v>
       </c>
       <c r="G3" s="17" t="n">
         <v>46322</v>
@@ -973,7 +973,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="20" t="n">
-        <v>0.3398182986142974</v>
+        <v>0.3412542871141597</v>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="20" t="n">
-        <v>0.2847572726438468</v>
+        <v>0.2861342479176874</v>
       </c>
       <c r="Q3" s="21" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>596.9299999999999</v>
+        <v>593.87</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>0.0848</v>
+        <v>0.0793</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.0604</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>46232</v>
@@ -1064,7 +1064,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="9" t="n">
-        <v>0.3988239827115408</v>
+        <v>0.4060316230824928</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>0.5579716214631533</v>
+        <v>0.5659992927745129</v>
       </c>
       <c r="Q4" s="10" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="E5" s="20" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.04389999999999999</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>0.0699</v>
+        <v>0.06709999999999999</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>46238</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>70.86</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-0.04</v>
+        <v>-0.0462</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-0.1795</v>
+        <v>-0.1848</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>46315</v>
@@ -1220,7 +1220,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>0.1289867344058707</v>
+        <v>0.1363636363636363</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0.4112334180073384</v>
+        <v>0.4204545454545454</v>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>82.63</v>
+        <v>82.41</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>0.1305</v>
+        <v>0.1275</v>
       </c>
       <c r="F7" s="20" t="n">
-        <v>0.1153</v>
+        <v>0.1123</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>46231</v>
@@ -1307,7 +1307,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="20" t="n">
-        <v>0.1012949292024689</v>
+        <v>0.1042349229462444</v>
       </c>
       <c r="N7" s="14" t="inlineStr"/>
       <c r="O7" s="19" t="n"/>
@@ -1351,13 +1351,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>496.36</v>
+        <v>494.72</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.079</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.0394</v>
+        <v>-0.0426</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>46238</v>
@@ -1386,7 +1386,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>0.1482190345716817</v>
+        <v>0.1520253880983181</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>0.3055846562978482</v>
+        <v>0.3099126778783957</v>
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>182.91</v>
+        <v>182.86</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>-0.1527</v>
+        <v>-0.153</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>-0.08789999999999999</v>
+        <v>-0.0882</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>46237</v>
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>180.42</v>
+        <v>177.21</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.0124</v>
+        <v>-0.0299</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0.0454</v>
+        <v>-0.0624</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>46317</v>
@@ -1542,7 +1542,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>-0.05775412925396291</v>
+        <v>-0.0406861915241804</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>0.4965081476554707</v>
+        <v>0.5236160487557134</v>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
@@ -1594,13 +1594,13 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>47.43</v>
+        <v>47.32</v>
       </c>
       <c r="E11" s="20" t="n">
-        <v>0.0191</v>
+        <v>0.0168</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>-0.0121</v>
+        <v>-0.0144</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>46316</v>
@@ -1629,7 +1629,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>-0.09340080118068732</v>
+        <v>-0.09129332206255283</v>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="20" t="n">
-        <v>0.05418511490617753</v>
+        <v>0.0566356720202874</v>
       </c>
       <c r="Q11" s="21" t="inlineStr">
         <is>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>145.95</v>
+        <v>146.86</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.0027</v>
+        <v>0.0089</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>0.0851</v>
+        <v>0.0919</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>46240</v>
@@ -1720,7 +1720,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>0.2401507365536144</v>
+        <v>0.2324662944300693</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>0.06200753682768079</v>
+        <v>0.05542693721912016</v>
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
@@ -1772,13 +1772,13 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>231.86</v>
+        <v>231.39</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>-0.0036</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>-0.1538</v>
+        <v>-0.1555</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>46233</v>
@@ -1807,7 +1807,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="20" t="n">
-        <v>0.3887690847925471</v>
+        <v>0.3915899563507499</v>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="20" t="n">
-        <v>0.2291900284654532</v>
+        <v>0.231686762608583</v>
       </c>
       <c r="Q13" s="21" t="inlineStr">
         <is>
@@ -1871,13 +1871,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3088.13</v>
+        <v>3075.26</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.013</v>
+        <v>-0.0171</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>0.027</v>
+        <v>0.0227</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>46287</v>
@@ -1906,7 +1906,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>0.3438553428774047</v>
+        <v>0.3494793936122473</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>0.1981360888304572</v>
+        <v>0.2031503027386301</v>
       </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>88.59</v>
+        <v>88.45</v>
       </c>
       <c r="E15" s="20" t="n">
-        <v>0.14</v>
+        <v>0.1382</v>
       </c>
       <c r="F15" s="20" t="n">
-        <v>0.1853</v>
+        <v>0.1834</v>
       </c>
       <c r="G15" s="17" t="n">
         <v>46261</v>
@@ -1993,7 +1993,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="16" t="n">
-        <v>-0.2662828761711254</v>
+        <v>-0.2651215375918599</v>
       </c>
       <c r="N15" s="14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>-0.04052376114685634</v>
+        <v>-0.0390050876201244</v>
       </c>
       <c r="Q15" s="21" t="inlineStr"/>
       <c r="R15" s="19" t="n"/>
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>186.23</v>
+        <v>186.79</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.0263</v>
+        <v>0.0294</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0999</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>46238</v>
@@ -2074,7 +2074,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>0.1491166836707298</v>
+        <v>0.14567160982922</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>0.3155775116791065</v>
+        <v>0.3116333850848547</v>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
@@ -2134,13 +2134,13 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>353.3</v>
+        <v>358.01</v>
       </c>
       <c r="E17" s="20" t="n">
-        <v>0.1014</v>
+        <v>0.1161</v>
       </c>
       <c r="F17" s="20" t="n">
-        <v>0.1756</v>
+        <v>0.1913</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>46261</v>
@@ -2169,7 +2169,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="20" t="n">
-        <v>0.06142088876309083</v>
+        <v>0.04745677495042041</v>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="20" t="n">
-        <v>0.06142088876309083</v>
+        <v>0.04745677495042041</v>
       </c>
       <c r="Q17" s="21" t="inlineStr"/>
       <c r="R17" s="19" t="n"/>
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>33.18</v>
+        <v>33.2</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-0.0048</v>
+        <v>-0.0042</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>0.0234</v>
+        <v>0.0241</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>46232</v>
@@ -2254,7 +2254,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>0.3562386980108499</v>
+        <v>0.3554216867469878</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>0.3562386980108499</v>
+        <v>0.3554216867469878</v>
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
@@ -2306,13 +2306,13 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>147.39</v>
+        <v>147.65</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>-0.1137</v>
+        <v>-0.1121</v>
       </c>
       <c r="F19" s="20" t="n">
-        <v>0.0032</v>
+        <v>0.005</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>46324</v>
@@ -2341,7 +2341,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="20" t="n">
-        <v>0.1534025374855826</v>
+        <v>0.1513714866237724</v>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="20" t="n">
-        <v>0.2008955831467536</v>
+        <v>0.1987809007788689</v>
       </c>
       <c r="Q19" s="21" t="inlineStr">
         <is>
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>205.07</v>
+        <v>205.6</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-0.1426</v>
+        <v>-0.1404</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.09380000000000001</v>
+        <v>-0.0915</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>46261</v>
@@ -2428,7 +2428,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>0.07280440825084121</v>
+        <v>0.0700389105058366</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="8" t="n"/>
@@ -2472,13 +2472,13 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>124.11</v>
+        <v>125.54</v>
       </c>
       <c r="E21" s="20" t="n">
-        <v>0.0019</v>
+        <v>0.0135</v>
       </c>
       <c r="F21" s="20" t="n">
-        <v>0.0983</v>
+        <v>0.111</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>46267</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>85.45</v>
+        <v>87.04000000000001</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.0941</v>
+        <v>0.1145</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.013</v>
+        <v>0.0319</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>46315</v>
@@ -2568,7 +2568,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-0.286132241076653</v>
+        <v>-0.2991727941176471</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>0.1702750146284376</v>
+        <v>0.1488970588235293</v>
       </c>
       <c r="Q22" s="10" t="inlineStr">
         <is>
@@ -2620,13 +2620,13 @@
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>127.72</v>
+        <v>127.7</v>
       </c>
       <c r="E23" s="20" t="n">
-        <v>0.1009</v>
+        <v>0.1007</v>
       </c>
       <c r="F23" s="20" t="n">
-        <v>0.2868</v>
+        <v>0.2865</v>
       </c>
       <c r="G23" s="17" t="n">
         <v>46315</v>
@@ -2658,7 +2658,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="20" t="n">
-        <v>0.1352959599123082</v>
+        <v>0.1354737666405638</v>
       </c>
       <c r="Q23" s="21" t="inlineStr"/>
       <c r="R23" s="19" t="n"/>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>337.82</v>
+        <v>336.09</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-0.0316</v>
+        <v>-0.0366</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0.0517</v>
+        <v>0.0463</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>46252</v>
@@ -2728,7 +2728,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>0.06565626665087919</v>
+        <v>0.07114165848433464</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="9" t="n">
-        <v>0.1840625185009769</v>
+        <v>0.1901573983159274</v>
       </c>
       <c r="Q24" s="10" t="inlineStr">
         <is>
@@ -2788,13 +2788,13 @@
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>211.58</v>
+        <v>211.55</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>-0.049</v>
+        <v>-0.0491</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>-0.0291</v>
+        <v>-0.0292</v>
       </c>
       <c r="G25" s="17" t="n">
         <v>46253</v>
@@ -2823,7 +2823,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="20" t="n">
-        <v>0.2052178844881368</v>
+        <v>0.2053887969747104</v>
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="20" t="n">
-        <v>0.08705926836184888</v>
+        <v>0.08721342472228781</v>
       </c>
       <c r="Q25" s="21" t="inlineStr">
         <is>
@@ -2879,13 +2879,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>269.92</v>
+        <v>270.67</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0034</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.029</v>
+        <v>-0.0263</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>46238</v>
@@ -2914,7 +2914,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="9" t="n">
-        <v>0.1114404267931238</v>
+        <v>0.1083607344737133</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="9" t="n">
-        <v>0.2966804979253111</v>
+        <v>0.2930875235526655</v>
       </c>
       <c r="Q26" s="10" t="inlineStr">
         <is>
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>42.12</v>
+        <v>42.14</v>
       </c>
       <c r="E27" s="20" t="n">
-        <v>0.0336</v>
+        <v>0.0341</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>-0.1108</v>
+        <v>-0.1104</v>
       </c>
       <c r="G27" s="17" t="n">
         <v>46289</v>
@@ -3027,13 +3027,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>91.17</v>
+        <v>90.59</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>0.0181</v>
+        <v>0.0116</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>0.0217</v>
+        <v>0.0152</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>46232</v>
@@ -3062,7 +3062,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="9" t="n">
-        <v>0.2065372381265767</v>
+        <v>0.2142620598300033</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0.2613798398596029</v>
+        <v>0.2694557898222761</v>
       </c>
       <c r="Q28" s="10" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>186.5</v>
+        <v>184.61</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>-0.1187</v>
-      </c>
-      <c r="F29" s="20" t="n">
-        <v>0.0097</v>
+        <v>-0.1276</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>-0.0005</v>
       </c>
       <c r="G29" s="17" t="n">
         <v>46317</v>
@@ -3179,13 +3179,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>242.3</v>
+        <v>243.35</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.1362</v>
+        <v>0.1411</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>0.0665</v>
+        <v>0.0711</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>46254</v>
@@ -3214,7 +3214,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="9" t="n">
-        <v>0.01114321089558394</v>
+        <v>0.006780357509759629</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="9" t="n">
-        <v>0.09368551382583569</v>
+        <v>0.08896650914320939</v>
       </c>
       <c r="Q30" s="10" t="inlineStr">
         <is>
@@ -3266,13 +3266,13 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>104</v>
+        <v>103.65</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>0.0323</v>
+        <v>0.0288</v>
       </c>
       <c r="G31" s="17" t="n">
         <v>46232</v>
@@ -3301,7 +3301,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="20" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.1577424023154848</v>
       </c>
       <c r="N31" s="14" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="20" t="n">
-        <v>0.1057692307692308</v>
+        <v>0.1095031355523395</v>
       </c>
       <c r="Q31" s="21" t="inlineStr">
         <is>
@@ -3353,13 +3353,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>14.71</v>
+        <v>14.68</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.0114</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>0.1272</v>
+        <v>0.1249</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>46237</v>
@@ -3414,13 +3414,13 @@
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>156.87</v>
+        <v>156.38</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.0061</v>
       </c>
       <c r="F33" s="20" t="n">
-        <v>0.0128</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="G33" s="17" t="n">
         <v>46253</v>
@@ -3449,7 +3449,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="20" t="n">
-        <v>0.01995282718174281</v>
+        <v>0.0231487402481136</v>
       </c>
       <c r="N33" s="14" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="20" t="n">
-        <v>0.1155734047300312</v>
+        <v>0.1190689346463742</v>
       </c>
       <c r="Q33" s="21" t="inlineStr">
         <is>
@@ -3505,13 +3505,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>31.86</v>
+        <v>31.8</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.0208</v>
+        <v>0.0189</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>0.0156</v>
+        <v>0.0137</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>46317</v>
@@ -3540,7 +3540,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="9" t="n">
-        <v>0.09855618330194603</v>
+        <v>0.10062893081761</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="9" t="n">
-        <v>0.2554927809165097</v>
+        <v>0.2578616352201258</v>
       </c>
       <c r="Q34" s="10" t="inlineStr">
         <is>
@@ -3592,13 +3592,13 @@
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>307.21</v>
+        <v>309.22</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>-0.1909</v>
+        <v>-0.1856</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>-0.3051</v>
+        <v>-0.3006</v>
       </c>
       <c r="G35" s="17" t="n">
         <v>46323</v>
@@ -3627,7 +3627,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="16" t="n">
-        <v>-0.5768366915139481</v>
+        <v>-0.5795873488131428</v>
       </c>
       <c r="N35" s="14" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>-0.02346928810911097</v>
+        <v>-0.02981695879956027</v>
       </c>
       <c r="Q35" s="21" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>67.79000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>-0.1104</v>
+        <v>-0.1052</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-0.0442</v>
+        <v>-0.0386</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>46239</v>
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="D37" s="15" t="n">
-        <v>480.23</v>
+        <v>480.51</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>-0.0168</v>
+        <v>-0.0163</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0762</v>
       </c>
       <c r="G37" s="17" t="n">
         <v>46261</v>
@@ -3775,7 +3775,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="16" t="n">
-        <v>-0.06294900360244053</v>
+        <v>-0.06349503652369355</v>
       </c>
       <c r="N37" s="14" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="20" t="n">
-        <v>0.3222830726943339</v>
+        <v>0.3215125595721213</v>
       </c>
       <c r="Q37" s="21" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>98.98</v>
+        <v>98.7</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>0.0138</v>
+        <v>0.011</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>46234</v>
@@ -3866,7 +3866,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="9" t="n">
-        <v>0.1113356233582541</v>
+        <v>0.1144883485309017</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="9" t="n">
-        <v>0.06082036775106078</v>
+        <v>0.06382978723404252</v>
       </c>
       <c r="Q38" s="10" t="inlineStr">
         <is>
@@ -3922,13 +3922,13 @@
         </is>
       </c>
       <c r="D39" s="15" t="n">
-        <v>91.69</v>
+        <v>91.98</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>-0.004099999999999999</v>
+        <v>-0.001</v>
       </c>
       <c r="F39" s="20" t="n">
-        <v>0.0004</v>
+        <v>0.0035</v>
       </c>
       <c r="G39" s="17" t="n">
         <v>46234</v>
@@ -3957,7 +3957,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="20" t="n">
-        <v>0.03609990184316722</v>
+        <v>0.03283322461404649</v>
       </c>
       <c r="N39" s="14" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="20" t="n">
-        <v>0.09063147562438655</v>
+        <v>0.08719286801478578</v>
       </c>
       <c r="Q39" s="21" t="inlineStr">
         <is>
@@ -4013,13 +4013,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>950.27</v>
+        <v>951.58</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.001</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-0.0451</v>
+        <v>-0.0438</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>46289</v>
@@ -4048,7 +4048,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="9" t="n">
-        <v>0.05233249497511236</v>
+        <v>0.05088379327014014</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="9" t="n">
-        <v>0.1575657444726236</v>
+        <v>0.1559721725971542</v>
       </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
@@ -4108,13 +4108,13 @@
         </is>
       </c>
       <c r="D41" s="15" t="n">
-        <v>123.57</v>
+        <v>123.22</v>
       </c>
       <c r="E41" s="20" t="n">
-        <v>0.0339</v>
+        <v>0.031</v>
       </c>
       <c r="F41" s="20" t="n">
-        <v>0.1244</v>
+        <v>0.1212</v>
       </c>
       <c r="G41" s="17" t="n">
         <v>46261</v>
@@ -4143,7 +4143,7 @@
         <v>125</v>
       </c>
       <c r="M41" s="20" t="n">
-        <v>0.01157238812009393</v>
+        <v>0.01444570686576855</v>
       </c>
       <c r="N41" s="14" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="20" t="n">
-        <v>0.09249817916970145</v>
+        <v>0.09560136341503003</v>
       </c>
       <c r="Q41" s="21" t="inlineStr">
         <is>
@@ -4198,10 +4198,10 @@
         <v>26.22</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.1061</v>
+        <v>0.1063</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>0.0713</v>
+        <v>0.07150000000000001</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>46239</v>
@@ -4256,13 +4256,13 @@
         </is>
       </c>
       <c r="D43" s="15" t="n">
-        <v>83.7</v>
+        <v>84.06999999999999</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>0.0129</v>
+        <v>0.0174</v>
       </c>
       <c r="F43" s="20" t="n">
-        <v>0.0409</v>
+        <v>0.0455</v>
       </c>
       <c r="G43" s="17" t="n">
         <v>46231</v>
@@ -4291,7 +4291,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="20" t="n">
-        <v>0.07526881720430104</v>
+        <v>0.07053645771381001</v>
       </c>
       <c r="N43" s="14" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>88</v>
       </c>
       <c r="P43" s="20" t="n">
-        <v>0.05137395459976102</v>
+        <v>0.04674675865350312</v>
       </c>
       <c r="Q43" s="21" t="inlineStr">
         <is>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>58.21</v>
+        <v>57.98</v>
       </c>
       <c r="E44" s="9" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.0043</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>-0.0857</v>
+        <v>-0.0892</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>46275</v>
@@ -4385,8 +4385,8 @@
       <c r="L44" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="M44" s="5" t="n">
-        <v>-0.003607627555402866</v>
+      <c r="M44" s="9" t="n">
+        <v>0.0003449465332873944</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="9" t="n">
-        <v>0.3399759491496306</v>
+        <v>0.3452914798206279</v>
       </c>
       <c r="Q44" s="10" t="inlineStr">
         <is>
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="D45" s="15" t="n">
-        <v>60.66</v>
+        <v>60.67</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>-0.0021</v>
+        <v>-0.002</v>
       </c>
       <c r="F45" s="16" t="n">
-        <v>-0.0277</v>
+        <v>-0.0276</v>
       </c>
       <c r="G45" s="17" t="n">
         <v>46231</v>
@@ -4473,7 +4473,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="20" t="n">
-        <v>0.1539729640619849</v>
+        <v>0.1537827591890555</v>
       </c>
       <c r="N45" s="14" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="20" t="n">
-        <v>0.1704582921200133</v>
+        <v>0.1702653700346135</v>
       </c>
       <c r="Q45" s="21" t="inlineStr">
         <is>
@@ -4533,13 +4533,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>50.9</v>
+        <v>50.61</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0086</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>0.08689999999999999</v>
+        <v>0.08070000000000001</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>46301</v>
@@ -4604,13 +4604,13 @@
         </is>
       </c>
       <c r="D47" s="15" t="n">
-        <v>95.29000000000001</v>
+        <v>95.33</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>-0.0113</v>
+        <v>-0.0109</v>
       </c>
       <c r="F47" s="20" t="n">
-        <v>0.083</v>
+        <v>0.0834</v>
       </c>
       <c r="G47" s="17" t="n">
         <v>46240</v>
@@ -4665,13 +4665,13 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>72.98999999999999</v>
+        <v>72.89</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0122</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>0.0141</v>
+        <v>0.0128</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>46233</v>
@@ -4726,13 +4726,13 @@
         </is>
       </c>
       <c r="D49" s="15" t="n">
-        <v>139.69</v>
+        <v>139.79</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>-0.012</v>
+        <v>-0.0113</v>
       </c>
       <c r="F49" s="16" t="n">
-        <v>-0.0451</v>
+        <v>-0.0444</v>
       </c>
       <c r="G49" s="17" t="n">
         <v>46303</v>
@@ -4761,7 +4761,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="20" t="n">
-        <v>0.002219199656382005</v>
+        <v>0.001502253380070162</v>
       </c>
       <c r="N49" s="14" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="20" t="n">
-        <v>0.07380628534612357</v>
+        <v>0.07303812862150375</v>
       </c>
       <c r="Q49" s="21" t="inlineStr">
         <is>
@@ -4821,13 +4821,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>148.8</v>
+        <v>148.63</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0026</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>0.0198</v>
+        <v>0.0186</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>46232</v>
@@ -4856,7 +4856,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="9" t="n">
-        <v>0.1021505376344085</v>
+        <v>0.1034111552176546</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="9" t="n">
-        <v>0.08870967741935476</v>
+        <v>0.08995492161743932</v>
       </c>
       <c r="Q50" s="10" t="inlineStr">
         <is>
@@ -4920,13 +4920,13 @@
         </is>
       </c>
       <c r="D51" s="15" t="n">
-        <v>83.72</v>
+        <v>84.09</v>
       </c>
       <c r="E51" s="20" t="n">
-        <v>0.0109</v>
+        <v>0.0153</v>
       </c>
       <c r="F51" s="20" t="n">
-        <v>0.1027</v>
+        <v>0.1076</v>
       </c>
       <c r="G51" s="17" t="n">
         <v>46238</v>
@@ -4955,7 +4955,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="20" t="n">
-        <v>0.1944577161968467</v>
+        <v>0.1892020454275181</v>
       </c>
       <c r="N51" s="14" t="inlineStr"/>
       <c r="O51" s="19" t="n"/>
@@ -4999,13 +4999,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>139.97</v>
+        <v>140.34</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0004</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>46253</v>
@@ -5033,8 +5033,8 @@
       <c r="L52" s="8" t="n">
         <v>140</v>
       </c>
-      <c r="M52" s="9" t="n">
-        <v>0.0002143316424948284</v>
+      <c r="M52" s="5" t="n">
+        <v>-0.002422687758301293</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>-0.03550760877330856</v>
+        <v>-0.03805044890979054</v>
       </c>
       <c r="Q52" s="10" t="inlineStr">
         <is>
@@ -5090,13 +5090,13 @@
         </is>
       </c>
       <c r="D53" s="15" t="n">
-        <v>111.44</v>
+        <v>111.74</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>-0.0367</v>
+        <v>-0.0341</v>
       </c>
       <c r="F53" s="16" t="n">
-        <v>-0.06269999999999999</v>
+        <v>-0.0602</v>
       </c>
       <c r="G53" s="17" t="n">
         <v>46254</v>
@@ -5125,7 +5125,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="20" t="n">
-        <v>0.2562814070351759</v>
+        <v>0.2529085376767496</v>
       </c>
       <c r="N53" s="14" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="20" t="n">
-        <v>0.2562814070351759</v>
+        <v>0.2529085376767496</v>
       </c>
       <c r="Q53" s="21" t="inlineStr">
         <is>
@@ -5185,13 +5185,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>60.72</v>
+        <v>60.59</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>0.0736</v>
+        <v>0.0713</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>-0.0616</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="G54" s="6" t="n">
         <v>46316</v>
@@ -5227,7 +5227,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="9" t="n">
-        <v>0.2516469038208169</v>
+        <v>0.2543323980854926</v>
       </c>
       <c r="Q54" s="10" t="inlineStr">
         <is>
@@ -5268,13 +5268,13 @@
         </is>
       </c>
       <c r="D55" s="15" t="n">
-        <v>117.17</v>
+        <v>115.58</v>
       </c>
       <c r="E55" s="20" t="n">
-        <v>0.1057</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="F55" s="20" t="n">
-        <v>0.0189</v>
+        <v>0.0051</v>
       </c>
       <c r="G55" s="17" t="n">
         <v>46240</v>
@@ -5303,7 +5303,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="20" t="n">
-        <v>0.5618332337629086</v>
+        <v>0.5833189133068005</v>
       </c>
       <c r="N55" s="14" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="20" t="n">
-        <v>0.2375181360416489</v>
+        <v>0.2545423083578474</v>
       </c>
       <c r="Q55" s="21" t="inlineStr">
         <is>
@@ -5355,13 +5355,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>191.71</v>
+        <v>190</v>
       </c>
       <c r="E56" s="9" t="n">
-        <v>0.1207</v>
+        <v>0.1107</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>0.0475</v>
+        <v>0.0381</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>46234</v>
@@ -5390,7 +5390,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="9" t="n">
-        <v>0.1579990610818423</v>
+        <v>0.1684210526315789</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="9" t="n">
-        <v>0.1736476970424078</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="Q56" s="10" t="inlineStr">
         <is>
@@ -5446,13 +5446,13 @@
         </is>
       </c>
       <c r="D57" s="15" t="n">
-        <v>142.13</v>
+        <v>140.31</v>
       </c>
       <c r="E57" s="20" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0581</v>
       </c>
       <c r="F57" s="20" t="n">
-        <v>0.0561</v>
+        <v>0.0426</v>
       </c>
       <c r="G57" s="17" t="n">
         <v>46238</v>
@@ -5481,7 +5481,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="20" t="n">
-        <v>0.3790192077675368</v>
+        <v>0.3969068491198061</v>
       </c>
       <c r="N57" s="14" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="20" t="n">
-        <v>0.1960880883698023</v>
+        <v>0.2116028793386074</v>
       </c>
       <c r="Q57" s="21" t="inlineStr">
         <is>
@@ -5537,13 +5537,13 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>38.35</v>
+        <v>38.12</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>0.0488</v>
+        <v>0.0424</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>0.0228</v>
+        <v>0.0165</v>
       </c>
       <c r="G58" s="6" t="n">
         <v>46233</v>
@@ -5598,13 +5598,13 @@
         </is>
       </c>
       <c r="D59" s="15" t="n">
-        <v>19.98</v>
+        <v>19.91</v>
       </c>
       <c r="E59" s="20" t="n">
-        <v>0.042</v>
+        <v>0.0386</v>
       </c>
       <c r="F59" s="20" t="n">
-        <v>0.0286</v>
+        <v>0.0252</v>
       </c>
       <c r="G59" s="17" t="n">
         <v>46238</v>
@@ -5659,13 +5659,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>199.47</v>
+        <v>195.8</v>
       </c>
       <c r="E60" s="9" t="n">
-        <v>0.1087</v>
+        <v>0.0883</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>0.0275</v>
+        <v>0.0086</v>
       </c>
       <c r="G60" s="6" t="n">
         <v>46237</v>
@@ -5720,13 +5720,13 @@
         </is>
       </c>
       <c r="D61" s="15" t="n">
-        <v>32.58</v>
+        <v>32.13</v>
       </c>
       <c r="E61" s="16" t="n">
-        <v>-0.0478</v>
+        <v>-0.0608</v>
       </c>
       <c r="F61" s="16" t="n">
-        <v>-0.1718</v>
+        <v>-0.1831</v>
       </c>
       <c r="G61" s="17" t="n">
         <v>46315</v>
@@ -5762,7 +5762,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="20" t="n">
-        <v>0.319828115408226</v>
+        <v>0.3383131030189853</v>
       </c>
       <c r="Q61" s="21" t="inlineStr">
         <is>
@@ -5807,13 +5807,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>31.93</v>
+        <v>31.75</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>-0.0378</v>
-      </c>
-      <c r="F62" s="9" t="n">
-        <v>0.0008</v>
+        <v>-0.0434</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>-0.005</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>46316</v>
@@ -5842,7 +5842,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="9" t="n">
-        <v>0.0961478233636079</v>
+        <v>0.1023622047244094</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="8" t="n"/>
@@ -5886,13 +5886,13 @@
         </is>
       </c>
       <c r="D63" s="15" t="n">
-        <v>207.05</v>
+        <v>207.82</v>
       </c>
       <c r="E63" s="20" t="n">
-        <v>0.2062</v>
+        <v>0.2107</v>
       </c>
       <c r="F63" s="20" t="n">
-        <v>0.1717</v>
+        <v>0.1761</v>
       </c>
       <c r="G63" s="17" t="n">
         <v>46239</v>
@@ -5947,13 +5947,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>52.32</v>
+        <v>51.53</v>
       </c>
       <c r="E64" s="9" t="n">
-        <v>0.1132</v>
+        <v>0.0964</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>-0.0508</v>
+        <v>-0.06509999999999999</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>46311</v>
@@ -5989,7 +5989,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="9" t="n">
-        <v>0.2041284403669725</v>
+        <v>0.2225887832330681</v>
       </c>
       <c r="Q64" s="10" t="inlineStr">
         <is>
@@ -6038,13 +6038,13 @@
         </is>
       </c>
       <c r="D65" s="15" t="n">
-        <v>43.6</v>
+        <v>43.04</v>
       </c>
       <c r="E65" s="20" t="n">
-        <v>0.0243</v>
+        <v>0.011</v>
       </c>
       <c r="F65" s="16" t="n">
-        <v>-0.031</v>
+        <v>-0.0436</v>
       </c>
       <c r="G65" s="17" t="n">
         <v>46237</v>
@@ -6099,13 +6099,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>71.70999999999999</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.0915</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>-0.0195</v>
+        <v>-0.032</v>
       </c>
       <c r="G66" s="6" t="n">
         <v>46237</v>
@@ -6134,7 +6134,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="9" t="n">
-        <v>0.2411100264956074</v>
+        <v>0.257239723124735</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="8" t="n"/>
@@ -6190,13 +6190,13 @@
         </is>
       </c>
       <c r="D67" s="15" t="n">
-        <v>154.65</v>
+        <v>154.77</v>
       </c>
       <c r="E67" s="20" t="n">
-        <v>0.1326</v>
+        <v>0.1335</v>
       </c>
       <c r="F67" s="20" t="n">
-        <v>0.05230000000000001</v>
+        <v>0.05309999999999999</v>
       </c>
       <c r="G67" s="17" t="n">
         <v>46234</v>
@@ -6225,7 +6225,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="20" t="n">
-        <v>0.196249595861623</v>
+        <v>0.1953220908444788</v>
       </c>
       <c r="N67" s="14" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="20" t="n">
-        <v>0.196249595861623</v>
+        <v>0.1953220908444788</v>
       </c>
       <c r="Q67" s="21" t="inlineStr">
         <is>
@@ -6281,13 +6281,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>126.23</v>
+        <v>126.56</v>
       </c>
       <c r="E68" s="9" t="n">
-        <v>0.0506</v>
+        <v>0.0533</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>0.1207</v>
+        <v>0.1237</v>
       </c>
       <c r="G68" s="6" t="n">
         <v>46240</v>
@@ -6316,7 +6316,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>-0.04935435316485783</v>
+        <v>-0.05183312262958283</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>115</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>-0.08896458844965542</v>
+        <v>-0.0913400758533502</v>
       </c>
       <c r="Q68" s="10" t="inlineStr"/>
       <c r="R68" s="8" t="n"/>
@@ -6362,13 +6362,13 @@
         </is>
       </c>
       <c r="D69" s="15" t="n">
-        <v>369.28</v>
+        <v>367.17</v>
       </c>
       <c r="E69" s="20" t="n">
-        <v>0.1235</v>
+        <v>0.1171</v>
       </c>
       <c r="F69" s="20" t="n">
-        <v>0.1602</v>
+        <v>0.1535</v>
       </c>
       <c r="G69" s="17" t="n">
         <v>46232</v>
@@ -6397,7 +6397,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="20" t="n">
-        <v>0.09943674176776438</v>
+        <v>0.1057548274641174</v>
       </c>
       <c r="N69" s="14" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="20" t="n">
-        <v>0.1806759098786829</v>
+        <v>0.1874608491979192</v>
       </c>
       <c r="Q69" s="21" t="inlineStr">
         <is>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>333.34</v>
+        <v>335.39</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>-0.0206</v>
+        <v>-0.0146</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>0.0578</v>
+        <v>0.0643</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>46311</v>
@@ -6480,7 +6480,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="9" t="n">
-        <v>0.2449751004979901</v>
+        <v>0.2373654551417753</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="9" t="n">
-        <v>0.139977200455991</v>
+        <v>0.133009332418975</v>
       </c>
       <c r="Q70" s="10" t="inlineStr">
         <is>
@@ -6540,13 +6540,13 @@
         </is>
       </c>
       <c r="D71" s="15" t="n">
-        <v>61.91</v>
+        <v>62.13</v>
       </c>
       <c r="E71" s="20" t="n">
-        <v>0.0696</v>
+        <v>0.07339999999999999</v>
       </c>
       <c r="F71" s="20" t="n">
-        <v>0.2194</v>
+        <v>0.2238</v>
       </c>
       <c r="G71" s="17" t="n">
         <v>46309</v>
@@ -6601,13 +6601,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1055.34</v>
+        <v>1062.14</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>0.094</v>
+        <v>0.101</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.015</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>46308</v>
@@ -6639,7 +6639,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="9" t="n">
-        <v>0.1797145943487408</v>
+        <v>0.1721618619014441</v>
       </c>
       <c r="Q72" s="10" t="inlineStr">
         <is>
@@ -6684,13 +6684,13 @@
         </is>
       </c>
       <c r="D73" s="15" t="n">
-        <v>22.69</v>
+        <v>22.8</v>
       </c>
       <c r="E73" s="16" t="n">
-        <v>-0.0258</v>
+        <v>-0.021</v>
       </c>
       <c r="F73" s="16" t="n">
-        <v>-0.3666</v>
+        <v>-0.3635</v>
       </c>
       <c r="G73" s="17" t="n">
         <v>46281</v>
@@ -6745,13 +6745,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>17.57</v>
+        <v>17.92</v>
       </c>
       <c r="E74" s="9" t="n">
-        <v>0.2954</v>
+        <v>0.3215</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>46346</v>
@@ -6806,13 +6806,13 @@
         </is>
       </c>
       <c r="D75" s="15" t="n">
-        <v>494.46</v>
+        <v>497.18</v>
       </c>
       <c r="E75" s="16" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.003</v>
       </c>
       <c r="F75" s="20" t="n">
-        <v>0.0357</v>
+        <v>0.0414</v>
       </c>
       <c r="G75" s="17" t="n">
         <v>46241</v>
@@ -6889,13 +6889,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>69.78</v>
+        <v>69.7</v>
       </c>
       <c r="E76" s="9" t="n">
-        <v>0.0866</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>0.2277</v>
+        <v>0.2262</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>46230</v>
@@ -6924,7 +6924,7 @@
         <v>68</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>-0.02550874175981658</v>
+        <v>-0.02439024390243906</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="8" t="n"/>
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="D77" s="15" t="n">
-        <v>130.88</v>
+        <v>132.6</v>
       </c>
       <c r="E77" s="20" t="n">
-        <v>0.1341</v>
+        <v>0.149</v>
       </c>
       <c r="F77" s="20" t="n">
-        <v>0.1269</v>
+        <v>0.1417</v>
       </c>
       <c r="G77" s="17" t="n">
         <v>46310</v>
@@ -7031,13 +7031,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>131.2</v>
+        <v>133.1</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>-0.0745</v>
+        <v>-0.0611</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>0.05230000000000001</v>
+        <v>0.0675</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>46308</v>
@@ -7069,7 +7069,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="9" t="n">
-        <v>0.0670731707317074</v>
+        <v>0.05184072126220891</v>
       </c>
       <c r="Q78" s="10" t="inlineStr">
         <is>
@@ -7118,13 +7118,13 @@
         </is>
       </c>
       <c r="D79" s="15" t="n">
-        <v>358.07</v>
+        <v>358.91</v>
       </c>
       <c r="E79" s="20" t="n">
-        <v>0.0487</v>
+        <v>0.0512</v>
       </c>
       <c r="F79" s="20" t="n">
-        <v>0.1323</v>
+        <v>0.135</v>
       </c>
       <c r="G79" s="17" t="n">
         <v>46315</v>
@@ -7153,7 +7153,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="16" t="n">
-        <v>-0.0001954925014661747</v>
+        <v>-0.002535454570783832</v>
       </c>
       <c r="N79" s="14" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="20" t="n">
-        <v>0.04448850783366383</v>
+        <v>0.04204396645398561</v>
       </c>
       <c r="Q79" s="21" t="inlineStr">
         <is>
@@ -7209,13 +7209,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>59.08</v>
+        <v>59</v>
       </c>
       <c r="E80" s="9" t="n">
-        <v>0.0222</v>
+        <v>0.0209</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>0.1358</v>
+        <v>0.1344</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>46310</v>
@@ -7244,7 +7244,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>-0.03520649966147594</v>
+        <v>-0.03389830508474576</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="8" t="n"/>
@@ -7286,13 +7286,13 @@
         </is>
       </c>
       <c r="D81" s="15" t="n">
-        <v>13.92</v>
+        <v>14.02</v>
       </c>
       <c r="E81" s="16" t="n">
-        <v>-0.1476</v>
+        <v>-0.1412</v>
       </c>
       <c r="F81" s="16" t="n">
-        <v>-0.2326</v>
+        <v>-0.2268</v>
       </c>
       <c r="G81" s="17" t="n">
         <v>46240</v>
@@ -7347,13 +7347,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>379.34</v>
+        <v>379.71</v>
       </c>
       <c r="E82" s="9" t="n">
-        <v>0.1409</v>
+        <v>0.1421</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>0.0765</v>
+        <v>0.0776</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>46239</v>
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="D83" s="15" t="n">
-        <v>63.74</v>
+        <v>65.67</v>
       </c>
       <c r="E83" s="16" t="n">
-        <v>-0.1336</v>
+        <v>-0.1074</v>
       </c>
       <c r="F83" s="16" t="n">
-        <v>-0.4111</v>
+        <v>-0.3933</v>
       </c>
       <c r="G83" s="17" t="n">
         <v>46239</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>49.84</v>
+        <v>49.97</v>
       </c>
       <c r="E84" s="9" t="n">
-        <v>0.046</v>
+        <v>0.0487</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>0.1371</v>
+        <v>0.1401</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>46238</v>
@@ -7542,13 +7542,13 @@
         </is>
       </c>
       <c r="D85" s="15" t="n">
-        <v>1035.75</v>
+        <v>1048.23</v>
       </c>
       <c r="E85" s="20" t="n">
-        <v>0.0158</v>
+        <v>0.0281</v>
       </c>
       <c r="F85" s="20" t="n">
-        <v>0.0272</v>
+        <v>0.0395</v>
       </c>
       <c r="G85" s="17" t="n">
         <v>46308</v>
@@ -7577,7 +7577,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="20" t="n">
-        <v>0.2792662321988897</v>
+        <v>0.2640355647138509</v>
       </c>
       <c r="N85" s="14" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="20" t="n">
-        <v>0.1682355780835144</v>
+        <v>0.1543268175877431</v>
       </c>
       <c r="Q85" s="21" t="inlineStr">
         <is>
@@ -7629,13 +7629,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>141.73</v>
+        <v>141.25</v>
       </c>
       <c r="E86" s="9" t="n">
-        <v>0.023</v>
+        <v>0.0195</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-0.0277</v>
+        <v>-0.031</v>
       </c>
       <c r="G86" s="6" t="n">
         <v>46232</v>
@@ -7690,13 +7690,13 @@
         </is>
       </c>
       <c r="D87" s="15" t="n">
-        <v>94.40000000000001</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>-0.0435</v>
+        <v>-0.0308</v>
       </c>
       <c r="F87" s="20" t="n">
-        <v>0.1127</v>
+        <v>0.1274</v>
       </c>
       <c r="G87" s="17" t="n">
         <v>46232</v>
@@ -7751,13 +7751,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>102.53</v>
+        <v>104.59</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>-0.1666</v>
+        <v>-0.1498</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.1748</v>
+        <v>-0.1582</v>
       </c>
       <c r="G88" s="6" t="n">
         <v>46238</v>
@@ -7812,13 +7812,13 @@
         </is>
       </c>
       <c r="D89" s="15" t="n">
-        <v>147.75</v>
+        <v>148.73</v>
       </c>
       <c r="E89" s="20" t="n">
-        <v>0.1929</v>
-      </c>
-      <c r="F89" s="16" t="n">
-        <v>-0.0037</v>
+        <v>0.2008</v>
+      </c>
+      <c r="F89" s="20" t="n">
+        <v>0.0029</v>
       </c>
       <c r="G89" s="17" t="n">
         <v>46233</v>
@@ -7873,13 +7873,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>154.48</v>
+        <v>152.98</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>0.1443</v>
+        <v>0.1332</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>0.134</v>
+        <v>0.123</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>46252</v>
@@ -7948,13 +7948,13 @@
         </is>
       </c>
       <c r="D91" s="15" t="n">
-        <v>352.92</v>
+        <v>356.2</v>
       </c>
       <c r="E91" s="20" t="n">
-        <v>0.0725</v>
+        <v>0.0825</v>
       </c>
       <c r="F91" s="20" t="n">
-        <v>0.1893</v>
+        <v>0.2004</v>
       </c>
       <c r="G91" s="17" t="n">
         <v>46308</v>
@@ -7983,7 +7983,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="16" t="n">
-        <v>-0.4446333446673467</v>
+        <v>-0.4497473329590118</v>
       </c>
       <c r="N91" s="14" t="inlineStr"/>
       <c r="O91" s="19" t="n"/>
@@ -8027,13 +8027,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>100.69</v>
+        <v>101.63</v>
       </c>
       <c r="E92" s="9" t="n">
-        <v>0.1172</v>
+        <v>0.1276</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>0.0708</v>
+        <v>0.0808</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>46233</v>
@@ -8062,7 +8062,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="9" t="n">
-        <v>2.724302314033171</v>
+        <v>2.68985535766998</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="9" t="n">
-        <v>2.654782004171218</v>
+        <v>2.62097805766014</v>
       </c>
       <c r="Q92" s="10" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         </is>
       </c>
       <c r="D93" s="15" t="n">
-        <v>361.53</v>
+        <v>361.55</v>
       </c>
       <c r="E93" s="20" t="n">
         <v>0.1008</v>
@@ -8164,7 +8164,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="16" t="n">
-        <v>-0.6819074488977401</v>
+        <v>-0.6819250449453741</v>
       </c>
       <c r="Q93" s="21" t="inlineStr">
         <is>
@@ -8213,13 +8213,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>551.84</v>
+        <v>551.71</v>
       </c>
       <c r="E94" s="9" t="n">
-        <v>0.1058</v>
+        <v>0.1056</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>0.1176</v>
+        <v>0.1174</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>46233</v>
@@ -8248,7 +8248,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>-0.3367642795013048</v>
+        <v>-0.3366080005800149</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="8" t="n"/>
@@ -8290,13 +8290,13 @@
         </is>
       </c>
       <c r="D95" s="15" t="n">
-        <v>2011.25</v>
+        <v>2014.95</v>
       </c>
       <c r="E95" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.04940000000000001</v>
       </c>
       <c r="F95" s="20" t="n">
-        <v>0.08929999999999999</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="G95" s="17" t="n">
         <v>46232</v>
@@ -8361,13 +8361,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>212.21</v>
+        <v>214.56</v>
       </c>
       <c r="E96" s="9" t="n">
-        <v>0.0008</v>
+        <v>0.0119</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>0.0413</v>
+        <v>0.0528</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>46309</v>
@@ -8396,7 +8396,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="9" t="n">
-        <v>2.147825267423778</v>
+        <v>2.113348247576436</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="9" t="n">
-        <v>1.591772301022572</v>
+        <v>1.563385533184191</v>
       </c>
       <c r="Q96" s="10" t="inlineStr">
         <is>
@@ -8456,13 +8456,13 @@
         </is>
       </c>
       <c r="D97" s="15" t="n">
-        <v>110.6</v>
+        <v>111.29</v>
       </c>
       <c r="E97" s="20" t="n">
-        <v>0.0265</v>
+        <v>0.0329</v>
       </c>
       <c r="F97" s="20" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0771</v>
       </c>
       <c r="G97" s="17" t="n">
         <v>46230</v>
@@ -8491,7 +8491,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="20" t="n">
-        <v>1.16998191681736</v>
+        <v>1.156527989936202</v>
       </c>
       <c r="N97" s="14" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="20" t="n">
-        <v>1.16998191681736</v>
+        <v>1.156527989936202</v>
       </c>
       <c r="Q97" s="21" t="inlineStr">
         <is>
@@ -8551,13 +8551,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>248.43</v>
+        <v>249.64</v>
       </c>
       <c r="E98" s="9" t="n">
-        <v>0.0141</v>
+        <v>0.019</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>0.1304</v>
+        <v>0.1359</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>46310</v>
@@ -8586,7 +8586,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>-0.5451435011874572</v>
+        <v>-0.5473481813811889</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="5" t="n">
-        <v>-0.5411182224369038</v>
+        <v>-0.5433424130748278</v>
       </c>
       <c r="Q98" s="10" t="inlineStr"/>
       <c r="R98" s="8" t="n"/>
@@ -8636,13 +8636,13 @@
         </is>
       </c>
       <c r="D99" s="15" t="n">
-        <v>21.25</v>
+        <v>21.97</v>
       </c>
       <c r="E99" s="16" t="n">
-        <v>-0.2562</v>
+        <v>-0.231</v>
       </c>
       <c r="F99" s="16" t="n">
-        <v>-0.234</v>
+        <v>-0.208</v>
       </c>
       <c r="G99" s="17" t="n">
         <v>46233</v>
@@ -8697,13 +8697,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>13.84</v>
+        <v>13.99</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>0.0336</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>0.1152</v>
+        <v>0.1273</v>
       </c>
       <c r="G100" s="6" t="n">
         <v>46323</v>
@@ -8758,13 +8758,13 @@
         </is>
       </c>
       <c r="D101" s="15" t="n">
-        <v>100.18</v>
+        <v>101.52</v>
       </c>
       <c r="E101" s="20" t="n">
-        <v>0.1482</v>
+        <v>0.1636</v>
       </c>
       <c r="F101" s="20" t="n">
-        <v>0.1307</v>
+        <v>0.1458</v>
       </c>
       <c r="G101" s="17" t="n">
         <v>46323</v>
@@ -8793,7 +8793,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="20" t="n">
-        <v>1.844879217408664</v>
+        <v>1.807328605200946</v>
       </c>
       <c r="N101" s="14" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="20" t="n">
-        <v>1.844879217408664</v>
+        <v>1.807328605200946</v>
       </c>
       <c r="Q101" s="21" t="inlineStr">
         <is>
@@ -8845,13 +8845,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>441.14</v>
+        <v>439.83</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>0.1424</v>
+        <v>0.139</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>0.1164</v>
+        <v>0.1131</v>
       </c>
       <c r="G102" s="6" t="n">
         <v>46231</v>
@@ -8920,13 +8920,13 @@
         </is>
       </c>
       <c r="D103" s="15" t="n">
-        <v>51.86</v>
+        <v>52.12</v>
       </c>
       <c r="E103" s="20" t="n">
-        <v>0.0271</v>
+        <v>0.0323</v>
       </c>
       <c r="F103" s="20" t="n">
-        <v>0.0849</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="G103" s="17" t="n">
         <v>46311</v>
@@ -8981,13 +8981,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>362.71</v>
+        <v>362.53</v>
       </c>
       <c r="E104" s="9" t="n">
-        <v>0.0788</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>0.1162</v>
+        <v>0.1156</v>
       </c>
       <c r="G104" s="6" t="n">
         <v>46231</v>
@@ -9016,7 +9016,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="9" t="n">
-        <v>0.4474373466405669</v>
+        <v>0.4481560146746477</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="9" t="n">
-        <v>0.4970637699539578</v>
+        <v>0.4978070780349214</v>
       </c>
       <c r="Q104" s="10" t="inlineStr">
         <is>
@@ -9072,13 +9072,13 @@
         </is>
       </c>
       <c r="D105" s="15" t="n">
-        <v>75.54000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="E105" s="20" t="n">
-        <v>0.0599</v>
+        <v>0.0622</v>
       </c>
       <c r="F105" s="20" t="n">
-        <v>0.1748</v>
+        <v>0.1773</v>
       </c>
       <c r="G105" s="17" t="n">
         <v>46314</v>
@@ -9107,7 +9107,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="20" t="n">
-        <v>4.454064072014826</v>
+        <v>4.442536327608983</v>
       </c>
       <c r="N105" s="14" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="20" t="n">
-        <v>3.633306857294148</v>
+        <v>3.623513870541612</v>
       </c>
       <c r="Q105" s="21" t="inlineStr">
         <is>
@@ -9163,13 +9163,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>79.84999999999999</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>0.0261</v>
+        <v>0.04389999999999999</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.09269999999999999</v>
       </c>
       <c r="G106" s="6" t="n">
         <v>46239</v>
@@ -9198,7 +9198,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>-0.1484032561051972</v>
+        <v>-0.1629739044805514</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="5" t="n">
-        <v>-0.1484032561051972</v>
+        <v>-0.1629739044805514</v>
       </c>
       <c r="Q106" s="10" t="inlineStr">
         <is>
@@ -9254,13 +9254,13 @@
         </is>
       </c>
       <c r="D107" s="15" t="n">
-        <v>258.98</v>
+        <v>256.91</v>
       </c>
       <c r="E107" s="20" t="n">
-        <v>0.0222</v>
+        <v>0.0141</v>
       </c>
       <c r="F107" s="20" t="n">
-        <v>0.1846</v>
+        <v>0.1751</v>
       </c>
       <c r="G107" s="17" t="n">
         <v>46234</v>
@@ -9289,7 +9289,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="20" t="n">
-        <v>0.1390840991582361</v>
+        <v>0.148262037289323</v>
       </c>
       <c r="N107" s="14" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="16" t="n">
-        <v>-0.05011970036296245</v>
+        <v>-0.04246623331127641</v>
       </c>
       <c r="Q107" s="21" t="inlineStr">
         <is>
@@ -9337,13 +9337,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>105.62</v>
+        <v>104.49</v>
       </c>
       <c r="E108" s="9" t="n">
-        <v>0.1222</v>
+        <v>0.1102</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>0.2239</v>
+        <v>0.2108</v>
       </c>
       <c r="G108" s="6" t="n">
         <v>46316</v>
@@ -9372,7 +9372,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="9" t="n">
-        <v>0.06040522628290092</v>
+        <v>0.07187290649822954</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="9" t="n">
-        <v>0.1361484567316796</v>
+        <v>0.1484352569623888</v>
       </c>
       <c r="Q108" s="10" t="inlineStr">
         <is>
@@ -9436,13 +9436,13 @@
         </is>
       </c>
       <c r="D109" s="15" t="n">
-        <v>376.35</v>
+        <v>376.26</v>
       </c>
       <c r="E109" s="20" t="n">
-        <v>0.0503</v>
+        <v>0.05</v>
       </c>
       <c r="F109" s="20" t="n">
-        <v>0.1185</v>
+        <v>0.1182</v>
       </c>
       <c r="G109" s="17" t="n">
         <v>46238</v>
@@ -9471,7 +9471,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="20" t="n">
-        <v>0.03626943005181341</v>
+        <v>0.03651730186573117</v>
       </c>
       <c r="N109" s="14" t="inlineStr">
         <is>
@@ -9519,13 +9519,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>160.18</v>
+        <v>158.92</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>0.0273</v>
+        <v>0.0192</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>0.0793</v>
+        <v>0.0708</v>
       </c>
       <c r="G110" s="6" t="n">
         <v>46240</v>
@@ -9554,7 +9554,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="9" t="n">
-        <v>0.005119240854039163</v>
+        <v>0.01308834633778009</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="9" t="n">
-        <v>0.1237357972281183</v>
+        <v>0.1326453561540399</v>
       </c>
       <c r="Q110" s="10" t="inlineStr">
         <is>
@@ -9606,13 +9606,13 @@
         </is>
       </c>
       <c r="D111" s="15" t="n">
-        <v>46.19</v>
+        <v>45.51</v>
       </c>
       <c r="E111" s="20" t="n">
-        <v>0.0442</v>
+        <v>0.0289</v>
       </c>
       <c r="F111" s="16" t="n">
-        <v>-0.0596</v>
+        <v>-0.0733</v>
       </c>
       <c r="G111" s="17" t="n">
         <v>46232</v>
@@ -9641,7 +9641,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="20" t="n">
-        <v>0.1907339250920113</v>
+        <v>0.2085255987695013</v>
       </c>
       <c r="N111" s="14" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="20" t="n">
-        <v>0.4072310023814679</v>
+        <v>0.4282575258185015</v>
       </c>
       <c r="Q111" s="21" t="inlineStr">
         <is>
@@ -9693,13 +9693,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>312.14</v>
+        <v>311.15</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>0.166</v>
+        <v>0.1623</v>
       </c>
       <c r="G112" s="6" t="n">
         <v>46239</v>
@@ -9728,7 +9728,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="9" t="n">
-        <v>0.06042160568975465</v>
+        <v>0.06379559697894914</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0.05721791503812396</v>
+        <v>0.06058171300016077</v>
       </c>
       <c r="Q112" s="10" t="inlineStr">
         <is>
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="D113" s="15" t="n">
-        <v>106.87</v>
+        <v>107.07</v>
       </c>
       <c r="E113" s="20" t="n">
-        <v>0.0242</v>
+        <v>0.0262</v>
       </c>
       <c r="F113" s="20" t="n">
-        <v>0.1495</v>
+        <v>0.1517</v>
       </c>
       <c r="G113" s="17" t="n">
         <v>46239</v>
@@ -9823,7 +9823,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="20" t="n">
-        <v>0.1509310377093665</v>
+        <v>0.1487811711964136</v>
       </c>
       <c r="N113" s="14" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="20" t="n">
-        <v>0.2164311780668101</v>
+        <v>0.2141589614271038</v>
       </c>
       <c r="Q113" s="21" t="inlineStr">
         <is>
@@ -9875,13 +9875,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>194.91</v>
-      </c>
-      <c r="E114" s="5" t="n">
-        <v>-0.006500000000000001</v>
+        <v>196.5</v>
+      </c>
+      <c r="E114" s="9" t="n">
+        <v>0.0016</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>0.0791</v>
+        <v>0.08789999999999999</v>
       </c>
       <c r="G114" s="6" t="n">
         <v>46315</v>
@@ -9910,7 +9910,7 @@
         <v>212</v>
       </c>
       <c r="M114" s="9" t="n">
-        <v>0.08768149402288238</v>
+        <v>0.07888040712468193</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="9" t="n">
-        <v>0.05176748242778721</v>
+        <v>0.04325699745547074</v>
       </c>
       <c r="Q114" s="10" t="inlineStr">
         <is>
@@ -9966,13 +9966,13 @@
         </is>
       </c>
       <c r="D115" s="15" t="n">
-        <v>73.89</v>
+        <v>73.37</v>
       </c>
       <c r="E115" s="20" t="n">
-        <v>0.0534</v>
+        <v>0.0461</v>
       </c>
       <c r="F115" s="20" t="n">
-        <v>0.0214</v>
+        <v>0.0142</v>
       </c>
       <c r="G115" s="17" t="n">
         <v>46233</v>
@@ -10001,7 +10001,7 @@
         <v>85</v>
       </c>
       <c r="M115" s="20" t="n">
-        <v>0.1503586412234403</v>
+        <v>0.1585116532642769</v>
       </c>
       <c r="N115" s="14" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="20" t="n">
-        <v>0.218026796589525</v>
+        <v>0.2266593975739402</v>
       </c>
       <c r="Q115" s="21" t="inlineStr">
         <is>
@@ -10053,13 +10053,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>131.56</v>
+        <v>130.52</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>0.0288</v>
+        <v>0.0206</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>-0.0342</v>
+        <v>-0.0418</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>46238</v>
@@ -10088,7 +10088,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="9" t="n">
-        <v>0.254180602006689</v>
+        <v>0.2641740729390131</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="8" t="n"/>
@@ -10136,13 +10136,13 @@
         </is>
       </c>
       <c r="D117" s="15" t="n">
-        <v>558.55</v>
+        <v>556.2</v>
       </c>
       <c r="E117" s="20" t="n">
-        <v>0.0128</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F117" s="16" t="n">
-        <v>-0.0167</v>
+        <v>-0.0208</v>
       </c>
       <c r="G117" s="17" t="n">
         <v>46238</v>
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>358.92</v>
+        <v>356.83</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>-0.1131</v>
+        <v>-0.1183</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>-0.1528</v>
+        <v>-0.1577</v>
       </c>
       <c r="G118" s="6" t="n">
         <v>46315</v>
@@ -10242,7 +10242,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="9" t="n">
-        <v>0.3568483227460157</v>
+        <v>0.3647955609113584</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>375</v>
       </c>
       <c r="P118" s="9" t="n">
-        <v>0.04480106987629551</v>
+        <v>0.05092060645125134</v>
       </c>
       <c r="Q118" s="10" t="inlineStr">
         <is>
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="D119" s="15" t="n">
-        <v>268.09</v>
+        <v>265.95</v>
       </c>
       <c r="E119" s="20" t="n">
-        <v>0.0527</v>
+        <v>0.0443</v>
       </c>
       <c r="F119" s="20" t="n">
-        <v>0.1616</v>
+        <v>0.1523</v>
       </c>
       <c r="G119" s="17" t="n">
         <v>46315</v>
@@ -10333,7 +10333,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="20" t="n">
-        <v>0.01458465440710219</v>
+        <v>0.02274863696183498</v>
       </c>
       <c r="N119" s="14" t="inlineStr"/>
       <c r="O119" s="19" t="n"/>
@@ -10385,13 +10385,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1196.33</v>
+        <v>1197.53</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F120" s="9" t="n">
-        <v>0.0617</v>
+        <v>0.06280000000000001</v>
       </c>
       <c r="G120" s="6" t="n">
         <v>46239</v>
@@ -10420,7 +10420,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="9" t="n">
-        <v>0.06993889645833513</v>
+        <v>0.06886675072858302</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -10480,13 +10480,13 @@
         </is>
       </c>
       <c r="D121" s="15" t="n">
-        <v>84.95999999999999</v>
+        <v>84.22</v>
       </c>
       <c r="E121" s="20" t="n">
-        <v>0.0491</v>
+        <v>0.04</v>
       </c>
       <c r="F121" s="20" t="n">
-        <v>0.1243</v>
+        <v>0.1145</v>
       </c>
       <c r="G121" s="17" t="n">
         <v>46266</v>
@@ -10515,7 +10515,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="20" t="n">
-        <v>0.2005649717514125</v>
+        <v>0.2111137497031584</v>
       </c>
       <c r="N121" s="14" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="20" t="n">
-        <v>0.2358757062146894</v>
+        <v>0.2467347423414866</v>
       </c>
       <c r="Q121" s="21" t="inlineStr">
         <is>
@@ -10567,13 +10567,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>131.41</v>
+        <v>130.76</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>0.0214</v>
+        <v>0.0163</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>0.09609999999999999</v>
+        <v>0.0907</v>
       </c>
       <c r="G122" s="6" t="n">
         <v>46238</v>
@@ -10602,7 +10602,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="9" t="n">
-        <v>0.1414656418841793</v>
+        <v>0.1471397981033956</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="8" t="n"/>
@@ -10646,13 +10646,13 @@
         </is>
       </c>
       <c r="D123" s="15" t="n">
-        <v>156.42</v>
+        <v>156.11</v>
       </c>
       <c r="E123" s="20" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="F123" s="20" t="n">
-        <v>0.0332</v>
+        <v>0.0311</v>
       </c>
       <c r="G123" s="17" t="n">
         <v>46322</v>
@@ -10725,13 +10725,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>24.77</v>
+        <v>24.67</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>0.0198</v>
+        <v>0.0156</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>-0.0524</v>
+        <v>-0.0562</v>
       </c>
       <c r="G124" s="6" t="n">
         <v>46238</v>
@@ -10760,7 +10760,7 @@
         <v>28</v>
       </c>
       <c r="M124" s="9" t="n">
-        <v>0.1303996770286637</v>
+        <v>0.1349817592217267</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="8" t="n"/>
@@ -10804,13 +10804,13 @@
         </is>
       </c>
       <c r="D125" s="15" t="n">
-        <v>336.61</v>
+        <v>336.74</v>
       </c>
       <c r="E125" s="20" t="n">
-        <v>0.0117</v>
+        <v>0.0121</v>
       </c>
       <c r="F125" s="20" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0946</v>
       </c>
       <c r="G125" s="17" t="n">
         <v>46233</v>
@@ -10839,7 +10839,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="20" t="n">
-        <v>0.2417931731083449</v>
+        <v>0.2413137732375126</v>
       </c>
       <c r="N125" s="14" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="20" t="n">
-        <v>0.03977897269837493</v>
+        <v>0.03937756132327609</v>
       </c>
       <c r="Q125" s="21" t="inlineStr">
         <is>
@@ -10895,13 +10895,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>563</v>
+        <v>559.53</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>0.0974</v>
+        <v>0.0906</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>0.1555</v>
+        <v>0.1484</v>
       </c>
       <c r="G126" s="6" t="n">
         <v>46323</v>
@@ -10930,7 +10930,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="9" t="n">
-        <v>0.09236234458259325</v>
+        <v>0.09913677550801571</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="9" t="n">
-        <v>0.01243339253996448</v>
+        <v>0.0187121333976731</v>
       </c>
       <c r="Q126" s="10" t="inlineStr">
         <is>
@@ -10990,13 +10990,13 @@
         </is>
       </c>
       <c r="D127" s="15" t="n">
-        <v>418.34</v>
+        <v>417.64</v>
       </c>
       <c r="E127" s="16" t="n">
-        <v>-0.0223</v>
+        <v>-0.024</v>
       </c>
       <c r="F127" s="20" t="n">
-        <v>0.09359999999999999</v>
+        <v>0.09179999999999999</v>
       </c>
       <c r="G127" s="17" t="n">
         <v>46322</v>
@@ -11025,7 +11025,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="20" t="n">
-        <v>0.2573504804704308</v>
+        <v>0.2594579063308113</v>
       </c>
       <c r="N127" s="14" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="20" t="n">
-        <v>0.1473920734330928</v>
+        <v>0.149315199693516</v>
       </c>
       <c r="Q127" s="21" t="inlineStr">
         <is>
@@ -11081,13 +11081,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>77.06</v>
+        <v>76.92</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>0.0127</v>
+        <v>0.0109</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>-0.0155</v>
+        <v>-0.0172</v>
       </c>
       <c r="G128" s="6" t="n">
         <v>46240</v>
@@ -11160,13 +11160,13 @@
         </is>
       </c>
       <c r="D129" s="15" t="n">
-        <v>257.33</v>
+        <v>254.98</v>
       </c>
       <c r="E129" s="20" t="n">
-        <v>0.1511</v>
+        <v>0.1406</v>
       </c>
       <c r="F129" s="20" t="n">
-        <v>0.1704</v>
+        <v>0.1597</v>
       </c>
       <c r="G129" s="17" t="n">
         <v>46232</v>
@@ -11195,7 +11195,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="16" t="n">
-        <v>-0.03625694633350167</v>
+        <v>-0.02737469605459248</v>
       </c>
       <c r="N129" s="14" t="inlineStr"/>
       <c r="O129" s="19" t="n"/>
@@ -11251,13 +11251,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>118.07</v>
+        <v>120.24</v>
       </c>
       <c r="E130" s="9" t="n">
-        <v>0.0061</v>
+        <v>0.0246</v>
       </c>
       <c r="F130" s="9" t="n">
-        <v>0.0369</v>
+        <v>0.0559</v>
       </c>
       <c r="G130" s="6" t="n">
         <v>46233</v>
@@ -11312,13 +11312,13 @@
         </is>
       </c>
       <c r="D131" s="15" t="n">
-        <v>239.1</v>
+        <v>243.12</v>
       </c>
       <c r="E131" s="20" t="n">
-        <v>0.0067</v>
+        <v>0.0236</v>
       </c>
       <c r="F131" s="20" t="n">
-        <v>0.0605</v>
+        <v>0.0784</v>
       </c>
       <c r="G131" s="17" t="n">
         <v>46238</v>
@@ -11373,13 +11373,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>212.52</v>
+        <v>211.5</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>-0.0218</v>
+        <v>-0.0265</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>-0.0711</v>
+        <v>-0.0755</v>
       </c>
       <c r="G132" s="6" t="n">
         <v>46231</v>
@@ -11408,7 +11408,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="9" t="n">
-        <v>0.1763598720120459</v>
+        <v>0.182033096926714</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="8" t="n"/>
@@ -11452,13 +11452,13 @@
         </is>
       </c>
       <c r="D133" s="15" t="n">
-        <v>153.96</v>
+        <v>152.78</v>
       </c>
       <c r="E133" s="20" t="n">
-        <v>0.1162</v>
+        <v>0.1077</v>
       </c>
       <c r="F133" s="20" t="n">
-        <v>0.0283</v>
+        <v>0.0204</v>
       </c>
       <c r="G133" s="17" t="n">
         <v>46238</v>
@@ -11523,13 +11523,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>851.76</v>
+        <v>873.28</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>-0.1461</v>
+        <v>-0.1245</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>-0.0405</v>
+        <v>-0.0162</v>
       </c>
       <c r="G134" s="6" t="n">
         <v>46238</v>
@@ -11558,7 +11558,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="9" t="n">
-        <v>0.3560157790927022</v>
+        <v>0.3225998534261635</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="9" t="n">
-        <v>0.2949657180426412</v>
+        <v>0.263054232319531</v>
       </c>
       <c r="Q134" s="10" t="inlineStr">
         <is>
@@ -11610,13 +11610,13 @@
         </is>
       </c>
       <c r="D135" s="15" t="n">
-        <v>647.98</v>
+        <v>661.84</v>
       </c>
       <c r="E135" s="16" t="n">
-        <v>-0.0552</v>
+        <v>-0.035</v>
       </c>
       <c r="F135" s="16" t="n">
-        <v>-0.031</v>
+        <v>-0.0102</v>
       </c>
       <c r="G135" s="17" t="n">
         <v>46238</v>
@@ -11645,7 +11645,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="20" t="n">
-        <v>0.3488070619463564</v>
+        <v>0.3205608606309682</v>
       </c>
       <c r="N135" s="14" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="20" t="n">
-        <v>0.3040525942158708</v>
+        <v>0.2767436238365767</v>
       </c>
       <c r="Q135" s="21" t="inlineStr">
         <is>
@@ -11705,13 +11705,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>211.2</v>
+        <v>210.98</v>
       </c>
       <c r="E136" s="9" t="n">
-        <v>0.2286</v>
+        <v>0.2273</v>
       </c>
       <c r="F136" s="9" t="n">
-        <v>0.2204</v>
+        <v>0.2191</v>
       </c>
       <c r="G136" s="6" t="n">
         <v>46288</v>
@@ -11740,7 +11740,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="9" t="n">
-        <v>0.1837121212121213</v>
+        <v>0.184946440420893</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="8" t="n"/>
@@ -11784,13 +11784,13 @@
         </is>
       </c>
       <c r="D137" s="15" t="n">
-        <v>615.54</v>
+        <v>625.02</v>
       </c>
       <c r="E137" s="20" t="n">
-        <v>0.0038</v>
+        <v>0.0192</v>
       </c>
       <c r="F137" s="20" t="n">
-        <v>0.142</v>
+        <v>0.1596</v>
       </c>
       <c r="G137" s="17" t="n">
         <v>46254</v>
@@ -11819,7 +11819,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="20" t="n">
-        <v>0.2184423433083147</v>
+        <v>0.1999616012287607</v>
       </c>
       <c r="N137" s="14" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="20" t="n">
-        <v>0.04183318712025214</v>
+        <v>0.02603116700265589</v>
       </c>
       <c r="Q137" s="21" t="inlineStr">
         <is>
@@ -11871,13 +11871,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>147.8</v>
+        <v>149.3</v>
       </c>
       <c r="E138" s="9" t="n">
-        <v>0.03</v>
+        <v>0.0405</v>
       </c>
       <c r="F138" s="9" t="n">
-        <v>0.0424</v>
+        <v>0.053</v>
       </c>
       <c r="G138" s="6" t="n">
         <v>46238</v>
@@ -11913,7 +11913,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="9" t="n">
-        <v>0.2516914749661704</v>
+        <v>0.2391158740790354</v>
       </c>
       <c r="Q138" s="10" t="inlineStr">
         <is>
@@ -11952,13 +11952,13 @@
         </is>
       </c>
       <c r="D139" s="15" t="n">
-        <v>391.76</v>
+        <v>398.64</v>
       </c>
       <c r="E139" s="16" t="n">
-        <v>-0.0271</v>
+        <v>-0.01</v>
       </c>
       <c r="F139" s="16" t="n">
-        <v>-0.0253</v>
+        <v>-0.008199999999999999</v>
       </c>
       <c r="G139" s="17" t="n">
         <v>46234</v>
@@ -11994,7 +11994,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="20" t="n">
-        <v>0.1563201960383909</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="Q139" s="21" t="inlineStr">
         <is>
@@ -12035,13 +12035,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>47.32</v>
+        <v>47.64</v>
       </c>
       <c r="E140" s="9" t="n">
-        <v>0.0046</v>
+        <v>0.0115</v>
       </c>
       <c r="F140" s="9" t="n">
-        <v>0.0571</v>
+        <v>0.0643</v>
       </c>
       <c r="G140" s="6" t="n">
         <v>46309</v>
@@ -12114,13 +12114,13 @@
         </is>
       </c>
       <c r="D141" s="15" t="n">
-        <v>311.81</v>
+        <v>310.79</v>
       </c>
       <c r="E141" s="16" t="n">
-        <v>-0.0211</v>
+        <v>-0.0243</v>
       </c>
       <c r="F141" s="16" t="n">
-        <v>-0.0594</v>
+        <v>-0.0625</v>
       </c>
       <c r="G141" s="17" t="n">
         <v>46282</v>
@@ -12149,7 +12149,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="20" t="n">
-        <v>0.363009525031269</v>
+        <v>0.3674828662440875</v>
       </c>
       <c r="N141" s="14" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="20" t="n">
-        <v>0.03588723902376446</v>
+        <v>0.03928697834550655</v>
       </c>
       <c r="Q141" s="21" t="inlineStr">
         <is>
@@ -12201,13 +12201,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>232.35</v>
+        <v>234.1</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>-0.0263</v>
+        <v>-0.0189</v>
       </c>
       <c r="F142" s="9" t="n">
-        <v>0.0259</v>
+        <v>0.0336</v>
       </c>
       <c r="G142" s="6" t="n">
         <v>46244</v>
@@ -12236,7 +12236,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="9" t="n">
-        <v>0.2265978050355068</v>
+        <v>0.2174284493806066</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="8" t="n"/>
@@ -12284,13 +12284,13 @@
         </is>
       </c>
       <c r="D143" s="15" t="n">
-        <v>1679.2</v>
+        <v>1730.42</v>
       </c>
       <c r="E143" s="16" t="n">
-        <v>-0.0944</v>
+        <v>-0.0668</v>
       </c>
       <c r="F143" s="16" t="n">
-        <v>-0.09480000000000001</v>
+        <v>-0.0672</v>
       </c>
       <c r="G143" s="17" t="n">
         <v>46317</v>
@@ -12345,13 +12345,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>50.66</v>
+        <v>51.7</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>-0.0556</v>
+        <v>-0.0362</v>
       </c>
       <c r="F144" s="9" t="n">
-        <v>0.0786</v>
+        <v>0.1007</v>
       </c>
       <c r="G144" s="6" t="n">
         <v>46241</v>
@@ -12406,13 +12406,13 @@
         </is>
       </c>
       <c r="D145" s="15" t="n">
-        <v>390.41</v>
+        <v>389.14</v>
       </c>
       <c r="E145" s="20" t="n">
-        <v>0.126</v>
+        <v>0.1224</v>
       </c>
       <c r="F145" s="20" t="n">
-        <v>0.1188</v>
+        <v>0.1151</v>
       </c>
       <c r="G145" s="17" t="n">
         <v>46232</v>
@@ -12441,7 +12441,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="20" t="n">
-        <v>0.02456391998155778</v>
+        <v>0.0279076938890888</v>
       </c>
       <c r="N145" s="14" t="inlineStr"/>
       <c r="O145" s="19" t="n"/>
@@ -12493,13 +12493,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>359.21</v>
+        <v>361.61</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>-0.0265</v>
+        <v>-0.02</v>
       </c>
       <c r="F146" s="9" t="n">
-        <v>0.1197</v>
+        <v>0.1271</v>
       </c>
       <c r="G146" s="6" t="n">
         <v>46315</v>
@@ -12528,7 +12528,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="9" t="n">
-        <v>0.08571587650677882</v>
+        <v>0.07850999695804868</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="8" t="n"/>
@@ -12580,13 +12580,13 @@
         </is>
       </c>
       <c r="D147" s="15" t="n">
-        <v>972.58</v>
+        <v>996.5700000000001</v>
       </c>
       <c r="E147" s="16" t="n">
-        <v>-0.06950000000000001</v>
-      </c>
-      <c r="F147" s="16" t="n">
-        <v>-0.0235</v>
+        <v>-0.04650000000000001</v>
+      </c>
+      <c r="F147" s="20" t="n">
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G147" s="17" t="n">
         <v>46316</v>
@@ -12615,7 +12615,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="20" t="n">
-        <v>0.2944950543914125</v>
+        <v>0.2633332329891527</v>
       </c>
       <c r="N147" s="14" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="20" t="n">
-        <v>0.3880606222624359</v>
+        <v>0.3546464372798699</v>
       </c>
       <c r="Q147" s="21" t="inlineStr">
         <is>
@@ -12671,13 +12671,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1383.45</v>
+        <v>1398.95</v>
       </c>
       <c r="E148" s="9" t="n">
-        <v>0.022</v>
+        <v>0.0335</v>
       </c>
       <c r="F148" s="9" t="n">
-        <v>0.1091</v>
+        <v>0.1215</v>
       </c>
       <c r="G148" s="6" t="n">
         <v>46238</v>
@@ -12746,13 +12746,13 @@
         </is>
       </c>
       <c r="D149" s="15" t="n">
-        <v>243.73</v>
+        <v>245.75</v>
       </c>
       <c r="E149" s="20" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="F149" s="16" t="n">
-        <v>-0.0026</v>
+        <v>0.0091</v>
+      </c>
+      <c r="F149" s="20" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="G149" s="17" t="n">
         <v>46317</v>
@@ -12807,13 +12807,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>483.69</v>
+        <v>497.96</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>-0.0645</v>
+        <v>-0.0369</v>
       </c>
       <c r="F150" s="9" t="n">
-        <v>0.0206</v>
+        <v>0.0507</v>
       </c>
       <c r="G150" s="6" t="n">
         <v>46231</v>
@@ -12874,13 +12874,13 @@
         </is>
       </c>
       <c r="D151" s="15" t="n">
-        <v>284.6</v>
+        <v>284.82</v>
       </c>
       <c r="E151" s="20" t="n">
-        <v>0.06309999999999999</v>
+        <v>0.0639</v>
       </c>
       <c r="F151" s="20" t="n">
-        <v>0.14</v>
+        <v>0.1409</v>
       </c>
       <c r="G151" s="17" t="n">
         <v>46231</v>
@@ -12912,7 +12912,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="16" t="n">
-        <v>-0.0442726633872102</v>
+        <v>-0.04501088406713009</v>
       </c>
       <c r="Q151" s="21" t="inlineStr">
         <is>
@@ -12965,13 +12965,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>304.98</v>
+        <v>303.48</v>
       </c>
       <c r="E152" s="9" t="n">
-        <v>0.0471</v>
+        <v>0.042</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>-0.0311</v>
+        <v>-0.0359</v>
       </c>
       <c r="G152" s="6" t="n">
         <v>46232</v>
@@ -13036,13 +13036,13 @@
         </is>
       </c>
       <c r="D153" s="15" t="n">
-        <v>546.11</v>
+        <v>547.35</v>
       </c>
       <c r="E153" s="16" t="n">
-        <v>-0.0315</v>
+        <v>-0.0293</v>
       </c>
       <c r="F153" s="20" t="n">
-        <v>0.09880000000000001</v>
+        <v>0.1013</v>
       </c>
       <c r="G153" s="17" t="n">
         <v>46232</v>
@@ -13097,13 +13097,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>583.23</v>
+        <v>580</v>
       </c>
       <c r="E154" s="9" t="n">
-        <v>0.1495</v>
+        <v>0.1431</v>
       </c>
       <c r="F154" s="9" t="n">
-        <v>0.0857</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="G154" s="6" t="n">
         <v>46315</v>
@@ -13164,13 +13164,13 @@
         </is>
       </c>
       <c r="D155" s="15" t="n">
-        <v>225.69</v>
+        <v>226.77</v>
       </c>
       <c r="E155" s="20" t="n">
-        <v>0.0315</v>
+        <v>0.0365</v>
       </c>
       <c r="F155" s="20" t="n">
-        <v>0.0219</v>
+        <v>0.0268</v>
       </c>
       <c r="G155" s="17" t="n">
         <v>46232</v>
@@ -13199,7 +13199,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="20" t="n">
-        <v>1.547742478621118</v>
+        <v>1.535608766591701</v>
       </c>
       <c r="N155" s="14" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="20" t="n">
-        <v>0.05011298684035625</v>
+        <v>0.04511178727344882</v>
       </c>
       <c r="Q155" s="21" t="inlineStr">
         <is>
@@ -13259,13 +13259,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>116.52</v>
+        <v>115.48</v>
       </c>
       <c r="E156" s="9" t="n">
-        <v>0.1664</v>
+        <v>0.156</v>
       </c>
       <c r="F156" s="9" t="n">
-        <v>0.22</v>
+        <v>0.2091</v>
       </c>
       <c r="G156" s="6" t="n">
         <v>46294</v>
@@ -13294,7 +13294,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="9" t="n">
-        <v>1.14555441125987</v>
+        <v>1.164877034984413</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="8" t="n"/>
@@ -13338,13 +13338,13 @@
         </is>
       </c>
       <c r="D157" s="15" t="n">
-        <v>131.77</v>
+        <v>133.44</v>
       </c>
       <c r="E157" s="20" t="n">
-        <v>0.0919</v>
+        <v>0.1057</v>
       </c>
       <c r="F157" s="20" t="n">
-        <v>0.1742</v>
+        <v>0.1891</v>
       </c>
       <c r="G157" s="17" t="n">
         <v>46231</v>
@@ -13373,7 +13373,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="16" t="n">
-        <v>-0.2790468240115353</v>
+        <v>-0.2880695443645084</v>
       </c>
       <c r="N157" s="14" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="20" t="n">
-        <v>0.05486833118312202</v>
+        <v>0.04166666666666669</v>
       </c>
       <c r="Q157" s="21" t="inlineStr">
         <is>
@@ -13429,13 +13429,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>979.34</v>
+        <v>987.3099999999999</v>
       </c>
       <c r="E158" s="9" t="n">
-        <v>0.0108</v>
+        <v>0.019</v>
       </c>
       <c r="F158" s="9" t="n">
-        <v>0.1484</v>
+        <v>0.1577</v>
       </c>
       <c r="G158" s="6" t="n">
         <v>46240</v>
@@ -13464,7 +13464,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="5" t="n">
-        <v>-0.8723630199930565</v>
+        <v>-0.8733933617607438</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="9" t="n">
-        <v>0.08644597381910263</v>
+        <v>0.0776757046925485</v>
       </c>
       <c r="Q158" s="10" t="inlineStr">
         <is>
@@ -13520,13 +13520,13 @@
         </is>
       </c>
       <c r="D159" s="15" t="n">
-        <v>578.98</v>
+        <v>584.97</v>
       </c>
       <c r="E159" s="16" t="n">
-        <v>-0.0815</v>
+        <v>-0.07200000000000001</v>
       </c>
       <c r="F159" s="20" t="n">
-        <v>0.002</v>
+        <v>0.0124</v>
       </c>
       <c r="G159" s="17" t="n">
         <v>46234</v>
@@ -13601,13 +13601,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>457.36</v>
+        <v>466</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>-0.0408</v>
+        <v>-0.0227</v>
       </c>
       <c r="F160" s="9" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.0246</v>
       </c>
       <c r="G160" s="6" t="n">
         <v>46238</v>
@@ -13662,13 +13662,13 @@
         </is>
       </c>
       <c r="D161" s="15" t="n">
-        <v>39.39</v>
+        <v>39.07</v>
       </c>
       <c r="E161" s="16" t="n">
-        <v>-0.0897</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="F161" s="16" t="n">
-        <v>-0.203</v>
+        <v>-0.2094</v>
       </c>
       <c r="G161" s="17" t="n">
         <v>46323</v>
@@ -13737,13 +13737,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>218.95</v>
+        <v>218.42</v>
       </c>
       <c r="E162" s="9" t="n">
-        <v>0.1647</v>
+        <v>0.1619</v>
       </c>
       <c r="F162" s="9" t="n">
-        <v>0.2235</v>
+        <v>0.2205</v>
       </c>
       <c r="G162" s="6" t="n">
         <v>46322</v>
@@ -13816,13 +13816,13 @@
         </is>
       </c>
       <c r="D163" s="15" t="n">
-        <v>40.93</v>
-      </c>
-      <c r="E163" s="16" t="n">
-        <v>-0.0075</v>
+        <v>41.49</v>
+      </c>
+      <c r="E163" s="20" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F163" s="16" t="n">
-        <v>-0.1614</v>
+        <v>-0.15</v>
       </c>
       <c r="G163" s="17" t="n">
         <v>46239</v>
@@ -13877,13 +13877,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>475.92</v>
-      </c>
-      <c r="E164" s="5" t="n">
-        <v>-0.004099999999999999</v>
+        <v>483.34</v>
+      </c>
+      <c r="E164" s="9" t="n">
+        <v>0.0114</v>
       </c>
       <c r="F164" s="9" t="n">
-        <v>0.05230000000000001</v>
+        <v>0.0687</v>
       </c>
       <c r="G164" s="6" t="n">
         <v>46233</v>
@@ -13915,7 +13915,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="9" t="n">
-        <v>0.176668347621449</v>
+        <v>0.1586047089005669</v>
       </c>
       <c r="Q164" s="10" t="inlineStr">
         <is>
@@ -13968,13 +13968,13 @@
         </is>
       </c>
       <c r="D165" s="15" t="n">
-        <v>299.68</v>
+        <v>299.3</v>
       </c>
       <c r="E165" s="20" t="n">
-        <v>0.1168</v>
+        <v>0.1153</v>
       </c>
       <c r="F165" s="20" t="n">
-        <v>0.1224</v>
+        <v>0.121</v>
       </c>
       <c r="G165" s="17" t="n">
         <v>46317</v>
@@ -14006,7 +14006,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="16" t="n">
-        <v>-0.01895355045381743</v>
+        <v>-0.01770798529903111</v>
       </c>
       <c r="Q165" s="21" t="inlineStr">
         <is>
@@ -14051,13 +14051,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>280.12</v>
+        <v>287.6</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>-0.0784</v>
+        <v>-0.0538</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>-0.1084</v>
+        <v>-0.08460000000000001</v>
       </c>
       <c r="G166" s="6" t="n">
         <v>46232</v>
@@ -14089,7 +14089,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="9" t="n">
-        <v>0.5172069113237184</v>
+        <v>0.4777468706536855</v>
       </c>
       <c r="Q166" s="10" t="inlineStr">
         <is>
@@ -14130,13 +14130,13 @@
         </is>
       </c>
       <c r="D167" s="15" t="n">
-        <v>239.52</v>
+        <v>237.9</v>
       </c>
       <c r="E167" s="20" t="n">
-        <v>0.062</v>
+        <v>0.0548</v>
       </c>
       <c r="F167" s="20" t="n">
-        <v>0.1172</v>
+        <v>0.1096</v>
       </c>
       <c r="G167" s="17" t="n">
         <v>46231</v>
@@ -14165,7 +14165,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="20" t="n">
-        <v>0.1189044756179024</v>
+        <v>0.1265237494745691</v>
       </c>
       <c r="N167" s="14" t="inlineStr"/>
       <c r="O167" s="19" t="n"/>
@@ -14213,13 +14213,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>365.48</v>
+        <v>364.37</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>-0.1102</v>
-      </c>
-      <c r="F168" s="9" t="n">
-        <v>0.0002</v>
+        <v>-0.1129</v>
+      </c>
+      <c r="F168" s="5" t="n">
+        <v>-0.0029</v>
       </c>
       <c r="G168" s="6" t="n">
         <v>46232</v>
@@ -14288,13 +14288,13 @@
         </is>
       </c>
       <c r="D169" s="15" t="n">
-        <v>413.09</v>
+        <v>419.76</v>
       </c>
       <c r="E169" s="16" t="n">
-        <v>-0.0429</v>
+        <v>-0.0275</v>
       </c>
       <c r="F169" s="20" t="n">
-        <v>0.1638</v>
+        <v>0.1826</v>
       </c>
       <c r="G169" s="17" t="n">
         <v>46232</v>
@@ -14367,13 +14367,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>120.46</v>
+        <v>120.16</v>
       </c>
       <c r="E170" s="9" t="n">
-        <v>0.0345</v>
+        <v>0.0319</v>
       </c>
       <c r="F170" s="9" t="n">
-        <v>0.1027</v>
+        <v>0.0999</v>
       </c>
       <c r="G170" s="6" t="n">
         <v>46231</v>
@@ -14446,13 +14446,13 @@
         </is>
       </c>
       <c r="D171" s="15" t="n">
-        <v>95.86</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="E171" s="16" t="n">
-        <v>-0.2935</v>
+        <v>-0.2791</v>
       </c>
       <c r="F171" s="16" t="n">
-        <v>-0.4328</v>
+        <v>-0.4213</v>
       </c>
       <c r="G171" s="17" t="n">
         <v>46240</v>
@@ -14507,13 +14507,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>336.16</v>
+        <v>336.91</v>
       </c>
       <c r="E172" s="9" t="n">
-        <v>0.1846</v>
+        <v>0.1872</v>
       </c>
       <c r="F172" s="9" t="n">
-        <v>0.0757</v>
+        <v>0.0781</v>
       </c>
       <c r="G172" s="6" t="n">
         <v>46233</v>
@@ -14542,7 +14542,7 @@
         <v>310</v>
       </c>
       <c r="M172" s="5" t="n">
-        <v>-0.07782008567348889</v>
+        <v>-0.07987296310587404</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="9" t="n">
-        <v>0.08579247977153728</v>
+        <v>0.08337538214953541</v>
       </c>
       <c r="Q172" s="10" t="inlineStr">
         <is>
@@ -14610,13 +14610,13 @@
         </is>
       </c>
       <c r="D173" s="15" t="n">
-        <v>123.88</v>
+        <v>128.11</v>
       </c>
       <c r="E173" s="16" t="n">
-        <v>-0.2849</v>
+        <v>-0.2605</v>
       </c>
       <c r="F173" s="16" t="n">
-        <v>-0.2036</v>
+        <v>-0.1764</v>
       </c>
       <c r="G173" s="17" t="n">
         <v>46240</v>
@@ -14671,13 +14671,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>156.09</v>
+        <v>154.06</v>
       </c>
       <c r="E174" s="9" t="n">
-        <v>0.2102</v>
+        <v>0.1944</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>-0.1251</v>
+        <v>-0.1364</v>
       </c>
       <c r="G174" s="6" t="n">
         <v>46296</v>
@@ -14732,13 +14732,13 @@
         </is>
       </c>
       <c r="D175" s="15" t="n">
-        <v>240.07</v>
+        <v>237.75</v>
       </c>
       <c r="E175" s="20" t="n">
-        <v>0.1842</v>
+        <v>0.1727</v>
       </c>
       <c r="F175" s="16" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0153</v>
       </c>
       <c r="G175" s="17" t="n">
         <v>46275</v>
@@ -14793,13 +14793,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>366.33</v>
+        <v>371.89</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>-0.0532</v>
+        <v>-0.0388</v>
       </c>
       <c r="F176" s="5" t="n">
-        <v>-0.1257</v>
+        <v>-0.1125</v>
       </c>
       <c r="G176" s="6" t="n">
         <v>46253</v>
@@ -14828,7 +14828,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="9" t="n">
-        <v>0.4058362678459313</v>
+        <v>0.3848180913711044</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="9" t="n">
-        <v>0.29391532225043</v>
+        <v>0.2745704374949582</v>
       </c>
       <c r="Q176" s="10" t="inlineStr">
         <is>
@@ -14888,13 +14888,13 @@
         </is>
       </c>
       <c r="D177" s="15" t="n">
-        <v>225.39</v>
+        <v>225.91</v>
       </c>
       <c r="E177" s="20" t="n">
-        <v>0.1484</v>
+        <v>0.1511</v>
       </c>
       <c r="F177" s="16" t="n">
-        <v>-0.0646</v>
+        <v>-0.0624</v>
       </c>
       <c r="G177" s="17" t="n">
         <v>46261</v>
@@ -14949,13 +14949,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>283.67</v>
+        <v>291.95</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>-0.1851</v>
+        <v>-0.1613</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>-0.1054</v>
+        <v>-0.0793</v>
       </c>
       <c r="G178" s="6" t="n">
         <v>46237</v>
@@ -15010,13 +15010,13 @@
         </is>
       </c>
       <c r="D179" s="15" t="n">
-        <v>274.2</v>
+        <v>282.52</v>
       </c>
       <c r="E179" s="16" t="n">
-        <v>-0.3001</v>
+        <v>-0.2788</v>
       </c>
       <c r="F179" s="16" t="n">
-        <v>-0.2147</v>
+        <v>-0.1909</v>
       </c>
       <c r="G179" s="17" t="n">
         <v>46238</v>
@@ -15071,13 +15071,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>45.14</v>
+        <v>46.8</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>-0.2202</v>
+        <v>-0.1916</v>
       </c>
       <c r="F180" s="5" t="n">
-        <v>-0.1166</v>
+        <v>-0.08410000000000001</v>
       </c>
       <c r="G180" s="6" t="n">
         <v>46233</v>
@@ -15132,13 +15132,13 @@
         </is>
       </c>
       <c r="D181" s="15" t="n">
-        <v>503.84</v>
+        <v>516.89</v>
       </c>
       <c r="E181" s="16" t="n">
-        <v>-0.1962</v>
+        <v>-0.1754</v>
       </c>
       <c r="F181" s="20" t="n">
-        <v>0.1204</v>
+        <v>0.1495</v>
       </c>
       <c r="G181" s="17" t="n">
         <v>46247</v>
@@ -15167,7 +15167,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="20" t="n">
-        <v>0.468720228644014</v>
+        <v>0.4316392269148175</v>
       </c>
       <c r="N181" s="14" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="20" t="n">
-        <v>0.3893299460146079</v>
+        <v>0.3542533227572598</v>
       </c>
       <c r="Q181" s="21" t="inlineStr">
         <is>
@@ -15219,13 +15219,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>67.09999999999999</v>
+        <v>68.28</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>-0.1628</v>
+        <v>-0.1481</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>-0.1913</v>
+        <v>-0.1771</v>
       </c>
       <c r="G182" s="6" t="n">
         <v>46268</v>
@@ -15284,13 +15284,13 @@
         </is>
       </c>
       <c r="D183" s="15" t="n">
-        <v>480.27</v>
+        <v>494.95</v>
       </c>
       <c r="E183" s="16" t="n">
-        <v>-0.07919999999999999</v>
+        <v>-0.05110000000000001</v>
       </c>
       <c r="F183" s="16" t="n">
-        <v>-0.073</v>
+        <v>-0.0447</v>
       </c>
       <c r="G183" s="17" t="n">
         <v>46238</v>
@@ -15319,7 +15319,7 @@
         <v>615</v>
       </c>
       <c r="M183" s="20" t="n">
-        <v>0.2805297020426011</v>
+        <v>0.2425497525002526</v>
       </c>
       <c r="N183" s="14" t="inlineStr">
         <is>
@@ -15330,7 +15330,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="20" t="n">
-        <v>0.2055718658254732</v>
+        <v>0.1698151328417012</v>
       </c>
       <c r="Q183" s="21" t="inlineStr">
         <is>
@@ -15371,13 +15371,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>59.4</v>
+        <v>60.71</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>-0.2454</v>
+        <v>-0.2288</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>-0.1584</v>
+        <v>-0.1398</v>
       </c>
       <c r="G184" s="6" t="n">
         <v>46230</v>
@@ -15432,13 +15432,13 @@
         </is>
       </c>
       <c r="D185" s="15" t="n">
-        <v>169.27</v>
+        <v>170.76</v>
       </c>
       <c r="E185" s="20" t="n">
-        <v>0.0741</v>
+        <v>0.08349999999999999</v>
       </c>
       <c r="F185" s="20" t="n">
-        <v>0.0902</v>
+        <v>0.0998</v>
       </c>
       <c r="G185" s="17" t="n">
         <v>46238</v>
@@ -15467,7 +15467,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="20" t="n">
-        <v>0.1815442783718319</v>
+        <v>0.1712344811431249</v>
       </c>
       <c r="N185" s="14" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="20" t="n">
-        <v>0.1815442783718319</v>
+        <v>0.1712344811431249</v>
       </c>
       <c r="Q185" s="21" t="inlineStr">
         <is>
@@ -15523,13 +15523,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>147.98</v>
+        <v>149.28</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>-0.09609999999999999</v>
+        <v>-0.0882</v>
       </c>
       <c r="F186" s="9" t="n">
-        <v>0.002</v>
+        <v>0.0108</v>
       </c>
       <c r="G186" s="6" t="n">
         <v>46232</v>
@@ -15561,7 +15561,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="9" t="n">
-        <v>0.2163805919718882</v>
+        <v>0.2057877813504823</v>
       </c>
       <c r="Q186" s="10" t="inlineStr">
         <is>
@@ -15614,13 +15614,13 @@
         </is>
       </c>
       <c r="D187" s="15" t="n">
-        <v>26.2</v>
+        <v>26.38</v>
       </c>
       <c r="E187" s="16" t="n">
-        <v>-0.3308</v>
+        <v>-0.3265</v>
       </c>
       <c r="F187" s="16" t="n">
-        <v>-0.4722</v>
+        <v>-0.4688000000000001</v>
       </c>
       <c r="G187" s="17" t="n">
         <v>46230</v>
@@ -15675,13 +15675,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>259.14</v>
+        <v>266.33</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>-0.2248</v>
+        <v>-0.2032</v>
       </c>
       <c r="F188" s="5" t="n">
-        <v>-0.2271</v>
+        <v>-0.2056</v>
       </c>
       <c r="G188" s="6" t="n">
         <v>46232</v>
@@ -15736,13 +15736,13 @@
         </is>
       </c>
       <c r="D189" s="15" t="n">
-        <v>1631.84</v>
+        <v>1655.26</v>
       </c>
       <c r="E189" s="16" t="n">
-        <v>-0.0907</v>
+        <v>-0.07769999999999999</v>
       </c>
       <c r="F189" s="20" t="n">
-        <v>0.0162</v>
+        <v>0.0308</v>
       </c>
       <c r="G189" s="17" t="n">
         <v>46309</v>
@@ -15815,13 +15815,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>35.48</v>
+        <v>36.55</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>-0.1176</v>
+        <v>-0.091</v>
       </c>
       <c r="F190" s="5" t="n">
-        <v>-0.1261</v>
+        <v>-0.0998</v>
       </c>
       <c r="G190" s="6" t="n">
         <v>46233</v>
@@ -15876,13 +15876,13 @@
         </is>
       </c>
       <c r="D191" s="15" t="n">
-        <v>379.2</v>
+        <v>383.22</v>
       </c>
       <c r="E191" s="20" t="n">
-        <v>0.0389</v>
+        <v>0.0499</v>
       </c>
       <c r="F191" s="16" t="n">
-        <v>-0.1111</v>
+        <v>-0.1016</v>
       </c>
       <c r="G191" s="17" t="n">
         <v>46268</v>
@@ -15911,7 +15911,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="20" t="n">
-        <v>0.4372362869198312</v>
+        <v>0.4221595950106987</v>
       </c>
       <c r="N191" s="14" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="20" t="n">
-        <v>0.5348101265822786</v>
+        <v>0.5187098794426177</v>
       </c>
       <c r="Q191" s="21" t="inlineStr">
         <is>
@@ -15975,13 +15975,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>147.22</v>
+        <v>151.46</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>-0.0423</v>
+        <v>-0.0147</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>-0.1577</v>
+        <v>-0.1334</v>
       </c>
       <c r="G192" s="6" t="n">
         <v>46244</v>
@@ -16036,13 +16036,13 @@
         </is>
       </c>
       <c r="D193" s="15" t="n">
-        <v>339.79</v>
+        <v>338.61</v>
       </c>
       <c r="E193" s="16" t="n">
-        <v>-0.0993</v>
+        <v>-0.1025</v>
       </c>
       <c r="F193" s="16" t="n">
-        <v>-0.0911</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="G193" s="17" t="n">
         <v>46230</v>
@@ -16071,7 +16071,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="20" t="n">
-        <v>0.2507725359781041</v>
+        <v>0.2551312719647972</v>
       </c>
       <c r="N193" s="14" t="inlineStr"/>
       <c r="O193" s="19" t="n"/>
@@ -16115,13 +16115,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>133.68</v>
+        <v>132.75</v>
       </c>
       <c r="E194" s="9" t="n">
-        <v>0.0279</v>
+        <v>0.0208</v>
       </c>
       <c r="F194" s="9" t="n">
-        <v>0.0179</v>
+        <v>0.0108</v>
       </c>
       <c r="G194" s="6" t="n">
         <v>46233</v>
@@ -16176,13 +16176,13 @@
         </is>
       </c>
       <c r="D195" s="15" t="n">
-        <v>368.39</v>
+        <v>377.27</v>
       </c>
       <c r="E195" s="16" t="n">
-        <v>-0.2317</v>
+        <v>-0.2132</v>
       </c>
       <c r="F195" s="16" t="n">
-        <v>-0.3539</v>
+        <v>-0.3383</v>
       </c>
       <c r="G195" s="17" t="n">
         <v>46268</v>
@@ -16237,13 +16237,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>14.79</v>
+        <v>14.64</v>
       </c>
       <c r="E196" s="9" t="n">
-        <v>0.07490000000000001</v>
+        <v>0.064</v>
       </c>
       <c r="F196" s="9" t="n">
-        <v>0.1205</v>
+        <v>0.1091</v>
       </c>
       <c r="G196" s="6" t="n">
         <v>46247</v>
@@ -16298,13 +16298,13 @@
         </is>
       </c>
       <c r="D197" s="15" t="n">
-        <v>303.1</v>
+        <v>318.24</v>
       </c>
       <c r="E197" s="16" t="n">
-        <v>-0.102</v>
+        <v>-0.0572</v>
       </c>
       <c r="F197" s="16" t="n">
-        <v>-0.1365</v>
+        <v>-0.0934</v>
       </c>
       <c r="G197" s="17" t="n">
         <v>46230</v>
@@ -16359,13 +16359,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>259.24</v>
+        <v>271.31</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>-0.3188</v>
+        <v>-0.2871</v>
       </c>
       <c r="F198" s="5" t="n">
-        <v>-0.3123</v>
+        <v>-0.2802</v>
       </c>
       <c r="G198" s="6" t="n">
         <v>46246</v>
@@ -16420,13 +16420,13 @@
         </is>
       </c>
       <c r="D199" s="15" t="n">
-        <v>46.64</v>
+        <v>47.81</v>
       </c>
       <c r="E199" s="16" t="n">
-        <v>-0.2722</v>
+        <v>-0.2539</v>
       </c>
       <c r="F199" s="16" t="n">
-        <v>-0.1371</v>
+        <v>-0.1154</v>
       </c>
       <c r="G199" s="17" t="n">
         <v>46233</v>
@@ -16481,13 +16481,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>20.58</v>
+        <v>20.74</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>-0.2434</v>
+        <v>-0.2375</v>
       </c>
       <c r="F200" s="5" t="n">
-        <v>-0.2586</v>
+        <v>-0.2529</v>
       </c>
       <c r="G200" s="6" t="n">
         <v>46248</v>
@@ -16542,13 +16542,13 @@
         </is>
       </c>
       <c r="D201" s="15" t="n">
-        <v>202.8</v>
+        <v>208.14</v>
       </c>
       <c r="E201" s="16" t="n">
-        <v>-0.1479</v>
+        <v>-0.1255</v>
       </c>
       <c r="F201" s="16" t="n">
-        <v>-0.08789999999999999</v>
+        <v>-0.0639</v>
       </c>
       <c r="G201" s="17" t="n">
         <v>46267</v>
@@ -16603,13 +16603,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>175.51</v>
+        <v>173.6</v>
       </c>
       <c r="E202" s="9" t="n">
-        <v>0.1082</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0146</v>
       </c>
       <c r="G202" s="6" t="n">
         <v>46267</v>
@@ -16638,7 +16638,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="9" t="n">
-        <v>0.1395362087630335</v>
+        <v>0.152073732718894</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="9" t="n">
-        <v>0.4244202609537919</v>
+        <v>0.4400921658986175</v>
       </c>
       <c r="Q202" s="10" t="inlineStr">
         <is>
@@ -16694,13 +16694,13 @@
         </is>
       </c>
       <c r="D203" s="15" t="n">
-        <v>181.6</v>
+        <v>180.11</v>
       </c>
       <c r="E203" s="20" t="n">
-        <v>0.0361</v>
+        <v>0.0276</v>
       </c>
       <c r="F203" s="20" t="n">
-        <v>0.08259999999999999</v>
+        <v>0.0737</v>
       </c>
       <c r="G203" s="17" t="n">
         <v>46260</v>
@@ -16728,8 +16728,8 @@
       <c r="L203" s="19" t="n">
         <v>181.25</v>
       </c>
-      <c r="M203" s="16" t="n">
-        <v>-0.001927312775330365</v>
+      <c r="M203" s="20" t="n">
+        <v>0.006329465326744691</v>
       </c>
       <c r="N203" s="14" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="16" t="n">
-        <v>-0.02257709251101319</v>
+        <v>-0.0144911443007052</v>
       </c>
       <c r="Q203" s="21" t="inlineStr">
         <is>
@@ -16781,13 +16781,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>70.34999999999999</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>-0.2716</v>
+        <v>-0.267</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>-0.3417</v>
+        <v>-0.3375</v>
       </c>
       <c r="G204" s="6" t="n">
         <v>46245</v>
@@ -16842,13 +16842,13 @@
         </is>
       </c>
       <c r="D205" s="15" t="n">
-        <v>113.82</v>
+        <v>114.57</v>
       </c>
       <c r="E205" s="20" t="n">
-        <v>0.0004</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F205" s="16" t="n">
-        <v>-0.0406</v>
+        <v>-0.0343</v>
       </c>
       <c r="G205" s="17" t="n">
         <v>46246</v>
@@ -16877,7 +16877,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="20" t="n">
-        <v>0.1421542786856441</v>
+        <v>0.1346774897442612</v>
       </c>
       <c r="N205" s="14" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="20" t="n">
-        <v>0.3178703215603585</v>
+        <v>0.3092432573972245</v>
       </c>
       <c r="Q205" s="21" t="inlineStr">
         <is>
@@ -16945,13 +16945,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>254.02</v>
+        <v>251.86</v>
       </c>
       <c r="E206" s="9" t="n">
-        <v>0.0594</v>
+        <v>0.0504</v>
       </c>
       <c r="F206" s="9" t="n">
-        <v>0.1278</v>
+        <v>0.1182</v>
       </c>
       <c r="G206" s="6" t="n">
         <v>46240</v>
@@ -17006,13 +17006,13 @@
         </is>
       </c>
       <c r="D207" s="15" t="n">
-        <v>422.74</v>
+        <v>426.91</v>
       </c>
       <c r="E207" s="20" t="n">
-        <v>0.0582</v>
+        <v>0.06860000000000001</v>
       </c>
       <c r="F207" s="20" t="n">
-        <v>0.3334</v>
+        <v>0.3465</v>
       </c>
       <c r="G207" s="17" t="n">
         <v>46261</v>
@@ -17067,13 +17067,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>54</v>
+        <v>52.91</v>
       </c>
       <c r="E208" s="9" t="n">
-        <v>0.1944</v>
+        <v>0.1703</v>
       </c>
       <c r="F208" s="9" t="n">
-        <v>0.0891</v>
+        <v>0.0672</v>
       </c>
       <c r="G208" s="6" t="n">
         <v>46268</v>
@@ -17128,13 +17128,13 @@
         </is>
       </c>
       <c r="D209" s="15" t="n">
-        <v>43.79</v>
+        <v>43.72</v>
       </c>
       <c r="E209" s="20" t="n">
-        <v>0.0097</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F209" s="20" t="n">
-        <v>0.081</v>
+        <v>0.07919999999999999</v>
       </c>
       <c r="G209" s="17" t="n">
         <v>46239</v>
@@ -17189,13 +17189,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>461.54</v>
+        <v>470.82</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>-0.1205</v>
+        <v>-0.1028</v>
       </c>
       <c r="F210" s="5" t="n">
-        <v>-0.309</v>
+        <v>-0.2951</v>
       </c>
       <c r="G210" s="6" t="n">
         <v>46251</v>
@@ -17250,13 +17250,13 @@
         </is>
       </c>
       <c r="D211" s="15" t="n">
-        <v>95.68000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="E211" s="16" t="n">
-        <v>-0.2681</v>
+        <v>-0.2443</v>
       </c>
       <c r="F211" s="16" t="n">
-        <v>-0.2652</v>
+        <v>-0.2413</v>
       </c>
       <c r="G211" s="17" t="n">
         <v>46232</v>
@@ -17311,13 +17311,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>152.43</v>
+        <v>152.38</v>
       </c>
       <c r="E212" s="9" t="n">
-        <v>0.0072</v>
+        <v>0.0068</v>
       </c>
       <c r="F212" s="9" t="n">
-        <v>0.1753</v>
+        <v>0.1749</v>
       </c>
       <c r="G212" s="6" t="n">
         <v>46232</v>
@@ -17372,13 +17372,13 @@
         </is>
       </c>
       <c r="D213" s="15" t="n">
-        <v>51.71</v>
+        <v>53.18</v>
       </c>
       <c r="E213" s="16" t="n">
-        <v>-0.3518</v>
+        <v>-0.3334</v>
       </c>
       <c r="F213" s="16" t="n">
-        <v>-0.3587</v>
+        <v>-0.3404</v>
       </c>
       <c r="G213" s="17" t="n">
         <v>46239</v>
@@ -17433,13 +17433,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>139.47</v>
+        <v>143.36</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>-0.3691</v>
+        <v>-0.3515</v>
       </c>
       <c r="F214" s="5" t="n">
-        <v>-0.2377</v>
+        <v>-0.2165</v>
       </c>
       <c r="G214" s="6" t="n">
         <v>46231</v>
@@ -17494,13 +17494,13 @@
         </is>
       </c>
       <c r="D215" s="15" t="n">
-        <v>33.22</v>
+        <v>32.88</v>
       </c>
       <c r="E215" s="20" t="n">
-        <v>0.1428</v>
+        <v>0.1311</v>
       </c>
       <c r="F215" s="20" t="n">
-        <v>0.1894</v>
+        <v>0.1772</v>
       </c>
       <c r="G215" s="17" t="n">
         <v>46267</v>
@@ -17555,13 +17555,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>151.16</v>
+        <v>149.28</v>
       </c>
       <c r="E216" s="9" t="n">
-        <v>0.2443</v>
+        <v>0.2288</v>
       </c>
       <c r="F216" s="9" t="n">
-        <v>0.0636</v>
+        <v>0.0503</v>
       </c>
       <c r="G216" s="6" t="n">
         <v>46268</v>
@@ -17590,7 +17590,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="9" t="n">
-        <v>0.2569462820852078</v>
+        <v>0.2727759914255091</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="8" t="n"/>
@@ -17634,13 +17634,13 @@
         </is>
       </c>
       <c r="D217" s="15" t="n">
-        <v>47.1</v>
+        <v>48.19</v>
       </c>
       <c r="E217" s="20" t="n">
-        <v>0.0776</v>
+        <v>0.1025</v>
       </c>
       <c r="F217" s="20" t="n">
-        <v>0.2327</v>
+        <v>0.2612</v>
       </c>
       <c r="G217" s="17" t="n">
         <v>46267</v>
@@ -17669,7 +17669,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="20" t="n">
-        <v>0.4225053078556263</v>
+        <v>0.3903299439717784</v>
       </c>
       <c r="N217" s="14" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="20" t="n">
-        <v>0.4861995753715498</v>
+        <v>0.4525835235526043</v>
       </c>
       <c r="Q217" s="21" t="inlineStr">
         <is>
@@ -17721,13 +17721,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>226.68</v>
+        <v>223.01</v>
       </c>
       <c r="E218" s="9" t="n">
-        <v>0.2222</v>
+        <v>0.2024</v>
       </c>
       <c r="F218" s="9" t="n">
-        <v>0.1402</v>
+        <v>0.1218</v>
       </c>
       <c r="G218" s="6" t="n">
         <v>46239</v>
@@ -17782,13 +17782,13 @@
         </is>
       </c>
       <c r="D219" s="15" t="n">
-        <v>217.3</v>
+        <v>216.28</v>
       </c>
       <c r="E219" s="16" t="n">
-        <v>-0.2</v>
+        <v>-0.2038</v>
       </c>
       <c r="F219" s="16" t="n">
-        <v>-0.1776</v>
+        <v>-0.1814</v>
       </c>
       <c r="G219" s="17" t="n">
         <v>46316</v>
@@ -17824,7 +17824,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="20" t="n">
-        <v>0.1504832029452369</v>
+        <v>0.1559090068429813</v>
       </c>
       <c r="Q219" s="21" t="inlineStr">
         <is>
@@ -17861,13 +17861,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>9.52</v>
+        <v>9.76</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>-0.3012</v>
+        <v>-0.2839</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>-0.464</v>
+        <v>-0.4508</v>
       </c>
       <c r="G220" s="6" t="n">
         <v>46247</v>
@@ -17922,13 +17922,13 @@
         </is>
       </c>
       <c r="D221" s="15" t="n">
-        <v>89.77</v>
+        <v>91.67</v>
       </c>
       <c r="E221" s="16" t="n">
-        <v>-0.3004</v>
+        <v>-0.2856</v>
       </c>
       <c r="F221" s="16" t="n">
-        <v>-0.2574</v>
+        <v>-0.2417</v>
       </c>
       <c r="G221" s="17" t="n">
         <v>46317</v>
@@ -17983,13 +17983,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>307.8</v>
+        <v>303.91</v>
       </c>
       <c r="E222" s="9" t="n">
-        <v>0.1497</v>
+        <v>0.1352</v>
       </c>
       <c r="F222" s="5" t="n">
-        <v>-0.0166</v>
+        <v>-0.029</v>
       </c>
       <c r="G222" s="6" t="n">
         <v>46254</v>
@@ -18044,13 +18044,13 @@
         </is>
       </c>
       <c r="D223" s="15" t="n">
-        <v>34.92</v>
+        <v>35.92</v>
       </c>
       <c r="E223" s="16" t="n">
-        <v>-0.2919</v>
+        <v>-0.2715</v>
       </c>
       <c r="F223" s="16" t="n">
-        <v>-0.5022</v>
+        <v>-0.4879</v>
       </c>
       <c r="G223" s="17" t="n">
         <v>46239</v>
@@ -18105,13 +18105,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>35.81</v>
+        <v>36.29</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>-0.2415</v>
+        <v>-0.2313</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>-0.4409</v>
+        <v>-0.4334</v>
       </c>
       <c r="G224" s="6" t="n">
         <v>46261</v>
@@ -18166,13 +18166,13 @@
         </is>
       </c>
       <c r="D225" s="15" t="n">
-        <v>303.85</v>
+        <v>311.49</v>
       </c>
       <c r="E225" s="16" t="n">
-        <v>-0.1527</v>
+        <v>-0.1314</v>
       </c>
       <c r="F225" s="16" t="n">
-        <v>-0.1644</v>
+        <v>-0.1434</v>
       </c>
       <c r="G225" s="17" t="n">
         <v>46289</v>
@@ -18231,13 +18231,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>308.84</v>
+        <v>313.68</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>-0.0603</v>
+        <v>-0.04559999999999999</v>
       </c>
       <c r="F226" s="5" t="n">
-        <v>-0.08929999999999999</v>
+        <v>-0.075</v>
       </c>
       <c r="G226" s="6" t="n">
         <v>46252</v>
@@ -18266,7 +18266,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="9" t="n">
-        <v>0.262789794068126</v>
+        <v>0.2433052792654935</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="8" t="n"/>
@@ -18322,13 +18322,13 @@
         </is>
       </c>
       <c r="D227" s="15" t="n">
-        <v>198.43</v>
+        <v>203.36</v>
       </c>
       <c r="E227" s="16" t="n">
-        <v>-0.2019</v>
+        <v>-0.1821</v>
       </c>
       <c r="F227" s="20" t="n">
-        <v>0.0294</v>
+        <v>0.055</v>
       </c>
       <c r="G227" s="17" t="n">
         <v>46231</v>
@@ -18357,7 +18357,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="20" t="n">
-        <v>0.5370659678476036</v>
+        <v>0.4998033044846577</v>
       </c>
       <c r="N227" s="14" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="16" t="n">
-        <v>-0.0676812981907978</v>
+        <v>-0.0902832415420929</v>
       </c>
       <c r="Q227" s="21" t="inlineStr">
         <is>
@@ -18409,13 +18409,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>95.40000000000001</v>
+        <v>98.22</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>-0.2381</v>
+        <v>-0.2156</v>
       </c>
       <c r="F228" s="5" t="n">
-        <v>-0.0892</v>
+        <v>-0.0623</v>
       </c>
       <c r="G228" s="6" t="n">
         <v>46239</v>
@@ -18470,13 +18470,13 @@
         </is>
       </c>
       <c r="D229" s="15" t="n">
-        <v>703.8</v>
+        <v>711.96</v>
       </c>
       <c r="E229" s="16" t="n">
-        <v>-0.1385</v>
+        <v>-0.1285</v>
       </c>
       <c r="F229" s="16" t="n">
-        <v>-0.1822</v>
+        <v>-0.1727</v>
       </c>
       <c r="G229" s="17" t="n">
         <v>46245</v>
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>106.96</v>
+        <v>107.82</v>
       </c>
       <c r="E230" s="9" t="n">
-        <v>0.09849999999999999</v>
+        <v>0.1073</v>
       </c>
       <c r="F230" s="5" t="n">
-        <v>-0.0429</v>
+        <v>-0.0353</v>
       </c>
       <c r="G230" s="6" t="n">
         <v>46231</v>
@@ -18592,13 +18592,13 @@
         </is>
       </c>
       <c r="D231" s="15" t="n">
-        <v>282.52</v>
+        <v>291.61</v>
       </c>
       <c r="E231" s="16" t="n">
-        <v>-0.2547</v>
+        <v>-0.2308</v>
       </c>
       <c r="F231" s="16" t="n">
-        <v>-0.1116</v>
+        <v>-0.083</v>
       </c>
       <c r="G231" s="17" t="n">
         <v>46232</v>
@@ -18627,7 +18627,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="20" t="n">
-        <v>0.5928075888432678</v>
+        <v>0.5431569562086348</v>
       </c>
       <c r="N231" s="14" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="20" t="n">
-        <v>0.2565482089763557</v>
+        <v>0.2173793765645896</v>
       </c>
       <c r="Q231" s="21" t="inlineStr">
         <is>
@@ -18683,13 +18683,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>76.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>-0.1266</v>
+        <v>-0.1141</v>
       </c>
       <c r="F232" s="5" t="n">
-        <v>-0.2003</v>
+        <v>-0.1889</v>
       </c>
       <c r="G232" s="6" t="n">
         <v>46240</v>
@@ -18744,13 +18744,13 @@
         </is>
       </c>
       <c r="D233" s="15" t="n">
-        <v>312.17</v>
+        <v>309.71</v>
       </c>
       <c r="E233" s="16" t="n">
-        <v>-0.0059</v>
+        <v>-0.0137</v>
       </c>
       <c r="F233" s="16" t="n">
-        <v>-0.0415</v>
+        <v>-0.049</v>
       </c>
       <c r="G233" s="17" t="n">
         <v>46259</v>
@@ -18805,13 +18805,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>303.67</v>
+        <v>315.7</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>-0.2186</v>
+        <v>-0.1876</v>
       </c>
       <c r="F234" s="5" t="n">
-        <v>-0.061</v>
+        <v>-0.0238</v>
       </c>
       <c r="G234" s="6" t="n">
         <v>46239</v>
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="D235" s="15" t="n">
-        <v>1309.51</v>
-      </c>
-      <c r="E235" s="16" t="n">
-        <v>-0.0029</v>
+        <v>1339.08</v>
+      </c>
+      <c r="E235" s="20" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F235" s="16" t="n">
-        <v>-0.1982</v>
+        <v>-0.1801</v>
       </c>
       <c r="G235" s="17" t="n">
         <v>46233</v>
@@ -18927,13 +18927,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>186.15</v>
+        <v>189.17</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>-0.3022</v>
+        <v>-0.2909</v>
       </c>
       <c r="F236" s="5" t="n">
-        <v>-0.09119999999999999</v>
+        <v>-0.0765</v>
       </c>
       <c r="G236" s="6" t="n">
         <v>46261</v>
@@ -18962,7 +18962,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="9" t="n">
-        <v>0.2892828364222401</v>
+        <v>0.2687001110112598</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="9" t="n">
-        <v>0.3483749664249261</v>
+        <v>0.3268488660992759</v>
       </c>
       <c r="Q236" s="10" t="inlineStr">
         <is>
@@ -19014,13 +19014,13 @@
         </is>
       </c>
       <c r="D237" s="15" t="n">
-        <v>392.12</v>
+        <v>389.1</v>
       </c>
       <c r="E237" s="20" t="n">
-        <v>0.0513</v>
+        <v>0.0432</v>
       </c>
       <c r="F237" s="16" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.08869999999999999</v>
       </c>
       <c r="G237" s="17" t="n">
         <v>46232</v>
@@ -19049,7 +19049,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="20" t="n">
-        <v>0.5938998265836989</v>
+        <v>0.6062708815214597</v>
       </c>
       <c r="N237" s="14" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="20" t="n">
-        <v>0.338875854330307</v>
+        <v>0.3492675404780262</v>
       </c>
       <c r="Q237" s="21" t="inlineStr">
         <is>
@@ -19113,13 +19113,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>424.64</v>
+        <v>423.8</v>
       </c>
       <c r="E238" s="9" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.0519</v>
       </c>
       <c r="F238" s="9" t="n">
-        <v>0.0318</v>
+        <v>0.0298</v>
       </c>
       <c r="G238" s="6" t="n">
         <v>46239</v>
@@ -19151,7 +19151,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="9" t="n">
-        <v>0.2363413715146948</v>
+        <v>0.2387918829636621</v>
       </c>
       <c r="Q238" s="10" t="inlineStr">
         <is>
@@ -19200,13 +19200,13 @@
         </is>
       </c>
       <c r="D239" s="15" t="n">
-        <v>97.90000000000001</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="E239" s="20" t="n">
-        <v>0.1894</v>
+        <v>0.1985</v>
       </c>
       <c r="F239" s="16" t="n">
-        <v>-0.3544</v>
+        <v>-0.3494</v>
       </c>
       <c r="G239" s="17" t="n">
         <v>46233</v>
@@ -19261,13 +19261,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>257.04</v>
+        <v>263.08</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>-0.3038</v>
+        <v>-0.2874</v>
       </c>
       <c r="F240" s="5" t="n">
-        <v>-0.3428</v>
+        <v>-0.3273</v>
       </c>
       <c r="G240" s="6" t="n">
         <v>46240</v>
@@ -19322,13 +19322,13 @@
         </is>
       </c>
       <c r="D241" s="15" t="n">
-        <v>869.47</v>
+        <v>900.2</v>
       </c>
       <c r="E241" s="16" t="n">
-        <v>-0.2321</v>
+        <v>-0.205</v>
       </c>
       <c r="F241" s="16" t="n">
-        <v>-0.0585</v>
+        <v>-0.0253</v>
       </c>
       <c r="G241" s="17" t="n">
         <v>46294</v>
@@ -19357,7 +19357,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="20" t="n">
-        <v>0.7539420566552036</v>
+        <v>0.6940679848922461</v>
       </c>
       <c r="N241" s="14" t="inlineStr">
         <is>
@@ -19405,13 +19405,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>185.71</v>
+        <v>187.88</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>-0.2272</v>
+        <v>-0.2181</v>
       </c>
       <c r="F242" s="5" t="n">
-        <v>-0.1795</v>
+        <v>-0.1699</v>
       </c>
       <c r="G242" s="6" t="n">
         <v>46240</v>
@@ -19466,13 +19466,13 @@
         </is>
       </c>
       <c r="D243" s="15" t="n">
-        <v>265.52</v>
+        <v>265.61</v>
       </c>
       <c r="E243" s="20" t="n">
-        <v>0.1192</v>
+        <v>0.1196</v>
       </c>
       <c r="F243" s="20" t="n">
-        <v>0.164</v>
+        <v>0.1644</v>
       </c>
       <c r="G243" s="17" t="n">
         <v>46240</v>
@@ -19527,13 +19527,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>106.97</v>
+        <v>105.56</v>
       </c>
       <c r="E244" s="9" t="n">
-        <v>0.08779999999999999</v>
+        <v>0.07339999999999999</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0292</v>
       </c>
       <c r="G244" s="6" t="n">
         <v>46323</v>
@@ -19562,7 +19562,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="9" t="n">
-        <v>0.49574647097317</v>
+        <v>0.5157256536566881</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="9" t="n">
-        <v>0.402262316537347</v>
+        <v>0.4209928003031451</v>
       </c>
       <c r="Q244" s="10" t="inlineStr">
         <is>
@@ -19618,13 +19618,13 @@
         </is>
       </c>
       <c r="D245" s="15" t="n">
-        <v>57.28</v>
+        <v>56.85</v>
       </c>
       <c r="E245" s="20" t="n">
-        <v>0.152</v>
+        <v>0.1434</v>
       </c>
       <c r="F245" s="20" t="n">
-        <v>0.1734</v>
+        <v>0.1647</v>
       </c>
       <c r="G245" s="17" t="n">
         <v>46260</v>
@@ -19679,13 +19679,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>195.8</v>
+        <v>196.51</v>
       </c>
       <c r="E246" s="9" t="n">
-        <v>0.017</v>
+        <v>0.0207</v>
       </c>
       <c r="F246" s="5" t="n">
-        <v>-0.0861</v>
+        <v>-0.0828</v>
       </c>
       <c r="G246" s="6" t="n">
         <v>46260</v>
@@ -19714,7 +19714,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="9" t="n">
-        <v>0.6087844739530132</v>
+        <v>0.6029718589384765</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="9" t="n">
-        <v>1.109295199182839</v>
+        <v>1.101674215052669</v>
       </c>
       <c r="Q246" s="10" t="inlineStr">
         <is>
@@ -19774,13 +19774,13 @@
         </is>
       </c>
       <c r="D247" s="15" t="n">
-        <v>416.06</v>
+        <v>428.88</v>
       </c>
       <c r="E247" s="16" t="n">
-        <v>-0.1484</v>
+        <v>-0.1222</v>
       </c>
       <c r="F247" s="16" t="n">
-        <v>-0.1777</v>
+        <v>-0.1524</v>
       </c>
       <c r="G247" s="17" t="n">
         <v>46240</v>
@@ -19835,13 +19835,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>263.1</v>
+        <v>267.67</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>-0.05019999999999999</v>
+        <v>-0.0338</v>
       </c>
       <c r="F248" s="5" t="n">
-        <v>-0.2034</v>
+        <v>-0.1896</v>
       </c>
       <c r="G248" s="6" t="n">
         <v>46231</v>
@@ -19892,13 +19892,13 @@
         </is>
       </c>
       <c r="D249" s="15" t="n">
-        <v>15.22</v>
+        <v>15.8</v>
       </c>
       <c r="E249" s="16" t="n">
-        <v>-0.1042</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F249" s="16" t="n">
-        <v>-0.3948</v>
+        <v>-0.3718</v>
       </c>
       <c r="G249" s="17" t="n"/>
       <c r="H249" s="23" t="inlineStr">
@@ -19943,13 +19943,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>137.99</v>
+        <v>137.43</v>
       </c>
       <c r="E250" s="9" t="n">
-        <v>0.1103</v>
+        <v>0.1058</v>
       </c>
       <c r="F250" s="9" t="n">
-        <v>0.4568</v>
+        <v>0.4509</v>
       </c>
       <c r="G250" s="6" t="n">
         <v>46259</v>
@@ -19978,7 +19978,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="9" t="n">
-        <v>0.08703529241249358</v>
+        <v>0.0914647456887142</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="5" t="n">
-        <v>-0.05790274657583889</v>
+        <v>-0.05406388706978103</v>
       </c>
       <c r="Q250" s="10" t="inlineStr">
         <is>
@@ -20030,13 +20030,13 @@
         </is>
       </c>
       <c r="D251" s="15" t="n">
-        <v>86.81</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="E251" s="16" t="n">
-        <v>-0.0424</v>
+        <v>-0.0178</v>
       </c>
       <c r="F251" s="16" t="n">
-        <v>-0.2986</v>
+        <v>-0.2806</v>
       </c>
       <c r="G251" s="17" t="n">
         <v>46237</v>
@@ -20091,13 +20091,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>252.92</v>
+        <v>262.33</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>-0.2192</v>
-      </c>
-      <c r="F252" s="5" t="n">
-        <v>-0.0228</v>
+        <v>-0.1901</v>
+      </c>
+      <c r="F252" s="9" t="n">
+        <v>0.0136</v>
       </c>
       <c r="G252" s="6" t="n">
         <v>46240</v>
@@ -20152,13 +20152,13 @@
         </is>
       </c>
       <c r="D253" s="15" t="n">
-        <v>120.04</v>
+        <v>119.9</v>
       </c>
       <c r="E253" s="16" t="n">
-        <v>-0.1918</v>
+        <v>-0.1928</v>
       </c>
       <c r="F253" s="16" t="n">
-        <v>-0.4107</v>
+        <v>-0.4114</v>
       </c>
       <c r="G253" s="17" t="n">
         <v>46273</v>
@@ -20187,7 +20187,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="20" t="n">
-        <v>1.332555814728424</v>
+        <v>1.335279399499583</v>
       </c>
       <c r="N253" s="14" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="20" t="n">
-        <v>1.040986337887371</v>
+        <v>1.043369474562135</v>
       </c>
       <c r="Q253" s="21" t="inlineStr">
         <is>
@@ -20239,13 +20239,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>318.98</v>
+        <v>317.32</v>
       </c>
       <c r="E254" s="9" t="n">
-        <v>0.0486</v>
+        <v>0.0431</v>
       </c>
       <c r="F254" s="9" t="n">
-        <v>0.2375</v>
+        <v>0.231</v>
       </c>
       <c r="G254" s="6" t="n">
         <v>46251</v>
@@ -20274,7 +20274,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="9" t="n">
-        <v>0.3166969715969652</v>
+        <v>0.3235850245808647</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="9" t="n">
-        <v>0.3010220076493823</v>
+        <v>0.3078280600025212</v>
       </c>
       <c r="Q254" s="10" t="inlineStr">
         <is>
@@ -20334,13 +20334,13 @@
         </is>
       </c>
       <c r="D255" s="15" t="n">
-        <v>11.59</v>
+        <v>11.62</v>
       </c>
       <c r="E255" s="20" t="n">
-        <v>0.1002</v>
+        <v>0.1035</v>
       </c>
       <c r="F255" s="20" t="n">
-        <v>0.0004</v>
+        <v>0.0035</v>
       </c>
       <c r="G255" s="17" t="n">
         <v>46268</v>
@@ -20395,13 +20395,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>29.38</v>
+        <v>28.6</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>-0.0455</v>
+        <v>-0.0708</v>
       </c>
       <c r="F256" s="5" t="n">
-        <v>-0.1318</v>
+        <v>-0.1548</v>
       </c>
       <c r="G256" s="6" t="n">
         <v>46315</v>
@@ -20456,13 +20456,13 @@
         </is>
       </c>
       <c r="D257" s="15" t="n">
-        <v>127.88</v>
+        <v>130.29</v>
       </c>
       <c r="E257" s="16" t="n">
-        <v>-0.0351</v>
+        <v>-0.0169</v>
       </c>
       <c r="F257" s="16" t="n">
-        <v>-0.1849</v>
+        <v>-0.1695</v>
       </c>
       <c r="G257" s="17" t="n">
         <v>46232</v>
@@ -20517,13 +20517,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>131.6</v>
+        <v>131.53</v>
       </c>
       <c r="E258" s="9" t="n">
-        <v>0.1653</v>
+        <v>0.1647</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>-0.0819</v>
+        <v>-0.0824</v>
       </c>
       <c r="G258" s="6" t="n">
         <v>46237</v>
@@ -20578,13 +20578,13 @@
         </is>
       </c>
       <c r="D259" s="15" t="n">
-        <v>130.32</v>
+        <v>132.97</v>
       </c>
       <c r="E259" s="16" t="n">
-        <v>-0.1763</v>
+        <v>-0.1595</v>
       </c>
       <c r="F259" s="16" t="n">
-        <v>-0.1802</v>
+        <v>-0.1635</v>
       </c>
       <c r="G259" s="17" t="n">
         <v>46238</v>
@@ -20649,13 +20649,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>18.95</v>
+        <v>19.51</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>-0.1674</v>
+        <v>-0.1428</v>
       </c>
       <c r="F260" s="5" t="n">
-        <v>-0.3574</v>
+        <v>-0.3384</v>
       </c>
       <c r="G260" s="6" t="n">
         <v>46240</v>
@@ -20710,13 +20710,13 @@
         </is>
       </c>
       <c r="D261" s="15" t="n">
-        <v>167.8</v>
+        <v>170.04</v>
       </c>
       <c r="E261" s="16" t="n">
-        <v>-0.114</v>
+        <v>-0.1022</v>
       </c>
       <c r="F261" s="16" t="n">
-        <v>-0.3103</v>
+        <v>-0.3011</v>
       </c>
       <c r="G261" s="17" t="n">
         <v>46232</v>
@@ -20745,7 +20745,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="20" t="n">
-        <v>0.5792610250297973</v>
+        <v>0.5584568336861916</v>
       </c>
       <c r="N261" s="14" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>179</v>
       </c>
       <c r="P261" s="20" t="n">
-        <v>0.06674612634088194</v>
+        <v>0.05269348388614448</v>
       </c>
       <c r="Q261" s="21" t="inlineStr">
         <is>
@@ -20801,13 +20801,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>88.72</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>-0.055</v>
+        <v>-0.04389999999999999</v>
       </c>
       <c r="F262" s="5" t="n">
-        <v>-0.1663</v>
+        <v>-0.1565</v>
       </c>
       <c r="G262" s="6" t="n">
         <v>46231</v>
@@ -20862,13 +20862,13 @@
         </is>
       </c>
       <c r="D263" s="15" t="n">
-        <v>7.8</v>
+        <v>7.96</v>
       </c>
       <c r="E263" s="16" t="n">
-        <v>-0.1503</v>
+        <v>-0.1329</v>
       </c>
       <c r="F263" s="16" t="n">
-        <v>-0.3627</v>
+        <v>-0.3497</v>
       </c>
       <c r="G263" s="17" t="n">
         <v>46247</v>
@@ -20923,13 +20923,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>74.91</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="E264" s="9" t="n">
-        <v>0.0357</v>
+        <v>0.0344</v>
       </c>
       <c r="F264" s="9" t="n">
-        <v>0.0653</v>
+        <v>0.064</v>
       </c>
       <c r="G264" s="6" t="n">
         <v>46273</v>
@@ -20984,13 +20984,13 @@
         </is>
       </c>
       <c r="D265" s="15" t="n">
-        <v>15.16</v>
+        <v>15.64</v>
       </c>
       <c r="E265" s="16" t="n">
-        <v>-0.1743</v>
+        <v>-0.1481</v>
       </c>
       <c r="F265" s="16" t="n">
-        <v>-0.4391</v>
+        <v>-0.4214</v>
       </c>
       <c r="G265" s="17" t="n">
         <v>46240</v>
@@ -21045,13 +21045,13 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>379.15</v>
+        <v>375.02</v>
       </c>
       <c r="E266" s="9" t="n">
-        <v>0.1207</v>
+        <v>0.1085</v>
       </c>
       <c r="F266" s="9" t="n">
-        <v>0.1858</v>
+        <v>0.1729</v>
       </c>
       <c r="G266" s="6" t="n">
         <v>46317</v>
@@ -21120,13 +21120,13 @@
         </is>
       </c>
       <c r="D267" s="15" t="n">
-        <v>3.81</v>
+        <v>3.86</v>
       </c>
       <c r="E267" s="16" t="n">
-        <v>-0.3637</v>
+        <v>-0.3545</v>
       </c>
       <c r="F267" s="16" t="n">
-        <v>-0.2155</v>
+        <v>-0.2041</v>
       </c>
       <c r="G267" s="17" t="n">
         <v>46240</v>
@@ -21181,13 +21181,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>18.27</v>
+        <v>18.14</v>
       </c>
       <c r="E268" s="9" t="n">
-        <v>0.1486</v>
+        <v>0.1402</v>
       </c>
       <c r="F268" s="9" t="n">
-        <v>0.0142</v>
+        <v>0.0067</v>
       </c>
       <c r="G268" s="6" t="n">
         <v>46261</v>
@@ -21242,13 +21242,13 @@
         </is>
       </c>
       <c r="D269" s="15" t="n">
-        <v>15.73</v>
+        <v>15.34</v>
       </c>
       <c r="E269" s="20" t="n">
-        <v>0.1939</v>
+        <v>0.1639</v>
       </c>
       <c r="F269" s="16" t="n">
-        <v>-0.0492</v>
+        <v>-0.0731</v>
       </c>
       <c r="G269" s="17" t="n">
         <v>46273</v>
@@ -21303,13 +21303,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>201.2</v>
+        <v>208.9</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>-0.1494</v>
+        <v>-0.1169</v>
       </c>
       <c r="F270" s="5" t="n">
-        <v>-0.2356</v>
+        <v>-0.2064</v>
       </c>
       <c r="G270" s="6" t="n">
         <v>46230</v>
@@ -21364,13 +21364,13 @@
         </is>
       </c>
       <c r="D271" s="15" t="n">
-        <v>172.66</v>
+        <v>171.01</v>
       </c>
       <c r="E271" s="20" t="n">
-        <v>0.1133</v>
+        <v>0.1027</v>
       </c>
       <c r="F271" s="16" t="n">
-        <v>-0.016</v>
+        <v>-0.0254</v>
       </c>
       <c r="G271" s="17" t="n">
         <v>46316</v>
@@ -21445,13 +21445,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>28.93</v>
+        <v>29.81</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>-0.0553</v>
+        <v>-0.0268</v>
       </c>
       <c r="F272" s="5" t="n">
-        <v>-0.2994</v>
+        <v>-0.2782</v>
       </c>
       <c r="G272" s="6" t="n">
         <v>46245</v>
@@ -21506,13 +21506,13 @@
         </is>
       </c>
       <c r="D273" s="15" t="n">
-        <v>270.46</v>
+        <v>272.92</v>
       </c>
       <c r="E273" s="20" t="n">
-        <v>0.0864</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="F273" s="20" t="n">
-        <v>0.1307</v>
+        <v>0.141</v>
       </c>
       <c r="G273" s="17" t="n">
         <v>46260</v>
@@ -21541,7 +21541,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="20" t="n">
-        <v>0.1831694150706205</v>
+        <v>0.1725047633006008</v>
       </c>
       <c r="N273" s="14" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="20" t="n">
-        <v>0.03527323818679295</v>
+        <v>0.02594166788802573</v>
       </c>
       <c r="Q273" s="21" t="inlineStr">
         <is>
@@ -21593,13 +21593,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>390.02</v>
+        <v>388.99</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>-0.1416</v>
+        <v>-0.1438</v>
       </c>
       <c r="F274" s="5" t="n">
-        <v>-0.1885</v>
+        <v>-0.1907</v>
       </c>
       <c r="G274" s="6" t="n">
         <v>46260</v>
@@ -21628,7 +21628,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="9" t="n">
-        <v>0.3717245269473361</v>
+        <v>0.3753566929741124</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="8" t="n"/>
@@ -21672,13 +21672,13 @@
         </is>
       </c>
       <c r="D275" s="15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="E275" s="16" t="n">
-        <v>-0.0019</v>
+        <v>6.41</v>
+      </c>
+      <c r="E275" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="F275" s="16" t="n">
-        <v>-0.2526</v>
+        <v>-0.2512</v>
       </c>
       <c r="G275" s="17" t="n">
         <v>46239</v>
@@ -21733,13 +21733,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>62.25</v>
+        <v>63.44</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>-0.08460000000000001</v>
+        <v>-0.06709999999999999</v>
       </c>
       <c r="F276" s="5" t="n">
-        <v>-0.2354</v>
+        <v>-0.2207</v>
       </c>
       <c r="G276" s="6" t="n">
         <v>46231</v>
@@ -21794,13 +21794,13 @@
         </is>
       </c>
       <c r="D277" s="15" t="n">
-        <v>113.42</v>
+        <v>116.42</v>
       </c>
       <c r="E277" s="16" t="n">
-        <v>-0.0626</v>
+        <v>-0.0379</v>
       </c>
       <c r="F277" s="16" t="n">
-        <v>-0.2083</v>
+        <v>-0.1874</v>
       </c>
       <c r="G277" s="17" t="n">
         <v>46240</v>
@@ -21855,13 +21855,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>205.43</v>
+        <v>207.58</v>
       </c>
       <c r="E278" s="9" t="n">
-        <v>0.0389</v>
+        <v>0.0498</v>
       </c>
       <c r="F278" s="5" t="n">
-        <v>-0.0233</v>
+        <v>-0.0131</v>
       </c>
       <c r="G278" s="6" t="n">
         <v>46330</v>
@@ -21916,13 +21916,13 @@
         </is>
       </c>
       <c r="D279" s="15" t="n">
-        <v>327.67</v>
+        <v>334.77</v>
       </c>
       <c r="E279" s="16" t="n">
-        <v>-0.2499</v>
+        <v>-0.2337</v>
       </c>
       <c r="F279" s="16" t="n">
-        <v>-0.1437</v>
+        <v>-0.1251</v>
       </c>
       <c r="G279" s="17" t="n">
         <v>46231</v>
@@ -21977,13 +21977,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>55.72</v>
+        <v>55.77</v>
       </c>
       <c r="E280" s="9" t="n">
-        <v>0.099</v>
+        <v>0.1</v>
       </c>
       <c r="F280" s="9" t="n">
-        <v>0.0146</v>
+        <v>0.0155</v>
       </c>
       <c r="G280" s="6" t="n">
         <v>46239</v>
@@ -22038,13 +22038,13 @@
         </is>
       </c>
       <c r="D281" s="15" t="n">
-        <v>392</v>
+        <v>399.09</v>
       </c>
       <c r="E281" s="16" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F281" s="16" t="n">
-        <v>-0.07730000000000001</v>
+        <v>-0.0607</v>
       </c>
       <c r="G281" s="17" t="n">
         <v>46310</v>
@@ -22121,13 +22121,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>121.79</v>
+        <v>123.71</v>
       </c>
       <c r="E282" s="5" t="n">
-        <v>-0.364</v>
+        <v>-0.354</v>
       </c>
       <c r="F282" s="5" t="n">
-        <v>-0.3515</v>
+        <v>-0.3411999999999999</v>
       </c>
       <c r="G282" s="6" t="n">
         <v>46239</v>
@@ -22182,13 +22182,13 @@
         </is>
       </c>
       <c r="D283" s="15" t="n">
-        <v>195.11</v>
+        <v>194.47</v>
       </c>
       <c r="E283" s="20" t="n">
-        <v>0.0185</v>
+        <v>0.0151</v>
       </c>
       <c r="F283" s="20" t="n">
-        <v>0.05690000000000001</v>
+        <v>0.0535</v>
       </c>
       <c r="G283" s="17" t="n">
         <v>46240</v>
@@ -22243,13 +22243,13 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>276.93</v>
+        <v>279.41</v>
       </c>
       <c r="E284" s="5" t="n">
-        <v>-0.0298</v>
+        <v>-0.0211</v>
       </c>
       <c r="F284" s="5" t="n">
-        <v>-0.1235</v>
+        <v>-0.1157</v>
       </c>
       <c r="G284" s="6" t="n">
         <v>46315</v>
@@ -22278,7 +22278,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="9" t="n">
-        <v>0.08330625067706637</v>
+        <v>0.07369099173257927</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="9" t="n">
-        <v>0.1410825840465099</v>
+        <v>0.1309545112916502</v>
       </c>
       <c r="Q284" s="10" t="inlineStr">
         <is>
@@ -22346,13 +22346,13 @@
         </is>
       </c>
       <c r="D285" s="15" t="n">
-        <v>320.15</v>
+        <v>315.88</v>
       </c>
       <c r="E285" s="20" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.073</v>
       </c>
       <c r="F285" s="20" t="n">
-        <v>0.0461</v>
+        <v>0.0322</v>
       </c>
       <c r="G285" s="17" t="n">
         <v>46232</v>
@@ -22381,7 +22381,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="20" t="n">
-        <v>0.04638450726222091</v>
+        <v>0.06052931492972016</v>
       </c>
       <c r="N285" s="14" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="20" t="n">
-        <v>0.1713259409651726</v>
+        <v>0.1871596808914778</v>
       </c>
       <c r="Q285" s="21" t="inlineStr">
         <is>
@@ -22433,13 +22433,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>30.61</v>
+        <v>30.44</v>
       </c>
       <c r="E286" s="9" t="n">
-        <v>0.0843</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="F286" s="9" t="n">
-        <v>0.0224</v>
+        <v>0.0167</v>
       </c>
       <c r="G286" s="6" t="n">
         <v>46240</v>
@@ -22494,13 +22494,13 @@
         </is>
       </c>
       <c r="D287" s="15" t="n">
-        <v>7.11</v>
+        <v>7.17</v>
       </c>
       <c r="E287" s="16" t="n">
-        <v>-0.0699</v>
+        <v>-0.06269999999999999</v>
       </c>
       <c r="F287" s="16" t="n">
-        <v>-0.33</v>
+        <v>-0.3249</v>
       </c>
       <c r="G287" s="17" t="n">
         <v>46254</v>
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>148.75</v>
+        <v>147.54</v>
       </c>
       <c r="E288" s="9" t="n">
-        <v>0.1976</v>
+        <v>0.1878</v>
       </c>
       <c r="F288" s="9" t="n">
-        <v>0.1441</v>
+        <v>0.1348</v>
       </c>
       <c r="G288" s="6" t="n">
         <v>46254</v>
@@ -22616,13 +22616,13 @@
         </is>
       </c>
       <c r="D289" s="15" t="n">
-        <v>488.34</v>
+        <v>497.92</v>
       </c>
       <c r="E289" s="16" t="n">
-        <v>-0.1673</v>
+        <v>-0.151</v>
       </c>
       <c r="F289" s="16" t="n">
-        <v>-0.08070000000000001</v>
+        <v>-0.0626</v>
       </c>
       <c r="G289" s="17" t="n">
         <v>46239</v>
@@ -22651,7 +22651,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="20" t="n">
-        <v>0.4948601384281444</v>
+        <v>0.466098971722365</v>
       </c>
       <c r="N289" s="14" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="20" t="n">
-        <v>0.1774583282139494</v>
+        <v>0.1548039845758354</v>
       </c>
       <c r="Q289" s="21" t="inlineStr">
         <is>
@@ -22703,13 +22703,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>22.6</v>
+        <v>23.8</v>
       </c>
       <c r="E290" s="5" t="n">
-        <v>-0.5083</v>
+        <v>-0.4823</v>
       </c>
       <c r="F290" s="5" t="n">
-        <v>-0.6525</v>
+        <v>-0.6341</v>
       </c>
       <c r="G290" s="6" t="n">
         <v>46238</v>
@@ -22764,13 +22764,13 @@
         </is>
       </c>
       <c r="D291" s="15" t="n">
-        <v>91.27</v>
+        <v>91.22</v>
       </c>
       <c r="E291" s="20" t="n">
-        <v>0.0553</v>
+        <v>0.0548</v>
       </c>
       <c r="F291" s="16" t="n">
-        <v>-0.0915</v>
+        <v>-0.092</v>
       </c>
       <c r="G291" s="17" t="n">
         <v>46254</v>
@@ -22825,13 +22825,13 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>147.57</v>
+        <v>147.3</v>
       </c>
       <c r="E292" s="9" t="n">
-        <v>0.1158</v>
+        <v>0.1137</v>
       </c>
       <c r="F292" s="9" t="n">
-        <v>0.1348</v>
+        <v>0.1327</v>
       </c>
       <c r="G292" s="6" t="n">
         <v>46266</v>
@@ -22886,13 +22886,13 @@
         </is>
       </c>
       <c r="D293" s="15" t="n">
-        <v>293.11</v>
+        <v>292.58</v>
       </c>
       <c r="E293" s="20" t="n">
-        <v>0.0551</v>
+        <v>0.0532</v>
       </c>
       <c r="F293" s="20" t="n">
-        <v>0.0334</v>
+        <v>0.0315</v>
       </c>
       <c r="G293" s="17" t="n">
         <v>46233</v>
@@ -22947,13 +22947,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>82.92</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="E294" s="9" t="n">
-        <v>0.0235</v>
+        <v>0.0359</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>-0.0556</v>
+        <v>-0.0441</v>
       </c>
       <c r="G294" s="6" t="n">
         <v>46252</v>
@@ -23008,13 +23008,13 @@
         </is>
       </c>
       <c r="D295" s="15" t="n">
-        <v>137.68</v>
+        <v>139.96</v>
       </c>
       <c r="E295" s="20" t="n">
-        <v>0.0034</v>
+        <v>0.02</v>
       </c>
       <c r="F295" s="16" t="n">
-        <v>-0.0381</v>
+        <v>-0.0221</v>
       </c>
       <c r="G295" s="17" t="n">
         <v>46238</v>
@@ -23043,7 +23043,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="20" t="n">
-        <v>0.2056943637420104</v>
+        <v>0.1860531580451557</v>
       </c>
       <c r="N295" s="14" t="inlineStr"/>
       <c r="O295" s="19" t="n"/>
@@ -23091,13 +23091,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>28.8</v>
+        <v>28.75</v>
       </c>
       <c r="E296" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.01</v>
       </c>
       <c r="F296" s="5" t="n">
-        <v>-0.1717</v>
+        <v>-0.1731</v>
       </c>
       <c r="G296" s="6" t="n">
         <v>46317</v>
@@ -23152,13 +23152,13 @@
         </is>
       </c>
       <c r="D297" s="15" t="n">
-        <v>271.6</v>
+        <v>271.38</v>
       </c>
       <c r="E297" s="16" t="n">
-        <v>-0.0425</v>
+        <v>-0.0433</v>
       </c>
       <c r="F297" s="20" t="n">
-        <v>0.0436</v>
+        <v>0.0428</v>
       </c>
       <c r="G297" s="17" t="n">
         <v>46231</v>
@@ -23187,7 +23187,7 @@
         <v>275</v>
       </c>
       <c r="M297" s="20" t="n">
-        <v>0.01251840942562584</v>
+        <v>0.0133392291252119</v>
       </c>
       <c r="N297" s="14" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="20" t="n">
-        <v>0.1487481590574373</v>
+        <v>0.149679416316604</v>
       </c>
       <c r="Q297" s="21" t="inlineStr">
         <is>
@@ -23251,13 +23251,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>37.03</v>
+        <v>37.84</v>
       </c>
       <c r="E298" s="5" t="n">
-        <v>-0.1891</v>
+        <v>-0.1713</v>
       </c>
       <c r="F298" s="5" t="n">
-        <v>-0.1168</v>
+        <v>-0.0973</v>
       </c>
       <c r="G298" s="6" t="n">
         <v>46230</v>
@@ -23316,13 +23316,13 @@
         </is>
       </c>
       <c r="D299" s="15" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="E299" s="16" t="n">
-        <v>-0.0135</v>
+        <v>62.72</v>
+      </c>
+      <c r="E299" s="20" t="n">
+        <v>0.0043</v>
       </c>
       <c r="F299" s="16" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.0478</v>
       </c>
       <c r="G299" s="17" t="n">
         <v>46310</v>
@@ -23377,13 +23377,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>508.26</v>
+        <v>507.02</v>
       </c>
       <c r="E300" s="5" t="n">
-        <v>-0.0219</v>
+        <v>-0.0242</v>
       </c>
       <c r="F300" s="9" t="n">
-        <v>0.0125</v>
+        <v>0.01</v>
       </c>
       <c r="G300" s="6" t="n">
         <v>46234</v>
@@ -23412,7 +23412,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="9" t="n">
-        <v>0.1214732617164444</v>
+        <v>0.1242160072580964</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="9" t="n">
-        <v>0.03293589894935665</v>
+        <v>0.03546211194824665</v>
       </c>
       <c r="Q300" s="10" t="inlineStr">
         <is>
@@ -23476,13 +23476,13 @@
         </is>
       </c>
       <c r="D301" s="15" t="n">
-        <v>571.3099999999999</v>
+        <v>572.03</v>
       </c>
       <c r="E301" s="16" t="n">
-        <v>-0.0726</v>
+        <v>-0.07150000000000001</v>
       </c>
       <c r="F301" s="16" t="n">
-        <v>-0.0067</v>
+        <v>-0.0054</v>
       </c>
       <c r="G301" s="17" t="n">
         <v>46233</v>
@@ -23511,7 +23511,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="20" t="n">
-        <v>0.07822373142427064</v>
+        <v>0.0768665979057043</v>
       </c>
       <c r="N301" s="14" t="inlineStr"/>
       <c r="O301" s="19" t="n"/>
@@ -23555,13 +23555,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>245.79</v>
+        <v>247.86</v>
       </c>
       <c r="E302" s="9" t="n">
-        <v>0.025</v>
+        <v>0.0337</v>
       </c>
       <c r="F302" s="5" t="n">
-        <v>-0.0141</v>
+        <v>-0.0058</v>
       </c>
       <c r="G302" s="6" t="n">
         <v>46230</v>
@@ -23590,7 +23590,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="9" t="n">
-        <v>0.1513893974531104</v>
+        <v>0.1417735818607278</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="8" t="n"/>
@@ -23636,13 +23636,13 @@
         </is>
       </c>
       <c r="D303" s="15" t="n">
-        <v>250.6</v>
+        <v>252.37</v>
       </c>
       <c r="E303" s="20" t="n">
-        <v>0.0375</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="F303" s="20" t="n">
-        <v>0.1488</v>
+        <v>0.1569</v>
       </c>
       <c r="G303" s="17" t="n">
         <v>46321</v>
@@ -23671,7 +23671,7 @@
         <v>246</v>
       </c>
       <c r="M303" s="16" t="n">
-        <v>-0.01835594573024739</v>
+        <v>-0.02524071799342237</v>
       </c>
       <c r="N303" s="14" t="inlineStr"/>
       <c r="O303" s="19" t="n"/>
@@ -23719,13 +23719,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>118.2</v>
+        <v>118.47</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>-0.0409</v>
+        <v>-0.0387</v>
       </c>
       <c r="F304" s="9" t="n">
-        <v>0.0473</v>
+        <v>0.04969999999999999</v>
       </c>
       <c r="G304" s="6" t="n">
         <v>46231</v>
@@ -23754,7 +23754,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="9" t="n">
-        <v>0.09983079526226732</v>
+        <v>0.09732421710137588</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="9" t="n">
-        <v>0.08291032148900167</v>
+        <v>0.08044230606904702</v>
       </c>
       <c r="Q304" s="10" t="inlineStr">
         <is>
@@ -23814,13 +23814,13 @@
         </is>
       </c>
       <c r="D305" s="15" t="n">
-        <v>108.53</v>
+        <v>107.77</v>
       </c>
       <c r="E305" s="16" t="n">
-        <v>-0.0349</v>
+        <v>-0.0417</v>
       </c>
       <c r="F305" s="20" t="n">
-        <v>0.0152</v>
+        <v>0.008</v>
       </c>
       <c r="G305" s="17" t="n">
         <v>46302</v>
@@ -23849,7 +23849,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="20" t="n">
-        <v>0.2438956970422924</v>
+        <v>0.2526677182889487</v>
       </c>
       <c r="N305" s="14" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="20" t="n">
-        <v>0.1517552750391597</v>
+        <v>0.1598775169342118</v>
       </c>
       <c r="Q305" s="21" t="inlineStr"/>
       <c r="R305" s="19" t="n"/>
@@ -23895,13 +23895,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>327.3</v>
+        <v>327.27</v>
       </c>
       <c r="E306" s="5" t="n">
         <v>-0.0488</v>
       </c>
       <c r="F306" s="9" t="n">
-        <v>0.0726</v>
+        <v>0.0725</v>
       </c>
       <c r="G306" s="6" t="n">
         <v>46231</v>
@@ -23930,7 +23930,7 @@
         <v>350</v>
       </c>
       <c r="M306" s="9" t="n">
-        <v>0.06935533150015273</v>
+        <v>0.06945335655574914</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="9" t="n">
-        <v>0.2221203788573174</v>
+        <v>0.2222324074922847</v>
       </c>
       <c r="Q306" s="10" t="inlineStr">
         <is>
@@ -23982,13 +23982,13 @@
         </is>
       </c>
       <c r="D307" s="15" t="n">
-        <v>73.16</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="E307" s="20" t="n">
-        <v>0.0578</v>
+        <v>0.073</v>
       </c>
       <c r="F307" s="20" t="n">
-        <v>0.0016</v>
+        <v>0.016</v>
       </c>
       <c r="G307" s="17" t="n">
         <v>46260</v>
@@ -24039,13 +24039,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>51.67</v>
+        <v>52.83</v>
       </c>
       <c r="E308" s="5" t="n">
-        <v>-0.3163</v>
+        <v>-0.3009</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>-0.1443</v>
+        <v>-0.125</v>
       </c>
       <c r="G308" s="6" t="n">
         <v>46267</v>
@@ -24100,13 +24100,13 @@
         </is>
       </c>
       <c r="D309" s="15" t="n">
-        <v>81.02</v>
+        <v>80.45</v>
       </c>
       <c r="E309" s="20" t="n">
-        <v>0.0518</v>
+        <v>0.0444</v>
       </c>
       <c r="F309" s="20" t="n">
-        <v>0.0868</v>
+        <v>0.0791</v>
       </c>
       <c r="G309" s="17" t="n">
         <v>46233</v>
@@ -24135,14 +24135,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="20" t="n">
-        <v>0.02443841026906942</v>
+        <v>0.03169670602858915</v>
       </c>
       <c r="N309" s="14" t="inlineStr"/>
       <c r="O309" s="19" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="20" t="n">
-        <v>0.07380893606516915</v>
+        <v>0.08141702921068983</v>
       </c>
       <c r="Q309" s="21" t="inlineStr"/>
       <c r="R309" s="19" t="n"/>
@@ -24177,13 +24177,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>167.47</v>
+        <v>166.74</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>-0.0462</v>
+        <v>-0.0504</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>-0.1029</v>
+        <v>-0.1068</v>
       </c>
       <c r="G310" s="6" t="n">
         <v>46231</v>
@@ -24212,7 +24212,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="9" t="n">
-        <v>0.1942437451483848</v>
+        <v>0.1994722322178241</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="8" t="n"/>
@@ -24260,13 +24260,13 @@
         </is>
       </c>
       <c r="D311" s="15" t="n">
-        <v>143.08</v>
+        <v>143.88</v>
       </c>
       <c r="E311" s="20" t="n">
-        <v>0.0413</v>
+        <v>0.0472</v>
       </c>
       <c r="F311" s="20" t="n">
-        <v>0.1318</v>
+        <v>0.1381</v>
       </c>
       <c r="G311" s="17" t="n">
         <v>46232</v>
@@ -24325,13 +24325,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>192.38</v>
-      </c>
-      <c r="E312" s="5" t="n">
-        <v>-0.0032</v>
+        <v>195.76</v>
+      </c>
+      <c r="E312" s="9" t="n">
+        <v>0.0143</v>
       </c>
       <c r="F312" s="9" t="n">
-        <v>0.005</v>
+        <v>0.0226</v>
       </c>
       <c r="G312" s="6" t="n">
         <v>46317</v>
@@ -24360,7 +24360,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="9" t="n">
-        <v>0.1435700176733548</v>
+        <v>0.1238250919493258</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="9" t="n">
-        <v>0.1955504730221437</v>
+        <v>0.1749080506742951</v>
       </c>
       <c r="Q312" s="10" t="inlineStr">
         <is>
@@ -24412,13 +24412,13 @@
         </is>
       </c>
       <c r="D313" s="15" t="n">
-        <v>1045.2</v>
+        <v>1046.79</v>
       </c>
       <c r="E313" s="16" t="n">
-        <v>-0.04219999999999999</v>
+        <v>-0.0408</v>
       </c>
       <c r="F313" s="16" t="n">
-        <v>-0.0227</v>
+        <v>-0.0212</v>
       </c>
       <c r="G313" s="17" t="n">
         <v>46232</v>
@@ -24447,7 +24447,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="20" t="n">
-        <v>0.148105625717566</v>
+        <v>0.1463617344453043</v>
       </c>
       <c r="N313" s="14" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="20" t="n">
-        <v>0.1863758132414848</v>
+        <v>0.1845737922601477</v>
       </c>
       <c r="Q313" s="21" t="inlineStr">
         <is>
@@ -24503,13 +24503,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>126.81</v>
+        <v>127.13</v>
       </c>
       <c r="E314" s="9" t="n">
-        <v>0.0138</v>
+        <v>0.0164</v>
       </c>
       <c r="F314" s="9" t="n">
-        <v>0.0478</v>
+        <v>0.0505</v>
       </c>
       <c r="G314" s="6" t="n">
         <v>46234</v>
@@ -24538,7 +24538,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="9" t="n">
-        <v>0.01726993139342321</v>
+        <v>0.01470935263116499</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>122</v>
       </c>
       <c r="P314" s="5" t="n">
-        <v>-0.03793076255815789</v>
+        <v>-0.04035239518603002</v>
       </c>
       <c r="Q314" s="10" t="inlineStr">
         <is>
@@ -24590,13 +24590,13 @@
         </is>
       </c>
       <c r="D315" s="15" t="n">
-        <v>65.76000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="E315" s="20" t="n">
-        <v>0.0417</v>
+        <v>0.0377</v>
       </c>
       <c r="F315" s="20" t="n">
-        <v>0.0659</v>
+        <v>0.06179999999999999</v>
       </c>
       <c r="G315" s="17" t="n">
         <v>46239</v>
@@ -24625,14 +24625,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="16" t="n">
-        <v>-0.01155717761557185</v>
+        <v>-0.007633587786259542</v>
       </c>
       <c r="N315" s="14" t="inlineStr"/>
       <c r="O315" s="19" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="20" t="n">
-        <v>0.0188564476885644</v>
+        <v>0.02290076335877863</v>
       </c>
       <c r="Q315" s="21" t="inlineStr">
         <is>
@@ -24673,13 +24673,13 @@
         </is>
       </c>
       <c r="D316" s="4" t="n">
-        <v>145.91</v>
+        <v>147.26</v>
       </c>
       <c r="E316" s="9" t="n">
-        <v>0.0424</v>
+        <v>0.0521</v>
       </c>
       <c r="F316" s="9" t="n">
-        <v>0.0019</v>
+        <v>0.0111</v>
       </c>
       <c r="G316" s="6" t="n">
         <v>46309</v>
@@ -24708,7 +24708,7 @@
         <v>167</v>
       </c>
       <c r="M316" s="9" t="n">
-        <v>0.1445411555068193</v>
+        <v>0.1340486214858075</v>
       </c>
       <c r="N316" s="3" t="inlineStr"/>
       <c r="O316" s="8" t="n"/>
@@ -24752,13 +24752,13 @@
         </is>
       </c>
       <c r="D317" s="15" t="n">
-        <v>324.36</v>
+        <v>324.02</v>
       </c>
       <c r="E317" s="16" t="n">
-        <v>-0.0001</v>
+        <v>-0.0011</v>
       </c>
       <c r="F317" s="20" t="n">
-        <v>0.0489</v>
+        <v>0.0478</v>
       </c>
       <c r="G317" s="17" t="n">
         <v>46232</v>
@@ -24794,7 +24794,7 @@
         <v>316</v>
       </c>
       <c r="P317" s="16" t="n">
-        <v>-0.02577383154519674</v>
+        <v>-0.02475155854576873</v>
       </c>
       <c r="Q317" s="21" t="inlineStr">
         <is>
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>230.27</v>
+        <v>231.67</v>
       </c>
       <c r="E318" s="9" t="n">
-        <v>0.0149</v>
+        <v>0.0211</v>
       </c>
       <c r="F318" s="9" t="n">
-        <v>0.1137</v>
+        <v>0.1204</v>
       </c>
       <c r="G318" s="6" t="n">
         <v>46244</v>
@@ -24877,7 +24877,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="5" t="n">
-        <v>-0.06631345811438751</v>
+        <v>-0.07195579919713381</v>
       </c>
       <c r="Q318" s="10" t="inlineStr">
         <is>
@@ -24918,13 +24918,13 @@
         </is>
       </c>
       <c r="D319" s="15" t="n">
-        <v>122.43</v>
+        <v>121.44</v>
       </c>
       <c r="E319" s="20" t="n">
-        <v>0.0097</v>
+        <v>0.0016</v>
       </c>
       <c r="F319" s="16" t="n">
-        <v>-0.0206</v>
+        <v>-0.0285</v>
       </c>
       <c r="G319" s="17" t="n">
         <v>46230</v>
@@ -24953,7 +24953,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="20" t="n">
-        <v>0.1598464428653107</v>
+        <v>0.1693017127799737</v>
       </c>
       <c r="N319" s="14" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="20" t="n">
-        <v>0.1190067793841378</v>
+        <v>0.1281291172595521</v>
       </c>
       <c r="Q319" s="21" t="inlineStr">
         <is>
@@ -25013,13 +25013,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>249.57</v>
+        <v>248.34</v>
       </c>
       <c r="E320" s="9" t="n">
-        <v>0.09789999999999999</v>
+        <v>0.0924</v>
       </c>
       <c r="F320" s="9" t="n">
-        <v>0.1868</v>
+        <v>0.1809</v>
       </c>
       <c r="G320" s="6" t="n">
         <v>46230</v>
@@ -25048,7 +25048,7 @@
         <v>237</v>
       </c>
       <c r="M320" s="5" t="n">
-        <v>-0.05036663060463995</v>
+        <v>-0.04566320367238465</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -25059,7 +25059,7 @@
         <v>236</v>
       </c>
       <c r="P320" s="5" t="n">
-        <v>-0.05437352245862882</v>
+        <v>-0.04968994120963197</v>
       </c>
       <c r="Q320" s="10" t="inlineStr">
         <is>
@@ -25100,13 +25100,13 @@
         </is>
       </c>
       <c r="D321" s="15" t="n">
-        <v>177.91</v>
+        <v>178.22</v>
       </c>
       <c r="E321" s="20" t="n">
-        <v>0.0156</v>
+        <v>0.0174</v>
       </c>
       <c r="F321" s="20" t="n">
-        <v>0.0282</v>
+        <v>0.03</v>
       </c>
       <c r="G321" s="17" t="n">
         <v>46239</v>
@@ -25135,7 +25135,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="20" t="n">
-        <v>0.1241639030970716</v>
+        <v>0.1222085063404781</v>
       </c>
       <c r="N321" s="14" t="inlineStr"/>
       <c r="O321" s="19" t="n"/>
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>134.96</v>
+        <v>134.56</v>
       </c>
       <c r="E322" s="9" t="n">
-        <v>0.0172</v>
+        <v>0.0142</v>
       </c>
       <c r="F322" s="9" t="n">
-        <v>0.1031</v>
+        <v>0.0998</v>
       </c>
       <c r="G322" s="6" t="n">
         <v>46232</v>
@@ -25214,7 +25214,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="5" t="n">
-        <v>-0.02934202726733853</v>
+        <v>-0.02645659928656363</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="8" t="n"/>
@@ -25258,13 +25258,13 @@
         </is>
       </c>
       <c r="D323" s="15" t="n">
-        <v>32.46</v>
+        <v>32.6</v>
       </c>
       <c r="E323" s="16" t="n">
-        <v>-0.1392</v>
+        <v>-0.1355</v>
       </c>
       <c r="F323" s="16" t="n">
-        <v>-0.1856</v>
+        <v>-0.1821</v>
       </c>
       <c r="G323" s="17" t="n">
         <v>46234</v>
@@ -25337,13 +25337,13 @@
         </is>
       </c>
       <c r="D324" s="4" t="n">
-        <v>40.33</v>
+        <v>40.41</v>
       </c>
       <c r="E324" s="9" t="n">
-        <v>0.1019</v>
+        <v>0.1041</v>
       </c>
       <c r="F324" s="9" t="n">
-        <v>0.0195</v>
+        <v>0.0215</v>
       </c>
       <c r="G324" s="6" t="n">
         <v>46233</v>
@@ -25398,13 +25398,13 @@
         </is>
       </c>
       <c r="D325" s="15" t="n">
-        <v>271.83</v>
+        <v>270</v>
       </c>
       <c r="E325" s="20" t="n">
-        <v>0.0296</v>
+        <v>0.0226</v>
       </c>
       <c r="F325" s="16" t="n">
-        <v>-0.0506</v>
+        <v>-0.057</v>
       </c>
       <c r="G325" s="17" t="n">
         <v>46240</v>
@@ -25433,7 +25433,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="20" t="n">
-        <v>0.4126476106390024</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="N325" s="14" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="20" t="n">
-        <v>0.3979325313615128</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="Q325" s="21" t="inlineStr"/>
       <c r="R325" s="19" t="n"/>
@@ -25487,13 +25487,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>74.12</v>
+        <v>74.27</v>
       </c>
       <c r="E326" s="5" t="n">
-        <v>-0.0595</v>
+        <v>-0.0576</v>
       </c>
       <c r="F326" s="9" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="G326" s="6" t="n">
         <v>46231</v>
@@ -25522,7 +25522,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="9" t="n">
-        <v>0.06583917970858061</v>
+        <v>0.06368654907768957</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="8" t="n"/>
@@ -25574,13 +25574,13 @@
         </is>
       </c>
       <c r="D327" s="15" t="n">
-        <v>129.12</v>
+        <v>128.83</v>
       </c>
       <c r="E327" s="20" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.0033</v>
       </c>
       <c r="F327" s="20" t="n">
-        <v>0.0433</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="G327" s="17" t="n">
         <v>46238</v>
@@ -25609,7 +25609,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="20" t="n">
-        <v>0.05328376703841384</v>
+        <v>0.05565473880307371</v>
       </c>
       <c r="N327" s="14" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="20" t="n">
-        <v>0.08426270136307307</v>
+        <v>0.08670340759139941</v>
       </c>
       <c r="Q327" s="21" t="inlineStr">
         <is>
@@ -25661,13 +25661,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>113.72</v>
+        <v>113.76</v>
       </c>
       <c r="E328" s="5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0185</v>
       </c>
       <c r="F328" s="9" t="n">
-        <v>0.0374</v>
+        <v>0.0378</v>
       </c>
       <c r="G328" s="6" t="n">
         <v>46232</v>
@@ -25696,7 +25696,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="9" t="n">
-        <v>0.151952163207879</v>
+        <v>0.1515471167369901</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="9" t="n">
-        <v>0.06401688357368977</v>
+        <v>0.06364275668073131</v>
       </c>
       <c r="Q328" s="10" t="inlineStr">
         <is>
@@ -25752,13 +25752,13 @@
         </is>
       </c>
       <c r="D329" s="15" t="n">
-        <v>88.56</v>
-      </c>
-      <c r="E329" s="16" t="n">
-        <v>-0.0001</v>
+        <v>88.83</v>
+      </c>
+      <c r="E329" s="20" t="n">
+        <v>0.003</v>
       </c>
       <c r="F329" s="20" t="n">
-        <v>0.015</v>
+        <v>0.0181</v>
       </c>
       <c r="G329" s="17" t="n">
         <v>46318</v>
@@ -25794,7 +25794,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="20" t="n">
-        <v>0.2082204155374887</v>
+        <v>0.2045480130586514</v>
       </c>
       <c r="Q329" s="21" t="inlineStr">
         <is>
@@ -25843,13 +25843,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>59.66</v>
+        <v>59.52</v>
       </c>
       <c r="E330" s="9" t="n">
-        <v>0.0356</v>
+        <v>0.0332</v>
       </c>
       <c r="F330" s="9" t="n">
-        <v>0.0738</v>
+        <v>0.0713</v>
       </c>
       <c r="G330" s="6" t="n">
         <v>46237</v>
@@ -25878,7 +25878,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="9" t="n">
-        <v>0.05598390881662762</v>
+        <v>0.05846774193548381</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="8" t="n"/>
@@ -25922,13 +25922,13 @@
         </is>
       </c>
       <c r="D331" s="15" t="n">
-        <v>40.9</v>
+        <v>41.81</v>
       </c>
       <c r="E331" s="16" t="n">
-        <v>-0.182</v>
+        <v>-0.1638</v>
       </c>
       <c r="F331" s="16" t="n">
-        <v>-0.3993</v>
+        <v>-0.386</v>
       </c>
       <c r="G331" s="17" t="n">
         <v>46244</v>
@@ -25983,13 +25983,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>-0.1787</v>
+        <v>-0.1545</v>
       </c>
       <c r="F332" s="5" t="n">
-        <v>-0.3195</v>
+        <v>-0.2994</v>
       </c>
       <c r="G332" s="6" t="n">
         <v>46239</v>
@@ -26044,13 +26044,13 @@
         </is>
       </c>
       <c r="D333" s="15" t="n">
-        <v>96.77</v>
+        <v>96.48</v>
       </c>
       <c r="E333" s="16" t="n">
-        <v>-0.004</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F333" s="20" t="n">
-        <v>0.0459</v>
+        <v>0.0428</v>
       </c>
       <c r="G333" s="17" t="n">
         <v>46233</v>
@@ -26079,7 +26079,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="20" t="n">
-        <v>0.02304433192104995</v>
+        <v>0.02611940298507458</v>
       </c>
       <c r="N333" s="14" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="20" t="n">
-        <v>0.1573834866177535</v>
+        <v>0.1608623548922056</v>
       </c>
       <c r="Q333" s="21" t="inlineStr">
         <is>
@@ -26131,13 +26131,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>114.1</v>
+        <v>113.82</v>
       </c>
       <c r="E334" s="5" t="n">
-        <v>-0.04</v>
+        <v>-0.0423</v>
       </c>
       <c r="F334" s="9" t="n">
-        <v>0.0217</v>
+        <v>0.0193</v>
       </c>
       <c r="G334" s="6" t="n">
         <v>46232</v>
@@ -26166,7 +26166,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="9" t="n">
-        <v>0.1130587204206837</v>
+        <v>0.1157968722544369</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="8" t="n"/>
@@ -40676,7 +40676,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of July 27, 2026 at 17:21 UTC</t>
+          <t>Data as of July 27, 2026 at 21:48 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>98.75</v>
+        <v>98.89</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.0012</v>
+        <v>0.0026</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>-0.0302</v>
+        <v>-0.0289</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>46239</v>
@@ -878,7 +878,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>0.2658227848101266</v>
+        <v>0.2640307412276267</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.4582278481012658</v>
+        <v>0.4561634138942259</v>
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>333.86</v>
+        <v>333.71</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>-0.0559</v>
+        <v>-0.0564</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>-0.1222</v>
+        <v>-0.1226</v>
       </c>
       <c r="G3" s="17" t="n">
         <v>46322</v>
@@ -973,7 +973,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="20" t="n">
-        <v>0.3119271550949499</v>
+        <v>0.3125168559527735</v>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="20" t="n">
-        <v>0.2580123405020068</v>
+        <v>0.2585778070780019</v>
       </c>
       <c r="Q3" s="21" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>596.92</v>
+        <v>593.41</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.061</v>
+        <v>0.0548</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>-0.0563</v>
+        <v>-0.06179999999999999</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>46232</v>
@@ -1064,7 +1064,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.3988474167392617</v>
+        <v>0.4071215517096106</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.5579977216377405</v>
+        <v>0.5672132252574107</v>
       </c>
       <c r="Q4" s="10" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>39.42</v>
+        <v>39.28</v>
       </c>
       <c r="E5" s="20" t="n">
-        <v>0.0178</v>
+        <v>0.0142</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>0.0911</v>
+        <v>0.0872</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>46238</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>73.20999999999999</v>
+        <v>72.39</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0188</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-0.149</v>
+        <v>-0.1585</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>46315</v>
@@ -1220,7 +1220,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.09274689250102454</v>
+        <v>0.1051250172675784</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0.3659336156262807</v>
+        <v>0.381406271584473</v>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>86.47</v>
+        <v>86.22</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>0.1696</v>
+        <v>0.1662</v>
       </c>
       <c r="F7" s="20" t="n">
-        <v>0.1892</v>
+        <v>0.1858</v>
       </c>
       <c r="G7" s="17" t="n">
         <v>46231</v>
@@ -1307,7 +1307,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="20" t="n">
-        <v>0.0523881114837516</v>
+        <v>0.05543957318487591</v>
       </c>
       <c r="N7" s="14" t="inlineStr"/>
       <c r="O7" s="19" t="n"/>
@@ -1351,13 +1351,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>509.71</v>
+        <v>511.56</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.1026</v>
+        <v>0.1066</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.0242</v>
+        <v>0.0279</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>46238</v>
@@ -1386,7 +1386,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.1181456122108649</v>
+        <v>0.11410196262413</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.2713896137019089</v>
+        <v>0.2667917741809367</v>
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>186.34</v>
+        <v>186.06</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>-0.1195</v>
+        <v>-0.1208</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>-0.09179999999999999</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>46237</v>
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>184.25</v>
+        <v>182.39</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.0591</v>
+        <v>0.0484</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-0.0175</v>
+        <v>-0.0274</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>46317</v>
@@ -1542,7 +1542,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>-0.07734056987788331</v>
+        <v>-0.06793135588573929</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.4654002713704206</v>
+        <v>0.4803443171226494</v>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
@@ -1594,13 +1594,13 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>48.22</v>
+        <v>48.19</v>
       </c>
       <c r="E11" s="20" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.09269999999999999</v>
       </c>
       <c r="F11" s="20" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>46316</v>
@@ -1629,7 +1629,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>-0.108253836582331</v>
+        <v>-0.1076986926748288</v>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="20" t="n">
-        <v>0.03691414350891749</v>
+        <v>0.03755965968043167</v>
       </c>
       <c r="Q11" s="21" t="inlineStr">
         <is>
@@ -1685,13 +1685,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>151.2</v>
+        <v>153.11</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.0273</v>
+        <v>0.0404</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1342</v>
+        <v>0.1485</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>46240</v>
@@ -1720,7 +1720,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.1970899470899472</v>
+        <v>0.1821566194239435</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0.02513227513227521</v>
+        <v>0.01234406635752065</v>
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
@@ -1772,13 +1772,13 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>231.56</v>
+        <v>230.86</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>-0.0357</v>
+        <v>-0.0386</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>-0.1444</v>
+        <v>-0.147</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>46233</v>
@@ -1807,7 +1807,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="20" t="n">
-        <v>0.3905683192261185</v>
+        <v>0.3947847180109156</v>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="20" t="n">
-        <v>0.2307825185697011</v>
+        <v>0.2345144243264315</v>
       </c>
       <c r="Q13" s="21" t="inlineStr">
         <is>
@@ -1871,13 +1871,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3116.48</v>
+        <v>3118.8</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-0.0118</v>
+        <v>-0.011</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.06179999999999999</v>
+        <v>0.0626</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>46287</v>
@@ -1906,7 +1906,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0.3316305575521101</v>
+        <v>0.3306399897396434</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0.187236882636821</v>
+        <v>0.1863537257919712</v>
       </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
@@ -1958,13 +1958,13 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>90.26000000000001</v>
+        <v>89.47</v>
       </c>
       <c r="E15" s="20" t="n">
-        <v>0.1625</v>
+        <v>0.1524</v>
       </c>
       <c r="F15" s="20" t="n">
-        <v>0.1579</v>
+        <v>0.1478</v>
       </c>
       <c r="G15" s="17" t="n">
         <v>46261</v>
@@ -1993,7 +1993,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="16" t="n">
-        <v>-0.2798581874584534</v>
+        <v>-0.2734994970381133</v>
       </c>
       <c r="N15" s="14" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>-0.05827609129182367</v>
+        <v>-0.0499608807421482</v>
       </c>
       <c r="Q15" s="21" t="inlineStr"/>
       <c r="R15" s="19" t="n"/>
@@ -2039,13 +2039,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>197.18</v>
+        <v>199.31</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.081</v>
+        <v>0.0926</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.1777</v>
+        <v>0.1904</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>46238</v>
@@ -2074,7 +2074,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.0853027690435135</v>
+        <v>0.0737042797651899</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.2425195253068262</v>
+        <v>0.2292408810395866</v>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
@@ -2134,13 +2134,13 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>372.78</v>
+        <v>370.01</v>
       </c>
       <c r="E17" s="20" t="n">
-        <v>0.1861</v>
+        <v>0.1773</v>
       </c>
       <c r="F17" s="20" t="n">
-        <v>0.1512</v>
+        <v>0.1426</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>46261</v>
@@ -2169,7 +2169,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="20" t="n">
-        <v>0.005955255110252769</v>
+        <v>0.01348612199670282</v>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="20" t="n">
-        <v>0.005955255110252769</v>
+        <v>0.01348612199670282</v>
       </c>
       <c r="Q17" s="21" t="inlineStr"/>
       <c r="R17" s="19" t="n"/>
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>33.22</v>
+        <v>33.51</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.0164</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.04269999999999999</v>
+        <v>0.0518</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>46232</v>
@@ -2254,7 +2254,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.3546056592414209</v>
+        <v>0.3428827215756491</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.3546056592414209</v>
+        <v>0.3428827215756491</v>
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
@@ -2306,13 +2306,13 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>151.55</v>
+        <v>151.16</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>-0.07719999999999999</v>
+        <v>-0.0796</v>
       </c>
       <c r="F19" s="20" t="n">
-        <v>0.0304</v>
+        <v>0.0277</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>46324</v>
@@ -2341,7 +2341,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="20" t="n">
-        <v>0.1217419993401517</v>
+        <v>0.1246361471288701</v>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="20" t="n">
-        <v>0.1679313757835697</v>
+        <v>0.1709446943635883</v>
       </c>
       <c r="Q19" s="21" t="inlineStr">
         <is>
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>207.86</v>
+        <v>211.37</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-0.1054</v>
+        <v>-0.09029999999999999</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.0866</v>
+        <v>-0.0712</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>46261</v>
@@ -2428,7 +2428,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0.05840469546810346</v>
+        <v>0.04082887827033162</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="9" t="n"/>
@@ -2472,13 +2472,13 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>127.68</v>
+        <v>126.76</v>
       </c>
       <c r="E21" s="20" t="n">
-        <v>0.0412</v>
+        <v>0.0338</v>
       </c>
       <c r="F21" s="20" t="n">
-        <v>0.0965</v>
+        <v>0.0886</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>46267</v>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>90.63</v>
+        <v>90.3</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.1718</v>
+        <v>0.1676</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.08869999999999999</v>
+        <v>0.0848</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>46315</v>
@@ -2568,7 +2568,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>-0.3269336864173011</v>
+        <v>-0.3244739756367663</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.1033873993158999</v>
+        <v>0.1074197120708749</v>
       </c>
       <c r="Q22" s="10" t="inlineStr">
         <is>
@@ -2620,13 +2620,13 @@
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>130.01</v>
+        <v>129.71</v>
       </c>
       <c r="E23" s="20" t="n">
-        <v>0.1095</v>
+        <v>0.1069</v>
       </c>
       <c r="F23" s="20" t="n">
-        <v>0.3172</v>
+        <v>0.3142</v>
       </c>
       <c r="G23" s="17" t="n">
         <v>46315</v>
@@ -2658,7 +2658,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="20" t="n">
-        <v>0.1152988231674487</v>
+        <v>0.1178783439981497</v>
       </c>
       <c r="Q23" s="21" t="inlineStr"/>
       <c r="R23" s="19" t="n"/>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>345.51</v>
+        <v>344.47</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>-0.0151</v>
+        <v>-0.0181</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.0862</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>46252</v>
@@ -2728,7 +2728,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0.04193800468872105</v>
+        <v>0.04508375185066906</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0.1577088940985789</v>
+        <v>0.1612041687229656</v>
       </c>
       <c r="Q24" s="10" t="inlineStr">
         <is>
@@ -2788,13 +2788,13 @@
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>217.57</v>
+        <v>218.24</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>-0.0095</v>
+        <v>-0.0064</v>
       </c>
       <c r="F25" s="20" t="n">
-        <v>0.015</v>
+        <v>0.0181</v>
       </c>
       <c r="G25" s="17" t="n">
         <v>46253</v>
@@ -2823,7 +2823,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="20" t="n">
-        <v>0.1720365859263686</v>
+        <v>0.1684384164222874</v>
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="20" t="n">
-        <v>0.0571310382865285</v>
+        <v>0.05388563049853368</v>
       </c>
       <c r="Q25" s="21" t="inlineStr">
         <is>
@@ -2879,13 +2879,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>273.62</v>
+        <v>273.02</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0.0241</v>
+        <v>0.0219</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-0.02</v>
+        <v>-0.0221</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>46238</v>
@@ -2914,7 +2914,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.09641108106132591</v>
+        <v>0.09882059922350019</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0.2791462612382136</v>
+        <v>0.2819573657607502</v>
       </c>
       <c r="Q26" s="10" t="inlineStr">
         <is>
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>43.03</v>
+        <v>43.05</v>
       </c>
       <c r="E27" s="20" t="n">
-        <v>0.0372</v>
+        <v>0.0378</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>-0.0693</v>
+        <v>-0.0688</v>
       </c>
       <c r="G27" s="17" t="n">
         <v>46289</v>
@@ -3027,13 +3027,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>92.14</v>
+        <v>91.17</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.022</v>
+        <v>0.0112</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.0605</v>
+        <v>0.04940000000000001</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>46232</v>
@@ -3062,7 +3062,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.1938354677664424</v>
+        <v>0.2065372381265767</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.2481007163012807</v>
+        <v>0.2613798398596029</v>
       </c>
       <c r="Q28" s="10" t="inlineStr">
         <is>
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>189.58</v>
+        <v>192.16</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>-0.1041</v>
+        <v>-0.092</v>
       </c>
       <c r="F29" s="20" t="n">
-        <v>0.0451</v>
+        <v>0.0593</v>
       </c>
       <c r="G29" s="17" t="n">
         <v>46317</v>
@@ -3179,13 +3179,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>251.81</v>
+        <v>251.03</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.2058</v>
+        <v>0.2021</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.0867</v>
+        <v>0.0833</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>46254</v>
@@ -3214,7 +3214,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.02704419999205751</v>
+        <v>-0.02402103334262837</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.05238076327389698</v>
+        <v>0.05565071903756522</v>
       </c>
       <c r="Q30" s="10" t="inlineStr">
         <is>
@@ -3266,13 +3266,13 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>103.25</v>
+        <v>103.1</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0092</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>0.0412</v>
+        <v>0.0397</v>
       </c>
       <c r="G31" s="17" t="n">
         <v>46232</v>
@@ -3301,7 +3301,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="20" t="n">
-        <v>0.162227602905569</v>
+        <v>0.1639185257032008</v>
       </c>
       <c r="N31" s="14" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="20" t="n">
-        <v>0.1138014527845036</v>
+        <v>0.1154219204655675</v>
       </c>
       <c r="Q31" s="21" t="inlineStr">
         <is>
@@ -3353,13 +3353,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>15.04</v>
+        <v>14.82</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-0.0046</v>
+        <v>-0.0192</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.1385</v>
+        <v>0.1219</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>46237</v>
@@ -3414,13 +3414,13 @@
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>159.86</v>
+        <v>160.8</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>0.0571</v>
+        <v>0.0633</v>
       </c>
       <c r="F33" s="20" t="n">
-        <v>0.033</v>
+        <v>0.0391</v>
       </c>
       <c r="G33" s="17" t="n">
         <v>46253</v>
@@ -3448,8 +3448,8 @@
       <c r="L33" s="19" t="n">
         <v>160</v>
       </c>
-      <c r="M33" s="20" t="n">
-        <v>0.0008757662955084846</v>
+      <c r="M33" s="16" t="n">
+        <v>-0.004975124378109523</v>
       </c>
       <c r="N33" s="14" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="20" t="n">
-        <v>0.09470786938571241</v>
+        <v>0.0883084577114427</v>
       </c>
       <c r="Q33" s="21" t="inlineStr">
         <is>
@@ -3505,13 +3505,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>31.82</v>
+        <v>31.46</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.0199</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>0.0092</v>
+        <v>0.0083</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>-0.0022</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>46317</v>
@@ -3540,7 +3540,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.09993714644877434</v>
+        <v>0.112523839796567</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0.257071024512885</v>
+        <v>0.2714558169103624</v>
       </c>
       <c r="Q34" s="10" t="inlineStr">
         <is>
@@ -3592,13 +3592,13 @@
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>306.42</v>
+        <v>307.44</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>-0.256</v>
+        <v>-0.2535</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>-0.2969</v>
+        <v>-0.2945</v>
       </c>
       <c r="G35" s="17" t="n">
         <v>46323</v>
@@ -3627,7 +3627,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="16" t="n">
-        <v>-0.5757457085046668</v>
+        <v>-0.5771532656778559</v>
       </c>
       <c r="N35" s="14" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>-0.02095163501076958</v>
+        <v>-0.02419984387197501</v>
       </c>
       <c r="Q35" s="21" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>69.38</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>-0.08109999999999999</v>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>-0.0145</v>
+        <v>-0.063</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0.0048</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>46239</v>
@@ -3740,13 +3740,13 @@
         </is>
       </c>
       <c r="D37" s="15" t="n">
-        <v>501.17</v>
+        <v>501.52</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>0.0916</v>
+        <v>0.0924</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>-0.0151</v>
+        <v>-0.0144</v>
       </c>
       <c r="G37" s="17" t="n">
         <v>46261</v>
@@ -3775,7 +3775,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="16" t="n">
-        <v>-0.1021010834646927</v>
+        <v>-0.1027277077683841</v>
       </c>
       <c r="N37" s="14" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="20" t="n">
-        <v>0.2670351377776004</v>
+        <v>0.2661509012601692</v>
       </c>
       <c r="Q37" s="21" t="inlineStr">
         <is>
@@ -3831,13 +3831,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>100.82</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.0299</v>
+        <v>0.0207</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.05429999999999999</v>
+        <v>0.045</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>46234</v>
@@ -3866,7 +3866,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.09105336242808974</v>
+        <v>0.1007705393775642</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.04146002777226748</v>
+        <v>0.05073551486040221</v>
       </c>
       <c r="Q38" s="10" t="inlineStr">
         <is>
@@ -3922,13 +3922,13 @@
         </is>
       </c>
       <c r="D39" s="15" t="n">
-        <v>93.88</v>
+        <v>92.73</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>0.016</v>
+        <v>0.0036</v>
       </c>
       <c r="F39" s="20" t="n">
-        <v>0.0416</v>
+        <v>0.0288</v>
       </c>
       <c r="G39" s="17" t="n">
         <v>46234</v>
@@ -3957,7 +3957,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="20" t="n">
-        <v>0.01193012356199408</v>
+        <v>0.02447967216650486</v>
       </c>
       <c r="N39" s="14" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="20" t="n">
-        <v>0.06518960374946746</v>
+        <v>0.07839965491211039</v>
       </c>
       <c r="Q39" s="21" t="inlineStr">
         <is>
@@ -4013,13 +4013,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>973.05</v>
+        <v>966.58</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.0279</v>
+        <v>0.021</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0107</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>46289</v>
@@ -4048,7 +4048,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0.02769641847798165</v>
+        <v>0.03457551366674249</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0.1304660603257798</v>
+        <v>0.1380330650334168</v>
       </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
@@ -4108,13 +4108,13 @@
         </is>
       </c>
       <c r="D41" s="15" t="n">
-        <v>126.73</v>
+        <v>125.97</v>
       </c>
       <c r="E41" s="20" t="n">
-        <v>0.0784</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="F41" s="20" t="n">
-        <v>0.1457</v>
+        <v>0.1389</v>
       </c>
       <c r="G41" s="17" t="n">
         <v>46261</v>
@@ -4143,7 +4143,7 @@
         <v>125</v>
       </c>
       <c r="M41" s="16" t="n">
-        <v>-0.01365106920224102</v>
+        <v>-0.00770024609033896</v>
       </c>
       <c r="N41" s="14" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="20" t="n">
-        <v>0.0652568452615797</v>
+        <v>0.07168373422243392</v>
       </c>
       <c r="Q41" s="21" t="inlineStr">
         <is>
@@ -4195,13 +4195,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>27.08</v>
+        <v>27.3</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.1197</v>
+        <v>0.1286</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.1281</v>
+        <v>0.137</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>46239</v>
@@ -4256,13 +4256,13 @@
         </is>
       </c>
       <c r="D43" s="15" t="n">
-        <v>88.29000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>0.0682</v>
+        <v>0.068</v>
       </c>
       <c r="F43" s="20" t="n">
-        <v>0.1175</v>
+        <v>0.1172</v>
       </c>
       <c r="G43" s="17" t="n">
         <v>46231</v>
@@ -4291,7 +4291,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="20" t="n">
-        <v>0.01936799184505599</v>
+        <v>0.01959895774328769</v>
       </c>
       <c r="N43" s="14" t="inlineStr">
         <is>
@@ -4302,7 +4302,7 @@
         <v>88</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>-0.003284630195945251</v>
+        <v>-0.003058796873229818</v>
       </c>
       <c r="Q43" s="21" t="inlineStr">
         <is>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>59.78</v>
+        <v>59.19</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.0693</v>
+        <v>0.0587</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>-0.0381</v>
+        <v>-0.0476</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>46275</v>
@@ -4386,7 +4386,7 @@
         <v>58</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>-0.02977584476413518</v>
+        <v>-0.02010474742355124</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.3047842087654734</v>
+        <v>0.3177901672579828</v>
       </c>
       <c r="Q44" s="10" t="inlineStr">
         <is>
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="D45" s="15" t="n">
-        <v>62.33</v>
+        <v>62.48</v>
       </c>
       <c r="E45" s="20" t="n">
-        <v>0.0362</v>
+        <v>0.0387</v>
       </c>
       <c r="F45" s="20" t="n">
-        <v>0.019</v>
+        <v>0.0214</v>
       </c>
       <c r="G45" s="17" t="n">
         <v>46231</v>
@@ -4473,7 +4473,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="20" t="n">
-        <v>0.1230547088079577</v>
+        <v>0.120358514724712</v>
       </c>
       <c r="N45" s="14" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="20" t="n">
-        <v>0.1390983475052142</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="Q45" s="21" t="inlineStr">
         <is>
@@ -4533,13 +4533,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>51.42</v>
+        <v>51.53</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>-0.0123</v>
+        <v>-0.0102</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.08779999999999999</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>46301</v>
@@ -4604,13 +4604,13 @@
         </is>
       </c>
       <c r="D47" s="15" t="n">
-        <v>98.19</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="E47" s="20" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.001</v>
       </c>
       <c r="F47" s="20" t="n">
-        <v>0.1148</v>
+        <v>0.1097</v>
       </c>
       <c r="G47" s="17" t="n">
         <v>46240</v>
@@ -4665,13 +4665,13 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>74.93000000000001</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.0119</v>
+        <v>0.0104</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>46233</v>
@@ -4726,13 +4726,13 @@
         </is>
       </c>
       <c r="D49" s="15" t="n">
-        <v>142.14</v>
+        <v>142.86</v>
       </c>
       <c r="E49" s="20" t="n">
-        <v>0.0249</v>
+        <v>0.0301</v>
       </c>
       <c r="F49" s="16" t="n">
-        <v>-0.0142</v>
+        <v>-0.0092</v>
       </c>
       <c r="G49" s="17" t="n">
         <v>46303</v>
@@ -4761,7 +4761,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="16" t="n">
-        <v>-0.0150555790066131</v>
+        <v>-0.02001959960800793</v>
       </c>
       <c r="N49" s="14" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="20" t="n">
-        <v>0.05529759392148596</v>
+        <v>0.0499790004199915</v>
       </c>
       <c r="Q49" s="21" t="inlineStr">
         <is>
@@ -4821,13 +4821,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>151.51</v>
+        <v>148.88</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.0206</v>
+        <v>0.0029</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.0554</v>
+        <v>0.0371</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>46232</v>
@@ -4856,7 +4856,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.08243680285129701</v>
+        <v>0.1015583019881784</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0.06923635403603728</v>
+        <v>0.0881246641590543</v>
       </c>
       <c r="Q50" s="10" t="inlineStr">
         <is>
@@ -4920,13 +4920,13 @@
         </is>
       </c>
       <c r="D51" s="15" t="n">
-        <v>85.51000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="E51" s="20" t="n">
-        <v>0.0253</v>
+        <v>0.0216</v>
       </c>
       <c r="F51" s="20" t="n">
-        <v>0.128</v>
+        <v>0.1239</v>
       </c>
       <c r="G51" s="17" t="n">
         <v>46238</v>
@@ -4955,7 +4955,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="20" t="n">
-        <v>0.1694538650450239</v>
+        <v>0.1737089201877934</v>
       </c>
       <c r="N51" s="14" t="inlineStr"/>
       <c r="O51" s="19" t="n"/>
@@ -4999,13 +4999,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>144.35</v>
+        <v>144.2</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.0779</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.136</v>
+        <v>0.1348</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>46253</v>
@@ -5034,7 +5034,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-0.03013508832698299</v>
+        <v>-0.02912621359223293</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>-0.06477312088673359</v>
+        <v>-0.06380027739251033</v>
       </c>
       <c r="Q52" s="10" t="inlineStr">
         <is>
@@ -5090,13 +5090,13 @@
         </is>
       </c>
       <c r="D53" s="15" t="n">
-        <v>113.8</v>
+        <v>113.1</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.0131</v>
       </c>
       <c r="F53" s="16" t="n">
-        <v>-0.0168</v>
+        <v>-0.0229</v>
       </c>
       <c r="G53" s="17" t="n">
         <v>46254</v>
@@ -5125,7 +5125,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="20" t="n">
-        <v>0.2302284710017575</v>
+        <v>0.237842617152962</v>
       </c>
       <c r="N53" s="14" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="20" t="n">
-        <v>0.2302284710017575</v>
+        <v>0.237842617152962</v>
       </c>
       <c r="Q53" s="21" t="inlineStr">
         <is>
@@ -5185,13 +5185,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>58.12</v>
+        <v>58.46</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0.0321</v>
+        <v>0.0382</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>-0.0902</v>
+        <v>-0.0848</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>46316</v>
@@ -5227,7 +5227,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>0.307639366827254</v>
+        <v>0.3000342114266165</v>
       </c>
       <c r="Q54" s="10" t="inlineStr">
         <is>
@@ -5268,13 +5268,13 @@
         </is>
       </c>
       <c r="D55" s="15" t="n">
-        <v>113.41</v>
+        <v>114.1</v>
       </c>
       <c r="E55" s="20" t="n">
-        <v>0.08839999999999999</v>
-      </c>
-      <c r="F55" s="16" t="n">
-        <v>-0.005</v>
+        <v>0.095</v>
+      </c>
+      <c r="F55" s="20" t="n">
+        <v>0.0011</v>
       </c>
       <c r="G55" s="17" t="n">
         <v>46240</v>
@@ -5303,7 +5303,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="20" t="n">
-        <v>0.613614319724892</v>
+        <v>0.6038562664329536</v>
       </c>
       <c r="N55" s="14" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="20" t="n">
-        <v>0.2785468653557888</v>
+        <v>0.2708150744960561</v>
       </c>
       <c r="Q55" s="21" t="inlineStr">
         <is>
@@ -5355,13 +5355,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>186.92</v>
+        <v>187.58</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.1095</v>
+        <v>0.1134</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.0244</v>
+        <v>0.0281</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>46234</v>
@@ -5390,7 +5390,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>0.1876738711748342</v>
+        <v>0.183495042115364</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>0.2037235180826023</v>
+        <v>0.1994882183601663</v>
       </c>
       <c r="Q56" s="10" t="inlineStr">
         <is>
@@ -5446,13 +5446,13 @@
         </is>
       </c>
       <c r="D57" s="15" t="n">
-        <v>139.3</v>
+        <v>139.64</v>
       </c>
       <c r="E57" s="20" t="n">
-        <v>0.0559</v>
+        <v>0.0584</v>
       </c>
       <c r="F57" s="20" t="n">
-        <v>0.0444</v>
+        <v>0.0469</v>
       </c>
       <c r="G57" s="17" t="n">
         <v>46238</v>
@@ -5481,7 +5481,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="20" t="n">
-        <v>0.4070351758793969</v>
+        <v>0.4036092810083072</v>
       </c>
       <c r="N57" s="14" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="20" t="n">
-        <v>0.2203876525484565</v>
+        <v>0.2174162131194501</v>
       </c>
       <c r="Q57" s="21" t="inlineStr">
         <is>
@@ -5537,13 +5537,13 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>38.49</v>
+        <v>38.63</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.0501</v>
+        <v>0.0537</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.0463</v>
+        <v>0.05</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>46233</v>
@@ -5598,13 +5598,13 @@
         </is>
       </c>
       <c r="D59" s="15" t="n">
-        <v>19.95</v>
+        <v>20.2</v>
       </c>
       <c r="E59" s="20" t="n">
-        <v>0.047</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="F59" s="20" t="n">
-        <v>0.0409</v>
+        <v>0.0537</v>
       </c>
       <c r="G59" s="17" t="n">
         <v>46238</v>
@@ -5659,13 +5659,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>190.57</v>
+        <v>190.3</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0.0556</v>
+        <v>0.0541</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>-0.004699999999999999</v>
+        <v>-0.0061</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>46237</v>
@@ -5720,13 +5720,13 @@
         </is>
       </c>
       <c r="D61" s="15" t="n">
-        <v>31.5</v>
+        <v>31.23</v>
       </c>
       <c r="E61" s="16" t="n">
-        <v>-0.076</v>
+        <v>-0.0839</v>
       </c>
       <c r="F61" s="16" t="n">
-        <v>-0.1892</v>
+        <v>-0.1961</v>
       </c>
       <c r="G61" s="17" t="n">
         <v>46315</v>
@@ -5762,7 +5762,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="20" t="n">
-        <v>0.3650793650793651</v>
+        <v>0.3768812039705411</v>
       </c>
       <c r="Q61" s="21" t="inlineStr">
         <is>
@@ -5807,13 +5807,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>31.58</v>
+        <v>31.61</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>-0.0215</v>
+        <v>-0.0205</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.0171</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>46316</v>
@@ -5842,7 +5842,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.1082963901203294</v>
+        <v>0.1072445428661816</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="9" t="n"/>
@@ -5886,13 +5886,13 @@
         </is>
       </c>
       <c r="D63" s="15" t="n">
-        <v>205.33</v>
+        <v>205.85</v>
       </c>
       <c r="E63" s="20" t="n">
-        <v>0.1797</v>
+        <v>0.1827</v>
       </c>
       <c r="F63" s="20" t="n">
-        <v>0.1674</v>
+        <v>0.1704</v>
       </c>
       <c r="G63" s="17" t="n">
         <v>46239</v>
@@ -5947,13 +5947,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>50.44</v>
+        <v>49.98</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.0776</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.08380000000000001</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>46311</v>
@@ -5989,7 +5989,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0.2490087232355274</v>
+        <v>0.2605042016806723</v>
       </c>
       <c r="Q64" s="10" t="inlineStr">
         <is>
@@ -6038,13 +6038,13 @@
         </is>
       </c>
       <c r="D65" s="15" t="n">
-        <v>42.11</v>
+        <v>42.04</v>
       </c>
       <c r="E65" s="16" t="n">
-        <v>-0.0071</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F65" s="16" t="n">
-        <v>-0.0745</v>
+        <v>-0.076</v>
       </c>
       <c r="G65" s="17" t="n">
         <v>46237</v>
@@ -6099,13 +6099,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>69.40000000000001</v>
+        <v>70.16</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0653</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>-0.0279</v>
+        <v>-0.0172</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>46237</v>
@@ -6134,7 +6134,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0.2824207492795388</v>
+        <v>0.2685290763968073</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="9" t="n"/>
@@ -6190,13 +6190,13 @@
         </is>
       </c>
       <c r="D67" s="15" t="n">
-        <v>152.06</v>
+        <v>153.04</v>
       </c>
       <c r="E67" s="20" t="n">
-        <v>0.1176</v>
+        <v>0.1248</v>
       </c>
       <c r="F67" s="20" t="n">
-        <v>0.04679999999999999</v>
+        <v>0.0536</v>
       </c>
       <c r="G67" s="17" t="n">
         <v>46234</v>
@@ -6225,7 +6225,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="20" t="n">
-        <v>0.2166250164408786</v>
+        <v>0.2088342916884475</v>
       </c>
       <c r="N67" s="14" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="20" t="n">
-        <v>0.2166250164408786</v>
+        <v>0.2088342916884475</v>
       </c>
       <c r="Q67" s="21" t="inlineStr">
         <is>
@@ -6281,13 +6281,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>129</v>
+        <v>129.55</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0.07429999999999999</v>
+        <v>0.0789</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.1475</v>
+        <v>0.1524</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>46240</v>
@@ -6316,7 +6316,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="6" t="n">
-        <v>-0.06976744186046512</v>
+        <v>-0.0737167116943266</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>115</v>
       </c>
       <c r="P68" s="6" t="n">
-        <v>-0.1085271317829457</v>
+        <v>-0.112311848707063</v>
       </c>
       <c r="Q68" s="10" t="inlineStr"/>
       <c r="R68" s="9" t="n"/>
@@ -6362,13 +6362,13 @@
         </is>
       </c>
       <c r="D69" s="15" t="n">
-        <v>380.22</v>
+        <v>381.26</v>
       </c>
       <c r="E69" s="20" t="n">
-        <v>0.1607</v>
+        <v>0.1639</v>
       </c>
       <c r="F69" s="20" t="n">
-        <v>0.203</v>
+        <v>0.2063</v>
       </c>
       <c r="G69" s="17" t="n">
         <v>46232</v>
@@ -6397,7 +6397,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="20" t="n">
-        <v>0.06780285098101092</v>
+        <v>0.06489010124324611</v>
       </c>
       <c r="N69" s="14" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="20" t="n">
-        <v>0.1467045394771447</v>
+        <v>0.1435765619262446</v>
       </c>
       <c r="Q69" s="21" t="inlineStr">
         <is>
@@ -6445,13 +6445,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>335.74</v>
+        <v>336.63</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>-0.0151</v>
+        <v>-0.0125</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.0609</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>46311</v>
@@ -6480,7 +6480,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.2360755346398999</v>
+        <v>0.2328075334937469</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.1318282003931613</v>
+        <v>0.1288358138015032</v>
       </c>
       <c r="Q70" s="10" t="inlineStr">
         <is>
@@ -6540,13 +6540,13 @@
         </is>
       </c>
       <c r="D71" s="15" t="n">
-        <v>62.35</v>
+        <v>62.62</v>
       </c>
       <c r="E71" s="20" t="n">
-        <v>0.07730000000000001</v>
+        <v>0.0819</v>
       </c>
       <c r="F71" s="20" t="n">
-        <v>0.2084</v>
+        <v>0.2136</v>
       </c>
       <c r="G71" s="17" t="n">
         <v>46309</v>
@@ -6601,13 +6601,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1096.35</v>
+        <v>1097.55</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0.1539</v>
+        <v>0.1551</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.0473</v>
+        <v>0.0484</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>46308</v>
@@ -6639,7 +6639,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.1355862635107403</v>
+        <v>0.1343446767801012</v>
       </c>
       <c r="Q72" s="10" t="inlineStr">
         <is>
@@ -6684,13 +6684,13 @@
         </is>
       </c>
       <c r="D73" s="15" t="n">
-        <v>22.72</v>
+        <v>22.69</v>
       </c>
       <c r="E73" s="16" t="n">
-        <v>-0.0409</v>
+        <v>-0.04219999999999999</v>
       </c>
       <c r="F73" s="16" t="n">
-        <v>-0.3492</v>
+        <v>-0.35</v>
       </c>
       <c r="G73" s="17" t="n">
         <v>46281</v>
@@ -6745,13 +6745,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>17.72</v>
+        <v>17.57</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0.2841</v>
+        <v>0.2732</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>-0.08039999999999999</v>
+        <v>-0.0882</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>46346</v>
@@ -6806,13 +6806,13 @@
         </is>
       </c>
       <c r="D75" s="15" t="n">
-        <v>508.42</v>
+        <v>512.37</v>
       </c>
       <c r="E75" s="20" t="n">
-        <v>0.025</v>
+        <v>0.033</v>
       </c>
       <c r="F75" s="20" t="n">
-        <v>0.07150000000000001</v>
+        <v>0.0799</v>
       </c>
       <c r="G75" s="17" t="n">
         <v>46241</v>
@@ -6889,13 +6889,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>72.83</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0.1387</v>
+        <v>0.1515</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.2948</v>
+        <v>0.3093</v>
       </c>
       <c r="G76" s="7" t="n"/>
       <c r="H76" s="12" t="inlineStr">
@@ -6914,7 +6914,7 @@
         <v>68</v>
       </c>
       <c r="M76" s="6" t="n">
-        <v>-0.06631882466016749</v>
+        <v>-0.07671418873048208</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="9" t="n"/>
@@ -6956,13 +6956,13 @@
         </is>
       </c>
       <c r="D77" s="15" t="n">
-        <v>132.38</v>
+        <v>133.9</v>
       </c>
       <c r="E77" s="20" t="n">
-        <v>0.1523</v>
+        <v>0.1656</v>
       </c>
       <c r="F77" s="20" t="n">
-        <v>0.1317</v>
+        <v>0.1447</v>
       </c>
       <c r="G77" s="17" t="n">
         <v>46310</v>
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>132.07</v>
+        <v>132.47</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>-0.0731</v>
+        <v>-0.0703</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.049</v>
+        <v>0.0522</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>46308</v>
@@ -7059,7 +7059,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.06004391610509584</v>
+        <v>0.05684305880576735</v>
       </c>
       <c r="Q78" s="10" t="inlineStr">
         <is>
@@ -7108,13 +7108,13 @@
         </is>
       </c>
       <c r="D79" s="15" t="n">
-        <v>362.64</v>
+        <v>363.5</v>
       </c>
       <c r="E79" s="20" t="n">
-        <v>0.0564</v>
+        <v>0.05889999999999999</v>
       </c>
       <c r="F79" s="20" t="n">
-        <v>0.1633</v>
+        <v>0.1661</v>
       </c>
       <c r="G79" s="17" t="n">
         <v>46315</v>
@@ -7143,7 +7143,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="16" t="n">
-        <v>-0.01279505846018086</v>
+        <v>-0.01513067400275103</v>
       </c>
       <c r="N79" s="14" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="20" t="n">
-        <v>0.03132583278182223</v>
+        <v>0.02888583218707015</v>
       </c>
       <c r="Q79" s="21" t="inlineStr">
         <is>
@@ -7199,13 +7199,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>59.68</v>
+        <v>60.01</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0331</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0.1429</v>
+        <v>0.1492</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>46310</v>
@@ -7234,7 +7234,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="6" t="n">
-        <v>-0.04490616621983914</v>
+        <v>-0.05015830694884183</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="9" t="n"/>
@@ -7276,13 +7276,13 @@
         </is>
       </c>
       <c r="D81" s="15" t="n">
-        <v>13.61</v>
+        <v>13.48</v>
       </c>
       <c r="E81" s="16" t="n">
-        <v>-0.1142</v>
+        <v>-0.123</v>
       </c>
       <c r="F81" s="16" t="n">
-        <v>-0.2556</v>
+        <v>-0.263</v>
       </c>
       <c r="G81" s="17" t="n">
         <v>46240</v>
@@ -7337,13 +7337,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>385.32</v>
+        <v>384.32</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0.149</v>
+        <v>0.1461</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.065</v>
+        <v>0.0622</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>46239</v>
@@ -7410,13 +7410,13 @@
         </is>
       </c>
       <c r="D83" s="15" t="n">
-        <v>64.5</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="E83" s="16" t="n">
-        <v>-0.1509</v>
+        <v>-0.1532</v>
       </c>
       <c r="F83" s="16" t="n">
-        <v>-0.4292</v>
+        <v>-0.4308</v>
       </c>
       <c r="G83" s="17" t="n">
         <v>46239</v>
@@ -7471,13 +7471,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>53.44</v>
+        <v>54.84</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0.1081</v>
+        <v>0.1371</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0.1994</v>
+        <v>0.2307</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>46240</v>
@@ -7532,13 +7532,13 @@
         </is>
       </c>
       <c r="D85" s="15" t="n">
-        <v>1042.75</v>
+        <v>1033.34</v>
       </c>
       <c r="E85" s="20" t="n">
-        <v>0.0221</v>
+        <v>0.0129</v>
       </c>
       <c r="F85" s="20" t="n">
-        <v>0.0168</v>
+        <v>0.0076</v>
       </c>
       <c r="G85" s="17" t="n">
         <v>46308</v>
@@ -7567,7 +7567,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="20" t="n">
-        <v>0.2706784943658595</v>
+        <v>0.2822497919368263</v>
       </c>
       <c r="N85" s="14" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="20" t="n">
-        <v>0.1603931910812755</v>
+        <v>0.1709601873536301</v>
       </c>
       <c r="Q85" s="21" t="inlineStr">
         <is>
@@ -7619,13 +7619,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>146.31</v>
+        <v>145.47</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0.1007</v>
+        <v>0.0944</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0269</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>46232</v>
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="D87" s="15" t="n">
-        <v>92.93000000000001</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0891</v>
       </c>
       <c r="F87" s="16" t="n">
-        <v>-0.0145</v>
+        <v>-0.0163</v>
       </c>
       <c r="G87" s="17" t="n">
         <v>46232</v>
@@ -7741,13 +7741,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>101.23</v>
+        <v>101.14</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>-0.1441</v>
+        <v>-0.1448</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>-0.1891</v>
+        <v>-0.1898</v>
       </c>
       <c r="G88" s="7" t="n">
         <v>46238</v>
@@ -7802,13 +7802,13 @@
         </is>
       </c>
       <c r="D89" s="15" t="n">
-        <v>152.66</v>
+        <v>152.72</v>
       </c>
       <c r="E89" s="20" t="n">
-        <v>0.2421</v>
+        <v>0.2425</v>
       </c>
       <c r="F89" s="20" t="n">
-        <v>0.0326</v>
+        <v>0.0329</v>
       </c>
       <c r="G89" s="17" t="n">
         <v>46233</v>
@@ -7863,13 +7863,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>158.21</v>
+        <v>157.43</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0.1571</v>
+        <v>0.1514</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.1605</v>
+        <v>0.1549</v>
       </c>
       <c r="G90" s="7" t="n">
         <v>46252</v>
@@ -7938,13 +7938,13 @@
         </is>
       </c>
       <c r="D91" s="15" t="n">
-        <v>355.75</v>
+        <v>357.31</v>
       </c>
       <c r="E91" s="20" t="n">
-        <v>0.08</v>
+        <v>0.0848</v>
       </c>
       <c r="F91" s="20" t="n">
-        <v>0.1886</v>
+        <v>0.1938</v>
       </c>
       <c r="G91" s="17" t="n">
         <v>46308</v>
@@ -7973,7 +7973,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="16" t="n">
-        <v>-0.4490513000702741</v>
+        <v>-0.4514567182558563</v>
       </c>
       <c r="N91" s="14" t="inlineStr"/>
       <c r="O91" s="19" t="n"/>
@@ -8017,13 +8017,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>102.24</v>
+        <v>102.66</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0.1495</v>
+        <v>0.1543</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.06570000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G92" s="7" t="n">
         <v>46233</v>
@@ -8052,7 +8052,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>2.667840375586854</v>
+        <v>2.652834599649328</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -8063,7 +8063,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>2.599374021909233</v>
+        <v>2.584648353789207</v>
       </c>
       <c r="Q92" s="10" t="inlineStr">
         <is>
@@ -8116,13 +8116,13 @@
         </is>
       </c>
       <c r="D93" s="15" t="n">
-        <v>373.29</v>
+        <v>370.26</v>
       </c>
       <c r="E93" s="20" t="n">
-        <v>0.1243</v>
+        <v>0.1152</v>
       </c>
       <c r="F93" s="20" t="n">
-        <v>0.2248</v>
+        <v>0.2149</v>
       </c>
       <c r="G93" s="17" t="n">
         <v>46317</v>
@@ -8154,7 +8154,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="16" t="n">
-        <v>-0.6919285274183611</v>
+        <v>-0.6894074434181386</v>
       </c>
       <c r="Q93" s="21" t="inlineStr">
         <is>
@@ -8203,13 +8203,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>561.55</v>
+        <v>562.75</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0.1019</v>
+        <v>0.1042</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.1368</v>
+        <v>0.1392</v>
       </c>
       <c r="G94" s="7" t="n">
         <v>46233</v>
@@ -8238,7 +8238,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="6" t="n">
-        <v>-0.3482325705636185</v>
+        <v>-0.3496223900488672</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="9" t="n"/>
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="D95" s="15" t="n">
-        <v>2046.91</v>
+        <v>2039.35</v>
       </c>
       <c r="E95" s="20" t="n">
-        <v>0.0464</v>
+        <v>0.0426</v>
       </c>
       <c r="F95" s="20" t="n">
-        <v>0.1274</v>
+        <v>0.1232</v>
       </c>
       <c r="G95" s="17" t="n">
         <v>46232</v>
@@ -8351,13 +8351,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>211.93</v>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>0.001</v>
+        <v>211.58</v>
+      </c>
+      <c r="E96" s="6" t="n">
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.0189</v>
+        <v>0.0172</v>
       </c>
       <c r="G96" s="7" t="n">
         <v>46309</v>
@@ -8386,7 +8386,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>2.151984145708489</v>
+        <v>2.157198222894413</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>1.595196527155193</v>
+        <v>1.599489554778334</v>
       </c>
       <c r="Q96" s="10" t="inlineStr">
         <is>
@@ -8446,13 +8446,13 @@
         </is>
       </c>
       <c r="D97" s="15" t="n">
-        <v>114.21</v>
+        <v>114.09</v>
       </c>
       <c r="E97" s="20" t="n">
-        <v>0.0525</v>
+        <v>0.05139999999999999</v>
       </c>
       <c r="F97" s="20" t="n">
-        <v>0.1022</v>
+        <v>0.101</v>
       </c>
       <c r="G97" s="17" t="n"/>
       <c r="H97" s="23" t="inlineStr">
@@ -8471,7 +8471,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="20" t="n">
-        <v>1.101392172314158</v>
+        <v>1.103602419142782</v>
       </c>
       <c r="N97" s="14" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="20" t="n">
-        <v>1.101392172314158</v>
+        <v>1.103602419142782</v>
       </c>
       <c r="Q97" s="21" t="inlineStr">
         <is>
@@ -8531,13 +8531,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>251.1</v>
+        <v>251.6</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0.0177</v>
+        <v>0.0197</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.1356</v>
+        <v>0.1378</v>
       </c>
       <c r="G98" s="7" t="n">
         <v>46310</v>
@@ -8566,7 +8566,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="6" t="n">
-        <v>-0.5499800876144962</v>
+        <v>-0.5508744038155803</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="6" t="n">
-        <v>-0.5459976105137395</v>
+        <v>-0.5468998410174881</v>
       </c>
       <c r="Q98" s="10" t="inlineStr"/>
       <c r="R98" s="9" t="n"/>
@@ -8616,13 +8616,13 @@
         </is>
       </c>
       <c r="D99" s="15" t="n">
-        <v>20.97</v>
+        <v>21.24</v>
       </c>
       <c r="E99" s="16" t="n">
-        <v>-0.2443</v>
+        <v>-0.2346</v>
       </c>
       <c r="F99" s="16" t="n">
-        <v>-0.2265</v>
+        <v>-0.2165</v>
       </c>
       <c r="G99" s="17" t="n">
         <v>46233</v>
@@ -8677,13 +8677,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>13.94</v>
+        <v>13.98</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0.0214</v>
+        <v>0.0242</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.1172</v>
+        <v>0.1202</v>
       </c>
       <c r="G100" s="7" t="n">
         <v>46323</v>
@@ -8738,13 +8738,13 @@
         </is>
       </c>
       <c r="D101" s="15" t="n">
-        <v>103.25</v>
+        <v>103.14</v>
       </c>
       <c r="E101" s="20" t="n">
-        <v>0.1938</v>
+        <v>0.1925</v>
       </c>
       <c r="F101" s="20" t="n">
-        <v>0.1749</v>
+        <v>0.1736</v>
       </c>
       <c r="G101" s="17" t="n">
         <v>46323</v>
@@ -8773,7 +8773,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="20" t="n">
-        <v>1.760290556900726</v>
+        <v>1.763234438627109</v>
       </c>
       <c r="N101" s="14" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="20" t="n">
-        <v>1.760290556900726</v>
+        <v>1.763234438627109</v>
       </c>
       <c r="Q101" s="21" t="inlineStr">
         <is>
@@ -8825,13 +8825,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>434.63</v>
+        <v>424.36</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0.1244</v>
+        <v>0.09789999999999999</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0.08349999999999999</v>
+        <v>0.0579</v>
       </c>
       <c r="G102" s="7" t="n">
         <v>46231</v>
@@ -8900,13 +8900,13 @@
         </is>
       </c>
       <c r="D103" s="15" t="n">
-        <v>52.72</v>
+        <v>52.99</v>
       </c>
       <c r="E103" s="20" t="n">
-        <v>0.04219999999999999</v>
+        <v>0.0476</v>
       </c>
       <c r="F103" s="20" t="n">
-        <v>0.0934</v>
+        <v>0.09910000000000001</v>
       </c>
       <c r="G103" s="17" t="n">
         <v>46311</v>
@@ -8961,13 +8961,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>368.6</v>
+        <v>366.59</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0.0789</v>
+        <v>0.073</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.1294</v>
+        <v>0.1233</v>
       </c>
       <c r="G104" s="7" t="n">
         <v>46231</v>
@@ -8996,7 +8996,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>0.4243081931633206</v>
+        <v>0.4321176245942334</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>0.4731416169289202</v>
+        <v>0.4812188002946072</v>
       </c>
       <c r="Q104" s="10" t="inlineStr">
         <is>
@@ -9052,13 +9052,13 @@
         </is>
       </c>
       <c r="D105" s="15" t="n">
-        <v>76.77</v>
+        <v>76.17</v>
       </c>
       <c r="E105" s="20" t="n">
-        <v>0.08109999999999999</v>
+        <v>0.0727</v>
       </c>
       <c r="F105" s="20" t="n">
-        <v>0.2082</v>
+        <v>0.1988</v>
       </c>
       <c r="G105" s="17" t="n">
         <v>46314</v>
@@ -9087,7 +9087,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="20" t="n">
-        <v>4.366679692588251</v>
+        <v>4.408953656295129</v>
       </c>
       <c r="N105" s="14" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="20" t="n">
-        <v>3.559072554383223</v>
+        <v>3.594984902192464</v>
       </c>
       <c r="Q105" s="21" t="inlineStr">
         <is>
@@ -9143,13 +9143,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>82.67</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0.0596</v>
+        <v>0.06509999999999999</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.09179999999999999</v>
+        <v>0.0975</v>
       </c>
       <c r="G106" s="7" t="n">
         <v>46239</v>
@@ -9178,7 +9178,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="6" t="n">
-        <v>-0.1774525220757228</v>
+        <v>-0.1817087845968712</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="6" t="n">
-        <v>-0.1774525220757228</v>
+        <v>-0.1817087845968712</v>
       </c>
       <c r="Q106" s="10" t="inlineStr">
         <is>
@@ -9234,13 +9234,13 @@
         </is>
       </c>
       <c r="D107" s="15" t="n">
-        <v>264.83</v>
+        <v>263.2</v>
       </c>
       <c r="E107" s="20" t="n">
-        <v>0.0414</v>
+        <v>0.035</v>
       </c>
       <c r="F107" s="20" t="n">
-        <v>0.2164</v>
+        <v>0.2089</v>
       </c>
       <c r="G107" s="17" t="n">
         <v>46234</v>
@@ -9269,7 +9269,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="20" t="n">
-        <v>0.1139221387305064</v>
+        <v>0.1208206686930092</v>
       </c>
       <c r="N107" s="14" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="16" t="n">
-        <v>-0.07110221651625566</v>
+        <v>-0.06534954407294828</v>
       </c>
       <c r="Q107" s="21" t="inlineStr">
         <is>
@@ -9317,13 +9317,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>107.54</v>
+        <v>107.27</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0.16</v>
+        <v>0.157</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.2563</v>
+        <v>0.2532</v>
       </c>
       <c r="G108" s="7" t="n">
         <v>46316</v>
@@ -9352,7 +9352,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0.04147294030128319</v>
+        <v>0.04409434138156058</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>0.1158638646085177</v>
+        <v>0.1186725086231006</v>
       </c>
       <c r="Q108" s="10" t="inlineStr">
         <is>
@@ -9416,13 +9416,13 @@
         </is>
       </c>
       <c r="D109" s="15" t="n">
-        <v>390.76</v>
+        <v>393.1</v>
       </c>
       <c r="E109" s="20" t="n">
-        <v>0.08380000000000001</v>
+        <v>0.09029999999999999</v>
       </c>
       <c r="F109" s="20" t="n">
-        <v>0.1602</v>
+        <v>0.1672</v>
       </c>
       <c r="G109" s="17" t="n">
         <v>46238</v>
@@ -9451,7 +9451,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="16" t="n">
-        <v>-0.001944927832940912</v>
+        <v>-0.007886034088018374</v>
       </c>
       <c r="N109" s="14" t="inlineStr">
         <is>
@@ -9499,13 +9499,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>164.52</v>
+        <v>166.34</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0.0601</v>
+        <v>0.0718</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.1183</v>
+        <v>0.1306</v>
       </c>
       <c r="G110" s="7" t="n">
         <v>46240</v>
@@ -9534,7 +9534,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="6" t="n">
-        <v>-0.02139557500607835</v>
+        <v>-0.03210292172658413</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>0.0940919037199124</v>
+        <v>0.08212095707586868</v>
       </c>
       <c r="Q110" s="10" t="inlineStr">
         <is>
@@ -9586,13 +9586,13 @@
         </is>
       </c>
       <c r="D111" s="15" t="n">
-        <v>46.42</v>
+        <v>46.06</v>
       </c>
       <c r="E111" s="20" t="n">
-        <v>0.0675</v>
+        <v>0.0593</v>
       </c>
       <c r="F111" s="16" t="n">
-        <v>-0.0392</v>
+        <v>-0.0466</v>
       </c>
       <c r="G111" s="17" t="n">
         <v>46232</v>
@@ -9621,7 +9621,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="20" t="n">
-        <v>0.1848341232227488</v>
+        <v>0.1940946591402518</v>
       </c>
       <c r="N111" s="14" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="20" t="n">
-        <v>0.4002585092632486</v>
+        <v>0.4112027789839339</v>
       </c>
       <c r="Q111" s="21" t="inlineStr">
         <is>
@@ -9673,13 +9673,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>318.21</v>
+        <v>319.58</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0.1298</v>
+        <v>0.1347</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.1814</v>
+        <v>0.1864</v>
       </c>
       <c r="G112" s="7" t="n">
         <v>46239</v>
@@ -9708,7 +9708,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>0.04019358285409013</v>
+        <v>0.03573440140183996</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="5" t="n">
-        <v>0.03705100405392672</v>
+        <v>0.03260529444896432</v>
       </c>
       <c r="Q112" s="10" t="inlineStr">
         <is>
@@ -9768,13 +9768,13 @@
         </is>
       </c>
       <c r="D113" s="15" t="n">
-        <v>108.65</v>
+        <v>109.34</v>
       </c>
       <c r="E113" s="20" t="n">
-        <v>0.049</v>
+        <v>0.0556</v>
       </c>
       <c r="F113" s="20" t="n">
-        <v>0.1943</v>
+        <v>0.2018</v>
       </c>
       <c r="G113" s="17" t="n">
         <v>46239</v>
@@ -9803,7 +9803,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="20" t="n">
-        <v>0.1320754716981132</v>
+        <v>0.1249314066215474</v>
       </c>
       <c r="N113" s="14" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="20" t="n">
-        <v>0.1965025310630464</v>
+        <v>0.1889518931772453</v>
       </c>
       <c r="Q113" s="21" t="inlineStr">
         <is>
@@ -9855,13 +9855,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>200.03</v>
+        <v>199.05</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0.03759999999999999</v>
+        <v>0.0325</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.095</v>
+        <v>0.0897</v>
       </c>
       <c r="G114" s="7" t="n">
         <v>46315</v>
@@ -9890,7 +9890,7 @@
         <v>212</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>0.05984102384642303</v>
+        <v>0.06505903039437322</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="5" t="n">
-        <v>0.02484627305904114</v>
+        <v>0.02989198693795523</v>
       </c>
       <c r="Q114" s="10" t="inlineStr">
         <is>
@@ -9946,13 +9946,13 @@
         </is>
       </c>
       <c r="D115" s="15" t="n">
-        <v>75.67</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="E115" s="20" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0696</v>
       </c>
       <c r="F115" s="20" t="n">
-        <v>0.0261</v>
+        <v>0.0151</v>
       </c>
       <c r="G115" s="17" t="n">
         <v>46233</v>
@@ -9981,7 +9981,7 @@
         <v>85</v>
       </c>
       <c r="M115" s="20" t="n">
-        <v>0.1232985331042685</v>
+        <v>0.1356045424181698</v>
       </c>
       <c r="N115" s="14" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="20" t="n">
-        <v>0.1893749174045196</v>
+        <v>0.2024048096192386</v>
       </c>
       <c r="Q115" s="21" t="inlineStr">
         <is>
@@ -10033,13 +10033,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>133.19</v>
+        <v>134.32</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0.05429999999999999</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>-0.0092</v>
+        <v>-0.0008</v>
       </c>
       <c r="G116" s="7" t="n">
         <v>46238</v>
@@ -10068,7 +10068,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>0.2388317441249343</v>
+        <v>0.2284097677188804</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="9" t="n"/>
@@ -10116,13 +10116,13 @@
         </is>
       </c>
       <c r="D117" s="15" t="n">
-        <v>570.5599999999999</v>
+        <v>569.54</v>
       </c>
       <c r="E117" s="20" t="n">
-        <v>0.0646</v>
+        <v>0.06269999999999999</v>
       </c>
       <c r="F117" s="20" t="n">
-        <v>0.0125</v>
+        <v>0.0107</v>
       </c>
       <c r="G117" s="17" t="n">
         <v>46238</v>
@@ -10187,13 +10187,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>364.68</v>
+        <v>361.8</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>-0.1017</v>
+        <v>-0.1088</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>-0.1412</v>
+        <v>-0.148</v>
       </c>
       <c r="G118" s="7" t="n">
         <v>46315</v>
@@ -10222,7 +10222,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>0.3354173521991883</v>
+        <v>0.3460475400773908</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -10233,7 +10233,7 @@
         <v>375</v>
       </c>
       <c r="P118" s="5" t="n">
-        <v>0.02829878249424151</v>
+        <v>0.03648424543946929</v>
       </c>
       <c r="Q118" s="10" t="inlineStr">
         <is>
@@ -10278,13 +10278,13 @@
         </is>
       </c>
       <c r="D119" s="15" t="n">
-        <v>269.04</v>
+        <v>266.73</v>
       </c>
       <c r="E119" s="20" t="n">
-        <v>0.0407</v>
+        <v>0.0318</v>
       </c>
       <c r="F119" s="20" t="n">
-        <v>0.194</v>
+        <v>0.1837</v>
       </c>
       <c r="G119" s="17" t="n">
         <v>46315</v>
@@ -10313,7 +10313,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="20" t="n">
-        <v>0.01100208147487355</v>
+        <v>0.01975780752071376</v>
       </c>
       <c r="N119" s="14" t="inlineStr"/>
       <c r="O119" s="19" t="n"/>
@@ -10365,13 +10365,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1218.08</v>
+        <v>1220.66</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0075</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>0.1023</v>
+        <v>0.1047</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>46239</v>
@@ -10400,7 +10400,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>0.050834099566531</v>
+        <v>0.04861304540166788</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -10460,13 +10460,13 @@
         </is>
       </c>
       <c r="D121" s="15" t="n">
-        <v>86.89</v>
+        <v>86.88</v>
       </c>
       <c r="E121" s="20" t="n">
-        <v>0.0737</v>
+        <v>0.0735</v>
       </c>
       <c r="F121" s="20" t="n">
-        <v>0.1773</v>
+        <v>0.1771</v>
       </c>
       <c r="G121" s="17" t="n">
         <v>46266</v>
@@ -10495,7 +10495,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="20" t="n">
-        <v>0.1738980319944758</v>
+        <v>0.1740331491712708</v>
       </c>
       <c r="N121" s="14" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="20" t="n">
-        <v>0.2084244447001956</v>
+        <v>0.2085635359116023</v>
       </c>
       <c r="Q121" s="21" t="inlineStr">
         <is>
@@ -10547,13 +10547,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>131.86</v>
+        <v>131.82</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0.0192</v>
+        <v>0.0189</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0.1107</v>
+        <v>0.1103</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>46238</v>
@@ -10582,7 +10582,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>0.1375701501592597</v>
+        <v>0.1379153390987711</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="9" t="n"/>
@@ -10626,13 +10626,13 @@
         </is>
       </c>
       <c r="D123" s="15" t="n">
-        <v>159.43</v>
+        <v>159.85</v>
       </c>
       <c r="E123" s="20" t="n">
-        <v>0.0117</v>
+        <v>0.0143</v>
       </c>
       <c r="F123" s="20" t="n">
-        <v>0.0617</v>
+        <v>0.0645</v>
       </c>
       <c r="G123" s="17" t="n">
         <v>46322</v>
@@ -10705,13 +10705,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>25.17</v>
+        <v>25.25</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.0326</v>
+        <v>0.0361</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>-0.0388</v>
+        <v>-0.0355</v>
       </c>
       <c r="G124" s="7" t="n">
         <v>46238</v>
@@ -10740,7 +10740,7 @@
         <v>28</v>
       </c>
       <c r="M124" s="5" t="n">
-        <v>0.1124354390147</v>
+        <v>0.1089108910891089</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="9" t="n"/>
@@ -10784,13 +10784,13 @@
         </is>
       </c>
       <c r="D125" s="15" t="n">
-        <v>345.48</v>
+        <v>346.6</v>
       </c>
       <c r="E125" s="20" t="n">
-        <v>0.0453</v>
+        <v>0.0487</v>
       </c>
       <c r="F125" s="20" t="n">
-        <v>0.1324</v>
+        <v>0.1361</v>
       </c>
       <c r="G125" s="17" t="n">
         <v>46233</v>
@@ -10819,7 +10819,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="20" t="n">
-        <v>0.2099108486743081</v>
+        <v>0.2060011540680899</v>
       </c>
       <c r="N125" s="14" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="20" t="n">
-        <v>0.01308324649762644</v>
+        <v>0.009809578765147077</v>
       </c>
       <c r="Q125" s="21" t="inlineStr">
         <is>
@@ -10875,13 +10875,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>576.47</v>
+        <v>576.41</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0.1383</v>
+        <v>0.1382</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>0.1705</v>
+        <v>0.1704</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>46323</v>
@@ -10910,7 +10910,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>0.06683782330390128</v>
+        <v>0.06694887319789739</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="6" t="n">
-        <v>-0.01122348084028662</v>
+        <v>-0.01112055654829022</v>
       </c>
       <c r="Q126" s="10" t="inlineStr">
         <is>
@@ -10970,13 +10970,13 @@
         </is>
       </c>
       <c r="D127" s="15" t="n">
-        <v>427.15</v>
+        <v>428.79</v>
       </c>
       <c r="E127" s="20" t="n">
-        <v>0.0175</v>
+        <v>0.0214</v>
       </c>
       <c r="F127" s="20" t="n">
-        <v>0.1232</v>
+        <v>0.1275</v>
       </c>
       <c r="G127" s="17" t="n">
         <v>46322</v>
@@ -11005,7 +11005,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="20" t="n">
-        <v>0.2314175348238325</v>
+        <v>0.2267077124000093</v>
       </c>
       <c r="N127" s="14" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="20" t="n">
-        <v>0.1237270279761209</v>
+        <v>0.1194290911635066</v>
       </c>
       <c r="Q127" s="21" t="inlineStr">
         <is>
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>78.17</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0.06709999999999999</v>
-      </c>
-      <c r="F128" s="5" t="n">
-        <v>0.0061</v>
+        <v>0.0582</v>
+      </c>
+      <c r="F128" s="6" t="n">
+        <v>-0.0023</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>46240</v>
@@ -11140,13 +11140,13 @@
         </is>
       </c>
       <c r="D129" s="15" t="n">
-        <v>266.4</v>
+        <v>264.17</v>
       </c>
       <c r="E129" s="20" t="n">
-        <v>0.1842</v>
+        <v>0.1742</v>
       </c>
       <c r="F129" s="20" t="n">
-        <v>0.2009</v>
+        <v>0.1908</v>
       </c>
       <c r="G129" s="17" t="n">
         <v>46232</v>
@@ -11175,7 +11175,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="16" t="n">
-        <v>-0.06906906906906898</v>
+        <v>-0.06121058409357617</v>
       </c>
       <c r="N129" s="14" t="inlineStr"/>
       <c r="O129" s="19" t="n"/>
@@ -11231,13 +11231,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>123.83</v>
+        <v>123.71</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0.0382</v>
+        <v>0.0371</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>0.1029</v>
+        <v>0.1018</v>
       </c>
       <c r="G130" s="7" t="n">
         <v>46233</v>
@@ -11292,13 +11292,13 @@
         </is>
       </c>
       <c r="D131" s="15" t="n">
-        <v>243.03</v>
+        <v>241.43</v>
       </c>
       <c r="E131" s="20" t="n">
-        <v>0.0223</v>
+        <v>0.0156</v>
       </c>
       <c r="F131" s="20" t="n">
-        <v>0.0761</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G131" s="17" t="n">
         <v>46238</v>
@@ -11353,13 +11353,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>222.82</v>
+        <v>221.56</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0.0379</v>
+        <v>0.032</v>
       </c>
       <c r="F132" s="6" t="n">
-        <v>-0.036</v>
+        <v>-0.0415</v>
       </c>
       <c r="G132" s="7" t="n">
         <v>46231</v>
@@ -11388,7 +11388,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>0.1219818687730007</v>
+        <v>0.1283625203105254</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="9" t="n"/>
@@ -11432,13 +11432,13 @@
         </is>
       </c>
       <c r="D133" s="15" t="n">
-        <v>160.01</v>
+        <v>158.18</v>
       </c>
       <c r="E133" s="20" t="n">
-        <v>0.1814</v>
+        <v>0.1679</v>
       </c>
       <c r="F133" s="20" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.029</v>
       </c>
       <c r="G133" s="17" t="n">
         <v>46238</v>
@@ -11503,13 +11503,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>837.9299999999999</v>
+        <v>840.85</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>-0.189</v>
+        <v>-0.1862</v>
       </c>
       <c r="F134" s="6" t="n">
-        <v>-0.0433</v>
+        <v>-0.04</v>
       </c>
       <c r="G134" s="7" t="n">
         <v>46238</v>
@@ -11538,7 +11538,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>0.3783967634527945</v>
+        <v>0.3736100374620919</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="5" t="n">
-        <v>0.3163390736696384</v>
+        <v>0.3117678539573051</v>
       </c>
       <c r="Q134" s="10" t="inlineStr">
         <is>
@@ -11590,13 +11590,13 @@
         </is>
       </c>
       <c r="D135" s="15" t="n">
-        <v>638.02</v>
+        <v>641.6</v>
       </c>
       <c r="E135" s="16" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.0716</v>
       </c>
       <c r="F135" s="16" t="n">
-        <v>-0.0133</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="G135" s="17" t="n">
         <v>46238</v>
@@ -11625,7 +11625,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="20" t="n">
-        <v>0.3698630136986302</v>
+        <v>0.362219451371571</v>
       </c>
       <c r="N135" s="14" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="20" t="n">
-        <v>0.3244098931067992</v>
+        <v>0.3170199501246883</v>
       </c>
       <c r="Q135" s="21" t="inlineStr">
         <is>
@@ -11685,13 +11685,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>216.31</v>
+        <v>214.9</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0.2793</v>
+        <v>0.271</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>0.2631</v>
+        <v>0.2548</v>
       </c>
       <c r="G136" s="7" t="n">
         <v>46288</v>
@@ -11720,7 +11720,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>0.1557486940039758</v>
+        <v>0.1633317822242903</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="9" t="n"/>
@@ -11764,13 +11764,13 @@
         </is>
       </c>
       <c r="D137" s="15" t="n">
-        <v>640.2</v>
+        <v>639.84</v>
       </c>
       <c r="E137" s="20" t="n">
-        <v>0.0217</v>
+        <v>0.0211</v>
       </c>
       <c r="F137" s="20" t="n">
-        <v>0.1808</v>
+        <v>0.1801</v>
       </c>
       <c r="G137" s="17" t="n">
         <v>46254</v>
@@ -11799,7 +11799,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="20" t="n">
-        <v>0.1715089034676663</v>
+        <v>0.1721680420105026</v>
       </c>
       <c r="N137" s="14" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="20" t="n">
-        <v>0.001702592939706214</v>
+        <v>0.002266191547886865</v>
       </c>
       <c r="Q137" s="21" t="inlineStr">
         <is>
@@ -11851,13 +11851,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>151.63</v>
+        <v>151.81</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0.0617</v>
+        <v>0.0629</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.05429999999999999</v>
+        <v>0.0556</v>
       </c>
       <c r="G138" s="7" t="n">
         <v>46238</v>
@@ -11893,7 +11893,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="5" t="n">
-        <v>0.2200751830112775</v>
+        <v>0.2186285488439497</v>
       </c>
       <c r="Q138" s="10" t="inlineStr">
         <is>
@@ -11932,13 +11932,13 @@
         </is>
       </c>
       <c r="D139" s="15" t="n">
-        <v>386.39</v>
+        <v>386.26</v>
       </c>
       <c r="E139" s="16" t="n">
-        <v>-0.0536</v>
+        <v>-0.0539</v>
       </c>
       <c r="F139" s="16" t="n">
-        <v>-0.0355</v>
+        <v>-0.0358</v>
       </c>
       <c r="G139" s="17" t="n">
         <v>46234</v>
@@ -11974,7 +11974,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="20" t="n">
-        <v>0.1723905898185771</v>
+        <v>0.1727851706104697</v>
       </c>
       <c r="Q139" s="21" t="inlineStr">
         <is>
@@ -12015,13 +12015,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>48.17</v>
+        <v>48.1</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0.0164</v>
+        <v>0.0148</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>0.08990000000000001</v>
+        <v>0.0882</v>
       </c>
       <c r="G140" s="7" t="n">
         <v>46309</v>
@@ -12094,13 +12094,13 @@
         </is>
       </c>
       <c r="D141" s="15" t="n">
-        <v>310.54</v>
+        <v>312.64</v>
       </c>
       <c r="E141" s="16" t="n">
-        <v>-0.0457</v>
+        <v>-0.0392</v>
       </c>
       <c r="F141" s="16" t="n">
-        <v>-0.064</v>
+        <v>-0.05769999999999999</v>
       </c>
       <c r="G141" s="17" t="n">
         <v>46282</v>
@@ -12129,7 +12129,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="20" t="n">
-        <v>0.3685837573259483</v>
+        <v>0.3593909928352099</v>
       </c>
       <c r="N141" s="14" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="20" t="n">
-        <v>0.04012365556772068</v>
+        <v>0.03313715455475951</v>
       </c>
       <c r="Q141" s="21" t="inlineStr">
         <is>
@@ -12181,13 +12181,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>231.01</v>
+        <v>232.02</v>
       </c>
       <c r="E142" s="6" t="n">
-        <v>-0.0319</v>
+        <v>-0.0276</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>0.0223</v>
+        <v>0.0268</v>
       </c>
       <c r="G142" s="7" t="n">
         <v>46244</v>
@@ -12216,7 +12216,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="5" t="n">
-        <v>0.2337128262845765</v>
+        <v>0.2283423842772174</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="9" t="n"/>
@@ -12264,13 +12264,13 @@
         </is>
       </c>
       <c r="D143" s="15" t="n">
-        <v>1609.83</v>
+        <v>1626.32</v>
       </c>
       <c r="E143" s="16" t="n">
-        <v>-0.1739</v>
+        <v>-0.1654</v>
       </c>
       <c r="F143" s="16" t="n">
-        <v>-0.1194</v>
+        <v>-0.1104</v>
       </c>
       <c r="G143" s="17" t="n">
         <v>46317</v>
@@ -12325,13 +12325,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>49.6</v>
+        <v>49.34</v>
       </c>
       <c r="E144" s="6" t="n">
-        <v>-0.07690000000000001</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>0.0839</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="G144" s="7" t="n">
         <v>46241</v>
@@ -12386,13 +12386,13 @@
         </is>
       </c>
       <c r="D145" s="15" t="n">
-        <v>392.6</v>
+        <v>393.19</v>
       </c>
       <c r="E145" s="20" t="n">
-        <v>0.1279</v>
+        <v>0.1296</v>
       </c>
       <c r="F145" s="20" t="n">
-        <v>0.132</v>
+        <v>0.1337</v>
       </c>
       <c r="G145" s="17" t="n">
         <v>46232</v>
@@ -12421,7 +12421,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="20" t="n">
-        <v>0.01884870096790621</v>
+        <v>0.01731987080037642</v>
       </c>
       <c r="N145" s="14" t="inlineStr"/>
       <c r="O145" s="19" t="n"/>
@@ -12473,13 +12473,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>361.18</v>
+        <v>363.59</v>
       </c>
       <c r="E146" s="6" t="n">
-        <v>-0.0335</v>
+        <v>-0.0271</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>0.1156</v>
+        <v>0.123</v>
       </c>
       <c r="G146" s="7" t="n">
         <v>46315</v>
@@ -12508,7 +12508,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="5" t="n">
-        <v>0.07979400852760395</v>
+        <v>0.07263676118705142</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="9" t="n"/>
@@ -12560,13 +12560,13 @@
         </is>
       </c>
       <c r="D147" s="15" t="n">
-        <v>943.73</v>
+        <v>943.38</v>
       </c>
       <c r="E147" s="16" t="n">
-        <v>-0.144</v>
+        <v>-0.1443</v>
       </c>
       <c r="F147" s="16" t="n">
-        <v>-0.0254</v>
+        <v>-0.0258</v>
       </c>
       <c r="G147" s="17" t="n">
         <v>46316</v>
@@ -12595,7 +12595,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="20" t="n">
-        <v>0.3340680067392157</v>
+        <v>0.3345629544828171</v>
       </c>
       <c r="N147" s="14" t="inlineStr">
         <is>
@@ -12606,7 +12606,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="20" t="n">
-        <v>0.4304938912612717</v>
+        <v>0.4310246136233543</v>
       </c>
       <c r="Q147" s="21" t="inlineStr">
         <is>
@@ -12651,13 +12651,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1404.05</v>
+        <v>1398.9</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0.0375</v>
+        <v>0.0337</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>0.1376</v>
+        <v>0.1334</v>
       </c>
       <c r="G148" s="7" t="n">
         <v>46238</v>
@@ -12726,13 +12726,13 @@
         </is>
       </c>
       <c r="D149" s="15" t="n">
-        <v>249.06</v>
+        <v>247.05</v>
       </c>
       <c r="E149" s="20" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.08449999999999999</v>
       </c>
       <c r="F149" s="16" t="n">
-        <v>-0.0016</v>
+        <v>-0.0097</v>
       </c>
       <c r="G149" s="17" t="n">
         <v>46317</v>
@@ -12787,13 +12787,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>486.85</v>
+        <v>483.66</v>
       </c>
       <c r="E150" s="6" t="n">
-        <v>-0.0541</v>
+        <v>-0.0603</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>0.028</v>
+        <v>0.0212</v>
       </c>
       <c r="G150" s="7" t="n">
         <v>46231</v>
@@ -12854,13 +12854,13 @@
         </is>
       </c>
       <c r="D151" s="15" t="n">
-        <v>299.91</v>
+        <v>295.16</v>
       </c>
       <c r="E151" s="20" t="n">
-        <v>0.1213</v>
+        <v>0.1035</v>
       </c>
       <c r="F151" s="20" t="n">
-        <v>0.2128</v>
+        <v>0.1936</v>
       </c>
       <c r="G151" s="17" t="n">
         <v>46231</v>
@@ -12892,7 +12892,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="16" t="n">
-        <v>-0.09306125170884606</v>
+        <v>-0.07846591679089315</v>
       </c>
       <c r="Q151" s="21" t="inlineStr">
         <is>
@@ -12945,13 +12945,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>305.1</v>
+        <v>305.2</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>0.05429999999999999</v>
+        <v>0.0547</v>
       </c>
       <c r="F152" s="6" t="n">
-        <v>-0.032</v>
+        <v>-0.0317</v>
       </c>
       <c r="G152" s="7" t="n">
         <v>46232</v>
@@ -13016,13 +13016,13 @@
         </is>
       </c>
       <c r="D153" s="15" t="n">
-        <v>549.95</v>
+        <v>544.11</v>
       </c>
       <c r="E153" s="16" t="n">
-        <v>-0.0332</v>
+        <v>-0.0435</v>
       </c>
       <c r="F153" s="20" t="n">
-        <v>0.09519999999999999</v>
+        <v>0.08349999999999999</v>
       </c>
       <c r="G153" s="17" t="n">
         <v>46232</v>
@@ -13077,13 +13077,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>580.64</v>
+        <v>581.3099999999999</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0.1565</v>
+        <v>0.1578</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0.0946</v>
+        <v>0.0959</v>
       </c>
       <c r="G154" s="7" t="n">
         <v>46315</v>
@@ -13144,13 +13144,13 @@
         </is>
       </c>
       <c r="D155" s="15" t="n">
-        <v>229.39</v>
+        <v>226.28</v>
       </c>
       <c r="E155" s="20" t="n">
-        <v>0.0442</v>
+        <v>0.03</v>
       </c>
       <c r="F155" s="20" t="n">
-        <v>0.0188</v>
+        <v>0.005</v>
       </c>
       <c r="G155" s="17" t="n">
         <v>46232</v>
@@ -13179,7 +13179,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="20" t="n">
-        <v>1.506648066611448</v>
+        <v>1.54109952271522</v>
       </c>
       <c r="N155" s="14" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="20" t="n">
-        <v>0.03317494223810983</v>
+        <v>0.04737493371044723</v>
       </c>
       <c r="Q155" s="21" t="inlineStr">
         <is>
@@ -13239,13 +13239,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>119.07</v>
+        <v>118.87</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0.193</v>
+        <v>0.191</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.2278</v>
+        <v>0.2257</v>
       </c>
       <c r="G156" s="7" t="n">
         <v>46294</v>
@@ -13274,7 +13274,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="5" t="n">
-        <v>1.099605274208449</v>
+        <v>1.103137881719525</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="9" t="n"/>
@@ -13318,13 +13318,13 @@
         </is>
       </c>
       <c r="D157" s="15" t="n">
-        <v>138.59</v>
+        <v>138.21</v>
       </c>
       <c r="E157" s="20" t="n">
-        <v>0.1587</v>
+        <v>0.1556</v>
       </c>
       <c r="F157" s="20" t="n">
-        <v>0.2556</v>
+        <v>0.2522</v>
       </c>
       <c r="G157" s="17" t="n">
         <v>46231</v>
@@ -13353,7 +13353,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="16" t="n">
-        <v>-0.3145248574933256</v>
+        <v>-0.3126401852253817</v>
       </c>
       <c r="N157" s="14" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="20" t="n">
-        <v>0.002958366404502465</v>
+        <v>0.005715939512336242</v>
       </c>
       <c r="Q157" s="21" t="inlineStr">
         <is>
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>995.77</v>
+        <v>990.96</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>0.0332</v>
+        <v>0.0282</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>0.1789</v>
+        <v>0.1732</v>
       </c>
       <c r="G158" s="7" t="n">
         <v>46240</v>
@@ -13444,7 +13444,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="6" t="n">
-        <v>-0.8744690038864397</v>
+        <v>-0.873859691612174</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="5" t="n">
-        <v>0.0685198389186258</v>
+        <v>0.07370630499717441</v>
       </c>
       <c r="Q158" s="10" t="inlineStr">
         <is>
@@ -13500,13 +13500,13 @@
         </is>
       </c>
       <c r="D159" s="15" t="n">
-        <v>578.34</v>
+        <v>576.37</v>
       </c>
       <c r="E159" s="16" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.092</v>
       </c>
       <c r="F159" s="20" t="n">
-        <v>0.0112</v>
+        <v>0.0077</v>
       </c>
       <c r="G159" s="17" t="n">
         <v>46234</v>
@@ -13581,13 +13581,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>471.98</v>
+        <v>471.17</v>
       </c>
       <c r="E160" s="6" t="n">
-        <v>-0.0215</v>
+        <v>-0.0231</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>0.0464</v>
+        <v>0.0446</v>
       </c>
       <c r="G160" s="7" t="n">
         <v>46238</v>
@@ -13642,13 +13642,13 @@
         </is>
       </c>
       <c r="D161" s="15" t="n">
-        <v>38.86</v>
+        <v>39.01</v>
       </c>
       <c r="E161" s="16" t="n">
-        <v>-0.0809</v>
+        <v>-0.07730000000000001</v>
       </c>
       <c r="F161" s="16" t="n">
-        <v>-0.1836</v>
+        <v>-0.1805</v>
       </c>
       <c r="G161" s="17" t="n">
         <v>46323</v>
@@ -13717,13 +13717,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>217.54</v>
+        <v>218.58</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>0.1613</v>
+        <v>0.1668</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>0.2108</v>
+        <v>0.2166</v>
       </c>
       <c r="G162" s="7" t="n">
         <v>46322</v>
@@ -13796,13 +13796,13 @@
         </is>
       </c>
       <c r="D163" s="15" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="E163" s="16" t="n">
-        <v>-0.0247</v>
+        <v>42.34</v>
+      </c>
+      <c r="E163" s="20" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F163" s="16" t="n">
-        <v>-0.1147</v>
+        <v>-0.08800000000000001</v>
       </c>
       <c r="G163" s="17" t="n">
         <v>46239</v>
@@ -13857,13 +13857,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>467.24</v>
+        <v>470.03</v>
       </c>
       <c r="E164" s="6" t="n">
-        <v>-0.0273</v>
+        <v>-0.0215</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>0.0353</v>
+        <v>0.0415</v>
       </c>
       <c r="G164" s="7" t="n">
         <v>46233</v>
@@ -13895,7 +13895,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="5" t="n">
-        <v>0.1985275233284821</v>
+        <v>0.1914133140437845</v>
       </c>
       <c r="Q164" s="10" t="inlineStr">
         <is>
@@ -13948,13 +13948,13 @@
         </is>
       </c>
       <c r="D165" s="15" t="n">
-        <v>298.28</v>
+        <v>294.45</v>
       </c>
       <c r="E165" s="20" t="n">
-        <v>0.09380000000000001</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="F165" s="20" t="n">
-        <v>0.1357</v>
+        <v>0.1211</v>
       </c>
       <c r="G165" s="17" t="n">
         <v>46317</v>
@@ -13986,7 +13986,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="16" t="n">
-        <v>-0.01434893388762228</v>
+        <v>-0.001528273051451821</v>
       </c>
       <c r="Q165" s="21" t="inlineStr">
         <is>
@@ -14031,13 +14031,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>267.4</v>
+        <v>269.56</v>
       </c>
       <c r="E166" s="6" t="n">
-        <v>-0.1289</v>
+        <v>-0.1219</v>
       </c>
       <c r="F166" s="6" t="n">
-        <v>-0.153</v>
+        <v>-0.1462</v>
       </c>
       <c r="G166" s="7" t="n">
         <v>46232</v>
@@ -14069,7 +14069,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="5" t="n">
-        <v>0.5893792071802544</v>
+        <v>0.576643418904882</v>
       </c>
       <c r="Q166" s="10" t="inlineStr">
         <is>
@@ -14110,13 +14110,13 @@
         </is>
       </c>
       <c r="D167" s="15" t="n">
-        <v>239.21</v>
+        <v>239.41</v>
       </c>
       <c r="E167" s="20" t="n">
-        <v>0.0709</v>
+        <v>0.0718</v>
       </c>
       <c r="F167" s="20" t="n">
-        <v>0.1313</v>
+        <v>0.1322</v>
       </c>
       <c r="G167" s="17" t="n">
         <v>46231</v>
@@ -14145,7 +14145,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="20" t="n">
-        <v>0.1203545002299235</v>
+        <v>0.119418570652855</v>
       </c>
       <c r="N167" s="14" t="inlineStr"/>
       <c r="O167" s="19" t="n"/>
@@ -14193,13 +14193,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>367.64</v>
+        <v>367.51</v>
       </c>
       <c r="E168" s="6" t="n">
-        <v>-0.1046</v>
+        <v>-0.1049</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0011</v>
       </c>
       <c r="G168" s="7" t="n">
         <v>46232</v>
@@ -14268,13 +14268,13 @@
         </is>
       </c>
       <c r="D169" s="15" t="n">
-        <v>410.74</v>
+        <v>410.55</v>
       </c>
       <c r="E169" s="16" t="n">
-        <v>-0.0297</v>
+        <v>-0.0302</v>
       </c>
       <c r="F169" s="20" t="n">
-        <v>0.1734</v>
+        <v>0.1729</v>
       </c>
       <c r="G169" s="17" t="n">
         <v>46232</v>
@@ -14347,13 +14347,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>124.81</v>
+        <v>124.97</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>0.0692</v>
+        <v>0.0706</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>0.1394</v>
+        <v>0.1409</v>
       </c>
       <c r="G170" s="7" t="n">
         <v>46231</v>
@@ -14426,13 +14426,13 @@
         </is>
       </c>
       <c r="D171" s="15" t="n">
-        <v>87.59999999999999</v>
+        <v>88.14</v>
       </c>
       <c r="E171" s="16" t="n">
-        <v>-0.4164</v>
+        <v>-0.4128</v>
       </c>
       <c r="F171" s="16" t="n">
-        <v>-0.447</v>
+        <v>-0.4436</v>
       </c>
       <c r="G171" s="17" t="n">
         <v>46240</v>
@@ -14487,7 +14487,7 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>340.09</v>
+        <v>340.08</v>
       </c>
       <c r="E172" s="5" t="n">
         <v>0.2071</v>
@@ -14522,7 +14522,7 @@
         <v>310</v>
       </c>
       <c r="M172" s="6" t="n">
-        <v>-0.08847657972889522</v>
+        <v>-0.08844977652317097</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="5" t="n">
-        <v>0.0732453174159782</v>
+        <v>0.07327687602916966</v>
       </c>
       <c r="Q172" s="10" t="inlineStr">
         <is>
@@ -14590,13 +14590,13 @@
         </is>
       </c>
       <c r="D173" s="15" t="n">
-        <v>116.49</v>
+        <v>120.03</v>
       </c>
       <c r="E173" s="16" t="n">
-        <v>-0.3386</v>
+        <v>-0.3185</v>
       </c>
       <c r="F173" s="16" t="n">
-        <v>-0.2255</v>
+        <v>-0.202</v>
       </c>
       <c r="G173" s="17" t="n">
         <v>46240</v>
@@ -14651,13 +14651,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>165.02</v>
+        <v>164.66</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>0.3229</v>
+        <v>0.32</v>
       </c>
       <c r="F174" s="6" t="n">
-        <v>-0.1179</v>
+        <v>-0.1198</v>
       </c>
       <c r="G174" s="7" t="n">
         <v>46296</v>
@@ -14712,13 +14712,13 @@
         </is>
       </c>
       <c r="D175" s="15" t="n">
-        <v>252.98</v>
+        <v>249.18</v>
       </c>
       <c r="E175" s="20" t="n">
-        <v>0.2255</v>
+        <v>0.2071</v>
       </c>
       <c r="F175" s="16" t="n">
-        <v>-0.024</v>
+        <v>-0.0387</v>
       </c>
       <c r="G175" s="17" t="n">
         <v>46275</v>
@@ -14773,13 +14773,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>369.64</v>
+        <v>365.83</v>
       </c>
       <c r="E176" s="6" t="n">
-        <v>-0.0565</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="F176" s="6" t="n">
-        <v>-0.1068</v>
+        <v>-0.116</v>
       </c>
       <c r="G176" s="7" t="n">
         <v>46253</v>
@@ -14808,7 +14808,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="5" t="n">
-        <v>0.393247484038524</v>
+        <v>0.4077577016647077</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="5" t="n">
-        <v>0.2823287522995347</v>
+        <v>0.2956837875515951</v>
       </c>
       <c r="Q176" s="10" t="inlineStr">
         <is>
@@ -14868,13 +14868,13 @@
         </is>
       </c>
       <c r="D177" s="15" t="n">
-        <v>240.93</v>
+        <v>237.38</v>
       </c>
       <c r="E177" s="20" t="n">
-        <v>0.234</v>
+        <v>0.2158</v>
       </c>
       <c r="F177" s="20" t="n">
-        <v>0.0416</v>
+        <v>0.0262</v>
       </c>
       <c r="G177" s="17" t="n">
         <v>46261</v>
@@ -14929,13 +14929,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>271.27</v>
+        <v>273.42</v>
       </c>
       <c r="E178" s="6" t="n">
-        <v>-0.2208</v>
+        <v>-0.2146</v>
       </c>
       <c r="F178" s="6" t="n">
-        <v>-0.1023</v>
+        <v>-0.09519999999999999</v>
       </c>
       <c r="G178" s="7" t="n">
         <v>46237</v>
@@ -14990,13 +14990,13 @@
         </is>
       </c>
       <c r="D179" s="15" t="n">
-        <v>263.99</v>
+        <v>260.23</v>
       </c>
       <c r="E179" s="16" t="n">
-        <v>-0.421</v>
+        <v>-0.4293</v>
       </c>
       <c r="F179" s="16" t="n">
-        <v>-0.23</v>
+        <v>-0.241</v>
       </c>
       <c r="G179" s="17" t="n">
         <v>46238</v>
@@ -15051,13 +15051,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>43.98</v>
+        <v>44.52</v>
       </c>
       <c r="E180" s="6" t="n">
-        <v>-0.3374</v>
+        <v>-0.3292</v>
       </c>
       <c r="F180" s="6" t="n">
-        <v>-0.08130000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G180" s="7" t="n">
         <v>46233</v>
@@ -15112,13 +15112,13 @@
         </is>
       </c>
       <c r="D181" s="15" t="n">
-        <v>475.25</v>
+        <v>476.46</v>
       </c>
       <c r="E181" s="16" t="n">
-        <v>-0.3158</v>
+        <v>-0.3141</v>
       </c>
       <c r="F181" s="20" t="n">
-        <v>0.05599999999999999</v>
+        <v>0.0587</v>
       </c>
       <c r="G181" s="17" t="n">
         <v>46247</v>
@@ -15147,7 +15147,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="20" t="n">
-        <v>0.5570752235665439</v>
+        <v>0.5531209335516099</v>
       </c>
       <c r="N181" s="14" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="20" t="n">
-        <v>0.4729089952656497</v>
+        <v>0.4691684506569282</v>
       </c>
       <c r="Q181" s="21" t="inlineStr">
         <is>
@@ -15199,13 +15199,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>62.38</v>
+        <v>60.32</v>
       </c>
       <c r="E182" s="6" t="n">
-        <v>-0.2666</v>
+        <v>-0.2908</v>
       </c>
       <c r="F182" s="6" t="n">
-        <v>-0.217</v>
+        <v>-0.2428</v>
       </c>
       <c r="G182" s="7" t="n">
         <v>46268</v>
@@ -15264,13 +15264,13 @@
         </is>
       </c>
       <c r="D183" s="15" t="n">
-        <v>460.07</v>
+        <v>454.62</v>
       </c>
       <c r="E183" s="16" t="n">
-        <v>-0.1472</v>
+        <v>-0.1573</v>
       </c>
       <c r="F183" s="16" t="n">
-        <v>-0.1086</v>
+        <v>-0.1191</v>
       </c>
       <c r="G183" s="17" t="n">
         <v>46238</v>
@@ -15299,7 +15299,7 @@
         <v>615</v>
       </c>
       <c r="M183" s="20" t="n">
-        <v>0.3367531027887061</v>
+        <v>0.352778144384321</v>
       </c>
       <c r="N183" s="14" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="20" t="n">
-        <v>0.2585041406742453</v>
+        <v>0.2735911310545071</v>
       </c>
       <c r="Q183" s="21" t="inlineStr">
         <is>
@@ -15351,13 +15351,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>45.67</v>
+        <v>45.69</v>
       </c>
       <c r="E184" s="6" t="n">
-        <v>-0.4454</v>
+        <v>-0.4451</v>
       </c>
       <c r="F184" s="6" t="n">
-        <v>-0.3435</v>
+        <v>-0.3432</v>
       </c>
       <c r="G184" s="7" t="n"/>
       <c r="H184" s="12" t="inlineStr">
@@ -15402,13 +15402,13 @@
         </is>
       </c>
       <c r="D185" s="15" t="n">
-        <v>166.93</v>
+        <v>169.71</v>
       </c>
       <c r="E185" s="20" t="n">
-        <v>0.0172</v>
+        <v>0.0342</v>
       </c>
       <c r="F185" s="20" t="n">
-        <v>0.04679999999999999</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="G185" s="17" t="n">
         <v>46238</v>
@@ -15437,7 +15437,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="20" t="n">
-        <v>0.1981069909542922</v>
+        <v>0.1784809380708267</v>
       </c>
       <c r="N185" s="14" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="20" t="n">
-        <v>0.1981069909542922</v>
+        <v>0.1784809380708267</v>
       </c>
       <c r="Q185" s="21" t="inlineStr">
         <is>
@@ -15493,13 +15493,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>143.65</v>
+        <v>143.85</v>
       </c>
       <c r="E186" s="6" t="n">
-        <v>-0.1369</v>
+        <v>-0.1356</v>
       </c>
       <c r="F186" s="6" t="n">
-        <v>-0.0344</v>
+        <v>-0.033</v>
       </c>
       <c r="G186" s="7" t="n">
         <v>46232</v>
@@ -15531,7 +15531,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="5" t="n">
-        <v>0.2530455969369996</v>
+        <v>0.251303441084463</v>
       </c>
       <c r="Q186" s="10" t="inlineStr">
         <is>
@@ -15584,13 +15584,13 @@
         </is>
       </c>
       <c r="D187" s="15" t="n">
-        <v>26.81</v>
+        <v>26.62</v>
       </c>
       <c r="E187" s="16" t="n">
-        <v>-0.2902</v>
+        <v>-0.2952</v>
       </c>
       <c r="F187" s="16" t="n">
-        <v>-0.433</v>
+        <v>-0.4370000000000001</v>
       </c>
       <c r="G187" s="17" t="n"/>
       <c r="H187" s="23" t="inlineStr">
@@ -15635,13 +15635,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>246.03</v>
+        <v>244.74</v>
       </c>
       <c r="E188" s="6" t="n">
-        <v>-0.2839</v>
+        <v>-0.2877</v>
       </c>
       <c r="F188" s="6" t="n">
-        <v>-0.3036</v>
+        <v>-0.3073</v>
       </c>
       <c r="G188" s="7" t="n">
         <v>46232</v>
@@ -15696,13 +15696,13 @@
         </is>
       </c>
       <c r="D189" s="15" t="n">
-        <v>1579.03</v>
+        <v>1582.95</v>
       </c>
       <c r="E189" s="16" t="n">
-        <v>-0.1615</v>
+        <v>-0.1594</v>
       </c>
       <c r="F189" s="16" t="n">
-        <v>-0.0209</v>
+        <v>-0.0185</v>
       </c>
       <c r="G189" s="17" t="n">
         <v>46309</v>
@@ -15775,13 +15775,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>33.73</v>
+        <v>33.93</v>
       </c>
       <c r="E190" s="6" t="n">
-        <v>-0.1994</v>
+        <v>-0.1946</v>
       </c>
       <c r="F190" s="6" t="n">
-        <v>-0.1205</v>
+        <v>-0.1153</v>
       </c>
       <c r="G190" s="7" t="n">
         <v>46233</v>
@@ -15836,13 +15836,13 @@
         </is>
       </c>
       <c r="D191" s="15" t="n">
-        <v>381.36</v>
+        <v>380.91</v>
       </c>
       <c r="E191" s="20" t="n">
-        <v>0.0239</v>
+        <v>0.0227</v>
       </c>
       <c r="F191" s="16" t="n">
-        <v>-0.1464</v>
+        <v>-0.1474</v>
       </c>
       <c r="G191" s="17" t="n">
         <v>46268</v>
@@ -15871,7 +15871,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="20" t="n">
-        <v>0.4290958674218586</v>
+        <v>0.4307841747394397</v>
       </c>
       <c r="N191" s="14" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="20" t="n">
-        <v>0.5261170547514159</v>
+        <v>0.5279199810978971</v>
       </c>
       <c r="Q191" s="21" t="inlineStr">
         <is>
@@ -15935,13 +15935,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>138.72</v>
+        <v>140.06</v>
       </c>
       <c r="E192" s="6" t="n">
-        <v>-0.1182</v>
+        <v>-0.1097</v>
       </c>
       <c r="F192" s="6" t="n">
-        <v>-0.1919</v>
+        <v>-0.1841</v>
       </c>
       <c r="G192" s="7" t="n">
         <v>46244</v>
@@ -15996,13 +15996,13 @@
         </is>
       </c>
       <c r="D193" s="15" t="n">
-        <v>345.81</v>
+        <v>344.72</v>
       </c>
       <c r="E193" s="16" t="n">
-        <v>-0.0722</v>
+        <v>-0.0751</v>
       </c>
       <c r="F193" s="16" t="n">
-        <v>-0.07769999999999999</v>
+        <v>-0.0806</v>
       </c>
       <c r="G193" s="17" t="n"/>
       <c r="H193" s="23" t="inlineStr">
@@ -16021,7 +16021,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="20" t="n">
-        <v>0.2289985830369278</v>
+        <v>0.2328846600139242</v>
       </c>
       <c r="N193" s="14" t="inlineStr"/>
       <c r="O193" s="19" t="n"/>
@@ -16065,13 +16065,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>138.35</v>
+        <v>137.64</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>0.0745</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="F194" s="5" t="n">
-        <v>0.0244</v>
+        <v>0.0192</v>
       </c>
       <c r="G194" s="7" t="n">
         <v>46233</v>
@@ -16126,13 +16126,13 @@
         </is>
       </c>
       <c r="D195" s="15" t="n">
-        <v>341.1</v>
+        <v>350.51</v>
       </c>
       <c r="E195" s="16" t="n">
-        <v>-0.2878</v>
+        <v>-0.2681</v>
       </c>
       <c r="F195" s="16" t="n">
-        <v>-0.4121</v>
+        <v>-0.3959</v>
       </c>
       <c r="G195" s="17" t="n">
         <v>46268</v>
@@ -16187,13 +16187,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>14.82</v>
+        <v>14.85</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>0.0451</v>
+        <v>0.0472</v>
       </c>
       <c r="F196" s="5" t="n">
-        <v>0.0061</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="G196" s="7" t="n">
         <v>46247</v>
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="D197" s="15" t="n">
-        <v>335.05</v>
-      </c>
-      <c r="E197" s="16" t="n">
-        <v>-0.0239</v>
+        <v>350.2</v>
+      </c>
+      <c r="E197" s="20" t="n">
+        <v>0.0202</v>
       </c>
       <c r="F197" s="16" t="n">
-        <v>-0.1306</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="G197" s="17" t="n"/>
       <c r="H197" s="23" t="inlineStr">
@@ -16299,13 +16299,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>239.28</v>
+        <v>243.33</v>
       </c>
       <c r="E198" s="6" t="n">
-        <v>-0.3884</v>
+        <v>-0.3779999999999999</v>
       </c>
       <c r="F198" s="6" t="n">
-        <v>-0.338</v>
+        <v>-0.3268</v>
       </c>
       <c r="G198" s="7" t="n">
         <v>46246</v>
@@ -16360,13 +16360,13 @@
         </is>
       </c>
       <c r="D199" s="15" t="n">
-        <v>42.28</v>
+        <v>42.47</v>
       </c>
       <c r="E199" s="16" t="n">
-        <v>-0.3794</v>
+        <v>-0.3765</v>
       </c>
       <c r="F199" s="16" t="n">
-        <v>-0.1986</v>
+        <v>-0.1949</v>
       </c>
       <c r="G199" s="17" t="n">
         <v>46233</v>
@@ -16421,13 +16421,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>20.3</v>
+        <v>20.75</v>
       </c>
       <c r="E200" s="6" t="n">
-        <v>-0.2174</v>
+        <v>-0.2003</v>
       </c>
       <c r="F200" s="6" t="n">
-        <v>-0.2439</v>
+        <v>-0.2274</v>
       </c>
       <c r="G200" s="7" t="n">
         <v>46248</v>
@@ -16482,13 +16482,13 @@
         </is>
       </c>
       <c r="D201" s="15" t="n">
-        <v>195.85</v>
+        <v>192.28</v>
       </c>
       <c r="E201" s="16" t="n">
-        <v>-0.2028</v>
+        <v>-0.2174</v>
       </c>
       <c r="F201" s="16" t="n">
-        <v>-0.1702</v>
+        <v>-0.1854</v>
       </c>
       <c r="G201" s="17" t="n">
         <v>46267</v>
@@ -16543,13 +16543,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>182.77</v>
+        <v>181.5</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>0.1573</v>
+        <v>0.1492</v>
       </c>
       <c r="F202" s="6" t="n">
-        <v>-0.0436</v>
+        <v>-0.05019999999999999</v>
       </c>
       <c r="G202" s="7" t="n">
         <v>46267</v>
@@ -16578,7 +16578,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="5" t="n">
-        <v>0.09427148875636039</v>
+        <v>0.1019283746556474</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="5" t="n">
-        <v>0.3678393609454505</v>
+        <v>0.3774104683195592</v>
       </c>
       <c r="Q202" s="10" t="inlineStr">
         <is>
@@ -16634,13 +16634,13 @@
         </is>
       </c>
       <c r="D203" s="15" t="n">
-        <v>181.42</v>
+        <v>181.8</v>
       </c>
       <c r="E203" s="16" t="n">
-        <v>-0.0232</v>
+        <v>-0.0211</v>
       </c>
       <c r="F203" s="16" t="n">
-        <v>-0.0073</v>
+        <v>-0.0052</v>
       </c>
       <c r="G203" s="17" t="n">
         <v>46260</v>
@@ -16669,7 +16669,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="16" t="n">
-        <v>-0.0009370521441957199</v>
+        <v>-0.003025302530253088</v>
       </c>
       <c r="N203" s="14" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="16" t="n">
-        <v>-0.02160732003086753</v>
+        <v>-0.02365236523652371</v>
       </c>
       <c r="Q203" s="21" t="inlineStr">
         <is>
@@ -16721,13 +16721,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>66.88</v>
+        <v>67.3</v>
       </c>
       <c r="E204" s="6" t="n">
-        <v>-0.2998</v>
+        <v>-0.2954</v>
       </c>
       <c r="F204" s="6" t="n">
-        <v>-0.3894</v>
+        <v>-0.3856</v>
       </c>
       <c r="G204" s="7" t="n">
         <v>46245</v>
@@ -16782,13 +16782,13 @@
         </is>
       </c>
       <c r="D205" s="15" t="n">
-        <v>116.45</v>
+        <v>115.58</v>
       </c>
       <c r="E205" s="16" t="n">
-        <v>-0.0106</v>
+        <v>-0.018</v>
       </c>
       <c r="F205" s="16" t="n">
-        <v>-0.033</v>
+        <v>-0.04019999999999999</v>
       </c>
       <c r="G205" s="17" t="n">
         <v>46246</v>
@@ -16817,7 +16817,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="20" t="n">
-        <v>0.1163589523400601</v>
+        <v>0.124762069562208</v>
       </c>
       <c r="N205" s="14" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="20" t="n">
-        <v>0.2881064834693001</v>
+        <v>0.2978023879563939</v>
       </c>
       <c r="Q205" s="21" t="inlineStr">
         <is>
@@ -16885,13 +16885,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>251.87</v>
+        <v>250.88</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="F206" s="5" t="n">
-        <v>0.0183</v>
+        <v>0.0143</v>
       </c>
       <c r="G206" s="7" t="n">
         <v>46240</v>
@@ -16946,13 +16946,13 @@
         </is>
       </c>
       <c r="D207" s="15" t="n">
-        <v>383.95</v>
+        <v>392.1</v>
       </c>
       <c r="E207" s="16" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.05429999999999999</v>
       </c>
       <c r="F207" s="16" t="n">
-        <v>-0.08779999999999999</v>
+        <v>-0.0684</v>
       </c>
       <c r="G207" s="17" t="n">
         <v>46261</v>
@@ -17007,13 +17007,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>55.65</v>
+        <v>55.97</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>0.2356</v>
+        <v>0.2427</v>
       </c>
       <c r="F208" s="5" t="n">
-        <v>0.0596</v>
+        <v>0.06570000000000001</v>
       </c>
       <c r="G208" s="7" t="n">
         <v>46268</v>
@@ -17068,13 +17068,13 @@
         </is>
       </c>
       <c r="D209" s="15" t="n">
-        <v>44.35</v>
-      </c>
-      <c r="E209" s="20" t="n">
-        <v>0.0026</v>
+        <v>43.9</v>
+      </c>
+      <c r="E209" s="16" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F209" s="20" t="n">
-        <v>0.0414</v>
+        <v>0.0308</v>
       </c>
       <c r="G209" s="17" t="n">
         <v>46239</v>
@@ -17129,13 +17129,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>443.32</v>
+        <v>449.72</v>
       </c>
       <c r="E210" s="6" t="n">
-        <v>-0.1607</v>
+        <v>-0.1486</v>
       </c>
       <c r="F210" s="6" t="n">
-        <v>-0.3223</v>
+        <v>-0.3125</v>
       </c>
       <c r="G210" s="7" t="n">
         <v>46251</v>
@@ -17190,13 +17190,13 @@
         </is>
       </c>
       <c r="D211" s="15" t="n">
-        <v>88.55</v>
+        <v>88.23</v>
       </c>
       <c r="E211" s="16" t="n">
-        <v>-0.3858</v>
+        <v>-0.388</v>
       </c>
       <c r="F211" s="16" t="n">
-        <v>-0.2893</v>
+        <v>-0.2918</v>
       </c>
       <c r="G211" s="17" t="n">
         <v>46232</v>
@@ -17251,13 +17251,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>151.94</v>
+        <v>149.98</v>
       </c>
       <c r="E212" s="6" t="n">
-        <v>-0.0224</v>
+        <v>-0.035</v>
       </c>
       <c r="F212" s="5" t="n">
-        <v>0.1013</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G212" s="7" t="n">
         <v>46232</v>
@@ -17312,13 +17312,13 @@
         </is>
       </c>
       <c r="D213" s="15" t="n">
-        <v>49.36</v>
+        <v>49.02</v>
       </c>
       <c r="E213" s="16" t="n">
-        <v>-0.3906</v>
+        <v>-0.3948</v>
       </c>
       <c r="F213" s="16" t="n">
-        <v>-0.3828</v>
+        <v>-0.387</v>
       </c>
       <c r="G213" s="17" t="n">
         <v>46239</v>
@@ -17373,13 +17373,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>121.36</v>
+        <v>126.01</v>
       </c>
       <c r="E214" s="6" t="n">
-        <v>-0.5254</v>
+        <v>-0.5072</v>
       </c>
       <c r="F214" s="6" t="n">
-        <v>-0.3301</v>
+        <v>-0.3044</v>
       </c>
       <c r="G214" s="7" t="n">
         <v>46231</v>
@@ -17434,13 +17434,13 @@
         </is>
       </c>
       <c r="D215" s="15" t="n">
-        <v>34.17</v>
+        <v>32.97</v>
       </c>
       <c r="E215" s="20" t="n">
-        <v>0.1446</v>
+        <v>0.1044</v>
       </c>
       <c r="F215" s="20" t="n">
-        <v>0.1003</v>
+        <v>0.0617</v>
       </c>
       <c r="G215" s="17" t="n">
         <v>46267</v>
@@ -17495,13 +17495,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>158.09</v>
+        <v>159.4</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>0.3079</v>
+        <v>0.3188</v>
       </c>
       <c r="F216" s="5" t="n">
-        <v>0.0355</v>
+        <v>0.0441</v>
       </c>
       <c r="G216" s="7" t="n">
         <v>46268</v>
@@ -17530,7 +17530,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="5" t="n">
-        <v>0.2018470491492188</v>
+        <v>0.191969887076537</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="9" t="n"/>
@@ -17574,13 +17574,13 @@
         </is>
       </c>
       <c r="D217" s="15" t="n">
-        <v>44.75</v>
+        <v>45.59</v>
       </c>
       <c r="E217" s="20" t="n">
-        <v>0.0076</v>
+        <v>0.0266</v>
       </c>
       <c r="F217" s="20" t="n">
-        <v>0.0396</v>
+        <v>0.0592</v>
       </c>
       <c r="G217" s="17" t="n">
         <v>46267</v>
@@ -17609,7 +17609,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="20" t="n">
-        <v>0.4972067039106145</v>
+        <v>0.4696205308181617</v>
       </c>
       <c r="N217" s="14" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="20" t="n">
-        <v>0.5642458100558659</v>
+        <v>0.5354244351831541</v>
       </c>
       <c r="Q217" s="21" t="inlineStr">
         <is>
@@ -17661,13 +17661,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>237.12</v>
+        <v>238.05</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>0.2854</v>
+        <v>0.2905</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>0.0747</v>
+        <v>0.079</v>
       </c>
       <c r="G218" s="7" t="n">
         <v>46239</v>
@@ -17722,13 +17722,13 @@
         </is>
       </c>
       <c r="D219" s="15" t="n">
-        <v>226.03</v>
+        <v>227.55</v>
       </c>
       <c r="E219" s="16" t="n">
-        <v>-0.1869</v>
+        <v>-0.1815</v>
       </c>
       <c r="F219" s="16" t="n">
-        <v>-0.241</v>
+        <v>-0.2359</v>
       </c>
       <c r="G219" s="17" t="n">
         <v>46316</v>
@@ -17764,7 +17764,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="20" t="n">
-        <v>0.1060478697518029</v>
+        <v>0.09865963524500104</v>
       </c>
       <c r="Q219" s="21" t="inlineStr">
         <is>
@@ -17801,13 +17801,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>9.470000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="E220" s="6" t="n">
-        <v>-0.3148</v>
+        <v>-0.3082</v>
       </c>
       <c r="F220" s="6" t="n">
-        <v>-0.4162</v>
+        <v>-0.4106</v>
       </c>
       <c r="G220" s="7" t="n">
         <v>46247</v>
@@ -17862,13 +17862,13 @@
         </is>
       </c>
       <c r="D221" s="15" t="n">
-        <v>86.73999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="E221" s="16" t="n">
-        <v>-0.3415</v>
+        <v>-0.3448</v>
       </c>
       <c r="F221" s="16" t="n">
-        <v>-0.2437</v>
+        <v>-0.2475</v>
       </c>
       <c r="G221" s="17" t="n">
         <v>46317</v>
@@ -17923,13 +17923,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>315.3</v>
+        <v>312.99</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>0.1836</v>
+        <v>0.1749</v>
       </c>
       <c r="F222" s="6" t="n">
-        <v>-0.049</v>
+        <v>-0.0559</v>
       </c>
       <c r="G222" s="7" t="n">
         <v>46254</v>
@@ -17984,13 +17984,13 @@
         </is>
       </c>
       <c r="D223" s="15" t="n">
-        <v>33.77</v>
+        <v>33.88</v>
       </c>
       <c r="E223" s="16" t="n">
-        <v>-0.3732</v>
+        <v>-0.3712</v>
       </c>
       <c r="F223" s="16" t="n">
-        <v>-0.5314</v>
+        <v>-0.5299</v>
       </c>
       <c r="G223" s="17" t="n">
         <v>46239</v>
@@ -18045,13 +18045,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>34.11</v>
+        <v>33.93</v>
       </c>
       <c r="E224" s="6" t="n">
-        <v>-0.257</v>
+        <v>-0.2609</v>
       </c>
       <c r="F224" s="6" t="n">
-        <v>-0.4632</v>
+        <v>-0.466</v>
       </c>
       <c r="G224" s="7" t="n">
         <v>46261</v>
@@ -18106,13 +18106,13 @@
         </is>
       </c>
       <c r="D225" s="15" t="n">
-        <v>299.73</v>
+        <v>302.95</v>
       </c>
       <c r="E225" s="16" t="n">
-        <v>-0.1977</v>
+        <v>-0.1891</v>
       </c>
       <c r="F225" s="16" t="n">
-        <v>-0.1778</v>
+        <v>-0.169</v>
       </c>
       <c r="G225" s="17" t="n">
         <v>46289</v>
@@ -18171,13 +18171,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>303.39</v>
+        <v>305.17</v>
       </c>
       <c r="E226" s="6" t="n">
-        <v>-0.108</v>
+        <v>-0.1028</v>
       </c>
       <c r="F226" s="6" t="n">
-        <v>-0.1033</v>
+        <v>-0.098</v>
       </c>
       <c r="G226" s="7" t="n">
         <v>46252</v>
@@ -18206,7 +18206,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>0.2854741421932167</v>
+        <v>0.2779762099813218</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="9" t="n"/>
@@ -18262,13 +18262,13 @@
         </is>
       </c>
       <c r="D227" s="15" t="n">
-        <v>191.13</v>
+        <v>190.8</v>
       </c>
       <c r="E227" s="16" t="n">
-        <v>-0.3134</v>
+        <v>-0.3146</v>
       </c>
       <c r="F227" s="16" t="n">
-        <v>-0.0054</v>
+        <v>-0.0071</v>
       </c>
       <c r="G227" s="17" t="n">
         <v>46231</v>
@@ -18297,7 +18297,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="20" t="n">
-        <v>0.5957725108564852</v>
+        <v>0.5985324947589098</v>
       </c>
       <c r="N227" s="14" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="16" t="n">
-        <v>-0.03207241144770573</v>
+        <v>-0.0303983228511531</v>
       </c>
       <c r="Q227" s="21" t="inlineStr">
         <is>
@@ -18349,13 +18349,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>89.52</v>
+        <v>90.93000000000001</v>
       </c>
       <c r="E228" s="6" t="n">
-        <v>-0.3067</v>
+        <v>-0.2958</v>
       </c>
       <c r="F228" s="6" t="n">
-        <v>-0.1214</v>
+        <v>-0.1076</v>
       </c>
       <c r="G228" s="7" t="n">
         <v>46239</v>
@@ -18410,13 +18410,13 @@
         </is>
       </c>
       <c r="D229" s="15" t="n">
-        <v>644.17</v>
+        <v>651.9299999999999</v>
       </c>
       <c r="E229" s="16" t="n">
-        <v>-0.2434</v>
+        <v>-0.2343</v>
       </c>
       <c r="F229" s="16" t="n">
-        <v>-0.2465</v>
+        <v>-0.2375</v>
       </c>
       <c r="G229" s="17" t="n">
         <v>46245</v>
@@ -18471,13 +18471,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>108.71</v>
+        <v>111.66</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>0.1023</v>
+        <v>0.1321</v>
       </c>
       <c r="F230" s="6" t="n">
-        <v>-0.1079</v>
+        <v>-0.08380000000000001</v>
       </c>
       <c r="G230" s="7" t="n">
         <v>46231</v>
@@ -18532,13 +18532,13 @@
         </is>
       </c>
       <c r="D231" s="15" t="n">
-        <v>267.92</v>
+        <v>269.61</v>
       </c>
       <c r="E231" s="16" t="n">
-        <v>-0.348</v>
+        <v>-0.3439</v>
       </c>
       <c r="F231" s="16" t="n">
-        <v>-0.158</v>
+        <v>-0.1526</v>
       </c>
       <c r="G231" s="17" t="n">
         <v>46232</v>
@@ -18567,7 +18567,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="20" t="n">
-        <v>0.6796058524932814</v>
+        <v>0.6690775564704572</v>
       </c>
       <c r="N231" s="14" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="20" t="n">
-        <v>0.3250223947446998</v>
+        <v>0.3167167389933607</v>
       </c>
       <c r="Q231" s="21" t="inlineStr">
         <is>
@@ -18623,13 +18623,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>76.70999999999999</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="E232" s="6" t="n">
-        <v>-0.1387</v>
+        <v>-0.1499</v>
       </c>
       <c r="F232" s="6" t="n">
-        <v>-0.1896</v>
+        <v>-0.2001</v>
       </c>
       <c r="G232" s="7" t="n">
         <v>46240</v>
@@ -18684,13 +18684,13 @@
         </is>
       </c>
       <c r="D233" s="15" t="n">
-        <v>312.3</v>
+        <v>310.62</v>
       </c>
       <c r="E233" s="16" t="n">
-        <v>-0.0765</v>
+        <v>-0.0815</v>
       </c>
       <c r="F233" s="16" t="n">
-        <v>-0.0693</v>
+        <v>-0.07429999999999999</v>
       </c>
       <c r="G233" s="17" t="n">
         <v>46259</v>
@@ -18745,13 +18745,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>284.27</v>
+        <v>285.31</v>
       </c>
       <c r="E234" s="6" t="n">
-        <v>-0.3167</v>
+        <v>-0.3142</v>
       </c>
       <c r="F234" s="6" t="n">
-        <v>-0.1233</v>
+        <v>-0.1201</v>
       </c>
       <c r="G234" s="7" t="n">
         <v>46239</v>
@@ -18806,13 +18806,13 @@
         </is>
       </c>
       <c r="D235" s="15" t="n">
-        <v>1297.68</v>
+        <v>1282.01</v>
       </c>
       <c r="E235" s="16" t="n">
-        <v>-0.0115</v>
+        <v>-0.0234</v>
       </c>
       <c r="F235" s="16" t="n">
-        <v>-0.1715</v>
+        <v>-0.1815</v>
       </c>
       <c r="G235" s="17" t="n">
         <v>46233</v>
@@ -18867,13 +18867,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>176.66</v>
+        <v>174.47</v>
       </c>
       <c r="E236" s="6" t="n">
-        <v>-0.364</v>
+        <v>-0.3718</v>
       </c>
       <c r="F236" s="6" t="n">
-        <v>-0.1382</v>
+        <v>-0.1489</v>
       </c>
       <c r="G236" s="7" t="n">
         <v>46261</v>
@@ -18902,7 +18902,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="5" t="n">
-        <v>0.3585418317672365</v>
+        <v>0.3755946581074111</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="5" t="n">
-        <v>0.4208083323899015</v>
+        <v>0.4386427466040007</v>
       </c>
       <c r="Q236" s="10" t="inlineStr">
         <is>
@@ -18954,13 +18954,13 @@
         </is>
       </c>
       <c r="D237" s="15" t="n">
-        <v>398.39</v>
+        <v>393.35</v>
       </c>
       <c r="E237" s="20" t="n">
-        <v>0.0809</v>
+        <v>0.0672</v>
       </c>
       <c r="F237" s="16" t="n">
-        <v>-0.1152</v>
+        <v>-0.1264</v>
       </c>
       <c r="G237" s="17" t="n">
         <v>46232</v>
@@ -18989,7 +18989,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="20" t="n">
-        <v>0.5688144782750572</v>
+        <v>0.5889157239100037</v>
       </c>
       <c r="N237" s="14" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="20" t="n">
-        <v>0.317804161751048</v>
+        <v>0.3346892080844031</v>
       </c>
       <c r="Q237" s="21" t="inlineStr">
         <is>
@@ -19053,13 +19053,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>439.9</v>
+        <v>440.31</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0672</v>
       </c>
       <c r="F238" s="5" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.09179999999999999</v>
       </c>
       <c r="G238" s="7" t="n">
         <v>46239</v>
@@ -19091,7 +19091,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="5" t="n">
-        <v>0.1934530575130712</v>
+        <v>0.1923417592150984</v>
       </c>
       <c r="Q238" s="10" t="inlineStr">
         <is>
@@ -19140,13 +19140,13 @@
         </is>
       </c>
       <c r="D239" s="15" t="n">
-        <v>97.36</v>
+        <v>96.16</v>
       </c>
       <c r="E239" s="20" t="n">
-        <v>0.0505</v>
+        <v>0.0375</v>
       </c>
       <c r="F239" s="16" t="n">
-        <v>-0.388</v>
+        <v>-0.3956</v>
       </c>
       <c r="G239" s="17" t="n">
         <v>46233</v>
@@ -19201,13 +19201,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>250.8</v>
+        <v>249.23</v>
       </c>
       <c r="E240" s="6" t="n">
-        <v>-0.3269</v>
+        <v>-0.3311</v>
       </c>
       <c r="F240" s="6" t="n">
-        <v>-0.3122</v>
+        <v>-0.3165</v>
       </c>
       <c r="G240" s="7" t="n">
         <v>46240</v>
@@ -19262,13 +19262,13 @@
         </is>
       </c>
       <c r="D241" s="15" t="n">
-        <v>820.29</v>
+        <v>820.53</v>
       </c>
       <c r="E241" s="16" t="n">
-        <v>-0.2838</v>
+        <v>-0.2836</v>
       </c>
       <c r="F241" s="16" t="n">
-        <v>-0.1552</v>
+        <v>-0.155</v>
       </c>
       <c r="G241" s="17" t="n">
         <v>46294</v>
@@ -19297,7 +19297,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="20" t="n">
-        <v>0.8590986114666765</v>
+        <v>0.8585548365081107</v>
       </c>
       <c r="N241" s="14" t="inlineStr">
         <is>
@@ -19345,13 +19345,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>169.36</v>
+        <v>169.69</v>
       </c>
       <c r="E242" s="6" t="n">
-        <v>-0.3515</v>
+        <v>-0.3502</v>
       </c>
       <c r="F242" s="6" t="n">
-        <v>-0.2671</v>
+        <v>-0.2657</v>
       </c>
       <c r="G242" s="7" t="n">
         <v>46240</v>
@@ -19406,13 +19406,13 @@
         </is>
       </c>
       <c r="D243" s="15" t="n">
-        <v>266.17</v>
+        <v>264.1</v>
       </c>
       <c r="E243" s="20" t="n">
-        <v>0.0919</v>
+        <v>0.0834</v>
       </c>
       <c r="F243" s="20" t="n">
-        <v>0.1007</v>
+        <v>0.09210000000000002</v>
       </c>
       <c r="G243" s="17" t="n">
         <v>46240</v>
@@ -19467,13 +19467,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>110.54</v>
+        <v>110.62</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>0.1057</v>
+        <v>0.1065</v>
       </c>
       <c r="F244" s="6" t="n">
-        <v>-0.1112</v>
+        <v>-0.1106</v>
       </c>
       <c r="G244" s="7" t="n">
         <v>46323</v>
@@ -19502,7 +19502,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="5" t="n">
-        <v>0.4474398407816174</v>
+        <v>0.4463930573133248</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="5" t="n">
-        <v>0.3569748507327664</v>
+        <v>0.355993491231242</v>
       </c>
       <c r="Q244" s="10" t="inlineStr">
         <is>
@@ -19558,13 +19558,13 @@
         </is>
       </c>
       <c r="D245" s="15" t="n">
-        <v>58.75</v>
+        <v>59.05</v>
       </c>
       <c r="E245" s="20" t="n">
-        <v>0.1507</v>
+        <v>0.1565</v>
       </c>
       <c r="F245" s="20" t="n">
-        <v>0.1284</v>
+        <v>0.1341</v>
       </c>
       <c r="G245" s="17" t="n">
         <v>46260</v>
@@ -19619,13 +19619,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>197.26</v>
+        <v>197.01</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0105</v>
       </c>
       <c r="F246" s="6" t="n">
-        <v>-0.06570000000000001</v>
+        <v>-0.0669</v>
       </c>
       <c r="G246" s="7" t="n">
         <v>46260</v>
@@ -19654,7 +19654,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="5" t="n">
-        <v>0.5968772178850249</v>
+        <v>0.5989036089538603</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="5" t="n">
-        <v>1.093683463449255</v>
+        <v>1.096340287295061</v>
       </c>
       <c r="Q246" s="10" t="inlineStr">
         <is>
@@ -19714,13 +19714,13 @@
         </is>
       </c>
       <c r="D247" s="15" t="n">
-        <v>402.43</v>
+        <v>402.32</v>
       </c>
       <c r="E247" s="16" t="n">
-        <v>-0.2267</v>
+        <v>-0.2269</v>
       </c>
       <c r="F247" s="16" t="n">
-        <v>-0.1989</v>
+        <v>-0.1991</v>
       </c>
       <c r="G247" s="17" t="n">
         <v>46240</v>
@@ -19775,13 +19775,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>262.22</v>
+        <v>259.12</v>
       </c>
       <c r="E248" s="6" t="n">
-        <v>-0.058</v>
+        <v>-0.0692</v>
       </c>
       <c r="F248" s="6" t="n">
-        <v>-0.184</v>
+        <v>-0.1937</v>
       </c>
       <c r="G248" s="7" t="n">
         <v>46231</v>
@@ -19832,13 +19832,13 @@
         </is>
       </c>
       <c r="D249" s="15" t="n">
-        <v>15.18</v>
+        <v>14.86</v>
       </c>
       <c r="E249" s="16" t="n">
-        <v>-0.1153</v>
+        <v>-0.1339</v>
       </c>
       <c r="F249" s="16" t="n">
-        <v>-0.363</v>
+        <v>-0.3763</v>
       </c>
       <c r="G249" s="17" t="n"/>
       <c r="H249" s="23" t="inlineStr">
@@ -19883,13 +19883,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>135.92</v>
+        <v>136.21</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>0.0351</v>
+        <v>0.0373</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>0.1026</v>
+        <v>0.105</v>
       </c>
       <c r="G250" s="7" t="n">
         <v>46259</v>
@@ -19918,7 +19918,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="5" t="n">
-        <v>0.103590347263096</v>
+        <v>0.1012407312238455</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="6" t="n">
-        <v>-0.04355503237198343</v>
+        <v>-0.04559136627266726</v>
       </c>
       <c r="Q250" s="10" t="inlineStr">
         <is>
@@ -19970,13 +19970,13 @@
         </is>
       </c>
       <c r="D251" s="15" t="n">
-        <v>85.45999999999999</v>
+        <v>84.39</v>
       </c>
       <c r="E251" s="16" t="n">
-        <v>-0.0351</v>
+        <v>-0.0472</v>
       </c>
       <c r="F251" s="16" t="n">
-        <v>-0.2915</v>
+        <v>-0.3004</v>
       </c>
       <c r="G251" s="17" t="n">
         <v>46237</v>
@@ -20031,13 +20031,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>236.37</v>
+        <v>241.89</v>
       </c>
       <c r="E252" s="6" t="n">
-        <v>-0.3274</v>
+        <v>-0.3117</v>
       </c>
       <c r="F252" s="6" t="n">
-        <v>-0.08470000000000001</v>
+        <v>-0.0633</v>
       </c>
       <c r="G252" s="7" t="n">
         <v>46240</v>
@@ -20092,13 +20092,13 @@
         </is>
       </c>
       <c r="D253" s="15" t="n">
-        <v>120.61</v>
+        <v>119.96</v>
       </c>
       <c r="E253" s="16" t="n">
-        <v>-0.1837</v>
+        <v>-0.1881</v>
       </c>
       <c r="F253" s="16" t="n">
-        <v>-0.4658</v>
+        <v>-0.4686999999999999</v>
       </c>
       <c r="G253" s="17" t="n">
         <v>46273</v>
@@ -20127,7 +20127,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="20" t="n">
-        <v>1.321532211259431</v>
+        <v>1.334111370456819</v>
       </c>
       <c r="N253" s="14" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="20" t="n">
-        <v>1.031340684852002</v>
+        <v>1.042347449149717</v>
       </c>
       <c r="Q253" s="21" t="inlineStr">
         <is>
@@ -20179,13 +20179,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>320.19</v>
+        <v>319</v>
       </c>
       <c r="E254" s="6" t="n">
-        <v>-0.0356</v>
+        <v>-0.0392</v>
       </c>
       <c r="F254" s="5" t="n">
-        <v>0.1367</v>
+        <v>0.1325</v>
       </c>
       <c r="G254" s="7" t="n">
         <v>46251</v>
@@ -20214,7 +20214,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="5" t="n">
-        <v>0.31172116555795</v>
+        <v>0.3166144200626959</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="5" t="n">
-        <v>0.2961054373965458</v>
+        <v>0.3009404388714734</v>
       </c>
       <c r="Q254" s="10" t="inlineStr">
         <is>
@@ -20274,13 +20274,13 @@
         </is>
       </c>
       <c r="D255" s="15" t="n">
-        <v>11.94</v>
+        <v>12.19</v>
       </c>
       <c r="E255" s="20" t="n">
-        <v>0.1175</v>
+        <v>0.1414</v>
       </c>
       <c r="F255" s="20" t="n">
-        <v>0.0183</v>
+        <v>0.0401</v>
       </c>
       <c r="G255" s="17" t="n">
         <v>46268</v>
@@ -20335,13 +20335,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>29.81</v>
+        <v>29.53</v>
       </c>
       <c r="E256" s="6" t="n">
-        <v>-0.021</v>
+        <v>-0.0302</v>
       </c>
       <c r="F256" s="6" t="n">
-        <v>-0.1657</v>
+        <v>-0.1735</v>
       </c>
       <c r="G256" s="7" t="n">
         <v>46315</v>
@@ -20396,13 +20396,13 @@
         </is>
       </c>
       <c r="D257" s="15" t="n">
-        <v>132.99</v>
+        <v>133.03</v>
       </c>
       <c r="E257" s="16" t="n">
-        <v>-0.0023</v>
+        <v>-0.002</v>
       </c>
       <c r="F257" s="16" t="n">
-        <v>-0.1193</v>
+        <v>-0.119</v>
       </c>
       <c r="G257" s="17" t="n">
         <v>46232</v>
@@ -20457,13 +20457,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>123.89</v>
+        <v>123.53</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>0.0708</v>
+        <v>0.0677</v>
       </c>
       <c r="F258" s="6" t="n">
-        <v>-0.2086</v>
+        <v>-0.2109</v>
       </c>
       <c r="G258" s="7" t="n">
         <v>46237</v>
@@ -20518,13 +20518,13 @@
         </is>
       </c>
       <c r="D259" s="15" t="n">
-        <v>127.18</v>
+        <v>127.89</v>
       </c>
       <c r="E259" s="16" t="n">
-        <v>-0.1963</v>
+        <v>-0.1917</v>
       </c>
       <c r="F259" s="16" t="n">
-        <v>-0.1848</v>
+        <v>-0.1802</v>
       </c>
       <c r="G259" s="17" t="n">
         <v>46238</v>
@@ -20589,13 +20589,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>17.94</v>
+        <v>17.64</v>
       </c>
       <c r="E260" s="6" t="n">
-        <v>-0.247</v>
+        <v>-0.26</v>
       </c>
       <c r="F260" s="6" t="n">
-        <v>-0.4046</v>
+        <v>-0.4149</v>
       </c>
       <c r="G260" s="7" t="n">
         <v>46240</v>
@@ -20650,13 +20650,13 @@
         </is>
       </c>
       <c r="D261" s="15" t="n">
-        <v>165.18</v>
+        <v>162.88</v>
       </c>
       <c r="E261" s="16" t="n">
-        <v>-0.1247</v>
+        <v>-0.1369</v>
       </c>
       <c r="F261" s="16" t="n">
-        <v>-0.342</v>
+        <v>-0.3511</v>
       </c>
       <c r="G261" s="17" t="n">
         <v>46232</v>
@@ -20685,7 +20685,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="20" t="n">
-        <v>0.6043104492069257</v>
+        <v>0.6269646365422398</v>
       </c>
       <c r="N261" s="14" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>179</v>
       </c>
       <c r="P261" s="20" t="n">
-        <v>0.08366630342656492</v>
+        <v>0.09896856581532419</v>
       </c>
       <c r="Q261" s="21" t="inlineStr">
         <is>
@@ -20741,13 +20741,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>90.37</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="E262" s="6" t="n">
-        <v>-0.0339</v>
+        <v>-0.019</v>
       </c>
       <c r="F262" s="6" t="n">
-        <v>-0.1274</v>
+        <v>-0.1139</v>
       </c>
       <c r="G262" s="7" t="n">
         <v>46231</v>
@@ -20802,13 +20802,13 @@
         </is>
       </c>
       <c r="D263" s="15" t="n">
-        <v>7.74</v>
+        <v>7.72</v>
       </c>
       <c r="E263" s="16" t="n">
-        <v>-0.2196</v>
+        <v>-0.2218</v>
       </c>
       <c r="F263" s="16" t="n">
-        <v>-0.3527</v>
+        <v>-0.3545</v>
       </c>
       <c r="G263" s="17" t="n">
         <v>46247</v>
@@ -20863,13 +20863,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>73.05</v>
+        <v>71.45</v>
       </c>
       <c r="E264" s="6" t="n">
-        <v>-0.0453</v>
+        <v>-0.0663</v>
       </c>
       <c r="F264" s="6" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="G264" s="7" t="n">
         <v>46273</v>
@@ -20924,13 +20924,13 @@
         </is>
       </c>
       <c r="D265" s="15" t="n">
-        <v>14.72</v>
+        <v>14.52</v>
       </c>
       <c r="E265" s="16" t="n">
-        <v>-0.2431</v>
+        <v>-0.2531</v>
       </c>
       <c r="F265" s="16" t="n">
-        <v>-0.4238</v>
+        <v>-0.4315</v>
       </c>
       <c r="G265" s="17" t="n">
         <v>46240</v>
@@ -20985,13 +20985,13 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>394.44</v>
+        <v>390.92</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>0.1781</v>
+        <v>0.1676</v>
       </c>
       <c r="F266" s="5" t="n">
-        <v>0.2117</v>
+        <v>0.2009</v>
       </c>
       <c r="G266" s="7" t="n">
         <v>46317</v>
@@ -21060,13 +21060,13 @@
         </is>
       </c>
       <c r="D267" s="15" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="E267" s="16" t="n">
-        <v>-0.4221</v>
+        <v>-0.4205</v>
       </c>
       <c r="F267" s="16" t="n">
-        <v>-0.265</v>
+        <v>-0.2631</v>
       </c>
       <c r="G267" s="17" t="n">
         <v>46240</v>
@@ -21121,13 +21121,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>18.27</v>
+        <v>18.34</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>0.09230000000000001</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="F268" s="5" t="n">
-        <v>0.1042</v>
+        <v>0.1082</v>
       </c>
       <c r="G268" s="7" t="n">
         <v>46261</v>
@@ -21182,13 +21182,13 @@
         </is>
       </c>
       <c r="D269" s="15" t="n">
-        <v>15.77</v>
+        <v>15.78</v>
       </c>
       <c r="E269" s="20" t="n">
-        <v>0.1491</v>
+        <v>0.1501</v>
       </c>
       <c r="F269" s="16" t="n">
-        <v>-0.1628</v>
+        <v>-0.162</v>
       </c>
       <c r="G269" s="17" t="n">
         <v>46273</v>
@@ -21243,13 +21243,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>168.93</v>
+        <v>172.43</v>
       </c>
       <c r="E270" s="6" t="n">
-        <v>-0.2973</v>
+        <v>-0.2828</v>
       </c>
       <c r="F270" s="6" t="n">
-        <v>-0.3496</v>
+        <v>-0.3361</v>
       </c>
       <c r="G270" s="7" t="n"/>
       <c r="H270" s="12" t="inlineStr">
@@ -21294,13 +21294,13 @@
         </is>
       </c>
       <c r="D271" s="15" t="n">
-        <v>180.38</v>
+        <v>179.17</v>
       </c>
       <c r="E271" s="20" t="n">
-        <v>0.1645</v>
+        <v>0.1567</v>
       </c>
       <c r="F271" s="16" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0144</v>
       </c>
       <c r="G271" s="17" t="n">
         <v>46316</v>
@@ -21375,13 +21375,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>28.37</v>
+        <v>28.45</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0107</v>
       </c>
       <c r="F272" s="6" t="n">
-        <v>-0.3845</v>
+        <v>-0.3827</v>
       </c>
       <c r="G272" s="7" t="n">
         <v>46245</v>
@@ -21436,13 +21436,13 @@
         </is>
       </c>
       <c r="D273" s="15" t="n">
-        <v>272.57</v>
+        <v>270.36</v>
       </c>
       <c r="E273" s="20" t="n">
-        <v>0.08310000000000001</v>
+        <v>0.07429999999999999</v>
       </c>
       <c r="F273" s="20" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="G273" s="17" t="n">
         <v>46260</v>
@@ -21471,7 +21471,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="20" t="n">
-        <v>0.1740103459661738</v>
+        <v>0.1836070424619026</v>
       </c>
       <c r="N273" s="14" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="20" t="n">
-        <v>0.02725905272040213</v>
+        <v>0.03565616215416476</v>
       </c>
       <c r="Q273" s="21" t="inlineStr">
         <is>
@@ -21523,13 +21523,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>385.82</v>
+        <v>383.82</v>
       </c>
       <c r="E274" s="6" t="n">
-        <v>-0.1374</v>
+        <v>-0.1418</v>
       </c>
       <c r="F274" s="6" t="n">
-        <v>-0.1888</v>
+        <v>-0.193</v>
       </c>
       <c r="G274" s="7" t="n">
         <v>46260</v>
@@ -21558,7 +21558,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="5" t="n">
-        <v>0.3866569903063605</v>
+        <v>0.3938825491115627</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="9" t="n"/>
@@ -21602,13 +21602,13 @@
         </is>
       </c>
       <c r="D275" s="15" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="E275" s="20" t="n">
-        <v>0.0039</v>
+        <v>6.24</v>
+      </c>
+      <c r="E275" s="16" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F275" s="16" t="n">
-        <v>-0.2861</v>
+        <v>-0.3067</v>
       </c>
       <c r="G275" s="17" t="n">
         <v>46239</v>
@@ -21663,13 +21663,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>64.03</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="E276" s="6" t="n">
-        <v>-0.0544</v>
+        <v>-0.0447</v>
       </c>
       <c r="F276" s="6" t="n">
-        <v>-0.1776</v>
+        <v>-0.1692</v>
       </c>
       <c r="G276" s="7" t="n">
         <v>46231</v>
@@ -21724,13 +21724,13 @@
         </is>
       </c>
       <c r="D277" s="15" t="n">
-        <v>111.93</v>
+        <v>110.87</v>
       </c>
       <c r="E277" s="16" t="n">
-        <v>-0.0464</v>
+        <v>-0.0555</v>
       </c>
       <c r="F277" s="16" t="n">
-        <v>-0.1846</v>
+        <v>-0.1924</v>
       </c>
       <c r="G277" s="17" t="n">
         <v>46240</v>
@@ -21785,13 +21785,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>209.94</v>
+        <v>214.29</v>
       </c>
       <c r="E278" s="5" t="n">
-        <v>0.0587</v>
-      </c>
-      <c r="F278" s="6" t="n">
-        <v>-0.0163</v>
+        <v>0.0806</v>
+      </c>
+      <c r="F278" s="5" t="n">
+        <v>0.004099999999999999</v>
       </c>
       <c r="G278" s="7" t="n">
         <v>46330</v>
@@ -21846,13 +21846,13 @@
         </is>
       </c>
       <c r="D279" s="15" t="n">
-        <v>311.04</v>
+        <v>320.65</v>
       </c>
       <c r="E279" s="16" t="n">
-        <v>-0.3285</v>
+        <v>-0.3078</v>
       </c>
       <c r="F279" s="16" t="n">
-        <v>-0.169</v>
+        <v>-0.1434</v>
       </c>
       <c r="G279" s="17" t="n">
         <v>46231</v>
@@ -21907,13 +21907,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>57.91</v>
+        <v>58.38</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>0.1406</v>
+        <v>0.1499</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>0.0266</v>
+        <v>0.0349</v>
       </c>
       <c r="G280" s="7" t="n">
         <v>46239</v>
@@ -21968,13 +21968,13 @@
         </is>
       </c>
       <c r="D281" s="15" t="n">
-        <v>391.01</v>
+        <v>392.31</v>
       </c>
       <c r="E281" s="16" t="n">
-        <v>-0.1408</v>
+        <v>-0.138</v>
       </c>
       <c r="F281" s="16" t="n">
-        <v>-0.06559999999999999</v>
+        <v>-0.0625</v>
       </c>
       <c r="G281" s="17" t="n">
         <v>46310</v>
@@ -22051,13 +22051,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>108.54</v>
+        <v>108.69</v>
       </c>
       <c r="E282" s="6" t="n">
-        <v>-0.4189</v>
+        <v>-0.4181</v>
       </c>
       <c r="F282" s="6" t="n">
-        <v>-0.3752</v>
+        <v>-0.3743</v>
       </c>
       <c r="G282" s="7" t="n">
         <v>46239</v>
@@ -22112,13 +22112,13 @@
         </is>
       </c>
       <c r="D283" s="15" t="n">
-        <v>193.2</v>
+        <v>194.33</v>
       </c>
       <c r="E283" s="16" t="n">
-        <v>-0.028</v>
+        <v>-0.0223</v>
       </c>
       <c r="F283" s="20" t="n">
-        <v>0.0134</v>
+        <v>0.0194</v>
       </c>
       <c r="G283" s="17" t="n">
         <v>46240</v>
@@ -22173,13 +22173,13 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>278.54</v>
+        <v>277.07</v>
       </c>
       <c r="E284" s="6" t="n">
-        <v>-0.0243</v>
+        <v>-0.0295</v>
       </c>
       <c r="F284" s="6" t="n">
-        <v>-0.0888</v>
+        <v>-0.09359999999999999</v>
       </c>
       <c r="G284" s="7" t="n">
         <v>46315</v>
@@ -22208,7 +22208,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="5" t="n">
-        <v>0.07704458964601127</v>
+        <v>0.08275886959974016</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="5" t="n">
-        <v>0.1344869677604652</v>
+        <v>0.1405060093117263</v>
       </c>
       <c r="Q284" s="10" t="inlineStr">
         <is>
@@ -22276,13 +22276,13 @@
         </is>
       </c>
       <c r="D285" s="15" t="n">
-        <v>333.65</v>
+        <v>333.35</v>
       </c>
       <c r="E285" s="20" t="n">
-        <v>0.1476</v>
+        <v>0.1465</v>
       </c>
       <c r="F285" s="20" t="n">
-        <v>0.0655</v>
+        <v>0.0645</v>
       </c>
       <c r="G285" s="17" t="n">
         <v>46232</v>
@@ -22311,7 +22311,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="20" t="n">
-        <v>0.004046156151655995</v>
+        <v>0.004949752512374313</v>
       </c>
       <c r="N285" s="14" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="20" t="n">
-        <v>0.1239322643488687</v>
+        <v>0.1249437528123593</v>
       </c>
       <c r="Q285" s="21" t="inlineStr">
         <is>
@@ -22363,13 +22363,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>31.44</v>
+        <v>31.83</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>0.1107</v>
+        <v>0.1243</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>0.032</v>
+        <v>0.0446</v>
       </c>
       <c r="G286" s="7" t="n">
         <v>46240</v>
@@ -22424,13 +22424,13 @@
         </is>
       </c>
       <c r="D287" s="15" t="n">
-        <v>6.64</v>
+        <v>6.75</v>
       </c>
       <c r="E287" s="16" t="n">
-        <v>-0.1152</v>
+        <v>-0.1012</v>
       </c>
       <c r="F287" s="16" t="n">
-        <v>-0.3408</v>
+        <v>-0.3304</v>
       </c>
       <c r="G287" s="17" t="n">
         <v>46254</v>
@@ -22485,13 +22485,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>157.7</v>
+        <v>159.69</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>0.2761</v>
+        <v>0.2922</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.09230000000000001</v>
       </c>
       <c r="G288" s="7" t="n">
         <v>46254</v>
@@ -22546,13 +22546,13 @@
         </is>
       </c>
       <c r="D289" s="15" t="n">
-        <v>453.83</v>
+        <v>463.51</v>
       </c>
       <c r="E289" s="16" t="n">
-        <v>-0.3038</v>
+        <v>-0.289</v>
       </c>
       <c r="F289" s="16" t="n">
-        <v>-0.1457</v>
+        <v>-0.1274</v>
       </c>
       <c r="G289" s="17" t="n">
         <v>46239</v>
@@ -22581,7 +22581,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="20" t="n">
-        <v>0.6085318290990018</v>
+        <v>0.5749390520161377</v>
       </c>
       <c r="N289" s="14" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="20" t="n">
-        <v>0.266994248947844</v>
+        <v>0.2405341848072318</v>
       </c>
       <c r="Q289" s="21" t="inlineStr">
         <is>
@@ -22633,13 +22633,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>21.49</v>
+        <v>21.88</v>
       </c>
       <c r="E290" s="6" t="n">
-        <v>-0.5142</v>
+        <v>-0.5054</v>
       </c>
       <c r="F290" s="6" t="n">
-        <v>-0.6375</v>
+        <v>-0.6309</v>
       </c>
       <c r="G290" s="7" t="n">
         <v>46238</v>
@@ -22694,13 +22694,13 @@
         </is>
       </c>
       <c r="D291" s="15" t="n">
-        <v>91.03</v>
+        <v>91.48</v>
       </c>
       <c r="E291" s="20" t="n">
-        <v>0.0568</v>
+        <v>0.062</v>
       </c>
       <c r="F291" s="16" t="n">
-        <v>-0.1039</v>
+        <v>-0.09949999999999999</v>
       </c>
       <c r="G291" s="17" t="n">
         <v>46254</v>
@@ -22755,13 +22755,13 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>152.98</v>
+        <v>151.63</v>
       </c>
       <c r="E292" s="5" t="n">
-        <v>0.1118</v>
+        <v>0.102</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>0.09480000000000001</v>
+        <v>0.0852</v>
       </c>
       <c r="G292" s="7" t="n">
         <v>46266</v>
@@ -22816,13 +22816,13 @@
         </is>
       </c>
       <c r="D293" s="15" t="n">
-        <v>295.62</v>
+        <v>292.85</v>
       </c>
       <c r="E293" s="20" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.07919999999999999</v>
       </c>
       <c r="F293" s="20" t="n">
-        <v>0.061</v>
+        <v>0.05110000000000001</v>
       </c>
       <c r="G293" s="17" t="n">
         <v>46233</v>
@@ -22877,13 +22877,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>83.98999999999999</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0251</v>
       </c>
       <c r="F294" s="6" t="n">
-        <v>-0.0554</v>
+        <v>-0.0576</v>
       </c>
       <c r="G294" s="7" t="n">
         <v>46252</v>
@@ -22938,13 +22938,13 @@
         </is>
       </c>
       <c r="D295" s="15" t="n">
-        <v>141.51</v>
+        <v>140.77</v>
       </c>
       <c r="E295" s="20" t="n">
-        <v>0.0425</v>
+        <v>0.0371</v>
       </c>
       <c r="F295" s="16" t="n">
-        <v>-0.0258</v>
+        <v>-0.0309</v>
       </c>
       <c r="G295" s="17" t="n">
         <v>46238</v>
@@ -22973,7 +22973,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="20" t="n">
-        <v>0.1730619744187691</v>
+        <v>0.1792285288058534</v>
       </c>
       <c r="N295" s="14" t="inlineStr"/>
       <c r="O295" s="19" t="n"/>
@@ -23021,13 +23021,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>28.71</v>
+        <v>28.85</v>
       </c>
       <c r="E296" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.0333</v>
       </c>
       <c r="F296" s="6" t="n">
-        <v>-0.1493</v>
+        <v>-0.1452</v>
       </c>
       <c r="G296" s="7" t="n">
         <v>46317</v>
@@ -23082,13 +23082,13 @@
         </is>
       </c>
       <c r="D297" s="15" t="n">
-        <v>280.91</v>
+        <v>282.9</v>
       </c>
       <c r="E297" s="20" t="n">
-        <v>0.0083</v>
+        <v>0.0154</v>
       </c>
       <c r="F297" s="20" t="n">
-        <v>0.0973</v>
+        <v>0.1051</v>
       </c>
       <c r="G297" s="17" t="n">
         <v>46231</v>
@@ -23117,7 +23117,7 @@
         <v>275</v>
       </c>
       <c r="M297" s="16" t="n">
-        <v>-0.02103876686483224</v>
+        <v>-0.02792506185931417</v>
       </c>
       <c r="N297" s="14" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="20" t="n">
-        <v>0.1106760172297176</v>
+        <v>0.102863202545069</v>
       </c>
       <c r="Q297" s="21" t="inlineStr">
         <is>
@@ -23181,13 +23181,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>35.9</v>
+        <v>36.5</v>
       </c>
       <c r="E298" s="6" t="n">
-        <v>-0.2245</v>
+        <v>-0.2117</v>
       </c>
       <c r="F298" s="6" t="n">
-        <v>-0.1538</v>
+        <v>-0.1398</v>
       </c>
       <c r="G298" s="7" t="n"/>
       <c r="H298" s="12" t="inlineStr">
@@ -23236,13 +23236,13 @@
         </is>
       </c>
       <c r="D299" s="15" t="n">
-        <v>62.06</v>
+        <v>61.64</v>
       </c>
       <c r="E299" s="20" t="n">
-        <v>0.0071</v>
+        <v>0.0003</v>
       </c>
       <c r="F299" s="16" t="n">
-        <v>-0.0555</v>
+        <v>-0.0619</v>
       </c>
       <c r="G299" s="17" t="n">
         <v>46310</v>
@@ -23297,13 +23297,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>518.1799999999999</v>
+        <v>511.18</v>
       </c>
       <c r="E300" s="5" t="n">
-        <v>0.0139</v>
+        <v>0.0002</v>
       </c>
       <c r="F300" s="5" t="n">
-        <v>0.0412</v>
+        <v>0.0271</v>
       </c>
       <c r="G300" s="7" t="n">
         <v>46234</v>
@@ -23332,7 +23332,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="5" t="n">
-        <v>0.1000038596626656</v>
+        <v>0.115067099651786</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="5" t="n">
-        <v>0.01316144968929725</v>
+        <v>0.02703548652138189</v>
       </c>
       <c r="Q300" s="10" t="inlineStr">
         <is>
@@ -23396,13 +23396,13 @@
         </is>
       </c>
       <c r="D301" s="15" t="n">
-        <v>579.22</v>
-      </c>
-      <c r="E301" s="16" t="n">
-        <v>-0.0035</v>
-      </c>
-      <c r="F301" s="16" t="n">
-        <v>-0.0042</v>
+        <v>583.67</v>
+      </c>
+      <c r="E301" s="20" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="F301" s="20" t="n">
+        <v>0.0035</v>
       </c>
       <c r="G301" s="17" t="n">
         <v>46233</v>
@@ -23431,7 +23431,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="20" t="n">
-        <v>0.06349918856393075</v>
+        <v>0.05539088868710066</v>
       </c>
       <c r="N301" s="14" t="inlineStr"/>
       <c r="O301" s="19" t="n"/>
@@ -23475,13 +23475,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>264.5</v>
+        <v>265.62</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>0.1571</v>
+        <v>0.162</v>
       </c>
       <c r="F302" s="5" t="n">
-        <v>0.058</v>
+        <v>0.0625</v>
       </c>
       <c r="G302" s="7" t="n"/>
       <c r="H302" s="12" t="inlineStr">
@@ -23500,7 +23500,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="5" t="n">
-        <v>0.06994328922495274</v>
+        <v>0.06543181989308032</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="9" t="n"/>
@@ -23546,13 +23546,13 @@
         </is>
       </c>
       <c r="D303" s="15" t="n">
-        <v>254.93</v>
+        <v>253.24</v>
       </c>
       <c r="E303" s="20" t="n">
-        <v>0.0727</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="F303" s="20" t="n">
-        <v>0.1645</v>
+        <v>0.1568</v>
       </c>
       <c r="G303" s="17" t="n">
         <v>46321</v>
@@ -23581,7 +23581,7 @@
         <v>246</v>
       </c>
       <c r="M303" s="16" t="n">
-        <v>-0.03502922370846902</v>
+        <v>-0.02858948033486025</v>
       </c>
       <c r="N303" s="14" t="inlineStr"/>
       <c r="O303" s="19" t="n"/>
@@ -23629,13 +23629,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>122.08</v>
-      </c>
-      <c r="E304" s="5" t="n">
-        <v>0.0097</v>
+        <v>119.01</v>
+      </c>
+      <c r="E304" s="6" t="n">
+        <v>-0.0157</v>
       </c>
       <c r="F304" s="5" t="n">
-        <v>0.0805</v>
+        <v>0.0534</v>
       </c>
       <c r="G304" s="7" t="n">
         <v>46231</v>
@@ -23664,7 +23664,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="5" t="n">
-        <v>0.06487549148099608</v>
+        <v>0.09234518107722035</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="5" t="n">
-        <v>0.04849279161205768</v>
+        <v>0.07553987059910927</v>
       </c>
       <c r="Q304" s="10" t="inlineStr">
         <is>
@@ -23724,13 +23724,13 @@
         </is>
       </c>
       <c r="D305" s="15" t="n">
-        <v>111.83</v>
+        <v>111.77</v>
       </c>
       <c r="E305" s="20" t="n">
-        <v>0.0109</v>
+        <v>0.0103</v>
       </c>
       <c r="F305" s="20" t="n">
-        <v>0.0553</v>
+        <v>0.0547</v>
       </c>
       <c r="G305" s="17" t="n">
         <v>46302</v>
@@ -23759,7 +23759,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="20" t="n">
-        <v>0.2071894840382724</v>
+        <v>0.2078375234857297</v>
       </c>
       <c r="N305" s="14" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="20" t="n">
-        <v>0.1177680407761781</v>
+        <v>0.1183680773016015</v>
       </c>
       <c r="Q305" s="21" t="inlineStr"/>
       <c r="R305" s="19" t="n"/>
@@ -23805,13 +23805,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>354.48</v>
+        <v>354.27</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>0.0296</v>
+        <v>0.029</v>
       </c>
       <c r="F306" s="5" t="n">
-        <v>0.1667</v>
+        <v>0.166</v>
       </c>
       <c r="G306" s="7" t="n">
         <v>46231</v>
@@ -23840,7 +23840,7 @@
         <v>350</v>
       </c>
       <c r="M306" s="6" t="n">
-        <v>-0.01263823064770937</v>
+        <v>-0.0120529539616676</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="5" t="n">
-        <v>0.1284134506883322</v>
+        <v>0.1290823383295227</v>
       </c>
       <c r="Q306" s="10" t="inlineStr">
         <is>
@@ -23892,13 +23892,13 @@
         </is>
       </c>
       <c r="D307" s="15" t="n">
-        <v>72.54000000000001</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="E307" s="20" t="n">
-        <v>0.003</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="F307" s="16" t="n">
-        <v>-0.0877</v>
+        <v>-0.08199999999999999</v>
       </c>
       <c r="G307" s="17" t="n">
         <v>46260</v>
@@ -23949,13 +23949,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>50.73</v>
+        <v>49.78</v>
       </c>
       <c r="E308" s="6" t="n">
-        <v>-0.3035</v>
+        <v>-0.3166</v>
       </c>
       <c r="F308" s="6" t="n">
-        <v>-0.1598</v>
+        <v>-0.1756</v>
       </c>
       <c r="G308" s="7" t="n">
         <v>46267</v>
@@ -24010,13 +24010,13 @@
         </is>
       </c>
       <c r="D309" s="15" t="n">
-        <v>80.67</v>
+        <v>81.12</v>
       </c>
       <c r="E309" s="20" t="n">
-        <v>0.0486</v>
+        <v>0.0545</v>
       </c>
       <c r="F309" s="20" t="n">
-        <v>0.08789999999999999</v>
+        <v>0.094</v>
       </c>
       <c r="G309" s="17" t="n">
         <v>46233</v>
@@ -24045,14 +24045,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="20" t="n">
-        <v>0.02888310400396676</v>
+        <v>0.02317554240631158</v>
       </c>
       <c r="N309" s="14" t="inlineStr"/>
       <c r="O309" s="19" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="20" t="n">
-        <v>0.07846783190777239</v>
+        <v>0.07248520710059166</v>
       </c>
       <c r="Q309" s="21" t="inlineStr"/>
       <c r="R309" s="19" t="n"/>
@@ -24087,13 +24087,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>175.01</v>
+        <v>171.5</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>0.03759999999999999</v>
+        <v>0.0168</v>
       </c>
       <c r="F310" s="6" t="n">
-        <v>-0.0639</v>
+        <v>-0.0827</v>
       </c>
       <c r="G310" s="7" t="n">
         <v>46231</v>
@@ -24122,7 +24122,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="5" t="n">
-        <v>0.1427918404662591</v>
+        <v>0.1661807580174927</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="9" t="n"/>
@@ -24170,13 +24170,13 @@
         </is>
       </c>
       <c r="D311" s="15" t="n">
-        <v>147.96</v>
+        <v>147.05</v>
       </c>
       <c r="E311" s="20" t="n">
-        <v>0.0872</v>
+        <v>0.0805</v>
       </c>
       <c r="F311" s="20" t="n">
-        <v>0.1833</v>
+        <v>0.176</v>
       </c>
       <c r="G311" s="17" t="n">
         <v>46232</v>
@@ -24235,13 +24235,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>194.78</v>
+        <v>193.18</v>
       </c>
       <c r="E312" s="5" t="n">
-        <v>0.022</v>
+        <v>0.0136</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>0.0252</v>
+        <v>0.0167</v>
       </c>
       <c r="G312" s="7" t="n">
         <v>46317</v>
@@ -24270,7 +24270,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="5" t="n">
-        <v>0.1294794126707054</v>
+        <v>0.1388342478517444</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="5" t="n">
-        <v>0.1808193859739193</v>
+        <v>0.1905994409359147</v>
       </c>
       <c r="Q312" s="10" t="inlineStr">
         <is>
@@ -24322,13 +24322,13 @@
         </is>
       </c>
       <c r="D313" s="15" t="n">
-        <v>1047.66</v>
+        <v>1034.86</v>
       </c>
       <c r="E313" s="16" t="n">
-        <v>-0.0346</v>
+        <v>-0.0464</v>
       </c>
       <c r="F313" s="16" t="n">
-        <v>-0.0191</v>
+        <v>-0.0311</v>
       </c>
       <c r="G313" s="17" t="n">
         <v>46232</v>
@@ -24357,7 +24357,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="20" t="n">
-        <v>0.1454097703453409</v>
+        <v>0.1595771408692964</v>
       </c>
       <c r="N313" s="14" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="20" t="n">
-        <v>0.183590096023519</v>
+        <v>0.1982297122316063</v>
       </c>
       <c r="Q313" s="21" t="inlineStr">
         <is>
@@ -24413,13 +24413,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>127.18</v>
+        <v>126.12</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>0.014</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F314" s="5" t="n">
-        <v>0.06309999999999999</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="G314" s="7" t="n">
         <v>46234</v>
@@ -24448,7 +24448,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="5" t="n">
-        <v>0.01431042616763637</v>
+        <v>0.02283539486203612</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>122</v>
       </c>
       <c r="P314" s="6" t="n">
-        <v>-0.04072967447711909</v>
+        <v>-0.03266730098319065</v>
       </c>
       <c r="Q314" s="10" t="inlineStr">
         <is>
@@ -24500,13 +24500,13 @@
         </is>
       </c>
       <c r="D315" s="15" t="n">
-        <v>65.73999999999999</v>
+        <v>65.73</v>
       </c>
       <c r="E315" s="20" t="n">
-        <v>0.0428</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="F315" s="20" t="n">
-        <v>0.0727</v>
+        <v>0.0726</v>
       </c>
       <c r="G315" s="17" t="n">
         <v>46239</v>
@@ -24535,14 +24535,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="16" t="n">
-        <v>-0.01125646486157583</v>
+        <v>-0.01110603986003353</v>
       </c>
       <c r="N315" s="14" t="inlineStr"/>
       <c r="O315" s="19" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="20" t="n">
-        <v>0.01916641314268338</v>
+        <v>0.01932146660581159</v>
       </c>
       <c r="Q315" s="21" t="inlineStr">
         <is>
@@ -24583,13 +24583,13 @@
         </is>
       </c>
       <c r="D316" s="4" t="n">
-        <v>147.82</v>
+        <v>147.12</v>
       </c>
       <c r="E316" s="5" t="n">
-        <v>0.0643</v>
+        <v>0.0593</v>
       </c>
       <c r="F316" s="5" t="n">
-        <v>0.0303</v>
+        <v>0.0254</v>
       </c>
       <c r="G316" s="7" t="n">
         <v>46309</v>
@@ -24618,7 +24618,7 @@
         <v>167</v>
       </c>
       <c r="M316" s="5" t="n">
-        <v>0.1297524015694765</v>
+        <v>0.1351277868406743</v>
       </c>
       <c r="N316" s="3" t="inlineStr"/>
       <c r="O316" s="9" t="n"/>
@@ -24662,13 +24662,13 @@
         </is>
       </c>
       <c r="D317" s="15" t="n">
-        <v>333.58</v>
+        <v>330.47</v>
       </c>
       <c r="E317" s="20" t="n">
-        <v>0.0281</v>
+        <v>0.0186</v>
       </c>
       <c r="F317" s="20" t="n">
-        <v>0.0984</v>
+        <v>0.0882</v>
       </c>
       <c r="G317" s="17" t="n">
         <v>46232</v>
@@ -24704,7 +24704,7 @@
         <v>316</v>
       </c>
       <c r="P317" s="16" t="n">
-        <v>-0.05270100125906824</v>
+        <v>-0.04378612279480747</v>
       </c>
       <c r="Q317" s="21" t="inlineStr">
         <is>
@@ -24745,13 +24745,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>236.3</v>
+        <v>236.7</v>
       </c>
       <c r="E318" s="5" t="n">
-        <v>0.0384</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="F318" s="5" t="n">
-        <v>0.1532</v>
+        <v>0.1551</v>
       </c>
       <c r="G318" s="7" t="n">
         <v>46244</v>
@@ -24787,7 +24787,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="6" t="n">
-        <v>-0.09013965298349561</v>
+        <v>-0.0916772285593578</v>
       </c>
       <c r="Q318" s="10" t="inlineStr">
         <is>
@@ -24828,13 +24828,13 @@
         </is>
       </c>
       <c r="D319" s="15" t="n">
-        <v>126.28</v>
+        <v>124.09</v>
       </c>
       <c r="E319" s="20" t="n">
-        <v>0.0417</v>
+        <v>0.0236</v>
       </c>
       <c r="F319" s="20" t="n">
-        <v>0.0212</v>
+        <v>0.0035</v>
       </c>
       <c r="G319" s="17" t="n"/>
       <c r="H319" s="23" t="inlineStr">
@@ -24853,7 +24853,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="20" t="n">
-        <v>0.1244852708267342</v>
+        <v>0.1443307276976388</v>
       </c>
       <c r="N319" s="14" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="20" t="n">
-        <v>0.0848907190370605</v>
+        <v>0.1040373922153276</v>
       </c>
       <c r="Q319" s="21" t="inlineStr">
         <is>
@@ -24913,13 +24913,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>244.1</v>
+        <v>243.57</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0696</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>0.1888</v>
+        <v>0.1862</v>
       </c>
       <c r="G320" s="7" t="n"/>
       <c r="H320" s="12" t="inlineStr">
@@ -24938,7 +24938,7 @@
         <v>237</v>
       </c>
       <c r="M320" s="6" t="n">
-        <v>-0.02908643998361325</v>
+        <v>-0.02697376524202485</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>236</v>
       </c>
       <c r="P320" s="6" t="n">
-        <v>-0.0331831216714461</v>
+        <v>-0.03107936116927369</v>
       </c>
       <c r="Q320" s="10" t="inlineStr">
         <is>
@@ -24990,13 +24990,13 @@
         </is>
       </c>
       <c r="D321" s="15" t="n">
-        <v>181.4</v>
+        <v>179.38</v>
       </c>
       <c r="E321" s="20" t="n">
-        <v>0.0375</v>
+        <v>0.026</v>
       </c>
       <c r="F321" s="20" t="n">
-        <v>0.0726</v>
+        <v>0.06059999999999999</v>
       </c>
       <c r="G321" s="17" t="n">
         <v>46239</v>
@@ -25025,7 +25025,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="20" t="n">
-        <v>0.1025358324145534</v>
+        <v>0.114951499609767</v>
       </c>
       <c r="N321" s="14" t="inlineStr"/>
       <c r="O321" s="19" t="n"/>
@@ -25069,13 +25069,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>138.21</v>
+        <v>138.04</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>0.0431</v>
+        <v>0.0418</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>0.1212</v>
+        <v>0.1198</v>
       </c>
       <c r="G322" s="7" t="n">
         <v>46232</v>
@@ -25104,7 +25104,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="6" t="n">
-        <v>-0.05216699225815793</v>
+        <v>-0.0509997102289191</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="9" t="n"/>
@@ -25148,13 +25148,13 @@
         </is>
       </c>
       <c r="D323" s="15" t="n">
-        <v>32.01</v>
+        <v>32.54</v>
       </c>
       <c r="E323" s="16" t="n">
-        <v>-0.1402</v>
+        <v>-0.126</v>
       </c>
       <c r="F323" s="16" t="n">
-        <v>-0.1993</v>
+        <v>-0.1861</v>
       </c>
       <c r="G323" s="17" t="n">
         <v>46234</v>
@@ -25227,13 +25227,13 @@
         </is>
       </c>
       <c r="D324" s="4" t="n">
-        <v>41.45</v>
+        <v>41.93</v>
       </c>
       <c r="E324" s="5" t="n">
-        <v>0.1372</v>
+        <v>0.1503</v>
       </c>
       <c r="F324" s="5" t="n">
-        <v>0.0617</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="G324" s="7" t="n">
         <v>46233</v>
@@ -25288,13 +25288,13 @@
         </is>
       </c>
       <c r="D325" s="15" t="n">
-        <v>261.62</v>
+        <v>259.82</v>
       </c>
       <c r="E325" s="20" t="n">
-        <v>0.0089</v>
+        <v>0.0019</v>
       </c>
       <c r="F325" s="16" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="G325" s="17" t="n">
         <v>46240</v>
@@ -25323,7 +25323,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="20" t="n">
-        <v>0.467777692836939</v>
+        <v>0.4779462704949581</v>
       </c>
       <c r="N325" s="14" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="20" t="n">
-        <v>0.4524883418698876</v>
+        <v>0.4625509968439689</v>
       </c>
       <c r="Q325" s="21" t="inlineStr"/>
       <c r="R325" s="19" t="n"/>
@@ -25377,13 +25377,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>75.39</v>
+        <v>74.37</v>
       </c>
       <c r="E326" s="6" t="n">
-        <v>-0.0325</v>
+        <v>-0.0457</v>
       </c>
       <c r="F326" s="5" t="n">
-        <v>0.0389</v>
+        <v>0.0248</v>
       </c>
       <c r="G326" s="7" t="n">
         <v>46231</v>
@@ -25412,7 +25412,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="5" t="n">
-        <v>0.04788433479241278</v>
+        <v>0.06225628613688309</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="9" t="n"/>
@@ -25464,13 +25464,13 @@
         </is>
       </c>
       <c r="D327" s="15" t="n">
-        <v>130.63</v>
+        <v>129.24</v>
       </c>
       <c r="E327" s="20" t="n">
-        <v>0.018</v>
+        <v>0.0071</v>
       </c>
       <c r="F327" s="20" t="n">
-        <v>0.0644</v>
+        <v>0.053</v>
       </c>
       <c r="G327" s="17" t="n">
         <v>46238</v>
@@ -25499,7 +25499,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="20" t="n">
-        <v>0.0411084743167726</v>
+        <v>0.05230578768183217</v>
       </c>
       <c r="N327" s="14" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="20" t="n">
-        <v>0.07172931179667767</v>
+        <v>0.08325595790776842</v>
       </c>
       <c r="Q327" s="21" t="inlineStr">
         <is>
@@ -25551,13 +25551,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>113.66</v>
+        <v>112.32</v>
       </c>
       <c r="E328" s="6" t="n">
-        <v>-0.023</v>
+        <v>-0.0345</v>
       </c>
       <c r="F328" s="5" t="n">
-        <v>0.0423</v>
+        <v>0.03</v>
       </c>
       <c r="G328" s="7" t="n">
         <v>46232</v>
@@ -25586,7 +25586,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="5" t="n">
-        <v>0.1525602674643674</v>
+        <v>0.1663105413105414</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -25597,7 +25597,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="5" t="n">
-        <v>0.06457856765792719</v>
+        <v>0.07727920227920235</v>
       </c>
       <c r="Q328" s="10" t="inlineStr">
         <is>
@@ -25642,13 +25642,13 @@
         </is>
       </c>
       <c r="D329" s="15" t="n">
-        <v>89.93000000000001</v>
+        <v>89.28</v>
       </c>
       <c r="E329" s="20" t="n">
-        <v>0.0144</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F329" s="20" t="n">
-        <v>0.0336</v>
+        <v>0.0261</v>
       </c>
       <c r="G329" s="17" t="n">
         <v>46318</v>
@@ -25684,7 +25684,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="20" t="n">
-        <v>0.1898143000111197</v>
+        <v>0.1984767025089605</v>
       </c>
       <c r="Q329" s="21" t="inlineStr">
         <is>
@@ -25733,13 +25733,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>60.41</v>
+        <v>59.86</v>
       </c>
       <c r="E330" s="5" t="n">
-        <v>0.0611</v>
+        <v>0.0515</v>
       </c>
       <c r="F330" s="5" t="n">
-        <v>0.0934</v>
+        <v>0.0834</v>
       </c>
       <c r="G330" s="7" t="n">
         <v>46237</v>
@@ -25768,7 +25768,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="5" t="n">
-        <v>0.04287369640787955</v>
+        <v>0.05245573003675243</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="9" t="n"/>
@@ -25812,13 +25812,13 @@
         </is>
       </c>
       <c r="D331" s="15" t="n">
-        <v>39.94</v>
+        <v>39.58</v>
       </c>
       <c r="E331" s="16" t="n">
-        <v>-0.243</v>
+        <v>-0.2498</v>
       </c>
       <c r="F331" s="16" t="n">
-        <v>-0.4028</v>
+        <v>-0.4082</v>
       </c>
       <c r="G331" s="17" t="n">
         <v>46241</v>
@@ -25873,13 +25873,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>8.23</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="E332" s="6" t="n">
-        <v>-0.1983</v>
+        <v>-0.1988</v>
       </c>
       <c r="F332" s="6" t="n">
-        <v>-0.3508</v>
+        <v>-0.3512</v>
       </c>
       <c r="G332" s="7" t="n">
         <v>46239</v>
@@ -25934,13 +25934,13 @@
         </is>
       </c>
       <c r="D333" s="15" t="n">
-        <v>97.51000000000001</v>
+        <v>96.78</v>
       </c>
       <c r="E333" s="20" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0003</v>
       </c>
       <c r="F333" s="20" t="n">
-        <v>0.0593</v>
+        <v>0.05139999999999999</v>
       </c>
       <c r="G333" s="17" t="n">
         <v>46233</v>
@@ -25969,7 +25969,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="20" t="n">
-        <v>0.0152804840529176</v>
+        <v>0.02293862368257903</v>
       </c>
       <c r="N333" s="14" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="20" t="n">
-        <v>0.1486001435750179</v>
+        <v>0.1572638974994834</v>
       </c>
       <c r="Q333" s="21" t="inlineStr">
         <is>
@@ -26021,13 +26021,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>114.89</v>
+        <v>113.61</v>
       </c>
       <c r="E334" s="6" t="n">
-        <v>-0.0299</v>
+        <v>-0.0408</v>
       </c>
       <c r="F334" s="5" t="n">
-        <v>0.0346</v>
+        <v>0.0231</v>
       </c>
       <c r="G334" s="7" t="n">
         <v>46232</v>
@@ -26056,7 +26056,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="5" t="n">
-        <v>0.1054051701627644</v>
+        <v>0.1178593433676613</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="9" t="n"/>
@@ -40153,7 +40153,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of July 28, 2026 at 16:28 UTC</t>
+          <t>Data as of July 28, 2026 at 21:47 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>95.36</v>
+        <v>96.16</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-0.0092</v>
+        <v>-0.0009</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.0728</v>
+        <v>-0.065</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>46239</v>
@@ -878,7 +878,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="9" t="n">
-        <v>0.3108221476510067</v>
+        <v>0.2999168053244593</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0.5100671140939598</v>
+        <v>0.4975041597337771</v>
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>333.85</v>
+        <v>333.66</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>-0.0658</v>
+        <v>-0.0663</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>-0.113</v>
+        <v>-0.1135</v>
       </c>
       <c r="G3" s="17" t="n">
         <v>46322</v>
@@ -973,7 +973,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="20" t="n">
-        <v>0.3119664519994008</v>
+        <v>0.3127135407300844</v>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="20" t="n">
-        <v>0.2580500224651789</v>
+        <v>0.258766408919259</v>
       </c>
       <c r="Q3" s="21" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>532.14</v>
+        <v>539.03</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-0.0553</v>
+        <v>-0.0431</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.1138</v>
+        <v>-0.1023</v>
       </c>
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="12" t="inlineStr">
@@ -1054,7 +1054,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="9" t="n">
-        <v>0.5691359416694856</v>
+        <v>0.5490789009888133</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>0.7476603901229001</v>
+        <v>0.7253214106821514</v>
       </c>
       <c r="Q4" s="10" t="inlineStr">
         <is>
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>39.04</v>
+        <v>39.31</v>
       </c>
       <c r="E5" s="20" t="n">
-        <v>0.0261</v>
+        <v>0.0331</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>0.0622</v>
+        <v>0.0694</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>46238</v>
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>72.09999999999999</v>
+        <v>73.17</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0.0098</v>
+        <v>0.0248</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-0.1602</v>
+        <v>-0.1477</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>46315</v>
@@ -1210,7 +1210,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>0.1095700416088767</v>
+        <v>0.09334426677600106</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0.3869625520110958</v>
+        <v>0.3666803334700013</v>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
@@ -1262,13 +1262,13 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>79.11</v>
+        <v>79.61</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>0.0862</v>
+        <v>0.0931</v>
       </c>
       <c r="F7" s="20" t="n">
-        <v>0.0413</v>
+        <v>0.0479</v>
       </c>
       <c r="G7" s="17" t="n"/>
       <c r="H7" s="23" t="inlineStr">
@@ -1287,7 +1287,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="20" t="n">
-        <v>0.1502970547339148</v>
+        <v>0.1430724783318679</v>
       </c>
       <c r="N7" s="14" t="inlineStr"/>
       <c r="O7" s="19" t="n"/>
@@ -1331,13 +1331,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>515.86</v>
+        <v>522.61</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.1236</v>
+        <v>0.1383</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>0.016</v>
+        <v>0.0292</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>46238</v>
@@ -1366,7 +1366,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>0.104815259954251</v>
+        <v>0.09054553108436489</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>0.2562323110921567</v>
+        <v>0.2400068885019421</v>
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>182.23</v>
+        <v>183.81</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>-0.09480000000000001</v>
+        <v>-0.08689999999999999</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>-0.1259</v>
+        <v>-0.1183</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>46237</v>
@@ -1487,13 +1487,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>175.9</v>
+        <v>173.34</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.0487</v>
+        <v>0.0334</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-0.058</v>
+        <v>-0.0718</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>46317</v>
@@ -1522,7 +1522,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>-0.03354178510517342</v>
+        <v>-0.01926848967347412</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>0.534963047185901</v>
+        <v>0.557632398753894</v>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>46.01</v>
+        <v>46.11</v>
       </c>
       <c r="E11" s="20" t="n">
-        <v>0.0866</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>-0.0361</v>
+        <v>-0.0339</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>46316</v>
@@ -1609,7 +1609,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>-0.06542056074766352</v>
+        <v>-0.06744740837128604</v>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="20" t="n">
-        <v>0.08672027820039127</v>
+        <v>0.08436347863803949</v>
       </c>
       <c r="Q11" s="21" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>150.73</v>
+        <v>152.08</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.0533</v>
+        <v>0.06280000000000001</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.1031</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>46240</v>
@@ -1700,7 +1700,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>0.2008226630398727</v>
+        <v>0.1901630720673329</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>0.02832879984077497</v>
+        <v>0.01920042083114142</v>
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
@@ -1752,13 +1752,13 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>238.77</v>
-      </c>
-      <c r="E13" s="20" t="n">
-        <v>0.0018</v>
+        <v>235.5</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>-0.0119</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>-0.0861</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="G13" s="17" t="n">
         <v>46233</v>
@@ -1787,7 +1787,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="20" t="n">
-        <v>0.3485781295807681</v>
+        <v>0.3673036093418259</v>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="20" t="n">
-        <v>0.1936172886040959</v>
+        <v>0.2101910828025478</v>
       </c>
       <c r="Q13" s="21" t="inlineStr">
         <is>
@@ -1851,13 +1851,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3009.78</v>
+        <v>3006.57</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.0582</v>
+        <v>-0.0593</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0048</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>46287</v>
@@ -1886,7 +1886,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>0.3788383204088006</v>
+        <v>0.380310453440299</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>0.2293257314488101</v>
+        <v>0.230638235597375</v>
       </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
@@ -1938,13 +1938,13 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>88.14</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="E15" s="20" t="n">
-        <v>0.1616</v>
+        <v>0.1574</v>
       </c>
       <c r="F15" s="20" t="n">
-        <v>0.1756</v>
+        <v>0.1712</v>
       </c>
       <c r="G15" s="17" t="n">
         <v>46261</v>
@@ -1973,7 +1973,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="16" t="n">
-        <v>-0.2625368731563422</v>
+        <v>-0.2598496925529492</v>
       </c>
       <c r="N15" s="14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>-0.03562514181983209</v>
+        <v>-0.03211113641539505</v>
       </c>
       <c r="Q15" s="21" t="inlineStr"/>
       <c r="R15" s="19" t="n"/>
@@ -2019,13 +2019,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>190.6</v>
+        <v>193.24</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.0693</v>
+        <v>0.0842</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.1261</v>
+        <v>0.1417</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>46238</v>
@@ -2054,7 +2054,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>0.1227701993704093</v>
+        <v>0.1074311736700476</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>0.2854144805876181</v>
+        <v>0.2678534464914096</v>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>369.24</v>
+        <v>372.19</v>
       </c>
       <c r="E17" s="20" t="n">
-        <v>0.1655</v>
+        <v>0.1748</v>
       </c>
       <c r="F17" s="20" t="n">
-        <v>0.1759</v>
+        <v>0.1853</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>46261</v>
@@ -2149,7 +2149,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="20" t="n">
-        <v>0.01559961000974973</v>
+        <v>0.007549907305408534</v>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="20" t="n">
-        <v>0.01559961000974973</v>
+        <v>0.007549907305408534</v>
       </c>
       <c r="Q17" s="21" t="inlineStr"/>
       <c r="R17" s="19" t="n"/>
@@ -2199,13 +2199,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>38.53</v>
+        <v>38.52</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.1334</v>
+        <v>0.1329</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>0.2614</v>
+        <v>0.2609</v>
       </c>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="12" t="inlineStr">
@@ -2224,7 +2224,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>0.1679211004412146</v>
+        <v>0.1682242990654205</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>0.1679211004412146</v>
+        <v>0.1682242990654205</v>
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
@@ -2276,13 +2276,13 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>144.85</v>
+        <v>145.53</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>-0.1107</v>
+        <v>-0.1065</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>-0.0145</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>46324</v>
@@ -2311,7 +2311,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="20" t="n">
-        <v>0.1736278909216431</v>
+        <v>0.1681440252868824</v>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="20" t="n">
-        <v>0.2219537452537108</v>
+        <v>0.2162440733869305</v>
       </c>
       <c r="Q19" s="21" t="inlineStr">
         <is>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>199.64</v>
+        <v>199.91</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-0.1198</v>
+        <v>-0.1186</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.07980000000000001</v>
+        <v>-0.0786</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>46261</v>
@@ -2398,7 +2398,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>0.1019835704267683</v>
+        <v>0.1004952228502826</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="8" t="n"/>
@@ -2442,13 +2442,13 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>128.41</v>
+        <v>128.57</v>
       </c>
       <c r="E21" s="20" t="n">
-        <v>0.0617</v>
+        <v>0.063</v>
       </c>
       <c r="F21" s="20" t="n">
-        <v>0.1532</v>
+        <v>0.1546</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>46267</v>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>86.97</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1284</v>
+        <v>0.1469</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.0519</v>
+        <v>0.0692</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>46315</v>
@@ -2538,7 +2538,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-0.2986087156490744</v>
+        <v>-0.3099547511312218</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>0.1498217776244682</v>
+        <v>0.1312217194570135</v>
       </c>
       <c r="Q22" s="10" t="inlineStr">
         <is>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>124.14</v>
+        <v>124.83</v>
       </c>
       <c r="E23" s="20" t="n">
-        <v>0.0522</v>
+        <v>0.0581</v>
       </c>
       <c r="F23" s="20" t="n">
-        <v>0.2763</v>
+        <v>0.2835</v>
       </c>
       <c r="G23" s="17" t="n">
         <v>46315</v>
@@ -2628,7 +2628,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="20" t="n">
-        <v>0.1680360882874174</v>
+        <v>0.1615797484579028</v>
       </c>
       <c r="Q23" s="21" t="inlineStr"/>
       <c r="R23" s="19" t="n"/>
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>331.9</v>
+        <v>333.35</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-0.05889999999999999</v>
+        <v>-0.0548</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0.0683</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>46252</v>
@@ -2698,7 +2698,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>0.08466405543838514</v>
+        <v>0.07994600269986493</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="9" t="n">
-        <v>0.2051822838204279</v>
+        <v>0.1999400029998499</v>
       </c>
       <c r="Q24" s="10" t="inlineStr">
         <is>
@@ -2758,13 +2758,13 @@
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>209.84</v>
+        <v>210.08</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>-0.0483</v>
+        <v>-0.0472</v>
       </c>
       <c r="F25" s="20" t="n">
-        <v>0.0103</v>
+        <v>0.0115</v>
       </c>
       <c r="G25" s="17" t="n">
         <v>46253</v>
@@ -2793,7 +2793,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="20" t="n">
-        <v>0.2152115897826916</v>
+        <v>0.2138233054074637</v>
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="20" t="n">
-        <v>0.09607319862752571</v>
+        <v>0.09482102056359476</v>
       </c>
       <c r="Q25" s="21" t="inlineStr">
         <is>
@@ -2849,13 +2849,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>267.48</v>
+        <v>268.44</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>-0.0105</v>
+        <v>-0.0069</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.0313</v>
+        <v>-0.0278</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>46238</v>
@@ -2884,7 +2884,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="9" t="n">
-        <v>0.1215791834903543</v>
+        <v>0.1175681716584712</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="9" t="n">
-        <v>0.3085090474054134</v>
+        <v>0.3038295336015497</v>
       </c>
       <c r="Q26" s="10" t="inlineStr">
         <is>
@@ -2936,13 +2936,13 @@
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>41.91</v>
+        <v>42.29</v>
       </c>
       <c r="E27" s="20" t="n">
-        <v>0.021</v>
+        <v>0.0302</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.0793</v>
       </c>
       <c r="G27" s="17" t="n">
         <v>46289</v>
@@ -2997,13 +2997,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>88.39</v>
+        <v>87.36</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-0.04019999999999999</v>
+        <v>-0.05139999999999999</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>0.0202</v>
+        <v>0.0083</v>
       </c>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="12" t="inlineStr">
@@ -3022,7 +3022,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="9" t="n">
-        <v>0.2444846702115624</v>
+        <v>0.2591575091575092</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0.3010521552211788</v>
+        <v>0.3163919413919414</v>
       </c>
       <c r="Q28" s="10" t="inlineStr">
         <is>
@@ -3078,13 +3078,13 @@
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>186.04</v>
+        <v>190.68</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>-0.1343</v>
+        <v>-0.1127</v>
       </c>
       <c r="F29" s="20" t="n">
-        <v>0.0218</v>
+        <v>0.0473</v>
       </c>
       <c r="G29" s="17" t="n">
         <v>46317</v>
@@ -3139,13 +3139,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>250.38</v>
+        <v>252.57</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.1763</v>
+        <v>0.1866</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>0.1174</v>
+        <v>0.1272</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>46254</v>
@@ -3174,7 +3174,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>-0.02148733924434857</v>
+        <v>-0.02997188898127249</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="9" t="n">
-        <v>0.05839124530713317</v>
+        <v>0.04921407926515424</v>
       </c>
       <c r="Q30" s="10" t="inlineStr">
         <is>
@@ -3226,13 +3226,13 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>107.6</v>
+        <v>105.85</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>0.0529</v>
+        <v>0.0358</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>0.1149</v>
+        <v>0.0968</v>
       </c>
       <c r="G31" s="17" t="n"/>
       <c r="H31" s="23" t="inlineStr">
@@ -3251,7 +3251,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="20" t="n">
-        <v>0.1152416356877324</v>
+        <v>0.1336797354747284</v>
       </c>
       <c r="N31" s="14" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="20" t="n">
-        <v>0.06877323420074355</v>
+        <v>0.0864430798299481</v>
       </c>
       <c r="Q31" s="21" t="inlineStr">
         <is>
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>14.23</v>
+        <v>14.7</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>-0.0491</v>
+        <v>-0.018</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>0.0338</v>
+        <v>0.0675</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>46237</v>
@@ -3364,13 +3364,13 @@
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>157.99</v>
+        <v>159.26</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>0.0429</v>
+        <v>0.0512</v>
       </c>
       <c r="F33" s="20" t="n">
-        <v>0.0343</v>
+        <v>0.0426</v>
       </c>
       <c r="G33" s="17" t="n">
         <v>46253</v>
@@ -3399,7 +3399,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="20" t="n">
-        <v>0.01272232419773398</v>
+        <v>0.004646490016325563</v>
       </c>
       <c r="N33" s="14" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="20" t="n">
-        <v>0.1076650420912715</v>
+        <v>0.09883209845535608</v>
       </c>
       <c r="Q33" s="21" t="inlineStr">
         <is>
@@ -3455,13 +3455,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>29.83</v>
+        <v>30.21</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>-0.0565</v>
+        <v>-0.0443</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>-0.06150000000000001</v>
+        <v>-0.04940000000000001</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>46317</v>
@@ -3490,7 +3490,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="9" t="n">
-        <v>0.1733154542406974</v>
+        <v>0.1585567692816948</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="9" t="n">
-        <v>0.3409319477036541</v>
+        <v>0.3240648791790797</v>
       </c>
       <c r="Q34" s="10" t="inlineStr">
         <is>
@@ -3542,13 +3542,13 @@
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>307</v>
+        <v>308.85</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>-0.2701</v>
+        <v>-0.2657</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>-0.2618</v>
+        <v>-0.2574</v>
       </c>
       <c r="G35" s="17" t="n">
         <v>46323</v>
@@ -3577,7 +3577,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="16" t="n">
-        <v>-0.5765472312703583</v>
+        <v>-0.5790836975878259</v>
       </c>
       <c r="N35" s="14" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>-0.02280130293159609</v>
+        <v>-0.02865468674113655</v>
       </c>
       <c r="Q35" s="21" t="inlineStr">
         <is>
@@ -3629,13 +3629,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>69.11</v>
+        <v>70.37</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>-0.0423</v>
+        <v>-0.0248</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0461</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>46239</v>
@@ -3690,13 +3690,13 @@
         </is>
       </c>
       <c r="D37" s="15" t="n">
-        <v>511.17</v>
+        <v>516.73</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>0.1335</v>
+        <v>0.1458</v>
       </c>
       <c r="F37" s="20" t="n">
-        <v>0.0208</v>
+        <v>0.0319</v>
       </c>
       <c r="G37" s="17" t="n">
         <v>46261</v>
@@ -3725,7 +3725,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="16" t="n">
-        <v>-0.1196666471037033</v>
+        <v>-0.1291390087666673</v>
       </c>
       <c r="N37" s="14" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="20" t="n">
-        <v>0.2422481757536631</v>
+        <v>0.2288816209625916</v>
       </c>
       <c r="Q37" s="21" t="inlineStr">
         <is>
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>98.12</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.0128</v>
+        <v>0.0083</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>0.0296</v>
+        <v>0.025</v>
       </c>
       <c r="G38" s="6" t="n">
         <v>46234</v>
@@ -3816,7 +3816,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="9" t="n">
-        <v>0.1210762331838564</v>
+        <v>0.1261261261261261</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="9" t="n">
-        <v>0.07011822258459025</v>
+        <v>0.07493857493857486</v>
       </c>
       <c r="Q38" s="10" t="inlineStr">
         <is>
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="D39" s="15" t="n">
-        <v>91.5</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>-0.002</v>
+        <v>-0.0009</v>
       </c>
       <c r="F39" s="20" t="n">
-        <v>0.0347</v>
+        <v>0.0358</v>
       </c>
       <c r="G39" s="17" t="n">
         <v>46234</v>
@@ -3907,7 +3907,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="20" t="n">
-        <v>0.03825136612021858</v>
+        <v>0.03711790393013107</v>
       </c>
       <c r="N39" s="14" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="20" t="n">
-        <v>0.09289617486338798</v>
+        <v>0.09170305676855901</v>
       </c>
       <c r="Q39" s="21" t="inlineStr">
         <is>
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>953.65</v>
+        <v>954.17</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0.0194</v>
+        <v>0.02</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>0.008</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>46289</v>
@@ -3998,7 +3998,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="9" t="n">
-        <v>0.04860273685314321</v>
+        <v>0.04803127325319392</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="9" t="n">
-        <v>0.1534630105384575</v>
+        <v>0.1528344005785133</v>
       </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="D41" s="15" t="n">
-        <v>126.74</v>
+        <v>127.5</v>
       </c>
       <c r="E41" s="20" t="n">
-        <v>0.101</v>
+        <v>0.1076</v>
       </c>
       <c r="F41" s="20" t="n">
-        <v>0.1529</v>
+        <v>0.1598</v>
       </c>
       <c r="G41" s="17" t="n">
         <v>46261</v>
@@ -4093,7 +4093,7 @@
         <v>125</v>
       </c>
       <c r="M41" s="16" t="n">
-        <v>-0.01372889379832724</v>
+        <v>-0.0196078431372549</v>
       </c>
       <c r="N41" s="14" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="20" t="n">
-        <v>0.06517279469780658</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="Q41" s="21" t="inlineStr">
         <is>
@@ -4145,13 +4145,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>26.36</v>
+        <v>26.38</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.1162</v>
+        <v>0.1169</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>0.1157</v>
+        <v>0.1164</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>46239</v>
@@ -4206,13 +4206,13 @@
         </is>
       </c>
       <c r="D43" s="15" t="n">
-        <v>88.03</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>0.0832</v>
+        <v>0.0888</v>
       </c>
       <c r="F43" s="20" t="n">
-        <v>0.1194</v>
+        <v>0.1253</v>
       </c>
       <c r="G43" s="17" t="n"/>
       <c r="H43" s="23" t="inlineStr">
@@ -4231,7 +4231,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="20" t="n">
-        <v>0.02237873452232192</v>
+        <v>0.01706407503672737</v>
       </c>
       <c r="N43" s="14" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>88</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>-0.0003407929115074536</v>
+        <v>-0.00553734885297768</v>
       </c>
       <c r="Q43" s="21" t="inlineStr">
         <is>
@@ -4291,13 +4291,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>57.92</v>
+        <v>57.86</v>
       </c>
       <c r="E44" s="9" t="n">
-        <v>0.0429</v>
+        <v>0.042</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>-0.05860000000000001</v>
+        <v>-0.0595</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>46275</v>
@@ -4326,7 +4326,7 @@
         <v>58</v>
       </c>
       <c r="M44" s="9" t="n">
-        <v>0.00138121546961323</v>
+        <v>0.002419633598340833</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="9" t="n">
-        <v>0.3466850828729282</v>
+        <v>0.3480815762184584</v>
       </c>
       <c r="Q44" s="10" t="inlineStr">
         <is>
@@ -4378,13 +4378,13 @@
         </is>
       </c>
       <c r="D45" s="15" t="n">
-        <v>62.74</v>
+        <v>63.08</v>
       </c>
       <c r="E45" s="20" t="n">
-        <v>0.08470000000000001</v>
+        <v>0.0906</v>
       </c>
       <c r="F45" s="20" t="n">
-        <v>0.0277</v>
+        <v>0.0333</v>
       </c>
       <c r="G45" s="17" t="n"/>
       <c r="H45" s="23" t="inlineStr">
@@ -4403,7 +4403,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="20" t="n">
-        <v>0.1157156518967166</v>
+        <v>0.1097019657577679</v>
       </c>
       <c r="N45" s="14" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="20" t="n">
-        <v>0.1316544469238125</v>
+        <v>0.1255548509828789</v>
       </c>
       <c r="Q45" s="21" t="inlineStr">
         <is>
@@ -4463,13 +4463,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>50.37</v>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>-0.001</v>
+        <v>50.96</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>0.0107</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>0.0814</v>
+        <v>0.094</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>46301</v>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="D47" s="15" t="n">
-        <v>96.34</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="E47" s="20" t="n">
-        <v>0.0023</v>
+        <v>0.0159</v>
       </c>
       <c r="F47" s="20" t="n">
-        <v>0.08130000000000001</v>
+        <v>0.096</v>
       </c>
       <c r="G47" s="17" t="n">
         <v>46240</v>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>68.03</v>
+        <v>67.94</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>-0.0546</v>
+        <v>-0.0557</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>-0.0091</v>
+        <v>-0.0103</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>46233</v>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="D49" s="15" t="n">
-        <v>140.11</v>
+        <v>140.2</v>
       </c>
       <c r="E49" s="20" t="n">
-        <v>0.0348</v>
+        <v>0.0355</v>
       </c>
       <c r="F49" s="16" t="n">
-        <v>-0.01</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="G49" s="17" t="n">
         <v>46303</v>
@@ -4691,7 +4691,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="16" t="n">
-        <v>-0.0007850974234530985</v>
+        <v>-0.001426533523537722</v>
       </c>
       <c r="N49" s="14" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="20" t="n">
-        <v>0.07058739561772882</v>
+        <v>0.06990014265335244</v>
       </c>
       <c r="Q49" s="21" t="inlineStr">
         <is>
@@ -4751,13 +4751,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>143.12</v>
+        <v>143.96</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>-0.024</v>
+        <v>-0.0183</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>0.0202</v>
+        <v>0.0262</v>
       </c>
       <c r="G50" s="6" t="n"/>
       <c r="H50" s="12" t="inlineStr">
@@ -4776,7 +4776,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="9" t="n">
-        <v>0.1458915595304639</v>
+        <v>0.1392053348152264</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="9" t="n">
-        <v>0.1319172722191168</v>
+        <v>0.1253125868296749</v>
       </c>
       <c r="Q50" s="10" t="inlineStr">
         <is>
@@ -4840,13 +4840,13 @@
         </is>
       </c>
       <c r="D51" s="15" t="n">
-        <v>84.26000000000001</v>
+        <v>84.70999999999999</v>
       </c>
       <c r="E51" s="20" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0135</v>
       </c>
       <c r="F51" s="20" t="n">
-        <v>0.143</v>
+        <v>0.1491</v>
       </c>
       <c r="G51" s="17" t="n">
         <v>46238</v>
@@ -4875,7 +4875,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="20" t="n">
-        <v>0.1868027533823878</v>
+        <v>0.1804981702278362</v>
       </c>
       <c r="N51" s="14" t="inlineStr"/>
       <c r="O51" s="19" t="n"/>
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>143.43</v>
+        <v>144.51</v>
       </c>
       <c r="E52" s="9" t="n">
-        <v>0.09820000000000001</v>
+        <v>0.1064</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>0.1594</v>
+        <v>0.1681</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>46253</v>
@@ -4954,7 +4954,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>-0.02391410444119087</v>
+        <v>-0.03120891287800146</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>-0.05877431499686263</v>
+        <v>-0.06580859456092998</v>
       </c>
       <c r="Q52" s="10" t="inlineStr">
         <is>
@@ -5010,13 +5010,13 @@
         </is>
       </c>
       <c r="D53" s="15" t="n">
-        <v>111.03</v>
+        <v>111.1</v>
       </c>
       <c r="E53" s="16" t="n">
-        <v>-0.0197</v>
+        <v>-0.0191</v>
       </c>
       <c r="F53" s="16" t="n">
-        <v>-0.0312</v>
+        <v>-0.0305</v>
       </c>
       <c r="G53" s="17" t="n">
         <v>46254</v>
@@ -5045,7 +5045,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="20" t="n">
-        <v>0.2609204719445195</v>
+        <v>0.2601260126012602</v>
       </c>
       <c r="N53" s="14" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="20" t="n">
-        <v>0.2609204719445195</v>
+        <v>0.2601260126012602</v>
       </c>
       <c r="Q53" s="21" t="inlineStr">
         <is>
@@ -5188,13 +5188,13 @@
         </is>
       </c>
       <c r="D55" s="15" t="n">
-        <v>117.62</v>
+        <v>119.03</v>
       </c>
       <c r="E55" s="20" t="n">
-        <v>0.1314</v>
+        <v>0.145</v>
       </c>
       <c r="F55" s="20" t="n">
-        <v>0.0177</v>
+        <v>0.0298</v>
       </c>
       <c r="G55" s="17" t="n">
         <v>46240</v>
@@ -5223,7 +5223,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="20" t="n">
-        <v>0.5558578473048801</v>
+        <v>0.5374275392758128</v>
       </c>
       <c r="N55" s="14" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="20" t="n">
-        <v>0.2327835402142492</v>
+        <v>0.2181802906830211</v>
       </c>
       <c r="Q55" s="21" t="inlineStr">
         <is>
@@ -5275,13 +5275,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>190.96</v>
+        <v>192.31</v>
       </c>
       <c r="E56" s="9" t="n">
-        <v>0.152</v>
+        <v>0.1602</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>0.0276</v>
+        <v>0.0349</v>
       </c>
       <c r="G56" s="6" t="n">
         <v>46234</v>
@@ -5310,7 +5310,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="9" t="n">
-        <v>0.1625471302890657</v>
+        <v>0.1543861473662316</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="9" t="n">
-        <v>0.1782572266443234</v>
+        <v>0.169985960168478</v>
       </c>
       <c r="Q56" s="10" t="inlineStr">
         <is>
@@ -5366,13 +5366,13 @@
         </is>
       </c>
       <c r="D57" s="15" t="n">
-        <v>144.07</v>
+        <v>145.51</v>
       </c>
       <c r="E57" s="20" t="n">
-        <v>0.1106</v>
+        <v>0.1216</v>
       </c>
       <c r="F57" s="20" t="n">
-        <v>0.0546</v>
+        <v>0.06509999999999999</v>
       </c>
       <c r="G57" s="17" t="n">
         <v>46238</v>
@@ -5401,7 +5401,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="20" t="n">
-        <v>0.3604497813562852</v>
+        <v>0.3469864614115869</v>
       </c>
       <c r="N57" s="14" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="20" t="n">
-        <v>0.1799819532171862</v>
+        <v>0.1683045838773968</v>
       </c>
       <c r="Q57" s="21" t="inlineStr">
         <is>
@@ -5457,13 +5457,13 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>38.23</v>
+        <v>38.12</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>0.04</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>0.0274</v>
+        <v>0.0245</v>
       </c>
       <c r="G58" s="6" t="n">
         <v>46233</v>
@@ -5518,13 +5518,13 @@
         </is>
       </c>
       <c r="D59" s="15" t="n">
-        <v>20.19</v>
+        <v>20.24</v>
       </c>
       <c r="E59" s="20" t="n">
-        <v>0.05599999999999999</v>
+        <v>0.05860000000000001</v>
       </c>
       <c r="F59" s="20" t="n">
-        <v>0.04769999999999999</v>
+        <v>0.0503</v>
       </c>
       <c r="G59" s="17" t="n">
         <v>46238</v>
@@ -5579,13 +5579,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>196.81</v>
+        <v>199.77</v>
       </c>
       <c r="E60" s="9" t="n">
-        <v>0.1196</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>-0.0112</v>
+        <v>0.1365</v>
+      </c>
+      <c r="F60" s="9" t="n">
+        <v>0.0037</v>
       </c>
       <c r="G60" s="6" t="n">
         <v>46237</v>
@@ -5640,13 +5640,13 @@
         </is>
       </c>
       <c r="D61" s="15" t="n">
-        <v>31.52</v>
+        <v>31.64</v>
       </c>
       <c r="E61" s="16" t="n">
-        <v>-0.0716</v>
+        <v>-0.068</v>
       </c>
       <c r="F61" s="16" t="n">
-        <v>-0.199</v>
+        <v>-0.1959</v>
       </c>
       <c r="G61" s="17" t="n">
         <v>46315</v>
@@ -5682,7 +5682,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="20" t="n">
-        <v>0.3642131979695432</v>
+        <v>0.3590391908975979</v>
       </c>
       <c r="Q61" s="21" t="inlineStr">
         <is>
@@ -5727,13 +5727,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>31.4</v>
+        <v>31.66</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.0097</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>0.0177</v>
+        <v>0.0263</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>46316</v>
@@ -5762,7 +5762,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="9" t="n">
-        <v>0.1146496815286625</v>
+        <v>0.1054958938723942</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="8" t="n"/>
@@ -5806,13 +5806,13 @@
         </is>
       </c>
       <c r="D63" s="15" t="n">
-        <v>210.01</v>
+        <v>210.6</v>
       </c>
       <c r="E63" s="20" t="n">
-        <v>0.2423</v>
+        <v>0.2458</v>
       </c>
       <c r="F63" s="20" t="n">
-        <v>0.1652</v>
+        <v>0.1684</v>
       </c>
       <c r="G63" s="17" t="n">
         <v>46239</v>
@@ -5867,13 +5867,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>48.87</v>
+        <v>48.91</v>
       </c>
       <c r="E64" s="9" t="n">
-        <v>0.0512</v>
+        <v>0.0521</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>-0.1074</v>
+        <v>-0.1067</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>46311</v>
@@ -5909,7 +5909,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="9" t="n">
-        <v>0.2891344383057091</v>
+        <v>0.2880801472091598</v>
       </c>
       <c r="Q64" s="10" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="D65" s="15" t="n">
-        <v>42.96</v>
+        <v>43.46</v>
       </c>
       <c r="E65" s="20" t="n">
-        <v>0.0132</v>
+        <v>0.025</v>
       </c>
       <c r="F65" s="16" t="n">
-        <v>-0.0581</v>
+        <v>-0.0471</v>
       </c>
       <c r="G65" s="17" t="n">
         <v>46237</v>
@@ -6019,13 +6019,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>70.14</v>
+        <v>70.91</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>-0.0566</v>
+        <v>-0.0461</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>0.0014</v>
+        <v>0.0124</v>
       </c>
       <c r="G66" s="6" t="n">
         <v>46237</v>
@@ -6054,7 +6054,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="9" t="n">
-        <v>0.2688907898488737</v>
+        <v>0.2551121139472571</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="8" t="n"/>
@@ -6110,13 +6110,13 @@
         </is>
       </c>
       <c r="D67" s="15" t="n">
-        <v>155.82</v>
+        <v>156.97</v>
       </c>
       <c r="E67" s="20" t="n">
-        <v>0.1397</v>
+        <v>0.1481</v>
       </c>
       <c r="F67" s="20" t="n">
-        <v>0.0431</v>
+        <v>0.0508</v>
       </c>
       <c r="G67" s="17" t="n">
         <v>46234</v>
@@ -6145,7 +6145,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="20" t="n">
-        <v>0.1872673597740984</v>
+        <v>0.1785691533414028</v>
       </c>
       <c r="N67" s="14" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="20" t="n">
-        <v>0.1872673597740984</v>
+        <v>0.1785691533414028</v>
       </c>
       <c r="Q67" s="21" t="inlineStr">
         <is>
@@ -6201,13 +6201,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>126.88</v>
+        <v>127.36</v>
       </c>
       <c r="E68" s="9" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0862</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>0.1317</v>
+        <v>0.136</v>
       </c>
       <c r="G68" s="6" t="n">
         <v>46240</v>
@@ -6236,7 +6236,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>-0.0542244640605296</v>
+        <v>-0.05778894472361808</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>115</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>-0.09363177805800753</v>
+        <v>-0.09704773869346733</v>
       </c>
       <c r="Q68" s="10" t="inlineStr"/>
       <c r="R68" s="8" t="n"/>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="D69" s="15" t="n">
-        <v>362.37</v>
+        <v>366.57</v>
       </c>
       <c r="E69" s="20" t="n">
-        <v>0.0925</v>
+        <v>0.1052</v>
       </c>
       <c r="F69" s="20" t="n">
-        <v>0.131</v>
+        <v>0.1441</v>
       </c>
       <c r="G69" s="17" t="n"/>
       <c r="H69" s="23" t="inlineStr">
@@ -6307,7 +6307,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="20" t="n">
-        <v>0.1204017992659436</v>
+        <v>0.1075647216084241</v>
       </c>
       <c r="N69" s="14" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="20" t="n">
-        <v>0.2031901095565306</v>
+        <v>0.1894044793627411</v>
       </c>
       <c r="Q69" s="21" t="inlineStr">
         <is>
@@ -6355,13 +6355,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>336.18</v>
+        <v>337.52</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0022</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>0.0722</v>
+        <v>0.0765</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>46311</v>
@@ -6390,7 +6390,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="9" t="n">
-        <v>0.2344577309774525</v>
+        <v>0.2295567670063997</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="9" t="n">
-        <v>0.1303468380034505</v>
+        <v>0.1258592083432094</v>
       </c>
       <c r="Q70" s="10" t="inlineStr">
         <is>
@@ -6450,13 +6450,13 @@
         </is>
       </c>
       <c r="D71" s="15" t="n">
-        <v>61.62</v>
+        <v>61.73</v>
       </c>
       <c r="E71" s="20" t="n">
-        <v>0.08130000000000001</v>
+        <v>0.0834</v>
       </c>
       <c r="F71" s="20" t="n">
-        <v>0.1962</v>
+        <v>0.1984</v>
       </c>
       <c r="G71" s="17" t="n">
         <v>46309</v>
@@ -6511,13 +6511,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1096.57</v>
+        <v>1098.37</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>0.1404</v>
+        <v>0.1423</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>0.07429999999999999</v>
+        <v>0.0761</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>46308</v>
@@ -6549,7 +6549,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="9" t="n">
-        <v>0.1353584358499686</v>
+        <v>0.1334978194961626</v>
       </c>
       <c r="Q72" s="10" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         </is>
       </c>
       <c r="D73" s="15" t="n">
-        <v>22.16</v>
+        <v>22.59</v>
       </c>
       <c r="E73" s="16" t="n">
-        <v>-0.0542</v>
+        <v>-0.0359</v>
       </c>
       <c r="F73" s="16" t="n">
-        <v>-0.3101</v>
+        <v>-0.2967</v>
       </c>
       <c r="G73" s="17" t="n">
         <v>46281</v>
@@ -6655,13 +6655,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>17.8</v>
+        <v>18.08</v>
       </c>
       <c r="E74" s="9" t="n">
-        <v>0.3373</v>
+        <v>0.3584000000000001</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>-0.0557</v>
+        <v>-0.0408</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>46346</v>
@@ -6716,13 +6716,13 @@
         </is>
       </c>
       <c r="D75" s="15" t="n">
-        <v>505.72</v>
+        <v>509.68</v>
       </c>
       <c r="E75" s="20" t="n">
-        <v>0.0107</v>
+        <v>0.0186</v>
       </c>
       <c r="F75" s="20" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.08380000000000001</v>
       </c>
       <c r="G75" s="17" t="n">
         <v>46241</v>
@@ -6799,13 +6799,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>70.88</v>
+        <v>70.87</v>
       </c>
       <c r="E76" s="9" t="n">
-        <v>0.1049</v>
+        <v>0.1048</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>0.2439</v>
+        <v>0.2438</v>
       </c>
       <c r="G76" s="6" t="n"/>
       <c r="H76" s="12" t="inlineStr">
@@ -6824,7 +6824,7 @@
         <v>68</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>-0.04063205417607217</v>
+        <v>-0.04049668406942295</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="8" t="n"/>
@@ -6866,13 +6866,13 @@
         </is>
       </c>
       <c r="D77" s="15" t="n">
-        <v>127.61</v>
+        <v>128.07</v>
       </c>
       <c r="E77" s="20" t="n">
-        <v>0.08439999999999999</v>
+        <v>0.08839999999999999</v>
       </c>
       <c r="F77" s="20" t="n">
-        <v>0.09119999999999999</v>
+        <v>0.09519999999999999</v>
       </c>
       <c r="G77" s="17" t="n">
         <v>46310</v>
@@ -6931,13 +6931,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>131.52</v>
+        <v>132.32</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>-0.0603</v>
+        <v>-0.0546</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>0.0189</v>
+        <v>0.025</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>46308</v>
@@ -6969,7 +6969,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="9" t="n">
-        <v>0.06447688564476878</v>
+        <v>0.05804111245465544</v>
       </c>
       <c r="Q78" s="10" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         </is>
       </c>
       <c r="D79" s="15" t="n">
-        <v>349.11</v>
+        <v>350.15</v>
       </c>
       <c r="E79" s="20" t="n">
-        <v>0.0246</v>
+        <v>0.0276</v>
       </c>
       <c r="F79" s="20" t="n">
-        <v>0.127</v>
+        <v>0.1303</v>
       </c>
       <c r="G79" s="17" t="n">
         <v>46315</v>
@@ -7053,7 +7053,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="20" t="n">
-        <v>0.02546475322964105</v>
+        <v>0.02241896330144231</v>
       </c>
       <c r="N79" s="14" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="20" t="n">
-        <v>0.07129558018962501</v>
+        <v>0.06811366557189782</v>
       </c>
       <c r="Q79" s="21" t="inlineStr">
         <is>
@@ -7109,13 +7109,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>59.57</v>
+        <v>59.44</v>
       </c>
       <c r="E80" s="9" t="n">
-        <v>0.0315</v>
+        <v>0.0293</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>0.1578</v>
+        <v>0.1553</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>46310</v>
@@ -7144,7 +7144,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>-0.04314252140339098</v>
+        <v>-0.04104979811574694</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="8" t="n"/>
@@ -7186,13 +7186,13 @@
         </is>
       </c>
       <c r="D81" s="15" t="n">
-        <v>14.63</v>
-      </c>
-      <c r="E81" s="20" t="n">
-        <v>0.0052</v>
+        <v>14.54</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="F81" s="16" t="n">
-        <v>-0.2225</v>
+        <v>-0.227</v>
       </c>
       <c r="G81" s="17" t="n">
         <v>46240</v>
@@ -7247,13 +7247,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>388.55</v>
+        <v>390.12</v>
       </c>
       <c r="E82" s="9" t="n">
-        <v>0.1659</v>
+        <v>0.1706</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>0.06709999999999999</v>
+        <v>0.07139999999999999</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>46239</v>
@@ -7320,13 +7320,13 @@
         </is>
       </c>
       <c r="D83" s="15" t="n">
-        <v>62.53</v>
-      </c>
-      <c r="E83" s="16" t="n">
-        <v>-0.0016</v>
+        <v>64.23999999999999</v>
+      </c>
+      <c r="E83" s="20" t="n">
+        <v>0.0257</v>
       </c>
       <c r="F83" s="16" t="n">
-        <v>-0.4043</v>
+        <v>-0.388</v>
       </c>
       <c r="G83" s="17" t="n">
         <v>46239</v>
@@ -7381,13 +7381,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>52.98</v>
+        <v>53.73</v>
       </c>
       <c r="E84" s="9" t="n">
-        <v>0.0892</v>
+        <v>0.1046</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>0.1719</v>
+        <v>0.1885</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>46240</v>
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="D85" s="15" t="n">
-        <v>1018.3</v>
+        <v>1024.86</v>
       </c>
       <c r="E85" s="20" t="n">
-        <v>0.0069</v>
+        <v>0.0133</v>
       </c>
       <c r="F85" s="16" t="n">
-        <v>-0.0289</v>
+        <v>-0.0226</v>
       </c>
       <c r="G85" s="17" t="n">
         <v>46308</v>
@@ -7477,7 +7477,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="20" t="n">
-        <v>0.3011882549346951</v>
+        <v>0.2928595125187832</v>
       </c>
       <c r="N85" s="14" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="20" t="n">
-        <v>0.1882549346950801</v>
+        <v>0.180649064262436</v>
       </c>
       <c r="Q85" s="21" t="inlineStr">
         <is>
@@ -7529,13 +7529,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>123.47</v>
+        <v>128.34</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>-0.0795</v>
+        <v>-0.0432</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-0.1203</v>
+        <v>-0.08560000000000001</v>
       </c>
       <c r="G86" s="6" t="n"/>
       <c r="H86" s="12" t="inlineStr">
@@ -7580,13 +7580,13 @@
         </is>
       </c>
       <c r="D87" s="15" t="n">
-        <v>87.22</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>-0.1302</v>
+        <v>-0.1364</v>
       </c>
       <c r="F87" s="16" t="n">
-        <v>-0.0386</v>
+        <v>-0.0455</v>
       </c>
       <c r="G87" s="17" t="n"/>
       <c r="H87" s="23" t="inlineStr">
@@ -7631,13 +7631,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>107.17</v>
+        <v>108.27</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>-0.0717</v>
+        <v>-0.0622</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.1904</v>
+        <v>-0.1821</v>
       </c>
       <c r="G88" s="6" t="n">
         <v>46238</v>
@@ -7692,13 +7692,13 @@
         </is>
       </c>
       <c r="D89" s="15" t="n">
-        <v>151.8</v>
+        <v>156.27</v>
       </c>
       <c r="E89" s="20" t="n">
-        <v>0.233</v>
+        <v>0.2694</v>
       </c>
       <c r="F89" s="20" t="n">
-        <v>0.0472</v>
+        <v>0.078</v>
       </c>
       <c r="G89" s="17" t="n">
         <v>46233</v>
@@ -7753,13 +7753,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>154.57</v>
+        <v>154.24</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>0.1222</v>
+        <v>0.1198</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>0.1025</v>
+        <v>0.1001</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>46252</v>
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="D91" s="15" t="n">
-        <v>350.22</v>
+        <v>350.85</v>
       </c>
       <c r="E91" s="20" t="n">
-        <v>0.0699</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="F91" s="20" t="n">
-        <v>0.1809</v>
+        <v>0.183</v>
       </c>
       <c r="G91" s="17" t="n">
         <v>46308</v>
@@ -7863,7 +7863,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="16" t="n">
-        <v>-0.4403517788818457</v>
+        <v>-0.4413567051446488</v>
       </c>
       <c r="N91" s="14" t="inlineStr"/>
       <c r="O91" s="19" t="n"/>
@@ -7907,13 +7907,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>100.47</v>
+        <v>100.98</v>
       </c>
       <c r="E92" s="9" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>0.0575</v>
+        <v>0.06280000000000001</v>
       </c>
       <c r="G92" s="6" t="n">
         <v>46233</v>
@@ -7942,7 +7942,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="9" t="n">
-        <v>2.73245744998507</v>
+        <v>2.713606654783125</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="9" t="n">
-        <v>2.662784910918682</v>
+        <v>2.644285997227173</v>
       </c>
       <c r="Q92" s="10" t="inlineStr">
         <is>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="D93" s="15" t="n">
-        <v>354.65</v>
+        <v>355.87</v>
       </c>
       <c r="E93" s="20" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.079</v>
       </c>
       <c r="F93" s="20" t="n">
-        <v>0.1684</v>
+        <v>0.1724</v>
       </c>
       <c r="G93" s="17" t="n">
         <v>46317</v>
@@ -8044,7 +8044,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="16" t="n">
-        <v>-0.6757366417594811</v>
+        <v>-0.6768482872959227</v>
       </c>
       <c r="Q93" s="21" t="inlineStr">
         <is>
@@ -8093,13 +8093,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>573.72</v>
+        <v>577.35</v>
       </c>
       <c r="E94" s="9" t="n">
-        <v>0.1171</v>
+        <v>0.1241</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>0.1584</v>
+        <v>0.1658</v>
       </c>
       <c r="G94" s="6" t="n">
         <v>46233</v>
@@ -8128,7 +8128,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>-0.3620581468312069</v>
+        <v>-0.366069108859444</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="8" t="n"/>
@@ -8170,13 +8170,13 @@
         </is>
       </c>
       <c r="D95" s="15" t="n">
-        <v>1895.98</v>
+        <v>1886.16</v>
       </c>
       <c r="E95" s="16" t="n">
-        <v>-0.0292</v>
+        <v>-0.0342</v>
       </c>
       <c r="F95" s="20" t="n">
-        <v>0.0594</v>
+        <v>0.0539</v>
       </c>
       <c r="G95" s="17" t="n"/>
       <c r="H95" s="23" t="inlineStr">
@@ -8231,13 +8231,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>209.65</v>
+        <v>210.06</v>
       </c>
       <c r="E96" s="9" t="n">
-        <v>0.0029</v>
+        <v>0.0049</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.004500000000000001</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>46309</v>
@@ -8266,7 +8266,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="9" t="n">
-        <v>2.186262818984021</v>
+        <v>2.180043797010378</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="9" t="n">
-        <v>1.623419985690437</v>
+        <v>1.618299533466629</v>
       </c>
       <c r="Q96" s="10" t="inlineStr">
         <is>
@@ -8326,13 +8326,13 @@
         </is>
       </c>
       <c r="D97" s="15" t="n">
-        <v>113.69</v>
+        <v>113.95</v>
       </c>
       <c r="E97" s="20" t="n">
-        <v>0.0548</v>
+        <v>0.0572</v>
       </c>
       <c r="F97" s="20" t="n">
-        <v>0.1049</v>
+        <v>0.1074</v>
       </c>
       <c r="G97" s="17" t="n"/>
       <c r="H97" s="23" t="inlineStr">
@@ -8351,7 +8351,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="20" t="n">
-        <v>1.111003606297827</v>
+        <v>1.106186924089513</v>
       </c>
       <c r="N97" s="14" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="20" t="n">
-        <v>1.111003606297827</v>
+        <v>1.106186924089513</v>
       </c>
       <c r="Q97" s="21" t="inlineStr">
         <is>
@@ -8411,13 +8411,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>248.62</v>
+        <v>248.71</v>
       </c>
       <c r="E98" s="9" t="n">
-        <v>0.0098</v>
+        <v>0.0101</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>0.1507</v>
+        <v>0.1511</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>46310</v>
@@ -8446,7 +8446,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>-0.5454911109323466</v>
+        <v>-0.5456555828072857</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="5" t="n">
-        <v>-0.5414689083742258</v>
+        <v>-0.5416348357524828</v>
       </c>
       <c r="Q98" s="10" t="inlineStr"/>
       <c r="R98" s="8" t="n"/>
@@ -8496,13 +8496,13 @@
         </is>
       </c>
       <c r="D99" s="15" t="n">
-        <v>22.57</v>
+        <v>22.12</v>
       </c>
       <c r="E99" s="16" t="n">
-        <v>-0.1759</v>
+        <v>-0.1921</v>
       </c>
       <c r="F99" s="16" t="n">
-        <v>-0.2012</v>
+        <v>-0.217</v>
       </c>
       <c r="G99" s="17" t="n">
         <v>46239</v>
@@ -8557,13 +8557,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>14.09</v>
+        <v>14.11</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>0.0207</v>
+        <v>0.0225</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>0.1414</v>
+        <v>0.1434</v>
       </c>
       <c r="G100" s="6" t="n">
         <v>46323</v>
@@ -8618,13 +8618,13 @@
         </is>
       </c>
       <c r="D101" s="15" t="n">
-        <v>102.45</v>
+        <v>103.04</v>
       </c>
       <c r="E101" s="20" t="n">
-        <v>0.1681</v>
+        <v>0.1748</v>
       </c>
       <c r="F101" s="20" t="n">
-        <v>0.16</v>
+        <v>0.1667</v>
       </c>
       <c r="G101" s="17" t="n">
         <v>46323</v>
@@ -8653,7 +8653,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="20" t="n">
-        <v>1.781844802342606</v>
+        <v>1.765916149068323</v>
       </c>
       <c r="N101" s="14" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="20" t="n">
-        <v>1.781844802342606</v>
+        <v>1.765916149068323</v>
       </c>
       <c r="Q101" s="21" t="inlineStr">
         <is>
@@ -8705,13 +8705,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>410.05</v>
+        <v>415</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0771</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>0.0113</v>
+        <v>0.0236</v>
       </c>
       <c r="G102" s="6" t="n"/>
       <c r="H102" s="12" t="inlineStr">
@@ -8770,13 +8770,13 @@
         </is>
       </c>
       <c r="D103" s="15" t="n">
-        <v>51.96</v>
+        <v>52.01</v>
       </c>
       <c r="E103" s="20" t="n">
-        <v>0.0429</v>
+        <v>0.044</v>
       </c>
       <c r="F103" s="20" t="n">
-        <v>0.1085</v>
+        <v>0.1097</v>
       </c>
       <c r="G103" s="17" t="n">
         <v>46311</v>
@@ -8831,13 +8831,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>362.92</v>
+        <v>366.27</v>
       </c>
       <c r="E104" s="9" t="n">
-        <v>0.0578</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>0.1244</v>
+        <v>0.1348</v>
       </c>
       <c r="G104" s="6" t="n"/>
       <c r="H104" s="12" t="inlineStr">
@@ -8856,7 +8856,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="9" t="n">
-        <v>0.44659980160917</v>
+        <v>0.4333688262756983</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="9" t="n">
-        <v>0.496197509092913</v>
+        <v>0.4825129003194366</v>
       </c>
       <c r="Q104" s="10" t="inlineStr">
         <is>
@@ -8912,13 +8912,13 @@
         </is>
       </c>
       <c r="D105" s="15" t="n">
-        <v>73.18000000000001</v>
+        <v>73.38</v>
       </c>
       <c r="E105" s="20" t="n">
-        <v>0.03759999999999999</v>
+        <v>0.0404</v>
       </c>
       <c r="F105" s="20" t="n">
-        <v>0.1373</v>
+        <v>0.1403</v>
       </c>
       <c r="G105" s="17" t="n">
         <v>46314</v>
@@ -8947,7 +8947,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="20" t="n">
-        <v>4.629953539218365</v>
+        <v>4.614608885254838</v>
       </c>
       <c r="N105" s="14" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="20" t="n">
-        <v>3.78272752118065</v>
+        <v>3.769692014172799</v>
       </c>
       <c r="Q105" s="21" t="inlineStr">
         <is>
@@ -9003,13 +9003,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>81.68000000000001</v>
+        <v>82.59</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0867</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>0.07339999999999999</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="G106" s="6" t="n">
         <v>46239</v>
@@ -9038,7 +9038,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>-0.1674828599412342</v>
+        <v>-0.1766557694636155</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="5" t="n">
-        <v>-0.1674828599412342</v>
+        <v>-0.1766557694636155</v>
       </c>
       <c r="Q106" s="10" t="inlineStr">
         <is>
@@ -9094,13 +9094,13 @@
         </is>
       </c>
       <c r="D107" s="15" t="n">
-        <v>258.16</v>
+        <v>257.41</v>
       </c>
       <c r="E107" s="20" t="n">
-        <v>0.0259</v>
+        <v>0.0229</v>
       </c>
       <c r="F107" s="20" t="n">
-        <v>0.2124</v>
+        <v>0.2089</v>
       </c>
       <c r="G107" s="17" t="n">
         <v>46234</v>
@@ -9129,7 +9129,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="20" t="n">
-        <v>0.1427022001859311</v>
+        <v>0.1460316227030806</v>
       </c>
       <c r="N107" s="14" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="16" t="n">
-        <v>-0.04710257204834221</v>
+        <v>-0.04432617225438026</v>
       </c>
       <c r="Q107" s="21" t="inlineStr">
         <is>
@@ -9177,13 +9177,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>105.46</v>
+        <v>105.61</v>
       </c>
       <c r="E108" s="9" t="n">
-        <v>0.1623</v>
+        <v>0.1639</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>0.2015</v>
+        <v>0.2031</v>
       </c>
       <c r="G108" s="6" t="n">
         <v>46316</v>
@@ -9212,7 +9212,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="9" t="n">
-        <v>0.0620140337568747</v>
+        <v>0.06050563393618029</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="9" t="n">
-        <v>0.1378721790252229</v>
+        <v>0.1362560363601932</v>
       </c>
       <c r="Q108" s="10" t="inlineStr">
         <is>
@@ -9276,13 +9276,13 @@
         </is>
       </c>
       <c r="D109" s="15" t="n">
-        <v>382.39</v>
+        <v>387.64</v>
       </c>
       <c r="E109" s="20" t="n">
-        <v>0.05599999999999999</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="F109" s="20" t="n">
-        <v>0.1618</v>
+        <v>0.1778</v>
       </c>
       <c r="G109" s="17" t="n">
         <v>46238</v>
@@ -9311,7 +9311,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="20" t="n">
-        <v>0.01990114804257437</v>
+        <v>0.006088123000722355</v>
       </c>
       <c r="N109" s="14" t="inlineStr">
         <is>
@@ -9359,13 +9359,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>165.05</v>
+        <v>165.45</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>0.0907</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>0.1357</v>
+        <v>0.1384</v>
       </c>
       <c r="G110" s="6" t="n">
         <v>46240</v>
@@ -9394,7 +9394,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="5" t="n">
-        <v>-0.02453801878218728</v>
+        <v>-0.02689634330613472</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="9" t="n">
-        <v>0.09057861254165397</v>
+        <v>0.08794197642792392</v>
       </c>
       <c r="Q110" s="10" t="inlineStr">
         <is>
@@ -9446,13 +9446,13 @@
         </is>
       </c>
       <c r="D111" s="15" t="n">
-        <v>45.1</v>
+        <v>46</v>
       </c>
       <c r="E111" s="20" t="n">
-        <v>0.0567</v>
+        <v>0.07780000000000001</v>
       </c>
       <c r="F111" s="16" t="n">
-        <v>-0.06</v>
+        <v>-0.0413</v>
       </c>
       <c r="G111" s="17" t="n"/>
       <c r="H111" s="23" t="inlineStr">
@@ -9471,7 +9471,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="20" t="n">
-        <v>0.2195121951219512</v>
+        <v>0.1956521739130435</v>
       </c>
       <c r="N111" s="14" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="20" t="n">
-        <v>0.4412416851441241</v>
+        <v>0.4130434782608696</v>
       </c>
       <c r="Q111" s="21" t="inlineStr">
         <is>
@@ -9523,13 +9523,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>312.35</v>
+        <v>312.23</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>0.1038</v>
+        <v>0.1034</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>0.1801</v>
+        <v>0.1796</v>
       </c>
       <c r="G112" s="6" t="n">
         <v>46239</v>
@@ -9558,7 +9558,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="9" t="n">
-        <v>0.05970866015687522</v>
+        <v>0.06011594017230881</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0.05650712341924116</v>
+        <v>0.05691317298145591</v>
       </c>
       <c r="Q112" s="10" t="inlineStr">
         <is>
@@ -9618,13 +9618,13 @@
         </is>
       </c>
       <c r="D113" s="15" t="n">
-        <v>104.95</v>
+        <v>105.22</v>
       </c>
       <c r="E113" s="20" t="n">
-        <v>0.0145</v>
+        <v>0.0171</v>
       </c>
       <c r="F113" s="20" t="n">
-        <v>0.1581</v>
+        <v>0.1611</v>
       </c>
       <c r="G113" s="17" t="n">
         <v>46239</v>
@@ -9653,7 +9653,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="20" t="n">
-        <v>0.1719866603144354</v>
+        <v>0.1689792815054172</v>
       </c>
       <c r="N113" s="14" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="20" t="n">
-        <v>0.2386850881372082</v>
+        <v>0.2355065576886524</v>
       </c>
       <c r="Q113" s="21" t="inlineStr">
         <is>
@@ -9705,13 +9705,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>195.79</v>
+        <v>196.17</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>0.0279</v>
+        <v>0.0299</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>0.0885</v>
+        <v>0.0906</v>
       </c>
       <c r="G114" s="6" t="n">
         <v>46315</v>
@@ -9740,7 +9740,7 @@
         <v>212</v>
       </c>
       <c r="M114" s="9" t="n">
-        <v>0.08279278819142964</v>
+        <v>0.08069531528776068</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="9" t="n">
-        <v>0.04704019612850507</v>
+        <v>0.04501197940561764</v>
       </c>
       <c r="Q114" s="10" t="inlineStr">
         <is>
@@ -9796,13 +9796,13 @@
         </is>
       </c>
       <c r="D115" s="15" t="n">
-        <v>73.53</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="E115" s="20" t="n">
-        <v>0.09179999999999999</v>
+        <v>0.1068</v>
       </c>
       <c r="F115" s="16" t="n">
-        <v>-0.0179</v>
+        <v>-0.0044</v>
       </c>
       <c r="G115" s="17" t="n">
         <v>46233</v>
@@ -9831,7 +9831,7 @@
         <v>85</v>
       </c>
       <c r="M115" s="20" t="n">
-        <v>0.1559907520739834</v>
+        <v>0.140327341024953</v>
       </c>
       <c r="N115" s="14" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="20" t="n">
-        <v>0.2239902080783354</v>
+        <v>0.2074054199087737</v>
       </c>
       <c r="Q115" s="21" t="inlineStr">
         <is>
@@ -9883,13 +9883,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>129.66</v>
+        <v>131.28</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>0.0263</v>
-      </c>
-      <c r="F116" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0391</v>
+      </c>
+      <c r="F116" s="9" t="n">
+        <v>0.0014</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>46238</v>
@@ -9918,7 +9918,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="9" t="n">
-        <v>0.2725590004627488</v>
+        <v>0.2568555758683729</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="8" t="n"/>
@@ -9966,13 +9966,13 @@
         </is>
       </c>
       <c r="D117" s="15" t="n">
-        <v>556.51</v>
+        <v>558.8</v>
       </c>
       <c r="E117" s="20" t="n">
-        <v>0.0571</v>
+        <v>0.06150000000000001</v>
       </c>
       <c r="F117" s="16" t="n">
-        <v>-0.0181</v>
+        <v>-0.0141</v>
       </c>
       <c r="G117" s="17" t="n">
         <v>46238</v>
@@ -10037,13 +10037,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>348.92</v>
+        <v>352.97</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>-0.1226</v>
+        <v>-0.1124</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>-0.1536</v>
+        <v>-0.1438</v>
       </c>
       <c r="G118" s="6" t="n">
         <v>46315</v>
@@ -10072,7 +10072,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="9" t="n">
-        <v>0.3957354121288547</v>
+        <v>0.3797206561464146</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>375</v>
       </c>
       <c r="P118" s="9" t="n">
-        <v>0.07474492720394355</v>
+        <v>0.06241323625237264</v>
       </c>
       <c r="Q118" s="10" t="inlineStr">
         <is>
@@ -10128,13 +10128,13 @@
         </is>
       </c>
       <c r="D119" s="15" t="n">
-        <v>256.13</v>
+        <v>255.82</v>
       </c>
       <c r="E119" s="20" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0073</v>
       </c>
       <c r="F119" s="20" t="n">
-        <v>0.1459</v>
+        <v>0.1446</v>
       </c>
       <c r="G119" s="17" t="n">
         <v>46315</v>
@@ -10163,7 +10163,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="20" t="n">
-        <v>0.06196072307031587</v>
+        <v>0.06324759596591356</v>
       </c>
       <c r="N119" s="14" t="inlineStr"/>
       <c r="O119" s="19" t="n"/>
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1163.12</v>
+        <v>1154.97</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>-0.0303</v>
+        <v>-0.0371</v>
       </c>
       <c r="F120" s="9" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0672</v>
       </c>
       <c r="G120" s="6" t="n">
         <v>46239</v>
@@ -10250,7 +10250,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="9" t="n">
-        <v>0.1004883417016302</v>
+        <v>0.1082538940405378</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -10310,13 +10310,13 @@
         </is>
       </c>
       <c r="D121" s="15" t="n">
-        <v>85.31</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="E121" s="20" t="n">
-        <v>0.09050000000000001</v>
+        <v>0.0956</v>
       </c>
       <c r="F121" s="20" t="n">
-        <v>0.1531</v>
+        <v>0.1586</v>
       </c>
       <c r="G121" s="17" t="n">
         <v>46266</v>
@@ -10345,7 +10345,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="20" t="n">
-        <v>0.1956394326573672</v>
+        <v>0.1900595029751488</v>
       </c>
       <c r="N121" s="14" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="20" t="n">
-        <v>0.2308052983237604</v>
+        <v>0.2250612530626532</v>
       </c>
       <c r="Q121" s="21" t="inlineStr">
         <is>
@@ -10397,13 +10397,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>128.98</v>
+        <v>129.79</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>0.0037</v>
+        <v>0.01</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>0.1199</v>
+        <v>0.1269</v>
       </c>
       <c r="G122" s="6" t="n">
         <v>46238</v>
@@ -10432,7 +10432,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="9" t="n">
-        <v>0.1629710032563189</v>
+        <v>0.1557130749672549</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="8" t="n"/>
@@ -10476,13 +10476,13 @@
         </is>
       </c>
       <c r="D123" s="15" t="n">
-        <v>157.42</v>
+        <v>158.44</v>
       </c>
       <c r="E123" s="20" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.011</v>
       </c>
       <c r="F123" s="20" t="n">
-        <v>0.0806</v>
+        <v>0.0876</v>
       </c>
       <c r="G123" s="17" t="n">
         <v>46322</v>
@@ -10555,13 +10555,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>24.68</v>
+        <v>24.91</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>0.0251</v>
+        <v>0.0345</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>-0.0369</v>
+        <v>-0.0281</v>
       </c>
       <c r="G124" s="6" t="n">
         <v>46238</v>
@@ -10590,7 +10590,7 @@
         <v>28</v>
       </c>
       <c r="M124" s="9" t="n">
-        <v>0.1345218800648298</v>
+        <v>0.1240465676435167</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="8" t="n"/>
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="D125" s="15" t="n">
-        <v>345.93</v>
+        <v>348.04</v>
       </c>
       <c r="E125" s="20" t="n">
-        <v>0.0987</v>
+        <v>0.1055</v>
       </c>
       <c r="F125" s="20" t="n">
-        <v>0.1552</v>
+        <v>0.1622</v>
       </c>
       <c r="G125" s="17" t="n">
         <v>46233</v>
@@ -10669,7 +10669,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="20" t="n">
-        <v>0.2083369467811407</v>
+        <v>0.2010113780025284</v>
       </c>
       <c r="N125" s="14" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="20" t="n">
-        <v>0.01176538606076372</v>
+        <v>0.005631536604987874</v>
       </c>
       <c r="Q125" s="21" t="inlineStr">
         <is>
@@ -10725,13 +10725,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>567.66</v>
+        <v>576.77</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>0.1322</v>
+        <v>0.1504</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>0.149</v>
+        <v>0.1675</v>
       </c>
       <c r="G126" s="6" t="n">
         <v>46323</v>
@@ -10760,7 +10760,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="9" t="n">
-        <v>0.0833949899587782</v>
+        <v>0.06628292040154658</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10770,8 +10770,8 @@
       <c r="O126" s="8" t="n">
         <v>570</v>
       </c>
-      <c r="P126" s="9" t="n">
-        <v>0.004122185815452969</v>
+      <c r="P126" s="5" t="n">
+        <v>-0.01173778109124951</v>
       </c>
       <c r="Q126" s="10" t="inlineStr">
         <is>
@@ -10820,13 +10820,13 @@
         </is>
       </c>
       <c r="D127" s="15" t="n">
-        <v>423.74</v>
+        <v>421.47</v>
       </c>
       <c r="E127" s="20" t="n">
-        <v>0.0195</v>
+        <v>0.0141</v>
       </c>
       <c r="F127" s="20" t="n">
-        <v>0.1155</v>
+        <v>0.1095</v>
       </c>
       <c r="G127" s="17" t="n">
         <v>46322</v>
@@ -10855,7 +10855,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="20" t="n">
-        <v>0.2413272289611554</v>
+        <v>0.2480129072057322</v>
       </c>
       <c r="N127" s="14" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="20" t="n">
-        <v>0.1327700948694954</v>
+        <v>0.1388710940280446</v>
       </c>
       <c r="Q127" s="21" t="inlineStr">
         <is>
@@ -10911,13 +10911,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>75.59</v>
+        <v>76.03</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>0.0519</v>
+        <v>0.058</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0197</v>
       </c>
       <c r="G128" s="6" t="n">
         <v>46240</v>
@@ -10990,13 +10990,13 @@
         </is>
       </c>
       <c r="D129" s="15" t="n">
-        <v>259.4</v>
+        <v>263.87</v>
       </c>
       <c r="E129" s="20" t="n">
-        <v>0.1583</v>
+        <v>0.1783</v>
       </c>
       <c r="F129" s="20" t="n">
-        <v>0.1098</v>
+        <v>0.1289</v>
       </c>
       <c r="G129" s="17" t="n"/>
       <c r="H129" s="23" t="inlineStr">
@@ -11015,7 +11015,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="16" t="n">
-        <v>-0.04394757131842705</v>
+        <v>-0.06014325235911624</v>
       </c>
       <c r="N129" s="14" t="inlineStr"/>
       <c r="O129" s="19" t="n"/>
@@ -11071,13 +11071,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>106.16</v>
+        <v>107.13</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>-0.1131</v>
+        <v>-0.105</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>-0.0524</v>
+        <v>-0.0437</v>
       </c>
       <c r="G130" s="6" t="n">
         <v>46233</v>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="D131" s="15" t="n">
-        <v>238.04</v>
+        <v>240.01</v>
       </c>
       <c r="E131" s="16" t="n">
-        <v>-0.0161</v>
+        <v>-0.008</v>
       </c>
       <c r="F131" s="20" t="n">
-        <v>0.06570000000000001</v>
+        <v>0.0745</v>
       </c>
       <c r="G131" s="17" t="n">
         <v>46238</v>
@@ -11193,13 +11193,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>219.6</v>
+        <v>220.9</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>0.0145</v>
+        <v>0.0205</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>-0.021</v>
+        <v>-0.0152</v>
       </c>
       <c r="G132" s="6" t="n"/>
       <c r="H132" s="12" t="inlineStr">
@@ -11218,7 +11218,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="9" t="n">
-        <v>0.1384335154826958</v>
+        <v>0.1317338162064282</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="8" t="n"/>
@@ -11262,13 +11262,13 @@
         </is>
       </c>
       <c r="D133" s="15" t="n">
-        <v>151.69</v>
+        <v>154.77</v>
       </c>
       <c r="E133" s="20" t="n">
-        <v>0.1076</v>
+        <v>0.1301</v>
       </c>
       <c r="F133" s="16" t="n">
-        <v>-0.0517</v>
+        <v>-0.03240000000000001</v>
       </c>
       <c r="G133" s="17" t="n">
         <v>46238</v>
@@ -11333,13 +11333,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>807.8099999999999</v>
+        <v>809.14</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>-0.2414</v>
+        <v>-0.2402</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>-0.0665</v>
+        <v>-0.065</v>
       </c>
       <c r="G134" s="6" t="n">
         <v>46238</v>
@@ -11368,7 +11368,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="9" t="n">
-        <v>0.4297916589296989</v>
+        <v>0.4274414810786761</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="9" t="n">
-        <v>0.3654200864064571</v>
+        <v>0.3631757174283808</v>
       </c>
       <c r="Q134" s="10" t="inlineStr">
         <is>
@@ -11420,13 +11420,13 @@
         </is>
       </c>
       <c r="D135" s="15" t="n">
-        <v>634.28</v>
+        <v>632.98</v>
       </c>
       <c r="E135" s="16" t="n">
-        <v>-0.1107</v>
+        <v>-0.1125</v>
       </c>
       <c r="F135" s="16" t="n">
-        <v>-0.0143</v>
+        <v>-0.0163</v>
       </c>
       <c r="G135" s="17" t="n">
         <v>46238</v>
@@ -11455,7 +11455,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="20" t="n">
-        <v>0.3779403418048812</v>
+        <v>0.3807703244968245</v>
       </c>
       <c r="N135" s="14" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="20" t="n">
-        <v>0.3322192091820648</v>
+        <v>0.3349552908464722</v>
       </c>
       <c r="Q135" s="21" t="inlineStr">
         <is>
@@ -11594,13 +11594,13 @@
         </is>
       </c>
       <c r="D137" s="15" t="n">
-        <v>596.86</v>
+        <v>599.47</v>
       </c>
       <c r="E137" s="16" t="n">
-        <v>-0.0591</v>
+        <v>-0.055</v>
       </c>
       <c r="F137" s="20" t="n">
-        <v>0.1003</v>
+        <v>0.1052</v>
       </c>
       <c r="G137" s="17" t="n">
         <v>46254</v>
@@ -11629,7 +11629,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="20" t="n">
-        <v>0.2565760814931474</v>
+        <v>0.2511051428762073</v>
       </c>
       <c r="N137" s="14" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="20" t="n">
-        <v>0.07443956706765396</v>
+        <v>0.06976162276677721</v>
       </c>
       <c r="Q137" s="21" t="inlineStr">
         <is>
@@ -11681,13 +11681,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>148.84</v>
+        <v>148.64</v>
       </c>
       <c r="E138" s="9" t="n">
-        <v>0.0397</v>
+        <v>0.0384</v>
       </c>
       <c r="F138" s="9" t="n">
-        <v>0.0508</v>
+        <v>0.0493</v>
       </c>
       <c r="G138" s="6" t="n">
         <v>46238</v>
@@ -11723,7 +11723,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="9" t="n">
-        <v>0.2429454447729105</v>
+        <v>0.2446178686759958</v>
       </c>
       <c r="Q138" s="10" t="inlineStr">
         <is>
@@ -11762,13 +11762,13 @@
         </is>
       </c>
       <c r="D139" s="15" t="n">
-        <v>383.97</v>
+        <v>386.89</v>
       </c>
       <c r="E139" s="16" t="n">
-        <v>-0.0989</v>
+        <v>-0.09210000000000002</v>
       </c>
       <c r="F139" s="16" t="n">
-        <v>-0.0403</v>
+        <v>-0.033</v>
       </c>
       <c r="G139" s="17" t="n">
         <v>46234</v>
@@ -11804,7 +11804,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="20" t="n">
-        <v>0.1797796702867411</v>
+        <v>0.1708754426322728</v>
       </c>
       <c r="Q139" s="21" t="inlineStr">
         <is>
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>46.61</v>
+        <v>46.66</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>-0.0296</v>
+        <v>-0.0285</v>
       </c>
       <c r="F140" s="9" t="n">
-        <v>0.0596</v>
+        <v>0.0607</v>
       </c>
       <c r="G140" s="6" t="n">
         <v>46309</v>
@@ -11924,13 +11924,13 @@
         </is>
       </c>
       <c r="D141" s="15" t="n">
-        <v>306.52</v>
+        <v>308.55</v>
       </c>
       <c r="E141" s="16" t="n">
-        <v>-0.0211</v>
+        <v>-0.0146</v>
       </c>
       <c r="F141" s="16" t="n">
-        <v>-0.0944</v>
+        <v>-0.0885</v>
       </c>
       <c r="G141" s="17" t="n">
         <v>46282</v>
@@ -11959,7 +11959,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="20" t="n">
-        <v>0.3865326895471748</v>
+        <v>0.3774104683195592</v>
       </c>
       <c r="N141" s="14" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="20" t="n">
-        <v>0.05376484405585286</v>
+        <v>0.04683195592286497</v>
       </c>
       <c r="Q141" s="21" t="inlineStr">
         <is>
@@ -12011,13 +12011,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>226.1</v>
+        <v>226.36</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>-0.0473</v>
+        <v>-0.0462</v>
       </c>
       <c r="F142" s="9" t="n">
-        <v>0.0076</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="G142" s="6" t="n">
         <v>46244</v>
@@ -12046,7 +12046,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="9" t="n">
-        <v>0.2605042016806723</v>
+        <v>0.2590563703834599</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="8" t="n"/>
@@ -12094,13 +12094,13 @@
         </is>
       </c>
       <c r="D143" s="15" t="n">
-        <v>1685.28</v>
+        <v>1697.84</v>
       </c>
       <c r="E143" s="16" t="n">
-        <v>-0.1497</v>
+        <v>-0.1433</v>
       </c>
       <c r="F143" s="16" t="n">
-        <v>-0.0574</v>
+        <v>-0.0504</v>
       </c>
       <c r="G143" s="17" t="n">
         <v>46317</v>
@@ -12155,13 +12155,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>49.35</v>
+        <v>50.07</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>-0.0581</v>
+        <v>-0.0443</v>
       </c>
       <c r="F144" s="9" t="n">
-        <v>0.06</v>
+        <v>0.0756</v>
       </c>
       <c r="G144" s="6" t="n">
         <v>46241</v>
@@ -12216,13 +12216,13 @@
         </is>
       </c>
       <c r="D145" s="15" t="n">
-        <v>379.22</v>
+        <v>382.2</v>
       </c>
       <c r="E145" s="20" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0789</v>
       </c>
       <c r="F145" s="20" t="n">
-        <v>0.118</v>
+        <v>0.1268</v>
       </c>
       <c r="G145" s="17" t="n"/>
       <c r="H145" s="23" t="inlineStr">
@@ -12241,7 +12241,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="20" t="n">
-        <v>0.0547966879383998</v>
+        <v>0.04657247514390375</v>
       </c>
       <c r="N145" s="14" t="inlineStr"/>
       <c r="O145" s="19" t="n"/>
@@ -12293,13 +12293,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>353.52</v>
+        <v>355.04</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>-0.0541</v>
+        <v>-0.05</v>
       </c>
       <c r="F146" s="9" t="n">
-        <v>0.0891</v>
+        <v>0.09380000000000001</v>
       </c>
       <c r="G146" s="6" t="n">
         <v>46315</v>
@@ -12328,7 +12328,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="9" t="n">
-        <v>0.1031907671418874</v>
+        <v>0.09846777827850377</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="8" t="n"/>
@@ -12380,13 +12380,13 @@
         </is>
       </c>
       <c r="D147" s="15" t="n">
-        <v>968.91</v>
+        <v>981.98</v>
       </c>
       <c r="E147" s="16" t="n">
-        <v>-0.1753</v>
+        <v>-0.1642</v>
       </c>
       <c r="F147" s="20" t="n">
-        <v>0.0193</v>
+        <v>0.0331</v>
       </c>
       <c r="G147" s="17" t="n">
         <v>46316</v>
@@ -12415,7 +12415,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="20" t="n">
-        <v>0.2993982929271037</v>
+        <v>0.2821035051630379</v>
       </c>
       <c r="N147" s="14" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="20" t="n">
-        <v>0.3933182648543209</v>
+        <v>0.3747734169738691</v>
       </c>
       <c r="Q147" s="21" t="inlineStr">
         <is>
@@ -12471,13 +12471,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1347.39</v>
+        <v>1355.49</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0036</v>
       </c>
       <c r="F148" s="9" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.09050000000000001</v>
       </c>
       <c r="G148" s="6" t="n">
         <v>46238</v>
@@ -12546,13 +12546,13 @@
         </is>
       </c>
       <c r="D149" s="15" t="n">
-        <v>239.05</v>
+        <v>241.91</v>
       </c>
       <c r="E149" s="20" t="n">
-        <v>0.0677</v>
+        <v>0.08039999999999999</v>
       </c>
       <c r="F149" s="16" t="n">
-        <v>-0.0364</v>
+        <v>-0.0249</v>
       </c>
       <c r="G149" s="17" t="n">
         <v>46317</v>
@@ -12607,13 +12607,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>470.43</v>
+        <v>473.69</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>-0.1009</v>
+        <v>-0.0946</v>
       </c>
       <c r="F150" s="9" t="n">
-        <v>0.0162</v>
+        <v>0.0232</v>
       </c>
       <c r="G150" s="6" t="n"/>
       <c r="H150" s="12" t="inlineStr">
@@ -12664,13 +12664,13 @@
         </is>
       </c>
       <c r="D151" s="15" t="n">
-        <v>283.11</v>
+        <v>283.7</v>
       </c>
       <c r="E151" s="20" t="n">
-        <v>0.0467</v>
+        <v>0.0489</v>
       </c>
       <c r="F151" s="20" t="n">
-        <v>0.1517</v>
+        <v>0.1541</v>
       </c>
       <c r="G151" s="17" t="n"/>
       <c r="H151" s="23" t="inlineStr">
@@ -12692,7 +12692,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="16" t="n">
-        <v>-0.03924269718483986</v>
+        <v>-0.04124074726824106</v>
       </c>
       <c r="Q151" s="21" t="inlineStr">
         <is>
@@ -12745,13 +12745,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>265.44</v>
+        <v>271.9</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>-0.08650000000000001</v>
+        <v>-0.0643</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>-0.1426</v>
+        <v>-0.1217</v>
       </c>
       <c r="G152" s="6" t="n"/>
       <c r="H152" s="12" t="inlineStr">
@@ -12806,13 +12806,13 @@
         </is>
       </c>
       <c r="D153" s="15" t="n">
-        <v>411.89</v>
+        <v>417.45</v>
       </c>
       <c r="E153" s="16" t="n">
-        <v>-0.2811</v>
+        <v>-0.2714</v>
       </c>
       <c r="F153" s="16" t="n">
-        <v>-0.1709</v>
+        <v>-0.1597</v>
       </c>
       <c r="G153" s="17" t="n"/>
       <c r="H153" s="23" t="inlineStr">
@@ -12857,13 +12857,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>559.41</v>
+        <v>574.11</v>
       </c>
       <c r="E154" s="9" t="n">
-        <v>0.098</v>
+        <v>0.1269</v>
       </c>
       <c r="F154" s="9" t="n">
-        <v>0.08310000000000001</v>
+        <v>0.1115</v>
       </c>
       <c r="G154" s="6" t="n">
         <v>46315</v>
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="D155" s="15" t="n">
-        <v>206.28</v>
+        <v>212.47</v>
       </c>
       <c r="E155" s="16" t="n">
-        <v>-0.0476</v>
+        <v>-0.0191</v>
       </c>
       <c r="F155" s="16" t="n">
-        <v>-0.0974</v>
+        <v>-0.0703</v>
       </c>
       <c r="G155" s="17" t="n"/>
       <c r="H155" s="23" t="inlineStr">
@@ -12949,7 +12949,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="20" t="n">
-        <v>1.787473337211557</v>
+        <v>1.706264413799595</v>
       </c>
       <c r="N155" s="14" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="20" t="n">
-        <v>0.1489237929028505</v>
+        <v>0.115451593166094</v>
       </c>
       <c r="Q155" s="21" t="inlineStr">
         <is>
@@ -13009,13 +13009,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>114.94</v>
+        <v>116.33</v>
       </c>
       <c r="E156" s="9" t="n">
-        <v>0.1689</v>
+        <v>0.1831</v>
       </c>
       <c r="F156" s="9" t="n">
-        <v>0.122</v>
+        <v>0.1356</v>
       </c>
       <c r="G156" s="6" t="n">
         <v>46294</v>
@@ -13044,7 +13044,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="9" t="n">
-        <v>1.175047851052723</v>
+        <v>1.14905871228402</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="8" t="n"/>
@@ -13088,13 +13088,13 @@
         </is>
       </c>
       <c r="D157" s="15" t="n">
-        <v>132.02</v>
+        <v>133.76</v>
       </c>
       <c r="E157" s="20" t="n">
-        <v>0.09910000000000001</v>
+        <v>0.1136</v>
       </c>
       <c r="F157" s="20" t="n">
-        <v>0.206</v>
+        <v>0.2219</v>
       </c>
       <c r="G157" s="17" t="n"/>
       <c r="H157" s="23" t="inlineStr">
@@ -13113,7 +13113,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="16" t="n">
-        <v>-0.280412058778973</v>
+        <v>-0.2897727272727272</v>
       </c>
       <c r="N157" s="14" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="20" t="n">
-        <v>0.05287077715497644</v>
+        <v>0.03917464114832543</v>
       </c>
       <c r="Q157" s="21" t="inlineStr">
         <is>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>953.11</v>
+        <v>962.79</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>-0.0256</v>
+        <v>-0.0157</v>
       </c>
       <c r="F158" s="9" t="n">
-        <v>0.1577</v>
+        <v>0.1694</v>
       </c>
       <c r="G158" s="6" t="n">
         <v>46240</v>
@@ -13204,7 +13204,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="5" t="n">
-        <v>-0.8688503950226102</v>
+        <v>-0.8701689880451604</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="9" t="n">
-        <v>0.116345437567542</v>
+        <v>0.1051215737595945</v>
       </c>
       <c r="Q158" s="10" t="inlineStr">
         <is>
@@ -13260,13 +13260,13 @@
         </is>
       </c>
       <c r="D159" s="15" t="n">
-        <v>561.3</v>
+        <v>561.9</v>
       </c>
       <c r="E159" s="16" t="n">
-        <v>-0.1285</v>
+        <v>-0.1276</v>
       </c>
       <c r="F159" s="16" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0075</v>
       </c>
       <c r="G159" s="17" t="n">
         <v>46234</v>
@@ -13341,13 +13341,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>473.54</v>
+        <v>471.01</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>-0.0435</v>
+        <v>-0.0486</v>
       </c>
       <c r="F160" s="9" t="n">
-        <v>0.0368</v>
+        <v>0.0313</v>
       </c>
       <c r="G160" s="6" t="n">
         <v>46238</v>
@@ -13402,13 +13402,13 @@
         </is>
       </c>
       <c r="D161" s="15" t="n">
-        <v>37.67</v>
+        <v>38.35</v>
       </c>
       <c r="E161" s="16" t="n">
-        <v>-0.0975</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="F161" s="16" t="n">
-        <v>-0.1867</v>
+        <v>-0.1721</v>
       </c>
       <c r="G161" s="17" t="n">
         <v>46323</v>
@@ -13477,13 +13477,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>210.79</v>
+        <v>214.38</v>
       </c>
       <c r="E162" s="9" t="n">
-        <v>0.111</v>
+        <v>0.1299</v>
       </c>
       <c r="F162" s="9" t="n">
-        <v>0.2086</v>
+        <v>0.2292</v>
       </c>
       <c r="G162" s="6" t="n">
         <v>46322</v>
@@ -13556,13 +13556,13 @@
         </is>
       </c>
       <c r="D163" s="15" t="n">
-        <v>42.91</v>
+        <v>42.94</v>
       </c>
       <c r="E163" s="16" t="n">
-        <v>-0.0454</v>
+        <v>-0.0447</v>
       </c>
       <c r="F163" s="16" t="n">
-        <v>-0.1134</v>
+        <v>-0.1128</v>
       </c>
       <c r="G163" s="17" t="n">
         <v>46239</v>
@@ -13617,13 +13617,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>444.48</v>
+        <v>440.28</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>-0.095</v>
+        <v>-0.1036</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>-0.0089</v>
+        <v>-0.0183</v>
       </c>
       <c r="G164" s="6" t="n">
         <v>46233</v>
@@ -13655,7 +13655,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="9" t="n">
-        <v>0.2598992080633549</v>
+        <v>0.2719178704460798</v>
       </c>
       <c r="Q164" s="10" t="inlineStr">
         <is>
@@ -13708,13 +13708,13 @@
         </is>
       </c>
       <c r="D165" s="15" t="n">
-        <v>285.15</v>
+        <v>289.46</v>
       </c>
       <c r="E165" s="20" t="n">
-        <v>0.0483</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="F165" s="20" t="n">
-        <v>0.08220000000000001</v>
+        <v>0.09849999999999999</v>
       </c>
       <c r="G165" s="17" t="n">
         <v>46317</v>
@@ -13746,7 +13746,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="20" t="n">
-        <v>0.03103629668595484</v>
+        <v>0.01568437780695095</v>
       </c>
       <c r="Q165" s="21" t="inlineStr">
         <is>
@@ -13791,13 +13791,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>228.8</v>
+        <v>227.5</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>-0.3166</v>
+        <v>-0.3205</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>-0.2925</v>
+        <v>-0.2965</v>
       </c>
       <c r="G166" s="6" t="n"/>
       <c r="H166" s="12" t="inlineStr">
@@ -13819,7 +13819,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="9" t="n">
-        <v>0.8575174825174824</v>
+        <v>0.8681318681318682</v>
       </c>
       <c r="Q166" s="10" t="inlineStr">
         <is>
@@ -13860,13 +13860,13 @@
         </is>
       </c>
       <c r="D167" s="15" t="n">
-        <v>225.57</v>
+        <v>226.33</v>
       </c>
       <c r="E167" s="20" t="n">
-        <v>0.0121</v>
+        <v>0.0155</v>
       </c>
       <c r="F167" s="20" t="n">
-        <v>0.06150000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="G167" s="17" t="n"/>
       <c r="H167" s="23" t="inlineStr">
@@ -13885,7 +13885,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="20" t="n">
-        <v>0.1881012545994592</v>
+        <v>0.1841116953121548</v>
       </c>
       <c r="N167" s="14" t="inlineStr"/>
       <c r="O167" s="19" t="n"/>
@@ -13933,13 +13933,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>302.11</v>
+        <v>310.73</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>-0.275</v>
+        <v>-0.2544</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>-0.1596</v>
+        <v>-0.1356</v>
       </c>
       <c r="G168" s="6" t="n"/>
       <c r="H168" s="12" t="inlineStr">
@@ -13998,13 +13998,13 @@
         </is>
       </c>
       <c r="D169" s="15" t="n">
-        <v>352.35</v>
+        <v>356.28</v>
       </c>
       <c r="E169" s="16" t="n">
-        <v>-0.1718</v>
+        <v>-0.1626</v>
       </c>
       <c r="F169" s="20" t="n">
-        <v>0.031</v>
+        <v>0.0425</v>
       </c>
       <c r="G169" s="17" t="n"/>
       <c r="H169" s="23" t="inlineStr">
@@ -14067,13 +14067,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>117.43</v>
+        <v>116.82</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>-0.0066</v>
+        <v>-0.0118</v>
       </c>
       <c r="F170" s="9" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0784</v>
       </c>
       <c r="G170" s="6" t="n"/>
       <c r="H170" s="12" t="inlineStr">
@@ -14136,13 +14136,13 @@
         </is>
       </c>
       <c r="D171" s="15" t="n">
-        <v>90.03</v>
+        <v>90.11</v>
       </c>
       <c r="E171" s="16" t="n">
-        <v>-0.3923</v>
+        <v>-0.3918</v>
       </c>
       <c r="F171" s="16" t="n">
-        <v>-0.5151</v>
+        <v>-0.5146999999999999</v>
       </c>
       <c r="G171" s="17" t="n">
         <v>46240</v>
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>331.55</v>
+        <v>333.43</v>
       </c>
       <c r="E172" s="9" t="n">
-        <v>0.1458</v>
+        <v>0.1523</v>
       </c>
       <c r="F172" s="9" t="n">
-        <v>0.0824</v>
+        <v>0.0885</v>
       </c>
       <c r="G172" s="6" t="n">
         <v>46233</v>
@@ -14232,7 +14232,7 @@
         <v>310</v>
       </c>
       <c r="M172" s="5" t="n">
-        <v>-0.06499773789775301</v>
+        <v>-0.07026962180967522</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="9" t="n">
-        <v>0.1008897602171618</v>
+        <v>0.09468254206280176</v>
       </c>
       <c r="Q172" s="10" t="inlineStr">
         <is>
@@ -14300,13 +14300,13 @@
         </is>
       </c>
       <c r="D173" s="15" t="n">
-        <v>124.74</v>
+        <v>125.21</v>
       </c>
       <c r="E173" s="16" t="n">
-        <v>-0.3416</v>
+        <v>-0.3391</v>
       </c>
       <c r="F173" s="16" t="n">
-        <v>-0.1707</v>
+        <v>-0.1676</v>
       </c>
       <c r="G173" s="17" t="n">
         <v>46240</v>
@@ -14361,13 +14361,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>162.11</v>
+        <v>163.29</v>
       </c>
       <c r="E174" s="9" t="n">
-        <v>0.3027</v>
+        <v>0.3122</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>-0.1754</v>
+        <v>-0.1694</v>
       </c>
       <c r="G174" s="6" t="n">
         <v>46296</v>
@@ -14422,13 +14422,13 @@
         </is>
       </c>
       <c r="D175" s="15" t="n">
-        <v>245.88</v>
+        <v>247.9</v>
       </c>
       <c r="E175" s="20" t="n">
-        <v>0.1993</v>
+        <v>0.2092</v>
       </c>
       <c r="F175" s="16" t="n">
-        <v>-0.1027</v>
+        <v>-0.09539999999999998</v>
       </c>
       <c r="G175" s="17" t="n">
         <v>46275</v>
@@ -14483,13 +14483,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>367.09</v>
+        <v>366.67</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>-0.0757</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="F176" s="5" t="n">
-        <v>-0.08839999999999999</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="G176" s="6" t="n">
         <v>46253</v>
@@ -14518,7 +14518,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="9" t="n">
-        <v>0.4029257130403989</v>
+        <v>0.4045326860664902</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="9" t="n">
-        <v>0.2912364815167943</v>
+        <v>0.292715520767993</v>
       </c>
       <c r="Q176" s="10" t="inlineStr">
         <is>
@@ -14578,13 +14578,13 @@
         </is>
       </c>
       <c r="D177" s="15" t="n">
-        <v>233.93</v>
+        <v>234.97</v>
       </c>
       <c r="E177" s="20" t="n">
-        <v>0.2032</v>
+        <v>0.2086</v>
       </c>
       <c r="F177" s="16" t="n">
-        <v>-0.0573</v>
+        <v>-0.0532</v>
       </c>
       <c r="G177" s="17" t="n">
         <v>46261</v>
@@ -14639,13 +14639,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>271.89</v>
+        <v>274.26</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>-0.2708</v>
+        <v>-0.2645</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>-0.07719999999999999</v>
+        <v>-0.0692</v>
       </c>
       <c r="G178" s="6" t="n">
         <v>46237</v>
@@ -14700,13 +14700,13 @@
         </is>
       </c>
       <c r="D179" s="15" t="n">
-        <v>293.58</v>
+        <v>299.69</v>
       </c>
       <c r="E179" s="16" t="n">
-        <v>-0.3922</v>
+        <v>-0.3795</v>
       </c>
       <c r="F179" s="16" t="n">
-        <v>-0.0828</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="G179" s="17" t="n">
         <v>46238</v>
@@ -14761,13 +14761,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>40.17</v>
+        <v>41.45</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>-0.423</v>
+        <v>-0.4046</v>
       </c>
       <c r="F180" s="5" t="n">
-        <v>-0.1477</v>
+        <v>-0.1205</v>
       </c>
       <c r="G180" s="6" t="n">
         <v>46233</v>
@@ -14822,13 +14822,13 @@
         </is>
       </c>
       <c r="D181" s="15" t="n">
-        <v>501.14</v>
+        <v>501.77</v>
       </c>
       <c r="E181" s="16" t="n">
-        <v>-0.3069</v>
+        <v>-0.306</v>
       </c>
       <c r="F181" s="20" t="n">
-        <v>0.09380000000000001</v>
+        <v>0.09519999999999999</v>
       </c>
       <c r="G181" s="17" t="n">
         <v>46247</v>
@@ -14857,7 +14857,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="20" t="n">
-        <v>0.4766332761304227</v>
+        <v>0.4747792813440421</v>
       </c>
       <c r="N181" s="14" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="20" t="n">
-        <v>0.3968152612044539</v>
+        <v>0.3950614823524723</v>
       </c>
       <c r="Q181" s="21" t="inlineStr">
         <is>
@@ -14909,13 +14909,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>62.12</v>
+        <v>63.23</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>-0.2965</v>
+        <v>-0.2839</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>-0.1974</v>
+        <v>-0.1831</v>
       </c>
       <c r="G182" s="6" t="n">
         <v>46245</v>
@@ -14974,13 +14974,13 @@
         </is>
       </c>
       <c r="D183" s="15" t="n">
-        <v>487.2</v>
+        <v>485.39</v>
       </c>
       <c r="E183" s="16" t="n">
-        <v>-0.1613</v>
+        <v>-0.1644</v>
       </c>
       <c r="F183" s="16" t="n">
-        <v>-0.045</v>
+        <v>-0.04849999999999999</v>
       </c>
       <c r="G183" s="17" t="n">
         <v>46238</v>
@@ -15009,7 +15009,7 @@
         <v>615</v>
       </c>
       <c r="M183" s="20" t="n">
-        <v>0.2623152709359606</v>
+        <v>0.2670223943632956</v>
       </c>
       <c r="N183" s="14" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="20" t="n">
-        <v>0.1884236453201971</v>
+        <v>0.1928552298152002</v>
       </c>
       <c r="Q183" s="21" t="inlineStr">
         <is>
@@ -15061,13 +15061,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>48.43</v>
+        <v>48.26</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>-0.4384</v>
+        <v>-0.4403</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>-0.3343</v>
+        <v>-0.3366</v>
       </c>
       <c r="G184" s="6" t="n"/>
       <c r="H184" s="12" t="inlineStr">
@@ -15112,13 +15112,13 @@
         </is>
       </c>
       <c r="D185" s="15" t="n">
-        <v>168.31</v>
-      </c>
-      <c r="E185" s="16" t="n">
-        <v>-0.0092</v>
-      </c>
-      <c r="F185" s="16" t="n">
-        <v>-0.0139</v>
+        <v>171.02</v>
+      </c>
+      <c r="E185" s="20" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="F185" s="20" t="n">
+        <v>0.002</v>
       </c>
       <c r="G185" s="17" t="n">
         <v>46238</v>
@@ -15147,7 +15147,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="20" t="n">
-        <v>0.1882835244489335</v>
+        <v>0.1694538650450239</v>
       </c>
       <c r="N185" s="14" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="20" t="n">
-        <v>0.1882835244489335</v>
+        <v>0.1694538650450239</v>
       </c>
       <c r="Q185" s="21" t="inlineStr">
         <is>
@@ -15203,13 +15203,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>157.12</v>
+        <v>159.82</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>-0.1089</v>
+        <v>-0.09359999999999999</v>
       </c>
       <c r="F186" s="9" t="n">
-        <v>0.0736</v>
+        <v>0.09210000000000002</v>
       </c>
       <c r="G186" s="6" t="n"/>
       <c r="H186" s="12" t="inlineStr">
@@ -15231,7 +15231,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="9" t="n">
-        <v>0.1456211812627291</v>
+        <v>0.1262670504317358</v>
       </c>
       <c r="Q186" s="10" t="inlineStr">
         <is>
@@ -15284,13 +15284,13 @@
         </is>
       </c>
       <c r="D187" s="15" t="n">
-        <v>28.2</v>
+        <v>27.97</v>
       </c>
       <c r="E187" s="16" t="n">
-        <v>-0.244</v>
+        <v>-0.2501</v>
       </c>
       <c r="F187" s="16" t="n">
-        <v>-0.4118</v>
+        <v>-0.4166</v>
       </c>
       <c r="G187" s="17" t="n"/>
       <c r="H187" s="23" t="inlineStr">
@@ -15335,13 +15335,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>241.37</v>
+        <v>241.54</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>-0.3193</v>
+        <v>-0.3188</v>
       </c>
       <c r="F188" s="5" t="n">
-        <v>-0.4096</v>
+        <v>-0.4092</v>
       </c>
       <c r="G188" s="6" t="n"/>
       <c r="H188" s="12" t="inlineStr">
@@ -15386,13 +15386,13 @@
         </is>
       </c>
       <c r="D189" s="15" t="n">
-        <v>1660.98</v>
+        <v>1651.44</v>
       </c>
       <c r="E189" s="16" t="n">
-        <v>-0.1651</v>
+        <v>-0.1699</v>
       </c>
       <c r="F189" s="20" t="n">
-        <v>0.0199</v>
+        <v>0.014</v>
       </c>
       <c r="G189" s="17" t="n">
         <v>46309</v>
@@ -15465,13 +15465,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>34.78</v>
+        <v>34.77</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>-0.2292</v>
+        <v>-0.2294</v>
       </c>
       <c r="F190" s="5" t="n">
-        <v>-0.0888</v>
+        <v>-0.0891</v>
       </c>
       <c r="G190" s="6" t="n">
         <v>46233</v>
@@ -15526,13 +15526,13 @@
         </is>
       </c>
       <c r="D191" s="15" t="n">
-        <v>387</v>
+        <v>387.84</v>
       </c>
       <c r="E191" s="20" t="n">
-        <v>0.0245</v>
+        <v>0.0267</v>
       </c>
       <c r="F191" s="16" t="n">
-        <v>-0.1586</v>
+        <v>-0.1568</v>
       </c>
       <c r="G191" s="17" t="n">
         <v>46268</v>
@@ -15561,7 +15561,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="20" t="n">
-        <v>0.4082687338501292</v>
+        <v>0.4052186468646866</v>
       </c>
       <c r="N191" s="14" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="20" t="n">
-        <v>0.5038759689922481</v>
+        <v>0.5006188118811882</v>
       </c>
       <c r="Q191" s="21" t="inlineStr">
         <is>
@@ -15625,13 +15625,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>137.06</v>
+        <v>137.23</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>-0.1598</v>
+        <v>-0.1587</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>-0.1596</v>
+        <v>-0.1586</v>
       </c>
       <c r="G192" s="6" t="n">
         <v>46244</v>
@@ -15686,10 +15686,10 @@
         </is>
       </c>
       <c r="D193" s="15" t="n">
-        <v>332.8</v>
+        <v>332.82</v>
       </c>
       <c r="E193" s="16" t="n">
-        <v>-0.1133</v>
+        <v>-0.1132</v>
       </c>
       <c r="F193" s="16" t="n">
         <v>-0.1964</v>
@@ -15711,7 +15711,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="20" t="n">
-        <v>0.2770432692307692</v>
+        <v>0.2769665284538189</v>
       </c>
       <c r="N193" s="14" t="inlineStr"/>
       <c r="O193" s="19" t="n"/>
@@ -15755,13 +15755,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>125.64</v>
+        <v>128.23</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>-0.044</v>
+        <v>-0.0243</v>
       </c>
       <c r="F194" s="5" t="n">
-        <v>-0.0964</v>
+        <v>-0.07780000000000001</v>
       </c>
       <c r="G194" s="6" t="n">
         <v>46233</v>
@@ -15816,13 +15816,13 @@
         </is>
       </c>
       <c r="D195" s="15" t="n">
-        <v>365.25</v>
+        <v>372.07</v>
       </c>
       <c r="E195" s="16" t="n">
-        <v>-0.2554</v>
+        <v>-0.2415</v>
       </c>
       <c r="F195" s="16" t="n">
-        <v>-0.3588</v>
+        <v>-0.3468</v>
       </c>
       <c r="G195" s="17" t="n">
         <v>46268</v>
@@ -15877,13 +15877,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>14.3</v>
+        <v>14.57</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>-0.0205</v>
+        <v>-0.0021</v>
       </c>
       <c r="F196" s="5" t="n">
-        <v>-0.0989</v>
+        <v>-0.0819</v>
       </c>
       <c r="G196" s="6" t="n">
         <v>46247</v>
@@ -15938,13 +15938,13 @@
         </is>
       </c>
       <c r="D197" s="15" t="n">
-        <v>349.24</v>
+        <v>352.59</v>
       </c>
       <c r="E197" s="16" t="n">
-        <v>-0.0426</v>
+        <v>-0.0335</v>
       </c>
       <c r="F197" s="16" t="n">
-        <v>-0.1812</v>
+        <v>-0.1734</v>
       </c>
       <c r="G197" s="17" t="n"/>
       <c r="H197" s="23" t="inlineStr">
@@ -15989,13 +15989,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>247.1</v>
+        <v>249.06</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>-0.3736</v>
+        <v>-0.3686</v>
       </c>
       <c r="F198" s="5" t="n">
-        <v>-0.3191</v>
+        <v>-0.3137</v>
       </c>
       <c r="G198" s="6" t="n">
         <v>46246</v>
@@ -16050,13 +16050,13 @@
         </is>
       </c>
       <c r="D199" s="15" t="n">
-        <v>45.34</v>
+        <v>46.45</v>
       </c>
       <c r="E199" s="16" t="n">
-        <v>-0.3865999999999999</v>
+        <v>-0.3715</v>
       </c>
       <c r="F199" s="16" t="n">
-        <v>-0.1681</v>
+        <v>-0.1477</v>
       </c>
       <c r="G199" s="17" t="n">
         <v>46233</v>
@@ -16111,13 +16111,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>22.28</v>
+        <v>21.81</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>-0.1292</v>
+        <v>-0.1477</v>
       </c>
       <c r="F200" s="5" t="n">
-        <v>-0.2194</v>
+        <v>-0.2361</v>
       </c>
       <c r="G200" s="6" t="n"/>
       <c r="H200" s="12" t="inlineStr">
@@ -16162,13 +16162,13 @@
         </is>
       </c>
       <c r="D201" s="15" t="n">
-        <v>200.19</v>
+        <v>201.08</v>
       </c>
       <c r="E201" s="16" t="n">
-        <v>-0.2639</v>
+        <v>-0.2606</v>
       </c>
       <c r="F201" s="16" t="n">
-        <v>-0.1146</v>
+        <v>-0.1107</v>
       </c>
       <c r="G201" s="17" t="n">
         <v>46267</v>
@@ -16223,13 +16223,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>179.08</v>
+        <v>180.71</v>
       </c>
       <c r="E202" s="9" t="n">
-        <v>0.1431</v>
+        <v>0.1535</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>-0.1456</v>
+        <v>-0.1378</v>
       </c>
       <c r="G202" s="6" t="n">
         <v>46267</v>
@@ -16258,7 +16258,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="9" t="n">
-        <v>0.1168192986374804</v>
+        <v>0.1067456145205024</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="9" t="n">
-        <v>0.3960241232968505</v>
+        <v>0.383432018150628</v>
       </c>
       <c r="Q202" s="10" t="inlineStr">
         <is>
@@ -16314,13 +16314,13 @@
         </is>
       </c>
       <c r="D203" s="15" t="n">
-        <v>182.74</v>
+        <v>185.22</v>
       </c>
       <c r="E203" s="16" t="n">
-        <v>-0.04219999999999999</v>
+        <v>-0.0292</v>
       </c>
       <c r="F203" s="16" t="n">
-        <v>-0.0655</v>
+        <v>-0.0528</v>
       </c>
       <c r="G203" s="17" t="n">
         <v>46260</v>
@@ -16349,7 +16349,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="16" t="n">
-        <v>-0.008153660939039121</v>
+        <v>-0.02143397041356224</v>
       </c>
       <c r="N203" s="14" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="16" t="n">
-        <v>-0.02867461967823141</v>
+        <v>-0.04168016412914372</v>
       </c>
       <c r="Q203" s="21" t="inlineStr">
         <is>
@@ -16401,13 +16401,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>75.63</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>-0.2402</v>
+        <v>-0.2576</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>-0.3941</v>
+        <v>-0.4079</v>
       </c>
       <c r="G204" s="6" t="n">
         <v>46245</v>
@@ -16462,13 +16462,13 @@
         </is>
       </c>
       <c r="D205" s="15" t="n">
-        <v>113.42</v>
+        <v>113.56</v>
       </c>
       <c r="E205" s="16" t="n">
-        <v>-0.0344</v>
+        <v>-0.0332</v>
       </c>
       <c r="F205" s="16" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.064</v>
       </c>
       <c r="G205" s="17" t="n">
         <v>46246</v>
@@ -16497,7 +16497,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="20" t="n">
-        <v>0.1461823311585258</v>
+        <v>0.1447692849594928</v>
       </c>
       <c r="N205" s="14" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="20" t="n">
-        <v>0.3225180744136836</v>
+        <v>0.3208876364917224</v>
       </c>
       <c r="Q205" s="21" t="inlineStr">
         <is>
@@ -16565,13 +16565,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>267.47</v>
+        <v>268.56</v>
       </c>
       <c r="E206" s="9" t="n">
-        <v>0.0273</v>
+        <v>0.0315</v>
       </c>
       <c r="F206" s="5" t="n">
-        <v>-0.0361</v>
+        <v>-0.0322</v>
       </c>
       <c r="G206" s="6" t="n">
         <v>46240</v>
@@ -16626,13 +16626,13 @@
         </is>
       </c>
       <c r="D207" s="15" t="n">
-        <v>408.79</v>
+        <v>404.81</v>
       </c>
       <c r="E207" s="16" t="n">
-        <v>-0.0525</v>
+        <v>-0.06179999999999999</v>
       </c>
       <c r="F207" s="16" t="n">
-        <v>-0.1227</v>
+        <v>-0.1312</v>
       </c>
       <c r="G207" s="17" t="n">
         <v>46261</v>
@@ -16687,13 +16687,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>53.97</v>
+        <v>54.29</v>
       </c>
       <c r="E208" s="9" t="n">
-        <v>0.215</v>
+        <v>0.2222</v>
       </c>
       <c r="F208" s="5" t="n">
-        <v>-0.0535</v>
+        <v>-0.0479</v>
       </c>
       <c r="G208" s="6" t="n">
         <v>46268</v>
@@ -16748,13 +16748,13 @@
         </is>
       </c>
       <c r="D209" s="15" t="n">
-        <v>43.83</v>
-      </c>
-      <c r="E209" s="16" t="n">
-        <v>-0.0018</v>
+        <v>44.1</v>
+      </c>
+      <c r="E209" s="20" t="n">
+        <v>0.0043</v>
       </c>
       <c r="F209" s="16" t="n">
-        <v>-0.0144</v>
+        <v>-0.0083</v>
       </c>
       <c r="G209" s="17" t="n">
         <v>46239</v>
@@ -16809,13 +16809,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>437.27</v>
+        <v>439.33</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>-0.222</v>
+        <v>-0.2184</v>
       </c>
       <c r="F210" s="5" t="n">
-        <v>-0.2974</v>
+        <v>-0.2941</v>
       </c>
       <c r="G210" s="6" t="n">
         <v>46251</v>
@@ -16870,13 +16870,13 @@
         </is>
       </c>
       <c r="D211" s="15" t="n">
-        <v>106.79</v>
+        <v>105.38</v>
       </c>
       <c r="E211" s="16" t="n">
-        <v>-0.3322</v>
+        <v>-0.3411</v>
       </c>
       <c r="F211" s="16" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.0842</v>
       </c>
       <c r="G211" s="17" t="n"/>
       <c r="H211" s="23" t="inlineStr">
@@ -16921,13 +16921,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>154.37</v>
+        <v>154.25</v>
       </c>
       <c r="E212" s="9" t="n">
-        <v>0.0049</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="F212" s="9" t="n">
-        <v>0.0491</v>
+        <v>0.0483</v>
       </c>
       <c r="G212" s="6" t="n"/>
       <c r="H212" s="12" t="inlineStr">
@@ -16972,13 +16972,13 @@
         </is>
       </c>
       <c r="D213" s="15" t="n">
-        <v>50.05</v>
+        <v>49.89</v>
       </c>
       <c r="E213" s="16" t="n">
-        <v>-0.3926</v>
+        <v>-0.3946</v>
       </c>
       <c r="F213" s="16" t="n">
-        <v>-0.3738</v>
+        <v>-0.3758</v>
       </c>
       <c r="G213" s="17" t="n">
         <v>46239</v>
@@ -17033,13 +17033,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>134.74</v>
+        <v>135.22</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>-0.4725</v>
+        <v>-0.4706</v>
       </c>
       <c r="F214" s="5" t="n">
-        <v>-0.2375</v>
+        <v>-0.2347</v>
       </c>
       <c r="G214" s="6" t="n"/>
       <c r="H214" s="12" t="inlineStr">
@@ -17084,13 +17084,13 @@
         </is>
       </c>
       <c r="D215" s="15" t="n">
-        <v>32.79</v>
+        <v>33.72</v>
       </c>
       <c r="E215" s="20" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.1045</v>
       </c>
       <c r="F215" s="16" t="n">
-        <v>-0.0296</v>
+        <v>-0.0021</v>
       </c>
       <c r="G215" s="17" t="n">
         <v>46267</v>
@@ -17145,13 +17145,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>152.54</v>
+        <v>153.21</v>
       </c>
       <c r="E216" s="9" t="n">
-        <v>0.2396</v>
+        <v>0.2451</v>
       </c>
       <c r="F216" s="5" t="n">
-        <v>-0.1102</v>
+        <v>-0.1062</v>
       </c>
       <c r="G216" s="6" t="n">
         <v>46268</v>
@@ -17180,7 +17180,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="9" t="n">
-        <v>0.245574931165596</v>
+        <v>0.2401279289863585</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="8" t="n"/>
@@ -17224,13 +17224,13 @@
         </is>
       </c>
       <c r="D217" s="15" t="n">
-        <v>46.58</v>
+        <v>47.14</v>
       </c>
       <c r="E217" s="20" t="n">
-        <v>0.0326</v>
-      </c>
-      <c r="F217" s="16" t="n">
-        <v>-0.0089</v>
+        <v>0.045</v>
+      </c>
+      <c r="F217" s="20" t="n">
+        <v>0.003</v>
       </c>
       <c r="G217" s="17" t="n">
         <v>46267</v>
@@ -17259,7 +17259,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="20" t="n">
-        <v>0.4383855732073852</v>
+        <v>0.4212982605006364</v>
       </c>
       <c r="N217" s="14" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="20" t="n">
-        <v>0.5027908973808503</v>
+        <v>0.4849384811200679</v>
       </c>
       <c r="Q217" s="21" t="inlineStr">
         <is>
@@ -17311,13 +17311,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>231.15</v>
+        <v>233.1</v>
       </c>
       <c r="E218" s="9" t="n">
-        <v>0.2665</v>
+        <v>0.2772</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>-0.1184</v>
+        <v>-0.111</v>
       </c>
       <c r="G218" s="6" t="n">
         <v>46239</v>
@@ -17372,13 +17372,13 @@
         </is>
       </c>
       <c r="D219" s="15" t="n">
-        <v>222.59</v>
+        <v>221.74</v>
       </c>
       <c r="E219" s="16" t="n">
-        <v>-0.2085</v>
+        <v>-0.2115</v>
       </c>
       <c r="F219" s="16" t="n">
-        <v>-0.3053</v>
+        <v>-0.308</v>
       </c>
       <c r="G219" s="17" t="n">
         <v>46316</v>
@@ -17414,7 +17414,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="20" t="n">
-        <v>0.1231412013118289</v>
+        <v>0.1274465590331018</v>
       </c>
       <c r="Q219" s="21" t="inlineStr">
         <is>
@@ -17451,13 +17451,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.98</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>-0.2714</v>
+        <v>-0.2508</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>-0.4514</v>
+        <v>-0.4358</v>
       </c>
       <c r="G220" s="6" t="n">
         <v>46246</v>
@@ -17512,13 +17512,13 @@
         </is>
       </c>
       <c r="D221" s="15" t="n">
-        <v>92.97</v>
+        <v>91.13</v>
       </c>
       <c r="E221" s="16" t="n">
-        <v>-0.3342</v>
+        <v>-0.3472999999999999</v>
       </c>
       <c r="F221" s="16" t="n">
-        <v>-0.1496</v>
+        <v>-0.1665</v>
       </c>
       <c r="G221" s="17" t="n">
         <v>46317</v>
@@ -17573,13 +17573,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>309.19</v>
+        <v>315.5</v>
       </c>
       <c r="E222" s="9" t="n">
-        <v>0.1846</v>
+        <v>0.2088</v>
       </c>
       <c r="F222" s="5" t="n">
-        <v>-0.126</v>
+        <v>-0.1082</v>
       </c>
       <c r="G222" s="6" t="n">
         <v>46254</v>
@@ -17634,13 +17634,13 @@
         </is>
       </c>
       <c r="D223" s="15" t="n">
-        <v>34.76</v>
+        <v>35.77</v>
       </c>
       <c r="E223" s="16" t="n">
-        <v>-0.3474</v>
+        <v>-0.3284</v>
       </c>
       <c r="F223" s="16" t="n">
-        <v>-0.4983</v>
+        <v>-0.4837</v>
       </c>
       <c r="G223" s="17" t="n">
         <v>46239</v>
@@ -17695,13 +17695,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>37.79</v>
+        <v>38.26</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>-0.1736</v>
+        <v>-0.1634</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>-0.4216</v>
+        <v>-0.4144</v>
       </c>
       <c r="G224" s="6" t="n">
         <v>46261</v>
@@ -17756,13 +17756,13 @@
         </is>
       </c>
       <c r="D225" s="15" t="n">
-        <v>306.68</v>
+        <v>308.52</v>
       </c>
       <c r="E225" s="16" t="n">
-        <v>-0.2044</v>
+        <v>-0.1996</v>
       </c>
       <c r="F225" s="16" t="n">
-        <v>-0.148</v>
+        <v>-0.1429</v>
       </c>
       <c r="G225" s="17" t="n">
         <v>46289</v>
@@ -17821,13 +17821,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>313.23</v>
+        <v>312.69</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>-0.1052</v>
+        <v>-0.1068</v>
       </c>
       <c r="F226" s="5" t="n">
-        <v>-0.0508</v>
+        <v>-0.0525</v>
       </c>
       <c r="G226" s="6" t="n">
         <v>46252</v>
@@ -17856,7 +17856,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="9" t="n">
-        <v>0.2450914663346422</v>
+        <v>0.2472416770603473</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="8" t="n"/>
@@ -17912,13 +17912,13 @@
         </is>
       </c>
       <c r="D227" s="15" t="n">
-        <v>184.02</v>
+        <v>180.33</v>
       </c>
       <c r="E227" s="16" t="n">
-        <v>-0.3901</v>
+        <v>-0.4023</v>
       </c>
       <c r="F227" s="16" t="n">
-        <v>-0.05139999999999999</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="G227" s="17" t="n"/>
       <c r="H227" s="23" t="inlineStr">
@@ -17937,7 +17937,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="20" t="n">
-        <v>0.657428540376046</v>
+        <v>0.6913436477568901</v>
       </c>
       <c r="N227" s="14" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="20" t="n">
-        <v>0.005325508096945928</v>
+        <v>0.02589696667221198</v>
       </c>
       <c r="Q227" s="21" t="inlineStr">
         <is>
@@ -17989,13 +17989,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>91.68000000000001</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>-0.3146</v>
+        <v>-0.3397</v>
       </c>
       <c r="F228" s="5" t="n">
-        <v>-0.1128</v>
+        <v>-0.1453</v>
       </c>
       <c r="G228" s="6" t="n">
         <v>46239</v>
@@ -18050,13 +18050,13 @@
         </is>
       </c>
       <c r="D229" s="15" t="n">
-        <v>688.37</v>
+        <v>693.24</v>
       </c>
       <c r="E229" s="16" t="n">
-        <v>-0.1978</v>
+        <v>-0.1921</v>
       </c>
       <c r="F229" s="16" t="n">
-        <v>-0.2394</v>
+        <v>-0.234</v>
       </c>
       <c r="G229" s="17" t="n">
         <v>46245</v>
@@ -18111,13 +18111,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>101.79</v>
+        <v>101.57</v>
       </c>
       <c r="E230" s="9" t="n">
-        <v>0.0825</v>
+        <v>0.0801</v>
       </c>
       <c r="F230" s="5" t="n">
-        <v>-0.1964</v>
+        <v>-0.1982</v>
       </c>
       <c r="G230" s="6" t="n"/>
       <c r="H230" s="12" t="inlineStr">
@@ -18162,13 +18162,13 @@
         </is>
       </c>
       <c r="D231" s="15" t="n">
-        <v>299.02</v>
+        <v>297.72</v>
       </c>
       <c r="E231" s="16" t="n">
-        <v>-0.3099</v>
+        <v>-0.3129</v>
       </c>
       <c r="F231" s="16" t="n">
-        <v>-0.0571</v>
+        <v>-0.0612</v>
       </c>
       <c r="G231" s="17" t="n"/>
       <c r="H231" s="23" t="inlineStr">
@@ -18187,7 +18187,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="20" t="n">
-        <v>0.50491605912648</v>
+        <v>0.5114873035066504</v>
       </c>
       <c r="N231" s="14" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="20" t="n">
-        <v>0.1872115577553342</v>
+        <v>0.1923955394330242</v>
       </c>
       <c r="Q231" s="21" t="inlineStr">
         <is>
@@ -18243,13 +18243,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>75.75</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>-0.1695</v>
+        <v>-0.1775</v>
       </c>
       <c r="F232" s="5" t="n">
-        <v>-0.1724</v>
+        <v>-0.1804</v>
       </c>
       <c r="G232" s="6" t="n">
         <v>46240</v>
@@ -18304,13 +18304,13 @@
         </is>
       </c>
       <c r="D233" s="15" t="n">
-        <v>326.71</v>
+        <v>325.88</v>
       </c>
       <c r="E233" s="16" t="n">
-        <v>-0.0273</v>
+        <v>-0.0298</v>
       </c>
       <c r="F233" s="16" t="n">
-        <v>-0.1911</v>
+        <v>-0.1931</v>
       </c>
       <c r="G233" s="17" t="n">
         <v>46259</v>
@@ -18365,13 +18365,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>293.11</v>
+        <v>293.3</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>-0.341</v>
+        <v>-0.3406</v>
       </c>
       <c r="F234" s="5" t="n">
-        <v>-0.07719999999999999</v>
+        <v>-0.0766</v>
       </c>
       <c r="G234" s="6" t="n">
         <v>46239</v>
@@ -18426,13 +18426,13 @@
         </is>
       </c>
       <c r="D235" s="15" t="n">
-        <v>1335.81</v>
+        <v>1316.18</v>
       </c>
       <c r="E235" s="16" t="n">
-        <v>-0.0337</v>
+        <v>-0.0479</v>
       </c>
       <c r="F235" s="16" t="n">
-        <v>-0.1339</v>
+        <v>-0.1467</v>
       </c>
       <c r="G235" s="17" t="n">
         <v>46233</v>
@@ -18487,13 +18487,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>183.21</v>
+        <v>183.3</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>-0.385</v>
+        <v>-0.3847</v>
       </c>
       <c r="F236" s="5" t="n">
-        <v>-0.1651</v>
+        <v>-0.1647</v>
       </c>
       <c r="G236" s="6" t="n">
         <v>46261</v>
@@ -18522,7 +18522,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="9" t="n">
-        <v>0.3099721630915342</v>
+        <v>0.3093289689034369</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="9" t="n">
-        <v>0.3700125538998962</v>
+        <v>0.3693398799781777</v>
       </c>
       <c r="Q236" s="10" t="inlineStr">
         <is>
@@ -18574,13 +18574,13 @@
         </is>
       </c>
       <c r="D237" s="15" t="n">
-        <v>455.52</v>
+        <v>451.1</v>
       </c>
       <c r="E237" s="20" t="n">
-        <v>0.2212</v>
+        <v>0.2093</v>
       </c>
       <c r="F237" s="16" t="n">
-        <v>-0.0109</v>
+        <v>-0.0205</v>
       </c>
       <c r="G237" s="17" t="n"/>
       <c r="H237" s="23" t="inlineStr">
@@ -18599,7 +18599,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="20" t="n">
-        <v>0.3720583069898139</v>
+        <v>0.385502105963201</v>
       </c>
       <c r="N237" s="14" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="20" t="n">
-        <v>0.1525289778714437</v>
+        <v>0.1638217690090888</v>
       </c>
       <c r="Q237" s="21" t="inlineStr">
         <is>
@@ -18663,13 +18663,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>425.08</v>
+        <v>430.82</v>
       </c>
       <c r="E238" s="9" t="n">
-        <v>0.0236</v>
+        <v>0.0374</v>
       </c>
       <c r="F238" s="9" t="n">
-        <v>0.0328</v>
+        <v>0.0467</v>
       </c>
       <c r="G238" s="6" t="n">
         <v>46239</v>
@@ -18701,7 +18701,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="9" t="n">
-        <v>0.2350616354568552</v>
+        <v>0.2186063785339585</v>
       </c>
       <c r="Q238" s="10" t="inlineStr">
         <is>
@@ -18750,13 +18750,13 @@
         </is>
       </c>
       <c r="D239" s="15" t="n">
-        <v>96.47</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="E239" s="20" t="n">
-        <v>0.1097</v>
+        <v>0.1244</v>
       </c>
       <c r="F239" s="16" t="n">
-        <v>-0.3559</v>
+        <v>-0.3474</v>
       </c>
       <c r="G239" s="17" t="n">
         <v>46233</v>
@@ -18811,13 +18811,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>252.55</v>
+        <v>248.71</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>-0.336</v>
+        <v>-0.3461</v>
       </c>
       <c r="F240" s="5" t="n">
-        <v>-0.2862</v>
+        <v>-0.297</v>
       </c>
       <c r="G240" s="6" t="n">
         <v>46240</v>
@@ -18872,13 +18872,13 @@
         </is>
       </c>
       <c r="D241" s="15" t="n">
-        <v>864.45</v>
+        <v>874.66</v>
       </c>
       <c r="E241" s="16" t="n">
-        <v>-0.2511</v>
+        <v>-0.2423</v>
       </c>
       <c r="F241" s="16" t="n">
-        <v>-0.1652</v>
+        <v>-0.1553</v>
       </c>
       <c r="G241" s="17" t="n">
         <v>46287</v>
@@ -18907,7 +18907,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="20" t="n">
-        <v>0.7641274799005147</v>
+        <v>0.7435346305993187</v>
       </c>
       <c r="N241" s="14" t="inlineStr">
         <is>
@@ -18955,13 +18955,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>191.63</v>
+        <v>188.43</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>-0.3061</v>
+        <v>-0.3177</v>
       </c>
       <c r="F242" s="5" t="n">
-        <v>-0.2755</v>
+        <v>-0.2876</v>
       </c>
       <c r="G242" s="6" t="n">
         <v>46246</v>
@@ -19016,10 +19016,10 @@
         </is>
       </c>
       <c r="D243" s="15" t="n">
-        <v>283.38</v>
+        <v>283.39</v>
       </c>
       <c r="E243" s="20" t="n">
-        <v>0.1553</v>
+        <v>0.1554</v>
       </c>
       <c r="F243" s="20" t="n">
         <v>0.0464</v>
@@ -19077,13 +19077,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>108.63</v>
+        <v>110.07</v>
       </c>
       <c r="E244" s="9" t="n">
-        <v>0.0941</v>
+        <v>0.1087</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>-0.2005</v>
+        <v>-0.1898</v>
       </c>
       <c r="G244" s="6" t="n">
         <v>46323</v>
@@ -19112,7 +19112,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="9" t="n">
-        <v>0.4728896253337016</v>
+        <v>0.4536204233669484</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="9" t="n">
-        <v>0.3808340237503453</v>
+        <v>0.3627691469065141</v>
       </c>
       <c r="Q244" s="10" t="inlineStr">
         <is>
@@ -19168,13 +19168,13 @@
         </is>
       </c>
       <c r="D245" s="15" t="n">
-        <v>59.14</v>
+        <v>59.26</v>
       </c>
       <c r="E245" s="20" t="n">
-        <v>0.1605</v>
+        <v>0.1629</v>
       </c>
       <c r="F245" s="20" t="n">
-        <v>0.0585</v>
+        <v>0.0607</v>
       </c>
       <c r="G245" s="17" t="n">
         <v>46260</v>
@@ -19229,13 +19229,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>194.11</v>
+        <v>195.04</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>-0.0299</v>
+        <v>-0.0252</v>
       </c>
       <c r="F246" s="5" t="n">
-        <v>-0.1348</v>
+        <v>-0.1307</v>
       </c>
       <c r="G246" s="6" t="n">
         <v>46260</v>
@@ -19264,7 +19264,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="9" t="n">
-        <v>0.6227912008654886</v>
+        <v>0.6150533223954061</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="9" t="n">
-        <v>1.127659574468085</v>
+        <v>1.117514356029532</v>
       </c>
       <c r="Q246" s="10" t="inlineStr">
         <is>
@@ -19324,13 +19324,13 @@
         </is>
       </c>
       <c r="D247" s="15" t="n">
-        <v>400.02</v>
+        <v>394.07</v>
       </c>
       <c r="E247" s="16" t="n">
-        <v>-0.2632</v>
+        <v>-0.2742</v>
       </c>
       <c r="F247" s="16" t="n">
-        <v>-0.1698</v>
+        <v>-0.1821</v>
       </c>
       <c r="G247" s="17" t="n">
         <v>46240</v>
@@ -19385,13 +19385,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>250.04</v>
+        <v>245.16</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>-0.1103</v>
+        <v>-0.1276</v>
       </c>
       <c r="F248" s="5" t="n">
-        <v>-0.197</v>
+        <v>-0.2127</v>
       </c>
       <c r="G248" s="6" t="n"/>
       <c r="H248" s="12" t="inlineStr">
@@ -19432,13 +19432,13 @@
         </is>
       </c>
       <c r="D249" s="15" t="n">
-        <v>13.34</v>
+        <v>13.01</v>
       </c>
       <c r="E249" s="16" t="n">
-        <v>-0.3099</v>
+        <v>-0.3268</v>
       </c>
       <c r="F249" s="16" t="n">
-        <v>-0.4002000000000001</v>
+        <v>-0.4149</v>
       </c>
       <c r="G249" s="17" t="n"/>
       <c r="H249" s="23" t="inlineStr">
@@ -19483,13 +19483,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>137.64</v>
+        <v>140.42</v>
       </c>
       <c r="E250" s="9" t="n">
-        <v>0.008699999999999999</v>
-      </c>
-      <c r="F250" s="5" t="n">
-        <v>-0.0154</v>
+        <v>0.0291</v>
+      </c>
+      <c r="F250" s="9" t="n">
+        <v>0.004500000000000001</v>
       </c>
       <c r="G250" s="6" t="n">
         <v>46259</v>
@@ -19518,7 +19518,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="9" t="n">
-        <v>0.0897994768962512</v>
+        <v>0.06822389972938338</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="5" t="n">
-        <v>-0.05550712002324897</v>
+        <v>-0.07420595356786774</v>
       </c>
       <c r="Q250" s="10" t="inlineStr">
         <is>
@@ -19570,13 +19570,13 @@
         </is>
       </c>
       <c r="D251" s="15" t="n">
-        <v>84.58</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="E251" s="16" t="n">
-        <v>-0.1054</v>
+        <v>-0.1142</v>
       </c>
       <c r="F251" s="16" t="n">
-        <v>-0.3005</v>
+        <v>-0.3075</v>
       </c>
       <c r="G251" s="17" t="n">
         <v>46237</v>
@@ -19631,13 +19631,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>251.66</v>
+        <v>250.52</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>-0.335</v>
+        <v>-0.338</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>-0.0158</v>
+        <v>-0.0203</v>
       </c>
       <c r="G252" s="6" t="n">
         <v>46240</v>
@@ -19692,13 +19692,13 @@
         </is>
       </c>
       <c r="D253" s="15" t="n">
-        <v>126.32</v>
+        <v>127.56</v>
       </c>
       <c r="E253" s="16" t="n">
-        <v>-0.1381</v>
+        <v>-0.1296</v>
       </c>
       <c r="F253" s="16" t="n">
-        <v>-0.491</v>
+        <v>-0.486</v>
       </c>
       <c r="G253" s="17" t="n">
         <v>46273</v>
@@ -19727,7 +19727,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="20" t="n">
-        <v>1.216592780240659</v>
+        <v>1.195045468798996</v>
       </c>
       <c r="N253" s="14" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="20" t="n">
-        <v>0.9395186827105764</v>
+        <v>0.920664785199122</v>
       </c>
       <c r="Q253" s="21" t="inlineStr">
         <is>
@@ -19779,13 +19779,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>319.89</v>
+        <v>325.68</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>-0.062</v>
+        <v>-0.045</v>
       </c>
       <c r="F254" s="9" t="n">
-        <v>0.0646</v>
+        <v>0.0839</v>
       </c>
       <c r="G254" s="6" t="n">
         <v>46251</v>
@@ -19814,7 +19814,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="9" t="n">
-        <v>0.3129513270186627</v>
+        <v>0.2896094325718496</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="9" t="n">
-        <v>0.2973209540779643</v>
+        <v>0.2742569393269467</v>
       </c>
       <c r="Q254" s="10" t="inlineStr">
         <is>
@@ -19874,13 +19874,13 @@
         </is>
       </c>
       <c r="D255" s="15" t="n">
-        <v>12.02</v>
+        <v>12.37</v>
       </c>
       <c r="E255" s="20" t="n">
-        <v>0.1063</v>
+        <v>0.138</v>
       </c>
       <c r="F255" s="16" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.0557</v>
       </c>
       <c r="G255" s="17" t="n">
         <v>46268</v>
@@ -19935,13 +19935,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E256" s="5" t="n">
-        <v>-0.0289</v>
+        <v>30.03</v>
+      </c>
+      <c r="E256" s="9" t="n">
+        <v>0.002</v>
       </c>
       <c r="F256" s="5" t="n">
-        <v>-0.2327</v>
+        <v>-0.2083</v>
       </c>
       <c r="G256" s="6" t="n">
         <v>46315</v>
@@ -19996,13 +19996,13 @@
         </is>
       </c>
       <c r="D257" s="15" t="n">
-        <v>142.69</v>
-      </c>
-      <c r="E257" s="16" t="n">
-        <v>-0.0038</v>
+        <v>147.49</v>
+      </c>
+      <c r="E257" s="20" t="n">
+        <v>0.0297</v>
       </c>
       <c r="F257" s="20" t="n">
-        <v>0.0001</v>
+        <v>0.0338</v>
       </c>
       <c r="G257" s="17" t="n"/>
       <c r="H257" s="23" t="inlineStr">
@@ -20047,13 +20047,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>121.85</v>
+        <v>122.26</v>
       </c>
       <c r="E258" s="9" t="n">
-        <v>0.0444</v>
+        <v>0.0479</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>-0.2415</v>
+        <v>-0.239</v>
       </c>
       <c r="G258" s="6" t="n">
         <v>46237</v>
@@ -20108,13 +20108,13 @@
         </is>
       </c>
       <c r="D259" s="15" t="n">
-        <v>134.53</v>
+        <v>130.52</v>
       </c>
       <c r="E259" s="16" t="n">
-        <v>-0.1762</v>
+        <v>-0.2008</v>
       </c>
       <c r="F259" s="16" t="n">
-        <v>-0.1145</v>
+        <v>-0.1409</v>
       </c>
       <c r="G259" s="17" t="n">
         <v>46238</v>
@@ -20179,13 +20179,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>17.66</v>
+        <v>17.98</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>-0.2639</v>
+        <v>-0.2505</v>
       </c>
       <c r="F260" s="5" t="n">
-        <v>-0.3948</v>
+        <v>-0.3838</v>
       </c>
       <c r="G260" s="6" t="n">
         <v>46240</v>
@@ -20240,13 +20240,13 @@
         </is>
       </c>
       <c r="D261" s="15" t="n">
-        <v>153.26</v>
+        <v>151.6</v>
       </c>
       <c r="E261" s="16" t="n">
-        <v>-0.1706</v>
+        <v>-0.1796</v>
       </c>
       <c r="F261" s="16" t="n">
-        <v>-0.3307</v>
+        <v>-0.338</v>
       </c>
       <c r="G261" s="17" t="n"/>
       <c r="H261" s="23" t="inlineStr">
@@ -20265,7 +20265,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="20" t="n">
-        <v>0.7290878246117709</v>
+        <v>0.7480211081794196</v>
       </c>
       <c r="N261" s="14" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>179</v>
       </c>
       <c r="P261" s="20" t="n">
-        <v>0.1679498890773849</v>
+        <v>0.1807387862796834</v>
       </c>
       <c r="Q261" s="21" t="inlineStr">
         <is>
@@ -20321,13 +20321,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>89.94</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>-0.0357</v>
+        <v>-0.0271</v>
       </c>
       <c r="F262" s="5" t="n">
-        <v>-0.1003</v>
+        <v>-0.09230000000000001</v>
       </c>
       <c r="G262" s="6" t="n"/>
       <c r="H262" s="12" t="inlineStr">
@@ -20372,13 +20372,13 @@
         </is>
       </c>
       <c r="D263" s="15" t="n">
-        <v>7.86</v>
+        <v>8.02</v>
       </c>
       <c r="E263" s="16" t="n">
-        <v>-0.1897</v>
+        <v>-0.1732</v>
       </c>
       <c r="F263" s="16" t="n">
-        <v>-0.3656</v>
+        <v>-0.3527</v>
       </c>
       <c r="G263" s="17" t="n">
         <v>46244</v>
@@ -20433,13 +20433,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>71.12</v>
+        <v>71.58</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>-0.1141</v>
+        <v>-0.1084</v>
       </c>
       <c r="F264" s="5" t="n">
-        <v>-0.164</v>
+        <v>-0.1586</v>
       </c>
       <c r="G264" s="6" t="n">
         <v>46273</v>
@@ -20494,13 +20494,13 @@
         </is>
       </c>
       <c r="D265" s="15" t="n">
-        <v>14.48</v>
+        <v>14.86</v>
       </c>
       <c r="E265" s="16" t="n">
-        <v>-0.2505</v>
+        <v>-0.2308</v>
       </c>
       <c r="F265" s="16" t="n">
-        <v>-0.435</v>
+        <v>-0.4202</v>
       </c>
       <c r="G265" s="17" t="n">
         <v>46240</v>
@@ -20555,13 +20555,13 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>383.6</v>
+        <v>389.25</v>
       </c>
       <c r="E266" s="9" t="n">
-        <v>0.1336</v>
+        <v>0.1503</v>
       </c>
       <c r="F266" s="9" t="n">
-        <v>0.1143</v>
+        <v>0.1307</v>
       </c>
       <c r="G266" s="6" t="n">
         <v>46317</v>
@@ -20630,13 +20630,13 @@
         </is>
       </c>
       <c r="D267" s="15" t="n">
-        <v>4.09</v>
+        <v>4.21</v>
       </c>
       <c r="E267" s="16" t="n">
-        <v>-0.3729</v>
+        <v>-0.3553</v>
       </c>
       <c r="F267" s="16" t="n">
-        <v>-0.3083</v>
+        <v>-0.2889</v>
       </c>
       <c r="G267" s="17" t="n">
         <v>46240</v>
@@ -20691,13 +20691,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>18.19</v>
+        <v>18.4</v>
       </c>
       <c r="E268" s="9" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0843</v>
       </c>
       <c r="F268" s="9" t="n">
-        <v>0.0213</v>
+        <v>0.0331</v>
       </c>
       <c r="G268" s="6" t="n">
         <v>46261</v>
@@ -20752,13 +20752,13 @@
         </is>
       </c>
       <c r="D269" s="15" t="n">
-        <v>15.88</v>
+        <v>16.17</v>
       </c>
       <c r="E269" s="20" t="n">
-        <v>0.08439999999999999</v>
+        <v>0.1045</v>
       </c>
       <c r="F269" s="16" t="n">
-        <v>-0.1753</v>
+        <v>-0.16</v>
       </c>
       <c r="G269" s="17" t="n">
         <v>46273</v>
@@ -20813,13 +20813,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>183.76</v>
+        <v>183.48</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>-0.2739</v>
+        <v>-0.275</v>
       </c>
       <c r="F270" s="5" t="n">
-        <v>-0.3063</v>
+        <v>-0.3073</v>
       </c>
       <c r="G270" s="6" t="n"/>
       <c r="H270" s="12" t="inlineStr">
@@ -20864,13 +20864,13 @@
         </is>
       </c>
       <c r="D271" s="15" t="n">
-        <v>179.09</v>
+        <v>180.88</v>
       </c>
       <c r="E271" s="20" t="n">
-        <v>0.1621</v>
+        <v>0.1737</v>
       </c>
       <c r="F271" s="16" t="n">
-        <v>-0.0868</v>
+        <v>-0.07769999999999999</v>
       </c>
       <c r="G271" s="17" t="n">
         <v>46316</v>
@@ -20945,13 +20945,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>27.99</v>
+        <v>27.73</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>-0.0457</v>
+        <v>-0.0546</v>
       </c>
       <c r="F272" s="5" t="n">
-        <v>-0.4029</v>
+        <v>-0.4085</v>
       </c>
       <c r="G272" s="6" t="n">
         <v>46245</v>
@@ -21006,13 +21006,13 @@
         </is>
       </c>
       <c r="D273" s="15" t="n">
-        <v>297.43</v>
+        <v>298.1</v>
       </c>
       <c r="E273" s="20" t="n">
-        <v>0.1687</v>
+        <v>0.1713</v>
       </c>
       <c r="F273" s="20" t="n">
-        <v>0.0617</v>
+        <v>0.064</v>
       </c>
       <c r="G273" s="17" t="n">
         <v>46260</v>
@@ -21041,7 +21041,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="20" t="n">
-        <v>0.07588340113640182</v>
+        <v>0.07346528010734645</v>
       </c>
       <c r="N273" s="14" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="16" t="n">
-        <v>-0.05860202400564841</v>
+        <v>-0.06071787990607186</v>
       </c>
       <c r="Q273" s="21" t="inlineStr">
         <is>
@@ -21093,13 +21093,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>372.39</v>
+        <v>372.33</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>-0.1652</v>
+        <v>-0.1653</v>
       </c>
       <c r="F274" s="5" t="n">
-        <v>-0.2436</v>
+        <v>-0.2437</v>
       </c>
       <c r="G274" s="6" t="n">
         <v>46260</v>
@@ -21128,7 +21128,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="9" t="n">
-        <v>0.4366658610596418</v>
+        <v>0.4368973759836705</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="8" t="n"/>
@@ -21172,13 +21172,13 @@
         </is>
       </c>
       <c r="D275" s="15" t="n">
-        <v>6.11</v>
+        <v>6.14</v>
       </c>
       <c r="E275" s="16" t="n">
-        <v>-0.0564</v>
+        <v>-0.051</v>
       </c>
       <c r="F275" s="16" t="n">
-        <v>-0.34</v>
+        <v>-0.3362</v>
       </c>
       <c r="G275" s="17" t="n">
         <v>46239</v>
@@ -21233,13 +21233,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>61.48</v>
+        <v>62.48</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.0785</v>
       </c>
       <c r="F276" s="5" t="n">
-        <v>-0.1856</v>
+        <v>-0.1723</v>
       </c>
       <c r="G276" s="6" t="n"/>
       <c r="H276" s="12" t="inlineStr">
@@ -21284,13 +21284,13 @@
         </is>
       </c>
       <c r="D277" s="15" t="n">
-        <v>110.07</v>
+        <v>108.85</v>
       </c>
       <c r="E277" s="16" t="n">
-        <v>-0.114</v>
+        <v>-0.1238</v>
       </c>
       <c r="F277" s="16" t="n">
-        <v>-0.1842</v>
+        <v>-0.1933</v>
       </c>
       <c r="G277" s="17" t="n">
         <v>46240</v>
@@ -21345,13 +21345,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>206.21</v>
+        <v>206.58</v>
       </c>
       <c r="E278" s="9" t="n">
-        <v>0.0228</v>
+        <v>0.0247</v>
       </c>
       <c r="F278" s="5" t="n">
-        <v>-0.0231</v>
+        <v>-0.0214</v>
       </c>
       <c r="G278" s="6" t="n">
         <v>46330</v>
@@ -21406,13 +21406,13 @@
         </is>
       </c>
       <c r="D279" s="15" t="n">
-        <v>360.69</v>
+        <v>365.49</v>
       </c>
       <c r="E279" s="16" t="n">
-        <v>-0.2545</v>
+        <v>-0.2446</v>
       </c>
       <c r="F279" s="16" t="n">
-        <v>-0.0238</v>
+        <v>-0.0108</v>
       </c>
       <c r="G279" s="17" t="n"/>
       <c r="H279" s="23" t="inlineStr">
@@ -21457,13 +21457,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>56.19</v>
+        <v>57.06</v>
       </c>
       <c r="E280" s="9" t="n">
-        <v>0.09789999999999999</v>
+        <v>0.1149</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>-0.0337</v>
+        <v>-0.0187</v>
       </c>
       <c r="G280" s="6" t="n">
         <v>46239</v>
@@ -21518,13 +21518,13 @@
         </is>
       </c>
       <c r="D281" s="15" t="n">
-        <v>404.26</v>
+        <v>403.31</v>
       </c>
       <c r="E281" s="16" t="n">
-        <v>-0.1535</v>
+        <v>-0.1555</v>
       </c>
       <c r="F281" s="16" t="n">
-        <v>-0.07200000000000001</v>
+        <v>-0.0742</v>
       </c>
       <c r="G281" s="17" t="n">
         <v>46310</v>
@@ -21601,13 +21601,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>115.42</v>
+        <v>115.51</v>
       </c>
       <c r="E282" s="5" t="n">
-        <v>-0.3829</v>
+        <v>-0.3824</v>
       </c>
       <c r="F282" s="5" t="n">
-        <v>-0.3307</v>
+        <v>-0.3301</v>
       </c>
       <c r="G282" s="6" t="n">
         <v>46239</v>
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="D283" s="15" t="n">
-        <v>190.29</v>
+        <v>190.94</v>
       </c>
       <c r="E283" s="16" t="n">
-        <v>-0.07780000000000001</v>
+        <v>-0.0746</v>
       </c>
       <c r="F283" s="16" t="n">
-        <v>-0.1637</v>
+        <v>-0.1609</v>
       </c>
       <c r="G283" s="17" t="n">
         <v>46240</v>
@@ -21723,13 +21723,13 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>281.79</v>
+        <v>278.76</v>
       </c>
       <c r="E284" s="5" t="n">
-        <v>-0.0546</v>
+        <v>-0.06480000000000001</v>
       </c>
       <c r="F284" s="5" t="n">
-        <v>-0.0389</v>
+        <v>-0.0492</v>
       </c>
       <c r="G284" s="6" t="n">
         <v>46315</v>
@@ -21758,7 +21758,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="9" t="n">
-        <v>0.06462259129138713</v>
+        <v>0.0761945759793371</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="9" t="n">
-        <v>0.1214024628269278</v>
+        <v>0.1335916200315684</v>
       </c>
       <c r="Q284" s="10" t="inlineStr">
         <is>
@@ -21826,13 +21826,13 @@
         </is>
       </c>
       <c r="D285" s="15" t="n">
-        <v>318.77</v>
+        <v>323.31</v>
       </c>
       <c r="E285" s="20" t="n">
-        <v>0.09</v>
+        <v>0.1055</v>
       </c>
       <c r="F285" s="16" t="n">
-        <v>-0.0335</v>
+        <v>-0.0198</v>
       </c>
       <c r="G285" s="17" t="n"/>
       <c r="H285" s="23" t="inlineStr">
@@ -21851,7 +21851,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="20" t="n">
-        <v>0.05091445242651448</v>
+        <v>0.03615724846122916</v>
       </c>
       <c r="N285" s="14" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="20" t="n">
-        <v>0.1763967751043072</v>
+        <v>0.1598775169342117</v>
       </c>
       <c r="Q285" s="21" t="inlineStr">
         <is>
@@ -21903,13 +21903,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>32.57</v>
+        <v>33.34</v>
       </c>
       <c r="E286" s="9" t="n">
-        <v>0.1396</v>
+        <v>0.1666</v>
       </c>
       <c r="F286" s="9" t="n">
-        <v>0.0124</v>
+        <v>0.0364</v>
       </c>
       <c r="G286" s="6" t="n">
         <v>46240</v>
@@ -21964,13 +21964,13 @@
         </is>
       </c>
       <c r="D287" s="15" t="n">
-        <v>7.16</v>
+        <v>7.32</v>
       </c>
       <c r="E287" s="16" t="n">
-        <v>-0.1088</v>
+        <v>-0.08960000000000001</v>
       </c>
       <c r="F287" s="16" t="n">
-        <v>-0.3240999999999999</v>
+        <v>-0.3094</v>
       </c>
       <c r="G287" s="17" t="n">
         <v>46254</v>
@@ -22025,13 +22025,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>153.19</v>
+        <v>158.11</v>
       </c>
       <c r="E288" s="9" t="n">
-        <v>0.2513</v>
-      </c>
-      <c r="F288" s="5" t="n">
-        <v>-0.0257</v>
+        <v>0.2915</v>
+      </c>
+      <c r="F288" s="9" t="n">
+        <v>0.005600000000000001</v>
       </c>
       <c r="G288" s="6" t="n">
         <v>46254</v>
@@ -22086,13 +22086,13 @@
         </is>
       </c>
       <c r="D289" s="15" t="n">
-        <v>528.73</v>
+        <v>533.04</v>
       </c>
       <c r="E289" s="16" t="n">
-        <v>-0.1722</v>
+        <v>-0.1655</v>
       </c>
       <c r="F289" s="16" t="n">
-        <v>-0.032</v>
+        <v>-0.0241</v>
       </c>
       <c r="G289" s="17" t="n">
         <v>46239</v>
@@ -22121,7 +22121,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="20" t="n">
-        <v>0.380666881016776</v>
+        <v>0.3695032267747262</v>
       </c>
       <c r="N289" s="14" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="20" t="n">
-        <v>0.08751158436252904</v>
+        <v>0.07871829506228432</v>
       </c>
       <c r="Q289" s="21" t="inlineStr">
         <is>
@@ -22173,13 +22173,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>23.18</v>
+        <v>23.79</v>
       </c>
       <c r="E290" s="5" t="n">
-        <v>-0.5196000000000001</v>
+        <v>-0.5069</v>
       </c>
       <c r="F290" s="5" t="n">
-        <v>-0.5622</v>
+        <v>-0.5507</v>
       </c>
       <c r="G290" s="6" t="n">
         <v>46238</v>
@@ -22234,13 +22234,13 @@
         </is>
       </c>
       <c r="D291" s="15" t="n">
-        <v>91.56999999999999</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="E291" s="20" t="n">
-        <v>0.0609</v>
+        <v>0.0696</v>
       </c>
       <c r="F291" s="16" t="n">
-        <v>-0.1796</v>
+        <v>-0.1729</v>
       </c>
       <c r="G291" s="17" t="n">
         <v>46254</v>
@@ -22295,13 +22295,13 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>145.98</v>
+        <v>148.39</v>
       </c>
       <c r="E292" s="9" t="n">
-        <v>0.0342</v>
+        <v>0.0513</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>-0.0625</v>
+        <v>-0.047</v>
       </c>
       <c r="G292" s="6" t="n">
         <v>46266</v>
@@ -22356,13 +22356,13 @@
         </is>
       </c>
       <c r="D293" s="15" t="n">
-        <v>298.83</v>
+        <v>300.2</v>
       </c>
       <c r="E293" s="20" t="n">
-        <v>0.0193</v>
+        <v>0.0239</v>
       </c>
       <c r="F293" s="20" t="n">
-        <v>0.07150000000000001</v>
+        <v>0.0764</v>
       </c>
       <c r="G293" s="17" t="n">
         <v>46233</v>
@@ -22417,13 +22417,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>85.63</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="E294" s="9" t="n">
-        <v>0.0278</v>
+        <v>0.0311</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>-0.0613</v>
+        <v>-0.0583</v>
       </c>
       <c r="G294" s="6" t="n">
         <v>46252</v>
@@ -22478,13 +22478,13 @@
         </is>
       </c>
       <c r="D295" s="15" t="n">
-        <v>139.95</v>
+        <v>138.84</v>
       </c>
       <c r="E295" s="20" t="n">
-        <v>0.0318</v>
+        <v>0.0236</v>
       </c>
       <c r="F295" s="16" t="n">
-        <v>-0.0198</v>
+        <v>-0.0275</v>
       </c>
       <c r="G295" s="17" t="n">
         <v>46238</v>
@@ -22513,7 +22513,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="20" t="n">
-        <v>0.1861379063951412</v>
+        <v>0.1956208585422068</v>
       </c>
       <c r="N295" s="14" t="inlineStr"/>
       <c r="O295" s="19" t="n"/>
@@ -22561,13 +22561,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>29.77</v>
+        <v>30.09</v>
       </c>
       <c r="E296" s="9" t="n">
-        <v>0.0883</v>
+        <v>0.0998</v>
       </c>
       <c r="F296" s="5" t="n">
-        <v>-0.1417</v>
+        <v>-0.1326</v>
       </c>
       <c r="G296" s="6" t="n">
         <v>46317</v>
@@ -22622,13 +22622,13 @@
         </is>
       </c>
       <c r="D297" s="15" t="n">
-        <v>276.79</v>
-      </c>
-      <c r="E297" s="16" t="n">
-        <v>-0.006500000000000001</v>
+        <v>279.34</v>
+      </c>
+      <c r="E297" s="20" t="n">
+        <v>0.0026</v>
       </c>
       <c r="F297" s="20" t="n">
-        <v>0.1051</v>
+        <v>0.1153</v>
       </c>
       <c r="G297" s="17" t="n"/>
       <c r="H297" s="23" t="inlineStr">
@@ -22647,7 +22647,7 @@
         <v>275</v>
       </c>
       <c r="M297" s="16" t="n">
-        <v>-0.006466996640052098</v>
+        <v>-0.01553662203766011</v>
       </c>
       <c r="N297" s="14" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="20" t="n">
-        <v>0.1272083529029227</v>
+        <v>0.1169184506336365</v>
       </c>
       <c r="Q297" s="21" t="inlineStr">
         <is>
@@ -22711,13 +22711,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>36.12</v>
+        <v>35.62</v>
       </c>
       <c r="E298" s="5" t="n">
-        <v>-0.2436</v>
+        <v>-0.254</v>
       </c>
       <c r="F298" s="5" t="n">
-        <v>-0.1336</v>
+        <v>-0.1456</v>
       </c>
       <c r="G298" s="6" t="n"/>
       <c r="H298" s="12" t="inlineStr">
@@ -22766,13 +22766,13 @@
         </is>
       </c>
       <c r="D299" s="15" t="n">
-        <v>63.08</v>
+        <v>63.44</v>
       </c>
       <c r="E299" s="20" t="n">
-        <v>0.0031</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F299" s="16" t="n">
-        <v>-0.059</v>
+        <v>-0.0537</v>
       </c>
       <c r="G299" s="17" t="n">
         <v>46310</v>
@@ -22827,13 +22827,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>504.77</v>
+        <v>508.64</v>
       </c>
       <c r="E300" s="5" t="n">
-        <v>-0.0273</v>
+        <v>-0.0198</v>
       </c>
       <c r="F300" s="9" t="n">
-        <v>0.0148</v>
+        <v>0.0226</v>
       </c>
       <c r="G300" s="6" t="n">
         <v>46234</v>
@@ -22862,7 +22862,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="9" t="n">
-        <v>0.1292271727717575</v>
+        <v>0.1206354199433785</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="9" t="n">
-        <v>0.04007765913188188</v>
+        <v>0.03216420257942752</v>
       </c>
       <c r="Q300" s="10" t="inlineStr">
         <is>
@@ -22926,13 +22926,13 @@
         </is>
       </c>
       <c r="D301" s="15" t="n">
-        <v>542.53</v>
+        <v>540</v>
       </c>
       <c r="E301" s="16" t="n">
-        <v>-0.0593</v>
+        <v>-0.0636</v>
       </c>
       <c r="F301" s="16" t="n">
-        <v>-0.0498</v>
+        <v>-0.0542</v>
       </c>
       <c r="G301" s="17" t="n">
         <v>46233</v>
@@ -22961,7 +22961,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="20" t="n">
-        <v>0.1354210827051039</v>
+        <v>0.1407407407407407</v>
       </c>
       <c r="N301" s="14" t="inlineStr"/>
       <c r="O301" s="19" t="n"/>
@@ -23005,13 +23005,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>258.04</v>
+        <v>257.04</v>
       </c>
       <c r="E302" s="9" t="n">
-        <v>0.1584</v>
+        <v>0.1539</v>
       </c>
       <c r="F302" s="9" t="n">
-        <v>0.026</v>
+        <v>0.0221</v>
       </c>
       <c r="G302" s="6" t="n"/>
       <c r="H302" s="12" t="inlineStr">
@@ -23030,7 +23030,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="9" t="n">
-        <v>0.09672918927298084</v>
+        <v>0.1009959539371303</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="8" t="n"/>
@@ -23076,13 +23076,13 @@
         </is>
       </c>
       <c r="D303" s="15" t="n">
-        <v>245.8</v>
+        <v>248.63</v>
       </c>
       <c r="E303" s="20" t="n">
-        <v>0.0316</v>
+        <v>0.0434</v>
       </c>
       <c r="F303" s="20" t="n">
-        <v>0.1089</v>
+        <v>0.1216</v>
       </c>
       <c r="G303" s="17" t="n">
         <v>46321</v>
@@ -23110,8 +23110,8 @@
       <c r="L303" s="19" t="n">
         <v>246</v>
       </c>
-      <c r="M303" s="20" t="n">
-        <v>0.0008136696501220041</v>
+      <c r="M303" s="16" t="n">
+        <v>-0.010577967260588</v>
       </c>
       <c r="N303" s="14" t="inlineStr"/>
       <c r="O303" s="19" t="n"/>
@@ -23159,13 +23159,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>111.32</v>
+        <v>112.03</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>-0.08220000000000001</v>
+        <v>-0.07629999999999999</v>
       </c>
       <c r="F304" s="5" t="n">
-        <v>-0.0067</v>
+        <v>-0.0004</v>
       </c>
       <c r="G304" s="6" t="n"/>
       <c r="H304" s="12" t="inlineStr">
@@ -23184,7 +23184,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="9" t="n">
-        <v>0.167804527488322</v>
+        <v>0.1604034633580291</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="9" t="n">
-        <v>0.1498383039885017</v>
+        <v>0.1425511023832902</v>
       </c>
       <c r="Q304" s="10" t="inlineStr">
         <is>
@@ -23244,13 +23244,13 @@
         </is>
       </c>
       <c r="D305" s="15" t="n">
-        <v>106.87</v>
+        <v>107.83</v>
       </c>
       <c r="E305" s="16" t="n">
-        <v>-0.0385</v>
+        <v>-0.0299</v>
       </c>
       <c r="F305" s="20" t="n">
-        <v>0.0215</v>
+        <v>0.0307</v>
       </c>
       <c r="G305" s="17" t="n">
         <v>46302</v>
@@ -23279,7 +23279,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="20" t="n">
-        <v>0.2632169926078413</v>
+        <v>0.2519706946118891</v>
       </c>
       <c r="N305" s="14" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="20" t="n">
-        <v>0.1696453635257789</v>
+        <v>0.1592321246406381</v>
       </c>
       <c r="Q305" s="21" t="inlineStr"/>
       <c r="R305" s="19" t="n"/>
@@ -23325,13 +23325,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>341.9</v>
-      </c>
-      <c r="E306" s="5" t="n">
-        <v>-0.006999999999999999</v>
+        <v>344.84</v>
+      </c>
+      <c r="E306" s="9" t="n">
+        <v>0.0015</v>
       </c>
       <c r="F306" s="9" t="n">
-        <v>0.1595</v>
+        <v>0.1695</v>
       </c>
       <c r="G306" s="6" t="n"/>
       <c r="H306" s="12" t="inlineStr">
@@ -23350,7 +23350,7 @@
         <v>350</v>
       </c>
       <c r="M306" s="9" t="n">
-        <v>0.02369113775957889</v>
+        <v>0.01496346131539272</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -23361,7 +23361,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="9" t="n">
-        <v>0.1699327288680902</v>
+        <v>0.159958241503306</v>
       </c>
       <c r="Q306" s="10" t="inlineStr">
         <is>
@@ -23402,13 +23402,13 @@
         </is>
       </c>
       <c r="D307" s="15" t="n">
-        <v>73.66</v>
+        <v>75.06</v>
       </c>
       <c r="E307" s="16" t="n">
-        <v>-0.06509999999999999</v>
+        <v>-0.0473</v>
       </c>
       <c r="F307" s="16" t="n">
-        <v>-0.1278</v>
+        <v>-0.1112</v>
       </c>
       <c r="G307" s="17" t="n">
         <v>46260</v>
@@ -23459,13 +23459,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>51.2</v>
+        <v>51.55</v>
       </c>
       <c r="E308" s="5" t="n">
-        <v>-0.3736</v>
+        <v>-0.3693</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>-0.152</v>
+        <v>-0.1462</v>
       </c>
       <c r="G308" s="6" t="n">
         <v>46245</v>
@@ -23520,13 +23520,13 @@
         </is>
       </c>
       <c r="D309" s="15" t="n">
-        <v>77.61</v>
+        <v>78.41</v>
       </c>
       <c r="E309" s="20" t="n">
-        <v>0.0248</v>
+        <v>0.0353</v>
       </c>
       <c r="F309" s="20" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="G309" s="17" t="n">
         <v>46233</v>
@@ -23555,14 +23555,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="20" t="n">
-        <v>0.06944981316840614</v>
+        <v>0.05853845172809595</v>
       </c>
       <c r="N309" s="14" t="inlineStr"/>
       <c r="O309" s="19" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="20" t="n">
-        <v>0.1209895632006185</v>
+        <v>0.109552353016197</v>
       </c>
       <c r="Q309" s="21" t="inlineStr"/>
       <c r="R309" s="19" t="n"/>
@@ -23597,13 +23597,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>173.36</v>
+        <v>174.46</v>
       </c>
       <c r="E310" s="9" t="n">
-        <v>0.0599</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>-0.0756</v>
+        <v>-0.0697</v>
       </c>
       <c r="G310" s="6" t="n"/>
       <c r="H310" s="12" t="inlineStr">
@@ -23622,7 +23622,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="9" t="n">
-        <v>0.1536686663590216</v>
+        <v>0.1463945890175398</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="8" t="n"/>
@@ -23670,13 +23670,13 @@
         </is>
       </c>
       <c r="D311" s="15" t="n">
-        <v>147.2</v>
+        <v>149.46</v>
       </c>
       <c r="E311" s="20" t="n">
-        <v>0.0929</v>
+        <v>0.1097</v>
       </c>
       <c r="F311" s="20" t="n">
-        <v>0.181</v>
+        <v>0.1991</v>
       </c>
       <c r="G311" s="17" t="n"/>
       <c r="H311" s="23" t="inlineStr">
@@ -23725,13 +23725,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>193.04</v>
+        <v>193.19</v>
       </c>
       <c r="E312" s="9" t="n">
-        <v>0.075</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="F312" s="9" t="n">
-        <v>0.0435</v>
+        <v>0.0443</v>
       </c>
       <c r="G312" s="6" t="n">
         <v>46317</v>
@@ -23760,7 +23760,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="9" t="n">
-        <v>0.1396601740571903</v>
+        <v>0.138775298928516</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="9" t="n">
-        <v>0.191462909241608</v>
+        <v>0.1905378125161758</v>
       </c>
       <c r="Q312" s="10" t="inlineStr">
         <is>
@@ -23812,13 +23812,13 @@
         </is>
       </c>
       <c r="D313" s="15" t="n">
-        <v>1052.27</v>
+        <v>1047.53</v>
       </c>
       <c r="E313" s="20" t="n">
-        <v>0.0095</v>
-      </c>
-      <c r="F313" s="20" t="n">
-        <v>0.0014</v>
+        <v>0.0049</v>
+      </c>
+      <c r="F313" s="16" t="n">
+        <v>-0.0031</v>
       </c>
       <c r="G313" s="17" t="n"/>
       <c r="H313" s="23" t="inlineStr">
@@ -23837,7 +23837,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="20" t="n">
-        <v>0.1403917245573855</v>
+        <v>0.1455519173675217</v>
       </c>
       <c r="N313" s="14" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="20" t="n">
-        <v>0.1784047820426317</v>
+        <v>0.1837369812797724</v>
       </c>
       <c r="Q313" s="21" t="inlineStr">
         <is>
@@ -23893,13 +23893,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>124.03</v>
+        <v>124.09</v>
       </c>
       <c r="E314" s="9" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.0053</v>
       </c>
       <c r="F314" s="9" t="n">
-        <v>0.0443</v>
+        <v>0.0449</v>
       </c>
       <c r="G314" s="6" t="n">
         <v>46234</v>
@@ -23928,7 +23928,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="9" t="n">
-        <v>0.04007095057647343</v>
+        <v>0.0395680554436296</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -23939,7 +23939,7 @@
         <v>122</v>
       </c>
       <c r="P314" s="5" t="n">
-        <v>-0.01636700798193986</v>
+        <v>-0.01684261423160612</v>
       </c>
       <c r="Q314" s="10" t="inlineStr">
         <is>
@@ -23980,13 +23980,13 @@
         </is>
       </c>
       <c r="D315" s="15" t="n">
-        <v>63.79</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="E315" s="20" t="n">
-        <v>0.0296</v>
+        <v>0.0399</v>
       </c>
       <c r="F315" s="20" t="n">
-        <v>0.0713</v>
+        <v>0.0819</v>
       </c>
       <c r="G315" s="17" t="n">
         <v>46239</v>
@@ -24015,14 +24015,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="20" t="n">
-        <v>0.01896849035899045</v>
+        <v>0.008846810492006722</v>
       </c>
       <c r="N315" s="14" t="inlineStr"/>
       <c r="O315" s="19" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="20" t="n">
-        <v>0.05032136698542092</v>
+        <v>0.0398882508148377</v>
       </c>
       <c r="Q315" s="21" t="inlineStr">
         <is>
@@ -24063,13 +24063,13 @@
         </is>
       </c>
       <c r="D316" s="4" t="n">
-        <v>144.95</v>
+        <v>146.19</v>
       </c>
       <c r="E316" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0791</v>
       </c>
       <c r="F316" s="9" t="n">
-        <v>0.04269999999999999</v>
+        <v>0.0516</v>
       </c>
       <c r="G316" s="6" t="n">
         <v>46309</v>
@@ -24098,7 +24098,7 @@
         <v>167</v>
       </c>
       <c r="M316" s="9" t="n">
-        <v>0.1521214211797172</v>
+        <v>0.1423489978794719</v>
       </c>
       <c r="N316" s="3" t="inlineStr"/>
       <c r="O316" s="8" t="n"/>
@@ -24142,13 +24142,13 @@
         </is>
       </c>
       <c r="D317" s="15" t="n">
-        <v>309.86</v>
+        <v>317.45</v>
       </c>
       <c r="E317" s="16" t="n">
-        <v>-0.0265</v>
+        <v>-0.0027</v>
       </c>
       <c r="F317" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.0732</v>
       </c>
       <c r="G317" s="17" t="n"/>
       <c r="H317" s="23" t="inlineStr">
@@ -24173,8 +24173,8 @@
       <c r="O317" s="19" t="n">
         <v>316</v>
       </c>
-      <c r="P317" s="20" t="n">
-        <v>0.01981540050345313</v>
+      <c r="P317" s="16" t="n">
+        <v>-0.004567648448574543</v>
       </c>
       <c r="Q317" s="21" t="inlineStr">
         <is>
@@ -24215,13 +24215,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>229.5</v>
+        <v>230.44</v>
       </c>
       <c r="E318" s="9" t="n">
-        <v>0.0262</v>
+        <v>0.0304</v>
       </c>
       <c r="F318" s="9" t="n">
-        <v>0.1322</v>
+        <v>0.1369</v>
       </c>
       <c r="G318" s="6" t="n">
         <v>46244</v>
@@ -24257,7 +24257,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="5" t="n">
-        <v>-0.06318082788671024</v>
+        <v>-0.06700225655268181</v>
       </c>
       <c r="Q318" s="10" t="inlineStr">
         <is>
@@ -24298,13 +24298,13 @@
         </is>
       </c>
       <c r="D319" s="15" t="n">
-        <v>123.68</v>
+        <v>124.43</v>
       </c>
       <c r="E319" s="20" t="n">
-        <v>0.0314</v>
+        <v>0.0377</v>
       </c>
       <c r="F319" s="20" t="n">
-        <v>0.0277</v>
+        <v>0.0339</v>
       </c>
       <c r="G319" s="17" t="n"/>
       <c r="H319" s="23" t="inlineStr">
@@ -24323,7 +24323,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="20" t="n">
-        <v>0.1481241914618369</v>
+        <v>0.1412038897372016</v>
       </c>
       <c r="N319" s="14" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="20" t="n">
-        <v>0.1076972833117723</v>
+        <v>0.1010206541830748</v>
       </c>
       <c r="Q319" s="21" t="inlineStr">
         <is>
@@ -24383,13 +24383,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>235.36</v>
+        <v>235.63</v>
       </c>
       <c r="E320" s="9" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0382</v>
       </c>
       <c r="F320" s="9" t="n">
-        <v>0.1925</v>
+        <v>0.1939</v>
       </c>
       <c r="G320" s="6" t="n"/>
       <c r="H320" s="12" t="inlineStr">
@@ -24408,7 +24408,7 @@
         <v>237</v>
       </c>
       <c r="M320" s="9" t="n">
-        <v>0.006968048946294979</v>
+        <v>0.005814200229172875</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>236</v>
       </c>
       <c r="P320" s="9" t="n">
-        <v>0.002719238613188249</v>
+        <v>0.001570258456054002</v>
       </c>
       <c r="Q320" s="10" t="inlineStr">
         <is>
@@ -24460,13 +24460,13 @@
         </is>
       </c>
       <c r="D321" s="15" t="n">
-        <v>174.99</v>
+        <v>174.26</v>
       </c>
       <c r="E321" s="20" t="n">
-        <v>0.0158</v>
+        <v>0.0116</v>
       </c>
       <c r="F321" s="20" t="n">
-        <v>0.0469</v>
+        <v>0.0425</v>
       </c>
       <c r="G321" s="17" t="n">
         <v>46239</v>
@@ -24495,7 +24495,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="20" t="n">
-        <v>0.1429224527115835</v>
+        <v>0.1477103179157581</v>
       </c>
       <c r="N321" s="14" t="inlineStr"/>
       <c r="O321" s="19" t="n"/>
@@ -24539,13 +24539,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>136.62</v>
+        <v>136.81</v>
       </c>
       <c r="E322" s="9" t="n">
-        <v>0.0383</v>
+        <v>0.0397</v>
       </c>
       <c r="F322" s="9" t="n">
-        <v>0.1278</v>
+        <v>0.1294</v>
       </c>
       <c r="G322" s="6" t="n"/>
       <c r="H322" s="12" t="inlineStr">
@@ -24564,7 +24564,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="5" t="n">
-        <v>-0.04113599765773682</v>
+        <v>-0.0424676558731087</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="8" t="n"/>
@@ -24608,13 +24608,13 @@
         </is>
       </c>
       <c r="D323" s="15" t="n">
-        <v>33.21</v>
+        <v>33.14</v>
       </c>
       <c r="E323" s="16" t="n">
-        <v>-0.1053</v>
+        <v>-0.1072</v>
       </c>
       <c r="F323" s="16" t="n">
-        <v>-0.1467</v>
+        <v>-0.1485</v>
       </c>
       <c r="G323" s="17" t="n">
         <v>46234</v>
@@ -24687,13 +24687,13 @@
         </is>
       </c>
       <c r="D324" s="4" t="n">
-        <v>43.16</v>
+        <v>42.39</v>
       </c>
       <c r="E324" s="9" t="n">
-        <v>0.1828</v>
+        <v>0.1617</v>
       </c>
       <c r="F324" s="9" t="n">
-        <v>0.1101</v>
+        <v>0.09029999999999999</v>
       </c>
       <c r="G324" s="6" t="n">
         <v>46233</v>
@@ -24748,13 +24748,13 @@
         </is>
       </c>
       <c r="D325" s="15" t="n">
-        <v>268.7</v>
+        <v>263.56</v>
       </c>
       <c r="E325" s="20" t="n">
-        <v>0.0818</v>
-      </c>
-      <c r="F325" s="20" t="n">
-        <v>0.0113</v>
+        <v>0.0612</v>
+      </c>
+      <c r="F325" s="16" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="G325" s="17" t="n">
         <v>46240</v>
@@ -24783,7 +24783,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="20" t="n">
-        <v>0.4291030889467808</v>
+        <v>0.4569737441189862</v>
       </c>
       <c r="N325" s="14" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="20" t="n">
-        <v>0.4142165984369185</v>
+        <v>0.4417969342844134</v>
       </c>
       <c r="Q325" s="21" t="inlineStr"/>
       <c r="R325" s="19" t="n"/>
@@ -24837,13 +24837,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>72.25</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="E326" s="5" t="n">
-        <v>-0.0555</v>
+        <v>-0.0554</v>
       </c>
       <c r="F326" s="9" t="n">
-        <v>0.0237</v>
+        <v>0.0238</v>
       </c>
       <c r="G326" s="6" t="n"/>
       <c r="H326" s="12" t="inlineStr">
@@ -24862,7 +24862,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="9" t="n">
-        <v>0.09342560553633218</v>
+        <v>0.09327428729587593</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="8" t="n"/>
@@ -24914,13 +24914,13 @@
         </is>
       </c>
       <c r="D327" s="15" t="n">
-        <v>125.74</v>
+        <v>126.27</v>
       </c>
       <c r="E327" s="16" t="n">
-        <v>-0.0067</v>
+        <v>-0.0024</v>
       </c>
       <c r="F327" s="20" t="n">
-        <v>0.0488</v>
+        <v>0.0532</v>
       </c>
       <c r="G327" s="17" t="n">
         <v>46238</v>
@@ -24949,7 +24949,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="20" t="n">
-        <v>0.08159694607921111</v>
+        <v>0.07705709986536789</v>
       </c>
       <c r="N327" s="14" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="20" t="n">
-        <v>0.1134086209638938</v>
+        <v>0.1087352498614081</v>
       </c>
       <c r="Q327" s="21" t="inlineStr">
         <is>
@@ -25001,13 +25001,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>108.41</v>
+        <v>108.03</v>
       </c>
       <c r="E328" s="5" t="n">
-        <v>-0.0562</v>
+        <v>-0.0595</v>
       </c>
       <c r="F328" s="9" t="n">
-        <v>0.0328</v>
+        <v>0.0292</v>
       </c>
       <c r="G328" s="6" t="n"/>
       <c r="H328" s="12" t="inlineStr">
@@ -25026,7 +25026,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="9" t="n">
-        <v>0.2083756111059866</v>
+        <v>0.2126261223734148</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="9" t="n">
-        <v>0.1161331980444609</v>
+        <v>0.1200592428029251</v>
       </c>
       <c r="Q328" s="10" t="inlineStr">
         <is>
@@ -25082,13 +25082,13 @@
         </is>
       </c>
       <c r="D329" s="15" t="n">
-        <v>87.26000000000001</v>
-      </c>
-      <c r="E329" s="16" t="n">
-        <v>-0.0058</v>
+        <v>87.93000000000001</v>
+      </c>
+      <c r="E329" s="20" t="n">
+        <v>0.0018</v>
       </c>
       <c r="F329" s="20" t="n">
-        <v>0.0431</v>
+        <v>0.051</v>
       </c>
       <c r="G329" s="17" t="n">
         <v>46318</v>
@@ -25124,7 +25124,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="20" t="n">
-        <v>0.2262204904881961</v>
+        <v>0.2168770612987603</v>
       </c>
       <c r="Q329" s="21" t="inlineStr">
         <is>
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>58.68</v>
+        <v>58.58</v>
       </c>
       <c r="E330" s="9" t="n">
-        <v>0.0471</v>
+        <v>0.0453</v>
       </c>
       <c r="F330" s="9" t="n">
-        <v>0.09359999999999999</v>
+        <v>0.0917</v>
       </c>
       <c r="G330" s="6" t="n">
         <v>46237</v>
@@ -25208,7 +25208,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="9" t="n">
-        <v>0.0736196319018405</v>
+        <v>0.07545237282348928</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="8" t="n"/>
@@ -25252,13 +25252,13 @@
         </is>
       </c>
       <c r="D331" s="15" t="n">
-        <v>41</v>
+        <v>41.09</v>
       </c>
       <c r="E331" s="16" t="n">
-        <v>-0.2165</v>
+        <v>-0.2148</v>
       </c>
       <c r="F331" s="16" t="n">
-        <v>-0.3871</v>
+        <v>-0.3857</v>
       </c>
       <c r="G331" s="17" t="n">
         <v>46241</v>
@@ -25313,13 +25313,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>8.390000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>-0.164</v>
+        <v>-0.1426</v>
       </c>
       <c r="F332" s="5" t="n">
-        <v>-0.3495</v>
+        <v>-0.3328</v>
       </c>
       <c r="G332" s="6" t="n">
         <v>46239</v>
@@ -25374,13 +25374,13 @@
         </is>
       </c>
       <c r="D333" s="15" t="n">
-        <v>93.93000000000001</v>
+        <v>94.34</v>
       </c>
       <c r="E333" s="16" t="n">
-        <v>-0.0185</v>
+        <v>-0.0143</v>
       </c>
       <c r="F333" s="20" t="n">
-        <v>0.0551</v>
+        <v>0.0596</v>
       </c>
       <c r="G333" s="17" t="n">
         <v>46233</v>
@@ -25409,7 +25409,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="20" t="n">
-        <v>0.05397636537847326</v>
+        <v>0.04939580241679029</v>
       </c>
       <c r="N333" s="14" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="20" t="n">
-        <v>0.1923773022463536</v>
+        <v>0.1871952512189951</v>
       </c>
       <c r="Q333" s="21" t="inlineStr">
         <is>
@@ -25461,13 +25461,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>109.32</v>
+        <v>110.05</v>
       </c>
       <c r="E334" s="5" t="n">
-        <v>-0.0638</v>
+        <v>-0.0575</v>
       </c>
       <c r="F334" s="9" t="n">
-        <v>0.0067</v>
+        <v>0.0134</v>
       </c>
       <c r="G334" s="6" t="n"/>
       <c r="H334" s="12" t="inlineStr">
@@ -25486,7 +25486,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="9" t="n">
-        <v>0.1617270398829126</v>
+        <v>0.154020899591095</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="8" t="n"/>
@@ -37404,7 +37404,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of July 30, 2026 at 16:18 UTC</t>
+          <t>Data as of July 30, 2026 at 21:50 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>96.08</v>
+        <v>96.19</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.0039</v>
+        <v>0.005</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>-0.0658</v>
+        <v>-0.06480000000000001</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>46239</v>
@@ -878,7 +878,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>0.3009991673605329</v>
+        <v>0.2995113837197214</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.4987510407993339</v>
+        <v>0.4970371140451191</v>
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>353.04</v>
+        <v>356.13</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>-0.0226</v>
+        <v>-0.0141</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>-0.062</v>
+        <v>-0.0538</v>
       </c>
       <c r="G3" s="17" t="n">
         <v>46322</v>
@@ -973,7 +973,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="20" t="n">
-        <v>0.2406526172671651</v>
+        <v>0.2298879622609721</v>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="20" t="n">
-        <v>0.1896668932698844</v>
+        <v>0.1793446213461377</v>
       </c>
       <c r="Q3" s="21" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>549</v>
+        <v>556.71</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>-0.1043</v>
+        <v>-0.0917</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>-0.0857</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="12" t="inlineStr">
@@ -1054,7 +1054,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.5209471766848816</v>
+        <v>0.4998832426218318</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.6939890710382514</v>
+        <v>0.6705286414829982</v>
       </c>
       <c r="Q4" s="10" t="inlineStr">
         <is>
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>39.11</v>
+        <v>39.41</v>
       </c>
       <c r="E5" s="20" t="n">
-        <v>0.0225</v>
+        <v>0.0303</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>0.0639</v>
+        <v>0.0721</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>46238</v>
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>71.43000000000001</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>-0.0371</v>
+        <v>-0.0334</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-0.1679</v>
+        <v>-0.1647</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>46315</v>
@@ -1210,7 +1210,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.1199776004479909</v>
+        <v>0.1156045181982988</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0.3999720005599887</v>
+        <v>0.3945056477478735</v>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
@@ -1262,13 +1262,13 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>78.73999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>0.0346</v>
+        <v>0.034</v>
       </c>
       <c r="F7" s="20" t="n">
-        <v>0.0365</v>
+        <v>0.0359</v>
       </c>
       <c r="G7" s="17" t="n"/>
       <c r="H7" s="23" t="inlineStr">
@@ -1287,7 +1287,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="20" t="n">
-        <v>0.1557023114046229</v>
+        <v>0.1562897077509529</v>
       </c>
       <c r="N7" s="14" t="inlineStr"/>
       <c r="O7" s="19" t="n"/>
@@ -1331,13 +1331,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>510.53</v>
+        <v>499.94</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.0805</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0581</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.0154</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>46238</v>
@@ -1366,7 +1366,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.1163496758270816</v>
+        <v>0.1399967996159538</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.2693475407909428</v>
+        <v>0.2962355482657918</v>
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>182.63</v>
+        <v>181.81</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>-0.0978</v>
+        <v>-0.1019</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>-0.124</v>
+        <v>-0.1279</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>46237</v>
@@ -1487,13 +1487,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>172.47</v>
+        <v>172.71</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>-0.0034</v>
+        <v>-0.002</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-0.0764</v>
+        <v>-0.0751</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>46317</v>
@@ -1522,7 +1522,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>-0.01432133124601379</v>
+        <v>-0.01569104278848942</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.5654896503739781</v>
+        <v>0.563314226159458</v>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>46.47</v>
+        <v>46.81</v>
       </c>
       <c r="E11" s="20" t="n">
-        <v>0.1067</v>
+        <v>0.1148</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>-0.0264</v>
+        <v>-0.0193</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>46316</v>
@@ -1609,7 +1609,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="16" t="n">
-        <v>-0.07467183128900363</v>
+        <v>-0.08139286477248456</v>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="20" t="n">
-        <v>0.07596298687325159</v>
+        <v>0.06814783165990168</v>
       </c>
       <c r="Q11" s="21" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>151.61</v>
+        <v>151.52</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.0292</v>
+        <v>0.0286</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.09970000000000001</v>
+        <v>0.099</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>46240</v>
@@ -1700,7 +1700,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.1938526482422003</v>
+        <v>0.1945617740232312</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0.0223600026383483</v>
+        <v>0.02296726504751841</v>
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
@@ -1752,13 +1752,13 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>271.18</v>
+        <v>271.58</v>
       </c>
       <c r="E13" s="20" t="n">
-        <v>0.122</v>
+        <v>0.1236</v>
       </c>
       <c r="F13" s="20" t="n">
-        <v>0.038</v>
+        <v>0.0395</v>
       </c>
       <c r="G13" s="17" t="n"/>
       <c r="H13" s="23" t="inlineStr">
@@ -1777,7 +1777,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="20" t="n">
-        <v>0.1874032008260196</v>
+        <v>0.1856543191693056</v>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="20" t="n">
-        <v>0.05096246035843349</v>
+        <v>0.04941453715295684</v>
       </c>
       <c r="Q13" s="21" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3016.22</v>
+        <v>3016.25</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>-0.06269999999999999</v>
@@ -1876,7 +1876,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0.375894331315355</v>
+        <v>0.3758806464981351</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0.2267009700883889</v>
+        <v>0.226688769167012</v>
       </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>86.27</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="E15" s="20" t="n">
-        <v>0.1171</v>
+        <v>0.1169</v>
       </c>
       <c r="F15" s="20" t="n">
-        <v>0.1506</v>
+        <v>0.1504</v>
       </c>
       <c r="G15" s="17" t="n">
         <v>46261</v>
@@ -1963,7 +1963,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="16" t="n">
-        <v>-0.2465515242842239</v>
+        <v>-0.2464641780663112</v>
       </c>
       <c r="N15" s="14" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>-0.01472122406398512</v>
+        <v>-0.01460700208671464</v>
       </c>
       <c r="Q15" s="21" t="inlineStr"/>
       <c r="R15" s="19" t="n"/>
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>193.81</v>
+        <v>192.9</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.0612</v>
+        <v>0.0562</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.1451</v>
+        <v>0.1397</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>46238</v>
@@ -2044,7 +2044,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.1041741912182034</v>
+        <v>0.1093831000518403</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.264124658170373</v>
+        <v>0.2700881285640228</v>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
@@ -2104,13 +2104,13 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>370.48</v>
+        <v>368.48</v>
       </c>
       <c r="E17" s="20" t="n">
-        <v>0.1762</v>
+        <v>0.1699</v>
       </c>
       <c r="F17" s="20" t="n">
-        <v>0.1798</v>
+        <v>0.1735</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>46261</v>
@@ -2139,7 +2139,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="20" t="n">
-        <v>0.0122003886849492</v>
+        <v>0.01769431176726004</v>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="20" t="n">
-        <v>0.0122003886849492</v>
+        <v>0.01769431176726004</v>
       </c>
       <c r="Q17" s="21" t="inlineStr"/>
       <c r="R17" s="19" t="n"/>
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>37.69</v>
+        <v>37.22</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.0634</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.2337</v>
+        <v>0.2183</v>
       </c>
       <c r="G18" s="7" t="n"/>
       <c r="H18" s="12" t="inlineStr">
@@ -2214,7 +2214,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.1939506500397984</v>
+        <v>0.2090274046211714</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.1939506500397984</v>
+        <v>0.2090274046211714</v>
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
@@ -2266,13 +2266,13 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>143.91</v>
+        <v>143.06</v>
       </c>
       <c r="E19" s="16" t="n">
-        <v>-0.0837</v>
+        <v>-0.0891</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>-0.0209</v>
+        <v>-0.0267</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>46324</v>
@@ -2301,7 +2301,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="20" t="n">
-        <v>0.1812938642206935</v>
+        <v>0.1883125961135188</v>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="20" t="n">
-        <v>0.2299353762768397</v>
+        <v>0.2372431147770166</v>
       </c>
       <c r="Q19" s="21" t="inlineStr">
         <is>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>196.09</v>
+        <v>195.91</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-0.1465</v>
+        <v>-0.1473</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.09699999999999999</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>46261</v>
@@ -2388,7 +2388,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0.1219338059054516</v>
+        <v>0.1229646266142617</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="9" t="n"/>
@@ -2432,13 +2432,13 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>127.85</v>
+        <v>127.21</v>
       </c>
       <c r="E21" s="20" t="n">
-        <v>0.0553</v>
+        <v>0.05</v>
       </c>
       <c r="F21" s="20" t="n">
-        <v>0.1482</v>
+        <v>0.1424</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>46267</v>
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>88.3</v>
+        <v>88.86</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.1692</v>
+        <v>0.1766</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.068</v>
+        <v>0.0747</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>46315</v>
@@ -2528,7 +2528,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>-0.3091732729331823</v>
+        <v>-0.3135268962412784</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.1325028312570782</v>
+        <v>0.1253657438667567</v>
       </c>
       <c r="Q22" s="10" t="inlineStr">
         <is>
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>124.74</v>
+        <v>124.37</v>
       </c>
       <c r="E23" s="20" t="n">
-        <v>0.0625</v>
+        <v>0.0594</v>
       </c>
       <c r="F23" s="20" t="n">
-        <v>0.2825</v>
+        <v>0.2787</v>
       </c>
       <c r="G23" s="17" t="n">
         <v>46315</v>
@@ -2618,7 +2618,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="20" t="n">
-        <v>0.1624178290844958</v>
+        <v>0.1658760151161855</v>
       </c>
       <c r="Q23" s="21" t="inlineStr"/>
       <c r="R23" s="19" t="n"/>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>331.5</v>
+        <v>331.96</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>-0.0551</v>
+        <v>-0.0538</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.067</v>
+        <v>0.06849999999999999</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>46252</v>
@@ -2688,7 +2688,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0.08597285067873303</v>
+        <v>0.08446800819375835</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0.2066365007541478</v>
+        <v>0.2049644535486204</v>
       </c>
       <c r="Q24" s="10" t="inlineStr">
         <is>
@@ -2748,13 +2748,13 @@
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>208.9</v>
+        <v>207.81</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>-0.0587</v>
+        <v>-0.0636</v>
       </c>
       <c r="F25" s="20" t="n">
-        <v>0.0058</v>
+        <v>0.0005</v>
       </c>
       <c r="G25" s="17" t="n">
         <v>46253</v>
@@ -2783,7 +2783,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="20" t="n">
-        <v>0.2206797510770703</v>
+        <v>0.2270824310668399</v>
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="20" t="n">
-        <v>0.1010052656773576</v>
+        <v>0.1067802319426399</v>
       </c>
       <c r="Q25" s="21" t="inlineStr">
         <is>
@@ -2839,13 +2839,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>269.8</v>
+        <v>270.64</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-0.0229</v>
+        <v>-0.0198</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>46238</v>
@@ -2874,7 +2874,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.111934766493699</v>
+        <v>0.1084835944428023</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0.2972572275759822</v>
+        <v>0.2932308601832693</v>
       </c>
       <c r="Q26" s="10" t="inlineStr">
         <is>
@@ -2926,13 +2926,13 @@
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>41.67</v>
+        <v>41.71</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>-0.0323</v>
+        <v>-0.0314</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>-0.09269999999999999</v>
+        <v>-0.0919</v>
       </c>
       <c r="G27" s="17" t="n">
         <v>46289</v>
@@ -2987,13 +2987,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>88.98999999999999</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>-0.0399</v>
+        <v>-0.036</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.0271</v>
+        <v>0.0313</v>
       </c>
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="12" t="inlineStr">
@@ -3012,7 +3012,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.2360939431396787</v>
+        <v>0.2311135982092894</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.2922800314642096</v>
+        <v>0.2870733072188025</v>
       </c>
       <c r="Q28" s="10" t="inlineStr">
         <is>
@@ -3068,13 +3068,13 @@
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>185.82</v>
+        <v>185.71</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>-0.1385</v>
+        <v>-0.139</v>
       </c>
       <c r="F29" s="20" t="n">
-        <v>0.0206</v>
+        <v>0.02</v>
       </c>
       <c r="G29" s="17" t="n">
         <v>46317</v>
@@ -3129,13 +3129,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>251.95</v>
+        <v>251.07</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.189</v>
+        <v>0.1849</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.1244</v>
+        <v>0.1205</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>46254</v>
@@ -3164,7 +3164,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.02758483826155979</v>
+        <v>-0.02417652447524592</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.0517959912681088</v>
+        <v>0.05548253475126461</v>
       </c>
       <c r="Q30" s="10" t="inlineStr">
         <is>
@@ -3216,13 +3216,13 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>105.15</v>
+        <v>105.25</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="F31" s="20" t="n">
-        <v>0.0895</v>
+        <v>0.0906</v>
       </c>
       <c r="G31" s="17" t="n"/>
       <c r="H31" s="23" t="inlineStr">
@@ -3241,7 +3241,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="20" t="n">
-        <v>0.1412268188302425</v>
+        <v>0.1401425178147268</v>
       </c>
       <c r="N31" s="14" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="20" t="n">
-        <v>0.09367570137898235</v>
+        <v>0.09263657957244656</v>
       </c>
       <c r="Q31" s="21" t="inlineStr">
         <is>
@@ -3293,13 +3293,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>14.72</v>
+        <v>14.54</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-0.0265</v>
+        <v>-0.0384</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0559</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>46237</v>
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>157.77</v>
+        <v>157.34</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>0.0424</v>
+        <v>0.0396</v>
       </c>
       <c r="F33" s="20" t="n">
-        <v>0.0329</v>
+        <v>0.03</v>
       </c>
       <c r="G33" s="17" t="n">
         <v>46253</v>
@@ -3389,7 +3389,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="20" t="n">
-        <v>0.01413449958800779</v>
+        <v>0.01690606330240242</v>
       </c>
       <c r="N33" s="14" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="20" t="n">
-        <v>0.1092096089243835</v>
+        <v>0.1122410067370026</v>
       </c>
       <c r="Q33" s="21" t="inlineStr">
         <is>
@@ -3445,13 +3445,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>30.51</v>
+        <v>30.77</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>-0.0542</v>
+        <v>-0.0462</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>-0.04</v>
+        <v>-0.0318</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>46317</v>
@@ -3480,7 +3480,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.1471648639790232</v>
+        <v>0.1374715632109197</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0.3110455588331694</v>
+        <v>0.2999675008124797</v>
       </c>
       <c r="Q34" s="10" t="inlineStr">
         <is>
@@ -3532,13 +3532,13 @@
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>309.95</v>
+        <v>311.21</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>-0.2712</v>
+        <v>-0.2683</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>-0.2547</v>
+        <v>-0.2517</v>
       </c>
       <c r="G35" s="17" t="n">
         <v>46323</v>
@@ -3567,7 +3567,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="16" t="n">
-        <v>-0.5805775125020164</v>
+        <v>-0.582275633816394</v>
       </c>
       <c r="N35" s="14" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>-0.03210195192773024</v>
+        <v>-0.0360206934224478</v>
       </c>
       <c r="Q35" s="21" t="inlineStr">
         <is>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>69.88</v>
+        <v>70.36</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>-0.0383</v>
+        <v>-0.0317</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>-0.0527</v>
+        <v>-0.0462</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>46239</v>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="D37" s="15" t="n">
-        <v>508.26</v>
+        <v>512.83</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>0.1176</v>
+        <v>0.1276</v>
       </c>
       <c r="F37" s="20" t="n">
-        <v>0.015</v>
+        <v>0.0241</v>
       </c>
       <c r="G37" s="17" t="n">
         <v>46261</v>
@@ -3715,7 +3715,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="16" t="n">
-        <v>-0.1146263723291229</v>
+        <v>-0.1225162334496813</v>
       </c>
       <c r="N37" s="14" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="20" t="n">
-        <v>0.2493605634911266</v>
+        <v>0.2382270927987831</v>
       </c>
       <c r="Q37" s="21" t="inlineStr">
         <is>
@@ -3771,13 +3771,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>98.83</v>
+        <v>98.81</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0165</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.0371</v>
+        <v>0.0368</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>46234</v>
@@ -3806,7 +3806,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.1130223616310837</v>
+        <v>0.1132476469992915</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.06243043610239808</v>
+        <v>0.06264548122659648</v>
       </c>
       <c r="Q38" s="10" t="inlineStr">
         <is>
@@ -3862,13 +3862,13 @@
         </is>
       </c>
       <c r="D39" s="15" t="n">
-        <v>91.38</v>
+        <v>91.3</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>-0.0149</v>
+        <v>-0.0157</v>
       </c>
       <c r="F39" s="20" t="n">
-        <v>0.0334</v>
+        <v>0.0325</v>
       </c>
       <c r="G39" s="17" t="n">
         <v>46234</v>
@@ -3897,7 +3897,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="20" t="n">
-        <v>0.03961479536003507</v>
+        <v>0.04052573932092007</v>
       </c>
       <c r="N39" s="14" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="20" t="n">
-        <v>0.09433136353687901</v>
+        <v>0.09529025191675798</v>
       </c>
       <c r="Q39" s="21" t="inlineStr">
         <is>
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>951.38</v>
+        <v>951.89</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.0289</v>
+        <v>0.0294</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.0061</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>46289</v>
@@ -3988,7 +3988,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0.05110471105131494</v>
+        <v>0.05054155417117526</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0.1562151821564464</v>
+        <v>0.1555957095882928</v>
       </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
@@ -4048,13 +4048,13 @@
         </is>
       </c>
       <c r="D41" s="15" t="n">
-        <v>127.31</v>
+        <v>127.05</v>
       </c>
       <c r="E41" s="20" t="n">
-        <v>0.1051</v>
+        <v>0.1029</v>
       </c>
       <c r="F41" s="20" t="n">
-        <v>0.1581</v>
+        <v>0.1557</v>
       </c>
       <c r="G41" s="17" t="n">
         <v>46261</v>
@@ -4083,7 +4083,7 @@
         <v>125</v>
       </c>
       <c r="M41" s="16" t="n">
-        <v>-0.01814468619904173</v>
+        <v>-0.01613537977174339</v>
       </c>
       <c r="N41" s="14" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="20" t="n">
-        <v>0.06040373890503493</v>
+        <v>0.06257378984651714</v>
       </c>
       <c r="Q41" s="21" t="inlineStr">
         <is>
@@ -4135,13 +4135,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>26.02</v>
+        <v>25.85</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.0406</v>
+        <v>0.0336</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.1014</v>
+        <v>0.09390000000000001</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>46239</v>
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="D43" s="15" t="n">
-        <v>87.34</v>
+        <v>87.59</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>0.07440000000000001</v>
+        <v>0.0775</v>
       </c>
       <c r="F43" s="20" t="n">
-        <v>0.1106</v>
+        <v>0.1138</v>
       </c>
       <c r="G43" s="17" t="n"/>
       <c r="H43" s="23" t="inlineStr">
@@ -4221,7 +4221,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="20" t="n">
-        <v>0.03045569040531253</v>
+        <v>0.02751455645621642</v>
       </c>
       <c r="N43" s="14" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>88</v>
       </c>
       <c r="P43" s="20" t="n">
-        <v>0.007556675062972253</v>
+        <v>0.00468089964607828</v>
       </c>
       <c r="Q43" s="21" t="inlineStr">
         <is>
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>57.97</v>
+        <v>57.74</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.0308</v>
+        <v>0.0267</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>-0.05769999999999999</v>
+        <v>-0.0614</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>46275</v>
@@ -4316,7 +4316,7 @@
         <v>58</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>0.0005175090564085068</v>
+        <v>0.004502944232767544</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.3455235466620666</v>
+        <v>0.3508832698302736</v>
       </c>
       <c r="Q44" s="10" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         </is>
       </c>
       <c r="D45" s="15" t="n">
-        <v>62.24</v>
+        <v>62.31</v>
       </c>
       <c r="E45" s="20" t="n">
-        <v>0.0488</v>
+        <v>0.0499</v>
       </c>
       <c r="F45" s="20" t="n">
-        <v>0.0196</v>
+        <v>0.0206</v>
       </c>
       <c r="G45" s="17" t="n"/>
       <c r="H45" s="23" t="inlineStr">
@@ -4393,7 +4393,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="20" t="n">
-        <v>0.1246786632390745</v>
+        <v>0.1234151821537473</v>
       </c>
       <c r="N45" s="14" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="20" t="n">
-        <v>0.140745501285347</v>
+        <v>0.1394639704702295</v>
       </c>
       <c r="Q45" s="21" t="inlineStr">
         <is>
@@ -4453,13 +4453,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>51.08</v>
+        <v>50.9</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>-0.0346</v>
+        <v>-0.038</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.09269999999999999</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>46301</v>
@@ -4524,13 +4524,13 @@
         </is>
       </c>
       <c r="D47" s="15" t="n">
-        <v>96.56999999999999</v>
+        <v>96.38</v>
       </c>
       <c r="E47" s="16" t="n">
-        <v>-0.008</v>
+        <v>-0.01</v>
       </c>
       <c r="F47" s="20" t="n">
-        <v>0.0839</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="G47" s="17" t="n">
         <v>46240</v>
@@ -4585,13 +4585,13 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>69.26000000000001</v>
+        <v>68.33</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>-0.0319</v>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>0.0089</v>
+        <v>-0.0449</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="G48" s="7" t="n"/>
       <c r="H48" s="12" t="inlineStr">
@@ -4636,13 +4636,13 @@
         </is>
       </c>
       <c r="D49" s="15" t="n">
-        <v>139.58</v>
+        <v>139.56</v>
       </c>
       <c r="E49" s="16" t="n">
-        <v>-0.0112</v>
+        <v>-0.0113</v>
       </c>
       <c r="F49" s="16" t="n">
-        <v>-0.0137</v>
+        <v>-0.0138</v>
       </c>
       <c r="G49" s="17" t="n">
         <v>46303</v>
@@ -4671,7 +4671,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="20" t="n">
-        <v>0.003009027081243641</v>
+        <v>0.00315276583548293</v>
       </c>
       <c r="N49" s="14" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="20" t="n">
-        <v>0.07465252901561818</v>
+        <v>0.07480653482373172</v>
       </c>
       <c r="Q49" s="21" t="inlineStr">
         <is>
@@ -4731,13 +4731,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>143.89</v>
+        <v>144.49</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>-0.024</v>
+        <v>-0.0199</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.0257</v>
+        <v>0.03</v>
       </c>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="12" t="inlineStr">
@@ -4756,7 +4756,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.1397595385363821</v>
+        <v>0.1350266454425911</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0.1258600319688652</v>
+        <v>0.1211848570835351</v>
       </c>
       <c r="Q50" s="10" t="inlineStr">
         <is>
@@ -4820,13 +4820,13 @@
         </is>
       </c>
       <c r="D51" s="15" t="n">
-        <v>85.34999999999999</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="E51" s="20" t="n">
-        <v>0.0218</v>
+        <v>0.0205</v>
       </c>
       <c r="F51" s="20" t="n">
-        <v>0.1578</v>
+        <v>0.1563</v>
       </c>
       <c r="G51" s="17" t="n">
         <v>46238</v>
@@ -4855,7 +4855,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="20" t="n">
-        <v>0.1716461628588167</v>
+        <v>0.1731581417175036</v>
       </c>
       <c r="N51" s="14" t="inlineStr"/>
       <c r="O51" s="19" t="n"/>
@@ -4899,13 +4899,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>143.93</v>
+        <v>144.49</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.1047</v>
+        <v>0.109</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.1635</v>
+        <v>0.168</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>46253</v>
@@ -4934,7 +4934,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-0.02730493990134097</v>
+        <v>-0.03107481486608076</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>-0.0620440491905788</v>
+        <v>-0.06567928576372073</v>
       </c>
       <c r="Q52" s="10" t="inlineStr">
         <is>
@@ -4990,13 +4990,13 @@
         </is>
       </c>
       <c r="D53" s="15" t="n">
-        <v>111.6</v>
+        <v>111.2</v>
       </c>
       <c r="E53" s="20" t="n">
-        <v>0.0255</v>
+        <v>0.0219</v>
       </c>
       <c r="F53" s="16" t="n">
-        <v>-0.0262</v>
+        <v>-0.0297</v>
       </c>
       <c r="G53" s="17" t="n">
         <v>46254</v>
@@ -5025,7 +5025,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="20" t="n">
-        <v>0.2544802867383513</v>
+        <v>0.2589928057553956</v>
       </c>
       <c r="N53" s="14" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="20" t="n">
-        <v>0.2544802867383513</v>
+        <v>0.2589928057553956</v>
       </c>
       <c r="Q53" s="21" t="inlineStr">
         <is>
@@ -5085,13 +5085,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>60.48</v>
+        <v>60.49</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0.1237</v>
+        <v>0.1239</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>-0.0395</v>
+        <v>-0.0394</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>46316</v>
@@ -5127,7 +5127,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>0.2566137566137567</v>
+        <v>0.2564060175235576</v>
       </c>
       <c r="Q54" s="10" t="inlineStr">
         <is>
@@ -5168,13 +5168,13 @@
         </is>
       </c>
       <c r="D55" s="15" t="n">
-        <v>119.13</v>
+        <v>120.48</v>
       </c>
       <c r="E55" s="20" t="n">
-        <v>0.1541</v>
+        <v>0.1672</v>
       </c>
       <c r="F55" s="20" t="n">
-        <v>0.0307</v>
+        <v>0.0424</v>
       </c>
       <c r="G55" s="17" t="n">
         <v>46240</v>
@@ -5203,7 +5203,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="20" t="n">
-        <v>0.5361369932007052</v>
+        <v>0.5189243027888446</v>
       </c>
       <c r="N55" s="14" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="20" t="n">
-        <v>0.2171577268530178</v>
+        <v>0.2035192563081009</v>
       </c>
       <c r="Q55" s="21" t="inlineStr">
         <is>
@@ -5255,13 +5255,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>195.46</v>
+        <v>196.83</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.1797</v>
+        <v>0.1879</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.0518</v>
+        <v>0.0592</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>46234</v>
@@ -5290,7 +5290,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>0.1357822572393328</v>
+        <v>0.127876848041457</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>0.1511306661209454</v>
+        <v>0.1431184270690443</v>
       </c>
       <c r="Q56" s="10" t="inlineStr">
         <is>
@@ -5346,13 +5346,13 @@
         </is>
       </c>
       <c r="D57" s="15" t="n">
-        <v>146.82</v>
+        <v>148.69</v>
       </c>
       <c r="E57" s="20" t="n">
-        <v>0.1417</v>
+        <v>0.1563</v>
       </c>
       <c r="F57" s="20" t="n">
-        <v>0.0746</v>
+        <v>0.0883</v>
       </c>
       <c r="G57" s="17" t="n">
         <v>46238</v>
@@ -5381,7 +5381,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="20" t="n">
-        <v>0.3349679880125324</v>
+        <v>0.3181787611809806</v>
       </c>
       <c r="N57" s="14" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="20" t="n">
-        <v>0.157880397765972</v>
+        <v>0.1433183132692178</v>
       </c>
       <c r="Q57" s="21" t="inlineStr">
         <is>
@@ -5437,13 +5437,13 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>37.94</v>
+        <v>38.05</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.0389</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.0196</v>
+        <v>0.0226</v>
       </c>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="12" t="inlineStr">
@@ -5488,13 +5488,13 @@
         </is>
       </c>
       <c r="D59" s="15" t="n">
-        <v>20.41</v>
+        <v>20.36</v>
       </c>
       <c r="E59" s="20" t="n">
-        <v>0.07139999999999999</v>
+        <v>0.0688</v>
       </c>
       <c r="F59" s="20" t="n">
-        <v>0.0592</v>
+        <v>0.0566</v>
       </c>
       <c r="G59" s="17" t="n">
         <v>46238</v>
@@ -5549,13 +5549,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>201.73</v>
+        <v>202.95</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0.1731</v>
+        <v>0.1802</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0197</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>46237</v>
@@ -5610,13 +5610,13 @@
         </is>
       </c>
       <c r="D61" s="15" t="n">
-        <v>32.06</v>
+        <v>32.25</v>
       </c>
       <c r="E61" s="16" t="n">
-        <v>-0.0286</v>
+        <v>-0.023</v>
       </c>
       <c r="F61" s="16" t="n">
-        <v>-0.1851</v>
+        <v>-0.1804</v>
       </c>
       <c r="G61" s="17" t="n">
         <v>46315</v>
@@ -5652,7 +5652,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="20" t="n">
-        <v>0.3412351840299437</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Q61" s="21" t="inlineStr">
         <is>
@@ -5697,13 +5697,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>32.04</v>
+        <v>32.18</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0145</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>0.0387</v>
+        <v>0.0431</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>46316</v>
@@ -5732,7 +5732,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.09238451935081152</v>
+        <v>0.08763206960845246</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="9" t="n"/>
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="D63" s="15" t="n">
-        <v>209.83</v>
+        <v>211.68</v>
       </c>
       <c r="E63" s="20" t="n">
-        <v>0.2025</v>
+        <v>0.2131</v>
       </c>
       <c r="F63" s="20" t="n">
-        <v>0.1642</v>
+        <v>0.1744</v>
       </c>
       <c r="G63" s="17" t="n">
         <v>46239</v>
@@ -5837,13 +5837,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>49.4</v>
+        <v>49.59</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0.09570000000000001</v>
+        <v>0.0998</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>-0.09759999999999999</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>46311</v>
@@ -5879,7 +5879,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0.2753036437246964</v>
+        <v>0.2704174228675135</v>
       </c>
       <c r="Q64" s="10" t="inlineStr">
         <is>
@@ -5928,13 +5928,13 @@
         </is>
       </c>
       <c r="D65" s="15" t="n">
-        <v>44.18</v>
+        <v>44.61</v>
       </c>
       <c r="E65" s="20" t="n">
-        <v>0.0718</v>
+        <v>0.08220000000000001</v>
       </c>
       <c r="F65" s="16" t="n">
-        <v>-0.0314</v>
+        <v>-0.0219</v>
       </c>
       <c r="G65" s="17" t="n">
         <v>46237</v>
@@ -5989,13 +5989,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>71.29000000000001</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>-0.0204</v>
+        <v>-0.0169</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.0178</v>
+        <v>0.0214</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>46237</v>
@@ -6024,7 +6024,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0.2484219385608079</v>
+        <v>0.2440592675426334</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="9" t="n"/>
@@ -6080,13 +6080,13 @@
         </is>
       </c>
       <c r="D67" s="15" t="n">
-        <v>153.96</v>
+        <v>155.44</v>
       </c>
       <c r="E67" s="20" t="n">
-        <v>0.1298</v>
+        <v>0.1406</v>
       </c>
       <c r="F67" s="20" t="n">
-        <v>0.0307</v>
+        <v>0.0406</v>
       </c>
       <c r="G67" s="17" t="n">
         <v>46234</v>
@@ -6115,7 +6115,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="20" t="n">
-        <v>0.2016108080020784</v>
+        <v>0.1901698404529079</v>
       </c>
       <c r="N67" s="14" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="20" t="n">
-        <v>0.2016108080020784</v>
+        <v>0.1901698404529079</v>
       </c>
       <c r="Q67" s="21" t="inlineStr">
         <is>
@@ -6171,13 +6171,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>127.95</v>
+        <v>127.48</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0.07980000000000001</v>
+        <v>0.0759</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.1413</v>
+        <v>0.1371</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>46240</v>
@@ -6206,7 +6206,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="6" t="n">
-        <v>-0.06213364595545137</v>
+        <v>-0.05867587072481961</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>115</v>
       </c>
       <c r="P68" s="6" t="n">
-        <v>-0.1012114107073076</v>
+        <v>-0.09789770944461879</v>
       </c>
       <c r="Q68" s="10" t="inlineStr"/>
       <c r="R68" s="9" t="n"/>
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="D69" s="15" t="n">
-        <v>363.85</v>
+        <v>360.55</v>
       </c>
       <c r="E69" s="20" t="n">
-        <v>0.059</v>
+        <v>0.0495</v>
       </c>
       <c r="F69" s="20" t="n">
-        <v>0.1356</v>
+        <v>0.1253</v>
       </c>
       <c r="G69" s="17" t="n"/>
       <c r="H69" s="23" t="inlineStr">
@@ -6277,7 +6277,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="20" t="n">
-        <v>0.1158444413906829</v>
+        <v>0.126057412286784</v>
       </c>
       <c r="N69" s="14" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="20" t="n">
-        <v>0.1982960010993541</v>
+        <v>0.2092636250173346</v>
       </c>
       <c r="Q69" s="21" t="inlineStr">
         <is>
@@ -6325,13 +6325,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>337.36</v>
+        <v>336.25</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>-0.0306</v>
+        <v>-0.0338</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.076</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>46311</v>
@@ -6360,7 +6360,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.2301399098885463</v>
+        <v>0.2342007434944238</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.1263931705003556</v>
+        <v>0.1301115241635688</v>
       </c>
       <c r="Q70" s="10" t="inlineStr">
         <is>
@@ -6420,13 +6420,13 @@
         </is>
       </c>
       <c r="D71" s="15" t="n">
-        <v>62.08</v>
+        <v>61.95</v>
       </c>
       <c r="E71" s="20" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.06150000000000001</v>
       </c>
       <c r="F71" s="20" t="n">
-        <v>0.2051</v>
+        <v>0.2027</v>
       </c>
       <c r="G71" s="17" t="n">
         <v>46309</v>
@@ -6481,13 +6481,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1094.05</v>
+        <v>1090.39</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0.1159</v>
+        <v>0.1122</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.0718</v>
+        <v>0.0682</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>46308</v>
@@ -6519,7 +6519,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.1379735843882821</v>
+        <v>0.1417933033134932</v>
       </c>
       <c r="Q72" s="10" t="inlineStr">
         <is>
@@ -6564,13 +6564,13 @@
         </is>
       </c>
       <c r="D73" s="15" t="n">
-        <v>21.37</v>
+        <v>21.79</v>
       </c>
       <c r="E73" s="16" t="n">
-        <v>-0.153</v>
+        <v>-0.1363</v>
       </c>
       <c r="F73" s="16" t="n">
-        <v>-0.3347</v>
+        <v>-0.3215999999999999</v>
       </c>
       <c r="G73" s="17" t="n">
         <v>46281</v>
@@ -6625,13 +6625,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>16.91</v>
+        <v>17.28</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0.1951</v>
+        <v>0.2212</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>-0.1029</v>
+        <v>-0.0833</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>46346</v>
@@ -6686,13 +6686,13 @@
         </is>
       </c>
       <c r="D75" s="15" t="n">
-        <v>512.66</v>
+        <v>511.54</v>
       </c>
       <c r="E75" s="20" t="n">
-        <v>0.0259</v>
+        <v>0.0236</v>
       </c>
       <c r="F75" s="20" t="n">
-        <v>0.0901</v>
+        <v>0.0877</v>
       </c>
       <c r="G75" s="17" t="n">
         <v>46241</v>
@@ -6769,13 +6769,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>70.62</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0.0484</v>
+        <v>0.0451</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.2394</v>
+        <v>0.2355</v>
       </c>
       <c r="G76" s="7" t="n"/>
       <c r="H76" s="12" t="inlineStr">
@@ -6794,7 +6794,7 @@
         <v>68</v>
       </c>
       <c r="M76" s="6" t="n">
-        <v>-0.037099971679411</v>
+        <v>-0.03409090909090917</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="9" t="n"/>
@@ -6836,13 +6836,13 @@
         </is>
       </c>
       <c r="D77" s="15" t="n">
-        <v>128.49</v>
+        <v>127.75</v>
       </c>
       <c r="E77" s="20" t="n">
-        <v>0.0747</v>
+        <v>0.06860000000000001</v>
       </c>
       <c r="F77" s="20" t="n">
-        <v>0.0987</v>
+        <v>0.0924</v>
       </c>
       <c r="G77" s="17" t="n">
         <v>46310</v>
@@ -6901,13 +6901,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>133.03</v>
+        <v>132.45</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>-0.0507</v>
+        <v>-0.0548</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.0305</v>
+        <v>0.026</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>46308</v>
@@ -6939,7 +6939,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.05239419679771479</v>
+        <v>0.05700264250660636</v>
       </c>
       <c r="Q78" s="10" t="inlineStr">
         <is>
@@ -6988,13 +6988,13 @@
         </is>
       </c>
       <c r="D79" s="15" t="n">
-        <v>352.45</v>
-      </c>
-      <c r="E79" s="20" t="n">
-        <v>0.002</v>
+        <v>350.68</v>
+      </c>
+      <c r="E79" s="16" t="n">
+        <v>-0.003</v>
       </c>
       <c r="F79" s="20" t="n">
-        <v>0.1377</v>
+        <v>0.132</v>
       </c>
       <c r="G79" s="17" t="n">
         <v>46315</v>
@@ -7023,7 +7023,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="20" t="n">
-        <v>0.01574691445595123</v>
+        <v>0.02087373103684268</v>
       </c>
       <c r="N79" s="14" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="20" t="n">
-        <v>0.06114342459923397</v>
+        <v>0.06649937264742783</v>
       </c>
       <c r="Q79" s="21" t="inlineStr">
         <is>
@@ -7079,13 +7079,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>59.55</v>
+        <v>59.27</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0.1574</v>
+        <v>0.152</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>46310</v>
@@ -7114,7 +7114,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="6" t="n">
-        <v>-0.04282115869017628</v>
+        <v>-0.03829930825037967</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="9" t="n"/>
@@ -7156,13 +7156,13 @@
         </is>
       </c>
       <c r="D81" s="15" t="n">
-        <v>13.87</v>
+        <v>13.76</v>
       </c>
       <c r="E81" s="20" t="n">
-        <v>0.0184</v>
+        <v>0.0103</v>
       </c>
       <c r="F81" s="16" t="n">
-        <v>-0.2626</v>
+        <v>-0.2685</v>
       </c>
       <c r="G81" s="17" t="n">
         <v>46240</v>
@@ -7217,13 +7217,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>380.8</v>
+        <v>382.11</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0.1169</v>
+        <v>0.1208</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.0458</v>
+        <v>0.04940000000000001</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>46239</v>
@@ -7290,13 +7290,13 @@
         </is>
       </c>
       <c r="D83" s="15" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="E83" s="16" t="n">
-        <v>-0.0169</v>
+        <v>62.61</v>
+      </c>
+      <c r="E83" s="20" t="n">
+        <v>0.0107</v>
       </c>
       <c r="F83" s="16" t="n">
-        <v>-0.4198</v>
+        <v>-0.4035</v>
       </c>
       <c r="G83" s="17" t="n">
         <v>46239</v>
@@ -7351,13 +7351,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>52.21</v>
+        <v>53</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0.0611</v>
+        <v>0.07719999999999999</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0.1547</v>
+        <v>0.1723</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>46240</v>
@@ -7412,13 +7412,13 @@
         </is>
       </c>
       <c r="D85" s="15" t="n">
-        <v>1022.13</v>
-      </c>
-      <c r="E85" s="20" t="n">
-        <v>0.0025</v>
+        <v>1018.38</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>-0.0012</v>
       </c>
       <c r="F85" s="16" t="n">
-        <v>-0.0252</v>
+        <v>-0.0288</v>
       </c>
       <c r="G85" s="17" t="n">
         <v>46308</v>
@@ -7447,7 +7447,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="20" t="n">
-        <v>0.2963126021151908</v>
+        <v>0.3010860386103419</v>
       </c>
       <c r="N85" s="14" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="20" t="n">
-        <v>0.183802451742929</v>
+        <v>0.1881615899762368</v>
       </c>
       <c r="Q85" s="21" t="inlineStr">
         <is>
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>126.1</v>
+        <v>125.49</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>-0.1016</v>
+        <v>-0.1059</v>
       </c>
       <c r="G86" s="7" t="n"/>
       <c r="H86" s="12" t="inlineStr">
@@ -7550,13 +7550,13 @@
         </is>
       </c>
       <c r="D87" s="15" t="n">
-        <v>86.17</v>
+        <v>86.56</v>
       </c>
       <c r="E87" s="16" t="n">
-        <v>-0.2069</v>
+        <v>-0.2033</v>
       </c>
       <c r="F87" s="16" t="n">
-        <v>-0.0503</v>
+        <v>-0.046</v>
       </c>
       <c r="G87" s="17" t="n"/>
       <c r="H87" s="23" t="inlineStr">
@@ -7601,13 +7601,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>108.2</v>
+        <v>107.63</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0.0228</v>
+        <v>0.0174</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>-0.1827</v>
+        <v>-0.187</v>
       </c>
       <c r="G88" s="7" t="n">
         <v>46238</v>
@@ -7662,13 +7662,13 @@
         </is>
       </c>
       <c r="D89" s="15" t="n">
-        <v>153.76</v>
+        <v>152.48</v>
       </c>
       <c r="E89" s="20" t="n">
-        <v>0.2133</v>
+        <v>0.2032</v>
       </c>
       <c r="F89" s="20" t="n">
-        <v>0.0607</v>
+        <v>0.0519</v>
       </c>
       <c r="G89" s="17" t="n"/>
       <c r="H89" s="23" t="inlineStr">
@@ -7713,13 +7713,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>152.94</v>
+        <v>154.04</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0987</v>
       </c>
       <c r="G90" s="7" t="n">
         <v>46252</v>
@@ -7788,13 +7788,13 @@
         </is>
       </c>
       <c r="D91" s="15" t="n">
-        <v>353.11</v>
+        <v>351.79</v>
       </c>
       <c r="E91" s="20" t="n">
-        <v>0.057</v>
+        <v>0.053</v>
       </c>
       <c r="F91" s="20" t="n">
-        <v>0.1906</v>
+        <v>0.1862</v>
       </c>
       <c r="G91" s="17" t="n">
         <v>46308</v>
@@ -7823,7 +7823,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="16" t="n">
-        <v>-0.4449321741100507</v>
+        <v>-0.4428494272151</v>
       </c>
       <c r="N91" s="14" t="inlineStr"/>
       <c r="O91" s="19" t="n"/>
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>100.48</v>
+        <v>101.43</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0.08560000000000001</v>
+        <v>0.0958</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.0576</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="12" t="inlineStr">
@@ -7892,7 +7892,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>2.732085987261146</v>
+        <v>2.697131026323573</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>2.662420382165605</v>
+        <v>2.628117913832199</v>
       </c>
       <c r="Q92" s="10" t="inlineStr">
         <is>
@@ -7956,13 +7956,13 @@
         </is>
       </c>
       <c r="D93" s="15" t="n">
-        <v>354.38</v>
+        <v>356.42</v>
       </c>
       <c r="E93" s="20" t="n">
-        <v>0.0264</v>
+        <v>0.0323</v>
       </c>
       <c r="F93" s="20" t="n">
-        <v>0.1675</v>
+        <v>0.1742</v>
       </c>
       <c r="G93" s="17" t="n">
         <v>46317</v>
@@ -7994,7 +7994,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="16" t="n">
-        <v>-0.6754895874485016</v>
+        <v>-0.67734695022726</v>
       </c>
       <c r="Q93" s="21" t="inlineStr">
         <is>
@@ -8043,13 +8043,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>572.84</v>
+        <v>573.1</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0.0965</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.1567</v>
+        <v>0.1572</v>
       </c>
       <c r="G94" s="7" t="n"/>
       <c r="H94" s="12" t="inlineStr">
@@ -8068,7 +8068,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="6" t="n">
-        <v>-0.3610781370016061</v>
+        <v>-0.3613679986040831</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="9" t="n"/>
@@ -8110,13 +8110,13 @@
         </is>
       </c>
       <c r="D95" s="15" t="n">
-        <v>1883.52</v>
+        <v>1882.34</v>
       </c>
       <c r="E95" s="16" t="n">
-        <v>-0.0173</v>
+        <v>-0.0179</v>
       </c>
       <c r="F95" s="20" t="n">
-        <v>0.0524</v>
+        <v>0.0518</v>
       </c>
       <c r="G95" s="17" t="n"/>
       <c r="H95" s="23" t="inlineStr">
@@ -8171,13 +8171,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>210.83</v>
+        <v>210.42</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>-0.0049</v>
+        <v>-0.0068</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>-0.0009</v>
+        <v>-0.0028</v>
       </c>
       <c r="G96" s="7" t="n">
         <v>46309</v>
@@ -8206,7 +8206,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>2.16842954038799</v>
+        <v>2.174603174603175</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>1.60873689702604</v>
+        <v>1.613819979089441</v>
       </c>
       <c r="Q96" s="10" t="inlineStr">
         <is>
@@ -8266,13 +8266,13 @@
         </is>
       </c>
       <c r="D97" s="15" t="n">
-        <v>113.84</v>
+        <v>113.7</v>
       </c>
       <c r="E97" s="20" t="n">
-        <v>0.0451</v>
+        <v>0.0438</v>
       </c>
       <c r="F97" s="20" t="n">
-        <v>0.1063</v>
+        <v>0.105</v>
       </c>
       <c r="G97" s="17" t="n"/>
       <c r="H97" s="23" t="inlineStr">
@@ -8291,7 +8291,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="20" t="n">
-        <v>1.108222066057625</v>
+        <v>1.110817941952507</v>
       </c>
       <c r="N97" s="14" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="20" t="n">
-        <v>1.108222066057625</v>
+        <v>1.110817941952507</v>
       </c>
       <c r="Q97" s="21" t="inlineStr">
         <is>
@@ -8351,13 +8351,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>250.21</v>
+        <v>249.87</v>
       </c>
       <c r="E98" s="6" t="n">
-        <v>-0.005600000000000001</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.158</v>
+        <v>0.1564</v>
       </c>
       <c r="G98" s="7" t="n">
         <v>46310</v>
@@ -8386,7 +8386,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="6" t="n">
-        <v>-0.5483793613364774</v>
+        <v>-0.5477648377156121</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="6" t="n">
-        <v>-0.5443827185164462</v>
+        <v>-0.5437627566334494</v>
       </c>
       <c r="Q98" s="10" t="inlineStr"/>
       <c r="R98" s="9" t="n"/>
@@ -8436,13 +8436,13 @@
         </is>
       </c>
       <c r="D99" s="15" t="n">
-        <v>20.48</v>
+        <v>20.17</v>
       </c>
       <c r="E99" s="16" t="n">
-        <v>-0.1452</v>
+        <v>-0.1582</v>
       </c>
       <c r="F99" s="16" t="n">
-        <v>-0.275</v>
+        <v>-0.286</v>
       </c>
       <c r="G99" s="17" t="n">
         <v>46239</v>
@@ -8497,13 +8497,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>14.03</v>
+        <v>14.1</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.021</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.1369</v>
+        <v>0.1426</v>
       </c>
       <c r="G100" s="7" t="n">
         <v>46323</v>
@@ -8558,13 +8558,13 @@
         </is>
       </c>
       <c r="D101" s="15" t="n">
-        <v>102.33</v>
+        <v>102.98</v>
       </c>
       <c r="E101" s="20" t="n">
-        <v>0.1364</v>
+        <v>0.1436</v>
       </c>
       <c r="F101" s="20" t="n">
-        <v>0.1586</v>
+        <v>0.166</v>
       </c>
       <c r="G101" s="17" t="n">
         <v>46323</v>
@@ -8593,7 +8593,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="20" t="n">
-        <v>1.785107006742891</v>
+        <v>1.767527675276753</v>
       </c>
       <c r="N101" s="14" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="20" t="n">
-        <v>1.785107006742891</v>
+        <v>1.767527675276753</v>
       </c>
       <c r="Q101" s="21" t="inlineStr">
         <is>
@@ -8645,13 +8645,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>413.56</v>
+        <v>411.93</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>-0.0034</v>
+        <v>-0.0073</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="G102" s="7" t="n"/>
       <c r="H102" s="12" t="inlineStr">
@@ -8710,13 +8710,13 @@
         </is>
       </c>
       <c r="D103" s="15" t="n">
-        <v>52.03</v>
+        <v>51.84</v>
       </c>
       <c r="E103" s="20" t="n">
-        <v>0.0225</v>
+        <v>0.0187</v>
       </c>
       <c r="F103" s="20" t="n">
-        <v>0.1102</v>
+        <v>0.106</v>
       </c>
       <c r="G103" s="17" t="n">
         <v>46311</v>
@@ -8771,13 +8771,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>365.92</v>
+        <v>366.13</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0.0423</v>
+        <v>0.0429</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.1337</v>
+        <v>0.1343</v>
       </c>
       <c r="G104" s="7" t="n"/>
       <c r="H104" s="12" t="inlineStr">
@@ -8796,7 +8796,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>0.434739833843463</v>
+        <v>0.4339169147570535</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>0.4839309138609532</v>
+        <v>0.4830797804058668</v>
       </c>
       <c r="Q104" s="10" t="inlineStr">
         <is>
@@ -8852,13 +8852,13 @@
         </is>
       </c>
       <c r="D105" s="15" t="n">
-        <v>73.15000000000001</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="E105" s="20" t="n">
-        <v>0.0352</v>
+        <v>0.0266</v>
       </c>
       <c r="F105" s="20" t="n">
-        <v>0.1368</v>
+        <v>0.1273</v>
       </c>
       <c r="G105" s="17" t="n">
         <v>46314</v>
@@ -8887,7 +8887,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="20" t="n">
-        <v>4.632262474367738</v>
+        <v>4.679625034463744</v>
       </c>
       <c r="N105" s="14" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="20" t="n">
-        <v>3.784688995215311</v>
+        <v>3.824924179762889</v>
       </c>
       <c r="Q105" s="21" t="inlineStr">
         <is>
@@ -8943,13 +8943,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>81.06</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0.051</v>
+        <v>0.0533</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0675</v>
       </c>
       <c r="G106" s="7" t="n">
         <v>46239</v>
@@ -8978,7 +8978,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="6" t="n">
-        <v>-0.1611152232913891</v>
+        <v>-0.1629739044805514</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="6" t="n">
-        <v>-0.1611152232913891</v>
+        <v>-0.1629739044805514</v>
       </c>
       <c r="Q106" s="10" t="inlineStr">
         <is>
@@ -9034,13 +9034,13 @@
         </is>
       </c>
       <c r="D107" s="15" t="n">
-        <v>252.3</v>
-      </c>
-      <c r="E107" s="20" t="n">
-        <v>0.005</v>
+        <v>250.94</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>-0.0005</v>
       </c>
       <c r="F107" s="20" t="n">
-        <v>0.1849</v>
+        <v>0.1785</v>
       </c>
       <c r="G107" s="17" t="n">
         <v>46234</v>
@@ -9069,7 +9069,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="20" t="n">
-        <v>0.1692429647245342</v>
+        <v>0.1755798198772615</v>
       </c>
       <c r="N107" s="14" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="16" t="n">
-        <v>-0.02497027348394773</v>
+        <v>-0.01968598071252091</v>
       </c>
       <c r="Q107" s="21" t="inlineStr">
         <is>
@@ -9117,13 +9117,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>105.4</v>
+        <v>105.7</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0.1435</v>
+        <v>0.1467</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.2008</v>
+        <v>0.2041</v>
       </c>
       <c r="G108" s="7" t="n">
         <v>46316</v>
@@ -9152,7 +9152,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0.06261859582542689</v>
+        <v>0.05960264900662249</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -9163,7 +9163,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>0.1385199240986717</v>
+        <v>0.1352885525070955</v>
       </c>
       <c r="Q108" s="10" t="inlineStr">
         <is>
@@ -9216,13 +9216,13 @@
         </is>
       </c>
       <c r="D109" s="15" t="n">
-        <v>383.21</v>
+        <v>385.16</v>
       </c>
       <c r="E109" s="20" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="F109" s="20" t="n">
-        <v>0.1643</v>
+        <v>0.1702</v>
       </c>
       <c r="G109" s="17" t="n">
         <v>46238</v>
@@ -9251,7 +9251,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="20" t="n">
-        <v>0.01771874429164171</v>
+        <v>0.01256620625194718</v>
       </c>
       <c r="N109" s="14" t="inlineStr">
         <is>
@@ -9299,13 +9299,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>164.98</v>
+        <v>165.62</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0.079</v>
+        <v>0.0832</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.1352</v>
+        <v>0.1396</v>
       </c>
       <c r="G110" s="7" t="n">
         <v>46240</v>
@@ -9334,7 +9334,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="6" t="n">
-        <v>-0.02412413625894042</v>
+        <v>-0.02789518174133561</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>0.09104133834404177</v>
+        <v>0.08682526264943845</v>
       </c>
       <c r="Q110" s="10" t="inlineStr">
         <is>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="D111" s="15" t="n">
-        <v>45.53</v>
+        <v>46.73</v>
       </c>
       <c r="E111" s="20" t="n">
-        <v>0.0575</v>
+        <v>0.0852</v>
       </c>
       <c r="F111" s="16" t="n">
-        <v>-0.051</v>
+        <v>-0.0261</v>
       </c>
       <c r="G111" s="17" t="n"/>
       <c r="H111" s="23" t="inlineStr">
@@ -9411,7 +9411,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="20" t="n">
-        <v>0.2079947287502745</v>
+        <v>0.1769741065696555</v>
       </c>
       <c r="N111" s="14" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="20" t="n">
-        <v>0.4276301339775971</v>
+        <v>0.3909693986732293</v>
       </c>
       <c r="Q111" s="21" t="inlineStr">
         <is>
@@ -9463,13 +9463,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>312.14</v>
+        <v>311.34</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0.08220000000000001</v>
+        <v>0.0795</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.1793</v>
+        <v>0.1762</v>
       </c>
       <c r="G112" s="7" t="n">
         <v>46239</v>
@@ -9498,7 +9498,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>0.06042160568975465</v>
+        <v>0.0631463994347017</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="5" t="n">
-        <v>0.05721791503812396</v>
+        <v>0.05993447677779928</v>
       </c>
       <c r="Q112" s="10" t="inlineStr">
         <is>
@@ -9558,13 +9558,13 @@
         </is>
       </c>
       <c r="D113" s="15" t="n">
-        <v>105.4</v>
-      </c>
-      <c r="E113" s="20" t="n">
-        <v>0.005699999999999999</v>
+        <v>104.43</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>-0.0036</v>
       </c>
       <c r="F113" s="20" t="n">
-        <v>0.1632</v>
+        <v>0.1524</v>
       </c>
       <c r="G113" s="17" t="n">
         <v>46239</v>
@@ -9593,7 +9593,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="20" t="n">
-        <v>0.1669829222011384</v>
+        <v>0.1778224648089629</v>
       </c>
       <c r="N113" s="14" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="20" t="n">
-        <v>0.2333965844402277</v>
+        <v>0.2448530115867087</v>
       </c>
       <c r="Q113" s="21" t="inlineStr">
         <is>
@@ -9645,13 +9645,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>195.18</v>
+        <v>194.98</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.0851</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="G114" s="7" t="n">
         <v>46315</v>
@@ -9680,7 +9680,7 @@
         <v>212</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>0.08617686238344088</v>
+        <v>0.0872910042055596</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="5" t="n">
-        <v>0.0503125320217235</v>
+        <v>0.05138988614216848</v>
       </c>
       <c r="Q114" s="10" t="inlineStr">
         <is>
@@ -9736,13 +9736,13 @@
         </is>
       </c>
       <c r="D115" s="15" t="n">
-        <v>82.64</v>
+        <v>83.45</v>
       </c>
       <c r="E115" s="20" t="n">
-        <v>0.2</v>
+        <v>0.2119</v>
       </c>
       <c r="F115" s="20" t="n">
-        <v>0.1037</v>
+        <v>0.1146</v>
       </c>
       <c r="G115" s="17" t="n"/>
       <c r="H115" s="23" t="inlineStr">
@@ -9761,7 +9761,7 @@
         <v>85</v>
       </c>
       <c r="M115" s="20" t="n">
-        <v>0.02855759922555662</v>
+        <v>0.01857399640503292</v>
       </c>
       <c r="N115" s="14" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="20" t="n">
-        <v>0.08906098741529525</v>
+        <v>0.07849011384062309</v>
       </c>
       <c r="Q115" s="21" t="inlineStr">
         <is>
@@ -9813,13 +9813,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>130.1</v>
+        <v>130.21</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0337</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>-0.0076</v>
+        <v>-0.0068</v>
       </c>
       <c r="G116" s="7" t="n">
         <v>46238</v>
@@ -9848,7 +9848,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>0.2682551883166795</v>
+        <v>0.2671837800476153</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="9" t="n"/>
@@ -9896,13 +9896,13 @@
         </is>
       </c>
       <c r="D117" s="15" t="n">
-        <v>555.7</v>
+        <v>559.0700000000001</v>
       </c>
       <c r="E117" s="20" t="n">
-        <v>0.0337</v>
+        <v>0.04</v>
       </c>
       <c r="F117" s="16" t="n">
-        <v>-0.0196</v>
+        <v>-0.0136</v>
       </c>
       <c r="G117" s="17" t="n">
         <v>46238</v>
@@ -9967,13 +9967,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>353.59</v>
+        <v>353.33</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>-0.1213</v>
+        <v>-0.1219</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>-0.1423</v>
+        <v>-0.1429</v>
       </c>
       <c r="G118" s="7" t="n">
         <v>46315</v>
@@ -10002,7 +10002,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>0.3773013942702</v>
+        <v>0.3783148897631111</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>375</v>
       </c>
       <c r="P118" s="5" t="n">
-        <v>0.06055035493085219</v>
+        <v>0.0613307672713894</v>
       </c>
       <c r="Q118" s="10" t="inlineStr">
         <is>
@@ -10058,13 +10058,13 @@
         </is>
       </c>
       <c r="D119" s="15" t="n">
-        <v>257.59</v>
+        <v>256.35</v>
       </c>
       <c r="E119" s="20" t="n">
-        <v>0.0142</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="F119" s="20" t="n">
-        <v>0.1525</v>
+        <v>0.1469</v>
       </c>
       <c r="G119" s="17" t="n">
         <v>46315</v>
@@ -10093,7 +10093,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="20" t="n">
-        <v>0.05594161264024235</v>
+        <v>0.06104934659645007</v>
       </c>
       <c r="N119" s="14" t="inlineStr"/>
       <c r="O119" s="19" t="n"/>
@@ -10145,13 +10145,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1142.61</v>
+        <v>1148.84</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>-0.0412</v>
+        <v>-0.036</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>0.0558</v>
+        <v>0.0616</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>46239</v>
@@ -10180,7 +10180,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>0.1202422523870788</v>
+        <v>0.1141673340064762</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -10240,13 +10240,13 @@
         </is>
       </c>
       <c r="D121" s="15" t="n">
-        <v>85.34999999999999</v>
+        <v>85.39</v>
       </c>
       <c r="E121" s="20" t="n">
-        <v>0.07769999999999999</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="F121" s="20" t="n">
-        <v>0.1537</v>
+        <v>0.1542</v>
       </c>
       <c r="G121" s="17" t="n">
         <v>46266</v>
@@ -10275,7 +10275,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="20" t="n">
-        <v>0.1950790861159931</v>
+        <v>0.1945192645508842</v>
       </c>
       <c r="N121" s="14" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="20" t="n">
-        <v>0.2302284710017576</v>
+        <v>0.2296521840964984</v>
       </c>
       <c r="Q121" s="21" t="inlineStr">
         <is>
@@ -10327,13 +10327,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>130.94</v>
+        <v>130.2</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0.0444</v>
+        <v>0.0385</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0.1369</v>
+        <v>0.1305</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>46238</v>
@@ -10362,7 +10362,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>0.1455628532152131</v>
+        <v>0.1520737327188941</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="9" t="n"/>
@@ -10406,13 +10406,13 @@
         </is>
       </c>
       <c r="D123" s="15" t="n">
-        <v>156.51</v>
+        <v>156.15</v>
       </c>
       <c r="E123" s="20" t="n">
-        <v>0.0154</v>
+        <v>0.013</v>
       </c>
       <c r="F123" s="20" t="n">
-        <v>0.07429999999999999</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="G123" s="17" t="n">
         <v>46322</v>
@@ -10485,13 +10485,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>25.08</v>
+        <v>25.01</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.05</v>
+        <v>0.0473</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>-0.0217</v>
+        <v>-0.0242</v>
       </c>
       <c r="G124" s="7" t="n">
         <v>46238</v>
@@ -10520,7 +10520,7 @@
         <v>28</v>
       </c>
       <c r="M124" s="5" t="n">
-        <v>0.116427432216906</v>
+        <v>0.1195521791283486</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="9" t="n"/>
@@ -10564,13 +10564,13 @@
         </is>
       </c>
       <c r="D125" s="15" t="n">
-        <v>324.81</v>
+        <v>325.7</v>
       </c>
       <c r="E125" s="20" t="n">
-        <v>0.0364</v>
+        <v>0.0393</v>
       </c>
       <c r="F125" s="20" t="n">
-        <v>0.08470000000000001</v>
+        <v>0.0876</v>
       </c>
       <c r="G125" s="17" t="n"/>
       <c r="H125" s="23" t="inlineStr">
@@ -10589,7 +10589,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="20" t="n">
-        <v>0.2869061913118439</v>
+        <v>0.2833896223518576</v>
       </c>
       <c r="N125" s="14" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="20" t="n">
-        <v>0.07755303100274005</v>
+        <v>0.07460853546208171</v>
       </c>
       <c r="Q125" s="21" t="inlineStr">
         <is>
@@ -10645,13 +10645,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>570.7</v>
+        <v>574.3</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0.1118</v>
+        <v>0.1188</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>0.1552</v>
+        <v>0.1625</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>46323</v>
@@ -10680,7 +10680,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>0.07762397056246706</v>
+        <v>0.07086888385861057</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="6" t="n">
-        <v>-0.001226563868932969</v>
+        <v>-0.007487375935921913</v>
       </c>
       <c r="Q126" s="10" t="inlineStr">
         <is>
@@ -10740,13 +10740,13 @@
         </is>
       </c>
       <c r="D127" s="15" t="n">
-        <v>419.01</v>
+        <v>414.4</v>
       </c>
       <c r="E127" s="16" t="n">
-        <v>-0.0177</v>
+        <v>-0.0285</v>
       </c>
       <c r="F127" s="20" t="n">
-        <v>0.1031</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="G127" s="17" t="n">
         <v>46322</v>
@@ -10775,7 +10775,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="20" t="n">
-        <v>0.2553399680198564</v>
+        <v>0.2693050193050194</v>
       </c>
       <c r="N127" s="14" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="20" t="n">
-        <v>0.1455573852652682</v>
+        <v>0.1583011583011584</v>
       </c>
       <c r="Q127" s="21" t="inlineStr">
         <is>
@@ -10831,13 +10831,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>76.84999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0.0608</v>
+        <v>0.0668</v>
       </c>
       <c r="F128" s="6" t="n">
-        <v>-0.0091</v>
+        <v>-0.0035</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>46240</v>
@@ -10910,13 +10910,13 @@
         </is>
       </c>
       <c r="D129" s="15" t="n">
-        <v>264.68</v>
+        <v>266.46</v>
       </c>
       <c r="E129" s="20" t="n">
-        <v>0.1228</v>
+        <v>0.1304</v>
       </c>
       <c r="F129" s="20" t="n">
-        <v>0.1324</v>
+        <v>0.14</v>
       </c>
       <c r="G129" s="17" t="n"/>
       <c r="H129" s="23" t="inlineStr">
@@ -10935,7 +10935,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="16" t="n">
-        <v>-0.06301949523953455</v>
+        <v>-0.0692786909855137</v>
       </c>
       <c r="N129" s="14" t="inlineStr"/>
       <c r="O129" s="19" t="n"/>
@@ -10991,13 +10991,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>103.05</v>
+        <v>102.16</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>-0.1158</v>
+        <v>-0.1234</v>
       </c>
       <c r="F130" s="6" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.08810000000000001</v>
       </c>
       <c r="G130" s="7" t="n"/>
       <c r="H130" s="12" t="inlineStr">
@@ -11042,13 +11042,13 @@
         </is>
       </c>
       <c r="D131" s="15" t="n">
-        <v>243.04</v>
+        <v>241.71</v>
       </c>
       <c r="E131" s="20" t="n">
-        <v>0.0249</v>
+        <v>0.0193</v>
       </c>
       <c r="F131" s="20" t="n">
-        <v>0.08810000000000001</v>
+        <v>0.08220000000000001</v>
       </c>
       <c r="G131" s="17" t="n">
         <v>46238</v>
@@ -11103,13 +11103,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>214.71</v>
+        <v>216.14</v>
       </c>
       <c r="E132" s="6" t="n">
-        <v>-0.0177</v>
+        <v>-0.0112</v>
       </c>
       <c r="F132" s="6" t="n">
-        <v>-0.0428</v>
+        <v>-0.0364</v>
       </c>
       <c r="G132" s="7" t="n"/>
       <c r="H132" s="12" t="inlineStr">
@@ -11128,7 +11128,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>0.1643612314284383</v>
+        <v>0.1566577218469511</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="9" t="n"/>
@@ -11172,13 +11172,13 @@
         </is>
       </c>
       <c r="D133" s="15" t="n">
-        <v>153.4</v>
+        <v>153.95</v>
       </c>
       <c r="E133" s="20" t="n">
-        <v>0.08839999999999999</v>
+        <v>0.0924</v>
       </c>
       <c r="F133" s="16" t="n">
-        <v>-0.04099999999999999</v>
+        <v>-0.03759999999999999</v>
       </c>
       <c r="G133" s="17" t="n">
         <v>46238</v>
@@ -11243,13 +11243,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>818.78</v>
+        <v>814.8099999999999</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>-0.1741</v>
+        <v>-0.1781</v>
       </c>
       <c r="F134" s="6" t="n">
-        <v>-0.0538</v>
+        <v>-0.0584</v>
       </c>
       <c r="G134" s="7" t="n">
         <v>46238</v>
@@ -11278,7 +11278,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>0.4106353354991573</v>
+        <v>0.4175083761858594</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="5" t="n">
-        <v>0.3471262121693252</v>
+        <v>0.3536898172580112</v>
       </c>
       <c r="Q134" s="10" t="inlineStr">
         <is>
@@ -11330,13 +11330,13 @@
         </is>
       </c>
       <c r="D135" s="15" t="n">
-        <v>638.8200000000001</v>
+        <v>634.2</v>
       </c>
       <c r="E135" s="16" t="n">
-        <v>-0.0638</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="F135" s="16" t="n">
-        <v>-0.0073</v>
+        <v>-0.0145</v>
       </c>
       <c r="G135" s="17" t="n">
         <v>46238</v>
@@ -11365,7 +11365,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="20" t="n">
-        <v>0.3681475219936757</v>
+        <v>0.3781141595711131</v>
       </c>
       <c r="N135" s="14" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="20" t="n">
-        <v>0.3227513227513226</v>
+        <v>0.3323872595395773</v>
       </c>
       <c r="Q135" s="21" t="inlineStr">
         <is>
@@ -11425,13 +11425,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>205.49</v>
+        <v>204.63</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0.1794</v>
+        <v>0.1745</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>0.1885</v>
+        <v>0.1835</v>
       </c>
       <c r="G136" s="7" t="n">
         <v>46288</v>
@@ -11460,7 +11460,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>0.2166042143169983</v>
+        <v>0.2217172457606412</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="9" t="n"/>
@@ -11504,13 +11504,13 @@
         </is>
       </c>
       <c r="D137" s="15" t="n">
-        <v>596.67</v>
+        <v>592.67</v>
       </c>
       <c r="E137" s="16" t="n">
-        <v>-0.0493</v>
+        <v>-0.0557</v>
       </c>
       <c r="F137" s="20" t="n">
-        <v>0.1</v>
+        <v>0.0926</v>
       </c>
       <c r="G137" s="17" t="n">
         <v>46254</v>
@@ -11539,7 +11539,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="20" t="n">
-        <v>0.2569762180099553</v>
+        <v>0.2654596993267755</v>
       </c>
       <c r="N137" s="14" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="20" t="n">
-        <v>0.07478170513013895</v>
+        <v>0.08203553410835711</v>
       </c>
       <c r="Q137" s="21" t="inlineStr">
         <is>
@@ -11591,13 +11591,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>149.99</v>
+        <v>149.82</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0.075</v>
+        <v>0.0738</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.05889999999999999</v>
+        <v>0.05769999999999999</v>
       </c>
       <c r="G138" s="7" t="n">
         <v>46238</v>
@@ -11633,7 +11633,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="5" t="n">
-        <v>0.2334155610374024</v>
+        <v>0.2348151114670939</v>
       </c>
       <c r="Q138" s="10" t="inlineStr">
         <is>
@@ -11672,13 +11672,13 @@
         </is>
       </c>
       <c r="D139" s="15" t="n">
-        <v>414.24</v>
+        <v>415.2</v>
       </c>
       <c r="E139" s="20" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F139" s="20" t="n">
-        <v>0.0354</v>
+        <v>0.0378</v>
       </c>
       <c r="G139" s="17" t="n">
         <v>46234</v>
@@ -11714,7 +11714,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="20" t="n">
-        <v>0.09356894553881805</v>
+        <v>0.09104046242774569</v>
       </c>
       <c r="Q139" s="21" t="inlineStr">
         <is>
@@ -11755,13 +11755,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>47.24</v>
+        <v>47.71</v>
       </c>
       <c r="E140" s="6" t="n">
-        <v>-0.0107</v>
+        <v>-0.0008</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.08460000000000001</v>
       </c>
       <c r="G140" s="7" t="n">
         <v>46309</v>
@@ -11834,13 +11834,13 @@
         </is>
       </c>
       <c r="D141" s="15" t="n">
-        <v>309.39</v>
+        <v>307.4</v>
       </c>
       <c r="E141" s="16" t="n">
-        <v>-0.0143</v>
+        <v>-0.0207</v>
       </c>
       <c r="F141" s="16" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.09179999999999999</v>
       </c>
       <c r="G141" s="17" t="n">
         <v>46282</v>
@@ -11869,7 +11869,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="20" t="n">
-        <v>0.3736707715181487</v>
+        <v>0.3825634352635005</v>
       </c>
       <c r="N141" s="14" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="20" t="n">
-        <v>0.04398978635379299</v>
+        <v>0.05074821080026033</v>
       </c>
       <c r="Q141" s="21" t="inlineStr">
         <is>
@@ -11921,13 +11921,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>234.48</v>
+        <v>234.33</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0.023</v>
+        <v>0.0224</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>0.045</v>
+        <v>0.0443</v>
       </c>
       <c r="G142" s="7" t="n">
         <v>46244</v>
@@ -11956,7 +11956,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="5" t="n">
-        <v>0.2154554759467759</v>
+        <v>0.2162335168352323</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="9" t="n"/>
@@ -12004,13 +12004,13 @@
         </is>
       </c>
       <c r="D143" s="15" t="n">
-        <v>1753.15</v>
+        <v>1729.69</v>
       </c>
       <c r="E143" s="16" t="n">
-        <v>-0.06</v>
+        <v>-0.0726</v>
       </c>
       <c r="F143" s="16" t="n">
-        <v>-0.0194</v>
+        <v>-0.0325</v>
       </c>
       <c r="G143" s="17" t="n">
         <v>46317</v>
@@ -12065,13 +12065,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>50.1</v>
+        <v>50.17</v>
       </c>
       <c r="E144" s="6" t="n">
-        <v>-0.0049</v>
+        <v>-0.0036</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>0.0764</v>
+        <v>0.07780000000000001</v>
       </c>
       <c r="G144" s="7" t="n">
         <v>46241</v>
@@ -12126,13 +12126,13 @@
         </is>
       </c>
       <c r="D145" s="15" t="n">
-        <v>382.8</v>
+        <v>383.42</v>
       </c>
       <c r="E145" s="20" t="n">
-        <v>0.055</v>
+        <v>0.0567</v>
       </c>
       <c r="F145" s="20" t="n">
-        <v>0.1286</v>
+        <v>0.1304</v>
       </c>
       <c r="G145" s="17" t="n"/>
       <c r="H145" s="23" t="inlineStr">
@@ -12151,7 +12151,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="20" t="n">
-        <v>0.044932079414838</v>
+        <v>0.04324239737102911</v>
       </c>
       <c r="N145" s="14" t="inlineStr"/>
       <c r="O145" s="19" t="n"/>
@@ -12203,13 +12203,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>360.45</v>
+        <v>360.07</v>
       </c>
       <c r="E146" s="6" t="n">
-        <v>-0.0386</v>
+        <v>-0.0397</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>0.1104</v>
+        <v>0.1093</v>
       </c>
       <c r="G146" s="7" t="n">
         <v>46315</v>
@@ -12238,7 +12238,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="5" t="n">
-        <v>0.08198085726175618</v>
+        <v>0.08312272613658457</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="9" t="n"/>
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="D147" s="15" t="n">
-        <v>997.72</v>
+        <v>990.29</v>
       </c>
       <c r="E147" s="16" t="n">
-        <v>-0.1204</v>
+        <v>-0.127</v>
       </c>
       <c r="F147" s="20" t="n">
-        <v>0.0496</v>
+        <v>0.0418</v>
       </c>
       <c r="G147" s="17" t="n">
         <v>46316</v>
@@ -12325,7 +12325,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="20" t="n">
-        <v>0.2618770797418113</v>
+        <v>0.2713447575962598</v>
       </c>
       <c r="N147" s="14" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="20" t="n">
-        <v>0.3530850338772401</v>
+        <v>0.3632370315766089</v>
       </c>
       <c r="Q147" s="21" t="inlineStr">
         <is>
@@ -12381,13 +12381,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1385.14</v>
+        <v>1382.22</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0.035</v>
+        <v>0.0329</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>0.1143</v>
+        <v>0.112</v>
       </c>
       <c r="G148" s="7" t="n">
         <v>46238</v>
@@ -12456,13 +12456,13 @@
         </is>
       </c>
       <c r="D149" s="15" t="n">
-        <v>243.71</v>
+        <v>243.05</v>
       </c>
       <c r="E149" s="20" t="n">
-        <v>0.099</v>
+        <v>0.09609999999999999</v>
       </c>
       <c r="F149" s="16" t="n">
-        <v>-0.0176</v>
+        <v>-0.0203</v>
       </c>
       <c r="G149" s="17" t="n">
         <v>46317</v>
@@ -12517,13 +12517,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>476.72</v>
+        <v>472.55</v>
       </c>
       <c r="E150" s="6" t="n">
-        <v>-0.0273</v>
+        <v>-0.0358</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>0.0298</v>
+        <v>0.0208</v>
       </c>
       <c r="G150" s="7" t="n"/>
       <c r="H150" s="12" t="inlineStr">
@@ -12574,13 +12574,13 @@
         </is>
       </c>
       <c r="D151" s="15" t="n">
-        <v>286.28</v>
+        <v>286.95</v>
       </c>
       <c r="E151" s="20" t="n">
-        <v>0.0644</v>
+        <v>0.0668</v>
       </c>
       <c r="F151" s="20" t="n">
-        <v>0.1646</v>
+        <v>0.1674</v>
       </c>
       <c r="G151" s="17" t="n"/>
       <c r="H151" s="23" t="inlineStr">
@@ -12602,7 +12602,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="16" t="n">
-        <v>-0.04988123515439421</v>
+        <v>-0.05209966893186962</v>
       </c>
       <c r="Q151" s="21" t="inlineStr">
         <is>
@@ -12655,13 +12655,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>277.6</v>
+        <v>277.06</v>
       </c>
       <c r="E152" s="6" t="n">
-        <v>-0.0501</v>
+        <v>-0.0519</v>
       </c>
       <c r="F152" s="6" t="n">
-        <v>-0.1033</v>
+        <v>-0.1051</v>
       </c>
       <c r="G152" s="7" t="n"/>
       <c r="H152" s="12" t="inlineStr">
@@ -12716,13 +12716,13 @@
         </is>
       </c>
       <c r="D153" s="15" t="n">
-        <v>422.33</v>
+        <v>415.88</v>
       </c>
       <c r="E153" s="16" t="n">
-        <v>-0.2605</v>
+        <v>-0.2718</v>
       </c>
       <c r="F153" s="16" t="n">
-        <v>-0.1498</v>
+        <v>-0.1628</v>
       </c>
       <c r="G153" s="17" t="n"/>
       <c r="H153" s="23" t="inlineStr">
@@ -12767,13 +12767,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>580.3099999999999</v>
+        <v>582.74</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0.1121</v>
+        <v>0.1167</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0.1235</v>
+        <v>0.1282</v>
       </c>
       <c r="G154" s="7" t="n">
         <v>46315</v>
@@ -12834,13 +12834,13 @@
         </is>
       </c>
       <c r="D155" s="15" t="n">
-        <v>213.27</v>
+        <v>212.14</v>
       </c>
       <c r="E155" s="16" t="n">
-        <v>-0.0215</v>
+        <v>-0.0267</v>
       </c>
       <c r="F155" s="16" t="n">
-        <v>-0.0668</v>
+        <v>-0.0717</v>
       </c>
       <c r="G155" s="17" t="n"/>
       <c r="H155" s="23" t="inlineStr">
@@ -12859,7 +12859,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="20" t="n">
-        <v>1.696112908519717</v>
+        <v>1.710474215140945</v>
       </c>
       <c r="N155" s="14" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="20" t="n">
-        <v>0.111267407511605</v>
+        <v>0.1171867634580938</v>
       </c>
       <c r="Q155" s="21" t="inlineStr">
         <is>
@@ -12919,13 +12919,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>116.27</v>
+        <v>116.84</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0.132</v>
+        <v>0.1376</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.135</v>
+        <v>0.1406</v>
       </c>
       <c r="G156" s="7" t="n">
         <v>46294</v>
@@ -12954,7 +12954,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="5" t="n">
-        <v>1.150167713081621</v>
+        <v>1.139678192399863</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="9" t="n"/>
@@ -12998,13 +12998,13 @@
         </is>
       </c>
       <c r="D157" s="15" t="n">
-        <v>133.3</v>
+        <v>132.68</v>
       </c>
       <c r="E157" s="20" t="n">
-        <v>0.09949999999999999</v>
+        <v>0.0944</v>
       </c>
       <c r="F157" s="20" t="n">
-        <v>0.2177</v>
+        <v>0.212</v>
       </c>
       <c r="G157" s="17" t="n"/>
       <c r="H157" s="23" t="inlineStr">
@@ -13023,7 +13023,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="16" t="n">
-        <v>-0.2873218304576144</v>
+        <v>-0.2839915586373229</v>
       </c>
       <c r="N157" s="14" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="20" t="n">
-        <v>0.04276069017254305</v>
+        <v>0.04763340367802225</v>
       </c>
       <c r="Q157" s="21" t="inlineStr">
         <is>
@@ -13079,13 +13079,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>972.63</v>
+        <v>976.53</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0132</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>0.1814</v>
+        <v>0.1861</v>
       </c>
       <c r="G158" s="7" t="n">
         <v>46240</v>
@@ -13114,7 +13114,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="6" t="n">
-        <v>-0.8714824753503387</v>
+        <v>-0.8719957400182278</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="5" t="n">
-        <v>0.09394116981791638</v>
+        <v>0.08957226096484494</v>
       </c>
       <c r="Q158" s="10" t="inlineStr">
         <is>
@@ -13170,13 +13170,13 @@
         </is>
       </c>
       <c r="D159" s="15" t="n">
-        <v>566.13</v>
+        <v>551.3099999999999</v>
       </c>
       <c r="E159" s="16" t="n">
-        <v>-0.0876</v>
-      </c>
-      <c r="F159" s="20" t="n">
-        <v>0</v>
+        <v>-0.1115</v>
+      </c>
+      <c r="F159" s="16" t="n">
+        <v>-0.0262</v>
       </c>
       <c r="G159" s="17" t="n">
         <v>46234</v>
@@ -13251,13 +13251,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>477.83</v>
+        <v>480.08</v>
       </c>
       <c r="E160" s="6" t="n">
-        <v>-0.0103</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>0.0463</v>
+        <v>0.0512</v>
       </c>
       <c r="G160" s="7" t="n">
         <v>46238</v>
@@ -13312,13 +13312,13 @@
         </is>
       </c>
       <c r="D161" s="15" t="n">
-        <v>37.92</v>
+        <v>37.97</v>
       </c>
       <c r="E161" s="16" t="n">
-        <v>-0.1001</v>
+        <v>-0.099</v>
       </c>
       <c r="F161" s="16" t="n">
-        <v>-0.1813</v>
+        <v>-0.1803</v>
       </c>
       <c r="G161" s="17" t="n">
         <v>46323</v>
@@ -13387,13 +13387,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>214.94</v>
+        <v>215.22</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>0.1208</v>
+        <v>0.1222</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>0.2324</v>
+        <v>0.234</v>
       </c>
       <c r="G162" s="7" t="n">
         <v>46322</v>
@@ -13466,13 +13466,13 @@
         </is>
       </c>
       <c r="D163" s="15" t="n">
-        <v>42.53</v>
+        <v>43.05</v>
       </c>
       <c r="E163" s="16" t="n">
-        <v>-0.05400000000000001</v>
+        <v>-0.0425</v>
       </c>
       <c r="F163" s="16" t="n">
-        <v>-0.1213</v>
+        <v>-0.1105</v>
       </c>
       <c r="G163" s="17" t="n">
         <v>46239</v>
@@ -13527,13 +13527,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>455.87</v>
+        <v>454.95</v>
       </c>
       <c r="E164" s="6" t="n">
-        <v>-0.0592</v>
+        <v>-0.0611</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0144</v>
       </c>
       <c r="G164" s="7" t="n"/>
       <c r="H164" s="12" t="inlineStr">
@@ -13555,7 +13555,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="5" t="n">
-        <v>0.2284203830039266</v>
+        <v>0.2309044949994505</v>
       </c>
       <c r="Q164" s="10" t="inlineStr">
         <is>
@@ -13608,13 +13608,13 @@
         </is>
       </c>
       <c r="D165" s="15" t="n">
-        <v>292.79</v>
+        <v>292.13</v>
       </c>
       <c r="E165" s="20" t="n">
-        <v>0.0542</v>
+        <v>0.0518</v>
       </c>
       <c r="F165" s="20" t="n">
-        <v>0.1112</v>
+        <v>0.1087</v>
       </c>
       <c r="G165" s="17" t="n">
         <v>46317</v>
@@ -13646,7 +13646,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="20" t="n">
-        <v>0.004132654803784212</v>
+        <v>0.006401259713141426</v>
       </c>
       <c r="Q165" s="21" t="inlineStr">
         <is>
@@ -13691,13 +13691,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>245.69</v>
+        <v>241.57</v>
       </c>
       <c r="E166" s="6" t="n">
-        <v>-0.2111</v>
+        <v>-0.2243</v>
       </c>
       <c r="F166" s="6" t="n">
-        <v>-0.2403</v>
+        <v>-0.253</v>
       </c>
       <c r="G166" s="7" t="n"/>
       <c r="H166" s="12" t="inlineStr">
@@ -13719,7 +13719,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="5" t="n">
-        <v>0.7298221335829704</v>
+        <v>0.7593244194229416</v>
       </c>
       <c r="Q166" s="10" t="inlineStr">
         <is>
@@ -13760,13 +13760,13 @@
         </is>
       </c>
       <c r="D167" s="15" t="n">
-        <v>227.07</v>
+        <v>226.55</v>
       </c>
       <c r="E167" s="20" t="n">
-        <v>0.0134</v>
+        <v>0.011</v>
       </c>
       <c r="F167" s="20" t="n">
-        <v>0.06849999999999999</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="G167" s="17" t="n"/>
       <c r="H167" s="23" t="inlineStr">
@@ -13785,7 +13785,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="20" t="n">
-        <v>0.1802527854846523</v>
+        <v>0.1829618185830942</v>
       </c>
       <c r="N167" s="14" t="inlineStr"/>
       <c r="O167" s="19" t="n"/>
@@ -13833,13 +13833,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>310.2</v>
+        <v>309.3</v>
       </c>
       <c r="E168" s="6" t="n">
-        <v>-0.239</v>
+        <v>-0.2412</v>
       </c>
       <c r="F168" s="6" t="n">
-        <v>-0.1371</v>
+        <v>-0.1396</v>
       </c>
       <c r="G168" s="7" t="n"/>
       <c r="H168" s="12" t="inlineStr">
@@ -13898,13 +13898,13 @@
         </is>
       </c>
       <c r="D169" s="15" t="n">
-        <v>363.23</v>
+        <v>360.75</v>
       </c>
       <c r="E169" s="16" t="n">
-        <v>-0.1371</v>
+        <v>-0.143</v>
       </c>
       <c r="F169" s="20" t="n">
-        <v>0.06280000000000001</v>
+        <v>0.0556</v>
       </c>
       <c r="G169" s="17" t="n"/>
       <c r="H169" s="23" t="inlineStr">
@@ -13967,13 +13967,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>117.46</v>
-      </c>
-      <c r="E170" s="5" t="n">
-        <v>0.0016</v>
+        <v>116.97</v>
+      </c>
+      <c r="E170" s="6" t="n">
+        <v>-0.0026</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>0.0843</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="G170" s="7" t="n"/>
       <c r="H170" s="12" t="inlineStr">
@@ -14036,13 +14036,13 @@
         </is>
       </c>
       <c r="D171" s="15" t="n">
-        <v>95.68000000000001</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="E171" s="16" t="n">
-        <v>-0.3117</v>
+        <v>-0.3214</v>
       </c>
       <c r="F171" s="16" t="n">
-        <v>-0.4847</v>
+        <v>-0.492</v>
       </c>
       <c r="G171" s="17" t="n">
         <v>46240</v>
@@ -14097,13 +14097,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>300.93</v>
+        <v>308.91</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>0.0223</v>
-      </c>
-      <c r="F172" s="6" t="n">
-        <v>-0.0175</v>
+        <v>0.04940000000000001</v>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="G172" s="7" t="n"/>
       <c r="H172" s="12" t="inlineStr">
@@ -14122,7 +14122,7 @@
         <v>310</v>
       </c>
       <c r="M172" s="5" t="n">
-        <v>0.03013989964443556</v>
+        <v>0.00352853581949427</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="5" t="n">
-        <v>0.2129066560329644</v>
+        <v>0.1815739212068239</v>
       </c>
       <c r="Q172" s="10" t="inlineStr">
         <is>
@@ -14190,13 +14190,13 @@
         </is>
       </c>
       <c r="D173" s="15" t="n">
-        <v>130.33</v>
+        <v>130.38</v>
       </c>
       <c r="E173" s="16" t="n">
-        <v>-0.2692</v>
+        <v>-0.2689</v>
       </c>
       <c r="F173" s="16" t="n">
-        <v>-0.1336</v>
+        <v>-0.1332</v>
       </c>
       <c r="G173" s="17" t="n">
         <v>46240</v>
@@ -14251,13 +14251,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>164.71</v>
+        <v>165.92</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>0.2561</v>
+        <v>0.2653</v>
       </c>
       <c r="F174" s="6" t="n">
-        <v>-0.1621</v>
+        <v>-0.156</v>
       </c>
       <c r="G174" s="7" t="n">
         <v>46289</v>
@@ -14312,13 +14312,13 @@
         </is>
       </c>
       <c r="D175" s="15" t="n">
-        <v>248.13</v>
+        <v>250.41</v>
       </c>
       <c r="E175" s="20" t="n">
-        <v>0.1761</v>
+        <v>0.1869</v>
       </c>
       <c r="F175" s="16" t="n">
-        <v>-0.09449999999999999</v>
+        <v>-0.0862</v>
       </c>
       <c r="G175" s="17" t="n">
         <v>46275</v>
@@ -14373,13 +14373,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>367.69</v>
+        <v>367.41</v>
       </c>
       <c r="E176" s="6" t="n">
-        <v>-0.0547</v>
+        <v>-0.0555</v>
       </c>
       <c r="F176" s="6" t="n">
-        <v>-0.08689999999999999</v>
+        <v>-0.0876</v>
       </c>
       <c r="G176" s="7" t="n">
         <v>46253</v>
@@ -14408,7 +14408,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="5" t="n">
-        <v>0.400636405667818</v>
+        <v>0.4017038186222475</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="5" t="n">
-        <v>0.2891294296826131</v>
+        <v>0.2901118641299909</v>
       </c>
       <c r="Q176" s="10" t="inlineStr">
         <is>
@@ -14468,13 +14468,13 @@
         </is>
       </c>
       <c r="D177" s="15" t="n">
-        <v>233.43</v>
+        <v>234.2</v>
       </c>
       <c r="E177" s="20" t="n">
-        <v>0.1685</v>
+        <v>0.1724</v>
       </c>
       <c r="F177" s="16" t="n">
-        <v>-0.0594</v>
+        <v>-0.0563</v>
       </c>
       <c r="G177" s="17" t="n">
         <v>46261</v>
@@ -14529,13 +14529,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>292.87</v>
+        <v>289.52</v>
       </c>
       <c r="E178" s="6" t="n">
-        <v>-0.1781</v>
+        <v>-0.1875</v>
       </c>
       <c r="F178" s="6" t="n">
-        <v>-0.006</v>
+        <v>-0.0174</v>
       </c>
       <c r="G178" s="7" t="n">
         <v>46237</v>
@@ -14590,13 +14590,13 @@
         </is>
       </c>
       <c r="D179" s="15" t="n">
-        <v>313.12</v>
+        <v>311.23</v>
       </c>
       <c r="E179" s="16" t="n">
-        <v>-0.2733</v>
+        <v>-0.2777</v>
       </c>
       <c r="F179" s="16" t="n">
-        <v>-0.0218</v>
+        <v>-0.0277</v>
       </c>
       <c r="G179" s="17" t="n">
         <v>46238</v>
@@ -14651,13 +14651,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>41.96</v>
+        <v>41.5</v>
       </c>
       <c r="E180" s="6" t="n">
-        <v>-0.3361</v>
+        <v>-0.3434</v>
       </c>
       <c r="F180" s="6" t="n">
-        <v>-0.1097</v>
+        <v>-0.1195</v>
       </c>
       <c r="G180" s="7" t="n"/>
       <c r="H180" s="12" t="inlineStr">
@@ -14702,13 +14702,13 @@
         </is>
       </c>
       <c r="D181" s="15" t="n">
-        <v>518.63</v>
+        <v>507.67</v>
       </c>
       <c r="E181" s="16" t="n">
-        <v>-0.2032</v>
+        <v>-0.2201</v>
       </c>
       <c r="F181" s="20" t="n">
-        <v>0.132</v>
+        <v>0.108</v>
       </c>
       <c r="G181" s="17" t="n">
         <v>46247</v>
@@ -14737,7 +14737,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="20" t="n">
-        <v>0.4268360873840696</v>
+        <v>0.4576398053853881</v>
       </c>
       <c r="N181" s="14" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="20" t="n">
-        <v>0.3497098123903361</v>
+        <v>0.3788484645537455</v>
       </c>
       <c r="Q181" s="21" t="inlineStr">
         <is>
@@ -14789,13 +14789,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>63.67</v>
+        <v>63.59</v>
       </c>
       <c r="E182" s="6" t="n">
-        <v>-0.2797</v>
+        <v>-0.2807</v>
       </c>
       <c r="F182" s="6" t="n">
-        <v>-0.1774</v>
+        <v>-0.1784</v>
       </c>
       <c r="G182" s="7" t="n">
         <v>46245</v>
@@ -14854,13 +14854,13 @@
         </is>
       </c>
       <c r="D183" s="15" t="n">
-        <v>488.9</v>
+        <v>476.15</v>
       </c>
       <c r="E183" s="16" t="n">
-        <v>-0.09609999999999999</v>
+        <v>-0.1197</v>
       </c>
       <c r="F183" s="16" t="n">
-        <v>-0.0416</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="G183" s="17" t="n">
         <v>46238</v>
@@ -14889,7 +14889,7 @@
         <v>615</v>
       </c>
       <c r="M183" s="20" t="n">
-        <v>0.2579259562282676</v>
+        <v>0.2916097868318808</v>
       </c>
       <c r="N183" s="14" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="20" t="n">
-        <v>0.1842912661075885</v>
+        <v>0.2160033602856243</v>
       </c>
       <c r="Q183" s="21" t="inlineStr">
         <is>
@@ -14941,13 +14941,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>50.79</v>
+        <v>49.87</v>
       </c>
       <c r="E184" s="6" t="n">
-        <v>-0.365</v>
+        <v>-0.3765</v>
       </c>
       <c r="F184" s="6" t="n">
-        <v>-0.3018</v>
+        <v>-0.3145</v>
       </c>
       <c r="G184" s="7" t="n"/>
       <c r="H184" s="12" t="inlineStr">
@@ -14992,13 +14992,13 @@
         </is>
       </c>
       <c r="D185" s="15" t="n">
-        <v>179.84</v>
+        <v>180.35</v>
       </c>
       <c r="E185" s="20" t="n">
-        <v>0.0793</v>
+        <v>0.0824</v>
       </c>
       <c r="F185" s="20" t="n">
-        <v>0.0536</v>
+        <v>0.0567</v>
       </c>
       <c r="G185" s="17" t="n">
         <v>46238</v>
@@ -15027,7 +15027,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="20" t="n">
-        <v>0.1120996441281139</v>
+        <v>0.1089548100914888</v>
       </c>
       <c r="N185" s="14" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="20" t="n">
-        <v>0.1120996441281139</v>
+        <v>0.1089548100914888</v>
       </c>
       <c r="Q185" s="21" t="inlineStr">
         <is>
@@ -15083,13 +15083,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>160.75</v>
+        <v>160.7</v>
       </c>
       <c r="E186" s="6" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0669</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>0.09849999999999999</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="G186" s="7" t="n"/>
       <c r="H186" s="12" t="inlineStr">
@@ -15111,7 +15111,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="5" t="n">
-        <v>0.119751166407465</v>
+        <v>0.120099564405725</v>
       </c>
       <c r="Q186" s="10" t="inlineStr">
         <is>
@@ -15164,13 +15164,13 @@
         </is>
       </c>
       <c r="D187" s="15" t="n">
-        <v>27.45</v>
+        <v>27.39</v>
       </c>
       <c r="E187" s="16" t="n">
-        <v>-0.2272</v>
+        <v>-0.2289</v>
       </c>
       <c r="F187" s="16" t="n">
-        <v>-0.4274</v>
+        <v>-0.4287</v>
       </c>
       <c r="G187" s="17" t="n"/>
       <c r="H187" s="23" t="inlineStr">
@@ -15215,13 +15215,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>243.74</v>
+        <v>239.69</v>
       </c>
       <c r="E188" s="6" t="n">
-        <v>-0.2778</v>
+        <v>-0.2897</v>
       </c>
       <c r="F188" s="6" t="n">
-        <v>-0.4039</v>
+        <v>-0.4137</v>
       </c>
       <c r="G188" s="7" t="n"/>
       <c r="H188" s="12" t="inlineStr">
@@ -15266,13 +15266,13 @@
         </is>
       </c>
       <c r="D189" s="15" t="n">
-        <v>1652.82</v>
+        <v>1629</v>
       </c>
       <c r="E189" s="16" t="n">
-        <v>-0.1032</v>
+        <v>-0.1161</v>
       </c>
       <c r="F189" s="20" t="n">
-        <v>0.0149</v>
+        <v>0.0003</v>
       </c>
       <c r="G189" s="17" t="n">
         <v>46309</v>
@@ -15345,13 +15345,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>35.46</v>
+        <v>35.17</v>
       </c>
       <c r="E190" s="6" t="n">
-        <v>-0.1753</v>
+        <v>-0.1819</v>
       </c>
       <c r="F190" s="6" t="n">
-        <v>-0.0711</v>
+        <v>-0.0786</v>
       </c>
       <c r="G190" s="7" t="n"/>
       <c r="H190" s="12" t="inlineStr">
@@ -15396,13 +15396,13 @@
         </is>
       </c>
       <c r="D191" s="15" t="n">
-        <v>387.85</v>
+        <v>389.28</v>
       </c>
       <c r="E191" s="20" t="n">
-        <v>0.0501</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="F191" s="16" t="n">
-        <v>-0.1568</v>
+        <v>-0.1537</v>
       </c>
       <c r="G191" s="17" t="n">
         <v>46268</v>
@@ -15431,7 +15431,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="20" t="n">
-        <v>0.4051824158824287</v>
+        <v>0.4000205507603782</v>
       </c>
       <c r="N191" s="14" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="20" t="n">
-        <v>0.5005801211808688</v>
+        <v>0.4950678175092479</v>
       </c>
       <c r="Q191" s="21" t="inlineStr">
         <is>
@@ -15495,13 +15495,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>135.35</v>
+        <v>132.46</v>
       </c>
       <c r="E192" s="6" t="n">
-        <v>-0.1294</v>
+        <v>-0.1481</v>
       </c>
       <c r="F192" s="6" t="n">
-        <v>-0.1701</v>
+        <v>-0.1878</v>
       </c>
       <c r="G192" s="7" t="n">
         <v>46244</v>
@@ -15556,13 +15556,13 @@
         </is>
       </c>
       <c r="D193" s="15" t="n">
-        <v>338.27</v>
+        <v>340.02</v>
       </c>
       <c r="E193" s="16" t="n">
-        <v>-0.1045</v>
+        <v>-0.0998</v>
       </c>
       <c r="F193" s="16" t="n">
-        <v>-0.1832</v>
+        <v>-0.179</v>
       </c>
       <c r="G193" s="17" t="n"/>
       <c r="H193" s="23" t="inlineStr">
@@ -15581,7 +15581,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="20" t="n">
-        <v>0.2563928223017117</v>
+        <v>0.2499264749132405</v>
       </c>
       <c r="N193" s="14" t="inlineStr"/>
       <c r="O193" s="19" t="n"/>
@@ -15625,13 +15625,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>128.02</v>
+        <v>127.13</v>
       </c>
       <c r="E194" s="6" t="n">
-        <v>-0.0467</v>
+        <v>-0.0533</v>
       </c>
       <c r="F194" s="6" t="n">
-        <v>-0.0793</v>
+        <v>-0.0857</v>
       </c>
       <c r="G194" s="7" t="n"/>
       <c r="H194" s="12" t="inlineStr">
@@ -15676,13 +15676,13 @@
         </is>
       </c>
       <c r="D195" s="15" t="n">
-        <v>381.6</v>
+        <v>377.05</v>
       </c>
       <c r="E195" s="16" t="n">
-        <v>-0.1748</v>
+        <v>-0.1847</v>
       </c>
       <c r="F195" s="16" t="n">
-        <v>-0.3301</v>
+        <v>-0.3381</v>
       </c>
       <c r="G195" s="17" t="n">
         <v>46268</v>
@@ -15737,13 +15737,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>14.6</v>
+        <v>14.75</v>
       </c>
       <c r="E196" s="6" t="n">
-        <v>-0.055</v>
+        <v>-0.0453</v>
       </c>
       <c r="F196" s="6" t="n">
-        <v>-0.08</v>
+        <v>-0.0706</v>
       </c>
       <c r="G196" s="7" t="n">
         <v>46247</v>
@@ -15798,13 +15798,13 @@
         </is>
       </c>
       <c r="D197" s="15" t="n">
-        <v>339</v>
+        <v>331.44</v>
       </c>
       <c r="E197" s="16" t="n">
-        <v>-0.0626</v>
+        <v>-0.08349999999999999</v>
       </c>
       <c r="F197" s="16" t="n">
-        <v>-0.2053</v>
+        <v>-0.223</v>
       </c>
       <c r="G197" s="17" t="n"/>
       <c r="H197" s="23" t="inlineStr">
@@ -15849,13 +15849,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>261.59</v>
+        <v>262.89</v>
       </c>
       <c r="E198" s="6" t="n">
-        <v>-0.2904</v>
+        <v>-0.2869</v>
       </c>
       <c r="F198" s="6" t="n">
-        <v>-0.2792</v>
+        <v>-0.2756</v>
       </c>
       <c r="G198" s="7" t="n">
         <v>46246</v>
@@ -15910,13 +15910,13 @@
         </is>
       </c>
       <c r="D199" s="15" t="n">
-        <v>48.12</v>
+        <v>47.99</v>
       </c>
       <c r="E199" s="16" t="n">
-        <v>-0.3037</v>
+        <v>-0.3056</v>
       </c>
       <c r="F199" s="16" t="n">
-        <v>-0.1171</v>
+        <v>-0.1194</v>
       </c>
       <c r="G199" s="17" t="n"/>
       <c r="H199" s="23" t="inlineStr">
@@ -15961,13 +15961,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>21.18</v>
+        <v>20.72</v>
       </c>
       <c r="E200" s="6" t="n">
-        <v>-0.1065</v>
+        <v>-0.1261</v>
       </c>
       <c r="F200" s="6" t="n">
-        <v>-0.258</v>
+        <v>-0.2743</v>
       </c>
       <c r="G200" s="7" t="n"/>
       <c r="H200" s="12" t="inlineStr">
@@ -16012,13 +16012,13 @@
         </is>
       </c>
       <c r="D201" s="15" t="n">
-        <v>209.4</v>
+        <v>206.99</v>
       </c>
       <c r="E201" s="16" t="n">
-        <v>-0.1918</v>
+        <v>-0.2011</v>
       </c>
       <c r="F201" s="16" t="n">
-        <v>-0.07389999999999999</v>
+        <v>-0.08449999999999999</v>
       </c>
       <c r="G201" s="17" t="n">
         <v>46267</v>
@@ -16073,13 +16073,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>183.09</v>
+        <v>184.02</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>0.1217</v>
+        <v>0.1274</v>
       </c>
       <c r="F202" s="6" t="n">
-        <v>-0.1265</v>
+        <v>-0.122</v>
       </c>
       <c r="G202" s="7" t="n">
         <v>46267</v>
@@ -16108,7 +16108,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="5" t="n">
-        <v>0.0923589491506909</v>
+        <v>0.08683838713183344</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="5" t="n">
-        <v>0.3654486864383636</v>
+        <v>0.3585479839147918</v>
       </c>
       <c r="Q202" s="10" t="inlineStr">
         <is>
@@ -16164,13 +16164,13 @@
         </is>
       </c>
       <c r="D203" s="15" t="n">
-        <v>189.63</v>
+        <v>190.86</v>
       </c>
       <c r="E203" s="16" t="n">
-        <v>-0.0184</v>
+        <v>-0.012</v>
       </c>
       <c r="F203" s="16" t="n">
-        <v>-0.0302</v>
+        <v>-0.0239</v>
       </c>
       <c r="G203" s="17" t="n">
         <v>46260</v>
@@ -16199,7 +16199,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="16" t="n">
-        <v>-0.04419131993882822</v>
+        <v>-0.05035104264906221</v>
       </c>
       <c r="N203" s="14" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="16" t="n">
-        <v>-0.06396667194009384</v>
+        <v>-0.0699989521114954</v>
       </c>
       <c r="Q203" s="21" t="inlineStr">
         <is>
@@ -16251,13 +16251,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>72</v>
+        <v>71.77</v>
       </c>
       <c r="E204" s="6" t="n">
-        <v>-0.1597</v>
+        <v>-0.1624</v>
       </c>
       <c r="F204" s="6" t="n">
-        <v>-0.4231</v>
+        <v>-0.425</v>
       </c>
       <c r="G204" s="7" t="n">
         <v>46245</v>
@@ -16312,13 +16312,13 @@
         </is>
       </c>
       <c r="D205" s="15" t="n">
-        <v>115.4</v>
+        <v>115.99</v>
       </c>
       <c r="E205" s="16" t="n">
-        <v>-0.0137</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F205" s="16" t="n">
-        <v>-0.0488</v>
+        <v>-0.044</v>
       </c>
       <c r="G205" s="17" t="n">
         <v>46246</v>
@@ -16347,7 +16347,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="20" t="n">
-        <v>0.1265164644714037</v>
+        <v>0.1207862746788517</v>
       </c>
       <c r="N205" s="14" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="20" t="n">
-        <v>0.2998266897746966</v>
+        <v>0.2932149323217519</v>
       </c>
       <c r="Q205" s="21" t="inlineStr">
         <is>
@@ -16415,13 +16415,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>271.2</v>
+        <v>267.97</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>0.0254</v>
+        <v>0.0132</v>
       </c>
       <c r="F206" s="6" t="n">
-        <v>-0.0227</v>
+        <v>-0.0343</v>
       </c>
       <c r="G206" s="7" t="n">
         <v>46240</v>
@@ -16476,13 +16476,13 @@
         </is>
       </c>
       <c r="D207" s="15" t="n">
-        <v>406.42</v>
+        <v>405.37</v>
       </c>
       <c r="E207" s="16" t="n">
-        <v>-0.0443</v>
+        <v>-0.0467</v>
       </c>
       <c r="F207" s="16" t="n">
-        <v>-0.1278</v>
+        <v>-0.13</v>
       </c>
       <c r="G207" s="17" t="n">
         <v>46261</v>
@@ -16537,13 +16537,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>54.81</v>
+        <v>54.83</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>0.191</v>
+        <v>0.1914</v>
       </c>
       <c r="F208" s="6" t="n">
-        <v>-0.0388</v>
+        <v>-0.0384</v>
       </c>
       <c r="G208" s="7" t="n">
         <v>46268</v>
@@ -16598,13 +16598,13 @@
         </is>
       </c>
       <c r="D209" s="15" t="n">
-        <v>43.99</v>
+        <v>44.32</v>
       </c>
       <c r="E209" s="16" t="n">
-        <v>-0.0305</v>
+        <v>-0.0234</v>
       </c>
       <c r="F209" s="16" t="n">
-        <v>-0.0107</v>
+        <v>-0.0034</v>
       </c>
       <c r="G209" s="17" t="n">
         <v>46239</v>
@@ -16659,13 +16659,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>443.01</v>
+        <v>435.41</v>
       </c>
       <c r="E210" s="6" t="n">
-        <v>-0.1904</v>
+        <v>-0.2043</v>
       </c>
       <c r="F210" s="6" t="n">
-        <v>-0.2882</v>
+        <v>-0.3004</v>
       </c>
       <c r="G210" s="7" t="n">
         <v>46251</v>
@@ -16720,13 +16720,13 @@
         </is>
       </c>
       <c r="D211" s="15" t="n">
-        <v>108.29</v>
+        <v>106.2</v>
       </c>
       <c r="E211" s="16" t="n">
-        <v>-0.264</v>
+        <v>-0.2782</v>
       </c>
       <c r="F211" s="16" t="n">
-        <v>-0.05889999999999999</v>
+        <v>-0.0771</v>
       </c>
       <c r="G211" s="17" t="n"/>
       <c r="H211" s="23" t="inlineStr">
@@ -16771,13 +16771,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>159.29</v>
+        <v>161.95</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0187</v>
       </c>
       <c r="F212" s="5" t="n">
-        <v>0.08259999999999999</v>
+        <v>0.1007</v>
       </c>
       <c r="G212" s="7" t="n"/>
       <c r="H212" s="12" t="inlineStr">
@@ -16822,13 +16822,13 @@
         </is>
       </c>
       <c r="D213" s="15" t="n">
-        <v>50.56</v>
+        <v>49.99</v>
       </c>
       <c r="E213" s="16" t="n">
-        <v>-0.3453</v>
+        <v>-0.3527</v>
       </c>
       <c r="F213" s="16" t="n">
-        <v>-0.3674</v>
+        <v>-0.3746</v>
       </c>
       <c r="G213" s="17" t="n">
         <v>46239</v>
@@ -16883,13 +16883,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>139.6</v>
+        <v>138.25</v>
       </c>
       <c r="E214" s="6" t="n">
-        <v>-0.3673</v>
+        <v>-0.3734</v>
       </c>
       <c r="F214" s="6" t="n">
-        <v>-0.21</v>
+        <v>-0.2176</v>
       </c>
       <c r="G214" s="7" t="n"/>
       <c r="H214" s="12" t="inlineStr">
@@ -16934,13 +16934,13 @@
         </is>
       </c>
       <c r="D215" s="15" t="n">
-        <v>34.19</v>
+        <v>34.51</v>
       </c>
       <c r="E215" s="20" t="n">
-        <v>0.08439999999999999</v>
+        <v>0.09449999999999999</v>
       </c>
       <c r="F215" s="20" t="n">
-        <v>0.0118</v>
+        <v>0.0213</v>
       </c>
       <c r="G215" s="17" t="n">
         <v>46267</v>
@@ -16995,13 +16995,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>153.12</v>
+        <v>151.94</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>0.1995</v>
+        <v>0.1903</v>
       </c>
       <c r="F216" s="6" t="n">
-        <v>-0.1068</v>
+        <v>-0.1136</v>
       </c>
       <c r="G216" s="7" t="n">
         <v>46268</v>
@@ -17030,7 +17030,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="5" t="n">
-        <v>0.2408568443051201</v>
+        <v>0.2504936159010136</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="9" t="n"/>
@@ -17074,13 +17074,13 @@
         </is>
       </c>
       <c r="D217" s="15" t="n">
-        <v>47.67</v>
+        <v>47.9</v>
       </c>
       <c r="E217" s="20" t="n">
-        <v>0.08460000000000001</v>
+        <v>0.08990000000000001</v>
       </c>
       <c r="F217" s="20" t="n">
-        <v>0.0143</v>
+        <v>0.0191</v>
       </c>
       <c r="G217" s="17" t="n">
         <v>46267</v>
@@ -17109,7 +17109,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="20" t="n">
-        <v>0.4054961191525068</v>
+        <v>0.3987473903966597</v>
       </c>
       <c r="N217" s="14" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="20" t="n">
-        <v>0.4684287812041115</v>
+        <v>0.4613778705636744</v>
       </c>
       <c r="Q217" s="21" t="inlineStr">
         <is>
@@ -17161,13 +17161,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>235.3</v>
+        <v>237.36</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>0.2535</v>
+        <v>0.2644</v>
       </c>
       <c r="F218" s="6" t="n">
-        <v>-0.1026</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="G218" s="7" t="n">
         <v>46239</v>
@@ -17222,13 +17222,13 @@
         </is>
       </c>
       <c r="D219" s="15" t="n">
-        <v>220.47</v>
+        <v>223.65</v>
       </c>
       <c r="E219" s="16" t="n">
-        <v>-0.2298</v>
+        <v>-0.2187</v>
       </c>
       <c r="F219" s="16" t="n">
-        <v>-0.3119</v>
+        <v>-0.302</v>
       </c>
       <c r="G219" s="17" t="n">
         <v>46316</v>
@@ -17264,7 +17264,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="20" t="n">
-        <v>0.1339411257767497</v>
+        <v>0.1178180192264699</v>
       </c>
       <c r="Q219" s="21" t="inlineStr">
         <is>
@@ -17304,10 +17304,10 @@
         <v>9.83</v>
       </c>
       <c r="E220" s="6" t="n">
-        <v>-0.2399</v>
+        <v>-0.2398</v>
       </c>
       <c r="F220" s="6" t="n">
-        <v>-0.4444</v>
+        <v>-0.4443</v>
       </c>
       <c r="G220" s="7" t="n">
         <v>46246</v>
@@ -17362,13 +17362,13 @@
         </is>
       </c>
       <c r="D221" s="15" t="n">
-        <v>92.15000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="E221" s="16" t="n">
-        <v>-0.2745</v>
+        <v>-0.2899</v>
       </c>
       <c r="F221" s="16" t="n">
-        <v>-0.1571</v>
+        <v>-0.175</v>
       </c>
       <c r="G221" s="17" t="n">
         <v>46317</v>
@@ -17423,13 +17423,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>315.03</v>
+        <v>316.07</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>0.1795</v>
+        <v>0.1834</v>
       </c>
       <c r="F222" s="6" t="n">
-        <v>-0.1095</v>
+        <v>-0.1065</v>
       </c>
       <c r="G222" s="7" t="n">
         <v>46254</v>
@@ -17484,13 +17484,13 @@
         </is>
       </c>
       <c r="D223" s="15" t="n">
-        <v>36.19</v>
+        <v>36.44</v>
       </c>
       <c r="E223" s="16" t="n">
-        <v>-0.296</v>
+        <v>-0.2911</v>
       </c>
       <c r="F223" s="16" t="n">
-        <v>-0.4777</v>
+        <v>-0.474</v>
       </c>
       <c r="G223" s="17" t="n">
         <v>46239</v>
@@ -17545,13 +17545,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>36.65</v>
+        <v>36.8</v>
       </c>
       <c r="E224" s="6" t="n">
-        <v>-0.1539</v>
+        <v>-0.1505</v>
       </c>
       <c r="F224" s="6" t="n">
-        <v>-0.4389</v>
+        <v>-0.4367</v>
       </c>
       <c r="G224" s="7" t="n">
         <v>46261</v>
@@ -17606,13 +17606,13 @@
         </is>
       </c>
       <c r="D225" s="15" t="n">
-        <v>313.69</v>
+        <v>315.05</v>
       </c>
       <c r="E225" s="16" t="n">
-        <v>-0.1643</v>
+        <v>-0.1606</v>
       </c>
       <c r="F225" s="16" t="n">
-        <v>-0.1286</v>
+        <v>-0.1248</v>
       </c>
       <c r="G225" s="17" t="n">
         <v>46289</v>
@@ -17671,13 +17671,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>321.38</v>
+        <v>319.08</v>
       </c>
       <c r="E226" s="6" t="n">
-        <v>-0.0424</v>
+        <v>-0.0492</v>
       </c>
       <c r="F226" s="6" t="n">
-        <v>-0.0261</v>
+        <v>-0.0331</v>
       </c>
       <c r="G226" s="7" t="n">
         <v>46252</v>
@@ -17706,7 +17706,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>0.2135167091916112</v>
+        <v>0.2222640090259497</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="9" t="n"/>
@@ -17762,13 +17762,13 @@
         </is>
       </c>
       <c r="D227" s="15" t="n">
-        <v>186.34</v>
+        <v>182.82</v>
       </c>
       <c r="E227" s="16" t="n">
-        <v>-0.3</v>
+        <v>-0.3132</v>
       </c>
       <c r="F227" s="16" t="n">
-        <v>-0.0395</v>
+        <v>-0.0576</v>
       </c>
       <c r="G227" s="17" t="n"/>
       <c r="H227" s="23" t="inlineStr">
@@ -17787,7 +17787,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="20" t="n">
-        <v>0.6367929591070086</v>
+        <v>0.6683076249863255</v>
       </c>
       <c r="N227" s="14" t="inlineStr">
         <is>
@@ -17797,8 +17797,8 @@
       <c r="O227" s="19" t="n">
         <v>185</v>
       </c>
-      <c r="P227" s="16" t="n">
-        <v>-0.007191155951486548</v>
+      <c r="P227" s="20" t="n">
+        <v>0.01192429712285312</v>
       </c>
       <c r="Q227" s="21" t="inlineStr">
         <is>
@@ -17839,13 +17839,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>91.2</v>
+        <v>89.2</v>
       </c>
       <c r="E228" s="6" t="n">
-        <v>-0.3184</v>
+        <v>-0.3334</v>
       </c>
       <c r="F228" s="6" t="n">
-        <v>-0.1175</v>
+        <v>-0.1368</v>
       </c>
       <c r="G228" s="7" t="n">
         <v>46239</v>
@@ -17900,13 +17900,13 @@
         </is>
       </c>
       <c r="D229" s="15" t="n">
-        <v>718.6799999999999</v>
+        <v>713.9400000000001</v>
       </c>
       <c r="E229" s="16" t="n">
-        <v>-0.1029</v>
+        <v>-0.1089</v>
       </c>
       <c r="F229" s="16" t="n">
-        <v>-0.2059</v>
+        <v>-0.2111</v>
       </c>
       <c r="G229" s="17" t="n">
         <v>46245</v>
@@ -17961,13 +17961,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>101.66</v>
+        <v>102.48</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>0.0742</v>
+        <v>0.0828</v>
       </c>
       <c r="F230" s="6" t="n">
-        <v>-0.1974</v>
+        <v>-0.191</v>
       </c>
       <c r="G230" s="7" t="n"/>
       <c r="H230" s="12" t="inlineStr">
@@ -18012,13 +18012,13 @@
         </is>
       </c>
       <c r="D231" s="15" t="n">
-        <v>302.03</v>
+        <v>293.02</v>
       </c>
       <c r="E231" s="16" t="n">
-        <v>-0.2281</v>
+        <v>-0.2511</v>
       </c>
       <c r="F231" s="16" t="n">
-        <v>-0.0476</v>
+        <v>-0.076</v>
       </c>
       <c r="G231" s="17" t="n"/>
       <c r="H231" s="23" t="inlineStr">
@@ -18037,7 +18037,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="20" t="n">
-        <v>0.4899182200443666</v>
+        <v>0.5357313493959458</v>
       </c>
       <c r="N231" s="14" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="20" t="n">
-        <v>0.1753799291461114</v>
+        <v>0.2115213978568017</v>
       </c>
       <c r="Q231" s="21" t="inlineStr">
         <is>
@@ -18093,13 +18093,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>74.90000000000001</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="E232" s="6" t="n">
-        <v>-0.1555</v>
+        <v>-0.1624</v>
       </c>
       <c r="F232" s="6" t="n">
-        <v>-0.1816</v>
+        <v>-0.1883</v>
       </c>
       <c r="G232" s="7" t="n">
         <v>46240</v>
@@ -18154,13 +18154,13 @@
         </is>
       </c>
       <c r="D233" s="15" t="n">
-        <v>333.73</v>
+        <v>337.48</v>
       </c>
       <c r="E233" s="16" t="n">
-        <v>-0.07139999999999999</v>
+        <v>-0.0609</v>
       </c>
       <c r="F233" s="16" t="n">
-        <v>-0.1737</v>
+        <v>-0.1644</v>
       </c>
       <c r="G233" s="17" t="n">
         <v>46259</v>
@@ -18215,13 +18215,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>302.77</v>
+        <v>297.45</v>
       </c>
       <c r="E234" s="6" t="n">
-        <v>-0.2634</v>
+        <v>-0.2764</v>
       </c>
       <c r="F234" s="6" t="n">
-        <v>-0.04679999999999999</v>
+        <v>-0.0635</v>
       </c>
       <c r="G234" s="7" t="n">
         <v>46239</v>
@@ -18276,13 +18276,13 @@
         </is>
       </c>
       <c r="D235" s="15" t="n">
-        <v>1437.42</v>
+        <v>1426.03</v>
       </c>
       <c r="E235" s="20" t="n">
-        <v>0.0794</v>
+        <v>0.0708</v>
       </c>
       <c r="F235" s="16" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="G235" s="17" t="n"/>
       <c r="H235" s="23" t="inlineStr">
@@ -18327,13 +18327,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>191.8</v>
+        <v>187.56</v>
       </c>
       <c r="E236" s="6" t="n">
-        <v>-0.295</v>
+        <v>-0.3106</v>
       </c>
       <c r="F236" s="6" t="n">
-        <v>-0.1259</v>
+        <v>-0.1452</v>
       </c>
       <c r="G236" s="7" t="n">
         <v>46261</v>
@@ -18362,7 +18362,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="5" t="n">
-        <v>0.2513034410844629</v>
+        <v>0.2795905310300704</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="5" t="n">
-        <v>0.3086548488008341</v>
+        <v>0.3382384303689486</v>
       </c>
       <c r="Q236" s="10" t="inlineStr">
         <is>
@@ -18414,13 +18414,13 @@
         </is>
       </c>
       <c r="D237" s="15" t="n">
-        <v>462</v>
+        <v>464.72</v>
       </c>
       <c r="E237" s="20" t="n">
-        <v>0.2022</v>
+        <v>0.2093</v>
       </c>
       <c r="F237" s="20" t="n">
-        <v>0.0032</v>
+        <v>0.0091</v>
       </c>
       <c r="G237" s="17" t="n"/>
       <c r="H237" s="23" t="inlineStr">
@@ -18439,7 +18439,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="20" t="n">
-        <v>0.3528138528138528</v>
+        <v>0.3448958512652779</v>
       </c>
       <c r="N237" s="14" t="inlineStr">
         <is>
@@ -18450,7 +18450,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="20" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1297125150628335</v>
       </c>
       <c r="Q237" s="21" t="inlineStr">
         <is>
@@ -18503,13 +18503,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>435.63</v>
+        <v>435.75</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>0.0398</v>
+        <v>0.0401</v>
       </c>
       <c r="F238" s="5" t="n">
-        <v>0.0584</v>
+        <v>0.0587</v>
       </c>
       <c r="G238" s="7" t="n">
         <v>46239</v>
@@ -18541,7 +18541,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="5" t="n">
-        <v>0.205151160388403</v>
+        <v>0.2048192771084337</v>
       </c>
       <c r="Q238" s="10" t="inlineStr">
         <is>
@@ -18590,13 +18590,13 @@
         </is>
       </c>
       <c r="D239" s="15" t="n">
-        <v>92.89</v>
+        <v>93.28</v>
       </c>
       <c r="E239" s="16" t="n">
-        <v>-0.0054</v>
+        <v>-0.0012</v>
       </c>
       <c r="F239" s="16" t="n">
-        <v>-0.3798</v>
+        <v>-0.3772</v>
       </c>
       <c r="G239" s="17" t="n"/>
       <c r="H239" s="23" t="inlineStr">
@@ -18641,13 +18641,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>254.38</v>
+        <v>251.44</v>
       </c>
       <c r="E240" s="6" t="n">
-        <v>-0.2745</v>
+        <v>-0.2829</v>
       </c>
       <c r="F240" s="6" t="n">
-        <v>-0.281</v>
+        <v>-0.2893</v>
       </c>
       <c r="G240" s="7" t="n">
         <v>46240</v>
@@ -18702,13 +18702,13 @@
         </is>
       </c>
       <c r="D241" s="15" t="n">
-        <v>836.46</v>
+        <v>823.03</v>
       </c>
       <c r="E241" s="16" t="n">
-        <v>-0.1897</v>
+        <v>-0.2027</v>
       </c>
       <c r="F241" s="16" t="n">
-        <v>-0.1922</v>
+        <v>-0.2052</v>
       </c>
       <c r="G241" s="17" t="n">
         <v>46287</v>
@@ -18737,7 +18737,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="20" t="n">
-        <v>0.8231595055352318</v>
+        <v>0.8529093714688408</v>
       </c>
       <c r="N241" s="14" t="inlineStr">
         <is>
@@ -18785,13 +18785,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>187.69</v>
+        <v>190.41</v>
       </c>
       <c r="E242" s="6" t="n">
-        <v>-0.181</v>
+        <v>-0.1692</v>
       </c>
       <c r="F242" s="6" t="n">
-        <v>-0.2904</v>
+        <v>-0.2801</v>
       </c>
       <c r="G242" s="7" t="n">
         <v>46246</v>
@@ -18846,13 +18846,13 @@
         </is>
       </c>
       <c r="D243" s="15" t="n">
-        <v>278.64</v>
+        <v>278.98</v>
       </c>
       <c r="E243" s="20" t="n">
-        <v>0.1313</v>
+        <v>0.1326</v>
       </c>
       <c r="F243" s="20" t="n">
-        <v>0.0289</v>
+        <v>0.0301</v>
       </c>
       <c r="G243" s="17" t="n">
         <v>46240</v>
@@ -18907,13 +18907,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>110.9</v>
+        <v>111.23</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>0.0482</v>
+        <v>0.0513</v>
       </c>
       <c r="F244" s="6" t="n">
-        <v>-0.1837</v>
+        <v>-0.1813</v>
       </c>
       <c r="G244" s="7" t="n">
         <v>46323</v>
@@ -18942,7 +18942,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="5" t="n">
-        <v>0.4427412082957619</v>
+        <v>0.4384608468938235</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="5" t="n">
-        <v>0.3525698827772767</v>
+        <v>0.3485570439629596</v>
       </c>
       <c r="Q244" s="10" t="inlineStr">
         <is>
@@ -18998,13 +18998,13 @@
         </is>
       </c>
       <c r="D245" s="15" t="n">
-        <v>58.84</v>
+        <v>59.01</v>
       </c>
       <c r="E245" s="20" t="n">
-        <v>0.1492</v>
+        <v>0.1525</v>
       </c>
       <c r="F245" s="20" t="n">
-        <v>0.0532</v>
+        <v>0.0562</v>
       </c>
       <c r="G245" s="17" t="n">
         <v>46260</v>
@@ -19059,13 +19059,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>198.23</v>
+        <v>200.75</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.016</v>
       </c>
       <c r="F246" s="6" t="n">
-        <v>-0.1165</v>
+        <v>-0.1052</v>
       </c>
       <c r="G246" s="7" t="n">
         <v>46260</v>
@@ -19094,7 +19094,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="5" t="n">
-        <v>0.5890632094032185</v>
+        <v>0.5691158156911582</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="5" t="n">
-        <v>1.083438430106442</v>
+        <v>1.057285180572852</v>
       </c>
       <c r="Q246" s="10" t="inlineStr">
         <is>
@@ -19154,13 +19154,13 @@
         </is>
       </c>
       <c r="D247" s="15" t="n">
-        <v>399.55</v>
+        <v>390.87</v>
       </c>
       <c r="E247" s="16" t="n">
-        <v>-0.205</v>
+        <v>-0.2223</v>
       </c>
       <c r="F247" s="16" t="n">
-        <v>-0.1707</v>
+        <v>-0.1888</v>
       </c>
       <c r="G247" s="17" t="n">
         <v>46240</v>
@@ -19215,13 +19215,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>235.88</v>
+        <v>229.16</v>
       </c>
       <c r="E248" s="6" t="n">
-        <v>-0.1551</v>
+        <v>-0.1792</v>
       </c>
       <c r="F248" s="6" t="n">
-        <v>-0.2425</v>
+        <v>-0.2641</v>
       </c>
       <c r="G248" s="7" t="n"/>
       <c r="H248" s="12" t="inlineStr">
@@ -19262,13 +19262,13 @@
         </is>
       </c>
       <c r="D249" s="15" t="n">
-        <v>12.16</v>
+        <v>11.42</v>
       </c>
       <c r="E249" s="16" t="n">
-        <v>-0.3072</v>
+        <v>-0.3496</v>
       </c>
       <c r="F249" s="16" t="n">
-        <v>-0.453</v>
+        <v>-0.4864</v>
       </c>
       <c r="G249" s="17" t="n"/>
       <c r="H249" s="23" t="inlineStr">
@@ -19313,13 +19313,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>140.68</v>
+        <v>141.93</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>0.0016</v>
+        <v>0.0105</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0153</v>
       </c>
       <c r="G250" s="7" t="n">
         <v>46259</v>
@@ -19348,7 +19348,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="5" t="n">
-        <v>0.06624964458345176</v>
+        <v>0.05685901500739796</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="6" t="n">
-        <v>-0.07591697469434182</v>
+        <v>-0.08405552032692176</v>
       </c>
       <c r="Q250" s="10" t="inlineStr">
         <is>
@@ -19400,13 +19400,13 @@
         </is>
       </c>
       <c r="D251" s="15" t="n">
-        <v>83.37</v>
+        <v>81.61</v>
       </c>
       <c r="E251" s="16" t="n">
-        <v>-0.119</v>
+        <v>-0.1376</v>
       </c>
       <c r="F251" s="16" t="n">
-        <v>-0.3105</v>
+        <v>-0.3251</v>
       </c>
       <c r="G251" s="17" t="n">
         <v>46237</v>
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>261.01</v>
+        <v>258.58</v>
       </c>
       <c r="E252" s="6" t="n">
-        <v>-0.2572</v>
+        <v>-0.2641</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>0.0207</v>
+        <v>0.0112</v>
       </c>
       <c r="G252" s="7" t="n">
         <v>46240</v>
@@ -19522,13 +19522,13 @@
         </is>
       </c>
       <c r="D253" s="15" t="n">
-        <v>128.22</v>
+        <v>129.87</v>
       </c>
       <c r="E253" s="16" t="n">
-        <v>-0.1002</v>
+        <v>-0.0886</v>
       </c>
       <c r="F253" s="16" t="n">
-        <v>-0.4833</v>
+        <v>-0.4766</v>
       </c>
       <c r="G253" s="17" t="n">
         <v>46273</v>
@@ -19557,7 +19557,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="20" t="n">
-        <v>1.183746685384495</v>
+        <v>1.156002156002156</v>
       </c>
       <c r="N253" s="14" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="20" t="n">
-        <v>0.9107783497114335</v>
+        <v>0.8865018865018864</v>
       </c>
       <c r="Q253" s="21" t="inlineStr">
         <is>
@@ -19609,13 +19609,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>330.38</v>
+        <v>331.83</v>
       </c>
       <c r="E254" s="6" t="n">
-        <v>-0.06150000000000001</v>
+        <v>-0.0574</v>
       </c>
       <c r="F254" s="5" t="n">
-        <v>0.09949999999999999</v>
+        <v>0.1043</v>
       </c>
       <c r="G254" s="7" t="n">
         <v>46251</v>
@@ -19644,7 +19644,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="5" t="n">
-        <v>0.2712633936678976</v>
+        <v>0.2657083446343008</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -19655,7 +19655,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="5" t="n">
-        <v>0.2561293056480416</v>
+        <v>0.2506403881505591</v>
       </c>
       <c r="Q254" s="10" t="inlineStr">
         <is>
@@ -19704,13 +19704,13 @@
         </is>
       </c>
       <c r="D255" s="15" t="n">
-        <v>12.6</v>
+        <v>12.76</v>
       </c>
       <c r="E255" s="20" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.1048</v>
       </c>
       <c r="F255" s="16" t="n">
-        <v>-0.0378</v>
+        <v>-0.026</v>
       </c>
       <c r="G255" s="17" t="n">
         <v>46268</v>
@@ -19765,13 +19765,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>30.2</v>
+        <v>30.55</v>
       </c>
       <c r="E256" s="6" t="n">
-        <v>-0.0286</v>
+        <v>-0.0174</v>
       </c>
       <c r="F256" s="6" t="n">
-        <v>-0.2038</v>
+        <v>-0.1946</v>
       </c>
       <c r="G256" s="7" t="n">
         <v>46315</v>
@@ -19826,13 +19826,13 @@
         </is>
       </c>
       <c r="D257" s="15" t="n">
-        <v>149.75</v>
+        <v>151.36</v>
       </c>
       <c r="E257" s="20" t="n">
-        <v>0.0428</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="F257" s="20" t="n">
-        <v>0.0496</v>
+        <v>0.0609</v>
       </c>
       <c r="G257" s="17" t="n"/>
       <c r="H257" s="23" t="inlineStr">
@@ -19877,13 +19877,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>122.15</v>
+        <v>123.06</v>
       </c>
       <c r="E258" s="6" t="n">
-        <v>-0.0285</v>
+        <v>-0.0212</v>
       </c>
       <c r="F258" s="6" t="n">
-        <v>-0.2397</v>
+        <v>-0.234</v>
       </c>
       <c r="G258" s="7" t="n">
         <v>46237</v>
@@ -19938,13 +19938,13 @@
         </is>
       </c>
       <c r="D259" s="15" t="n">
-        <v>132.84</v>
+        <v>131.18</v>
       </c>
       <c r="E259" s="16" t="n">
-        <v>-0.1339</v>
+        <v>-0.1447</v>
       </c>
       <c r="F259" s="16" t="n">
-        <v>-0.1256</v>
+        <v>-0.1365</v>
       </c>
       <c r="G259" s="17" t="n">
         <v>46238</v>
@@ -20009,13 +20009,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>18.16</v>
+        <v>18.08</v>
       </c>
       <c r="E260" s="6" t="n">
-        <v>-0.2272</v>
+        <v>-0.2306</v>
       </c>
       <c r="F260" s="6" t="n">
-        <v>-0.3777</v>
+        <v>-0.3804</v>
       </c>
       <c r="G260" s="7" t="n">
         <v>46240</v>
@@ -20070,13 +20070,13 @@
         </is>
       </c>
       <c r="D261" s="15" t="n">
-        <v>148.3</v>
+        <v>147.61</v>
       </c>
       <c r="E261" s="16" t="n">
-        <v>-0.1848</v>
+        <v>-0.1886</v>
       </c>
       <c r="F261" s="16" t="n">
-        <v>-0.3524</v>
+        <v>-0.3554</v>
       </c>
       <c r="G261" s="17" t="n"/>
       <c r="H261" s="23" t="inlineStr">
@@ -20095,7 +20095,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="20" t="n">
-        <v>0.7869184086311529</v>
+        <v>0.7952713230810919</v>
       </c>
       <c r="N261" s="14" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>179</v>
       </c>
       <c r="P261" s="20" t="n">
-        <v>0.2070128118678354</v>
+        <v>0.21265496917553</v>
       </c>
       <c r="Q261" s="21" t="inlineStr">
         <is>
@@ -20151,13 +20151,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>90.29000000000001</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="E262" s="6" t="n">
-        <v>-0.006500000000000001</v>
+        <v>-0.0034</v>
       </c>
       <c r="F262" s="6" t="n">
-        <v>-0.0968</v>
+        <v>-0.094</v>
       </c>
       <c r="G262" s="7" t="n"/>
       <c r="H262" s="12" t="inlineStr">
@@ -20202,13 +20202,13 @@
         </is>
       </c>
       <c r="D263" s="15" t="n">
-        <v>7.98</v>
+        <v>8.1</v>
       </c>
       <c r="E263" s="16" t="n">
-        <v>-0.1538</v>
+        <v>-0.141</v>
       </c>
       <c r="F263" s="16" t="n">
-        <v>-0.3559</v>
+        <v>-0.3462</v>
       </c>
       <c r="G263" s="17" t="n">
         <v>46244</v>
@@ -20263,13 +20263,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>71.26000000000001</v>
+        <v>72.36</v>
       </c>
       <c r="E264" s="6" t="n">
-        <v>-0.1311</v>
+        <v>-0.1177</v>
       </c>
       <c r="F264" s="6" t="n">
-        <v>-0.1623</v>
+        <v>-0.1494</v>
       </c>
       <c r="G264" s="7" t="n">
         <v>46273</v>
@@ -20324,13 +20324,13 @@
         </is>
       </c>
       <c r="D265" s="15" t="n">
-        <v>14.96</v>
+        <v>14.95</v>
       </c>
       <c r="E265" s="16" t="n">
-        <v>-0.1991</v>
+        <v>-0.1997</v>
       </c>
       <c r="F265" s="16" t="n">
-        <v>-0.4163</v>
+        <v>-0.4167</v>
       </c>
       <c r="G265" s="17" t="n">
         <v>46240</v>
@@ -20385,13 +20385,13 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>391.3</v>
+        <v>391.97</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>0.1032</v>
+        <v>0.1051</v>
       </c>
       <c r="F266" s="5" t="n">
-        <v>0.1367</v>
+        <v>0.1386</v>
       </c>
       <c r="G266" s="7" t="n">
         <v>46317</v>
@@ -20460,13 +20460,13 @@
         </is>
       </c>
       <c r="D267" s="15" t="n">
-        <v>4.16</v>
+        <v>4.13</v>
       </c>
       <c r="E267" s="16" t="n">
-        <v>-0.359</v>
+        <v>-0.3636</v>
       </c>
       <c r="F267" s="16" t="n">
-        <v>-0.2973</v>
+        <v>-0.3024</v>
       </c>
       <c r="G267" s="17" t="n">
         <v>46245</v>
@@ -20521,13 +20521,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>18.67</v>
+        <v>19.06</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>0.0611</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="F268" s="5" t="n">
-        <v>0.048</v>
+        <v>0.0702</v>
       </c>
       <c r="G268" s="7" t="n">
         <v>46261</v>
@@ -20582,13 +20582,13 @@
         </is>
       </c>
       <c r="D269" s="15" t="n">
-        <v>16.39</v>
+        <v>16.77</v>
       </c>
       <c r="E269" s="20" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.09539999999999998</v>
       </c>
       <c r="F269" s="16" t="n">
-        <v>-0.1486</v>
+        <v>-0.1288</v>
       </c>
       <c r="G269" s="17" t="n">
         <v>46273</v>
@@ -20643,13 +20643,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>189.45</v>
+        <v>185.56</v>
       </c>
       <c r="E270" s="6" t="n">
-        <v>-0.2311</v>
+        <v>-0.2469</v>
       </c>
       <c r="F270" s="6" t="n">
-        <v>-0.2848</v>
+        <v>-0.2995</v>
       </c>
       <c r="G270" s="7" t="n"/>
       <c r="H270" s="12" t="inlineStr">
@@ -20694,13 +20694,13 @@
         </is>
       </c>
       <c r="D271" s="15" t="n">
-        <v>182.44</v>
+        <v>183.62</v>
       </c>
       <c r="E271" s="20" t="n">
-        <v>0.1463</v>
+        <v>0.1538</v>
       </c>
       <c r="F271" s="16" t="n">
-        <v>-0.0697</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="G271" s="17" t="n">
         <v>46316</v>
@@ -20775,13 +20775,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>28.04</v>
+        <v>28.4</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0271</v>
       </c>
       <c r="F272" s="6" t="n">
-        <v>-0.4019</v>
+        <v>-0.3942</v>
       </c>
       <c r="G272" s="7" t="n">
         <v>46245</v>
@@ -20836,13 +20836,13 @@
         </is>
       </c>
       <c r="D273" s="15" t="n">
-        <v>297.47</v>
+        <v>293.28</v>
       </c>
       <c r="E273" s="20" t="n">
-        <v>0.1389</v>
+        <v>0.1229</v>
       </c>
       <c r="F273" s="20" t="n">
-        <v>0.06179999999999999</v>
+        <v>0.04679999999999999</v>
       </c>
       <c r="G273" s="17" t="n">
         <v>46260</v>
@@ -20871,7 +20871,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="20" t="n">
-        <v>0.07573872995596184</v>
+        <v>0.0911074740861976</v>
       </c>
       <c r="N273" s="14" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="16" t="n">
-        <v>-0.05872861128853338</v>
+        <v>-0.0452809601745771</v>
       </c>
       <c r="Q273" s="21" t="inlineStr">
         <is>
@@ -20923,13 +20923,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>384.99</v>
+        <v>388.76</v>
       </c>
       <c r="E274" s="6" t="n">
-        <v>-0.153</v>
+        <v>-0.1447</v>
       </c>
       <c r="F274" s="6" t="n">
-        <v>-0.218</v>
+        <v>-0.2103</v>
       </c>
       <c r="G274" s="7" t="n">
         <v>46260</v>
@@ -20958,7 +20958,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="5" t="n">
-        <v>0.3896464843242681</v>
+        <v>0.3761703878999897</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="9" t="n"/>
@@ -21002,13 +21002,13 @@
         </is>
       </c>
       <c r="D275" s="15" t="n">
-        <v>6.14</v>
+        <v>6.13</v>
       </c>
       <c r="E275" s="16" t="n">
-        <v>-0.0814</v>
+        <v>-0.0823</v>
       </c>
       <c r="F275" s="16" t="n">
-        <v>-0.3366</v>
+        <v>-0.3373</v>
       </c>
       <c r="G275" s="17" t="n">
         <v>46239</v>
@@ -21063,13 +21063,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>62.16</v>
+        <v>62.28</v>
       </c>
       <c r="E276" s="6" t="n">
-        <v>-0.0572</v>
+        <v>-0.0554</v>
       </c>
       <c r="F276" s="6" t="n">
-        <v>-0.1766</v>
+        <v>-0.175</v>
       </c>
       <c r="G276" s="7" t="n"/>
       <c r="H276" s="12" t="inlineStr">
@@ -21114,13 +21114,13 @@
         </is>
       </c>
       <c r="D277" s="15" t="n">
-        <v>109.1</v>
+        <v>107.32</v>
       </c>
       <c r="E277" s="16" t="n">
-        <v>-0.1388</v>
+        <v>-0.1528</v>
       </c>
       <c r="F277" s="16" t="n">
-        <v>-0.1914</v>
+        <v>-0.2046</v>
       </c>
       <c r="G277" s="17" t="n">
         <v>46240</v>
@@ -21175,13 +21175,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>207.73</v>
+        <v>205.69</v>
       </c>
       <c r="E278" s="5" t="n">
-        <v>0.0312</v>
+        <v>0.0211</v>
       </c>
       <c r="F278" s="6" t="n">
-        <v>-0.0159</v>
+        <v>-0.0256</v>
       </c>
       <c r="G278" s="7" t="n">
         <v>46330</v>
@@ -21236,13 +21236,13 @@
         </is>
       </c>
       <c r="D279" s="15" t="n">
-        <v>377.11</v>
+        <v>367.69</v>
       </c>
       <c r="E279" s="16" t="n">
-        <v>-0.1175</v>
-      </c>
-      <c r="F279" s="20" t="n">
-        <v>0.0207</v>
+        <v>-0.1396</v>
+      </c>
+      <c r="F279" s="16" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="G279" s="17" t="n"/>
       <c r="H279" s="23" t="inlineStr">
@@ -21287,13 +21287,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>56.76</v>
+        <v>56.58</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>0.0795</v>
+        <v>0.0761</v>
       </c>
       <c r="F280" s="6" t="n">
-        <v>-0.0239</v>
+        <v>-0.027</v>
       </c>
       <c r="G280" s="7" t="n">
         <v>46239</v>
@@ -21348,13 +21348,13 @@
         </is>
       </c>
       <c r="D281" s="15" t="n">
-        <v>406.88</v>
+        <v>404.25</v>
       </c>
       <c r="E281" s="16" t="n">
-        <v>-0.08410000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="F281" s="16" t="n">
-        <v>-0.066</v>
+        <v>-0.07200000000000001</v>
       </c>
       <c r="G281" s="17" t="n">
         <v>46310</v>
@@ -21431,13 +21431,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>117.47</v>
+        <v>115.44</v>
       </c>
       <c r="E282" s="6" t="n">
-        <v>-0.3463000000000001</v>
+        <v>-0.3576</v>
       </c>
       <c r="F282" s="6" t="n">
-        <v>-0.3188</v>
+        <v>-0.3305</v>
       </c>
       <c r="G282" s="7" t="n">
         <v>46239</v>
@@ -21492,13 +21492,13 @@
         </is>
       </c>
       <c r="D283" s="15" t="n">
-        <v>195</v>
+        <v>197.35</v>
       </c>
       <c r="E283" s="16" t="n">
-        <v>-0.0682</v>
+        <v>-0.057</v>
       </c>
       <c r="F283" s="16" t="n">
-        <v>-0.143</v>
+        <v>-0.1327</v>
       </c>
       <c r="G283" s="17" t="n">
         <v>46240</v>
@@ -21553,13 +21553,13 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>276.04</v>
+        <v>275.74</v>
       </c>
       <c r="E284" s="6" t="n">
-        <v>-0.075</v>
+        <v>-0.076</v>
       </c>
       <c r="F284" s="6" t="n">
-        <v>-0.0585</v>
+        <v>-0.0595</v>
       </c>
       <c r="G284" s="7" t="n">
         <v>46315</v>
@@ -21588,7 +21588,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="5" t="n">
-        <v>0.08679901463555999</v>
+        <v>0.08798143178356418</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="5" t="n">
-        <v>0.1447616287494565</v>
+        <v>0.1460071081453543</v>
       </c>
       <c r="Q284" s="10" t="inlineStr">
         <is>
@@ -21656,13 +21656,13 @@
         </is>
       </c>
       <c r="D285" s="15" t="n">
-        <v>310.17</v>
+        <v>309.6</v>
       </c>
       <c r="E285" s="20" t="n">
-        <v>0.0282</v>
+        <v>0.0263</v>
       </c>
       <c r="F285" s="16" t="n">
-        <v>-0.0596</v>
+        <v>-0.0613</v>
       </c>
       <c r="G285" s="17" t="n"/>
       <c r="H285" s="23" t="inlineStr">
@@ -21681,7 +21681,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="20" t="n">
-        <v>0.08005287423026076</v>
+        <v>0.08204134366925056</v>
       </c>
       <c r="N285" s="14" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="20" t="n">
-        <v>0.2090144114517845</v>
+        <v>0.2112403100775193</v>
       </c>
       <c r="Q285" s="21" t="inlineStr">
         <is>
@@ -21733,13 +21733,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>31.46</v>
+        <v>31.71</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>0.0421</v>
+        <v>0.0503</v>
       </c>
       <c r="F286" s="6" t="n">
-        <v>-0.0221</v>
+        <v>-0.0143</v>
       </c>
       <c r="G286" s="7" t="n">
         <v>46240</v>
@@ -21794,13 +21794,13 @@
         </is>
       </c>
       <c r="D287" s="15" t="n">
-        <v>7.13</v>
+        <v>7.17</v>
       </c>
       <c r="E287" s="16" t="n">
-        <v>-0.1913</v>
+        <v>-0.1862</v>
       </c>
       <c r="F287" s="16" t="n">
-        <v>-0.3278</v>
+        <v>-0.3236</v>
       </c>
       <c r="G287" s="17" t="n">
         <v>46254</v>
@@ -21855,13 +21855,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>159.04</v>
+        <v>160.34</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>0.2209</v>
+        <v>0.2308</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0198</v>
       </c>
       <c r="G288" s="7" t="n">
         <v>46254</v>
@@ -21916,13 +21916,13 @@
         </is>
       </c>
       <c r="D289" s="15" t="n">
-        <v>552.54</v>
+        <v>544.84</v>
       </c>
       <c r="E289" s="16" t="n">
-        <v>-0.0766</v>
-      </c>
-      <c r="F289" s="20" t="n">
-        <v>0.0116</v>
+        <v>-0.0895</v>
+      </c>
+      <c r="F289" s="16" t="n">
+        <v>-0.0025</v>
       </c>
       <c r="G289" s="17" t="n">
         <v>46239</v>
@@ -21951,7 +21951,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="20" t="n">
-        <v>0.3211713179136353</v>
+        <v>0.3398428896556787</v>
       </c>
       <c r="N289" s="14" t="inlineStr">
         <is>
@@ -21962,7 +21962,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="20" t="n">
-        <v>0.04064864082238397</v>
+        <v>0.05535570075618524</v>
       </c>
       <c r="Q289" s="21" t="inlineStr">
         <is>
@@ -22003,13 +22003,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>23.91</v>
+        <v>23.62</v>
       </c>
       <c r="E290" s="6" t="n">
-        <v>-0.4635</v>
+        <v>-0.4699</v>
       </c>
       <c r="F290" s="6" t="n">
-        <v>-0.5485</v>
+        <v>-0.5539000000000001</v>
       </c>
       <c r="G290" s="7" t="n">
         <v>46238</v>
@@ -22064,13 +22064,13 @@
         </is>
       </c>
       <c r="D291" s="15" t="n">
-        <v>94.8</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="E291" s="20" t="n">
-        <v>0.0518</v>
+        <v>0.0659</v>
       </c>
       <c r="F291" s="16" t="n">
-        <v>-0.1507</v>
+        <v>-0.1393</v>
       </c>
       <c r="G291" s="17" t="n">
         <v>46259</v>
@@ -22125,13 +22125,13 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>150.02</v>
+        <v>151.2</v>
       </c>
       <c r="E292" s="5" t="n">
-        <v>0.0244</v>
+        <v>0.03240000000000001</v>
       </c>
       <c r="F292" s="6" t="n">
-        <v>-0.0365</v>
+        <v>-0.029</v>
       </c>
       <c r="G292" s="7" t="n">
         <v>46266</v>
@@ -22186,13 +22186,13 @@
         </is>
       </c>
       <c r="D293" s="15" t="n">
-        <v>294.61</v>
+        <v>294.89</v>
       </c>
       <c r="E293" s="16" t="n">
-        <v>-0.0385</v>
+        <v>-0.03759999999999999</v>
       </c>
       <c r="F293" s="20" t="n">
-        <v>0.0563</v>
+        <v>0.0574</v>
       </c>
       <c r="G293" s="17" t="n"/>
       <c r="H293" s="23" t="inlineStr">
@@ -22237,13 +22237,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>84.72</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>0.0304</v>
+        <v>0.0276</v>
       </c>
       <c r="F294" s="6" t="n">
-        <v>-0.0713</v>
+        <v>-0.0738</v>
       </c>
       <c r="G294" s="7" t="n">
         <v>46252</v>
@@ -22298,13 +22298,13 @@
         </is>
       </c>
       <c r="D295" s="15" t="n">
-        <v>137.63</v>
+        <v>137</v>
       </c>
       <c r="E295" s="16" t="n">
-        <v>-0.0061</v>
+        <v>-0.0106</v>
       </c>
       <c r="F295" s="16" t="n">
-        <v>-0.036</v>
+        <v>-0.0404</v>
       </c>
       <c r="G295" s="17" t="n">
         <v>46238</v>
@@ -22333,7 +22333,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="20" t="n">
-        <v>0.2061323839279227</v>
+        <v>0.2116788321167883</v>
       </c>
       <c r="N295" s="14" t="inlineStr"/>
       <c r="O295" s="19" t="n"/>
@@ -22381,13 +22381,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>30.06</v>
+        <v>30.29</v>
       </c>
       <c r="E296" s="5" t="n">
-        <v>0.1125</v>
+        <v>0.121</v>
       </c>
       <c r="F296" s="6" t="n">
-        <v>-0.1335</v>
+        <v>-0.1268</v>
       </c>
       <c r="G296" s="7" t="n">
         <v>46317</v>
@@ -22442,13 +22442,13 @@
         </is>
       </c>
       <c r="D297" s="15" t="n">
-        <v>278.77</v>
-      </c>
-      <c r="E297" s="20" t="n">
-        <v>0.0014</v>
+        <v>277.63</v>
+      </c>
+      <c r="E297" s="16" t="n">
+        <v>-0.0027</v>
       </c>
       <c r="F297" s="20" t="n">
-        <v>0.113</v>
+        <v>0.1084</v>
       </c>
       <c r="G297" s="17" t="n"/>
       <c r="H297" s="23" t="inlineStr">
@@ -22467,7 +22467,7 @@
         <v>275</v>
       </c>
       <c r="M297" s="16" t="n">
-        <v>-0.01352369336729197</v>
+        <v>-0.009473039657097559</v>
       </c>
       <c r="N297" s="14" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="20" t="n">
-        <v>0.1192022097069269</v>
+        <v>0.1237978604617657</v>
       </c>
       <c r="Q297" s="21" t="inlineStr">
         <is>
@@ -22531,13 +22531,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>36.79</v>
+        <v>36.73</v>
       </c>
       <c r="E298" s="6" t="n">
-        <v>-0.1957</v>
+        <v>-0.197</v>
       </c>
       <c r="F298" s="6" t="n">
-        <v>-0.1175</v>
+        <v>-0.119</v>
       </c>
       <c r="G298" s="7" t="n"/>
       <c r="H298" s="12" t="inlineStr">
@@ -22586,13 +22586,13 @@
         </is>
       </c>
       <c r="D299" s="15" t="n">
-        <v>62.46</v>
+        <v>62.63</v>
       </c>
       <c r="E299" s="20" t="n">
-        <v>0.0318</v>
+        <v>0.0347</v>
       </c>
       <c r="F299" s="16" t="n">
-        <v>-0.0684</v>
+        <v>-0.0658</v>
       </c>
       <c r="G299" s="17" t="n">
         <v>46310</v>
@@ -22647,13 +22647,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>479.8</v>
+        <v>478.38</v>
       </c>
       <c r="E300" s="6" t="n">
-        <v>-0.1007</v>
+        <v>-0.1034</v>
       </c>
       <c r="F300" s="6" t="n">
-        <v>-0.0354</v>
+        <v>-0.0383</v>
       </c>
       <c r="G300" s="7" t="n">
         <v>46234</v>
@@ -22682,7 +22682,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="5" t="n">
-        <v>0.1879949979157982</v>
+        <v>0.1915213846732723</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="5" t="n">
-        <v>0.09420591913297205</v>
+        <v>0.0974539069359087</v>
       </c>
       <c r="Q300" s="10" t="inlineStr">
         <is>
@@ -22746,13 +22746,13 @@
         </is>
       </c>
       <c r="D301" s="15" t="n">
-        <v>537.2</v>
+        <v>525.14</v>
       </c>
       <c r="E301" s="16" t="n">
-        <v>-0.0726</v>
+        <v>-0.0934</v>
       </c>
       <c r="F301" s="16" t="n">
-        <v>-0.0591</v>
+        <v>-0.0803</v>
       </c>
       <c r="G301" s="17" t="n"/>
       <c r="H301" s="23" t="inlineStr">
@@ -22771,7 +22771,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="20" t="n">
-        <v>0.1466865227103499</v>
+        <v>0.1730205278592376</v>
       </c>
       <c r="N301" s="14" t="inlineStr"/>
       <c r="O301" s="19" t="n"/>
@@ -22815,13 +22815,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>257.52</v>
+        <v>257.29</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>0.1758</v>
+        <v>0.1747</v>
       </c>
       <c r="F302" s="5" t="n">
-        <v>0.024</v>
+        <v>0.0231</v>
       </c>
       <c r="G302" s="7" t="n"/>
       <c r="H302" s="12" t="inlineStr">
@@ -22840,7 +22840,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="5" t="n">
-        <v>0.09894377135756453</v>
+        <v>0.09992615336779501</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="9" t="n"/>
@@ -22886,13 +22886,13 @@
         </is>
       </c>
       <c r="D303" s="15" t="n">
-        <v>245.93</v>
+        <v>245.84</v>
       </c>
       <c r="E303" s="20" t="n">
-        <v>0.0336</v>
+        <v>0.0332</v>
       </c>
       <c r="F303" s="20" t="n">
-        <v>0.1095</v>
+        <v>0.109</v>
       </c>
       <c r="G303" s="17" t="n">
         <v>46321</v>
@@ -22921,7 +22921,7 @@
         <v>246</v>
       </c>
       <c r="M303" s="20" t="n">
-        <v>0.0002846338388972194</v>
+        <v>0.0006508298080051927</v>
       </c>
       <c r="N303" s="14" t="inlineStr"/>
       <c r="O303" s="19" t="n"/>
@@ -22969,13 +22969,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>111.11</v>
+        <v>110.52</v>
       </c>
       <c r="E304" s="6" t="n">
-        <v>-0.09380000000000001</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="F304" s="6" t="n">
-        <v>-0.0086</v>
+        <v>-0.0138</v>
       </c>
       <c r="G304" s="7" t="n"/>
       <c r="H304" s="12" t="inlineStr">
@@ -22994,7 +22994,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="5" t="n">
-        <v>0.1700117001170012</v>
+        <v>0.1762576909156714</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="5" t="n">
-        <v>0.1520115201152012</v>
+        <v>0.158161418747738</v>
       </c>
       <c r="Q304" s="10" t="inlineStr">
         <is>
@@ -23054,13 +23054,13 @@
         </is>
       </c>
       <c r="D305" s="15" t="n">
-        <v>107.36</v>
+        <v>107.07</v>
       </c>
       <c r="E305" s="16" t="n">
-        <v>-0.03</v>
+        <v>-0.0326</v>
       </c>
       <c r="F305" s="20" t="n">
-        <v>0.0262</v>
+        <v>0.0234</v>
       </c>
       <c r="G305" s="17" t="n">
         <v>46302</v>
@@ -23089,7 +23089,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="20" t="n">
-        <v>0.257451564828614</v>
+        <v>0.260857383020454</v>
       </c>
       <c r="N305" s="14" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="20" t="n">
-        <v>0.1643070044709389</v>
+        <v>0.1674605398337537</v>
       </c>
       <c r="Q305" s="21" t="inlineStr"/>
       <c r="R305" s="19" t="n"/>
@@ -23135,13 +23135,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>340.88</v>
+        <v>340.85</v>
       </c>
       <c r="E306" s="6" t="n">
-        <v>-0.0149</v>
+        <v>-0.015</v>
       </c>
       <c r="F306" s="5" t="n">
-        <v>0.1561</v>
+        <v>0.156</v>
       </c>
       <c r="G306" s="7" t="n"/>
       <c r="H306" s="12" t="inlineStr">
@@ -23160,7 +23160,7 @@
         <v>350</v>
       </c>
       <c r="M306" s="5" t="n">
-        <v>0.02675428303215209</v>
+        <v>0.02684465307319929</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="5" t="n">
-        <v>0.1734334663224595</v>
+        <v>0.1735367463693706</v>
       </c>
       <c r="Q306" s="10" t="inlineStr">
         <is>
@@ -23212,13 +23212,13 @@
         </is>
       </c>
       <c r="D307" s="15" t="n">
-        <v>76.98999999999999</v>
-      </c>
-      <c r="E307" s="16" t="n">
-        <v>-0.0019</v>
+        <v>77.17</v>
+      </c>
+      <c r="E307" s="20" t="n">
+        <v>0.0004</v>
       </c>
       <c r="F307" s="16" t="n">
-        <v>-0.0883</v>
+        <v>-0.0862</v>
       </c>
       <c r="G307" s="17" t="n">
         <v>46260</v>
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>52.26</v>
+        <v>51.41</v>
       </c>
       <c r="E308" s="6" t="n">
-        <v>-0.3335</v>
+        <v>-0.3443</v>
       </c>
       <c r="F308" s="6" t="n">
-        <v>-0.1345</v>
+        <v>-0.1486</v>
       </c>
       <c r="G308" s="7" t="n">
         <v>46245</v>
@@ -23330,13 +23330,13 @@
         </is>
       </c>
       <c r="D309" s="15" t="n">
-        <v>77.45999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E309" s="20" t="n">
-        <v>0.0155</v>
+        <v>0.0199</v>
       </c>
       <c r="F309" s="20" t="n">
-        <v>0.0689</v>
+        <v>0.0735</v>
       </c>
       <c r="G309" s="17" t="n"/>
       <c r="H309" s="23" t="inlineStr">
@@ -23355,14 +23355,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="20" t="n">
-        <v>0.07152078492124976</v>
+        <v>0.06683804627249361</v>
       </c>
       <c r="N309" s="14" t="inlineStr"/>
       <c r="O309" s="19" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="20" t="n">
-        <v>0.123160340821069</v>
+        <v>0.1182519280205656</v>
       </c>
       <c r="Q309" s="21" t="inlineStr"/>
       <c r="R309" s="19" t="n"/>
@@ -23397,13 +23397,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>171.29</v>
+        <v>173.36</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>0.0313</v>
+        <v>0.0438</v>
       </c>
       <c r="F310" s="6" t="n">
-        <v>-0.0866</v>
+        <v>-0.0756</v>
       </c>
       <c r="G310" s="7" t="n"/>
       <c r="H310" s="12" t="inlineStr">
@@ -23422,7 +23422,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="5" t="n">
-        <v>0.1676104851421566</v>
+        <v>0.1536686663590216</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="9" t="n"/>
@@ -23470,13 +23470,13 @@
         </is>
       </c>
       <c r="D311" s="15" t="n">
-        <v>146.9</v>
+        <v>146.81</v>
       </c>
       <c r="E311" s="20" t="n">
-        <v>0.0621</v>
+        <v>0.06150000000000001</v>
       </c>
       <c r="F311" s="20" t="n">
-        <v>0.1786</v>
+        <v>0.1779</v>
       </c>
       <c r="G311" s="17" t="n"/>
       <c r="H311" s="23" t="inlineStr">
@@ -23525,13 +23525,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>190.73</v>
+        <v>188.52</v>
       </c>
       <c r="E312" s="5" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.0692</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>0.031</v>
+        <v>0.019</v>
       </c>
       <c r="G312" s="7" t="n">
         <v>46317</v>
@@ -23560,7 +23560,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="5" t="n">
-        <v>0.1534630105384576</v>
+        <v>0.1669849352853808</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -23571,7 +23571,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="5" t="n">
-        <v>0.2058931473811147</v>
+        <v>0.2200297050710799</v>
       </c>
       <c r="Q312" s="10" t="inlineStr">
         <is>
@@ -23612,13 +23612,13 @@
         </is>
       </c>
       <c r="D313" s="15" t="n">
-        <v>1033.73</v>
+        <v>1019.28</v>
       </c>
       <c r="E313" s="20" t="n">
-        <v>0.0198</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F313" s="16" t="n">
-        <v>-0.0162</v>
+        <v>-0.03</v>
       </c>
       <c r="G313" s="17" t="n"/>
       <c r="H313" s="23" t="inlineStr">
@@ -23637,7 +23637,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="20" t="n">
-        <v>0.1608447079991874</v>
+        <v>0.1773016246762421</v>
       </c>
       <c r="N313" s="14" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="20" t="n">
-        <v>0.1995395315991603</v>
+        <v>0.2165450121654502</v>
       </c>
       <c r="Q313" s="21" t="inlineStr">
         <is>
@@ -23693,13 +23693,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>125</v>
+        <v>124.09</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>0.0381</v>
+        <v>0.0306</v>
       </c>
       <c r="F314" s="5" t="n">
-        <v>0.0525</v>
+        <v>0.0449</v>
       </c>
       <c r="G314" s="7" t="n">
         <v>46234</v>
@@ -23728,7 +23728,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="5" t="n">
-        <v>0.032</v>
+        <v>0.0395680554436296</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>122</v>
       </c>
       <c r="P314" s="6" t="n">
-        <v>-0.024</v>
+        <v>-0.01684261423160612</v>
       </c>
       <c r="Q314" s="10" t="inlineStr">
         <is>
@@ -23780,13 +23780,13 @@
         </is>
       </c>
       <c r="D315" s="15" t="n">
-        <v>63.72</v>
+        <v>63.87</v>
       </c>
       <c r="E315" s="20" t="n">
-        <v>0.0307</v>
+        <v>0.0332</v>
       </c>
       <c r="F315" s="20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0725</v>
       </c>
       <c r="G315" s="17" t="n">
         <v>46239</v>
@@ -23815,14 +23815,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="20" t="n">
-        <v>0.02008788449466417</v>
+        <v>0.0176921872553625</v>
       </c>
       <c r="N315" s="14" t="inlineStr"/>
       <c r="O315" s="19" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="20" t="n">
-        <v>0.05147520401757692</v>
+        <v>0.04900579301706596</v>
       </c>
       <c r="Q315" s="21" t="inlineStr">
         <is>
@@ -23863,13 +23863,13 @@
         </is>
       </c>
       <c r="D316" s="4" t="n">
-        <v>144.67</v>
+        <v>144.61</v>
       </c>
       <c r="E316" s="5" t="n">
-        <v>0.0575</v>
+        <v>0.0571</v>
       </c>
       <c r="F316" s="5" t="n">
-        <v>0.0406</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="G316" s="7" t="n">
         <v>46309</v>
@@ -23898,7 +23898,7 @@
         <v>167</v>
       </c>
       <c r="M316" s="5" t="n">
-        <v>0.1543512822285202</v>
+        <v>0.1548302330405918</v>
       </c>
       <c r="N316" s="3" t="inlineStr"/>
       <c r="O316" s="9" t="n"/>
@@ -23942,13 +23942,13 @@
         </is>
       </c>
       <c r="D317" s="15" t="n">
-        <v>323.31</v>
+        <v>324.17</v>
       </c>
       <c r="E317" s="20" t="n">
-        <v>0.0008</v>
+        <v>0.0035</v>
       </c>
       <c r="F317" s="20" t="n">
-        <v>0.09300000000000001</v>
+        <v>0.0959</v>
       </c>
       <c r="G317" s="17" t="n"/>
       <c r="H317" s="23" t="inlineStr">
@@ -23974,7 +23974,7 @@
         <v>316</v>
       </c>
       <c r="P317" s="16" t="n">
-        <v>-0.02260987906343757</v>
+        <v>-0.02520282567788511</v>
       </c>
       <c r="Q317" s="21" t="inlineStr">
         <is>
@@ -24015,13 +24015,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>231.07</v>
+        <v>229.37</v>
       </c>
       <c r="E318" s="5" t="n">
-        <v>0.0362</v>
+        <v>0.0286</v>
       </c>
       <c r="F318" s="5" t="n">
-        <v>0.14</v>
+        <v>0.1316</v>
       </c>
       <c r="G318" s="7" t="n">
         <v>46244</v>
@@ -24057,7 +24057,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="6" t="n">
-        <v>-0.06954602501406497</v>
+        <v>-0.06264986702707417</v>
       </c>
       <c r="Q318" s="10" t="inlineStr">
         <is>
@@ -24098,13 +24098,13 @@
         </is>
       </c>
       <c r="D319" s="15" t="n">
-        <v>123.61</v>
+        <v>123.48</v>
       </c>
       <c r="E319" s="20" t="n">
-        <v>0.0235</v>
+        <v>0.0224</v>
       </c>
       <c r="F319" s="20" t="n">
-        <v>0.0271</v>
+        <v>0.026</v>
       </c>
       <c r="G319" s="17" t="n"/>
       <c r="H319" s="23" t="inlineStr">
@@ -24123,7 +24123,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="20" t="n">
-        <v>0.1487743710055821</v>
+        <v>0.1499838030450275</v>
       </c>
       <c r="N319" s="14" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="20" t="n">
-        <v>0.1083245692096109</v>
+        <v>0.1094914156138646</v>
       </c>
       <c r="Q319" s="21" t="inlineStr">
         <is>
@@ -24183,13 +24183,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>236.8</v>
+        <v>234.44</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>0.0287</v>
+        <v>0.0185</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>0.1999</v>
+        <v>0.1879</v>
       </c>
       <c r="G320" s="7" t="n"/>
       <c r="H320" s="12" t="inlineStr">
@@ -24208,7 +24208,7 @@
         <v>237</v>
       </c>
       <c r="M320" s="5" t="n">
-        <v>0.0008445945945945465</v>
+        <v>0.01091963828698175</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -24218,8 +24218,8 @@
       <c r="O320" s="9" t="n">
         <v>236</v>
       </c>
-      <c r="P320" s="6" t="n">
-        <v>-0.003378378378378426</v>
+      <c r="P320" s="5" t="n">
+        <v>0.00665415458112951</v>
       </c>
       <c r="Q320" s="10" t="inlineStr">
         <is>
@@ -24260,13 +24260,13 @@
         </is>
       </c>
       <c r="D321" s="15" t="n">
-        <v>174.38</v>
-      </c>
-      <c r="E321" s="20" t="n">
-        <v>0.007800000000000001</v>
+        <v>172.78</v>
+      </c>
+      <c r="E321" s="16" t="n">
+        <v>-0.0014</v>
       </c>
       <c r="F321" s="20" t="n">
-        <v>0.0432</v>
+        <v>0.0337</v>
       </c>
       <c r="G321" s="17" t="n">
         <v>46239</v>
@@ -24295,7 +24295,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="20" t="n">
-        <v>0.1469205184080744</v>
+        <v>0.1575413821044102</v>
       </c>
       <c r="N321" s="14" t="inlineStr"/>
       <c r="O321" s="19" t="n"/>
@@ -24339,13 +24339,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>136.32</v>
+        <v>134.17</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>0.0344</v>
+        <v>0.0181</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>0.1254</v>
+        <v>0.1077</v>
       </c>
       <c r="G322" s="7" t="n"/>
       <c r="H322" s="12" t="inlineStr">
@@ -24364,7 +24364,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="6" t="n">
-        <v>-0.03902582159624408</v>
+        <v>-0.02362674219274046</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="9" t="n"/>
@@ -24408,13 +24408,13 @@
         </is>
       </c>
       <c r="D323" s="15" t="n">
-        <v>33.34</v>
+        <v>33.35</v>
       </c>
       <c r="E323" s="16" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.0925</v>
       </c>
       <c r="F323" s="16" t="n">
-        <v>-0.1434</v>
+        <v>-0.1431</v>
       </c>
       <c r="G323" s="17" t="n">
         <v>46234</v>
@@ -24487,13 +24487,13 @@
         </is>
       </c>
       <c r="D324" s="4" t="n">
-        <v>41.92</v>
+        <v>41.76</v>
       </c>
       <c r="E324" s="5" t="n">
-        <v>0.1644</v>
+        <v>0.16</v>
       </c>
       <c r="F324" s="5" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0741</v>
       </c>
       <c r="G324" s="7" t="n"/>
       <c r="H324" s="12" t="inlineStr">
@@ -24538,13 +24538,13 @@
         </is>
       </c>
       <c r="D325" s="15" t="n">
-        <v>263.48</v>
+        <v>262.75</v>
       </c>
       <c r="E325" s="20" t="n">
-        <v>0.1141</v>
+        <v>0.111</v>
       </c>
       <c r="F325" s="16" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0111</v>
       </c>
       <c r="G325" s="17" t="n">
         <v>46240</v>
@@ -24573,7 +24573,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="20" t="n">
-        <v>0.4574161226658569</v>
+        <v>0.461465271170314</v>
       </c>
       <c r="N325" s="14" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="20" t="n">
-        <v>0.4422347047214209</v>
+        <v>0.4462416745956232</v>
       </c>
       <c r="Q325" s="21" t="inlineStr"/>
       <c r="R325" s="19" t="n"/>
@@ -24627,13 +24627,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>72.41</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="E326" s="6" t="n">
-        <v>-0.0462</v>
+        <v>-0.0518</v>
       </c>
       <c r="F326" s="5" t="n">
-        <v>0.0259</v>
+        <v>0.02</v>
       </c>
       <c r="G326" s="7" t="n"/>
       <c r="H326" s="12" t="inlineStr">
@@ -24652,7 +24652,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="5" t="n">
-        <v>0.09100952907057042</v>
+        <v>0.09737463536602314</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="9" t="n"/>
@@ -24704,13 +24704,13 @@
         </is>
       </c>
       <c r="D327" s="15" t="n">
-        <v>125.91</v>
-      </c>
-      <c r="E327" s="20" t="n">
-        <v>0.0011</v>
+        <v>125.43</v>
+      </c>
+      <c r="E327" s="16" t="n">
+        <v>-0.0027</v>
       </c>
       <c r="F327" s="20" t="n">
-        <v>0.05019999999999999</v>
+        <v>0.0462</v>
       </c>
       <c r="G327" s="17" t="n">
         <v>46238</v>
@@ -24739,7 +24739,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="20" t="n">
-        <v>0.08013660551187358</v>
+        <v>0.08427011081878333</v>
       </c>
       <c r="N327" s="14" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="20" t="n">
-        <v>0.1119053292033993</v>
+        <v>0.1161604081958064</v>
       </c>
       <c r="Q327" s="21" t="inlineStr">
         <is>
@@ -24791,13 +24791,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>108.56</v>
+        <v>107.62</v>
       </c>
       <c r="E328" s="6" t="n">
-        <v>-0.0381</v>
+        <v>-0.0464</v>
       </c>
       <c r="F328" s="5" t="n">
-        <v>0.0342</v>
+        <v>0.0252</v>
       </c>
       <c r="G328" s="7" t="n"/>
       <c r="H328" s="12" t="inlineStr">
@@ -24816,7 +24816,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="5" t="n">
-        <v>0.2067059690493736</v>
+        <v>0.2172458650808399</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="5" t="n">
-        <v>0.1145910095799558</v>
+        <v>0.1243263333952796</v>
       </c>
       <c r="Q328" s="10" t="inlineStr">
         <is>
@@ -24872,13 +24872,13 @@
         </is>
       </c>
       <c r="D329" s="15" t="n">
-        <v>87.84999999999999</v>
+        <v>86.92</v>
       </c>
       <c r="E329" s="20" t="n">
-        <v>0.0171</v>
+        <v>0.0064</v>
       </c>
       <c r="F329" s="20" t="n">
-        <v>0.05</v>
+        <v>0.039</v>
       </c>
       <c r="G329" s="17" t="n">
         <v>46318</v>
@@ -24914,7 +24914,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="20" t="n">
-        <v>0.2179852020489471</v>
+        <v>0.2310170271514036</v>
       </c>
       <c r="Q329" s="21" t="inlineStr">
         <is>
@@ -24963,13 +24963,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>58.18</v>
+        <v>57.89</v>
       </c>
       <c r="E330" s="5" t="n">
-        <v>0.0352</v>
+        <v>0.0301</v>
       </c>
       <c r="F330" s="5" t="n">
-        <v>0.0842</v>
+        <v>0.0788</v>
       </c>
       <c r="G330" s="7" t="n">
         <v>46237</v>
@@ -24998,7 +24998,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="5" t="n">
-        <v>0.08284633894809214</v>
+        <v>0.08827085852478839</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="9" t="n"/>
@@ -25042,13 +25042,13 @@
         </is>
       </c>
       <c r="D331" s="15" t="n">
-        <v>39.57</v>
+        <v>38.83</v>
       </c>
       <c r="E331" s="16" t="n">
-        <v>-0.2456</v>
+        <v>-0.2597</v>
       </c>
       <c r="F331" s="16" t="n">
-        <v>-0.4084</v>
+        <v>-0.4195</v>
       </c>
       <c r="G331" s="17" t="n">
         <v>46241</v>
@@ -25103,13 +25103,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>8.609999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="E332" s="6" t="n">
-        <v>-0.1512</v>
+        <v>-0.1704</v>
       </c>
       <c r="F332" s="6" t="n">
-        <v>-0.3317</v>
+        <v>-0.3468</v>
       </c>
       <c r="G332" s="7" t="n">
         <v>46239</v>
@@ -25164,13 +25164,13 @@
         </is>
       </c>
       <c r="D333" s="15" t="n">
-        <v>94.98</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="E333" s="16" t="n">
-        <v>-0.0015</v>
+        <v>-0.0061</v>
       </c>
       <c r="F333" s="20" t="n">
-        <v>0.0668</v>
+        <v>0.0619</v>
       </c>
       <c r="G333" s="17" t="n"/>
       <c r="H333" s="23" t="inlineStr">
@@ -25189,7 +25189,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="20" t="n">
-        <v>0.04232469993682876</v>
+        <v>0.04717579860376554</v>
       </c>
       <c r="N333" s="14" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="20" t="n">
-        <v>0.1791956201305538</v>
+        <v>0.1846837317537549</v>
       </c>
       <c r="Q333" s="21" t="inlineStr">
         <is>
@@ -25241,13 +25241,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>110.12</v>
+        <v>109.42</v>
       </c>
       <c r="E334" s="6" t="n">
-        <v>-0.0525</v>
+        <v>-0.0585</v>
       </c>
       <c r="F334" s="5" t="n">
-        <v>0.014</v>
+        <v>0.0076</v>
       </c>
       <c r="G334" s="7" t="n"/>
       <c r="H334" s="12" t="inlineStr">
@@ -25266,7 +25266,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="5" t="n">
-        <v>0.1532873229204504</v>
+        <v>0.1606653262657649</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="9" t="n"/>
@@ -36351,7 +36351,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of July 31, 2026 at 17:01 UTC</t>
+          <t>Data as of July 31, 2026 at 21:45 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>97.45999999999999</v>
+        <v>98.14</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>-0.0205</v>
+        <v>-0.0137</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>-0.0189</v>
+        <v>-0.0121</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>46239</v>
@@ -878,7 +878,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="9" t="n">
-        <v>0.2825774676790479</v>
+        <v>0.2736906460158957</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="9" t="n">
-        <v>0.4775292427662632</v>
+        <v>0.4672916242103118</v>
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>374.61</v>
+        <v>373.51</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>0.0408</v>
+        <v>0.0378</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0035</v>
       </c>
       <c r="G3" s="17" t="n">
         <v>46322</v>
@@ -973,7 +973,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="16" t="n">
-        <v>0.1692159846240089</v>
+        <v>0.1726593665497577</v>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="16" t="n">
-        <v>0.1211660126531592</v>
+        <v>0.1244678857326444</v>
       </c>
       <c r="Q3" s="20" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>594.04</v>
+        <v>590.24</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>0.0191</v>
+        <v>0.0126</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-0.0534</v>
+        <v>-0.0595</v>
       </c>
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="12" t="inlineStr">
@@ -1054,7 +1054,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="9" t="n">
-        <v>0.4056292505555182</v>
+        <v>0.4146787747357007</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>0.5655511413372838</v>
+        <v>0.5756302521008403</v>
       </c>
       <c r="Q4" s="10" t="inlineStr">
         <is>
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>40.42</v>
+        <v>40.54</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>0.0664</v>
+        <v>0.0697</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>0.1627</v>
+        <v>0.1663</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>46238</v>
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>72.90000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-0.0611</v>
+        <v>-0.0556</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-0.1061</v>
+        <v>-0.1009</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>46315</v>
@@ -1210,7 +1210,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>0.09739368998628249</v>
+        <v>0.0909586799399973</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0.3717421124828531</v>
+        <v>0.3636983499249966</v>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
@@ -1262,13 +1262,13 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>79.45</v>
+        <v>79.27</v>
       </c>
       <c r="E7" s="16" t="n">
-        <v>0.0106</v>
+        <v>0.0083</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>0.0505</v>
+        <v>0.0481</v>
       </c>
       <c r="G7" s="17" t="n"/>
       <c r="H7" s="22" t="inlineStr">
@@ -1287,7 +1287,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>0.145374449339207</v>
+        <v>0.1479752743787058</v>
       </c>
       <c r="N7" s="14" t="inlineStr"/>
       <c r="O7" s="19" t="n"/>
@@ -1331,13 +1331,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>488.86</v>
+        <v>486.33</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>0.006</v>
+        <v>0.0007000000000000001</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0147</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>46238</v>
@@ -1366,7 +1366,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>0.1658347993290511</v>
+        <v>0.1718997388604445</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>0.3256146954138198</v>
+        <v>0.3325108465445273</v>
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>185.07</v>
+        <v>183.91</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>-0.0481</v>
+        <v>-0.0541</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.09179999999999999</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>46237</v>
@@ -1487,13 +1487,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>176.13</v>
+        <v>177.09</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-0.007800000000000001</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.0024</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>0.0004</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>46317</v>
@@ -1522,7 +1522,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>-0.03480383807414975</v>
+        <v>-0.04003613981591283</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>0.5329586101175269</v>
+        <v>0.5246484838217855</v>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>47.28</v>
+        <v>47.36</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>0.111</v>
+        <v>0.1128</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>0.0538</v>
+        <v>0.0555</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>46316</v>
@@ -1609,7 +1609,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="26" t="n">
-        <v>-0.09052453468697126</v>
+        <v>-0.0920608108108108</v>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>0.05752961082910319</v>
+        <v>0.05574324324324326</v>
       </c>
       <c r="Q11" s="20" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>151.4</v>
+        <v>150.64</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>0.0166</v>
+        <v>0.0115</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>0.1323</v>
+        <v>0.1265</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>46240</v>
@@ -1700,7 +1700,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>0.1955085865257595</v>
+        <v>0.2015400955921403</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>0.02377807133421396</v>
+        <v>0.02894317578332458</v>
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
@@ -1752,13 +1752,13 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>284.14</v>
+        <v>284.02</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>0.1709</v>
+        <v>0.1704</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>0.1196</v>
+        <v>0.1191</v>
       </c>
       <c r="G13" s="17" t="n"/>
       <c r="H13" s="22" t="inlineStr">
@@ -1777,7 +1777,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="16" t="n">
-        <v>0.1332441754064898</v>
+        <v>0.1337229772551229</v>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>0.003026676990216139</v>
+        <v>0.003450461235124351</v>
       </c>
       <c r="Q13" s="20" t="inlineStr">
         <is>
@@ -1841,13 +1841,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2998.11</v>
+        <v>2990.27</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>-0.051</v>
+        <v>-0.0535</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-0.0272</v>
+        <v>-0.0297</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>46287</v>
@@ -1876,7 +1876,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>0.3842053827244497</v>
+        <v>0.3878345433689934</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>0.234110823151919</v>
+        <v>0.2373464603530785</v>
       </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>84.02</v>
+        <v>85.25</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.07730000000000001</v>
+        <v>0.0931</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>0.1835</v>
+        <v>0.2009</v>
       </c>
       <c r="G15" s="17" t="n">
         <v>46261</v>
@@ -1963,7 +1963,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="26" t="n">
-        <v>-0.2263746726969769</v>
+        <v>-0.2375366568914956</v>
       </c>
       <c r="N15" s="14" t="inlineStr">
         <is>
@@ -1973,8 +1973,8 @@
       <c r="O15" s="19" t="n">
         <v>85</v>
       </c>
-      <c r="P15" s="16" t="n">
-        <v>0.01166388955010716</v>
+      <c r="P15" s="26" t="n">
+        <v>-0.002932551319648094</v>
       </c>
       <c r="Q15" s="20" t="inlineStr"/>
       <c r="R15" s="19" t="n"/>
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>193.24</v>
+        <v>192.71</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>0.047</v>
+        <v>0.0442</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.1537</v>
+        <v>0.1506</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>46238</v>
@@ -2044,7 +2044,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>0.1074311736700476</v>
+        <v>0.1104768823620984</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>0.2678534464914096</v>
+        <v>0.2713403559752996</v>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
@@ -2104,13 +2104,13 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>368.14</v>
+        <v>368.23</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.1755</v>
+        <v>0.1758</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>0.1434</v>
+        <v>0.1437</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>46261</v>
@@ -2139,7 +2139,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="16" t="n">
-        <v>0.01863421524420061</v>
+        <v>0.01838524835021585</v>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>0.01863421524420061</v>
+        <v>0.01838524835021585</v>
       </c>
       <c r="Q17" s="20" t="inlineStr"/>
       <c r="R17" s="19" t="n"/>
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>37.23</v>
+        <v>37.46</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0.052</v>
+        <v>0.0585</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>0.3211</v>
+        <v>0.3293</v>
       </c>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="12" t="inlineStr">
@@ -2214,7 +2214,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>0.2087026591458502</v>
+        <v>0.201281366791244</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>0.2087026591458502</v>
+        <v>0.201281366791244</v>
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
@@ -2266,13 +2266,13 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>145.04</v>
+        <v>146.66</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>-0.08529999999999999</v>
-      </c>
-      <c r="F19" s="26" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.0751</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>0.0017</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>46324</v>
@@ -2301,7 +2301,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="16" t="n">
-        <v>0.1720904578047436</v>
+        <v>0.1591435974362471</v>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.2203530060672919</v>
+        <v>0.206873039683622</v>
       </c>
       <c r="Q19" s="20" t="inlineStr">
         <is>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>198.33</v>
+        <v>200.82</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-0.1603</v>
+        <v>-0.1497</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.0886</v>
+        <v>-0.0771</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>46261</v>
@@ -2388,7 +2388,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>0.1092623405435385</v>
+        <v>0.09550841549646454</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="8" t="n"/>
@@ -2432,13 +2432,13 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>129.48</v>
+        <v>129.35</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>0.0437</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>0.1849</v>
+        <v>0.1838</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>46267</v>
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>87.59999999999999</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>0.1526</v>
+        <v>0.1537</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.0526</v>
+        <v>0.0536</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>46315</v>
@@ -2528,7 +2528,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>-0.3036529680365296</v>
+        <v>-0.3042883211678833</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>0.1415525114155252</v>
+        <v>0.1405109489051094</v>
       </c>
       <c r="Q22" s="10" t="inlineStr">
         <is>
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>127.48</v>
+        <v>128.52</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>-0.0384</v>
+        <v>-0.0305</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>0.2925</v>
+        <v>0.3031</v>
       </c>
       <c r="G23" s="17" t="n">
         <v>46315</v>
@@ -2618,7 +2618,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>0.1374333228741763</v>
+        <v>0.1282290694055399</v>
       </c>
       <c r="Q23" s="20" t="inlineStr"/>
       <c r="R23" s="19" t="n"/>
@@ -2653,13 +2653,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>336.11</v>
+        <v>340.02</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-0.0609</v>
+        <v>-0.05</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0.08439999999999999</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>46252</v>
@@ -2688,7 +2688,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>0.07107792091874679</v>
+        <v>0.05876124933827428</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="9" t="n">
-        <v>0.1900865787986075</v>
+        <v>0.1764013881536381</v>
       </c>
       <c r="Q24" s="10" t="inlineStr">
         <is>
@@ -2748,13 +2748,13 @@
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>209.1</v>
+        <v>212.06</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>-0.0809</v>
+        <v>-0.0679</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>0.0076</v>
+        <v>0.0218</v>
       </c>
       <c r="G25" s="17" t="n">
         <v>46253</v>
@@ -2783,7 +2783,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="16" t="n">
-        <v>0.2195121951219512</v>
+        <v>0.2024898613599924</v>
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
@@ -2794,7 +2794,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>0.09995217599234819</v>
+        <v>0.0845986984815618</v>
       </c>
       <c r="Q25" s="20" t="inlineStr">
         <is>
@@ -2839,13 +2839,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>267.8</v>
+        <v>265.23</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>-0.0457</v>
+        <v>-0.0549</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.018</v>
+        <v>-0.0275</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>46238</v>
@@ -2874,7 +2874,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="9" t="n">
-        <v>0.1202389843166542</v>
+        <v>0.1310937676733401</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="9" t="n">
-        <v>0.3069454817027632</v>
+        <v>0.3196093956188967</v>
       </c>
       <c r="Q26" s="10" t="inlineStr">
         <is>
@@ -2926,13 +2926,13 @@
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>42.23</v>
+        <v>42.64</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>-0.04219999999999999</v>
+        <v>-0.0329</v>
       </c>
       <c r="F27" s="26" t="n">
-        <v>-0.0319</v>
+        <v>-0.0225</v>
       </c>
       <c r="G27" s="17" t="n">
         <v>46289</v>
@@ -2987,13 +2987,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>90.01000000000001</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.0054</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>0.0182</v>
+        <v>0.0154</v>
       </c>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="12" t="inlineStr">
@@ -3012,7 +3012,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="9" t="n">
-        <v>0.2220864348405732</v>
+        <v>0.2254901960784313</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0.2776358182424175</v>
+        <v>0.2811942959001782</v>
       </c>
       <c r="Q28" s="10" t="inlineStr">
         <is>
@@ -3068,13 +3068,13 @@
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>191.27</v>
+        <v>195.58</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>-0.1285</v>
+        <v>-0.1089</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>0.04389999999999999</v>
+        <v>0.0675</v>
       </c>
       <c r="G29" s="17" t="n">
         <v>46317</v>
@@ -3129,13 +3129,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>252.06</v>
+        <v>252.91</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>0.181</v>
+        <v>0.185</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>0.0815</v>
+        <v>0.0852</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>46254</v>
@@ -3164,7 +3164,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>-0.02800920415774023</v>
+        <v>-0.03127594796567948</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="9" t="n">
-        <v>0.05133698325795445</v>
+        <v>0.04780356648610179</v>
       </c>
       <c r="Q30" s="10" t="inlineStr">
         <is>
@@ -3216,13 +3216,13 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>104.46</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>0.0018</v>
+        <v>103.37</v>
+      </c>
+      <c r="E31" s="26" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F31" s="16" t="n">
-        <v>0.1096</v>
+        <v>0.098</v>
       </c>
       <c r="G31" s="17" t="n"/>
       <c r="H31" s="22" t="inlineStr">
@@ -3241,7 +3241,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="16" t="n">
-        <v>0.1487650775416428</v>
+        <v>0.1608783979878107</v>
       </c>
       <c r="N31" s="14" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>0.1008998659774077</v>
+        <v>0.1125084647383186</v>
       </c>
       <c r="Q31" s="20" t="inlineStr">
         <is>
@@ -3293,13 +3293,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>12.27</v>
+        <v>12.34</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>-0.1826</v>
+        <v>-0.1779</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-0.1378</v>
+        <v>-0.1328</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>46237</v>
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>155.85</v>
+        <v>157.5</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>0.0103</v>
+        <v>0.021</v>
       </c>
       <c r="F33" s="26" t="n">
-        <v>-0.0175</v>
+        <v>-0.0071</v>
       </c>
       <c r="G33" s="17" t="n">
         <v>46253</v>
@@ -3389,7 +3389,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="16" t="n">
-        <v>0.02662816811036257</v>
+        <v>0.01587301587301587</v>
       </c>
       <c r="N33" s="14" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>0.1228745588707091</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="Q33" s="20" t="inlineStr">
         <is>
@@ -3445,13 +3445,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>31.8</v>
+        <v>32.11</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>0.0011</v>
+        <v>0.011</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>0.08259999999999999</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>46317</v>
@@ -3480,7 +3480,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="9" t="n">
-        <v>0.10062893081761</v>
+        <v>0.09000311429461229</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="9" t="n">
-        <v>0.2578616352201258</v>
+        <v>0.2457178449081283</v>
       </c>
       <c r="Q34" s="10" t="inlineStr">
         <is>
@@ -3532,13 +3532,13 @@
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>322</v>
+        <v>322.08</v>
       </c>
       <c r="E35" s="26" t="n">
-        <v>-0.1816</v>
+        <v>-0.1814</v>
       </c>
       <c r="F35" s="26" t="n">
-        <v>-0.2305</v>
+        <v>-0.2303</v>
       </c>
       <c r="G35" s="17" t="n">
         <v>46323</v>
@@ -3567,7 +3567,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="26" t="n">
-        <v>-0.5962732919254659</v>
+        <v>-0.5963735717834078</v>
       </c>
       <c r="N35" s="14" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="26" t="n">
-        <v>-0.06832298136645963</v>
+        <v>-0.06855439642324884</v>
       </c>
       <c r="Q35" s="20" t="inlineStr">
         <is>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>71.34999999999999</v>
+        <v>71.61</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>-0.0414</v>
+        <v>-0.0379</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-0.0119</v>
+        <v>-0.0083</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>46239</v>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="D37" s="15" t="n">
-        <v>525.13</v>
+        <v>534.41</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>0.1383</v>
+        <v>0.1584</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>0.1354</v>
+        <v>0.1554</v>
       </c>
       <c r="G37" s="17" t="n">
         <v>46261</v>
@@ -3715,7 +3715,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="26" t="n">
-        <v>-0.1430693352122332</v>
+        <v>-0.157949888662263</v>
       </c>
       <c r="N37" s="14" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>0.2092243825338488</v>
+        <v>0.1882262682210289</v>
       </c>
       <c r="Q37" s="20" t="inlineStr">
         <is>
@@ -3771,13 +3771,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>99.7</v>
+        <v>100.01</v>
       </c>
       <c r="E38" s="9" t="n">
-        <v>0.0112</v>
+        <v>0.0143</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>0.0593</v>
+        <v>0.0626</v>
       </c>
       <c r="G38" s="6" t="n"/>
       <c r="H38" s="12" t="inlineStr">
@@ -3796,7 +3796,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="9" t="n">
-        <v>0.1033099297893681</v>
+        <v>0.09989001099890005</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="9" t="n">
-        <v>0.05315947843530588</v>
+        <v>0.04989501049895005</v>
       </c>
       <c r="Q38" s="10" t="inlineStr">
         <is>
@@ -3852,13 +3852,13 @@
         </is>
       </c>
       <c r="D39" s="15" t="n">
-        <v>90.58</v>
+        <v>89.88</v>
       </c>
       <c r="E39" s="26" t="n">
-        <v>-0.0478</v>
+        <v>-0.0552</v>
       </c>
       <c r="F39" s="16" t="n">
-        <v>0.0644</v>
+        <v>0.0562</v>
       </c>
       <c r="G39" s="17" t="n"/>
       <c r="H39" s="22" t="inlineStr">
@@ -3877,7 +3877,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="16" t="n">
-        <v>0.04879664385073969</v>
+        <v>0.05696484201157104</v>
       </c>
       <c r="N39" s="14" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.1039964672113049</v>
+        <v>0.1125945705384958</v>
       </c>
       <c r="Q39" s="20" t="inlineStr">
         <is>
@@ -3933,13 +3933,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>951.6799999999999</v>
+        <v>954.08</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-0.0213</v>
+        <v>-0.0188</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>46289</v>
@@ -3968,7 +3968,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="9" t="n">
-        <v>0.05077336919973106</v>
+        <v>0.04813013583766556</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="9" t="n">
-        <v>0.1558507061197042</v>
+        <v>0.1529431494214321</v>
       </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
@@ -4028,13 +4028,13 @@
         </is>
       </c>
       <c r="D41" s="15" t="n">
-        <v>127.61</v>
+        <v>127.72</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>0.0799</v>
+        <v>0.0808</v>
       </c>
       <c r="F41" s="16" t="n">
-        <v>0.2328</v>
+        <v>0.2338</v>
       </c>
       <c r="G41" s="17" t="n">
         <v>46261</v>
@@ -4063,7 +4063,7 @@
         <v>125</v>
       </c>
       <c r="M41" s="26" t="n">
-        <v>-0.02045294255936055</v>
+        <v>-0.02129658628249294</v>
       </c>
       <c r="N41" s="14" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>0.05791082203589061</v>
+        <v>0.05699968681490762</v>
       </c>
       <c r="Q41" s="20" t="inlineStr">
         <is>
@@ -4115,13 +4115,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>26.2</v>
+        <v>26.42</v>
       </c>
       <c r="E42" s="9" t="n">
-        <v>0.0327</v>
+        <v>0.0414</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>0.166</v>
+        <v>0.1758</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>46239</v>
@@ -4182,7 +4182,7 @@
         <v>0.0323</v>
       </c>
       <c r="F43" s="16" t="n">
-        <v>0.1306</v>
+        <v>0.1307</v>
       </c>
       <c r="G43" s="17" t="n"/>
       <c r="H43" s="22" t="inlineStr">
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>58.07</v>
-      </c>
-      <c r="E44" s="5" t="n">
-        <v>-0.0026</v>
+        <v>58.22</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>-0.067</v>
+        <v>-0.0646</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>46275</v>
@@ -4296,7 +4296,7 @@
         <v>58</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>-0.001205441708283111</v>
+        <v>-0.003778770182067999</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="9" t="n">
-        <v>0.3432064749440331</v>
+        <v>0.3397457918241155</v>
       </c>
       <c r="Q44" s="10" t="inlineStr">
         <is>
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="D45" s="15" t="n">
-        <v>61.57</v>
+        <v>61.73</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>0.0108</v>
+        <v>0.0135</v>
       </c>
       <c r="F45" s="16" t="n">
-        <v>0.0095</v>
+        <v>0.0121</v>
       </c>
       <c r="G45" s="17" t="n"/>
       <c r="H45" s="22" t="inlineStr">
@@ -4373,7 +4373,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="16" t="n">
-        <v>0.1369173298684424</v>
+        <v>0.1339705167665641</v>
       </c>
       <c r="N45" s="14" t="inlineStr">
         <is>
@@ -4384,7 +4384,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.1531590060094202</v>
+        <v>0.150170095577515</v>
       </c>
       <c r="Q45" s="20" t="inlineStr">
         <is>
@@ -4433,13 +4433,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>51.51</v>
+        <v>51.52</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>-0.0363</v>
+        <v>-0.0361</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>0.1049</v>
+        <v>0.1051</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>46301</v>
@@ -4504,13 +4504,13 @@
         </is>
       </c>
       <c r="D47" s="15" t="n">
-        <v>92.84</v>
+        <v>93.55</v>
       </c>
       <c r="E47" s="26" t="n">
-        <v>-0.0488</v>
+        <v>-0.0415</v>
       </c>
       <c r="F47" s="16" t="n">
-        <v>0.0486</v>
+        <v>0.0566</v>
       </c>
       <c r="G47" s="17" t="n">
         <v>46240</v>
@@ -4565,13 +4565,13 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>67.89</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.0612</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>-0.0383</v>
+        <v>-0.0331</v>
       </c>
       <c r="G48" s="6" t="n"/>
       <c r="H48" s="12" t="inlineStr">
@@ -4616,13 +4616,13 @@
         </is>
       </c>
       <c r="D49" s="15" t="n">
-        <v>138.94</v>
+        <v>139.63</v>
       </c>
       <c r="E49" s="26" t="n">
-        <v>-0.0366</v>
+        <v>-0.0318</v>
       </c>
       <c r="F49" s="26" t="n">
-        <v>-0.0226</v>
+        <v>-0.0177</v>
       </c>
       <c r="G49" s="17" t="n">
         <v>46303</v>
@@ -4651,7 +4651,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="16" t="n">
-        <v>0.007629192457175775</v>
+        <v>0.002649860345198056</v>
       </c>
       <c r="N49" s="14" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>0.0796027062041169</v>
+        <v>0.07426770751271221</v>
       </c>
       <c r="Q49" s="20" t="inlineStr">
         <is>
@@ -4711,13 +4711,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>144.32</v>
+        <v>144.97</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>-0.04679999999999999</v>
+        <v>-0.0425</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>0.0251</v>
+        <v>0.0298</v>
       </c>
       <c r="G50" s="6" t="n"/>
       <c r="H50" s="12" t="inlineStr">
@@ -4736,7 +4736,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="9" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1312685383182728</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="9" t="n">
-        <v>0.1225055432372506</v>
+        <v>0.1174725805339036</v>
       </c>
       <c r="Q50" s="10" t="inlineStr">
         <is>
@@ -4800,13 +4800,13 @@
         </is>
       </c>
       <c r="D51" s="15" t="n">
-        <v>82.19</v>
-      </c>
-      <c r="E51" s="26" t="n">
-        <v>-0.0311</v>
+        <v>84.98</v>
+      </c>
+      <c r="E51" s="16" t="n">
+        <v>0.0018</v>
       </c>
       <c r="F51" s="16" t="n">
-        <v>0.1054</v>
+        <v>0.143</v>
       </c>
       <c r="G51" s="17" t="n">
         <v>46238</v>
@@ -4835,7 +4835,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="16" t="n">
-        <v>0.2166930283489476</v>
+        <v>0.1767474699929395</v>
       </c>
       <c r="N51" s="14" t="inlineStr"/>
       <c r="O51" s="19" t="n"/>
@@ -4879,13 +4879,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>149.45</v>
+        <v>149.35</v>
       </c>
       <c r="E52" s="9" t="n">
-        <v>0.1478</v>
+        <v>0.147</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>0.2067</v>
+        <v>0.2059</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>46253</v>
@@ -4914,7 +4914,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>-0.06323185011709595</v>
+        <v>-0.06260462002008702</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="5" t="n">
-        <v>-0.0966878554700568</v>
+        <v>-0.09608302644794105</v>
       </c>
       <c r="Q52" s="10" t="inlineStr">
         <is>
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="D53" s="15" t="n">
-        <v>110.51</v>
+        <v>110.71</v>
       </c>
       <c r="E53" s="26" t="n">
-        <v>-0.0119</v>
+        <v>-0.0101</v>
       </c>
       <c r="F53" s="26" t="n">
-        <v>-0.0614</v>
+        <v>-0.0597</v>
       </c>
       <c r="G53" s="17" t="n">
         <v>46254</v>
@@ -5005,7 +5005,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="16" t="n">
-        <v>0.2668536784001447</v>
+        <v>0.2645650799385784</v>
       </c>
       <c r="N53" s="14" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>0.2668536784001447</v>
+        <v>0.2645650799385784</v>
       </c>
       <c r="Q53" s="20" t="inlineStr">
         <is>
@@ -5065,13 +5065,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>60.49</v>
+        <v>60.81</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>0.1462</v>
+        <v>0.1521</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>-0.0849</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="G54" s="6" t="n">
         <v>46316</v>
@@ -5107,7 +5107,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="9" t="n">
-        <v>0.2564060175235576</v>
+        <v>0.2497944417036671</v>
       </c>
       <c r="Q54" s="10" t="inlineStr">
         <is>
@@ -5148,13 +5148,13 @@
         </is>
       </c>
       <c r="D55" s="15" t="n">
-        <v>118.99</v>
+        <v>119.16</v>
       </c>
       <c r="E55" s="16" t="n">
-        <v>0.1362</v>
+        <v>0.1378</v>
       </c>
       <c r="F55" s="26" t="n">
-        <v>-0.002</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="G55" s="17" t="n">
         <v>46240</v>
@@ -5183,7 +5183,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="16" t="n">
-        <v>0.5379443650726953</v>
+        <v>0.5357502517623364</v>
       </c>
       <c r="N55" s="14" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>0.2185897974619717</v>
+        <v>0.2168512923799933</v>
       </c>
       <c r="Q55" s="20" t="inlineStr">
         <is>
@@ -5235,13 +5235,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>194.28</v>
+        <v>193.18</v>
       </c>
       <c r="E56" s="9" t="n">
-        <v>0.1482</v>
+        <v>0.1417</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>0.0315</v>
+        <v>0.0256</v>
       </c>
       <c r="G56" s="6" t="n"/>
       <c r="H56" s="12" t="inlineStr">
@@ -5260,7 +5260,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="9" t="n">
-        <v>0.1426806670784435</v>
+        <v>0.1491872864685785</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="9" t="n">
-        <v>0.1581222977146386</v>
+        <v>0.1647168443938296</v>
       </c>
       <c r="Q56" s="10" t="inlineStr">
         <is>
@@ -5316,13 +5316,13 @@
         </is>
       </c>
       <c r="D57" s="15" t="n">
-        <v>146.12</v>
+        <v>145.68</v>
       </c>
       <c r="E57" s="16" t="n">
-        <v>0.1173</v>
+        <v>0.1139</v>
       </c>
       <c r="F57" s="16" t="n">
-        <v>0.0372</v>
+        <v>0.0341</v>
       </c>
       <c r="G57" s="17" t="n">
         <v>46238</v>
@@ -5351,7 +5351,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="16" t="n">
-        <v>0.3413632630714481</v>
+        <v>0.3454146073585941</v>
       </c>
       <c r="N57" s="14" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>0.1634273200109499</v>
+        <v>0.1669412410763316</v>
       </c>
       <c r="Q57" s="20" t="inlineStr">
         <is>
@@ -5407,13 +5407,13 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>37.6</v>
+        <v>37.87</v>
       </c>
       <c r="E58" s="9" t="n">
-        <v>0.0231</v>
+        <v>0.0305</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>-0.0152</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="G58" s="6" t="n"/>
       <c r="H58" s="12" t="inlineStr">
@@ -5458,13 +5458,13 @@
         </is>
       </c>
       <c r="D59" s="15" t="n">
-        <v>20.25</v>
+        <v>20.28</v>
       </c>
       <c r="E59" s="16" t="n">
-        <v>0.0476</v>
+        <v>0.0491</v>
       </c>
       <c r="F59" s="16" t="n">
-        <v>0.0321</v>
+        <v>0.0336</v>
       </c>
       <c r="G59" s="17" t="n">
         <v>46238</v>
@@ -5519,13 +5519,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>198.98</v>
+        <v>198.75</v>
       </c>
       <c r="E60" s="9" t="n">
-        <v>0.1566</v>
+        <v>0.1553</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-0.0195</v>
+        <v>-0.0206</v>
       </c>
       <c r="G60" s="6" t="n">
         <v>46237</v>
@@ -5580,13 +5580,13 @@
         </is>
       </c>
       <c r="D61" s="15" t="n">
-        <v>31.86</v>
+        <v>31.89</v>
       </c>
       <c r="E61" s="26" t="n">
-        <v>-0.0332</v>
+        <v>-0.0325</v>
       </c>
       <c r="F61" s="26" t="n">
-        <v>-0.227</v>
+        <v>-0.2263</v>
       </c>
       <c r="G61" s="17" t="n">
         <v>46315</v>
@@ -5622,7 +5622,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.349654739485248</v>
+        <v>0.3483850736908121</v>
       </c>
       <c r="Q61" s="20" t="inlineStr">
         <is>
@@ -5670,10 +5670,10 @@
         <v>31.4</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>-0.0205</v>
+        <v>-0.0206</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.0095</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>46316</v>
@@ -5746,13 +5746,13 @@
         </is>
       </c>
       <c r="D63" s="15" t="n">
-        <v>208.6</v>
+        <v>206.19</v>
       </c>
       <c r="E63" s="16" t="n">
-        <v>0.1824</v>
+        <v>0.1687</v>
       </c>
       <c r="F63" s="16" t="n">
-        <v>0.1328</v>
+        <v>0.1197</v>
       </c>
       <c r="G63" s="17" t="n">
         <v>46239</v>
@@ -5807,13 +5807,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>49.15</v>
+        <v>49.31</v>
       </c>
       <c r="E64" s="9" t="n">
-        <v>0.0891</v>
+        <v>0.0926</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>-0.1527</v>
+        <v>-0.15</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>46311</v>
@@ -5849,7 +5849,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="9" t="n">
-        <v>0.2817904374364192</v>
+        <v>0.2776313121070776</v>
       </c>
       <c r="Q64" s="10" t="inlineStr">
         <is>
@@ -5898,13 +5898,13 @@
         </is>
       </c>
       <c r="D65" s="15" t="n">
-        <v>43.6</v>
+        <v>43.69</v>
       </c>
       <c r="E65" s="16" t="n">
-        <v>0.0701</v>
+        <v>0.0721</v>
       </c>
       <c r="F65" s="26" t="n">
-        <v>-0.0596</v>
+        <v>-0.0578</v>
       </c>
       <c r="G65" s="17" t="n">
         <v>46237</v>
@@ -5959,13 +5959,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>70.41</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>-0.0373</v>
+        <v>-0.0371</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0276</v>
       </c>
       <c r="G66" s="6" t="n">
         <v>46237</v>
@@ -5994,7 +5994,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="9" t="n">
-        <v>0.2640249964493681</v>
+        <v>0.2636660513985516</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="8" t="n"/>
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="D67" s="15" t="n">
-        <v>155.07</v>
+        <v>155.06</v>
       </c>
       <c r="E67" s="16" t="n">
         <v>0.1311</v>
@@ -6075,7 +6075,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="16" t="n">
-        <v>0.1930096085638744</v>
+        <v>0.1930865471430414</v>
       </c>
       <c r="N67" s="14" t="inlineStr">
         <is>
@@ -6086,7 +6086,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>0.1930096085638744</v>
+        <v>0.1930865471430414</v>
       </c>
       <c r="Q67" s="20" t="inlineStr">
         <is>
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>126.83</v>
+        <v>126.71</v>
       </c>
       <c r="E68" s="9" t="n">
-        <v>0.0492</v>
+        <v>0.0482</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>0.1001</v>
+        <v>0.09910000000000001</v>
       </c>
       <c r="G68" s="6" t="n">
         <v>46240</v>
@@ -6166,7 +6166,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>-0.05385161239454386</v>
+        <v>-0.0529555678320574</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>115</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>-0.09327446187810454</v>
+        <v>-0.09241575250572168</v>
       </c>
       <c r="Q68" s="10" t="inlineStr"/>
       <c r="R68" s="8" t="n"/>
@@ -6212,13 +6212,13 @@
         </is>
       </c>
       <c r="D69" s="15" t="n">
-        <v>356.96</v>
-      </c>
-      <c r="E69" s="26" t="n">
-        <v>-0.0014</v>
+        <v>357.63</v>
+      </c>
+      <c r="E69" s="16" t="n">
+        <v>0.0005</v>
       </c>
       <c r="F69" s="16" t="n">
-        <v>0.1077</v>
+        <v>0.1098</v>
       </c>
       <c r="G69" s="17" t="n"/>
       <c r="H69" s="22" t="inlineStr">
@@ -6237,7 +6237,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="16" t="n">
-        <v>0.1373823397579561</v>
+        <v>0.1352515169309063</v>
       </c>
       <c r="N69" s="14" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>0.2214253697893322</v>
+        <v>0.2191370969996924</v>
       </c>
       <c r="Q69" s="20" t="inlineStr">
         <is>
@@ -6285,13 +6285,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>342.94</v>
+        <v>344.72</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>-0.0256</v>
+        <v>-0.0206</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>0.0973</v>
+        <v>0.103</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>46311</v>
@@ -6320,7 +6320,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="9" t="n">
-        <v>0.2101242199801715</v>
+        <v>0.2038756091900672</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="9" t="n">
-        <v>0.1080655508252173</v>
+        <v>0.1023439313065676</v>
       </c>
       <c r="Q70" s="10" t="inlineStr">
         <is>
@@ -6380,13 +6380,13 @@
         </is>
       </c>
       <c r="D71" s="15" t="n">
-        <v>61.85</v>
+        <v>62.48</v>
       </c>
       <c r="E71" s="16" t="n">
-        <v>0.053</v>
+        <v>0.0639</v>
       </c>
       <c r="F71" s="16" t="n">
-        <v>0.1417</v>
+        <v>0.1534</v>
       </c>
       <c r="G71" s="17" t="n">
         <v>46309</v>
@@ -6441,13 +6441,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1109.18</v>
+        <v>1126.63</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>0.1139</v>
+        <v>0.1315</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>0.08470000000000001</v>
+        <v>0.1018</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>46308</v>
@@ -6479,7 +6479,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="9" t="n">
-        <v>0.1224508195243332</v>
+        <v>0.1050655494705448</v>
       </c>
       <c r="Q72" s="10" t="inlineStr">
         <is>
@@ -6524,13 +6524,13 @@
         </is>
       </c>
       <c r="D73" s="15" t="n">
-        <v>23.1</v>
+        <v>22.93</v>
       </c>
       <c r="E73" s="26" t="n">
-        <v>-0.0965</v>
+        <v>-0.1032</v>
       </c>
       <c r="F73" s="26" t="n">
-        <v>-0.2211</v>
+        <v>-0.2269</v>
       </c>
       <c r="G73" s="17" t="n">
         <v>46247</v>
@@ -6585,13 +6585,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>17.33</v>
+        <v>17.42</v>
       </c>
       <c r="E74" s="9" t="n">
-        <v>0.2065</v>
+        <v>0.2131</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>-0.0316</v>
+        <v>-0.0263</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>46346</v>
@@ -6646,13 +6646,13 @@
         </is>
       </c>
       <c r="D75" s="15" t="n">
-        <v>511.65</v>
+        <v>513.14</v>
       </c>
       <c r="E75" s="16" t="n">
-        <v>0.0076</v>
+        <v>0.0106</v>
       </c>
       <c r="F75" s="16" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0721</v>
       </c>
       <c r="G75" s="17" t="n">
         <v>46241</v>
@@ -6729,13 +6729,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>71.64</v>
+        <v>71.78</v>
       </c>
       <c r="E76" s="9" t="n">
-        <v>0.0235</v>
+        <v>0.0254</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>0.2486</v>
+        <v>0.251</v>
       </c>
       <c r="G76" s="6" t="n"/>
       <c r="H76" s="12" t="inlineStr">
@@ -6754,7 +6754,7 @@
         <v>68</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>-0.05080960357342268</v>
+        <v>-0.05266090833101144</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="8" t="n"/>
@@ -6796,13 +6796,13 @@
         </is>
       </c>
       <c r="D77" s="15" t="n">
-        <v>131.66</v>
+        <v>134.68</v>
       </c>
       <c r="E77" s="16" t="n">
-        <v>0.0723</v>
+        <v>0.0969</v>
       </c>
       <c r="F77" s="16" t="n">
-        <v>0.1106</v>
+        <v>0.1361</v>
       </c>
       <c r="G77" s="17" t="n">
         <v>46310</v>
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>131.66</v>
+        <v>133.57</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>-0.0593</v>
+        <v>-0.0457</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>-0.0258</v>
+        <v>-0.0117</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>46308</v>
@@ -6899,7 +6899,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="9" t="n">
-        <v>0.06334497949263257</v>
+        <v>0.048139552294677</v>
       </c>
       <c r="Q78" s="10" t="inlineStr">
         <is>
@@ -6948,13 +6948,13 @@
         </is>
       </c>
       <c r="D79" s="15" t="n">
-        <v>346.98</v>
+        <v>348.23</v>
       </c>
       <c r="E79" s="26" t="n">
-        <v>-0.0393</v>
+        <v>-0.0358</v>
       </c>
       <c r="F79" s="16" t="n">
-        <v>0.1033</v>
+        <v>0.1072</v>
       </c>
       <c r="G79" s="17" t="n">
         <v>46315</v>
@@ -6983,7 +6983,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="16" t="n">
-        <v>0.03175975560551035</v>
+        <v>0.02805616977285122</v>
       </c>
       <c r="N79" s="14" t="inlineStr">
         <is>
@@ -6994,7 +6994,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>0.07787192345380131</v>
+        <v>0.07400281423197307</v>
       </c>
       <c r="Q79" s="20" t="inlineStr">
         <is>
@@ -7039,13 +7039,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>59.45</v>
+        <v>59.67</v>
       </c>
       <c r="E80" s="9" t="n">
-        <v>0.0245</v>
+        <v>0.0283</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>0.1335</v>
+        <v>0.1377</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>46310</v>
@@ -7074,7 +7074,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>-0.04121110176619012</v>
+        <v>-0.04474610356963301</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="8" t="n"/>
@@ -7116,13 +7116,13 @@
         </is>
       </c>
       <c r="D81" s="15" t="n">
-        <v>14.52</v>
+        <v>14.65</v>
       </c>
       <c r="E81" s="16" t="n">
-        <v>0.1502</v>
+        <v>0.1609</v>
       </c>
       <c r="F81" s="26" t="n">
-        <v>-0.135</v>
+        <v>-0.1269</v>
       </c>
       <c r="G81" s="17" t="n">
         <v>46240</v>
@@ -7177,13 +7177,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>384.06</v>
+        <v>385.78</v>
       </c>
       <c r="E82" s="9" t="n">
-        <v>0.0897</v>
+        <v>0.09449999999999999</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0801</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>46239</v>
@@ -7250,13 +7250,13 @@
         </is>
       </c>
       <c r="D83" s="15" t="n">
-        <v>60.57</v>
+        <v>60.35</v>
       </c>
       <c r="E83" s="26" t="n">
-        <v>-0.06269999999999999</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="F83" s="26" t="n">
-        <v>-0.331</v>
+        <v>-0.3334</v>
       </c>
       <c r="G83" s="17" t="n">
         <v>46239</v>
@@ -7311,13 +7311,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>54.69</v>
+        <v>54.28</v>
       </c>
       <c r="E84" s="9" t="n">
-        <v>0.06509999999999999</v>
+        <v>0.0571</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>0.3921</v>
+        <v>0.3815</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>46240</v>
@@ -7372,13 +7372,13 @@
         </is>
       </c>
       <c r="D85" s="15" t="n">
-        <v>1011.38</v>
-      </c>
-      <c r="E85" s="26" t="n">
-        <v>-0.009399999999999999</v>
+        <v>1027.06</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>0.0059</v>
       </c>
       <c r="F85" s="26" t="n">
-        <v>-0.07429999999999999</v>
+        <v>-0.06</v>
       </c>
       <c r="G85" s="17" t="n">
         <v>46308</v>
@@ -7407,7 +7407,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="16" t="n">
-        <v>0.3100911625699539</v>
+        <v>0.2900901602632758</v>
       </c>
       <c r="N85" s="14" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="16" t="n">
-        <v>0.1963851371393542</v>
+        <v>0.1781200708819349</v>
       </c>
       <c r="Q85" s="20" t="inlineStr">
         <is>
@@ -7459,13 +7459,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>122.78</v>
+        <v>125.48</v>
       </c>
       <c r="E86" s="5" t="n">
-        <v>-0.1239</v>
+        <v>-0.1047</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-0.1305</v>
+        <v>-0.1113</v>
       </c>
       <c r="G86" s="6" t="n"/>
       <c r="H86" s="12" t="inlineStr">
@@ -7510,13 +7510,13 @@
         </is>
       </c>
       <c r="D87" s="15" t="n">
-        <v>91.59999999999999</v>
+        <v>90.34</v>
       </c>
       <c r="E87" s="26" t="n">
-        <v>-0.1874</v>
+        <v>-0.1986</v>
       </c>
       <c r="F87" s="16" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.0228</v>
       </c>
       <c r="G87" s="17" t="n"/>
       <c r="H87" s="22" t="inlineStr">
@@ -7561,13 +7561,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>110.64</v>
+        <v>112.08</v>
       </c>
       <c r="E88" s="9" t="n">
-        <v>0.139</v>
+        <v>0.1538</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.134</v>
+        <v>-0.1227</v>
       </c>
       <c r="G88" s="6" t="n">
         <v>46238</v>
@@ -7622,13 +7622,13 @@
         </is>
       </c>
       <c r="D89" s="15" t="n">
-        <v>151.4</v>
+        <v>151.8</v>
       </c>
       <c r="E89" s="16" t="n">
-        <v>0.1385</v>
+        <v>0.1414</v>
       </c>
       <c r="F89" s="16" t="n">
-        <v>0.0658</v>
+        <v>0.06860000000000001</v>
       </c>
       <c r="G89" s="17" t="n"/>
       <c r="H89" s="22" t="inlineStr">
@@ -7673,13 +7673,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>156.52</v>
+        <v>156.53</v>
       </c>
       <c r="E90" s="9" t="n">
-        <v>0.06570000000000001</v>
+        <v>0.0658</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>0.1973</v>
+        <v>0.1974</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>46252</v>
@@ -7748,13 +7748,13 @@
         </is>
       </c>
       <c r="D91" s="15" t="n">
-        <v>351.41</v>
+        <v>352.64</v>
       </c>
       <c r="E91" s="16" t="n">
-        <v>0.0506</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="F91" s="16" t="n">
-        <v>0.1303</v>
+        <v>0.1343</v>
       </c>
       <c r="G91" s="17" t="n">
         <v>46308</v>
@@ -7783,7 +7783,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="26" t="n">
-        <v>-0.4422469480094477</v>
+        <v>-0.4441923774954628</v>
       </c>
       <c r="N91" s="14" t="inlineStr"/>
       <c r="O91" s="19" t="n"/>
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>104.75</v>
+        <v>106.56</v>
       </c>
       <c r="E92" s="9" t="n">
-        <v>0.1162</v>
+        <v>0.1355</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>0.0973</v>
+        <v>0.1163</v>
       </c>
       <c r="G92" s="6" t="n"/>
       <c r="H92" s="12" t="inlineStr">
@@ -7852,7 +7852,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="9" t="n">
-        <v>2.579952267303103</v>
+        <v>2.519144144144144</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="9" t="n">
-        <v>2.513126491646778</v>
+        <v>2.453453453453454</v>
       </c>
       <c r="Q92" s="10" t="inlineStr">
         <is>
@@ -7916,13 +7916,13 @@
         </is>
       </c>
       <c r="D93" s="15" t="n">
-        <v>359.61</v>
+        <v>360.44</v>
       </c>
       <c r="E93" s="16" t="n">
-        <v>0.0134</v>
+        <v>0.0158</v>
       </c>
       <c r="F93" s="16" t="n">
-        <v>0.2161</v>
+        <v>0.2189</v>
       </c>
       <c r="G93" s="17" t="n">
         <v>46317</v>
@@ -7954,7 +7954,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="26" t="n">
-        <v>-0.6802091154306054</v>
+        <v>-0.6809455110420597</v>
       </c>
       <c r="Q93" s="20" t="inlineStr">
         <is>
@@ -8003,13 +8003,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>575.21</v>
+        <v>570.97</v>
       </c>
       <c r="E94" s="9" t="n">
-        <v>0.0664</v>
+        <v>0.0585</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>0.194</v>
+        <v>0.1852</v>
       </c>
       <c r="G94" s="6" t="n"/>
       <c r="H94" s="12" t="inlineStr">
@@ -8028,7 +8028,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>-0.3637106448079832</v>
+        <v>-0.358985585932711</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="8" t="n"/>
@@ -8070,13 +8070,13 @@
         </is>
       </c>
       <c r="D95" s="15" t="n">
-        <v>1864.99</v>
+        <v>1879.09</v>
       </c>
       <c r="E95" s="26" t="n">
-        <v>-0.0579</v>
+        <v>-0.0508</v>
       </c>
       <c r="F95" s="16" t="n">
-        <v>0.0487</v>
+        <v>0.0566</v>
       </c>
       <c r="G95" s="17" t="n"/>
       <c r="H95" s="22" t="inlineStr">
@@ -8131,13 +8131,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>209.08</v>
+        <v>211.23</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>-0.0227</v>
+        <v>-0.0126</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.0421</v>
+        <v>-0.0323</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>46309</v>
@@ -8166,7 +8166,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="9" t="n">
-        <v>2.194949301702697</v>
+        <v>2.162429579131752</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="9" t="n">
-        <v>1.630572029845035</v>
+        <v>1.603796809165365</v>
       </c>
       <c r="Q96" s="10" t="inlineStr">
         <is>
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="D97" s="15" t="n">
-        <v>114.85</v>
+        <v>115.13</v>
       </c>
       <c r="E97" s="16" t="n">
-        <v>0.0359</v>
+        <v>0.0384</v>
       </c>
       <c r="F97" s="16" t="n">
-        <v>0.1095</v>
+        <v>0.1123</v>
       </c>
       <c r="G97" s="17" t="n"/>
       <c r="H97" s="22" t="inlineStr">
@@ -8251,7 +8251,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="16" t="n">
-        <v>1.089682194166304</v>
+        <v>1.084600017371667</v>
       </c>
       <c r="N97" s="14" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="16" t="n">
-        <v>1.089682194166304</v>
+        <v>1.084600017371667</v>
       </c>
       <c r="Q97" s="20" t="inlineStr">
         <is>
@@ -8311,13 +8311,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>250.21</v>
+        <v>251.72</v>
       </c>
       <c r="E98" s="9" t="n">
-        <v>0.0029</v>
+        <v>0.0089</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>0.1019</v>
+        <v>0.1085</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>46310</v>
@@ -8346,7 +8346,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>-0.5483793613364774</v>
+        <v>-0.5510885110440171</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="5" t="n">
-        <v>-0.5443827185164462</v>
+        <v>-0.5471158430001589</v>
       </c>
       <c r="Q98" s="10" t="inlineStr"/>
       <c r="R98" s="8" t="n"/>
@@ -8396,13 +8396,13 @@
         </is>
       </c>
       <c r="D99" s="15" t="n">
-        <v>21.13</v>
+        <v>21.42</v>
       </c>
       <c r="E99" s="26" t="n">
-        <v>-0.0446</v>
+        <v>-0.0312</v>
       </c>
       <c r="F99" s="26" t="n">
-        <v>-0.231</v>
+        <v>-0.2202</v>
       </c>
       <c r="G99" s="17" t="n">
         <v>46239</v>
@@ -8457,13 +8457,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>14.34</v>
+        <v>14.45</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>0.028</v>
+        <v>0.0358</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>0.15</v>
+        <v>0.1588</v>
       </c>
       <c r="G100" s="6" t="n">
         <v>46323</v>
@@ -8518,13 +8518,13 @@
         </is>
       </c>
       <c r="D101" s="15" t="n">
-        <v>103.09</v>
+        <v>104.19</v>
       </c>
       <c r="E101" s="16" t="n">
-        <v>0.1275</v>
+        <v>0.1396</v>
       </c>
       <c r="F101" s="16" t="n">
-        <v>0.1638</v>
+        <v>0.1762</v>
       </c>
       <c r="G101" s="17" t="n">
         <v>46323</v>
@@ -8553,7 +8553,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="16" t="n">
-        <v>1.764574643515375</v>
+        <v>1.735387273250792</v>
       </c>
       <c r="N101" s="14" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="16" t="n">
-        <v>1.764574643515375</v>
+        <v>1.735387273250792</v>
       </c>
       <c r="Q101" s="20" t="inlineStr">
         <is>
@@ -8605,13 +8605,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>413.76</v>
+        <v>416.25</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>-0.0594</v>
+        <v>-0.0537</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.0473</v>
       </c>
       <c r="G102" s="6" t="n"/>
       <c r="H102" s="12" t="inlineStr">
@@ -8670,13 +8670,13 @@
         </is>
       </c>
       <c r="D103" s="15" t="n">
-        <v>51.38</v>
+        <v>51.92</v>
       </c>
       <c r="E103" s="16" t="n">
-        <v>0.0077</v>
+        <v>0.0184</v>
       </c>
       <c r="F103" s="16" t="n">
-        <v>0.0446</v>
+        <v>0.0557</v>
       </c>
       <c r="G103" s="17" t="n">
         <v>46311</v>
@@ -8731,13 +8731,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>365.62</v>
+        <v>365.67</v>
       </c>
       <c r="E104" s="9" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0098</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>0.1419</v>
+        <v>0.1421</v>
       </c>
       <c r="G104" s="6" t="n"/>
       <c r="H104" s="12" t="inlineStr">
@@ -8756,7 +8756,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="9" t="n">
-        <v>0.4359170723702204</v>
+        <v>0.4357207318073673</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="9" t="n">
-        <v>0.4851485148514851</v>
+        <v>0.4849454426121912</v>
       </c>
       <c r="Q104" s="10" t="inlineStr">
         <is>
@@ -8812,13 +8812,13 @@
         </is>
       </c>
       <c r="D105" s="15" t="n">
-        <v>71.92</v>
-      </c>
-      <c r="E105" s="26" t="n">
-        <v>-0.0022</v>
+        <v>72.09</v>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>0.0001</v>
       </c>
       <c r="F105" s="16" t="n">
-        <v>0.08460000000000001</v>
+        <v>0.0872</v>
       </c>
       <c r="G105" s="17" t="n">
         <v>46314</v>
@@ -8847,7 +8847,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="16" t="n">
-        <v>4.728587319243604</v>
+        <v>4.715078374254404</v>
       </c>
       <c r="N105" s="14" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="16" t="n">
-        <v>3.866518353726362</v>
+        <v>3.855042308225828</v>
       </c>
       <c r="Q105" s="20" t="inlineStr">
         <is>
@@ -8903,13 +8903,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>81.97</v>
+        <v>82.09</v>
       </c>
       <c r="E106" s="9" t="n">
-        <v>0.0399</v>
+        <v>0.0414</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>0.1564</v>
+        <v>0.158</v>
       </c>
       <c r="G106" s="6" t="n">
         <v>46239</v>
@@ -8938,7 +8938,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>-0.170428205441015</v>
+        <v>-0.1716408819588257</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="5" t="n">
-        <v>-0.170428205441015</v>
+        <v>-0.1716408819588257</v>
       </c>
       <c r="Q106" s="10" t="inlineStr">
         <is>
@@ -8994,13 +8994,13 @@
         </is>
       </c>
       <c r="D107" s="15" t="n">
-        <v>245.3</v>
+        <v>245.1</v>
       </c>
       <c r="E107" s="26" t="n">
-        <v>-0.0604</v>
+        <v>-0.0612</v>
       </c>
       <c r="F107" s="16" t="n">
-        <v>0.09050000000000001</v>
+        <v>0.08960000000000001</v>
       </c>
       <c r="G107" s="17" t="n"/>
       <c r="H107" s="22" t="inlineStr">
@@ -9019,7 +9019,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="16" t="n">
-        <v>0.2026090501426824</v>
+        <v>0.2035903712770298</v>
       </c>
       <c r="N107" s="14" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="16" t="n">
-        <v>0.002853648593558861</v>
+        <v>0.003671970624235029</v>
       </c>
       <c r="Q107" s="20" t="inlineStr">
         <is>
@@ -9067,13 +9067,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>106.9</v>
+        <v>107.12</v>
       </c>
       <c r="E108" s="9" t="n">
-        <v>0.1205</v>
+        <v>0.1229</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>0.1776</v>
+        <v>0.18</v>
       </c>
       <c r="G108" s="6" t="n">
         <v>46316</v>
@@ -9102,7 +9102,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="9" t="n">
-        <v>0.04770813844714681</v>
+        <v>0.04555638536221056</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="9" t="n">
-        <v>0.1225444340505144</v>
+        <v>0.1202389843166542</v>
       </c>
       <c r="Q108" s="10" t="inlineStr">
         <is>
@@ -9166,13 +9166,13 @@
         </is>
       </c>
       <c r="D109" s="15" t="n">
-        <v>377.48</v>
+        <v>378.87</v>
       </c>
       <c r="E109" s="16" t="n">
-        <v>0.0089</v>
+        <v>0.0126</v>
       </c>
       <c r="F109" s="16" t="n">
-        <v>0.0922</v>
+        <v>0.09630000000000001</v>
       </c>
       <c r="G109" s="17" t="n">
         <v>46238</v>
@@ -9201,7 +9201,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="16" t="n">
-        <v>0.03316732012292037</v>
+        <v>0.02937683110301685</v>
       </c>
       <c r="N109" s="14" t="inlineStr">
         <is>
@@ -9249,13 +9249,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>168.71</v>
+        <v>170.21</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>0.0672</v>
+        <v>0.0767</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>0.128</v>
+        <v>0.1381</v>
       </c>
       <c r="G110" s="6" t="n">
         <v>46240</v>
@@ -9284,7 +9284,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="5" t="n">
-        <v>-0.04569972141544667</v>
+        <v>-0.05410962928147587</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="9" t="n">
-        <v>0.0669195661193764</v>
+        <v>0.05751718465425058</v>
       </c>
       <c r="Q110" s="10" t="inlineStr">
         <is>
@@ -9413,13 +9413,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>309.82</v>
+        <v>308.37</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>0.0449</v>
+        <v>0.04</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>0.1461</v>
+        <v>0.1408</v>
       </c>
       <c r="G112" s="6" t="n">
         <v>46239</v>
@@ -9448,7 +9448,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="9" t="n">
-        <v>0.06836227486927896</v>
+        <v>0.0733858676265525</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="9" t="n">
-        <v>0.06513459428055002</v>
+        <v>0.07014301002042998</v>
       </c>
       <c r="Q112" s="10" t="inlineStr">
         <is>
@@ -9508,13 +9508,13 @@
         </is>
       </c>
       <c r="D113" s="15" t="n">
-        <v>105.04</v>
+        <v>105.37</v>
       </c>
       <c r="E113" s="16" t="n">
-        <v>0.0031</v>
+        <v>0.0062</v>
       </c>
       <c r="F113" s="16" t="n">
-        <v>0.1078</v>
+        <v>0.1113</v>
       </c>
       <c r="G113" s="17" t="n">
         <v>46239</v>
@@ -9543,7 +9543,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="16" t="n">
-        <v>0.1709824828636709</v>
+        <v>0.1673151750972762</v>
       </c>
       <c r="N113" s="14" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="16" t="n">
-        <v>0.2376237623762376</v>
+        <v>0.2337477460377716</v>
       </c>
       <c r="Q113" s="20" t="inlineStr">
         <is>
@@ -9595,13 +9595,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>197.75</v>
+        <v>197.5</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.0022</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>0.0595</v>
+        <v>0.0582</v>
       </c>
       <c r="G114" s="6" t="n">
         <v>46315</v>
@@ -9630,7 +9630,7 @@
         <v>212</v>
       </c>
       <c r="M114" s="9" t="n">
-        <v>0.07206068268015171</v>
+        <v>0.07341772151898734</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="9" t="n">
-        <v>0.03666245259165613</v>
+        <v>0.0379746835443038</v>
       </c>
       <c r="Q114" s="10" t="inlineStr">
         <is>
@@ -9686,13 +9686,13 @@
         </is>
       </c>
       <c r="D115" s="15" t="n">
-        <v>86.45</v>
+        <v>87.31</v>
       </c>
       <c r="E115" s="16" t="n">
-        <v>0.2133</v>
+        <v>0.2254</v>
       </c>
       <c r="F115" s="16" t="n">
-        <v>0.1909</v>
+        <v>0.2028</v>
       </c>
       <c r="G115" s="17" t="n"/>
       <c r="H115" s="22" t="inlineStr">
@@ -9711,7 +9711,7 @@
         <v>85</v>
       </c>
       <c r="M115" s="26" t="n">
-        <v>-0.01677270098322733</v>
+        <v>-0.02645745046386442</v>
       </c>
       <c r="N115" s="14" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="16" t="n">
-        <v>0.04106419895893577</v>
+        <v>0.03080975833237885</v>
       </c>
       <c r="Q115" s="20" t="inlineStr">
         <is>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>129.37</v>
+        <v>131.15</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>-0.0145</v>
+        <v>-0.0009</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>0.0015</v>
+        <v>0.0153</v>
       </c>
       <c r="G116" s="6" t="n">
         <v>46238</v>
@@ -9798,7 +9798,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="9" t="n">
-        <v>0.2754116101105356</v>
+        <v>0.2581014105985512</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="8" t="n"/>
@@ -9846,13 +9846,13 @@
         </is>
       </c>
       <c r="D117" s="15" t="n">
-        <v>575.8200000000001</v>
+        <v>567.84</v>
       </c>
       <c r="E117" s="16" t="n">
-        <v>0.0323</v>
+        <v>0.018</v>
       </c>
       <c r="F117" s="16" t="n">
-        <v>0.0196</v>
+        <v>0.005500000000000001</v>
       </c>
       <c r="G117" s="17" t="n">
         <v>46238</v>
@@ -9917,13 +9917,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>374.44</v>
+        <v>375.41</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>-0.1211</v>
+        <v>-0.1188</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>-0.106</v>
+        <v>-0.1036</v>
       </c>
       <c r="G118" s="6" t="n">
         <v>46315</v>
@@ -9952,7 +9952,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="9" t="n">
-        <v>0.3006089093045615</v>
+        <v>0.2972483418129511</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -9962,8 +9962,8 @@
       <c r="O118" s="8" t="n">
         <v>375</v>
       </c>
-      <c r="P118" s="9" t="n">
-        <v>0.001495566712958023</v>
+      <c r="P118" s="5" t="n">
+        <v>-0.001092139261074625</v>
       </c>
       <c r="Q118" s="10" t="inlineStr">
         <is>
@@ -10008,13 +10008,13 @@
         </is>
       </c>
       <c r="D119" s="15" t="n">
-        <v>252.45</v>
+        <v>254.41</v>
       </c>
       <c r="E119" s="26" t="n">
-        <v>-0.0403</v>
+        <v>-0.0328</v>
       </c>
       <c r="F119" s="16" t="n">
-        <v>0.1064</v>
+        <v>0.115</v>
       </c>
       <c r="G119" s="17" t="n">
         <v>46315</v>
@@ -10043,7 +10043,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="16" t="n">
-        <v>0.07744107744107749</v>
+        <v>0.06914036397940335</v>
       </c>
       <c r="N119" s="14" t="inlineStr"/>
       <c r="O119" s="19" t="n"/>
@@ -10095,13 +10095,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1115.7</v>
+        <v>1121.36</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>-0.0809</v>
+        <v>-0.0762</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0035</v>
       </c>
       <c r="G120" s="6" t="n">
         <v>46239</v>
@@ -10130,7 +10130,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="9" t="n">
-        <v>0.1472618087299453</v>
+        <v>0.1414710708425484</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -10190,13 +10190,13 @@
         </is>
       </c>
       <c r="D121" s="15" t="n">
-        <v>86.13</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="E121" s="16" t="n">
-        <v>0.0353</v>
+        <v>0.042</v>
       </c>
       <c r="F121" s="16" t="n">
-        <v>0.0513</v>
+        <v>0.058</v>
       </c>
       <c r="G121" s="17" t="n">
         <v>46266</v>
@@ -10225,7 +10225,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="16" t="n">
-        <v>0.1842563566701498</v>
+        <v>0.176742039686202</v>
       </c>
       <c r="N121" s="14" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="16" t="n">
-        <v>0.2190874259839778</v>
+        <v>0.2113520996769727</v>
       </c>
       <c r="Q121" s="20" t="inlineStr">
         <is>
@@ -10277,13 +10277,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>126.83</v>
+        <v>127.77</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>-0.0211</v>
+        <v>-0.0138</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>0.0546</v>
+        <v>0.0624</v>
       </c>
       <c r="G122" s="6" t="n">
         <v>46238</v>
@@ -10312,7 +10312,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="9" t="n">
-        <v>0.1826854845068202</v>
+        <v>0.1739845034045551</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="8" t="n"/>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="D123" s="15" t="n">
-        <v>153.26</v>
+        <v>153.67</v>
       </c>
       <c r="E123" s="26" t="n">
-        <v>-0.0415</v>
+        <v>-0.039</v>
       </c>
       <c r="F123" s="16" t="n">
-        <v>0.0327</v>
+        <v>0.0355</v>
       </c>
       <c r="G123" s="17" t="n">
         <v>46322</v>
@@ -10435,13 +10435,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>24.89</v>
+        <v>25.03</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>0.0232</v>
+        <v>0.0292</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>-0.0313</v>
+        <v>-0.0257</v>
       </c>
       <c r="G124" s="6" t="n">
         <v>46238</v>
@@ -10470,7 +10470,7 @@
         <v>28</v>
       </c>
       <c r="M124" s="9" t="n">
-        <v>0.1249497790277219</v>
+        <v>0.1186576108669596</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="8" t="n"/>
@@ -10514,13 +10514,13 @@
         </is>
       </c>
       <c r="D125" s="15" t="n">
-        <v>338.12</v>
+        <v>341.2</v>
       </c>
       <c r="E125" s="16" t="n">
-        <v>0.0355</v>
+        <v>0.0449</v>
       </c>
       <c r="F125" s="16" t="n">
-        <v>0.1225</v>
+        <v>0.1328</v>
       </c>
       <c r="G125" s="17" t="n"/>
       <c r="H125" s="22" t="inlineStr">
@@ -10539,7 +10539,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="16" t="n">
-        <v>0.2362474860996096</v>
+        <v>0.2250879249706917</v>
       </c>
       <c r="N125" s="14" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="16" t="n">
-        <v>0.03513545486809416</v>
+        <v>0.02579132473622512</v>
       </c>
       <c r="Q125" s="20" t="inlineStr">
         <is>
@@ -10595,13 +10595,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>574.08</v>
+        <v>574.03</v>
       </c>
       <c r="E126" s="9" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>0.191</v>
+        <v>0.1909</v>
       </c>
       <c r="G126" s="6" t="n">
         <v>46323</v>
@@ -10630,7 +10630,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="9" t="n">
-        <v>0.07127926421404675</v>
+        <v>0.07137257634618405</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="5" t="n">
-        <v>-0.007107023411371308</v>
+        <v>-0.007020538996219663</v>
       </c>
       <c r="Q126" s="10" t="inlineStr">
         <is>
@@ -10690,13 +10690,13 @@
         </is>
       </c>
       <c r="D127" s="15" t="n">
-        <v>415.96</v>
+        <v>415.36</v>
       </c>
       <c r="E127" s="26" t="n">
-        <v>-0.0221</v>
+        <v>-0.0235</v>
       </c>
       <c r="F127" s="16" t="n">
-        <v>0.0492</v>
+        <v>0.0476</v>
       </c>
       <c r="G127" s="17" t="n">
         <v>46322</v>
@@ -10725,7 +10725,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="16" t="n">
-        <v>0.2645446677565151</v>
+        <v>0.2663713405238828</v>
       </c>
       <c r="N127" s="14" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="16" t="n">
-        <v>0.1539571112606982</v>
+        <v>0.1556240369799692</v>
       </c>
       <c r="Q127" s="20" t="inlineStr">
         <is>
@@ -10781,13 +10781,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>77.98999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E128" s="9" t="n">
-        <v>0.0426</v>
+        <v>0.0307</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>-0.0192</v>
+        <v>-0.0304</v>
       </c>
       <c r="G128" s="6" t="n">
         <v>46240</v>
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="D129" s="15" t="n">
-        <v>270.56</v>
+        <v>269.78</v>
       </c>
       <c r="E129" s="16" t="n">
-        <v>0.1168</v>
+        <v>0.1136</v>
       </c>
       <c r="F129" s="16" t="n">
-        <v>0.1697</v>
+        <v>0.1663</v>
       </c>
       <c r="G129" s="17" t="n"/>
       <c r="H129" s="22" t="inlineStr">
@@ -10885,7 +10885,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="26" t="n">
-        <v>-0.08338261383796571</v>
+        <v>-0.08073244866187254</v>
       </c>
       <c r="N129" s="14" t="inlineStr"/>
       <c r="O129" s="19" t="n"/>
@@ -10941,13 +10941,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>103.22</v>
+        <v>103.92</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>-0.1139</v>
+        <v>-0.1079</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>-0.1389</v>
+        <v>-0.1331</v>
       </c>
       <c r="G130" s="6" t="n"/>
       <c r="H130" s="12" t="inlineStr">
@@ -10992,13 +10992,13 @@
         </is>
       </c>
       <c r="D131" s="15" t="n">
-        <v>241.73</v>
+        <v>243.77</v>
       </c>
       <c r="E131" s="16" t="n">
-        <v>0.0303</v>
+        <v>0.039</v>
       </c>
       <c r="F131" s="16" t="n">
-        <v>0.0567</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="G131" s="17" t="n">
         <v>46238</v>
@@ -11053,13 +11053,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>229.18</v>
+        <v>233.49</v>
       </c>
       <c r="E132" s="9" t="n">
-        <v>0.0119</v>
+        <v>0.0309</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>0.0541</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="G132" s="6" t="n"/>
       <c r="H132" s="12" t="inlineStr">
@@ -11078,7 +11078,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="9" t="n">
-        <v>0.09084562352735838</v>
+        <v>0.07070966636686792</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="8" t="n"/>
@@ -11122,13 +11122,13 @@
         </is>
       </c>
       <c r="D133" s="15" t="n">
-        <v>158.2</v>
+        <v>157.34</v>
       </c>
       <c r="E133" s="16" t="n">
-        <v>0.099</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="F133" s="16" t="n">
-        <v>0.0266</v>
+        <v>0.021</v>
       </c>
       <c r="G133" s="17" t="n">
         <v>46238</v>
@@ -11193,13 +11193,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>823.92</v>
+        <v>830.03</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>-0.1449</v>
+        <v>-0.1386</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>-0.1239</v>
+        <v>-0.1174</v>
       </c>
       <c r="G134" s="6" t="n">
         <v>46238</v>
@@ -11228,7 +11228,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="9" t="n">
-        <v>0.4018351296242355</v>
+        <v>0.3915159693023144</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="9" t="n">
-        <v>0.3387222060394214</v>
+        <v>0.3288676312904353</v>
       </c>
       <c r="Q134" s="10" t="inlineStr">
         <is>
@@ -11280,13 +11280,13 @@
         </is>
       </c>
       <c r="D135" s="15" t="n">
-        <v>646.1900000000001</v>
+        <v>648.85</v>
       </c>
       <c r="E135" s="26" t="n">
-        <v>-0.0234</v>
+        <v>-0.0194</v>
       </c>
       <c r="F135" s="26" t="n">
-        <v>-0.0471</v>
+        <v>-0.0431</v>
       </c>
       <c r="G135" s="17" t="n">
         <v>46238</v>
@@ -11315,7 +11315,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="16" t="n">
-        <v>0.3525433695971772</v>
+        <v>0.3469985358711566</v>
       </c>
       <c r="N135" s="14" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="16" t="n">
-        <v>0.3076649282718704</v>
+        <v>0.3023040764429374</v>
       </c>
       <c r="Q135" s="20" t="inlineStr">
         <is>
@@ -11375,13 +11375,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>204.54</v>
+        <v>204.01</v>
       </c>
       <c r="E136" s="9" t="n">
-        <v>0.1277</v>
+        <v>0.1248</v>
       </c>
       <c r="F136" s="9" t="n">
-        <v>0.1366</v>
+        <v>0.1336</v>
       </c>
       <c r="G136" s="6" t="n">
         <v>46288</v>
@@ -11410,7 +11410,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="9" t="n">
-        <v>0.2222548156839738</v>
+        <v>0.225430125974217</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="8" t="n"/>
@@ -11454,13 +11454,13 @@
         </is>
       </c>
       <c r="D137" s="15" t="n">
-        <v>608.97</v>
+        <v>605.0599999999999</v>
       </c>
       <c r="E137" s="26" t="n">
-        <v>-0.0198</v>
+        <v>-0.0261</v>
       </c>
       <c r="F137" s="16" t="n">
-        <v>0.0291</v>
+        <v>0.0225</v>
       </c>
       <c r="G137" s="17" t="n">
         <v>46254</v>
@@ -11489,7 +11489,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="16" t="n">
-        <v>0.2315877629439873</v>
+        <v>0.2395464912570655</v>
       </c>
       <c r="N137" s="14" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="16" t="n">
-        <v>0.05307322199779946</v>
+        <v>0.05987835917099135</v>
       </c>
       <c r="Q137" s="20" t="inlineStr">
         <is>
@@ -11541,13 +11541,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>152.35</v>
+        <v>154.85</v>
       </c>
       <c r="E138" s="9" t="n">
-        <v>0.0956</v>
+        <v>0.1136</v>
       </c>
       <c r="F138" s="9" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="G138" s="6" t="n">
         <v>46238</v>
@@ -11583,7 +11583,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="9" t="n">
-        <v>0.2143091565474237</v>
+        <v>0.1947045527930256</v>
       </c>
       <c r="Q138" s="10" t="inlineStr">
         <is>
@@ -11622,13 +11622,13 @@
         </is>
       </c>
       <c r="D139" s="15" t="n">
-        <v>431.24</v>
+        <v>438.23</v>
       </c>
       <c r="E139" s="16" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="F139" s="16" t="n">
-        <v>0.0302</v>
+        <v>0.0469</v>
       </c>
       <c r="G139" s="17" t="n"/>
       <c r="H139" s="22" t="inlineStr">
@@ -11654,7 +11654,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="16" t="n">
-        <v>0.0504591410815323</v>
+        <v>0.03370376286424932</v>
       </c>
       <c r="Q139" s="20" t="inlineStr">
         <is>
@@ -11695,13 +11695,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>47.9</v>
+        <v>48.11</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>-0.0143</v>
+        <v>-0.0101</v>
       </c>
       <c r="F140" s="9" t="n">
-        <v>0.0158</v>
+        <v>0.0201</v>
       </c>
       <c r="G140" s="6" t="n">
         <v>46309</v>
@@ -11774,13 +11774,13 @@
         </is>
       </c>
       <c r="D141" s="15" t="n">
-        <v>307.98</v>
+        <v>309.24</v>
       </c>
       <c r="E141" s="26" t="n">
-        <v>-0.016</v>
+        <v>-0.012</v>
       </c>
       <c r="F141" s="26" t="n">
-        <v>-0.061</v>
+        <v>-0.0572</v>
       </c>
       <c r="G141" s="17" t="n">
         <v>46282</v>
@@ -11809,7 +11809,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="16" t="n">
-        <v>0.3799597376453016</v>
+        <v>0.3743370844651403</v>
       </c>
       <c r="N141" s="14" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="16" t="n">
-        <v>0.04876940061042918</v>
+        <v>0.04449618419350663</v>
       </c>
       <c r="Q141" s="20" t="inlineStr">
         <is>
@@ -11861,13 +11861,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>253.93</v>
+        <v>250.08</v>
       </c>
       <c r="E142" s="9" t="n">
-        <v>0.1029</v>
+        <v>0.0862</v>
       </c>
       <c r="F142" s="9" t="n">
-        <v>0.1012</v>
+        <v>0.08449999999999999</v>
       </c>
       <c r="G142" s="6" t="n">
         <v>46244</v>
@@ -11896,7 +11896,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="9" t="n">
-        <v>0.1223565549560902</v>
+        <v>0.1396353166986564</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="8" t="n"/>
@@ -11944,13 +11944,13 @@
         </is>
       </c>
       <c r="D143" s="15" t="n">
-        <v>1747.55</v>
+        <v>1770.96</v>
       </c>
       <c r="E143" s="16" t="n">
-        <v>0.0036</v>
+        <v>0.017</v>
       </c>
       <c r="F143" s="26" t="n">
-        <v>-0.0873</v>
+        <v>-0.075</v>
       </c>
       <c r="G143" s="17" t="n">
         <v>46317</v>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>50.28</v>
+        <v>50.17</v>
       </c>
       <c r="E144" s="9" t="n">
-        <v>0.0169</v>
+        <v>0.0146</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0048</v>
       </c>
       <c r="G144" s="6" t="n">
         <v>46241</v>
@@ -12066,13 +12066,13 @@
         </is>
       </c>
       <c r="D145" s="15" t="n">
-        <v>382.36</v>
+        <v>382.43</v>
       </c>
       <c r="E145" s="16" t="n">
-        <v>0.0236</v>
+        <v>0.0238</v>
       </c>
       <c r="F145" s="16" t="n">
-        <v>0.1196</v>
+        <v>0.1199</v>
       </c>
       <c r="G145" s="17" t="n"/>
       <c r="H145" s="22" t="inlineStr">
@@ -12091,7 +12091,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="16" t="n">
-        <v>0.04613453290093102</v>
+        <v>0.04594304840101455</v>
       </c>
       <c r="N145" s="14" t="inlineStr"/>
       <c r="O145" s="19" t="n"/>
@@ -12143,13 +12143,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>364.3</v>
+        <v>368.93</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>-0.035</v>
+        <v>-0.0228</v>
       </c>
       <c r="F146" s="9" t="n">
-        <v>0.1119</v>
+        <v>0.126</v>
       </c>
       <c r="G146" s="6" t="n">
         <v>46315</v>
@@ -12178,7 +12178,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="9" t="n">
-        <v>0.07054625308811416</v>
+        <v>0.05711110508768599</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="8" t="n"/>
@@ -12230,13 +12230,13 @@
         </is>
       </c>
       <c r="D147" s="15" t="n">
-        <v>1002.26</v>
+        <v>1006.76</v>
       </c>
       <c r="E147" s="26" t="n">
-        <v>-0.09960000000000001</v>
+        <v>-0.0955</v>
       </c>
       <c r="F147" s="16" t="n">
-        <v>0.0404</v>
+        <v>0.0451</v>
       </c>
       <c r="G147" s="17" t="n">
         <v>46316</v>
@@ -12265,7 +12265,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="16" t="n">
-        <v>0.2561610759683116</v>
+        <v>0.2505463069649172</v>
       </c>
       <c r="N147" s="14" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="16" t="n">
-        <v>0.3469558797118512</v>
+        <v>0.3409352775239382</v>
       </c>
       <c r="Q147" s="20" t="inlineStr">
         <is>
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1367.05</v>
+        <v>1371.25</v>
       </c>
       <c r="E148" s="9" t="n">
-        <v>0.0179</v>
+        <v>0.0211</v>
       </c>
       <c r="F148" s="9" t="n">
-        <v>0.0602</v>
+        <v>0.0635</v>
       </c>
       <c r="G148" s="6" t="n">
         <v>46238</v>
@@ -12396,13 +12396,13 @@
         </is>
       </c>
       <c r="D149" s="15" t="n">
-        <v>243.14</v>
+        <v>246.77</v>
       </c>
       <c r="E149" s="16" t="n">
-        <v>0.0578</v>
+        <v>0.0736</v>
       </c>
       <c r="F149" s="16" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.08109999999999999</v>
       </c>
       <c r="G149" s="17" t="n">
         <v>46317</v>
@@ -12457,13 +12457,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>470.11</v>
+        <v>476.04</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>-0.0349</v>
+        <v>-0.0227</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.019</v>
       </c>
       <c r="G150" s="6" t="n"/>
       <c r="H150" s="12" t="inlineStr">
@@ -12514,13 +12514,13 @@
         </is>
       </c>
       <c r="D151" s="15" t="n">
-        <v>285.98</v>
+        <v>288.49</v>
       </c>
       <c r="E151" s="16" t="n">
-        <v>0.04849999999999999</v>
+        <v>0.05769999999999999</v>
       </c>
       <c r="F151" s="16" t="n">
-        <v>0.1388</v>
+        <v>0.1488</v>
       </c>
       <c r="G151" s="17" t="n"/>
       <c r="H151" s="22" t="inlineStr">
@@ -12542,7 +12542,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="26" t="n">
-        <v>-0.04888453738023644</v>
+        <v>-0.05715969357690044</v>
       </c>
       <c r="Q151" s="20" t="inlineStr">
         <is>
@@ -12595,13 +12595,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>275.8</v>
+        <v>277.86</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.0801</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>-0.1097</v>
+        <v>-0.103</v>
       </c>
       <c r="G152" s="6" t="n"/>
       <c r="H152" s="12" t="inlineStr">
@@ -12656,13 +12656,13 @@
         </is>
       </c>
       <c r="D153" s="15" t="n">
-        <v>427.07</v>
+        <v>435</v>
       </c>
       <c r="E153" s="26" t="n">
-        <v>-0.2508</v>
+        <v>-0.2369</v>
       </c>
       <c r="F153" s="26" t="n">
-        <v>-0.1757</v>
+        <v>-0.1604</v>
       </c>
       <c r="G153" s="17" t="n"/>
       <c r="H153" s="22" t="inlineStr">
@@ -12707,13 +12707,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>580.11</v>
+        <v>586.29</v>
       </c>
       <c r="E154" s="9" t="n">
-        <v>0.06269999999999999</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="F154" s="9" t="n">
-        <v>0.1176</v>
+        <v>0.1295</v>
       </c>
       <c r="G154" s="6" t="n">
         <v>46315</v>
@@ -12774,13 +12774,13 @@
         </is>
       </c>
       <c r="D155" s="15" t="n">
-        <v>210.79</v>
+        <v>211.52</v>
       </c>
       <c r="E155" s="26" t="n">
-        <v>-0.0315</v>
+        <v>-0.0282</v>
       </c>
       <c r="F155" s="26" t="n">
-        <v>-0.1415</v>
+        <v>-0.1385</v>
       </c>
       <c r="G155" s="17" t="n"/>
       <c r="H155" s="22" t="inlineStr">
@@ -12799,7 +12799,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="16" t="n">
-        <v>1.727833388680678</v>
+        <v>1.718419062027231</v>
       </c>
       <c r="N155" s="14" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="16" t="n">
-        <v>0.1243417619431662</v>
+        <v>0.1204614220877458</v>
       </c>
       <c r="Q155" s="20" t="inlineStr">
         <is>
@@ -12859,13 +12859,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>118.22</v>
+        <v>117.67</v>
       </c>
       <c r="E156" s="9" t="n">
-        <v>0.1116</v>
+        <v>0.1064</v>
       </c>
       <c r="F156" s="9" t="n">
-        <v>0.1884</v>
+        <v>0.1829</v>
       </c>
       <c r="G156" s="6" t="n">
         <v>46294</v>
@@ -12894,7 +12894,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="9" t="n">
-        <v>1.114701404161732</v>
+        <v>1.124585705787371</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="8" t="n"/>
@@ -12938,13 +12938,13 @@
         </is>
       </c>
       <c r="D157" s="15" t="n">
-        <v>132.51</v>
+        <v>132.06</v>
       </c>
       <c r="E157" s="16" t="n">
-        <v>0.1089</v>
+        <v>0.1051</v>
       </c>
       <c r="F157" s="16" t="n">
-        <v>0.1223</v>
+        <v>0.1185</v>
       </c>
       <c r="G157" s="17" t="n"/>
       <c r="H157" s="22" t="inlineStr">
@@ -12963,7 +12963,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="26" t="n">
-        <v>-0.2830729756244811</v>
+        <v>-0.2806300166590944</v>
       </c>
       <c r="N157" s="14" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="16" t="n">
-        <v>0.04897743566523288</v>
+        <v>0.05255187036195667</v>
       </c>
       <c r="Q157" s="20" t="inlineStr">
         <is>
@@ -13019,13 +13019,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>981.8200000000001</v>
+        <v>997.52</v>
       </c>
       <c r="E158" s="9" t="n">
-        <v>0.0197</v>
+        <v>0.036</v>
       </c>
       <c r="F158" s="9" t="n">
-        <v>0.1256</v>
+        <v>0.1436</v>
       </c>
       <c r="G158" s="6" t="n">
         <v>46240</v>
@@ -13054,7 +13054,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="5" t="n">
-        <v>-0.8726854209529241</v>
+        <v>-0.8746892292886358</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="9" t="n">
-        <v>0.08370169684870948</v>
+        <v>0.06664528029513195</v>
       </c>
       <c r="Q158" s="10" t="inlineStr">
         <is>
@@ -13110,13 +13110,13 @@
         </is>
       </c>
       <c r="D159" s="15" t="n">
-        <v>567.75</v>
+        <v>570.27</v>
       </c>
       <c r="E159" s="26" t="n">
-        <v>-0.0609</v>
+        <v>-0.0567</v>
       </c>
       <c r="F159" s="26" t="n">
-        <v>-0.0373</v>
+        <v>-0.033</v>
       </c>
       <c r="G159" s="17" t="n"/>
       <c r="H159" s="22" t="inlineStr">
@@ -13181,13 +13181,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>472.4</v>
+        <v>480.98</v>
       </c>
       <c r="E160" s="9" t="n">
-        <v>0.0015</v>
+        <v>0.0197</v>
       </c>
       <c r="F160" s="9" t="n">
-        <v>0.022</v>
+        <v>0.0405</v>
       </c>
       <c r="G160" s="6" t="n">
         <v>46238</v>
@@ -13242,13 +13242,13 @@
         </is>
       </c>
       <c r="D161" s="15" t="n">
-        <v>38.25</v>
+        <v>38.19</v>
       </c>
       <c r="E161" s="26" t="n">
-        <v>-0.1183</v>
+        <v>-0.1196</v>
       </c>
       <c r="F161" s="26" t="n">
-        <v>-0.1774</v>
+        <v>-0.1787</v>
       </c>
       <c r="G161" s="17" t="n">
         <v>46323</v>
@@ -13317,13 +13317,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>215.5</v>
+        <v>216.65</v>
       </c>
       <c r="E162" s="9" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.0873</v>
       </c>
       <c r="F162" s="9" t="n">
-        <v>0.2012</v>
+        <v>0.2076</v>
       </c>
       <c r="G162" s="6" t="n">
         <v>46322</v>
@@ -13396,13 +13396,13 @@
         </is>
       </c>
       <c r="D163" s="15" t="n">
-        <v>45.63</v>
+        <v>45.85</v>
       </c>
       <c r="E163" s="16" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0728</v>
       </c>
       <c r="F163" s="26" t="n">
-        <v>-0.0375</v>
+        <v>-0.0329</v>
       </c>
       <c r="G163" s="17" t="n">
         <v>46239</v>
@@ -13457,13 +13457,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>460.73</v>
+        <v>461.21</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>-0.0364</v>
+        <v>-0.0354</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>-0.006500000000000001</v>
+        <v>-0.005500000000000001</v>
       </c>
       <c r="G164" s="6" t="n"/>
       <c r="H164" s="12" t="inlineStr">
@@ -13485,7 +13485,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="9" t="n">
-        <v>0.2154624183361187</v>
+        <v>0.2141974371761237</v>
       </c>
       <c r="Q164" s="10" t="inlineStr">
         <is>
@@ -13538,13 +13538,13 @@
         </is>
       </c>
       <c r="D165" s="15" t="n">
-        <v>289.58</v>
+        <v>291.23</v>
       </c>
       <c r="E165" s="16" t="n">
-        <v>0.026</v>
+        <v>0.0318</v>
       </c>
       <c r="F165" s="16" t="n">
-        <v>0.0973</v>
+        <v>0.1036</v>
       </c>
       <c r="G165" s="17" t="n">
         <v>46317</v>
@@ -13576,7 +13576,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="16" t="n">
-        <v>0.01526348504730995</v>
+        <v>0.009511382755897338</v>
       </c>
       <c r="Q165" s="20" t="inlineStr">
         <is>
@@ -13621,13 +13621,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>259.3</v>
+        <v>263.05</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>-0.1372</v>
+        <v>-0.1247</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>-0.1995</v>
+        <v>-0.1879</v>
       </c>
       <c r="G166" s="6" t="n"/>
       <c r="H166" s="12" t="inlineStr">
@@ -13649,7 +13649,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="9" t="n">
-        <v>0.6390281527188584</v>
+        <v>0.615662421592853</v>
       </c>
       <c r="Q166" s="10" t="inlineStr">
         <is>
@@ -13690,13 +13690,13 @@
         </is>
       </c>
       <c r="D167" s="15" t="n">
-        <v>225.58</v>
+        <v>226.43</v>
       </c>
       <c r="E167" s="26" t="n">
-        <v>-0.0209</v>
+        <v>-0.0172</v>
       </c>
       <c r="F167" s="16" t="n">
-        <v>0.03</v>
+        <v>0.0339</v>
       </c>
       <c r="G167" s="17" t="n"/>
       <c r="H167" s="22" t="inlineStr">
@@ -13715,7 +13715,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="16" t="n">
-        <v>0.1880485858675414</v>
+        <v>0.1835887470741509</v>
       </c>
       <c r="N167" s="14" t="inlineStr"/>
       <c r="O167" s="19" t="n"/>
@@ -13763,13 +13763,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>316.18</v>
+        <v>318.01</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>-0.2187</v>
+        <v>-0.2142</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>-0.1433</v>
+        <v>-0.1383</v>
       </c>
       <c r="G168" s="6" t="n"/>
       <c r="H168" s="12" t="inlineStr">
@@ -13828,13 +13828,13 @@
         </is>
       </c>
       <c r="D169" s="15" t="n">
-        <v>363.89</v>
+        <v>363.57</v>
       </c>
       <c r="E169" s="26" t="n">
-        <v>-0.1295</v>
+        <v>-0.1303</v>
       </c>
       <c r="F169" s="16" t="n">
-        <v>0.0098</v>
+        <v>0.0089</v>
       </c>
       <c r="G169" s="17" t="n"/>
       <c r="H169" s="22" t="inlineStr">
@@ -13897,13 +13897,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>118.58</v>
+        <v>119.08</v>
       </c>
       <c r="E170" s="9" t="n">
-        <v>0.0039</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F170" s="9" t="n">
-        <v>0.0762</v>
+        <v>0.0808</v>
       </c>
       <c r="G170" s="6" t="n"/>
       <c r="H170" s="12" t="inlineStr">
@@ -13966,13 +13966,13 @@
         </is>
       </c>
       <c r="D171" s="15" t="n">
-        <v>108.04</v>
+        <v>110.21</v>
       </c>
       <c r="E171" s="26" t="n">
-        <v>-0.1067</v>
+        <v>-0.0888</v>
       </c>
       <c r="F171" s="26" t="n">
-        <v>-0.4675</v>
+        <v>-0.4568</v>
       </c>
       <c r="G171" s="17" t="n">
         <v>46240</v>
@@ -14027,13 +14027,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>307.3</v>
+        <v>303.42</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0169</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0251</v>
       </c>
       <c r="G172" s="6" t="n"/>
       <c r="H172" s="12" t="inlineStr">
@@ -14052,7 +14052,7 @@
         <v>310</v>
       </c>
       <c r="M172" s="9" t="n">
-        <v>0.008786202408070253</v>
+        <v>0.02168611166040467</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="9" t="n">
-        <v>0.1877643996095021</v>
+        <v>0.2029530024388636</v>
       </c>
       <c r="Q172" s="10" t="inlineStr">
         <is>
@@ -14120,13 +14120,13 @@
         </is>
       </c>
       <c r="D173" s="15" t="n">
-        <v>130.52</v>
+        <v>131.12</v>
       </c>
       <c r="E173" s="26" t="n">
-        <v>-0.09669999999999999</v>
+        <v>-0.0926</v>
       </c>
       <c r="F173" s="26" t="n">
-        <v>-0.1937</v>
+        <v>-0.19</v>
       </c>
       <c r="G173" s="17" t="n">
         <v>46240</v>
@@ -14181,13 +14181,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>166.85</v>
+        <v>165.76</v>
       </c>
       <c r="E174" s="9" t="n">
-        <v>0.2148</v>
+        <v>0.2068</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>-0.06709999999999999</v>
+        <v>-0.0732</v>
       </c>
       <c r="G174" s="6" t="n">
         <v>46289</v>
@@ -14242,13 +14242,13 @@
         </is>
       </c>
       <c r="D175" s="15" t="n">
-        <v>254.12</v>
+        <v>251.34</v>
       </c>
       <c r="E175" s="16" t="n">
-        <v>0.1566</v>
+        <v>0.1439</v>
       </c>
       <c r="F175" s="26" t="n">
-        <v>-0.0166</v>
+        <v>-0.0274</v>
       </c>
       <c r="G175" s="17" t="n">
         <v>46275</v>
@@ -14303,13 +14303,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>361.06</v>
+        <v>361.88</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>-0.04269999999999999</v>
+        <v>-0.0405</v>
       </c>
       <c r="F176" s="5" t="n">
-        <v>-0.1579</v>
+        <v>-0.156</v>
       </c>
       <c r="G176" s="6" t="n">
         <v>46253</v>
@@ -14338,7 +14338,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="9" t="n">
-        <v>0.4263557303495264</v>
+        <v>0.4231236874101912</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="9" t="n">
-        <v>0.3128011964770398</v>
+        <v>0.309826461810545</v>
       </c>
       <c r="Q176" s="10" t="inlineStr">
         <is>
@@ -14398,13 +14398,13 @@
         </is>
       </c>
       <c r="D177" s="15" t="n">
-        <v>236.24</v>
+        <v>234.71</v>
       </c>
       <c r="E177" s="16" t="n">
-        <v>0.1386</v>
+        <v>0.1312</v>
       </c>
       <c r="F177" s="16" t="n">
-        <v>0.0111</v>
+        <v>0.0046</v>
       </c>
       <c r="G177" s="17" t="n">
         <v>46261</v>
@@ -14459,13 +14459,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>293.57</v>
+        <v>296.38</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>-0.05690000000000001</v>
+        <v>-0.0478</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>-0.0852</v>
+        <v>-0.0765</v>
       </c>
       <c r="G178" s="6" t="n">
         <v>46237</v>
@@ -14520,13 +14520,13 @@
         </is>
       </c>
       <c r="D179" s="15" t="n">
-        <v>321.5</v>
+        <v>321.05</v>
       </c>
       <c r="E179" s="26" t="n">
-        <v>-0.2089</v>
+        <v>-0.2101</v>
       </c>
       <c r="F179" s="26" t="n">
-        <v>-0.1021</v>
+        <v>-0.1033</v>
       </c>
       <c r="G179" s="17" t="n">
         <v>46238</v>
@@ -14581,13 +14581,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>40.99</v>
+        <v>41.52</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>-0.2612</v>
+        <v>-0.2517</v>
       </c>
       <c r="F180" s="5" t="n">
-        <v>-0.2355</v>
+        <v>-0.2257</v>
       </c>
       <c r="G180" s="6" t="n"/>
       <c r="H180" s="12" t="inlineStr">
@@ -14632,13 +14632,13 @@
         </is>
       </c>
       <c r="D181" s="15" t="n">
-        <v>513.8200000000001</v>
+        <v>518.21</v>
       </c>
       <c r="E181" s="26" t="n">
-        <v>-0.148</v>
+        <v>-0.1407</v>
       </c>
       <c r="F181" s="16" t="n">
-        <v>0.0241</v>
+        <v>0.0329</v>
       </c>
       <c r="G181" s="17" t="n">
         <v>46247</v>
@@ -14667,7 +14667,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="16" t="n">
-        <v>0.4401930637188119</v>
+        <v>0.4279925126879063</v>
       </c>
       <c r="N181" s="14" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="16" t="n">
-        <v>0.3623447900042815</v>
+        <v>0.3508037282182898</v>
       </c>
       <c r="Q181" s="20" t="inlineStr">
         <is>
@@ -14719,13 +14719,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>64.22</v>
+        <v>64.91</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>-0.2249</v>
+        <v>-0.2165</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>-0.2445</v>
+        <v>-0.2364</v>
       </c>
       <c r="G182" s="6" t="n">
         <v>46245</v>
@@ -14784,13 +14784,13 @@
         </is>
       </c>
       <c r="D183" s="15" t="n">
-        <v>482.3</v>
+        <v>484.64</v>
       </c>
       <c r="E183" s="26" t="n">
-        <v>-0.06860000000000001</v>
+        <v>-0.0641</v>
       </c>
       <c r="F183" s="26" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0737</v>
       </c>
       <c r="G183" s="17" t="n">
         <v>46238</v>
@@ -14819,7 +14819,7 @@
         <v>615</v>
       </c>
       <c r="M183" s="16" t="n">
-        <v>0.2751399543852374</v>
+        <v>0.2689831627599868</v>
       </c>
       <c r="N183" s="14" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="16" t="n">
-        <v>0.2004976155919552</v>
+        <v>0.1947012215252559</v>
       </c>
       <c r="Q183" s="20" t="inlineStr">
         <is>
@@ -14871,13 +14871,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>50.19</v>
+        <v>50.84</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>-0.2793</v>
+        <v>-0.2701</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>-0.32</v>
+        <v>-0.3113</v>
       </c>
       <c r="G184" s="6" t="n"/>
       <c r="H184" s="12" t="inlineStr">
@@ -14922,13 +14922,13 @@
         </is>
       </c>
       <c r="D185" s="15" t="n">
-        <v>183.16</v>
+        <v>184.89</v>
       </c>
       <c r="E185" s="16" t="n">
-        <v>0.1449</v>
+        <v>0.1556</v>
       </c>
       <c r="F185" s="16" t="n">
-        <v>0.1033</v>
+        <v>0.1137</v>
       </c>
       <c r="G185" s="17" t="n">
         <v>46238</v>
@@ -14957,7 +14957,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="16" t="n">
-        <v>0.0919414719371042</v>
+        <v>0.08172426848396351</v>
       </c>
       <c r="N185" s="14" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="16" t="n">
-        <v>0.0919414719371042</v>
+        <v>0.08172426848396351</v>
       </c>
       <c r="Q185" s="20" t="inlineStr">
         <is>
@@ -15013,13 +15013,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>162.05</v>
+        <v>163.34</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>-0.0154</v>
+        <v>-0.0076</v>
       </c>
       <c r="F186" s="9" t="n">
-        <v>0.1041</v>
+        <v>0.1129</v>
       </c>
       <c r="G186" s="6" t="n"/>
       <c r="H186" s="12" t="inlineStr">
@@ -15041,7 +15041,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="9" t="n">
-        <v>0.1107682813946312</v>
+        <v>0.1019958369046161</v>
       </c>
       <c r="Q186" s="10" t="inlineStr">
         <is>
@@ -15094,13 +15094,13 @@
         </is>
       </c>
       <c r="D187" s="15" t="n">
-        <v>29.46</v>
+        <v>29.49</v>
       </c>
       <c r="E187" s="26" t="n">
-        <v>-0.1089</v>
+        <v>-0.108</v>
       </c>
       <c r="F187" s="26" t="n">
-        <v>-0.3327000000000001</v>
+        <v>-0.332</v>
       </c>
       <c r="G187" s="17" t="n"/>
       <c r="H187" s="22" t="inlineStr">
@@ -15145,13 +15145,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>237.81</v>
+        <v>239.06</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>-0.2457</v>
+        <v>-0.2418</v>
       </c>
       <c r="F188" s="5" t="n">
-        <v>-0.3956</v>
+        <v>-0.3924</v>
       </c>
       <c r="G188" s="6" t="n"/>
       <c r="H188" s="12" t="inlineStr">
@@ -15196,13 +15196,13 @@
         </is>
       </c>
       <c r="D189" s="15" t="n">
-        <v>1645.14</v>
+        <v>1642.52</v>
       </c>
       <c r="E189" s="26" t="n">
-        <v>-0.0702</v>
+        <v>-0.0717</v>
       </c>
       <c r="F189" s="26" t="n">
-        <v>-0.0639</v>
+        <v>-0.0654</v>
       </c>
       <c r="G189" s="17" t="n">
         <v>46309</v>
@@ -15275,13 +15275,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>36.08</v>
+        <v>36.68</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>-0.1384</v>
+        <v>-0.124</v>
       </c>
       <c r="F190" s="5" t="n">
-        <v>-0.0605</v>
+        <v>-0.04480000000000001</v>
       </c>
       <c r="G190" s="6" t="n"/>
       <c r="H190" s="12" t="inlineStr">
@@ -15326,13 +15326,13 @@
         </is>
       </c>
       <c r="D191" s="15" t="n">
-        <v>389.68</v>
+        <v>392.23</v>
       </c>
       <c r="E191" s="16" t="n">
-        <v>0.08109999999999999</v>
+        <v>0.0882</v>
       </c>
       <c r="F191" s="26" t="n">
-        <v>-0.0698</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="G191" s="17" t="n">
         <v>46268</v>
@@ -15361,7 +15361,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="16" t="n">
-        <v>0.3985834530897146</v>
+        <v>0.3894908599546184</v>
       </c>
       <c r="N191" s="14" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="16" t="n">
-        <v>0.4935331554095668</v>
+        <v>0.4838232669607118</v>
       </c>
       <c r="Q191" s="20" t="inlineStr">
         <is>
@@ -15425,13 +15425,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>136.57</v>
+        <v>139.79</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>-0.0416</v>
+        <v>-0.019</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>-0.2461</v>
+        <v>-0.2284</v>
       </c>
       <c r="G192" s="6" t="n">
         <v>46244</v>
@@ -15486,13 +15486,13 @@
         </is>
       </c>
       <c r="D193" s="15" t="n">
-        <v>337.63</v>
+        <v>336.15</v>
       </c>
       <c r="E193" s="26" t="n">
-        <v>-0.09519999999999999</v>
+        <v>-0.09910000000000001</v>
       </c>
       <c r="F193" s="26" t="n">
-        <v>-0.1799</v>
+        <v>-0.1835</v>
       </c>
       <c r="G193" s="17" t="n"/>
       <c r="H193" s="22" t="inlineStr">
@@ -15511,7 +15511,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="16" t="n">
-        <v>0.2587743980096556</v>
+        <v>0.2643165253607022</v>
       </c>
       <c r="N193" s="14" t="inlineStr"/>
       <c r="O193" s="19" t="n"/>
@@ -15555,13 +15555,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>123.71</v>
+        <v>122.97</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.09960000000000001</v>
       </c>
       <c r="F194" s="5" t="n">
-        <v>-0.0935</v>
+        <v>-0.0989</v>
       </c>
       <c r="G194" s="6" t="n"/>
       <c r="H194" s="12" t="inlineStr">
@@ -15606,13 +15606,13 @@
         </is>
       </c>
       <c r="D195" s="15" t="n">
-        <v>386.29</v>
+        <v>390.76</v>
       </c>
       <c r="E195" s="26" t="n">
-        <v>-0.08560000000000001</v>
+        <v>-0.075</v>
       </c>
       <c r="F195" s="26" t="n">
-        <v>-0.2788</v>
+        <v>-0.2705</v>
       </c>
       <c r="G195" s="17" t="n">
         <v>46268</v>
@@ -15667,13 +15667,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>15.02</v>
+        <v>15.07</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>-0.0403</v>
+        <v>-0.0371</v>
       </c>
       <c r="F196" s="9" t="n">
-        <v>0.05110000000000001</v>
+        <v>0.0546</v>
       </c>
       <c r="G196" s="6" t="n">
         <v>46247</v>
@@ -15728,13 +15728,13 @@
         </is>
       </c>
       <c r="D197" s="15" t="n">
-        <v>336.81</v>
+        <v>341.91</v>
       </c>
       <c r="E197" s="16" t="n">
-        <v>0.0018</v>
+        <v>0.017</v>
       </c>
       <c r="F197" s="26" t="n">
-        <v>-0.2082</v>
+        <v>-0.1962</v>
       </c>
       <c r="G197" s="17" t="n"/>
       <c r="H197" s="22" t="inlineStr">
@@ -15779,13 +15779,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>288.1</v>
+        <v>288.14</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>-0.1358</v>
+        <v>-0.1356</v>
       </c>
       <c r="F198" s="5" t="n">
-        <v>-0.3171</v>
+        <v>-0.317</v>
       </c>
       <c r="G198" s="6" t="n">
         <v>46246</v>
@@ -15840,13 +15840,13 @@
         </is>
       </c>
       <c r="D199" s="15" t="n">
-        <v>48.26</v>
+        <v>48.84</v>
       </c>
       <c r="E199" s="26" t="n">
-        <v>-0.1858</v>
+        <v>-0.176</v>
       </c>
       <c r="F199" s="26" t="n">
-        <v>-0.1364</v>
+        <v>-0.126</v>
       </c>
       <c r="G199" s="17" t="n"/>
       <c r="H199" s="22" t="inlineStr">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>22.63</v>
+        <v>22.83</v>
       </c>
       <c r="E200" s="9" t="n">
-        <v>0.05599999999999999</v>
+        <v>0.0653</v>
       </c>
       <c r="F200" s="5" t="n">
-        <v>-0.1892</v>
+        <v>-0.182</v>
       </c>
       <c r="G200" s="6" t="n"/>
       <c r="H200" s="12" t="inlineStr">
@@ -15942,13 +15942,13 @@
         </is>
       </c>
       <c r="D201" s="15" t="n">
-        <v>215.02</v>
+        <v>218.35</v>
       </c>
       <c r="E201" s="26" t="n">
-        <v>-0.1112</v>
-      </c>
-      <c r="F201" s="26" t="n">
-        <v>-0.0114</v>
+        <v>-0.0974</v>
+      </c>
+      <c r="F201" s="16" t="n">
+        <v>0.0039</v>
       </c>
       <c r="G201" s="17" t="n">
         <v>46267</v>
@@ -16003,13 +16003,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>188.54</v>
+        <v>185.95</v>
       </c>
       <c r="E202" s="9" t="n">
-        <v>0.135</v>
+        <v>0.1194</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>-0.0011</v>
+        <v>-0.0148</v>
       </c>
       <c r="G202" s="6" t="n">
         <v>46267</v>
@@ -16038,7 +16038,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="9" t="n">
-        <v>0.06078285774901882</v>
+        <v>0.07555794568432381</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="9" t="n">
-        <v>0.3259785721862735</v>
+        <v>0.3444474321054047</v>
       </c>
       <c r="Q202" s="10" t="inlineStr">
         <is>
@@ -16094,13 +16094,13 @@
         </is>
       </c>
       <c r="D203" s="15" t="n">
-        <v>199.17</v>
+        <v>202.54</v>
       </c>
       <c r="E203" s="16" t="n">
-        <v>0.0268</v>
+        <v>0.0441</v>
       </c>
       <c r="F203" s="16" t="n">
-        <v>0.1079</v>
+        <v>0.1266</v>
       </c>
       <c r="G203" s="17" t="n">
         <v>46260</v>
@@ -16129,7 +16129,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="26" t="n">
-        <v>-0.08997338956670176</v>
+        <v>-0.105115039004641</v>
       </c>
       <c r="N203" s="14" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="26" t="n">
-        <v>-0.1088015263342872</v>
+        <v>-0.123629900266614</v>
       </c>
       <c r="Q203" s="20" t="inlineStr">
         <is>
@@ -16181,13 +16181,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>83.25</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="E204" s="9" t="n">
-        <v>0.0184</v>
+        <v>0.0491</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>-0.2294</v>
+        <v>-0.2061</v>
       </c>
       <c r="G204" s="6" t="n">
         <v>46245</v>
@@ -16242,13 +16242,13 @@
         </is>
       </c>
       <c r="D205" s="15" t="n">
-        <v>115.13</v>
+        <v>115.86</v>
       </c>
       <c r="E205" s="16" t="n">
-        <v>0.0217</v>
+        <v>0.0281</v>
       </c>
       <c r="F205" s="26" t="n">
-        <v>-0.1144</v>
+        <v>-0.1088</v>
       </c>
       <c r="G205" s="17" t="n">
         <v>46246</v>
@@ -16277,7 +16277,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="16" t="n">
-        <v>0.1291583427429862</v>
+        <v>0.1220438460210599</v>
       </c>
       <c r="N205" s="14" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="16" t="n">
-        <v>0.3028750108572918</v>
+        <v>0.294665976178146</v>
       </c>
       <c r="Q205" s="20" t="inlineStr">
         <is>
@@ -16345,13 +16345,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>274.4</v>
+        <v>273.6</v>
       </c>
       <c r="E206" s="9" t="n">
-        <v>0.0539</v>
+        <v>0.0509</v>
       </c>
       <c r="F206" s="9" t="n">
-        <v>0.1264</v>
+        <v>0.1232</v>
       </c>
       <c r="G206" s="6" t="n">
         <v>46240</v>
@@ -16406,13 +16406,13 @@
         </is>
       </c>
       <c r="D207" s="15" t="n">
-        <v>422.5</v>
+        <v>429.02</v>
       </c>
       <c r="E207" s="16" t="n">
-        <v>0.07150000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="F207" s="16" t="n">
-        <v>0.0011</v>
+        <v>0.0165</v>
       </c>
       <c r="G207" s="17" t="n">
         <v>46261</v>
@@ -16467,13 +16467,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>56.2</v>
+        <v>55.13</v>
       </c>
       <c r="E208" s="9" t="n">
-        <v>0.2279</v>
+        <v>0.2045</v>
       </c>
       <c r="F208" s="9" t="n">
-        <v>0.1033</v>
+        <v>0.0823</v>
       </c>
       <c r="G208" s="6" t="n">
         <v>46268</v>
@@ -16528,13 +16528,13 @@
         </is>
       </c>
       <c r="D209" s="15" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="E209" s="16" t="n">
-        <v>0.0029</v>
+        <v>44.54</v>
+      </c>
+      <c r="E209" s="26" t="n">
+        <v>-0.0051</v>
       </c>
       <c r="F209" s="16" t="n">
-        <v>0.0382</v>
+        <v>0.0298</v>
       </c>
       <c r="G209" s="17" t="n">
         <v>46239</v>
@@ -16589,13 +16589,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>451.18</v>
+        <v>455.94</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>-0.0969</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="F210" s="5" t="n">
-        <v>-0.3688</v>
+        <v>-0.3621</v>
       </c>
       <c r="G210" s="6" t="n">
         <v>46251</v>
@@ -16650,13 +16650,13 @@
         </is>
       </c>
       <c r="D211" s="15" t="n">
-        <v>108.6</v>
+        <v>108.8</v>
       </c>
       <c r="E211" s="26" t="n">
-        <v>-0.1213</v>
+        <v>-0.1197</v>
       </c>
       <c r="F211" s="26" t="n">
-        <v>-0.1422</v>
+        <v>-0.1407</v>
       </c>
       <c r="G211" s="17" t="n"/>
       <c r="H211" s="22" t="inlineStr">
@@ -16701,13 +16701,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>162.98</v>
+        <v>163.21</v>
       </c>
       <c r="E212" s="9" t="n">
-        <v>0.0431</v>
+        <v>0.0445</v>
       </c>
       <c r="F212" s="9" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.09050000000000001</v>
       </c>
       <c r="G212" s="6" t="n"/>
       <c r="H212" s="12" t="inlineStr">
@@ -16752,13 +16752,13 @@
         </is>
       </c>
       <c r="D213" s="15" t="n">
-        <v>50.17</v>
+        <v>50.01</v>
       </c>
       <c r="E213" s="26" t="n">
-        <v>-0.2817</v>
+        <v>-0.2839</v>
       </c>
       <c r="F213" s="26" t="n">
-        <v>-0.4077</v>
+        <v>-0.4096</v>
       </c>
       <c r="G213" s="17" t="n">
         <v>46239</v>
@@ -16813,13 +16813,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>146.34</v>
+        <v>146.64</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>-0.2564</v>
+        <v>-0.2548</v>
       </c>
       <c r="F214" s="5" t="n">
-        <v>-0.2598</v>
+        <v>-0.2583</v>
       </c>
       <c r="G214" s="6" t="n"/>
       <c r="H214" s="12" t="inlineStr">
@@ -16864,13 +16864,13 @@
         </is>
       </c>
       <c r="D215" s="15" t="n">
-        <v>35.86</v>
+        <v>35.58</v>
       </c>
       <c r="E215" s="16" t="n">
-        <v>0.1182</v>
+        <v>0.1096</v>
       </c>
       <c r="F215" s="16" t="n">
-        <v>0.1628</v>
+        <v>0.1539</v>
       </c>
       <c r="G215" s="17" t="n">
         <v>46267</v>
@@ -16925,13 +16925,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>156.65</v>
+        <v>157.33</v>
       </c>
       <c r="E216" s="9" t="n">
-        <v>0.1649</v>
+        <v>0.17</v>
       </c>
       <c r="F216" s="9" t="n">
-        <v>0.0363</v>
+        <v>0.0407</v>
       </c>
       <c r="G216" s="6" t="n">
         <v>46268</v>
@@ -16960,7 +16960,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="9" t="n">
-        <v>0.2128949888285988</v>
+        <v>0.2076527045064513</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="8" t="n"/>
@@ -17004,13 +17004,13 @@
         </is>
       </c>
       <c r="D217" s="15" t="n">
-        <v>49.39</v>
+        <v>50.24</v>
       </c>
       <c r="E217" s="16" t="n">
-        <v>0.1979</v>
+        <v>0.2185</v>
       </c>
       <c r="F217" s="26" t="n">
-        <v>-0.0801</v>
+        <v>-0.0643</v>
       </c>
       <c r="G217" s="17" t="n">
         <v>46267</v>
@@ -17039,7 +17039,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="16" t="n">
-        <v>0.356549908888439</v>
+        <v>0.3335987261146496</v>
       </c>
       <c r="N217" s="14" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="16" t="n">
-        <v>0.4172909495849362</v>
+        <v>0.393312101910828</v>
       </c>
       <c r="Q217" s="20" t="inlineStr">
         <is>
@@ -17091,13 +17091,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>244.64</v>
+        <v>239.92</v>
       </c>
       <c r="E218" s="9" t="n">
-        <v>0.2734</v>
+        <v>0.2488</v>
       </c>
       <c r="F218" s="9" t="n">
-        <v>0.1101</v>
+        <v>0.08869999999999999</v>
       </c>
       <c r="G218" s="6" t="n">
         <v>46239</v>
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="D219" s="15" t="n">
-        <v>227.05</v>
+        <v>226.31</v>
       </c>
       <c r="E219" s="26" t="n">
-        <v>-0.2158</v>
+        <v>-0.2183</v>
       </c>
       <c r="F219" s="26" t="n">
-        <v>-0.2476</v>
+        <v>-0.2501</v>
       </c>
       <c r="G219" s="17" t="n">
         <v>46316</v>
@@ -17194,7 +17194,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="16" t="n">
-        <v>0.1010790574763267</v>
+        <v>0.1046794220317264</v>
       </c>
       <c r="Q219" s="20" t="inlineStr">
         <is>
@@ -17231,13 +17231,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>10.88</v>
+        <v>10.98</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>-0.1166</v>
+        <v>-0.108</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>-0.3584000000000001</v>
+        <v>-0.3522</v>
       </c>
       <c r="G220" s="6" t="n">
         <v>46246</v>
@@ -17292,13 +17292,13 @@
         </is>
       </c>
       <c r="D221" s="15" t="n">
-        <v>90.42</v>
+        <v>91</v>
       </c>
       <c r="E221" s="26" t="n">
-        <v>-0.2487</v>
+        <v>-0.2439</v>
       </c>
       <c r="F221" s="26" t="n">
-        <v>-0.1911</v>
+        <v>-0.1859</v>
       </c>
       <c r="G221" s="17" t="n">
         <v>46317</v>
@@ -17353,13 +17353,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>323.15</v>
+        <v>318.39</v>
       </c>
       <c r="E222" s="9" t="n">
-        <v>0.1736</v>
+        <v>0.1563</v>
       </c>
       <c r="F222" s="9" t="n">
-        <v>0.0701</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="G222" s="6" t="n">
         <v>46259</v>
@@ -17414,13 +17414,13 @@
         </is>
       </c>
       <c r="D223" s="15" t="n">
-        <v>39.79</v>
+        <v>38.85</v>
       </c>
       <c r="E223" s="26" t="n">
-        <v>-0.1899</v>
+        <v>-0.2091</v>
       </c>
       <c r="F223" s="26" t="n">
-        <v>-0.394</v>
+        <v>-0.4083</v>
       </c>
       <c r="G223" s="17" t="n">
         <v>46239</v>
@@ -17475,13 +17475,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>39.76</v>
+        <v>39.75</v>
       </c>
       <c r="E224" s="9" t="n">
-        <v>0.0242</v>
+        <v>0.024</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>-0.3573</v>
+        <v>-0.3574</v>
       </c>
       <c r="G224" s="6" t="n">
         <v>46261</v>
@@ -17536,13 +17536,13 @@
         </is>
       </c>
       <c r="D225" s="15" t="n">
-        <v>317.21</v>
+        <v>318.39</v>
       </c>
       <c r="E225" s="26" t="n">
-        <v>-0.0706</v>
+        <v>-0.06709999999999999</v>
       </c>
       <c r="F225" s="26" t="n">
-        <v>-0.1514</v>
+        <v>-0.1483</v>
       </c>
       <c r="G225" s="17" t="n">
         <v>46289</v>
@@ -17601,13 +17601,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>321.33</v>
+        <v>321.89</v>
       </c>
       <c r="E226" s="9" t="n">
-        <v>0.0238</v>
+        <v>0.0256</v>
       </c>
       <c r="F226" s="5" t="n">
-        <v>-0.0635</v>
+        <v>-0.06179999999999999</v>
       </c>
       <c r="G226" s="6" t="n">
         <v>46252</v>
@@ -17636,7 +17636,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="9" t="n">
-        <v>0.2137055363644852</v>
+        <v>0.2115940228028209</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="8" t="n"/>
@@ -17692,13 +17692,13 @@
         </is>
       </c>
       <c r="D227" s="15" t="n">
-        <v>179.51</v>
+        <v>182.75</v>
       </c>
       <c r="E227" s="26" t="n">
-        <v>-0.2379</v>
+        <v>-0.2242</v>
       </c>
       <c r="F227" s="26" t="n">
-        <v>-0.1577</v>
+        <v>-0.1425</v>
       </c>
       <c r="G227" s="17" t="n"/>
       <c r="H227" s="22" t="inlineStr">
@@ -17717,7 +17717,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="16" t="n">
-        <v>0.6990696897108797</v>
+        <v>0.6689466484268126</v>
       </c>
       <c r="N227" s="14" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="16" t="n">
-        <v>0.03058325441479589</v>
+        <v>0.01231190150478796</v>
       </c>
       <c r="Q227" s="20" t="inlineStr">
         <is>
@@ -17769,13 +17769,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>88.93000000000001</v>
+        <v>90.16</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>-0.267</v>
+        <v>-0.2569</v>
       </c>
       <c r="F228" s="5" t="n">
-        <v>-0.1729</v>
+        <v>-0.1615</v>
       </c>
       <c r="G228" s="6" t="n">
         <v>46239</v>
@@ -17830,13 +17830,13 @@
         </is>
       </c>
       <c r="D229" s="15" t="n">
-        <v>767.16</v>
+        <v>779.89</v>
       </c>
       <c r="E229" s="16" t="n">
-        <v>0.0533</v>
+        <v>0.0708</v>
       </c>
       <c r="F229" s="26" t="n">
-        <v>-0.1883</v>
+        <v>-0.1748</v>
       </c>
       <c r="G229" s="17" t="n">
         <v>46245</v>
@@ -17891,13 +17891,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>105.55</v>
+        <v>105.11</v>
       </c>
       <c r="E230" s="9" t="n">
-        <v>0.1229</v>
+        <v>0.1182</v>
       </c>
       <c r="F230" s="5" t="n">
-        <v>-0.1107</v>
+        <v>-0.1144</v>
       </c>
       <c r="G230" s="6" t="n"/>
       <c r="H230" s="12" t="inlineStr">
@@ -17942,13 +17942,13 @@
         </is>
       </c>
       <c r="D231" s="15" t="n">
-        <v>291.7</v>
+        <v>294.61</v>
       </c>
       <c r="E231" s="26" t="n">
-        <v>-0.1699</v>
+        <v>-0.1616</v>
       </c>
       <c r="F231" s="26" t="n">
-        <v>-0.1329</v>
+        <v>-0.1243</v>
       </c>
       <c r="G231" s="17" t="n"/>
       <c r="H231" s="22" t="inlineStr">
@@ -17967,7 +17967,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="16" t="n">
-        <v>0.5426808364758314</v>
+        <v>0.5274430603170293</v>
       </c>
       <c r="N231" s="14" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="16" t="n">
-        <v>0.2170037709976003</v>
+        <v>0.2049828586945453</v>
       </c>
       <c r="Q231" s="20" t="inlineStr">
         <is>
@@ -18023,13 +18023,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>74.68000000000001</v>
+        <v>75.22</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>-0.1177</v>
+        <v>-0.1113</v>
       </c>
       <c r="F232" s="5" t="n">
-        <v>-0.2245</v>
+        <v>-0.2189</v>
       </c>
       <c r="G232" s="6" t="n">
         <v>46240</v>
@@ -18084,13 +18084,13 @@
         </is>
       </c>
       <c r="D233" s="15" t="n">
-        <v>358.89</v>
+        <v>357.97</v>
       </c>
       <c r="E233" s="16" t="n">
-        <v>0.0113</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F233" s="26" t="n">
-        <v>-0.05599999999999999</v>
+        <v>-0.0584</v>
       </c>
       <c r="G233" s="17" t="n">
         <v>46259</v>
@@ -18145,13 +18145,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>308.61</v>
+        <v>309.98</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>-0.1558</v>
+        <v>-0.152</v>
       </c>
       <c r="F234" s="5" t="n">
-        <v>-0.0655</v>
+        <v>-0.0613</v>
       </c>
       <c r="G234" s="6" t="n">
         <v>46239</v>
@@ -18206,13 +18206,13 @@
         </is>
       </c>
       <c r="D235" s="15" t="n">
-        <v>1347.95</v>
+        <v>1344.37</v>
       </c>
       <c r="E235" s="16" t="n">
-        <v>0.0464</v>
+        <v>0.0436</v>
       </c>
       <c r="F235" s="26" t="n">
-        <v>-0.1843</v>
+        <v>-0.1865</v>
       </c>
       <c r="G235" s="17" t="n"/>
       <c r="H235" s="22" t="inlineStr">
@@ -18257,13 +18257,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>191.21</v>
+        <v>193.77</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>-0.2205</v>
+        <v>-0.21</v>
       </c>
       <c r="F236" s="5" t="n">
-        <v>-0.3957</v>
+        <v>-0.3876</v>
       </c>
       <c r="G236" s="6" t="n">
         <v>46261</v>
@@ -18292,7 +18292,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="9" t="n">
-        <v>0.2551644788452486</v>
+        <v>0.2385818238117355</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="9" t="n">
-        <v>0.3126928507923225</v>
+        <v>0.2953501574031067</v>
       </c>
       <c r="Q236" s="10" t="inlineStr">
         <is>
@@ -18344,13 +18344,13 @@
         </is>
       </c>
       <c r="D237" s="15" t="n">
-        <v>489.7</v>
+        <v>487.65</v>
       </c>
       <c r="E237" s="16" t="n">
-        <v>0.2541</v>
+        <v>0.2488</v>
       </c>
       <c r="F237" s="16" t="n">
-        <v>0.144</v>
+        <v>0.1392</v>
       </c>
       <c r="G237" s="17" t="n"/>
       <c r="H237" s="22" t="inlineStr">
@@ -18369,7 +18369,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="16" t="n">
-        <v>0.2762916071063917</v>
+        <v>0.2816569260740286</v>
       </c>
       <c r="N237" s="14" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="16" t="n">
-        <v>0.07208494996936902</v>
+        <v>0.07659181790218399</v>
       </c>
       <c r="Q237" s="20" t="inlineStr">
         <is>
@@ -18433,13 +18433,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>436.45</v>
+        <v>437.19</v>
       </c>
       <c r="E238" s="9" t="n">
-        <v>0.0326</v>
+        <v>0.0344</v>
       </c>
       <c r="F238" s="9" t="n">
-        <v>0.06269999999999999</v>
+        <v>0.0644</v>
       </c>
       <c r="G238" s="6" t="n">
         <v>46239</v>
@@ -18471,7 +18471,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="9" t="n">
-        <v>0.2028869286287089</v>
+        <v>0.2008508886296576</v>
       </c>
       <c r="Q238" s="10" t="inlineStr">
         <is>
@@ -18520,13 +18520,13 @@
         </is>
       </c>
       <c r="D239" s="15" t="n">
-        <v>95.45999999999999</v>
+        <v>94.86</v>
       </c>
       <c r="E239" s="26" t="n">
-        <v>-0.0527</v>
+        <v>-0.05860000000000001</v>
       </c>
       <c r="F239" s="26" t="n">
-        <v>-0.2621</v>
+        <v>-0.2668</v>
       </c>
       <c r="G239" s="17" t="n"/>
       <c r="H239" s="22" t="inlineStr">
@@ -18571,13 +18571,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>253.93</v>
+        <v>256.1</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>-0.212</v>
+        <v>-0.2053</v>
       </c>
       <c r="F240" s="5" t="n">
-        <v>-0.3365</v>
+        <v>-0.3309</v>
       </c>
       <c r="G240" s="6" t="n">
         <v>46240</v>
@@ -18632,13 +18632,13 @@
         </is>
       </c>
       <c r="D241" s="15" t="n">
-        <v>823.24</v>
+        <v>829.5</v>
       </c>
       <c r="E241" s="26" t="n">
-        <v>-0.1561</v>
+        <v>-0.1497</v>
       </c>
       <c r="F241" s="26" t="n">
-        <v>-0.1735</v>
+        <v>-0.1672</v>
       </c>
       <c r="G241" s="17" t="n">
         <v>46287</v>
@@ -18667,7 +18667,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="16" t="n">
-        <v>0.8524367134735922</v>
+        <v>0.838456901748041</v>
       </c>
       <c r="N241" s="14" t="inlineStr">
         <is>
@@ -18715,13 +18715,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>218.89</v>
-      </c>
-      <c r="E242" s="9" t="n">
-        <v>0.0152</v>
+        <v>212.58</v>
+      </c>
+      <c r="E242" s="5" t="n">
+        <v>-0.0141</v>
       </c>
       <c r="F242" s="5" t="n">
-        <v>-0.157</v>
+        <v>-0.1813</v>
       </c>
       <c r="G242" s="6" t="n">
         <v>46246</v>
@@ -18776,13 +18776,13 @@
         </is>
       </c>
       <c r="D243" s="15" t="n">
-        <v>283.95</v>
+        <v>282.74</v>
       </c>
       <c r="E243" s="16" t="n">
-        <v>0.1714</v>
+        <v>0.1664</v>
       </c>
       <c r="F243" s="16" t="n">
-        <v>0.057</v>
+        <v>0.0525</v>
       </c>
       <c r="G243" s="17" t="n">
         <v>46240</v>
@@ -18837,13 +18837,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>115.52</v>
+        <v>114.19</v>
       </c>
       <c r="E244" s="9" t="n">
-        <v>0.08650000000000001</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0433</v>
       </c>
       <c r="G244" s="6" t="n">
         <v>46323</v>
@@ -18872,7 +18872,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="9" t="n">
-        <v>0.3850415512465374</v>
+        <v>0.4011734827918382</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="9" t="n">
-        <v>0.2984764542936288</v>
+        <v>0.3136001401173483</v>
       </c>
       <c r="Q244" s="10" t="inlineStr">
         <is>
@@ -18928,13 +18928,13 @@
         </is>
       </c>
       <c r="D245" s="15" t="n">
-        <v>60.76</v>
+        <v>61.06</v>
       </c>
       <c r="E245" s="16" t="n">
-        <v>0.1849</v>
+        <v>0.1907</v>
       </c>
       <c r="F245" s="16" t="n">
-        <v>0.1053</v>
+        <v>0.1108</v>
       </c>
       <c r="G245" s="17" t="n">
         <v>46260</v>
@@ -18989,13 +18989,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>208.64</v>
+        <v>206.64</v>
       </c>
       <c r="E246" s="9" t="n">
-        <v>0.0709</v>
+        <v>0.06059999999999999</v>
       </c>
       <c r="F246" s="5" t="n">
-        <v>-0.0458</v>
+        <v>-0.055</v>
       </c>
       <c r="G246" s="6" t="n">
         <v>46260</v>
@@ -19024,7 +19024,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="9" t="n">
-        <v>0.5097776073619633</v>
+        <v>0.5243902439024392</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="9" t="n">
-        <v>0.9794861963190186</v>
+        <v>0.9986449864498647</v>
       </c>
       <c r="Q246" s="10" t="inlineStr">
         <is>
@@ -19084,13 +19084,13 @@
         </is>
       </c>
       <c r="D247" s="15" t="n">
-        <v>391.04</v>
+        <v>393.69</v>
       </c>
       <c r="E247" s="26" t="n">
-        <v>-0.1682</v>
+        <v>-0.1626</v>
       </c>
       <c r="F247" s="26" t="n">
-        <v>-0.2486</v>
+        <v>-0.2435</v>
       </c>
       <c r="G247" s="17" t="n">
         <v>46240</v>
@@ -19145,13 +19145,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>221.76</v>
+        <v>224.17</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>-0.1888</v>
+        <v>-0.1799</v>
       </c>
       <c r="F248" s="5" t="n">
-        <v>-0.3118</v>
+        <v>-0.3043</v>
       </c>
       <c r="G248" s="6" t="n"/>
       <c r="H248" s="12" t="inlineStr">
@@ -19192,13 +19192,13 @@
         </is>
       </c>
       <c r="D249" s="15" t="n">
-        <v>10.41</v>
+        <v>10.81</v>
       </c>
       <c r="E249" s="26" t="n">
-        <v>-0.366</v>
+        <v>-0.3415</v>
       </c>
       <c r="F249" s="26" t="n">
-        <v>-0.5653</v>
+        <v>-0.5486</v>
       </c>
       <c r="G249" s="17" t="n"/>
       <c r="H249" s="22" t="inlineStr">
@@ -19243,13 +19243,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>143.49</v>
+        <v>141.57</v>
       </c>
       <c r="E250" s="9" t="n">
-        <v>0.0146</v>
+        <v>0.0011</v>
       </c>
       <c r="F250" s="9" t="n">
-        <v>0.162</v>
+        <v>0.1465</v>
       </c>
       <c r="G250" s="6" t="n">
         <v>46259</v>
@@ -19278,7 +19278,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="9" t="n">
-        <v>0.04536901526238755</v>
+        <v>0.05954651409196869</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="5" t="n">
-        <v>-0.09401352010593078</v>
+        <v>-0.08172635445362714</v>
       </c>
       <c r="Q250" s="10" t="inlineStr">
         <is>
@@ -19330,13 +19330,13 @@
         </is>
       </c>
       <c r="D251" s="15" t="n">
-        <v>81.28</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E251" s="26" t="n">
-        <v>-0.109</v>
+        <v>-0.1186</v>
       </c>
       <c r="F251" s="26" t="n">
-        <v>-0.3834</v>
+        <v>-0.3901</v>
       </c>
       <c r="G251" s="17" t="n">
         <v>46237</v>
@@ -19391,13 +19391,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>269.78</v>
+        <v>268.49</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>-0.1229</v>
+        <v>-0.1271</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>-0.0181</v>
+        <v>-0.0228</v>
       </c>
       <c r="G252" s="6" t="n">
         <v>46240</v>
@@ -19452,13 +19452,13 @@
         </is>
       </c>
       <c r="D253" s="15" t="n">
-        <v>140.12</v>
-      </c>
-      <c r="E253" s="26" t="n">
-        <v>-0.0011</v>
+        <v>141.85</v>
+      </c>
+      <c r="E253" s="16" t="n">
+        <v>0.0113</v>
       </c>
       <c r="F253" s="26" t="n">
-        <v>-0.4071</v>
+        <v>-0.3998</v>
       </c>
       <c r="G253" s="17" t="n">
         <v>46273</v>
@@ -19487,7 +19487,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="16" t="n">
-        <v>0.9982871824150727</v>
+        <v>0.973916108565386</v>
       </c>
       <c r="N253" s="14" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="16" t="n">
-        <v>0.7485012846131887</v>
+        <v>0.7271765949947128</v>
       </c>
       <c r="Q253" s="20" t="inlineStr">
         <is>
@@ -19539,13 +19539,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>343.03</v>
+        <v>347.13</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>-0.0145</v>
+        <v>-0.0027</v>
       </c>
       <c r="F254" s="9" t="n">
-        <v>0.2284</v>
+        <v>0.2431</v>
       </c>
       <c r="G254" s="6" t="n">
         <v>46251</v>
@@ -19574,7 +19574,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="9" t="n">
-        <v>0.2243827070518614</v>
+        <v>0.2099213551119177</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="9" t="n">
-        <v>0.2098067224441012</v>
+        <v>0.1955175294558235</v>
       </c>
       <c r="Q254" s="10" t="inlineStr">
         <is>
@@ -19634,13 +19634,13 @@
         </is>
       </c>
       <c r="D255" s="15" t="n">
-        <v>13.09</v>
+        <v>13.05</v>
       </c>
       <c r="E255" s="16" t="n">
-        <v>0.1174</v>
+        <v>0.1144</v>
       </c>
       <c r="F255" s="16" t="n">
-        <v>0.1213</v>
+        <v>0.1183</v>
       </c>
       <c r="G255" s="17" t="n">
         <v>46268</v>
@@ -19695,13 +19695,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>31.52</v>
+        <v>31.37</v>
       </c>
       <c r="E256" s="9" t="n">
-        <v>0.0151</v>
+        <v>0.0103</v>
       </c>
       <c r="F256" s="5" t="n">
-        <v>-0.1106</v>
+        <v>-0.1148</v>
       </c>
       <c r="G256" s="6" t="n">
         <v>46315</v>
@@ -19756,13 +19756,13 @@
         </is>
       </c>
       <c r="D257" s="15" t="n">
-        <v>158.91</v>
+        <v>161.44</v>
       </c>
       <c r="E257" s="16" t="n">
-        <v>0.1224</v>
+        <v>0.1403</v>
       </c>
       <c r="F257" s="16" t="n">
-        <v>0.1669</v>
+        <v>0.1855</v>
       </c>
       <c r="G257" s="17" t="n"/>
       <c r="H257" s="22" t="inlineStr">
@@ -19807,13 +19807,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>125.59</v>
+        <v>125.65</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>-0.0287</v>
+        <v>-0.0282</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>-0.1137</v>
+        <v>-0.1133</v>
       </c>
       <c r="G258" s="6" t="n">
         <v>46237</v>
@@ -19868,13 +19868,13 @@
         </is>
       </c>
       <c r="D259" s="15" t="n">
-        <v>133.63</v>
+        <v>133.3</v>
       </c>
       <c r="E259" s="26" t="n">
-        <v>-0.0572</v>
+        <v>-0.0596</v>
       </c>
       <c r="F259" s="26" t="n">
-        <v>-0.1367</v>
+        <v>-0.1389</v>
       </c>
       <c r="G259" s="17" t="n">
         <v>46238</v>
@@ -19939,13 +19939,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>20.04</v>
+        <v>19.98</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>-0.1105</v>
+        <v>-0.1132</v>
       </c>
       <c r="F260" s="5" t="n">
-        <v>-0.275</v>
+        <v>-0.2771</v>
       </c>
       <c r="G260" s="6" t="n">
         <v>46240</v>
@@ -20000,13 +20000,13 @@
         </is>
       </c>
       <c r="D261" s="15" t="n">
-        <v>149.68</v>
+        <v>151.57</v>
       </c>
       <c r="E261" s="26" t="n">
-        <v>-0.1508</v>
+        <v>-0.14</v>
       </c>
       <c r="F261" s="26" t="n">
-        <v>-0.3829</v>
+        <v>-0.3751</v>
       </c>
       <c r="G261" s="17" t="n"/>
       <c r="H261" s="22" t="inlineStr">
@@ -20025,7 +20025,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="16" t="n">
-        <v>0.7704436130411544</v>
+        <v>0.7483670911130171</v>
       </c>
       <c r="N261" s="14" t="inlineStr">
         <is>
@@ -20036,7 +20036,7 @@
         <v>179</v>
       </c>
       <c r="P261" s="16" t="n">
-        <v>0.1958845537145911</v>
+        <v>0.1809724879593588</v>
       </c>
       <c r="Q261" s="20" t="inlineStr">
         <is>
@@ -20081,13 +20081,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>88.81</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="E262" s="9" t="n">
-        <v>0.0142</v>
+        <v>0.0219</v>
       </c>
       <c r="F262" s="5" t="n">
-        <v>-0.1458</v>
+        <v>-0.1393</v>
       </c>
       <c r="G262" s="6" t="n"/>
       <c r="H262" s="12" t="inlineStr">
@@ -20132,13 +20132,13 @@
         </is>
       </c>
       <c r="D263" s="15" t="n">
-        <v>8.68</v>
+        <v>8.74</v>
       </c>
       <c r="E263" s="26" t="n">
-        <v>-0.0414</v>
+        <v>-0.0343</v>
       </c>
       <c r="F263" s="26" t="n">
-        <v>-0.2248</v>
+        <v>-0.2189</v>
       </c>
       <c r="G263" s="17" t="n">
         <v>46244</v>
@@ -20193,13 +20193,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>74.04000000000001</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>-0.1148</v>
+        <v>-0.1064</v>
       </c>
       <c r="F264" s="5" t="n">
-        <v>-0.0384</v>
+        <v>-0.0294</v>
       </c>
       <c r="G264" s="6" t="n">
         <v>46273</v>
@@ -20254,13 +20254,13 @@
         </is>
       </c>
       <c r="D265" s="15" t="n">
-        <v>16.13</v>
+        <v>16.02</v>
       </c>
       <c r="E265" s="26" t="n">
-        <v>-0.1009</v>
+        <v>-0.107</v>
       </c>
       <c r="F265" s="26" t="n">
-        <v>-0.3324</v>
+        <v>-0.3369</v>
       </c>
       <c r="G265" s="17" t="n">
         <v>46240</v>
@@ -20315,13 +20315,13 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>391.94</v>
+        <v>392.57</v>
       </c>
       <c r="E266" s="9" t="n">
-        <v>0.0762</v>
+        <v>0.0779</v>
       </c>
       <c r="F266" s="9" t="n">
-        <v>0.1813</v>
+        <v>0.1832</v>
       </c>
       <c r="G266" s="6" t="n">
         <v>46317</v>
@@ -20390,13 +20390,13 @@
         </is>
       </c>
       <c r="D267" s="15" t="n">
-        <v>4.57</v>
+        <v>4.77</v>
       </c>
       <c r="E267" s="26" t="n">
-        <v>-0.2002</v>
+        <v>-0.1661</v>
       </c>
       <c r="F267" s="26" t="n">
-        <v>-0.1816</v>
+        <v>-0.1467</v>
       </c>
       <c r="G267" s="17" t="n">
         <v>46245</v>
@@ -20451,13 +20451,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>19.88</v>
+        <v>20.05</v>
       </c>
       <c r="E268" s="9" t="n">
-        <v>0.1351</v>
+        <v>0.1451</v>
       </c>
       <c r="F268" s="9" t="n">
-        <v>0.2024</v>
+        <v>0.2129</v>
       </c>
       <c r="G268" s="6" t="n">
         <v>46261</v>
@@ -20512,13 +20512,13 @@
         </is>
       </c>
       <c r="D269" s="15" t="n">
-        <v>17.11</v>
+        <v>17.2</v>
       </c>
       <c r="E269" s="16" t="n">
-        <v>0.1205</v>
+        <v>0.1264</v>
       </c>
       <c r="F269" s="26" t="n">
-        <v>-0.0806</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="G269" s="17" t="n">
         <v>46273</v>
@@ -20573,13 +20573,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>189.9</v>
+        <v>193.23</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>-0.1359</v>
+        <v>-0.1208</v>
       </c>
       <c r="F270" s="5" t="n">
-        <v>-0.3221</v>
+        <v>-0.3102</v>
       </c>
       <c r="G270" s="6" t="n"/>
       <c r="H270" s="12" t="inlineStr">
@@ -20624,13 +20624,13 @@
         </is>
       </c>
       <c r="D271" s="15" t="n">
-        <v>190.13</v>
+        <v>189.65</v>
       </c>
       <c r="E271" s="16" t="n">
-        <v>0.1694</v>
+        <v>0.1664</v>
       </c>
       <c r="F271" s="16" t="n">
-        <v>0.016</v>
+        <v>0.0134</v>
       </c>
       <c r="G271" s="17" t="n">
         <v>46316</v>
@@ -20705,13 +20705,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>28.69</v>
+        <v>28.64</v>
       </c>
       <c r="E272" s="9" t="n">
-        <v>0.0542</v>
+        <v>0.0522</v>
       </c>
       <c r="F272" s="5" t="n">
-        <v>-0.3882</v>
+        <v>-0.3893</v>
       </c>
       <c r="G272" s="6" t="n">
         <v>46245</v>
@@ -20766,13 +20766,13 @@
         </is>
       </c>
       <c r="D273" s="15" t="n">
-        <v>309.74</v>
+        <v>307.53</v>
       </c>
       <c r="E273" s="16" t="n">
-        <v>0.1906</v>
+        <v>0.1821</v>
       </c>
       <c r="F273" s="16" t="n">
-        <v>0.2685</v>
+        <v>0.2594</v>
       </c>
       <c r="G273" s="17" t="n">
         <v>46260</v>
@@ -20801,7 +20801,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="16" t="n">
-        <v>0.03312455607929228</v>
+        <v>0.04054888953923204</v>
       </c>
       <c r="N273" s="14" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="26" t="n">
-        <v>-0.09601601343061926</v>
+        <v>-0.08951972165317197</v>
       </c>
       <c r="Q273" s="20" t="inlineStr">
         <is>
@@ -20853,13 +20853,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>390.79</v>
+        <v>392.07</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>-0.1061</v>
+        <v>-0.1031</v>
       </c>
       <c r="F274" s="5" t="n">
-        <v>-0.2097</v>
+        <v>-0.2071</v>
       </c>
       <c r="G274" s="6" t="n">
         <v>46260</v>
@@ -20888,7 +20888,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="9" t="n">
-        <v>0.3690217252232656</v>
+        <v>0.3645522483230036</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="8" t="n"/>
@@ -20932,13 +20932,13 @@
         </is>
       </c>
       <c r="D275" s="15" t="n">
-        <v>6.14</v>
+        <v>6.1</v>
       </c>
       <c r="E275" s="26" t="n">
-        <v>-0.0626</v>
+        <v>-0.0687</v>
       </c>
       <c r="F275" s="26" t="n">
-        <v>-0.2335</v>
+        <v>-0.2385</v>
       </c>
       <c r="G275" s="17" t="n">
         <v>46239</v>
@@ -20993,13 +20993,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>60.44</v>
+        <v>61.29</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>-0.0339</v>
+        <v>-0.0203</v>
       </c>
       <c r="F276" s="5" t="n">
-        <v>-0.2438</v>
+        <v>-0.2332</v>
       </c>
       <c r="G276" s="6" t="n"/>
       <c r="H276" s="12" t="inlineStr">
@@ -21044,13 +21044,13 @@
         </is>
       </c>
       <c r="D277" s="15" t="n">
-        <v>106.39</v>
+        <v>105.72</v>
       </c>
       <c r="E277" s="26" t="n">
-        <v>-0.1099</v>
+        <v>-0.1155</v>
       </c>
       <c r="F277" s="26" t="n">
-        <v>-0.2459</v>
+        <v>-0.2507</v>
       </c>
       <c r="G277" s="17" t="n">
         <v>46240</v>
@@ -21105,13 +21105,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>201.44</v>
+        <v>204.97</v>
       </c>
       <c r="E278" s="9" t="n">
-        <v>0.0203</v>
+        <v>0.0381</v>
       </c>
       <c r="F278" s="5" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.07150000000000001</v>
       </c>
       <c r="G278" s="6" t="n">
         <v>46330</v>
@@ -21166,13 +21166,13 @@
         </is>
       </c>
       <c r="D279" s="15" t="n">
-        <v>360.84</v>
+        <v>365.8</v>
       </c>
       <c r="E279" s="26" t="n">
-        <v>-0.0224</v>
+        <v>-0.0089</v>
       </c>
       <c r="F279" s="26" t="n">
-        <v>-0.1131</v>
+        <v>-0.1009</v>
       </c>
       <c r="G279" s="17" t="n"/>
       <c r="H279" s="22" t="inlineStr">
@@ -21217,13 +21217,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>57.33</v>
+        <v>57.79</v>
       </c>
       <c r="E280" s="9" t="n">
-        <v>0.0809</v>
+        <v>0.08960000000000001</v>
       </c>
       <c r="F280" s="9" t="n">
-        <v>0.0293</v>
+        <v>0.0375</v>
       </c>
       <c r="G280" s="6" t="n">
         <v>46239</v>
@@ -21278,13 +21278,13 @@
         </is>
       </c>
       <c r="D281" s="15" t="n">
-        <v>403.36</v>
+        <v>406.11</v>
       </c>
       <c r="E281" s="26" t="n">
-        <v>-0.0709</v>
+        <v>-0.0646</v>
       </c>
       <c r="F281" s="26" t="n">
-        <v>-0.0934</v>
+        <v>-0.0872</v>
       </c>
       <c r="G281" s="17" t="n">
         <v>46310</v>
@@ -21361,13 +21361,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>119.71</v>
+        <v>121.21</v>
       </c>
       <c r="E282" s="5" t="n">
-        <v>-0.2325</v>
+        <v>-0.2229</v>
       </c>
       <c r="F282" s="5" t="n">
-        <v>-0.3524</v>
+        <v>-0.3442</v>
       </c>
       <c r="G282" s="6" t="n">
         <v>46239</v>
@@ -21422,13 +21422,13 @@
         </is>
       </c>
       <c r="D283" s="15" t="n">
-        <v>198.88</v>
+        <v>196.59</v>
       </c>
       <c r="E283" s="26" t="n">
-        <v>-0.0498</v>
+        <v>-0.0608</v>
       </c>
       <c r="F283" s="26" t="n">
-        <v>-0.1596</v>
+        <v>-0.1692</v>
       </c>
       <c r="G283" s="17" t="n">
         <v>46240</v>
@@ -21483,13 +21483,13 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>267.58</v>
+        <v>269.04</v>
       </c>
       <c r="E284" s="5" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.08199999999999999</v>
       </c>
       <c r="F284" s="5" t="n">
-        <v>-0.1238</v>
+        <v>-0.119</v>
       </c>
       <c r="G284" s="6" t="n">
         <v>46315</v>
@@ -21518,7 +21518,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="9" t="n">
-        <v>0.1211600269078407</v>
+        <v>0.1150758251561105</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="9" t="n">
-        <v>0.1809552283429255</v>
+        <v>0.1745465358311031</v>
       </c>
       <c r="Q284" s="10" t="inlineStr">
         <is>
@@ -21586,13 +21586,13 @@
         </is>
       </c>
       <c r="D285" s="15" t="n">
-        <v>309.44</v>
+        <v>305.54</v>
       </c>
       <c r="E285" s="26" t="n">
-        <v>-0.0272</v>
-      </c>
-      <c r="F285" s="16" t="n">
-        <v>0.0042</v>
+        <v>-0.0395</v>
+      </c>
+      <c r="F285" s="26" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="G285" s="17" t="n"/>
       <c r="H285" s="22" t="inlineStr">
@@ -21611,7 +21611,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="16" t="n">
-        <v>0.08260082730093073</v>
+        <v>0.09641945408129861</v>
       </c>
       <c r="N285" s="14" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="16" t="n">
-        <v>0.2118665977249224</v>
+        <v>0.2273352097924984</v>
       </c>
       <c r="Q285" s="20" t="inlineStr">
         <is>
@@ -21663,13 +21663,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>33.3</v>
+        <v>33.38</v>
       </c>
       <c r="E286" s="9" t="n">
-        <v>0.1357</v>
+        <v>0.1385</v>
       </c>
       <c r="F286" s="9" t="n">
-        <v>0.1089</v>
+        <v>0.1116</v>
       </c>
       <c r="G286" s="6" t="n">
         <v>46240</v>
@@ -21724,13 +21724,13 @@
         </is>
       </c>
       <c r="D287" s="15" t="n">
-        <v>7.14</v>
+        <v>7.15</v>
       </c>
       <c r="E287" s="26" t="n">
-        <v>-0.09849999999999999</v>
+        <v>-0.09720000000000001</v>
       </c>
       <c r="F287" s="26" t="n">
-        <v>-0.2647</v>
+        <v>-0.2636</v>
       </c>
       <c r="G287" s="17" t="n">
         <v>46254</v>
@@ -21785,13 +21785,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>165.01</v>
+        <v>165.05</v>
       </c>
       <c r="E288" s="9" t="n">
-        <v>0.2187</v>
+        <v>0.219</v>
       </c>
       <c r="F288" s="9" t="n">
-        <v>0.1156</v>
+        <v>0.1159</v>
       </c>
       <c r="G288" s="6" t="n">
         <v>46254</v>
@@ -21846,13 +21846,13 @@
         </is>
       </c>
       <c r="D289" s="15" t="n">
-        <v>527.6</v>
+        <v>527.22</v>
       </c>
       <c r="E289" s="26" t="n">
-        <v>-0.0212</v>
+        <v>-0.0219</v>
       </c>
       <c r="F289" s="26" t="n">
-        <v>-0.0832</v>
+        <v>-0.0839</v>
       </c>
       <c r="G289" s="17" t="n">
         <v>46239</v>
@@ -21881,7 +21881,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="16" t="n">
-        <v>0.3836239575435936</v>
+        <v>0.3846212207427638</v>
       </c>
       <c r="N289" s="14" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="16" t="n">
-        <v>0.08984078847611822</v>
+        <v>0.09062630400971126</v>
       </c>
       <c r="Q289" s="20" t="inlineStr">
         <is>
@@ -21933,13 +21933,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>25.15</v>
+        <v>24.35</v>
       </c>
       <c r="E290" s="5" t="n">
-        <v>-0.3713</v>
+        <v>-0.3912</v>
       </c>
       <c r="F290" s="5" t="n">
-        <v>-0.625</v>
+        <v>-0.6369</v>
       </c>
       <c r="G290" s="6" t="n">
         <v>46238</v>
@@ -21994,13 +21994,13 @@
         </is>
       </c>
       <c r="D291" s="15" t="n">
-        <v>98.36</v>
+        <v>98.25</v>
       </c>
       <c r="E291" s="16" t="n">
-        <v>0.1286</v>
+        <v>0.1274</v>
       </c>
       <c r="F291" s="26" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="G291" s="17" t="n">
         <v>46259</v>
@@ -22055,13 +22055,13 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>154.68</v>
+        <v>154.46</v>
       </c>
       <c r="E292" s="9" t="n">
-        <v>0.0499</v>
+        <v>0.0484</v>
       </c>
       <c r="F292" s="9" t="n">
-        <v>0.1436</v>
+        <v>0.1419</v>
       </c>
       <c r="G292" s="6" t="n">
         <v>46266</v>
@@ -22116,13 +22116,13 @@
         </is>
       </c>
       <c r="D293" s="15" t="n">
-        <v>290.56</v>
+        <v>292.94</v>
       </c>
       <c r="E293" s="26" t="n">
-        <v>-0.07519999999999999</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="F293" s="16" t="n">
-        <v>0.0273</v>
+        <v>0.0357</v>
       </c>
       <c r="G293" s="17" t="n"/>
       <c r="H293" s="22" t="inlineStr">
@@ -22167,13 +22167,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>83.37</v>
+        <v>83.5</v>
       </c>
       <c r="E294" s="9" t="n">
-        <v>0.0005</v>
+        <v>0.002</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>-0.0609</v>
+        <v>-0.0595</v>
       </c>
       <c r="G294" s="6" t="n">
         <v>46252</v>
@@ -22228,13 +22228,13 @@
         </is>
       </c>
       <c r="D295" s="15" t="n">
-        <v>138.92</v>
-      </c>
-      <c r="E295" s="26" t="n">
-        <v>-0.0071</v>
+        <v>141.28</v>
+      </c>
+      <c r="E295" s="16" t="n">
+        <v>0.0098</v>
       </c>
       <c r="F295" s="26" t="n">
-        <v>-0.0282</v>
+        <v>-0.0117</v>
       </c>
       <c r="G295" s="17" t="n">
         <v>46238</v>
@@ -22263,7 +22263,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="16" t="n">
-        <v>0.194932335156925</v>
+        <v>0.1749716874292186</v>
       </c>
       <c r="N295" s="14" t="inlineStr"/>
       <c r="O295" s="19" t="n"/>
@@ -22311,13 +22311,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>30.27</v>
+        <v>29.89</v>
       </c>
       <c r="E296" s="9" t="n">
-        <v>0.0924</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="F296" s="5" t="n">
-        <v>-0.1299</v>
+        <v>-0.1408</v>
       </c>
       <c r="G296" s="6" t="n">
         <v>46317</v>
@@ -22372,13 +22372,13 @@
         </is>
       </c>
       <c r="D297" s="15" t="n">
-        <v>277.24</v>
+        <v>279.43</v>
       </c>
       <c r="E297" s="26" t="n">
-        <v>-0.0216</v>
+        <v>-0.0139</v>
       </c>
       <c r="F297" s="16" t="n">
-        <v>0.0901</v>
+        <v>0.0987</v>
       </c>
       <c r="G297" s="17" t="n"/>
       <c r="H297" s="22" t="inlineStr">
@@ -22397,7 +22397,7 @@
         <v>275</v>
       </c>
       <c r="M297" s="26" t="n">
-        <v>-0.008079642187274597</v>
+        <v>-0.01585370217943673</v>
       </c>
       <c r="N297" s="14" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="16" t="n">
-        <v>0.1253787332275285</v>
+        <v>0.1165587088000572</v>
       </c>
       <c r="Q297" s="20" t="inlineStr">
         <is>
@@ -22461,13 +22461,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>36.99</v>
+        <v>37.69</v>
       </c>
       <c r="E298" s="5" t="n">
-        <v>-0.1524</v>
+        <v>-0.1363</v>
       </c>
       <c r="F298" s="5" t="n">
-        <v>-0.1195</v>
+        <v>-0.1028</v>
       </c>
       <c r="G298" s="6" t="n"/>
       <c r="H298" s="12" t="inlineStr">
@@ -22516,13 +22516,13 @@
         </is>
       </c>
       <c r="D299" s="15" t="n">
-        <v>63.04</v>
+        <v>63.64</v>
       </c>
       <c r="E299" s="16" t="n">
-        <v>0.034</v>
+        <v>0.0438</v>
       </c>
       <c r="F299" s="26" t="n">
-        <v>-0.09539999999999998</v>
+        <v>-0.0868</v>
       </c>
       <c r="G299" s="17" t="n">
         <v>46310</v>
@@ -22577,13 +22577,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>477</v>
+        <v>480.46</v>
       </c>
       <c r="E300" s="5" t="n">
-        <v>-0.1274</v>
+        <v>-0.1211</v>
       </c>
       <c r="F300" s="5" t="n">
-        <v>-0.06</v>
+        <v>-0.0532</v>
       </c>
       <c r="G300" s="6" t="n"/>
       <c r="H300" s="12" t="inlineStr">
@@ -22602,7 +22602,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="9" t="n">
-        <v>0.1949685534591195</v>
+        <v>0.1863630687258045</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="9" t="n">
-        <v>0.1006289308176101</v>
+        <v>0.09270282645797782</v>
       </c>
       <c r="Q300" s="10" t="inlineStr">
         <is>
@@ -22666,13 +22666,13 @@
         </is>
       </c>
       <c r="D301" s="15" t="n">
-        <v>544.23</v>
+        <v>542.27</v>
       </c>
       <c r="E301" s="26" t="n">
-        <v>-0.09210000000000002</v>
+        <v>-0.0953</v>
       </c>
       <c r="F301" s="26" t="n">
-        <v>-0.06309999999999999</v>
+        <v>-0.0664</v>
       </c>
       <c r="G301" s="17" t="n"/>
       <c r="H301" s="22" t="inlineStr">
@@ -22691,7 +22691,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="16" t="n">
-        <v>0.1318743913418959</v>
+        <v>0.1359654784516938</v>
       </c>
       <c r="N301" s="14" t="inlineStr"/>
       <c r="O301" s="19" t="n"/>
@@ -22735,13 +22735,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>258.57</v>
+        <v>261.28</v>
       </c>
       <c r="E302" s="9" t="n">
-        <v>0.1713</v>
+        <v>0.1836</v>
       </c>
       <c r="F302" s="5" t="n">
-        <v>-0.0141</v>
+        <v>-0.0038</v>
       </c>
       <c r="G302" s="6" t="n"/>
       <c r="H302" s="12" t="inlineStr">
@@ -22760,7 +22760,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="9" t="n">
-        <v>0.09448118497892256</v>
+        <v>0.083129210042866</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="8" t="n"/>
@@ -22806,13 +22806,13 @@
         </is>
       </c>
       <c r="D303" s="15" t="n">
-        <v>247.3</v>
+        <v>251.09</v>
       </c>
       <c r="E303" s="16" t="n">
-        <v>0.0382</v>
+        <v>0.0541</v>
       </c>
       <c r="F303" s="16" t="n">
-        <v>0.1006</v>
+        <v>0.1175</v>
       </c>
       <c r="G303" s="17" t="n">
         <v>46321</v>
@@ -22841,7 +22841,7 @@
         <v>246</v>
       </c>
       <c r="M303" s="26" t="n">
-        <v>-0.005256773150020264</v>
+        <v>-0.02027161575530688</v>
       </c>
       <c r="N303" s="14" t="inlineStr"/>
       <c r="O303" s="19" t="n"/>
@@ -22889,13 +22889,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>112.58</v>
+        <v>114.01</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>-0.1017</v>
+        <v>-0.09029999999999999</v>
       </c>
       <c r="F304" s="9" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0183</v>
       </c>
       <c r="G304" s="6" t="n"/>
       <c r="H304" s="12" t="inlineStr">
@@ -22914,7 +22914,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="9" t="n">
-        <v>0.1547344110854504</v>
+        <v>0.1402508551881413</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="9" t="n">
-        <v>0.1369692662995204</v>
+        <v>0.122708534339093</v>
       </c>
       <c r="Q304" s="10" t="inlineStr">
         <is>
@@ -22974,13 +22974,13 @@
         </is>
       </c>
       <c r="D305" s="15" t="n">
-        <v>109.63</v>
+        <v>111.49</v>
       </c>
       <c r="E305" s="26" t="n">
-        <v>-0.0178</v>
+        <v>-0.0012</v>
       </c>
       <c r="F305" s="16" t="n">
-        <v>0.0524</v>
+        <v>0.0703</v>
       </c>
       <c r="G305" s="17" t="n">
         <v>46302</v>
@@ -23009,7 +23009,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="16" t="n">
-        <v>0.2314147587339233</v>
+        <v>0.2108709301282627</v>
       </c>
       <c r="N305" s="14" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="16" t="n">
-        <v>0.1401988506795586</v>
+        <v>0.1211767871557988</v>
       </c>
       <c r="Q305" s="20" t="inlineStr"/>
       <c r="R305" s="19" t="n"/>
@@ -23055,13 +23055,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>349.85</v>
-      </c>
-      <c r="E306" s="5" t="n">
-        <v>-0.0075</v>
+        <v>354.22</v>
+      </c>
+      <c r="E306" s="9" t="n">
+        <v>0.0049</v>
       </c>
       <c r="F306" s="9" t="n">
-        <v>0.1658</v>
+        <v>0.1804</v>
       </c>
       <c r="G306" s="6" t="n"/>
       <c r="H306" s="12" t="inlineStr">
@@ -23079,8 +23079,8 @@
       <c r="L306" s="8" t="n">
         <v>350</v>
       </c>
-      <c r="M306" s="9" t="n">
-        <v>0.0004287551807917029</v>
+      <c r="M306" s="5" t="n">
+        <v>-0.0119135000846932</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="9" t="n">
-        <v>0.1433471487780477</v>
+        <v>0.1292417141889221</v>
       </c>
       <c r="Q306" s="10" t="inlineStr">
         <is>
@@ -23132,13 +23132,13 @@
         </is>
       </c>
       <c r="D307" s="15" t="n">
-        <v>80</v>
+        <v>80.14</v>
       </c>
       <c r="E307" s="16" t="n">
-        <v>0.1002</v>
+        <v>0.1022</v>
       </c>
       <c r="F307" s="16" t="n">
-        <v>0.0189</v>
+        <v>0.0208</v>
       </c>
       <c r="G307" s="17" t="n">
         <v>46260</v>
@@ -23189,13 +23189,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>53.76</v>
+        <v>55.65</v>
       </c>
       <c r="E308" s="5" t="n">
-        <v>-0.2789</v>
+        <v>-0.2536</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>-0.1096</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="G308" s="6" t="n">
         <v>46245</v>
@@ -23250,13 +23250,13 @@
         </is>
       </c>
       <c r="D309" s="15" t="n">
-        <v>76.55</v>
+        <v>76.91</v>
       </c>
       <c r="E309" s="26" t="n">
-        <v>-0.0162</v>
+        <v>-0.0116</v>
       </c>
       <c r="F309" s="16" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.06480000000000001</v>
       </c>
       <c r="G309" s="17" t="n"/>
       <c r="H309" s="22" t="inlineStr">
@@ -23275,14 +23275,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="16" t="n">
-        <v>0.0842586544741999</v>
+        <v>0.07918346118840208</v>
       </c>
       <c r="N309" s="14" t="inlineStr"/>
       <c r="O309" s="19" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="16" t="n">
-        <v>0.1365120836054866</v>
+        <v>0.1311923026914576</v>
       </c>
       <c r="Q309" s="20" t="inlineStr"/>
       <c r="R309" s="19" t="n"/>
@@ -23317,13 +23317,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>172.36</v>
+        <v>173</v>
       </c>
       <c r="E310" s="9" t="n">
-        <v>0.0381</v>
+        <v>0.042</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>-0.1111</v>
+        <v>-0.1078</v>
       </c>
       <c r="G310" s="6" t="n"/>
       <c r="H310" s="12" t="inlineStr">
@@ -23342,7 +23342,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="9" t="n">
-        <v>0.1603620329542816</v>
+        <v>0.1560693641618497</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="8" t="n"/>
@@ -23390,13 +23390,13 @@
         </is>
       </c>
       <c r="D311" s="15" t="n">
-        <v>146.57</v>
+        <v>148.43</v>
       </c>
       <c r="E311" s="16" t="n">
-        <v>0.0352</v>
+        <v>0.0484</v>
       </c>
       <c r="F311" s="16" t="n">
-        <v>0.1193</v>
+        <v>0.1335</v>
       </c>
       <c r="G311" s="17" t="n"/>
       <c r="H311" s="22" t="inlineStr">
@@ -23445,13 +23445,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>191.24</v>
+        <v>191.22</v>
       </c>
       <c r="E312" s="9" t="n">
-        <v>0.1035</v>
+        <v>0.1034</v>
       </c>
       <c r="F312" s="9" t="n">
-        <v>0.0135</v>
+        <v>0.0134</v>
       </c>
       <c r="G312" s="6" t="n">
         <v>46317</v>
@@ -23480,7 +23480,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="9" t="n">
-        <v>0.1503869483371679</v>
+        <v>0.1505072691141094</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -23491,7 +23491,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="9" t="n">
-        <v>0.2026772641706755</v>
+        <v>0.2028030540738417</v>
       </c>
       <c r="Q312" s="10" t="inlineStr">
         <is>
@@ -23532,13 +23532,13 @@
         </is>
       </c>
       <c r="D313" s="15" t="n">
-        <v>1025.65</v>
+        <v>1031.44</v>
       </c>
       <c r="E313" s="16" t="n">
-        <v>0.0236</v>
+        <v>0.0294</v>
       </c>
       <c r="F313" s="26" t="n">
-        <v>-0.0583</v>
+        <v>-0.053</v>
       </c>
       <c r="G313" s="17" t="n"/>
       <c r="H313" s="22" t="inlineStr">
@@ -23557,7 +23557,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="16" t="n">
-        <v>0.1699897625895772</v>
+        <v>0.1634220119444659</v>
       </c>
       <c r="N313" s="14" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="16" t="n">
-        <v>0.2089894213425632</v>
+        <v>0.2022027456759481</v>
       </c>
       <c r="Q313" s="20" t="inlineStr">
         <is>
@@ -23613,13 +23613,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>123.2</v>
+        <v>123.65</v>
       </c>
       <c r="E314" s="9" t="n">
-        <v>0.0124</v>
+        <v>0.0161</v>
       </c>
       <c r="F314" s="9" t="n">
-        <v>0.0198</v>
+        <v>0.0235</v>
       </c>
       <c r="G314" s="6" t="n"/>
       <c r="H314" s="12" t="inlineStr">
@@ -23638,7 +23638,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="9" t="n">
-        <v>0.04707792207792205</v>
+        <v>0.04326728669632021</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>122</v>
       </c>
       <c r="P314" s="5" t="n">
-        <v>-0.009740259740259763</v>
+        <v>-0.01334411645774368</v>
       </c>
       <c r="Q314" s="10" t="inlineStr">
         <is>
@@ -23690,13 +23690,13 @@
         </is>
       </c>
       <c r="D315" s="15" t="n">
-        <v>62.99</v>
+        <v>63.48</v>
       </c>
       <c r="E315" s="26" t="n">
-        <v>-0.0133</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F315" s="16" t="n">
-        <v>0.0542</v>
+        <v>0.0624</v>
       </c>
       <c r="G315" s="17" t="n">
         <v>46239</v>
@@ -23725,14 +23725,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="16" t="n">
-        <v>0.03190982695665975</v>
+        <v>0.02394454946439829</v>
       </c>
       <c r="N315" s="14" t="inlineStr"/>
       <c r="O315" s="19" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="16" t="n">
-        <v>0.06366089855532621</v>
+        <v>0.05545053560176439</v>
       </c>
       <c r="Q315" s="20" t="inlineStr">
         <is>
@@ -23773,13 +23773,13 @@
         </is>
       </c>
       <c r="D316" s="4" t="n">
-        <v>143.15</v>
+        <v>144.15</v>
       </c>
       <c r="E316" s="9" t="n">
-        <v>0.0267</v>
-      </c>
-      <c r="F316" s="5" t="n">
-        <v>-0.004500000000000001</v>
+        <v>0.0339</v>
+      </c>
+      <c r="F316" s="9" t="n">
+        <v>0.0025</v>
       </c>
       <c r="G316" s="6" t="n">
         <v>46309</v>
@@ -23808,7 +23808,7 @@
         <v>167</v>
       </c>
       <c r="M316" s="9" t="n">
-        <v>0.1666084526720223</v>
+        <v>0.1585154353104405</v>
       </c>
       <c r="N316" s="3" t="inlineStr"/>
       <c r="O316" s="8" t="n"/>
@@ -23852,13 +23852,13 @@
         </is>
       </c>
       <c r="D317" s="15" t="n">
-        <v>325.42</v>
+        <v>325.9</v>
       </c>
       <c r="E317" s="26" t="n">
-        <v>-0.0128</v>
+        <v>-0.0113</v>
       </c>
       <c r="F317" s="16" t="n">
-        <v>0.0612</v>
+        <v>0.06269999999999999</v>
       </c>
       <c r="G317" s="17" t="n"/>
       <c r="H317" s="22" t="inlineStr">
@@ -23884,7 +23884,7 @@
         <v>316</v>
       </c>
       <c r="P317" s="26" t="n">
-        <v>-0.02894720668674333</v>
+        <v>-0.03037741638539422</v>
       </c>
       <c r="Q317" s="20" t="inlineStr">
         <is>
@@ -23925,13 +23925,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>227.9</v>
+        <v>229.16</v>
       </c>
       <c r="E318" s="9" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.0137</v>
       </c>
       <c r="F318" s="9" t="n">
-        <v>0.1052</v>
+        <v>0.1112</v>
       </c>
       <c r="G318" s="6" t="n">
         <v>46244</v>
@@ -23967,7 +23967,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="5" t="n">
-        <v>-0.05660377358490568</v>
+        <v>-0.06179088846220979</v>
       </c>
       <c r="Q318" s="10" t="inlineStr">
         <is>
@@ -24008,13 +24008,13 @@
         </is>
       </c>
       <c r="D319" s="15" t="n">
-        <v>122.39</v>
+        <v>122.46</v>
       </c>
       <c r="E319" s="26" t="n">
-        <v>-0.01</v>
+        <v>-0.0095</v>
       </c>
       <c r="F319" s="26" t="n">
-        <v>-0.0024</v>
+        <v>-0.0019</v>
       </c>
       <c r="G319" s="17" t="n"/>
       <c r="H319" s="22" t="inlineStr">
@@ -24033,7 +24033,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="16" t="n">
-        <v>0.1602255086199853</v>
+        <v>0.1595623060591214</v>
       </c>
       <c r="N319" s="14" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="16" t="n">
-        <v>0.1193724977530844</v>
+        <v>0.1187326473950678</v>
       </c>
       <c r="Q319" s="20" t="inlineStr">
         <is>
@@ -24093,13 +24093,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>233</v>
+        <v>233.1</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>-0.013</v>
+        <v>-0.0125</v>
       </c>
       <c r="F320" s="9" t="n">
-        <v>0.1601</v>
+        <v>0.1606</v>
       </c>
       <c r="G320" s="6" t="n"/>
       <c r="H320" s="12" t="inlineStr">
@@ -24118,7 +24118,7 @@
         <v>237</v>
       </c>
       <c r="M320" s="9" t="n">
-        <v>0.01716738197424893</v>
+        <v>0.01673101673101676</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>236</v>
       </c>
       <c r="P320" s="9" t="n">
-        <v>0.0128755364806867</v>
+        <v>0.01244101244101247</v>
       </c>
       <c r="Q320" s="10" t="inlineStr">
         <is>
@@ -24170,13 +24170,13 @@
         </is>
       </c>
       <c r="D321" s="15" t="n">
-        <v>172.3</v>
+        <v>172.89</v>
       </c>
       <c r="E321" s="26" t="n">
-        <v>-0.0258</v>
+        <v>-0.0225</v>
       </c>
       <c r="F321" s="16" t="n">
-        <v>0.0259</v>
+        <v>0.0294</v>
       </c>
       <c r="G321" s="17" t="n">
         <v>46239</v>
@@ -24205,7 +24205,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="16" t="n">
-        <v>0.1607661056297155</v>
+        <v>0.1568049048527967</v>
       </c>
       <c r="N321" s="14" t="inlineStr"/>
       <c r="O321" s="19" t="n"/>
@@ -24249,13 +24249,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>132.16</v>
+        <v>131.3</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>-0.0343</v>
+        <v>-0.0406</v>
       </c>
       <c r="F322" s="9" t="n">
-        <v>0.08109999999999999</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="G322" s="6" t="n"/>
       <c r="H322" s="12" t="inlineStr">
@@ -24274,7 +24274,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="5" t="n">
-        <v>-0.008777239709443073</v>
+        <v>-0.002284843869002371</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="8" t="n"/>
@@ -24318,13 +24318,13 @@
         </is>
       </c>
       <c r="D323" s="15" t="n">
-        <v>34.1</v>
+        <v>34.16</v>
       </c>
       <c r="E323" s="26" t="n">
-        <v>-0.0654</v>
+        <v>-0.0639</v>
       </c>
       <c r="F323" s="26" t="n">
-        <v>-0.1218</v>
+        <v>-0.1203</v>
       </c>
       <c r="G323" s="17" t="n"/>
       <c r="H323" s="22" t="inlineStr">
@@ -24387,13 +24387,13 @@
         </is>
       </c>
       <c r="D324" s="4" t="n">
-        <v>40.63</v>
+        <v>40.08</v>
       </c>
       <c r="E324" s="9" t="n">
-        <v>0.09789999999999999</v>
+        <v>0.083</v>
       </c>
       <c r="F324" s="9" t="n">
-        <v>0.0411</v>
+        <v>0.0269</v>
       </c>
       <c r="G324" s="6" t="n"/>
       <c r="H324" s="12" t="inlineStr">
@@ -24438,13 +24438,13 @@
         </is>
       </c>
       <c r="D325" s="15" t="n">
-        <v>274.27</v>
+        <v>273.71</v>
       </c>
       <c r="E325" s="16" t="n">
-        <v>0.1464</v>
+        <v>0.144</v>
       </c>
       <c r="F325" s="16" t="n">
-        <v>0.0366</v>
+        <v>0.0345</v>
       </c>
       <c r="G325" s="17" t="n">
         <v>46240</v>
@@ -24473,7 +24473,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="16" t="n">
-        <v>0.4000802129288658</v>
+        <v>0.4029447225165322</v>
       </c>
       <c r="N325" s="14" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="16" t="n">
-        <v>0.3854960440441901</v>
+        <v>0.3883307149903183</v>
       </c>
       <c r="Q325" s="20" t="inlineStr"/>
       <c r="R325" s="19" t="n"/>
@@ -24527,13 +24527,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>71.63</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="E326" s="5" t="n">
-        <v>-0.0785</v>
+        <v>-0.0771</v>
       </c>
       <c r="F326" s="9" t="n">
-        <v>0.018</v>
+        <v>0.0196</v>
       </c>
       <c r="G326" s="6" t="n"/>
       <c r="H326" s="12" t="inlineStr">
@@ -24552,7 +24552,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="9" t="n">
-        <v>0.1028898506212482</v>
+        <v>0.1011987733482019</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="8" t="n"/>
@@ -24604,13 +24604,13 @@
         </is>
       </c>
       <c r="D327" s="15" t="n">
-        <v>124</v>
+        <v>124.28</v>
       </c>
       <c r="E327" s="26" t="n">
-        <v>-0.0432</v>
+        <v>-0.04099999999999999</v>
       </c>
       <c r="F327" s="16" t="n">
-        <v>0.0179</v>
+        <v>0.0202</v>
       </c>
       <c r="G327" s="17" t="n">
         <v>46238</v>
@@ -24639,7 +24639,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="16" t="n">
-        <v>0.09677419354838709</v>
+        <v>0.09430318635339555</v>
       </c>
       <c r="N327" s="14" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="16" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.126488574187319</v>
       </c>
       <c r="Q327" s="20" t="inlineStr">
         <is>
@@ -24691,13 +24691,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>107.88</v>
+        <v>108.06</v>
       </c>
       <c r="E328" s="5" t="n">
-        <v>-0.0629</v>
+        <v>-0.0612</v>
       </c>
       <c r="F328" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0112</v>
       </c>
       <c r="G328" s="6" t="n"/>
       <c r="H328" s="12" t="inlineStr">
@@ -24716,7 +24716,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="9" t="n">
-        <v>0.2143121987393401</v>
+        <v>0.212289468813622</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="9" t="n">
-        <v>0.1216166110493141</v>
+        <v>0.1197482879881547</v>
       </c>
       <c r="Q328" s="10" t="inlineStr">
         <is>
@@ -24772,13 +24772,13 @@
         </is>
       </c>
       <c r="D329" s="15" t="n">
-        <v>86.12</v>
+        <v>86.55</v>
       </c>
       <c r="E329" s="26" t="n">
-        <v>-0.0251</v>
+        <v>-0.0203</v>
       </c>
       <c r="F329" s="16" t="n">
-        <v>0.0051</v>
+        <v>0.0102</v>
       </c>
       <c r="G329" s="17" t="n">
         <v>46318</v>
@@ -24814,7 +24814,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="16" t="n">
-        <v>0.2424523920111472</v>
+        <v>0.2362796071634894</v>
       </c>
       <c r="Q329" s="20" t="inlineStr">
         <is>
@@ -24863,13 +24863,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>58.06</v>
+        <v>58.08</v>
       </c>
       <c r="E330" s="9" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0103</v>
       </c>
       <c r="F330" s="9" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0635</v>
       </c>
       <c r="G330" s="6" t="n">
         <v>46237</v>
@@ -24898,7 +24898,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="9" t="n">
-        <v>0.08508439545297963</v>
+        <v>0.08471074380165293</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="8" t="n"/>
@@ -24942,13 +24942,13 @@
         </is>
       </c>
       <c r="D331" s="15" t="n">
-        <v>41.63</v>
+        <v>41.22</v>
       </c>
       <c r="E331" s="26" t="n">
-        <v>-0.2048</v>
+        <v>-0.2128</v>
       </c>
       <c r="F331" s="26" t="n">
-        <v>-0.3633</v>
+        <v>-0.3696</v>
       </c>
       <c r="G331" s="17" t="n">
         <v>46241</v>
@@ -25003,13 +25003,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>9.050000000000001</v>
+        <v>9.01</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>-0.0727</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="F332" s="5" t="n">
-        <v>-0.2458</v>
+        <v>-0.2492</v>
       </c>
       <c r="G332" s="6" t="n">
         <v>46239</v>
@@ -25064,13 +25064,13 @@
         </is>
       </c>
       <c r="D333" s="15" t="n">
-        <v>93.56999999999999</v>
+        <v>92.94</v>
       </c>
       <c r="E333" s="26" t="n">
-        <v>-0.045</v>
+        <v>-0.05139999999999999</v>
       </c>
       <c r="F333" s="16" t="n">
-        <v>0.0213</v>
+        <v>0.0144</v>
       </c>
       <c r="G333" s="17" t="n"/>
       <c r="H333" s="22" t="inlineStr">
@@ -25089,7 +25089,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="16" t="n">
-        <v>0.05803142032702797</v>
+        <v>0.06520335700451907</v>
       </c>
       <c r="N333" s="14" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="16" t="n">
-        <v>0.1969648391578498</v>
+        <v>0.2050785452980418</v>
       </c>
       <c r="Q333" s="20" t="inlineStr">
         <is>
@@ -25141,13 +25141,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>109.08</v>
+        <v>109.28</v>
       </c>
       <c r="E334" s="5" t="n">
-        <v>-0.08199999999999999</v>
+        <v>-0.08039999999999999</v>
       </c>
       <c r="F334" s="5" t="n">
-        <v>-0.0193</v>
+        <v>-0.0175</v>
       </c>
       <c r="G334" s="6" t="n"/>
       <c r="H334" s="12" t="inlineStr">
@@ -25166,7 +25166,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="9" t="n">
-        <v>0.1642830949761643</v>
+        <v>0.1621522693997072</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="8" t="n"/>
@@ -35861,7 +35861,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of August 03, 2026 at 17:29 UTC</t>
+          <t>Data as of August 03, 2026 at 21:48 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>98.47</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>-0.0124</v>
+        <v>-0.0153</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>46239</v>
@@ -878,7 +878,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>0.2694221590332081</v>
+        <v>0.2731717254023222</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.4623743272062557</v>
+        <v>0.4666938276634752</v>
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>377.64</v>
+        <v>377.65</v>
       </c>
       <c r="E3" s="16" t="n">
         <v>0.0305</v>
@@ -973,7 +973,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="16" t="n">
-        <v>0.1598347632666031</v>
+        <v>0.1598040513703165</v>
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="16" t="n">
-        <v>0.1121703209405784</v>
+        <v>0.1121408711770158</v>
       </c>
       <c r="Q3" s="20" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>586.6799999999999</v>
+        <v>587.9400000000001</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>-0.0227</v>
+        <v>-0.0206</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>-0.0106</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="12" t="inlineStr">
@@ -1054,7 +1054,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.4232631076566443</v>
+        <v>0.4202129468993434</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.585191245653508</v>
+        <v>0.5817940606184303</v>
       </c>
       <c r="Q4" s="10" t="inlineStr">
         <is>
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>41.19</v>
+        <v>41.24</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>0.09359999999999999</v>
+        <v>0.09480000000000001</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>0.1968</v>
+        <v>0.1981</v>
       </c>
       <c r="G5" s="17" t="n">
         <v>46238</v>
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>72.59</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>-0.0451</v>
+        <v>-0.0322</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-0.1167</v>
+        <v>-0.1048</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>46315</v>
@@ -1210,7 +1210,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.1020801763328282</v>
+        <v>0.08739975533505515</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0.3776002204160352</v>
+        <v>0.3592496941688189</v>
       </c>
       <c r="Q6" s="10" t="inlineStr">
         <is>
@@ -1262,13 +1262,13 @@
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>79.89</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>-0.0001</v>
+        <v>81.81</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0.0239</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>0.0609</v>
+        <v>0.0863</v>
       </c>
       <c r="G7" s="17" t="n"/>
       <c r="H7" s="22" t="inlineStr">
@@ -1287,7 +1287,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="16" t="n">
-        <v>0.1390662160470647</v>
+        <v>0.112333455567779</v>
       </c>
       <c r="N7" s="14" t="inlineStr"/>
       <c r="O7" s="19" t="n"/>
@@ -1331,13 +1331,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>477.88</v>
+        <v>478.17</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-0.0106</v>
+        <v>-0.01</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.0384</v>
+        <v>-0.0378</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>46238</v>
@@ -1366,7 +1366,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.1926215786389888</v>
+        <v>0.1918982788548005</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.3560726542228174</v>
+        <v>0.3552502248154421</v>
       </c>
       <c r="Q8" s="10" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>183.84</v>
+        <v>184.51</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>-0.044</v>
+        <v>-0.0405</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="G9" s="17" t="n"/>
       <c r="H9" s="22" t="inlineStr">
@@ -1477,13 +1477,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>176.33</v>
+        <v>177.21</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>-0.03</v>
+        <v>-0.0252</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-0.009899999999999999</v>
+        <v>-0.005</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>46317</v>
@@ -1512,7 +1512,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="6" t="n">
-        <v>-0.03589859921737658</v>
+        <v>-0.0406861915241804</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.5312198718312254</v>
+        <v>0.5236160487557134</v>
       </c>
       <c r="Q10" s="10" t="inlineStr">
         <is>
@@ -1564,13 +1564,13 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>46.81</v>
+        <v>46.88</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>0.1126</v>
+        <v>0.1143</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>0.0316</v>
+        <v>0.0333</v>
       </c>
       <c r="G11" s="17" t="n">
         <v>46316</v>
@@ -1599,7 +1599,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="26" t="n">
-        <v>-0.08139286477248456</v>
+        <v>-0.08276450511945398</v>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>0.06814783165990168</v>
+        <v>0.06655290102389072</v>
       </c>
       <c r="Q11" s="20" t="inlineStr">
         <is>
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>148.93</v>
+        <v>149.92</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0154</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1153</v>
+        <v>0.1227</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>46240</v>
@@ -1690,7 +1690,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.2153360639226482</v>
+        <v>0.2073105656350054</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0.04075740280668766</v>
+        <v>0.0338847385272146</v>
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
@@ -1742,13 +1742,13 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>278.84</v>
+        <v>277.42</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>0.142</v>
+        <v>0.1362</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>0.1334</v>
+        <v>0.1276</v>
       </c>
       <c r="G13" s="17" t="n"/>
       <c r="H13" s="22" t="inlineStr">
@@ -1767,7 +1767,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="16" t="n">
-        <v>0.1547841055802612</v>
+        <v>0.1606949751279647</v>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>0.02209152201979639</v>
+        <v>0.02732319227164582</v>
       </c>
       <c r="Q13" s="20" t="inlineStr">
         <is>
@@ -1831,13 +1831,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3015.89</v>
+        <v>3028.03</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.0197</v>
+        <v>0.0238</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.0323</v>
+        <v>-0.0284</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>46287</v>
@@ -1866,7 +1866,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0.3760448822735578</v>
+        <v>0.3705280330776115</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0.2268351962438949</v>
+        <v>0.2219165596113644</v>
       </c>
       <c r="Q14" s="10" t="inlineStr">
         <is>
@@ -1918,13 +1918,13 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>86.2</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>0.1051</v>
+        <v>0.1071</v>
       </c>
       <c r="F15" s="16" t="n">
-        <v>0.2049</v>
+        <v>0.207</v>
       </c>
       <c r="G15" s="17" t="n">
         <v>46261</v>
@@ -1953,7 +1953,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="26" t="n">
-        <v>-0.2459396751740139</v>
+        <v>-0.2472495657209033</v>
       </c>
       <c r="N15" s="14" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="26" t="n">
-        <v>-0.01392111368909516</v>
+        <v>-0.01563404748118117</v>
       </c>
       <c r="Q15" s="20" t="inlineStr"/>
       <c r="R15" s="19" t="n"/>
@@ -1999,13 +1999,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>191.52</v>
+        <v>194.27</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.0579</v>
+        <v>0.0731</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.1548</v>
+        <v>0.1714</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>46238</v>
@@ -2034,7 +2034,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.1173767752715121</v>
+        <v>0.1015596849745199</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.2792397660818713</v>
+        <v>0.2611314150409224</v>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>370.74</v>
+        <v>367.82</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.1869</v>
+        <v>0.1776</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>0.1694</v>
+        <v>0.1601</v>
       </c>
       <c r="G17" s="17" t="n">
         <v>46261</v>
@@ -2129,7 +2129,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="16" t="n">
-        <v>0.01149053244861626</v>
+        <v>0.01952041759556307</v>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>0.01149053244861626</v>
+        <v>0.01952041759556307</v>
       </c>
       <c r="Q17" s="20" t="inlineStr"/>
       <c r="R17" s="19" t="n"/>
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>35.06</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>0.0319</v>
+        <v>33.82</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.1951</v>
+        <v>0.1527</v>
       </c>
       <c r="G18" s="7" t="n"/>
       <c r="H18" s="12" t="inlineStr">
@@ -2204,7 +2204,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.2835139760410724</v>
+        <v>0.3305736250739207</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.2835139760410724</v>
+        <v>0.3305736250739207</v>
       </c>
       <c r="Q18" s="10" t="inlineStr">
         <is>
@@ -2256,13 +2256,13 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>149.63</v>
+        <v>150.37</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>-0.0462</v>
+        <v>-0.0415</v>
       </c>
       <c r="F19" s="16" t="n">
-        <v>0.0277</v>
+        <v>0.0328</v>
       </c>
       <c r="G19" s="17" t="n">
         <v>46324</v>
@@ -2291,7 +2291,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="16" t="n">
-        <v>0.1361358016440554</v>
+        <v>0.1305446565139323</v>
       </c>
       <c r="N19" s="14" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.182917864064693</v>
+        <v>0.1770964953115648</v>
       </c>
       <c r="Q19" s="20" t="inlineStr">
         <is>
@@ -2343,13 +2343,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>201.15</v>
+        <v>200.74</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-0.1217</v>
+        <v>-0.1235</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.06559999999999999</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>46261</v>
@@ -2378,7 +2378,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0.09371116082525476</v>
+        <v>0.09594500348709768</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="9" t="n"/>
@@ -2422,13 +2422,13 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>131.03</v>
+        <v>130.71</v>
       </c>
       <c r="E21" s="16" t="n">
-        <v>0.0788</v>
+        <v>0.0762</v>
       </c>
       <c r="F21" s="16" t="n">
-        <v>0.2043</v>
+        <v>0.2014</v>
       </c>
       <c r="G21" s="17" t="n">
         <v>46267</v>
@@ -2483,13 +2483,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>88.14</v>
+        <v>88.31</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.1322</v>
+        <v>0.1344</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.0735</v>
+        <v>0.0755</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>46315</v>
@@ -2518,7 +2518,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>-0.3079192194236442</v>
+        <v>-0.3092515003963311</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.1345586566825505</v>
+        <v>0.1323745895142113</v>
       </c>
       <c r="Q22" s="10" t="inlineStr">
         <is>
@@ -2570,13 +2570,13 @@
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>131.6</v>
+        <v>132.55</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.0229</v>
+        <v>0.0302</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>0.3408</v>
+        <v>0.3505</v>
       </c>
       <c r="G23" s="17" t="n">
         <v>46315</v>
@@ -2608,7 +2608,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>0.101823708206687</v>
+        <v>0.09392682006789881</v>
       </c>
       <c r="Q23" s="20" t="inlineStr"/>
       <c r="R23" s="19" t="n"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>350.13</v>
+        <v>348.24</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>-0.0015</v>
+        <v>-0.0069</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.1266</v>
+        <v>0.1205</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>46252</v>
@@ -2678,7 +2678,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0.02818952960329022</v>
+        <v>0.03376981392143347</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0.1424328106703225</v>
+        <v>0.1486331265793705</v>
       </c>
       <c r="Q24" s="10" t="inlineStr">
         <is>
@@ -2738,13 +2738,13 @@
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>218.49</v>
+        <v>218.08</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>-0.0236</v>
+        <v>-0.0255</v>
       </c>
       <c r="F25" s="16" t="n">
-        <v>0.0368</v>
+        <v>0.0348</v>
       </c>
       <c r="G25" s="17" t="n">
         <v>46253</v>
@@ -2773,7 +2773,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="16" t="n">
-        <v>0.1671014691747906</v>
+        <v>0.1692956713132795</v>
       </c>
       <c r="N25" s="14" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>0.05267975651059541</v>
+        <v>0.05465884079236971</v>
       </c>
       <c r="Q25" s="20" t="inlineStr">
         <is>
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>267.08</v>
+        <v>268.34</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-0.0444</v>
+        <v>-0.0399</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-0.04559999999999999</v>
+        <v>-0.0411</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>46238</v>
@@ -2864,7 +2864,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.1232589486296242</v>
+        <v>0.1179846463441903</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0.3104687734012282</v>
+        <v>0.3043154207348887</v>
       </c>
       <c r="Q26" s="10" t="inlineStr">
         <is>
@@ -2916,13 +2916,13 @@
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>41.99</v>
+        <v>41.53</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>-0.0313</v>
+        <v>-0.0418</v>
       </c>
       <c r="F27" s="26" t="n">
-        <v>-0.0232</v>
+        <v>-0.0337</v>
       </c>
       <c r="G27" s="17" t="n">
         <v>46289</v>
@@ -2977,13 +2977,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>91.28</v>
+        <v>91.83</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0901</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0166</v>
       </c>
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="12" t="inlineStr">
@@ -3002,7 +3002,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.2050832602979842</v>
+        <v>0.19786562125667</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.2598597721297108</v>
+        <v>0.2523140585865186</v>
       </c>
       <c r="Q28" s="10" t="inlineStr">
         <is>
@@ -3058,13 +3058,13 @@
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>201.73</v>
+        <v>203.44</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>-0.06269999999999999</v>
+        <v>-0.0547</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="G29" s="17" t="n">
         <v>46317</v>
@@ -3119,13 +3119,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>252.39</v>
+        <v>251.06</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.1941</v>
+        <v>0.1878</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.0956</v>
+        <v>0.0898</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>46254</v>
@@ -3154,7 +3154,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>-0.02928008241213989</v>
+        <v>-0.02413765633713057</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.04996235983993032</v>
+        <v>0.05552457579861387</v>
       </c>
       <c r="Q30" s="10" t="inlineStr">
         <is>
@@ -3206,13 +3206,13 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>104.6</v>
+        <v>104.97</v>
       </c>
       <c r="E31" s="16" t="n">
-        <v>0.0244</v>
+        <v>0.028</v>
       </c>
       <c r="F31" s="16" t="n">
-        <v>0.0977</v>
+        <v>0.1016</v>
       </c>
       <c r="G31" s="17" t="n"/>
       <c r="H31" s="22" t="inlineStr">
@@ -3231,7 +3231,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="16" t="n">
-        <v>0.1472275334608031</v>
+        <v>0.1431837667905116</v>
       </c>
       <c r="N31" s="14" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>0.09942638623326966</v>
+        <v>0.09555110984090694</v>
       </c>
       <c r="Q31" s="20" t="inlineStr">
         <is>
@@ -3283,13 +3283,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>12.61</v>
+        <v>12.91</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-0.2174</v>
+        <v>-0.1991</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-0.0924</v>
+        <v>-0.0712</v>
       </c>
       <c r="G32" s="7" t="n"/>
       <c r="H32" s="12" t="inlineStr">
@@ -3334,13 +3334,13 @@
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>157.77</v>
+        <v>157.55</v>
       </c>
       <c r="E33" s="16" t="n">
-        <v>0.04269999999999999</v>
+        <v>0.0412</v>
       </c>
       <c r="F33" s="26" t="n">
-        <v>-0.0183</v>
+        <v>-0.0197</v>
       </c>
       <c r="G33" s="17" t="n">
         <v>46253</v>
@@ -3369,7 +3369,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="16" t="n">
-        <v>0.01413449958800779</v>
+        <v>0.01555061885115829</v>
       </c>
       <c r="N33" s="14" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>0.1092096089243835</v>
+        <v>0.1107584893684544</v>
       </c>
       <c r="Q33" s="20" t="inlineStr">
         <is>
@@ -3425,13 +3425,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>32.92</v>
+        <v>33.12</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.08929999999999999</v>
+        <v>0.096</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.1054</v>
+        <v>0.1122</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>46317</v>
@@ -3460,7 +3460,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.06318347509112995</v>
+        <v>0.05676328502415467</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0.2150668286755771</v>
+        <v>0.2077294685990339</v>
       </c>
       <c r="Q34" s="10" t="inlineStr">
         <is>
@@ -3512,13 +3512,13 @@
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>326.27</v>
+        <v>327.35</v>
       </c>
       <c r="E35" s="26" t="n">
-        <v>-0.2227</v>
+        <v>-0.2202</v>
       </c>
       <c r="F35" s="26" t="n">
-        <v>-0.1655</v>
+        <v>-0.1628</v>
       </c>
       <c r="G35" s="17" t="n">
         <v>46323</v>
@@ -3547,7 +3547,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="26" t="n">
-        <v>-0.6015569926747786</v>
+        <v>-0.6028715442187261</v>
       </c>
       <c r="N35" s="14" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="26" t="n">
-        <v>-0.08051613694179661</v>
+        <v>-0.0835497174278296</v>
       </c>
       <c r="Q35" s="20" t="inlineStr">
         <is>
@@ -3599,13 +3599,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>71.48999999999999</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>-0.0129</v>
+        <v>-0.0059</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.011</v>
+        <v>0.0181</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>46239</v>
@@ -3660,13 +3660,13 @@
         </is>
       </c>
       <c r="D37" s="15" t="n">
-        <v>544.41</v>
+        <v>543.86</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>0.2031</v>
+        <v>0.2019</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>0.1656</v>
+        <v>0.1644</v>
       </c>
       <c r="G37" s="17" t="n">
         <v>46261</v>
@@ -3695,7 +3695,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="26" t="n">
-        <v>-0.1734170937345015</v>
+        <v>-0.1725811789798845</v>
       </c>
       <c r="N37" s="14" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>0.166400323285759</v>
+        <v>0.1675798918839407</v>
       </c>
       <c r="Q37" s="20" t="inlineStr">
         <is>
@@ -3751,13 +3751,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>102.41</v>
+        <v>103</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.0509</v>
+        <v>0.057</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.05860000000000001</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="G38" s="7" t="n"/>
       <c r="H38" s="12" t="inlineStr">
@@ -3776,7 +3776,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.07411385606874332</v>
+        <v>0.06796116504854369</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.02529049897470954</v>
+        <v>0.01941747572815534</v>
       </c>
       <c r="Q38" s="10" t="inlineStr">
         <is>
@@ -3832,13 +3832,13 @@
         </is>
       </c>
       <c r="D39" s="15" t="n">
-        <v>91.72</v>
+        <v>92.53</v>
       </c>
       <c r="E39" s="26" t="n">
-        <v>-0.0178</v>
+        <v>-0.0092</v>
       </c>
       <c r="F39" s="16" t="n">
-        <v>0.0355</v>
+        <v>0.0446</v>
       </c>
       <c r="G39" s="17" t="n"/>
       <c r="H39" s="22" t="inlineStr">
@@ -3857,7 +3857,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="16" t="n">
-        <v>0.03576101177496731</v>
+        <v>0.02669404517453797</v>
       </c>
       <c r="N39" s="14" t="inlineStr">
         <is>
@@ -3868,7 +3868,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.09027474923680769</v>
+        <v>0.08073057386793471</v>
       </c>
       <c r="Q39" s="20" t="inlineStr">
         <is>
@@ -3913,13 +3913,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>942.48</v>
+        <v>947.85</v>
       </c>
       <c r="E40" s="6" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.0025</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>-0.0302</v>
+        <v>-0.0247</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>46289</v>
@@ -3948,7 +3948,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0.06103047279517865</v>
+        <v>0.05501925410138733</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0.1671335200746965</v>
+        <v>0.1605211795115261</v>
       </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
@@ -4008,13 +4008,13 @@
         </is>
       </c>
       <c r="D41" s="15" t="n">
-        <v>127.47</v>
+        <v>127.26</v>
       </c>
       <c r="E41" s="16" t="n">
-        <v>0.0964</v>
+        <v>0.09449999999999999</v>
       </c>
       <c r="F41" s="16" t="n">
-        <v>0.2293</v>
+        <v>0.2272</v>
       </c>
       <c r="G41" s="17" t="n">
         <v>46261</v>
@@ -4043,7 +4043,7 @@
         <v>125</v>
       </c>
       <c r="M41" s="26" t="n">
-        <v>-0.01937710833921706</v>
+        <v>-0.0177589187490178</v>
       </c>
       <c r="N41" s="14" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>0.05907272299364557</v>
+        <v>0.06082036775106078</v>
       </c>
       <c r="Q41" s="20" t="inlineStr">
         <is>
@@ -4095,13 +4095,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>26.42</v>
+        <v>26.64</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.0643</v>
+        <v>0.0733</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.1698</v>
+        <v>0.1798</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>46239</v>
@@ -4156,13 +4156,13 @@
         </is>
       </c>
       <c r="D43" s="15" t="n">
-        <v>86.27</v>
+        <v>86.56</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>0.0399</v>
+        <v>0.0434</v>
       </c>
       <c r="F43" s="16" t="n">
-        <v>0.08539999999999999</v>
+        <v>0.0891</v>
       </c>
       <c r="G43" s="17" t="n"/>
       <c r="H43" s="22" t="inlineStr">
@@ -4181,7 +4181,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="16" t="n">
-        <v>0.04323635099107458</v>
+        <v>0.0397412199630314</v>
       </c>
       <c r="N43" s="14" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>88</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>0.0200533209690507</v>
+        <v>0.01663585951940848</v>
       </c>
       <c r="Q43" s="20" t="inlineStr">
         <is>
@@ -4241,13 +4241,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>57.63</v>
+        <v>57.79</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>-0.0107</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>-0.0935</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>46275</v>
@@ -4276,7 +4276,7 @@
         <v>58</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>0.006420267221932977</v>
+        <v>0.003633846686277917</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.3534617386777719</v>
+        <v>0.3497144834746496</v>
       </c>
       <c r="Q44" s="10" t="inlineStr">
         <is>
@@ -4328,13 +4328,13 @@
         </is>
       </c>
       <c r="D45" s="15" t="n">
-        <v>61.74</v>
+        <v>62.08</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>0.0434</v>
-      </c>
-      <c r="F45" s="26" t="n">
-        <v>-0.0048</v>
+        <v>0.0492</v>
+      </c>
+      <c r="F45" s="16" t="n">
+        <v>0.0005999999999999999</v>
       </c>
       <c r="G45" s="17" t="n"/>
       <c r="H45" s="22" t="inlineStr">
@@ -4353,7 +4353,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="16" t="n">
-        <v>0.1337868480725623</v>
+        <v>0.1275773195876289</v>
       </c>
       <c r="N45" s="14" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.1499838030450275</v>
+        <v>0.1436855670103093</v>
       </c>
       <c r="Q45" s="20" t="inlineStr">
         <is>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>51.94</v>
+        <v>52.06</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0054</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.09949999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>46301</v>
@@ -4484,13 +4484,13 @@
         </is>
       </c>
       <c r="D47" s="15" t="n">
-        <v>93.37</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="E47" s="26" t="n">
-        <v>-0.0411</v>
+        <v>-0.0328</v>
       </c>
       <c r="F47" s="16" t="n">
-        <v>0.04269999999999999</v>
+        <v>0.0517</v>
       </c>
       <c r="G47" s="17" t="n">
         <v>46240</v>
@@ -4548,7 +4548,7 @@
         <v>68.06999999999999</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>-0.05309999999999999</v>
+        <v>-0.053</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>-0.0571</v>
@@ -4596,13 +4596,13 @@
         </is>
       </c>
       <c r="D49" s="15" t="n">
-        <v>138.4</v>
+        <v>139.1</v>
       </c>
       <c r="E49" s="26" t="n">
-        <v>-0.0341</v>
+        <v>-0.0292</v>
       </c>
       <c r="F49" s="26" t="n">
-        <v>-0.0248</v>
+        <v>-0.0199</v>
       </c>
       <c r="G49" s="17" t="n">
         <v>46303</v>
@@ -4631,7 +4631,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="16" t="n">
-        <v>0.01156069364161845</v>
+        <v>0.006470165348670062</v>
       </c>
       <c r="N49" s="14" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>0.08381502890173406</v>
+        <v>0.07836089144500363</v>
       </c>
       <c r="Q49" s="20" t="inlineStr">
         <is>
@@ -4691,13 +4691,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>147.14</v>
+        <v>148.01</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>-0.0145</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="12" t="inlineStr">
@@ -4716,7 +4716,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.1145847492184315</v>
+        <v>0.10803324099723</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0.1009922522767433</v>
+        <v>0.09452064049726376</v>
       </c>
       <c r="Q50" s="10" t="inlineStr">
         <is>
@@ -4780,13 +4780,13 @@
         </is>
       </c>
       <c r="D51" s="15" t="n">
-        <v>82.76000000000001</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="E51" s="26" t="n">
-        <v>-0.0175</v>
+        <v>-0.0171</v>
       </c>
       <c r="F51" s="16" t="n">
-        <v>0.0848</v>
+        <v>0.0852</v>
       </c>
       <c r="G51" s="17" t="n">
         <v>46238</v>
@@ -4815,7 +4815,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="16" t="n">
-        <v>0.2083131947800869</v>
+        <v>0.2078753472641622</v>
       </c>
       <c r="N51" s="14" t="inlineStr"/>
       <c r="O51" s="19" t="n"/>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>149.71</v>
+        <v>148.11</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.1872</v>
+        <v>0.1745</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.2214</v>
+        <v>0.2084</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>46253</v>
@@ -4894,7 +4894,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="6" t="n">
-        <v>-0.06485872687195249</v>
+        <v>-0.05475659982445488</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>-0.09825662948366848</v>
+        <v>-0.0885152926878672</v>
       </c>
       <c r="Q52" s="10" t="inlineStr">
         <is>
@@ -4950,13 +4950,13 @@
         </is>
       </c>
       <c r="D53" s="15" t="n">
-        <v>110.13</v>
-      </c>
-      <c r="E53" s="26" t="n">
-        <v>-0.004699999999999999</v>
+        <v>111.55</v>
+      </c>
+      <c r="E53" s="16" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F53" s="26" t="n">
-        <v>-0.0736</v>
+        <v>-0.0617</v>
       </c>
       <c r="G53" s="17" t="n">
         <v>46254</v>
@@ -4985,7 +4985,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="16" t="n">
-        <v>0.2712249160083538</v>
+        <v>0.2550425818018826</v>
       </c>
       <c r="N53" s="14" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>0.2712249160083538</v>
+        <v>0.2550425818018826</v>
       </c>
       <c r="Q53" s="20" t="inlineStr">
         <is>
@@ -5045,13 +5045,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>61.34</v>
+        <v>61.73</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0.1519</v>
+        <v>0.1592</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>-0.02</v>
+        <v>-0.0137</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>46316</v>
@@ -5087,7 +5087,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>0.2389957613302901</v>
+        <v>0.2311679896322696</v>
       </c>
       <c r="Q54" s="10" t="inlineStr">
         <is>
@@ -5128,13 +5128,13 @@
         </is>
       </c>
       <c r="D55" s="15" t="n">
-        <v>118.03</v>
+        <v>117.94</v>
       </c>
       <c r="E55" s="16" t="n">
-        <v>0.1395</v>
+        <v>0.1386</v>
       </c>
       <c r="F55" s="16" t="n">
-        <v>0.0076</v>
+        <v>0.0068</v>
       </c>
       <c r="G55" s="17" t="n">
         <v>46240</v>
@@ -5163,7 +5163,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="16" t="n">
-        <v>0.5504532745912056</v>
+        <v>0.5516364253010005</v>
       </c>
       <c r="N55" s="14" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>0.2285012285012285</v>
+        <v>0.2294386976428693</v>
       </c>
       <c r="Q55" s="20" t="inlineStr">
         <is>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>190.77</v>
+        <v>190.4</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.1349</v>
+        <v>0.1327</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.0185</v>
+        <v>0.0165</v>
       </c>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="12" t="inlineStr">
@@ -5240,7 +5240,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>0.163704985060544</v>
+        <v>0.1659663865546218</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>0.1794307281019027</v>
+        <v>0.1817226890756302</v>
       </c>
       <c r="Q56" s="10" t="inlineStr">
         <is>
@@ -5296,13 +5296,13 @@
         </is>
       </c>
       <c r="D57" s="15" t="n">
-        <v>143.77</v>
+        <v>143.52</v>
       </c>
       <c r="E57" s="16" t="n">
-        <v>0.1111</v>
+        <v>0.1092</v>
       </c>
       <c r="F57" s="16" t="n">
-        <v>0.0435</v>
+        <v>0.0417</v>
       </c>
       <c r="G57" s="17" t="n">
         <v>46238</v>
@@ -5331,7 +5331,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="16" t="n">
-        <v>0.3632885859358697</v>
+        <v>0.3656633221850612</v>
       </c>
       <c r="N57" s="14" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>0.1824441816790706</v>
+        <v>0.1845039018952062</v>
       </c>
       <c r="Q57" s="20" t="inlineStr">
         <is>
@@ -5387,13 +5387,13 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>37.99</v>
+        <v>38.12</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.0415</v>
+        <v>0.0452</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="12" t="inlineStr">
@@ -5438,13 +5438,13 @@
         </is>
       </c>
       <c r="D59" s="15" t="n">
-        <v>20.58</v>
+        <v>20.33</v>
       </c>
       <c r="E59" s="16" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0561</v>
       </c>
       <c r="F59" s="16" t="n">
-        <v>0.0614</v>
+        <v>0.04849999999999999</v>
       </c>
       <c r="G59" s="17" t="n">
         <v>46238</v>
@@ -5499,13 +5499,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>191.72</v>
+        <v>191.87</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0.1036</v>
+        <v>0.1044</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>-0.004699999999999999</v>
+        <v>-0.0039</v>
       </c>
       <c r="G60" s="7" t="n"/>
       <c r="H60" s="12" t="inlineStr">
@@ -5550,13 +5550,13 @@
         </is>
       </c>
       <c r="D61" s="15" t="n">
-        <v>32.33</v>
+        <v>32.36</v>
       </c>
       <c r="E61" s="26" t="n">
-        <v>-0.0205</v>
+        <v>-0.0194</v>
       </c>
       <c r="F61" s="26" t="n">
-        <v>-0.175</v>
+        <v>-0.1741</v>
       </c>
       <c r="G61" s="17" t="n">
         <v>46315</v>
@@ -5592,7 +5592,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.3300340241261986</v>
+        <v>0.3288009888751545</v>
       </c>
       <c r="Q61" s="20" t="inlineStr">
         <is>
@@ -5637,13 +5637,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>31.45</v>
+        <v>31.38</v>
       </c>
       <c r="E62" s="6" t="n">
-        <v>-0.0074</v>
+        <v>-0.0098</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>-0.0071</v>
+        <v>-0.0095</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>46316</v>
@@ -5672,7 +5672,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.1128775834658188</v>
+        <v>0.1153601019757808</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="9" t="n"/>
@@ -5716,13 +5716,13 @@
         </is>
       </c>
       <c r="D63" s="15" t="n">
-        <v>206.06</v>
+        <v>205.89</v>
       </c>
       <c r="E63" s="16" t="n">
-        <v>0.162</v>
+        <v>0.1611</v>
       </c>
       <c r="F63" s="16" t="n">
-        <v>0.1255</v>
+        <v>0.1246</v>
       </c>
       <c r="G63" s="17" t="n">
         <v>46239</v>
@@ -5777,13 +5777,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>50.6</v>
+        <v>50.81</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0.1068</v>
+        <v>0.1113</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>-0.07769999999999999</v>
+        <v>-0.07400000000000001</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>46311</v>
@@ -5819,7 +5819,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0.2450592885375494</v>
+        <v>0.2399134028734501</v>
       </c>
       <c r="Q64" s="10" t="inlineStr">
         <is>
@@ -5868,13 +5868,13 @@
         </is>
       </c>
       <c r="D65" s="15" t="n">
-        <v>42.43</v>
+        <v>42.34</v>
       </c>
       <c r="E65" s="16" t="n">
-        <v>0.0482</v>
+        <v>0.0459</v>
       </c>
       <c r="F65" s="26" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.06860000000000001</v>
       </c>
       <c r="G65" s="17" t="n"/>
       <c r="H65" s="22" t="inlineStr">
@@ -5919,13 +5919,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>72.16</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>-0.0091</v>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>0.0028</v>
+        <v>-0.018</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>-0.0063</v>
       </c>
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="12" t="inlineStr">
@@ -5944,7 +5944,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0.2333702882483371</v>
+        <v>0.2445811774576981</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="9" t="n"/>
@@ -6000,13 +6000,13 @@
         </is>
       </c>
       <c r="D67" s="15" t="n">
-        <v>154.11</v>
+        <v>153.96</v>
       </c>
       <c r="E67" s="16" t="n">
-        <v>0.1295</v>
+        <v>0.1284</v>
       </c>
       <c r="F67" s="16" t="n">
-        <v>0.0279</v>
+        <v>0.0269</v>
       </c>
       <c r="G67" s="17" t="n"/>
       <c r="H67" s="22" t="inlineStr">
@@ -6025,7 +6025,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="16" t="n">
-        <v>0.2004412432677956</v>
+        <v>0.2016108080020784</v>
       </c>
       <c r="N67" s="14" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>0.2004412432677956</v>
+        <v>0.2016108080020784</v>
       </c>
       <c r="Q67" s="20" t="inlineStr">
         <is>
@@ -6081,13 +6081,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>125.24</v>
+        <v>125.15</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0.0396</v>
+        <v>0.0388</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.0592</v>
+        <v>0.0584</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>46240</v>
@@ -6116,7 +6116,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="6" t="n">
-        <v>-0.04183966783775148</v>
+        <v>-0.04115061925689177</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>115</v>
       </c>
       <c r="P68" s="6" t="n">
-        <v>-0.0817630150111785</v>
+        <v>-0.08110267678785461</v>
       </c>
       <c r="Q68" s="10" t="inlineStr"/>
       <c r="R68" s="9" t="n"/>
@@ -6162,13 +6162,13 @@
         </is>
       </c>
       <c r="D69" s="15" t="n">
-        <v>354.52</v>
+        <v>356.65</v>
       </c>
       <c r="E69" s="26" t="n">
-        <v>-0.0067</v>
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="F69" s="16" t="n">
-        <v>0.0791</v>
+        <v>0.08560000000000001</v>
       </c>
       <c r="G69" s="17" t="n"/>
       <c r="H69" s="22" t="inlineStr">
@@ -6187,7 +6187,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="16" t="n">
-        <v>0.1452104253638723</v>
+        <v>0.1383709519136409</v>
       </c>
       <c r="N69" s="14" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>0.2298318853661289</v>
+        <v>0.222487032104304</v>
       </c>
       <c r="Q69" s="20" t="inlineStr">
         <is>
@@ -6235,13 +6235,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>347.89</v>
+        <v>346.71</v>
       </c>
       <c r="E70" s="6" t="n">
-        <v>-0.0229</v>
+        <v>-0.0262</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.1198</v>
+        <v>0.116</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>46311</v>
@@ -6270,7 +6270,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.1929058035585962</v>
+        <v>0.1969657638948978</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.09229929000546154</v>
+        <v>0.09601684404834017</v>
       </c>
       <c r="Q70" s="10" t="inlineStr">
         <is>
@@ -6330,13 +6330,13 @@
         </is>
       </c>
       <c r="D71" s="15" t="n">
-        <v>63.29</v>
+        <v>62.9</v>
       </c>
       <c r="E71" s="16" t="n">
-        <v>0.0567</v>
+        <v>0.0501</v>
       </c>
       <c r="F71" s="16" t="n">
-        <v>0.1758</v>
+        <v>0.1685</v>
       </c>
       <c r="G71" s="17" t="n">
         <v>46309</v>
@@ -6391,13 +6391,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1134.9</v>
+        <v>1131.13</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0.1223</v>
+        <v>0.1186</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.1399</v>
+        <v>0.1361</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>46308</v>
@@ -6429,7 +6429,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.09701295268305569</v>
+        <v>0.1006692422621625</v>
       </c>
       <c r="Q72" s="10" t="inlineStr">
         <is>
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="D73" s="15" t="n">
-        <v>23.45</v>
+        <v>23.8</v>
       </c>
       <c r="E73" s="26" t="n">
-        <v>-0.1174</v>
+        <v>-0.1043</v>
       </c>
       <c r="F73" s="26" t="n">
-        <v>-0.1302</v>
+        <v>-0.1172</v>
       </c>
       <c r="G73" s="17" t="n">
         <v>46247</v>
@@ -6535,13 +6535,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>17.7</v>
+        <v>18.1</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0.1386</v>
+        <v>0.164</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.1135</v>
+        <v>0.1384</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>46346</v>
@@ -6596,13 +6596,13 @@
         </is>
       </c>
       <c r="D75" s="15" t="n">
-        <v>515.3200000000001</v>
+        <v>517.22</v>
       </c>
       <c r="E75" s="16" t="n">
-        <v>0.0173</v>
+        <v>0.021</v>
       </c>
       <c r="F75" s="16" t="n">
-        <v>0.0557</v>
+        <v>0.0596</v>
       </c>
       <c r="G75" s="17" t="n">
         <v>46241</v>
@@ -6679,13 +6679,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>70.90000000000001</v>
+        <v>71.17</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0.0361</v>
+        <v>0.04</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.2046</v>
+        <v>0.2091</v>
       </c>
       <c r="G76" s="7" t="n"/>
       <c r="H76" s="12" t="inlineStr">
@@ -6704,7 +6704,7 @@
         <v>68</v>
       </c>
       <c r="M76" s="6" t="n">
-        <v>-0.04090267983074761</v>
+        <v>-0.04454123928621612</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="9" t="n"/>
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="D77" s="15" t="n">
-        <v>137.12</v>
+        <v>137.2</v>
       </c>
       <c r="E77" s="16" t="n">
-        <v>0.111</v>
+        <v>0.1117</v>
       </c>
       <c r="F77" s="16" t="n">
-        <v>0.1887</v>
+        <v>0.1894</v>
       </c>
       <c r="G77" s="17" t="n">
         <v>46310</v>
@@ -6811,13 +6811,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>137.19</v>
+        <v>136.87</v>
       </c>
       <c r="E78" s="6" t="n">
-        <v>-0.0464</v>
+        <v>-0.0486</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.0356</v>
+        <v>0.0332</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>46308</v>
@@ -6849,7 +6849,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.02048254245936294</v>
+        <v>0.02286841528457657</v>
       </c>
       <c r="Q78" s="10" t="inlineStr">
         <is>
@@ -6898,13 +6898,13 @@
         </is>
       </c>
       <c r="D79" s="15" t="n">
-        <v>346.83</v>
+        <v>348.3</v>
       </c>
       <c r="E79" s="26" t="n">
-        <v>-0.0272</v>
+        <v>-0.0231</v>
       </c>
       <c r="F79" s="16" t="n">
-        <v>0.063</v>
+        <v>0.0675</v>
       </c>
       <c r="G79" s="17" t="n">
         <v>46315</v>
@@ -6933,7 +6933,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="16" t="n">
-        <v>0.0322059798748667</v>
+        <v>0.02784955498133789</v>
       </c>
       <c r="N79" s="14" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>0.07833809070726297</v>
+        <v>0.07378696525983344</v>
       </c>
       <c r="Q79" s="20" t="inlineStr">
         <is>
@@ -6989,13 +6989,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>60.32</v>
+        <v>59.93</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0203</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0.137</v>
+        <v>0.1297</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>46310</v>
@@ -7024,7 +7024,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="6" t="n">
-        <v>-0.05503978779840849</v>
+        <v>-0.04889037210078424</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="9" t="n"/>
@@ -7066,13 +7066,13 @@
         </is>
       </c>
       <c r="D81" s="15" t="n">
-        <v>14.49</v>
+        <v>14.17</v>
       </c>
       <c r="E81" s="16" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0489</v>
       </c>
       <c r="F81" s="26" t="n">
-        <v>-0.0702</v>
+        <v>-0.0911</v>
       </c>
       <c r="G81" s="17" t="n">
         <v>46240</v>
@@ -7127,13 +7127,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>395.1</v>
+        <v>396.52</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0.1081</v>
+        <v>0.1121</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.1371</v>
+        <v>0.1412</v>
       </c>
       <c r="G82" s="7" t="n">
         <v>46239</v>
@@ -7200,13 +7200,13 @@
         </is>
       </c>
       <c r="D83" s="15" t="n">
-        <v>63.22</v>
+        <v>63.25</v>
       </c>
       <c r="E83" s="26" t="n">
-        <v>-0.07919999999999999</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="F83" s="26" t="n">
-        <v>-0.2126</v>
+        <v>-0.2121</v>
       </c>
       <c r="G83" s="17" t="n">
         <v>46239</v>
@@ -7261,13 +7261,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>54.07</v>
+        <v>55.61</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0.0524</v>
+        <v>0.0823</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0.42</v>
+        <v>0.4603</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>46240</v>
@@ -7322,13 +7322,13 @@
         </is>
       </c>
       <c r="D85" s="15" t="n">
-        <v>1060.73</v>
-      </c>
-      <c r="E85" s="16" t="n">
-        <v>0.0052</v>
+        <v>1052.98</v>
+      </c>
+      <c r="E85" s="26" t="n">
+        <v>-0.0022</v>
       </c>
       <c r="F85" s="16" t="n">
-        <v>0.0212</v>
+        <v>0.0138</v>
       </c>
       <c r="G85" s="17" t="n">
         <v>46308</v>
@@ -7357,7 +7357,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="16" t="n">
-        <v>0.2491397433842731</v>
+        <v>0.2583334916142757</v>
       </c>
       <c r="N85" s="14" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="16" t="n">
-        <v>0.1407238411282796</v>
+        <v>0.149119641398697</v>
       </c>
       <c r="Q85" s="20" t="inlineStr">
         <is>
@@ -7409,13 +7409,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>127.71</v>
+        <v>128.25</v>
       </c>
       <c r="E86" s="6" t="n">
-        <v>-0.1034</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>-0.0828</v>
+        <v>-0.079</v>
       </c>
       <c r="G86" s="7" t="n"/>
       <c r="H86" s="12" t="inlineStr">
@@ -7460,13 +7460,13 @@
         </is>
       </c>
       <c r="D87" s="15" t="n">
-        <v>93.2</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="E87" s="26" t="n">
-        <v>-0.2071</v>
+        <v>-0.2045</v>
       </c>
       <c r="F87" s="16" t="n">
-        <v>0.1301</v>
+        <v>0.1339</v>
       </c>
       <c r="G87" s="17" t="n"/>
       <c r="H87" s="22" t="inlineStr">
@@ -7511,13 +7511,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>105.53</v>
-      </c>
-      <c r="E88" s="5" t="n">
-        <v>0.0169</v>
+        <v>101.16</v>
+      </c>
+      <c r="E88" s="6" t="n">
+        <v>-0.0252</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>-0.05980000000000001</v>
+        <v>-0.0987</v>
       </c>
       <c r="G88" s="7" t="n">
         <v>46238</v>
@@ -7572,13 +7572,13 @@
         </is>
       </c>
       <c r="D89" s="15" t="n">
-        <v>148.14</v>
+        <v>149.2</v>
       </c>
       <c r="E89" s="16" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.1059</v>
       </c>
       <c r="F89" s="16" t="n">
-        <v>0.0469</v>
+        <v>0.0544</v>
       </c>
       <c r="G89" s="17" t="n"/>
       <c r="H89" s="22" t="inlineStr">
@@ -7623,13 +7623,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>155.03</v>
+        <v>156.63</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0.0591</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.1915</v>
+        <v>0.2038</v>
       </c>
       <c r="G90" s="7" t="n">
         <v>46252</v>
@@ -7698,13 +7698,13 @@
         </is>
       </c>
       <c r="D91" s="15" t="n">
-        <v>360.41</v>
+        <v>357.52</v>
       </c>
       <c r="E91" s="16" t="n">
-        <v>0.0672</v>
+        <v>0.05860000000000001</v>
       </c>
       <c r="F91" s="16" t="n">
-        <v>0.1538</v>
+        <v>0.1445</v>
       </c>
       <c r="G91" s="17" t="n">
         <v>46308</v>
@@ -7733,7 +7733,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="26" t="n">
-        <v>-0.456174911905885</v>
+        <v>-0.4517789214589393</v>
       </c>
       <c r="N91" s="14" t="inlineStr"/>
       <c r="O91" s="19" t="n"/>
@@ -7777,13 +7777,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>107.07</v>
+        <v>108.21</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0.1157</v>
+        <v>0.1275</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.1464</v>
+        <v>0.1586</v>
       </c>
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="12" t="inlineStr">
@@ -7802,7 +7802,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>2.502381619501261</v>
+        <v>2.465483781535903</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>2.437003829270571</v>
+        <v>2.400794750947233</v>
       </c>
       <c r="Q92" s="10" t="inlineStr">
         <is>
@@ -7866,13 +7866,13 @@
         </is>
       </c>
       <c r="D93" s="15" t="n">
-        <v>362.46</v>
+        <v>362.82</v>
       </c>
       <c r="E93" s="16" t="n">
-        <v>0.04389999999999999</v>
+        <v>0.0449</v>
       </c>
       <c r="F93" s="16" t="n">
-        <v>0.184</v>
+        <v>0.1852</v>
       </c>
       <c r="G93" s="17" t="n">
         <v>46317</v>
@@ -7904,7 +7904,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="26" t="n">
-        <v>-0.6827236108812007</v>
+        <v>-0.6830384212557191</v>
       </c>
       <c r="Q93" s="20" t="inlineStr">
         <is>
@@ -7953,13 +7953,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>571.4</v>
+        <v>571.1</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0.0718</v>
+        <v>0.0713</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.1636</v>
+        <v>0.1629</v>
       </c>
       <c r="G94" s="7" t="n"/>
       <c r="H94" s="12" t="inlineStr">
@@ -7978,7 +7978,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="6" t="n">
-        <v>-0.3594679733986699</v>
+        <v>-0.3591315006128524</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="9" t="n"/>
@@ -8020,13 +8020,13 @@
         </is>
       </c>
       <c r="D95" s="15" t="n">
-        <v>1872.44</v>
+        <v>1887.65</v>
       </c>
       <c r="E95" s="26" t="n">
-        <v>-0.0534</v>
+        <v>-0.0457</v>
       </c>
       <c r="F95" s="16" t="n">
-        <v>0.0296</v>
+        <v>0.0379</v>
       </c>
       <c r="G95" s="17" t="n"/>
       <c r="H95" s="22" t="inlineStr">
@@ -8081,13 +8081,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>217.76</v>
+        <v>217.04</v>
       </c>
       <c r="E96" s="6" t="n">
-        <v>-0.0195</v>
+        <v>-0.0228</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0241</v>
       </c>
       <c r="G96" s="7" t="n">
         <v>46309</v>
@@ -8116,7 +8116,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>2.067597354886113</v>
+        <v>2.077773682270549</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>1.525716385011021</v>
+        <v>1.534095097677848</v>
       </c>
       <c r="Q96" s="10" t="inlineStr">
         <is>
@@ -8176,13 +8176,13 @@
         </is>
       </c>
       <c r="D97" s="15" t="n">
-        <v>115.05</v>
+        <v>115.25</v>
       </c>
       <c r="E97" s="16" t="n">
-        <v>0.0222</v>
+        <v>0.024</v>
       </c>
       <c r="F97" s="16" t="n">
-        <v>0.0934</v>
+        <v>0.0953</v>
       </c>
       <c r="G97" s="17" t="n"/>
       <c r="H97" s="22" t="inlineStr">
@@ -8201,7 +8201,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="16" t="n">
-        <v>1.086049543676662</v>
+        <v>1.082429501084599</v>
       </c>
       <c r="N97" s="14" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="16" t="n">
-        <v>1.086049543676662</v>
+        <v>1.082429501084599</v>
       </c>
       <c r="Q97" s="20" t="inlineStr">
         <is>
@@ -8261,13 +8261,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>255.91</v>
+        <v>254.14</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0.0108</v>
+        <v>0.0038</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.1206</v>
+        <v>0.1128</v>
       </c>
       <c r="G98" s="7" t="n">
         <v>46310</v>
@@ -8296,7 +8296,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="6" t="n">
-        <v>-0.5584385135399164</v>
+        <v>-0.5553631856457071</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="6" t="n">
-        <v>-0.5545308897659333</v>
+        <v>-0.5514283465806248</v>
       </c>
       <c r="Q98" s="10" t="inlineStr"/>
       <c r="R98" s="9" t="n"/>
@@ -8346,13 +8346,13 @@
         </is>
       </c>
       <c r="D99" s="15" t="n">
-        <v>22.11</v>
+        <v>21.56</v>
       </c>
       <c r="E99" s="26" t="n">
-        <v>-0.0332</v>
+        <v>-0.0573</v>
       </c>
       <c r="F99" s="26" t="n">
-        <v>-0.1034</v>
+        <v>-0.1257</v>
       </c>
       <c r="G99" s="17" t="n">
         <v>46239</v>
@@ -8407,13 +8407,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>14.52</v>
+        <v>14.47</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0.0101</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.1947</v>
+        <v>0.1909</v>
       </c>
       <c r="G100" s="7" t="n">
         <v>46323</v>
@@ -8468,13 +8468,13 @@
         </is>
       </c>
       <c r="D101" s="15" t="n">
-        <v>104.85</v>
+        <v>104.72</v>
       </c>
       <c r="E101" s="16" t="n">
-        <v>0.1038</v>
+        <v>0.1024</v>
       </c>
       <c r="F101" s="16" t="n">
-        <v>0.1726</v>
+        <v>0.1711</v>
       </c>
       <c r="G101" s="17" t="n">
         <v>46323</v>
@@ -8503,7 +8503,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="16" t="n">
-        <v>1.718168812589414</v>
+        <v>1.721543162719633</v>
       </c>
       <c r="N101" s="14" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="16" t="n">
-        <v>1.718168812589414</v>
+        <v>1.721543162719633</v>
       </c>
       <c r="Q101" s="20" t="inlineStr">
         <is>
@@ -8555,13 +8555,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>413.11</v>
+        <v>412.53</v>
       </c>
       <c r="E102" s="6" t="n">
-        <v>-0.07629999999999999</v>
+        <v>-0.0776</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0.0288</v>
+        <v>0.0273</v>
       </c>
       <c r="G102" s="7" t="n"/>
       <c r="H102" s="12" t="inlineStr">
@@ -8620,13 +8620,13 @@
         </is>
       </c>
       <c r="D103" s="15" t="n">
-        <v>52.78</v>
+        <v>52.66</v>
       </c>
       <c r="E103" s="16" t="n">
-        <v>0.0264</v>
+        <v>0.0241</v>
       </c>
       <c r="F103" s="16" t="n">
-        <v>0.0727</v>
+        <v>0.0703</v>
       </c>
       <c r="G103" s="17" t="n">
         <v>46311</v>
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>369.09</v>
+        <v>369.59</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0.0331</v>
+        <v>0.0345</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.1407</v>
+        <v>0.1422</v>
       </c>
       <c r="G104" s="7" t="n"/>
       <c r="H104" s="12" t="inlineStr">
@@ -8706,7 +8706,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>0.4224172965943267</v>
+        <v>0.4204929787061339</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>0.4711858896204179</v>
+        <v>0.4691955951189157</v>
       </c>
       <c r="Q104" s="10" t="inlineStr">
         <is>
@@ -8762,13 +8762,13 @@
         </is>
       </c>
       <c r="D105" s="15" t="n">
-        <v>71.40000000000001</v>
+        <v>71.39</v>
       </c>
       <c r="E105" s="16" t="n">
-        <v>0.0068</v>
+        <v>0.0066</v>
       </c>
       <c r="F105" s="16" t="n">
-        <v>0.0413</v>
+        <v>0.0411</v>
       </c>
       <c r="G105" s="17" t="n">
         <v>46314</v>
@@ -8797,7 +8797,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="16" t="n">
-        <v>4.7703081232493</v>
+        <v>4.771116402857543</v>
       </c>
       <c r="N105" s="14" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="16" t="n">
-        <v>3.901960784313725</v>
+        <v>3.902647429611991</v>
       </c>
       <c r="Q105" s="20" t="inlineStr">
         <is>
@@ -8853,13 +8853,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>84.39</v>
+        <v>84.64</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0.0693</v>
+        <v>0.0725</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.2383</v>
+        <v>0.242</v>
       </c>
       <c r="G106" s="7" t="n">
         <v>46239</v>
@@ -8888,7 +8888,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="6" t="n">
-        <v>-0.194217324327527</v>
+        <v>-0.1965973534971645</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="6" t="n">
-        <v>-0.194217324327527</v>
+        <v>-0.1965973534971645</v>
       </c>
       <c r="Q106" s="10" t="inlineStr">
         <is>
@@ -8944,13 +8944,13 @@
         </is>
       </c>
       <c r="D107" s="15" t="n">
-        <v>243.77</v>
+        <v>243.8</v>
       </c>
       <c r="E107" s="26" t="n">
-        <v>-0.0431</v>
+        <v>-0.043</v>
       </c>
       <c r="F107" s="16" t="n">
-        <v>0.0728</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="G107" s="17" t="n"/>
       <c r="H107" s="22" t="inlineStr">
@@ -8969,7 +8969,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="16" t="n">
-        <v>0.2101571153136153</v>
+        <v>0.210008203445447</v>
       </c>
       <c r="N107" s="14" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="16" t="n">
-        <v>0.009147967346268982</v>
+        <v>0.009023789991796507</v>
       </c>
       <c r="Q107" s="20" t="inlineStr">
         <is>
@@ -9017,13 +9017,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>106.09</v>
+        <v>105.46</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0.1094</v>
+        <v>0.1028</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.1649</v>
+        <v>0.158</v>
       </c>
       <c r="G108" s="7" t="n">
         <v>46316</v>
@@ -9052,7 +9052,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0.05570741822980485</v>
+        <v>0.0620140337568747</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>0.1311150909605052</v>
+        <v>0.1378721790252229</v>
       </c>
       <c r="Q108" s="10" t="inlineStr">
         <is>
@@ -9116,13 +9116,13 @@
         </is>
       </c>
       <c r="D109" s="15" t="n">
-        <v>387.02</v>
+        <v>390.02</v>
       </c>
       <c r="E109" s="16" t="n">
-        <v>0.0562</v>
+        <v>0.0643</v>
       </c>
       <c r="F109" s="16" t="n">
-        <v>0.1071</v>
+        <v>0.1157</v>
       </c>
       <c r="G109" s="17" t="n">
         <v>46238</v>
@@ -9150,8 +9150,8 @@
       <c r="L109" s="19" t="n">
         <v>390</v>
       </c>
-      <c r="M109" s="16" t="n">
-        <v>0.007699860472327059</v>
+      <c r="M109" s="26" t="n">
+        <v>-5.127942156807808e-05</v>
       </c>
       <c r="N109" s="14" t="inlineStr">
         <is>
@@ -9199,13 +9199,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>170.5</v>
+        <v>170.12</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.09369999999999999</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.1279</v>
+        <v>0.1254</v>
       </c>
       <c r="G110" s="7" t="n">
         <v>46240</v>
@@ -9234,7 +9234,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="6" t="n">
-        <v>-0.05571847507331378</v>
+        <v>-0.05360921702327771</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>0.05571847507331378</v>
+        <v>0.05807665177521747</v>
       </c>
       <c r="Q110" s="10" t="inlineStr">
         <is>
@@ -9286,13 +9286,13 @@
         </is>
       </c>
       <c r="D111" s="15" t="n">
-        <v>48.83</v>
+        <v>49.09</v>
       </c>
       <c r="E111" s="16" t="n">
-        <v>0.09480000000000001</v>
+        <v>0.1007</v>
       </c>
       <c r="F111" s="16" t="n">
-        <v>0.0058</v>
+        <v>0.0111</v>
       </c>
       <c r="G111" s="17" t="n"/>
       <c r="H111" s="22" t="inlineStr">
@@ -9311,7 +9311,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="16" t="n">
-        <v>0.1263567479008806</v>
+        <v>0.1203911183540435</v>
       </c>
       <c r="N111" s="14" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="16" t="n">
-        <v>0.331148883882859</v>
+        <v>0.324098594418415</v>
       </c>
       <c r="Q111" s="20" t="inlineStr">
         <is>
@@ -9363,13 +9363,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>304.91</v>
+        <v>306.28</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0.0213</v>
+        <v>0.0259</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.1086</v>
+        <v>0.1136</v>
       </c>
       <c r="G112" s="7" t="n">
         <v>46239</v>
@@ -9398,7 +9398,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>0.08556623265881727</v>
+        <v>0.08071046101606383</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="5" t="n">
-        <v>0.08228657636679668</v>
+        <v>0.07744547472900623</v>
       </c>
       <c r="Q112" s="10" t="inlineStr">
         <is>
@@ -9458,13 +9458,13 @@
         </is>
       </c>
       <c r="D113" s="15" t="n">
-        <v>104.53</v>
+        <v>104.42</v>
       </c>
       <c r="E113" s="16" t="n">
-        <v>0.024</v>
+        <v>0.0229</v>
       </c>
       <c r="F113" s="16" t="n">
-        <v>0.08960000000000001</v>
+        <v>0.0885</v>
       </c>
       <c r="G113" s="17" t="n">
         <v>46239</v>
@@ -9493,7 +9493,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="16" t="n">
-        <v>0.1766956854491533</v>
+        <v>0.1779352614441678</v>
       </c>
       <c r="N113" s="14" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="16" t="n">
-        <v>0.2436621065722759</v>
+        <v>0.2449722275426163</v>
       </c>
       <c r="Q113" s="20" t="inlineStr">
         <is>
@@ -9545,13 +9545,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>198.1</v>
+        <v>194.78</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0.0231</v>
+        <v>0.006</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.07490000000000001</v>
+        <v>0.05690000000000001</v>
       </c>
       <c r="G114" s="7" t="n">
         <v>46315</v>
@@ -9580,7 +9580,7 @@
         <v>212</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>0.07016658253407373</v>
+        <v>0.08840743402813429</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="5" t="n">
-        <v>0.03483089348813733</v>
+        <v>0.05246945271588458</v>
       </c>
       <c r="Q114" s="10" t="inlineStr">
         <is>
@@ -9636,13 +9636,13 @@
         </is>
       </c>
       <c r="D115" s="15" t="n">
-        <v>87.14</v>
+        <v>86.94</v>
       </c>
       <c r="E115" s="16" t="n">
-        <v>0.2039</v>
+        <v>0.2012</v>
       </c>
       <c r="F115" s="16" t="n">
-        <v>0.196</v>
+        <v>0.1932</v>
       </c>
       <c r="G115" s="17" t="n"/>
       <c r="H115" s="22" t="inlineStr">
@@ -9661,7 +9661,7 @@
         <v>85</v>
       </c>
       <c r="M115" s="26" t="n">
-        <v>-0.02455818223548314</v>
+        <v>-0.02231423970554403</v>
       </c>
       <c r="N115" s="14" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="16" t="n">
-        <v>0.03282074822125315</v>
+        <v>0.03519668737060044</v>
       </c>
       <c r="Q115" s="20" t="inlineStr">
         <is>
@@ -9713,13 +9713,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>131.26</v>
+        <v>135.25</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0.0127</v>
+        <v>0.0435</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0472</v>
       </c>
       <c r="G116" s="7" t="n">
         <v>46238</v>
@@ -9748,7 +9748,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>0.2570470821270761</v>
+        <v>0.2199630314232902</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="9" t="n"/>
@@ -9796,13 +9796,13 @@
         </is>
       </c>
       <c r="D117" s="15" t="n">
-        <v>598.98</v>
+        <v>588.09</v>
       </c>
       <c r="E117" s="16" t="n">
-        <v>0.0602</v>
+        <v>0.0409</v>
       </c>
       <c r="F117" s="16" t="n">
-        <v>0.0655</v>
+        <v>0.0461</v>
       </c>
       <c r="G117" s="17" t="n">
         <v>46238</v>
@@ -9867,13 +9867,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>366.84</v>
+        <v>368.27</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>-0.1525</v>
+        <v>-0.1492</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>-0.1308</v>
+        <v>-0.1275</v>
       </c>
       <c r="G118" s="7" t="n">
         <v>46315</v>
@@ -9902,7 +9902,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>0.3275542470831971</v>
+        <v>0.3223993265810411</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>375</v>
       </c>
       <c r="P118" s="5" t="n">
-        <v>0.02224403009486432</v>
+        <v>0.01827463545768056</v>
       </c>
       <c r="Q118" s="10" t="inlineStr">
         <is>
@@ -9958,13 +9958,13 @@
         </is>
       </c>
       <c r="D119" s="15" t="n">
-        <v>253.57</v>
+        <v>254.93</v>
       </c>
       <c r="E119" s="26" t="n">
-        <v>-0.0222</v>
+        <v>-0.017</v>
       </c>
       <c r="F119" s="16" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.09519999999999999</v>
       </c>
       <c r="G119" s="17" t="n">
         <v>46315</v>
@@ -9993,7 +9993,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="16" t="n">
-        <v>0.07268209961746266</v>
+        <v>0.06695955752559524</v>
       </c>
       <c r="N119" s="14" t="inlineStr"/>
       <c r="O119" s="19" t="n"/>
@@ -10045,13 +10045,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1118.9</v>
+        <v>1115.68</v>
       </c>
       <c r="E120" s="6" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0703</v>
       </c>
       <c r="F120" s="6" t="n">
-        <v>-0.0111</v>
+        <v>-0.0139</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>46239</v>
@@ -10080,7 +10080,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>0.1439806953257663</v>
+        <v>0.1472823748745159</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -10140,13 +10140,13 @@
         </is>
       </c>
       <c r="D121" s="15" t="n">
-        <v>86.06999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="E121" s="16" t="n">
-        <v>0.0362</v>
+        <v>0.0378</v>
       </c>
       <c r="F121" s="16" t="n">
-        <v>0.0539</v>
+        <v>0.0555</v>
       </c>
       <c r="G121" s="17" t="n">
         <v>46266</v>
@@ -10175,7 +10175,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="16" t="n">
-        <v>0.1850819100731963</v>
+        <v>0.1832946635730858</v>
       </c>
       <c r="N121" s="14" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="16" t="n">
-        <v>0.2199372603694668</v>
+        <v>0.2180974477958236</v>
       </c>
       <c r="Q121" s="20" t="inlineStr">
         <is>
@@ -10227,13 +10227,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>128.79</v>
+        <v>128</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0597</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>46238</v>
@@ -10262,7 +10262,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>0.1646866992778943</v>
+        <v>0.171875</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="9" t="n"/>
@@ -10306,13 +10306,13 @@
         </is>
       </c>
       <c r="D123" s="15" t="n">
-        <v>153.35</v>
+        <v>153.27</v>
       </c>
       <c r="E123" s="26" t="n">
-        <v>-0.0138</v>
+        <v>-0.0143</v>
       </c>
       <c r="F123" s="16" t="n">
-        <v>0.0281</v>
+        <v>0.0276</v>
       </c>
       <c r="G123" s="17" t="n">
         <v>46322</v>
@@ -10385,13 +10385,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>25.46</v>
+        <v>25.41</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.07339999999999999</v>
+        <v>0.0712</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>-0.0223</v>
+        <v>-0.0242</v>
       </c>
       <c r="G124" s="7" t="n">
         <v>46238</v>
@@ -10420,7 +10420,7 @@
         <v>28</v>
       </c>
       <c r="M124" s="5" t="n">
-        <v>0.09976433621366847</v>
+        <v>0.1019283746556474</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="9" t="n"/>
@@ -10464,13 +10464,13 @@
         </is>
       </c>
       <c r="D125" s="15" t="n">
-        <v>335.79</v>
+        <v>335.96</v>
       </c>
       <c r="E125" s="16" t="n">
-        <v>0.034</v>
+        <v>0.0346</v>
       </c>
       <c r="F125" s="16" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.09910000000000001</v>
       </c>
       <c r="G125" s="17" t="n"/>
       <c r="H125" s="22" t="inlineStr">
@@ -10489,7 +10489,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="16" t="n">
-        <v>0.2448256350695374</v>
+        <v>0.2441957375878082</v>
       </c>
       <c r="N125" s="14" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="16" t="n">
-        <v>0.04231811548884713</v>
+        <v>0.04179068936778194</v>
       </c>
       <c r="Q125" s="20" t="inlineStr">
         <is>
@@ -10545,13 +10545,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>567.76</v>
+        <v>564.75</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0.0969</v>
+        <v>0.0911</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>0.2008</v>
+        <v>0.1945</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>46323</v>
@@ -10580,7 +10580,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>0.08320417077638441</v>
+        <v>0.08897742363877822</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="5" t="n">
-        <v>0.003945329012258717</v>
+        <v>0.009296148738379814</v>
       </c>
       <c r="Q126" s="10" t="inlineStr">
         <is>
@@ -10640,13 +10640,13 @@
         </is>
       </c>
       <c r="D127" s="15" t="n">
-        <v>411.18</v>
+        <v>407.55</v>
       </c>
       <c r="E127" s="26" t="n">
-        <v>-0.0163</v>
+        <v>-0.025</v>
       </c>
       <c r="F127" s="16" t="n">
-        <v>0.0293</v>
+        <v>0.0202</v>
       </c>
       <c r="G127" s="17" t="n">
         <v>46322</v>
@@ -10675,7 +10675,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="16" t="n">
-        <v>0.2792450994698186</v>
+        <v>0.2906391853760275</v>
       </c>
       <c r="N127" s="14" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="16" t="n">
-        <v>0.1673719538888078</v>
+        <v>0.1777695988222304</v>
       </c>
       <c r="Q127" s="20" t="inlineStr">
         <is>
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>75.58</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="F128" s="6" t="n">
-        <v>-0.04849999999999999</v>
+        <v>-0.0428</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>46240</v>
@@ -10810,13 +10810,13 @@
         </is>
       </c>
       <c r="D129" s="15" t="n">
-        <v>267.19</v>
+        <v>270.62</v>
       </c>
       <c r="E129" s="16" t="n">
-        <v>0.1157</v>
+        <v>0.13</v>
       </c>
       <c r="F129" s="16" t="n">
-        <v>0.1519</v>
+        <v>0.1667</v>
       </c>
       <c r="G129" s="17" t="n"/>
       <c r="H129" s="22" t="inlineStr">
@@ -10835,7 +10835,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="26" t="n">
-        <v>-0.07182155020771734</v>
+        <v>-0.08358583992313948</v>
       </c>
       <c r="N129" s="14" t="inlineStr"/>
       <c r="O129" s="19" t="n"/>
@@ -10891,13 +10891,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>107.07</v>
+        <v>107.2</v>
       </c>
       <c r="E130" s="6" t="n">
-        <v>-0.0951</v>
+        <v>-0.094</v>
       </c>
       <c r="F130" s="6" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.0791</v>
       </c>
       <c r="G130" s="7" t="n"/>
       <c r="H130" s="12" t="inlineStr">
@@ -10942,13 +10942,13 @@
         </is>
       </c>
       <c r="D131" s="15" t="n">
-        <v>246.7</v>
+        <v>254.05</v>
       </c>
       <c r="E131" s="16" t="n">
-        <v>0.0403</v>
+        <v>0.0713</v>
       </c>
       <c r="F131" s="16" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1214</v>
       </c>
       <c r="G131" s="17" t="n">
         <v>46238</v>
@@ -11003,13 +11003,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>237.65</v>
+        <v>237.16</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0112</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>0.103</v>
+        <v>0.1008</v>
       </c>
       <c r="G132" s="7" t="n"/>
       <c r="H132" s="12" t="inlineStr">
@@ -11028,7 +11028,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>0.0519671786240269</v>
+        <v>0.05414066453027493</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="9" t="n"/>
@@ -11072,13 +11072,13 @@
         </is>
       </c>
       <c r="D133" s="15" t="n">
-        <v>168.66</v>
+        <v>168.41</v>
       </c>
       <c r="E133" s="16" t="n">
-        <v>0.165</v>
+        <v>0.1633</v>
       </c>
       <c r="F133" s="16" t="n">
-        <v>0.1144</v>
+        <v>0.1128</v>
       </c>
       <c r="G133" s="17" t="n">
         <v>46238</v>
@@ -11143,13 +11143,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>884.1900000000001</v>
+        <v>876.54</v>
       </c>
       <c r="E134" s="6" t="n">
-        <v>-0.08839999999999999</v>
+        <v>-0.09630000000000001</v>
       </c>
       <c r="F134" s="6" t="n">
-        <v>-0.0222</v>
+        <v>-0.0307</v>
       </c>
       <c r="G134" s="7" t="n">
         <v>46238</v>
@@ -11178,7 +11178,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>0.3062803243646727</v>
+        <v>0.3176808816482991</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="5" t="n">
-        <v>0.2474694353023671</v>
+        <v>0.2583567207429211</v>
       </c>
       <c r="Q134" s="10" t="inlineStr">
         <is>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="D135" s="15" t="n">
-        <v>627.1</v>
+        <v>635.96</v>
       </c>
       <c r="E135" s="26" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0623</v>
       </c>
       <c r="F135" s="26" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.0234</v>
       </c>
       <c r="G135" s="17" t="n">
         <v>46238</v>
@@ -11265,7 +11265,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="16" t="n">
-        <v>0.3937171105086907</v>
+        <v>0.3743002704572614</v>
       </c>
       <c r="N135" s="14" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="16" t="n">
-        <v>0.3474724924254504</v>
+        <v>0.3286999182338511</v>
       </c>
       <c r="Q135" s="20" t="inlineStr">
         <is>
@@ -11325,13 +11325,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>203.7</v>
+        <v>203.65</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0.1428</v>
+        <v>0.1426</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>0.1326</v>
+        <v>0.1323</v>
       </c>
       <c r="G136" s="7" t="n">
         <v>46288</v>
@@ -11360,7 +11360,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>0.2272950417280315</v>
+        <v>0.2275963663147557</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="9" t="n"/>
@@ -11404,13 +11404,13 @@
         </is>
       </c>
       <c r="D137" s="15" t="n">
-        <v>620.36</v>
+        <v>617.37</v>
       </c>
       <c r="E137" s="26" t="n">
-        <v>-0.0234</v>
+        <v>-0.0281</v>
       </c>
       <c r="F137" s="16" t="n">
-        <v>0.0633</v>
+        <v>0.0582</v>
       </c>
       <c r="G137" s="17" t="n">
         <v>46254</v>
@@ -11439,7 +11439,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="16" t="n">
-        <v>0.2089754336191888</v>
+        <v>0.2148306526070266</v>
       </c>
       <c r="N137" s="14" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="16" t="n">
-        <v>0.03373847443419942</v>
+        <v>0.0387449989471467</v>
       </c>
       <c r="Q137" s="20" t="inlineStr">
         <is>
@@ -11491,13 +11491,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>153.97</v>
+        <v>158.84</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0.0877</v>
+        <v>0.1221</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.1148</v>
+        <v>0.15</v>
       </c>
       <c r="G138" s="7" t="n">
         <v>46238</v>
@@ -11533,7 +11533,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="5" t="n">
-        <v>0.2015327661232708</v>
+        <v>0.1646940317300428</v>
       </c>
       <c r="Q138" s="10" t="inlineStr">
         <is>
@@ -11572,13 +11572,13 @@
         </is>
       </c>
       <c r="D139" s="15" t="n">
-        <v>441.53</v>
+        <v>444.77</v>
       </c>
       <c r="E139" s="16" t="n">
-        <v>0.068</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="F139" s="16" t="n">
-        <v>0.1151</v>
+        <v>0.1233</v>
       </c>
       <c r="G139" s="17" t="n"/>
       <c r="H139" s="22" t="inlineStr">
@@ -11604,7 +11604,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="16" t="n">
-        <v>0.02597784974973394</v>
+        <v>0.01850394585965784</v>
       </c>
       <c r="Q139" s="20" t="inlineStr">
         <is>
@@ -11645,13 +11645,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>49.02</v>
+        <v>49.71</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.029</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>0.04769999999999999</v>
+        <v>0.0624</v>
       </c>
       <c r="G140" s="7" t="n">
         <v>46309</v>
@@ -11724,13 +11724,13 @@
         </is>
       </c>
       <c r="D141" s="15" t="n">
-        <v>314.79</v>
+        <v>313.34</v>
       </c>
       <c r="E141" s="16" t="n">
-        <v>0.0157</v>
+        <v>0.011</v>
       </c>
       <c r="F141" s="26" t="n">
-        <v>-0.049</v>
+        <v>-0.0534</v>
       </c>
       <c r="G141" s="17" t="n">
         <v>46282</v>
@@ -11759,7 +11759,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="16" t="n">
-        <v>0.3501064201531179</v>
+        <v>0.3563541201251038</v>
       </c>
       <c r="N141" s="14" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="16" t="n">
-        <v>0.02608087931636958</v>
+        <v>0.03082913129507891</v>
       </c>
       <c r="Q141" s="20" t="inlineStr">
         <is>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>255.38</v>
+        <v>255.51</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0.1156</v>
+        <v>0.1162</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>0.1124</v>
+        <v>0.1129</v>
       </c>
       <c r="G142" s="7" t="n">
         <v>46244</v>
@@ -11846,7 +11846,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="5" t="n">
-        <v>0.1159840238076592</v>
+        <v>0.1154162263707879</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="9" t="n"/>
@@ -11894,13 +11894,13 @@
         </is>
       </c>
       <c r="D143" s="15" t="n">
-        <v>1780.08</v>
+        <v>1775.86</v>
       </c>
       <c r="E143" s="26" t="n">
-        <v>-0.0072</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F143" s="26" t="n">
-        <v>-0.0346</v>
+        <v>-0.0369</v>
       </c>
       <c r="G143" s="17" t="n">
         <v>46317</v>
@@ -12016,13 +12016,13 @@
         </is>
       </c>
       <c r="D145" s="15" t="n">
-        <v>385.72</v>
+        <v>385.76</v>
       </c>
       <c r="E145" s="16" t="n">
-        <v>0.0235</v>
+        <v>0.0236</v>
       </c>
       <c r="F145" s="16" t="n">
-        <v>0.1134</v>
+        <v>0.1135</v>
       </c>
       <c r="G145" s="17" t="n"/>
       <c r="H145" s="22" t="inlineStr">
@@ -12041,7 +12041,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="16" t="n">
-        <v>0.03702167375298136</v>
+        <v>0.03691414350891749</v>
       </c>
       <c r="N145" s="14" t="inlineStr"/>
       <c r="O145" s="19" t="n"/>
@@ -12093,13 +12093,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>376.92</v>
+        <v>377.28</v>
       </c>
       <c r="E146" s="6" t="n">
-        <v>-0.0046</v>
+        <v>-0.0037</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>0.1491</v>
+        <v>0.1502</v>
       </c>
       <c r="G146" s="7" t="n">
         <v>46315</v>
@@ -12128,7 +12128,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="5" t="n">
-        <v>0.03470232410060486</v>
+        <v>0.03371501272264638</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="9" t="n"/>
@@ -12180,13 +12180,13 @@
         </is>
       </c>
       <c r="D147" s="15" t="n">
-        <v>1019.26</v>
+        <v>1018.53</v>
       </c>
       <c r="E147" s="26" t="n">
-        <v>-0.1153</v>
+        <v>-0.1159</v>
       </c>
       <c r="F147" s="16" t="n">
-        <v>0.0917</v>
+        <v>0.091</v>
       </c>
       <c r="G147" s="17" t="n">
         <v>46316</v>
@@ -12215,7 +12215,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="16" t="n">
-        <v>0.2352098581323706</v>
+        <v>0.2360951567455058</v>
       </c>
       <c r="N147" s="14" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="16" t="n">
-        <v>0.3244903165041305</v>
+        <v>0.3254396041353716</v>
       </c>
       <c r="Q147" s="20" t="inlineStr">
         <is>
@@ -12271,13 +12271,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1303.26</v>
+        <v>1300.45</v>
       </c>
       <c r="E148" s="6" t="n">
-        <v>-0.0488</v>
+        <v>-0.0509</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0003</v>
       </c>
       <c r="G148" s="7" t="n">
         <v>46238</v>
@@ -12346,13 +12346,13 @@
         </is>
       </c>
       <c r="D149" s="15" t="n">
-        <v>249.17</v>
+        <v>248.79</v>
       </c>
       <c r="E149" s="16" t="n">
-        <v>0.07780000000000001</v>
+        <v>0.0762</v>
       </c>
       <c r="F149" s="16" t="n">
-        <v>0.1104</v>
+        <v>0.1087</v>
       </c>
       <c r="G149" s="17" t="n">
         <v>46317</v>
@@ -12407,13 +12407,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>497.41</v>
+        <v>502.24</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>0.0037</v>
+        <v>0.0134</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>0.0432</v>
+        <v>0.0533</v>
       </c>
       <c r="G150" s="7" t="n"/>
       <c r="H150" s="12" t="inlineStr">
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="D151" s="15" t="n">
-        <v>295.35</v>
+        <v>295.06</v>
       </c>
       <c r="E151" s="16" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="F151" s="16" t="n">
-        <v>0.1687</v>
+        <v>0.1675</v>
       </c>
       <c r="G151" s="17" t="n"/>
       <c r="H151" s="22" t="inlineStr">
@@ -12492,7 +12492,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="26" t="n">
-        <v>-0.07905874386321321</v>
+        <v>-0.07815359587880431</v>
       </c>
       <c r="Q151" s="20" t="inlineStr">
         <is>
@@ -12545,13 +12545,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>285.04</v>
+        <v>285.3</v>
       </c>
       <c r="E152" s="6" t="n">
-        <v>-0.0539</v>
+        <v>-0.053</v>
       </c>
       <c r="F152" s="6" t="n">
-        <v>-0.07400000000000001</v>
+        <v>-0.0732</v>
       </c>
       <c r="G152" s="7" t="n"/>
       <c r="H152" s="12" t="inlineStr">
@@ -12606,13 +12606,13 @@
         </is>
       </c>
       <c r="D153" s="15" t="n">
-        <v>446.45</v>
+        <v>446.74</v>
       </c>
       <c r="E153" s="26" t="n">
-        <v>-0.214</v>
+        <v>-0.2135</v>
       </c>
       <c r="F153" s="26" t="n">
-        <v>-0.1219</v>
+        <v>-0.1213</v>
       </c>
       <c r="G153" s="17" t="n"/>
       <c r="H153" s="22" t="inlineStr">
@@ -12657,13 +12657,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>588.9299999999999</v>
+        <v>589.33</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.09539999999999998</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0.1244</v>
+        <v>0.1252</v>
       </c>
       <c r="G154" s="7" t="n">
         <v>46315</v>
@@ -12724,13 +12724,13 @@
         </is>
       </c>
       <c r="D155" s="15" t="n">
-        <v>217.47</v>
+        <v>219.32</v>
       </c>
       <c r="E155" s="16" t="n">
-        <v>0.0048</v>
+        <v>0.0133</v>
       </c>
       <c r="F155" s="26" t="n">
-        <v>-0.1035</v>
+        <v>-0.0958</v>
       </c>
       <c r="G155" s="17" t="n"/>
       <c r="H155" s="22" t="inlineStr">
@@ -12749,7 +12749,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="16" t="n">
-        <v>1.644042856485952</v>
+        <v>1.621739923399599</v>
       </c>
       <c r="N155" s="14" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="16" t="n">
-        <v>0.0898054904124707</v>
+        <v>0.0806128032099216</v>
       </c>
       <c r="Q155" s="20" t="inlineStr">
         <is>
@@ -12809,13 +12809,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>117.41</v>
+        <v>118.66</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0.1141</v>
+        <v>0.1259</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.1679</v>
+        <v>0.1803</v>
       </c>
       <c r="G156" s="7" t="n">
         <v>46294</v>
@@ -12844,7 +12844,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="5" t="n">
-        <v>1.129290520398603</v>
+        <v>1.106859935951458</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="9" t="n"/>
@@ -12888,13 +12888,13 @@
         </is>
       </c>
       <c r="D157" s="15" t="n">
-        <v>135.16</v>
+        <v>135.96</v>
       </c>
       <c r="E157" s="16" t="n">
-        <v>0.0735</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="F157" s="16" t="n">
-        <v>0.1584</v>
+        <v>0.1652</v>
       </c>
       <c r="G157" s="17" t="n"/>
       <c r="H157" s="22" t="inlineStr">
@@ -12913,7 +12913,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="26" t="n">
-        <v>-0.2971293282036105</v>
+        <v>-0.3012650779641071</v>
       </c>
       <c r="N157" s="14" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="16" t="n">
-        <v>0.02841077241787514</v>
+        <v>0.02235951750514851</v>
       </c>
       <c r="Q157" s="20" t="inlineStr">
         <is>
@@ -12969,13 +12969,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>993.84</v>
+        <v>992.65</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>0.0231</v>
+        <v>0.0219</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>0.1264</v>
+        <v>0.125</v>
       </c>
       <c r="G158" s="7" t="n">
         <v>46240</v>
@@ -13004,7 +13004,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="6" t="n">
-        <v>-0.8742252274007889</v>
+        <v>-0.8740744471868231</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="5" t="n">
-        <v>0.0705948643644852</v>
+        <v>0.07187830554576137</v>
       </c>
       <c r="Q158" s="10" t="inlineStr">
         <is>
@@ -13060,13 +13060,13 @@
         </is>
       </c>
       <c r="D159" s="15" t="n">
-        <v>573.21</v>
+        <v>565.96</v>
       </c>
       <c r="E159" s="26" t="n">
-        <v>-0.0597</v>
+        <v>-0.0716</v>
       </c>
       <c r="F159" s="26" t="n">
-        <v>-0.0286</v>
+        <v>-0.0409</v>
       </c>
       <c r="G159" s="17" t="n"/>
       <c r="H159" s="22" t="inlineStr">
@@ -13131,13 +13131,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>444.67</v>
+        <v>445.23</v>
       </c>
       <c r="E160" s="6" t="n">
-        <v>-0.0791</v>
+        <v>-0.078</v>
       </c>
       <c r="F160" s="6" t="n">
-        <v>-0.0046</v>
+        <v>-0.0033</v>
       </c>
       <c r="G160" s="7" t="n">
         <v>46238</v>
@@ -13192,13 +13192,13 @@
         </is>
       </c>
       <c r="D161" s="15" t="n">
-        <v>37.79</v>
+        <v>37.81</v>
       </c>
       <c r="E161" s="26" t="n">
-        <v>-0.1156</v>
+        <v>-0.1151</v>
       </c>
       <c r="F161" s="26" t="n">
-        <v>-0.1977</v>
+        <v>-0.1972</v>
       </c>
       <c r="G161" s="17" t="n">
         <v>46323</v>
@@ -13267,13 +13267,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>217.38</v>
+        <v>217.93</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>0.0795</v>
+        <v>0.08220000000000001</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>0.2011</v>
+        <v>0.2041</v>
       </c>
       <c r="G162" s="7" t="n">
         <v>46322</v>
@@ -13346,13 +13346,13 @@
         </is>
       </c>
       <c r="D163" s="15" t="n">
-        <v>47.39</v>
+        <v>47.46</v>
       </c>
       <c r="E163" s="16" t="n">
-        <v>0.0659</v>
+        <v>0.0675</v>
       </c>
       <c r="F163" s="16" t="n">
-        <v>0.0766</v>
+        <v>0.0781</v>
       </c>
       <c r="G163" s="17" t="n">
         <v>46239</v>
@@ -13407,13 +13407,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>471.42</v>
+        <v>472.24</v>
       </c>
       <c r="E164" s="6" t="n">
-        <v>-0.0325</v>
+        <v>-0.0308</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>0.0319</v>
+        <v>0.0337</v>
       </c>
       <c r="G164" s="7" t="n"/>
       <c r="H164" s="12" t="inlineStr">
@@ -13435,7 +13435,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="5" t="n">
-        <v>0.1879003860676254</v>
+        <v>0.1858377096391665</v>
       </c>
       <c r="Q164" s="10" t="inlineStr">
         <is>
@@ -13488,13 +13488,13 @@
         </is>
       </c>
       <c r="D165" s="15" t="n">
-        <v>295.24</v>
+        <v>296.35</v>
       </c>
       <c r="E165" s="16" t="n">
-        <v>0.04480000000000001</v>
+        <v>0.0487</v>
       </c>
       <c r="F165" s="16" t="n">
-        <v>0.0842</v>
+        <v>0.0882</v>
       </c>
       <c r="G165" s="17" t="n">
         <v>46317</v>
@@ -13526,7 +13526,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="26" t="n">
-        <v>-0.004199972903400653</v>
+        <v>-0.007929812721444314</v>
       </c>
       <c r="Q165" s="20" t="inlineStr">
         <is>
@@ -13571,13 +13571,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>273.27</v>
+        <v>269.93</v>
       </c>
       <c r="E166" s="6" t="n">
-        <v>-0.1419</v>
+        <v>-0.1524</v>
       </c>
       <c r="F166" s="6" t="n">
-        <v>-0.0906</v>
+        <v>-0.1018</v>
       </c>
       <c r="G166" s="7" t="n"/>
       <c r="H166" s="12" t="inlineStr">
@@ -13599,7 +13599,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="5" t="n">
-        <v>0.5552384088996232</v>
+        <v>0.574482273181936</v>
       </c>
       <c r="Q166" s="10" t="inlineStr">
         <is>
@@ -13640,13 +13640,13 @@
         </is>
       </c>
       <c r="D167" s="15" t="n">
-        <v>225.56</v>
+        <v>225.25</v>
       </c>
       <c r="E167" s="26" t="n">
-        <v>-0.0149</v>
+        <v>-0.0163</v>
       </c>
       <c r="F167" s="16" t="n">
-        <v>0.0234</v>
+        <v>0.022</v>
       </c>
       <c r="G167" s="17" t="n"/>
       <c r="H167" s="22" t="inlineStr">
@@ -13665,7 +13665,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="16" t="n">
-        <v>0.1881539280014187</v>
+        <v>0.1897891231964484</v>
       </c>
       <c r="N167" s="14" t="inlineStr"/>
       <c r="O167" s="19" t="n"/>
@@ -13713,13 +13713,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>333.86</v>
+        <v>335.07</v>
       </c>
       <c r="E168" s="6" t="n">
-        <v>-0.1634</v>
+        <v>-0.1604</v>
       </c>
       <c r="F168" s="6" t="n">
-        <v>-0.101</v>
+        <v>-0.0978</v>
       </c>
       <c r="G168" s="7" t="n"/>
       <c r="H168" s="12" t="inlineStr">
@@ -13778,13 +13778,13 @@
         </is>
       </c>
       <c r="D169" s="15" t="n">
-        <v>374.67</v>
+        <v>373.67</v>
       </c>
       <c r="E169" s="26" t="n">
-        <v>-0.1153</v>
+        <v>-0.1176</v>
       </c>
       <c r="F169" s="16" t="n">
-        <v>0.0473</v>
+        <v>0.0445</v>
       </c>
       <c r="G169" s="17" t="n"/>
       <c r="H169" s="22" t="inlineStr">
@@ -13847,13 +13847,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>121.36</v>
+        <v>122.17</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.023</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>0.1039</v>
+        <v>0.1112</v>
       </c>
       <c r="G170" s="7" t="n"/>
       <c r="H170" s="12" t="inlineStr">
@@ -13916,13 +13916,13 @@
         </is>
       </c>
       <c r="D171" s="15" t="n">
-        <v>134.45</v>
+        <v>131.63</v>
       </c>
       <c r="E171" s="16" t="n">
-        <v>0.08990000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="F171" s="26" t="n">
-        <v>-0.2404</v>
+        <v>-0.2563</v>
       </c>
       <c r="G171" s="17" t="n">
         <v>46240</v>
@@ -13977,13 +13977,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>310.33</v>
+        <v>309.38</v>
       </c>
       <c r="E172" s="6" t="n">
-        <v>-0.0075</v>
+        <v>-0.0105</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>0.0097</v>
+        <v>0.0066</v>
       </c>
       <c r="G172" s="7" t="n"/>
       <c r="H172" s="12" t="inlineStr">
@@ -14001,8 +14001,8 @@
       <c r="L172" s="9" t="n">
         <v>310</v>
       </c>
-      <c r="M172" s="6" t="n">
-        <v>-0.00106338413946439</v>
+      <c r="M172" s="5" t="n">
+        <v>0.002004008016032079</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="5" t="n">
-        <v>0.1761673057712758</v>
+        <v>0.1797789126640378</v>
       </c>
       <c r="Q172" s="10" t="inlineStr">
         <is>
@@ -14070,13 +14070,13 @@
         </is>
       </c>
       <c r="D173" s="15" t="n">
-        <v>138.94</v>
+        <v>139.7</v>
       </c>
       <c r="E173" s="26" t="n">
-        <v>-0.0074</v>
+        <v>-0.0019</v>
       </c>
       <c r="F173" s="26" t="n">
-        <v>-0.0559</v>
+        <v>-0.0507</v>
       </c>
       <c r="G173" s="17" t="n">
         <v>46240</v>
@@ -14131,13 +14131,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>166.5</v>
+        <v>170.43</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>0.2157</v>
+        <v>0.2444</v>
       </c>
       <c r="F174" s="6" t="n">
-        <v>-0.0659</v>
+        <v>-0.04389999999999999</v>
       </c>
       <c r="G174" s="7" t="n">
         <v>46289</v>
@@ -14192,13 +14192,13 @@
         </is>
       </c>
       <c r="D175" s="15" t="n">
-        <v>254.18</v>
+        <v>257.49</v>
       </c>
       <c r="E175" s="16" t="n">
-        <v>0.1656</v>
+        <v>0.1808</v>
       </c>
       <c r="F175" s="16" t="n">
-        <v>0.0109</v>
+        <v>0.0241</v>
       </c>
       <c r="G175" s="17" t="n">
         <v>46275</v>
@@ -14253,13 +14253,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>377.82</v>
+        <v>380.29</v>
       </c>
       <c r="E176" s="6" t="n">
-        <v>-0.0283</v>
+        <v>-0.022</v>
       </c>
       <c r="F176" s="6" t="n">
-        <v>-0.0587</v>
+        <v>-0.0526</v>
       </c>
       <c r="G176" s="7" t="n">
         <v>46253</v>
@@ -14288,7 +14288,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="5" t="n">
-        <v>0.3630829495526971</v>
+        <v>0.3542296668332062</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="5" t="n">
-        <v>0.2545656661902493</v>
+        <v>0.2464172079202713</v>
       </c>
       <c r="Q176" s="10" t="inlineStr">
         <is>
@@ -14348,13 +14348,13 @@
         </is>
       </c>
       <c r="D177" s="15" t="n">
-        <v>235.16</v>
+        <v>237.21</v>
       </c>
       <c r="E177" s="16" t="n">
-        <v>0.1331</v>
+        <v>0.143</v>
       </c>
       <c r="F177" s="16" t="n">
-        <v>0.0226</v>
+        <v>0.0315</v>
       </c>
       <c r="G177" s="17" t="n">
         <v>46261</v>
@@ -14409,13 +14409,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>339.38</v>
+        <v>341.39</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>0.09179999999999999</v>
+        <v>0.0983</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>0.1512</v>
+        <v>0.158</v>
       </c>
       <c r="G178" s="7" t="n"/>
       <c r="H178" s="12" t="inlineStr">
@@ -14460,13 +14460,13 @@
         </is>
       </c>
       <c r="D179" s="15" t="n">
-        <v>356.76</v>
+        <v>361.67</v>
       </c>
       <c r="E179" s="26" t="n">
-        <v>-0.1756</v>
+        <v>-0.1642</v>
       </c>
       <c r="F179" s="16" t="n">
-        <v>0.1252</v>
+        <v>0.1407</v>
       </c>
       <c r="G179" s="17" t="n">
         <v>46238</v>
@@ -14521,13 +14521,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>42.77</v>
+        <v>42.85</v>
       </c>
       <c r="E180" s="6" t="n">
-        <v>-0.2438</v>
+        <v>-0.2424</v>
       </c>
       <c r="F180" s="6" t="n">
-        <v>-0.078</v>
+        <v>-0.07629999999999999</v>
       </c>
       <c r="G180" s="7" t="n"/>
       <c r="H180" s="12" t="inlineStr">
@@ -14572,13 +14572,13 @@
         </is>
       </c>
       <c r="D181" s="15" t="n">
-        <v>546.98</v>
+        <v>546.62</v>
       </c>
       <c r="E181" s="26" t="n">
-        <v>-0.07730000000000001</v>
+        <v>-0.0779</v>
       </c>
       <c r="F181" s="16" t="n">
-        <v>0.2074</v>
+        <v>0.2066</v>
       </c>
       <c r="G181" s="17" t="n">
         <v>46247</v>
@@ -14607,7 +14607,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="16" t="n">
-        <v>0.3528831035869684</v>
+        <v>0.3537741026673009</v>
       </c>
       <c r="N181" s="14" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="16" t="n">
-        <v>0.279754287176862</v>
+        <v>0.280597124144744</v>
       </c>
       <c r="Q181" s="20" t="inlineStr">
         <is>
@@ -14659,13 +14659,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>68.05</v>
+        <v>67.53</v>
       </c>
       <c r="E182" s="6" t="n">
-        <v>-0.1881</v>
+        <v>-0.1943</v>
       </c>
       <c r="F182" s="6" t="n">
-        <v>-0.08650000000000001</v>
+        <v>-0.0934</v>
       </c>
       <c r="G182" s="7" t="n">
         <v>46245</v>
@@ -14724,13 +14724,13 @@
         </is>
       </c>
       <c r="D183" s="15" t="n">
-        <v>525.79</v>
+        <v>518.58</v>
       </c>
       <c r="E183" s="26" t="n">
-        <v>-0.0476</v>
+        <v>-0.06059999999999999</v>
       </c>
       <c r="F183" s="16" t="n">
-        <v>0.1274</v>
+        <v>0.1119</v>
       </c>
       <c r="G183" s="17" t="n">
         <v>46238</v>
@@ -14759,7 +14759,7 @@
         <v>615</v>
       </c>
       <c r="M183" s="16" t="n">
-        <v>0.1696684988303316</v>
+        <v>0.1859308110609741</v>
       </c>
       <c r="N183" s="14" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="16" t="n">
-        <v>0.1012000988988</v>
+        <v>0.1165104709013073</v>
       </c>
       <c r="Q183" s="20" t="inlineStr">
         <is>
@@ -14811,13 +14811,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>56.21</v>
+        <v>55.87</v>
       </c>
       <c r="E184" s="6" t="n">
-        <v>-0.1956</v>
+        <v>-0.2005</v>
       </c>
       <c r="F184" s="6" t="n">
-        <v>-0.1346</v>
+        <v>-0.1398</v>
       </c>
       <c r="G184" s="7" t="n"/>
       <c r="H184" s="12" t="inlineStr">
@@ -14862,13 +14862,13 @@
         </is>
       </c>
       <c r="D185" s="15" t="n">
-        <v>193.57</v>
+        <v>190.51</v>
       </c>
       <c r="E185" s="16" t="n">
-        <v>0.1171</v>
+        <v>0.09939999999999999</v>
       </c>
       <c r="F185" s="16" t="n">
-        <v>0.2547</v>
+        <v>0.2349</v>
       </c>
       <c r="G185" s="17" t="n">
         <v>46238</v>
@@ -14897,7 +14897,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="16" t="n">
-        <v>0.0332179573280984</v>
+        <v>0.04981365807569162</v>
       </c>
       <c r="N185" s="14" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="16" t="n">
-        <v>0.0332179573280984</v>
+        <v>0.04981365807569162</v>
       </c>
       <c r="Q185" s="20" t="inlineStr">
         <is>
@@ -14953,13 +14953,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>171.05</v>
+        <v>171.33</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>0.0254</v>
+        <v>0.0271</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>0.2323</v>
+        <v>0.2343</v>
       </c>
       <c r="G186" s="7" t="n"/>
       <c r="H186" s="12" t="inlineStr">
@@ -14981,7 +14981,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="5" t="n">
-        <v>0.05232388190587541</v>
+        <v>0.05060409735597961</v>
       </c>
       <c r="Q186" s="10" t="inlineStr">
         <is>
@@ -15034,13 +15034,13 @@
         </is>
       </c>
       <c r="D187" s="15" t="n">
-        <v>31.42</v>
+        <v>31.27</v>
       </c>
       <c r="E187" s="26" t="n">
-        <v>-0.0622</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="F187" s="26" t="n">
-        <v>-0.2071</v>
+        <v>-0.2108</v>
       </c>
       <c r="G187" s="17" t="n"/>
       <c r="H187" s="22" t="inlineStr">
@@ -15085,13 +15085,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>275.56</v>
+        <v>280.56</v>
       </c>
       <c r="E188" s="6" t="n">
-        <v>-0.1449</v>
+        <v>-0.1293</v>
       </c>
       <c r="F188" s="6" t="n">
-        <v>-0.1965</v>
+        <v>-0.1819</v>
       </c>
       <c r="G188" s="7" t="n"/>
       <c r="H188" s="12" t="inlineStr">
@@ -15136,13 +15136,13 @@
         </is>
       </c>
       <c r="D189" s="15" t="n">
-        <v>1700.28</v>
+        <v>1711.89</v>
       </c>
       <c r="E189" s="26" t="n">
-        <v>-0.0684</v>
+        <v>-0.062</v>
       </c>
       <c r="F189" s="16" t="n">
-        <v>0.0357</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="G189" s="17" t="n">
         <v>46309</v>
@@ -15215,13 +15215,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>38.54</v>
+        <v>38.7</v>
       </c>
       <c r="E190" s="6" t="n">
-        <v>-0.1103</v>
+        <v>-0.1066</v>
       </c>
       <c r="F190" s="5" t="n">
-        <v>0.1325</v>
+        <v>0.1372</v>
       </c>
       <c r="G190" s="7" t="n"/>
       <c r="H190" s="12" t="inlineStr">
@@ -15266,13 +15266,13 @@
         </is>
       </c>
       <c r="D191" s="15" t="n">
-        <v>417.64</v>
+        <v>418.16</v>
       </c>
       <c r="E191" s="16" t="n">
-        <v>0.117</v>
+        <v>0.1184</v>
       </c>
       <c r="F191" s="16" t="n">
-        <v>0.0827</v>
+        <v>0.08410000000000001</v>
       </c>
       <c r="G191" s="17" t="n">
         <v>46268</v>
@@ -15301,7 +15301,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="16" t="n">
-        <v>0.3049516329853463</v>
+        <v>0.3033288693323129</v>
       </c>
       <c r="N191" s="14" t="inlineStr">
         <is>
@@ -15312,7 +15312,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="16" t="n">
-        <v>0.3935446796283881</v>
+        <v>0.3918117466998277</v>
       </c>
       <c r="Q191" s="20" t="inlineStr">
         <is>
@@ -15365,13 +15365,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>147.8</v>
+        <v>151.62</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>0.042</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="F192" s="6" t="n">
-        <v>-0.0999</v>
+        <v>-0.0767</v>
       </c>
       <c r="G192" s="7" t="n">
         <v>46244</v>
@@ -15426,13 +15426,13 @@
         </is>
       </c>
       <c r="D193" s="15" t="n">
-        <v>341.01</v>
+        <v>340.62</v>
       </c>
       <c r="E193" s="26" t="n">
-        <v>-0.0925</v>
+        <v>-0.0935</v>
       </c>
       <c r="F193" s="26" t="n">
-        <v>-0.0935</v>
+        <v>-0.0946</v>
       </c>
       <c r="G193" s="17" t="n"/>
       <c r="H193" s="22" t="inlineStr">
@@ -15451,7 +15451,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="16" t="n">
-        <v>0.2462977625289581</v>
+        <v>0.2477247372438494</v>
       </c>
       <c r="N193" s="14" t="inlineStr"/>
       <c r="O193" s="19" t="n"/>
@@ -15495,13 +15495,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>123.19</v>
+        <v>123.92</v>
       </c>
       <c r="E194" s="6" t="n">
-        <v>-0.1129</v>
+        <v>-0.1077</v>
       </c>
       <c r="F194" s="6" t="n">
-        <v>-0.09300000000000001</v>
+        <v>-0.0876</v>
       </c>
       <c r="G194" s="7" t="n"/>
       <c r="H194" s="12" t="inlineStr">
@@ -15546,13 +15546,13 @@
         </is>
       </c>
       <c r="D195" s="15" t="n">
-        <v>416.8</v>
+        <v>411.13</v>
       </c>
       <c r="E195" s="26" t="n">
-        <v>-0.0393</v>
+        <v>-0.05230000000000001</v>
       </c>
       <c r="F195" s="26" t="n">
-        <v>-0.1463</v>
+        <v>-0.1579</v>
       </c>
       <c r="G195" s="17" t="n">
         <v>46268</v>
@@ -15607,13 +15607,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>15.71</v>
+        <v>15.78</v>
       </c>
       <c r="E196" s="6" t="n">
-        <v>-0.0542</v>
+        <v>-0.05</v>
       </c>
       <c r="F196" s="5" t="n">
-        <v>0.1376</v>
+        <v>0.1427</v>
       </c>
       <c r="G196" s="7" t="n">
         <v>46247</v>
@@ -15668,13 +15668,13 @@
         </is>
       </c>
       <c r="D197" s="15" t="n">
-        <v>367.61</v>
+        <v>371.15</v>
       </c>
       <c r="E197" s="16" t="n">
-        <v>0.04969999999999999</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="F197" s="26" t="n">
-        <v>-0.011</v>
+        <v>-0.0015</v>
       </c>
       <c r="G197" s="17" t="n"/>
       <c r="H197" s="22" t="inlineStr">
@@ -15719,13 +15719,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>333.12</v>
+        <v>323.73</v>
       </c>
       <c r="E198" s="6" t="n">
-        <v>-0.0077</v>
+        <v>-0.0357</v>
       </c>
       <c r="F198" s="6" t="n">
-        <v>-0.1164</v>
+        <v>-0.1413</v>
       </c>
       <c r="G198" s="7" t="n">
         <v>46246</v>
@@ -15780,13 +15780,13 @@
         </is>
       </c>
       <c r="D199" s="15" t="n">
-        <v>52.77</v>
+        <v>52.84</v>
       </c>
       <c r="E199" s="26" t="n">
-        <v>-0.101</v>
+        <v>-0.0998</v>
       </c>
       <c r="F199" s="16" t="n">
-        <v>0.0594</v>
+        <v>0.0608</v>
       </c>
       <c r="G199" s="17" t="n"/>
       <c r="H199" s="22" t="inlineStr">
@@ -15831,13 +15831,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>23.16</v>
+        <v>22.81</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>0.0156</v>
+        <v>0.0004</v>
       </c>
       <c r="F200" s="6" t="n">
-        <v>-0.1043</v>
+        <v>-0.1176</v>
       </c>
       <c r="G200" s="7" t="n"/>
       <c r="H200" s="12" t="inlineStr">
@@ -15882,13 +15882,13 @@
         </is>
       </c>
       <c r="D201" s="15" t="n">
-        <v>239.69</v>
+        <v>237.92</v>
       </c>
       <c r="E201" s="26" t="n">
-        <v>-0.0974</v>
+        <v>-0.104</v>
       </c>
       <c r="F201" s="16" t="n">
-        <v>0.1585</v>
+        <v>0.15</v>
       </c>
       <c r="G201" s="17" t="n">
         <v>46267</v>
@@ -15943,13 +15943,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>189.63</v>
+        <v>190.99</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>0.1448</v>
+        <v>0.153</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>0.0214</v>
+        <v>0.0287</v>
       </c>
       <c r="G202" s="7" t="n">
         <v>46267</v>
@@ -15978,7 +15978,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="5" t="n">
-        <v>0.0546854400674999</v>
+        <v>0.04717524477721342</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="5" t="n">
-        <v>0.3183568000843749</v>
+        <v>0.3089690559715167</v>
       </c>
       <c r="Q202" s="10" t="inlineStr">
         <is>
@@ -16034,13 +16034,13 @@
         </is>
       </c>
       <c r="D203" s="15" t="n">
-        <v>209.62</v>
+        <v>211.22</v>
       </c>
       <c r="E203" s="16" t="n">
-        <v>0.05139999999999999</v>
+        <v>0.0594</v>
       </c>
       <c r="F203" s="16" t="n">
-        <v>0.2496</v>
+        <v>0.2591</v>
       </c>
       <c r="G203" s="17" t="n">
         <v>46260</v>
@@ -16069,7 +16069,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="26" t="n">
-        <v>-0.1353401392996852</v>
+        <v>-0.1418899725404791</v>
       </c>
       <c r="N203" s="14" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="26" t="n">
-        <v>-0.153229653659002</v>
+        <v>-0.1596439731086071</v>
       </c>
       <c r="Q203" s="20" t="inlineStr">
         <is>
@@ -16121,13 +16121,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>92.90000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>0.0745</v>
+        <v>0.0629</v>
       </c>
       <c r="F204" s="6" t="n">
-        <v>-0.0746</v>
+        <v>-0.08460000000000001</v>
       </c>
       <c r="G204" s="7" t="n">
         <v>46245</v>
@@ -16182,13 +16182,13 @@
         </is>
       </c>
       <c r="D205" s="15" t="n">
-        <v>120.85</v>
+        <v>121.74</v>
       </c>
       <c r="E205" s="16" t="n">
-        <v>0.0603</v>
-      </c>
-      <c r="F205" s="26" t="n">
-        <v>-0.006500000000000001</v>
+        <v>0.06809999999999999</v>
+      </c>
+      <c r="F205" s="16" t="n">
+        <v>0.0008</v>
       </c>
       <c r="G205" s="17" t="n">
         <v>46246</v>
@@ -16217,7 +16217,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="16" t="n">
-        <v>0.07571369466280518</v>
+        <v>0.06784951536060461</v>
       </c>
       <c r="N205" s="14" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="16" t="n">
-        <v>0.2412081092263137</v>
+        <v>0.232134056185313</v>
       </c>
       <c r="Q205" s="20" t="inlineStr">
         <is>
@@ -16285,13 +16285,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>287.52</v>
+        <v>288.15</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>0.1259</v>
+        <v>0.1284</v>
       </c>
       <c r="F206" s="5" t="n">
-        <v>0.2282</v>
+        <v>0.2308</v>
       </c>
       <c r="G206" s="7" t="n">
         <v>46240</v>
@@ -16346,13 +16346,13 @@
         </is>
       </c>
       <c r="D207" s="15" t="n">
-        <v>475.13</v>
+        <v>467.27</v>
       </c>
       <c r="E207" s="16" t="n">
-        <v>0.1538</v>
+        <v>0.1347</v>
       </c>
       <c r="F207" s="16" t="n">
-        <v>0.2047</v>
+        <v>0.1848</v>
       </c>
       <c r="G207" s="17" t="n">
         <v>46261</v>
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>56.78</v>
+        <v>57.54</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>0.2108</v>
+        <v>0.2269</v>
       </c>
       <c r="F208" s="5" t="n">
-        <v>0.2015</v>
+        <v>0.2175</v>
       </c>
       <c r="G208" s="7" t="n">
         <v>46268</v>
@@ -16468,13 +16468,13 @@
         </is>
       </c>
       <c r="D209" s="15" t="n">
-        <v>45.29</v>
-      </c>
-      <c r="E209" s="26" t="n">
-        <v>-0.0051</v>
+        <v>45.71</v>
+      </c>
+      <c r="E209" s="16" t="n">
+        <v>0.0042</v>
       </c>
       <c r="F209" s="16" t="n">
-        <v>0.0735</v>
+        <v>0.0834</v>
       </c>
       <c r="G209" s="17" t="n">
         <v>46239</v>
@@ -16529,13 +16529,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>535.53</v>
+        <v>531.03</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0605</v>
       </c>
       <c r="F210" s="6" t="n">
-        <v>-0.138</v>
+        <v>-0.1452</v>
       </c>
       <c r="G210" s="7" t="n">
         <v>46251</v>
@@ -16590,13 +16590,13 @@
         </is>
       </c>
       <c r="D211" s="15" t="n">
-        <v>120.61</v>
+        <v>120.3</v>
       </c>
       <c r="E211" s="16" t="n">
-        <v>0.0163</v>
+        <v>0.0137</v>
       </c>
       <c r="F211" s="16" t="n">
-        <v>0.0335</v>
+        <v>0.0308</v>
       </c>
       <c r="G211" s="17" t="n"/>
       <c r="H211" s="22" t="inlineStr">
@@ -16641,13 +16641,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>166.45</v>
+        <v>168.29</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>0.0252</v>
+        <v>0.0366</v>
       </c>
       <c r="F212" s="5" t="n">
-        <v>0.1504</v>
+        <v>0.1632</v>
       </c>
       <c r="G212" s="7" t="n"/>
       <c r="H212" s="12" t="inlineStr">
@@ -16692,13 +16692,13 @@
         </is>
       </c>
       <c r="D213" s="15" t="n">
-        <v>52.73</v>
+        <v>52.02</v>
       </c>
       <c r="E213" s="26" t="n">
-        <v>-0.2348</v>
+        <v>-0.2451</v>
       </c>
       <c r="F213" s="26" t="n">
-        <v>-0.3019</v>
+        <v>-0.3113</v>
       </c>
       <c r="G213" s="17" t="n">
         <v>46239</v>
@@ -16753,13 +16753,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>160.68</v>
+        <v>159.89</v>
       </c>
       <c r="E214" s="6" t="n">
-        <v>-0.1752</v>
+        <v>-0.1792</v>
       </c>
       <c r="F214" s="6" t="n">
-        <v>-0.09519999999999999</v>
+        <v>-0.09960000000000001</v>
       </c>
       <c r="G214" s="7" t="n"/>
       <c r="H214" s="12" t="inlineStr">
@@ -16804,13 +16804,13 @@
         </is>
       </c>
       <c r="D215" s="15" t="n">
-        <v>36.46</v>
+        <v>36.48</v>
       </c>
       <c r="E215" s="16" t="n">
-        <v>0.1099</v>
+        <v>0.1105</v>
       </c>
       <c r="F215" s="16" t="n">
-        <v>0.1716</v>
+        <v>0.1722</v>
       </c>
       <c r="G215" s="17" t="n">
         <v>46267</v>
@@ -16865,13 +16865,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>160.73</v>
+        <v>160.31</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>0.1682</v>
+        <v>0.1651</v>
       </c>
       <c r="F216" s="5" t="n">
-        <v>0.1813</v>
+        <v>0.1782</v>
       </c>
       <c r="G216" s="7" t="n">
         <v>46268</v>
@@ -16900,7 +16900,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="5" t="n">
-        <v>0.1821066384620171</v>
+        <v>0.1852036678934564</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="9" t="n"/>
@@ -16944,13 +16944,13 @@
         </is>
       </c>
       <c r="D217" s="15" t="n">
-        <v>53.18</v>
+        <v>52.39</v>
       </c>
       <c r="E217" s="16" t="n">
-        <v>0.2324</v>
+        <v>0.2141</v>
       </c>
       <c r="F217" s="16" t="n">
-        <v>0.0809</v>
+        <v>0.06480000000000001</v>
       </c>
       <c r="G217" s="17" t="n">
         <v>46267</v>
@@ -16979,7 +16979,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="16" t="n">
-        <v>0.2598721323805942</v>
+        <v>0.2788700133613285</v>
       </c>
       <c r="N217" s="14" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="16" t="n">
-        <v>0.3162843174125611</v>
+        <v>0.3361328497804925</v>
       </c>
       <c r="Q217" s="20" t="inlineStr">
         <is>
@@ -17031,13 +17031,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>245.52</v>
+        <v>248.89</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>0.2666</v>
+        <v>0.284</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>0.1547</v>
+        <v>0.1705</v>
       </c>
       <c r="G218" s="7" t="n">
         <v>46239</v>
@@ -17092,13 +17092,13 @@
         </is>
       </c>
       <c r="D219" s="15" t="n">
-        <v>231.97</v>
+        <v>235.15</v>
       </c>
       <c r="E219" s="26" t="n">
-        <v>-0.2255</v>
+        <v>-0.2149</v>
       </c>
       <c r="F219" s="26" t="n">
-        <v>-0.1856</v>
+        <v>-0.1744</v>
       </c>
       <c r="G219" s="17" t="n">
         <v>46316</v>
@@ -17134,7 +17134,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="16" t="n">
-        <v>0.07772556796137432</v>
+        <v>0.06315118009780989</v>
       </c>
       <c r="Q219" s="20" t="inlineStr">
         <is>
@@ -17171,13 +17171,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>11.39</v>
+        <v>11.46</v>
       </c>
       <c r="E220" s="6" t="n">
-        <v>-0.0762</v>
+        <v>-0.0706</v>
       </c>
       <c r="F220" s="6" t="n">
-        <v>-0.2177</v>
+        <v>-0.2129</v>
       </c>
       <c r="G220" s="7" t="n">
         <v>46246</v>
@@ -17232,13 +17232,13 @@
         </is>
       </c>
       <c r="D221" s="15" t="n">
-        <v>100.51</v>
+        <v>100.86</v>
       </c>
       <c r="E221" s="26" t="n">
-        <v>-0.1775</v>
+        <v>-0.1746</v>
       </c>
       <c r="F221" s="16" t="n">
-        <v>0.0135</v>
+        <v>0.017</v>
       </c>
       <c r="G221" s="17" t="n">
         <v>46317</v>
@@ -17293,13 +17293,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>319.75</v>
+        <v>323.6</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>0.1749</v>
+        <v>0.1891</v>
       </c>
       <c r="F222" s="5" t="n">
-        <v>0.0775</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="G222" s="7" t="n">
         <v>46259</v>
@@ -17354,13 +17354,13 @@
         </is>
       </c>
       <c r="D223" s="15" t="n">
-        <v>41.63</v>
+        <v>41.72</v>
       </c>
       <c r="E223" s="26" t="n">
-        <v>-0.1481</v>
+        <v>-0.1463</v>
       </c>
       <c r="F223" s="26" t="n">
-        <v>-0.2668</v>
+        <v>-0.2652</v>
       </c>
       <c r="G223" s="17" t="n">
         <v>46239</v>
@@ -17415,13 +17415,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>40.94</v>
+        <v>40.85</v>
       </c>
       <c r="E224" s="6" t="n">
-        <v>-0.0678</v>
+        <v>-0.0697</v>
       </c>
       <c r="F224" s="6" t="n">
-        <v>-0.2468</v>
+        <v>-0.2484</v>
       </c>
       <c r="G224" s="7" t="n">
         <v>46261</v>
@@ -17476,13 +17476,13 @@
         </is>
       </c>
       <c r="D225" s="15" t="n">
-        <v>343.21</v>
+        <v>340</v>
       </c>
       <c r="E225" s="16" t="n">
-        <v>0.0148</v>
+        <v>0.0053</v>
       </c>
       <c r="F225" s="26" t="n">
-        <v>-0.0284</v>
+        <v>-0.0375</v>
       </c>
       <c r="G225" s="17" t="n">
         <v>46289</v>
@@ -17541,13 +17541,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>342.44</v>
+        <v>341.24</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.0673</v>
       </c>
       <c r="F226" s="5" t="n">
-        <v>0.0382</v>
+        <v>0.0346</v>
       </c>
       <c r="G226" s="7" t="n">
         <v>46252</v>
@@ -17576,7 +17576,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>0.1388856442004439</v>
+        <v>0.1428906341577775</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="9" t="n"/>
@@ -17632,13 +17632,13 @@
         </is>
       </c>
       <c r="D227" s="15" t="n">
-        <v>195.12</v>
+        <v>195.45</v>
       </c>
       <c r="E227" s="26" t="n">
-        <v>-0.1637</v>
+        <v>-0.1623</v>
       </c>
       <c r="F227" s="16" t="n">
-        <v>0.0114</v>
+        <v>0.0131</v>
       </c>
       <c r="G227" s="17" t="n"/>
       <c r="H227" s="22" t="inlineStr">
@@ -17657,7 +17657,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="16" t="n">
-        <v>0.563140631406314</v>
+        <v>0.5605014070094654</v>
       </c>
       <c r="N227" s="14" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="26" t="n">
-        <v>-0.05186551865518657</v>
+        <v>-0.05346635968278327</v>
       </c>
       <c r="Q227" s="20" t="inlineStr">
         <is>
@@ -17709,13 +17709,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>93.94</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="E228" s="6" t="n">
-        <v>-0.2146</v>
+        <v>-0.2154</v>
       </c>
       <c r="F228" s="6" t="n">
-        <v>-0.043</v>
+        <v>-0.04389999999999999</v>
       </c>
       <c r="G228" s="7" t="n">
         <v>46239</v>
@@ -17770,13 +17770,13 @@
         </is>
       </c>
       <c r="D229" s="15" t="n">
-        <v>856.4299999999999</v>
+        <v>849.47</v>
       </c>
       <c r="E229" s="16" t="n">
-        <v>0.1712</v>
+        <v>0.1617</v>
       </c>
       <c r="F229" s="26" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0164</v>
       </c>
       <c r="G229" s="17" t="n">
         <v>46245</v>
@@ -17831,13 +17831,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>108.72</v>
+        <v>108.95</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>0.1159</v>
+        <v>0.1182</v>
       </c>
       <c r="F230" s="6" t="n">
-        <v>-0.0373</v>
+        <v>-0.0352</v>
       </c>
       <c r="G230" s="7" t="n"/>
       <c r="H230" s="12" t="inlineStr">
@@ -17882,13 +17882,13 @@
         </is>
       </c>
       <c r="D231" s="15" t="n">
-        <v>315.15</v>
+        <v>317.74</v>
       </c>
       <c r="E231" s="26" t="n">
-        <v>-0.1001</v>
+        <v>-0.09269999999999999</v>
       </c>
       <c r="F231" s="16" t="n">
-        <v>0.0391</v>
+        <v>0.04769999999999999</v>
       </c>
       <c r="G231" s="17" t="n"/>
       <c r="H231" s="22" t="inlineStr">
@@ -17907,7 +17907,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="16" t="n">
-        <v>0.4278914802475013</v>
+        <v>0.4162522817397872</v>
       </c>
       <c r="N231" s="14" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="16" t="n">
-        <v>0.1264477233063621</v>
+        <v>0.1172656889280543</v>
       </c>
       <c r="Q231" s="20" t="inlineStr">
         <is>
@@ -17963,13 +17963,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>80.34999999999999</v>
+        <v>80.67</v>
       </c>
       <c r="E232" s="6" t="n">
-        <v>-0.0827</v>
+        <v>-0.079</v>
       </c>
       <c r="F232" s="6" t="n">
-        <v>-0.09050000000000001</v>
+        <v>-0.0868</v>
       </c>
       <c r="G232" s="7" t="n">
         <v>46240</v>
@@ -18024,13 +18024,13 @@
         </is>
       </c>
       <c r="D233" s="15" t="n">
-        <v>374.2</v>
+        <v>380.04</v>
       </c>
       <c r="E233" s="16" t="n">
-        <v>0.0455</v>
+        <v>0.06179999999999999</v>
       </c>
       <c r="F233" s="16" t="n">
-        <v>0.0669</v>
+        <v>0.08349999999999999</v>
       </c>
       <c r="G233" s="17" t="n">
         <v>46259</v>
@@ -18085,13 +18085,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>326.18</v>
+        <v>320.76</v>
       </c>
       <c r="E234" s="6" t="n">
-        <v>-0.1138</v>
+        <v>-0.1285</v>
       </c>
       <c r="F234" s="5" t="n">
-        <v>0.08130000000000001</v>
+        <v>0.0634</v>
       </c>
       <c r="G234" s="7" t="n">
         <v>46239</v>
@@ -18146,13 +18146,13 @@
         </is>
       </c>
       <c r="D235" s="15" t="n">
-        <v>1345.19</v>
+        <v>1335.03</v>
       </c>
       <c r="E235" s="26" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F235" s="26" t="n">
-        <v>-0.0917</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="G235" s="17" t="n"/>
       <c r="H235" s="22" t="inlineStr">
@@ -18197,13 +18197,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>221.51</v>
+        <v>218.59</v>
       </c>
       <c r="E236" s="6" t="n">
-        <v>-0.1114</v>
+        <v>-0.1231</v>
       </c>
       <c r="F236" s="6" t="n">
-        <v>-0.1593</v>
+        <v>-0.1703</v>
       </c>
       <c r="G236" s="7" t="n">
         <v>46261</v>
@@ -18232,7 +18232,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="5" t="n">
-        <v>0.08347252945690944</v>
+        <v>0.09794592616313645</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="5" t="n">
-        <v>0.1331316870570178</v>
+        <v>0.1482684477789469</v>
       </c>
       <c r="Q236" s="10" t="inlineStr">
         <is>
@@ -18284,13 +18284,13 @@
         </is>
       </c>
       <c r="D237" s="15" t="n">
-        <v>495.2</v>
+        <v>492.81</v>
       </c>
       <c r="E237" s="16" t="n">
-        <v>0.2804</v>
+        <v>0.2743</v>
       </c>
       <c r="F237" s="16" t="n">
-        <v>0.1885</v>
+        <v>0.1827</v>
       </c>
       <c r="G237" s="17" t="n"/>
       <c r="H237" s="22" t="inlineStr">
@@ -18309,7 +18309,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="16" t="n">
-        <v>0.2621163166397416</v>
+        <v>0.2682372516791461</v>
       </c>
       <c r="N237" s="14" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="16" t="n">
-        <v>0.0601777059773829</v>
+        <v>0.06531929141048273</v>
       </c>
       <c r="Q237" s="20" t="inlineStr">
         <is>
@@ -18373,13 +18373,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>444.28</v>
+        <v>442.85</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>0.0507</v>
+        <v>0.0473</v>
       </c>
       <c r="F238" s="5" t="n">
-        <v>0.0827</v>
+        <v>0.07919999999999999</v>
       </c>
       <c r="G238" s="7" t="n">
         <v>46239</v>
@@ -18411,7 +18411,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="5" t="n">
-        <v>0.1816872242729811</v>
+        <v>0.1855029919837416</v>
       </c>
       <c r="Q238" s="10" t="inlineStr">
         <is>
@@ -18460,13 +18460,13 @@
         </is>
       </c>
       <c r="D239" s="15" t="n">
-        <v>96.06</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="E239" s="26" t="n">
-        <v>-0.0467</v>
+        <v>-0.031</v>
       </c>
       <c r="F239" s="26" t="n">
-        <v>-0.2024</v>
+        <v>-0.1892</v>
       </c>
       <c r="G239" s="17" t="n"/>
       <c r="H239" s="22" t="inlineStr">
@@ -18511,13 +18511,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>273.58</v>
+        <v>273.31</v>
       </c>
       <c r="E240" s="6" t="n">
-        <v>-0.165</v>
+        <v>-0.1658</v>
       </c>
       <c r="F240" s="6" t="n">
-        <v>-0.2079</v>
+        <v>-0.2087</v>
       </c>
       <c r="G240" s="7" t="n">
         <v>46240</v>
@@ -18572,13 +18572,13 @@
         </is>
       </c>
       <c r="D241" s="15" t="n">
-        <v>895.91</v>
+        <v>892.67</v>
       </c>
       <c r="E241" s="26" t="n">
-        <v>-0.0902</v>
+        <v>-0.0935</v>
       </c>
       <c r="F241" s="16" t="n">
-        <v>0.0369</v>
+        <v>0.0332</v>
       </c>
       <c r="G241" s="17" t="n">
         <v>46287</v>
@@ -18607,7 +18607,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="16" t="n">
-        <v>0.702179906463819</v>
+        <v>0.7083580718518603</v>
       </c>
       <c r="N241" s="14" t="inlineStr">
         <is>
@@ -18655,13 +18655,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>224.32</v>
+        <v>225.74</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>0.053</v>
+        <v>0.0597</v>
       </c>
       <c r="F242" s="6" t="n">
-        <v>-0.0153</v>
+        <v>-0.0091</v>
       </c>
       <c r="G242" s="7" t="n">
         <v>46246</v>
@@ -18716,13 +18716,13 @@
         </is>
       </c>
       <c r="D243" s="15" t="n">
-        <v>299.56</v>
+        <v>301.33</v>
       </c>
       <c r="E243" s="16" t="n">
-        <v>0.2101</v>
+        <v>0.2172</v>
       </c>
       <c r="F243" s="16" t="n">
-        <v>0.1977</v>
+        <v>0.2048</v>
       </c>
       <c r="G243" s="17" t="n">
         <v>46240</v>
@@ -18777,13 +18777,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>116</v>
+        <v>118.14</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0946</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>0.0316</v>
+        <v>0.0506</v>
       </c>
       <c r="G244" s="7" t="n">
         <v>46323</v>
@@ -18812,7 +18812,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="5" t="n">
-        <v>0.3793103448275862</v>
+        <v>0.3543253766717454</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="5" t="n">
-        <v>0.293103448275862</v>
+        <v>0.2696800406297613</v>
       </c>
       <c r="Q244" s="10" t="inlineStr">
         <is>
@@ -18868,13 +18868,13 @@
         </is>
       </c>
       <c r="D245" s="15" t="n">
-        <v>61.45</v>
+        <v>61.5</v>
       </c>
       <c r="E245" s="16" t="n">
-        <v>0.1723</v>
+        <v>0.1732</v>
       </c>
       <c r="F245" s="16" t="n">
-        <v>0.1456</v>
+        <v>0.1465</v>
       </c>
       <c r="G245" s="17" t="n">
         <v>46260</v>
@@ -18929,13 +18929,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>211.26</v>
+        <v>211.94</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>0.0803</v>
+        <v>0.08380000000000001</v>
       </c>
       <c r="F246" s="5" t="n">
-        <v>0.03</v>
+        <v>0.0333</v>
       </c>
       <c r="G246" s="7" t="n">
         <v>46260</v>
@@ -18964,7 +18964,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="5" t="n">
-        <v>0.4910536779324056</v>
+        <v>0.486269698971407</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="5" t="n">
-        <v>0.9549370444002652</v>
+        <v>0.948664716429178</v>
       </c>
       <c r="Q246" s="10" t="inlineStr">
         <is>
@@ -19024,13 +19024,13 @@
         </is>
       </c>
       <c r="D247" s="15" t="n">
-        <v>412.55</v>
+        <v>413.5</v>
       </c>
       <c r="E247" s="26" t="n">
-        <v>-0.1159</v>
+        <v>-0.1139</v>
       </c>
       <c r="F247" s="26" t="n">
-        <v>-0.1329</v>
+        <v>-0.1309</v>
       </c>
       <c r="G247" s="17" t="n">
         <v>46240</v>
@@ -19085,13 +19085,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>236.96</v>
+        <v>237.6</v>
       </c>
       <c r="E248" s="6" t="n">
-        <v>-0.1553</v>
+        <v>-0.153</v>
       </c>
       <c r="F248" s="6" t="n">
-        <v>-0.1994</v>
+        <v>-0.1972</v>
       </c>
       <c r="G248" s="7" t="n"/>
       <c r="H248" s="12" t="inlineStr">
@@ -19132,13 +19132,13 @@
         </is>
       </c>
       <c r="D249" s="15" t="n">
-        <v>11.9</v>
+        <v>12.08</v>
       </c>
       <c r="E249" s="26" t="n">
-        <v>-0.3181</v>
+        <v>-0.308</v>
       </c>
       <c r="F249" s="26" t="n">
-        <v>-0.4077</v>
+        <v>-0.3989</v>
       </c>
       <c r="G249" s="17" t="n"/>
       <c r="H249" s="22" t="inlineStr">
@@ -19183,13 +19183,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>146.85</v>
+        <v>147.82</v>
       </c>
       <c r="E250" s="6" t="n">
-        <v>-0.0118</v>
+        <v>-0.0052</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>0.2369</v>
+        <v>0.2451</v>
       </c>
       <c r="G250" s="7" t="n">
         <v>46260</v>
@@ -19218,7 +19218,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="5" t="n">
-        <v>0.02145045965270688</v>
+        <v>0.01474766608036806</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="6" t="n">
-        <v>-0.114742934967654</v>
+        <v>-0.1205520227303477</v>
       </c>
       <c r="Q250" s="10" t="inlineStr">
         <is>
@@ -19270,13 +19270,13 @@
         </is>
       </c>
       <c r="D251" s="15" t="n">
-        <v>81.03</v>
+        <v>80.78</v>
       </c>
       <c r="E251" s="26" t="n">
-        <v>-0.1443</v>
+        <v>-0.1469</v>
       </c>
       <c r="F251" s="26" t="n">
-        <v>-0.309</v>
+        <v>-0.3111</v>
       </c>
       <c r="G251" s="17" t="n"/>
       <c r="H251" s="22" t="inlineStr">
@@ -19321,13 +19321,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>291.71</v>
+        <v>287.6</v>
       </c>
       <c r="E252" s="6" t="n">
-        <v>-0.04</v>
+        <v>-0.0535</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>0.1519</v>
+        <v>0.1357</v>
       </c>
       <c r="G252" s="7" t="n">
         <v>46240</v>
@@ -19382,13 +19382,13 @@
         </is>
       </c>
       <c r="D253" s="15" t="n">
-        <v>148.15</v>
+        <v>145.74</v>
       </c>
       <c r="E253" s="16" t="n">
-        <v>0.0305</v>
+        <v>0.0138</v>
       </c>
       <c r="F253" s="26" t="n">
-        <v>-0.3067</v>
+        <v>-0.318</v>
       </c>
       <c r="G253" s="17" t="n">
         <v>46273</v>
@@ -19417,7 +19417,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="16" t="n">
-        <v>0.8899763752953087</v>
+        <v>0.9212295869356387</v>
       </c>
       <c r="N253" s="14" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="16" t="n">
-        <v>0.6537293283833951</v>
+        <v>0.6810758885686838</v>
       </c>
       <c r="Q253" s="20" t="inlineStr">
         <is>
@@ -19469,13 +19469,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>360.58</v>
+        <v>366.34</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0246</v>
       </c>
       <c r="F254" s="5" t="n">
-        <v>0.3254</v>
+        <v>0.3466</v>
       </c>
       <c r="G254" s="7" t="n">
         <v>46266</v>
@@ -19504,7 +19504,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="5" t="n">
-        <v>0.1647900604581508</v>
+        <v>0.1464759513020692</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="5" t="n">
-        <v>0.1509235121193633</v>
+        <v>0.1328274280722826</v>
       </c>
       <c r="Q254" s="10" t="inlineStr">
         <is>
@@ -19564,13 +19564,13 @@
         </is>
       </c>
       <c r="D255" s="15" t="n">
-        <v>13.66</v>
+        <v>14.1</v>
       </c>
       <c r="E255" s="16" t="n">
-        <v>0.1547</v>
+        <v>0.1919</v>
       </c>
       <c r="F255" s="16" t="n">
-        <v>0.2153</v>
+        <v>0.2544</v>
       </c>
       <c r="G255" s="17" t="n">
         <v>46268</v>
@@ -19625,13 +19625,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>31.63</v>
+        <v>31.75</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>0.0112</v>
+        <v>0.015</v>
       </c>
       <c r="F256" s="6" t="n">
-        <v>-0.08869999999999999</v>
+        <v>-0.08529999999999999</v>
       </c>
       <c r="G256" s="7" t="n">
         <v>46315</v>
@@ -19686,13 +19686,13 @@
         </is>
       </c>
       <c r="D257" s="15" t="n">
-        <v>169.41</v>
+        <v>167.63</v>
       </c>
       <c r="E257" s="16" t="n">
-        <v>0.1447</v>
+        <v>0.1326</v>
       </c>
       <c r="F257" s="16" t="n">
-        <v>0.4009</v>
+        <v>0.3862</v>
       </c>
       <c r="G257" s="17" t="n"/>
       <c r="H257" s="22" t="inlineStr">
@@ -19737,13 +19737,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>162.44</v>
+        <v>162.66</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>0.2256</v>
+        <v>0.2273</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>0.1986</v>
+        <v>0.2002</v>
       </c>
       <c r="G258" s="7" t="n"/>
       <c r="H258" s="12" t="inlineStr">
@@ -19788,13 +19788,13 @@
         </is>
       </c>
       <c r="D259" s="15" t="n">
-        <v>140.18</v>
+        <v>141.67</v>
       </c>
       <c r="E259" s="26" t="n">
-        <v>-0.0443</v>
+        <v>-0.0342</v>
       </c>
       <c r="F259" s="26" t="n">
-        <v>-0.0132</v>
+        <v>-0.0027</v>
       </c>
       <c r="G259" s="17" t="n"/>
       <c r="H259" s="22" t="inlineStr">
@@ -19849,13 +19849,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>21.58</v>
+        <v>21.83</v>
       </c>
       <c r="E260" s="6" t="n">
-        <v>-0.0432</v>
+        <v>-0.03240000000000001</v>
       </c>
       <c r="F260" s="6" t="n">
-        <v>-0.095</v>
+        <v>-0.08470000000000001</v>
       </c>
       <c r="G260" s="7" t="n">
         <v>46240</v>
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="D261" s="15" t="n">
-        <v>162.51</v>
+        <v>162.67</v>
       </c>
       <c r="E261" s="26" t="n">
-        <v>-0.1286</v>
+        <v>-0.1277</v>
       </c>
       <c r="F261" s="26" t="n">
-        <v>-0.2475</v>
+        <v>-0.2467</v>
       </c>
       <c r="G261" s="17" t="n"/>
       <c r="H261" s="22" t="inlineStr">
@@ -19935,7 +19935,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="16" t="n">
-        <v>0.6306688819149592</v>
+        <v>0.6290649781766768</v>
       </c>
       <c r="N261" s="14" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>179</v>
       </c>
       <c r="P261" s="16" t="n">
-        <v>0.101470678727463</v>
+        <v>0.1003872871457553</v>
       </c>
       <c r="Q261" s="20" t="inlineStr">
         <is>
@@ -19991,13 +19991,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>94.22</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>0.0814</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="F262" s="6" t="n">
-        <v>-0.0413</v>
+        <v>-0.033</v>
       </c>
       <c r="G262" s="7" t="n"/>
       <c r="H262" s="12" t="inlineStr">
@@ -20042,13 +20042,13 @@
         </is>
       </c>
       <c r="D263" s="15" t="n">
-        <v>9.32</v>
+        <v>9.23</v>
       </c>
       <c r="E263" s="26" t="n">
-        <v>-0.0053</v>
+        <v>-0.0149</v>
       </c>
       <c r="F263" s="26" t="n">
-        <v>-0.0638</v>
+        <v>-0.0728</v>
       </c>
       <c r="G263" s="17" t="n">
         <v>46244</v>
@@ -20103,13 +20103,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>80.29000000000001</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="E264" s="6" t="n">
-        <v>-0.0809</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="F264" s="5" t="n">
-        <v>0.09369999999999999</v>
+        <v>0.1033</v>
       </c>
       <c r="G264" s="7" t="n">
         <v>46273</v>
@@ -20164,13 +20164,13 @@
         </is>
       </c>
       <c r="D265" s="15" t="n">
-        <v>17.48</v>
+        <v>17.45</v>
       </c>
       <c r="E265" s="26" t="n">
-        <v>-0.027</v>
+        <v>-0.0284</v>
       </c>
       <c r="F265" s="26" t="n">
-        <v>-0.155</v>
+        <v>-0.1562</v>
       </c>
       <c r="G265" s="17" t="n">
         <v>46240</v>
@@ -20225,13 +20225,13 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>387.99</v>
+        <v>392.76</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="F266" s="5" t="n">
-        <v>0.168</v>
+        <v>0.1824</v>
       </c>
       <c r="G266" s="7" t="n">
         <v>46317</v>
@@ -20300,13 +20300,13 @@
         </is>
       </c>
       <c r="D267" s="15" t="n">
-        <v>5.07</v>
+        <v>5.15</v>
       </c>
       <c r="E267" s="26" t="n">
-        <v>-0.2117</v>
+        <v>-0.1984</v>
       </c>
       <c r="F267" s="16" t="n">
-        <v>0.0765</v>
+        <v>0.0946</v>
       </c>
       <c r="G267" s="17" t="n">
         <v>46245</v>
@@ -20361,13 +20361,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>20.76</v>
+        <v>20.98</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>0.1438</v>
+        <v>0.1559</v>
       </c>
       <c r="F268" s="5" t="n">
-        <v>0.3016</v>
+        <v>0.3154</v>
       </c>
       <c r="G268" s="7" t="n">
         <v>46261</v>
@@ -20422,13 +20422,13 @@
         </is>
       </c>
       <c r="D269" s="15" t="n">
-        <v>17.25</v>
+        <v>17.4</v>
       </c>
       <c r="E269" s="16" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.0978</v>
       </c>
       <c r="F269" s="26" t="n">
-        <v>-0.0546</v>
+        <v>-0.0461</v>
       </c>
       <c r="G269" s="17" t="n">
         <v>46273</v>
@@ -20483,13 +20483,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>208.01</v>
+        <v>207.46</v>
       </c>
       <c r="E270" s="6" t="n">
-        <v>-0.0441</v>
+        <v>-0.0466</v>
       </c>
       <c r="F270" s="6" t="n">
-        <v>-0.1748</v>
+        <v>-0.177</v>
       </c>
       <c r="G270" s="7" t="n"/>
       <c r="H270" s="12" t="inlineStr">
@@ -20534,13 +20534,13 @@
         </is>
       </c>
       <c r="D271" s="15" t="n">
-        <v>193.94</v>
+        <v>195.49</v>
       </c>
       <c r="E271" s="16" t="n">
-        <v>0.2084</v>
+        <v>0.2181</v>
       </c>
       <c r="F271" s="16" t="n">
-        <v>0.0496</v>
+        <v>0.058</v>
       </c>
       <c r="G271" s="17" t="n">
         <v>46316</v>
@@ -20615,13 +20615,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>31.49</v>
+        <v>31.69</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>0.158</v>
+        <v>0.1655</v>
       </c>
       <c r="F272" s="6" t="n">
-        <v>-0.2439</v>
+        <v>-0.239</v>
       </c>
       <c r="G272" s="7" t="n">
         <v>46245</v>
@@ -20676,13 +20676,13 @@
         </is>
       </c>
       <c r="D273" s="15" t="n">
-        <v>319</v>
+        <v>316.77</v>
       </c>
       <c r="E273" s="16" t="n">
-        <v>0.2171</v>
+        <v>0.2086</v>
       </c>
       <c r="F273" s="16" t="n">
-        <v>0.3389</v>
+        <v>0.3295</v>
       </c>
       <c r="G273" s="17" t="n">
         <v>46260</v>
@@ -20711,7 +20711,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="16" t="n">
-        <v>0.003134796238244514</v>
+        <v>0.01019667266470947</v>
       </c>
       <c r="N273" s="14" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="26" t="n">
-        <v>-0.122257053291536</v>
+        <v>-0.1160779114183792</v>
       </c>
       <c r="Q273" s="20" t="inlineStr">
         <is>
@@ -20763,13 +20763,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>400.98</v>
+        <v>403.86</v>
       </c>
       <c r="E274" s="6" t="n">
-        <v>-0.0934</v>
+        <v>-0.0868</v>
       </c>
       <c r="F274" s="6" t="n">
-        <v>-0.1374</v>
+        <v>-0.1312</v>
       </c>
       <c r="G274" s="7" t="n">
         <v>46260</v>
@@ -20798,7 +20798,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="5" t="n">
-        <v>0.3342311337223801</v>
+        <v>0.3247164859109592</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="9" t="n"/>
@@ -20842,13 +20842,13 @@
         </is>
       </c>
       <c r="D275" s="15" t="n">
-        <v>6.43</v>
+        <v>6.51</v>
       </c>
       <c r="E275" s="26" t="n">
-        <v>-0.07690000000000001</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="F275" s="26" t="n">
-        <v>-0.1306</v>
+        <v>-0.1191</v>
       </c>
       <c r="G275" s="17" t="n">
         <v>46239</v>
@@ -20903,13 +20903,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>66.09</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>0.0675</v>
+        <v>0.0788</v>
       </c>
       <c r="F276" s="6" t="n">
-        <v>-0.1017</v>
+        <v>-0.0922</v>
       </c>
       <c r="G276" s="7" t="n"/>
       <c r="H276" s="12" t="inlineStr">
@@ -20954,13 +20954,13 @@
         </is>
       </c>
       <c r="D277" s="15" t="n">
-        <v>106.52</v>
+        <v>106.56</v>
       </c>
       <c r="E277" s="26" t="n">
-        <v>-0.1424</v>
+        <v>-0.1421</v>
       </c>
       <c r="F277" s="26" t="n">
-        <v>-0.1324</v>
+        <v>-0.1321</v>
       </c>
       <c r="G277" s="17" t="n">
         <v>46240</v>
@@ -21015,13 +21015,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>213.89</v>
+        <v>216.82</v>
       </c>
       <c r="E278" s="5" t="n">
-        <v>0.06860000000000001</v>
+        <v>0.0833</v>
       </c>
       <c r="F278" s="5" t="n">
-        <v>0.0058</v>
+        <v>0.0196</v>
       </c>
       <c r="G278" s="7" t="n">
         <v>46330</v>
@@ -21076,13 +21076,13 @@
         </is>
       </c>
       <c r="D279" s="15" t="n">
-        <v>406.83</v>
+        <v>403.56</v>
       </c>
       <c r="E279" s="16" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.0633</v>
       </c>
       <c r="F279" s="16" t="n">
-        <v>0.1366</v>
+        <v>0.1275</v>
       </c>
       <c r="G279" s="17" t="n"/>
       <c r="H279" s="22" t="inlineStr">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>59</v>
+        <v>59.81</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>0.1245</v>
+        <v>0.1399</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>0.0888</v>
+        <v>0.1037</v>
       </c>
       <c r="G280" s="7" t="n">
         <v>46239</v>
@@ -21188,13 +21188,13 @@
         </is>
       </c>
       <c r="D281" s="15" t="n">
-        <v>418.84</v>
+        <v>417.17</v>
       </c>
       <c r="E281" s="26" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.0766</v>
       </c>
       <c r="F281" s="16" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0048</v>
       </c>
       <c r="G281" s="17" t="n">
         <v>46310</v>
@@ -21271,13 +21271,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>134.68</v>
+        <v>132.79</v>
       </c>
       <c r="E282" s="6" t="n">
-        <v>-0.09849999999999999</v>
+        <v>-0.1111</v>
       </c>
       <c r="F282" s="6" t="n">
-        <v>-0.1965</v>
+        <v>-0.2078</v>
       </c>
       <c r="G282" s="7" t="n">
         <v>46239</v>
@@ -21332,13 +21332,13 @@
         </is>
       </c>
       <c r="D283" s="15" t="n">
-        <v>198.44</v>
+        <v>194.05</v>
       </c>
       <c r="E283" s="26" t="n">
-        <v>-0.0509</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="F283" s="26" t="n">
-        <v>-0.1219</v>
+        <v>-0.1413</v>
       </c>
       <c r="G283" s="17" t="n">
         <v>46240</v>
@@ -21393,10 +21393,10 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>283.64</v>
+        <v>283.63</v>
       </c>
       <c r="E284" s="6" t="n">
-        <v>-0.0654</v>
+        <v>-0.0655</v>
       </c>
       <c r="F284" s="6" t="n">
         <v>-0.005</v>
@@ -21428,7 +21428,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="5" t="n">
-        <v>0.05767874770836277</v>
+        <v>0.05771603850086382</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="5" t="n">
-        <v>0.1140882809194754</v>
+        <v>0.1141275605542432</v>
       </c>
       <c r="Q284" s="10" t="inlineStr">
         <is>
@@ -21496,13 +21496,13 @@
         </is>
       </c>
       <c r="D285" s="15" t="n">
-        <v>306.65</v>
+        <v>313.33</v>
       </c>
       <c r="E285" s="26" t="n">
-        <v>-0.0387</v>
-      </c>
-      <c r="F285" s="26" t="n">
-        <v>-0.0174</v>
+        <v>-0.0178</v>
+      </c>
+      <c r="F285" s="16" t="n">
+        <v>0.004</v>
       </c>
       <c r="G285" s="17" t="n"/>
       <c r="H285" s="22" t="inlineStr">
@@ -21521,7 +21521,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="16" t="n">
-        <v>0.09245067666721025</v>
+        <v>0.06916031021606618</v>
       </c>
       <c r="N285" s="14" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="16" t="n">
-        <v>0.2228925485080712</v>
+        <v>0.1968212427791786</v>
       </c>
       <c r="Q285" s="20" t="inlineStr">
         <is>
@@ -21573,13 +21573,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>35.13</v>
+        <v>35.22</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>0.185</v>
+        <v>0.1879</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>0.2045</v>
+        <v>0.2074</v>
       </c>
       <c r="G286" s="7" t="n">
         <v>46240</v>
@@ -21634,13 +21634,13 @@
         </is>
       </c>
       <c r="D287" s="15" t="n">
-        <v>7.25</v>
+        <v>7.22</v>
       </c>
       <c r="E287" s="26" t="n">
-        <v>-0.0717</v>
+        <v>-0.0755</v>
       </c>
       <c r="F287" s="26" t="n">
-        <v>-0.1799</v>
+        <v>-0.1833</v>
       </c>
       <c r="G287" s="17" t="n">
         <v>46254</v>
@@ -21695,13 +21695,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>168.34</v>
+        <v>171.28</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>0.2199</v>
+        <v>0.2412</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>0.1668</v>
+        <v>0.1871</v>
       </c>
       <c r="G288" s="7" t="n">
         <v>46261</v>
@@ -21756,13 +21756,13 @@
         </is>
       </c>
       <c r="D289" s="15" t="n">
-        <v>551.36</v>
+        <v>548.5599999999999</v>
       </c>
       <c r="E289" s="26" t="n">
-        <v>-0.0452</v>
+        <v>-0.05</v>
       </c>
       <c r="F289" s="16" t="n">
-        <v>0.0775</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="G289" s="17" t="n">
         <v>46239</v>
@@ -21791,7 +21791,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="16" t="n">
-        <v>0.3239988392338943</v>
+        <v>0.3307568907685578</v>
       </c>
       <c r="N289" s="14" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="16" t="n">
-        <v>0.0428757980266976</v>
+        <v>0.04819892081085033</v>
       </c>
       <c r="Q289" s="20" t="inlineStr">
         <is>
@@ -21843,13 +21843,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>26.74</v>
+        <v>27.06</v>
       </c>
       <c r="E290" s="6" t="n">
-        <v>-0.3225</v>
+        <v>-0.3144</v>
       </c>
       <c r="F290" s="6" t="n">
-        <v>-0.5143</v>
+        <v>-0.5085000000000001</v>
       </c>
       <c r="G290" s="7" t="n">
         <v>46238</v>
@@ -21904,13 +21904,13 @@
         </is>
       </c>
       <c r="D291" s="15" t="n">
-        <v>101.58</v>
+        <v>102.12</v>
       </c>
       <c r="E291" s="16" t="n">
-        <v>0.1956</v>
-      </c>
-      <c r="F291" s="26" t="n">
-        <v>-0.0004</v>
+        <v>0.202</v>
+      </c>
+      <c r="F291" s="16" t="n">
+        <v>0.0049</v>
       </c>
       <c r="G291" s="17" t="n">
         <v>46259</v>
@@ -21965,13 +21965,13 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>161.94</v>
+        <v>163.22</v>
       </c>
       <c r="E292" s="5" t="n">
-        <v>0.0766</v>
+        <v>0.0851</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>0.2383</v>
+        <v>0.2481</v>
       </c>
       <c r="G292" s="7" t="n">
         <v>46266</v>
@@ -22026,13 +22026,13 @@
         </is>
       </c>
       <c r="D293" s="15" t="n">
-        <v>296.26</v>
+        <v>294.71</v>
       </c>
       <c r="E293" s="26" t="n">
-        <v>-0.0408</v>
+        <v>-0.0458</v>
       </c>
       <c r="F293" s="16" t="n">
-        <v>0.0492</v>
+        <v>0.0438</v>
       </c>
       <c r="G293" s="17" t="n"/>
       <c r="H293" s="22" t="inlineStr">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>87.36</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>0.0445</v>
+        <v>0.0457</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>0.0561</v>
+        <v>0.0573</v>
       </c>
       <c r="G294" s="7" t="n">
         <v>46252</v>
@@ -22138,13 +22138,13 @@
         </is>
       </c>
       <c r="D295" s="15" t="n">
-        <v>140.55</v>
-      </c>
-      <c r="E295" s="26" t="n">
-        <v>-0.0035</v>
+        <v>142.93</v>
+      </c>
+      <c r="E295" s="16" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F295" s="16" t="n">
-        <v>0</v>
+        <v>0.0169</v>
       </c>
       <c r="G295" s="17" t="n">
         <v>46238</v>
@@ -22173,7 +22173,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="16" t="n">
-        <v>0.1810743507648523</v>
+        <v>0.161407682082138</v>
       </c>
       <c r="N295" s="14" t="inlineStr"/>
       <c r="O295" s="19" t="n"/>
@@ -22221,13 +22221,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>30.01</v>
+        <v>30.33</v>
       </c>
       <c r="E296" s="5" t="n">
-        <v>0.09820000000000001</v>
+        <v>0.1098</v>
       </c>
       <c r="F296" s="6" t="n">
-        <v>-0.1164</v>
+        <v>-0.1072</v>
       </c>
       <c r="G296" s="7" t="n">
         <v>46317</v>
@@ -22282,13 +22282,13 @@
         </is>
       </c>
       <c r="D297" s="15" t="n">
-        <v>282.1</v>
+        <v>283.14</v>
       </c>
       <c r="E297" s="26" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.002</v>
       </c>
       <c r="F297" s="16" t="n">
-        <v>0.0935</v>
+        <v>0.09759999999999999</v>
       </c>
       <c r="G297" s="17" t="n"/>
       <c r="H297" s="22" t="inlineStr">
@@ -22307,7 +22307,7 @@
         <v>275</v>
       </c>
       <c r="M297" s="26" t="n">
-        <v>-0.02516838000708976</v>
+        <v>-0.0287490287490287</v>
       </c>
       <c r="N297" s="14" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="16" t="n">
-        <v>0.1059907834101382</v>
+        <v>0.1019283746556474</v>
       </c>
       <c r="Q297" s="20" t="inlineStr">
         <is>
@@ -22371,13 +22371,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>38.86</v>
+        <v>38.89</v>
       </c>
       <c r="E298" s="6" t="n">
-        <v>-0.0818</v>
+        <v>-0.081</v>
       </c>
       <c r="F298" s="6" t="n">
-        <v>-0.0246</v>
+        <v>-0.0238</v>
       </c>
       <c r="G298" s="7" t="n"/>
       <c r="H298" s="12" t="inlineStr">
@@ -22426,13 +22426,13 @@
         </is>
       </c>
       <c r="D299" s="15" t="n">
-        <v>67.43000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="E299" s="16" t="n">
-        <v>0.1053</v>
+        <v>0.1033</v>
       </c>
       <c r="F299" s="16" t="n">
-        <v>0.064</v>
+        <v>0.062</v>
       </c>
       <c r="G299" s="17" t="n">
         <v>46310</v>
@@ -22487,13 +22487,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>484.92</v>
+        <v>484.64</v>
       </c>
       <c r="E300" s="6" t="n">
-        <v>-0.1029</v>
+        <v>-0.1034</v>
       </c>
       <c r="F300" s="6" t="n">
-        <v>-0.0453</v>
+        <v>-0.0458</v>
       </c>
       <c r="G300" s="7" t="n"/>
       <c r="H300" s="12" t="inlineStr">
@@ -22512,7 +22512,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="5" t="n">
-        <v>0.1754516208859193</v>
+        <v>0.1761307362165732</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="5" t="n">
-        <v>0.08265280871071513</v>
+        <v>0.0832783096731595</v>
       </c>
       <c r="Q300" s="10" t="inlineStr">
         <is>
@@ -22576,13 +22576,13 @@
         </is>
       </c>
       <c r="D301" s="15" t="n">
-        <v>552.08</v>
+        <v>555.8200000000001</v>
       </c>
       <c r="E301" s="26" t="n">
-        <v>-0.08789999999999999</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="F301" s="26" t="n">
-        <v>-0.0412</v>
+        <v>-0.0347</v>
       </c>
       <c r="G301" s="17" t="n"/>
       <c r="H301" s="22" t="inlineStr">
@@ -22601,7 +22601,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="16" t="n">
-        <v>0.1157803216925083</v>
+        <v>0.1082724623079413</v>
       </c>
       <c r="N301" s="14" t="inlineStr"/>
       <c r="O301" s="19" t="n"/>
@@ -22645,13 +22645,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>272.62</v>
+        <v>274.04</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>0.2175</v>
+        <v>0.2238</v>
       </c>
       <c r="F302" s="5" t="n">
-        <v>0.0717</v>
+        <v>0.07719999999999999</v>
       </c>
       <c r="G302" s="7" t="n"/>
       <c r="H302" s="12" t="inlineStr">
@@ -22670,7 +22670,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="5" t="n">
-        <v>0.03807497615728852</v>
+        <v>0.03269595679462844</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="9" t="n"/>
@@ -22716,13 +22716,13 @@
         </is>
       </c>
       <c r="D303" s="15" t="n">
-        <v>254.77</v>
+        <v>255.48</v>
       </c>
       <c r="E303" s="16" t="n">
-        <v>0.07780000000000001</v>
+        <v>0.0808</v>
       </c>
       <c r="F303" s="16" t="n">
-        <v>0.1434</v>
+        <v>0.1466</v>
       </c>
       <c r="G303" s="17" t="n">
         <v>46321</v>
@@ -22751,7 +22751,7 @@
         <v>246</v>
       </c>
       <c r="M303" s="26" t="n">
-        <v>-0.03442320524394556</v>
+        <v>-0.03710662282761856</v>
       </c>
       <c r="N303" s="14" t="inlineStr"/>
       <c r="O303" s="19" t="n"/>
@@ -22799,13 +22799,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>117.96</v>
+        <v>117.8</v>
       </c>
       <c r="E304" s="6" t="n">
-        <v>-0.049</v>
+        <v>-0.0503</v>
       </c>
       <c r="F304" s="5" t="n">
-        <v>0.0366</v>
+        <v>0.0351</v>
       </c>
       <c r="G304" s="7" t="n"/>
       <c r="H304" s="12" t="inlineStr">
@@ -22824,7 +22824,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="5" t="n">
-        <v>0.1020684977958631</v>
+        <v>0.1035653650254669</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="5" t="n">
-        <v>0.08511359782977286</v>
+        <v>0.08658743633276743</v>
       </c>
       <c r="Q304" s="10" t="inlineStr">
         <is>
@@ -22884,13 +22884,13 @@
         </is>
       </c>
       <c r="D305" s="15" t="n">
-        <v>114.63</v>
+        <v>115.09</v>
       </c>
       <c r="E305" s="16" t="n">
-        <v>0.039</v>
+        <v>0.0431</v>
       </c>
       <c r="F305" s="16" t="n">
-        <v>0.09210000000000002</v>
+        <v>0.0965</v>
       </c>
       <c r="G305" s="17" t="n">
         <v>46302</v>
@@ -22919,7 +22919,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="16" t="n">
-        <v>0.1777021722062288</v>
+        <v>0.1729950473542445</v>
       </c>
       <c r="N305" s="14" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="16" t="n">
-        <v>0.09046497426502666</v>
+        <v>0.08610652532800414</v>
       </c>
       <c r="Q305" s="20" t="inlineStr"/>
       <c r="R305" s="19" t="n"/>
@@ -22965,13 +22965,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>361.48</v>
+        <v>361.57</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>0.0354</v>
+        <v>0.0356</v>
       </c>
       <c r="F306" s="5" t="n">
-        <v>0.184</v>
+        <v>0.1843</v>
       </c>
       <c r="G306" s="7" t="n"/>
       <c r="H306" s="12" t="inlineStr">
@@ -22990,7 +22990,7 @@
         <v>350</v>
       </c>
       <c r="M306" s="6" t="n">
-        <v>-0.03175832687838889</v>
+        <v>-0.03199933622811625</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -23001,7 +23001,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="5" t="n">
-        <v>0.1065619121389841</v>
+        <v>0.1062864728821529</v>
       </c>
       <c r="Q306" s="10" t="inlineStr">
         <is>
@@ -23042,13 +23042,13 @@
         </is>
       </c>
       <c r="D307" s="15" t="n">
-        <v>86.81</v>
+        <v>83.92</v>
       </c>
       <c r="E307" s="16" t="n">
-        <v>0.1168</v>
+        <v>0.0796</v>
       </c>
       <c r="F307" s="16" t="n">
-        <v>0.2029</v>
+        <v>0.1628</v>
       </c>
       <c r="G307" s="17" t="n">
         <v>46260</v>
@@ -23099,13 +23099,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>58.11</v>
+        <v>58.14</v>
       </c>
       <c r="E308" s="6" t="n">
-        <v>-0.3013</v>
+        <v>-0.3009</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>0.0329</v>
+        <v>0.0334</v>
       </c>
       <c r="G308" s="7" t="n">
         <v>46245</v>
@@ -23160,13 +23160,13 @@
         </is>
       </c>
       <c r="D309" s="15" t="n">
-        <v>76.06999999999999</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="E309" s="26" t="n">
-        <v>-0.0143</v>
+        <v>-0.011</v>
       </c>
       <c r="F309" s="16" t="n">
-        <v>0.0362</v>
+        <v>0.0396</v>
       </c>
       <c r="G309" s="17" t="n"/>
       <c r="H309" s="22" t="inlineStr">
@@ -23185,14 +23185,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="16" t="n">
-        <v>0.09110030235309594</v>
+        <v>0.08752620545073385</v>
       </c>
       <c r="N309" s="14" t="inlineStr"/>
       <c r="O309" s="19" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="16" t="n">
-        <v>0.1436834494544499</v>
+        <v>0.1399371069182391</v>
       </c>
       <c r="Q309" s="20" t="inlineStr"/>
       <c r="R309" s="19" t="n"/>
@@ -23227,13 +23227,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>175.45</v>
+        <v>175.25</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>0.0823</v>
+        <v>0.08109999999999999</v>
       </c>
       <c r="F310" s="6" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.09720000000000001</v>
       </c>
       <c r="G310" s="7" t="n"/>
       <c r="H310" s="12" t="inlineStr">
@@ -23252,7 +23252,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="5" t="n">
-        <v>0.139925904816187</v>
+        <v>0.1412268188302425</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="9" t="n"/>
@@ -23300,13 +23300,13 @@
         </is>
       </c>
       <c r="D311" s="15" t="n">
-        <v>149.85</v>
+        <v>151.05</v>
       </c>
       <c r="E311" s="16" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0747</v>
       </c>
       <c r="F311" s="16" t="n">
-        <v>0.1445</v>
+        <v>0.1537</v>
       </c>
       <c r="G311" s="17" t="n"/>
       <c r="H311" s="22" t="inlineStr">
@@ -23355,13 +23355,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>194.3</v>
+        <v>193.89</v>
       </c>
       <c r="E312" s="5" t="n">
-        <v>0.1186</v>
+        <v>0.1162</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>0.04019999999999999</v>
+        <v>0.038</v>
       </c>
       <c r="G312" s="7" t="n">
         <v>46317</v>
@@ -23390,7 +23390,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="5" t="n">
-        <v>0.1322696860524961</v>
+        <v>0.1346639847336119</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="5" t="n">
-        <v>0.1837364899639732</v>
+        <v>0.1862396204033216</v>
       </c>
       <c r="Q312" s="10" t="inlineStr">
         <is>
@@ -23442,13 +23442,13 @@
         </is>
       </c>
       <c r="D313" s="15" t="n">
-        <v>1047.9</v>
+        <v>1051.53</v>
       </c>
       <c r="E313" s="16" t="n">
-        <v>0.0491</v>
+        <v>0.0528</v>
       </c>
       <c r="F313" s="26" t="n">
-        <v>-0.0306</v>
+        <v>-0.0272</v>
       </c>
       <c r="G313" s="17" t="n"/>
       <c r="H313" s="22" t="inlineStr">
@@ -23467,7 +23467,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="16" t="n">
-        <v>0.145147437732608</v>
+        <v>0.1411942597928733</v>
       </c>
       <c r="N313" s="14" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="16" t="n">
-        <v>0.1833190189903616</v>
+        <v>0.1792340684526357</v>
       </c>
       <c r="Q313" s="20" t="inlineStr">
         <is>
@@ -23523,13 +23523,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>122.71</v>
+        <v>122.82</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.0187</v>
       </c>
       <c r="F314" s="5" t="n">
-        <v>0.0013</v>
+        <v>0.0021</v>
       </c>
       <c r="G314" s="7" t="n"/>
       <c r="H314" s="12" t="inlineStr">
@@ -23548,7 +23548,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="5" t="n">
-        <v>0.0512590660907832</v>
+        <v>0.0503175378602834</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>122</v>
       </c>
       <c r="P314" s="6" t="n">
-        <v>-0.005785999511042244</v>
+        <v>-0.006676437062367637</v>
       </c>
       <c r="Q314" s="10" t="inlineStr">
         <is>
@@ -23600,13 +23600,13 @@
         </is>
       </c>
       <c r="D315" s="15" t="n">
-        <v>62.92</v>
+        <v>62.9</v>
       </c>
       <c r="E315" s="26" t="n">
-        <v>-0.0044</v>
+        <v>-0.0046</v>
       </c>
       <c r="F315" s="16" t="n">
-        <v>0.0341</v>
+        <v>0.0339</v>
       </c>
       <c r="G315" s="17" t="n">
         <v>46239</v>
@@ -23635,14 +23635,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="16" t="n">
-        <v>0.03305785123966939</v>
+        <v>0.03338632750397458</v>
       </c>
       <c r="N315" s="14" t="inlineStr"/>
       <c r="O315" s="19" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="16" t="n">
-        <v>0.06484424666242845</v>
+        <v>0.06518282988871227</v>
       </c>
       <c r="Q315" s="20" t="inlineStr">
         <is>
@@ -23683,13 +23683,13 @@
         </is>
       </c>
       <c r="D316" s="4" t="n">
-        <v>140.88</v>
-      </c>
-      <c r="E316" s="5" t="n">
-        <v>0.0049</v>
+        <v>139.05</v>
+      </c>
+      <c r="E316" s="6" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F316" s="6" t="n">
-        <v>-0.0253</v>
+        <v>-0.038</v>
       </c>
       <c r="G316" s="7" t="n">
         <v>46309</v>
@@ -23718,7 +23718,7 @@
         <v>167</v>
       </c>
       <c r="M316" s="5" t="n">
-        <v>0.1854060193072118</v>
+        <v>0.2010068320747931</v>
       </c>
       <c r="N316" s="3" t="inlineStr"/>
       <c r="O316" s="9" t="n"/>
@@ -23762,13 +23762,13 @@
         </is>
       </c>
       <c r="D317" s="15" t="n">
-        <v>324.37</v>
+        <v>326.49</v>
       </c>
       <c r="E317" s="16" t="n">
-        <v>0.0011</v>
+        <v>0.0077</v>
       </c>
       <c r="F317" s="16" t="n">
-        <v>0.0474</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="G317" s="17" t="n"/>
       <c r="H317" s="22" t="inlineStr">
@@ -23794,7 +23794,7 @@
         <v>316</v>
       </c>
       <c r="P317" s="26" t="n">
-        <v>-0.02580386595554461</v>
+        <v>-0.03212962112162703</v>
       </c>
       <c r="Q317" s="20" t="inlineStr">
         <is>
@@ -23835,13 +23835,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>226.95</v>
+        <v>225.9</v>
       </c>
       <c r="E318" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.004</v>
       </c>
       <c r="F318" s="5" t="n">
-        <v>0.0791</v>
+        <v>0.0741</v>
       </c>
       <c r="G318" s="7" t="n">
         <v>46244</v>
@@ -23877,7 +23877,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="6" t="n">
-        <v>-0.05265476977307772</v>
+        <v>-0.04825143868968573</v>
       </c>
       <c r="Q318" s="10" t="inlineStr">
         <is>
@@ -23918,13 +23918,13 @@
         </is>
       </c>
       <c r="D319" s="15" t="n">
-        <v>122.01</v>
+        <v>121.67</v>
       </c>
       <c r="E319" s="26" t="n">
-        <v>-0.0014</v>
+        <v>-0.0042</v>
       </c>
       <c r="F319" s="26" t="n">
-        <v>-0.0136</v>
+        <v>-0.0163</v>
       </c>
       <c r="G319" s="17" t="n"/>
       <c r="H319" s="22" t="inlineStr">
@@ -23943,7 +23943,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="16" t="n">
-        <v>0.1638390295877387</v>
+        <v>0.167091312566779</v>
       </c>
       <c r="N319" s="14" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="16" t="n">
-        <v>0.1228587820670436</v>
+        <v>0.1259965480397797</v>
       </c>
       <c r="Q319" s="20" t="inlineStr">
         <is>
@@ -24003,13 +24003,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>228.71</v>
+        <v>231.57</v>
       </c>
       <c r="E320" s="6" t="n">
-        <v>-0.0171</v>
+        <v>-0.0048</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>0.1052</v>
+        <v>0.1191</v>
       </c>
       <c r="G320" s="7" t="n"/>
       <c r="H320" s="12" t="inlineStr">
@@ -24028,7 +24028,7 @@
         <v>237</v>
       </c>
       <c r="M320" s="5" t="n">
-        <v>0.03624677539241831</v>
+        <v>0.02344863324264804</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>236</v>
       </c>
       <c r="P320" s="5" t="n">
-        <v>0.03187442612915916</v>
+        <v>0.01913028457917695</v>
       </c>
       <c r="Q320" s="10" t="inlineStr">
         <is>
@@ -24080,13 +24080,13 @@
         </is>
       </c>
       <c r="D321" s="15" t="n">
-        <v>172.54</v>
+        <v>172.65</v>
       </c>
       <c r="E321" s="26" t="n">
-        <v>-0.0074</v>
+        <v>-0.0068</v>
       </c>
       <c r="F321" s="16" t="n">
-        <v>0.0135</v>
+        <v>0.0142</v>
       </c>
       <c r="G321" s="17" t="n">
         <v>46239</v>
@@ -24115,7 +24115,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="16" t="n">
-        <v>0.159151501101194</v>
+        <v>0.1584129742253113</v>
       </c>
       <c r="N321" s="14" t="inlineStr"/>
       <c r="O321" s="19" t="n"/>
@@ -24159,13 +24159,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>133.02</v>
-      </c>
-      <c r="E322" s="6" t="n">
-        <v>-0.0005</v>
+        <v>134.01</v>
+      </c>
+      <c r="E322" s="5" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>0.0687</v>
+        <v>0.0766</v>
       </c>
       <c r="G322" s="7" t="n"/>
       <c r="H322" s="12" t="inlineStr">
@@ -24184,7 +24184,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="6" t="n">
-        <v>-0.01518568636295302</v>
+        <v>-0.02246101037236021</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="9" t="n"/>
@@ -24228,13 +24228,13 @@
         </is>
       </c>
       <c r="D323" s="15" t="n">
-        <v>33.67</v>
+        <v>33.55</v>
       </c>
       <c r="E323" s="26" t="n">
-        <v>-0.0806</v>
+        <v>-0.08380000000000001</v>
       </c>
       <c r="F323" s="26" t="n">
-        <v>-0.1304</v>
+        <v>-0.1335</v>
       </c>
       <c r="G323" s="17" t="n"/>
       <c r="H323" s="22" t="inlineStr">
@@ -24297,13 +24297,13 @@
         </is>
       </c>
       <c r="D324" s="4" t="n">
-        <v>39.97</v>
+        <v>39.91</v>
       </c>
       <c r="E324" s="5" t="n">
-        <v>0.0713</v>
+        <v>0.0697</v>
       </c>
       <c r="F324" s="5" t="n">
-        <v>0.0302</v>
+        <v>0.0286</v>
       </c>
       <c r="G324" s="7" t="n"/>
       <c r="H324" s="12" t="inlineStr">
@@ -24348,13 +24348,13 @@
         </is>
       </c>
       <c r="D325" s="15" t="n">
-        <v>268.39</v>
+        <v>267.25</v>
       </c>
       <c r="E325" s="16" t="n">
-        <v>0.0916</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="F325" s="16" t="n">
-        <v>0.0532</v>
+        <v>0.0487</v>
       </c>
       <c r="G325" s="17" t="n">
         <v>46240</v>
@@ -24383,7 +24383,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="16" t="n">
-        <v>0.4307537538656434</v>
+        <v>0.4368568755846586</v>
       </c>
       <c r="N325" s="14" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="16" t="n">
-        <v>0.4158500689295429</v>
+        <v>0.421889616463985</v>
       </c>
       <c r="Q325" s="20" t="inlineStr"/>
       <c r="R325" s="19" t="n"/>
@@ -24437,13 +24437,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>71.65000000000001</v>
+        <v>71.73</v>
       </c>
       <c r="E326" s="6" t="n">
-        <v>-0.0608</v>
+        <v>-0.05980000000000001</v>
       </c>
       <c r="F326" s="6" t="n">
-        <v>-0.0054</v>
+        <v>-0.0043</v>
       </c>
       <c r="G326" s="7" t="n"/>
       <c r="H326" s="12" t="inlineStr">
@@ -24462,7 +24462,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="5" t="n">
-        <v>0.1025819958129797</v>
+        <v>0.1013522933221803</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="9" t="n"/>
@@ -24514,13 +24514,13 @@
         </is>
       </c>
       <c r="D327" s="15" t="n">
-        <v>123.91</v>
+        <v>124.27</v>
       </c>
       <c r="E327" s="26" t="n">
-        <v>-0.0164</v>
-      </c>
-      <c r="F327" s="26" t="n">
-        <v>-0.0025</v>
+        <v>-0.0135</v>
+      </c>
+      <c r="F327" s="16" t="n">
+        <v>0.0004</v>
       </c>
       <c r="G327" s="17" t="n">
         <v>46238</v>
@@ -24549,7 +24549,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="16" t="n">
-        <v>0.09757081752885162</v>
+        <v>0.09439124487004108</v>
       </c>
       <c r="N327" s="14" t="inlineStr">
         <is>
@@ -24560,7 +24560,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="16" t="n">
-        <v>0.1298523121620531</v>
+        <v>0.1265792226603364</v>
       </c>
       <c r="Q327" s="20" t="inlineStr">
         <is>
@@ -24601,13 +24601,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>108.71</v>
+        <v>108.86</v>
       </c>
       <c r="E328" s="6" t="n">
-        <v>-0.045</v>
+        <v>-0.0437</v>
       </c>
       <c r="F328" s="6" t="n">
-        <v>-0.0184</v>
+        <v>-0.017</v>
       </c>
       <c r="G328" s="7" t="n"/>
       <c r="H328" s="12" t="inlineStr">
@@ -24626,7 +24626,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="5" t="n">
-        <v>0.2050409345966333</v>
+        <v>0.203380488701084</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="5" t="n">
-        <v>0.1130530769938369</v>
+        <v>0.1115193826933676</v>
       </c>
       <c r="Q328" s="10" t="inlineStr">
         <is>
@@ -24682,13 +24682,13 @@
         </is>
       </c>
       <c r="D329" s="15" t="n">
-        <v>86.84999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="E329" s="26" t="n">
-        <v>-0.0068</v>
+        <v>-0.0027</v>
       </c>
       <c r="F329" s="16" t="n">
-        <v>0.0117</v>
+        <v>0.0158</v>
       </c>
       <c r="G329" s="17" t="n">
         <v>46318</v>
@@ -24724,7 +24724,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="16" t="n">
-        <v>0.2320092112838228</v>
+        <v>0.2270642201834862</v>
       </c>
       <c r="Q329" s="20" t="inlineStr">
         <is>
@@ -24773,13 +24773,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>56.72</v>
+        <v>57.39</v>
       </c>
       <c r="E330" s="5" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.0201</v>
       </c>
       <c r="F330" s="5" t="n">
-        <v>0.0236</v>
+        <v>0.0357</v>
       </c>
       <c r="G330" s="7" t="n"/>
       <c r="H330" s="12" t="inlineStr">
@@ -24798,7 +24798,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="5" t="n">
-        <v>0.110719322990127</v>
+        <v>0.09775222164140093</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="9" t="n"/>
@@ -24842,13 +24842,13 @@
         </is>
       </c>
       <c r="D331" s="15" t="n">
-        <v>43.78</v>
+        <v>43.33</v>
       </c>
       <c r="E331" s="26" t="n">
-        <v>-0.1555</v>
+        <v>-0.1642</v>
       </c>
       <c r="F331" s="26" t="n">
-        <v>-0.2463</v>
+        <v>-0.2541</v>
       </c>
       <c r="G331" s="17" t="n">
         <v>46241</v>
@@ -24903,13 +24903,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="E332" s="5" t="n">
-        <v>0.0005</v>
+        <v>9.49</v>
+      </c>
+      <c r="E332" s="6" t="n">
+        <v>-0.0125</v>
       </c>
       <c r="F332" s="6" t="n">
-        <v>-0.0843</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="G332" s="7" t="n">
         <v>46239</v>
@@ -24964,13 +24964,13 @@
         </is>
       </c>
       <c r="D333" s="15" t="n">
-        <v>92.86</v>
+        <v>93.25</v>
       </c>
       <c r="E333" s="26" t="n">
-        <v>-0.0326</v>
+        <v>-0.0285</v>
       </c>
       <c r="F333" s="16" t="n">
-        <v>0.0028</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="G333" s="17" t="n"/>
       <c r="H333" s="22" t="inlineStr">
@@ -24989,7 +24989,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="16" t="n">
-        <v>0.06612104242946372</v>
+        <v>0.06166219839142091</v>
       </c>
       <c r="N333" s="14" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="16" t="n">
-        <v>0.2061167348696963</v>
+        <v>0.2010723860589812</v>
       </c>
       <c r="Q333" s="20" t="inlineStr">
         <is>
@@ -25041,13 +25041,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>108.7</v>
+        <v>109.25</v>
       </c>
       <c r="E334" s="6" t="n">
-        <v>-0.068</v>
+        <v>-0.0633</v>
       </c>
       <c r="F334" s="6" t="n">
-        <v>-0.03759999999999999</v>
+        <v>-0.0328</v>
       </c>
       <c r="G334" s="7" t="n"/>
       <c r="H334" s="12" t="inlineStr">
@@ -25066,7 +25066,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="5" t="n">
-        <v>0.1683532658693652</v>
+        <v>0.1624713958810069</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="9" t="n"/>
@@ -35376,7 +35376,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of August 04, 2026 at 17:14 UTC</t>
+          <t>Data as of August 04, 2026 at 22:01 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>100.15</v>
+        <v>101.76</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.0281</v>
+        <v>0.0447</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0206</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>46239</v>
@@ -878,7 +878,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>0.2481278082875686</v>
+        <v>0.228380503144654</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.437843235147279</v>
+        <v>0.4150943396226414</v>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="D3" s="14" t="n">
-        <v>363.49</v>
+        <v>362.43</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>-0.008100000000000001</v>
+        <v>-0.011</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>-0.0137</v>
+        <v>-0.0166</v>
       </c>
       <c r="G3" s="16" t="n">
         <v>46322</v>
@@ -973,7 +973,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="19" t="n">
-        <v>0.2049850064651022</v>
+        <v>0.2085092293684297</v>
       </c>
       <c r="N3" s="13" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="19" t="n">
-        <v>0.1554650746925637</v>
+        <v>0.1588444665176724</v>
       </c>
       <c r="Q3" s="20" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>584.15</v>
+        <v>588.77</v>
       </c>
       <c r="E4" s="23" t="n">
-        <v>-0.0269</v>
+        <v>-0.0192</v>
       </c>
       <c r="F4" s="23" t="n">
-        <v>-0.0149</v>
+        <v>-0.0071</v>
       </c>
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="11" t="inlineStr">
@@ -1054,7 +1054,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.4294273731062228</v>
+        <v>0.4182108463406763</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.5920568347171103</v>
+        <v>0.5795641761638671</v>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>37.69</v>
+        <v>38.15</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>0.0005</v>
+        <v>0.0127</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.095</v>
+        <v>0.1084</v>
       </c>
       <c r="G5" s="16" t="n"/>
       <c r="H5" s="22" t="inlineStr">
@@ -1165,13 +1165,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>73.51000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>-0.033</v>
+        <v>-0.0239</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>-0.1054</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>46315</v>
@@ -1200,7 +1200,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.08828730784927213</v>
+        <v>0.07816711590296492</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0.3603591348115902</v>
+        <v>0.3477088948787062</v>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>81.76000000000001</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>0.0233</v>
+        <v>0.0227</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>0.0857</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="G7" s="16" t="n"/>
       <c r="H7" s="22" t="inlineStr">
@@ -1277,7 +1277,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>0.1130136986301369</v>
+        <v>0.1136947742014442</v>
       </c>
       <c r="N7" s="13" t="inlineStr"/>
       <c r="O7" s="18" t="n"/>
@@ -1321,13 +1321,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>489.42</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>0.0133</v>
+        <v>482.23</v>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>-0.0016</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>-0.0152</v>
+        <v>-0.0296</v>
       </c>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="11" t="inlineStr">
@@ -1346,7 +1346,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.1645008377262881</v>
+        <v>0.1818634261659373</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.3240979118139838</v>
+        <v>0.3438400763121331</v>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>184.3</v>
+        <v>183.07</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>-0.0416</v>
+        <v>-0.048</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.1003</v>
       </c>
       <c r="G9" s="16" t="n"/>
       <c r="H9" s="22" t="inlineStr">
@@ -1457,13 +1457,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>173.21</v>
+        <v>173.46</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>-0.0472</v>
+        <v>-0.0458</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>-0.0274</v>
+        <v>-0.0261</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>46317</v>
@@ -1492,7 +1492,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="23" t="n">
-        <v>-0.01853241729692286</v>
+        <v>-0.01994696183558173</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.5588014548813578</v>
+        <v>0.5565548253199584</v>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
@@ -1544,13 +1544,13 @@
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>45.87</v>
+        <v>46.47</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>0.09029999999999999</v>
+        <v>0.1046</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>0.011</v>
+        <v>0.0242</v>
       </c>
       <c r="G11" s="16" t="n">
         <v>46316</v>
@@ -1579,7 +1579,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="15" t="n">
-        <v>-0.0625681273163287</v>
+        <v>-0.07467183128900363</v>
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="19" t="n">
-        <v>0.0900370612600829</v>
+        <v>0.07596298687325159</v>
       </c>
       <c r="Q11" s="20" t="inlineStr">
         <is>
@@ -1635,13 +1635,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>151.37</v>
+        <v>152.49</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.0252</v>
+        <v>0.0328</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.1335</v>
+        <v>0.1419</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>46240</v>
@@ -1670,7 +1670,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.1957455242121952</v>
+        <v>0.1869630795461997</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>0.02398097377287438</v>
+        <v>0.01646009574398315</v>
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
@@ -1722,13 +1722,13 @@
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>273.17</v>
+        <v>272.65</v>
       </c>
       <c r="E13" s="19" t="n">
-        <v>0.1188</v>
+        <v>0.1167</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>0.1103</v>
+        <v>0.1082</v>
       </c>
       <c r="G13" s="16" t="n"/>
       <c r="H13" s="22" t="inlineStr">
@@ -1747,7 +1747,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="19" t="n">
-        <v>0.1787531573745286</v>
+        <v>0.1810012836970476</v>
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="19" t="n">
-        <v>0.04330636599919458</v>
+        <v>0.04529616724738685</v>
       </c>
       <c r="Q13" s="20" t="inlineStr">
         <is>
@@ -1811,13 +1811,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3047.92</v>
+        <v>3066.06</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.0305</v>
+        <v>0.0366</v>
       </c>
       <c r="F14" s="23" t="n">
-        <v>-0.022</v>
+        <v>-0.0162</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>46287</v>
@@ -1846,7 +1846,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0.3615842935510118</v>
+        <v>0.3535286328382354</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0.2139426231659623</v>
+        <v>0.2067604678316798</v>
       </c>
       <c r="Q14" s="9" t="inlineStr">
         <is>
@@ -1898,13 +1898,13 @@
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>84.55</v>
+        <v>84.5</v>
       </c>
       <c r="E15" s="19" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0833</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>0.1819</v>
+        <v>0.1812</v>
       </c>
       <c r="G15" s="16" t="n">
         <v>46261</v>
@@ -1933,7 +1933,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="15" t="n">
-        <v>-0.231224127735068</v>
+        <v>-0.2307692307692308</v>
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="19" t="n">
-        <v>0.005322294500295717</v>
+        <v>0.005917159763313609</v>
       </c>
       <c r="Q15" s="20" t="inlineStr"/>
       <c r="R15" s="18" t="n"/>
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>205.21</v>
+        <v>207.02</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.1336</v>
+        <v>0.1436</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.2374</v>
+        <v>0.2483</v>
       </c>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="11" t="inlineStr">
@@ -2004,7 +2004,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.0428341698747624</v>
+        <v>0.03371654912568829</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.1938989328005457</v>
+        <v>0.1834605352139889</v>
       </c>
       <c r="Q16" s="9" t="inlineStr">
         <is>
@@ -2064,13 +2064,13 @@
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>368.77</v>
+        <v>369.34</v>
       </c>
       <c r="E17" s="19" t="n">
-        <v>0.1806</v>
+        <v>0.1824</v>
       </c>
       <c r="F17" s="19" t="n">
-        <v>0.1631</v>
+        <v>0.1649</v>
       </c>
       <c r="G17" s="16" t="n">
         <v>46261</v>
@@ -2099,7 +2099,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="19" t="n">
-        <v>0.01689399896954746</v>
+        <v>0.01532463312936596</v>
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="19" t="n">
-        <v>0.01689399896954746</v>
+        <v>0.01532463312936596</v>
       </c>
       <c r="Q17" s="20" t="inlineStr"/>
       <c r="R17" s="18" t="n"/>
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>34.94</v>
+        <v>34.5</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.0284</v>
+        <v>0.0153</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.191</v>
+        <v>0.1759</v>
       </c>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="11" t="inlineStr">
@@ -2174,7 +2174,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.287922152261019</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.287922152261019</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="Q18" s="9" t="inlineStr">
         <is>
@@ -2226,13 +2226,13 @@
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>151.18</v>
+        <v>151.45</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>-0.0363</v>
+        <v>-0.0346</v>
       </c>
       <c r="F19" s="19" t="n">
-        <v>0.0384</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="G19" s="16" t="n">
         <v>46324</v>
@@ -2261,7 +2261,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="19" t="n">
-        <v>0.1244873660537108</v>
+        <v>0.1224826675470453</v>
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="19" t="n">
-        <v>0.1707897870088635</v>
+        <v>0.1687025420931001</v>
       </c>
       <c r="Q19" s="20" t="inlineStr">
         <is>
@@ -2313,13 +2313,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>199.88</v>
+        <v>200.32</v>
       </c>
       <c r="E20" s="23" t="n">
-        <v>-0.1272</v>
+        <v>-0.1253</v>
       </c>
       <c r="F20" s="23" t="n">
-        <v>-0.0696</v>
+        <v>-0.0675</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>46259</v>
@@ -2348,7 +2348,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0.1006603962377427</v>
+        <v>0.09824281150159749</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="8" t="n"/>
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>128.54</v>
+        <v>128.76</v>
       </c>
       <c r="E21" s="19" t="n">
-        <v>0.0583</v>
+        <v>0.0601</v>
       </c>
       <c r="F21" s="19" t="n">
-        <v>0.1814</v>
+        <v>0.1835</v>
       </c>
       <c r="G21" s="16" t="n">
         <v>46267</v>
@@ -2453,13 +2453,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>88.68000000000001</v>
+        <v>89.16</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.1392</v>
+        <v>0.1453</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.0801</v>
+        <v>0.0859</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>46315</v>
@@ -2488,7 +2488,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="23" t="n">
-        <v>-0.3121335137573298</v>
+        <v>-0.3158366980708838</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.1276499774470004</v>
+        <v>0.1215791834903545</v>
       </c>
       <c r="Q22" s="9" t="inlineStr">
         <is>
@@ -2540,13 +2540,13 @@
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>131.92</v>
+        <v>131.32</v>
       </c>
       <c r="E23" s="19" t="n">
-        <v>0.0253</v>
+        <v>0.0207</v>
       </c>
       <c r="F23" s="19" t="n">
-        <v>0.3441</v>
+        <v>0.338</v>
       </c>
       <c r="G23" s="16" t="n">
         <v>46315</v>
@@ -2578,7 +2578,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="19" t="n">
-        <v>0.09915100060642824</v>
+        <v>0.1041730124885776</v>
       </c>
       <c r="Q23" s="20" t="inlineStr"/>
       <c r="R23" s="18" t="n"/>
@@ -2613,13 +2613,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>351.77</v>
+        <v>353.14</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.0071</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.1319</v>
+        <v>0.1363</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>46252</v>
@@ -2648,7 +2648,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0.02339596895698899</v>
+        <v>0.01942572350908992</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0.1371066321744322</v>
+        <v>0.1326952483434332</v>
       </c>
       <c r="Q24" s="9" t="inlineStr">
         <is>
@@ -2708,13 +2708,13 @@
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>219.11</v>
+        <v>219.94</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>-0.0209</v>
+        <v>-0.0172</v>
       </c>
       <c r="F25" s="19" t="n">
-        <v>0.0397</v>
+        <v>0.0437</v>
       </c>
       <c r="G25" s="16" t="n">
         <v>46253</v>
@@ -2743,7 +2743,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>0.1637990050659485</v>
+        <v>0.159407111030281</v>
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="19" t="n">
-        <v>0.04970106339281632</v>
+        <v>0.04573974720378286</v>
       </c>
       <c r="Q25" s="20" t="inlineStr">
         <is>
@@ -2799,13 +2799,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>273.75</v>
+        <v>274</v>
       </c>
       <c r="E26" s="23" t="n">
-        <v>-0.0206</v>
+        <v>-0.0197</v>
       </c>
       <c r="F26" s="23" t="n">
-        <v>-0.0218</v>
+        <v>-0.0209</v>
       </c>
       <c r="G26" s="6" t="n"/>
       <c r="H26" s="11" t="inlineStr">
@@ -2824,7 +2824,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.0958904109589041</v>
+        <v>0.0948905109489051</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0.2785388127853881</v>
+        <v>0.2773722627737226</v>
       </c>
       <c r="Q26" s="9" t="inlineStr">
         <is>
@@ -2876,13 +2876,13 @@
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>41.68</v>
+        <v>42.45</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>-0.0383</v>
+        <v>-0.0205</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>-0.0302</v>
+        <v>-0.0123</v>
       </c>
       <c r="G27" s="16" t="n">
         <v>46294</v>
@@ -2937,13 +2937,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>93.03</v>
+        <v>93.44</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.1043</v>
+        <v>0.1092</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.0298</v>
+        <v>0.0344</v>
       </c>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="11" t="inlineStr">
@@ -2962,7 +2962,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.182414274965065</v>
+        <v>0.1772260273972603</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.236160378372568</v>
+        <v>0.230736301369863</v>
       </c>
       <c r="Q28" s="9" t="inlineStr">
         <is>
@@ -3018,13 +3018,13 @@
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>204.48</v>
+        <v>206.63</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>-0.0499</v>
+        <v>-0.0399</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>0.1022</v>
+        <v>0.1138</v>
       </c>
       <c r="G29" s="16" t="n">
         <v>46317</v>
@@ -3079,13 +3079,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>252.7</v>
+        <v>253.22</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.1956</v>
+        <v>0.1981</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.0969</v>
+        <v>0.0992</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>46254</v>
@@ -3114,7 +3114,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="23" t="n">
-        <v>-0.03047091412742378</v>
+        <v>-0.03246189084590474</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.04867431737237836</v>
+        <v>0.04652081194218467</v>
       </c>
       <c r="Q30" s="9" t="inlineStr">
         <is>
@@ -3166,13 +3166,13 @@
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>106.04</v>
+        <v>106</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>0.0385</v>
+        <v>0.0381</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>0.1128</v>
+        <v>0.1124</v>
       </c>
       <c r="G31" s="16" t="n"/>
       <c r="H31" s="22" t="inlineStr">
@@ -3191,7 +3191,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>0.1316484345529988</v>
+        <v>0.1320754716981132</v>
       </c>
       <c r="N31" s="13" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="19" t="n">
-        <v>0.08449641644662385</v>
+        <v>0.08490566037735849</v>
       </c>
       <c r="Q31" s="20" t="inlineStr">
         <is>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>12.02</v>
+        <v>12.65</v>
       </c>
       <c r="E32" s="23" t="n">
-        <v>-0.254</v>
+        <v>-0.2153</v>
       </c>
       <c r="F32" s="23" t="n">
-        <v>-0.1349</v>
+        <v>-0.08990000000000001</v>
       </c>
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="11" t="inlineStr">
@@ -3294,13 +3294,13 @@
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>159.3</v>
+        <v>159.92</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>0.0528</v>
+        <v>0.05690000000000001</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0049</v>
       </c>
       <c r="G33" s="16" t="n">
         <v>46253</v>
@@ -3329,7 +3329,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>0.004394224733207712</v>
+        <v>0.0005002501250626095</v>
       </c>
       <c r="N33" s="13" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="19" t="n">
-        <v>0.09855618330194593</v>
+        <v>0.09429714857428723</v>
       </c>
       <c r="Q33" s="20" t="inlineStr">
         <is>
@@ -3385,13 +3385,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>33.06</v>
+        <v>33.41</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.0941</v>
+        <v>0.1056</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.1103</v>
+        <v>0.1219</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>46317</v>
@@ -3420,7 +3420,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.05868118572292794</v>
+        <v>0.04759054175396599</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0.2099213551119176</v>
+        <v>0.197246333433104</v>
       </c>
       <c r="Q34" s="9" t="inlineStr">
         <is>
@@ -3472,13 +3472,13 @@
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>323.04</v>
+        <v>321.55</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>-0.2304</v>
+        <v>-0.234</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>-0.1738</v>
+        <v>-0.1776</v>
       </c>
       <c r="G35" s="16" t="n">
         <v>46323</v>
@@ -3507,7 +3507,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="15" t="n">
-        <v>-0.5975730559683011</v>
+        <v>-0.5957082879800965</v>
       </c>
       <c r="N35" s="13" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="15" t="n">
-        <v>-0.07132243684992576</v>
+        <v>-0.06701912610791481</v>
       </c>
       <c r="Q35" s="20" t="inlineStr">
         <is>
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>67.04000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="E36" s="23" t="n">
-        <v>-0.07429999999999999</v>
+        <v>-0.0585</v>
       </c>
       <c r="F36" s="23" t="n">
-        <v>-0.0519</v>
+        <v>-0.0358</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>46239</v>
@@ -3620,13 +3620,13 @@
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>537.3200000000001</v>
+        <v>539.47</v>
       </c>
       <c r="E37" s="19" t="n">
-        <v>0.1875</v>
+        <v>0.1922</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>0.1504</v>
+        <v>0.155</v>
       </c>
       <c r="G37" s="16" t="n">
         <v>46261</v>
@@ -3655,7 +3655,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="15" t="n">
-        <v>-0.1625102359860047</v>
+        <v>-0.1658479618885202</v>
       </c>
       <c r="N37" s="13" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="19" t="n">
-        <v>0.1817911114419712</v>
+        <v>0.1770812093350881</v>
       </c>
       <c r="Q37" s="20" t="inlineStr">
         <is>
@@ -3711,13 +3711,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>102.56</v>
+        <v>103.64</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.0524</v>
+        <v>0.0635</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.0602</v>
+        <v>0.0713</v>
       </c>
       <c r="G38" s="6" t="n"/>
       <c r="H38" s="11" t="inlineStr">
@@ -3736,7 +3736,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.07254290171606861</v>
+        <v>0.06136626785025086</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.0237909516380655</v>
+        <v>0.01312234658433037</v>
       </c>
       <c r="Q38" s="9" t="inlineStr">
         <is>
@@ -3792,13 +3792,13 @@
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>92.67</v>
+        <v>93.28</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>-0.0077</v>
+        <v>-0.0012</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>0.0462</v>
+        <v>0.05309999999999999</v>
       </c>
       <c r="G39" s="16" t="n"/>
       <c r="H39" s="22" t="inlineStr">
@@ -3817,7 +3817,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>0.02514298046832846</v>
+        <v>0.01843910806174956</v>
       </c>
       <c r="N39" s="13" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="19" t="n">
-        <v>0.07909787417718785</v>
+        <v>0.07204116638078902</v>
       </c>
       <c r="Q39" s="20" t="inlineStr">
         <is>
@@ -3873,13 +3873,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>940.42</v>
+        <v>941.99</v>
       </c>
       <c r="E40" s="23" t="n">
-        <v>-0.0103</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F40" s="23" t="n">
-        <v>-0.03240000000000001</v>
+        <v>-0.0307</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>46289</v>
@@ -3908,7 +3908,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0.06335467131707115</v>
+        <v>0.06158239471756599</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0.1696901384487783</v>
+        <v>0.1677406341893226</v>
       </c>
       <c r="Q40" s="9" t="inlineStr">
         <is>
@@ -3968,13 +3968,13 @@
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>127.21</v>
+        <v>126.94</v>
       </c>
       <c r="E41" s="19" t="n">
-        <v>0.0941</v>
+        <v>0.09179999999999999</v>
       </c>
       <c r="F41" s="19" t="n">
-        <v>0.2267</v>
+        <v>0.2241</v>
       </c>
       <c r="G41" s="16" t="n">
         <v>46261</v>
@@ -4003,7 +4003,7 @@
         <v>125</v>
       </c>
       <c r="M41" s="15" t="n">
-        <v>-0.01737284804653717</v>
+        <v>-0.0152828107767449</v>
       </c>
       <c r="N41" s="13" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="19" t="n">
-        <v>0.06123732410973985</v>
+        <v>0.0634945643611155</v>
       </c>
       <c r="Q41" s="20" t="inlineStr">
         <is>
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>25.75</v>
+        <v>25.73</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.0373</v>
+        <v>0.0367</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.1402</v>
+        <v>0.1395</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>46239</v>
@@ -4119,7 +4119,7 @@
         <v>86.83</v>
       </c>
       <c r="E43" s="19" t="n">
-        <v>0.0467</v>
+        <v>0.0466</v>
       </c>
       <c r="F43" s="19" t="n">
         <v>0.0925</v>
@@ -4201,13 +4201,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>56.93</v>
+        <v>56.68</v>
       </c>
       <c r="E44" s="23" t="n">
-        <v>-0.0227</v>
+        <v>-0.027</v>
       </c>
       <c r="F44" s="23" t="n">
-        <v>-0.1045</v>
+        <v>-0.1084</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>46275</v>
@@ -4236,7 +4236,7 @@
         <v>58</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>0.01879501141753031</v>
+        <v>0.02328863796753705</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.3701036360442649</v>
+        <v>0.3761467889908257</v>
       </c>
       <c r="Q44" s="9" t="inlineStr">
         <is>
@@ -4288,13 +4288,13 @@
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>62.25</v>
+        <v>62.6</v>
       </c>
       <c r="E45" s="19" t="n">
-        <v>0.0521</v>
+        <v>0.058</v>
       </c>
       <c r="F45" s="19" t="n">
-        <v>0.0034</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="G45" s="16" t="n"/>
       <c r="H45" s="22" t="inlineStr">
@@ -4313,7 +4313,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="19" t="n">
-        <v>0.1244979919678715</v>
+        <v>0.1182108626198083</v>
       </c>
       <c r="N45" s="13" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="19" t="n">
-        <v>0.1405622489959839</v>
+        <v>0.134185303514377</v>
       </c>
       <c r="Q45" s="20" t="inlineStr">
         <is>
@@ -4373,13 +4373,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>52.19</v>
+        <v>52.54</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0147</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.1049</v>
+        <v>0.1122</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>46301</v>
@@ -4444,13 +4444,13 @@
         </is>
       </c>
       <c r="D47" s="14" t="n">
-        <v>94.5</v>
+        <v>94.45999999999999</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>-0.0295</v>
+        <v>-0.0299</v>
       </c>
       <c r="F47" s="19" t="n">
-        <v>0.0553</v>
+        <v>0.0548</v>
       </c>
       <c r="G47" s="16" t="n">
         <v>46240</v>
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>68.01000000000001</v>
+        <v>68.44</v>
       </c>
       <c r="E48" s="23" t="n">
-        <v>-0.0538</v>
+        <v>-0.0479</v>
       </c>
       <c r="F48" s="23" t="n">
-        <v>-0.0578</v>
+        <v>-0.0519</v>
       </c>
       <c r="G48" s="6" t="n"/>
       <c r="H48" s="11" t="inlineStr">
@@ -4556,13 +4556,13 @@
         </is>
       </c>
       <c r="D49" s="14" t="n">
-        <v>138.59</v>
+        <v>138.78</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>-0.0328</v>
+        <v>-0.0315</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>-0.0235</v>
+        <v>-0.0221</v>
       </c>
       <c r="G49" s="16" t="n">
         <v>46303</v>
@@ -4591,7 +4591,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="19" t="n">
-        <v>0.01017389422036219</v>
+        <v>0.008790892059374542</v>
       </c>
       <c r="N49" s="13" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="19" t="n">
-        <v>0.08232917237895949</v>
+        <v>0.08084738434932986</v>
       </c>
       <c r="Q49" s="20" t="inlineStr">
         <is>
@@ -4651,13 +4651,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>145.8</v>
+        <v>146.8</v>
       </c>
       <c r="E50" s="23" t="n">
-        <v>-0.0235</v>
-      </c>
-      <c r="F50" s="23" t="n">
-        <v>-0.005</v>
+        <v>-0.0168</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0.0018</v>
       </c>
       <c r="G50" s="6" t="n"/>
       <c r="H50" s="11" t="inlineStr">
@@ -4676,7 +4676,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.1248285322359396</v>
+        <v>0.1171662125340599</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0.111111111111111</v>
+        <v>0.103542234332425</v>
       </c>
       <c r="Q50" s="9" t="inlineStr">
         <is>
@@ -4740,13 +4740,13 @@
         </is>
       </c>
       <c r="D51" s="14" t="n">
-        <v>84.55</v>
-      </c>
-      <c r="E51" s="19" t="n">
-        <v>0.0038</v>
+        <v>84.20999999999999</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>-0.0002</v>
       </c>
       <c r="F51" s="19" t="n">
-        <v>0.1083</v>
+        <v>0.1038</v>
       </c>
       <c r="G51" s="16" t="n"/>
       <c r="H51" s="22" t="inlineStr">
@@ -4765,7 +4765,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="19" t="n">
-        <v>0.1827321111768185</v>
+        <v>0.1875074219213871</v>
       </c>
       <c r="N51" s="13" t="inlineStr"/>
       <c r="O51" s="18" t="n"/>
@@ -4809,13 +4809,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>147.59</v>
+        <v>147.7</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.1704</v>
+        <v>0.1713</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.2041</v>
+        <v>0.205</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>46253</v>
@@ -4844,7 +4844,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="23" t="n">
-        <v>-0.05142624839081241</v>
+        <v>-0.05213270142180088</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="23" t="n">
-        <v>-0.08530388237685482</v>
+        <v>-0.08598510494245085</v>
       </c>
       <c r="Q52" s="9" t="inlineStr">
         <is>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>112.21</v>
+        <v>112.34</v>
       </c>
       <c r="E53" s="19" t="n">
-        <v>0.0141</v>
+        <v>0.0153</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>-0.0561</v>
+        <v>-0.055</v>
       </c>
       <c r="G53" s="16" t="n">
         <v>46254</v>
@@ -4935,7 +4935,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="19" t="n">
-        <v>0.2476606363069246</v>
+        <v>0.2462168417304611</v>
       </c>
       <c r="N53" s="13" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="19" t="n">
-        <v>0.2476606363069246</v>
+        <v>0.2462168417304611</v>
       </c>
       <c r="Q53" s="20" t="inlineStr">
         <is>
@@ -4995,13 +4995,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>61.47</v>
+        <v>61.67</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0.1544</v>
+        <v>0.1581</v>
       </c>
       <c r="F54" s="23" t="n">
-        <v>-0.0179</v>
+        <v>-0.0147</v>
       </c>
       <c r="G54" s="6" t="n">
         <v>46316</v>
@@ -5037,7 +5037,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>0.236375467707825</v>
+        <v>0.2323658180638884</v>
       </c>
       <c r="Q54" s="9" t="inlineStr">
         <is>
@@ -5078,13 +5078,13 @@
         </is>
       </c>
       <c r="D55" s="14" t="n">
-        <v>115.66</v>
+        <v>115.04</v>
       </c>
       <c r="E55" s="19" t="n">
-        <v>0.1166</v>
+        <v>0.1106</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>-0.0126</v>
+        <v>-0.0179</v>
       </c>
       <c r="G55" s="16" t="n">
         <v>46240</v>
@@ -5113,7 +5113,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="19" t="n">
-        <v>0.5822237592944839</v>
+        <v>0.590751043115438</v>
       </c>
       <c r="N55" s="13" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="19" t="n">
-        <v>0.2536745633754107</v>
+        <v>0.2604311543810848</v>
       </c>
       <c r="Q55" s="20" t="inlineStr">
         <is>
@@ -5165,13 +5165,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>187.37</v>
+        <v>186.41</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.1146</v>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.1089</v>
+      </c>
+      <c r="F56" s="23" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="G56" s="6" t="n"/>
       <c r="H56" s="11" t="inlineStr">
@@ -5190,7 +5190,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>0.1848214762235149</v>
+        <v>0.1909232337320959</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>0.2008325772535624</v>
+        <v>0.2070167909446918</v>
       </c>
       <c r="Q56" s="9" t="inlineStr">
         <is>
@@ -5246,13 +5246,13 @@
         </is>
       </c>
       <c r="D57" s="14" t="n">
-        <v>135.49</v>
+        <v>134.23</v>
       </c>
       <c r="E57" s="19" t="n">
-        <v>0.0472</v>
+        <v>0.0374</v>
       </c>
       <c r="F57" s="15" t="n">
-        <v>-0.0166</v>
+        <v>-0.0258</v>
       </c>
       <c r="G57" s="16" t="n"/>
       <c r="H57" s="22" t="inlineStr">
@@ -5271,7 +5271,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="19" t="n">
-        <v>0.4466012251826702</v>
+        <v>0.460180287566118</v>
       </c>
       <c r="N57" s="13" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="19" t="n">
-        <v>0.2547051442910915</v>
+        <v>0.2664829024808166</v>
       </c>
       <c r="Q57" s="20" t="inlineStr">
         <is>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>37.54</v>
+        <v>37.72</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.0295</v>
+        <v>0.0343</v>
       </c>
       <c r="F58" s="23" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.0024</v>
       </c>
       <c r="G58" s="6" t="n"/>
       <c r="H58" s="11" t="inlineStr">
@@ -5378,13 +5378,13 @@
         </is>
       </c>
       <c r="D59" s="14" t="n">
-        <v>20.39</v>
+        <v>20.34</v>
       </c>
       <c r="E59" s="19" t="n">
-        <v>0.059</v>
+        <v>0.0566</v>
       </c>
       <c r="F59" s="19" t="n">
-        <v>0.0513</v>
+        <v>0.049</v>
       </c>
       <c r="G59" s="16" t="n"/>
       <c r="H59" s="22" t="inlineStr">
@@ -5429,13 +5429,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>186.83</v>
+        <v>186.17</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0716</v>
       </c>
       <c r="F60" s="23" t="n">
-        <v>-0.0301</v>
+        <v>-0.0335</v>
       </c>
       <c r="G60" s="6" t="n"/>
       <c r="H60" s="11" t="inlineStr">
@@ -5480,13 +5480,13 @@
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>31.92</v>
+        <v>31.82</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>-0.0327</v>
+        <v>-0.0358</v>
       </c>
       <c r="F61" s="15" t="n">
-        <v>-0.1853</v>
+        <v>-0.1879</v>
       </c>
       <c r="G61" s="16" t="n">
         <v>46315</v>
@@ -5522,7 +5522,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="19" t="n">
-        <v>0.3471177944862155</v>
+        <v>0.3513513513513513</v>
       </c>
       <c r="Q61" s="20" t="inlineStr">
         <is>
@@ -5567,13 +5567,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>31.15</v>
+        <v>31.12</v>
       </c>
       <c r="E62" s="23" t="n">
-        <v>-0.0172</v>
+        <v>-0.018</v>
       </c>
       <c r="F62" s="23" t="n">
-        <v>-0.0169</v>
+        <v>-0.0177</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>46316</v>
@@ -5602,7 +5602,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.1235955056179776</v>
+        <v>0.1246786632390745</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="8" t="n"/>
@@ -5646,13 +5646,13 @@
         </is>
       </c>
       <c r="D63" s="14" t="n">
-        <v>202.49</v>
+        <v>202.55</v>
       </c>
       <c r="E63" s="19" t="n">
-        <v>0.1419</v>
+        <v>0.1422</v>
       </c>
       <c r="F63" s="19" t="n">
-        <v>0.106</v>
+        <v>0.1063</v>
       </c>
       <c r="G63" s="16" t="n">
         <v>46239</v>
@@ -5707,13 +5707,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>50.22</v>
+        <v>49.91</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0.0984</v>
+        <v>0.0916</v>
       </c>
       <c r="F64" s="23" t="n">
-        <v>-0.08470000000000001</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>46311</v>
@@ -5749,7 +5749,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0.2544802867383513</v>
+        <v>0.2622720897615709</v>
       </c>
       <c r="Q64" s="9" t="inlineStr">
         <is>
@@ -5798,13 +5798,13 @@
         </is>
       </c>
       <c r="D65" s="14" t="n">
-        <v>41.91</v>
+        <v>41.43</v>
       </c>
       <c r="E65" s="19" t="n">
-        <v>0.0353</v>
+        <v>0.0235</v>
       </c>
       <c r="F65" s="15" t="n">
-        <v>-0.0781</v>
+        <v>-0.0886</v>
       </c>
       <c r="G65" s="16" t="n"/>
       <c r="H65" s="22" t="inlineStr">
@@ -5849,13 +5849,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>71.84</v>
+        <v>71.81</v>
       </c>
       <c r="E66" s="23" t="n">
-        <v>-0.0135</v>
+        <v>-0.0139</v>
       </c>
       <c r="F66" s="23" t="n">
-        <v>-0.0017</v>
+        <v>-0.0021</v>
       </c>
       <c r="G66" s="6" t="n"/>
       <c r="H66" s="11" t="inlineStr">
@@ -5874,7 +5874,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0.2388641425389754</v>
+        <v>0.2393817017128533</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="8" t="n"/>
@@ -5930,13 +5930,13 @@
         </is>
       </c>
       <c r="D67" s="14" t="n">
-        <v>152.17</v>
+        <v>151.63</v>
       </c>
       <c r="E67" s="19" t="n">
-        <v>0.1153</v>
+        <v>0.1113</v>
       </c>
       <c r="F67" s="19" t="n">
-        <v>0.015</v>
+        <v>0.0114</v>
       </c>
       <c r="G67" s="16" t="n"/>
       <c r="H67" s="22" t="inlineStr">
@@ -5955,7 +5955,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="19" t="n">
-        <v>0.2157455477426563</v>
+        <v>0.2200751830112775</v>
       </c>
       <c r="N67" s="13" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="19" t="n">
-        <v>0.2157455477426563</v>
+        <v>0.2200751830112775</v>
       </c>
       <c r="Q67" s="20" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>124.86</v>
+        <v>125.56</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0.0364</v>
+        <v>0.0423</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.0559</v>
+        <v>0.0619</v>
       </c>
       <c r="G68" s="6" t="n">
         <v>46240</v>
@@ -6046,7 +6046,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="23" t="n">
-        <v>-0.03892359442575685</v>
+        <v>-0.04428161834979295</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>115</v>
       </c>
       <c r="P68" s="23" t="n">
-        <v>-0.07896844465801697</v>
+        <v>-0.08410321758521824</v>
       </c>
       <c r="Q68" s="9" t="inlineStr"/>
       <c r="R68" s="8" t="n"/>
@@ -6092,13 +6092,13 @@
         </is>
       </c>
       <c r="D69" s="14" t="n">
-        <v>358.43</v>
+        <v>359.97</v>
       </c>
       <c r="E69" s="19" t="n">
-        <v>0.0043</v>
+        <v>0.0086</v>
       </c>
       <c r="F69" s="19" t="n">
-        <v>0.091</v>
+        <v>0.09570000000000001</v>
       </c>
       <c r="G69" s="16" t="n"/>
       <c r="H69" s="22" t="inlineStr">
@@ -6117,7 +6117,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="19" t="n">
-        <v>0.1327176854615964</v>
+        <v>0.127871767091702</v>
       </c>
       <c r="N69" s="13" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="19" t="n">
-        <v>0.2164160366040789</v>
+        <v>0.2112120454482317</v>
       </c>
       <c r="Q69" s="20" t="inlineStr">
         <is>
@@ -6165,13 +6165,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>348.42</v>
+        <v>348.99</v>
       </c>
       <c r="E70" s="23" t="n">
-        <v>-0.0214</v>
+        <v>-0.0198</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.1216</v>
+        <v>0.1234</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>46311</v>
@@ -6200,7 +6200,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.1910912117559267</v>
+        <v>0.1891458207971575</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.09063773606566783</v>
+        <v>0.08885641422390324</v>
       </c>
       <c r="Q70" s="9" t="inlineStr">
         <is>
@@ -6260,13 +6260,13 @@
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>63.26</v>
+        <v>63.25</v>
       </c>
       <c r="E71" s="19" t="n">
-        <v>0.0561</v>
+        <v>0.0559</v>
       </c>
       <c r="F71" s="19" t="n">
-        <v>0.1752</v>
+        <v>0.175</v>
       </c>
       <c r="G71" s="16" t="n">
         <v>46309</v>
@@ -6321,13 +6321,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1124.66</v>
+        <v>1133.58</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0.1122</v>
+        <v>0.121</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.1296</v>
+        <v>0.1386</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>46308</v>
@@ -6359,7 +6359,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.1070012270375046</v>
+        <v>0.09829037209548518</v>
       </c>
       <c r="Q72" s="9" t="inlineStr">
         <is>
@@ -6404,13 +6404,13 @@
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>23.77</v>
+        <v>23.84</v>
       </c>
       <c r="E73" s="15" t="n">
-        <v>-0.1054</v>
+        <v>-0.1027</v>
       </c>
       <c r="F73" s="15" t="n">
-        <v>-0.1183</v>
+        <v>-0.1157</v>
       </c>
       <c r="G73" s="16" t="n">
         <v>46247</v>
@@ -6465,13 +6465,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>18.17</v>
+        <v>18.43</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0.1682</v>
+        <v>0.1852</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.1425</v>
+        <v>0.1591</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>46346</v>
@@ -6526,13 +6526,13 @@
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>515.1799999999999</v>
+        <v>518.85</v>
       </c>
       <c r="E75" s="19" t="n">
-        <v>0.017</v>
+        <v>0.0242</v>
       </c>
       <c r="F75" s="19" t="n">
-        <v>0.0554</v>
+        <v>0.0629</v>
       </c>
       <c r="G75" s="16" t="n">
         <v>46241</v>
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>71.05</v>
+        <v>70.95</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0.0383</v>
+        <v>0.0368</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.2071</v>
+        <v>0.2054</v>
       </c>
       <c r="G76" s="6" t="n"/>
       <c r="H76" s="11" t="inlineStr">
@@ -6634,7 +6634,7 @@
         <v>68</v>
       </c>
       <c r="M76" s="23" t="n">
-        <v>-0.04292751583391974</v>
+        <v>-0.04157857646229743</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="8" t="n"/>
@@ -6676,13 +6676,13 @@
         </is>
       </c>
       <c r="D77" s="14" t="n">
-        <v>135.38</v>
+        <v>136.03</v>
       </c>
       <c r="E77" s="19" t="n">
-        <v>0.0969</v>
+        <v>0.1022</v>
       </c>
       <c r="F77" s="19" t="n">
-        <v>0.1736</v>
+        <v>0.1793</v>
       </c>
       <c r="G77" s="16" t="n">
         <v>46310</v>
@@ -6741,13 +6741,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>138.6</v>
+        <v>137.64</v>
       </c>
       <c r="E78" s="23" t="n">
-        <v>-0.0366</v>
+        <v>-0.0432</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.0463</v>
+        <v>0.039</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>46308</v>
@@ -6779,7 +6779,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.01010101010101014</v>
+        <v>0.01714617843650112</v>
       </c>
       <c r="Q78" s="9" t="inlineStr">
         <is>
@@ -6828,13 +6828,13 @@
         </is>
       </c>
       <c r="D79" s="14" t="n">
-        <v>351.09</v>
+        <v>352.54</v>
       </c>
       <c r="E79" s="15" t="n">
-        <v>-0.0153</v>
+        <v>-0.0112</v>
       </c>
       <c r="F79" s="19" t="n">
-        <v>0.0761</v>
+        <v>0.0805</v>
       </c>
       <c r="G79" s="16" t="n">
         <v>46315</v>
@@ -6863,7 +6863,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="19" t="n">
-        <v>0.01968156313196054</v>
+        <v>0.01548760424349004</v>
       </c>
       <c r="N79" s="13" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="19" t="n">
-        <v>0.06525392349540012</v>
+        <v>0.06087252510353429</v>
       </c>
       <c r="Q79" s="20" t="inlineStr">
         <is>
@@ -6919,13 +6919,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>59.85</v>
+        <v>59.66</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0.0189</v>
+        <v>0.0157</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0.1282</v>
+        <v>0.1246</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>46310</v>
@@ -6954,7 +6954,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="23" t="n">
-        <v>-0.04761904761904764</v>
+        <v>-0.04458598726114645</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="8" t="n"/>
@@ -6996,13 +6996,13 @@
         </is>
       </c>
       <c r="D81" s="14" t="n">
-        <v>13.85</v>
-      </c>
-      <c r="E81" s="19" t="n">
-        <v>0.0252</v>
+        <v>13.5</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="F81" s="15" t="n">
-        <v>-0.1116</v>
+        <v>-0.1341</v>
       </c>
       <c r="G81" s="16" t="n">
         <v>46240</v>
@@ -7057,13 +7057,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>392.21</v>
+        <v>394.53</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0.1</v>
+        <v>0.1065</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.1288</v>
+        <v>0.1355</v>
       </c>
       <c r="G82" s="6" t="n">
         <v>46239</v>
@@ -7130,13 +7130,13 @@
         </is>
       </c>
       <c r="D83" s="14" t="n">
-        <v>63.13</v>
+        <v>63.28</v>
       </c>
       <c r="E83" s="15" t="n">
-        <v>-0.0803</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="F83" s="15" t="n">
-        <v>-0.2136</v>
+        <v>-0.2118</v>
       </c>
       <c r="G83" s="16" t="n">
         <v>46239</v>
@@ -7191,13 +7191,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>53.69</v>
+        <v>53.38</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0.045</v>
+        <v>0.0389</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0.4099</v>
+        <v>0.4018</v>
       </c>
       <c r="G84" s="6" t="n">
         <v>46240</v>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="D85" s="14" t="n">
-        <v>1073.31</v>
+        <v>1060.38</v>
       </c>
       <c r="E85" s="19" t="n">
-        <v>0.0171</v>
+        <v>0.0048</v>
       </c>
       <c r="F85" s="19" t="n">
-        <v>0.0333</v>
+        <v>0.0209</v>
       </c>
       <c r="G85" s="16" t="n">
         <v>46308</v>
@@ -7287,7 +7287,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="19" t="n">
-        <v>0.2344988866217589</v>
+        <v>0.2495520473792413</v>
       </c>
       <c r="N85" s="13" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="19" t="n">
-        <v>0.1273537002357195</v>
+        <v>0.1411003602482128</v>
       </c>
       <c r="Q85" s="20" t="inlineStr">
         <is>
@@ -7339,13 +7339,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>128.18</v>
+        <v>128.19</v>
       </c>
       <c r="E86" s="23" t="n">
-        <v>-0.1002</v>
+        <v>-0.1001</v>
       </c>
       <c r="F86" s="23" t="n">
-        <v>-0.0795</v>
+        <v>-0.0794</v>
       </c>
       <c r="G86" s="6" t="n"/>
       <c r="H86" s="11" t="inlineStr">
@@ -7390,13 +7390,13 @@
         </is>
       </c>
       <c r="D87" s="14" t="n">
-        <v>94.55</v>
+        <v>92.8</v>
       </c>
       <c r="E87" s="15" t="n">
-        <v>-0.1957</v>
+        <v>-0.2105</v>
       </c>
       <c r="F87" s="19" t="n">
-        <v>0.1465</v>
+        <v>0.1253</v>
       </c>
       <c r="G87" s="16" t="n"/>
       <c r="H87" s="22" t="inlineStr">
@@ -7441,13 +7441,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>97.62</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="E88" s="23" t="n">
-        <v>-0.0594</v>
+        <v>-0.1062</v>
       </c>
       <c r="F88" s="23" t="n">
-        <v>-0.1303</v>
+        <v>-0.1736</v>
       </c>
       <c r="G88" s="6" t="n"/>
       <c r="H88" s="11" t="inlineStr">
@@ -7492,13 +7492,13 @@
         </is>
       </c>
       <c r="D89" s="14" t="n">
-        <v>148.93</v>
+        <v>149.84</v>
       </c>
       <c r="E89" s="19" t="n">
-        <v>0.1039</v>
+        <v>0.1107</v>
       </c>
       <c r="F89" s="19" t="n">
-        <v>0.0525</v>
+        <v>0.05889999999999999</v>
       </c>
       <c r="G89" s="16" t="n"/>
       <c r="H89" s="22" t="inlineStr">
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>153.49</v>
+        <v>154.35</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0.0486</v>
+        <v>0.0544</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.1797</v>
+        <v>0.1863</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>46252</v>
@@ -7618,13 +7618,13 @@
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>359.94</v>
+        <v>359.24</v>
       </c>
       <c r="E91" s="19" t="n">
-        <v>0.0658</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="F91" s="19" t="n">
-        <v>0.1523</v>
+        <v>0.15</v>
       </c>
       <c r="G91" s="16" t="n">
         <v>46308</v>
@@ -7653,7 +7653,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="15" t="n">
-        <v>-0.455464799688837</v>
+        <v>-0.4544037412314887</v>
       </c>
       <c r="N91" s="13" t="inlineStr"/>
       <c r="O91" s="18" t="n"/>
@@ -7697,13 +7697,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>104.54</v>
+        <v>105.65</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0.08929999999999999</v>
+        <v>0.1009</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.1193</v>
+        <v>0.1312</v>
       </c>
       <c r="G92" s="6" t="n"/>
       <c r="H92" s="11" t="inlineStr">
@@ -7722,7 +7722,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>2.587143677061412</v>
+        <v>2.549455750118315</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>2.520183661756265</v>
+        <v>2.483199242782773</v>
       </c>
       <c r="Q92" s="9" t="inlineStr">
         <is>
@@ -7786,13 +7786,13 @@
         </is>
       </c>
       <c r="D93" s="14" t="n">
-        <v>369.27</v>
+        <v>370.97</v>
       </c>
       <c r="E93" s="19" t="n">
-        <v>0.0635</v>
+        <v>0.0684</v>
       </c>
       <c r="F93" s="19" t="n">
-        <v>0.2063</v>
+        <v>0.2118</v>
       </c>
       <c r="G93" s="16" t="n">
         <v>46317</v>
@@ -7824,7 +7824,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="15" t="n">
-        <v>-0.6885747555988843</v>
+        <v>-0.6900018869450361</v>
       </c>
       <c r="Q93" s="20" t="inlineStr">
         <is>
@@ -7873,13 +7873,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>570.6900000000001</v>
+        <v>570.48</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0701</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.1621</v>
+        <v>0.1617</v>
       </c>
       <c r="G94" s="6" t="n"/>
       <c r="H94" s="11" t="inlineStr">
@@ -7898,7 +7898,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="23" t="n">
-        <v>-0.3586710823739684</v>
+        <v>-0.3584350021034918</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="8" t="n"/>
@@ -7940,13 +7940,13 @@
         </is>
       </c>
       <c r="D95" s="14" t="n">
-        <v>1875.29</v>
+        <v>1878.03</v>
       </c>
       <c r="E95" s="15" t="n">
-        <v>-0.052</v>
+        <v>-0.0506</v>
       </c>
       <c r="F95" s="19" t="n">
-        <v>0.0311</v>
+        <v>0.0326</v>
       </c>
       <c r="G95" s="16" t="n"/>
       <c r="H95" s="22" t="inlineStr">
@@ -8001,13 +8001,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>217.99</v>
+        <v>218.27</v>
       </c>
       <c r="E96" s="23" t="n">
-        <v>-0.0185</v>
+        <v>-0.0172</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.0286</v>
+        <v>0.0299</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>46309</v>
@@ -8036,7 +8036,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>2.064360750493142</v>
+        <v>2.060429742978879</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>1.523051516124593</v>
+        <v>1.519814908141293</v>
       </c>
       <c r="Q96" s="9" t="inlineStr">
         <is>
@@ -8096,13 +8096,13 @@
         </is>
       </c>
       <c r="D97" s="14" t="n">
-        <v>114.05</v>
+        <v>114.85</v>
       </c>
       <c r="E97" s="19" t="n">
-        <v>0.0133</v>
+        <v>0.0204</v>
       </c>
       <c r="F97" s="19" t="n">
-        <v>0.0839</v>
+        <v>0.0915</v>
       </c>
       <c r="G97" s="16" t="n"/>
       <c r="H97" s="22" t="inlineStr">
@@ -8121,7 +8121,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>1.104340201665936</v>
+        <v>1.089682194166304</v>
       </c>
       <c r="N97" s="13" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="19" t="n">
-        <v>1.104340201665936</v>
+        <v>1.089682194166304</v>
       </c>
       <c r="Q97" s="20" t="inlineStr">
         <is>
@@ -8181,13 +8181,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>255.05</v>
+        <v>255.37</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0086</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.1168</v>
+        <v>0.1182</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>46310</v>
@@ -8216,7 +8216,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="23" t="n">
-        <v>-0.5569496177220153</v>
+        <v>-0.5575047969612719</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="23" t="n">
-        <v>-0.5530288178788473</v>
+        <v>-0.5535889102087168</v>
       </c>
       <c r="Q98" s="9" t="inlineStr"/>
       <c r="R98" s="8" t="n"/>
@@ -8266,13 +8266,13 @@
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>22.21</v>
+        <v>21.5</v>
       </c>
       <c r="E99" s="15" t="n">
-        <v>-0.0289</v>
+        <v>-0.0599</v>
       </c>
       <c r="F99" s="15" t="n">
-        <v>-0.09939999999999999</v>
+        <v>-0.1281</v>
       </c>
       <c r="G99" s="16" t="n">
         <v>46239</v>
@@ -8327,13 +8327,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>14.66</v>
+        <v>14.64</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0.0205</v>
+        <v>0.0188</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.207</v>
+        <v>0.2049</v>
       </c>
       <c r="G100" s="6" t="n">
         <v>46323</v>
@@ -8388,13 +8388,13 @@
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>104.63</v>
+        <v>104.76</v>
       </c>
       <c r="E101" s="19" t="n">
-        <v>0.1015</v>
+        <v>0.1029</v>
       </c>
       <c r="F101" s="19" t="n">
-        <v>0.1701</v>
+        <v>0.1716</v>
       </c>
       <c r="G101" s="16" t="n">
         <v>46323</v>
@@ -8423,7 +8423,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="19" t="n">
-        <v>1.7238841632419</v>
+        <v>1.720504009163803</v>
       </c>
       <c r="N101" s="13" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="19" t="n">
-        <v>1.7238841632419</v>
+        <v>1.720504009163803</v>
       </c>
       <c r="Q101" s="20" t="inlineStr">
         <is>
@@ -8475,13 +8475,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>410.31</v>
+        <v>410.03</v>
       </c>
       <c r="E102" s="23" t="n">
-        <v>-0.0825</v>
+        <v>-0.0832</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0.0218</v>
+        <v>0.0211</v>
       </c>
       <c r="G102" s="6" t="n"/>
       <c r="H102" s="11" t="inlineStr">
@@ -8540,13 +8540,13 @@
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>52.88</v>
+        <v>52.85</v>
       </c>
       <c r="E103" s="19" t="n">
-        <v>0.0285</v>
+        <v>0.0278</v>
       </c>
       <c r="F103" s="19" t="n">
-        <v>0.07490000000000001</v>
+        <v>0.0742</v>
       </c>
       <c r="G103" s="16" t="n">
         <v>46311</v>
@@ -8601,13 +8601,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>368.05</v>
+        <v>368.54</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0.0302</v>
+        <v>0.0316</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.1375</v>
+        <v>0.139</v>
       </c>
       <c r="G104" s="6" t="n"/>
       <c r="H104" s="11" t="inlineStr">
@@ -8626,7 +8626,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>0.4264366254584974</v>
+        <v>0.4245400770608346</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>0.4753430240456459</v>
+        <v>0.4733814511314918</v>
       </c>
       <c r="Q104" s="9" t="inlineStr">
         <is>
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>71.83</v>
+        <v>72.08</v>
       </c>
       <c r="E105" s="19" t="n">
-        <v>0.0128</v>
+        <v>0.0164</v>
       </c>
       <c r="F105" s="19" t="n">
-        <v>0.0475</v>
+        <v>0.0512</v>
       </c>
       <c r="G105" s="16" t="n">
         <v>46314</v>
@@ -8717,7 +8717,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="19" t="n">
-        <v>4.735765000696088</v>
+        <v>4.715871254162042</v>
       </c>
       <c r="N105" s="13" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="19" t="n">
-        <v>3.87261589864959</v>
+        <v>3.855715871254162</v>
       </c>
       <c r="Q105" s="20" t="inlineStr">
         <is>
@@ -8773,13 +8773,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>84.53</v>
+        <v>84.2</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0.0711</v>
+        <v>0.0669</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.2404</v>
+        <v>0.2355</v>
       </c>
       <c r="G106" s="6" t="n">
         <v>46239</v>
@@ -8808,7 +8808,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="23" t="n">
-        <v>-0.1955518750739383</v>
+        <v>-0.1923990498812352</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="23" t="n">
-        <v>-0.1955518750739383</v>
+        <v>-0.1923990498812352</v>
       </c>
       <c r="Q106" s="9" t="inlineStr">
         <is>
@@ -8864,13 +8864,13 @@
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>246.93</v>
+        <v>246.2</v>
       </c>
       <c r="E107" s="15" t="n">
-        <v>-0.0307</v>
+        <v>-0.0336</v>
       </c>
       <c r="F107" s="19" t="n">
-        <v>0.0867</v>
+        <v>0.08349999999999999</v>
       </c>
       <c r="G107" s="16" t="n"/>
       <c r="H107" s="22" t="inlineStr">
@@ -8889,7 +8889,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="19" t="n">
-        <v>0.1946705544081318</v>
+        <v>0.19821283509342</v>
       </c>
       <c r="N107" s="13" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="15" t="n">
-        <v>-0.003766249544405324</v>
+        <v>-0.0008123476848090522</v>
       </c>
       <c r="Q107" s="20" t="inlineStr">
         <is>
@@ -8937,13 +8937,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>104.79</v>
+        <v>105.71</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0.0958</v>
+        <v>0.1054</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.1507</v>
+        <v>0.1608</v>
       </c>
       <c r="G108" s="6" t="n">
         <v>46316</v>
@@ -8972,7 +8972,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0.06880427521710081</v>
+        <v>0.05950241225995655</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>0.145147437732608</v>
+        <v>0.1351811559928106</v>
       </c>
       <c r="Q108" s="9" t="inlineStr">
         <is>
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>409.83</v>
+        <v>407.83</v>
       </c>
       <c r="E109" s="19" t="n">
-        <v>0.1184</v>
+        <v>0.113</v>
       </c>
       <c r="F109" s="19" t="n">
-        <v>0.1723</v>
+        <v>0.1666</v>
       </c>
       <c r="G109" s="16" t="n"/>
       <c r="H109" s="22" t="inlineStr">
@@ -9061,7 +9061,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="15" t="n">
-        <v>-0.04838591611155842</v>
+        <v>-0.04371919672412521</v>
       </c>
       <c r="N109" s="13" t="inlineStr">
         <is>
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>169.07</v>
+        <v>170.66</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.09720000000000001</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.1185</v>
+        <v>0.129</v>
       </c>
       <c r="G110" s="6" t="n">
         <v>46240</v>
@@ -9144,7 +9144,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="23" t="n">
-        <v>-0.0477317087596853</v>
+        <v>-0.05660377358490564</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>0.0646477790264388</v>
+        <v>0.05472870033985704</v>
       </c>
       <c r="Q110" s="9" t="inlineStr">
         <is>
@@ -9196,13 +9196,13 @@
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>47.69</v>
+        <v>47.74</v>
       </c>
       <c r="E111" s="19" t="n">
-        <v>0.0694</v>
+        <v>0.0704</v>
       </c>
       <c r="F111" s="15" t="n">
-        <v>-0.0176</v>
+        <v>-0.0167</v>
       </c>
       <c r="G111" s="16" t="n"/>
       <c r="H111" s="22" t="inlineStr">
@@ -9221,7 +9221,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="19" t="n">
-        <v>0.1532816104005033</v>
+        <v>0.152073732718894</v>
       </c>
       <c r="N111" s="13" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="19" t="n">
-        <v>0.3629691759278675</v>
+        <v>0.3615416841223292</v>
       </c>
       <c r="Q111" s="20" t="inlineStr">
         <is>
@@ -9273,13 +9273,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>317.26</v>
+        <v>317.22</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0.06269999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.1535</v>
+        <v>0.1534</v>
       </c>
       <c r="G112" s="6" t="n">
         <v>46239</v>
@@ -9308,7 +9308,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>0.04330832755468704</v>
+        <v>0.04343988399218199</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="5" t="n">
-        <v>0.04015633864968798</v>
+        <v>0.04028749763571014</v>
       </c>
       <c r="Q112" s="9" t="inlineStr">
         <is>
@@ -9368,13 +9368,13 @@
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>98.94</v>
+        <v>99.12</v>
       </c>
       <c r="E113" s="15" t="n">
-        <v>-0.0307</v>
+        <v>-0.029</v>
       </c>
       <c r="F113" s="19" t="n">
-        <v>0.0314</v>
+        <v>0.0333</v>
       </c>
       <c r="G113" s="16" t="n">
         <v>46239</v>
@@ -9403,7 +9403,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="19" t="n">
-        <v>0.2431776834445118</v>
+        <v>0.2409200968523002</v>
       </c>
       <c r="N113" s="13" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="19" t="n">
-        <v>0.3139276329088337</v>
+        <v>0.3115415657788538</v>
       </c>
       <c r="Q113" s="20" t="inlineStr">
         <is>
@@ -9455,13 +9455,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>200.76</v>
+        <v>199.66</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0.0369</v>
+        <v>0.0312</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.08929999999999999</v>
+        <v>0.0833</v>
       </c>
       <c r="G114" s="6" t="n">
         <v>46315</v>
@@ -9490,7 +9490,7 @@
         <v>212</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>0.05598724845586775</v>
+        <v>0.06180506861664832</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="5" t="n">
-        <v>0.0211197449691174</v>
+        <v>0.0267454672944005</v>
       </c>
       <c r="Q114" s="9" t="inlineStr">
         <is>
@@ -9546,13 +9546,13 @@
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>83.19</v>
+        <v>82.66</v>
       </c>
       <c r="E115" s="19" t="n">
-        <v>0.1494</v>
+        <v>0.142</v>
       </c>
       <c r="F115" s="19" t="n">
-        <v>0.1418</v>
+        <v>0.1345</v>
       </c>
       <c r="G115" s="16" t="n"/>
       <c r="H115" s="22" t="inlineStr">
@@ -9571,7 +9571,7 @@
         <v>85</v>
       </c>
       <c r="M115" s="19" t="n">
-        <v>0.02175742276715954</v>
+        <v>0.02830873457536903</v>
       </c>
       <c r="N115" s="13" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="19" t="n">
-        <v>0.08186080057699245</v>
+        <v>0.08879748366803779</v>
       </c>
       <c r="Q115" s="20" t="inlineStr">
         <is>
@@ -9623,13 +9623,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>130.57</v>
+        <v>131.76</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0166</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0201</v>
       </c>
       <c r="G116" s="6" t="n"/>
       <c r="H116" s="11" t="inlineStr">
@@ -9648,7 +9648,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>0.2636899747262006</v>
+        <v>0.2522768670309655</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="8" t="n"/>
@@ -9696,13 +9696,13 @@
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>585.1799999999999</v>
+        <v>584.78</v>
       </c>
       <c r="E117" s="19" t="n">
-        <v>0.0358</v>
+        <v>0.035</v>
       </c>
       <c r="F117" s="19" t="n">
-        <v>0.0409</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="G117" s="16" t="n"/>
       <c r="H117" s="22" t="inlineStr">
@@ -9757,13 +9757,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>373.01</v>
+        <v>375.2</v>
       </c>
       <c r="E118" s="23" t="n">
-        <v>-0.1382</v>
+        <v>-0.1331</v>
       </c>
       <c r="F118" s="23" t="n">
-        <v>-0.1162</v>
+        <v>-0.111</v>
       </c>
       <c r="G118" s="6" t="n">
         <v>46315</v>
@@ -9792,7 +9792,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>0.3055950242620842</v>
+        <v>0.2979744136460555</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -9802,8 +9802,8 @@
       <c r="O118" s="8" t="n">
         <v>375</v>
       </c>
-      <c r="P118" s="5" t="n">
-        <v>0.00533497761454119</v>
+      <c r="P118" s="23" t="n">
+        <v>-0.0005330490405116968</v>
       </c>
       <c r="Q118" s="9" t="inlineStr">
         <is>
@@ -9848,13 +9848,13 @@
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>258.3</v>
+        <v>257.59</v>
       </c>
       <c r="E119" s="15" t="n">
-        <v>-0.004</v>
+        <v>-0.0067</v>
       </c>
       <c r="F119" s="19" t="n">
-        <v>0.1097</v>
+        <v>0.1066</v>
       </c>
       <c r="G119" s="16" t="n">
         <v>46315</v>
@@ -9883,7 +9883,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="19" t="n">
-        <v>0.05303910181958957</v>
+        <v>0.05594161264024235</v>
       </c>
       <c r="N119" s="13" t="inlineStr"/>
       <c r="O119" s="18" t="n"/>
@@ -9935,13 +9935,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1164.11</v>
+        <v>1169.86</v>
       </c>
       <c r="E120" s="23" t="n">
-        <v>-0.03</v>
+        <v>-0.0252</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>0.0289</v>
+        <v>0.034</v>
       </c>
       <c r="G120" s="6" t="n">
         <v>46239</v>
@@ -9970,7 +9970,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>0.09955244779273446</v>
+        <v>0.09414801771152113</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -10030,13 +10030,13 @@
         </is>
       </c>
       <c r="D121" s="14" t="n">
-        <v>85.59</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="E121" s="19" t="n">
-        <v>0.0305</v>
+        <v>0.0353</v>
       </c>
       <c r="F121" s="19" t="n">
-        <v>0.048</v>
+        <v>0.0529</v>
       </c>
       <c r="G121" s="16" t="n">
         <v>46266</v>
@@ -10065,7 +10065,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="19" t="n">
-        <v>0.1917280056081317</v>
+        <v>0.1861844400511688</v>
       </c>
       <c r="N121" s="13" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="19" t="n">
-        <v>0.2267788293024885</v>
+        <v>0.2210722176997326</v>
       </c>
       <c r="Q121" s="20" t="inlineStr">
         <is>
@@ -10117,13 +10117,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>129.32</v>
+        <v>128.33</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0.02</v>
+        <v>0.0122</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0.0706</v>
+        <v>0.0624</v>
       </c>
       <c r="G122" s="6" t="n"/>
       <c r="H122" s="11" t="inlineStr">
@@ -10142,7 +10142,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>0.1599133931333128</v>
+        <v>0.1688615288708797</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="8" t="n"/>
@@ -10186,13 +10186,13 @@
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>154.65</v>
+        <v>154.44</v>
       </c>
       <c r="E123" s="15" t="n">
-        <v>-0.0054</v>
+        <v>-0.0068</v>
       </c>
       <c r="F123" s="19" t="n">
-        <v>0.0368</v>
+        <v>0.0354</v>
       </c>
       <c r="G123" s="16" t="n">
         <v>46322</v>
@@ -10265,13 +10265,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>25.5</v>
+        <v>25.81</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.075</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="F124" s="23" t="n">
-        <v>-0.0207</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="G124" s="6" t="n"/>
       <c r="H124" s="11" t="inlineStr">
@@ -10290,7 +10290,7 @@
         <v>28</v>
       </c>
       <c r="M124" s="5" t="n">
-        <v>0.09803921568627451</v>
+        <v>0.08485083301046112</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="8" t="n"/>
@@ -10334,13 +10334,13 @@
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>334.27</v>
+        <v>337.03</v>
       </c>
       <c r="E125" s="19" t="n">
-        <v>0.0294</v>
+        <v>0.0379</v>
       </c>
       <c r="F125" s="19" t="n">
-        <v>0.09359999999999999</v>
+        <v>0.1026</v>
       </c>
       <c r="G125" s="16" t="n"/>
       <c r="H125" s="22" t="inlineStr">
@@ -10359,7 +10359,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="19" t="n">
-        <v>0.2504861339635625</v>
+        <v>0.240245675459158</v>
       </c>
       <c r="N125" s="13" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="19" t="n">
-        <v>0.04705776767283938</v>
+        <v>0.03848322107824238</v>
       </c>
       <c r="Q125" s="20" t="inlineStr">
         <is>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>576.74</v>
+        <v>577.83</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0.1143</v>
+        <v>0.1164</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>0.2198</v>
+        <v>0.2221</v>
       </c>
       <c r="G126" s="6" t="n">
         <v>46323</v>
@@ -10450,7 +10450,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>0.06633838471408258</v>
+        <v>0.06432687814755197</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="23" t="n">
-        <v>-0.01168637514304541</v>
+        <v>-0.0135506983022689</v>
       </c>
       <c r="Q126" s="9" t="inlineStr">
         <is>
@@ -10510,13 +10510,13 @@
         </is>
       </c>
       <c r="D127" s="14" t="n">
-        <v>414.65</v>
+        <v>412.75</v>
       </c>
       <c r="E127" s="15" t="n">
-        <v>-0.008</v>
+        <v>-0.0125</v>
       </c>
       <c r="F127" s="19" t="n">
-        <v>0.038</v>
+        <v>0.0332</v>
       </c>
       <c r="G127" s="16" t="n">
         <v>46322</v>
@@ -10545,7 +10545,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="19" t="n">
-        <v>0.2685397323043531</v>
+        <v>0.2743791641429437</v>
       </c>
       <c r="N127" s="13" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="19" t="n">
-        <v>0.1576027975400941</v>
+        <v>0.162931556632344</v>
       </c>
       <c r="Q127" s="20" t="inlineStr">
         <is>
@@ -10601,13 +10601,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>73.81999999999999</v>
+        <v>74.39</v>
       </c>
       <c r="E128" s="23" t="n">
-        <v>-0.0212</v>
+        <v>-0.0137</v>
       </c>
       <c r="F128" s="23" t="n">
-        <v>-0.0707</v>
+        <v>-0.0636</v>
       </c>
       <c r="G128" s="6" t="n">
         <v>46240</v>
@@ -10680,13 +10680,13 @@
         </is>
       </c>
       <c r="D129" s="14" t="n">
-        <v>268.38</v>
+        <v>270.09</v>
       </c>
       <c r="E129" s="19" t="n">
-        <v>0.1206</v>
+        <v>0.1278</v>
       </c>
       <c r="F129" s="19" t="n">
-        <v>0.1571</v>
+        <v>0.1644</v>
       </c>
       <c r="G129" s="16" t="n"/>
       <c r="H129" s="22" t="inlineStr">
@@ -10705,7 +10705,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="15" t="n">
-        <v>-0.07593710410611818</v>
+        <v>-0.08178755229738227</v>
       </c>
       <c r="N129" s="13" t="inlineStr"/>
       <c r="O129" s="18" t="n"/>
@@ -10761,13 +10761,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>104.68</v>
+        <v>103.83</v>
       </c>
       <c r="E130" s="23" t="n">
-        <v>-0.1153</v>
+        <v>-0.1225</v>
       </c>
       <c r="F130" s="23" t="n">
-        <v>-0.1008</v>
+        <v>-0.1081</v>
       </c>
       <c r="G130" s="6" t="n"/>
       <c r="H130" s="11" t="inlineStr">
@@ -10812,13 +10812,13 @@
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>255.49</v>
+        <v>254.76</v>
       </c>
       <c r="E131" s="19" t="n">
-        <v>0.0774</v>
+        <v>0.07429999999999999</v>
       </c>
       <c r="F131" s="19" t="n">
-        <v>0.1277</v>
+        <v>0.1245</v>
       </c>
       <c r="G131" s="16" t="n"/>
       <c r="H131" s="22" t="inlineStr">
@@ -10863,13 +10863,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>238.55</v>
+        <v>240.19</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0.0171</v>
+        <v>0.0241</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>0.1072</v>
+        <v>0.1148</v>
       </c>
       <c r="G132" s="6" t="n"/>
       <c r="H132" s="11" t="inlineStr">
@@ -10888,7 +10888,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>0.04799832320268282</v>
+        <v>0.04084266622257381</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="8" t="n"/>
@@ -10932,13 +10932,13 @@
         </is>
       </c>
       <c r="D133" s="14" t="n">
-        <v>161.66</v>
+        <v>163.41</v>
       </c>
       <c r="E133" s="19" t="n">
-        <v>0.1167</v>
+        <v>0.1288</v>
       </c>
       <c r="F133" s="19" t="n">
-        <v>0.0682</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="G133" s="16" t="n"/>
       <c r="H133" s="22" t="inlineStr">
@@ -10993,13 +10993,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>890.91</v>
+        <v>871.08</v>
       </c>
       <c r="E134" s="23" t="n">
-        <v>-0.0815</v>
+        <v>-0.1019</v>
       </c>
       <c r="F134" s="23" t="n">
-        <v>-0.0148</v>
+        <v>-0.0367</v>
       </c>
       <c r="G134" s="6" t="n"/>
       <c r="H134" s="11" t="inlineStr">
@@ -11018,7 +11018,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>0.296427248543624</v>
+        <v>0.3259402121504339</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="5" t="n">
-        <v>0.238059961163305</v>
+        <v>0.2662442025990723</v>
       </c>
       <c r="Q134" s="9" t="inlineStr">
         <is>
@@ -11070,13 +11070,13 @@
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>657.89</v>
+        <v>650.25</v>
       </c>
       <c r="E135" s="15" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="F135" s="19" t="n">
-        <v>0.0102</v>
+        <v>-0.0413</v>
+      </c>
+      <c r="F135" s="15" t="n">
+        <v>-0.0015</v>
       </c>
       <c r="G135" s="16" t="n"/>
       <c r="H135" s="22" t="inlineStr">
@@ -11095,7 +11095,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="19" t="n">
-        <v>0.3284895651248689</v>
+        <v>0.3440984236831988</v>
       </c>
       <c r="N135" s="13" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="19" t="n">
-        <v>0.2844092477465838</v>
+        <v>0.2995001922337562</v>
       </c>
       <c r="Q135" s="20" t="inlineStr">
         <is>
@@ -11155,13 +11155,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>200.38</v>
+        <v>201.4</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0.1242</v>
+        <v>0.1299</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>0.1142</v>
+        <v>0.1198</v>
       </c>
       <c r="G136" s="6" t="n">
         <v>46288</v>
@@ -11190,7 +11190,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>0.2476295039425093</v>
+        <v>0.2413108242303872</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="8" t="n"/>
@@ -11234,13 +11234,13 @@
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>615.15</v>
+        <v>612</v>
       </c>
       <c r="E137" s="15" t="n">
-        <v>-0.0316</v>
+        <v>-0.0366</v>
       </c>
       <c r="F137" s="19" t="n">
-        <v>0.05429999999999999</v>
+        <v>0.049</v>
       </c>
       <c r="G137" s="16" t="n">
         <v>46254</v>
@@ -11269,7 +11269,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="19" t="n">
-        <v>0.21921482565228</v>
+        <v>0.2254901960784314</v>
       </c>
       <c r="N137" s="13" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="19" t="n">
-        <v>0.04249370072340078</v>
+        <v>0.04785947712418295</v>
       </c>
       <c r="Q137" s="20" t="inlineStr">
         <is>
@@ -11321,13 +11321,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>164.08</v>
+        <v>162.47</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0.1591</v>
+        <v>0.1477</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.188</v>
+        <v>0.1763</v>
       </c>
       <c r="G138" s="6" t="n"/>
       <c r="H138" s="11" t="inlineStr">
@@ -11353,7 +11353,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="5" t="n">
-        <v>0.1274987810823987</v>
+        <v>0.1386717547854989</v>
       </c>
       <c r="Q138" s="9" t="inlineStr">
         <is>
@@ -11392,13 +11392,13 @@
         </is>
       </c>
       <c r="D139" s="14" t="n">
-        <v>448.54</v>
+        <v>447.28</v>
       </c>
       <c r="E139" s="19" t="n">
-        <v>0.0849</v>
+        <v>0.0819</v>
       </c>
       <c r="F139" s="19" t="n">
-        <v>0.1328</v>
+        <v>0.1297</v>
       </c>
       <c r="G139" s="16" t="n"/>
       <c r="H139" s="22" t="inlineStr">
@@ -11424,7 +11424,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="19" t="n">
-        <v>0.009943371828599411</v>
+        <v>0.01278840994455381</v>
       </c>
       <c r="Q139" s="20" t="inlineStr">
         <is>
@@ -11465,13 +11465,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>50.15</v>
+        <v>49.99</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0.0382</v>
+        <v>0.0348</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="G140" s="6" t="n">
         <v>46309</v>
@@ -11544,13 +11544,13 @@
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>310.85</v>
+        <v>310.72</v>
       </c>
       <c r="E141" s="19" t="n">
-        <v>0.003</v>
+        <v>0.0025</v>
       </c>
       <c r="F141" s="15" t="n">
-        <v>-0.0609</v>
+        <v>-0.0613</v>
       </c>
       <c r="G141" s="16" t="n">
         <v>46282</v>
@@ -11579,7 +11579,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="19" t="n">
-        <v>0.3672189158758242</v>
+        <v>0.3677909371781667</v>
       </c>
       <c r="N141" s="13" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="19" t="n">
-        <v>0.03908637606562643</v>
+        <v>0.03952111225540671</v>
       </c>
       <c r="Q141" s="20" t="inlineStr">
         <is>
@@ -11631,13 +11631,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>253.7</v>
+        <v>255.25</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0.1082</v>
+        <v>0.115</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>0.1051</v>
+        <v>0.1118</v>
       </c>
       <c r="G142" s="6" t="n">
         <v>46244</v>
@@ -11666,7 +11666,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="5" t="n">
-        <v>0.1233740638549468</v>
+        <v>0.1165523996082272</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="8" t="n"/>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>1770.31</v>
+        <v>1737</v>
       </c>
       <c r="E143" s="15" t="n">
-        <v>-0.0127</v>
+        <v>-0.0312</v>
       </c>
       <c r="F143" s="15" t="n">
-        <v>-0.0399</v>
+        <v>-0.058</v>
       </c>
       <c r="G143" s="16" t="n">
         <v>46317</v>
@@ -11775,13 +11775,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>50.56</v>
+        <v>50.42</v>
       </c>
       <c r="E144" s="23" t="n">
-        <v>-0.0175</v>
+        <v>-0.0202</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>0.06309999999999999</v>
+        <v>0.0601</v>
       </c>
       <c r="G144" s="6" t="n">
         <v>46241</v>
@@ -11836,13 +11836,13 @@
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>383.07</v>
+        <v>384.08</v>
       </c>
       <c r="E145" s="19" t="n">
-        <v>0.0164</v>
+        <v>0.0191</v>
       </c>
       <c r="F145" s="19" t="n">
-        <v>0.1057</v>
+        <v>0.1086</v>
       </c>
       <c r="G145" s="16" t="n"/>
       <c r="H145" s="22" t="inlineStr">
@@ -11861,7 +11861,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="19" t="n">
-        <v>0.0441955778317279</v>
+        <v>0.04144969797958763</v>
       </c>
       <c r="N145" s="13" t="inlineStr"/>
       <c r="O145" s="18" t="n"/>
@@ -11913,10 +11913,10 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>381.24</v>
+        <v>381.22</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0.0068</v>
+        <v>0.0067</v>
       </c>
       <c r="F146" s="5" t="n">
         <v>0.1623</v>
@@ -11948,7 +11948,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="5" t="n">
-        <v>0.02297765187283599</v>
+        <v>0.02303132049735054</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="8" t="n"/>
@@ -12000,13 +12000,13 @@
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>1030.58</v>
+        <v>1017.96</v>
       </c>
       <c r="E147" s="15" t="n">
-        <v>-0.1054</v>
+        <v>-0.1164</v>
       </c>
       <c r="F147" s="19" t="n">
-        <v>0.1039</v>
+        <v>0.09029999999999999</v>
       </c>
       <c r="G147" s="16" t="n">
         <v>46316</v>
@@ -12035,7 +12035,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="19" t="n">
-        <v>0.2216421820722313</v>
+        <v>0.2367873000903768</v>
       </c>
       <c r="N147" s="13" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="19" t="n">
-        <v>0.3099419744221701</v>
+        <v>0.3261817753153365</v>
       </c>
       <c r="Q147" s="20" t="inlineStr">
         <is>
@@ -12091,13 +12091,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1290.69</v>
+        <v>1285.07</v>
       </c>
       <c r="E148" s="23" t="n">
-        <v>-0.058</v>
+        <v>-0.0621</v>
       </c>
       <c r="F148" s="23" t="n">
-        <v>-0.0072</v>
+        <v>-0.0115</v>
       </c>
       <c r="G148" s="6" t="n"/>
       <c r="H148" s="11" t="inlineStr">
@@ -12156,13 +12156,13 @@
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>247.93</v>
+        <v>248.12</v>
       </c>
       <c r="E149" s="19" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0733</v>
       </c>
       <c r="F149" s="19" t="n">
-        <v>0.1048</v>
+        <v>0.1057</v>
       </c>
       <c r="G149" s="16" t="n">
         <v>46317</v>
@@ -12217,13 +12217,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>511.57</v>
+        <v>513.58</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>0.0322</v>
+        <v>0.0363</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0771</v>
       </c>
       <c r="G150" s="6" t="n"/>
       <c r="H150" s="11" t="inlineStr">
@@ -12274,13 +12274,13 @@
         </is>
       </c>
       <c r="D151" s="14" t="n">
-        <v>295.43</v>
+        <v>297.32</v>
       </c>
       <c r="E151" s="19" t="n">
-        <v>0.07719999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F151" s="19" t="n">
-        <v>0.169</v>
+        <v>0.1765</v>
       </c>
       <c r="G151" s="16" t="n"/>
       <c r="H151" s="22" t="inlineStr">
@@ -12302,7 +12302,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="15" t="n">
-        <v>-0.07930812713671599</v>
+        <v>-0.08516076954123501</v>
       </c>
       <c r="Q151" s="20" t="inlineStr">
         <is>
@@ -12355,13 +12355,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>285.3</v>
+        <v>286.12</v>
       </c>
       <c r="E152" s="23" t="n">
-        <v>-0.053</v>
+        <v>-0.0503</v>
       </c>
       <c r="F152" s="23" t="n">
-        <v>-0.0732</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="G152" s="6" t="n"/>
       <c r="H152" s="11" t="inlineStr">
@@ -12416,13 +12416,13 @@
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>450.68</v>
+        <v>446.87</v>
       </c>
       <c r="E153" s="15" t="n">
-        <v>-0.2065</v>
+        <v>-0.2133</v>
       </c>
       <c r="F153" s="15" t="n">
-        <v>-0.1136</v>
+        <v>-0.1211</v>
       </c>
       <c r="G153" s="16" t="n"/>
       <c r="H153" s="22" t="inlineStr">
@@ -12467,13 +12467,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>582.22</v>
+        <v>577.6</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0.08220000000000001</v>
+        <v>0.0736</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0.1116</v>
+        <v>0.1028</v>
       </c>
       <c r="G154" s="6" t="n">
         <v>46315</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>214.27</v>
+        <v>215.45</v>
       </c>
       <c r="E155" s="15" t="n">
-        <v>-0.01</v>
+        <v>-0.0046</v>
       </c>
       <c r="F155" s="15" t="n">
-        <v>-0.1167</v>
+        <v>-0.1118</v>
       </c>
       <c r="G155" s="16" t="n"/>
       <c r="H155" s="22" t="inlineStr">
@@ -12559,7 +12559,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="19" t="n">
-        <v>1.68353012554254</v>
+        <v>1.668832675794848</v>
       </c>
       <c r="N155" s="13" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="19" t="n">
-        <v>0.106081112614925</v>
+        <v>0.1000232072406591</v>
       </c>
       <c r="Q155" s="20" t="inlineStr">
         <is>
@@ -12619,13 +12619,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>116.92</v>
+        <v>118.27</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0.1094</v>
+        <v>0.1222</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.163</v>
+        <v>0.1765</v>
       </c>
       <c r="G156" s="6" t="n">
         <v>46294</v>
@@ -12654,7 +12654,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="5" t="n">
-        <v>1.138214163530619</v>
+        <v>1.113807389870635</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="8" t="n"/>
@@ -12698,13 +12698,13 @@
         </is>
       </c>
       <c r="D157" s="14" t="n">
-        <v>133.84</v>
+        <v>133.34</v>
       </c>
       <c r="E157" s="19" t="n">
-        <v>0.063</v>
+        <v>0.059</v>
       </c>
       <c r="F157" s="19" t="n">
-        <v>0.1471</v>
+        <v>0.1428</v>
       </c>
       <c r="G157" s="16" t="n"/>
       <c r="H157" s="22" t="inlineStr">
@@ -12723,7 +12723,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="15" t="n">
-        <v>-0.2901972504482965</v>
+        <v>-0.2875356232188391</v>
       </c>
       <c r="N157" s="13" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="19" t="n">
-        <v>0.0385534967124925</v>
+        <v>0.04244787760611967</v>
       </c>
       <c r="Q157" s="20" t="inlineStr">
         <is>
@@ -12779,13 +12779,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>1002.65</v>
+        <v>996.9</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>0.0322</v>
+        <v>0.0263</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>0.1364</v>
+        <v>0.1298</v>
       </c>
       <c r="G158" s="6" t="n">
         <v>46240</v>
@@ -12814,7 +12814,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="23" t="n">
-        <v>-0.875330374507555</v>
+        <v>-0.874611295014545</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="5" t="n">
-        <v>0.06118785219169204</v>
+        <v>0.06730865683619222</v>
       </c>
       <c r="Q158" s="9" t="inlineStr">
         <is>
@@ -12870,13 +12870,13 @@
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>568.71</v>
+        <v>572.17</v>
       </c>
       <c r="E159" s="15" t="n">
-        <v>-0.06709999999999999</v>
+        <v>-0.0614</v>
       </c>
       <c r="F159" s="15" t="n">
-        <v>-0.0362</v>
+        <v>-0.0304</v>
       </c>
       <c r="G159" s="16" t="n"/>
       <c r="H159" s="22" t="inlineStr">
@@ -12941,13 +12941,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>453.14</v>
+        <v>450.05</v>
       </c>
       <c r="E160" s="23" t="n">
-        <v>-0.0616</v>
+        <v>-0.068</v>
       </c>
       <c r="F160" s="5" t="n">
-        <v>0.0144</v>
+        <v>0.0075</v>
       </c>
       <c r="G160" s="6" t="n"/>
       <c r="H160" s="11" t="inlineStr">
@@ -12992,13 +12992,13 @@
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>37.46</v>
+        <v>37.57</v>
       </c>
       <c r="E161" s="15" t="n">
-        <v>-0.1233</v>
+        <v>-0.1208</v>
       </c>
       <c r="F161" s="15" t="n">
-        <v>-0.2047</v>
+        <v>-0.2023</v>
       </c>
       <c r="G161" s="16" t="n">
         <v>46323</v>
@@ -13067,13 +13067,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>220.68</v>
+        <v>222.31</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>0.0959</v>
+        <v>0.104</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>0.2193</v>
+        <v>0.2283</v>
       </c>
       <c r="G162" s="6" t="n">
         <v>46322</v>
@@ -13146,13 +13146,13 @@
         </is>
       </c>
       <c r="D163" s="14" t="n">
-        <v>47.15</v>
+        <v>46.52</v>
       </c>
       <c r="E163" s="19" t="n">
-        <v>0.0605</v>
+        <v>0.0463</v>
       </c>
       <c r="F163" s="19" t="n">
-        <v>0.0711</v>
+        <v>0.0568</v>
       </c>
       <c r="G163" s="16" t="n">
         <v>46239</v>
@@ -13207,13 +13207,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>482.93</v>
+        <v>483.58</v>
       </c>
       <c r="E164" s="23" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0075</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>0.0571</v>
+        <v>0.0585</v>
       </c>
       <c r="G164" s="6" t="n"/>
       <c r="H164" s="11" t="inlineStr">
@@ -13235,7 +13235,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="5" t="n">
-        <v>0.1595883461371213</v>
+        <v>0.158029695190041</v>
       </c>
       <c r="Q164" s="9" t="inlineStr">
         <is>
@@ -13288,13 +13288,13 @@
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>295.93</v>
+        <v>295.54</v>
       </c>
       <c r="E165" s="19" t="n">
-        <v>0.0472</v>
+        <v>0.0458</v>
       </c>
       <c r="F165" s="19" t="n">
-        <v>0.0867</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="G165" s="16" t="n">
         <v>46317</v>
@@ -13326,7 +13326,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="15" t="n">
-        <v>-0.006521812590815418</v>
+        <v>-0.00521080056845104</v>
       </c>
       <c r="Q165" s="20" t="inlineStr">
         <is>
@@ -13371,13 +13371,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>280.13</v>
+        <v>277.94</v>
       </c>
       <c r="E166" s="23" t="n">
-        <v>-0.1204</v>
+        <v>-0.1273</v>
       </c>
       <c r="F166" s="23" t="n">
-        <v>-0.0678</v>
+        <v>-0.0751</v>
       </c>
       <c r="G166" s="6" t="n"/>
       <c r="H166" s="11" t="inlineStr">
@@ -13399,7 +13399,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="5" t="n">
-        <v>0.5171527505086925</v>
+        <v>0.5291070015111176</v>
       </c>
       <c r="Q166" s="9" t="inlineStr">
         <is>
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>223.59</v>
+        <v>224.31</v>
       </c>
       <c r="E167" s="15" t="n">
-        <v>-0.0236</v>
+        <v>-0.0204</v>
       </c>
       <c r="F167" s="19" t="n">
-        <v>0.0145</v>
+        <v>0.0177</v>
       </c>
       <c r="G167" s="16" t="n"/>
       <c r="H167" s="22" t="inlineStr">
@@ -13465,7 +13465,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="19" t="n">
-        <v>0.1986224786439465</v>
+        <v>0.194775088047791</v>
       </c>
       <c r="N167" s="13" t="inlineStr"/>
       <c r="O167" s="18" t="n"/>
@@ -13513,13 +13513,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>333.92</v>
+        <v>333.12</v>
       </c>
       <c r="E168" s="23" t="n">
-        <v>-0.1632</v>
+        <v>-0.1652</v>
       </c>
       <c r="F168" s="23" t="n">
-        <v>-0.1009</v>
+        <v>-0.103</v>
       </c>
       <c r="G168" s="6" t="n"/>
       <c r="H168" s="11" t="inlineStr">
@@ -13578,13 +13578,13 @@
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>375.79</v>
+        <v>373.28</v>
       </c>
       <c r="E169" s="15" t="n">
-        <v>-0.1126</v>
+        <v>-0.1185</v>
       </c>
       <c r="F169" s="19" t="n">
-        <v>0.0505</v>
+        <v>0.0434</v>
       </c>
       <c r="G169" s="16" t="n"/>
       <c r="H169" s="22" t="inlineStr">
@@ -13647,13 +13647,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>121.68</v>
+        <v>122.25</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>0.019</v>
+        <v>0.0237</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>0.1068</v>
+        <v>0.112</v>
       </c>
       <c r="G170" s="6" t="n"/>
       <c r="H170" s="11" t="inlineStr">
@@ -13716,13 +13716,13 @@
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>133.51</v>
+        <v>128.56</v>
       </c>
       <c r="E171" s="19" t="n">
-        <v>0.0823</v>
+        <v>0.04219999999999999</v>
       </c>
       <c r="F171" s="15" t="n">
-        <v>-0.2457</v>
+        <v>-0.2737</v>
       </c>
       <c r="G171" s="16" t="n">
         <v>46240</v>
@@ -13777,13 +13777,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>308.89</v>
+        <v>311</v>
       </c>
       <c r="E172" s="23" t="n">
-        <v>-0.0121</v>
+        <v>-0.0053</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0119</v>
       </c>
       <c r="G172" s="6" t="n"/>
       <c r="H172" s="11" t="inlineStr">
@@ -13801,8 +13801,8 @@
       <c r="L172" s="8" t="n">
         <v>310</v>
       </c>
-      <c r="M172" s="5" t="n">
-        <v>0.003593512253553089</v>
+      <c r="M172" s="23" t="n">
+        <v>-0.003215434083601286</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="5" t="n">
-        <v>0.1816504257178932</v>
+        <v>0.1736334405144695</v>
       </c>
       <c r="Q172" s="9" t="inlineStr">
         <is>
@@ -13870,13 +13870,13 @@
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>136.43</v>
+        <v>136.67</v>
       </c>
       <c r="E173" s="15" t="n">
-        <v>-0.0253</v>
+        <v>-0.0236</v>
       </c>
       <c r="F173" s="15" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.0713</v>
       </c>
       <c r="G173" s="16" t="n">
         <v>46240</v>
@@ -13931,13 +13931,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>169.07</v>
+        <v>170.73</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>0.2344</v>
+        <v>0.2466</v>
       </c>
       <c r="F174" s="23" t="n">
-        <v>-0.0515</v>
+        <v>-0.04219999999999999</v>
       </c>
       <c r="G174" s="6" t="n">
         <v>46289</v>
@@ -13992,13 +13992,13 @@
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>256.87</v>
+        <v>259.32</v>
       </c>
       <c r="E175" s="19" t="n">
-        <v>0.1779</v>
+        <v>0.1892</v>
       </c>
       <c r="F175" s="19" t="n">
-        <v>0.0216</v>
+        <v>0.0313</v>
       </c>
       <c r="G175" s="16" t="n">
         <v>46275</v>
@@ -14053,13 +14053,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>377.05</v>
+        <v>377.69</v>
       </c>
       <c r="E176" s="23" t="n">
-        <v>-0.0303</v>
+        <v>-0.0287</v>
       </c>
       <c r="F176" s="23" t="n">
-        <v>-0.06059999999999999</v>
+        <v>-0.059</v>
       </c>
       <c r="G176" s="6" t="n">
         <v>46253</v>
@@ -14088,7 +14088,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="5" t="n">
-        <v>0.3658665959421827</v>
+        <v>0.3635521194630517</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="5" t="n">
-        <v>0.2571277018963002</v>
+        <v>0.2549974847096825</v>
       </c>
       <c r="Q176" s="9" t="inlineStr">
         <is>
@@ -14148,13 +14148,13 @@
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>236.8</v>
+        <v>240.03</v>
       </c>
       <c r="E177" s="19" t="n">
-        <v>0.141</v>
+        <v>0.1565</v>
       </c>
       <c r="F177" s="19" t="n">
-        <v>0.0298</v>
+        <v>0.0438</v>
       </c>
       <c r="G177" s="16" t="n">
         <v>46261</v>
@@ -14209,13 +14209,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>337.41</v>
+        <v>329.23</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.0592</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>0.1445</v>
+        <v>0.1168</v>
       </c>
       <c r="G178" s="6" t="n"/>
       <c r="H178" s="11" t="inlineStr">
@@ -14260,13 +14260,13 @@
         </is>
       </c>
       <c r="D179" s="14" t="n">
-        <v>329.98</v>
+        <v>318.43</v>
       </c>
       <c r="E179" s="15" t="n">
-        <v>-0.2375</v>
+        <v>-0.2642</v>
       </c>
       <c r="F179" s="19" t="n">
-        <v>0.0407</v>
+        <v>0.0043</v>
       </c>
       <c r="G179" s="16" t="n"/>
       <c r="H179" s="22" t="inlineStr">
@@ -14311,13 +14311,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>42.06</v>
+        <v>41.8</v>
       </c>
       <c r="E180" s="23" t="n">
-        <v>-0.2563</v>
+        <v>-0.261</v>
       </c>
       <c r="F180" s="23" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.0989</v>
       </c>
       <c r="G180" s="6" t="n"/>
       <c r="H180" s="11" t="inlineStr">
@@ -14362,13 +14362,13 @@
         </is>
       </c>
       <c r="D181" s="14" t="n">
-        <v>540.79</v>
+        <v>534.24</v>
       </c>
       <c r="E181" s="15" t="n">
-        <v>-0.0877</v>
+        <v>-0.09880000000000001</v>
       </c>
       <c r="F181" s="19" t="n">
-        <v>0.1938</v>
+        <v>0.1793</v>
       </c>
       <c r="G181" s="16" t="n">
         <v>46247</v>
@@ -14397,7 +14397,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="19" t="n">
-        <v>0.3683684979382016</v>
+        <v>0.3851452530697814</v>
       </c>
       <c r="N181" s="13" t="inlineStr">
         <is>
@@ -14408,7 +14408,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="19" t="n">
-        <v>0.2944026331847853</v>
+        <v>0.310272536687631</v>
       </c>
       <c r="Q181" s="20" t="inlineStr">
         <is>
@@ -14449,13 +14449,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>64.73</v>
+        <v>63.01</v>
       </c>
       <c r="E182" s="23" t="n">
-        <v>-0.2277</v>
+        <v>-0.2483</v>
       </c>
       <c r="F182" s="23" t="n">
-        <v>-0.131</v>
+        <v>-0.1541</v>
       </c>
       <c r="G182" s="6" t="n">
         <v>46245</v>
@@ -14514,13 +14514,13 @@
         </is>
       </c>
       <c r="D183" s="14" t="n">
-        <v>488.42</v>
+        <v>482.05</v>
       </c>
       <c r="E183" s="15" t="n">
-        <v>-0.1153</v>
+        <v>-0.1268</v>
       </c>
       <c r="F183" s="19" t="n">
-        <v>0.0473</v>
+        <v>0.0336</v>
       </c>
       <c r="G183" s="16" t="n"/>
       <c r="H183" s="22" t="inlineStr">
@@ -14539,7 +14539,7 @@
         <v>615</v>
       </c>
       <c r="M183" s="19" t="n">
-        <v>0.259162196470251</v>
+        <v>0.2758012654288974</v>
       </c>
       <c r="N183" s="13" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="19" t="n">
-        <v>0.1854551410671143</v>
+        <v>0.2011202157452546</v>
       </c>
       <c r="Q183" s="20" t="inlineStr">
         <is>
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>55.21</v>
+        <v>53.86</v>
       </c>
       <c r="E184" s="23" t="n">
-        <v>-0.21</v>
+        <v>-0.2293</v>
       </c>
       <c r="F184" s="23" t="n">
-        <v>-0.15</v>
+        <v>-0.1707</v>
       </c>
       <c r="G184" s="6" t="n"/>
       <c r="H184" s="11" t="inlineStr">
@@ -14642,13 +14642,13 @@
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>197.96</v>
+        <v>197.31</v>
       </c>
       <c r="E185" s="19" t="n">
-        <v>0.1424</v>
+        <v>0.1387</v>
       </c>
       <c r="F185" s="19" t="n">
-        <v>0.2832</v>
+        <v>0.279</v>
       </c>
       <c r="G185" s="16" t="n"/>
       <c r="H185" s="22" t="inlineStr">
@@ -14667,7 +14667,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="19" t="n">
-        <v>0.01030511214386741</v>
+        <v>0.01363336881050123</v>
       </c>
       <c r="N185" s="13" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="19" t="n">
-        <v>0.01030511214386741</v>
+        <v>0.01363336881050123</v>
       </c>
       <c r="Q185" s="20" t="inlineStr">
         <is>
@@ -14723,13 +14723,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>173.88</v>
+        <v>172.24</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>0.0424</v>
+        <v>0.0326</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>0.2526</v>
+        <v>0.2408</v>
       </c>
       <c r="G186" s="6" t="n"/>
       <c r="H186" s="11" t="inlineStr">
@@ -14751,7 +14751,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="5" t="n">
-        <v>0.03519668737060044</v>
+        <v>0.04505341384115183</v>
       </c>
       <c r="Q186" s="9" t="inlineStr">
         <is>
@@ -14804,13 +14804,13 @@
         </is>
       </c>
       <c r="D187" s="14" t="n">
-        <v>30.64</v>
+        <v>29.87</v>
       </c>
       <c r="E187" s="15" t="n">
-        <v>-0.08539999999999999</v>
+        <v>-0.1084</v>
       </c>
       <c r="F187" s="15" t="n">
-        <v>-0.2267</v>
+        <v>-0.2461</v>
       </c>
       <c r="G187" s="16" t="n"/>
       <c r="H187" s="22" t="inlineStr">
@@ -14855,13 +14855,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>280.64</v>
+        <v>274.58</v>
       </c>
       <c r="E188" s="23" t="n">
-        <v>-0.1291</v>
+        <v>-0.1479</v>
       </c>
       <c r="F188" s="23" t="n">
-        <v>-0.1816</v>
+        <v>-0.1993</v>
       </c>
       <c r="G188" s="6" t="n"/>
       <c r="H188" s="11" t="inlineStr">
@@ -14906,13 +14906,13 @@
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>1695</v>
+        <v>1678.22</v>
       </c>
       <c r="E189" s="15" t="n">
-        <v>-0.0713</v>
+        <v>-0.0805</v>
       </c>
       <c r="F189" s="19" t="n">
-        <v>0.03240000000000001</v>
+        <v>0.0222</v>
       </c>
       <c r="G189" s="16" t="n">
         <v>46309</v>
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>37.15</v>
+        <v>36.78</v>
       </c>
       <c r="E190" s="23" t="n">
-        <v>-0.1424</v>
+        <v>-0.151</v>
       </c>
       <c r="F190" s="5" t="n">
-        <v>0.0917</v>
+        <v>0.0808</v>
       </c>
       <c r="G190" s="6" t="n"/>
       <c r="H190" s="11" t="inlineStr">
@@ -15036,13 +15036,13 @@
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>419.58</v>
+        <v>418.28</v>
       </c>
       <c r="E191" s="19" t="n">
-        <v>0.1222</v>
+        <v>0.1187</v>
       </c>
       <c r="F191" s="19" t="n">
-        <v>0.0877</v>
+        <v>0.08439999999999999</v>
       </c>
       <c r="G191" s="16" t="n">
         <v>46268</v>
@@ -15071,7 +15071,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="19" t="n">
-        <v>0.2989179655846323</v>
+        <v>0.3029549584010711</v>
       </c>
       <c r="N191" s="13" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="19" t="n">
-        <v>0.3871013871013871</v>
+        <v>0.3914124509897677</v>
       </c>
       <c r="Q191" s="20" t="inlineStr">
         <is>
@@ -15135,13 +15135,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>152.05</v>
+        <v>147.6</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.0406</v>
       </c>
       <c r="F192" s="23" t="n">
-        <v>-0.0741</v>
+        <v>-0.1012</v>
       </c>
       <c r="G192" s="6" t="n">
         <v>46244</v>
@@ -15196,13 +15196,13 @@
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>336.7</v>
+        <v>337.07</v>
       </c>
       <c r="E193" s="15" t="n">
+        <v>-0.103</v>
+      </c>
+      <c r="F193" s="15" t="n">
         <v>-0.104</v>
-      </c>
-      <c r="F193" s="15" t="n">
-        <v>-0.105</v>
       </c>
       <c r="G193" s="16" t="n"/>
       <c r="H193" s="22" t="inlineStr">
@@ -15221,7 +15221,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="19" t="n">
-        <v>0.2622512622512623</v>
+        <v>0.2608656955528526</v>
       </c>
       <c r="N193" s="13" t="inlineStr"/>
       <c r="O193" s="18" t="n"/>
@@ -15265,13 +15265,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>124.33</v>
+        <v>125.35</v>
       </c>
       <c r="E194" s="23" t="n">
-        <v>-0.1047</v>
+        <v>-0.0974</v>
       </c>
       <c r="F194" s="23" t="n">
-        <v>-0.08460000000000001</v>
+        <v>-0.0771</v>
       </c>
       <c r="G194" s="6" t="n"/>
       <c r="H194" s="11" t="inlineStr">
@@ -15316,13 +15316,13 @@
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>408.06</v>
+        <v>408.83</v>
       </c>
       <c r="E195" s="15" t="n">
-        <v>-0.0594</v>
+        <v>-0.0576</v>
       </c>
       <c r="F195" s="15" t="n">
-        <v>-0.1642</v>
+        <v>-0.1626</v>
       </c>
       <c r="G195" s="16" t="n">
         <v>46268</v>
@@ -15377,13 +15377,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>15.55</v>
+        <v>15.64</v>
       </c>
       <c r="E196" s="23" t="n">
-        <v>-0.0638</v>
+        <v>-0.0584</v>
       </c>
       <c r="F196" s="5" t="n">
-        <v>0.126</v>
+        <v>0.1325</v>
       </c>
       <c r="G196" s="6" t="n">
         <v>46247</v>
@@ -15438,13 +15438,13 @@
         </is>
       </c>
       <c r="D197" s="14" t="n">
-        <v>369.87</v>
+        <v>362.76</v>
       </c>
       <c r="E197" s="19" t="n">
-        <v>0.0562</v>
+        <v>0.0359</v>
       </c>
       <c r="F197" s="15" t="n">
-        <v>-0.005</v>
+        <v>-0.0241</v>
       </c>
       <c r="G197" s="16" t="n"/>
       <c r="H197" s="22" t="inlineStr">
@@ -15489,13 +15489,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>334.8</v>
+        <v>328.22</v>
       </c>
       <c r="E198" s="23" t="n">
-        <v>-0.0027</v>
+        <v>-0.0223</v>
       </c>
       <c r="F198" s="23" t="n">
-        <v>-0.1119</v>
+        <v>-0.1294</v>
       </c>
       <c r="G198" s="6" t="n">
         <v>46246</v>
@@ -15550,13 +15550,13 @@
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>51.94</v>
+        <v>51.73</v>
       </c>
       <c r="E199" s="15" t="n">
-        <v>-0.1152</v>
+        <v>-0.1187</v>
       </c>
       <c r="F199" s="19" t="n">
-        <v>0.0428</v>
+        <v>0.0385</v>
       </c>
       <c r="G199" s="16" t="n"/>
       <c r="H199" s="22" t="inlineStr">
@@ -15601,13 +15601,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>22.36</v>
+        <v>21.77</v>
       </c>
       <c r="E200" s="23" t="n">
-        <v>-0.0193</v>
+        <v>-0.0452</v>
       </c>
       <c r="F200" s="23" t="n">
-        <v>-0.135</v>
+        <v>-0.1578</v>
       </c>
       <c r="G200" s="6" t="n"/>
       <c r="H200" s="11" t="inlineStr">
@@ -15652,13 +15652,13 @@
         </is>
       </c>
       <c r="D201" s="14" t="n">
-        <v>232.04</v>
+        <v>224.63</v>
       </c>
       <c r="E201" s="15" t="n">
-        <v>-0.1262</v>
+        <v>-0.1541</v>
       </c>
       <c r="F201" s="19" t="n">
-        <v>0.1216</v>
+        <v>0.0857</v>
       </c>
       <c r="G201" s="16" t="n">
         <v>46267</v>
@@ -15713,13 +15713,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>191.6</v>
+        <v>192.98</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>0.1567</v>
+        <v>0.165</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>0.032</v>
+        <v>0.0394</v>
       </c>
       <c r="G202" s="6" t="n">
         <v>46267</v>
@@ -15748,7 +15748,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="5" t="n">
-        <v>0.04384133611691026</v>
+        <v>0.03637682661415696</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="5" t="n">
-        <v>0.3048016701461378</v>
+        <v>0.2954710332676962</v>
       </c>
       <c r="Q202" s="9" t="inlineStr">
         <is>
@@ -15804,13 +15804,13 @@
         </is>
       </c>
       <c r="D203" s="14" t="n">
-        <v>212.76</v>
+        <v>209.86</v>
       </c>
       <c r="E203" s="19" t="n">
-        <v>0.06709999999999999</v>
+        <v>0.0526</v>
       </c>
       <c r="F203" s="19" t="n">
-        <v>0.2683</v>
+        <v>0.251</v>
       </c>
       <c r="G203" s="16" t="n">
         <v>46260</v>
@@ -15839,7 +15839,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="15" t="n">
-        <v>-0.1481011468321113</v>
+        <v>-0.136328981225579</v>
       </c>
       <c r="N203" s="13" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="15" t="n">
-        <v>-0.1657266403459297</v>
+        <v>-0.1541980367864291</v>
       </c>
       <c r="Q203" s="20" t="inlineStr">
         <is>
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>92.25</v>
+        <v>89.89</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>0.067</v>
+        <v>0.0397</v>
       </c>
       <c r="F204" s="23" t="n">
-        <v>-0.081</v>
+        <v>-0.1046</v>
       </c>
       <c r="G204" s="6" t="n">
         <v>46245</v>
@@ -15952,13 +15952,13 @@
         </is>
       </c>
       <c r="D205" s="14" t="n">
-        <v>122.07</v>
+        <v>121.5</v>
       </c>
       <c r="E205" s="19" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="F205" s="19" t="n">
-        <v>0.0036</v>
+        <v>0.066</v>
+      </c>
+      <c r="F205" s="15" t="n">
+        <v>-0.0012</v>
       </c>
       <c r="G205" s="16" t="n">
         <v>46246</v>
@@ -15987,7 +15987,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="19" t="n">
-        <v>0.0649627263045794</v>
+        <v>0.06995884773662552</v>
       </c>
       <c r="N205" s="13" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="19" t="n">
-        <v>0.2288031457360531</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="Q205" s="20" t="inlineStr">
         <is>
@@ -16055,13 +16055,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>287.05</v>
+        <v>283.17</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>0.1241</v>
+        <v>0.1089</v>
       </c>
       <c r="F206" s="5" t="n">
-        <v>0.2261</v>
+        <v>0.2096</v>
       </c>
       <c r="G206" s="6" t="n">
         <v>46240</v>
@@ -16116,13 +16116,13 @@
         </is>
       </c>
       <c r="D207" s="14" t="n">
-        <v>470.54</v>
+        <v>462.7</v>
       </c>
       <c r="E207" s="19" t="n">
-        <v>0.1426</v>
+        <v>0.1236</v>
       </c>
       <c r="F207" s="19" t="n">
-        <v>0.1931</v>
+        <v>0.1732</v>
       </c>
       <c r="G207" s="16" t="n">
         <v>46261</v>
@@ -16177,13 +16177,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>57.06</v>
+        <v>57.49</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>0.2166</v>
+        <v>0.2258</v>
       </c>
       <c r="F208" s="5" t="n">
-        <v>0.2074</v>
+        <v>0.2165</v>
       </c>
       <c r="G208" s="6" t="n">
         <v>46268</v>
@@ -16238,13 +16238,13 @@
         </is>
       </c>
       <c r="D209" s="14" t="n">
-        <v>51.39</v>
+        <v>50.86</v>
       </c>
       <c r="E209" s="19" t="n">
-        <v>0.129</v>
+        <v>0.1173</v>
       </c>
       <c r="F209" s="19" t="n">
-        <v>0.2181</v>
+        <v>0.2055</v>
       </c>
       <c r="G209" s="16" t="n">
         <v>46239</v>
@@ -16299,13 +16299,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>533.6</v>
+        <v>522.22</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>0.06559999999999999</v>
+        <v>0.0429</v>
       </c>
       <c r="F210" s="23" t="n">
-        <v>-0.1411</v>
+        <v>-0.1594</v>
       </c>
       <c r="G210" s="6" t="n">
         <v>46251</v>
@@ -16360,13 +16360,13 @@
         </is>
       </c>
       <c r="D211" s="14" t="n">
-        <v>116.57</v>
+        <v>114.44</v>
       </c>
       <c r="E211" s="15" t="n">
-        <v>-0.0177</v>
+        <v>-0.0356</v>
       </c>
       <c r="F211" s="15" t="n">
-        <v>-0.0011</v>
+        <v>-0.0194</v>
       </c>
       <c r="G211" s="16" t="n"/>
       <c r="H211" s="22" t="inlineStr">
@@ -16411,13 +16411,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>165.76</v>
+        <v>164.13</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>0.021</v>
+        <v>0.011</v>
       </c>
       <c r="F212" s="5" t="n">
-        <v>0.1457</v>
+        <v>0.1344</v>
       </c>
       <c r="G212" s="6" t="n"/>
       <c r="H212" s="11" t="inlineStr">
@@ -16462,13 +16462,13 @@
         </is>
       </c>
       <c r="D213" s="14" t="n">
-        <v>49.85</v>
+        <v>49.46</v>
       </c>
       <c r="E213" s="15" t="n">
-        <v>-0.2766</v>
+        <v>-0.2823</v>
       </c>
       <c r="F213" s="15" t="n">
-        <v>-0.34</v>
+        <v>-0.3452</v>
       </c>
       <c r="G213" s="16" t="n">
         <v>46239</v>
@@ -16523,13 +16523,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>158.75</v>
+        <v>156.7</v>
       </c>
       <c r="E214" s="23" t="n">
-        <v>-0.1851</v>
+        <v>-0.1956</v>
       </c>
       <c r="F214" s="23" t="n">
-        <v>-0.106</v>
+        <v>-0.1176</v>
       </c>
       <c r="G214" s="6" t="n"/>
       <c r="H214" s="11" t="inlineStr">
@@ -16574,13 +16574,13 @@
         </is>
       </c>
       <c r="D215" s="14" t="n">
-        <v>36.34</v>
+        <v>36.16</v>
       </c>
       <c r="E215" s="19" t="n">
-        <v>0.1062</v>
+        <v>0.1008</v>
       </c>
       <c r="F215" s="19" t="n">
-        <v>0.1677</v>
+        <v>0.162</v>
       </c>
       <c r="G215" s="16" t="n">
         <v>46267</v>
@@ -16635,13 +16635,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>158.63</v>
+        <v>160.33</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>0.1529</v>
+        <v>0.1653</v>
       </c>
       <c r="F216" s="5" t="n">
-        <v>0.1659</v>
+        <v>0.1784</v>
       </c>
       <c r="G216" s="6" t="n">
         <v>46268</v>
@@ -16670,7 +16670,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="5" t="n">
-        <v>0.1977557838996407</v>
+        <v>0.1850558223663693</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="8" t="n"/>
@@ -16714,13 +16714,13 @@
         </is>
       </c>
       <c r="D217" s="14" t="n">
-        <v>53.51</v>
+        <v>53.22</v>
       </c>
       <c r="E217" s="19" t="n">
-        <v>0.2401</v>
+        <v>0.2334</v>
       </c>
       <c r="F217" s="19" t="n">
-        <v>0.0876</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="G217" s="16" t="n">
         <v>46267</v>
@@ -16749,7 +16749,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="19" t="n">
-        <v>0.2521024107643431</v>
+        <v>0.2589252160841789</v>
       </c>
       <c r="N217" s="13" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="19" t="n">
-        <v>0.3081666978134929</v>
+        <v>0.3152950018789929</v>
       </c>
       <c r="Q217" s="20" t="inlineStr">
         <is>
@@ -16801,13 +16801,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>243.43</v>
+        <v>250.21</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>0.2559</v>
+        <v>0.2908</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>0.1448</v>
+        <v>0.1767</v>
       </c>
       <c r="G218" s="6" t="n">
         <v>46239</v>
@@ -16862,13 +16862,13 @@
         </is>
       </c>
       <c r="D219" s="14" t="n">
-        <v>237.11</v>
+        <v>235.92</v>
       </c>
       <c r="E219" s="15" t="n">
-        <v>-0.2084</v>
+        <v>-0.2123</v>
       </c>
       <c r="F219" s="15" t="n">
-        <v>-0.1676</v>
+        <v>-0.1717</v>
       </c>
       <c r="G219" s="16" t="n">
         <v>46316</v>
@@ -16904,7 +16904,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="19" t="n">
-        <v>0.0543629539032516</v>
+        <v>0.05968124788063756</v>
       </c>
       <c r="Q219" s="20" t="inlineStr">
         <is>
@@ -16941,13 +16941,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>11.19</v>
+        <v>10.85</v>
       </c>
       <c r="E220" s="23" t="n">
-        <v>-0.09210000000000002</v>
+        <v>-0.12</v>
       </c>
       <c r="F220" s="23" t="n">
-        <v>-0.2311</v>
+        <v>-0.2548</v>
       </c>
       <c r="G220" s="6" t="n">
         <v>46246</v>
@@ -17002,13 +17002,13 @@
         </is>
       </c>
       <c r="D221" s="14" t="n">
-        <v>101.65</v>
+        <v>101.06</v>
       </c>
       <c r="E221" s="15" t="n">
-        <v>-0.1682</v>
+        <v>-0.173</v>
       </c>
       <c r="F221" s="19" t="n">
-        <v>0.025</v>
+        <v>0.0191</v>
       </c>
       <c r="G221" s="16" t="n">
         <v>46317</v>
@@ -17063,13 +17063,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>323.61</v>
+        <v>327.94</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>0.1891</v>
+        <v>0.205</v>
       </c>
       <c r="F222" s="5" t="n">
-        <v>0.09050000000000001</v>
+        <v>0.1051</v>
       </c>
       <c r="G222" s="6" t="n">
         <v>46259</v>
@@ -17124,13 +17124,13 @@
         </is>
       </c>
       <c r="D223" s="14" t="n">
-        <v>40.55</v>
+        <v>39.93</v>
       </c>
       <c r="E223" s="15" t="n">
-        <v>-0.1702</v>
+        <v>-0.1829</v>
       </c>
       <c r="F223" s="15" t="n">
-        <v>-0.2858</v>
+        <v>-0.2968</v>
       </c>
       <c r="G223" s="16" t="n">
         <v>46239</v>
@@ -17185,13 +17185,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>40.36</v>
+        <v>38.89</v>
       </c>
       <c r="E224" s="23" t="n">
-        <v>-0.0808</v>
+        <v>-0.1143</v>
       </c>
       <c r="F224" s="23" t="n">
-        <v>-0.2574</v>
+        <v>-0.2845</v>
       </c>
       <c r="G224" s="6" t="n">
         <v>46261</v>
@@ -17246,13 +17246,13 @@
         </is>
       </c>
       <c r="D225" s="14" t="n">
-        <v>342.93</v>
+        <v>338.62</v>
       </c>
       <c r="E225" s="19" t="n">
-        <v>0.0139</v>
+        <v>0.0012</v>
       </c>
       <c r="F225" s="15" t="n">
-        <v>-0.0292</v>
+        <v>-0.0414</v>
       </c>
       <c r="G225" s="16" t="n">
         <v>46289</v>
@@ -17311,13 +17311,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>339.55</v>
+        <v>336.02</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>0.062</v>
+        <v>0.0509</v>
       </c>
       <c r="F226" s="5" t="n">
-        <v>0.0295</v>
+        <v>0.0188</v>
       </c>
       <c r="G226" s="6" t="n">
         <v>46252</v>
@@ -17346,7 +17346,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>0.1485790016197909</v>
+        <v>0.1606451996904947</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="8" t="n"/>
@@ -17402,13 +17402,13 @@
         </is>
       </c>
       <c r="D227" s="14" t="n">
-        <v>193.72</v>
+        <v>192.8</v>
       </c>
       <c r="E227" s="15" t="n">
-        <v>-0.1697</v>
-      </c>
-      <c r="F227" s="19" t="n">
-        <v>0.004099999999999999</v>
+        <v>-0.1736</v>
+      </c>
+      <c r="F227" s="15" t="n">
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="G227" s="16" t="n"/>
       <c r="H227" s="22" t="inlineStr">
@@ -17427,7 +17427,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="19" t="n">
-        <v>0.5744373322320876</v>
+        <v>0.5819502074688796</v>
       </c>
       <c r="N227" s="13" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="15" t="n">
-        <v>-0.04501342143299607</v>
+        <v>-0.04045643153526977</v>
       </c>
       <c r="Q227" s="20" t="inlineStr">
         <is>
@@ -17479,13 +17479,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>95.72</v>
+        <v>93.84</v>
       </c>
       <c r="E228" s="23" t="n">
-        <v>-0.1997</v>
+        <v>-0.2155</v>
       </c>
       <c r="F228" s="23" t="n">
-        <v>-0.0249</v>
+        <v>-0.044</v>
       </c>
       <c r="G228" s="6" t="n">
         <v>46239</v>
@@ -17540,13 +17540,13 @@
         </is>
       </c>
       <c r="D229" s="14" t="n">
-        <v>851.39</v>
+        <v>826.26</v>
       </c>
       <c r="E229" s="19" t="n">
-        <v>0.1643</v>
+        <v>0.1299</v>
       </c>
       <c r="F229" s="15" t="n">
-        <v>-0.0142</v>
+        <v>-0.0433</v>
       </c>
       <c r="G229" s="16" t="n">
         <v>46245</v>
@@ -17601,13 +17601,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>105.82</v>
+        <v>105.7</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>0.0861</v>
+        <v>0.0849</v>
       </c>
       <c r="F230" s="23" t="n">
-        <v>-0.063</v>
+        <v>-0.064</v>
       </c>
       <c r="G230" s="6" t="n"/>
       <c r="H230" s="11" t="inlineStr">
@@ -17652,13 +17652,13 @@
         </is>
       </c>
       <c r="D231" s="14" t="n">
-        <v>312.14</v>
+        <v>307.42</v>
       </c>
       <c r="E231" s="15" t="n">
-        <v>-0.1087</v>
+        <v>-0.1222</v>
       </c>
       <c r="F231" s="19" t="n">
-        <v>0.0292</v>
+        <v>0.0137</v>
       </c>
       <c r="G231" s="16" t="n"/>
       <c r="H231" s="22" t="inlineStr">
@@ -17677,7 +17677,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="19" t="n">
-        <v>0.4416607932338054</v>
+        <v>0.4637954589811983</v>
       </c>
       <c r="N231" s="13" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="19" t="n">
-        <v>0.1373101813288909</v>
+        <v>0.1547719731962786</v>
       </c>
       <c r="Q231" s="20" t="inlineStr">
         <is>
@@ -17733,13 +17733,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>78.08</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E232" s="23" t="n">
-        <v>-0.1086</v>
+        <v>-0.1119</v>
       </c>
       <c r="F232" s="23" t="n">
-        <v>-0.1161</v>
+        <v>-0.1194</v>
       </c>
       <c r="G232" s="6" t="n">
         <v>46240</v>
@@ -17794,13 +17794,13 @@
         </is>
       </c>
       <c r="D233" s="14" t="n">
-        <v>376.44</v>
+        <v>376.36</v>
       </c>
       <c r="E233" s="19" t="n">
-        <v>0.0518</v>
+        <v>0.0515</v>
       </c>
       <c r="F233" s="19" t="n">
-        <v>0.0733</v>
+        <v>0.073</v>
       </c>
       <c r="G233" s="16" t="n">
         <v>46259</v>
@@ -17855,13 +17855,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>315.41</v>
+        <v>313.1</v>
       </c>
       <c r="E234" s="23" t="n">
-        <v>-0.143</v>
+        <v>-0.1493</v>
       </c>
       <c r="F234" s="5" t="n">
-        <v>0.04559999999999999</v>
+        <v>0.038</v>
       </c>
       <c r="G234" s="6" t="n">
         <v>46239</v>
@@ -17916,13 +17916,13 @@
         </is>
       </c>
       <c r="D235" s="14" t="n">
-        <v>1334.26</v>
+        <v>1345.45</v>
       </c>
       <c r="E235" s="15" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0005</v>
       </c>
       <c r="F235" s="15" t="n">
-        <v>-0.09910000000000001</v>
+        <v>-0.0916</v>
       </c>
       <c r="G235" s="16" t="n"/>
       <c r="H235" s="22" t="inlineStr">
@@ -17967,13 +17967,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>216.4</v>
+        <v>211.02</v>
       </c>
       <c r="E236" s="23" t="n">
-        <v>-0.1319</v>
+        <v>-0.1534</v>
       </c>
       <c r="F236" s="23" t="n">
-        <v>-0.1787</v>
+        <v>-0.1991</v>
       </c>
       <c r="G236" s="6" t="n">
         <v>46261</v>
@@ -18002,7 +18002,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="5" t="n">
-        <v>0.1090573012939001</v>
+        <v>0.1373329542223485</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="5" t="n">
-        <v>0.1598890942698706</v>
+        <v>0.1894607146242062</v>
       </c>
       <c r="Q236" s="9" t="inlineStr">
         <is>
@@ -18054,13 +18054,13 @@
         </is>
       </c>
       <c r="D237" s="14" t="n">
-        <v>489.15</v>
+        <v>487.46</v>
       </c>
       <c r="E237" s="19" t="n">
-        <v>0.2648</v>
+        <v>0.2604</v>
       </c>
       <c r="F237" s="19" t="n">
-        <v>0.174</v>
+        <v>0.1699</v>
       </c>
       <c r="G237" s="16" t="n"/>
       <c r="H237" s="22" t="inlineStr">
@@ -18079,7 +18079,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="19" t="n">
-        <v>0.2777266687110294</v>
+        <v>0.2821564846346367</v>
       </c>
       <c r="N237" s="13" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="19" t="n">
-        <v>0.0732904017172647</v>
+        <v>0.07701144709309486</v>
       </c>
       <c r="Q237" s="20" t="inlineStr">
         <is>
@@ -18143,13 +18143,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>440.14</v>
+        <v>438.14</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>0.0409</v>
+        <v>0.0362</v>
       </c>
       <c r="F238" s="5" t="n">
-        <v>0.0726</v>
+        <v>0.0677</v>
       </c>
       <c r="G238" s="6" t="n">
         <v>46239</v>
@@ -18181,7 +18181,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="5" t="n">
-        <v>0.1928022901803972</v>
+        <v>0.198247135618752</v>
       </c>
       <c r="Q238" s="9" t="inlineStr">
         <is>
@@ -18230,13 +18230,13 @@
         </is>
       </c>
       <c r="D239" s="14" t="n">
-        <v>97.56999999999999</v>
+        <v>98.37</v>
       </c>
       <c r="E239" s="15" t="n">
-        <v>-0.0318</v>
+        <v>-0.0238</v>
       </c>
       <c r="F239" s="15" t="n">
-        <v>-0.1899</v>
+        <v>-0.1832</v>
       </c>
       <c r="G239" s="16" t="n"/>
       <c r="H239" s="22" t="inlineStr">
@@ -18281,13 +18281,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>268.9</v>
+        <v>263.46</v>
       </c>
       <c r="E240" s="23" t="n">
-        <v>-0.1793</v>
+        <v>-0.1959</v>
       </c>
       <c r="F240" s="23" t="n">
-        <v>-0.2215</v>
+        <v>-0.2372</v>
       </c>
       <c r="G240" s="6" t="n">
         <v>46240</v>
@@ -18342,13 +18342,13 @@
         </is>
       </c>
       <c r="D241" s="14" t="n">
-        <v>919.91</v>
+        <v>893.1900000000001</v>
       </c>
       <c r="E241" s="15" t="n">
-        <v>-0.0658</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="F241" s="19" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0338</v>
       </c>
       <c r="G241" s="16" t="n">
         <v>46287</v>
@@ -18377,7 +18377,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="19" t="n">
-        <v>0.6577708688893479</v>
+        <v>0.7073634948891052</v>
       </c>
       <c r="N241" s="13" t="inlineStr">
         <is>
@@ -18425,13 +18425,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>225.99</v>
+        <v>218.99</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>0.0609</v>
+        <v>0.028</v>
       </c>
       <c r="F242" s="23" t="n">
-        <v>-0.008</v>
+        <v>-0.0387</v>
       </c>
       <c r="G242" s="6" t="n">
         <v>46246</v>
@@ -18486,13 +18486,13 @@
         </is>
       </c>
       <c r="D243" s="14" t="n">
-        <v>295.29</v>
+        <v>292.96</v>
       </c>
       <c r="E243" s="19" t="n">
-        <v>0.1928</v>
+        <v>0.1834</v>
       </c>
       <c r="F243" s="19" t="n">
-        <v>0.1806</v>
+        <v>0.1713</v>
       </c>
       <c r="G243" s="16" t="n">
         <v>46240</v>
@@ -18547,13 +18547,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>116.36</v>
+        <v>117.22</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>0.0781</v>
+        <v>0.0861</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>0.0348</v>
+        <v>0.0424</v>
       </c>
       <c r="G244" s="6" t="n">
         <v>46323</v>
@@ -18582,7 +18582,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="5" t="n">
-        <v>0.3750429700928154</v>
+        <v>0.364954785872718</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="5" t="n">
-        <v>0.2891027844620144</v>
+        <v>0.2796451117556731</v>
       </c>
       <c r="Q244" s="9" t="inlineStr">
         <is>
@@ -18638,13 +18638,13 @@
         </is>
       </c>
       <c r="D245" s="14" t="n">
-        <v>60.7</v>
+        <v>60.96</v>
       </c>
       <c r="E245" s="19" t="n">
-        <v>0.158</v>
+        <v>0.1629</v>
       </c>
       <c r="F245" s="19" t="n">
-        <v>0.1316</v>
+        <v>0.1365</v>
       </c>
       <c r="G245" s="16" t="n">
         <v>46260</v>
@@ -18699,13 +18699,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>220.67</v>
+        <v>219.22</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>0.1285</v>
+        <v>0.121</v>
       </c>
       <c r="F246" s="5" t="n">
-        <v>0.0759</v>
+        <v>0.0688</v>
       </c>
       <c r="G246" s="6" t="n">
         <v>46260</v>
@@ -18734,7 +18734,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="5" t="n">
-        <v>0.4274708841256175</v>
+        <v>0.4369126904479518</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="5" t="n">
-        <v>0.8715729369646985</v>
+        <v>0.8839521941428702</v>
       </c>
       <c r="Q246" s="9" t="inlineStr">
         <is>
@@ -18794,13 +18794,13 @@
         </is>
       </c>
       <c r="D247" s="14" t="n">
-        <v>408.56</v>
+        <v>402.38</v>
       </c>
       <c r="E247" s="15" t="n">
-        <v>-0.1244</v>
+        <v>-0.1377</v>
       </c>
       <c r="F247" s="15" t="n">
-        <v>-0.1412</v>
+        <v>-0.1542</v>
       </c>
       <c r="G247" s="16" t="n">
         <v>46240</v>
@@ -18855,13 +18855,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>231.42</v>
+        <v>231.15</v>
       </c>
       <c r="E248" s="23" t="n">
-        <v>-0.175</v>
+        <v>-0.176</v>
       </c>
       <c r="F248" s="23" t="n">
-        <v>-0.2181</v>
+        <v>-0.219</v>
       </c>
       <c r="G248" s="6" t="n"/>
       <c r="H248" s="11" t="inlineStr">
@@ -18902,13 +18902,13 @@
         </is>
       </c>
       <c r="D249" s="14" t="n">
-        <v>11.43</v>
+        <v>11.47</v>
       </c>
       <c r="E249" s="15" t="n">
-        <v>-0.345</v>
+        <v>-0.3425</v>
       </c>
       <c r="F249" s="15" t="n">
-        <v>-0.4311</v>
+        <v>-0.4289</v>
       </c>
       <c r="G249" s="16" t="n"/>
       <c r="H249" s="22" t="inlineStr">
@@ -18953,13 +18953,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>147.93</v>
+        <v>147.04</v>
       </c>
       <c r="E250" s="23" t="n">
-        <v>-0.004500000000000001</v>
+        <v>-0.0105</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>0.2461</v>
+        <v>0.2385</v>
       </c>
       <c r="G250" s="6" t="n">
         <v>46260</v>
@@ -18988,7 +18988,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="5" t="n">
-        <v>0.01399310484688699</v>
+        <v>0.02013057671381942</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="23" t="n">
-        <v>-0.1212059757993646</v>
+        <v>-0.1158868335146898</v>
       </c>
       <c r="Q250" s="9" t="inlineStr">
         <is>
@@ -19040,13 +19040,13 @@
         </is>
       </c>
       <c r="D251" s="14" t="n">
-        <v>78.11</v>
+        <v>76.91</v>
       </c>
       <c r="E251" s="15" t="n">
-        <v>-0.1751</v>
+        <v>-0.1878</v>
       </c>
       <c r="F251" s="15" t="n">
-        <v>-0.3339</v>
+        <v>-0.3441</v>
       </c>
       <c r="G251" s="16" t="n"/>
       <c r="H251" s="22" t="inlineStr">
@@ -19091,13 +19091,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>283.91</v>
+        <v>276</v>
       </c>
       <c r="E252" s="23" t="n">
-        <v>-0.06570000000000001</v>
+        <v>-0.0917</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>0.1211</v>
+        <v>0.08990000000000001</v>
       </c>
       <c r="G252" s="6" t="n">
         <v>46240</v>
@@ -19152,13 +19152,13 @@
         </is>
       </c>
       <c r="D253" s="14" t="n">
-        <v>144.52</v>
+        <v>144.39</v>
       </c>
       <c r="E253" s="19" t="n">
-        <v>0.0053</v>
+        <v>0.0044</v>
       </c>
       <c r="F253" s="15" t="n">
-        <v>-0.3237</v>
+        <v>-0.3243</v>
       </c>
       <c r="G253" s="16" t="n">
         <v>46273</v>
@@ -19187,7 +19187,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="19" t="n">
-        <v>0.9374481040686409</v>
+        <v>0.9391924648521368</v>
       </c>
       <c r="N253" s="13" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="19" t="n">
-        <v>0.6952670910600608</v>
+        <v>0.6967934067456196</v>
       </c>
       <c r="Q253" s="20" t="inlineStr">
         <is>
@@ -19239,13 +19239,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>364.4</v>
+        <v>362.66</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>0.0192</v>
+        <v>0.0143</v>
       </c>
       <c r="F254" s="5" t="n">
-        <v>0.3395</v>
+        <v>0.3331</v>
       </c>
       <c r="G254" s="6" t="n">
         <v>46266</v>
@@ -19274,7 +19274,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="5" t="n">
-        <v>0.1525795828759605</v>
+        <v>0.1581095240721336</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="5" t="n">
-        <v>0.1388583973655325</v>
+        <v>0.1443225059284177</v>
       </c>
       <c r="Q254" s="9" t="inlineStr">
         <is>
@@ -19334,13 +19334,13 @@
         </is>
       </c>
       <c r="D255" s="14" t="n">
-        <v>13.87</v>
+        <v>13.82</v>
       </c>
       <c r="E255" s="19" t="n">
-        <v>0.1724</v>
+        <v>0.1682</v>
       </c>
       <c r="F255" s="19" t="n">
-        <v>0.234</v>
+        <v>0.2295</v>
       </c>
       <c r="G255" s="16" t="n">
         <v>46268</v>
@@ -19395,13 +19395,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>31.65</v>
+        <v>31.81</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>0.0118</v>
+        <v>0.0169</v>
       </c>
       <c r="F256" s="23" t="n">
-        <v>-0.0882</v>
+        <v>-0.08349999999999999</v>
       </c>
       <c r="G256" s="6" t="n">
         <v>46315</v>
@@ -19456,13 +19456,13 @@
         </is>
       </c>
       <c r="D257" s="14" t="n">
-        <v>163.16</v>
+        <v>163.39</v>
       </c>
       <c r="E257" s="19" t="n">
-        <v>0.1025</v>
+        <v>0.104</v>
       </c>
       <c r="F257" s="19" t="n">
-        <v>0.3493</v>
+        <v>0.3511</v>
       </c>
       <c r="G257" s="16" t="n"/>
       <c r="H257" s="22" t="inlineStr">
@@ -19507,13 +19507,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>160.67</v>
+        <v>158.43</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>0.2122</v>
+        <v>0.1953</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>0.1855</v>
+        <v>0.169</v>
       </c>
       <c r="G258" s="6" t="n"/>
       <c r="H258" s="11" t="inlineStr">
@@ -19558,13 +19558,13 @@
         </is>
       </c>
       <c r="D259" s="14" t="n">
-        <v>135.9</v>
+        <v>135.64</v>
       </c>
       <c r="E259" s="15" t="n">
-        <v>-0.0735</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="F259" s="15" t="n">
-        <v>-0.0433</v>
+        <v>-0.0451</v>
       </c>
       <c r="G259" s="16" t="n"/>
       <c r="H259" s="22" t="inlineStr">
@@ -19619,13 +19619,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>21.5</v>
+        <v>21.39</v>
       </c>
       <c r="E260" s="23" t="n">
-        <v>-0.047</v>
+        <v>-0.0519</v>
       </c>
       <c r="F260" s="23" t="n">
-        <v>-0.09849999999999999</v>
+        <v>-0.1031</v>
       </c>
       <c r="G260" s="6" t="n">
         <v>46240</v>
@@ -19680,13 +19680,13 @@
         </is>
       </c>
       <c r="D261" s="14" t="n">
-        <v>157.81</v>
+        <v>157.53</v>
       </c>
       <c r="E261" s="15" t="n">
-        <v>-0.1537</v>
+        <v>-0.1552</v>
       </c>
       <c r="F261" s="15" t="n">
-        <v>-0.2692</v>
+        <v>-0.2705</v>
       </c>
       <c r="G261" s="16" t="n"/>
       <c r="H261" s="22" t="inlineStr">
@@ -19705,7 +19705,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="19" t="n">
-        <v>0.6792345225270895</v>
+        <v>0.6822192598235257</v>
       </c>
       <c r="N261" s="13" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>179</v>
       </c>
       <c r="P261" s="19" t="n">
-        <v>0.1342753944616944</v>
+        <v>0.13629150003174</v>
       </c>
       <c r="Q261" s="20" t="inlineStr">
         <is>
@@ -19761,13 +19761,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>94.59999999999999</v>
+        <v>95.25</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>0.0857</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="F262" s="23" t="n">
-        <v>-0.0374</v>
+        <v>-0.0308</v>
       </c>
       <c r="G262" s="6" t="n"/>
       <c r="H262" s="11" t="inlineStr">
@@ -19812,13 +19812,13 @@
         </is>
       </c>
       <c r="D263" s="14" t="n">
-        <v>9</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="E263" s="15" t="n">
-        <v>-0.0395</v>
+        <v>-0.05230000000000001</v>
       </c>
       <c r="F263" s="15" t="n">
-        <v>-0.0959</v>
+        <v>-0.108</v>
       </c>
       <c r="G263" s="16" t="n">
         <v>46244</v>
@@ -19873,13 +19873,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>84.25</v>
+        <v>84.81</v>
       </c>
       <c r="E264" s="23" t="n">
-        <v>-0.0357</v>
+        <v>-0.0292</v>
       </c>
       <c r="F264" s="5" t="n">
-        <v>0.1476</v>
+        <v>0.1553</v>
       </c>
       <c r="G264" s="6" t="n">
         <v>46273</v>
@@ -19934,13 +19934,13 @@
         </is>
       </c>
       <c r="D265" s="14" t="n">
-        <v>16.94</v>
+        <v>16.78</v>
       </c>
       <c r="E265" s="15" t="n">
-        <v>-0.0565</v>
+        <v>-0.06570000000000001</v>
       </c>
       <c r="F265" s="15" t="n">
-        <v>-0.1806</v>
+        <v>-0.1886</v>
       </c>
       <c r="G265" s="16" t="n">
         <v>46240</v>
@@ -19995,13 +19995,13 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>393.8</v>
+        <v>394.53</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>0.08109999999999999</v>
+        <v>0.08310000000000001</v>
       </c>
       <c r="F266" s="5" t="n">
-        <v>0.1855</v>
+        <v>0.1877</v>
       </c>
       <c r="G266" s="6" t="n">
         <v>46317</v>
@@ -20070,13 +20070,13 @@
         </is>
       </c>
       <c r="D267" s="14" t="n">
-        <v>4.92</v>
+        <v>4.75</v>
       </c>
       <c r="E267" s="15" t="n">
-        <v>-0.2342</v>
+        <v>-0.2607</v>
       </c>
       <c r="F267" s="19" t="n">
-        <v>0.0457</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="G267" s="16" t="n">
         <v>46245</v>
@@ -20131,13 +20131,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>21.09</v>
+        <v>21</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>0.1623</v>
+        <v>0.157</v>
       </c>
       <c r="F268" s="5" t="n">
-        <v>0.3226</v>
+        <v>0.3166</v>
       </c>
       <c r="G268" s="6" t="n">
         <v>46261</v>
@@ -20192,13 +20192,13 @@
         </is>
       </c>
       <c r="D269" s="14" t="n">
-        <v>17.67</v>
+        <v>17.84</v>
       </c>
       <c r="E269" s="19" t="n">
-        <v>0.1151</v>
+        <v>0.1256</v>
       </c>
       <c r="F269" s="15" t="n">
-        <v>-0.031</v>
+        <v>-0.0219</v>
       </c>
       <c r="G269" s="16" t="n">
         <v>46273</v>
@@ -20253,13 +20253,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>203.42</v>
+        <v>199.17</v>
       </c>
       <c r="E270" s="23" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.08470000000000001</v>
       </c>
       <c r="F270" s="23" t="n">
-        <v>-0.193</v>
+        <v>-0.2099</v>
       </c>
       <c r="G270" s="6" t="n"/>
       <c r="H270" s="11" t="inlineStr">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="D271" s="14" t="n">
-        <v>195.93</v>
+        <v>197.33</v>
       </c>
       <c r="E271" s="19" t="n">
-        <v>0.2209</v>
+        <v>0.2295</v>
       </c>
       <c r="F271" s="19" t="n">
-        <v>0.0604</v>
+        <v>0.068</v>
       </c>
       <c r="G271" s="16" t="n">
         <v>46316</v>
@@ -20385,13 +20385,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>31.17</v>
+        <v>30.32</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>0.1464</v>
+        <v>0.1151</v>
       </c>
       <c r="F272" s="23" t="n">
-        <v>-0.2514</v>
+        <v>-0.2719</v>
       </c>
       <c r="G272" s="6" t="n">
         <v>46245</v>
@@ -20446,13 +20446,13 @@
         </is>
       </c>
       <c r="D273" s="14" t="n">
-        <v>317.57</v>
+        <v>316.84</v>
       </c>
       <c r="E273" s="19" t="n">
-        <v>0.2117</v>
+        <v>0.2089</v>
       </c>
       <c r="F273" s="19" t="n">
-        <v>0.3329</v>
+        <v>0.3298</v>
       </c>
       <c r="G273" s="16" t="n">
         <v>46267</v>
@@ -20481,7 +20481,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="19" t="n">
-        <v>0.007651856283654019</v>
+        <v>0.009973488195934936</v>
       </c>
       <c r="N273" s="13" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="15" t="n">
-        <v>-0.1183046257518027</v>
+        <v>-0.1162731978285569</v>
       </c>
       <c r="Q273" s="20" t="inlineStr">
         <is>
@@ -20533,13 +20533,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>402.82</v>
+        <v>400.82</v>
       </c>
       <c r="E274" s="23" t="n">
-        <v>-0.0892</v>
+        <v>-0.09369999999999999</v>
       </c>
       <c r="F274" s="23" t="n">
-        <v>-0.1334</v>
+        <v>-0.1377</v>
       </c>
       <c r="G274" s="6" t="n">
         <v>46260</v>
@@ -20568,7 +20568,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="5" t="n">
-        <v>0.3281366367111861</v>
+        <v>0.3347637343445936</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="8" t="n"/>
@@ -20612,13 +20612,13 @@
         </is>
       </c>
       <c r="D275" s="14" t="n">
-        <v>6.47</v>
+        <v>6.43</v>
       </c>
       <c r="E275" s="15" t="n">
-        <v>-0.0704</v>
+        <v>-0.0761</v>
       </c>
       <c r="F275" s="15" t="n">
-        <v>-0.1245</v>
+        <v>-0.1299</v>
       </c>
       <c r="G275" s="16" t="n">
         <v>46239</v>
@@ -20673,13 +20673,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>66.40000000000001</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>0.0726</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="F276" s="23" t="n">
-        <v>-0.0974</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="G276" s="6" t="n"/>
       <c r="H276" s="11" t="inlineStr">
@@ -20724,13 +20724,13 @@
         </is>
       </c>
       <c r="D277" s="14" t="n">
-        <v>101.64</v>
+        <v>100.12</v>
       </c>
       <c r="E277" s="15" t="n">
-        <v>-0.1817</v>
+        <v>-0.1939</v>
       </c>
       <c r="F277" s="15" t="n">
-        <v>-0.1722</v>
+        <v>-0.1846</v>
       </c>
       <c r="G277" s="16" t="n">
         <v>46240</v>
@@ -20785,13 +20785,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>216.9</v>
+        <v>218.02</v>
       </c>
       <c r="E278" s="5" t="n">
-        <v>0.0837</v>
+        <v>0.08929999999999999</v>
       </c>
       <c r="F278" s="5" t="n">
-        <v>0.02</v>
+        <v>0.0253</v>
       </c>
       <c r="G278" s="6" t="n">
         <v>46330</v>
@@ -20846,13 +20846,13 @@
         </is>
       </c>
       <c r="D279" s="14" t="n">
-        <v>395.46</v>
+        <v>389.39</v>
       </c>
       <c r="E279" s="19" t="n">
-        <v>0.042</v>
+        <v>0.026</v>
       </c>
       <c r="F279" s="19" t="n">
-        <v>0.1049</v>
+        <v>0.08789999999999999</v>
       </c>
       <c r="G279" s="16" t="n"/>
       <c r="H279" s="22" t="inlineStr">
@@ -20897,13 +20897,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>58.72</v>
+        <v>58.58</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>0.1191</v>
+        <v>0.1164</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="G280" s="6" t="n">
         <v>46239</v>
@@ -20958,13 +20958,13 @@
         </is>
       </c>
       <c r="D281" s="14" t="n">
-        <v>416.4</v>
+        <v>414</v>
       </c>
       <c r="E281" s="15" t="n">
-        <v>-0.07829999999999999</v>
-      </c>
-      <c r="F281" s="19" t="n">
-        <v>0.003</v>
+        <v>-0.08359999999999999</v>
+      </c>
+      <c r="F281" s="15" t="n">
+        <v>-0.0028</v>
       </c>
       <c r="G281" s="16" t="n">
         <v>46310</v>
@@ -21041,13 +21041,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>132.68</v>
+        <v>131.25</v>
       </c>
       <c r="E282" s="23" t="n">
-        <v>-0.1119</v>
+        <v>-0.1214</v>
       </c>
       <c r="F282" s="23" t="n">
-        <v>-0.2084</v>
+        <v>-0.217</v>
       </c>
       <c r="G282" s="6" t="n">
         <v>46239</v>
@@ -21102,13 +21102,13 @@
         </is>
       </c>
       <c r="D283" s="14" t="n">
-        <v>191.74</v>
+        <v>193.22</v>
       </c>
       <c r="E283" s="15" t="n">
-        <v>-0.08289999999999999</v>
+        <v>-0.0759</v>
       </c>
       <c r="F283" s="15" t="n">
-        <v>-0.1515</v>
+        <v>-0.145</v>
       </c>
       <c r="G283" s="16" t="n">
         <v>46240</v>
@@ -21163,13 +21163,13 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>278.99</v>
+        <v>277.72</v>
       </c>
       <c r="E284" s="23" t="n">
-        <v>-0.0808</v>
+        <v>-0.0849</v>
       </c>
       <c r="F284" s="23" t="n">
-        <v>-0.0213</v>
+        <v>-0.0257</v>
       </c>
       <c r="G284" s="6" t="n">
         <v>46315</v>
@@ -21198,7 +21198,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="5" t="n">
-        <v>0.07530735868669125</v>
+        <v>0.08022468673484075</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="5" t="n">
-        <v>0.1326570844833148</v>
+        <v>0.1378366700273656</v>
       </c>
       <c r="Q284" s="9" t="inlineStr">
         <is>
@@ -21266,13 +21266,13 @@
         </is>
       </c>
       <c r="D285" s="14" t="n">
-        <v>307.8</v>
+        <v>306.58</v>
       </c>
       <c r="E285" s="15" t="n">
-        <v>-0.0352</v>
+        <v>-0.039</v>
       </c>
       <c r="F285" s="15" t="n">
-        <v>-0.0137</v>
+        <v>-0.0176</v>
       </c>
       <c r="G285" s="16" t="n"/>
       <c r="H285" s="22" t="inlineStr">
@@ -21291,7 +21291,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="19" t="n">
-        <v>0.08836907082521113</v>
+        <v>0.09270011090090684</v>
       </c>
       <c r="N285" s="13" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="19" t="n">
-        <v>0.2183235867446393</v>
+        <v>0.2231717659338509</v>
       </c>
       <c r="Q285" s="20" t="inlineStr">
         <is>
@@ -21343,13 +21343,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>36.09</v>
+        <v>35.47</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>0.2172</v>
+        <v>0.1963</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>0.2372</v>
+        <v>0.216</v>
       </c>
       <c r="G286" s="6" t="n">
         <v>46240</v>
@@ -21404,13 +21404,13 @@
         </is>
       </c>
       <c r="D287" s="14" t="n">
-        <v>7.36</v>
+        <v>7.23</v>
       </c>
       <c r="E287" s="15" t="n">
-        <v>-0.0576</v>
+        <v>-0.07429999999999999</v>
       </c>
       <c r="F287" s="15" t="n">
-        <v>-0.1674</v>
+        <v>-0.1821</v>
       </c>
       <c r="G287" s="16" t="n">
         <v>46252</v>
@@ -21465,13 +21465,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>169.54</v>
+        <v>170.63</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>0.2286</v>
+        <v>0.2366</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>0.1751</v>
+        <v>0.1827</v>
       </c>
       <c r="G288" s="6" t="n">
         <v>46261</v>
@@ -21526,13 +21526,13 @@
         </is>
       </c>
       <c r="D289" s="14" t="n">
-        <v>548.49</v>
+        <v>519.17</v>
       </c>
       <c r="E289" s="15" t="n">
-        <v>-0.05019999999999999</v>
+        <v>-0.1009</v>
       </c>
       <c r="F289" s="19" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0146</v>
       </c>
       <c r="G289" s="16" t="n">
         <v>46239</v>
@@ -21561,7 +21561,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="19" t="n">
-        <v>0.3309267261025725</v>
+        <v>0.4060904905907508</v>
       </c>
       <c r="N289" s="13" t="inlineStr">
         <is>
@@ -21572,7 +21572,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="19" t="n">
-        <v>0.04833269521777971</v>
+        <v>0.1075370302598379</v>
       </c>
       <c r="Q289" s="20" t="inlineStr">
         <is>
@@ -21613,13 +21613,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>25.47</v>
+        <v>25.19</v>
       </c>
       <c r="E290" s="23" t="n">
-        <v>-0.3547</v>
+        <v>-0.3618</v>
       </c>
       <c r="F290" s="23" t="n">
-        <v>-0.5374</v>
+        <v>-0.5425</v>
       </c>
       <c r="G290" s="6" t="n"/>
       <c r="H290" s="11" t="inlineStr">
@@ -21664,13 +21664,13 @@
         </is>
       </c>
       <c r="D291" s="14" t="n">
-        <v>99.5</v>
+        <v>100.64</v>
       </c>
       <c r="E291" s="19" t="n">
-        <v>0.1711</v>
+        <v>0.1846</v>
       </c>
       <c r="F291" s="15" t="n">
-        <v>-0.0209</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="G291" s="16" t="n">
         <v>46259</v>
@@ -21725,13 +21725,13 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>162.13</v>
+        <v>161.65</v>
       </c>
       <c r="E292" s="5" t="n">
-        <v>0.07780000000000001</v>
+        <v>0.0747</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>0.2397</v>
+        <v>0.236</v>
       </c>
       <c r="G292" s="6" t="n">
         <v>46266</v>
@@ -21786,13 +21786,13 @@
         </is>
       </c>
       <c r="D293" s="14" t="n">
-        <v>294.83</v>
+        <v>295.09</v>
       </c>
       <c r="E293" s="15" t="n">
-        <v>-0.0454</v>
+        <v>-0.0446</v>
       </c>
       <c r="F293" s="19" t="n">
-        <v>0.0442</v>
+        <v>0.0451</v>
       </c>
       <c r="G293" s="16" t="n"/>
       <c r="H293" s="22" t="inlineStr">
@@ -21837,13 +21837,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>89.17</v>
+        <v>89.38</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.06860000000000001</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>0.078</v>
+        <v>0.0805</v>
       </c>
       <c r="G294" s="6" t="n">
         <v>46252</v>
@@ -21898,13 +21898,13 @@
         </is>
       </c>
       <c r="D295" s="14" t="n">
-        <v>145.76</v>
+        <v>147.37</v>
       </c>
       <c r="E295" s="19" t="n">
-        <v>0.0334</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="F295" s="19" t="n">
-        <v>0.0371</v>
+        <v>0.04849999999999999</v>
       </c>
       <c r="G295" s="16" t="n"/>
       <c r="H295" s="22" t="inlineStr">
@@ -21923,7 +21923,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="19" t="n">
-        <v>0.1388583973655325</v>
+        <v>0.1264165026803284</v>
       </c>
       <c r="N295" s="13" t="inlineStr"/>
       <c r="O295" s="18" t="n"/>
@@ -21971,13 +21971,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>29.55</v>
+        <v>29.67</v>
       </c>
       <c r="E296" s="5" t="n">
-        <v>0.081</v>
+        <v>0.08560000000000001</v>
       </c>
       <c r="F296" s="23" t="n">
-        <v>-0.1303</v>
+        <v>-0.1266</v>
       </c>
       <c r="G296" s="6" t="n">
         <v>46317</v>
@@ -22032,13 +22032,13 @@
         </is>
       </c>
       <c r="D297" s="14" t="n">
-        <v>283.22</v>
-      </c>
-      <c r="E297" s="15" t="n">
-        <v>-0.0018</v>
+        <v>285.47</v>
+      </c>
+      <c r="E297" s="19" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F297" s="19" t="n">
-        <v>0.09789999999999999</v>
+        <v>0.1066</v>
       </c>
       <c r="G297" s="16" t="n"/>
       <c r="H297" s="22" t="inlineStr">
@@ -22057,7 +22057,7 @@
         <v>275</v>
       </c>
       <c r="M297" s="15" t="n">
-        <v>-0.02902337405550465</v>
+        <v>-0.03667635828633491</v>
       </c>
       <c r="N297" s="13" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="19" t="n">
-        <v>0.1016171174352093</v>
+        <v>0.09293445896241276</v>
       </c>
       <c r="Q297" s="20" t="inlineStr">
         <is>
@@ -22121,13 +22121,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>38.38</v>
+        <v>38.34</v>
       </c>
       <c r="E298" s="23" t="n">
-        <v>-0.0931</v>
+        <v>-0.094</v>
       </c>
       <c r="F298" s="23" t="n">
-        <v>-0.0366</v>
+        <v>-0.0377</v>
       </c>
       <c r="G298" s="6" t="n"/>
       <c r="H298" s="11" t="inlineStr">
@@ -22176,13 +22176,13 @@
         </is>
       </c>
       <c r="D299" s="14" t="n">
-        <v>69.28</v>
+        <v>69.39</v>
       </c>
       <c r="E299" s="19" t="n">
-        <v>0.1357</v>
+        <v>0.1375</v>
       </c>
       <c r="F299" s="19" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.095</v>
       </c>
       <c r="G299" s="16" t="n">
         <v>46310</v>
@@ -22237,13 +22237,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>489.89</v>
+        <v>491.05</v>
       </c>
       <c r="E300" s="23" t="n">
-        <v>-0.09369999999999999</v>
+        <v>-0.0915</v>
       </c>
       <c r="F300" s="23" t="n">
-        <v>-0.0354</v>
+        <v>-0.0332</v>
       </c>
       <c r="G300" s="6" t="n"/>
       <c r="H300" s="11" t="inlineStr">
@@ -22262,7 +22262,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="5" t="n">
-        <v>0.1635265059503154</v>
+        <v>0.1607779248549027</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="5" t="n">
-        <v>0.07166915021739577</v>
+        <v>0.06913756236635778</v>
       </c>
       <c r="Q300" s="9" t="inlineStr">
         <is>
@@ -22326,13 +22326,13 @@
         </is>
       </c>
       <c r="D301" s="14" t="n">
-        <v>553.58</v>
+        <v>553.37</v>
       </c>
       <c r="E301" s="15" t="n">
-        <v>-0.08539999999999999</v>
+        <v>-0.0858</v>
       </c>
       <c r="F301" s="15" t="n">
-        <v>-0.0386</v>
+        <v>-0.039</v>
       </c>
       <c r="G301" s="16" t="n"/>
       <c r="H301" s="22" t="inlineStr">
@@ -22351,7 +22351,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="19" t="n">
-        <v>0.1127569637631416</v>
+        <v>0.1131792471583208</v>
       </c>
       <c r="N301" s="13" t="inlineStr"/>
       <c r="O301" s="18" t="n"/>
@@ -22395,13 +22395,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>274</v>
+        <v>274.74</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>0.2237</v>
+        <v>0.227</v>
       </c>
       <c r="F302" s="5" t="n">
-        <v>0.0771</v>
+        <v>0.08</v>
       </c>
       <c r="G302" s="6" t="n"/>
       <c r="H302" s="11" t="inlineStr">
@@ -22420,7 +22420,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="5" t="n">
-        <v>0.03284671532846715</v>
+        <v>0.0300647885273349</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="8" t="n"/>
@@ -22466,13 +22466,13 @@
         </is>
       </c>
       <c r="D303" s="14" t="n">
-        <v>257.12</v>
+        <v>256.01</v>
       </c>
       <c r="E303" s="19" t="n">
-        <v>0.0877</v>
+        <v>0.083</v>
       </c>
       <c r="F303" s="19" t="n">
-        <v>0.1539</v>
+        <v>0.149</v>
       </c>
       <c r="G303" s="16" t="n">
         <v>46321</v>
@@ -22501,7 +22501,7 @@
         <v>246</v>
       </c>
       <c r="M303" s="15" t="n">
-        <v>-0.04324828873677662</v>
+        <v>-0.03910003515487673</v>
       </c>
       <c r="N303" s="13" t="inlineStr"/>
       <c r="O303" s="18" t="n"/>
@@ -22549,13 +22549,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>118.38</v>
+        <v>119.13</v>
       </c>
       <c r="E304" s="23" t="n">
-        <v>-0.0457</v>
+        <v>-0.0396</v>
       </c>
       <c r="F304" s="5" t="n">
-        <v>0.04019999999999999</v>
+        <v>0.04679999999999999</v>
       </c>
       <c r="G304" s="6" t="n"/>
       <c r="H304" s="11" t="inlineStr">
@@ -22574,7 +22574,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="5" t="n">
-        <v>0.09815847271498568</v>
+        <v>0.09124485855787799</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="5" t="n">
-        <v>0.08126372698090897</v>
+        <v>0.07445647611852602</v>
       </c>
       <c r="Q304" s="9" t="inlineStr">
         <is>
@@ -22634,13 +22634,13 @@
         </is>
       </c>
       <c r="D305" s="14" t="n">
-        <v>115.44</v>
+        <v>116.72</v>
       </c>
       <c r="E305" s="19" t="n">
-        <v>0.0463</v>
+        <v>0.0579</v>
       </c>
       <c r="F305" s="19" t="n">
-        <v>0.0998</v>
+        <v>0.112</v>
       </c>
       <c r="G305" s="16" t="n">
         <v>46302</v>
@@ -22669,7 +22669,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="19" t="n">
-        <v>0.1694386694386694</v>
+        <v>0.156614119259767</v>
       </c>
       <c r="N305" s="13" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="19" t="n">
-        <v>0.08281358281358284</v>
+        <v>0.07093899931459906</v>
       </c>
       <c r="Q305" s="20" t="inlineStr"/>
       <c r="R305" s="18" t="n"/>
@@ -22715,13 +22715,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>365.39</v>
+        <v>369.68</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>0.0466</v>
+        <v>0.05889999999999999</v>
       </c>
       <c r="F306" s="5" t="n">
-        <v>0.1968</v>
+        <v>0.2109</v>
       </c>
       <c r="G306" s="6" t="n"/>
       <c r="H306" s="11" t="inlineStr">
@@ -22740,7 +22740,7 @@
         <v>350</v>
       </c>
       <c r="M306" s="23" t="n">
-        <v>-0.04211937929335775</v>
+        <v>-0.05323523046959534</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -22751,7 +22751,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="5" t="n">
-        <v>0.09472070937901972</v>
+        <v>0.08201687946331961</v>
       </c>
       <c r="Q306" s="9" t="inlineStr">
         <is>
@@ -22792,13 +22792,13 @@
         </is>
       </c>
       <c r="D307" s="14" t="n">
-        <v>84.54000000000001</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="E307" s="19" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.07730000000000001</v>
       </c>
       <c r="F307" s="19" t="n">
-        <v>0.1713</v>
+        <v>0.1603</v>
       </c>
       <c r="G307" s="16" t="n">
         <v>46260</v>
@@ -22849,13 +22849,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>57.27</v>
+        <v>56.91</v>
       </c>
       <c r="E308" s="23" t="n">
-        <v>-0.3114</v>
+        <v>-0.3157</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>0.018</v>
+        <v>0.0116</v>
       </c>
       <c r="G308" s="6" t="n">
         <v>46245</v>
@@ -22910,13 +22910,13 @@
         </is>
       </c>
       <c r="D309" s="14" t="n">
-        <v>75.61</v>
+        <v>76.08</v>
       </c>
       <c r="E309" s="15" t="n">
-        <v>-0.0202</v>
+        <v>-0.0141</v>
       </c>
       <c r="F309" s="19" t="n">
-        <v>0.03</v>
+        <v>0.0364</v>
       </c>
       <c r="G309" s="16" t="n"/>
       <c r="H309" s="22" t="inlineStr">
@@ -22935,14 +22935,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="19" t="n">
-        <v>0.09773839439227616</v>
+        <v>0.09095688748685597</v>
       </c>
       <c r="N309" s="13" t="inlineStr"/>
       <c r="O309" s="18" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="19" t="n">
-        <v>0.1506414495437112</v>
+        <v>0.1435331230283912</v>
       </c>
       <c r="Q309" s="20" t="inlineStr"/>
       <c r="R309" s="18" t="n"/>
@@ -22977,13 +22977,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>166.08</v>
+        <v>168.07</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>0.0245</v>
+        <v>0.0368</v>
       </c>
       <c r="F310" s="23" t="n">
-        <v>-0.1444</v>
+        <v>-0.1342</v>
       </c>
       <c r="G310" s="6" t="n"/>
       <c r="H310" s="11" t="inlineStr">
@@ -23002,7 +23002,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="5" t="n">
-        <v>0.2042389210019267</v>
+        <v>0.1899803653239722</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="8" t="n"/>
@@ -23050,13 +23050,13 @@
         </is>
       </c>
       <c r="D311" s="14" t="n">
-        <v>150.54</v>
+        <v>151.16</v>
       </c>
       <c r="E311" s="19" t="n">
-        <v>0.0711</v>
+        <v>0.0755</v>
       </c>
       <c r="F311" s="19" t="n">
-        <v>0.1498</v>
+        <v>0.1545</v>
       </c>
       <c r="G311" s="16" t="n"/>
       <c r="H311" s="22" t="inlineStr">
@@ -23105,13 +23105,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>193.69</v>
+        <v>194.93</v>
       </c>
       <c r="E312" s="5" t="n">
-        <v>0.1151</v>
+        <v>0.1222</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>0.0369</v>
+        <v>0.0436</v>
       </c>
       <c r="G312" s="6" t="n">
         <v>46317</v>
@@ -23140,7 +23140,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="5" t="n">
-        <v>0.1358356136093758</v>
+        <v>0.1286102703534602</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="5" t="n">
-        <v>0.1874645051370747</v>
+        <v>0.1799107371877084</v>
       </c>
       <c r="Q312" s="9" t="inlineStr">
         <is>
@@ -23192,13 +23192,13 @@
         </is>
       </c>
       <c r="D313" s="14" t="n">
-        <v>1049.05</v>
+        <v>1056.2</v>
       </c>
       <c r="E313" s="19" t="n">
-        <v>0.0503</v>
+        <v>0.0574</v>
       </c>
       <c r="F313" s="15" t="n">
-        <v>-0.0295</v>
+        <v>-0.0229</v>
       </c>
       <c r="G313" s="16" t="n"/>
       <c r="H313" s="22" t="inlineStr">
@@ -23217,7 +23217,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="19" t="n">
-        <v>0.1438920928459083</v>
+        <v>0.1361484567316796</v>
       </c>
       <c r="N313" s="13" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="19" t="n">
-        <v>0.1820218292741052</v>
+        <v>0.1740200719560689</v>
       </c>
       <c r="Q313" s="20" t="inlineStr">
         <is>
@@ -23273,13 +23273,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>122.03</v>
+        <v>121.83</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>0.0122</v>
+        <v>0.0105</v>
       </c>
       <c r="F314" s="23" t="n">
-        <v>-0.0043</v>
+        <v>-0.006</v>
       </c>
       <c r="G314" s="6" t="n"/>
       <c r="H314" s="11" t="inlineStr">
@@ -23298,7 +23298,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="5" t="n">
-        <v>0.05711710235188067</v>
+        <v>0.05885249938438809</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -23308,8 +23308,8 @@
       <c r="O314" s="8" t="n">
         <v>122</v>
       </c>
-      <c r="P314" s="23" t="n">
-        <v>-0.00024584118659347</v>
+      <c r="P314" s="5" t="n">
+        <v>0.001395387014692619</v>
       </c>
       <c r="Q314" s="9" t="inlineStr">
         <is>
@@ -23350,13 +23350,13 @@
         </is>
       </c>
       <c r="D315" s="14" t="n">
-        <v>62.38</v>
+        <v>62.7</v>
       </c>
       <c r="E315" s="15" t="n">
-        <v>-0.0128</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F315" s="19" t="n">
-        <v>0.0253</v>
+        <v>0.0306</v>
       </c>
       <c r="G315" s="16" t="n">
         <v>46239</v>
@@ -23385,14 +23385,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="19" t="n">
-        <v>0.04200064123116379</v>
+        <v>0.036682615629984</v>
       </c>
       <c r="N315" s="13" t="inlineStr"/>
       <c r="O315" s="18" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="19" t="n">
-        <v>0.07406219942289191</v>
+        <v>0.06858054226475274</v>
       </c>
       <c r="Q315" s="20" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>0.004</v>
       </c>
       <c r="F316" s="23" t="n">
-        <v>-0.0261</v>
+        <v>-0.0262</v>
       </c>
       <c r="G316" s="6" t="n">
         <v>46309</v>
@@ -23512,13 +23512,13 @@
         </is>
       </c>
       <c r="D317" s="14" t="n">
-        <v>326.21</v>
+        <v>327.34</v>
       </c>
       <c r="E317" s="19" t="n">
-        <v>0.0068</v>
+        <v>0.0103</v>
       </c>
       <c r="F317" s="19" t="n">
-        <v>0.0534</v>
+        <v>0.057</v>
       </c>
       <c r="G317" s="16" t="n"/>
       <c r="H317" s="22" t="inlineStr">
@@ -23544,7 +23544,7 @@
         <v>316</v>
       </c>
       <c r="P317" s="15" t="n">
-        <v>-0.03129885656478949</v>
+        <v>-0.03464287896376848</v>
       </c>
       <c r="Q317" s="20" t="inlineStr">
         <is>
@@ -23585,13 +23585,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>224.48</v>
+        <v>224.81</v>
       </c>
       <c r="E318" s="23" t="n">
-        <v>-0.0023</v>
+        <v>-0.0008</v>
       </c>
       <c r="F318" s="5" t="n">
-        <v>0.0674</v>
+        <v>0.0689</v>
       </c>
       <c r="G318" s="6" t="n">
         <v>46244</v>
@@ -23627,7 +23627,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="23" t="n">
-        <v>-0.04223093371347109</v>
+        <v>-0.04363684889462213</v>
       </c>
       <c r="Q318" s="9" t="inlineStr">
         <is>
@@ -23668,13 +23668,13 @@
         </is>
       </c>
       <c r="D319" s="14" t="n">
-        <v>120.01</v>
+        <v>120.86</v>
       </c>
       <c r="E319" s="15" t="n">
-        <v>-0.0177</v>
+        <v>-0.0108</v>
       </c>
       <c r="F319" s="15" t="n">
-        <v>-0.0297</v>
+        <v>-0.0229</v>
       </c>
       <c r="G319" s="16" t="n"/>
       <c r="H319" s="22" t="inlineStr">
@@ -23693,7 +23693,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="19" t="n">
-        <v>0.18323473043913</v>
+        <v>0.1749131226212146</v>
       </c>
       <c r="N319" s="13" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="19" t="n">
-        <v>0.1415715357053578</v>
+        <v>0.1335429422472282</v>
       </c>
       <c r="Q319" s="20" t="inlineStr">
         <is>
@@ -23753,13 +23753,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>236.17</v>
+        <v>237.25</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>0.015</v>
+        <v>0.0196</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>0.1413</v>
+        <v>0.1465</v>
       </c>
       <c r="G320" s="6" t="n"/>
       <c r="H320" s="11" t="inlineStr">
@@ -23777,8 +23777,8 @@
       <c r="L320" s="8" t="n">
         <v>237</v>
       </c>
-      <c r="M320" s="5" t="n">
-        <v>0.003514417580556432</v>
+      <c r="M320" s="23" t="n">
+        <v>-0.001053740779768177</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>236</v>
       </c>
       <c r="P320" s="23" t="n">
-        <v>-0.0007198204683066753</v>
+        <v>-0.005268703898840885</v>
       </c>
       <c r="Q320" s="9" t="inlineStr">
         <is>
@@ -23830,13 +23830,13 @@
         </is>
       </c>
       <c r="D321" s="14" t="n">
-        <v>171.17</v>
+        <v>172.2</v>
       </c>
       <c r="E321" s="15" t="n">
-        <v>-0.0153</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F321" s="19" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.0115</v>
       </c>
       <c r="G321" s="16" t="n">
         <v>46239</v>
@@ -23865,7 +23865,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="19" t="n">
-        <v>0.1684290471461121</v>
+        <v>0.1614401858304298</v>
       </c>
       <c r="N321" s="13" t="inlineStr"/>
       <c r="O321" s="18" t="n"/>
@@ -23909,13 +23909,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>133.23</v>
+        <v>134.16</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.008</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>0.0704</v>
+        <v>0.0779</v>
       </c>
       <c r="G322" s="6" t="n"/>
       <c r="H322" s="11" t="inlineStr">
@@ -23934,7 +23934,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="23" t="n">
-        <v>-0.01673797192824432</v>
+        <v>-0.02355396541443051</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="8" t="n"/>
@@ -23978,13 +23978,13 @@
         </is>
       </c>
       <c r="D323" s="14" t="n">
-        <v>33.13</v>
+        <v>33.3</v>
       </c>
       <c r="E323" s="15" t="n">
-        <v>-0.0953</v>
+        <v>-0.0907</v>
       </c>
       <c r="F323" s="15" t="n">
-        <v>-0.1444</v>
+        <v>-0.14</v>
       </c>
       <c r="G323" s="16" t="n"/>
       <c r="H323" s="22" t="inlineStr">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="D324" s="4" t="n">
-        <v>39.39</v>
+        <v>39.65</v>
       </c>
       <c r="E324" s="5" t="n">
-        <v>0.0557</v>
+        <v>0.06269999999999999</v>
       </c>
       <c r="F324" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0219</v>
       </c>
       <c r="G324" s="6" t="n"/>
       <c r="H324" s="11" t="inlineStr">
@@ -24098,13 +24098,13 @@
         </is>
       </c>
       <c r="D325" s="14" t="n">
-        <v>264.86</v>
+        <v>265.12</v>
       </c>
       <c r="E325" s="19" t="n">
-        <v>0.07730000000000001</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="F325" s="19" t="n">
-        <v>0.0394</v>
+        <v>0.0404</v>
       </c>
       <c r="G325" s="16" t="n">
         <v>46240</v>
@@ -24133,7 +24133,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="19" t="n">
-        <v>0.4498225477610813</v>
+        <v>0.4484007242003621</v>
       </c>
       <c r="N325" s="13" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="19" t="n">
-        <v>0.4347202295552366</v>
+        <v>0.4333132166566083</v>
       </c>
       <c r="Q325" s="20" t="inlineStr"/>
       <c r="R325" s="18" t="n"/>
@@ -24187,13 +24187,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>71.09999999999999</v>
+        <v>71.59</v>
       </c>
       <c r="E326" s="23" t="n">
-        <v>-0.068</v>
+        <v>-0.0616</v>
       </c>
       <c r="F326" s="23" t="n">
-        <v>-0.013</v>
+        <v>-0.0062</v>
       </c>
       <c r="G326" s="6" t="n"/>
       <c r="H326" s="11" t="inlineStr">
@@ -24212,7 +24212,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="5" t="n">
-        <v>0.1111111111111112</v>
+        <v>0.1035060762676351</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="8" t="n"/>
@@ -24264,13 +24264,13 @@
         </is>
       </c>
       <c r="D327" s="14" t="n">
-        <v>122.8</v>
+        <v>123.34</v>
       </c>
       <c r="E327" s="15" t="n">
-        <v>-0.0252</v>
+        <v>-0.0209</v>
       </c>
       <c r="F327" s="15" t="n">
-        <v>-0.0114</v>
+        <v>-0.0071</v>
       </c>
       <c r="G327" s="16" t="n"/>
       <c r="H327" s="22" t="inlineStr">
@@ -24289,7 +24289,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="19" t="n">
-        <v>0.1074918566775244</v>
+        <v>0.1026431003729528</v>
       </c>
       <c r="N327" s="13" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="19" t="n">
-        <v>0.1400651465798046</v>
+        <v>0.1350737797956867</v>
       </c>
       <c r="Q327" s="20" t="inlineStr">
         <is>
@@ -24341,13 +24341,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>107.07</v>
+        <v>106.86</v>
       </c>
       <c r="E328" s="23" t="n">
-        <v>-0.0594</v>
+        <v>-0.0612</v>
       </c>
       <c r="F328" s="23" t="n">
-        <v>-0.0331</v>
+        <v>-0.035</v>
       </c>
       <c r="G328" s="6" t="n"/>
       <c r="H328" s="11" t="inlineStr">
@@ -24366,7 +24366,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="5" t="n">
-        <v>0.2234986457457739</v>
+        <v>0.225903050720569</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -24377,7 +24377,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="5" t="n">
-        <v>0.1301018025590736</v>
+        <v>0.1323226651693805</v>
       </c>
       <c r="Q328" s="9" t="inlineStr">
         <is>
@@ -24422,13 +24422,13 @@
         </is>
       </c>
       <c r="D329" s="14" t="n">
-        <v>85.61</v>
+        <v>85.91</v>
       </c>
       <c r="E329" s="15" t="n">
-        <v>-0.0209</v>
-      </c>
-      <c r="F329" s="15" t="n">
-        <v>-0.0027</v>
+        <v>-0.0175</v>
+      </c>
+      <c r="F329" s="19" t="n">
+        <v>0.0008</v>
       </c>
       <c r="G329" s="16" t="n">
         <v>46318</v>
@@ -24464,7 +24464,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="19" t="n">
-        <v>0.2498539890199743</v>
+        <v>0.2454894657199395</v>
       </c>
       <c r="Q329" s="20" t="inlineStr">
         <is>
@@ -24513,13 +24513,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>55.89</v>
+        <v>55.4</v>
       </c>
       <c r="E330" s="23" t="n">
-        <v>-0.0066</v>
-      </c>
-      <c r="F330" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0153</v>
+      </c>
+      <c r="F330" s="23" t="n">
+        <v>-0.0002</v>
       </c>
       <c r="G330" s="6" t="n"/>
       <c r="H330" s="11" t="inlineStr">
@@ -24538,7 +24538,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="5" t="n">
-        <v>0.1272141706924315</v>
+        <v>0.1371841155234657</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="8" t="n"/>
@@ -24582,13 +24582,13 @@
         </is>
       </c>
       <c r="D331" s="14" t="n">
-        <v>43.37</v>
+        <v>42.99</v>
       </c>
       <c r="E331" s="15" t="n">
-        <v>-0.1635</v>
+        <v>-0.1707</v>
       </c>
       <c r="F331" s="15" t="n">
-        <v>-0.2535</v>
+        <v>-0.2599</v>
       </c>
       <c r="G331" s="16" t="n">
         <v>46241</v>
@@ -24643,13 +24643,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>9.390000000000001</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E332" s="23" t="n">
-        <v>-0.0229</v>
+        <v>-0.0239</v>
       </c>
       <c r="F332" s="23" t="n">
-        <v>-0.1057</v>
+        <v>-0.1067</v>
       </c>
       <c r="G332" s="6" t="n">
         <v>46239</v>
@@ -24704,13 +24704,13 @@
         </is>
       </c>
       <c r="D333" s="14" t="n">
-        <v>92.31999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="E333" s="15" t="n">
-        <v>-0.0382</v>
-      </c>
-      <c r="F333" s="15" t="n">
-        <v>-0.003</v>
+        <v>-0.0301</v>
+      </c>
+      <c r="F333" s="19" t="n">
+        <v>0.0054</v>
       </c>
       <c r="G333" s="16" t="n"/>
       <c r="H333" s="22" t="inlineStr">
@@ -24729,7 +24729,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="19" t="n">
-        <v>0.07235701906412487</v>
+        <v>0.06337271750805593</v>
       </c>
       <c r="N333" s="13" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="19" t="n">
-        <v>0.2131715771230503</v>
+        <v>0.2030075187969926</v>
       </c>
       <c r="Q333" s="20" t="inlineStr">
         <is>
@@ -24781,13 +24781,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>108</v>
+        <v>108.26</v>
       </c>
       <c r="E334" s="23" t="n">
-        <v>-0.07400000000000001</v>
+        <v>-0.0718</v>
       </c>
       <c r="F334" s="23" t="n">
-        <v>-0.04389999999999999</v>
+        <v>-0.0415</v>
       </c>
       <c r="G334" s="6" t="n"/>
       <c r="H334" s="11" t="inlineStr">
@@ -24806,7 +24806,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="5" t="n">
-        <v>0.1759259259259259</v>
+        <v>0.1731017919822649</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="8" t="n"/>
@@ -34095,7 +34095,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of August 05, 2026 at 16:25 UTC</t>
+          <t>Data as of August 05, 2026 at 22:02 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>104.94</v>
+        <v>104.91</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.0852</v>
+        <v>0.0849</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.0614</v>
+        <v>0.0611</v>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="7" t="inlineStr">
@@ -868,7 +868,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>0.1911568515342101</v>
+        <v>0.1914974740253551</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.37221269296741</v>
+        <v>0.3726050900772091</v>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="D3" s="13" t="n">
-        <v>356.06</v>
+        <v>354.3</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>-0.0162</v>
+        <v>-0.0211</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>-0.02</v>
+        <v>-0.0248</v>
       </c>
       <c r="G3" s="15" t="n">
         <v>46322</v>
@@ -963,7 +963,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="18" t="n">
-        <v>0.2301297534123462</v>
+        <v>0.2362404741744284</v>
       </c>
       <c r="N3" s="12" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="18" t="n">
-        <v>0.1795764758748525</v>
+        <v>0.1854360711261642</v>
       </c>
       <c r="Q3" s="19" t="inlineStr">
         <is>
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>593.79</v>
+        <v>592.1</v>
       </c>
       <c r="E4" s="22" t="n">
-        <v>-0.0155</v>
+        <v>-0.0183</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.0143</v>
+        <v>0.0115</v>
       </c>
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="7" t="inlineStr">
@@ -1044,7 +1044,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.4062210545815862</v>
+        <v>0.4102347576422901</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.5662102763603295</v>
+        <v>0.5706806282722513</v>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>37.44</v>
+        <v>37.26</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>-0.024</v>
+        <v>-0.0287</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>0.0951</v>
+        <v>0.0898</v>
       </c>
       <c r="G5" s="15" t="n"/>
       <c r="H5" s="21" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>74.23999999999999</v>
+        <v>74.14</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>-0.0179</v>
+        <v>-0.0192</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>-0.1017</v>
+        <v>-0.1029</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>46315</v>
@@ -1190,7 +1190,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.0775862068965518</v>
+        <v>0.07903965470731049</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0.3469827586206897</v>
+        <v>0.3487995683841381</v>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
@@ -1242,13 +1242,13 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>85.04000000000001</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>0.0819</v>
+        <v>0.08470000000000001</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>0.1328</v>
+        <v>0.1357</v>
       </c>
       <c r="G7" s="15" t="n"/>
       <c r="H7" s="21" t="inlineStr">
@@ -1267,7 +1267,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="18" t="n">
-        <v>0.07008466603951075</v>
+        <v>0.0673234811165845</v>
       </c>
       <c r="N7" s="12" t="inlineStr"/>
       <c r="O7" s="17" t="n"/>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>483.36</v>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>-0.0038</v>
+        <v>488.46</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.0067</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>-0.0393</v>
+        <v>-0.0292</v>
       </c>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="7" t="inlineStr">
@@ -1336,7 +1336,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.1791004634227076</v>
+        <v>0.1667895016992179</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.3406984442237668</v>
+        <v>0.326700241575564</v>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
@@ -1388,13 +1388,13 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>188.03</v>
+        <v>186.48</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>-0.0253</v>
+        <v>-0.0333</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>-0.07200000000000001</v>
+        <v>-0.0796</v>
       </c>
       <c r="G9" s="15" t="n"/>
       <c r="H9" s="21" t="inlineStr">
@@ -1447,13 +1447,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>179.35</v>
+        <v>177.19</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>-0.0044</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0.0052</v>
+        <v>-0.0164</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>46317</v>
@@ -1482,7 +1482,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="22" t="n">
-        <v>-0.05213270142180092</v>
+        <v>-0.04057791071730909</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.5054362977418456</v>
+        <v>0.523788024154862</v>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
@@ -1534,13 +1534,13 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>46.68</v>
+        <v>47.05</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>0.09960000000000001</v>
+        <v>0.1084</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>0.0273</v>
+        <v>0.0354</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>46316</v>
@@ -1569,7 +1569,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>-0.07883461868037703</v>
+        <v>-0.08607863974495213</v>
       </c>
       <c r="N11" s="12" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="18" t="n">
-        <v>0.07112253641816624</v>
+        <v>0.06269925611052078</v>
       </c>
       <c r="Q11" s="19" t="inlineStr">
         <is>
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>175.63</v>
+        <v>178.07</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.2286</v>
+        <v>0.2457</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.3064</v>
+        <v>0.3246</v>
       </c>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="7" t="inlineStr">
@@ -1650,7 +1650,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.03057564197460573</v>
+        <v>0.0164542034031561</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="22" t="n">
-        <v>-0.1174628480327962</v>
+        <v>-0.1295557926658056</v>
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
@@ -1702,13 +1702,13 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>276.45</v>
+        <v>274.48</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>0.1348</v>
+        <v>0.1267</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>0.1274</v>
+        <v>0.1193</v>
       </c>
       <c r="G13" s="15" t="n"/>
       <c r="H13" s="21" t="inlineStr">
@@ -1727,7 +1727,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>0.1647675890757823</v>
+        <v>0.1731273681142523</v>
       </c>
       <c r="N13" s="12" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="18" t="n">
-        <v>0.03092783505154643</v>
+        <v>0.03832701836199352</v>
       </c>
       <c r="Q13" s="19" t="inlineStr">
         <is>
@@ -1791,13 +1791,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3067.65</v>
-      </c>
-      <c r="E14" s="22" t="n">
-        <v>-0.0008</v>
-      </c>
-      <c r="F14" s="22" t="n">
-        <v>-0.0021</v>
+        <v>3126.83</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.0172</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>46287</v>
@@ -1826,7 +1826,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0.3528270826202467</v>
+        <v>0.3272227783410036</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0.2061349893240754</v>
+        <v>0.1833070553883646</v>
       </c>
       <c r="Q14" s="9" t="inlineStr">
         <is>
@@ -1878,13 +1878,13 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>81.56</v>
+        <v>81.98</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0.0447</v>
+        <v>0.0501</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>0.09960000000000001</v>
+        <v>0.1053</v>
       </c>
       <c r="G15" s="15" t="n">
         <v>46261</v>
@@ -1913,7 +1913,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>-0.2030407062285434</v>
+        <v>-0.2071236887045621</v>
       </c>
       <c r="N15" s="12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="18" t="n">
-        <v>0.04217753800882783</v>
+        <v>0.03683825323249568</v>
       </c>
       <c r="Q15" s="19" t="inlineStr"/>
       <c r="R15" s="17" t="n"/>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>215.6</v>
+        <v>214.42</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.237</v>
+        <v>0.2302</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.3284</v>
+        <v>0.3211</v>
       </c>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="7" t="inlineStr">
@@ -1984,7 +1984,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="22" t="n">
-        <v>-0.00742115027829311</v>
+        <v>-0.001958772502565001</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.1426172931629513</v>
       </c>
       <c r="Q16" s="9" t="inlineStr">
         <is>
@@ -2044,13 +2044,13 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>368.38</v>
+        <v>368.88</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>0.1615</v>
+        <v>0.1631</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>0.1732</v>
+        <v>0.1748</v>
       </c>
       <c r="G17" s="15" t="n">
         <v>46261</v>
@@ -2079,7 +2079,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>0.01797057386394485</v>
+        <v>0.01659076122316202</v>
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="18" t="n">
-        <v>0.01797057386394485</v>
+        <v>0.01659076122316202</v>
       </c>
       <c r="Q17" s="19" t="inlineStr"/>
       <c r="R17" s="17" t="n"/>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>33.21</v>
+        <v>32.81</v>
       </c>
       <c r="E18" s="22" t="n">
-        <v>-0.0067</v>
+        <v>-0.0186</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.1344</v>
+        <v>0.1209</v>
       </c>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="7" t="inlineStr">
@@ -2154,7 +2154,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.3550135501355013</v>
+        <v>0.3715330691862236</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.3550135501355013</v>
+        <v>0.3715330691862236</v>
       </c>
       <c r="Q18" s="9" t="inlineStr">
         <is>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>150.24</v>
+        <v>151.07</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>0.0116</v>
+        <v>0.0172</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>0.0413</v>
+        <v>0.047</v>
       </c>
       <c r="G19" s="15" t="n">
         <v>46324</v>
@@ -2241,7 +2241,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="18" t="n">
-        <v>0.1315228966986155</v>
+        <v>0.1253061494671345</v>
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="18" t="n">
-        <v>0.1781150159744408</v>
+        <v>0.1716422850334283</v>
       </c>
       <c r="Q19" s="19" t="inlineStr">
         <is>
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>201.43</v>
+        <v>208.9</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>-0.064</v>
+        <v>-0.0293</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>-0.05599999999999999</v>
+        <v>-0.021</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>46259</v>
@@ -2328,7 +2328,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0.09219083552598914</v>
+        <v>0.05313547151747244</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="8" t="n"/>
@@ -2372,13 +2372,13 @@
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>129.76</v>
+        <v>130.9</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>0.0498</v>
+        <v>0.059</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>0.2049</v>
+        <v>0.2155</v>
       </c>
       <c r="G21" s="15" t="n">
         <v>46267</v>
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>86.92</v>
+        <v>87.59</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.1401</v>
+        <v>0.1489</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.03759999999999999</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>46315</v>
@@ -2468,7 +2468,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="22" t="n">
-        <v>-0.2982052462034054</v>
+        <v>-0.3035734672907867</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.150483202945237</v>
+        <v>0.1416828405069071</v>
       </c>
       <c r="Q22" s="9" t="inlineStr">
         <is>
@@ -2520,13 +2520,13 @@
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>134.71</v>
+        <v>135.65</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>0.08</v>
+        <v>0.0876</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>0.3878</v>
+        <v>0.3975</v>
       </c>
       <c r="G23" s="15" t="n">
         <v>46315</v>
@@ -2558,7 +2558,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="18" t="n">
-        <v>0.0763863113354613</v>
+        <v>0.06892738665683741</v>
       </c>
       <c r="Q23" s="19" t="inlineStr"/>
       <c r="R23" s="17" t="n"/>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>356.39</v>
+        <v>355.66</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.06</v>
+        <v>0.0579</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.1507</v>
+        <v>0.1484</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>46252</v>
@@ -2628,7 +2628,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0.01012935267543987</v>
+        <v>0.01220266546701899</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0.1223659474171554</v>
+        <v>0.1246696282966878</v>
       </c>
       <c r="Q24" s="9" t="inlineStr">
         <is>
@@ -2688,13 +2688,13 @@
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>223.54</v>
+        <v>223.4</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>0.05019999999999999</v>
+        <v>0.0496</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0742</v>
       </c>
       <c r="G25" s="15" t="n">
         <v>46253</v>
@@ -2723,7 +2723,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>0.1407354388476336</v>
+        <v>0.1414503133393017</v>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="18" t="n">
-        <v>0.02889863111747342</v>
+        <v>0.02954341987466425</v>
       </c>
       <c r="Q25" s="19" t="inlineStr">
         <is>
@@ -2779,13 +2779,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>276.13</v>
+        <v>274.48</v>
       </c>
       <c r="E26" s="22" t="n">
-        <v>-0.0076</v>
+        <v>-0.0135</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>-0.0059</v>
+        <v>-0.0119</v>
       </c>
       <c r="G26" s="6" t="n"/>
       <c r="H26" s="7" t="inlineStr">
@@ -2804,7 +2804,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.08644479049722958</v>
+        <v>0.09297580880209844</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0.2675189222467678</v>
+        <v>0.2751384436024482</v>
       </c>
       <c r="Q26" s="9" t="inlineStr">
         <is>
@@ -2856,13 +2856,13 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>42.33</v>
+        <v>41.71</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>-0.0129</v>
+        <v>-0.0276</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>-0.0207</v>
+        <v>-0.0353</v>
       </c>
       <c r="G27" s="15" t="n">
         <v>46294</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>93.04000000000001</v>
+        <v>93.53</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.0949</v>
+        <v>0.1006</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.0452</v>
+        <v>0.0507</v>
       </c>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="7" t="inlineStr">
@@ -2942,7 +2942,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.1822871883061048</v>
+        <v>0.176093232118037</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.2360275150472914</v>
+        <v>0.2295520153961296</v>
       </c>
       <c r="Q28" s="9" t="inlineStr">
         <is>
@@ -2998,13 +2998,13 @@
         </is>
       </c>
       <c r="D29" s="13" t="n">
-        <v>209.07</v>
+        <v>206.31</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>0.0239</v>
+        <v>0.0103</v>
       </c>
       <c r="F29" s="18" t="n">
-        <v>0.1554</v>
+        <v>0.1401</v>
       </c>
       <c r="G29" s="15" t="n">
         <v>46317</v>
@@ -3059,13 +3059,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>254.75</v>
+        <v>255.23</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.1701</v>
+        <v>0.1723</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.1202</v>
+        <v>0.1223</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>46254</v>
@@ -3094,7 +3094,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="22" t="n">
-        <v>-0.03827281648675172</v>
+        <v>-0.04008149512204674</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.04023552502453386</v>
+        <v>0.03827919915370454</v>
       </c>
       <c r="Q30" s="9" t="inlineStr">
         <is>
@@ -3146,13 +3146,13 @@
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>105.94</v>
+        <v>105.58</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>0.0199</v>
+        <v>0.0165</v>
       </c>
       <c r="F31" s="18" t="n">
-        <v>0.1173</v>
+        <v>0.1135</v>
       </c>
       <c r="G31" s="15" t="n"/>
       <c r="H31" s="21" t="inlineStr">
@@ -3171,7 +3171,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="18" t="n">
-        <v>0.1327166320558807</v>
+        <v>0.1365788975184694</v>
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="18" t="n">
-        <v>0.08552010572021901</v>
+        <v>0.08922144345519986</v>
       </c>
       <c r="Q31" s="19" t="inlineStr">
         <is>
@@ -3223,13 +3223,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>12.97</v>
+        <v>13.02</v>
       </c>
       <c r="E32" s="22" t="n">
-        <v>-0.1974</v>
+        <v>-0.1943</v>
       </c>
       <c r="F32" s="22" t="n">
-        <v>-0.1501</v>
+        <v>-0.1468</v>
       </c>
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="7" t="inlineStr">
@@ -3274,13 +3274,13 @@
         </is>
       </c>
       <c r="D33" s="13" t="n">
-        <v>161.71</v>
+        <v>161.3</v>
       </c>
       <c r="E33" s="18" t="n">
-        <v>0.0583</v>
+        <v>0.0557</v>
       </c>
       <c r="F33" s="18" t="n">
-        <v>0.0122</v>
+        <v>0.0097</v>
       </c>
       <c r="G33" s="15" t="n">
         <v>46253</v>
@@ -3309,7 +3309,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>-0.01057448518953687</v>
+        <v>-0.008059516429014328</v>
       </c>
       <c r="N33" s="12" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="18" t="n">
-        <v>0.08218415682394405</v>
+        <v>0.08493490390576558</v>
       </c>
       <c r="Q33" s="19" t="inlineStr">
         <is>
@@ -3365,13 +3365,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>33.72</v>
+        <v>34.56</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.14</v>
+        <v>0.1684</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.1188</v>
+        <v>0.1466</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>46317</v>
@@ -3400,7 +3400,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.03795966785290632</v>
+        <v>0.01273148148148141</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0.1862396204033215</v>
+        <v>0.1574074074074073</v>
       </c>
       <c r="Q34" s="9" t="inlineStr">
         <is>
@@ -3452,13 +3452,13 @@
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>327.25</v>
+        <v>328.58</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>-0.1695</v>
+        <v>-0.1662</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>-0.1998</v>
+        <v>-0.1965</v>
       </c>
       <c r="G35" s="15" t="n">
         <v>46323</v>
@@ -3487,7 +3487,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="14" t="n">
-        <v>-0.6027501909854851</v>
+        <v>-0.6043581471787692</v>
       </c>
       <c r="N35" s="12" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="14" t="n">
-        <v>-0.08326967150496563</v>
+        <v>-0.08698033964331361</v>
       </c>
       <c r="Q35" s="19" t="inlineStr">
         <is>
@@ -3539,13 +3539,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>75.06999999999999</v>
+        <v>75</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.07150000000000001</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="G36" s="6" t="n"/>
       <c r="H36" s="7" t="inlineStr">
@@ -3590,13 +3590,13 @@
         </is>
       </c>
       <c r="D37" s="13" t="n">
-        <v>547</v>
+        <v>565.15</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>0.2019</v>
+        <v>0.2418</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>0.1819</v>
+        <v>0.2212</v>
       </c>
       <c r="G37" s="15" t="n">
         <v>46261</v>
@@ -3625,7 +3625,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>-0.1773308957952468</v>
+        <v>-0.203751216491197</v>
       </c>
       <c r="N37" s="12" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="18" t="n">
-        <v>0.1608775137111517</v>
+        <v>0.1235955056179776</v>
       </c>
       <c r="Q37" s="19" t="inlineStr">
         <is>
@@ -3681,13 +3681,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>103.41</v>
+        <v>103.25</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0736</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.08449999999999999</v>
+        <v>0.0828</v>
       </c>
       <c r="G38" s="6" t="n"/>
       <c r="H38" s="7" t="inlineStr">
@@ -3706,7 +3706,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.063726912290881</v>
+        <v>0.06537530266343826</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.01537568900493186</v>
+        <v>0.01694915254237288</v>
       </c>
       <c r="Q38" s="9" t="inlineStr">
         <is>
@@ -3762,13 +3762,13 @@
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>92.97</v>
-      </c>
-      <c r="E39" s="14" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>93.29000000000001</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>0.0027</v>
       </c>
       <c r="F39" s="18" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0839</v>
       </c>
       <c r="G39" s="15" t="n"/>
       <c r="H39" s="21" t="inlineStr">
@@ -3787,7 +3787,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="18" t="n">
-        <v>0.02183500053780791</v>
+        <v>0.0183299389002036</v>
       </c>
       <c r="N39" s="12" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="18" t="n">
-        <v>0.07561579003979779</v>
+        <v>0.07192625147389853</v>
       </c>
       <c r="Q39" s="19" t="inlineStr">
         <is>
@@ -3843,13 +3843,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>946.99</v>
+        <v>947.8200000000001</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>-0.0064</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>-0.0285</v>
+        <v>-0.0276</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>46289</v>
@@ -3878,7 +3878,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0.0559773598454049</v>
+        <v>0.05505264712709158</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0.1615750958299454</v>
+        <v>0.1605579118398008</v>
       </c>
       <c r="Q40" s="9" t="inlineStr">
         <is>
@@ -3938,13 +3938,13 @@
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>127.08</v>
+        <v>126.56</v>
       </c>
       <c r="E41" s="18" t="n">
-        <v>0.107</v>
+        <v>0.1024</v>
       </c>
       <c r="F41" s="18" t="n">
-        <v>0.1897</v>
+        <v>0.1848</v>
       </c>
       <c r="G41" s="15" t="n">
         <v>46261</v>
@@ -3973,7 +3973,7 @@
         <v>125</v>
       </c>
       <c r="M41" s="14" t="n">
-        <v>-0.01636764242996536</v>
+        <v>-0.01232616940581544</v>
       </c>
       <c r="N41" s="12" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="18" t="n">
-        <v>0.06232294617563741</v>
+        <v>0.06668773704171932</v>
       </c>
       <c r="Q41" s="19" t="inlineStr">
         <is>
@@ -4025,13 +4025,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>25.24</v>
+        <v>25.32</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0161</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.08070000000000001</v>
+        <v>0.08439999999999999</v>
       </c>
       <c r="G42" s="6" t="n"/>
       <c r="H42" s="7" t="inlineStr">
@@ -4076,13 +4076,13 @@
         </is>
       </c>
       <c r="D43" s="13" t="n">
-        <v>86.76000000000001</v>
+        <v>87.05</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>0.0403</v>
+        <v>0.0438</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0944</v>
       </c>
       <c r="G43" s="15" t="n"/>
       <c r="H43" s="21" t="inlineStr">
@@ -4101,7 +4101,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>0.0373443983402489</v>
+        <v>0.03388856978747849</v>
       </c>
       <c r="N43" s="12" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>88</v>
       </c>
       <c r="P43" s="18" t="n">
-        <v>0.01429230059935448</v>
+        <v>0.01091326823664564</v>
       </c>
       <c r="Q43" s="19" t="inlineStr">
         <is>
@@ -4161,13 +4161,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>56.54</v>
+        <v>56.74</v>
       </c>
       <c r="E44" s="22" t="n">
-        <v>-0.0469</v>
+        <v>-0.0435</v>
       </c>
       <c r="F44" s="22" t="n">
-        <v>-0.102</v>
+        <v>-0.09880000000000001</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>46275</v>
@@ -4196,7 +4196,7 @@
         <v>58</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>0.02582242660063673</v>
+        <v>0.02220655622136056</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.3795542978422356</v>
+        <v>0.3746915756080366</v>
       </c>
       <c r="Q44" s="9" t="inlineStr">
         <is>
@@ -4248,13 +4248,13 @@
         </is>
       </c>
       <c r="D45" s="13" t="n">
-        <v>62.9</v>
+        <v>62.61</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>0.0575</v>
+        <v>0.0526</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>0.0211</v>
+        <v>0.0164</v>
       </c>
       <c r="G45" s="15" t="n"/>
       <c r="H45" s="21" t="inlineStr">
@@ -4273,7 +4273,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="18" t="n">
-        <v>0.1128775834658188</v>
+        <v>0.1180322632167386</v>
       </c>
       <c r="N45" s="12" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="18" t="n">
-        <v>0.1287758346581876</v>
+        <v>0.1340041526912634</v>
       </c>
       <c r="Q45" s="19" t="inlineStr">
         <is>
@@ -4333,13 +4333,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>53.05</v>
+        <v>52.95</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.0287</v>
+        <v>0.0268</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.1143</v>
+        <v>0.1122</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>46301</v>
@@ -4404,13 +4404,13 @@
         </is>
       </c>
       <c r="D47" s="13" t="n">
-        <v>91.48</v>
+        <v>90.36</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>-0.0386</v>
+        <v>-0.0503</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>0.034</v>
+        <v>0.0214</v>
       </c>
       <c r="G47" s="15" t="n"/>
       <c r="H47" s="21" t="inlineStr">
@@ -4455,13 +4455,13 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>68.17</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="E48" s="22" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.0617</v>
       </c>
       <c r="F48" s="22" t="n">
-        <v>-0.0438</v>
+        <v>-0.0417</v>
       </c>
       <c r="G48" s="6" t="n"/>
       <c r="H48" s="7" t="inlineStr">
@@ -4506,13 +4506,13 @@
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>138.35</v>
+        <v>139.02</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>-0.0292</v>
+        <v>-0.0245</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>-0.0166</v>
+        <v>-0.0118</v>
       </c>
       <c r="G49" s="15" t="n">
         <v>46303</v>
@@ -4541,7 +4541,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>0.01192627394289849</v>
+        <v>0.007049345417925405</v>
       </c>
       <c r="N49" s="12" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="18" t="n">
-        <v>0.08420672208167695</v>
+        <v>0.07898144151920579</v>
       </c>
       <c r="Q49" s="19" t="inlineStr">
         <is>
@@ -4601,13 +4601,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>145.72</v>
+        <v>145.77</v>
       </c>
       <c r="E50" s="22" t="n">
-        <v>-0.0181</v>
+        <v>-0.0177</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.0043</v>
+        <v>0.0046</v>
       </c>
       <c r="G50" s="6" t="n"/>
       <c r="H50" s="7" t="inlineStr">
@@ -4626,7 +4626,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.1254460609387867</v>
+        <v>0.1250600260684639</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0.1117211089761186</v>
+        <v>0.1113397818481168</v>
       </c>
       <c r="Q50" s="9" t="inlineStr">
         <is>
@@ -4690,13 +4690,13 @@
         </is>
       </c>
       <c r="D51" s="13" t="n">
-        <v>83.70999999999999</v>
+        <v>84.27</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0132</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>0.09449999999999999</v>
+        <v>0.1019</v>
       </c>
       <c r="G51" s="15" t="n"/>
       <c r="H51" s="21" t="inlineStr">
@@ -4715,7 +4715,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>0.1946004061641382</v>
+        <v>0.1866619200189867</v>
       </c>
       <c r="N51" s="12" t="inlineStr"/>
       <c r="O51" s="17" t="n"/>
@@ -4759,13 +4759,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>147.6</v>
+        <v>149.7</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.1147</v>
+        <v>0.1305</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.1907</v>
+        <v>0.2076</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>46253</v>
@@ -4794,7 +4794,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="22" t="n">
-        <v>-0.05149051490514901</v>
+        <v>-0.06479625918503668</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="22" t="n">
-        <v>-0.08536585365853655</v>
+        <v>-0.09819639278557107</v>
       </c>
       <c r="Q52" s="9" t="inlineStr">
         <is>
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="D53" s="13" t="n">
-        <v>111.99</v>
+        <v>111.85</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>-0.0098</v>
+        <v>-0.0111</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>-0.0654</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="G53" s="15" t="n">
         <v>46254</v>
@@ -4885,7 +4885,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>0.2501116171086705</v>
+        <v>0.2516763522574877</v>
       </c>
       <c r="N53" s="12" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="18" t="n">
-        <v>0.2501116171086705</v>
+        <v>0.2516763522574877</v>
       </c>
       <c r="Q53" s="19" t="inlineStr">
         <is>
@@ -4945,13 +4945,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>62.38</v>
+        <v>61.55</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0.0834</v>
+        <v>0.0689</v>
       </c>
       <c r="F54" s="22" t="n">
-        <v>-0.0379</v>
+        <v>-0.0507</v>
       </c>
       <c r="G54" s="6" t="n">
         <v>46316</v>
@@ -4987,7 +4987,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>0.2183392112856684</v>
+        <v>0.2347684809098295</v>
       </c>
       <c r="Q54" s="9" t="inlineStr">
         <is>
@@ -5028,13 +5028,13 @@
         </is>
       </c>
       <c r="D55" s="13" t="n">
-        <v>116.74</v>
+        <v>117.61</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>0.0544</v>
+        <v>0.0622</v>
       </c>
       <c r="F55" s="14" t="n">
-        <v>-0.0181</v>
+        <v>-0.0108</v>
       </c>
       <c r="G55" s="15" t="n"/>
       <c r="H55" s="21" t="inlineStr">
@@ -5053,7 +5053,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="18" t="n">
-        <v>0.567586088744218</v>
+        <v>0.5559901368931214</v>
       </c>
       <c r="N55" s="12" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="18" t="n">
-        <v>0.2420764091142711</v>
+        <v>0.2328883598333475</v>
       </c>
       <c r="Q55" s="19" t="inlineStr">
         <is>
@@ -5105,13 +5105,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>186.43</v>
+        <v>186.57</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.0594</v>
+        <v>0.0602</v>
       </c>
       <c r="F56" s="22" t="n">
-        <v>-0.0149</v>
+        <v>-0.0141</v>
       </c>
       <c r="G56" s="6" t="n"/>
       <c r="H56" s="7" t="inlineStr">
@@ -5130,7 +5130,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>0.1907954728316258</v>
+        <v>0.189901913490915</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>0.2068873035455667</v>
+        <v>0.2059816690786301</v>
       </c>
       <c r="Q56" s="9" t="inlineStr">
         <is>
@@ -5186,13 +5186,13 @@
         </is>
       </c>
       <c r="D57" s="13" t="n">
-        <v>134.46</v>
+        <v>134.73</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>-0.0227</v>
+        <v>-0.0208</v>
       </c>
       <c r="F57" s="14" t="n">
-        <v>-0.0406</v>
+        <v>-0.0387</v>
       </c>
       <c r="G57" s="15" t="n"/>
       <c r="H57" s="21" t="inlineStr">
@@ -5211,7 +5211,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="18" t="n">
-        <v>0.4576825821805741</v>
+        <v>0.4547613746010541</v>
       </c>
       <c r="N57" s="12" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="18" t="n">
-        <v>0.264316525360702</v>
+        <v>0.2617828249090775</v>
       </c>
       <c r="Q57" s="19" t="inlineStr">
         <is>
@@ -5318,13 +5318,13 @@
         </is>
       </c>
       <c r="D59" s="13" t="n">
-        <v>20.22</v>
+        <v>20.14</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>0.0179</v>
+        <v>0.0141</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>0.0452</v>
+        <v>0.0414</v>
       </c>
       <c r="G59" s="15" t="n"/>
       <c r="H59" s="21" t="inlineStr">
@@ -5369,13 +5369,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>185.99</v>
-      </c>
-      <c r="E60" s="22" t="n">
-        <v>-0.0033</v>
+        <v>188.04</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0.0077</v>
       </c>
       <c r="F60" s="22" t="n">
-        <v>-0.0616</v>
+        <v>-0.0513</v>
       </c>
       <c r="G60" s="6" t="n"/>
       <c r="H60" s="7" t="inlineStr">
@@ -5420,13 +5420,13 @@
         </is>
       </c>
       <c r="D61" s="13" t="n">
-        <v>32.15</v>
+        <v>31.89</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>-0.0805</v>
+        <v>-0.0882</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>-0.206</v>
+        <v>-0.2127</v>
       </c>
       <c r="G61" s="15" t="n">
         <v>46315</v>
@@ -5462,7 +5462,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="18" t="n">
-        <v>0.3374805598755833</v>
+        <v>0.3483850736908121</v>
       </c>
       <c r="Q61" s="19" t="inlineStr">
         <is>
@@ -5507,13 +5507,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>30.84</v>
+        <v>30.85</v>
       </c>
       <c r="E62" s="22" t="n">
-        <v>-0.0505</v>
+        <v>-0.05019999999999999</v>
       </c>
       <c r="F62" s="22" t="n">
-        <v>-0.0144</v>
+        <v>-0.0141</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>46316</v>
@@ -5542,7 +5542,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.1348897535667964</v>
+        <v>0.1345218800648298</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="8" t="n"/>
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="D63" s="13" t="n">
-        <v>202.16</v>
+        <v>204</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>0.0764</v>
+        <v>0.0862</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>0.1022</v>
+        <v>0.1122</v>
       </c>
       <c r="G63" s="15" t="n"/>
       <c r="H63" s="21" t="inlineStr">
@@ -5637,13 +5637,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>51.43</v>
+        <v>50.52</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0.0843</v>
+        <v>0.06509999999999999</v>
       </c>
       <c r="F64" s="22" t="n">
-        <v>-0.0906</v>
+        <v>-0.1066</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>46311</v>
@@ -5679,7 +5679,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0.224965973167412</v>
+        <v>0.2470308788598574</v>
       </c>
       <c r="Q64" s="9" t="inlineStr">
         <is>
@@ -5728,13 +5728,13 @@
         </is>
       </c>
       <c r="D65" s="13" t="n">
-        <v>41.09</v>
+        <v>40.82</v>
       </c>
       <c r="E65" s="14" t="n">
-        <v>-0.0442</v>
+        <v>-0.0505</v>
       </c>
       <c r="F65" s="14" t="n">
-        <v>-0.1079</v>
+        <v>-0.1138</v>
       </c>
       <c r="G65" s="15" t="n"/>
       <c r="H65" s="21" t="inlineStr">
@@ -5779,13 +5779,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>70.63</v>
+        <v>70.39</v>
       </c>
       <c r="E66" s="22" t="n">
-        <v>-0.0617</v>
+        <v>-0.06480000000000001</v>
       </c>
       <c r="F66" s="22" t="n">
-        <v>-0.0135</v>
+        <v>-0.0168</v>
       </c>
       <c r="G66" s="6" t="n"/>
       <c r="H66" s="7" t="inlineStr">
@@ -5804,7 +5804,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0.2600877813960075</v>
+        <v>0.2643841454752096</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="8" t="n"/>
@@ -5860,13 +5860,13 @@
         </is>
       </c>
       <c r="D67" s="13" t="n">
-        <v>152.54</v>
+        <v>152.94</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>0.0808</v>
+        <v>0.0837</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>0.0052</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="G67" s="15" t="n"/>
       <c r="H67" s="21" t="inlineStr">
@@ -5885,7 +5885,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>0.2127966435033435</v>
+        <v>0.2096246894206879</v>
       </c>
       <c r="N67" s="12" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="18" t="n">
-        <v>0.2127966435033435</v>
+        <v>0.2096246894206879</v>
       </c>
       <c r="Q67" s="19" t="inlineStr">
         <is>
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>123.57</v>
+        <v>124.57</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0.0176</v>
+        <v>0.0258</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.0723</v>
+        <v>0.081</v>
       </c>
       <c r="G68" s="6" t="n"/>
       <c r="H68" s="7" t="inlineStr">
@@ -5966,7 +5966,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="22" t="n">
-        <v>-0.02889050740470983</v>
+        <v>-0.03668620052982254</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>115</v>
       </c>
       <c r="P68" s="22" t="n">
-        <v>-0.06935340292951359</v>
+        <v>-0.07682427550774659</v>
       </c>
       <c r="Q68" s="9" t="inlineStr"/>
       <c r="R68" s="8" t="n"/>
@@ -6012,13 +6012,13 @@
         </is>
       </c>
       <c r="D69" s="13" t="n">
-        <v>360.49</v>
+        <v>358.21</v>
       </c>
       <c r="E69" s="18" t="n">
-        <v>0.0083</v>
+        <v>0.002</v>
       </c>
       <c r="F69" s="18" t="n">
-        <v>0.1063</v>
+        <v>0.0993</v>
       </c>
       <c r="G69" s="15" t="n"/>
       <c r="H69" s="21" t="inlineStr">
@@ -6037,7 +6037,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="18" t="n">
-        <v>0.1262448334211767</v>
+        <v>0.1334133608776975</v>
       </c>
       <c r="N69" s="12" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="18" t="n">
-        <v>0.2094648950040223</v>
+        <v>0.2171631166075766</v>
       </c>
       <c r="Q69" s="19" t="inlineStr">
         <is>
@@ -6085,13 +6085,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>342.85</v>
+        <v>341.02</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0.0192</v>
+        <v>0.0137</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.0978</v>
+        <v>0.0919</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>46311</v>
@@ -6120,7 +6120,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.2104418842059209</v>
+        <v>0.2169374230250426</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.1083564240921685</v>
+        <v>0.1143041463843763</v>
       </c>
       <c r="Q70" s="9" t="inlineStr">
         <is>
@@ -6180,13 +6180,13 @@
         </is>
       </c>
       <c r="D71" s="13" t="n">
-        <v>62.94</v>
+        <v>63.15</v>
       </c>
       <c r="E71" s="18" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.0833</v>
       </c>
       <c r="F71" s="18" t="n">
-        <v>0.1737</v>
+        <v>0.1776</v>
       </c>
       <c r="G71" s="15" t="n">
         <v>46309</v>
@@ -6241,13 +6241,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1137.99</v>
+        <v>1136.39</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0.1491</v>
+        <v>0.1475</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.144</v>
+        <v>0.1424</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>46308</v>
@@ -6279,7 +6279,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.09403421822687369</v>
+        <v>0.09557458266968197</v>
       </c>
       <c r="Q72" s="9" t="inlineStr">
         <is>
@@ -6324,13 +6324,13 @@
         </is>
       </c>
       <c r="D73" s="13" t="n">
-        <v>23.69</v>
+        <v>23.65</v>
       </c>
       <c r="E73" s="14" t="n">
-        <v>-0.0708</v>
+        <v>-0.0727</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>-0.1292</v>
+        <v>-0.131</v>
       </c>
       <c r="G73" s="15" t="n">
         <v>46247</v>
@@ -6385,13 +6385,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>18.76</v>
+        <v>18.81</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0.2624</v>
+        <v>0.2658</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.1134</v>
+        <v>0.1163</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>46346</v>
@@ -6446,13 +6446,13 @@
         </is>
       </c>
       <c r="D75" s="13" t="n">
-        <v>520.47</v>
+        <v>520.77</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>0.0519</v>
+        <v>0.0525</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>0.0687</v>
+        <v>0.0693</v>
       </c>
       <c r="G75" s="15" t="n"/>
       <c r="H75" s="21" t="inlineStr">
@@ -6519,13 +6519,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>72.17</v>
+        <v>71.44</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0.055</v>
+        <v>0.0443</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.2443</v>
+        <v>0.2317</v>
       </c>
       <c r="G76" s="6" t="n"/>
       <c r="H76" s="7" t="inlineStr">
@@ -6544,7 +6544,7 @@
         <v>68</v>
       </c>
       <c r="M76" s="22" t="n">
-        <v>-0.05778024109740892</v>
+        <v>-0.04815229563269874</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="8" t="n"/>
@@ -6586,13 +6586,13 @@
         </is>
       </c>
       <c r="D77" s="13" t="n">
-        <v>137.93</v>
+        <v>137.12</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>0.1628</v>
+        <v>0.156</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>0.2079</v>
+        <v>0.2008</v>
       </c>
       <c r="G77" s="15" t="n">
         <v>46310</v>
@@ -6651,13 +6651,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>134.32</v>
+        <v>134.96</v>
       </c>
       <c r="E78" s="22" t="n">
-        <v>-0.0223</v>
+        <v>-0.0177</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0126</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>46308</v>
@@ -6689,7 +6689,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.04228707564026211</v>
+        <v>0.0373443983402489</v>
       </c>
       <c r="Q78" s="9" t="inlineStr">
         <is>
@@ -6738,13 +6738,13 @@
         </is>
       </c>
       <c r="D79" s="13" t="n">
-        <v>351.73</v>
+        <v>350.3</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>-0.0095</v>
+        <v>-0.0135</v>
       </c>
       <c r="F79" s="18" t="n">
-        <v>0.09269999999999999</v>
+        <v>0.0883</v>
       </c>
       <c r="G79" s="15" t="n">
         <v>46315</v>
@@ -6773,7 +6773,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="18" t="n">
-        <v>0.01782617348534382</v>
+        <v>0.02198115900656577</v>
       </c>
       <c r="N79" s="12" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="18" t="n">
-        <v>0.0633156114064765</v>
+        <v>0.06765629460462458</v>
       </c>
       <c r="Q79" s="19" t="inlineStr">
         <is>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>59.06</v>
+        <v>59.08</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0.0255</v>
+        <v>0.0259</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0.1058</v>
+        <v>0.1062</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>46310</v>
@@ -6864,7 +6864,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="22" t="n">
-        <v>-0.03487978327124961</v>
+        <v>-0.03520649966147594</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="8" t="n"/>
@@ -6906,13 +6906,13 @@
         </is>
       </c>
       <c r="D81" s="13" t="n">
-        <v>12.38</v>
+        <v>12.3</v>
       </c>
       <c r="E81" s="14" t="n">
-        <v>-0.0016</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F81" s="14" t="n">
-        <v>-0.2506</v>
+        <v>-0.2554</v>
       </c>
       <c r="G81" s="15" t="n"/>
       <c r="H81" s="21" t="inlineStr">
@@ -6957,13 +6957,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>400.15</v>
+        <v>393.04</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0.157</v>
+        <v>0.1364</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.1465</v>
+        <v>0.1262</v>
       </c>
       <c r="G82" s="6" t="n"/>
       <c r="H82" s="7" t="inlineStr">
@@ -7020,13 +7020,13 @@
         </is>
       </c>
       <c r="D83" s="13" t="n">
-        <v>68.06999999999999</v>
+        <v>66.69</v>
       </c>
       <c r="E83" s="18" t="n">
-        <v>0.0624</v>
+        <v>0.0409</v>
       </c>
       <c r="F83" s="14" t="n">
-        <v>-0.1753</v>
+        <v>-0.1919</v>
       </c>
       <c r="G83" s="15" t="n"/>
       <c r="H83" s="21" t="inlineStr">
@@ -7071,13 +7071,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>42.4</v>
+        <v>41.27</v>
       </c>
       <c r="E84" s="22" t="n">
-        <v>-0.1132</v>
+        <v>-0.137</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0.126</v>
+        <v>0.0959</v>
       </c>
       <c r="G84" s="6" t="n"/>
       <c r="H84" s="7" t="inlineStr">
@@ -7122,13 +7122,13 @@
         </is>
       </c>
       <c r="D85" s="13" t="n">
-        <v>1041.39</v>
+        <v>1039.46</v>
       </c>
       <c r="E85" s="18" t="n">
-        <v>0.0114</v>
+        <v>0.0095</v>
       </c>
       <c r="F85" s="14" t="n">
-        <v>-0.0035</v>
+        <v>-0.0053</v>
       </c>
       <c r="G85" s="15" t="n">
         <v>46308</v>
@@ -7157,7 +7157,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>0.2723379329549927</v>
+        <v>0.2747003251688376</v>
       </c>
       <c r="N85" s="12" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="18" t="n">
-        <v>0.1619086029249368</v>
+        <v>0.1640659573239951</v>
       </c>
       <c r="Q85" s="19" t="inlineStr">
         <is>
@@ -7209,13 +7209,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>129.46</v>
+        <v>128.99</v>
       </c>
       <c r="E86" s="22" t="n">
-        <v>-0.0361</v>
+        <v>-0.0396</v>
       </c>
       <c r="F86" s="22" t="n">
-        <v>-0.0557</v>
+        <v>-0.0592</v>
       </c>
       <c r="G86" s="6" t="n"/>
       <c r="H86" s="7" t="inlineStr">
@@ -7260,13 +7260,13 @@
         </is>
       </c>
       <c r="D87" s="13" t="n">
-        <v>95.23999999999999</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>-0.1611</v>
+        <v>-0.1783</v>
       </c>
       <c r="F87" s="18" t="n">
-        <v>0.1199</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="G87" s="15" t="n"/>
       <c r="H87" s="21" t="inlineStr">
@@ -7311,13 +7311,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>86.33</v>
+        <v>88.59</v>
       </c>
       <c r="E88" s="22" t="n">
-        <v>-0.1864</v>
+        <v>-0.1651</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>-0.2782</v>
+        <v>-0.2593</v>
       </c>
       <c r="G88" s="6" t="n"/>
       <c r="H88" s="7" t="inlineStr">
@@ -7362,13 +7362,13 @@
         </is>
       </c>
       <c r="D89" s="13" t="n">
-        <v>153.1</v>
+        <v>150.29</v>
       </c>
       <c r="E89" s="18" t="n">
-        <v>0.1162</v>
+        <v>0.0956</v>
       </c>
       <c r="F89" s="18" t="n">
-        <v>0.1011</v>
+        <v>0.0808</v>
       </c>
       <c r="G89" s="15" t="n"/>
       <c r="H89" s="21" t="inlineStr">
@@ -7413,13 +7413,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>157.59</v>
+        <v>155.95</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0.0693</v>
+        <v>0.0582</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.2471</v>
+        <v>0.2341</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>46252</v>
@@ -7488,13 +7488,13 @@
         </is>
       </c>
       <c r="D91" s="13" t="n">
-        <v>355.81</v>
+        <v>357.52</v>
       </c>
       <c r="E91" s="18" t="n">
-        <v>0.0762</v>
+        <v>0.0814</v>
       </c>
       <c r="F91" s="18" t="n">
-        <v>0.1437</v>
+        <v>0.1492</v>
       </c>
       <c r="G91" s="15" t="n">
         <v>46308</v>
@@ -7523,7 +7523,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="14" t="n">
-        <v>-0.4491442061774543</v>
+        <v>-0.4517789214589393</v>
       </c>
       <c r="N91" s="12" t="inlineStr"/>
       <c r="O91" s="17" t="n"/>
@@ -7567,13 +7567,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>104.26</v>
+        <v>102.79</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0.1175</v>
+        <v>0.1017</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.1185</v>
+        <v>0.1028</v>
       </c>
       <c r="G92" s="6" t="n"/>
       <c r="H92" s="7" t="inlineStr">
@@ -7592,7 +7592,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>2.596777287550355</v>
+        <v>2.648214806887829</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>2.529637444849415</v>
+        <v>2.580114797159256</v>
       </c>
       <c r="Q92" s="9" t="inlineStr">
         <is>
@@ -7656,13 +7656,13 @@
         </is>
       </c>
       <c r="D93" s="13" t="n">
-        <v>377.27</v>
+        <v>373.77</v>
       </c>
       <c r="E93" s="18" t="n">
-        <v>0.09050000000000001</v>
+        <v>0.08039999999999999</v>
       </c>
       <c r="F93" s="18" t="n">
-        <v>0.2615</v>
+        <v>0.2498</v>
       </c>
       <c r="G93" s="15" t="n">
         <v>46317</v>
@@ -7694,7 +7694,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="14" t="n">
-        <v>-0.6951785193627905</v>
+        <v>-0.6923241565668726</v>
       </c>
       <c r="Q93" s="19" t="inlineStr">
         <is>
@@ -7743,13 +7743,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>568.6900000000001</v>
+        <v>562.65</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0.09390000000000001</v>
+        <v>0.0823</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.1709</v>
+        <v>0.1585</v>
       </c>
       <c r="G94" s="6" t="n"/>
       <c r="H94" s="7" t="inlineStr">
@@ -7768,7 +7768,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="22" t="n">
-        <v>-0.3564156218678015</v>
+        <v>-0.3495067981871501</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="8" t="n"/>
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="D95" s="13" t="n">
-        <v>1875.34</v>
+        <v>1875.35</v>
       </c>
       <c r="E95" s="14" t="n">
         <v>-0.0418</v>
@@ -7871,13 +7871,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>214.63</v>
+        <v>216.25</v>
       </c>
       <c r="E96" s="22" t="n">
-        <v>-0.0158</v>
+        <v>-0.0083</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.0113</v>
+        <v>0.0189</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>46309</v>
@@ -7906,7 +7906,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>2.112332851884639</v>
+        <v>2.089017341040462</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>1.562549503797233</v>
+        <v>1.543352601156069</v>
       </c>
       <c r="Q96" s="9" t="inlineStr">
         <is>
@@ -7966,13 +7966,13 @@
         </is>
       </c>
       <c r="D97" s="13" t="n">
-        <v>114.35</v>
+        <v>113.4</v>
       </c>
       <c r="E97" s="18" t="n">
-        <v>0.0326</v>
+        <v>0.024</v>
       </c>
       <c r="F97" s="18" t="n">
-        <v>0.08869999999999999</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="G97" s="15" t="n"/>
       <c r="H97" s="21" t="inlineStr">
@@ -7991,7 +7991,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="18" t="n">
-        <v>1.09881941407958</v>
+        <v>1.116402116402116</v>
       </c>
       <c r="N97" s="12" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="18" t="n">
-        <v>1.09881941407958</v>
+        <v>1.116402116402116</v>
       </c>
       <c r="Q97" s="19" t="inlineStr">
         <is>
@@ -8051,13 +8051,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>251.74</v>
+        <v>252.51</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0.0212</v>
+        <v>0.0243</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.1083</v>
+        <v>0.1117</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>46310</v>
@@ -8086,7 +8086,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="22" t="n">
-        <v>-0.5511241757368714</v>
+        <v>-0.5524929705754228</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="22" t="n">
-        <v>-0.5471518233097641</v>
+        <v>-0.5485327313769751</v>
       </c>
       <c r="Q98" s="9" t="inlineStr"/>
       <c r="R98" s="8" t="n"/>
@@ -8136,13 +8136,13 @@
         </is>
       </c>
       <c r="D99" s="13" t="n">
-        <v>20.61</v>
+        <v>20.52</v>
       </c>
       <c r="E99" s="14" t="n">
-        <v>-0.0228</v>
+        <v>-0.027</v>
       </c>
       <c r="F99" s="14" t="n">
-        <v>-0.1977</v>
+        <v>-0.2012</v>
       </c>
       <c r="G99" s="15" t="n"/>
       <c r="H99" s="21" t="inlineStr">
@@ -8187,13 +8187,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>14.84</v>
+        <v>14.7</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0.09359999999999999</v>
+        <v>0.0833</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.2204</v>
+        <v>0.2089</v>
       </c>
       <c r="G100" s="6" t="n">
         <v>46323</v>
@@ -8248,13 +8248,13 @@
         </is>
       </c>
       <c r="D101" s="13" t="n">
-        <v>104.85</v>
+        <v>104.7</v>
       </c>
       <c r="E101" s="18" t="n">
-        <v>0.1094</v>
+        <v>0.1078</v>
       </c>
       <c r="F101" s="18" t="n">
-        <v>0.1882</v>
+        <v>0.1865</v>
       </c>
       <c r="G101" s="15" t="n">
         <v>46323</v>
@@ -8283,7 +8283,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="18" t="n">
-        <v>1.718168812589414</v>
+        <v>1.722063037249284</v>
       </c>
       <c r="N101" s="12" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="18" t="n">
-        <v>1.718168812589414</v>
+        <v>1.722063037249284</v>
       </c>
       <c r="Q101" s="19" t="inlineStr">
         <is>
@@ -8335,13 +8335,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>412.13</v>
+        <v>408.3</v>
       </c>
       <c r="E102" s="22" t="n">
-        <v>-0.0433</v>
+        <v>-0.0522</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0.0444</v>
+        <v>0.0347</v>
       </c>
       <c r="G102" s="6" t="n"/>
       <c r="H102" s="7" t="inlineStr">
@@ -8400,13 +8400,13 @@
         </is>
       </c>
       <c r="D103" s="13" t="n">
-        <v>52.6</v>
+        <v>52.35</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>0.0585</v>
+        <v>0.0535</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>0.0771</v>
+        <v>0.0721</v>
       </c>
       <c r="G103" s="15" t="n">
         <v>46311</v>
@@ -8461,13 +8461,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>366.86</v>
+        <v>362.39</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0.0556</v>
+        <v>0.0428</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.1476</v>
+        <v>0.1336</v>
       </c>
       <c r="G104" s="6" t="n"/>
       <c r="H104" s="7" t="inlineStr">
@@ -8486,7 +8486,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>0.4310636209998364</v>
+        <v>0.448715472281244</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>0.4801286594341165</v>
+        <v>0.4983857170451724</v>
       </c>
       <c r="Q104" s="9" t="inlineStr">
         <is>
@@ -8542,13 +8542,13 @@
         </is>
       </c>
       <c r="D105" s="13" t="n">
-        <v>71.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>0.003</v>
+        <v>0.0044</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>0.0711</v>
+        <v>0.0726</v>
       </c>
       <c r="G105" s="15" t="n">
         <v>46314</v>
@@ -8577,7 +8577,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="18" t="n">
-        <v>4.762237762237763</v>
+        <v>4.754189944134079</v>
       </c>
       <c r="N105" s="12" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="18" t="n">
-        <v>3.895104895104895</v>
+        <v>3.888268156424581</v>
       </c>
       <c r="Q105" s="19" t="inlineStr">
         <is>
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>79.81</v>
+        <v>78.98</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0.0425</v>
+        <v>0.0317</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.1414</v>
+        <v>0.1296</v>
       </c>
       <c r="G106" s="6" t="n"/>
       <c r="H106" s="7" t="inlineStr">
@@ -8658,7 +8658,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="22" t="n">
-        <v>-0.1479764440546298</v>
+        <v>-0.1390225373512282</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="22" t="n">
-        <v>-0.1479764440546298</v>
+        <v>-0.1390225373512282</v>
       </c>
       <c r="Q106" s="9" t="inlineStr">
         <is>
@@ -8714,13 +8714,13 @@
         </is>
       </c>
       <c r="D107" s="13" t="n">
-        <v>244.04</v>
+        <v>245.89</v>
       </c>
       <c r="E107" s="14" t="n">
-        <v>-0.0344</v>
+        <v>-0.0271</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>0.094</v>
+        <v>0.1023</v>
       </c>
       <c r="G107" s="15" t="n"/>
       <c r="H107" s="21" t="inlineStr">
@@ -8739,7 +8739,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>0.2088182265202426</v>
+        <v>0.1997234535768027</v>
       </c>
       <c r="N107" s="12" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="18" t="n">
-        <v>0.008031470250778593</v>
+        <v>0.0004473545081134395</v>
       </c>
       <c r="Q107" s="19" t="inlineStr">
         <is>
@@ -8787,13 +8787,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>107.78</v>
+        <v>107.8</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0.1323</v>
+        <v>0.1326</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.1909</v>
+        <v>0.1912</v>
       </c>
       <c r="G108" s="6" t="n">
         <v>46316</v>
@@ -8822,7 +8822,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0.03915383187975505</v>
+        <v>0.03896103896103899</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>0.1133791055854518</v>
+        <v>0.1131725417439703</v>
       </c>
       <c r="Q108" s="9" t="inlineStr">
         <is>
@@ -8886,13 +8886,13 @@
         </is>
       </c>
       <c r="D109" s="13" t="n">
-        <v>406.27</v>
+        <v>410.95</v>
       </c>
       <c r="E109" s="18" t="n">
-        <v>0.104</v>
+        <v>0.1167</v>
       </c>
       <c r="F109" s="18" t="n">
-        <v>0.1751</v>
+        <v>0.1886</v>
       </c>
       <c r="G109" s="15" t="n"/>
       <c r="H109" s="21" t="inlineStr">
@@ -8911,7 +8911,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="14" t="n">
-        <v>-0.04004725921185414</v>
+        <v>-0.05097943788782087</v>
       </c>
       <c r="N109" s="12" t="inlineStr">
         <is>
@@ -8959,13 +8959,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>176.82</v>
+        <v>176.87</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0.1744</v>
+        <v>0.1747</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.1789</v>
+        <v>0.1792</v>
       </c>
       <c r="G110" s="6" t="n"/>
       <c r="H110" s="7" t="inlineStr">
@@ -8984,7 +8984,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="22" t="n">
-        <v>-0.08946951702296117</v>
+        <v>-0.08972691807542266</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="5" t="n">
-        <v>0.01798439090600615</v>
+        <v>0.01769661333182561</v>
       </c>
       <c r="Q110" s="9" t="inlineStr">
         <is>
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="D111" s="13" t="n">
-        <v>49.92</v>
+        <v>49.31</v>
       </c>
       <c r="E111" s="18" t="n">
-        <v>0.114</v>
+        <v>0.1004</v>
       </c>
       <c r="F111" s="18" t="n">
-        <v>0.0251</v>
+        <v>0.0125</v>
       </c>
       <c r="G111" s="15" t="n"/>
       <c r="H111" s="21" t="inlineStr">
@@ -9061,7 +9061,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="18" t="n">
-        <v>0.1017628205128205</v>
+        <v>0.1153924153315757</v>
       </c>
       <c r="N111" s="12" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="18" t="n">
-        <v>0.3020833333333333</v>
+        <v>0.3181910363009531</v>
       </c>
       <c r="Q111" s="19" t="inlineStr">
         <is>
@@ -9113,13 +9113,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>325.62</v>
+        <v>320.64</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0.0518</v>
+        <v>0.0358</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.188</v>
+        <v>0.1699</v>
       </c>
       <c r="G112" s="6" t="n"/>
       <c r="H112" s="7" t="inlineStr">
@@ -9138,7 +9138,7 @@
         <v>331</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>0.01652232663841286</v>
+        <v>0.03231037924151701</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="5" t="n">
-        <v>0.0134512622074811</v>
+        <v>0.02919161676646711</v>
       </c>
       <c r="Q112" s="9" t="inlineStr">
         <is>
@@ -9198,13 +9198,13 @@
         </is>
       </c>
       <c r="D113" s="13" t="n">
-        <v>96.19</v>
+        <v>95.67</v>
       </c>
       <c r="E113" s="14" t="n">
-        <v>-0.0793</v>
+        <v>-0.0842</v>
       </c>
       <c r="F113" s="14" t="n">
-        <v>-0.0092</v>
+        <v>-0.0145</v>
       </c>
       <c r="G113" s="15" t="n"/>
       <c r="H113" s="21" t="inlineStr">
@@ -9223,7 +9223,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="18" t="n">
-        <v>0.2787192015802059</v>
+        <v>0.2856694888679837</v>
       </c>
       <c r="N113" s="12" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="18" t="n">
-        <v>0.3514918390685103</v>
+        <v>0.3588376711612836</v>
       </c>
       <c r="Q113" s="19" t="inlineStr">
         <is>
@@ -9275,13 +9275,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>202.44</v>
+        <v>204.82</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0.0612</v>
+        <v>0.0736</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.103</v>
+        <v>0.116</v>
       </c>
       <c r="G114" s="6" t="n">
         <v>46315</v>
@@ -9310,7 +9310,7 @@
         <v>212</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>0.0472238688006323</v>
+        <v>0.03505517039351629</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="5" t="n">
-        <v>0.01264572218929066</v>
+        <v>0.0008788204276926415</v>
       </c>
       <c r="Q114" s="9" t="inlineStr">
         <is>
@@ -9366,13 +9366,13 @@
         </is>
       </c>
       <c r="D115" s="13" t="n">
-        <v>83.68000000000001</v>
+        <v>84.75</v>
       </c>
       <c r="E115" s="18" t="n">
-        <v>0.1299</v>
+        <v>0.1443</v>
       </c>
       <c r="F115" s="18" t="n">
-        <v>0.09210000000000002</v>
+        <v>0.1061</v>
       </c>
       <c r="G115" s="15" t="n"/>
       <c r="H115" s="21" t="inlineStr">
@@ -9391,7 +9391,7 @@
         <v>85</v>
       </c>
       <c r="M115" s="18" t="n">
-        <v>0.01577437858508596</v>
+        <v>0.002949852507374631</v>
       </c>
       <c r="N115" s="12" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="18" t="n">
-        <v>0.07552581261950278</v>
+        <v>0.06194690265486726</v>
       </c>
       <c r="Q115" s="19" t="inlineStr">
         <is>
@@ -9443,13 +9443,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>132.56</v>
+        <v>133.21</v>
       </c>
       <c r="E116" s="22" t="n">
-        <v>-0.024</v>
+        <v>-0.0192</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0.0348</v>
+        <v>0.0399</v>
       </c>
       <c r="G116" s="6" t="n"/>
       <c r="H116" s="7" t="inlineStr">
@@ -9468,7 +9468,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>0.2447193723596862</v>
+        <v>0.2386457473162675</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="8" t="n"/>
@@ -9516,13 +9516,13 @@
         </is>
       </c>
       <c r="D117" s="13" t="n">
-        <v>600.14</v>
+        <v>586.67</v>
       </c>
       <c r="E117" s="18" t="n">
-        <v>0.08</v>
+        <v>0.0558</v>
       </c>
       <c r="F117" s="18" t="n">
-        <v>0.0694</v>
+        <v>0.0454</v>
       </c>
       <c r="G117" s="15" t="n"/>
       <c r="H117" s="21" t="inlineStr">
@@ -9577,13 +9577,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>379.38</v>
+        <v>378.81</v>
       </c>
       <c r="E118" s="22" t="n">
-        <v>-0.0861</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="F118" s="22" t="n">
-        <v>-0.09369999999999999</v>
+        <v>-0.0951</v>
       </c>
       <c r="G118" s="6" t="n">
         <v>46315</v>
@@ -9612,7 +9612,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>0.283673361800833</v>
+        <v>0.2856049206726327</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>375</v>
       </c>
       <c r="P118" s="22" t="n">
-        <v>-0.01154515261742842</v>
+        <v>-0.01005781262374278</v>
       </c>
       <c r="Q118" s="9" t="inlineStr">
         <is>
@@ -9668,13 +9668,13 @@
         </is>
       </c>
       <c r="D119" s="13" t="n">
-        <v>256.92</v>
+        <v>259.23</v>
       </c>
       <c r="E119" s="14" t="n">
-        <v>-0.0246</v>
+        <v>-0.0158</v>
       </c>
       <c r="F119" s="18" t="n">
-        <v>0.1067</v>
+        <v>0.1166</v>
       </c>
       <c r="G119" s="15" t="n">
         <v>46315</v>
@@ -9703,7 +9703,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="18" t="n">
-        <v>0.05869531371633187</v>
+        <v>0.04926127377232566</v>
       </c>
       <c r="N119" s="12" t="inlineStr"/>
       <c r="O119" s="17" t="n"/>
@@ -9755,13 +9755,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1188.64</v>
+        <v>1185.33</v>
       </c>
       <c r="E120" s="22" t="n">
-        <v>-0.0224</v>
+        <v>-0.0251</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>0.0344</v>
+        <v>0.0315</v>
       </c>
       <c r="G120" s="6" t="n"/>
       <c r="H120" s="7" t="inlineStr">
@@ -9780,7 +9780,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>0.07686095032978857</v>
+        <v>0.07986805362219811</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -9840,13 +9840,13 @@
         </is>
       </c>
       <c r="D121" s="13" t="n">
-        <v>86.5</v>
+        <v>87.16</v>
       </c>
       <c r="E121" s="18" t="n">
-        <v>0.0547</v>
+        <v>0.06280000000000001</v>
       </c>
       <c r="F121" s="18" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="G121" s="15" t="n">
         <v>46266</v>
@@ -9875,7 +9875,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="18" t="n">
-        <v>0.1791907514450867</v>
+        <v>0.1702615878843507</v>
       </c>
       <c r="N121" s="12" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="18" t="n">
-        <v>0.2138728323699422</v>
+        <v>0.2046810463515374</v>
       </c>
       <c r="Q121" s="19" t="inlineStr">
         <is>
@@ -9927,13 +9927,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>126.77</v>
+        <v>128.57</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0205</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0.0607</v>
+        <v>0.0757</v>
       </c>
       <c r="G122" s="6" t="n"/>
       <c r="H122" s="7" t="inlineStr">
@@ -9952,7 +9952,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>0.1832452472982567</v>
+        <v>0.1666796297736642</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="8" t="n"/>
@@ -9996,13 +9996,13 @@
         </is>
       </c>
       <c r="D123" s="13" t="n">
-        <v>156.37</v>
+        <v>156.35</v>
       </c>
       <c r="E123" s="18" t="n">
-        <v>0.0077</v>
+        <v>0.0076</v>
       </c>
       <c r="F123" s="18" t="n">
-        <v>0.0679</v>
+        <v>0.0678</v>
       </c>
       <c r="G123" s="15" t="n">
         <v>46322</v>
@@ -10075,13 +10075,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>26.4</v>
+        <v>26.74</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.0975</v>
+        <v>0.1119</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>0.0302</v>
+        <v>0.0437</v>
       </c>
       <c r="G124" s="6" t="n"/>
       <c r="H124" s="7" t="inlineStr">
@@ -10100,7 +10100,7 @@
         <v>28</v>
       </c>
       <c r="M124" s="5" t="n">
-        <v>0.06060606060606066</v>
+        <v>0.0471204188481676</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="8" t="n"/>
@@ -10144,13 +10144,13 @@
         </is>
       </c>
       <c r="D125" s="13" t="n">
-        <v>339.12</v>
+        <v>339</v>
       </c>
       <c r="E125" s="18" t="n">
-        <v>0.0375</v>
+        <v>0.0372</v>
       </c>
       <c r="F125" s="18" t="n">
-        <v>0.1247</v>
+        <v>0.1243</v>
       </c>
       <c r="G125" s="15" t="n"/>
       <c r="H125" s="21" t="inlineStr">
@@ -10169,7 +10169,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="18" t="n">
-        <v>0.2326020287803727</v>
+        <v>0.2330383480825959</v>
       </c>
       <c r="N125" s="12" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="18" t="n">
-        <v>0.03208303845246519</v>
+        <v>0.03244837758112094</v>
       </c>
       <c r="Q125" s="19" t="inlineStr">
         <is>
@@ -10225,13 +10225,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>585.24</v>
+        <v>593.88</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0.1472</v>
+        <v>0.1642</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>0.2462</v>
+        <v>0.2646</v>
       </c>
       <c r="G126" s="6" t="n">
         <v>46323</v>
@@ -10260,7 +10260,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>0.05085093295058436</v>
+        <v>0.03556273994746414</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="22" t="n">
-        <v>-0.02604059872872669</v>
+        <v>-0.04021014346332592</v>
       </c>
       <c r="Q126" s="9" t="inlineStr">
         <is>
@@ -10320,13 +10320,13 @@
         </is>
       </c>
       <c r="D127" s="13" t="n">
-        <v>409.35</v>
+        <v>407.1</v>
       </c>
       <c r="E127" s="14" t="n">
-        <v>-0.0382</v>
+        <v>-0.0435</v>
       </c>
       <c r="F127" s="18" t="n">
-        <v>0.0068</v>
+        <v>0.0013</v>
       </c>
       <c r="G127" s="15" t="n">
         <v>46322</v>
@@ -10355,7 +10355,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="18" t="n">
-        <v>0.2849639672651764</v>
+        <v>0.292065831491034</v>
       </c>
       <c r="N127" s="12" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="18" t="n">
-        <v>0.1725906925613777</v>
+        <v>0.1790714812085482</v>
       </c>
       <c r="Q127" s="19" t="inlineStr">
         <is>
@@ -10411,13 +10411,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="E128" s="5" t="n">
-        <v>0.0107</v>
+        <v>72.64</v>
+      </c>
+      <c r="E128" s="22" t="n">
+        <v>-0.0328</v>
       </c>
       <c r="F128" s="22" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.0784</v>
       </c>
       <c r="G128" s="6" t="n"/>
       <c r="H128" s="7" t="inlineStr">
@@ -10480,13 +10480,13 @@
         </is>
       </c>
       <c r="D129" s="13" t="n">
-        <v>274.8</v>
+        <v>271.32</v>
       </c>
       <c r="E129" s="18" t="n">
-        <v>0.1385</v>
+        <v>0.1241</v>
       </c>
       <c r="F129" s="18" t="n">
-        <v>0.1996</v>
+        <v>0.1844</v>
       </c>
       <c r="G129" s="15" t="n"/>
       <c r="H129" s="21" t="inlineStr">
@@ -10505,7 +10505,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="14" t="n">
-        <v>-0.09752547307132464</v>
+        <v>-0.08595016954150078</v>
       </c>
       <c r="N129" s="12" t="inlineStr"/>
       <c r="O129" s="17" t="n"/>
@@ -10561,13 +10561,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>103.6</v>
+        <v>102.8</v>
       </c>
       <c r="E130" s="22" t="n">
-        <v>-0.0891</v>
+        <v>-0.09609999999999999</v>
       </c>
       <c r="F130" s="22" t="n">
-        <v>-0.1041</v>
+        <v>-0.111</v>
       </c>
       <c r="G130" s="6" t="n"/>
       <c r="H130" s="7" t="inlineStr">
@@ -10612,13 +10612,13 @@
         </is>
       </c>
       <c r="D131" s="13" t="n">
-        <v>253.3</v>
+        <v>253.76</v>
       </c>
       <c r="E131" s="18" t="n">
-        <v>0.0949</v>
+        <v>0.0969</v>
       </c>
       <c r="F131" s="18" t="n">
-        <v>0.121</v>
+        <v>0.1231</v>
       </c>
       <c r="G131" s="15" t="n"/>
       <c r="H131" s="21" t="inlineStr">
@@ -10663,13 +10663,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>232.64</v>
+        <v>234.41</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0.0342</v>
+        <v>0.0421</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>0.0774</v>
+        <v>0.08560000000000001</v>
       </c>
       <c r="G132" s="6" t="n"/>
       <c r="H132" s="7" t="inlineStr">
@@ -10688,7 +10688,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>0.07462173314993129</v>
+        <v>0.06650740156136685</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="8" t="n"/>
@@ -10732,13 +10732,13 @@
         </is>
       </c>
       <c r="D133" s="13" t="n">
-        <v>167.39</v>
+        <v>166.5</v>
       </c>
       <c r="E133" s="18" t="n">
-        <v>0.1382</v>
+        <v>0.1321</v>
       </c>
       <c r="F133" s="18" t="n">
-        <v>0.1236</v>
+        <v>0.1176</v>
       </c>
       <c r="G133" s="15" t="n"/>
       <c r="H133" s="21" t="inlineStr">
@@ -10793,13 +10793,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>837.48</v>
+        <v>842.23</v>
       </c>
       <c r="E134" s="22" t="n">
-        <v>-0.1167</v>
+        <v>-0.1116</v>
       </c>
       <c r="F134" s="22" t="n">
-        <v>-0.08539999999999999</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="G134" s="6" t="n"/>
       <c r="H134" s="7" t="inlineStr">
@@ -10818,7 +10818,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>0.3791374122367101</v>
+        <v>0.3713593673937048</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="5" t="n">
-        <v>0.3170463772269188</v>
+        <v>0.3096185127577977</v>
       </c>
       <c r="Q134" s="9" t="inlineStr">
         <is>
@@ -10870,13 +10870,13 @@
         </is>
       </c>
       <c r="D135" s="13" t="n">
-        <v>639.49</v>
+        <v>643.99</v>
       </c>
       <c r="E135" s="14" t="n">
-        <v>-0.0444</v>
+        <v>-0.0377</v>
       </c>
       <c r="F135" s="14" t="n">
-        <v>-0.0493</v>
+        <v>-0.0426</v>
       </c>
       <c r="G135" s="15" t="n"/>
       <c r="H135" s="21" t="inlineStr">
@@ -10895,7 +10895,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="18" t="n">
-        <v>0.3667141002986755</v>
+        <v>0.3571639311169428</v>
       </c>
       <c r="N135" s="12" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="18" t="n">
-        <v>0.3213654631034105</v>
+        <v>0.3121321759654653</v>
       </c>
       <c r="Q135" s="19" t="inlineStr">
         <is>
@@ -10955,13 +10955,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>203.59</v>
+        <v>203.05</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0.13</v>
+        <v>0.127</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>0.1724</v>
+        <v>0.1693</v>
       </c>
       <c r="G136" s="6" t="n">
         <v>46288</v>
@@ -10990,7 +10990,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>0.2279581511862075</v>
+        <v>0.2312238364934744</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="8" t="n"/>
@@ -11034,13 +11034,13 @@
         </is>
       </c>
       <c r="D137" s="13" t="n">
-        <v>622.3200000000001</v>
+        <v>620.92</v>
       </c>
       <c r="E137" s="18" t="n">
-        <v>0.0429</v>
+        <v>0.0405</v>
       </c>
       <c r="F137" s="18" t="n">
-        <v>0.0848</v>
+        <v>0.0824</v>
       </c>
       <c r="G137" s="15" t="n">
         <v>46254</v>
@@ -11069,7 +11069,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="18" t="n">
-        <v>0.2051677593521017</v>
+        <v>0.2078850737615152</v>
       </c>
       <c r="N137" s="12" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="18" t="n">
-        <v>0.03048270985987902</v>
+        <v>0.03280615860336276</v>
       </c>
       <c r="Q137" s="19" t="inlineStr">
         <is>
@@ -11121,13 +11121,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>159.15</v>
+        <v>158.21</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0.1661</v>
+        <v>0.1592</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.1444</v>
+        <v>0.1376</v>
       </c>
       <c r="G138" s="6" t="n"/>
       <c r="H138" s="7" t="inlineStr">
@@ -11153,7 +11153,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="5" t="n">
-        <v>0.162425384857053</v>
+        <v>0.169331900638392</v>
       </c>
       <c r="Q138" s="9" t="inlineStr">
         <is>
@@ -11192,13 +11192,13 @@
         </is>
       </c>
       <c r="D139" s="13" t="n">
-        <v>448.39</v>
+        <v>448.64</v>
       </c>
       <c r="E139" s="18" t="n">
-        <v>0.1222</v>
+        <v>0.1228</v>
       </c>
       <c r="F139" s="18" t="n">
-        <v>0.1122</v>
+        <v>0.1129</v>
       </c>
       <c r="G139" s="15" t="n"/>
       <c r="H139" s="21" t="inlineStr">
@@ -11224,7 +11224,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="18" t="n">
-        <v>0.01028122839492409</v>
+        <v>0.009718259629101314</v>
       </c>
       <c r="Q139" s="19" t="inlineStr">
         <is>
@@ -11265,13 +11265,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>51.38</v>
+        <v>51.84</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0.1048</v>
+        <v>0.1146</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>0.1171</v>
+        <v>0.127</v>
       </c>
       <c r="G140" s="6" t="n">
         <v>46309</v>
@@ -11344,13 +11344,13 @@
         </is>
       </c>
       <c r="D141" s="13" t="n">
-        <v>317.18</v>
+        <v>318.55</v>
       </c>
       <c r="E141" s="18" t="n">
-        <v>0.0239</v>
+        <v>0.0284</v>
       </c>
       <c r="F141" s="14" t="n">
-        <v>-0.0395</v>
+        <v>-0.0353</v>
       </c>
       <c r="G141" s="15" t="n">
         <v>46282</v>
@@ -11379,7 +11379,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="18" t="n">
-        <v>0.3399331609811463</v>
+        <v>0.3341704598964055</v>
       </c>
       <c r="N141" s="12" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>323</v>
       </c>
       <c r="P141" s="18" t="n">
-        <v>0.01834920234567121</v>
+        <v>0.01396954952126821</v>
       </c>
       <c r="Q141" s="19" t="inlineStr">
         <is>
@@ -11431,13 +11431,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>260.88</v>
+        <v>256.53</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0.178</v>
+        <v>0.1584</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>0.1631</v>
+        <v>0.1437</v>
       </c>
       <c r="G142" s="6" t="n">
         <v>46244</v>
@@ -11466,7 +11466,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="5" t="n">
-        <v>0.0924563017479301</v>
+        <v>0.1109811717927729</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="8" t="n"/>
@@ -11514,13 +11514,13 @@
         </is>
       </c>
       <c r="D143" s="13" t="n">
-        <v>1677.69</v>
-      </c>
-      <c r="E143" s="14" t="n">
-        <v>-0.0043</v>
+        <v>1693.43</v>
+      </c>
+      <c r="E143" s="18" t="n">
+        <v>0.005</v>
       </c>
       <c r="F143" s="14" t="n">
-        <v>-0.0941</v>
+        <v>-0.08560000000000001</v>
       </c>
       <c r="G143" s="15" t="n">
         <v>46317</v>
@@ -11575,13 +11575,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>55.65</v>
+        <v>57.09</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>0.124</v>
+        <v>0.1531</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>0.1238</v>
+        <v>0.1529</v>
       </c>
       <c r="G144" s="6" t="n">
         <v>46241</v>
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="D145" s="13" t="n">
-        <v>385.1</v>
+        <v>391.99</v>
       </c>
       <c r="E145" s="18" t="n">
-        <v>0.0288</v>
+        <v>0.0472</v>
       </c>
       <c r="F145" s="18" t="n">
-        <v>0.1298</v>
+        <v>0.15</v>
       </c>
       <c r="G145" s="15" t="n"/>
       <c r="H145" s="21" t="inlineStr">
@@ -11661,7 +11661,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="18" t="n">
-        <v>0.03869124902622689</v>
+        <v>0.02043419474986604</v>
       </c>
       <c r="N145" s="12" t="inlineStr"/>
       <c r="O145" s="17" t="n"/>
@@ -11713,13 +11713,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>370.96</v>
+        <v>370.11</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0.04190000000000001</v>
+        <v>0.0396</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>0.1519</v>
+        <v>0.1493</v>
       </c>
       <c r="G146" s="6" t="n">
         <v>46315</v>
@@ -11748,7 +11748,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="5" t="n">
-        <v>0.05132628854863064</v>
+        <v>0.05374077976817699</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="8" t="n"/>
@@ -11800,13 +11800,13 @@
         </is>
       </c>
       <c r="D147" s="13" t="n">
-        <v>972.59</v>
+        <v>990.42</v>
       </c>
       <c r="E147" s="14" t="n">
-        <v>-0.0919</v>
+        <v>-0.07519999999999999</v>
       </c>
       <c r="F147" s="18" t="n">
-        <v>0.0415</v>
+        <v>0.06059999999999999</v>
       </c>
       <c r="G147" s="15" t="n">
         <v>46316</v>
@@ -11835,7 +11835,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="18" t="n">
-        <v>0.2944817446200351</v>
+        <v>0.2711778841299651</v>
       </c>
       <c r="N147" s="12" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="18" t="n">
-        <v>0.3880463504662807</v>
+        <v>0.3630580965650936</v>
       </c>
       <c r="Q147" s="19" t="inlineStr">
         <is>
@@ -11891,13 +11891,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1291.66</v>
+        <v>1277.12</v>
       </c>
       <c r="E148" s="22" t="n">
-        <v>-0.043</v>
+        <v>-0.0538</v>
       </c>
       <c r="F148" s="22" t="n">
-        <v>-0.009899999999999999</v>
+        <v>-0.021</v>
       </c>
       <c r="G148" s="6" t="n"/>
       <c r="H148" s="7" t="inlineStr">
@@ -11956,13 +11956,13 @@
         </is>
       </c>
       <c r="D149" s="13" t="n">
-        <v>243.63</v>
+        <v>246.21</v>
       </c>
       <c r="E149" s="18" t="n">
-        <v>0.1056</v>
+        <v>0.1173</v>
       </c>
       <c r="F149" s="18" t="n">
-        <v>0.0968</v>
+        <v>0.1084</v>
       </c>
       <c r="G149" s="15" t="n">
         <v>46317</v>
@@ -12017,13 +12017,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>516.79</v>
+        <v>513.91</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>0.0755</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>0.0655</v>
+        <v>0.0595</v>
       </c>
       <c r="G150" s="6" t="n"/>
       <c r="H150" s="7" t="inlineStr">
@@ -12074,13 +12074,13 @@
         </is>
       </c>
       <c r="D151" s="13" t="n">
-        <v>296.85</v>
+        <v>296.56</v>
       </c>
       <c r="E151" s="18" t="n">
-        <v>0.1198</v>
+        <v>0.1187</v>
       </c>
       <c r="F151" s="18" t="n">
-        <v>0.1762</v>
+        <v>0.175</v>
       </c>
       <c r="G151" s="15" t="n"/>
       <c r="H151" s="21" t="inlineStr">
@@ -12102,7 +12102,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="14" t="n">
-        <v>-0.0837123126157993</v>
+        <v>-0.08281629349878608</v>
       </c>
       <c r="Q151" s="19" t="inlineStr">
         <is>
@@ -12155,13 +12155,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>285.52</v>
+        <v>286.63</v>
       </c>
       <c r="E152" s="22" t="n">
-        <v>-0.027</v>
+        <v>-0.0232</v>
       </c>
       <c r="F152" s="22" t="n">
-        <v>-0.0549</v>
+        <v>-0.0512</v>
       </c>
       <c r="G152" s="6" t="n"/>
       <c r="H152" s="7" t="inlineStr">
@@ -12216,13 +12216,13 @@
         </is>
       </c>
       <c r="D153" s="13" t="n">
-        <v>442.58</v>
+        <v>439.61</v>
       </c>
       <c r="E153" s="14" t="n">
-        <v>-0.177</v>
+        <v>-0.1825</v>
       </c>
       <c r="F153" s="14" t="n">
-        <v>-0.138</v>
+        <v>-0.1438</v>
       </c>
       <c r="G153" s="15" t="n"/>
       <c r="H153" s="21" t="inlineStr">
@@ -12267,13 +12267,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>579.34</v>
+        <v>587.79</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0.0973</v>
+        <v>0.1133</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0.114</v>
+        <v>0.1302</v>
       </c>
       <c r="G154" s="6" t="n">
         <v>46315</v>
@@ -12334,13 +12334,13 @@
         </is>
       </c>
       <c r="D155" s="13" t="n">
-        <v>214.68</v>
+        <v>216.36</v>
       </c>
       <c r="E155" s="14" t="n">
-        <v>-0.0164</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F155" s="14" t="n">
-        <v>-0.1309</v>
+        <v>-0.1241</v>
       </c>
       <c r="G155" s="15" t="n"/>
       <c r="H155" s="21" t="inlineStr">
@@ -12359,7 +12359,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="18" t="n">
-        <v>1.678405068008198</v>
+        <v>1.657607690885561</v>
       </c>
       <c r="N155" s="12" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="18" t="n">
-        <v>0.1039686975964225</v>
+        <v>0.09539656128674424</v>
       </c>
       <c r="Q155" s="19" t="inlineStr">
         <is>
@@ -12419,13 +12419,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>121.28</v>
+        <v>120.04</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0.1379</v>
+        <v>0.1263</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.226</v>
+        <v>0.2135</v>
       </c>
       <c r="G156" s="6" t="n">
         <v>46294</v>
@@ -12454,7 +12454,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="5" t="n">
-        <v>1.061345646437995</v>
+        <v>1.082639120293235</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="8" t="n"/>
@@ -12498,13 +12498,13 @@
         </is>
       </c>
       <c r="D157" s="13" t="n">
-        <v>131.87</v>
+        <v>133.11</v>
       </c>
       <c r="E157" s="18" t="n">
-        <v>0.0764</v>
+        <v>0.0866</v>
       </c>
       <c r="F157" s="18" t="n">
-        <v>0.1133</v>
+        <v>0.1239</v>
       </c>
       <c r="G157" s="15" t="n"/>
       <c r="H157" s="21" t="inlineStr">
@@ -12523,7 +12523,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="14" t="n">
-        <v>-0.2795935390915296</v>
+        <v>-0.2863045601382316</v>
       </c>
       <c r="N157" s="12" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="18" t="n">
-        <v>0.05406840069765675</v>
+        <v>0.04424911727142954</v>
       </c>
       <c r="Q157" s="19" t="inlineStr">
         <is>
@@ -12579,13 +12579,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>1083.71</v>
+        <v>1073.86</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>0.154</v>
+        <v>0.1435</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>0.2271</v>
+        <v>0.216</v>
       </c>
       <c r="G158" s="6" t="n"/>
       <c r="H158" s="7" t="inlineStr">
@@ -12604,7 +12604,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="22" t="n">
-        <v>-0.8846554890145888</v>
+        <v>-0.8835974894306521</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>1064</v>
       </c>
       <c r="P158" s="22" t="n">
-        <v>-0.01818752249217968</v>
+        <v>-0.009181830033710075</v>
       </c>
       <c r="Q158" s="9" t="inlineStr">
         <is>
@@ -12660,13 +12660,13 @@
         </is>
       </c>
       <c r="D159" s="13" t="n">
-        <v>564.64</v>
+        <v>567.33</v>
       </c>
       <c r="E159" s="14" t="n">
-        <v>-0.0493</v>
+        <v>-0.0447</v>
       </c>
       <c r="F159" s="14" t="n">
-        <v>-0.0446</v>
+        <v>-0.04</v>
       </c>
       <c r="G159" s="15" t="n"/>
       <c r="H159" s="21" t="inlineStr">
@@ -12731,13 +12731,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>443.8</v>
+        <v>440.85</v>
       </c>
       <c r="E160" s="22" t="n">
-        <v>-0.04269999999999999</v>
+        <v>-0.0491</v>
       </c>
       <c r="F160" s="22" t="n">
-        <v>-0.0174</v>
+        <v>-0.0239</v>
       </c>
       <c r="G160" s="6" t="n"/>
       <c r="H160" s="7" t="inlineStr">
@@ -12782,13 +12782,13 @@
         </is>
       </c>
       <c r="D161" s="13" t="n">
-        <v>37.37</v>
+        <v>37.75</v>
       </c>
       <c r="E161" s="14" t="n">
-        <v>-0.1686</v>
+        <v>-0.1602</v>
       </c>
       <c r="F161" s="14" t="n">
-        <v>-0.1977</v>
+        <v>-0.1896</v>
       </c>
       <c r="G161" s="15" t="n">
         <v>46323</v>
@@ -12857,13 +12857,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>221.19</v>
+        <v>222.97</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>0.1348</v>
+        <v>0.144</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>0.238</v>
+        <v>0.248</v>
       </c>
       <c r="G162" s="6" t="n">
         <v>46322</v>
@@ -12936,13 +12936,13 @@
         </is>
       </c>
       <c r="D163" s="13" t="n">
-        <v>40.63</v>
+        <v>40.18</v>
       </c>
       <c r="E163" s="14" t="n">
-        <v>-0.0253</v>
+        <v>-0.0362</v>
       </c>
       <c r="F163" s="14" t="n">
-        <v>-0.0834</v>
+        <v>-0.09359999999999999</v>
       </c>
       <c r="G163" s="15" t="n"/>
       <c r="H163" s="21" t="inlineStr">
@@ -12987,13 +12987,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>480.99</v>
+        <v>482.27</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>0.0184</v>
+        <v>0.0211</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>0.0481</v>
+        <v>0.0509</v>
       </c>
       <c r="G164" s="6" t="n"/>
       <c r="H164" s="7" t="inlineStr">
@@ -13015,7 +13015,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="5" t="n">
-        <v>0.1642653693423979</v>
+        <v>0.1611752752607461</v>
       </c>
       <c r="Q164" s="9" t="inlineStr">
         <is>
@@ -13068,13 +13068,13 @@
         </is>
       </c>
       <c r="D165" s="13" t="n">
-        <v>294.54</v>
+        <v>293.08</v>
       </c>
       <c r="E165" s="18" t="n">
-        <v>0.0484</v>
+        <v>0.0432</v>
       </c>
       <c r="F165" s="18" t="n">
-        <v>0.09630000000000001</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="G165" s="15" t="n">
         <v>46317</v>
@@ -13105,8 +13105,8 @@
       <c r="O165" s="17" t="n">
         <v>294</v>
       </c>
-      <c r="P165" s="14" t="n">
-        <v>-0.001833367284579413</v>
+      <c r="P165" s="18" t="n">
+        <v>0.00313907465538425</v>
       </c>
       <c r="Q165" s="19" t="inlineStr">
         <is>
@@ -13151,13 +13151,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>274.52</v>
+        <v>272.47</v>
       </c>
       <c r="E166" s="22" t="n">
-        <v>-0.1362</v>
+        <v>-0.1427</v>
       </c>
       <c r="F166" s="22" t="n">
-        <v>-0.0867</v>
+        <v>-0.0935</v>
       </c>
       <c r="G166" s="6" t="n"/>
       <c r="H166" s="7" t="inlineStr">
@@ -13179,7 +13179,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="5" t="n">
-        <v>0.5481567827480694</v>
+        <v>0.5598047491466949</v>
       </c>
       <c r="Q166" s="9" t="inlineStr">
         <is>
@@ -13220,13 +13220,13 @@
         </is>
       </c>
       <c r="D167" s="13" t="n">
-        <v>230.87</v>
+        <v>227.69</v>
       </c>
       <c r="E167" s="14" t="n">
-        <v>-0.0131</v>
+        <v>-0.0267</v>
       </c>
       <c r="F167" s="18" t="n">
-        <v>0.0682</v>
+        <v>0.0534</v>
       </c>
       <c r="G167" s="15" t="n"/>
       <c r="H167" s="21" t="inlineStr">
@@ -13245,7 +13245,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="18" t="n">
-        <v>0.1608264391215836</v>
+        <v>0.1770389564759103</v>
       </c>
       <c r="N167" s="12" t="inlineStr"/>
       <c r="O167" s="17" t="n"/>
@@ -13293,13 +13293,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>333.46</v>
+        <v>330.05</v>
       </c>
       <c r="E168" s="22" t="n">
-        <v>-0.123</v>
+        <v>-0.132</v>
       </c>
       <c r="F168" s="22" t="n">
-        <v>-0.1032</v>
+        <v>-0.1124</v>
       </c>
       <c r="G168" s="6" t="n"/>
       <c r="H168" s="7" t="inlineStr">
@@ -13358,13 +13358,13 @@
         </is>
       </c>
       <c r="D169" s="13" t="n">
-        <v>362.8</v>
+        <v>362.89</v>
       </c>
       <c r="E169" s="14" t="n">
-        <v>-0.092</v>
+        <v>-0.09179999999999999</v>
       </c>
       <c r="F169" s="18" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0086</v>
       </c>
       <c r="G169" s="15" t="n"/>
       <c r="H169" s="21" t="inlineStr">
@@ -13427,13 +13427,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>122.13</v>
+        <v>120.33</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>0.0296</v>
+        <v>0.0145</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>0.1151</v>
+        <v>0.0987</v>
       </c>
       <c r="G170" s="6" t="n"/>
       <c r="H170" s="7" t="inlineStr">
@@ -13496,13 +13496,13 @@
         </is>
       </c>
       <c r="D171" s="13" t="n">
-        <v>141.75</v>
+        <v>135.63</v>
       </c>
       <c r="E171" s="18" t="n">
-        <v>0.2386</v>
+        <v>0.1852</v>
       </c>
       <c r="F171" s="14" t="n">
-        <v>-0.2791</v>
+        <v>-0.3103</v>
       </c>
       <c r="G171" s="15" t="n"/>
       <c r="H171" s="21" t="inlineStr">
@@ -13547,13 +13547,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>314.73</v>
-      </c>
-      <c r="E172" s="5" t="n">
-        <v>0.0043</v>
+        <v>313.33</v>
+      </c>
+      <c r="E172" s="22" t="n">
+        <v>-0.0002</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>0.0438</v>
+        <v>0.0391</v>
       </c>
       <c r="G172" s="6" t="n"/>
       <c r="H172" s="7" t="inlineStr">
@@ -13572,7 +13572,7 @@
         <v>310</v>
       </c>
       <c r="M172" s="22" t="n">
-        <v>-0.01502875480570654</v>
+        <v>-0.01062777263587905</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="5" t="n">
-        <v>0.1597242080513455</v>
+        <v>0.1649060096384005</v>
       </c>
       <c r="Q172" s="9" t="inlineStr">
         <is>
@@ -13640,13 +13640,13 @@
         </is>
       </c>
       <c r="D173" s="13" t="n">
-        <v>139.06</v>
+        <v>140.27</v>
       </c>
       <c r="E173" s="18" t="n">
-        <v>0.0268</v>
+        <v>0.0357</v>
       </c>
       <c r="F173" s="14" t="n">
-        <v>-0.1014</v>
+        <v>-0.09359999999999999</v>
       </c>
       <c r="G173" s="15" t="n"/>
       <c r="H173" s="21" t="inlineStr">
@@ -13691,13 +13691,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>174.5</v>
+        <v>175.65</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>0.272</v>
+        <v>0.2803</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="G174" s="6" t="n">
         <v>46289</v>
@@ -13752,13 +13752,13 @@
         </is>
       </c>
       <c r="D175" s="13" t="n">
-        <v>269.46</v>
+        <v>265.21</v>
       </c>
       <c r="E175" s="18" t="n">
-        <v>0.2196</v>
+        <v>0.2004</v>
       </c>
       <c r="F175" s="18" t="n">
-        <v>0.0999</v>
+        <v>0.0825</v>
       </c>
       <c r="G175" s="15" t="n">
         <v>46275</v>
@@ -13813,13 +13813,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>389.35</v>
+        <v>389.93</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0118</v>
       </c>
       <c r="F176" s="22" t="n">
-        <v>-0.036</v>
+        <v>-0.0346</v>
       </c>
       <c r="G176" s="6" t="n">
         <v>46253</v>
@@ -13848,7 +13848,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="5" t="n">
-        <v>0.3227173494285346</v>
+        <v>0.3207498781832636</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="5" t="n">
-        <v>0.2174136381148067</v>
+        <v>0.2156028005026543</v>
       </c>
       <c r="Q176" s="9" t="inlineStr">
         <is>
@@ -13908,13 +13908,13 @@
         </is>
       </c>
       <c r="D177" s="13" t="n">
-        <v>252.6</v>
+        <v>249.08</v>
       </c>
       <c r="E177" s="18" t="n">
-        <v>0.226</v>
+        <v>0.2089</v>
       </c>
       <c r="F177" s="18" t="n">
-        <v>0.1224</v>
+        <v>0.1068</v>
       </c>
       <c r="G177" s="15" t="n">
         <v>46261</v>
@@ -13969,13 +13969,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>324.33</v>
+        <v>325.02</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>0.1045</v>
+        <v>0.1069</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>0.0595</v>
+        <v>0.06179999999999999</v>
       </c>
       <c r="G178" s="6" t="n"/>
       <c r="H178" s="7" t="inlineStr">
@@ -14020,13 +14020,13 @@
         </is>
       </c>
       <c r="D179" s="13" t="n">
-        <v>336.7</v>
+        <v>334.17</v>
       </c>
       <c r="E179" s="14" t="n">
-        <v>-0.1436</v>
+        <v>-0.15</v>
       </c>
       <c r="F179" s="14" t="n">
-        <v>-0.0278</v>
+        <v>-0.0351</v>
       </c>
       <c r="G179" s="15" t="n"/>
       <c r="H179" s="21" t="inlineStr">
@@ -14071,13 +14071,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>43.49</v>
+        <v>43.77</v>
       </c>
       <c r="E180" s="22" t="n">
-        <v>-0.155</v>
+        <v>-0.1495</v>
       </c>
       <c r="F180" s="22" t="n">
-        <v>-0.0975</v>
+        <v>-0.0917</v>
       </c>
       <c r="G180" s="6" t="n"/>
       <c r="H180" s="7" t="inlineStr">
@@ -14122,13 +14122,13 @@
         </is>
       </c>
       <c r="D181" s="13" t="n">
-        <v>537.63</v>
+        <v>539.14</v>
       </c>
       <c r="E181" s="14" t="n">
-        <v>-0.0576</v>
+        <v>-0.055</v>
       </c>
       <c r="F181" s="18" t="n">
-        <v>0.0924</v>
+        <v>0.09539999999999998</v>
       </c>
       <c r="G181" s="15" t="n">
         <v>46247</v>
@@ -14157,7 +14157,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="18" t="n">
-        <v>0.3764112865725499</v>
+        <v>0.3725562933560856</v>
       </c>
       <c r="N181" s="12" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="18" t="n">
-        <v>0.3020106764875472</v>
+        <v>0.2983640612827837</v>
       </c>
       <c r="Q181" s="19" t="inlineStr">
         <is>
@@ -14209,13 +14209,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>66.92</v>
+        <v>67.63</v>
       </c>
       <c r="E182" s="22" t="n">
-        <v>-0.1832</v>
+        <v>-0.1745</v>
       </c>
       <c r="F182" s="22" t="n">
-        <v>-0.1545</v>
+        <v>-0.1455</v>
       </c>
       <c r="G182" s="6" t="n">
         <v>46245</v>
@@ -14274,13 +14274,13 @@
         </is>
       </c>
       <c r="D183" s="13" t="n">
-        <v>480.92</v>
+        <v>483.36</v>
       </c>
       <c r="E183" s="14" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0658</v>
       </c>
       <c r="F183" s="14" t="n">
-        <v>-0.0192</v>
+        <v>-0.0142</v>
       </c>
       <c r="G183" s="15" t="n"/>
       <c r="H183" s="21" t="inlineStr">
@@ -14299,7 +14299,7 @@
         <v>615</v>
       </c>
       <c r="M183" s="18" t="n">
-        <v>0.2787989686434334</v>
+        <v>0.272343594836147</v>
       </c>
       <c r="N183" s="12" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="18" t="n">
-        <v>0.2039424436496714</v>
+        <v>0.1978649453823237</v>
       </c>
       <c r="Q183" s="19" t="inlineStr">
         <is>
@@ -14351,13 +14351,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>54.35</v>
+        <v>55.27</v>
       </c>
       <c r="E184" s="22" t="n">
-        <v>-0.1877</v>
+        <v>-0.174</v>
       </c>
       <c r="F184" s="22" t="n">
-        <v>-0.2041</v>
+        <v>-0.1907</v>
       </c>
       <c r="G184" s="6" t="n"/>
       <c r="H184" s="7" t="inlineStr">
@@ -14402,13 +14402,13 @@
         </is>
       </c>
       <c r="D185" s="13" t="n">
-        <v>190.29</v>
+        <v>188.63</v>
       </c>
       <c r="E185" s="18" t="n">
-        <v>0.051</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="F185" s="18" t="n">
-        <v>0.2167</v>
+        <v>0.2061</v>
       </c>
       <c r="G185" s="15" t="n"/>
       <c r="H185" s="21" t="inlineStr">
@@ -14427,7 +14427,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="18" t="n">
-        <v>0.05102737926322985</v>
+        <v>0.0602767322271113</v>
       </c>
       <c r="N185" s="12" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="18" t="n">
-        <v>0.05102737926322985</v>
+        <v>0.0602767322271113</v>
       </c>
       <c r="Q185" s="19" t="inlineStr">
         <is>
@@ -14483,13 +14483,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>168.67</v>
+        <v>169.17</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>0.066</v>
+        <v>0.0692</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>0.1746</v>
+        <v>0.1781</v>
       </c>
       <c r="G186" s="6" t="n"/>
       <c r="H186" s="7" t="inlineStr">
@@ -14511,7 +14511,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="5" t="n">
-        <v>0.06717258552202533</v>
+        <v>0.06401844298634518</v>
       </c>
       <c r="Q186" s="9" t="inlineStr">
         <is>
@@ -14564,13 +14564,13 @@
         </is>
       </c>
       <c r="D187" s="13" t="n">
-        <v>28.59</v>
+        <v>29.22</v>
       </c>
       <c r="E187" s="14" t="n">
-        <v>-0.0906</v>
+        <v>-0.0706</v>
       </c>
       <c r="F187" s="14" t="n">
-        <v>-0.3017</v>
+        <v>-0.2864</v>
       </c>
       <c r="G187" s="15" t="n"/>
       <c r="H187" s="21" t="inlineStr">
@@ -14615,13 +14615,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>281.01</v>
+        <v>282.57</v>
       </c>
       <c r="E188" s="22" t="n">
-        <v>-0.064</v>
+        <v>-0.05889999999999999</v>
       </c>
       <c r="F188" s="22" t="n">
-        <v>-0.1887</v>
+        <v>-0.1842</v>
       </c>
       <c r="G188" s="6" t="n"/>
       <c r="H188" s="7" t="inlineStr">
@@ -14666,13 +14666,13 @@
         </is>
       </c>
       <c r="D189" s="13" t="n">
-        <v>1734.64</v>
+        <v>1740.99</v>
       </c>
       <c r="E189" s="14" t="n">
-        <v>-0.0192</v>
+        <v>-0.0156</v>
       </c>
       <c r="F189" s="14" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.0046</v>
       </c>
       <c r="G189" s="15" t="n">
         <v>46309</v>
@@ -14745,13 +14745,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>37.01</v>
+        <v>37.41</v>
       </c>
       <c r="E190" s="22" t="n">
-        <v>-0.0731</v>
+        <v>-0.06309999999999999</v>
       </c>
       <c r="F190" s="5" t="n">
-        <v>0.04190000000000001</v>
+        <v>0.0532</v>
       </c>
       <c r="G190" s="6" t="n"/>
       <c r="H190" s="7" t="inlineStr">
@@ -14796,13 +14796,13 @@
         </is>
       </c>
       <c r="D191" s="13" t="n">
-        <v>426.11</v>
+        <v>427.76</v>
       </c>
       <c r="E191" s="18" t="n">
-        <v>0.09630000000000001</v>
+        <v>0.1005</v>
       </c>
       <c r="F191" s="18" t="n">
-        <v>0.07440000000000001</v>
+        <v>0.0786</v>
       </c>
       <c r="G191" s="15" t="n">
         <v>46268</v>
@@ -14831,7 +14831,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="18" t="n">
-        <v>0.2790124615709558</v>
+        <v>0.2740789227604264</v>
       </c>
       <c r="N191" s="12" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="18" t="n">
-        <v>0.3658445002464152</v>
+        <v>0.3605760239386572</v>
       </c>
       <c r="Q191" s="19" t="inlineStr">
         <is>
@@ -14895,13 +14895,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>154.17</v>
+        <v>155.35</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>0.1008</v>
+        <v>0.1092</v>
       </c>
       <c r="F192" s="22" t="n">
-        <v>-0.08599999999999999</v>
+        <v>-0.079</v>
       </c>
       <c r="G192" s="6" t="n">
         <v>46244</v>
@@ -14956,13 +14956,13 @@
         </is>
       </c>
       <c r="D193" s="13" t="n">
-        <v>344.75</v>
+        <v>339.24</v>
       </c>
       <c r="E193" s="14" t="n">
-        <v>-0.0784</v>
+        <v>-0.0931</v>
       </c>
       <c r="F193" s="14" t="n">
-        <v>-0.1255</v>
+        <v>-0.1395</v>
       </c>
       <c r="G193" s="15" t="n"/>
       <c r="H193" s="21" t="inlineStr">
@@ -14981,7 +14981,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="18" t="n">
-        <v>0.2327773749093546</v>
+        <v>0.252800377313996</v>
       </c>
       <c r="N193" s="12" t="inlineStr"/>
       <c r="O193" s="17" t="n"/>
@@ -15025,13 +15025,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>126.89</v>
+        <v>127.82</v>
       </c>
       <c r="E194" s="22" t="n">
-        <v>-0.0728</v>
+        <v>-0.066</v>
       </c>
       <c r="F194" s="22" t="n">
-        <v>-0.0185</v>
+        <v>-0.0113</v>
       </c>
       <c r="G194" s="6" t="n"/>
       <c r="H194" s="7" t="inlineStr">
@@ -15076,13 +15076,13 @@
         </is>
       </c>
       <c r="D195" s="13" t="n">
-        <v>401.36</v>
+        <v>412.34</v>
       </c>
       <c r="E195" s="14" t="n">
-        <v>-0.0898</v>
+        <v>-0.0649</v>
       </c>
       <c r="F195" s="14" t="n">
-        <v>-0.1399</v>
+        <v>-0.1164</v>
       </c>
       <c r="G195" s="15" t="n">
         <v>46268</v>
@@ -15137,13 +15137,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>15.68</v>
+        <v>16.01</v>
       </c>
       <c r="E196" s="22" t="n">
-        <v>-0.0506</v>
+        <v>-0.0303</v>
       </c>
       <c r="F196" s="5" t="n">
-        <v>0.1672</v>
+        <v>0.1921</v>
       </c>
       <c r="G196" s="6" t="n">
         <v>46247</v>
@@ -15198,13 +15198,13 @@
         </is>
       </c>
       <c r="D197" s="13" t="n">
-        <v>309.9</v>
+        <v>317.99</v>
       </c>
       <c r="E197" s="14" t="n">
-        <v>-0.1409</v>
+        <v>-0.1185</v>
       </c>
       <c r="F197" s="14" t="n">
-        <v>-0.1982</v>
+        <v>-0.1773</v>
       </c>
       <c r="G197" s="15" t="n"/>
       <c r="H197" s="21" t="inlineStr">
@@ -15249,13 +15249,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>374.87</v>
+        <v>378.8</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>0.1824</v>
+        <v>0.1948</v>
       </c>
       <c r="F198" s="22" t="n">
-        <v>-0.0673</v>
+        <v>-0.0575</v>
       </c>
       <c r="G198" s="6" t="n">
         <v>46246</v>
@@ -15310,13 +15310,13 @@
         </is>
       </c>
       <c r="D199" s="13" t="n">
-        <v>52.85</v>
+        <v>52.88</v>
       </c>
       <c r="E199" s="18" t="n">
-        <v>0.0141</v>
+        <v>0.0146</v>
       </c>
       <c r="F199" s="18" t="n">
-        <v>0.0066</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="G199" s="15" t="n"/>
       <c r="H199" s="21" t="inlineStr">
@@ -15361,13 +15361,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>20.86</v>
+        <v>21.01</v>
       </c>
       <c r="E200" s="22" t="n">
-        <v>-0.1123</v>
+        <v>-0.106</v>
       </c>
       <c r="F200" s="22" t="n">
-        <v>-0.2317</v>
+        <v>-0.2262</v>
       </c>
       <c r="G200" s="6" t="n"/>
       <c r="H200" s="7" t="inlineStr">
@@ -15412,13 +15412,13 @@
         </is>
       </c>
       <c r="D201" s="13" t="n">
-        <v>240.88</v>
+        <v>249.89</v>
       </c>
       <c r="E201" s="14" t="n">
-        <v>-0.0688</v>
+        <v>-0.034</v>
       </c>
       <c r="F201" s="18" t="n">
-        <v>0.0837</v>
+        <v>0.1243</v>
       </c>
       <c r="G201" s="15" t="n">
         <v>46267</v>
@@ -15473,13 +15473,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>194.1</v>
+        <v>192.72</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>0.1652</v>
+        <v>0.1569</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>0.0633</v>
+        <v>0.0557</v>
       </c>
       <c r="G202" s="6" t="n">
         <v>46260</v>
@@ -15508,7 +15508,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="5" t="n">
-        <v>0.03039670273055129</v>
+        <v>0.03777501037775011</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="5" t="n">
-        <v>0.2879958784131891</v>
+        <v>0.2972187629721876</v>
       </c>
       <c r="Q202" s="9" t="inlineStr">
         <is>
@@ -15564,13 +15564,13 @@
         </is>
       </c>
       <c r="D203" s="13" t="n">
-        <v>212.12</v>
+        <v>214.42</v>
       </c>
       <c r="E203" s="18" t="n">
-        <v>0.1099</v>
+        <v>0.1219</v>
       </c>
       <c r="F203" s="18" t="n">
-        <v>0.2879</v>
+        <v>0.3019</v>
       </c>
       <c r="G203" s="15" t="n">
         <v>46260</v>
@@ -15599,7 +15599,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="14" t="n">
-        <v>-0.1455308316047521</v>
+        <v>-0.1546963902621024</v>
       </c>
       <c r="N203" s="12" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="14" t="n">
-        <v>-0.1632095040543089</v>
+        <v>-0.1721854304635761</v>
       </c>
       <c r="Q203" s="19" t="inlineStr">
         <is>
@@ -15651,13 +15651,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>87.45999999999999</v>
-      </c>
-      <c r="E204" s="22" t="n">
-        <v>-0.0282</v>
+        <v>90.67</v>
+      </c>
+      <c r="E204" s="5" t="n">
+        <v>0.0074</v>
       </c>
       <c r="F204" s="22" t="n">
-        <v>-0.1456</v>
+        <v>-0.1143</v>
       </c>
       <c r="G204" s="6" t="n">
         <v>46245</v>
@@ -15712,13 +15712,13 @@
         </is>
       </c>
       <c r="D205" s="13" t="n">
-        <v>120.31</v>
+        <v>121.43</v>
       </c>
       <c r="E205" s="18" t="n">
-        <v>0.057</v>
+        <v>0.0669</v>
       </c>
       <c r="F205" s="14" t="n">
-        <v>-0.031</v>
+        <v>-0.0219</v>
       </c>
       <c r="G205" s="15" t="n">
         <v>46246</v>
@@ -15747,7 +15747,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="18" t="n">
-        <v>0.08054193333887455</v>
+        <v>0.07057564028658481</v>
       </c>
       <c r="N205" s="12" t="inlineStr">
         <is>
@@ -15758,7 +15758,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="18" t="n">
-        <v>0.2467791538525476</v>
+        <v>0.2352795849460594</v>
       </c>
       <c r="Q205" s="19" t="inlineStr">
         <is>
@@ -15815,13 +15815,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>238.4</v>
+        <v>233.93</v>
       </c>
       <c r="E206" s="22" t="n">
-        <v>-0.08689999999999999</v>
+        <v>-0.104</v>
       </c>
       <c r="F206" s="5" t="n">
-        <v>0.029</v>
+        <v>0.0097</v>
       </c>
       <c r="G206" s="6" t="n"/>
       <c r="H206" s="7" t="inlineStr">
@@ -15866,13 +15866,13 @@
         </is>
       </c>
       <c r="D207" s="13" t="n">
-        <v>425.61</v>
-      </c>
-      <c r="E207" s="14" t="n">
-        <v>-0.0147</v>
+        <v>453.77</v>
+      </c>
+      <c r="E207" s="18" t="n">
+        <v>0.0505</v>
       </c>
       <c r="F207" s="18" t="n">
-        <v>0.062</v>
+        <v>0.1323</v>
       </c>
       <c r="G207" s="15" t="n">
         <v>46261</v>
@@ -15927,13 +15927,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>59.65</v>
+        <v>60.26</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>0.2632</v>
+        <v>0.2762</v>
       </c>
       <c r="F208" s="5" t="n">
-        <v>0.2922</v>
+        <v>0.3055</v>
       </c>
       <c r="G208" s="6" t="n">
         <v>46268</v>
@@ -15988,13 +15988,13 @@
         </is>
       </c>
       <c r="D209" s="13" t="n">
-        <v>50.19</v>
+        <v>48.95</v>
       </c>
       <c r="E209" s="18" t="n">
-        <v>0.1448</v>
+        <v>0.1166</v>
       </c>
       <c r="F209" s="18" t="n">
-        <v>0.1973</v>
+        <v>0.1677</v>
       </c>
       <c r="G209" s="15" t="n"/>
       <c r="H209" s="21" t="inlineStr">
@@ -16039,13 +16039,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>563.64</v>
+        <v>562.22</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>0.1741</v>
+        <v>0.1711</v>
       </c>
       <c r="F210" s="22" t="n">
-        <v>-0.09630000000000001</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="G210" s="6" t="n">
         <v>46251</v>
@@ -16100,13 +16100,13 @@
         </is>
       </c>
       <c r="D211" s="13" t="n">
-        <v>117.6</v>
+        <v>117.39</v>
       </c>
       <c r="E211" s="18" t="n">
-        <v>0.0539</v>
+        <v>0.052</v>
       </c>
       <c r="F211" s="14" t="n">
-        <v>-0.0535</v>
+        <v>-0.0552</v>
       </c>
       <c r="G211" s="15" t="n"/>
       <c r="H211" s="21" t="inlineStr">
@@ -16151,13 +16151,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>160.95</v>
+        <v>159.64</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>0.0271</v>
+        <v>0.0187</v>
       </c>
       <c r="F212" s="5" t="n">
-        <v>0.1252</v>
+        <v>0.1161</v>
       </c>
       <c r="G212" s="6" t="n"/>
       <c r="H212" s="7" t="inlineStr">
@@ -16202,13 +16202,13 @@
         </is>
       </c>
       <c r="D213" s="13" t="n">
-        <v>51.22</v>
+        <v>53.93</v>
       </c>
       <c r="E213" s="14" t="n">
-        <v>-0.2465</v>
+        <v>-0.2066</v>
       </c>
       <c r="F213" s="14" t="n">
-        <v>-0.3375</v>
+        <v>-0.3024</v>
       </c>
       <c r="G213" s="15" t="n"/>
       <c r="H213" s="21" t="inlineStr">
@@ -16253,13 +16253,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>165.88</v>
+        <v>165.69</v>
       </c>
       <c r="E214" s="22" t="n">
-        <v>-0.0987</v>
+        <v>-0.09970000000000001</v>
       </c>
       <c r="F214" s="22" t="n">
-        <v>-0.1155</v>
+        <v>-0.1165</v>
       </c>
       <c r="G214" s="6" t="n"/>
       <c r="H214" s="7" t="inlineStr">
@@ -16304,13 +16304,13 @@
         </is>
       </c>
       <c r="D215" s="13" t="n">
-        <v>38.68</v>
+        <v>38.97</v>
       </c>
       <c r="E215" s="18" t="n">
-        <v>0.2187</v>
+        <v>0.2278</v>
       </c>
       <c r="F215" s="18" t="n">
-        <v>0.2445</v>
+        <v>0.2539</v>
       </c>
       <c r="G215" s="15" t="n">
         <v>46267</v>
@@ -16365,13 +16365,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>169.62</v>
+        <v>170.5</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>0.2496</v>
+        <v>0.2561</v>
       </c>
       <c r="F216" s="5" t="n">
-        <v>0.3336</v>
+        <v>0.3405</v>
       </c>
       <c r="G216" s="6" t="n">
         <v>46268</v>
@@ -16400,7 +16400,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="5" t="n">
-        <v>0.1201509255983964</v>
+        <v>0.1143695014662757</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="8" t="n"/>
@@ -16444,13 +16444,13 @@
         </is>
       </c>
       <c r="D217" s="13" t="n">
-        <v>51.29</v>
+        <v>53.22</v>
       </c>
       <c r="E217" s="18" t="n">
-        <v>0.1481</v>
+        <v>0.1914</v>
       </c>
       <c r="F217" s="18" t="n">
-        <v>0.0284</v>
+        <v>0.0672</v>
       </c>
       <c r="G217" s="15" t="n">
         <v>46267</v>
@@ -16479,7 +16479,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="18" t="n">
-        <v>0.3062975238837981</v>
+        <v>0.2589252160841789</v>
       </c>
       <c r="N217" s="12" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="18" t="n">
-        <v>0.3647884577890427</v>
+        <v>0.3152950018789929</v>
       </c>
       <c r="Q217" s="19" t="inlineStr">
         <is>
@@ -16531,13 +16531,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>211.89</v>
+        <v>210.52</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>0.0711</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>0.0181</v>
+        <v>0.0115</v>
       </c>
       <c r="G218" s="6" t="n"/>
       <c r="H218" s="7" t="inlineStr">
@@ -16582,13 +16582,13 @@
         </is>
       </c>
       <c r="D219" s="13" t="n">
-        <v>235.97</v>
+        <v>237.15</v>
       </c>
       <c r="E219" s="14" t="n">
-        <v>-0.2188</v>
+        <v>-0.2149</v>
       </c>
       <c r="F219" s="14" t="n">
-        <v>-0.1597</v>
+        <v>-0.1555</v>
       </c>
       <c r="G219" s="15" t="n">
         <v>46316</v>
@@ -16624,7 +16624,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="18" t="n">
-        <v>0.05945671059880494</v>
+        <v>0.0541851149061775</v>
       </c>
       <c r="Q219" s="19" t="inlineStr">
         <is>
@@ -16661,13 +16661,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>11.41</v>
-      </c>
-      <c r="E220" s="22" t="n">
-        <v>-0.008699999999999999</v>
+        <v>11.91</v>
+      </c>
+      <c r="E220" s="5" t="n">
+        <v>0.0352</v>
       </c>
       <c r="F220" s="22" t="n">
-        <v>-0.2296</v>
+        <v>-0.1955</v>
       </c>
       <c r="G220" s="6" t="n">
         <v>46246</v>
@@ -16722,13 +16722,13 @@
         </is>
       </c>
       <c r="D221" s="13" t="n">
-        <v>99.59999999999999</v>
+        <v>101.65</v>
       </c>
       <c r="E221" s="14" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.0779</v>
       </c>
       <c r="F221" s="14" t="n">
-        <v>-0.0968</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="G221" s="15" t="n">
         <v>46317</v>
@@ -16783,13 +16783,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>335.29</v>
+        <v>325.25</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>0.2322</v>
+        <v>0.1953</v>
       </c>
       <c r="F222" s="5" t="n">
-        <v>0.0975</v>
+        <v>0.0646</v>
       </c>
       <c r="G222" s="6" t="n">
         <v>46259</v>
@@ -16844,13 +16844,13 @@
         </is>
       </c>
       <c r="D223" s="13" t="n">
-        <v>42.01</v>
+        <v>44.44</v>
       </c>
       <c r="E223" s="14" t="n">
-        <v>-0.068</v>
+        <v>-0.0143</v>
       </c>
       <c r="F223" s="14" t="n">
-        <v>-0.331</v>
+        <v>-0.2924</v>
       </c>
       <c r="G223" s="15" t="n"/>
       <c r="H223" s="21" t="inlineStr">
@@ -16895,13 +16895,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>38.57</v>
+        <v>41.23</v>
       </c>
       <c r="E224" s="22" t="n">
-        <v>-0.1031</v>
+        <v>-0.0413</v>
       </c>
       <c r="F224" s="22" t="n">
-        <v>-0.3484</v>
+        <v>-0.3034</v>
       </c>
       <c r="G224" s="6" t="n">
         <v>46261</v>
@@ -16956,13 +16956,13 @@
         </is>
       </c>
       <c r="D225" s="13" t="n">
-        <v>342.39</v>
+        <v>341.2</v>
       </c>
       <c r="E225" s="18" t="n">
-        <v>0.0528</v>
+        <v>0.0492</v>
       </c>
       <c r="F225" s="14" t="n">
-        <v>-0.0592</v>
+        <v>-0.0625</v>
       </c>
       <c r="G225" s="15" t="n">
         <v>46289</v>
@@ -17021,13 +17021,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>339.41</v>
+        <v>340.92</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>0.0699</v>
+        <v>0.0746</v>
       </c>
       <c r="F226" s="5" t="n">
-        <v>0.0236</v>
+        <v>0.0281</v>
       </c>
       <c r="G226" s="6" t="n">
         <v>46252</v>
@@ -17056,7 +17056,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>0.1490527680386552</v>
+        <v>0.1439633931714185</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="8" t="n"/>
@@ -17112,13 +17112,13 @@
         </is>
       </c>
       <c r="D227" s="13" t="n">
-        <v>197.4</v>
+        <v>198.11</v>
       </c>
       <c r="E227" s="14" t="n">
-        <v>-0.1075</v>
+        <v>-0.1043</v>
       </c>
       <c r="F227" s="14" t="n">
-        <v>-0.0636</v>
+        <v>-0.0602</v>
       </c>
       <c r="G227" s="15" t="n"/>
       <c r="H227" s="21" t="inlineStr">
@@ -17137,7 +17137,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="18" t="n">
-        <v>0.5450861195542046</v>
+        <v>0.5395487355509564</v>
       </c>
       <c r="N227" s="12" t="inlineStr">
         <is>
@@ -17148,7 +17148,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="14" t="n">
-        <v>-0.0628166160081054</v>
+        <v>-0.06617535712482971</v>
       </c>
       <c r="Q227" s="19" t="inlineStr">
         <is>
@@ -17189,13 +17189,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>94.28</v>
+        <v>91.31</v>
       </c>
       <c r="E228" s="22" t="n">
-        <v>-0.0955</v>
+        <v>-0.124</v>
       </c>
       <c r="F228" s="22" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.1092</v>
       </c>
       <c r="G228" s="6" t="n"/>
       <c r="H228" s="7" t="inlineStr">
@@ -17240,13 +17240,13 @@
         </is>
       </c>
       <c r="D229" s="13" t="n">
-        <v>876.8099999999999</v>
+        <v>890.17</v>
       </c>
       <c r="E229" s="18" t="n">
-        <v>0.24</v>
+        <v>0.2589</v>
       </c>
       <c r="F229" s="14" t="n">
-        <v>-0.0208</v>
+        <v>-0.0058</v>
       </c>
       <c r="G229" s="15" t="n">
         <v>46245</v>
@@ -17301,13 +17301,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>104.82</v>
+        <v>106.33</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>0.0711</v>
+        <v>0.0866</v>
       </c>
       <c r="F230" s="22" t="n">
-        <v>-0.0755</v>
+        <v>-0.0622</v>
       </c>
       <c r="G230" s="6" t="n"/>
       <c r="H230" s="7" t="inlineStr">
@@ -17352,13 +17352,13 @@
         </is>
       </c>
       <c r="D231" s="13" t="n">
-        <v>307.45</v>
+        <v>311.35</v>
       </c>
       <c r="E231" s="14" t="n">
-        <v>-0.07719999999999999</v>
+        <v>-0.0654</v>
       </c>
       <c r="F231" s="14" t="n">
-        <v>-0.0524</v>
+        <v>-0.0404</v>
       </c>
       <c r="G231" s="15" t="n"/>
       <c r="H231" s="21" t="inlineStr">
@@ -17377,7 +17377,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="18" t="n">
-        <v>0.4636526264433242</v>
+        <v>0.4453187730849525</v>
       </c>
       <c r="N231" s="12" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="18" t="n">
-        <v>0.154659294194178</v>
+        <v>0.1401959209892403</v>
       </c>
       <c r="Q231" s="19" t="inlineStr">
         <is>
@@ -17433,13 +17433,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>83.62</v>
+        <v>84.69</v>
       </c>
       <c r="E232" s="22" t="n">
-        <v>-0.0219</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="F232" s="22" t="n">
-        <v>-0.0848</v>
+        <v>-0.0731</v>
       </c>
       <c r="G232" s="6" t="n"/>
       <c r="H232" s="7" t="inlineStr">
@@ -17484,13 +17484,13 @@
         </is>
       </c>
       <c r="D233" s="13" t="n">
-        <v>393.65</v>
+        <v>398.8</v>
       </c>
       <c r="E233" s="18" t="n">
-        <v>0.0953</v>
+        <v>0.1096</v>
       </c>
       <c r="F233" s="18" t="n">
-        <v>0.1165</v>
+        <v>0.1312</v>
       </c>
       <c r="G233" s="15" t="n">
         <v>46266</v>
@@ -17545,13 +17545,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>307.14</v>
+        <v>304.99</v>
       </c>
       <c r="E234" s="22" t="n">
-        <v>-0.1209</v>
+        <v>-0.1271</v>
       </c>
       <c r="F234" s="22" t="n">
-        <v>-0.0158</v>
+        <v>-0.0227</v>
       </c>
       <c r="G234" s="6" t="n"/>
       <c r="H234" s="7" t="inlineStr">
@@ -17596,13 +17596,13 @@
         </is>
       </c>
       <c r="D235" s="13" t="n">
-        <v>1387.61</v>
+        <v>1401.54</v>
       </c>
       <c r="E235" s="18" t="n">
-        <v>0.0548</v>
+        <v>0.0654</v>
       </c>
       <c r="F235" s="14" t="n">
-        <v>-0.11</v>
+        <v>-0.1011</v>
       </c>
       <c r="G235" s="15" t="n"/>
       <c r="H235" s="21" t="inlineStr">
@@ -17647,13 +17647,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>211.81</v>
+        <v>218.72</v>
       </c>
       <c r="E236" s="22" t="n">
-        <v>-0.0859</v>
+        <v>-0.0561</v>
       </c>
       <c r="F236" s="22" t="n">
-        <v>-0.2667</v>
+        <v>-0.2428</v>
       </c>
       <c r="G236" s="6" t="n">
         <v>46261</v>
@@ -17682,7 +17682,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="5" t="n">
-        <v>0.1330909777630896</v>
+        <v>0.09729334308705194</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="5" t="n">
-        <v>0.1850243142438978</v>
+        <v>0.1475859546452085</v>
       </c>
       <c r="Q236" s="9" t="inlineStr">
         <is>
@@ -17734,13 +17734,13 @@
         </is>
       </c>
       <c r="D237" s="13" t="n">
-        <v>503.95</v>
+        <v>499.99</v>
       </c>
       <c r="E237" s="18" t="n">
-        <v>0.3146</v>
+        <v>0.3043</v>
       </c>
       <c r="F237" s="18" t="n">
-        <v>0.224</v>
+        <v>0.2143</v>
       </c>
       <c r="G237" s="15" t="n"/>
       <c r="H237" s="21" t="inlineStr">
@@ -17759,7 +17759,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="18" t="n">
-        <v>0.2402024010318484</v>
+        <v>0.25002500050001</v>
       </c>
       <c r="N237" s="12" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="18" t="n">
-        <v>0.04177001686675268</v>
+        <v>0.05002100042000838</v>
       </c>
       <c r="Q237" s="19" t="inlineStr">
         <is>
@@ -17823,13 +17823,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>472.38</v>
+        <v>467.59</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>0.1233</v>
+        <v>0.1119</v>
       </c>
       <c r="F238" s="5" t="n">
-        <v>0.1612</v>
+        <v>0.1494</v>
       </c>
       <c r="G238" s="6" t="n"/>
       <c r="H238" s="7" t="inlineStr">
@@ -17851,7 +17851,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="5" t="n">
-        <v>0.1113933697446971</v>
+        <v>0.1227785025342715</v>
       </c>
       <c r="Q238" s="9" t="inlineStr">
         <is>
@@ -17900,13 +17900,13 @@
         </is>
       </c>
       <c r="D239" s="13" t="n">
-        <v>104.14</v>
+        <v>100.01</v>
       </c>
       <c r="E239" s="18" t="n">
-        <v>0.1095</v>
+        <v>0.0654</v>
       </c>
       <c r="F239" s="14" t="n">
-        <v>-0.1813</v>
+        <v>-0.2138</v>
       </c>
       <c r="G239" s="15" t="n"/>
       <c r="H239" s="21" t="inlineStr">
@@ -17951,13 +17951,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>305.05</v>
-      </c>
-      <c r="E240" s="22" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>310.82</v>
+      </c>
+      <c r="E240" s="5" t="n">
+        <v>0.0183</v>
       </c>
       <c r="F240" s="22" t="n">
-        <v>-0.157</v>
+        <v>-0.141</v>
       </c>
       <c r="G240" s="6" t="n"/>
       <c r="H240" s="7" t="inlineStr">
@@ -18002,13 +18002,13 @@
         </is>
       </c>
       <c r="D241" s="13" t="n">
-        <v>859.38</v>
+        <v>877.5700000000001</v>
       </c>
       <c r="E241" s="14" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.0751</v>
       </c>
       <c r="F241" s="14" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0755</v>
       </c>
       <c r="G241" s="15" t="n">
         <v>46287</v>
@@ -18037,7 +18037,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="18" t="n">
-        <v>0.7745351299774256</v>
+        <v>0.7377531137117266</v>
       </c>
       <c r="N241" s="12" t="inlineStr">
         <is>
@@ -18085,13 +18085,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>182.62</v>
+        <v>187.97</v>
       </c>
       <c r="E242" s="22" t="n">
-        <v>-0.1564</v>
+        <v>-0.1317</v>
       </c>
       <c r="F242" s="22" t="n">
-        <v>-0.1623</v>
+        <v>-0.1378</v>
       </c>
       <c r="G242" s="6" t="n">
         <v>46246</v>
@@ -18146,13 +18146,13 @@
         </is>
       </c>
       <c r="D243" s="13" t="n">
-        <v>311.18</v>
+        <v>300.34</v>
       </c>
       <c r="E243" s="18" t="n">
-        <v>0.1382</v>
+        <v>0.09849999999999999</v>
       </c>
       <c r="F243" s="18" t="n">
-        <v>0.2558</v>
+        <v>0.2121</v>
       </c>
       <c r="G243" s="15" t="n"/>
       <c r="H243" s="21" t="inlineStr">
@@ -18197,13 +18197,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>126.04</v>
+        <v>124.85</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>0.1694</v>
+        <v>0.1584</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>0.1038</v>
+        <v>0.0934</v>
       </c>
       <c r="G244" s="6" t="n">
         <v>46323</v>
@@ -18232,7 +18232,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="5" t="n">
-        <v>0.2694382735639479</v>
+        <v>0.2815378454144974</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="5" t="n">
-        <v>0.1900983814662011</v>
+        <v>0.2014417300760914</v>
       </c>
       <c r="Q244" s="9" t="inlineStr">
         <is>
@@ -18288,13 +18288,13 @@
         </is>
       </c>
       <c r="D245" s="13" t="n">
-        <v>62.21</v>
+        <v>62.67</v>
       </c>
       <c r="E245" s="18" t="n">
-        <v>0.1535</v>
+        <v>0.1621</v>
       </c>
       <c r="F245" s="18" t="n">
-        <v>0.1998</v>
+        <v>0.2087</v>
       </c>
       <c r="G245" s="15" t="n">
         <v>46260</v>
@@ -18349,13 +18349,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>222.9</v>
+        <v>223.96</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>0.092</v>
+        <v>0.09720000000000001</v>
       </c>
       <c r="F246" s="5" t="n">
-        <v>0.0683</v>
+        <v>0.07339999999999999</v>
       </c>
       <c r="G246" s="6" t="n">
         <v>46260</v>
@@ -18384,7 +18384,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="5" t="n">
-        <v>0.4131897711978466</v>
+        <v>0.4065011609215931</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="5" t="n">
-        <v>0.8528488111260655</v>
+        <v>0.8440792998749777</v>
       </c>
       <c r="Q246" s="9" t="inlineStr">
         <is>
@@ -18444,13 +18444,13 @@
         </is>
       </c>
       <c r="D247" s="13" t="n">
-        <v>380.6</v>
+        <v>393.02</v>
       </c>
       <c r="E247" s="14" t="n">
-        <v>-0.1579</v>
+        <v>-0.1305</v>
       </c>
       <c r="F247" s="14" t="n">
-        <v>-0.2507</v>
+        <v>-0.2263</v>
       </c>
       <c r="G247" s="15" t="n"/>
       <c r="H247" s="21" t="inlineStr">
@@ -18495,13 +18495,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>239.19</v>
+        <v>239.71</v>
       </c>
       <c r="E248" s="22" t="n">
-        <v>-0.1572</v>
+        <v>-0.1554</v>
       </c>
       <c r="F248" s="22" t="n">
-        <v>-0.2057</v>
+        <v>-0.204</v>
       </c>
       <c r="G248" s="6" t="n"/>
       <c r="H248" s="7" t="inlineStr">
@@ -18593,13 +18593,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>148.26</v>
+        <v>148.32</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0106</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>0.2688</v>
+        <v>0.2693</v>
       </c>
       <c r="G250" s="6" t="n">
         <v>46260</v>
@@ -18628,7 +18628,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="5" t="n">
-        <v>0.01173613921489282</v>
+        <v>0.01132686084142399</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="22" t="n">
-        <v>-0.1231620126804262</v>
+        <v>-0.1235167206040992</v>
       </c>
       <c r="Q250" s="9" t="inlineStr">
         <is>
@@ -18680,13 +18680,13 @@
         </is>
       </c>
       <c r="D251" s="13" t="n">
-        <v>80.61</v>
+        <v>81.17</v>
       </c>
       <c r="E251" s="14" t="n">
-        <v>-0.1405</v>
+        <v>-0.1346</v>
       </c>
       <c r="F251" s="14" t="n">
-        <v>-0.3333</v>
+        <v>-0.3286</v>
       </c>
       <c r="G251" s="15" t="n"/>
       <c r="H251" s="21" t="inlineStr">
@@ -18731,13 +18731,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>305.93</v>
+        <v>308.75</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>0.04969999999999999</v>
+        <v>0.0594</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>0.1373</v>
+        <v>0.1478</v>
       </c>
       <c r="G252" s="6" t="n"/>
       <c r="H252" s="7" t="inlineStr">
@@ -18782,13 +18782,13 @@
         </is>
       </c>
       <c r="D253" s="13" t="n">
-        <v>144.81</v>
+        <v>146.93</v>
       </c>
       <c r="E253" s="18" t="n">
-        <v>0.0308</v>
+        <v>0.0459</v>
       </c>
       <c r="F253" s="14" t="n">
-        <v>-0.3163</v>
+        <v>-0.3063</v>
       </c>
       <c r="G253" s="15" t="n">
         <v>46273</v>
@@ -18817,7 +18817,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="18" t="n">
-        <v>0.9335681237483598</v>
+        <v>0.9056693663649356</v>
       </c>
       <c r="N253" s="12" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="18" t="n">
-        <v>0.6918721082798149</v>
+        <v>0.6674606955693186</v>
       </c>
       <c r="Q253" s="19" t="inlineStr">
         <is>
@@ -18869,13 +18869,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>364.22</v>
+        <v>363.86</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>0.1361</v>
+        <v>0.135</v>
       </c>
       <c r="F254" s="5" t="n">
-        <v>0.3676</v>
+        <v>0.3662</v>
       </c>
       <c r="G254" s="6" t="n">
         <v>46266</v>
@@ -18904,7 +18904,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="5" t="n">
-        <v>0.1531491955411564</v>
+        <v>0.1542901115813774</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>415</v>
       </c>
       <c r="P254" s="5" t="n">
-        <v>0.1394212289275712</v>
+        <v>0.1405485626339801</v>
       </c>
       <c r="Q254" s="9" t="inlineStr">
         <is>
@@ -18964,13 +18964,13 @@
         </is>
       </c>
       <c r="D255" s="13" t="n">
-        <v>14.97</v>
+        <v>15.04</v>
       </c>
       <c r="E255" s="18" t="n">
-        <v>0.3104</v>
+        <v>0.317</v>
       </c>
       <c r="F255" s="18" t="n">
-        <v>0.3397</v>
+        <v>0.3465</v>
       </c>
       <c r="G255" s="15" t="n">
         <v>46268</v>
@@ -19025,13 +19025,13 @@
         </is>
       </c>
       <c r="D256" s="4" t="n">
-        <v>32.75</v>
+        <v>32.74</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>0.038</v>
+        <v>0.0377</v>
       </c>
       <c r="F256" s="22" t="n">
-        <v>-0.0672</v>
+        <v>-0.0675</v>
       </c>
       <c r="G256" s="6" t="n">
         <v>46315</v>
@@ -19086,13 +19086,13 @@
         </is>
       </c>
       <c r="D257" s="13" t="n">
-        <v>179</v>
+        <v>183.36</v>
       </c>
       <c r="E257" s="18" t="n">
-        <v>0.2504</v>
+        <v>0.2809</v>
       </c>
       <c r="F257" s="18" t="n">
-        <v>0.3840999999999999</v>
+        <v>0.4178</v>
       </c>
       <c r="G257" s="15" t="n"/>
       <c r="H257" s="21" t="inlineStr">
@@ -19137,13 +19137,13 @@
         </is>
       </c>
       <c r="D258" s="4" t="n">
-        <v>170.83</v>
+        <v>172.01</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>0.292</v>
+        <v>0.3009</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>0.2517</v>
+        <v>0.2604</v>
       </c>
       <c r="G258" s="6" t="n"/>
       <c r="H258" s="7" t="inlineStr">
@@ -19188,13 +19188,13 @@
         </is>
       </c>
       <c r="D259" s="13" t="n">
-        <v>137.77</v>
+        <v>137.96</v>
       </c>
       <c r="E259" s="14" t="n">
-        <v>-0.0309</v>
+        <v>-0.0296</v>
       </c>
       <c r="F259" s="14" t="n">
-        <v>-0.0462</v>
+        <v>-0.0449</v>
       </c>
       <c r="G259" s="15" t="n"/>
       <c r="H259" s="21" t="inlineStr">
@@ -19249,13 +19249,13 @@
         </is>
       </c>
       <c r="D260" s="4" t="n">
-        <v>19.92</v>
-      </c>
-      <c r="E260" s="22" t="n">
-        <v>-0.0346</v>
+        <v>20.76</v>
+      </c>
+      <c r="E260" s="5" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F260" s="22" t="n">
-        <v>-0.2286</v>
+        <v>-0.1963</v>
       </c>
       <c r="G260" s="6" t="n"/>
       <c r="H260" s="7" t="inlineStr">
@@ -19300,13 +19300,13 @@
         </is>
       </c>
       <c r="D261" s="13" t="n">
-        <v>165</v>
+        <v>167.86</v>
       </c>
       <c r="E261" s="14" t="n">
-        <v>-0.1156</v>
+        <v>-0.1002</v>
       </c>
       <c r="F261" s="14" t="n">
-        <v>-0.2423</v>
+        <v>-0.2292</v>
       </c>
       <c r="G261" s="15" t="n"/>
       <c r="H261" s="21" t="inlineStr">
@@ -19325,7 +19325,7 @@
         <v>265</v>
       </c>
       <c r="M261" s="18" t="n">
-        <v>0.6060606060606061</v>
+        <v>0.578696532824973</v>
       </c>
       <c r="N261" s="12" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>179</v>
       </c>
       <c r="P261" s="18" t="n">
-        <v>0.08484848484848485</v>
+        <v>0.06636482783271766</v>
       </c>
       <c r="Q261" s="19" t="inlineStr">
         <is>
@@ -19381,13 +19381,13 @@
         </is>
       </c>
       <c r="D262" s="4" t="n">
-        <v>96.84</v>
+        <v>99.08</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>0.1546</v>
+        <v>0.1814</v>
       </c>
       <c r="F262" s="22" t="n">
-        <v>-0.0305</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="G262" s="6" t="n"/>
       <c r="H262" s="7" t="inlineStr">
@@ -19432,13 +19432,13 @@
         </is>
       </c>
       <c r="D263" s="13" t="n">
-        <v>8.960000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="E263" s="18" t="n">
-        <v>0.024</v>
+        <v>0.0491</v>
       </c>
       <c r="F263" s="14" t="n">
-        <v>-0.1426</v>
+        <v>-0.1215</v>
       </c>
       <c r="G263" s="15" t="n">
         <v>46244</v>
@@ -19493,13 +19493,13 @@
         </is>
       </c>
       <c r="D264" s="4" t="n">
-        <v>88.95999999999999</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.0669</v>
       </c>
       <c r="F264" s="5" t="n">
-        <v>0.2401</v>
+        <v>0.2553</v>
       </c>
       <c r="G264" s="6" t="n">
         <v>46261</v>
@@ -19554,13 +19554,13 @@
         </is>
       </c>
       <c r="D265" s="13" t="n">
-        <v>17.07</v>
+        <v>17.94</v>
       </c>
       <c r="E265" s="18" t="n">
-        <v>0.0086</v>
+        <v>0.0603</v>
       </c>
       <c r="F265" s="14" t="n">
-        <v>-0.2159</v>
+        <v>-0.1757</v>
       </c>
       <c r="G265" s="15" t="n"/>
       <c r="H265" s="21" t="inlineStr">
@@ -19605,13 +19605,13 @@
         </is>
       </c>
       <c r="D266" s="4" t="n">
-        <v>403.57</v>
+        <v>402.25</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>0.1372</v>
+        <v>0.1334</v>
       </c>
       <c r="F266" s="5" t="n">
-        <v>0.2092</v>
+        <v>0.2052</v>
       </c>
       <c r="G266" s="6" t="n">
         <v>46317</v>
@@ -19680,13 +19680,13 @@
         </is>
       </c>
       <c r="D267" s="13" t="n">
-        <v>4.91</v>
+        <v>4.9</v>
       </c>
       <c r="E267" s="14" t="n">
-        <v>-0.2546</v>
+        <v>-0.2553</v>
       </c>
       <c r="F267" s="18" t="n">
-        <v>0.0876</v>
+        <v>0.08650000000000001</v>
       </c>
       <c r="G267" s="15" t="n">
         <v>46245</v>
@@ -19741,13 +19741,13 @@
         </is>
       </c>
       <c r="D268" s="4" t="n">
-        <v>21.38</v>
+        <v>21.4</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>0.2002</v>
+        <v>0.2016</v>
       </c>
       <c r="F268" s="5" t="n">
-        <v>0.3571</v>
+        <v>0.3587</v>
       </c>
       <c r="G268" s="6" t="n">
         <v>46261</v>
@@ -19802,13 +19802,13 @@
         </is>
       </c>
       <c r="D269" s="13" t="n">
-        <v>18.44</v>
+        <v>18.66</v>
       </c>
       <c r="E269" s="18" t="n">
-        <v>0.2204</v>
+        <v>0.2349</v>
       </c>
       <c r="F269" s="18" t="n">
-        <v>0.0424</v>
+        <v>0.0548</v>
       </c>
       <c r="G269" s="15" t="n">
         <v>46273</v>
@@ -19863,13 +19863,13 @@
         </is>
       </c>
       <c r="D270" s="4" t="n">
-        <v>201.13</v>
+        <v>202.73</v>
       </c>
       <c r="E270" s="22" t="n">
-        <v>-0.0403</v>
+        <v>-0.0326</v>
       </c>
       <c r="F270" s="22" t="n">
-        <v>-0.2017</v>
+        <v>-0.1954</v>
       </c>
       <c r="G270" s="6" t="n"/>
       <c r="H270" s="7" t="inlineStr">
@@ -19914,13 +19914,13 @@
         </is>
       </c>
       <c r="D271" s="13" t="n">
-        <v>207.37</v>
+        <v>206.13</v>
       </c>
       <c r="E271" s="18" t="n">
-        <v>0.3173</v>
+        <v>0.3095</v>
       </c>
       <c r="F271" s="18" t="n">
-        <v>0.1399</v>
+        <v>0.1331</v>
       </c>
       <c r="G271" s="15" t="n">
         <v>46316</v>
@@ -19995,13 +19995,13 @@
         </is>
       </c>
       <c r="D272" s="4" t="n">
-        <v>30.13</v>
+        <v>31.13</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>0.0696</v>
+        <v>0.1051</v>
       </c>
       <c r="F272" s="22" t="n">
-        <v>-0.3151</v>
+        <v>-0.2923</v>
       </c>
       <c r="G272" s="6" t="n">
         <v>46245</v>
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="D273" s="13" t="n">
-        <v>325.68</v>
+        <v>330.3</v>
       </c>
       <c r="E273" s="18" t="n">
-        <v>0.2463</v>
+        <v>0.264</v>
       </c>
       <c r="F273" s="18" t="n">
-        <v>0.3545</v>
+        <v>0.3737</v>
       </c>
       <c r="G273" s="15" t="n">
         <v>46267</v>
@@ -20091,7 +20091,7 @@
         <v>320</v>
       </c>
       <c r="M273" s="14" t="n">
-        <v>-0.0174404323262098</v>
+        <v>-0.03118377232818653</v>
       </c>
       <c r="N273" s="12" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>280</v>
       </c>
       <c r="P273" s="14" t="n">
-        <v>-0.1402603782854336</v>
+        <v>-0.1522858007871632</v>
       </c>
       <c r="Q273" s="19" t="inlineStr">
         <is>
@@ -20143,13 +20143,13 @@
         </is>
       </c>
       <c r="D274" s="4" t="n">
-        <v>413.76</v>
+        <v>415.99</v>
       </c>
       <c r="E274" s="22" t="n">
-        <v>-0.04769999999999999</v>
+        <v>-0.0426</v>
       </c>
       <c r="F274" s="22" t="n">
-        <v>-0.1261</v>
+        <v>-0.1214</v>
       </c>
       <c r="G274" s="6" t="n">
         <v>46260</v>
@@ -20178,7 +20178,7 @@
         <v>535</v>
       </c>
       <c r="M274" s="5" t="n">
-        <v>0.2930201082753287</v>
+        <v>0.2860886078992283</v>
       </c>
       <c r="N274" s="3" t="inlineStr"/>
       <c r="O274" s="8" t="n"/>
@@ -20222,13 +20222,13 @@
         </is>
       </c>
       <c r="D275" s="13" t="n">
-        <v>7.66</v>
+        <v>8.02</v>
       </c>
       <c r="E275" s="18" t="n">
-        <v>0.1272</v>
+        <v>0.1794</v>
       </c>
       <c r="F275" s="18" t="n">
-        <v>0.0234</v>
+        <v>0.0708</v>
       </c>
       <c r="G275" s="15" t="n"/>
       <c r="H275" s="21" t="inlineStr">
@@ -20273,13 +20273,13 @@
         </is>
       </c>
       <c r="D276" s="4" t="n">
-        <v>68.42</v>
+        <v>70.62</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>0.1697</v>
+        <v>0.2074</v>
       </c>
       <c r="F276" s="22" t="n">
-        <v>-0.09230000000000001</v>
+        <v>-0.063</v>
       </c>
       <c r="G276" s="6" t="n"/>
       <c r="H276" s="7" t="inlineStr">
@@ -20324,13 +20324,13 @@
         </is>
       </c>
       <c r="D277" s="13" t="n">
-        <v>105.25</v>
+        <v>106.19</v>
       </c>
       <c r="E277" s="14" t="n">
-        <v>-0.1469</v>
+        <v>-0.1393</v>
       </c>
       <c r="F277" s="14" t="n">
-        <v>-0.2261</v>
+        <v>-0.2192</v>
       </c>
       <c r="G277" s="15" t="n"/>
       <c r="H277" s="21" t="inlineStr">
@@ -20375,13 +20375,13 @@
         </is>
       </c>
       <c r="D278" s="4" t="n">
-        <v>216.23</v>
+        <v>216.31</v>
       </c>
       <c r="E278" s="5" t="n">
-        <v>0.1019</v>
+        <v>0.1023</v>
       </c>
       <c r="F278" s="5" t="n">
-        <v>0.0517</v>
+        <v>0.052</v>
       </c>
       <c r="G278" s="6" t="n">
         <v>46330</v>
@@ -20436,13 +20436,13 @@
         </is>
       </c>
       <c r="D279" s="13" t="n">
-        <v>378.81</v>
+        <v>379.31</v>
       </c>
       <c r="E279" s="18" t="n">
-        <v>0.0775</v>
+        <v>0.0789</v>
       </c>
       <c r="F279" s="18" t="n">
-        <v>0.011</v>
+        <v>0.0123</v>
       </c>
       <c r="G279" s="15" t="n"/>
       <c r="H279" s="21" t="inlineStr">
@@ -20487,13 +20487,13 @@
         </is>
       </c>
       <c r="D280" s="4" t="n">
-        <v>59.79</v>
+        <v>59.51</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>0.141</v>
+        <v>0.1357</v>
       </c>
       <c r="F280" s="5" t="n">
-        <v>0.1149</v>
+        <v>0.1096</v>
       </c>
       <c r="G280" s="6" t="n">
         <v>46246</v>
@@ -20548,13 +20548,13 @@
         </is>
       </c>
       <c r="D281" s="13" t="n">
-        <v>416.02</v>
+        <v>419.91</v>
       </c>
       <c r="E281" s="14" t="n">
-        <v>-0.048</v>
+        <v>-0.0391</v>
       </c>
       <c r="F281" s="14" t="n">
-        <v>-0.0252</v>
+        <v>-0.0161</v>
       </c>
       <c r="G281" s="15" t="n">
         <v>46310</v>
@@ -20631,13 +20631,13 @@
         </is>
       </c>
       <c r="D282" s="4" t="n">
-        <v>139.86</v>
+        <v>137.21</v>
       </c>
       <c r="E282" s="22" t="n">
-        <v>-0.0374</v>
+        <v>-0.0556</v>
       </c>
       <c r="F282" s="22" t="n">
-        <v>-0.2159</v>
+        <v>-0.2308</v>
       </c>
       <c r="G282" s="6" t="n"/>
       <c r="H282" s="7" t="inlineStr">
@@ -20682,13 +20682,13 @@
         </is>
       </c>
       <c r="D283" s="13" t="n">
-        <v>244.13</v>
+        <v>241.38</v>
       </c>
       <c r="E283" s="18" t="n">
-        <v>0.1329</v>
+        <v>0.1201</v>
       </c>
       <c r="F283" s="18" t="n">
-        <v>0.1487</v>
+        <v>0.1357</v>
       </c>
       <c r="G283" s="15" t="n"/>
       <c r="H283" s="21" t="inlineStr">
@@ -20733,13 +20733,13 @@
         </is>
       </c>
       <c r="D284" s="4" t="n">
-        <v>283.32</v>
+        <v>286.08</v>
       </c>
       <c r="E284" s="22" t="n">
-        <v>-0.0597</v>
+        <v>-0.0506</v>
       </c>
       <c r="F284" s="22" t="n">
-        <v>-0.0261</v>
+        <v>-0.0166</v>
       </c>
       <c r="G284" s="6" t="n">
         <v>46315</v>
@@ -20768,7 +20768,7 @@
         <v>300</v>
       </c>
       <c r="M284" s="5" t="n">
-        <v>0.05887335874629397</v>
+        <v>0.04865771812080543</v>
       </c>
       <c r="N284" s="3" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>316</v>
       </c>
       <c r="P284" s="5" t="n">
-        <v>0.1153466045460963</v>
+        <v>0.1045861297539151</v>
       </c>
       <c r="Q284" s="9" t="inlineStr">
         <is>
@@ -20836,13 +20836,13 @@
         </is>
       </c>
       <c r="D285" s="13" t="n">
-        <v>315.2</v>
-      </c>
-      <c r="E285" s="18" t="n">
-        <v>0.0029</v>
+        <v>312.31</v>
+      </c>
+      <c r="E285" s="14" t="n">
+        <v>-0.0063</v>
       </c>
       <c r="F285" s="18" t="n">
-        <v>0.03759999999999999</v>
+        <v>0.0281</v>
       </c>
       <c r="G285" s="15" t="n"/>
       <c r="H285" s="21" t="inlineStr">
@@ -20861,7 +20861,7 @@
         <v>335</v>
       </c>
       <c r="M285" s="18" t="n">
-        <v>0.06281725888324877</v>
+        <v>0.07265217252089269</v>
       </c>
       <c r="N285" s="12" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>375</v>
       </c>
       <c r="P285" s="18" t="n">
-        <v>0.1897208121827412</v>
+        <v>0.2007300438666709</v>
       </c>
       <c r="Q285" s="19" t="inlineStr">
         <is>
@@ -20913,13 +20913,13 @@
         </is>
       </c>
       <c r="D286" s="4" t="n">
-        <v>42.6</v>
+        <v>43</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>0.446</v>
+        <v>0.4596</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>0.4792</v>
+        <v>0.4931</v>
       </c>
       <c r="G286" s="6" t="n"/>
       <c r="H286" s="7" t="inlineStr">
@@ -20964,13 +20964,13 @@
         </is>
       </c>
       <c r="D287" s="13" t="n">
-        <v>7.15</v>
+        <v>7.33</v>
       </c>
       <c r="E287" s="14" t="n">
-        <v>-0.1417</v>
+        <v>-0.12</v>
       </c>
       <c r="F287" s="14" t="n">
-        <v>-0.1939</v>
+        <v>-0.1736</v>
       </c>
       <c r="G287" s="15" t="n">
         <v>46252</v>
@@ -21025,13 +21025,13 @@
         </is>
       </c>
       <c r="D288" s="4" t="n">
-        <v>182.58</v>
+        <v>179.64</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>0.3242</v>
+        <v>0.3029</v>
       </c>
       <c r="F288" s="5" t="n">
-        <v>0.27</v>
+        <v>0.2496</v>
       </c>
       <c r="G288" s="6" t="n">
         <v>46261</v>
@@ -21086,13 +21086,13 @@
         </is>
       </c>
       <c r="D289" s="13" t="n">
-        <v>426.48</v>
+        <v>434.3</v>
       </c>
       <c r="E289" s="14" t="n">
-        <v>-0.225</v>
+        <v>-0.2108</v>
       </c>
       <c r="F289" s="14" t="n">
-        <v>-0.1906</v>
+        <v>-0.1758</v>
       </c>
       <c r="G289" s="15" t="n"/>
       <c r="H289" s="21" t="inlineStr">
@@ -21111,7 +21111,7 @@
         <v>730</v>
       </c>
       <c r="M289" s="18" t="n">
-        <v>0.7116863627837178</v>
+        <v>0.6808657609947041</v>
       </c>
       <c r="N289" s="12" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>575</v>
       </c>
       <c r="P289" s="18" t="n">
-        <v>0.3482461076721065</v>
+        <v>0.3239696062629518</v>
       </c>
       <c r="Q289" s="19" t="inlineStr">
         <is>
@@ -21163,13 +21163,13 @@
         </is>
       </c>
       <c r="D290" s="4" t="n">
-        <v>30.83</v>
+        <v>32.82</v>
       </c>
       <c r="E290" s="22" t="n">
-        <v>-0.1404</v>
+        <v>-0.0848</v>
       </c>
       <c r="F290" s="22" t="n">
-        <v>-0.4438</v>
+        <v>-0.4078</v>
       </c>
       <c r="G290" s="6" t="n">
         <v>46253</v>
@@ -21224,13 +21224,13 @@
         </is>
       </c>
       <c r="D291" s="13" t="n">
-        <v>105.17</v>
+        <v>104.5</v>
       </c>
       <c r="E291" s="18" t="n">
-        <v>0.2033</v>
+        <v>0.1957</v>
       </c>
       <c r="F291" s="18" t="n">
-        <v>0.0397</v>
+        <v>0.0331</v>
       </c>
       <c r="G291" s="15" t="n">
         <v>46259</v>
@@ -21285,7 +21285,7 @@
         </is>
       </c>
       <c r="D292" s="4" t="n">
-        <v>168.69</v>
+        <v>168.68</v>
       </c>
       <c r="E292" s="5" t="n">
         <v>0.1751</v>
@@ -21346,13 +21346,13 @@
         </is>
       </c>
       <c r="D293" s="13" t="n">
-        <v>300.57</v>
+        <v>303.4</v>
       </c>
       <c r="E293" s="18" t="n">
-        <v>0.0129</v>
+        <v>0.0224</v>
       </c>
       <c r="F293" s="18" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="G293" s="15" t="n"/>
       <c r="H293" s="21" t="inlineStr">
@@ -21397,13 +21397,13 @@
         </is>
       </c>
       <c r="D294" s="4" t="n">
-        <v>89.86</v>
+        <v>90.41</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>0.1476</v>
+        <v>0.1547</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>0.0736</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="G294" s="6" t="n">
         <v>46252</v>
@@ -21458,13 +21458,13 @@
         </is>
       </c>
       <c r="D295" s="13" t="n">
-        <v>144.68</v>
+        <v>142.44</v>
       </c>
       <c r="E295" s="18" t="n">
-        <v>0.0563</v>
+        <v>0.0399</v>
       </c>
       <c r="F295" s="18" t="n">
-        <v>0.0264</v>
+        <v>0.0104</v>
       </c>
       <c r="G295" s="15" t="n"/>
       <c r="H295" s="21" t="inlineStr">
@@ -21483,7 +21483,7 @@
         <v>166</v>
       </c>
       <c r="M295" s="18" t="n">
-        <v>0.1473596903511196</v>
+        <v>0.1654029766919405</v>
       </c>
       <c r="N295" s="12" t="inlineStr"/>
       <c r="O295" s="17" t="n"/>
@@ -21531,13 +21531,13 @@
         </is>
       </c>
       <c r="D296" s="4" t="n">
-        <v>29.74</v>
+        <v>29.34</v>
       </c>
       <c r="E296" s="5" t="n">
-        <v>0.0245</v>
+        <v>0.0109</v>
       </c>
       <c r="F296" s="22" t="n">
-        <v>-0.1304</v>
+        <v>-0.142</v>
       </c>
       <c r="G296" s="6" t="n">
         <v>46317</v>
@@ -21592,13 +21592,13 @@
         </is>
       </c>
       <c r="D297" s="13" t="n">
-        <v>287.1</v>
+        <v>285.05</v>
       </c>
       <c r="E297" s="18" t="n">
-        <v>0.0474</v>
+        <v>0.0399</v>
       </c>
       <c r="F297" s="18" t="n">
-        <v>0.1153</v>
+        <v>0.1074</v>
       </c>
       <c r="G297" s="15" t="n"/>
       <c r="H297" s="21" t="inlineStr">
@@ -21617,7 +21617,7 @@
         <v>275</v>
       </c>
       <c r="M297" s="14" t="n">
-        <v>-0.04214559386973188</v>
+        <v>-0.0352569724609718</v>
       </c>
       <c r="N297" s="12" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>312</v>
       </c>
       <c r="P297" s="18" t="n">
-        <v>0.08672936259143148</v>
+        <v>0.09454481669882472</v>
       </c>
       <c r="Q297" s="19" t="inlineStr">
         <is>
@@ -21681,13 +21681,13 @@
         </is>
       </c>
       <c r="D298" s="4" t="n">
-        <v>38.41</v>
+        <v>37.9</v>
       </c>
       <c r="E298" s="22" t="n">
-        <v>-0.0236</v>
+        <v>-0.0366</v>
       </c>
       <c r="F298" s="22" t="n">
-        <v>-0.0433</v>
+        <v>-0.05599999999999999</v>
       </c>
       <c r="G298" s="6" t="n"/>
       <c r="H298" s="7" t="inlineStr">
@@ -21736,13 +21736,13 @@
         </is>
       </c>
       <c r="D299" s="13" t="n">
-        <v>69.33</v>
+        <v>69.61</v>
       </c>
       <c r="E299" s="18" t="n">
-        <v>0.2057</v>
+        <v>0.2107</v>
       </c>
       <c r="F299" s="18" t="n">
-        <v>0.0848</v>
+        <v>0.08929999999999999</v>
       </c>
       <c r="G299" s="15" t="n">
         <v>46310</v>
@@ -21797,13 +21797,13 @@
         </is>
       </c>
       <c r="D300" s="4" t="n">
-        <v>492.51</v>
+        <v>489.98</v>
       </c>
       <c r="E300" s="22" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.07139999999999999</v>
       </c>
       <c r="F300" s="22" t="n">
-        <v>-0.0187</v>
+        <v>-0.0238</v>
       </c>
       <c r="G300" s="6" t="n"/>
       <c r="H300" s="7" t="inlineStr">
@@ -21822,7 +21822,7 @@
         <v>570</v>
       </c>
       <c r="M300" s="5" t="n">
-        <v>0.1573369068648353</v>
+        <v>0.1633127882770725</v>
       </c>
       <c r="N300" s="3" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>525</v>
       </c>
       <c r="P300" s="5" t="n">
-        <v>0.06596820369129562</v>
+        <v>0.07147230499204045</v>
       </c>
       <c r="Q300" s="9" t="inlineStr">
         <is>
@@ -21886,13 +21886,13 @@
         </is>
       </c>
       <c r="D301" s="13" t="n">
-        <v>553.8</v>
+        <v>548.4</v>
       </c>
       <c r="E301" s="14" t="n">
-        <v>-0.0284</v>
+        <v>-0.0379</v>
       </c>
       <c r="F301" s="14" t="n">
-        <v>-0.0003</v>
+        <v>-0.0101</v>
       </c>
       <c r="G301" s="15" t="n"/>
       <c r="H301" s="21" t="inlineStr">
@@ -21911,7 +21911,7 @@
         <v>616</v>
       </c>
       <c r="M301" s="18" t="n">
-        <v>0.1123149151318166</v>
+        <v>0.1232676878191102</v>
       </c>
       <c r="N301" s="12" t="inlineStr"/>
       <c r="O301" s="17" t="n"/>
@@ -21955,13 +21955,13 @@
         </is>
       </c>
       <c r="D302" s="4" t="n">
-        <v>269.95</v>
+        <v>272.57</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>0.1909</v>
+        <v>0.2024</v>
       </c>
       <c r="F302" s="5" t="n">
-        <v>0.0653</v>
+        <v>0.0757</v>
       </c>
       <c r="G302" s="6" t="n"/>
       <c r="H302" s="7" t="inlineStr">
@@ -21980,7 +21980,7 @@
         <v>283</v>
       </c>
       <c r="M302" s="5" t="n">
-        <v>0.04834228560844605</v>
+        <v>0.038265399713835</v>
       </c>
       <c r="N302" s="3" t="inlineStr"/>
       <c r="O302" s="8" t="n"/>
@@ -22026,13 +22026,13 @@
         </is>
       </c>
       <c r="D303" s="13" t="n">
-        <v>256.83</v>
+        <v>256.15</v>
       </c>
       <c r="E303" s="18" t="n">
-        <v>0.1442</v>
+        <v>0.1412</v>
       </c>
       <c r="F303" s="18" t="n">
-        <v>0.1704</v>
+        <v>0.1674</v>
       </c>
       <c r="G303" s="15" t="n">
         <v>46321</v>
@@ -22061,7 +22061,7 @@
         <v>246</v>
       </c>
       <c r="M303" s="14" t="n">
-        <v>-0.0421679710314215</v>
+        <v>-0.03962521959789177</v>
       </c>
       <c r="N303" s="12" t="inlineStr"/>
       <c r="O303" s="17" t="n"/>
@@ -22109,13 +22109,13 @@
         </is>
       </c>
       <c r="D304" s="4" t="n">
-        <v>119.79</v>
+        <v>119.68</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>0.0483</v>
+        <v>0.0473</v>
       </c>
       <c r="F304" s="5" t="n">
-        <v>0.0613</v>
+        <v>0.0602</v>
       </c>
       <c r="G304" s="6" t="n"/>
       <c r="H304" s="7" t="inlineStr">
@@ -22134,7 +22134,7 @@
         <v>130</v>
       </c>
       <c r="M304" s="5" t="n">
-        <v>0.08523249019116783</v>
+        <v>0.08622994652406411</v>
       </c>
       <c r="N304" s="3" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>128</v>
       </c>
       <c r="P304" s="5" t="n">
-        <v>0.06853660572668832</v>
+        <v>0.06951871657754005</v>
       </c>
       <c r="Q304" s="9" t="inlineStr">
         <is>
@@ -22194,13 +22194,13 @@
         </is>
       </c>
       <c r="D305" s="13" t="n">
-        <v>117.49</v>
+        <v>117.39</v>
       </c>
       <c r="E305" s="18" t="n">
-        <v>0.1352</v>
+        <v>0.1344</v>
       </c>
       <c r="F305" s="18" t="n">
-        <v>0.1231</v>
+        <v>0.1222</v>
       </c>
       <c r="G305" s="15" t="n">
         <v>46302</v>
@@ -22229,7 +22229,7 @@
         <v>135</v>
       </c>
       <c r="M305" s="18" t="n">
-        <v>0.14903396033705</v>
+        <v>0.1500127779197546</v>
       </c>
       <c r="N305" s="12" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>125</v>
       </c>
       <c r="P305" s="18" t="n">
-        <v>0.06392033364541667</v>
+        <v>0.06482664622199505</v>
       </c>
       <c r="Q305" s="19" t="inlineStr"/>
       <c r="R305" s="17" t="n"/>
@@ -22275,13 +22275,13 @@
         </is>
       </c>
       <c r="D306" s="4" t="n">
-        <v>371.93</v>
+        <v>369.7</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>0.1251</v>
+        <v>0.1184</v>
       </c>
       <c r="F306" s="5" t="n">
-        <v>0.2416</v>
+        <v>0.2342</v>
       </c>
       <c r="G306" s="6" t="n"/>
       <c r="H306" s="7" t="inlineStr">
@@ -22300,7 +22300,7 @@
         <v>350</v>
       </c>
       <c r="M306" s="22" t="n">
-        <v>-0.05896270803645849</v>
+        <v>-0.05328644847173381</v>
       </c>
       <c r="N306" s="3" t="inlineStr">
         <is>
@@ -22311,7 +22311,7 @@
         <v>400</v>
       </c>
       <c r="P306" s="5" t="n">
-        <v>0.07547119081547601</v>
+        <v>0.08195834460373279</v>
       </c>
       <c r="Q306" s="9" t="inlineStr">
         <is>
@@ -22352,13 +22352,13 @@
         </is>
       </c>
       <c r="D307" s="13" t="n">
-        <v>87.33</v>
+        <v>90.06999999999999</v>
       </c>
       <c r="E307" s="18" t="n">
-        <v>0.1235</v>
+        <v>0.1587</v>
       </c>
       <c r="F307" s="18" t="n">
-        <v>0.1838</v>
+        <v>0.2209</v>
       </c>
       <c r="G307" s="15" t="n">
         <v>46260</v>
@@ -22409,13 +22409,13 @@
         </is>
       </c>
       <c r="D308" s="4" t="n">
-        <v>61.01</v>
+        <v>58.71</v>
       </c>
       <c r="E308" s="22" t="n">
-        <v>-0.1931</v>
+        <v>-0.2235</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>0.0447</v>
+        <v>0.0053</v>
       </c>
       <c r="G308" s="6" t="n">
         <v>46245</v>
@@ -22470,13 +22470,13 @@
         </is>
       </c>
       <c r="D309" s="13" t="n">
-        <v>76.09999999999999</v>
+        <v>75.62</v>
       </c>
       <c r="E309" s="14" t="n">
-        <v>-0.0234</v>
+        <v>-0.0295</v>
       </c>
       <c r="F309" s="18" t="n">
-        <v>0.039</v>
+        <v>0.0325</v>
       </c>
       <c r="G309" s="15" t="n"/>
       <c r="H309" s="21" t="inlineStr">
@@ -22495,14 +22495,14 @@
         <v>83</v>
       </c>
       <c r="M309" s="18" t="n">
-        <v>0.09067017082785817</v>
+        <v>0.09759322930441676</v>
       </c>
       <c r="N309" s="12" t="inlineStr"/>
       <c r="O309" s="17" t="n">
         <v>87</v>
       </c>
       <c r="P309" s="18" t="n">
-        <v>0.1432325886990802</v>
+        <v>0.1504892885480031</v>
       </c>
       <c r="Q309" s="19" t="inlineStr"/>
       <c r="R309" s="17" t="n"/>
@@ -22537,13 +22537,13 @@
         </is>
       </c>
       <c r="D310" s="4" t="n">
-        <v>173.09</v>
+        <v>172.51</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>0.0488</v>
+        <v>0.0453</v>
       </c>
       <c r="F310" s="22" t="n">
-        <v>-0.08470000000000001</v>
+        <v>-0.0877</v>
       </c>
       <c r="G310" s="6" t="n"/>
       <c r="H310" s="7" t="inlineStr">
@@ -22562,7 +22562,7 @@
         <v>200</v>
       </c>
       <c r="M310" s="5" t="n">
-        <v>0.1554682535097348</v>
+        <v>0.1593530809808128</v>
       </c>
       <c r="N310" s="3" t="inlineStr"/>
       <c r="O310" s="8" t="n"/>
@@ -22610,13 +22610,13 @@
         </is>
       </c>
       <c r="D311" s="13" t="n">
-        <v>152.49</v>
+        <v>148.17</v>
       </c>
       <c r="E311" s="18" t="n">
-        <v>0.0897</v>
+        <v>0.0588</v>
       </c>
       <c r="F311" s="18" t="n">
-        <v>0.1578</v>
+        <v>0.125</v>
       </c>
       <c r="G311" s="15" t="n"/>
       <c r="H311" s="21" t="inlineStr">
@@ -22665,13 +22665,13 @@
         </is>
       </c>
       <c r="D312" s="4" t="n">
-        <v>195.04</v>
+        <v>193.8</v>
       </c>
       <c r="E312" s="5" t="n">
-        <v>0.1063</v>
+        <v>0.0993</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>0.0708</v>
+        <v>0.064</v>
       </c>
       <c r="G312" s="6" t="n">
         <v>46317</v>
@@ -22700,7 +22700,7 @@
         <v>220</v>
       </c>
       <c r="M312" s="5" t="n">
-        <v>0.1279737489745694</v>
+        <v>0.1351909184726522</v>
       </c>
       <c r="N312" s="3" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>230</v>
       </c>
       <c r="P312" s="5" t="n">
-        <v>0.179245283018868</v>
+        <v>0.1867905056759545</v>
       </c>
       <c r="Q312" s="9" t="inlineStr">
         <is>
@@ -22752,13 +22752,13 @@
         </is>
       </c>
       <c r="D313" s="13" t="n">
-        <v>1057.16</v>
+        <v>1042.62</v>
       </c>
       <c r="E313" s="18" t="n">
-        <v>0.0405</v>
+        <v>0.0262</v>
       </c>
       <c r="F313" s="14" t="n">
-        <v>-0.0053</v>
+        <v>-0.0189</v>
       </c>
       <c r="G313" s="15" t="n"/>
       <c r="H313" s="21" t="inlineStr">
@@ -22777,7 +22777,7 @@
         <v>1200</v>
       </c>
       <c r="M313" s="18" t="n">
-        <v>0.1351167278368458</v>
+        <v>0.1509466536226047</v>
       </c>
       <c r="N313" s="12" t="inlineStr">
         <is>
@@ -22788,7 +22788,7 @@
         <v>1240</v>
       </c>
       <c r="P313" s="18" t="n">
-        <v>0.172953952098074</v>
+        <v>0.1893115420766915</v>
       </c>
       <c r="Q313" s="19" t="inlineStr">
         <is>
@@ -22833,13 +22833,13 @@
         </is>
       </c>
       <c r="D314" s="4" t="n">
-        <v>118.05</v>
+        <v>118.65</v>
       </c>
       <c r="E314" s="22" t="n">
-        <v>-0.0198</v>
+        <v>-0.0148</v>
       </c>
       <c r="F314" s="22" t="n">
-        <v>-0.0332</v>
+        <v>-0.0283</v>
       </c>
       <c r="G314" s="6" t="n"/>
       <c r="H314" s="7" t="inlineStr">
@@ -22858,7 +22858,7 @@
         <v>129</v>
       </c>
       <c r="M314" s="5" t="n">
-        <v>0.09275730622617538</v>
+        <v>0.08723135271807833</v>
       </c>
       <c r="N314" s="3" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>122</v>
       </c>
       <c r="P314" s="5" t="n">
-        <v>0.03346039813638291</v>
+        <v>0.02823430257058571</v>
       </c>
       <c r="Q314" s="9" t="inlineStr">
         <is>
@@ -22910,13 +22910,13 @@
         </is>
       </c>
       <c r="D315" s="13" t="n">
-        <v>62.81</v>
+        <v>62.51</v>
       </c>
       <c r="E315" s="14" t="n">
-        <v>-0.0066</v>
+        <v>-0.0113</v>
       </c>
       <c r="F315" s="18" t="n">
-        <v>0.0467</v>
+        <v>0.0417</v>
       </c>
       <c r="G315" s="15" t="n"/>
       <c r="H315" s="21" t="inlineStr">
@@ -22935,14 +22935,14 @@
         <v>65</v>
       </c>
       <c r="M315" s="18" t="n">
-        <v>0.03486705938544814</v>
+        <v>0.03983362661974087</v>
       </c>
       <c r="N315" s="12" t="inlineStr"/>
       <c r="O315" s="17" t="n">
         <v>67</v>
       </c>
       <c r="P315" s="18" t="n">
-        <v>0.06670912275115423</v>
+        <v>0.07182850743880982</v>
       </c>
       <c r="Q315" s="19" t="inlineStr">
         <is>
@@ -22983,13 +22983,13 @@
         </is>
       </c>
       <c r="D316" s="4" t="n">
-        <v>140.13</v>
+        <v>140.11</v>
       </c>
       <c r="E316" s="22" t="n">
-        <v>-0.0062</v>
+        <v>-0.0063</v>
       </c>
       <c r="F316" s="22" t="n">
-        <v>-0.0186</v>
+        <v>-0.0187</v>
       </c>
       <c r="G316" s="6" t="n">
         <v>46309</v>
@@ -23018,7 +23018,7 @@
         <v>167</v>
       </c>
       <c r="M316" s="5" t="n">
-        <v>0.1917505173767217</v>
+        <v>0.1919206337877381</v>
       </c>
       <c r="N316" s="3" t="inlineStr"/>
       <c r="O316" s="8" t="n"/>
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="D317" s="13" t="n">
-        <v>329.93</v>
+        <v>328.27</v>
       </c>
       <c r="E317" s="18" t="n">
-        <v>0.0286</v>
+        <v>0.0234</v>
       </c>
       <c r="F317" s="18" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.0553</v>
       </c>
       <c r="G317" s="15" t="n"/>
       <c r="H317" s="21" t="inlineStr">
@@ -23094,7 +23094,7 @@
         <v>316</v>
       </c>
       <c r="P317" s="14" t="n">
-        <v>-0.04222107719819358</v>
+        <v>-0.0373777683004843</v>
       </c>
       <c r="Q317" s="19" t="inlineStr">
         <is>
@@ -23135,13 +23135,13 @@
         </is>
       </c>
       <c r="D318" s="4" t="n">
-        <v>222.26</v>
+        <v>222.93</v>
       </c>
       <c r="E318" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0175</v>
       </c>
       <c r="F318" s="5" t="n">
-        <v>0.07200000000000001</v>
+        <v>0.07519999999999999</v>
       </c>
       <c r="G318" s="6" t="n">
         <v>46244</v>
@@ -23177,7 +23177,7 @@
         <v>215</v>
       </c>
       <c r="P318" s="22" t="n">
-        <v>-0.03266444704400248</v>
+        <v>-0.03557170412237028</v>
       </c>
       <c r="Q318" s="9" t="inlineStr">
         <is>
@@ -23218,13 +23218,13 @@
         </is>
       </c>
       <c r="D319" s="13" t="n">
-        <v>120.45</v>
+        <v>120.41</v>
       </c>
       <c r="E319" s="18" t="n">
-        <v>0.0108</v>
+        <v>0.0105</v>
       </c>
       <c r="F319" s="14" t="n">
-        <v>-0.0142</v>
+        <v>-0.0146</v>
       </c>
       <c r="G319" s="15" t="n"/>
       <c r="H319" s="21" t="inlineStr">
@@ -23243,7 +23243,7 @@
         <v>142</v>
       </c>
       <c r="M319" s="18" t="n">
-        <v>0.1789124117891241</v>
+        <v>0.1793040445145752</v>
       </c>
       <c r="N319" s="12" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>137</v>
       </c>
       <c r="P319" s="18" t="n">
-        <v>0.1374014113740141</v>
+        <v>0.1377792542147663</v>
       </c>
       <c r="Q319" s="19" t="inlineStr">
         <is>
@@ -23303,13 +23303,13 @@
         </is>
       </c>
       <c r="D320" s="4" t="n">
-        <v>236.38</v>
+        <v>237.03</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>0.0106</v>
+        <v>0.0134</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>0.1819</v>
+        <v>0.1851</v>
       </c>
       <c r="G320" s="6" t="n"/>
       <c r="H320" s="7" t="inlineStr">
@@ -23327,8 +23327,8 @@
       <c r="L320" s="8" t="n">
         <v>237</v>
       </c>
-      <c r="M320" s="5" t="n">
-        <v>0.00262289533801508</v>
+      <c r="M320" s="22" t="n">
+        <v>-0.0001265662574357724</v>
       </c>
       <c r="N320" s="3" t="inlineStr">
         <is>
@@ -23339,7 +23339,7 @@
         <v>236</v>
       </c>
       <c r="P320" s="22" t="n">
-        <v>-0.001607581013622115</v>
+        <v>-0.004345441505294693</v>
       </c>
       <c r="Q320" s="9" t="inlineStr">
         <is>
@@ -23380,13 +23380,13 @@
         </is>
       </c>
       <c r="D321" s="13" t="n">
-        <v>171.68</v>
+        <v>170.2</v>
       </c>
       <c r="E321" s="14" t="n">
-        <v>-0.0306</v>
+        <v>-0.0389</v>
       </c>
       <c r="F321" s="18" t="n">
-        <v>0.0225</v>
+        <v>0.0138</v>
       </c>
       <c r="G321" s="15" t="n"/>
       <c r="H321" s="21" t="inlineStr">
@@ -23405,7 +23405,7 @@
         <v>200</v>
       </c>
       <c r="M321" s="18" t="n">
-        <v>0.1649580615097856</v>
+        <v>0.1750881316098708</v>
       </c>
       <c r="N321" s="12" t="inlineStr"/>
       <c r="O321" s="17" t="n"/>
@@ -23449,13 +23449,13 @@
         </is>
       </c>
       <c r="D322" s="4" t="n">
-        <v>135.56</v>
+        <v>135.28</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>0.0279</v>
+        <v>0.0258</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>0.1067</v>
+        <v>0.1044</v>
       </c>
       <c r="G322" s="6" t="n"/>
       <c r="H322" s="7" t="inlineStr">
@@ -23474,7 +23474,7 @@
         <v>131</v>
       </c>
       <c r="M322" s="22" t="n">
-        <v>-0.03363824136913546</v>
+        <v>-0.0316380839739799</v>
       </c>
       <c r="N322" s="3" t="inlineStr"/>
       <c r="O322" s="8" t="n"/>
@@ -23518,13 +23518,13 @@
         </is>
       </c>
       <c r="D323" s="13" t="n">
-        <v>33.38</v>
+        <v>33.73</v>
       </c>
       <c r="E323" s="14" t="n">
-        <v>-0.0707</v>
+        <v>-0.061</v>
       </c>
       <c r="F323" s="14" t="n">
-        <v>-0.1346</v>
+        <v>-0.1255</v>
       </c>
       <c r="G323" s="15" t="n"/>
       <c r="H323" s="21" t="inlineStr">
@@ -23587,13 +23587,13 @@
         </is>
       </c>
       <c r="D324" s="4" t="n">
-        <v>39.4</v>
+        <v>39.07</v>
       </c>
       <c r="E324" s="5" t="n">
-        <v>0.0546</v>
+        <v>0.0458</v>
       </c>
       <c r="F324" s="5" t="n">
-        <v>0.0189</v>
+        <v>0.0103</v>
       </c>
       <c r="G324" s="6" t="n"/>
       <c r="H324" s="7" t="inlineStr">
@@ -23638,13 +23638,13 @@
         </is>
       </c>
       <c r="D325" s="13" t="n">
-        <v>266.9</v>
+        <v>269.89</v>
       </c>
       <c r="E325" s="18" t="n">
-        <v>0.0915</v>
+        <v>0.1038</v>
       </c>
       <c r="F325" s="18" t="n">
-        <v>0.06480000000000001</v>
+        <v>0.0767</v>
       </c>
       <c r="G325" s="15" t="n"/>
       <c r="H325" s="21" t="inlineStr">
@@ -23663,7 +23663,7 @@
         <v>384</v>
       </c>
       <c r="M325" s="18" t="n">
-        <v>0.438741101536156</v>
+        <v>0.4228018822483235</v>
       </c>
       <c r="N325" s="12" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>380</v>
       </c>
       <c r="P325" s="18" t="n">
-        <v>0.423754215061821</v>
+        <v>0.4079810293082368</v>
       </c>
       <c r="Q325" s="19" t="inlineStr"/>
       <c r="R325" s="17" t="n"/>
@@ -23717,13 +23717,13 @@
         </is>
       </c>
       <c r="D326" s="4" t="n">
-        <v>71.12</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="E326" s="22" t="n">
-        <v>-0.0665</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="F326" s="5" t="n">
-        <v>0.003</v>
+        <v>0.0018</v>
       </c>
       <c r="G326" s="6" t="n"/>
       <c r="H326" s="7" t="inlineStr">
@@ -23742,7 +23742,7 @@
         <v>79</v>
       </c>
       <c r="M326" s="5" t="n">
-        <v>0.1107986501687288</v>
+        <v>0.1120495495495494</v>
       </c>
       <c r="N326" s="3" t="inlineStr"/>
       <c r="O326" s="8" t="n"/>
@@ -23794,13 +23794,13 @@
         </is>
       </c>
       <c r="D327" s="13" t="n">
-        <v>124.49</v>
+        <v>124.86</v>
       </c>
       <c r="E327" s="14" t="n">
-        <v>-0.0181</v>
+        <v>-0.0152</v>
       </c>
       <c r="F327" s="18" t="n">
-        <v>0.02</v>
+        <v>0.0231</v>
       </c>
       <c r="G327" s="15" t="n"/>
       <c r="H327" s="21" t="inlineStr">
@@ -23819,7 +23819,7 @@
         <v>136</v>
       </c>
       <c r="M327" s="18" t="n">
-        <v>0.09245722547995827</v>
+        <v>0.08921992631747558</v>
       </c>
       <c r="N327" s="12" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>140</v>
       </c>
       <c r="P327" s="18" t="n">
-        <v>0.1245883203470159</v>
+        <v>0.1212558065032837</v>
       </c>
       <c r="Q327" s="19" t="inlineStr">
         <is>
@@ -23871,13 +23871,13 @@
         </is>
       </c>
       <c r="D328" s="4" t="n">
-        <v>107.16</v>
+        <v>107.17</v>
       </c>
       <c r="E328" s="22" t="n">
-        <v>-0.06280000000000001</v>
+        <v>-0.06269999999999999</v>
       </c>
       <c r="F328" s="22" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="G328" s="6" t="n"/>
       <c r="H328" s="7" t="inlineStr">
@@ -23896,7 +23896,7 @@
         <v>131</v>
       </c>
       <c r="M328" s="5" t="n">
-        <v>0.2224710712952595</v>
+        <v>0.2223570028926005</v>
       </c>
       <c r="N328" s="3" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>121</v>
       </c>
       <c r="P328" s="5" t="n">
-        <v>0.1291526689063084</v>
+        <v>0.1290473080153028</v>
       </c>
       <c r="Q328" s="9" t="inlineStr">
         <is>
@@ -23952,13 +23952,13 @@
         </is>
       </c>
       <c r="D329" s="13" t="n">
-        <v>84.43000000000001</v>
+        <v>84.66</v>
       </c>
       <c r="E329" s="14" t="n">
-        <v>-0.0345</v>
+        <v>-0.0318</v>
       </c>
       <c r="F329" s="18" t="n">
-        <v>0.0049</v>
+        <v>0.0077</v>
       </c>
       <c r="G329" s="15" t="n">
         <v>46318</v>
@@ -23994,7 +23994,7 @@
         <v>107</v>
       </c>
       <c r="P329" s="18" t="n">
-        <v>0.2673220419282245</v>
+        <v>0.2638790455941413</v>
       </c>
       <c r="Q329" s="19" t="inlineStr">
         <is>
@@ -24043,13 +24043,13 @@
         </is>
       </c>
       <c r="D330" s="4" t="n">
-        <v>54.6</v>
+        <v>55.03</v>
       </c>
       <c r="E330" s="22" t="n">
-        <v>-0.0521</v>
+        <v>-0.0445</v>
       </c>
       <c r="F330" s="5" t="n">
-        <v>0.0029</v>
+        <v>0.0109</v>
       </c>
       <c r="G330" s="6" t="n"/>
       <c r="H330" s="7" t="inlineStr">
@@ -24068,7 +24068,7 @@
         <v>63</v>
       </c>
       <c r="M330" s="5" t="n">
-        <v>0.1538461538461538</v>
+        <v>0.1448300926767218</v>
       </c>
       <c r="N330" s="3" t="inlineStr"/>
       <c r="O330" s="8" t="n"/>
@@ -24112,13 +24112,13 @@
         </is>
       </c>
       <c r="D331" s="13" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="E331" s="14" t="n">
-        <v>-0.04190000000000001</v>
+        <v>48.43</v>
+      </c>
+      <c r="E331" s="18" t="n">
+        <v>0.0243</v>
       </c>
       <c r="F331" s="14" t="n">
-        <v>-0.2314</v>
+        <v>-0.1783</v>
       </c>
       <c r="G331" s="15" t="n">
         <v>46241</v>
@@ -24173,13 +24173,13 @@
         </is>
       </c>
       <c r="D332" s="4" t="n">
-        <v>9.449999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>0.0793</v>
+        <v>0.1221</v>
       </c>
       <c r="F332" s="22" t="n">
-        <v>-0.1213</v>
+        <v>-0.0864</v>
       </c>
       <c r="G332" s="6" t="n"/>
       <c r="H332" s="7" t="inlineStr">
@@ -24224,13 +24224,13 @@
         </is>
       </c>
       <c r="D333" s="13" t="n">
-        <v>93.18000000000001</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="E333" s="14" t="n">
-        <v>-0.0333</v>
+        <v>-0.0381</v>
       </c>
       <c r="F333" s="18" t="n">
-        <v>0.0208</v>
+        <v>0.0157</v>
       </c>
       <c r="G333" s="15" t="n"/>
       <c r="H333" s="21" t="inlineStr">
@@ -24249,7 +24249,7 @@
         <v>99</v>
       </c>
       <c r="M333" s="18" t="n">
-        <v>0.0624597553122987</v>
+        <v>0.06784597130838105</v>
       </c>
       <c r="N333" s="12" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>112</v>
       </c>
       <c r="P333" s="18" t="n">
-        <v>0.2019746726765399</v>
+        <v>0.2080681695609967</v>
       </c>
       <c r="Q333" s="19" t="inlineStr">
         <is>
@@ -24301,13 +24301,13 @@
         </is>
       </c>
       <c r="D334" s="4" t="n">
-        <v>108.21</v>
+        <v>107.63</v>
       </c>
       <c r="E334" s="22" t="n">
-        <v>-0.06909999999999999</v>
+        <v>-0.0741</v>
       </c>
       <c r="F334" s="22" t="n">
-        <v>-0.0274</v>
+        <v>-0.0325</v>
       </c>
       <c r="G334" s="6" t="n"/>
       <c r="H334" s="7" t="inlineStr">
@@ -24326,7 +24326,7 @@
         <v>127</v>
       </c>
       <c r="M334" s="5" t="n">
-        <v>0.173643840680159</v>
+        <v>0.1799684102945276</v>
       </c>
       <c r="N334" s="3" t="inlineStr"/>
       <c r="O334" s="8" t="n"/>
@@ -31733,7 +31733,7 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Data as of August 07, 2026 at 14:33 UTC</t>
+          <t>Data as of August 07, 2026 at 20:05 UTC</t>
         </is>
       </c>
     </row>

--- a/earnings-data.xlsx
+++ b/earnings-data.xlsx
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>103.61</v>
+        <v>103.52</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.0793</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.0357</v>
+        <v>0.0348</v>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="7" t="inlineStr">
@@ -868,7 +868,7 @@
         <v>125</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>0.2064472541260496</v>
+        <v>0.2074961360123648</v>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>144</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.3898272367532092</v>
+        <v>0.3910355486862442</v>
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="D3" s="13" t="n">
-        <v>352.2</v>
+        <v>343.8</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>-0.0009</v>
+        <v>-0.0247</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>-0.0208</v>
+        <v>-0.0442</v>
       </c>
       <c r="G3" s="15" t="n">
         <v>46322</v>
@@ -963,7 +963,7 @@
         <v>438</v>
       </c>
       <c r="M3" s="18" t="n">
-        <v>0.2436115843270869</v>
+        <v>0.2739965095986038</v>
       </c>
       <c r="N3" s="12" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>420</v>
       </c>
       <c r="P3" s="18" t="n">
-        <v>0.192504258943782</v>
+        <v>0.2216404886561954</v>
       </c>
       <c r="Q3" s="19" t="inlineStr">
         <is>
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>609.0700000000001</v>
+        <v>599.12</v>
       </c>
       <c r="E4" s="22" t="n">
-        <v>-0.0726</v>
+        <v>-0.0877</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.0742</v>
+        <v>0.0567</v>
       </c>
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="7" t="inlineStr">
@@ -1044,7 +1044,7 @@
         <v>835</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.3709425845961875</v>
+        <v>0.3937107758045133</v>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>930</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>0.5269180882328796</v>
+        <v>0.552276672452931</v>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>37.03</v>
+        <v>36.8</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>-0.0391</v>
+        <v>-0.0451</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>0.06150000000000001</v>
+        <v>0.0547</v>
       </c>
       <c r="G5" s="15" t="n"/>
       <c r="H5" s="21" t="inlineStr">
@@ -1155,13 +1155,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>76.27</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.033</v>
+        <v>0.013</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>-0.0507</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>46315</v>
@@ -1190,7 +1190,7 @@
         <v>80</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.04890520519208082</v>
+        <v>0.06966171948121398</v>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>100</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>0.311131506490101</v>
+        <v>0.3370771493515174</v>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
@@ -1242,13 +1242,13 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>84.81</v>
+        <v>85.95</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>0.0274</v>
+        <v>0.0412</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>0.106</v>
+        <v>0.1209</v>
       </c>
       <c r="G7" s="15" t="n"/>
       <c r="H7" s="21" t="inlineStr">
@@ -1267,7 +1267,7 @@
         <v>91</v>
       </c>
       <c r="M7" s="18" t="n">
-        <v>0.07298667609951653</v>
+        <v>0.0587550901687027</v>
       </c>
       <c r="N7" s="12" t="inlineStr"/>
       <c r="O7" s="17" t="n"/>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>506.9</v>
+        <v>501.16</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.0564</v>
+        <v>0.0444</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.0517</v>
+        <v>0.0398</v>
       </c>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="7" t="inlineStr">
@@ -1336,7 +1336,7 @@
         <v>569.9299999999999</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.1243440520812783</v>
+        <v>0.1372216457817861</v>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>648.04</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.2784375616492404</v>
+        <v>0.293080054274084</v>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
@@ -1388,13 +1388,13 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>191.12</v>
+        <v>194.79</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>0.0561</v>
+        <v>0.0764</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>-0.0602</v>
+        <v>-0.0421</v>
       </c>
       <c r="G9" s="15" t="n"/>
       <c r="H9" s="21" t="inlineStr">
@@ -1447,13 +1447,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>179.96</v>
+        <v>178.59</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>-0.04480000000000001</v>
+        <v>-0.0521</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>-0.0483</v>
+        <v>-0.0556</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>46317</v>
@@ -1482,7 +1482,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="22" t="n">
-        <v>-0.05534563236274732</v>
+        <v>-0.04809899770423878</v>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>270</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.5003334074238719</v>
+        <v>0.5118427683520913</v>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
@@ -1534,13 +1534,13 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>47.1</v>
+        <v>47.28</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>0.1034</v>
+        <v>0.1077</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>-0.0211</v>
+        <v>-0.0174</v>
       </c>
       <c r="G11" s="15" t="n">
         <v>46316</v>
@@ -1569,7 +1569,7 @@
         <v>43</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>-0.08704883227176223</v>
+        <v>-0.09052453468697126</v>
       </c>
       <c r="N11" s="12" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         <v>50</v>
       </c>
       <c r="P11" s="18" t="n">
-        <v>0.06157112526539275</v>
+        <v>0.05752961082910319</v>
       </c>
       <c r="Q11" s="19" t="inlineStr">
         <is>
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>182.6</v>
+        <v>184.98</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.2479</v>
+        <v>0.2641</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.3804</v>
+        <v>0.3984</v>
       </c>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="7" t="inlineStr">
@@ -1650,7 +1650,7 @@
         <v>181</v>
       </c>
       <c r="M12" s="22" t="n">
-        <v>-0.008762322015334032</v>
+        <v>-0.02151583955022159</v>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>155</v>
       </c>
       <c r="P12" s="22" t="n">
-        <v>-0.1511500547645126</v>
+        <v>-0.1620715753054384</v>
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
@@ -1702,13 +1702,13 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>274.19</v>
+        <v>272.27</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>0.1087</v>
+        <v>0.1009</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>0.1494</v>
+        <v>0.1414</v>
       </c>
       <c r="G13" s="15" t="n"/>
       <c r="H13" s="21" t="inlineStr">
@@ -1727,7 +1727,7 @@
         <v>322</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>0.1743681388817973</v>
+        <v>0.1826495757887392</v>
       </c>
       <c r="N13" s="12" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>285</v>
       </c>
       <c r="P13" s="18" t="n">
-        <v>0.03942521609103178</v>
+        <v>0.0467550593161201</v>
       </c>
       <c r="Q13" s="19" t="inlineStr">
         <is>
@@ -1791,13 +1791,13 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>3095.01</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>0.0052</v>
+        <v>3042.93</v>
+      </c>
+      <c r="E14" s="22" t="n">
+        <v>-0.0117</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.0068</v>
+        <v>-0.0235</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>46287</v>
@@ -1826,7 +1826,7 @@
         <v>4150</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0.3408680424295882</v>
+        <v>0.3638171104823312</v>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>3700</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>0.1954727125275846</v>
+        <v>0.2159333274179821</v>
       </c>
       <c r="Q14" s="9" t="inlineStr">
         <is>
@@ -1878,13 +1878,13 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>84.11</v>
+        <v>83.28</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0.0301</v>
+        <v>0.0199</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>0.0711</v>
+        <v>0.0605</v>
       </c>
       <c r="G15" s="15" t="n">
         <v>46261</v>
@@ -1913,7 +1913,7 @@
         <v>65</v>
       </c>
       <c r="M15" s="14" t="n">
-        <v>-0.2272024729520865</v>
+        <v>-0.2195004803073967</v>
       </c>
       <c r="N15" s="12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>85</v>
       </c>
       <c r="P15" s="18" t="n">
-        <v>0.01058138152419451</v>
+        <v>0.0206532180595581</v>
       </c>
       <c r="Q15" s="19" t="inlineStr"/>
       <c r="R15" s="17" t="n"/>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>213.59</v>
+        <v>212.87</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.215</v>
+        <v>0.2109</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.295</v>
+        <v>0.2906</v>
       </c>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="7" t="inlineStr">
@@ -1984,7 +1984,7 @@
         <v>214</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.001919565522730449</v>
+        <v>0.005308404190350897</v>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>245</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>0.147057446509668</v>
+        <v>0.1509371917132522</v>
       </c>
       <c r="Q16" s="9" t="inlineStr">
         <is>
@@ -2044,13 +2044,13 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>365.9</v>
+        <v>359.1</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>0.117</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>0.08109999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="G17" s="15" t="n">
         <v>46261</v>
@@ -2079,7 +2079,7 @@
         <v>375</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>0.02487018311013945</v>
+        <v>0.04427736006683369</v>
       </c>
       <c r="N17" s="12" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>375</v>
       </c>
       <c r="P17" s="18" t="n">
-        <v>0.02487018311013945</v>
+        <v>0.04427736006683369</v>
       </c>
       <c r="Q17" s="19" t="inlineStr"/>
       <c r="R17" s="17" t="n"/>
@@ -2129,13 +2129,13 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>32.05</v>
+        <v>31.98</v>
       </c>
       <c r="E18" s="22" t="n">
-        <v>-0.125</v>
+        <v>-0.1271</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>-0.005600000000000001</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="7" t="inlineStr">
@@ -2154,7 +2154,7 @@
         <v>45</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.40405616224649</v>
+        <v>0.4071294559099437</v>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>45</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.40405616224649</v>
+        <v>0.4071294559099437</v>
       </c>
       <c r="Q18" s="9" t="inlineStr">
         <is>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>149.16</v>
+        <v>150.79</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>0.0021</v>
+        <v>0.013</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>-0.032</v>
+        <v>-0.0214</v>
       </c>
       <c r="G19" s="15" t="n">
         <v>46324</v>
@@ -2241,7 +2241,7 @@
         <v>170</v>
       </c>
       <c r="M19" s="18" t="n">
-        <v>0.139715741485653</v>
+        <v>0.1273957158962797</v>
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>177</v>
       </c>
       <c r="P19" s="18" t="n">
-        <v>0.1866452131938858</v>
+        <v>0.1738178924331853</v>
       </c>
       <c r="Q19" s="19" t="inlineStr">
         <is>
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>207.04</v>
+        <v>204.94</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>-0.04190000000000001</v>
+        <v>-0.0516</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>-0.06309999999999999</v>
+        <v>-0.0726</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>46259</v>
@@ -2328,7 +2328,7 @@
         <v>220</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0.06259659969088104</v>
+        <v>0.07348492241631699</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="8" t="n"/>
@@ -2372,13 +2372,13 @@
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>128.82</v>
+        <v>128.06</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>0.0193</v>
+        <v>0.0133</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>0.13</v>
+        <v>0.1233</v>
       </c>
       <c r="G21" s="15" t="n">
         <v>46261</v>
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>89.43000000000001</v>
+        <v>89.36</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.1656</v>
+        <v>0.1648</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.09720000000000001</v>
+        <v>0.0964</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>46315</v>
@@ -2468,7 +2468,7 @@
         <v>61</v>
       </c>
       <c r="M22" s="22" t="n">
-        <v>-0.3179022699317903</v>
+        <v>-0.3173679498657117</v>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>100</v>
       </c>
       <c r="P22" s="5" t="n">
-        <v>0.1181930001118192</v>
+        <v>0.1190689346463742</v>
       </c>
       <c r="Q22" s="9" t="inlineStr">
         <is>
@@ -2520,13 +2520,13 @@
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>136.89</v>
+        <v>135.17</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>0.1082</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>0.3194</v>
+        <v>0.3028</v>
       </c>
       <c r="G23" s="15" t="n">
         <v>46315</v>
@@ -2558,7 +2558,7 @@
         <v>145</v>
       </c>
       <c r="P23" s="18" t="n">
-        <v>0.05924464898823883</v>
+        <v>0.07272323740474967</v>
       </c>
       <c r="Q23" s="19" t="inlineStr"/>
       <c r="R23" s="17" t="n"/>
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>358.02</v>
+        <v>354.51</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.062</v>
+        <v>0.0516</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.0902</v>
+        <v>0.0795</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>46252</v>
@@ -2628,7 +2628,7 @@
         <v>360</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0.005530417295123229</v>
+        <v>0.01548616400101551</v>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>400</v>
       </c>
       <c r="P24" s="5" t="n">
-        <v>0.1172560192168036</v>
+        <v>0.1283179600011284</v>
       </c>
       <c r="Q24" s="9" t="inlineStr">
         <is>
@@ -2688,13 +2688,13 @@
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>223.52</v>
+        <v>221.24</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>0.0762</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>0.0124</v>
+        <v>0.0021</v>
       </c>
       <c r="G25" s="15" t="n">
         <v>46253</v>
@@ -2723,7 +2723,7 @@
         <v>255</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>0.1408375089477451</v>
+        <v>0.1525944675465557</v>
       </c>
       <c r="N25" s="12" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>230</v>
       </c>
       <c r="P25" s="18" t="n">
-        <v>0.02899069434502501</v>
+        <v>0.03959500994395223</v>
       </c>
       <c r="Q25" s="19" t="inlineStr">
         <is>
@@ -2779,13 +2779,13 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>272.74</v>
+        <v>274.13</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>-0.0424</v>
+        <v>-0.0375</v>
       </c>
       <c r="G26" s="6" t="n"/>
       <c r="H26" s="7" t="inlineStr">
@@ -2804,7 +2804,7 @@
         <v>300</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.0999486690621104</v>
+        <v>0.0943712836975158</v>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>350</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0.2832734472391288</v>
+        <v>0.2767664976471018</v>
       </c>
       <c r="Q26" s="9" t="inlineStr">
         <is>
@@ -2856,13 +2856,13 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>41.43</v>
+        <v>41.3</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>-0.0534</v>
+        <v>-0.0562</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>-0.078</v>
+        <v>-0.0808</v>
       </c>
       <c r="G27" s="15" t="n">
         <v>46294</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>93.8</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.0747</v>
+        <v>0.06059999999999999</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.0305</v>
+        <v>0.017</v>
       </c>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="7" t="inlineStr">
@@ -2942,7 +2942,7 @@
         <v>110</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.1727078891257996</v>
+        <v>0.1882899427460301</v>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>115</v>
       </c>
       <c r="P28" s="5" t="n">
-        <v>0.2260127931769723</v>
+        <v>0.2423031219617588</v>
       </c>
       <c r="Q28" s="9" t="inlineStr">
         <is>
@@ -2998,13 +2998,13 @@
         </is>
       </c>
       <c r="D29" s="13" t="n">
-        <v>204.29</v>
+        <v>201.5</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>-0.031</v>
+        <v>-0.0442</v>
       </c>
       <c r="F29" s="18" t="n">
-        <v>0.0476</v>
+        <v>0.0333</v>
       </c>
       <c r="G29" s="15" t="n">
         <v>46317</v>
@@ -3059,13 +3059,13 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>252.2</v>
+        <v>251.81</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.1492</v>
+        <v>0.1474</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.0503</v>
+        <v>0.0486</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>46254</v>
@@ -3094,7 +3094,7 @@
         <v>245</v>
       </c>
       <c r="M30" s="22" t="n">
-        <v>-0.02854877081681201</v>
+        <v>-0.02704419999205751</v>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>265</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>0.05075337034099926</v>
+        <v>0.05238076327389698</v>
       </c>
       <c r="Q30" s="9" t="inlineStr">
         <is>
@@ -3146,13 +3146,13 @@
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>106.09</v>
+        <v>106.66</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>-0.0116</v>
+        <v>-0.0063</v>
       </c>
       <c r="F31" s="18" t="n">
-        <v>0.0296</v>
+        <v>0.0351</v>
       </c>
       <c r="G31" s="15" t="n"/>
       <c r="H31" s="21" t="inlineStr">
@@ -3171,7 +3171,7 @@
         <v>120</v>
       </c>
       <c r="M31" s="18" t="n">
-        <v>0.1311150909605052</v>
+        <v>0.125070316894806</v>
       </c>
       <c r="N31" s="12" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>115</v>
       </c>
       <c r="P31" s="18" t="n">
-        <v>0.08398529550381748</v>
+        <v>0.07819238702418904</v>
       </c>
       <c r="Q31" s="19" t="inlineStr">
         <is>
@@ -3223,13 +3223,13 @@
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>13.19</v>
+        <v>13.27</v>
       </c>
       <c r="E32" s="22" t="n">
-        <v>-0.1539</v>
+        <v>-0.1488</v>
       </c>
       <c r="F32" s="22" t="n">
-        <v>-0.1751</v>
+        <v>-0.1701</v>
       </c>
       <c r="G32" s="6" t="n"/>
       <c r="H32" s="7" t="inlineStr">
@@ -3274,13 +3274,13 @@
         </is>
       </c>
       <c r="D33" s="13" t="n">
-        <v>157.14</v>
+        <v>155.72</v>
       </c>
       <c r="E33" s="18" t="n">
-        <v>0.04389999999999999</v>
+        <v>0.0345</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>-0.0669</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="G33" s="15" t="n">
         <v>46253</v>
@@ -3309,7 +3309,7 @@
         <v>160</v>
       </c>
       <c r="M33" s="18" t="n">
-        <v>0.01820033091510764</v>
+        <v>0.0274852298998202</v>
       </c>
       <c r="N33" s="12" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>175</v>
       </c>
       <c r="P33" s="18" t="n">
-        <v>0.113656611938399</v>
+        <v>0.1238119702029283</v>
       </c>
       <c r="Q33" s="19" t="inlineStr">
         <is>
@@ -3365,13 +3365,13 @@
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>36.23</v>
+        <v>35.29</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.1981</v>
+        <v>0.167</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.1594</v>
+        <v>0.1293</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>46317</v>
@@ -3400,7 +3400,7 @@
         <v>35</v>
       </c>
       <c r="M34" s="22" t="n">
-        <v>-0.03394976538780008</v>
+        <v>-0.008217625389628766</v>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>40</v>
       </c>
       <c r="P34" s="5" t="n">
-        <v>0.1040574109853713</v>
+        <v>0.1334655709832814</v>
       </c>
       <c r="Q34" s="9" t="inlineStr">
         <is>
@@ -3452,13 +3452,13 @@
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>333.89</v>
+        <v>332.81</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>-0.1542</v>
+        <v>-0.1569</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>-0.1785</v>
+        <v>-0.1811</v>
       </c>
       <c r="G35" s="15" t="n">
         <v>46323</v>
@@ -3487,7 +3487,7 @@
         <v>130</v>
       </c>
       <c r="M35" s="14" t="n">
-        <v>-0.6106502141423822</v>
+        <v>-0.6093867371773685</v>
       </c>
       <c r="N35" s="12" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>300</v>
       </c>
       <c r="P35" s="14" t="n">
-        <v>-0.1015004941747282</v>
+        <v>-0.09858477810161954</v>
       </c>
       <c r="Q35" s="19" t="inlineStr">
         <is>
@@ -3539,13 +3539,13 @@
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>78.52</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.0574</v>
+        <v>0.0576</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.1405</v>
+        <v>0.1407</v>
       </c>
       <c r="G36" s="6" t="n"/>
       <c r="H36" s="7" t="inlineStr">
@@ -3590,13 +3590,13 @@
         </is>
       </c>
       <c r="D37" s="13" t="n">
-        <v>549.28</v>
+        <v>541.35</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>0.1605</v>
+        <v>0.1437</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>0.1743</v>
+        <v>0.1574</v>
       </c>
       <c r="G37" s="15" t="n">
         <v>46261</v>
@@ -3625,7 +3625,7 @@
         <v>450</v>
       </c>
       <c r="M37" s="14" t="n">
-        <v>-0.1807457034663559</v>
+        <v>-0.1687448046550291</v>
       </c>
       <c r="N37" s="12" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>635</v>
       </c>
       <c r="P37" s="18" t="n">
-        <v>0.1560588406641422</v>
+        <v>0.1729934423201256</v>
       </c>
       <c r="Q37" s="19" t="inlineStr">
         <is>
@@ -3681,13 +3681,13 @@
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>102.52</v>
+        <v>102.79</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.0552</v>
+        <v>0.0579</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.0508</v>
+        <v>0.0536</v>
       </c>
       <c r="G38" s="6" t="n"/>
       <c r="H38" s="7" t="inlineStr">
@@ -3706,7 +3706,7 @@
         <v>110</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.07296137339055798</v>
+        <v>0.07014301002042994</v>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>105</v>
       </c>
       <c r="P38" s="5" t="n">
-        <v>0.02419040187280535</v>
+        <v>0.02150014592859221</v>
       </c>
       <c r="Q38" s="9" t="inlineStr">
         <is>
@@ -3762,13 +3762,13 @@
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>92.51000000000001</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>-0.0075</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F39" s="18" t="n">
-        <v>0.0342</v>
+        <v>0.032</v>
       </c>
       <c r="G39" s="15" t="n"/>
       <c r="H39" s="21" t="inlineStr">
@@ -3787,7 +3787,7 @@
         <v>95</v>
       </c>
       <c r="M39" s="18" t="n">
-        <v>0.02691600908009939</v>
+        <v>0.02902946273830164</v>
       </c>
       <c r="N39" s="12" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="18" t="n">
-        <v>0.08096422008431516</v>
+        <v>0.08318890814558066</v>
       </c>
       <c r="Q39" s="19" t="inlineStr">
         <is>
@@ -3843,13 +3843,13 @@
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>945.51</v>
+        <v>944.3200000000001</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.0206</v>
+        <v>0.0193</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>-0.0375</v>
+        <v>-0.0387</v>
       </c>
       <c r="G40" s="6" t="n">
         <v>46289</v>
@@ -3878,7 +3878,7 @@
         <v>1000</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0.05763027360895179</v>
+        <v>0.05896306336834965</v>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>1100</v>
       </c>
       <c r="P40" s="5" t="n">
-        <v>0.163393300969847</v>
+        <v>0.1648593697051846</v>
       </c>
       <c r="Q40" s="9" t="inlineStr">
         <is>
@@ -3938,13 +3938,13 @@
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>121.91</v>
+        <v>120.07</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>-0.0124</v>
+        <v>-0.0273</v>
       </c>
       <c r="F41" s="18" t="n">
-        <v>0.0619</v>
+        <v>0.0459</v>
       </c>
       <c r="G41" s="15" t="n">
         <v>46261</v>
@@ -3973,7 +3973,7 @@
         <v>125</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>0.02534656713969324</v>
+        <v>0.04105938202715089</v>
       </c>
       <c r="N41" s="12" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>135</v>
       </c>
       <c r="P41" s="18" t="n">
-        <v>0.1073742925108687</v>
+        <v>0.124344132589323</v>
       </c>
       <c r="Q41" s="19" t="inlineStr">
         <is>
@@ -4025,13 +4025,13 @@
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>24.69</v>
+        <v>24.65</v>
       </c>
       <c r="E42" s="22" t="n">
-        <v>-0.0212</v>
+        <v>-0.023</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.0125</v>
+        <v>0.0107</v>
       </c>
       <c r="G42" s="6" t="n"/>
       <c r="H42" s="7" t="inlineStr">
@@ -4076,13 +4076,13 @@
         </is>
       </c>
       <c r="D43" s="13" t="n">
-        <v>86.48</v>
+        <v>86.5</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>0.0265</v>
+        <v>0.0268</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>0.0467</v>
+        <v>0.047</v>
       </c>
       <c r="G43" s="15" t="n"/>
       <c r="H43" s="21" t="inlineStr">
@@ -4101,7 +4101,7 @@
         <v>90</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>0.04070305272895462</v>
+        <v>0.04046242774566474</v>
       </c>
       <c r="N43" s="12" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>88</v>
       </c>
       <c r="P43" s="18" t="n">
-        <v>0.01757631822386674</v>
+        <v>0.01734104046242774</v>
       </c>
       <c r="Q43" s="19" t="inlineStr">
         <is>
@@ -4161,13 +4161,13 @@
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>56.63</v>
+        <v>56.26</v>
       </c>
       <c r="E44" s="22" t="n">
-        <v>-0.0453</v>
+        <v>-0.05139999999999999</v>
       </c>
       <c r="F44" s="22" t="n">
-        <v>-0.1249</v>
+        <v>-0.1306</v>
       </c>
       <c r="G44" s="6" t="n">
         <v>46275</v>
@@ -4196,7 +4196,7 @@
         <v>58</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>0.02419212431573366</v>
+        <v>0.03092783505154643</v>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>78</v>
       </c>
       <c r="P44" s="5" t="n">
-        <v>0.3773618223556418</v>
+        <v>0.3864201919658728</v>
       </c>
       <c r="Q44" s="9" t="inlineStr">
         <is>
@@ -4248,13 +4248,13 @@
         </is>
       </c>
       <c r="D45" s="13" t="n">
-        <v>61.35</v>
+        <v>61.78</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>0.0249</v>
+        <v>0.0321</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>-0.026</v>
+        <v>-0.0192</v>
       </c>
       <c r="G45" s="15" t="n"/>
       <c r="H45" s="21" t="inlineStr">
@@ -4273,7 +4273,7 @@
         <v>70</v>
       </c>
       <c r="M45" s="18" t="n">
-        <v>0.1409942950285248</v>
+        <v>0.1330527678860473</v>
       </c>
       <c r="N45" s="12" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>71</v>
       </c>
       <c r="P45" s="18" t="n">
-        <v>0.1572942135289323</v>
+        <v>0.1492392359987051</v>
       </c>
       <c r="Q45" s="19" t="inlineStr">
         <is>
@@ -4333,13 +4333,13 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>52.72</v>
+        <v>52.89</v>
       </c>
       <c r="E46" s="22" t="n">
-        <v>-0.0193</v>
+        <v>-0.016</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.0805</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>46301</v>
@@ -4404,13 +4404,13 @@
         </is>
       </c>
       <c r="D47" s="13" t="n">
-        <v>45.54</v>
+        <v>45.53</v>
       </c>
       <c r="E47" s="14" t="n">
-        <v>-0.0617</v>
+        <v>-0.0619</v>
       </c>
       <c r="F47" s="14" t="n">
-        <v>-0.0189</v>
+        <v>-0.0191</v>
       </c>
       <c r="G47" s="15" t="n"/>
       <c r="H47" s="21" t="inlineStr">
@@ -4455,13 +4455,13 @@
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>65.20999999999999</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="E48" s="22" t="n">
-        <v>-0.0926</v>
+        <v>-0.095</v>
       </c>
       <c r="F48" s="22" t="n">
-        <v>-0.0935</v>
+        <v>-0.0959</v>
       </c>
       <c r="G48" s="6" t="n"/>
       <c r="H48" s="7" t="inlineStr">
@@ -4506,13 +4506,13 @@
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>137.46</v>
+        <v>138.41</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>-0.0075</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>-0.0472</v>
+        <v>-0.0406</v>
       </c>
       <c r="G49" s="15" t="n">
         <v>46303</v>
@@ -4541,7 +4541,7 @@
         <v>140</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>0.01847810272079144</v>
+        <v>0.01148760927678638</v>
       </c>
       <c r="N49" s="12" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>150</v>
       </c>
       <c r="P49" s="18" t="n">
-        <v>0.0912265386294194</v>
+        <v>0.08373672422512828</v>
       </c>
       <c r="Q49" s="19" t="inlineStr">
         <is>
@@ -4601,13 +4601,13 @@
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>144.27</v>
+        <v>145.21</v>
       </c>
       <c r="E50" s="22" t="n">
-        <v>-0.0276</v>
+        <v>-0.0213</v>
       </c>
       <c r="F50" s="22" t="n">
-        <v>-0.0357</v>
+        <v>-0.0294</v>
       </c>
       <c r="G50" s="6" t="n"/>
       <c r="H50" s="7" t="inlineStr">
@@ -4626,7 +4626,7 @@
         <v>164</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.1367574686351978</v>
+        <v>0.1293988017354176</v>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>162</v>
       </c>
       <c r="P50" s="5" t="n">
-        <v>0.122894572676232</v>
+        <v>0.115625645616693</v>
       </c>
       <c r="Q50" s="9" t="inlineStr">
         <is>
@@ -4690,13 +4690,13 @@
         </is>
       </c>
       <c r="D51" s="13" t="n">
-        <v>84.27</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>0.0097</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>0.0641</v>
+        <v>0.064</v>
       </c>
       <c r="G51" s="15" t="n"/>
       <c r="H51" s="21" t="inlineStr">
@@ -4715,7 +4715,7 @@
         <v>100</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>0.1866619200189867</v>
+        <v>0.1868027533823878</v>
       </c>
       <c r="N51" s="12" t="inlineStr"/>
       <c r="O51" s="17" t="n"/>
@@ -4759,13 +4759,13 @@
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>154.39</v>
+        <v>152.36</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.1456</v>
+        <v>0.1305</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.1417</v>
+        <v>0.1267</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>46253</v>
@@ -4794,7 +4794,7 @@
         <v>140</v>
       </c>
       <c r="M52" s="22" t="n">
-        <v>-0.09320551849213024</v>
+        <v>-0.08112365450249417</v>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>135</v>
       </c>
       <c r="P52" s="22" t="n">
-        <v>-0.1255910356888399</v>
+        <v>-0.1139406668416908</v>
       </c>
       <c r="Q52" s="9" t="inlineStr">
         <is>
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="D53" s="13" t="n">
-        <v>112.89</v>
+        <v>113.26</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>-0.0165</v>
+        <v>-0.0132</v>
       </c>
       <c r="F53" s="14" t="n">
-        <v>-0.0673</v>
+        <v>-0.0643</v>
       </c>
       <c r="G53" s="15" t="n">
         <v>46254</v>
@@ -4885,7 +4885,7 @@
         <v>140</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>0.2401452741606874</v>
+        <v>0.2360939431396785</v>
       </c>
       <c r="N53" s="12" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         <v>140</v>
       </c>
       <c r="P53" s="18" t="n">
-        <v>0.2401452741606874</v>
+        <v>0.2360939431396785</v>
       </c>
       <c r="Q53" s="19" t="inlineStr">
         <is>
@@ -4945,13 +4945,13 @@
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>64.45999999999999</v>
+        <v>64.81</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0.1179</v>
+        <v>0.124</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.0209</v>
+        <v>0.0264</v>
       </c>
       <c r="G54" s="6" t="n">
         <v>46316</v>
@@ -4987,7 +4987,7 @@
         <v>76</v>
       </c>
       <c r="P54" s="5" t="n">
-        <v>0.1790257524045921</v>
+        <v>0.1726585403487116</v>
       </c>
       <c r="Q54" s="9" t="inlineStr">
         <is>
@@ -5028,13 +5028,13 @@
         </is>
       </c>
       <c r="D55" s="13" t="n">
-        <v>124.07</v>
+        <v>125.92</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>0.09939999999999999</v>
+        <v>0.1158</v>
       </c>
       <c r="F55" s="18" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.0764</v>
       </c>
       <c r="G55" s="15" t="n"/>
       <c r="H55" s="21" t="inlineStr">
@@ -5053,7 +5053,7 @@
         <v>183</v>
       </c>
       <c r="M55" s="18" t="n">
-        <v>0.4749738051100186</v>
+        <v>0.4533036848792884</v>
       </c>
       <c r="N55" s="12" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>145</v>
       </c>
       <c r="P55" s="18" t="n">
-        <v>0.1686950914806158</v>
+        <v>0.1515247776365946</v>
       </c>
       <c r="Q55" s="19" t="inlineStr">
         <is>
@@ -5105,13 +5105,13 @@
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>195.64</v>
+        <v>196.65</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.0738</v>
+        <v>0.0793</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.045</v>
+        <v>0.0504</v>
       </c>
       <c r="G56" s="6" t="n"/>
       <c r="H56" s="7" t="inlineStr">
@@ -5130,7 +5130,7 @@
         <v>222</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>0.1347372725414027</v>
+        <v>0.1289092295957284</v>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>225</v>
       </c>
       <c r="P56" s="5" t="n">
-        <v>0.1500715600081784</v>
+        <v>0.1441647597254004</v>
       </c>
       <c r="Q56" s="9" t="inlineStr">
         <is>
@@ -5186,13 +5186,13 @@
         </is>
       </c>
       <c r="D57" s="13" t="n">
-        <v>141.64</v>
+        <v>143.39</v>
       </c>
       <c r="E57" s="18" t="n">
-        <v>0.0145</v>
+        <v>0.0271</v>
       </c>
       <c r="F57" s="18" t="n">
-        <v>0.0365</v>
+        <v>0.0493</v>
       </c>
       <c r="G57" s="15" t="n"/>
       <c r="H57" s="21" t="inlineStr">
@@ -5211,7 +5211,7 @@
         <v>196</v>
       </c>
       <c r="M57" s="18" t="n">
-        <v>0.3837898898616212</v>
+        <v>0.3669014575632891</v>
       </c>
       <c r="N57" s="12" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>170</v>
       </c>
       <c r="P57" s="18" t="n">
-        <v>0.2002259248799775</v>
+        <v>0.1855777948253017</v>
       </c>
       <c r="Q57" s="19" t="inlineStr">
         <is>
@@ -5267,13 +5267,13 @@
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>37.78</v>
+        <v>37.88</v>
       </c>
       <c r="E58" s="22" t="n">
-        <v>-0.0137</v>
+        <v>-0.0112</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.0144</v>
+        <v>0.0169</v>
       </c>
       <c r="G58" s="6" t="n"/>
       <c r="H58" s="7" t="inlineStr">
@@ -5318,13 +5318,13 @@
         </is>
       </c>
       <c r="D59" s="13" t="n">
-        <v>20.72</v>
+        <v>20.79</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>0.0265</v>
+        <v>0.0302</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>0.0863</v>
+        <v>0.0902</v>
       </c>
       <c r="G59" s="15" t="n"/>
       <c r="H59" s="21" t="inlineStr">
@@ -5369,13 +5369,13 @@
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>201.15</v>
+        <v>201.71</v>
       </c>
       <c r="E60" s="5" t="n">
+        <v>0.0528</v>
+      </c>
+      <c r="F60" s="5" t="n">
         <v>0.0499</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>0.047</v>
       </c>
       <c r="G60" s="6" t="n"/>
       <c r="H60" s="7" t="inlineStr">
@@ -5420,13 +5420,13 @@
         </is>
       </c>
       <c r="D61" s="13" t="n">
-        <v>33.77</v>
+        <v>33.81</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>-0.0409</v>
+        <v>-0.0398</v>
       </c>
       <c r="F61" s="14" t="n">
-        <v>-0.1472</v>
+        <v>-0.1462</v>
       </c>
       <c r="G61" s="15" t="n">
         <v>46315</v>
@@ -5462,7 +5462,7 @@
         <v>43</v>
       </c>
       <c r="P61" s="18" t="n">
-        <v>0.2733195143618595</v>
+        <v>0.271813073055309</v>
       </c>
       <c r="Q61" s="19" t="inlineStr">
         <is>
@@ -5507,13 +5507,13 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>31.42</v>
+        <v>31.49</v>
       </c>
       <c r="E62" s="22" t="n">
-        <v>-0.0253</v>
+        <v>-0.0233</v>
       </c>
       <c r="F62" s="22" t="n">
-        <v>-0.0161</v>
+        <v>-0.0141</v>
       </c>
       <c r="G62" s="6" t="n">
         <v>46316</v>
@@ -5542,7 +5542,7 @@
         <v>35</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.1139401654996817</v>
+        <v>0.1114639568116863</v>
       </c>
       <c r="N62" s="3" t="inlineStr"/>
       <c r="O62" s="8" t="n"/>
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="D63" s="13" t="n">
-        <v>220.12</v>
+        <v>224.36</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>0.1101</v>
+        <v>0.1315</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>0.2266</v>
+        <v>0.2503</v>
       </c>
       <c r="G63" s="15" t="n"/>
       <c r="H63" s="21" t="inlineStr">
@@ -5637,13 +5637,13 @@
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>53.75</v>
+        <v>53.69</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0.1349</v>
+        <v>0.1338</v>
       </c>
       <c r="F64" s="22" t="n">
-        <v>-0.0433</v>
+        <v>-0.0442</v>
       </c>
       <c r="G64" s="6" t="n">
         <v>46311</v>
@@ -5679,7 +5679,7 @@
         <v>63</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0.172093023255814</v>
+        <v>0.1734028683181226</v>
       </c>
       <c r="Q64" s="9" t="inlineStr">
         <is>
@@ -5728,13 +5728,13 @@
         </is>
       </c>
       <c r="D65" s="13" t="n">
-        <v>42.28</v>
+        <v>42.88</v>
       </c>
       <c r="E65" s="14" t="n">
-        <v>-0.0214</v>
+        <v>-0.0076</v>
       </c>
       <c r="F65" s="14" t="n">
-        <v>-0.0472</v>
+        <v>-0.0338</v>
       </c>
       <c r="G65" s="15" t="n"/>
       <c r="H65" s="21" t="inlineStr">
@@ -5779,13 +5779,13 @@
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>72</v>
+        <v>72.31</v>
       </c>
       <c r="E66" s="22" t="n">
-        <v>-0.033</v>
-      </c>
-      <c r="F66" s="22" t="n">
-        <v>-0.0011</v>
+        <v>-0.0289</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.0032</v>
       </c>
       <c r="G66" s="6" t="n"/>
       <c r="H66" s="7" t="inlineStr">
@@ -5804,7 +5804,7 @@
         <v>89</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0.2361111111111111</v>
+        <v>0.2308117826026828</v>
       </c>
       <c r="N66" s="3" t="inlineStr"/>
       <c r="O66" s="8" t="n"/>
@@ -5860,13 +5860,13 @@
         </is>
       </c>
       <c r="D67" s="13" t="n">
-        <v>160.69</v>
+        <v>159.8</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>0.112</v>
+        <v>0.1058</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>0.0931</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G67" s="15" t="n"/>
       <c r="H67" s="21" t="inlineStr">
@@ -5885,7 +5885,7 @@
         <v>185</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>0.1512850830792209</v>
+        <v>0.1576971214017521</v>
       </c>
       <c r="N67" s="12" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>185</v>
       </c>
       <c r="P67" s="18" t="n">
-        <v>0.1512850830792209</v>
+        <v>0.1576971214017521</v>
       </c>
       <c r="Q67" s="19" t="inlineStr">
         <is>
@@ -5941,13 +5941,13 @@
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>121.23</v>
+        <v>121.08</v>
       </c>
       <c r="E68" s="22" t="n">
-        <v>-0.0168</v>
+        <v>-0.018</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.0291</v>
+        <v>0.0278</v>
       </c>
       <c r="G68" s="6" t="n"/>
       <c r="H68" s="7" t="inlineStr">
@@ -5966,7 +5966,7 @@
         <v>120</v>
       </c>
       <c r="M68" s="22" t="n">
-        <v>-0.01014600346448902</v>
+        <v>-0.008919722497522285</v>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>115</v>
       </c>
       <c r="P68" s="22" t="n">
-        <v>-0.05138991998680198</v>
+        <v>-0.05021473406012553</v>
       </c>
       <c r="Q68" s="9" t="inlineStr"/>
       <c r="R68" s="8" t="n"/>
@@ -6012,13 +6012,13 @@
         </is>
       </c>
       <c r="D69" s="13" t="n">
-        <v>356.14</v>
+        <v>356.36</v>
       </c>
       <c r="E69" s="14" t="n">
-        <v>-0.0305</v>
+        <v>-0.0299</v>
       </c>
       <c r="F69" s="18" t="n">
-        <v>0.0621</v>
+        <v>0.06280000000000001</v>
       </c>
       <c r="G69" s="15" t="n"/>
       <c r="H69" s="21" t="inlineStr">
@@ -6037,7 +6037,7 @@
         <v>406</v>
       </c>
       <c r="M69" s="18" t="n">
-        <v>0.140001123153816</v>
+        <v>0.1392973397687731</v>
       </c>
       <c r="N69" s="12" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>436</v>
       </c>
       <c r="P69" s="18" t="n">
-        <v>0.2242376593474477</v>
+        <v>0.2234818722640027</v>
       </c>
       <c r="Q69" s="19" t="inlineStr">
         <is>
@@ -6085,13 +6085,13 @@
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>341.12</v>
+        <v>340.87</v>
       </c>
       <c r="E70" s="22" t="n">
-        <v>-0.03759999999999999</v>
+        <v>-0.0383</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.0482</v>
+        <v>0.0474</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>46311</v>
@@ -6120,7 +6120,7 @@
         <v>415</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.2165806754221388</v>
+        <v>0.2174729368967641</v>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>380</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.1139774859287054</v>
+        <v>0.1147944964355913</v>
       </c>
       <c r="Q70" s="9" t="inlineStr">
         <is>
@@ -6180,13 +6180,13 @@
         </is>
       </c>
       <c r="D71" s="13" t="n">
-        <v>63.78</v>
+        <v>63.99</v>
       </c>
       <c r="E71" s="18" t="n">
-        <v>0.0718</v>
+        <v>0.0755</v>
       </c>
       <c r="F71" s="18" t="n">
-        <v>0.1384</v>
+        <v>0.1424</v>
       </c>
       <c r="G71" s="15" t="n">
         <v>46309</v>
@@ -6241,13 +6241,13 @@
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>1146.96</v>
+        <v>1148.58</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0.1119</v>
+        <v>0.1134</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.1114</v>
+        <v>0.113</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>46308</v>
@@ -6279,7 +6279,7 @@
         <v>1245</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.08547813350073234</v>
+        <v>0.08394713472287527</v>
       </c>
       <c r="Q72" s="9" t="inlineStr">
         <is>
@@ -6324,13 +6324,13 @@
         </is>
       </c>
       <c r="D73" s="13" t="n">
-        <v>24.42</v>
+        <v>24.53</v>
       </c>
       <c r="E73" s="18" t="n">
-        <v>0.0678</v>
+        <v>0.0726</v>
       </c>
       <c r="F73" s="14" t="n">
-        <v>-0.1025</v>
+        <v>-0.09849999999999999</v>
       </c>
       <c r="G73" s="15" t="n">
         <v>46247</v>
@@ -6385,13 +6385,13 @@
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>18.1</v>
+        <v>18.11</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0.2387</v>
+        <v>0.2399</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.1234</v>
+        <v>0.1245</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>46346</v>
@@ -6446,13 +6446,13 @@
         </is>
       </c>
       <c r="D75" s="13" t="n">
-        <v>524.12</v>
+        <v>516.15</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>0.0549</v>
+        <v>0.0388</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>0.0713</v>
+        <v>0.055</v>
       </c>
       <c r="G75" s="15" t="n"/>
       <c r="H75" s="21" t="inlineStr">
@@ -6519,13 +6519,13 @@
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>71.03</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0.0263</v>
+        <v>0.0321</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.184</v>
+        <v>0.1907</v>
       </c>
       <c r="G76" s="6" t="n"/>
       <c r="H76" s="7" t="inlineStr">
@@ -6544,7 +6544,7 @@
         <v>68</v>
       </c>
       <c r="M76" s="22" t="n">
-        <v>-0.0426580318175419</v>
+        <v>-0.04801903961920771</v>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
       <c r="O76" s="8" t="n"/>
@@ -6586,13 +6586,13 @@
         </is>
       </c>
       <c r="D77" s="13" t="n">
-        <v>145.21</v>
+        <v>147.18</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>0.1898</v>
+        <v>0.206</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>0.1825</v>
+        <v>0.1986</v>
       </c>
       <c r="G77" s="15" t="n">
         <v>46310</v>
@@ -6651,13 +6651,13 @@
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>135.57</v>
+        <v>135.76</v>
       </c>
       <c r="E78" s="22" t="n">
-        <v>-0.0365</v>
+        <v>-0.0352</v>
       </c>
       <c r="F78" s="22" t="n">
-        <v>-0.0304</v>
+        <v>-0.0291</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>46308</v>
@@ -6689,7 +6689,7 @@
         <v>140</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.03267684590986212</v>
+        <v>0.03123158515026524</v>
       </c>
       <c r="Q78" s="9" t="inlineStr">
         <is>
@@ -6738,13 +6738,13 @@
         </is>
       </c>
       <c r="D79" s="13" t="n">
-        <v>348</v>
+        <v>347.08</v>
       </c>
       <c r="E79" s="14" t="n">
-        <v>-0.019</v>
+        <v>-0.0216</v>
       </c>
       <c r="F79" s="18" t="n">
-        <v>0.0605</v>
+        <v>0.05769999999999999</v>
       </c>
       <c r="G79" s="15" t="n">
         <v>46315</v>
@@ -6773,7 +6773,7 @@
         <v>358</v>
       </c>
       <c r="M79" s="18" t="n">
-        <v>0.02873563218390805</v>
+        <v>0.03146248703468946</v>
       </c>
       <c r="N79" s="12" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>374</v>
       </c>
       <c r="P79" s="18" t="n">
-        <v>0.07471264367816093</v>
+        <v>0.07756136913679848</v>
       </c>
       <c r="Q79" s="19" t="inlineStr">
         <is>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>58.96</v>
+        <v>59.02</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0.008</v>
+        <v>0.0091</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0.0563</v>
+        <v>0.0573</v>
       </c>
       <c r="G80" s="6" t="n">
         <v>46310</v>
@@ -6864,7 +6864,7 @@
         <v>57</v>
       </c>
       <c r="M80" s="22" t="n">
-        <v>-0.03324287652645863</v>
+        <v>-0.03422568620806511</v>
       </c>
       <c r="N80" s="3" t="inlineStr"/>
       <c r="O80" s="8" t="n"/>
@@ -6906,13 +6906,13 @@
         </is>
       </c>
       <c r="D81" s="13" t="n">
-        <v>11.65</v>
+        <v>11.52</v>
       </c>
       <c r="E81" s="14" t="n">
-        <v>-0.0574</v>
+        <v>-0.068</v>
       </c>
       <c r="F81" s="14" t="n">
-        <v>-0.2931</v>
+        <v>-0.301</v>
       </c>
       <c r="G81" s="15" t="n"/>
       <c r="H81" s="21" t="inlineStr">
@@ -6957,13 +6957,13 @@
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>407.67</v>
+        <v>406.2</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0.126</v>
+        <v>0.1219</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.1448</v>
+        <v>0.1407</v>
       </c>
       <c r="G82" s="6" t="n"/>
       <c r="H82" s="7" t="inlineStr">
@@ -7020,13 +7020,13 @@
         </is>
       </c>
       <c r="D83" s="13" t="n">
-        <v>71.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="E83" s="18" t="n">
-        <v>0.1286</v>
+        <v>0.1302</v>
       </c>
       <c r="F83" s="14" t="n">
-        <v>-0.0866</v>
+        <v>-0.08529999999999999</v>
       </c>
       <c r="G83" s="15" t="n"/>
       <c r="H83" s="21" t="inlineStr">
@@ -7071,13 +7071,13 @@
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>42.86</v>
+        <v>41.08</v>
       </c>
       <c r="E84" s="22" t="n">
-        <v>-0.1294</v>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>0.0408</v>
+        <v>-0.1655</v>
+      </c>
+      <c r="F84" s="22" t="n">
+        <v>-0.0024</v>
       </c>
       <c r="G84" s="6" t="n"/>
       <c r="H84" s="7" t="inlineStr">
@@ -7122,13 +7122,13 @@
         </is>
       </c>
       <c r="D85" s="13" t="n">
-        <v>1030.35</v>
+        <v>1034.13</v>
       </c>
       <c r="E85" s="14" t="n">
-        <v>-0.0149</v>
+        <v>-0.0113</v>
       </c>
       <c r="F85" s="14" t="n">
-        <v>-0.0305</v>
+        <v>-0.0269</v>
       </c>
       <c r="G85" s="15" t="n">
         <v>46308</v>
@@ -7157,7 +7157,7 @@
         <v>1325</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>0.2859707866259039</v>
+        <v>0.2812702464873854</v>
       </c>
       <c r="N85" s="12" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>1210</v>
       </c>
       <c r="P85" s="18" t="n">
-        <v>0.1743582277866745</v>
+        <v>0.1700656590564048</v>
       </c>
       <c r="Q85" s="19" t="inlineStr">
         <is>
@@ -7209,13 +7209,13 @@
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>124.98</v>
+        <v>125.52</v>
       </c>
       <c r="E86" s="22" t="n">
-        <v>-0.05690000000000001</v>
+        <v>-0.0528</v>
       </c>
       <c r="F86" s="22" t="n">
-        <v>-0.09359999999999999</v>
+        <v>-0.0897</v>
       </c>
       <c r="G86" s="6" t="n"/>
       <c r="H86" s="7" t="inlineStr">
@@ -7260,13 +7260,13 @@
         </is>
       </c>
       <c r="D87" s="13" t="n">
-        <v>93.75</v>
+        <v>94.38</v>
       </c>
       <c r="E87" s="14" t="n">
-        <v>-0.1466</v>
+        <v>-0.1409</v>
       </c>
       <c r="F87" s="18" t="n">
-        <v>0.006</v>
+        <v>0.0128</v>
       </c>
       <c r="G87" s="15" t="n"/>
       <c r="H87" s="21" t="inlineStr">
@@ -7311,13 +7311,13 @@
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>92.03</v>
+        <v>88.78</v>
       </c>
       <c r="E88" s="22" t="n">
-        <v>-0.07200000000000001</v>
+        <v>-0.1048</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>-0.2257</v>
+        <v>-0.2531</v>
       </c>
       <c r="G88" s="6" t="n"/>
       <c r="H88" s="7" t="inlineStr">
@@ -7362,13 +7362,13 @@
         </is>
       </c>
       <c r="D89" s="13" t="n">
-        <v>150.68</v>
+        <v>151.24</v>
       </c>
       <c r="E89" s="18" t="n">
-        <v>0.09449999999999999</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="F89" s="18" t="n">
-        <v>0.0722</v>
+        <v>0.0762</v>
       </c>
       <c r="G89" s="15" t="n"/>
       <c r="H89" s="21" t="inlineStr">
@@ -7413,13 +7413,13 @@
         </is>
       </c>
       <c r="D90" s="4" t="n">
-        <v>155.4</v>
+        <v>153.63</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0.031</v>
+        <v>0.0192</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.2119</v>
+        <v>0.1981</v>
       </c>
       <c r="G90" s="6" t="n">
         <v>46252</v>
@@ -7488,13 +7488,13 @@
         </is>
       </c>
       <c r="D91" s="13" t="n">
-        <v>358.98</v>
+        <v>362.02</v>
       </c>
       <c r="E91" s="18" t="n">
-        <v>0.0731</v>
+        <v>0.08220000000000001</v>
       </c>
       <c r="F91" s="18" t="n">
-        <v>0.1193</v>
+        <v>0.1288</v>
       </c>
       <c r="G91" s="15" t="n">
         <v>46308</v>
@@ -7523,7 +7523,7 @@
         <v>196</v>
       </c>
       <c r="M91" s="14" t="n">
-        <v>-0.4540085798651736</v>
+        <v>-0.4585934478758079</v>
       </c>
       <c r="N91" s="12" t="inlineStr"/>
       <c r="O91" s="17" t="n"/>
@@ -7567,13 +7567,13 @@
         </is>
       </c>
       <c r="D92" s="4" t="n">
-        <v>107.99</v>
+        <v>111.01</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0.1143</v>
+        <v>0.1455</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.1221</v>
+        <v>0.1535</v>
       </c>
       <c r="G92" s="6" t="n"/>
       <c r="H92" s="7" t="inlineStr">
@@ -7592,7 +7592,7 @@
         <v>375</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>2.472543754051301</v>
+        <v>2.378074047383119</v>
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>368</v>
       </c>
       <c r="P92" s="5" t="n">
-        <v>2.40772293730901</v>
+        <v>2.315016665165301</v>
       </c>
       <c r="Q92" s="9" t="inlineStr">
         <is>
@@ -7656,13 +7656,13 @@
         </is>
       </c>
       <c r="D93" s="13" t="n">
-        <v>372.07</v>
+        <v>374.89</v>
       </c>
       <c r="E93" s="18" t="n">
-        <v>0.0786</v>
+        <v>0.0868</v>
       </c>
       <c r="F93" s="18" t="n">
-        <v>0.1949</v>
+        <v>0.204</v>
       </c>
       <c r="G93" s="15" t="n">
         <v>46317</v>
@@ -7694,7 +7694,7 @@
         <v>115</v>
       </c>
       <c r="P93" s="14" t="n">
-        <v>-0.6909183755744887</v>
+        <v>-0.6932433513830724</v>
       </c>
       <c r="Q93" s="19" t="inlineStr">
         <is>
@@ -7743,13 +7743,13 @@
         </is>
       </c>
       <c r="D94" s="4" t="n">
-        <v>567.09</v>
+        <v>561.4400000000001</v>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0.0547</v>
+        <v>0.0442</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.1574</v>
+        <v>0.1458</v>
       </c>
       <c r="G94" s="6" t="n"/>
       <c r="H94" s="7" t="inlineStr">
@@ -7768,7 +7768,7 @@
         <v>366</v>
       </c>
       <c r="M94" s="22" t="n">
-        <v>-0.3545997989737079</v>
+        <v>-0.3481048731832432</v>
       </c>
       <c r="N94" s="3" t="inlineStr"/>
       <c r="O94" s="8" t="n"/>
@@ -7810,13 +7810,13 @@
         </is>
       </c>
       <c r="D95" s="13" t="n">
-        <v>1846.31</v>
+        <v>1841.86</v>
       </c>
       <c r="E95" s="14" t="n">
-        <v>-0.0591</v>
-      </c>
-      <c r="F95" s="18" t="n">
-        <v>0.0002</v>
+        <v>-0.0614</v>
+      </c>
+      <c r="F95" s="14" t="n">
+        <v>-0.0022</v>
       </c>
       <c r="G95" s="15" t="n"/>
       <c r="H95" s="21" t="inlineStr">
@@ -7871,13 +7871,13 @@
         </is>
       </c>
       <c r="D96" s="4" t="n">
-        <v>213.88</v>
+        <v>215.1</v>
       </c>
       <c r="E96" s="22" t="n">
-        <v>-0.0326</v>
-      </c>
-      <c r="F96" s="22" t="n">
-        <v>-0.0008</v>
+        <v>-0.0271</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>0.005</v>
       </c>
       <c r="G96" s="6" t="n">
         <v>46309</v>
@@ -7906,7 +7906,7 @@
         <v>668</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>2.123246680381522</v>
+        <v>2.105532310553231</v>
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
@@ -7917,7 +7917,7 @@
         <v>550</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>1.571535440433888</v>
+        <v>1.556950255695025</v>
       </c>
       <c r="Q96" s="9" t="inlineStr">
         <is>
@@ -7966,13 +7966,13 @@
         </is>
       </c>
       <c r="D97" s="13" t="n">
-        <v>112.29</v>
+        <v>113.03</v>
       </c>
       <c r="E97" s="14" t="n">
-        <v>-0.0116</v>
+        <v>-0.0051</v>
       </c>
       <c r="F97" s="18" t="n">
-        <v>0.0105</v>
+        <v>0.0172</v>
       </c>
       <c r="G97" s="15" t="n"/>
       <c r="H97" s="21" t="inlineStr">
@@ -7991,7 +7991,7 @@
         <v>240</v>
       </c>
       <c r="M97" s="18" t="n">
-        <v>1.137323002938819</v>
+        <v>1.123330089356808</v>
       </c>
       <c r="N97" s="12" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>240</v>
       </c>
       <c r="P97" s="18" t="n">
-        <v>1.137323002938819</v>
+        <v>1.123330089356808</v>
       </c>
       <c r="Q97" s="19" t="inlineStr">
         <is>
@@ -8051,13 +8051,13 @@
         </is>
       </c>
       <c r="D98" s="4" t="n">
-        <v>251.88</v>
-      </c>
-      <c r="E98" s="22" t="n">
-        <v>-0.0038</v>
+        <v>254.24</v>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.05980000000000001</v>
+        <v>0.0698</v>
       </c>
       <c r="G98" s="6" t="n">
         <v>46310</v>
@@ -8086,7 +8086,7 @@
         <v>113</v>
       </c>
       <c r="M98" s="22" t="n">
-        <v>-0.5513736700015881</v>
+        <v>-0.5555380742605412</v>
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>114</v>
       </c>
       <c r="P98" s="22" t="n">
-        <v>-0.5474035254883277</v>
+        <v>-0.551604782882316</v>
       </c>
       <c r="Q98" s="9" t="inlineStr"/>
       <c r="R98" s="8" t="n"/>
@@ -8136,13 +8136,13 @@
         </is>
       </c>
       <c r="D99" s="13" t="n">
-        <v>20.43</v>
+        <v>20.24</v>
       </c>
       <c r="E99" s="18" t="n">
-        <v>0.0119</v>
+        <v>0.0025</v>
       </c>
       <c r="F99" s="14" t="n">
-        <v>-0.2322</v>
+        <v>-0.2394</v>
       </c>
       <c r="G99" s="15" t="n"/>
       <c r="H99" s="21" t="inlineStr">
@@ -8187,13 +8187,13 @@
         </is>
       </c>
       <c r="D100" s="4" t="n">
-        <v>14.74</v>
+        <v>14.71</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0.0791</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.1453</v>
+        <v>0.143</v>
       </c>
       <c r="G100" s="6" t="n">
         <v>46323</v>
@@ -8248,13 +8248,13 @@
         </is>
       </c>
       <c r="D101" s="13" t="n">
-        <v>104.57</v>
+        <v>104.63</v>
       </c>
       <c r="E101" s="18" t="n">
-        <v>0.0872</v>
+        <v>0.08789999999999999</v>
       </c>
       <c r="F101" s="18" t="n">
-        <v>0.1697</v>
+        <v>0.1704</v>
       </c>
       <c r="G101" s="15" t="n">
         <v>46323</v>
@@ -8283,7 +8283,7 @@
         <v>285</v>
       </c>
       <c r="M101" s="18" t="n">
-        <v>1.72544706894903</v>
+        <v>1.7238841632419</v>
       </c>
       <c r="N101" s="12" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>285</v>
       </c>
       <c r="P101" s="18" t="n">
-        <v>1.72544706894903</v>
+        <v>1.7238841632419</v>
       </c>
       <c r="Q101" s="19" t="inlineStr">
         <is>
@@ -8335,13 +8335,13 @@
         </is>
       </c>
       <c r="D102" s="4" t="n">
-        <v>410.71</v>
+        <v>408.68</v>
       </c>
       <c r="E102" s="22" t="n">
-        <v>-0.062</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0.0363</v>
+        <v>0.0312</v>
       </c>
       <c r="G102" s="6" t="n"/>
       <c r="H102" s="7" t="inlineStr">
@@ -8400,13 +8400,13 @@
         </is>
       </c>
       <c r="D103" s="13" t="n">
-        <v>51.92</v>
-      </c>
-      <c r="E103" s="14" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>52.32</v>
+      </c>
+      <c r="E103" s="18" t="n">
+        <v>0.0071</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>0.0049</v>
+        <v>0.0128</v>
       </c>
       <c r="G103" s="15" t="n">
         <v>46311</v>
@@ -8461,13 +8461,13 @@
         </is>
       </c>
       <c r="D104" s="4" t="n">
-        <v>364.38</v>
+        <v>362.59</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0.0185</v>
+        <v>0.0135</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.1302</v>
+        <v>0.1247</v>
       </c>
       <c r="G104" s="6" t="n"/>
       <c r="H104" s="7" t="inlineStr">
@@ -8486,7 +8486,7 @@
         <v>525</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>0.4408035567264943</v>
+        <v>0.4479163793816708</v>
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>543</v>
       </c>
       <c r="P104" s="5" t="n">
-        <v>0.4902025358142599</v>
+        <v>0.4975592266747567</v>
       </c>
       <c r="Q104" s="9" t="inlineStr">
         <is>
@@ -8542,13 +8542,13 @@
         </is>
       </c>
       <c r="D105" s="13" t="n">
-        <v>70.3</v>
+        <v>70.13</v>
       </c>
       <c r="E105" s="14" t="n">
-        <v>-0.0479</v>
+        <v>-0.05019999999999999</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>0.0297</v>
+        <v>0.0272</v>
       </c>
       <c r="G105" s="15" t="n">
         <v>46314</v>
@@ -8577,7 +8577,7 @@
         <v>412</v>
       </c>
       <c r="M105" s="18" t="n">
-        <v>4.860597439544808</v>
+        <v>4.874803935548268</v>
       </c>
       <c r="N105" s="12" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>350</v>
       </c>
       <c r="P105" s="18" t="n">
-        <v>3.978662873399716</v>
+        <v>3.990731498645373</v>
       </c>
       <c r="Q105" s="19" t="inlineStr">
         <is>
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="D106" s="4" t="n">
-        <v>79.59999999999999</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0044</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.1449</v>
+        <v>0.1374</v>
       </c>
       <c r="G106" s="6" t="n"/>
       <c r="H106" s="7" t="inlineStr">
@@ -8658,7 +8658,7 @@
         <v>68</v>
       </c>
       <c r="M106" s="22" t="n">
-        <v>-0.1457286432160803</v>
+        <v>-0.1400025294043252</v>
       </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>68</v>
       </c>
       <c r="P106" s="22" t="n">
-        <v>-0.1457286432160803</v>
+        <v>-0.1400025294043252</v>
       </c>
       <c r="Q106" s="9" t="inlineStr">
         <is>
@@ -8714,13 +8714,13 @@
         </is>
       </c>
       <c r="D107" s="13" t="n">
-        <v>248.64</v>
+        <v>249.94</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>0.0026</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>0.09179999999999999</v>
+        <v>0.0975</v>
       </c>
       <c r="G107" s="15" t="n"/>
       <c r="H107" s="21" t="inlineStr">
@@ -8739,7 +8739,7 @@
         <v>295</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>0.1864543114543115</v>
+        <v>0.1802832679843162</v>
       </c>
       <c r="N107" s="12" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>246</v>
       </c>
       <c r="P107" s="14" t="n">
-        <v>-0.01061776061776056</v>
+        <v>-0.01576378330799391</v>
       </c>
       <c r="Q107" s="19" t="inlineStr">
         <is>
@@ -8787,13 +8787,13 @@
         </is>
       </c>
       <c r="D108" s="4" t="n">
-        <v>109.94</v>
+        <v>109.74</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0.1936</v>
+        <v>0.1914</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.2468</v>
+        <v>0.2445</v>
       </c>
       <c r="G108" s="6" t="n">
         <v>46316</v>
@@ -8822,7 +8822,7 @@
         <v>112</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0.01873749317809717</v>
+        <v>0.02059413158374344</v>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>120</v>
       </c>
       <c r="P108" s="5" t="n">
-        <v>0.09150445697653267</v>
+        <v>0.09349371241115369</v>
       </c>
       <c r="Q108" s="9" t="inlineStr">
         <is>
@@ -8886,13 +8886,13 @@
         </is>
       </c>
       <c r="D109" s="13" t="n">
-        <v>413.88</v>
+        <v>414.3</v>
       </c>
       <c r="E109" s="18" t="n">
-        <v>0.1482</v>
+        <v>0.1494</v>
       </c>
       <c r="F109" s="18" t="n">
-        <v>0.1652</v>
+        <v>0.1664</v>
       </c>
       <c r="G109" s="15" t="n"/>
       <c r="H109" s="21" t="inlineStr">
@@ -8911,7 +8911,7 @@
         <v>390</v>
       </c>
       <c r="M109" s="14" t="n">
-        <v>-0.05769788344447665</v>
+        <v>-0.05865314989138308</v>
       </c>
       <c r="N109" s="12" t="inlineStr">
         <is>
@@ -8959,13 +8959,13 @@
         </is>
       </c>
       <c r="D110" s="4" t="n">
-        <v>180.75</v>
+        <v>181.34</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0.175</v>
+        <v>0.1788</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.236</v>
+        <v>0.24</v>
       </c>
       <c r="G110" s="6" t="n"/>
       <c r="H110" s="7" t="inlineStr">
@@ -8984,7 +8984,7 @@
         <v>161</v>
       </c>
       <c r="M110" s="22" t="n">
-        <v>-0.1092669432918396</v>
+        <v>-0.1121649939340466</v>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>180</v>
       </c>
       <c r="P110" s="22" t="n">
-        <v>-0.004149377593360996</v>
+        <v>-0.007389434211977519</v>
       </c>
       <c r="Q110" s="9" t="inlineStr">
         <is>
@@ -9036,13 +9036,13 @@
         </is>
       </c>
       <c r="D111" s="13" t="n">
-        <v>51.06</v>
+        <v>51.19</v>
       </c>
       <c r="E111" s="18" t="n">
-        <v>0.1436</v>
+        <v>0.1466</v>
       </c>
       <c r="F111" s="18" t="n">
-        <v>0.0885</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="G111" s="15" t="n"/>
       <c r="H111" s="21" t="inlineStr">
@@ -9061,7 +9061,7 @@
         <v>55</v>
       </c>
       <c r="M111" s="18" t="n">
-        <v>0.07716412064238147</v>
+        <v>0.07442859933580782</v>
       </c>
       <c r="N111" s="12" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>65</v>
       </c>
       <c r="P111" s="18" t="n">
-        <v>0.2730121425773599</v>
+        <v>0.2697792537605002</v>
       </c>
       <c r="Q111" s="19" t="inlineStr">
         <is>
@@ -9113,13 +9113,13 @@
         </is>
       </c>
       <c r="D112" s="4" t="n">
-        <v>330.41</v>
+        <v>333.9</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0.0793</v>
+        <v>0.0907</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.173</v>
+        <v>0.1854</v>
       </c>
       <c r="G112" s="6" t="n"/>
       <c r="H112" s="7" t="inlineStr">
@@ -9137,8 +9137,8 @@
       <c r="L112" s="8" t="n">
         <v>331</v>
       </c>
-      <c r="M112" s="5" t="n">
-        <v>0.001785660240307421</v>
+      <c r="M112" s="22" t="n">
+        <v>-0.008685235100329373</v>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>330</v>
       </c>
       <c r="P112" s="22" t="n">
-        <v>-0.001240882539874777</v>
+        <v>-0.01168014375561539</v>
       </c>
       <c r="Q112" s="9" t="inlineStr">
         <is>
@@ -9198,13 +9198,13 @@
         </is>
       </c>
       <c r="D113" s="13" t="n">
-        <v>93.84999999999999</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="E113" s="14" t="n">
-        <v>-0.1138</v>
+        <v>-0.117</v>
       </c>
       <c r="F113" s="14" t="n">
-        <v>-0.0796</v>
+        <v>-0.08289999999999999</v>
       </c>
       <c r="G113" s="15" t="n"/>
       <c r="H113" s="21" t="inlineStr">
@@ -9223,7 +9223,7 @@
         <v>123</v>
       </c>
       <c r="M113" s="18" t="n">
-        <v>0.3106020245071924</v>
+        <v>0.3153673403914019</v>
       </c>
       <c r="N113" s="12" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>130</v>
       </c>
       <c r="P113" s="18" t="n">
-        <v>0.3851891315929676</v>
+        <v>0.3902256443161158</v>
       </c>
       <c r="Q113" s="19" t="inlineStr">
         <is>
@@ -9275,13 +9275,13 @@
         </is>
       </c>
       <c r="D114" s="4" t="n">
-        <v>207.77</v>
+        <v>207.41</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0.038</v>
+        <v>0.0362</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.1536</v>
+        <v>0.1517</v>
       </c>
       <c r="G114" s="6" t="n">
         <v>46315</v>
@@ -9310,7 +9310,7 @@
         <v>212</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>0.02035905087356206</v>
+        <v>0.0221300805168507</v>
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>205</v>
       </c>
       <c r="P114" s="22" t="n">
-        <v>-0.01333204986282914</v>
+        <v>-0.01161949761342267</v>
       </c>
       <c r="Q114" s="9" t="inlineStr">
         <is>
@@ -9366,13 +9366,13 @@
         </is>
       </c>
       <c r="D115" s="13" t="n">
-        <v>89.34999999999999</v>
+        <v>89.53</v>
       </c>
       <c r="E115" s="18" t="n">
-        <v>0.1703</v>
+        <v>0.1726</v>
       </c>
       <c r="F115" s="18" t="n">
-        <v>0.1855</v>
+        <v>0.1879</v>
       </c>
       <c r="G115" s="15" t="n"/>
       <c r="H115" s="21" t="inlineStr">
@@ -9391,7 +9391,7 @@
         <v>85</v>
       </c>
       <c r="M115" s="14" t="n">
-        <v>-0.04868494683827638</v>
+        <v>-0.0505975650619904</v>
       </c>
       <c r="N115" s="12" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>90</v>
       </c>
       <c r="P115" s="18" t="n">
-        <v>0.007274762171236774</v>
+        <v>0.005249636993186629</v>
       </c>
       <c r="Q115" s="19" t="inlineStr">
         <is>
@@ -9443,13 +9443,13 @@
         </is>
       </c>
       <c r="D116" s="4" t="n">
-        <v>134.6</v>
+        <v>135.77</v>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0.0244</v>
+        <v>0.0333</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0.0718</v>
+        <v>0.08109999999999999</v>
       </c>
       <c r="G116" s="6" t="n"/>
       <c r="H116" s="7" t="inlineStr">
@@ -9468,7 +9468,7 @@
         <v>165</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>0.2258543833580981</v>
+        <v>0.2152905649259777</v>
       </c>
       <c r="N116" s="3" t="inlineStr"/>
       <c r="O116" s="8" t="n"/>
@@ -9516,13 +9516,13 @@
         </is>
       </c>
       <c r="D117" s="13" t="n">
-        <v>593.48</v>
+        <v>586.64</v>
       </c>
       <c r="E117" s="18" t="n">
-        <v>0.0519</v>
+        <v>0.0398</v>
       </c>
       <c r="F117" s="18" t="n">
-        <v>0.0581</v>
+        <v>0.0459</v>
       </c>
       <c r="G117" s="15" t="n"/>
       <c r="H117" s="21" t="inlineStr">
@@ -9577,13 +9577,13 @@
         </is>
       </c>
       <c r="D118" s="4" t="n">
-        <v>399.5</v>
+        <v>401.23</v>
       </c>
       <c r="E118" s="22" t="n">
-        <v>-0.0187</v>
+        <v>-0.0145</v>
       </c>
       <c r="F118" s="22" t="n">
-        <v>-0.0281</v>
+        <v>-0.0239</v>
       </c>
       <c r="G118" s="6" t="n">
         <v>46315</v>
@@ -9612,7 +9612,7 @@
         <v>487</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>0.2190237797246558</v>
+        <v>0.213767664431872</v>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>375</v>
       </c>
       <c r="P118" s="22" t="n">
-        <v>-0.06132665832290363</v>
+        <v>-0.06537397502679265</v>
       </c>
       <c r="Q118" s="9" t="inlineStr">
         <is>
@@ -9668,13 +9668,13 @@
         </is>
       </c>
       <c r="D119" s="13" t="n">
-        <v>259.67</v>
+        <v>259.74</v>
       </c>
       <c r="E119" s="18" t="n">
-        <v>0.0074</v>
+        <v>0.0076</v>
       </c>
       <c r="F119" s="18" t="n">
-        <v>0.078</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="G119" s="15" t="n">
         <v>46315</v>
@@ -9703,7 +9703,7 @@
         <v>272</v>
       </c>
       <c r="M119" s="18" t="n">
-        <v>0.04748334424461811</v>
+        <v>0.04720104720104716</v>
       </c>
       <c r="N119" s="12" t="inlineStr"/>
       <c r="O119" s="17" t="n"/>
@@ -9755,13 +9755,13 @@
         </is>
       </c>
       <c r="D120" s="4" t="n">
-        <v>1214.35</v>
+        <v>1214.65</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0277</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>0.0718</v>
+        <v>0.0721</v>
       </c>
       <c r="G120" s="6" t="n"/>
       <c r="H120" s="7" t="inlineStr">
@@ -9780,7 +9780,7 @@
         <v>1280</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>0.05406184378474089</v>
+        <v>0.0538015066068414</v>
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
@@ -9840,13 +9840,13 @@
         </is>
       </c>
       <c r="D121" s="13" t="n">
-        <v>90.23</v>
+        <v>90.63</v>
       </c>
       <c r="E121" s="18" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.08449999999999999</v>
       </c>
       <c r="F121" s="18" t="n">
-        <v>0.1251</v>
+        <v>0.13</v>
       </c>
       <c r="G121" s="15" t="n">
         <v>46266</v>
@@ -9875,7 +9875,7 @@
         <v>102</v>
       </c>
       <c r="M121" s="18" t="n">
-        <v>0.1304444198160257</v>
+        <v>0.1254551473022179</v>
       </c>
       <c r="N121" s="12" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>105</v>
       </c>
       <c r="P121" s="18" t="n">
-        <v>0.1636927851047323</v>
+        <v>0.1585567692816948</v>
       </c>
       <c r="Q121" s="19" t="inlineStr">
         <is>
@@ -9927,13 +9927,13 @@
         </is>
       </c>
       <c r="D122" s="4" t="n">
-        <v>130.1</v>
+        <v>130.45</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0.049</v>
+        <v>0.0518</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0.0929</v>
+        <v>0.0958</v>
       </c>
       <c r="G122" s="6" t="n"/>
       <c r="H122" s="7" t="inlineStr">
@@ -9952,7 +9952,7 @@
         <v>150</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>0.1529592621060723</v>
+        <v>0.1498658489842853</v>
       </c>
       <c r="N122" s="3" t="inlineStr"/>
       <c r="O122" s="8" t="n"/>
@@ -9996,13 +9996,13 @@
         </is>
       </c>
       <c r="D123" s="13" t="n">
-        <v>155.32</v>
+        <v>154.62</v>
       </c>
       <c r="E123" s="18" t="n">
-        <v>0.0127</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="F123" s="18" t="n">
-        <v>0.0147</v>
+        <v>0.0101</v>
       </c>
       <c r="G123" s="15" t="n">
         <v>46322</v>
@@ -10075,13 +10075,13 @@
         </is>
       </c>
       <c r="D124" s="4" t="n">
-        <v>26.88</v>
+        <v>26.6</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.098</v>
+        <v>0.0868</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>0.0256</v>
+        <v>0.0151</v>
       </c>
       <c r="G124" s="6" t="n"/>
       <c r="H124" s="7" t="inlineStr">
@@ -10100,7 +10100,7 @@
         <v>28</v>
       </c>
       <c r="M124" s="5" t="n">
-        <v>0.04166666666666671</v>
+        <v>0.05263157894736836</v>
       </c>
       <c r="N124" s="3" t="inlineStr"/>
       <c r="O124" s="8" t="n"/>
@@ -10144,13 +10144,13 @@
         </is>
       </c>
       <c r="D125" s="13" t="n">
-        <v>347.23</v>
+        <v>348.07</v>
       </c>
       <c r="E125" s="18" t="n">
-        <v>0.0476</v>
+        <v>0.0501</v>
       </c>
       <c r="F125" s="18" t="n">
-        <v>0.1122</v>
+        <v>0.1149</v>
       </c>
       <c r="G125" s="15" t="n"/>
       <c r="H125" s="21" t="inlineStr">
@@ -10169,7 +10169,7 @@
         <v>418</v>
       </c>
       <c r="M125" s="18" t="n">
-        <v>0.2038130345880252</v>
+        <v>0.2009078633608183</v>
       </c>
       <c r="N125" s="12" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>350</v>
       </c>
       <c r="P125" s="18" t="n">
-        <v>0.007977421305762698</v>
+        <v>0.005544861665756908</v>
       </c>
       <c r="Q125" s="19" t="inlineStr">
         <is>
@@ -10225,13 +10225,13 @@
         </is>
       </c>
       <c r="D126" s="4" t="n">
-        <v>600.72</v>
+        <v>604.9</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0.1366</v>
+        <v>0.1445</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>0.2799</v>
+        <v>0.2888</v>
       </c>
       <c r="G126" s="6" t="n">
         <v>46323</v>
@@ -10260,7 +10260,7 @@
         <v>615</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>0.02377147423092285</v>
+        <v>0.01669697470656311</v>
       </c>
       <c r="N126" s="3" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>570</v>
       </c>
       <c r="P126" s="22" t="n">
-        <v>-0.05113863363963248</v>
+        <v>-0.05769548685733176</v>
       </c>
       <c r="Q126" s="9" t="inlineStr">
         <is>
@@ -10320,13 +10320,13 @@
         </is>
       </c>
       <c r="D127" s="13" t="n">
-        <v>404.32</v>
+        <v>402.2</v>
       </c>
       <c r="E127" s="14" t="n">
-        <v>-0.05769999999999999</v>
+        <v>-0.06269999999999999</v>
       </c>
       <c r="F127" s="14" t="n">
-        <v>-0.0103</v>
+        <v>-0.0155</v>
       </c>
       <c r="G127" s="15" t="n">
         <v>46322</v>
@@ -10355,7 +10355,7 @@
         <v>526</v>
       </c>
       <c r="M127" s="18" t="n">
-        <v>0.3009497427779976</v>
+        <v>0.3078070611636002</v>
       </c>
       <c r="N127" s="12" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>480</v>
       </c>
       <c r="P127" s="18" t="n">
-        <v>0.1871784724970321</v>
+        <v>0.1934361014420687</v>
       </c>
       <c r="Q127" s="19" t="inlineStr">
         <is>
@@ -10411,13 +10411,13 @@
         </is>
       </c>
       <c r="D128" s="4" t="n">
-        <v>75.47</v>
-      </c>
-      <c r="E128" s="5" t="n">
-        <v>0.0011</v>
+        <v>75.34999999999999</v>
+      </c>
+      <c r="E128" s="22" t="n">
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="F128" s="22" t="n">
-        <v>-0.0515</v>
+        <v>-0.05309999999999999</v>
       </c>
       <c r="G128" s="6" t="n"/>
       <c r="H128" s="7" t="inlineStr">
@@ -10480,13 +10480,13 @@
         </is>
       </c>
       <c r="D129" s="13" t="n">
-        <v>272.29</v>
+        <v>271.09</v>
       </c>
       <c r="E129" s="18" t="n">
-        <v>0.08460000000000001</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="F129" s="18" t="n">
-        <v>0.2037</v>
+        <v>0.1984</v>
       </c>
       <c r="G129" s="15" t="n"/>
       <c r="H129" s="21" t="inlineStr">
@@ -10505,7 +10505,7 @@
         <v>248</v>
       </c>
       <c r="M129" s="14" t="n">
-        <v>-0.08920636086525402</v>
+        <v>-0.08517466524032601</v>
       </c>
       <c r="N129" s="12" t="inlineStr"/>
       <c r="O129" s="17" t="n"/>
@@ -10561,13 +10561,13 @@
         </is>
       </c>
       <c r="D130" s="4" t="n">
-        <v>102.32</v>
+        <v>101.46</v>
       </c>
       <c r="E130" s="22" t="n">
-        <v>-0.1031</v>
+        <v>-0.1107</v>
       </c>
       <c r="F130" s="22" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="G130" s="6" t="n"/>
       <c r="H130" s="7" t="inlineStr">
@@ -10612,13 +10612,13 @@
         </is>
       </c>
       <c r="D131" s="13" t="n">
-        <v>256.69</v>
+        <v>256.26</v>
       </c>
       <c r="E131" s="18" t="n">
-        <v>0.1059</v>
+        <v>0.1041</v>
       </c>
       <c r="F131" s="18" t="n">
-        <v>0.1302</v>
+        <v>0.1283</v>
       </c>
       <c r="G131" s="15" t="n"/>
       <c r="H131" s="21" t="inlineStr">
@@ -10663,13 +10663,13 @@
         </is>
       </c>
       <c r="D132" s="4" t="n">
-        <v>235.6</v>
+        <v>233.22</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.08220000000000001</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>0.0756</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="G132" s="6" t="n"/>
       <c r="H132" s="7" t="inlineStr">
@@ -10688,7 +10688,7 @@
         <v>250</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>0.06112054329371819</v>
+        <v>0.07194923248434955</v>
       </c>
       <c r="N132" s="3" t="inlineStr"/>
       <c r="O132" s="8" t="n"/>
@@ -10732,13 +10732,13 @@
         </is>
       </c>
       <c r="D133" s="13" t="n">
-        <v>173.72</v>
+        <v>170.72</v>
       </c>
       <c r="E133" s="18" t="n">
-        <v>0.1502</v>
+        <v>0.1303</v>
       </c>
       <c r="F133" s="18" t="n">
-        <v>0.1991</v>
+        <v>0.1784</v>
       </c>
       <c r="G133" s="15" t="n"/>
       <c r="H133" s="21" t="inlineStr">
@@ -10793,13 +10793,13 @@
         </is>
       </c>
       <c r="D134" s="4" t="n">
-        <v>854.33</v>
+        <v>843.22</v>
       </c>
       <c r="E134" s="22" t="n">
-        <v>-0.0828</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="F134" s="22" t="n">
-        <v>-0.06179999999999999</v>
+        <v>-0.07400000000000001</v>
       </c>
       <c r="G134" s="6" t="n"/>
       <c r="H134" s="7" t="inlineStr">
@@ -10818,7 +10818,7 @@
         <v>1155</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>0.3519366052930366</v>
+        <v>0.3697492943715756</v>
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>1103</v>
       </c>
       <c r="P134" s="5" t="n">
-        <v>0.2910701953577657</v>
+        <v>0.3080809278717297</v>
       </c>
       <c r="Q134" s="9" t="inlineStr">
         <is>
@@ -10870,13 +10870,13 @@
         </is>
       </c>
       <c r="D135" s="13" t="n">
-        <v>643.72</v>
+        <v>632.6799999999999</v>
       </c>
       <c r="E135" s="14" t="n">
-        <v>-0.0311</v>
+        <v>-0.04769999999999999</v>
       </c>
       <c r="F135" s="14" t="n">
-        <v>-0.024</v>
+        <v>-0.0408</v>
       </c>
       <c r="G135" s="15" t="n"/>
       <c r="H135" s="21" t="inlineStr">
@@ -10895,7 +10895,7 @@
         <v>874</v>
       </c>
       <c r="M135" s="18" t="n">
-        <v>0.357733175914994</v>
+        <v>0.3814250489979137</v>
       </c>
       <c r="N135" s="12" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>845</v>
       </c>
       <c r="P135" s="18" t="n">
-        <v>0.3126825327782265</v>
+        <v>0.3355882910792187</v>
       </c>
       <c r="Q135" s="19" t="inlineStr">
         <is>
@@ -10955,13 +10955,13 @@
         </is>
       </c>
       <c r="D136" s="4" t="n">
-        <v>206.32</v>
+        <v>205.28</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0.1228</v>
+        <v>0.1172</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>0.1704</v>
+        <v>0.1645</v>
       </c>
       <c r="G136" s="6" t="n">
         <v>46288</v>
@@ -10990,7 +10990,7 @@
         <v>250</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>0.2117099651027531</v>
+        <v>0.2178487918939984</v>
       </c>
       <c r="N136" s="3" t="inlineStr"/>
       <c r="O136" s="8" t="n"/>
@@ -11034,13 +11034,13 @@
         </is>
       </c>
       <c r="D137" s="13" t="n">
-        <v>619.6900000000001</v>
+        <v>618.05</v>
       </c>
       <c r="E137" s="18" t="n">
-        <v>0.0581</v>
+        <v>0.0553</v>
       </c>
       <c r="F137" s="18" t="n">
-        <v>0.0731</v>
+        <v>0.0703</v>
       </c>
       <c r="G137" s="15" t="n">
         <v>46254</v>
@@ -11069,7 +11069,7 @@
         <v>750</v>
       </c>
       <c r="M137" s="18" t="n">
-        <v>0.2102825606351562</v>
+        <v>0.2134940538791361</v>
       </c>
       <c r="N137" s="12" t="inlineStr">
         <is>
@@ -11080,7 +11080,7 @@
         <v>641.29</v>
       </c>
       <c r="P137" s="18" t="n">
-        <v>0.03485613774629235</v>
+        <v>0.03760213574953485</v>
       </c>
       <c r="Q137" s="19" t="inlineStr">
         <is>
@@ -11121,13 +11121,13 @@
         </is>
       </c>
       <c r="D138" s="4" t="n">
-        <v>162.26</v>
+        <v>164.37</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0.1986</v>
+        <v>0.2141</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.1341</v>
+        <v>0.1489</v>
       </c>
       <c r="G138" s="6" t="n"/>
       <c r="H138" s="7" t="inlineStr">
@@ -11153,7 +11153,7 @@
         <v>185</v>
       </c>
       <c r="P138" s="5" t="n">
-        <v>0.1401454455811661</v>
+        <v>0.1255095212021658</v>
       </c>
       <c r="Q138" s="9" t="inlineStr">
         <is>
@@ -11192,13 +11192,13 @@
         </is>
       </c>
       <c r="D139" s="13" t="n">
-        <v>461.29</v>
+        <v>459.41</v>
       </c>
       <c r="E139" s="18" t="n">
-        <v>0.1451</v>
+        <v>0.1404</v>
       </c>
       <c r="F139" s="18" t="n">
-        <v>0.1786</v>
+        <v>0.1738</v>
       </c>
       <c r="G139" s="15" t="n"/>
       <c r="H139" s="21" t="inlineStr">
@@ -11224,7 +11224,7 @@
         <v>453</v>
       </c>
       <c r="P139" s="14" t="n">
-        <v>-0.01797134123870021</v>
+        <v>-0.01395267843538457</v>
       </c>
       <c r="Q139" s="19" t="inlineStr">
         <is>
@@ -11265,13 +11265,13 @@
         </is>
       </c>
       <c r="D140" s="4" t="n">
-        <v>52.84</v>
+        <v>52.38</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0.1231</v>
+        <v>0.1133</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>0.1346</v>
+        <v>0.1248</v>
       </c>
       <c r="G140" s="6" t="n">
         <v>46309</v>
@@ -11344,13 +11344,13 @@
         </is>
       </c>
       <c r="D141" s="13" t="n">
-        <v>325.17</v>
+        <v>322.3</v>
       </c>
       <c r="E141" s="18" t="n">
-        <v>0.0364</v>
+        <v>0.0273</v>
       </c>
       <c r="F141" s="14" t="n">
-        <v>-0.0388</v>
+        <v>-0.0473</v>
       </c>
       <c r="G141" s="15" t="n">
         <v>46282</v>
@@ -11379,7 +11379,7 @@
         <v>425</v>
       </c>
       <c r="M141" s="18" t="n">
-        <v>0.307008641633607</v>
+        <v>0.3186472230840831</v>
       </c>
       <c r="N141" s="12" t="inlineStr">
         <is>
@@ -11389,8 +11389,8 @@
       <c r="O141" s="17" t="n">
         <v>323</v>
       </c>
-      <c r="P141" s="14" t="n">
-        <v>-0.006673432358458701</v>
+      <c r="P141" s="18" t="n">
+        <v>0.002171889543903161</v>
       </c>
       <c r="Q141" s="19" t="inlineStr">
         <is>
@@ -11431,13 +11431,13 @@
         </is>
       </c>
       <c r="D142" s="4" t="n">
-        <v>256.17</v>
+        <v>251.81</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>0.1134</v>
+        <v>0.0944</v>
       </c>
       <c r="G142" s="6" t="n"/>
       <c r="H142" s="7" t="inlineStr">
@@ -11456,7 +11456,7 @@
         <v>285</v>
       </c>
       <c r="M142" s="5" t="n">
-        <v>0.1125424522777842</v>
+        <v>0.1318057265398515</v>
       </c>
       <c r="N142" s="3" t="inlineStr"/>
       <c r="O142" s="8" t="n"/>
@@ -11504,13 +11504,13 @@
         </is>
       </c>
       <c r="D143" s="13" t="n">
-        <v>1701.29</v>
+        <v>1687.11</v>
       </c>
       <c r="E143" s="14" t="n">
-        <v>-0.0178</v>
+        <v>-0.0259</v>
       </c>
       <c r="F143" s="14" t="n">
-        <v>-0.09390000000000001</v>
+        <v>-0.1015</v>
       </c>
       <c r="G143" s="15" t="n">
         <v>46317</v>
@@ -11565,13 +11565,13 @@
         </is>
       </c>
       <c r="D144" s="4" t="n">
-        <v>53.26</v>
+        <v>52.97</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>0.0732</v>
+        <v>0.0673</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>0.0493</v>
+        <v>0.0435</v>
       </c>
       <c r="G144" s="6" t="n"/>
       <c r="H144" s="7" t="inlineStr">
@@ -11616,13 +11616,13 @@
         </is>
       </c>
       <c r="D145" s="13" t="n">
-        <v>396.59</v>
+        <v>391.95</v>
       </c>
       <c r="E145" s="18" t="n">
-        <v>0.0639</v>
+        <v>0.05139999999999999</v>
       </c>
       <c r="F145" s="18" t="n">
-        <v>0.101</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="G145" s="15" t="n"/>
       <c r="H145" s="21" t="inlineStr">
@@ -11641,7 +11641,7 @@
         <v>400</v>
       </c>
       <c r="M145" s="18" t="n">
-        <v>0.0085983005118637</v>
+        <v>0.02053833397116982</v>
       </c>
       <c r="N145" s="12" t="inlineStr"/>
       <c r="O145" s="17" t="n"/>
@@ -11693,13 +11693,13 @@
         </is>
       </c>
       <c r="D146" s="4" t="n">
-        <v>369.4</v>
+        <v>367.96</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0.0452</v>
+        <v>0.0411</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>0.1017</v>
+        <v>0.0974</v>
       </c>
       <c r="G146" s="6" t="n">
         <v>46315</v>
@@ -11728,7 +11728,7 @@
         <v>390</v>
       </c>
       <c r="M146" s="5" t="n">
-        <v>0.05576610720086633</v>
+        <v>0.05989781497988918</v>
       </c>
       <c r="N146" s="3" t="inlineStr"/>
       <c r="O146" s="8" t="n"/>
@@ -11780,13 +11780,13 @@
         </is>
       </c>
       <c r="D147" s="13" t="n">
-        <v>1021.5</v>
+        <v>1011.69</v>
       </c>
       <c r="E147" s="14" t="n">
-        <v>-0.0202</v>
+        <v>-0.0296</v>
       </c>
       <c r="F147" s="18" t="n">
-        <v>0.0859</v>
+        <v>0.0755</v>
       </c>
       <c r="G147" s="15" t="n">
         <v>46316</v>
@@ -11815,7 +11815,7 @@
         <v>1259</v>
       </c>
       <c r="M147" s="18" t="n">
-        <v>0.232501223690651</v>
+        <v>0.2444523520050608</v>
       </c>
       <c r="N147" s="12" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>1350</v>
       </c>
       <c r="P147" s="18" t="n">
-        <v>0.3215859030837004</v>
+        <v>0.3344008540165465</v>
       </c>
       <c r="Q147" s="19" t="inlineStr">
         <is>
@@ -11871,13 +11871,13 @@
         </is>
       </c>
       <c r="D148" s="4" t="n">
-        <v>1304.57</v>
+        <v>1301.48</v>
       </c>
       <c r="E148" s="22" t="n">
-        <v>-0.0626</v>
+        <v>-0.06480000000000001</v>
       </c>
       <c r="F148" s="22" t="n">
-        <v>-0.0086</v>
+        <v>-0.0109</v>
       </c>
       <c r="G148" s="6" t="n"/>
       <c r="H148" s="7" t="inlineStr">
@@ -11936,13 +11936,13 @@
         </is>
       </c>
       <c r="D149" s="13" t="n">
-        <v>236.56</v>
+        <v>230.12</v>
       </c>
       <c r="E149" s="18" t="n">
-        <v>0.0644</v>
-      </c>
-      <c r="F149" s="18" t="n">
-        <v>0.0238</v>
+        <v>0.0354</v>
+      </c>
+      <c r="F149" s="14" t="n">
+        <v>-0.004</v>
       </c>
       <c r="G149" s="15" t="n">
         <v>46317</v>
@@ -11997,13 +11997,13 @@
         </is>
       </c>
       <c r="D150" s="4" t="n">
-        <v>519.16</v>
+        <v>519.6799999999999</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>0.0883</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>0.0886</v>
+        <v>0.0897</v>
       </c>
       <c r="G150" s="6" t="n"/>
       <c r="H150" s="7" t="inlineStr">
@@ -12054,13 +12054,13 @@
         </is>
       </c>
       <c r="D151" s="13" t="n">
-        <v>295.89</v>
+        <v>293.1</v>
       </c>
       <c r="E151" s="18" t="n">
-        <v>0.0898</v>
+        <v>0.0796</v>
       </c>
       <c r="F151" s="18" t="n">
-        <v>0.1494</v>
+        <v>0.1386</v>
       </c>
       <c r="G151" s="15" t="n"/>
       <c r="H151" s="21" t="inlineStr">
@@ -12082,7 +12082,7 @@
         <v>272</v>
       </c>
       <c r="P151" s="14" t="n">
-        <v>-0.08073946398999624</v>
+        <v>-0.07198908222449683</v>
       </c>
       <c r="Q151" s="19" t="inlineStr">
         <is>
@@ -12135,13 +12135,13 @@
         </is>
       </c>
       <c r="D152" s="4" t="n">
-        <v>290.53</v>
-      </c>
-      <c r="E152" s="5" t="n">
-        <v>0.0064</v>
+        <v>285.88</v>
+      </c>
+      <c r="E152" s="22" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F152" s="22" t="n">
-        <v>-0.0561</v>
+        <v>-0.0712</v>
       </c>
       <c r="G152" s="6" t="n"/>
       <c r="H152" s="7" t="inlineStr">
@@ -12196,13 +12196,13 @@
         </is>
       </c>
       <c r="D153" s="13" t="n">
-        <v>429.39</v>
+        <v>431.03</v>
       </c>
       <c r="E153" s="14" t="n">
-        <v>-0.221</v>
+        <v>-0.218</v>
       </c>
       <c r="F153" s="14" t="n">
-        <v>-0.1616</v>
+        <v>-0.1584</v>
       </c>
       <c r="G153" s="15" t="n"/>
       <c r="H153" s="21" t="inlineStr">
@@ -12247,13 +12247,13 @@
         </is>
       </c>
       <c r="D154" s="4" t="n">
-        <v>599.22</v>
+        <v>597.59</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0.1508</v>
+        <v>0.1477</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>0.109</v>
+        <v>0.106</v>
       </c>
       <c r="G154" s="6" t="n">
         <v>46315</v>
@@ -12314,13 +12314,13 @@
         </is>
       </c>
       <c r="D155" s="13" t="n">
-        <v>211.63</v>
+        <v>209.44</v>
       </c>
       <c r="E155" s="14" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.1007</v>
       </c>
       <c r="F155" s="14" t="n">
-        <v>-0.1388</v>
+        <v>-0.1478</v>
       </c>
       <c r="G155" s="15" t="n"/>
       <c r="H155" s="21" t="inlineStr">
@@ -12339,7 +12339,7 @@
         <v>575</v>
       </c>
       <c r="M155" s="18" t="n">
-        <v>1.71700609554411</v>
+        <v>1.745416348357525</v>
       </c>
       <c r="N155" s="12" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>237</v>
       </c>
       <c r="P155" s="18" t="n">
-        <v>0.1198790341633984</v>
+        <v>0.1315889992360581</v>
       </c>
       <c r="Q155" s="19" t="inlineStr">
         <is>
@@ -12399,13 +12399,13 @@
         </is>
       </c>
       <c r="D156" s="4" t="n">
-        <v>121.27</v>
+        <v>121.3</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0.095</v>
+        <v>0.0953</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.2051</v>
+        <v>0.2054</v>
       </c>
       <c r="G156" s="6" t="n">
         <v>46294</v>
@@ -12434,7 +12434,7 @@
         <v>250</v>
       </c>
       <c r="M156" s="5" t="n">
-        <v>1.061515626288448</v>
+        <v>1.061005770816158</v>
       </c>
       <c r="N156" s="3" t="inlineStr"/>
       <c r="O156" s="8" t="n"/>
@@ -12478,13 +12478,13 @@
         </is>
       </c>
       <c r="D157" s="13" t="n">
-        <v>132.52</v>
+        <v>132.53</v>
       </c>
       <c r="E157" s="18" t="n">
-        <v>0.0665</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="F157" s="18" t="n">
-        <v>0.1181</v>
+        <v>0.1182</v>
       </c>
       <c r="G157" s="15" t="n"/>
       <c r="H157" s="21" t="inlineStr">
@@ -12503,7 +12503,7 @@
         <v>95</v>
       </c>
       <c r="M157" s="14" t="n">
-        <v>-0.2831270751584667</v>
+        <v>-0.2831811665283332</v>
       </c>
       <c r="N157" s="12" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>139</v>
       </c>
       <c r="P157" s="18" t="n">
-        <v>0.0488982795049803</v>
+        <v>0.04881913529012298</v>
       </c>
       <c r="Q157" s="19" t="inlineStr">
         <is>
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="D158" s="4" t="n">
-        <v>1072.05</v>
+        <v>1061.83</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>0.127</v>
+        <v>0.1162</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>0.1866</v>
+        <v>0.1753</v>
       </c>
       <c r="G158" s="6" t="n"/>
       <c r="H158" s="7" t="inlineStr">
@@ -12584,7 +12584,7 @@
         <v>125</v>
       </c>
       <c r="M158" s="22" t="n">
-        <v>-0.8834009607760832</v>
+        <v>-0.8822787075143855</v>
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
@@ -12594,8 +12594,8 @@
       <c r="O158" s="8" t="n">
         <v>1064</v>
       </c>
-      <c r="P158" s="22" t="n">
-        <v>-0.0075089781260202</v>
+      <c r="P158" s="5" t="n">
+        <v>0.002043641637550336</v>
       </c>
       <c r="Q158" s="9" t="inlineStr">
         <is>
@@ -12640,13 +12640,13 @@
         </is>
       </c>
       <c r="D159" s="13" t="n">
-        <v>561.78</v>
+        <v>552.3</v>
       </c>
       <c r="E159" s="14" t="n">
-        <v>-0.039</v>
+        <v>-0.0552</v>
       </c>
       <c r="F159" s="14" t="n">
-        <v>-0.0693</v>
+        <v>-0.0851</v>
       </c>
       <c r="G159" s="15" t="n"/>
       <c r="H159" s="21" t="inlineStr">
@@ -12711,13 +12711,13 @@
         </is>
       </c>
       <c r="D160" s="4" t="n">
-        <v>445.53</v>
+        <v>447.07</v>
       </c>
       <c r="E160" s="22" t="n">
-        <v>-0.03240000000000001</v>
+        <v>-0.0291</v>
       </c>
       <c r="F160" s="22" t="n">
-        <v>-0.0301</v>
+        <v>-0.0267</v>
       </c>
       <c r="G160" s="6" t="n"/>
       <c r="H160" s="7" t="inlineStr">
@@ -12762,13 +12762,13 @@
         </is>
       </c>
       <c r="D161" s="13" t="n">
-        <v>37.12</v>
+        <v>37.01</v>
       </c>
       <c r="E161" s="14" t="n">
-        <v>-0.1736</v>
+        <v>-0.1761</v>
       </c>
       <c r="F161" s="14" t="n">
-        <v>-0.2134</v>
+        <v>-0.2157</v>
       </c>
       <c r="G161" s="15" t="n">
         <v>46323</v>
@@ -12837,13 +12837,13 @@
         </is>
       </c>
       <c r="D162" s="4" t="n">
-        <v>224.97</v>
+        <v>223.85</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>0.1455</v>
+        <v>0.1398</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>0.2258</v>
+        <v>0.2197</v>
       </c>
       <c r="G162" s="6" t="n">
         <v>46322</v>
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="D163" s="13" t="n">
-        <v>41.67</v>
+        <v>41.69</v>
       </c>
       <c r="E163" s="14" t="n">
-        <v>-0.0179</v>
+        <v>-0.0174</v>
       </c>
       <c r="F163" s="18" t="n">
-        <v>0.001</v>
+        <v>0.0014</v>
       </c>
       <c r="G163" s="15" t="n"/>
       <c r="H163" s="21" t="inlineStr">
@@ -12967,13 +12967,13 @@
         </is>
       </c>
       <c r="D164" s="4" t="n">
-        <v>488.07</v>
+        <v>483.88</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>0.017</v>
+        <v>0.0083</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>0.06509999999999999</v>
+        <v>0.0559</v>
       </c>
       <c r="G164" s="6" t="n"/>
       <c r="H164" s="7" t="inlineStr">
@@ -12995,7 +12995,7 @@
         <v>560</v>
       </c>
       <c r="P164" s="5" t="n">
-        <v>0.1473764009260967</v>
+        <v>0.1573117301810366</v>
       </c>
       <c r="Q164" s="9" t="inlineStr">
         <is>
@@ -13048,13 +13048,13 @@
         </is>
       </c>
       <c r="D165" s="13" t="n">
-        <v>291.61</v>
+        <v>292.8</v>
       </c>
       <c r="E165" s="18" t="n">
-        <v>0.0086</v>
+        <v>0.0127</v>
       </c>
       <c r="F165" s="18" t="n">
-        <v>0.0693</v>
+        <v>0.0737</v>
       </c>
       <c r="G165" s="15" t="n">
         <v>46317</v>
@@ -13086,7 +13086,7 @@
         <v>294</v>
       </c>
       <c r="P165" s="18" t="n">
-        <v>0.008195878056308035</v>
+        <v>0.004098360655737666</v>
       </c>
       <c r="Q165" s="19" t="inlineStr">
         <is>
@@ -13131,13 +13131,13 @@
         </is>
       </c>
       <c r="D166" s="4" t="n">
-        <v>280.67</v>
+        <v>281.83</v>
       </c>
       <c r="E166" s="22" t="n">
-        <v>-0.0824</v>
+        <v>-0.0786</v>
       </c>
       <c r="F166" s="22" t="n">
-        <v>-0.0733</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="G166" s="6" t="n"/>
       <c r="H166" s="7" t="inlineStr">
@@ -13159,7 +13159,7 @@
         <v>425</v>
       </c>
       <c r="P166" s="5" t="n">
-        <v>0.5142337976983645</v>
+        <v>0.5080012773657879</v>
       </c>
       <c r="Q166" s="9" t="inlineStr">
         <is>
@@ -13200,13 +13200,13 @@
         </is>
       </c>
       <c r="D167" s="13" t="n">
-        <v>228.78</v>
+        <v>226.85</v>
       </c>
       <c r="E167" s="14" t="n">
-        <v>-0.0335</v>
+        <v>-0.0417</v>
       </c>
       <c r="F167" s="18" t="n">
-        <v>0.0425</v>
+        <v>0.0337</v>
       </c>
       <c r="G167" s="15" t="n"/>
       <c r="H167" s="21" t="inlineStr">
@@ -13225,7 +13225,7 @@
         <v>268</v>
       </c>
       <c r="M167" s="18" t="n">
-        <v>0.1714310691494012</v>
+        <v>0.1813973991624422</v>
       </c>
       <c r="N167" s="12" t="inlineStr"/>
       <c r="O167" s="17" t="n"/>
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="D168" s="4" t="n">
-        <v>327.49</v>
+        <v>318.71</v>
       </c>
       <c r="E168" s="22" t="n">
-        <v>-0.1682</v>
+        <v>-0.1905</v>
       </c>
       <c r="F168" s="22" t="n">
-        <v>-0.1392</v>
+        <v>-0.1623</v>
       </c>
       <c r="G168" s="6" t="n"/>
       <c r="H168" s="7" t="inlineStr">
@@ -13338,13 +13338,13 @@
         </is>
       </c>
       <c r="D169" s="13" t="n">
-        <v>358.35</v>
+        <v>356.58</v>
       </c>
       <c r="E169" s="14" t="n">
-        <v>-0.09720000000000001</v>
+        <v>-0.1017</v>
       </c>
       <c r="F169" s="14" t="n">
-        <v>-0.0737</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="G169" s="15" t="n"/>
       <c r="H169" s="21" t="inlineStr">
@@ -13407,13 +13407,13 @@
         </is>
       </c>
       <c r="D170" s="4" t="n">
-        <v>122.63</v>
+        <v>123.17</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>0.0117</v>
+        <v>0.0162</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>0.114</v>
+        <v>0.1189</v>
       </c>
       <c r="G170" s="6" t="n"/>
       <c r="H170" s="7" t="inlineStr">
@@ -13476,13 +13476,13 @@
         </is>
       </c>
       <c r="D171" s="13" t="n">
-        <v>129.96</v>
+        <v>134.33</v>
       </c>
       <c r="E171" s="18" t="n">
-        <v>0.1616</v>
+        <v>0.2007</v>
       </c>
       <c r="F171" s="14" t="n">
-        <v>-0.2313</v>
+        <v>-0.2054</v>
       </c>
       <c r="G171" s="15" t="n"/>
       <c r="H171" s="21" t="inlineStr">
@@ -13527,13 +13527,13 @@
         </is>
       </c>
       <c r="D172" s="4" t="n">
-        <v>306.78</v>
+        <v>304.91</v>
       </c>
       <c r="E172" s="22" t="n">
-        <v>-0.0332</v>
+        <v>-0.0391</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>0.0538</v>
+        <v>0.0473</v>
       </c>
       <c r="G172" s="6" t="n"/>
       <c r="H172" s="7" t="inlineStr">
@@ -13552,7 +13552,7 @@
         <v>310</v>
       </c>
       <c r="M172" s="5" t="n">
-        <v>0.01049612099876142</v>
+        <v>0.01669345052638475</v>
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>365</v>
       </c>
       <c r="P172" s="5" t="n">
-        <v>0.1897776908533804</v>
+        <v>0.1970745465875175</v>
       </c>
       <c r="Q172" s="9" t="inlineStr">
         <is>
@@ -13620,13 +13620,13 @@
         </is>
       </c>
       <c r="D173" s="13" t="n">
-        <v>133.98</v>
+        <v>135.36</v>
       </c>
       <c r="E173" s="14" t="n">
-        <v>-0.0189</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F173" s="14" t="n">
-        <v>-0.2562</v>
+        <v>-0.2485</v>
       </c>
       <c r="G173" s="15" t="n"/>
       <c r="H173" s="21" t="inlineStr">
@@ -13671,13 +13671,13 @@
         </is>
       </c>
       <c r="D174" s="4" t="n">
-        <v>179.41</v>
+        <v>179.85</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>0.2952</v>
+        <v>0.2984</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>0.0536</v>
+        <v>0.0562</v>
       </c>
       <c r="G174" s="6" t="n">
         <v>46289</v>
@@ -13732,13 +13732,13 @@
         </is>
       </c>
       <c r="D175" s="13" t="n">
-        <v>270.36</v>
+        <v>263.71</v>
       </c>
       <c r="E175" s="18" t="n">
-        <v>0.1724</v>
+        <v>0.1435</v>
       </c>
       <c r="F175" s="18" t="n">
-        <v>0.3252</v>
+        <v>0.2926</v>
       </c>
       <c r="G175" s="15" t="n">
         <v>46275</v>
@@ -13793,13 +13793,13 @@
         </is>
       </c>
       <c r="D176" s="4" t="n">
-        <v>391.57</v>
-      </c>
-      <c r="E176" s="5" t="n">
-        <v>0.0144</v>
+        <v>385.3</v>
+      </c>
+      <c r="E176" s="22" t="n">
+        <v>-0.0018</v>
       </c>
       <c r="F176" s="22" t="n">
-        <v>-0.06280000000000001</v>
+        <v>-0.07780000000000001</v>
       </c>
       <c r="G176" s="6" t="n">
         <v>46253</v>
@@ -13828,7 +13828,7 @@
         <v>515</v>
       </c>
       <c r="M176" s="5" t="n">
-        <v>0.3152182240723242</v>
+        <v>0.3366208149493901</v>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>474</v>
       </c>
       <c r="P176" s="5" t="n">
-        <v>0.2105115305054014</v>
+        <v>0.2302102257980794</v>
       </c>
       <c r="Q176" s="9" t="inlineStr">
         <is>
@@ -13888,13 +13888,13 @@
         </is>
       </c>
       <c r="D177" s="13" t="n">
-        <v>254.47</v>
+        <v>251.59</v>
       </c>
       <c r="E177" s="18" t="n">
-        <v>0.1991</v>
+        <v>0.1855</v>
       </c>
       <c r="F177" s="18" t="n">
-        <v>0.2824</v>
+        <v>0.2679</v>
       </c>
       <c r="G177" s="15" t="n">
         <v>46261</v>
@@ -13949,13 +13949,13 @@
         </is>
       </c>
       <c r="D178" s="4" t="n">
-        <v>322.95</v>
+        <v>327.59</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>0.0818</v>
+        <v>0.0974</v>
       </c>
       <c r="F178" s="22" t="n">
-        <v>-0.08869999999999999</v>
+        <v>-0.0756</v>
       </c>
       <c r="G178" s="6" t="n"/>
       <c r="H178" s="7" t="inlineStr">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="D179" s="13" t="n">
-        <v>309.4</v>
+        <v>311.99</v>
       </c>
       <c r="E179" s="14" t="n">
-        <v>-0.1454</v>
+        <v>-0.1383</v>
       </c>
       <c r="F179" s="14" t="n">
-        <v>-0.1573</v>
+        <v>-0.1502</v>
       </c>
       <c r="G179" s="15" t="n"/>
       <c r="H179" s="21" t="inlineStr">
@@ -14051,13 +14051,13 @@
         </is>
       </c>
       <c r="D180" s="4" t="n">
-        <v>43.51</v>
+        <v>42.52</v>
       </c>
       <c r="E180" s="22" t="n">
-        <v>-0.1444</v>
+        <v>-0.1639</v>
       </c>
       <c r="F180" s="22" t="n">
-        <v>-0.1368</v>
+        <v>-0.1564</v>
       </c>
       <c r="G180" s="6" t="n"/>
       <c r="H180" s="7" t="inlineStr">
@@ -14102,13 +14102,13 @@
         </is>
       </c>
       <c r="D181" s="13" t="n">
-        <v>533.35</v>
+        <v>525.61</v>
       </c>
       <c r="E181" s="14" t="n">
-        <v>-0.0731</v>
+        <v>-0.08650000000000001</v>
       </c>
       <c r="F181" s="14" t="n">
-        <v>-0.05980000000000001</v>
+        <v>-0.07339999999999999</v>
       </c>
       <c r="G181" s="15" t="n">
         <v>46247</v>
@@ -14137,7 +14137,7 @@
         <v>740</v>
       </c>
       <c r="M181" s="18" t="n">
-        <v>0.3874566419799381</v>
+        <v>0.4078879777782005</v>
       </c>
       <c r="N181" s="12" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>700</v>
       </c>
       <c r="P181" s="18" t="n">
-        <v>0.3124589856566982</v>
+        <v>0.3317859249253248</v>
       </c>
       <c r="Q181" s="19" t="inlineStr">
         <is>
@@ -14189,13 +14189,13 @@
         </is>
       </c>
       <c r="D182" s="4" t="n">
-        <v>63.97</v>
+        <v>65.23</v>
       </c>
       <c r="E182" s="22" t="n">
-        <v>-0.2136</v>
+        <v>-0.1982</v>
       </c>
       <c r="F182" s="22" t="n">
-        <v>-0.2449</v>
+        <v>-0.2301</v>
       </c>
       <c r="G182" s="6" t="n">
         <v>46245</v>
@@ -14254,13 +14254,13 @@
         </is>
       </c>
       <c r="D183" s="13" t="n">
-        <v>467.88</v>
+        <v>474.32</v>
       </c>
       <c r="E183" s="14" t="n">
-        <v>-0.1245</v>
+        <v>-0.1124</v>
       </c>
       <c r="F183" s="14" t="n">
-        <v>-0.08539999999999999</v>
+        <v>-0.0728</v>
       </c>
       <c r="G183" s="15" t="n"/>
       <c r="H183" s="21" t="inlineStr">
@@ -14279,7 +14279,7 @@
         <v>615</v>
       </c>
       <c r="M183" s="18" t="n">
-        <v>0.3144395998974096</v>
+        <v>0.2965930173722381</v>
       </c>
       <c r="N183" s="12" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>579</v>
       </c>
       <c r="P183" s="18" t="n">
-        <v>0.2374967940497563</v>
+        <v>0.2206948895260584</v>
       </c>
       <c r="Q183" s="19" t="inlineStr">
         <is>
@@ -14331,13 +14331,13 @@
         </is>
       </c>
       <c r="D184" s="4" t="n">
-        <v>53.99</v>
+        <v>54.3</v>
       </c>
       <c r="E184" s="22" t="n">
-        <v>-0.1827</v>
+        <v>-0.178</v>
       </c>
       <c r="F184" s="22" t="n">
-        <v>-0.3478</v>
+        <v>-0.344</v>
       </c>
       <c r="G184" s="6" t="n"/>
       <c r="H184" s="7" t="inlineStr">
@@ -14382,13 +14382,13 @@
         </is>
       </c>
       <c r="D185" s="13" t="n">
-        <v>196.05</v>
+        <v>197.77</v>
       </c>
       <c r="E185" s="18" t="n">
-        <v>0.0823</v>
+        <v>0.0917</v>
       </c>
       <c r="F185" s="18" t="n">
-        <v>0.201</v>
+        <v>0.2115</v>
       </c>
       <c r="G185" s="15" t="n"/>
       <c r="H185" s="21" t="inlineStr">
@@ -14407,7 +14407,7 @@
         <v>200</v>
       </c>
       <c r="M185" s="18" t="n">
-        <v>0.02014792144860999</v>
+        <v>0.0112757243262375</v>
       </c>
       <c r="N185" s="12" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>200</v>
       </c>
       <c r="P185" s="18" t="n">
-        <v>0.02014792144860999</v>
+        <v>0.0112757243262375</v>
       </c>
       <c r="Q185" s="19" t="inlineStr">
         <is>
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="D186" s="4" t="n">
-        <v>171.61</v>
+        <v>167.23</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>0.1001</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>0.1158</v>
+        <v>0.0873</v>
       </c>
       <c r="G186" s="6" t="n"/>
       <c r="H186" s="7" t="inlineStr">
@@ -14491,7 +14491,7 @@
         <v>180</v>
       </c>
       <c r="P186" s="5" t="n">
-        <v>0.0488899248295553</v>
+        <v>0.07636189678885374</v>
       </c>
       <c r="Q186" s="9" t="inlineStr">
         <is>
@@ -14544,13 +14544,13 @@
         </is>
       </c>
       <c r="D187" s="13" t="n">
-        <v>29.35</v>
+        <v>29.69</v>
       </c>
       <c r="E187" s="18" t="n">
-        <v>0.0179</v>
+        <v>0.0295</v>
       </c>
       <c r="F187" s="14" t="n">
-        <v>-0.3125</v>
+        <v>-0.3047</v>
       </c>
       <c r="G187" s="15" t="n"/>
       <c r="H187" s="21" t="inlineStr">
@@ -14595,13 +14595,13 @@
         </is>
       </c>
       <c r="D188" s="4" t="n">
-        <v>268.5</v>
+        <v>268.93</v>
       </c>
       <c r="E188" s="22" t="n">
-        <v>-0.102</v>
+        <v>-0.1005</v>
       </c>
       <c r="F188" s="22" t="n">
-        <v>-0.2949</v>
+        <v>-0.2938</v>
       </c>
       <c r="G188" s="6" t="n"/>
       <c r="H188" s="7" t="inlineStr">
@@ -14646,13 +14646,13 @@
         </is>
       </c>
       <c r="D189" s="13" t="n">
-        <v>1810.76</v>
+        <v>1799.38</v>
       </c>
       <c r="E189" s="18" t="n">
-        <v>0.0491</v>
+        <v>0.0425</v>
       </c>
       <c r="F189" s="14" t="n">
-        <v>-0.0283</v>
+        <v>-0.0344</v>
       </c>
       <c r="G189" s="15" t="n">
         <v>46309</v>
@@ -14725,13 +14725,13 @@
         </is>
       </c>
       <c r="D190" s="4" t="n">
-        <v>38.88</v>
+        <v>38.68</v>
       </c>
       <c r="E190" s="22" t="n">
-        <v>-0.0414</v>
+        <v>-0.0464</v>
       </c>
       <c r="F190" s="5" t="n">
-        <v>0.0199</v>
+        <v>0.0147</v>
       </c>
       <c r="G190" s="6" t="n"/>
       <c r="H190" s="7" t="inlineStr">
@@ -14776,13 +14776,13 @@
         </is>
       </c>
       <c r="D191" s="13" t="n">
-        <v>421.89</v>
+        <v>416.08</v>
       </c>
       <c r="E191" s="18" t="n">
-        <v>0.09849999999999999</v>
+        <v>0.0834</v>
       </c>
       <c r="F191" s="18" t="n">
-        <v>0.1042</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="G191" s="15" t="n">
         <v>46267</v>
@@ -14811,7 +14811,7 @@
         <v>545</v>
       </c>
       <c r="M191" s="18" t="n">
-        <v>0.2918059209746617</v>
+        <v>0.3098442607190925</v>
       </c>
       <c r="N191" s="12" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>582</v>
       </c>
       <c r="P191" s="18" t="n">
-        <v>0.3795065064353268</v>
+        <v>0.3987694674101135</v>
       </c>
       <c r="Q191" s="19" t="inlineStr">
         <is>
@@ -14875,13 +14875,13 @@
         </is>
       </c>
       <c r="D192" s="4" t="n">
-        <v>159.75</v>
+        <v>164.41</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>0.1679</v>
+        <v>0.202</v>
       </c>
       <c r="F192" s="22" t="n">
-        <v>-0.1734</v>
+        <v>-0.1493</v>
       </c>
       <c r="G192" s="6" t="n"/>
       <c r="H192" s="7" t="inlineStr">
@@ -14926,13 +14926,13 @@
         </is>
       </c>
       <c r="D193" s="13" t="n">
-        <v>326.91</v>
+        <v>327.53</v>
       </c>
       <c r="E193" s="14" t="n">
-        <v>-0.135</v>
+        <v>-0.1333</v>
       </c>
       <c r="F193" s="14" t="n">
-        <v>-0.1508</v>
+        <v>-0.1492</v>
       </c>
       <c r="G193" s="15" t="n"/>
       <c r="H193" s="21" t="inlineStr">
@@ -14951,7 +14951,7 @@
         <v>425</v>
       </c>
       <c r="M193" s="18" t="n">
-        <v>0.3000520020800831</v>
+        <v>0.2975910603608831</v>
       </c>
       <c r="N193" s="12" t="inlineStr"/>
       <c r="O193" s="17" t="n"/>
@@ -14995,13 +14995,13 @@
         </is>
       </c>
       <c r="D194" s="4" t="n">
-        <v>129.06</v>
+        <v>129.12</v>
       </c>
       <c r="E194" s="22" t="n">
-        <v>-0.0392</v>
+        <v>-0.0387</v>
       </c>
       <c r="F194" s="5" t="n">
-        <v>0.0403</v>
+        <v>0.0408</v>
       </c>
       <c r="G194" s="6" t="n"/>
       <c r="H194" s="7" t="inlineStr">
@@ -15046,13 +15046,13 @@
         </is>
       </c>
       <c r="D195" s="13" t="n">
-        <v>387.98</v>
+        <v>387.54</v>
       </c>
       <c r="E195" s="14" t="n">
-        <v>-0.129</v>
+        <v>-0.13</v>
       </c>
       <c r="F195" s="14" t="n">
-        <v>-0.1301</v>
+        <v>-0.131</v>
       </c>
       <c r="G195" s="15" t="n">
         <v>46268</v>
@@ -15107,13 +15107,13 @@
         </is>
       </c>
       <c r="D196" s="4" t="n">
-        <v>16.37</v>
-      </c>
-      <c r="E196" s="5" t="n">
-        <v>0.0149</v>
+        <v>16.03</v>
+      </c>
+      <c r="E196" s="22" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F196" s="5" t="n">
-        <v>0.2749</v>
+        <v>0.2484</v>
       </c>
       <c r="G196" s="6" t="n">
         <v>46247</v>
@@ -15168,13 +15168,13 @@
         </is>
       </c>
       <c r="D197" s="13" t="n">
-        <v>312.24</v>
+        <v>310.47</v>
       </c>
       <c r="E197" s="14" t="n">
-        <v>-0.09539999999999998</v>
+        <v>-0.1006</v>
       </c>
       <c r="F197" s="14" t="n">
-        <v>-0.2057</v>
+        <v>-0.2102</v>
       </c>
       <c r="G197" s="15" t="n"/>
       <c r="H197" s="21" t="inlineStr">
@@ -15219,13 +15219,13 @@
         </is>
       </c>
       <c r="D198" s="4" t="n">
-        <v>328.39</v>
+        <v>328.58</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>0.0683</v>
+        <v>0.0689</v>
       </c>
       <c r="F198" s="22" t="n">
-        <v>-0.1471</v>
+        <v>-0.1466</v>
       </c>
       <c r="G198" s="6" t="n">
         <v>46246</v>
@@ -15280,13 +15280,13 @@
         </is>
       </c>
       <c r="D199" s="13" t="n">
-        <v>52.11</v>
-      </c>
-      <c r="E199" s="14" t="n">
-        <v>-0.0133</v>
+        <v>52.82</v>
+      </c>
+      <c r="E199" s="18" t="n">
+        <v>0.0002</v>
       </c>
       <c r="F199" s="14" t="n">
-        <v>-0.1503</v>
+        <v>-0.1388</v>
       </c>
       <c r="G199" s="15" t="n"/>
       <c r="H199" s="21" t="inlineStr">
@@ -15331,13 +15331,13 @@
         </is>
       </c>
       <c r="D200" s="4" t="n">
-        <v>19.88</v>
+        <v>19.76</v>
       </c>
       <c r="E200" s="22" t="n">
-        <v>-0.1246</v>
+        <v>-0.1299</v>
       </c>
       <c r="F200" s="22" t="n">
-        <v>-0.2797</v>
+        <v>-0.2841</v>
       </c>
       <c r="G200" s="6" t="n"/>
       <c r="H200" s="7" t="inlineStr">
@@ -15382,13 +15382,13 @@
         </is>
       </c>
       <c r="D201" s="13" t="n">
-        <v>244.69</v>
+        <v>247.69</v>
       </c>
       <c r="E201" s="18" t="n">
-        <v>0.033</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="F201" s="14" t="n">
-        <v>-0.0244</v>
+        <v>-0.0124</v>
       </c>
       <c r="G201" s="15" t="n">
         <v>46267</v>
@@ -15443,13 +15443,13 @@
         </is>
       </c>
       <c r="D202" s="4" t="n">
-        <v>198.94</v>
+        <v>197.45</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>0.1619</v>
+        <v>0.1532</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>0.1992</v>
+        <v>0.1902</v>
       </c>
       <c r="G202" s="6" t="n">
         <v>46260</v>
@@ -15478,7 +15478,7 @@
         <v>200</v>
       </c>
       <c r="M202" s="5" t="n">
-        <v>0.005328239670252349</v>
+        <v>0.01291466193973164</v>
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>250</v>
       </c>
       <c r="P202" s="5" t="n">
-        <v>0.2566602995878154</v>
+        <v>0.2661433274246646</v>
       </c>
       <c r="Q202" s="9" t="inlineStr">
         <is>
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="D203" s="13" t="n">
-        <v>222.99</v>
+        <v>221.9</v>
       </c>
       <c r="E203" s="18" t="n">
-        <v>0.1867</v>
+        <v>0.1809</v>
       </c>
       <c r="F203" s="18" t="n">
-        <v>0.3063</v>
+        <v>0.2999</v>
       </c>
       <c r="G203" s="15" t="n">
         <v>46260</v>
@@ -15569,7 +15569,7 @@
         <v>181.25</v>
       </c>
       <c r="M203" s="14" t="n">
-        <v>-0.187183281761514</v>
+        <v>-0.183190626408292</v>
       </c>
       <c r="N203" s="12" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>177.5</v>
       </c>
       <c r="P203" s="14" t="n">
-        <v>-0.2040001793802413</v>
+        <v>-0.2000901306894998</v>
       </c>
       <c r="Q203" s="19" t="inlineStr">
         <is>
@@ -15621,13 +15621,13 @@
         </is>
       </c>
       <c r="D204" s="4" t="n">
-        <v>88.65000000000001</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>0.0641</v>
+        <v>0.08410000000000001</v>
       </c>
       <c r="F204" s="22" t="n">
-        <v>-0.1183</v>
+        <v>-0.1017</v>
       </c>
       <c r="G204" s="6" t="n">
         <v>46245</v>
@@ -15682,13 +15682,13 @@
         </is>
       </c>
       <c r="D205" s="13" t="n">
-        <v>121.9</v>
+        <v>120.43</v>
       </c>
       <c r="E205" s="18" t="n">
-        <v>0.0222</v>
-      </c>
-      <c r="F205" s="18" t="n">
-        <v>0.0066</v>
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F205" s="14" t="n">
+        <v>-0.005500000000000001</v>
       </c>
       <c r="G205" s="15" t="n">
         <v>46246</v>
@@ -15717,7 +15717,7 @@
         <v>130</v>
       </c>
       <c r="M205" s="18" t="n">
-        <v>0.06644790812141094</v>
+        <v>0.07946524952254415</v>
       </c>
       <c r="N205" s="12" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>150</v>
       </c>
       <c r="P205" s="18" t="n">
-        <v>0.2305168170631665</v>
+        <v>0.2455368263721663</v>
       </c>
       <c r="Q205" s="19" t="inlineStr">
         <is>
@@ -15785,13 +15785,13 @@
         </is>
       </c>
       <c r="D206" s="4" t="n">
-        <v>252.99</v>
+        <v>246.78</v>
       </c>
       <c r="E206" s="22" t="n">
-        <v>-0.0279</v>
+        <v>-0.0517</v>
       </c>
       <c r="F206" s="5" t="n">
-        <v>0.1004</v>
+        <v>0.07339999999999999</v>
       </c>
       <c r="G206" s="6" t="n"/>
       <c r="H206" s="7" t="inlineStr">
@@ -15836,13 +15836,13 @@
         </is>
       </c>
       <c r="D207" s="13" t="n">
-        <v>442.77</v>
+        <v>440.54</v>
       </c>
       <c r="E207" s="18" t="n">
-        <v>0.0367</v>
+        <v>0.0314</v>
       </c>
       <c r="F207" s="18" t="n">
-        <v>0.1193</v>
+        <v>0.1137</v>
       </c>
       <c r="G207" s="15" t="n">
         <v>46268</v>
@@ -15897,13 +15897,13 @@
         </is>
       </c>
       <c r="D208" s="4" t="n">
-        <v>60.22</v>
+        <v>59.34</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>0.2075</v>
+        <v>0.1899</v>
       </c>
       <c r="F208" s="5" t="n">
-        <v>0.3373</v>
+        <v>0.3178</v>
       </c>
       <c r="G208" s="6" t="n">
         <v>46268</v>
@@ -15958,13 +15958,13 @@
         </is>
       </c>
       <c r="D209" s="13" t="n">
-        <v>50.58</v>
+        <v>49.66</v>
       </c>
       <c r="E209" s="18" t="n">
-        <v>0.1343</v>
+        <v>0.1137</v>
       </c>
       <c r="F209" s="18" t="n">
-        <v>0.2412</v>
+        <v>0.2187</v>
       </c>
       <c r="G209" s="15" t="n"/>
       <c r="H209" s="21" t="inlineStr">
@@ -16009,13 +16009,13 @@
         </is>
       </c>
       <c r="D210" s="4" t="n">
-        <v>528.79</v>
+        <v>525.66</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>0.1141</v>
+        <v>0.1075</v>
       </c>
       <c r="F210" s="22" t="n">
-        <v>-0.1346</v>
+        <v>-0.1397</v>
       </c>
       <c r="G210" s="6" t="n">
         <v>46251</v>
@@ -16070,13 +16070,13 @@
         </is>
       </c>
       <c r="D211" s="13" t="n">
-        <v>118.91</v>
+        <v>121.07</v>
       </c>
       <c r="E211" s="18" t="n">
-        <v>0.0781</v>
+        <v>0.09759999999999999</v>
       </c>
       <c r="F211" s="14" t="n">
-        <v>-0.1458</v>
+        <v>-0.1303</v>
       </c>
       <c r="G211" s="15" t="n"/>
       <c r="H211" s="21" t="inlineStr">
@@ -16121,13 +16121,13 @@
         </is>
       </c>
       <c r="D212" s="4" t="n">
-        <v>162.16</v>
+        <v>161.89</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F212" s="5" t="n">
-        <v>0.1084</v>
+        <v>0.1066</v>
       </c>
       <c r="G212" s="6" t="n"/>
       <c r="H212" s="7" t="inlineStr">
@@ -16172,13 +16172,13 @@
         </is>
       </c>
       <c r="D213" s="13" t="n">
-        <v>51.18</v>
+        <v>50.82</v>
       </c>
       <c r="E213" s="14" t="n">
-        <v>-0.1996</v>
+        <v>-0.2052</v>
       </c>
       <c r="F213" s="14" t="n">
-        <v>-0.3711</v>
+        <v>-0.3754999999999999</v>
       </c>
       <c r="G213" s="15" t="n"/>
       <c r="H213" s="21" t="inlineStr">
@@ -16223,13 +16223,13 @@
         </is>
       </c>
       <c r="D214" s="4" t="n">
-        <v>159.97</v>
+        <v>159.2</v>
       </c>
       <c r="E214" s="22" t="n">
-        <v>-0.1264</v>
+        <v>-0.1306</v>
       </c>
       <c r="F214" s="22" t="n">
-        <v>-0.1073</v>
+        <v>-0.1116</v>
       </c>
       <c r="G214" s="6" t="n"/>
       <c r="H214" s="7" t="inlineStr">
@@ -16274,13 +16274,13 @@
         </is>
       </c>
       <c r="D215" s="13" t="n">
-        <v>41.74</v>
+        <v>42.11</v>
       </c>
       <c r="E215" s="18" t="n">
-        <v>0.2472</v>
+        <v>0.2581</v>
       </c>
       <c r="F215" s="18" t="n">
-        <v>0.5022</v>
+        <v>0.5153</v>
       </c>
       <c r="G215" s="15" t="n">
         <v>46267</v>
@@ -16335,13 +16335,13 @@
         </is>
       </c>
       <c r="D216" s="4" t="n">
-        <v>177.6</v>
+        <v>176.63</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>0.2657</v>
+        <v>0.2589</v>
       </c>
       <c r="F216" s="5" t="n">
-        <v>0.449</v>
+        <v>0.4412</v>
       </c>
       <c r="G216" s="6" t="n">
         <v>46268</v>
@@ -16370,7 +16370,7 @@
         <v>190</v>
       </c>
       <c r="M216" s="5" t="n">
-        <v>0.06981981981981986</v>
+        <v>0.0756949555568137</v>
       </c>
       <c r="N216" s="3" t="inlineStr"/>
       <c r="O216" s="8" t="n"/>
@@ -16414,13 +16414,13 @@
         </is>
       </c>
       <c r="D217" s="13" t="n">
-        <v>54.15</v>
+        <v>54.38</v>
       </c>
       <c r="E217" s="18" t="n">
-        <v>0.1462</v>
+        <v>0.151</v>
       </c>
       <c r="F217" s="18" t="n">
-        <v>0.124</v>
+        <v>0.1288</v>
       </c>
       <c r="G217" s="15" t="n">
         <v>46267</v>
@@ -16449,7 +16449,7 @@
         <v>67</v>
       </c>
       <c r="M217" s="18" t="n">
-        <v>0.2373037857802401</v>
+        <v>0.2320706141963957</v>
       </c>
       <c r="N217" s="12" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>70</v>
       </c>
       <c r="P217" s="18" t="n">
-        <v>0.2927054478301016</v>
+        <v>0.2872379551305627</v>
       </c>
       <c r="Q217" s="19" t="inlineStr">
         <is>
@@ -16501,13 +16501,13 @@
         </is>
       </c>
       <c r="D218" s="4" t="n">
-        <v>223.95</v>
+        <v>220.41</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>0.0292</v>
+        <v>0.013</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>0.1914</v>
+        <v>0.1725</v>
       </c>
       <c r="G218" s="6" t="n"/>
       <c r="H218" s="7" t="inlineStr">
@@ -16552,13 +16552,13 @@
         </is>
       </c>
       <c r="D219" s="13" t="n">
-        <v>240.51</v>
+        <v>238.44</v>
       </c>
       <c r="E219" s="14" t="n">
-        <v>-0.1713</v>
+        <v>-0.1784</v>
       </c>
       <c r="F219" s="14" t="n">
-        <v>-0.1165</v>
+        <v>-0.1242</v>
       </c>
       <c r="G219" s="15" t="n">
         <v>46316</v>
@@ -16594,7 +16594,7 @@
         <v>250</v>
       </c>
       <c r="P219" s="18" t="n">
-        <v>0.03945781880171306</v>
+        <v>0.04848179835598055</v>
       </c>
       <c r="Q219" s="19" t="inlineStr">
         <is>
@@ -16631,13 +16631,13 @@
         </is>
       </c>
       <c r="D220" s="4" t="n">
-        <v>11.69</v>
+        <v>11.82</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>0.154</v>
+        <v>0.1668</v>
       </c>
       <c r="F220" s="22" t="n">
-        <v>-0.1289</v>
+        <v>-0.1192</v>
       </c>
       <c r="G220" s="6" t="n">
         <v>46246</v>
@@ -16692,13 +16692,13 @@
         </is>
       </c>
       <c r="D221" s="13" t="n">
-        <v>97.54000000000001</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="E221" s="14" t="n">
-        <v>-0.0541</v>
+        <v>-0.0525</v>
       </c>
       <c r="F221" s="14" t="n">
-        <v>-0.217</v>
+        <v>-0.2156</v>
       </c>
       <c r="G221" s="15" t="n">
         <v>46317</v>
@@ -16753,13 +16753,13 @@
         </is>
       </c>
       <c r="D222" s="4" t="n">
-        <v>337.17</v>
+        <v>336.44</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>0.1636</v>
+        <v>0.1611</v>
       </c>
       <c r="F222" s="5" t="n">
-        <v>0.2184</v>
+        <v>0.2158</v>
       </c>
       <c r="G222" s="6" t="n">
         <v>46259</v>
@@ -16814,13 +16814,13 @@
         </is>
       </c>
       <c r="D223" s="13" t="n">
-        <v>43.03</v>
+        <v>43.42</v>
       </c>
       <c r="E223" s="18" t="n">
-        <v>0.1067</v>
+        <v>0.1169</v>
       </c>
       <c r="F223" s="14" t="n">
-        <v>-0.2562</v>
+        <v>-0.2494</v>
       </c>
       <c r="G223" s="15" t="n"/>
       <c r="H223" s="21" t="inlineStr">
@@ -16865,13 +16865,13 @@
         </is>
       </c>
       <c r="D224" s="4" t="n">
-        <v>39.91</v>
+        <v>39.75</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0198</v>
       </c>
       <c r="F224" s="22" t="n">
-        <v>-0.3323</v>
+        <v>-0.335</v>
       </c>
       <c r="G224" s="6" t="n">
         <v>46261</v>
@@ -16926,13 +16926,13 @@
         </is>
       </c>
       <c r="D225" s="13" t="n">
-        <v>351.32</v>
+        <v>356.57</v>
       </c>
       <c r="E225" s="18" t="n">
-        <v>0.09119999999999999</v>
+        <v>0.1075</v>
       </c>
       <c r="F225" s="14" t="n">
-        <v>-0.08710000000000001</v>
+        <v>-0.07339999999999999</v>
       </c>
       <c r="G225" s="15" t="n">
         <v>46289</v>
@@ -16991,13 +16991,13 @@
         </is>
       </c>
       <c r="D226" s="4" t="n">
-        <v>342.67</v>
+        <v>343.72</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0713</v>
       </c>
       <c r="F226" s="22" t="n">
-        <v>-0.0228</v>
+        <v>-0.0198</v>
       </c>
       <c r="G226" s="6" t="n">
         <v>46252</v>
@@ -17026,7 +17026,7 @@
         <v>390</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>0.1381212245017071</v>
+        <v>0.13464447806354</v>
       </c>
       <c r="N226" s="3" t="inlineStr"/>
       <c r="O226" s="8" t="n"/>
@@ -17082,13 +17082,13 @@
         </is>
       </c>
       <c r="D227" s="13" t="n">
-        <v>200.71</v>
+        <v>200.47</v>
       </c>
       <c r="E227" s="14" t="n">
-        <v>-0.0969</v>
+        <v>-0.098</v>
       </c>
       <c r="F227" s="14" t="n">
-        <v>-0.2115</v>
+        <v>-0.2124</v>
       </c>
       <c r="G227" s="15" t="n"/>
       <c r="H227" s="21" t="inlineStr">
@@ -17107,7 +17107,7 @@
         <v>305</v>
       </c>
       <c r="M227" s="18" t="n">
-        <v>0.5196054008270639</v>
+        <v>0.5214246520676411</v>
       </c>
       <c r="N227" s="12" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>185</v>
       </c>
       <c r="P227" s="14" t="n">
-        <v>-0.07827213392456782</v>
+        <v>-0.07716865366388985</v>
       </c>
       <c r="Q227" s="19" t="inlineStr">
         <is>
@@ -17159,13 +17159,13 @@
         </is>
       </c>
       <c r="D228" s="4" t="n">
-        <v>90.95999999999999</v>
+        <v>91.02</v>
       </c>
       <c r="E228" s="22" t="n">
-        <v>-0.1458</v>
+        <v>-0.1453</v>
       </c>
       <c r="F228" s="22" t="n">
-        <v>-0.196</v>
+        <v>-0.1954</v>
       </c>
       <c r="G228" s="6" t="n"/>
       <c r="H228" s="7" t="inlineStr">
@@ -17210,13 +17210,13 @@
         </is>
       </c>
       <c r="D229" s="13" t="n">
-        <v>806.55</v>
+        <v>820.59</v>
       </c>
       <c r="E229" s="18" t="n">
-        <v>0.05</v>
+        <v>0.0683</v>
       </c>
       <c r="F229" s="14" t="n">
-        <v>-0.1248</v>
+        <v>-0.1096</v>
       </c>
       <c r="G229" s="15" t="n">
         <v>46245</v>
@@ -17271,13 +17271,13 @@
         </is>
       </c>
       <c r="D230" s="4" t="n">
-        <v>105.04</v>
+        <v>103.66</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>0.0276</v>
+        <v>0.0141</v>
       </c>
       <c r="F230" s="22" t="n">
-        <v>-0.0521</v>
+        <v>-0.0645</v>
       </c>
       <c r="G230" s="6" t="n"/>
       <c r="H230" s="7" t="inlineStr">
@@ -17322,13 +17322,13 @@
         </is>
       </c>
       <c r="D231" s="13" t="n">
-        <v>313.5</v>
+        <v>311.41</v>
       </c>
       <c r="E231" s="14" t="n">
-        <v>-0.0498</v>
+        <v>-0.0561</v>
       </c>
       <c r="F231" s="14" t="n">
-        <v>-0.1453</v>
+        <v>-0.151</v>
       </c>
       <c r="G231" s="15" t="n"/>
       <c r="H231" s="21" t="inlineStr">
@@ -17347,7 +17347,7 @@
         <v>450</v>
       </c>
       <c r="M231" s="18" t="n">
-        <v>0.4354066985645933</v>
+        <v>0.4450403005683824</v>
       </c>
       <c r="N231" s="12" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>355</v>
       </c>
       <c r="P231" s="18" t="n">
-        <v>0.1323763955342903</v>
+        <v>0.1399762371150572</v>
       </c>
       <c r="Q231" s="19" t="inlineStr">
         <is>
@@ -17403,13 +17403,13 @@
         </is>
       </c>
       <c r="D232" s="4" t="n">
-        <v>82.55</v>
+        <v>81.02</v>
       </c>
       <c r="E232" s="22" t="n">
-        <v>-0.0199</v>
+        <v>-0.0381</v>
       </c>
       <c r="F232" s="22" t="n">
-        <v>-0.1332</v>
+        <v>-0.1493</v>
       </c>
       <c r="G232" s="6" t="n"/>
       <c r="H232" s="7" t="inlineStr">
@@ -17454,13 +17454,13 @@
         </is>
       </c>
       <c r="D233" s="13" t="n">
-        <v>432.96</v>
+        <v>439.16</v>
       </c>
       <c r="E233" s="18" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="F233" s="18" t="n">
         <v>0.2811</v>
-      </c>
-      <c r="F233" s="18" t="n">
-        <v>0.263</v>
       </c>
       <c r="G233" s="15" t="n">
         <v>46266</v>
@@ -17515,13 +17515,13 @@
         </is>
       </c>
       <c r="D234" s="4" t="n">
-        <v>296.17</v>
+        <v>294.38</v>
       </c>
       <c r="E234" s="22" t="n">
-        <v>-0.1587</v>
+        <v>-0.1638</v>
       </c>
       <c r="F234" s="22" t="n">
-        <v>-0.1673</v>
+        <v>-0.1724</v>
       </c>
       <c r="G234" s="6" t="n"/>
       <c r="H234" s="7" t="inlineStr">
@@ -17566,13 +17566,13 @@
         </is>
       </c>
       <c r="D235" s="13" t="n">
-        <v>1417.05</v>
+        <v>1402.11</v>
       </c>
       <c r="E235" s="18" t="n">
-        <v>0.0973</v>
+        <v>0.0857</v>
       </c>
       <c r="F235" s="14" t="n">
-        <v>-0.1016</v>
+        <v>-0.1111</v>
       </c>
       <c r="G235" s="15" t="n"/>
       <c r="H235" s="21" t="inlineStr">
@@ -17617,13 +17617,13 @@
         </is>
       </c>
       <c r="D236" s="4" t="n">
-        <v>210.76</v>
+        <v>212.31</v>
       </c>
       <c r="E236" s="22" t="n">
-        <v>-0.0311</v>
+        <v>-0.024</v>
       </c>
       <c r="F236" s="22" t="n">
-        <v>-0.2465</v>
+        <v>-0.2409</v>
       </c>
       <c r="G236" s="6" t="n">
         <v>46261</v>
@@ -17652,7 +17652,7 @@
         <v>240</v>
       </c>
       <c r="M236" s="5" t="n">
-        <v>0.1387360030366294</v>
+        <v>0.1304224954076586</v>
       </c>
       <c r="N236" s="3" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>251</v>
       </c>
       <c r="P236" s="5" t="n">
-        <v>0.1909280698424749</v>
+        <v>0.1822335264471763</v>
       </c>
       <c r="Q236" s="9" t="inlineStr">
         <is>
@@ -17704,13 +17704,13 @@
         </is>
       </c>
       <c r="D237" s="13" t="n">
-        <v>501.86</v>
+        <v>503.81</v>
       </c>
       <c r="E237" s="18" t="n">
-        <v>0.2835</v>
+        <v>0.2885</v>
       </c>
       <c r="F237" s="18" t="n">
-        <v>0.2844</v>
+        <v>0.2894</v>
       </c>
       <c r="G237" s="15" t="n"/>
       <c r="H237" s="21" t="inlineStr">
@@ -17729,7 +17729,7 @@
         <v>625</v>
       </c>
       <c r="M237" s="18" t="n">
-        <v>0.2453672338899294</v>
+        <v>0.2405470316190627</v>
       </c>
       <c r="N237" s="12" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>525</v>
       </c>
       <c r="P237" s="18" t="n">
-        <v>0.04610847646754072</v>
+        <v>0.0420595065600127</v>
       </c>
       <c r="Q237" s="19" t="inlineStr">
         <is>
@@ -17793,13 +17793,13 @@
         </is>
       </c>
       <c r="D238" s="4" t="n">
-        <v>469.42</v>
+        <v>466.89</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>0.1229</v>
+        <v>0.1168</v>
       </c>
       <c r="F238" s="5" t="n">
-        <v>0.1387</v>
+        <v>0.1325</v>
       </c>
       <c r="G238" s="6" t="n"/>
       <c r="H238" s="7" t="inlineStr">
@@ -17821,7 +17821,7 @@
         <v>525</v>
       </c>
       <c r="P238" s="5" t="n">
-        <v>0.1184014315538324</v>
+        <v>0.1244618646790465</v>
       </c>
       <c r="Q238" s="9" t="inlineStr">
         <is>
@@ -17870,13 +17870,13 @@
         </is>
       </c>
       <c r="D239" s="13" t="n">
-        <v>97.88</v>
+        <v>96.09</v>
       </c>
       <c r="E239" s="18" t="n">
-        <v>0.06280000000000001</v>
+        <v>0.0433</v>
       </c>
       <c r="F239" s="14" t="n">
-        <v>-0.2105</v>
+        <v>-0.2249</v>
       </c>
       <c r="G239" s="15" t="n"/>
       <c r="H239" s="21" t="inlineStr">
@@ -17921,13 +17921,13 @@
         </is>
       </c>
       <c r="D240" s="4" t="n">
-        <v>305.54</v>
+        <v>299.93</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>0.0384</v>
+        <v>0.0193</v>
       </c>
       <c r="F240" s="22" t="n">
-        <v>-0.1957</v>
+        <v>-0.2104</v>
       </c>
       <c r="G240" s="6" t="n"/>
       <c r="H240" s="7" t="inlineStr">
@@ -17972,13 +17972,13 @@
         </is>
       </c>
       <c r="D241" s="13" t="n">
-        <v>852.01</v>
+        <v>868.52</v>
       </c>
       <c r="E241" s="14" t="n">
-        <v>-0.0907</v>
+        <v>-0.0731</v>
       </c>
       <c r="F241" s="14" t="n">
-        <v>-0.132</v>
+        <v>-0.1152</v>
       </c>
       <c r="G241" s="15" t="n">
         <v>46287</v>
@@ -18007,7 +18007,7 @@
         <v>1525</v>
       </c>
       <c r="M241" s="18" t="n">
-        <v>0.789885095245361</v>
+        <v>0.755860544374338</v>
       </c>
       <c r="N241" s="12" t="inlineStr">
         <is>
@@ -18055,13 +18055,13 @@
         </is>
       </c>
       <c r="D242" s="4" t="n">
-        <v>190.64</v>
+        <v>193.23</v>
       </c>
       <c r="E242" s="22" t="n">
-        <v>-0.0944</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="F242" s="22" t="n">
-        <v>-0.1795</v>
+        <v>-0.1684</v>
       </c>
       <c r="G242" s="6" t="n">
         <v>46246</v>
@@ -18116,13 +18116,13 @@
         </is>
       </c>
       <c r="D243" s="13" t="n">
-        <v>311.62</v>
+        <v>306.86</v>
       </c>
       <c r="E243" s="18" t="n">
-        <v>0.1562</v>
+        <v>0.1385</v>
       </c>
       <c r="F243" s="18" t="n">
-        <v>0.3639</v>
+        <v>0.343</v>
       </c>
       <c r="G243" s="15" t="n"/>
       <c r="H243" s="21" t="inlineStr">
@@ -18167,13 +18167,13 @@
         </is>
       </c>
       <c r="D244" s="4" t="n">
-        <v>128.6</v>
+        <v>127.54</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>0.1559</v>
+        <v>0.1463</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>0.2589</v>
+        <v>0.2486</v>
       </c>
       <c r="G244" s="6" t="n">
         <v>46323</v>
@@ -18202,7 +18202,7 @@
         <v>160</v>
       </c>
       <c r="M244" s="5" t="n">
-        <v>0.2441679626749612</v>
+        <v>0.2545083895248549</v>
       </c>
       <c r="N244" s="3" t="inlineStr">
         <is>
@@ -18213,7 +18213,7 @@
         <v>150</v>
       </c>
       <c r="P244" s="5" t="n">
-        <v>0.1664074650077761</v>
+        <v>0.1761016151795514</v>
       </c>
       <c r="Q244" s="9" t="inlineStr">
         <is>
@@ -18258,13 +18258,13 @@
         </is>
       </c>
       <c r="D245" s="13" t="n">
-        <v>64.95</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="E245" s="18" t="n">
-        <v>0.1762</v>
+        <v>0.1648</v>
       </c>
       <c r="F245" s="18" t="n">
-        <v>0.3172</v>
+        <v>0.3044</v>
       </c>
       <c r="G245" s="15" t="n">
         <v>46260</v>
@@ -18319,13 +18319,13 @@
         </is>
       </c>
       <c r="D246" s="4" t="n">
-        <v>219.02</v>
+        <v>217.5</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>0.0761</v>
+        <v>0.06860000000000001</v>
       </c>
       <c r="F246" s="5" t="n">
-        <v>0.0674</v>
+        <v>0.06</v>
       </c>
       <c r="G246" s="6" t="n">
         <v>46260</v>
@@ -18354,7 +18354,7 @@
         <v>315</v>
       </c>
       <c r="M246" s="5" t="n">
-        <v>0.4382248196511733</v>
+        <v>0.4482758620689655</v>
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>413</v>
       </c>
       <c r="P246" s="5" t="n">
-        <v>0.8856725413204273</v>
+        <v>0.8988505747126436</v>
       </c>
       <c r="Q246" s="9" t="inlineStr">
         <is>
@@ -18414,13 +18414,13 @@
         </is>
       </c>
       <c r="D247" s="13" t="n">
-        <v>392.09</v>
+        <v>395.95</v>
       </c>
       <c r="E247" s="14" t="n">
-        <v>-0.1339</v>
+        <v>-0.1254</v>
       </c>
       <c r="F247" s="14" t="n">
-        <v>-0.3275</v>
+        <v>-0.3209</v>
       </c>
       <c r="G247" s="15" t="n"/>
       <c r="H247" s="21" t="inlineStr">
@@ -18465,13 +18465,13 @@
         </is>
       </c>
       <c r="D248" s="4" t="n">
-        <v>240.03</v>
+        <v>236.38</v>
       </c>
       <c r="E248" s="22" t="n">
-        <v>-0.1378</v>
+        <v>-0.1509</v>
       </c>
       <c r="F248" s="22" t="n">
-        <v>-0.2127</v>
+        <v>-0.2246</v>
       </c>
       <c r="G248" s="6" t="n"/>
       <c r="H248" s="7" t="inlineStr">
@@ -18512,13 +18512,13 @@
         </is>
       </c>
       <c r="D249" s="13" t="n">
-        <v>11.65</v>
+        <v>11.72</v>
       </c>
       <c r="E249" s="14" t="n">
-        <v>-0.3186</v>
+        <v>-0.3142</v>
       </c>
       <c r="F249" s="14" t="n">
-        <v>-0.4471</v>
+        <v>-0.4435</v>
       </c>
       <c r="G249" s="15" t="n"/>
       <c r="H249" s="21" t="inlineStr">
@@ -18563,13 +18563,13 @@
         </is>
       </c>
       <c r="D250" s="4" t="n">
-        <v>150.95</v>
+        <v>150.33</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>0.0818</v>
+        <v>0.0774</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>0.298</v>
+        <v>0.2927</v>
       </c>
       <c r="G250" s="6" t="n">
         <v>46260</v>
@@ -18598,7 +18598,7 @@
         <v>150</v>
       </c>
       <c r="M250" s="22" t="n">
-        <v>-0.006293474660483529</v>
+        <v>-0.002195170624625906</v>
       </c>
       <c r="N250" s="3" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>130</v>
       </c>
       <c r="P250" s="22" t="n">
-        <v>-0.1387876780390857</v>
+        <v>-0.1352358145413425</v>
       </c>
       <c r="Q250" s="9" t="inlineStr">
         <is>
@@ -18650,13 +18650,13 @@
         </is>
       </c>
       <c r="D251" s="13" t="n">
-        <v>81.78</v>
+        <v>81.11</v>
       </c>
       <c r="E251" s="14" t="n">
-        <v>-0.0951</v>
+        <v>-0.1025</v>
       </c>
       <c r="F251" s="14" t="n">
-        <v>-0.2998</v>
+        <v>-0.3055</v>
       </c>
       <c r="G251" s="15" t="n"/>
       <c r="H251" s="21" t="inlineStr">
@@ -18701,13 +18701,13 @@
         </is>
       </c>
       <c r="D252" s="4" t="n">
-        <v>310.76</v>
+        <v>319.82</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>0.0215</v>
+        <v>0.0513</v>
       </c>
       <c r="F252" s="22" t="n">
-        <v>-0.0405</v>
+        <v>-0.0125</v>
       </c>
       <c r="G252" s="6" t="n"/>
       <c r="H252" s="7" t="inlineStr">
@@ -18752,13 +18752,13 @@
         </is>
       </c>
       <c r="D253" s="13" t="n">
-        <v>145.63</v>
+        <v>145.45</v>
       </c>
       <c r="E253" s="18" t="n">
-        <v>0.1071</v>
+        <v>0.1057</v>
       </c>
       <c r="F253" s="14" t="n">
-        <v>-0.2091</v>
+        <v>-0.2101</v>
       </c>
       <c r="G253" s="15" t="n">
         <v>46273</v>
@@ -18787,7 +18787,7 @@
         <v>280</v>
       </c>
       <c r="M253" s="18" t="n">
-        <v>0.9226807663256198</v>
+        <v>0.9250601581299417</v>
       </c>
       <c r="N253" s="12" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>245</v>
       </c>
       <c r="P253" s="18" t="n">
-        <v>0.6823456705349173</v>
+        <v>0.684427638363699</v>
       </c>
       <c r="Q253" s="19" t="inlineStr">
         <is>
@@ -18839,13 +18839,13 @@
         </is>
       </c>
       <c r="D254" s="4" t="n">
-        <v>383.41</v>
+        <v>383.8</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>0.1608</v>
+        <v>0.162</v>
       </c>
       <c r="F254" s="5" t="n">
-        <v>0.3712</v>
+        <v>0.3726</v>
       </c>
       <c r="G254" s="6" t="n">
         <v>46266</v>
@@ -18874,7 +18874,7 @@
         <v>420</v>
       </c>
       <c r="M254" s="5" t="n">
-        <v>0.09543308729558429</v>
+        <v>0.0943199583116206</v>
       </c>
       <c r="N254" s="3" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <